--- a/earnings-data.xlsx
+++ b/earnings-data.xlsx
@@ -32277,7 +32277,7 @@
     <row r="2">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>Data as of September 07, 2026 at 16:04 UTC</t>
+          <t>Data as of September 07, 2026 at 20:49 UTC</t>
         </is>
       </c>
     </row>

--- a/earnings-data.xlsx
+++ b/earnings-data.xlsx
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>104.6</v>
+        <v>105.08</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.0137</v>
+        <v>0.0185</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.09390000000000001</v>
+        <v>0.099</v>
       </c>
       <c r="G2" s="6" t="n"/>
       <c r="H2" s="7" t="inlineStr">
@@ -868,7 +868,7 @@
         <v>125</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>0.1950286806883366</v>
+        <v>0.1895698515416825</v>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         <v>144</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>0.3766730401529638</v>
+        <v>0.3703844689760183</v>
       </c>
       <c r="Q2" s="9" t="inlineStr">
         <is>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="D3" s="13" t="n">
-        <v>336.31</v>
+        <v>338.36</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>-0.0593</v>
+        <v>-0.0536</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>-0.0584</v>
+        <v>-0.0527</v>
       </c>
       <c r="G3" s="15" t="n">
         <v>46322</v>
@@ -963,7 +963,7 @@
         <v>438</v>
       </c>
       <c r="M3" s="18" t="n">
-        <v>0.3023698373524427</v>
+        <v>0.2944792528667691</v>
       </c>
       <c r="N3" s="12" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>420</v>
       </c>
       <c r="P3" s="18" t="n">
-        <v>0.2488477892420683</v>
+        <v>0.2412814753516964</v>
       </c>
       <c r="Q3" s="19" t="inlineStr">
         <is>
@@ -1019,13 +1019,13 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>615.6</v>
+        <v>613.48</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.0348</v>
+        <v>0.0312</v>
       </c>
       <c r="F4" s="22" t="n">
-        <v>-0.0801</v>
+        <v>-0.0833</v>
       </c>
       <c r="G4" s="6" t="n"/>
       <c r="H4" s="7" t="inlineStr">
@@ -1044,7 +1044,7 @@
         <v>835</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>0.3564002599090318</v>
+        <v>0.361087566016822</v>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>930</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>0.5107212475633528</v>
+        <v>0.5159418399947838</v>
       </c>
       <c r="Q4" s="9" t="inlineStr">
         <is>
@@ -1104,13 +1104,13 @@
         </is>
       </c>
       <c r="D5" s="13" t="n">
-        <v>41.08</v>
+        <v>41.15</v>
       </c>
       <c r="E5" s="18" t="n">
-        <v>0.1184</v>
+        <v>0.1203</v>
       </c>
       <c r="F5" s="18" t="n">
-        <v>0.0574</v>
+        <v>0.0592</v>
       </c>
       <c r="G5" s="15" t="n"/>
       <c r="H5" s="21" t="inlineStr">
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>76.54000000000001</v>
+        <v>76.77</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0063</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.0433</v>
+        <v>0.0463</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>46315</v>
@@ -1190,7 +1190,7 @@
         <v>80</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>0.04520512150509529</v>
+        <v>0.04207372671616522</v>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>100</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>0.3065064018813691</v>
+        <v>0.3025921583952065</v>
       </c>
       <c r="Q6" s="9" t="inlineStr">
         <is>
@@ -1242,13 +1242,13 @@
         </is>
       </c>
       <c r="D7" s="13" t="n">
-        <v>81.03</v>
+        <v>81.13</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>-0.0428</v>
+        <v>-0.0416</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>-0.011</v>
+        <v>-0.0098</v>
       </c>
       <c r="G7" s="15" t="n">
         <v>46315</v>
@@ -1277,7 +1277,7 @@
         <v>91</v>
       </c>
       <c r="M7" s="18" t="n">
-        <v>0.1230408490682463</v>
+        <v>0.1216566005176877</v>
       </c>
       <c r="N7" s="12" t="inlineStr"/>
       <c r="O7" s="17" t="n"/>
@@ -1321,13 +1321,13 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>531.1900000000001</v>
+        <v>528.64</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.0378</v>
+        <v>0.0329</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.1072</v>
+        <v>0.1019</v>
       </c>
       <c r="G8" s="6" t="n"/>
       <c r="H8" s="7" t="inlineStr">
@@ -1346,7 +1346,7 @@
         <v>569.9299999999999</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>0.07293058980778985</v>
+        <v>0.07810608353510889</v>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>648.04</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>0.2199777857263877</v>
+        <v>0.2258625907990314</v>
       </c>
       <c r="Q8" s="9" t="inlineStr">
         <is>
@@ -1398,13 +1398,13 @@
         </is>
       </c>
       <c r="D9" s="13" t="n">
-        <v>184.03</v>
-      </c>
-      <c r="E9" s="14" t="n">
-        <v>-0.0285</v>
-      </c>
-      <c r="F9" s="14" t="n">
-        <v>-0.002</v>
+        <v>195.32</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>0.0311</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>0.0592</v>
       </c>
       <c r="G9" s="15" t="n"/>
       <c r="H9" s="21" t="inlineStr">
@@ -1457,13 +1457,13 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>180.99</v>
+        <v>181.69</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.0157</v>
+        <v>0.0196</v>
       </c>
       <c r="F10" s="22" t="n">
-        <v>-0.0353</v>
+        <v>-0.0316</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>46317</v>
@@ -1492,7 +1492,7 @@
         <v>170</v>
       </c>
       <c r="M10" s="22" t="n">
-        <v>-0.06072158682800159</v>
+        <v>-0.0643403599537674</v>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>270</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>0.4917951268025857</v>
+        <v>0.48604766360284</v>
       </c>
       <c r="Q10" s="9" t="inlineStr">
         <is>
@@ -1544,13 +1544,13 @@
         </is>
       </c>
       <c r="D11" s="13" t="n">
-        <v>50.31</v>
+        <v>50.41</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>0.0698</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>0.1946</v>
+        <v>0.1968</v>
       </c>
       <c r="G11" s="15" t="n">
         <v>46316</v>
@@ -1579,7 +1579,7 @@
         <v>43</v>
       </c>
       <c r="M11" s="14" t="n">
-        <v>-0.1452991452991453</v>
+        <v>-0.1469946439198571</v>
       </c>
       <c r="N11" s="12" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>50</v>
       </c>
       <c r="P11" s="14" t="n">
-        <v>-0.006161796859471323</v>
+        <v>-0.008133306883554783</v>
       </c>
       <c r="Q11" s="19" t="inlineStr">
         <is>
@@ -1635,13 +1635,13 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>176.29</v>
+        <v>174.54</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>-0.0455</v>
+        <v>-0.055</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.1862</v>
+        <v>0.1744</v>
       </c>
       <c r="G12" s="6" t="n"/>
       <c r="H12" s="7" t="inlineStr">
@@ -1660,7 +1660,7 @@
         <v>181</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>0.0267173407453628</v>
+        <v>0.03701157327833166</v>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>155</v>
       </c>
       <c r="P12" s="22" t="n">
-        <v>-0.1207669181462363</v>
+        <v>-0.11195141514839</v>
       </c>
       <c r="Q12" s="9" t="inlineStr">
         <is>
@@ -1712,13 +1712,13 @@
         </is>
       </c>
       <c r="D13" s="13" t="n">
-        <v>255.52</v>
+        <v>256.97</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.0759</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>0.0415</v>
+        <v>0.0474</v>
       </c>
       <c r="G13" s="15" t="n">
         <v>46324</v>
@@ -1747,7 +1747,7 @@
         <v>322</v>
       </c>
       <c r="M13" s="18" t="n">
-        <v>0.26017532874139</v>
+        <v>0.2530645600653771</v>
       </c>
       <c r="N13" s="12" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>285</v>
       </c>
       <c r="P13" s="18" t="n">
-        <v>0.1153725735754539</v>
+        <v>0.1090788808032065</v>
       </c>
       <c r="Q13" s="19" t="inlineStr">
         <is>
@@ -1811,13 +1811,13 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2956.87</v>
+        <v>2951.61</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>-0.0362</v>
+        <v>-0.0379</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>-0.0377</v>
+        <v>-0.0394</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>46287</v>
@@ -1846,7 +1846,7 @@
         <v>4150</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>0.403511145231275</v>
+        <v>0.4060123119246783</v>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>3700</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>0.2513231897242693</v>
+        <v>0.2535531455714</v>
       </c>
       <c r="Q14" s="9" t="inlineStr">
         <is>
@@ -1898,13 +1898,13 @@
         </is>
       </c>
       <c r="D15" s="13" t="n">
-        <v>88.20999999999999</v>
+        <v>89.33</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>0.0701</v>
+        <v>0.0837</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>0.0653</v>
+        <v>0.0789</v>
       </c>
       <c r="G15" s="15" t="n"/>
       <c r="H15" s="21" t="inlineStr">
@@ -1923,7 +1923,7 @@
         <v>65</v>
       </c>
       <c r="M15" s="14" t="n">
-        <v>-0.2631220950005668</v>
+        <v>-0.2723609089891414</v>
       </c>
       <c r="N15" s="12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>85</v>
       </c>
       <c r="P15" s="14" t="n">
-        <v>-0.03639043192381809</v>
+        <v>-0.04847195790887718</v>
       </c>
       <c r="Q15" s="19" t="inlineStr"/>
       <c r="R15" s="17" t="n"/>
@@ -1969,13 +1969,13 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>183.51</v>
+        <v>180.3</v>
       </c>
       <c r="E16" s="22" t="n">
-        <v>-0.138</v>
+        <v>-0.153</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.0287</v>
+        <v>0.0107</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>46322</v>
@@ -2004,7 +2004,7 @@
         <v>214</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>0.16614898370661</v>
+        <v>0.1869107043815862</v>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>245</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>0.3350771075145769</v>
+        <v>0.3588463671658346</v>
       </c>
       <c r="Q16" s="9" t="inlineStr">
         <is>
@@ -2064,13 +2064,13 @@
         </is>
       </c>
       <c r="D17" s="13" t="n">
-        <v>255.38</v>
+        <v>255.42</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>-0.3126</v>
+        <v>-0.3125</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>-0.2207</v>
+        <v>-0.2206</v>
       </c>
       <c r="G17" s="15" t="n"/>
       <c r="H17" s="21" t="inlineStr">
@@ -2089,7 +2089,7 @@
         <v>375</v>
       </c>
       <c r="M17" s="18" t="n">
-        <v>0.4684000313258674</v>
+        <v>0.4681700728212357</v>
       </c>
       <c r="N17" s="12" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>375</v>
       </c>
       <c r="P17" s="18" t="n">
-        <v>0.4684000313258674</v>
+        <v>0.4681700728212357</v>
       </c>
       <c r="Q17" s="19" t="inlineStr"/>
       <c r="R17" s="17" t="n"/>
@@ -2139,13 +2139,13 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>37.21</v>
+        <v>36.96</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.1577</v>
+        <v>0.15</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.0556</v>
+        <v>0.04849999999999999</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>46323</v>
@@ -2174,7 +2174,7 @@
         <v>45</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>0.2093523246439129</v>
+        <v>0.2175324675324675</v>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>45</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>0.2093523246439129</v>
+        <v>0.2175324675324675</v>
       </c>
       <c r="Q18" s="9" t="inlineStr">
         <is>
@@ -2226,13 +2226,13 @@
         </is>
       </c>
       <c r="D19" s="13" t="n">
-        <v>139.34</v>
+        <v>138.49</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>-0.0499</v>
+        <v>-0.0557</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>-0.08070000000000001</v>
+        <v>-0.0864</v>
       </c>
       <c r="G19" s="15" t="n">
         <v>46322</v>
@@ -2261,7 +2261,7 @@
         <v>170</v>
       </c>
       <c r="M19" s="18" t="n">
-        <v>0.2200373187885747</v>
+        <v>0.2275254531013069</v>
       </c>
       <c r="N19" s="12" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>177</v>
       </c>
       <c r="P19" s="18" t="n">
-        <v>0.2702741495622219</v>
+        <v>0.278070618817243</v>
       </c>
       <c r="Q19" s="19" t="inlineStr">
         <is>
@@ -2313,13 +2313,13 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>132</v>
+        <v>132.37</v>
       </c>
       <c r="E20" s="22" t="n">
-        <v>-0.3835</v>
+        <v>-0.3817</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>-0.3944</v>
+        <v>-0.3927</v>
       </c>
       <c r="G20" s="6" t="n"/>
       <c r="H20" s="7" t="inlineStr">
@@ -2338,7 +2338,7 @@
         <v>220</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6620080078567651</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="8" t="n"/>
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="D21" s="13" t="n">
-        <v>125.43</v>
+        <v>124.04</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>-0.0305</v>
-      </c>
-      <c r="F21" s="18" t="n">
-        <v>0.004099999999999999</v>
+        <v>-0.0412</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>-0.006999999999999999</v>
       </c>
       <c r="G21" s="15" t="n"/>
       <c r="H21" s="21" t="inlineStr">
@@ -2433,13 +2433,13 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>85.65000000000001</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="E22" s="22" t="n">
-        <v>-0.0263</v>
+        <v>-0.0247</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.1002</v>
+        <v>0.102</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>46315</v>
@@ -2468,7 +2468,7 @@
         <v>61</v>
       </c>
       <c r="M22" s="22" t="n">
-        <v>-0.2877991827203736</v>
+        <v>-0.2889614174146171</v>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>100</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0.1675423234092235</v>
+        <v>0.1656370206317752</v>
       </c>
       <c r="Q22" s="9" t="inlineStr">
         <is>
@@ -2520,13 +2520,13 @@
         </is>
       </c>
       <c r="D23" s="13" t="n">
-        <v>133.74</v>
+        <v>134.06</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>-0.006</v>
+        <v>-0.0036</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>0.0646</v>
+        <v>0.0672</v>
       </c>
       <c r="G23" s="15" t="n">
         <v>46315</v>
@@ -2558,7 +2558,7 @@
         <v>145</v>
       </c>
       <c r="P23" s="18" t="n">
-        <v>0.08419321070734254</v>
+        <v>0.08160525137997909</v>
       </c>
       <c r="Q23" s="19" t="inlineStr"/>
       <c r="R23" s="17" t="n"/>
@@ -2593,13 +2593,13 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>317.52</v>
+        <v>313.7</v>
       </c>
       <c r="E24" s="22" t="n">
-        <v>-0.09480000000000001</v>
+        <v>-0.1057</v>
       </c>
       <c r="F24" s="22" t="n">
-        <v>-0.0751</v>
+        <v>-0.0862</v>
       </c>
       <c r="G24" s="6" t="n"/>
       <c r="H24" s="7" t="inlineStr">
@@ -2618,7 +2618,7 @@
         <v>360</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>0.1337868480725624</v>
+        <v>0.1475932419509086</v>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>400</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0.2597631645250694</v>
+        <v>0.2751036021676762</v>
       </c>
       <c r="Q24" s="9" t="inlineStr">
         <is>
@@ -2678,13 +2678,13 @@
         </is>
       </c>
       <c r="D25" s="13" t="n">
-        <v>202.51</v>
+        <v>200.8</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>-0.07480000000000001</v>
+        <v>-0.08259999999999999</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>-0.0431</v>
+        <v>-0.0512</v>
       </c>
       <c r="G25" s="15" t="n"/>
       <c r="H25" s="21" t="inlineStr">
@@ -2703,7 +2703,7 @@
         <v>255</v>
       </c>
       <c r="M25" s="18" t="n">
-        <v>0.259197076687571</v>
+        <v>0.2699203187250995</v>
       </c>
       <c r="N25" s="12" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>230</v>
       </c>
       <c r="P25" s="18" t="n">
-        <v>0.1357463828946719</v>
+        <v>0.145418326693227</v>
       </c>
       <c r="Q25" s="19" t="inlineStr">
         <is>
@@ -2759,13 +2759,13 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>255.5</v>
+        <v>255.81</v>
       </c>
       <c r="E26" s="22" t="n">
-        <v>-0.06660000000000001</v>
+        <v>-0.0654</v>
       </c>
       <c r="F26" s="22" t="n">
-        <v>-0.0696</v>
+        <v>-0.0684</v>
       </c>
       <c r="G26" s="6" t="n"/>
       <c r="H26" s="7" t="inlineStr">
@@ -2784,7 +2784,7 @@
         <v>300</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>0.1741682974559687</v>
+        <v>0.1727453969743169</v>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>350</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>0.3698630136986301</v>
+        <v>0.368202963136703</v>
       </c>
       <c r="Q26" s="9" t="inlineStr">
         <is>
@@ -2836,13 +2836,13 @@
         </is>
       </c>
       <c r="D27" s="13" t="n">
-        <v>38.38</v>
+        <v>38.1</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>-0.0886</v>
+        <v>-0.09519999999999999</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>-0.135</v>
+        <v>-0.1413</v>
       </c>
       <c r="G27" s="15" t="n">
         <v>46289</v>
@@ -2897,13 +2897,13 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>86.19</v>
+        <v>85.89</v>
       </c>
       <c r="E28" s="22" t="n">
-        <v>-0.0654</v>
+        <v>-0.0687</v>
       </c>
       <c r="F28" s="22" t="n">
-        <v>-0.001</v>
+        <v>-0.004500000000000001</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>46323</v>
@@ -2932,7 +2932,7 @@
         <v>110</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>0.2762501450284256</v>
+        <v>0.2807078821748749</v>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>115</v>
       </c>
       <c r="P28" s="5" t="n">
-        <v>0.3342615152569904</v>
+        <v>0.3389218768191873</v>
       </c>
       <c r="Q28" s="9" t="inlineStr">
         <is>
@@ -2988,13 +2988,13 @@
         </is>
       </c>
       <c r="D29" s="13" t="n">
-        <v>181.5</v>
+        <v>177.34</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>-0.0924</v>
+        <v>-0.1132</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>-0.1375</v>
+        <v>-0.1573</v>
       </c>
       <c r="G29" s="15" t="n">
         <v>46317</v>
@@ -3049,13 +3049,13 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>227.65</v>
+        <v>229.31</v>
       </c>
       <c r="E30" s="22" t="n">
-        <v>-0.1067</v>
+        <v>-0.1001</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.0214</v>
+        <v>0.0288</v>
       </c>
       <c r="G30" s="6" t="n"/>
       <c r="H30" s="7" t="inlineStr">
@@ -3074,7 +3074,7 @@
         <v>245</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>0.07621348561388093</v>
+        <v>0.0684226592821944</v>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>265</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>0.16406764770481</v>
+        <v>0.1556408355501286</v>
       </c>
       <c r="Q30" s="9" t="inlineStr">
         <is>
@@ -3126,13 +3126,13 @@
         </is>
       </c>
       <c r="D31" s="13" t="n">
-        <v>103.34</v>
+        <v>102.01</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>-0.0125</v>
+        <v>-0.0252</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>-0.0252</v>
+        <v>-0.0377</v>
       </c>
       <c r="G31" s="15" t="n"/>
       <c r="H31" s="21" t="inlineStr">
@@ -3151,7 +3151,7 @@
         <v>120</v>
       </c>
       <c r="M31" s="18" t="n">
-        <v>0.1612154054577124</v>
+        <v>0.176355259288305</v>
       </c>
       <c r="N31" s="12" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>115</v>
       </c>
       <c r="P31" s="18" t="n">
-        <v>0.1128314302303077</v>
+        <v>0.127340456817959</v>
       </c>
       <c r="Q31" s="19" t="inlineStr">
         <is>
@@ -3203,13 +3203,13 @@
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>12.57</v>
+        <v>12.73</v>
       </c>
       <c r="E32" s="22" t="n">
-        <v>-0.05769999999999999</v>
+        <v>-0.0457</v>
       </c>
       <c r="F32" s="22" t="n">
-        <v>-0.1864</v>
+        <v>-0.1761</v>
       </c>
       <c r="G32" s="6" t="n"/>
       <c r="H32" s="7" t="inlineStr">
@@ -3254,13 +3254,13 @@
         </is>
       </c>
       <c r="D33" s="13" t="n">
-        <v>130.22</v>
+        <v>128.92</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>-0.1801</v>
+        <v>-0.1883</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>-0.1396</v>
+        <v>-0.1481</v>
       </c>
       <c r="G33" s="15" t="n"/>
       <c r="H33" s="21" t="inlineStr">
@@ -3279,7 +3279,7 @@
         <v>160</v>
       </c>
       <c r="M33" s="18" t="n">
-        <v>0.2286899093841192</v>
+        <v>0.2410797393732549</v>
       </c>
       <c r="N33" s="12" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>175</v>
       </c>
       <c r="P33" s="18" t="n">
-        <v>0.3438795883888804</v>
+        <v>0.3574309649394975</v>
       </c>
       <c r="Q33" s="19" t="inlineStr">
         <is>
@@ -3335,13 +3335,13 @@
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>35.28</v>
+        <v>35.29</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0.0192</v>
+        <v>0.0194</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.1595</v>
+        <v>0.1597</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>46317</v>
@@ -3370,7 +3370,7 @@
         <v>35</v>
       </c>
       <c r="M34" s="22" t="n">
-        <v>-0.007936507936507969</v>
+        <v>-0.008217625389628766</v>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>40</v>
       </c>
       <c r="P34" s="5" t="n">
-        <v>0.1337868480725623</v>
+        <v>0.1334655709832814</v>
       </c>
       <c r="Q34" s="9" t="inlineStr">
         <is>
@@ -3422,13 +3422,13 @@
         </is>
       </c>
       <c r="D35" s="13" t="n">
-        <v>364.18</v>
+        <v>368.16</v>
       </c>
       <c r="E35" s="18" t="n">
-        <v>0.1006</v>
+        <v>0.1127</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>-0.1069</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="G35" s="15" t="n">
         <v>46323</v>
@@ -3457,7 +3457,7 @@
         <v>130</v>
       </c>
       <c r="M35" s="14" t="n">
-        <v>-0.6430336646713164</v>
+        <v>-0.6468926553672316</v>
       </c>
       <c r="N35" s="12" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>300</v>
       </c>
       <c r="P35" s="14" t="n">
-        <v>-0.176231533856884</v>
+        <v>-0.1851368970013038</v>
       </c>
       <c r="Q35" s="19" t="inlineStr">
         <is>
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>73.06999999999999</v>
+        <v>73.13</v>
       </c>
       <c r="E36" s="22" t="n">
-        <v>-0.0636</v>
+        <v>-0.06280000000000001</v>
       </c>
       <c r="F36" s="22" t="n">
-        <v>-0.0197</v>
+        <v>-0.0189</v>
       </c>
       <c r="G36" s="6" t="n"/>
       <c r="H36" s="7" t="inlineStr">
@@ -3560,13 +3560,13 @@
         </is>
       </c>
       <c r="D37" s="13" t="n">
-        <v>550.5599999999999</v>
+        <v>549.23</v>
       </c>
       <c r="E37" s="18" t="n">
-        <v>0.0035</v>
+        <v>0.001</v>
       </c>
       <c r="F37" s="18" t="n">
-        <v>0.1734</v>
+        <v>0.1706</v>
       </c>
       <c r="G37" s="15" t="n"/>
       <c r="H37" s="21" t="inlineStr">
@@ -3585,7 +3585,7 @@
         <v>450</v>
       </c>
       <c r="M37" s="14" t="n">
-        <v>-0.1826503923278116</v>
+        <v>-0.1806711213881252</v>
       </c>
       <c r="N37" s="12" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>635</v>
       </c>
       <c r="P37" s="18" t="n">
-        <v>0.1533711130485325</v>
+        <v>0.1561640842634233</v>
       </c>
       <c r="Q37" s="19" t="inlineStr">
         <is>
@@ -3641,13 +3641,13 @@
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>97.20999999999999</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="E38" s="22" t="n">
-        <v>-0.059</v>
+        <v>-0.0654</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0019</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>46325</v>
@@ -3676,7 +3676,7 @@
         <v>110</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>0.1315708260467031</v>
+        <v>0.1394240729231406</v>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>105</v>
       </c>
       <c r="P38" s="5" t="n">
-        <v>0.08013578849912567</v>
+        <v>0.08763206960845238</v>
       </c>
       <c r="Q38" s="9" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="D39" s="13" t="n">
-        <v>88.59</v>
+        <v>88.41</v>
       </c>
       <c r="E39" s="14" t="n">
-        <v>-0.049</v>
+        <v>-0.0509</v>
       </c>
       <c r="F39" s="14" t="n">
-        <v>-0.0396</v>
+        <v>-0.0415</v>
       </c>
       <c r="G39" s="15" t="n">
         <v>46325</v>
@@ -3767,7 +3767,7 @@
         <v>95</v>
       </c>
       <c r="M39" s="18" t="n">
-        <v>0.07235579636527821</v>
+        <v>0.07453907928967315</v>
       </c>
       <c r="N39" s="12" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
         <v>100</v>
       </c>
       <c r="P39" s="18" t="n">
-        <v>0.1287955751213455</v>
+        <v>0.1310937676733402</v>
       </c>
       <c r="Q39" s="19" t="inlineStr">
         <is>
@@ -3823,13 +3823,13 @@
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>912.39</v>
+        <v>910.1799999999999</v>
       </c>
       <c r="E40" s="22" t="n">
-        <v>-0.0424</v>
+        <v>-0.0447</v>
       </c>
       <c r="F40" s="22" t="n">
-        <v>-0.0042</v>
+        <v>-0.0066</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>46289</v>
@@ -3858,7 +3858,7 @@
         <v>1000</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>0.09602253422330365</v>
+        <v>0.0986837768353513</v>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>1100</v>
       </c>
       <c r="P40" s="5" t="n">
-        <v>0.205624787645634</v>
+        <v>0.2085521545188865</v>
       </c>
       <c r="Q40" s="9" t="inlineStr">
         <is>
@@ -3918,13 +3918,13 @@
         </is>
       </c>
       <c r="D41" s="13" t="n">
-        <v>127.48</v>
+        <v>127.87</v>
       </c>
       <c r="E41" s="18" t="n">
-        <v>0.0413</v>
+        <v>0.0445</v>
       </c>
       <c r="F41" s="18" t="n">
-        <v>0.07200000000000001</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="G41" s="15" t="n"/>
       <c r="H41" s="21" t="inlineStr">
@@ -3943,7 +3943,7 @@
         <v>125</v>
       </c>
       <c r="M41" s="14" t="n">
-        <v>-0.01945403200502042</v>
+        <v>-0.02244467036834288</v>
       </c>
       <c r="N41" s="12" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>135</v>
       </c>
       <c r="P41" s="18" t="n">
-        <v>0.05898964543457794</v>
+        <v>0.05575975600218969</v>
       </c>
       <c r="Q41" s="19" t="inlineStr">
         <is>
@@ -3995,13 +3995,13 @@
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>24.74</v>
+        <v>24.9</v>
       </c>
       <c r="E42" s="22" t="n">
-        <v>-0.0076</v>
-      </c>
-      <c r="F42" s="22" t="n">
-        <v>-0.0044</v>
+        <v>-0.0012</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>0.002</v>
       </c>
       <c r="G42" s="6" t="n"/>
       <c r="H42" s="7" t="inlineStr">
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="D43" s="13" t="n">
-        <v>88.25</v>
+        <v>88.36</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>0.0159</v>
+        <v>0.0172</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>0.057</v>
+        <v>0.0583</v>
       </c>
       <c r="G43" s="15" t="n">
         <v>46315</v>
@@ -4081,7 +4081,7 @@
         <v>90</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>0.0198300283286119</v>
+        <v>0.01856043458578543</v>
       </c>
       <c r="N43" s="12" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>88</v>
       </c>
       <c r="P43" s="14" t="n">
-        <v>-0.0028328611898017</v>
+        <v>-0.004074241738343135</v>
       </c>
       <c r="Q43" s="19" t="inlineStr">
         <is>
@@ -4141,13 +4141,13 @@
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>57.55</v>
+        <v>57.2</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0.0189</v>
+        <v>0.0127</v>
       </c>
       <c r="F44" s="22" t="n">
-        <v>-0.04940000000000001</v>
+        <v>-0.0552</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>46276</v>
@@ -4176,7 +4176,7 @@
         <v>58</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>0.007819287576020901</v>
+        <v>0.01398601398601394</v>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>78</v>
       </c>
       <c r="P44" s="5" t="n">
-        <v>0.3553431798436143</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="Q44" s="9" t="inlineStr">
         <is>
@@ -4228,13 +4228,13 @@
         </is>
       </c>
       <c r="D45" s="13" t="n">
-        <v>61.08</v>
-      </c>
-      <c r="E45" s="14" t="n">
-        <v>-0.0074</v>
+        <v>61.63</v>
+      </c>
+      <c r="E45" s="18" t="n">
+        <v>0.0016</v>
       </c>
       <c r="F45" s="18" t="n">
-        <v>0.0382</v>
+        <v>0.0476</v>
       </c>
       <c r="G45" s="15" t="n">
         <v>46322</v>
@@ -4263,7 +4263,7 @@
         <v>70</v>
       </c>
       <c r="M45" s="18" t="n">
-        <v>0.14603798297315</v>
+        <v>0.1358104819081616</v>
       </c>
       <c r="N45" s="12" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>71</v>
       </c>
       <c r="P45" s="18" t="n">
-        <v>0.1624099541584807</v>
+        <v>0.152036345935421</v>
       </c>
       <c r="Q45" s="19" t="inlineStr">
         <is>
@@ -4323,13 +4323,13 @@
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>51.82</v>
+        <v>51.9</v>
       </c>
       <c r="E46" s="22" t="n">
-        <v>-0.0247</v>
+        <v>-0.0232</v>
       </c>
       <c r="F46" s="22" t="n">
-        <v>-0.012</v>
+        <v>-0.0105</v>
       </c>
       <c r="G46" s="6" t="n">
         <v>46296</v>
@@ -4394,13 +4394,13 @@
         </is>
       </c>
       <c r="D47" s="13" t="n">
-        <v>43.47</v>
+        <v>43.15</v>
       </c>
       <c r="E47" s="14" t="n">
-        <v>-0.049</v>
+        <v>-0.0561</v>
       </c>
       <c r="F47" s="14" t="n">
-        <v>-0.1072</v>
+        <v>-0.1139</v>
       </c>
       <c r="G47" s="15" t="n"/>
       <c r="H47" s="21" t="inlineStr">
@@ -4445,13 +4445,13 @@
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>68.5</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0.0451</v>
+        <v>0.04019999999999999</v>
       </c>
       <c r="F48" s="22" t="n">
-        <v>-0.0459</v>
+        <v>-0.0504</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>46324</v>
@@ -4506,13 +4506,13 @@
         </is>
       </c>
       <c r="D49" s="13" t="n">
-        <v>138.91</v>
+        <v>138.45</v>
       </c>
       <c r="E49" s="18" t="n">
-        <v>0.0086</v>
+        <v>0.0052</v>
       </c>
       <c r="F49" s="18" t="n">
-        <v>0.0111</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="G49" s="15" t="n">
         <v>46303</v>
@@ -4541,7 +4541,7 @@
         <v>140</v>
       </c>
       <c r="M49" s="18" t="n">
-        <v>0.00784680728529266</v>
+        <v>0.01119537739256057</v>
       </c>
       <c r="N49" s="12" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>150</v>
       </c>
       <c r="P49" s="18" t="n">
-        <v>0.07983586494852785</v>
+        <v>0.08342361863488633</v>
       </c>
       <c r="Q49" s="19" t="inlineStr">
         <is>
@@ -4601,13 +4601,13 @@
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>144.99</v>
+        <v>145.58</v>
       </c>
       <c r="E50" s="22" t="n">
+        <v>-0.0059</v>
+      </c>
+      <c r="F50" s="22" t="n">
         <v>-0.009899999999999999</v>
-      </c>
-      <c r="F50" s="22" t="n">
-        <v>-0.0139</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>46318</v>
@@ -4636,7 +4636,7 @@
         <v>164</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>0.1311124905165873</v>
+        <v>0.1265283692814946</v>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>162</v>
       </c>
       <c r="P50" s="5" t="n">
-        <v>0.1173184357541899</v>
+        <v>0.1127902184365983</v>
       </c>
       <c r="Q50" s="9" t="inlineStr">
         <is>
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="D51" s="13" t="n">
-        <v>80.09999999999999</v>
+        <v>79.84</v>
       </c>
       <c r="E51" s="14" t="n">
-        <v>-0.045</v>
+        <v>-0.0481</v>
       </c>
       <c r="F51" s="14" t="n">
-        <v>-0.0445</v>
+        <v>-0.0476</v>
       </c>
       <c r="G51" s="15" t="n">
         <v>46322</v>
@@ -4735,7 +4735,7 @@
         <v>100</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>0.2484394506866418</v>
+        <v>0.25250501002004</v>
       </c>
       <c r="N51" s="12" t="inlineStr"/>
       <c r="O51" s="17" t="n"/>
@@ -4779,13 +4779,13 @@
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>162.17</v>
+        <v>162.71</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0.0668</v>
+        <v>0.0703</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.2</v>
+        <v>0.204</v>
       </c>
       <c r="G52" s="6" t="n"/>
       <c r="H52" s="7" t="inlineStr">
@@ -4804,7 +4804,7 @@
         <v>140</v>
       </c>
       <c r="M52" s="22" t="n">
-        <v>-0.1367083924276992</v>
+        <v>-0.1395734742793928</v>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>135</v>
       </c>
       <c r="P52" s="22" t="n">
-        <v>-0.1675402355552814</v>
+        <v>-0.1703029930551288</v>
       </c>
       <c r="Q52" s="9" t="inlineStr">
         <is>
@@ -4860,13 +4860,13 @@
         </is>
       </c>
       <c r="D53" s="13" t="n">
-        <v>105.79</v>
+        <v>106.05</v>
       </c>
       <c r="E53" s="14" t="n">
-        <v>-0.061</v>
+        <v>-0.0587</v>
       </c>
       <c r="F53" s="14" t="n">
-        <v>-0.0712</v>
+        <v>-0.0689</v>
       </c>
       <c r="G53" s="15" t="n"/>
       <c r="H53" s="21" t="inlineStr">
@@ -4885,7 +4885,7 @@
         <v>140</v>
       </c>
       <c r="M53" s="18" t="n">
-        <v>0.3233765006144247</v>
+        <v>0.3201320132013202</v>
       </c>
       <c r="N53" s="12" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         <v>140</v>
       </c>
       <c r="P53" s="18" t="n">
-        <v>0.3233765006144247</v>
+        <v>0.3201320132013202</v>
       </c>
       <c r="Q53" s="19" t="inlineStr">
         <is>
@@ -4945,13 +4945,13 @@
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>64.51000000000001</v>
-      </c>
-      <c r="E54" s="5" t="n">
-        <v>0.0069</v>
+        <v>63.92</v>
+      </c>
+      <c r="E54" s="22" t="n">
+        <v>-0.0023</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>0.1207</v>
+        <v>0.1105</v>
       </c>
       <c r="G54" s="6" t="n">
         <v>46317</v>
@@ -4987,7 +4987,7 @@
         <v>76</v>
       </c>
       <c r="P54" s="5" t="n">
-        <v>0.17811192063246</v>
+        <v>0.1889862327909887</v>
       </c>
       <c r="Q54" s="9" t="inlineStr">
         <is>
@@ -5028,13 +5028,13 @@
         </is>
       </c>
       <c r="D55" s="13" t="n">
-        <v>136.26</v>
+        <v>135.04</v>
       </c>
       <c r="E55" s="18" t="n">
-        <v>0.1076</v>
+        <v>0.09759999999999999</v>
       </c>
       <c r="F55" s="18" t="n">
-        <v>0.2497</v>
+        <v>0.2384</v>
       </c>
       <c r="G55" s="15" t="n"/>
       <c r="H55" s="21" t="inlineStr">
@@ -5053,7 +5053,7 @@
         <v>183</v>
       </c>
       <c r="M55" s="18" t="n">
-        <v>0.3430206957287539</v>
+        <v>0.3551540284360191</v>
       </c>
       <c r="N55" s="12" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>145</v>
       </c>
       <c r="P55" s="18" t="n">
-        <v>0.06414208131513291</v>
+        <v>0.07375592417061617</v>
       </c>
       <c r="Q55" s="19" t="inlineStr">
         <is>
@@ -5105,13 +5105,13 @@
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>212.35</v>
+        <v>209.8</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0.0895</v>
+        <v>0.0764</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.2038</v>
+        <v>0.1893</v>
       </c>
       <c r="G56" s="6" t="n">
         <v>46325</v>
@@ -5140,7 +5140,7 @@
         <v>222</v>
       </c>
       <c r="M56" s="5" t="n">
-        <v>0.04544384271250297</v>
+        <v>0.05815061963775018</v>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>225</v>
       </c>
       <c r="P56" s="5" t="n">
-        <v>0.05957146220861788</v>
+        <v>0.07244995233555762</v>
       </c>
       <c r="Q56" s="9" t="inlineStr">
         <is>
@@ -5196,13 +5196,13 @@
         </is>
       </c>
       <c r="D57" s="13" t="n">
-        <v>146.85</v>
+        <v>145.36</v>
       </c>
       <c r="E57" s="18" t="n">
-        <v>0.0326</v>
+        <v>0.0221</v>
       </c>
       <c r="F57" s="18" t="n">
-        <v>0.0951</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="G57" s="15" t="n"/>
       <c r="H57" s="21" t="inlineStr">
@@ -5221,7 +5221,7 @@
         <v>196</v>
       </c>
       <c r="M57" s="18" t="n">
-        <v>0.334695267279537</v>
+        <v>0.3483764446890478</v>
       </c>
       <c r="N57" s="12" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>170</v>
       </c>
       <c r="P57" s="18" t="n">
-        <v>0.1576438542730678</v>
+        <v>0.1695101816180516</v>
       </c>
       <c r="Q57" s="19" t="inlineStr">
         <is>
@@ -5277,13 +5277,13 @@
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>39.08</v>
+        <v>38.83</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0.0288</v>
+        <v>0.0221</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0.0487</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="G58" s="6" t="n">
         <v>46324</v>
@@ -5338,13 +5338,13 @@
         </is>
       </c>
       <c r="D59" s="13" t="n">
-        <v>21.5</v>
+        <v>21.51</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>0.044</v>
+        <v>0.0447</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.0941</v>
       </c>
       <c r="G59" s="15" t="n"/>
       <c r="H59" s="21" t="inlineStr">
@@ -5389,13 +5389,13 @@
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>203.73</v>
+        <v>199.65</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0.0239</v>
+        <v>0.0034</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>0.1109</v>
+        <v>0.08869999999999999</v>
       </c>
       <c r="G60" s="6" t="n">
         <v>46328</v>
@@ -5450,13 +5450,13 @@
         </is>
       </c>
       <c r="D61" s="13" t="n">
-        <v>37.29</v>
+        <v>36.8</v>
       </c>
       <c r="E61" s="18" t="n">
-        <v>0.1087</v>
+        <v>0.09390000000000001</v>
       </c>
       <c r="F61" s="18" t="n">
-        <v>0.08449999999999999</v>
+        <v>0.0701</v>
       </c>
       <c r="G61" s="15" t="n">
         <v>46315</v>
@@ -5492,7 +5492,7 @@
         <v>43</v>
       </c>
       <c r="P61" s="18" t="n">
-        <v>0.1531241619737195</v>
+        <v>0.1684782608695653</v>
       </c>
       <c r="Q61" s="19" t="inlineStr">
         <is>
@@ -5537,13 +5537,13 @@
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>31.8</v>
+        <v>31.98</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>0.0129</v>
+        <v>0.0188</v>
       </c>
       <c r="F62" s="22" t="n">
-        <v>-0.0101</v>
+        <v>-0.0044</v>
       </c>
       <c r="G62" s="6" t="n">
         <v>46316</v>
@@ -5572,7 +5572,7 @@
         <v>35</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>0.10062893081761</v>
+        <v>0.09443402126328954</v>
       </c>
       <c r="N62" s="3" t="inlineStr"/>
       <c r="O62" s="8" t="n"/>
@@ -5616,13 +5616,13 @@
         </is>
       </c>
       <c r="D63" s="13" t="n">
-        <v>259.55</v>
+        <v>259.14</v>
       </c>
       <c r="E63" s="18" t="n">
-        <v>0.2043</v>
+        <v>0.2024</v>
       </c>
       <c r="F63" s="18" t="n">
-        <v>0.3779999999999999</v>
+        <v>0.3758</v>
       </c>
       <c r="G63" s="15" t="n"/>
       <c r="H63" s="21" t="inlineStr">
@@ -5667,13 +5667,13 @@
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>58.22</v>
+        <v>57.1</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.0733</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>0.2189</v>
+        <v>0.1956</v>
       </c>
       <c r="G64" s="6" t="n">
         <v>46311</v>
@@ -5709,7 +5709,7 @@
         <v>63</v>
       </c>
       <c r="P64" s="5" t="n">
-        <v>0.08210237031947787</v>
+        <v>0.1033274956217163</v>
       </c>
       <c r="Q64" s="9" t="inlineStr">
         <is>
@@ -5758,13 +5758,13 @@
         </is>
       </c>
       <c r="D65" s="13" t="n">
-        <v>45.25</v>
+        <v>44.89</v>
       </c>
       <c r="E65" s="18" t="n">
+        <v>0.0595</v>
+      </c>
+      <c r="F65" s="18" t="n">
         <v>0.068</v>
-      </c>
-      <c r="F65" s="18" t="n">
-        <v>0.0766</v>
       </c>
       <c r="G65" s="15" t="n">
         <v>46328</v>
@@ -5819,13 +5819,13 @@
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>75.11</v>
+        <v>75.83</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>0.0453</v>
+        <v>0.0554</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>0.0011</v>
+        <v>0.0108</v>
       </c>
       <c r="G66" s="6" t="n">
         <v>46328</v>
@@ -5854,7 +5854,7 @@
         <v>89</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>0.1849287711356677</v>
+        <v>0.1736779638665436</v>
       </c>
       <c r="N66" s="3" t="inlineStr"/>
       <c r="O66" s="8" t="n"/>
@@ -5910,13 +5910,13 @@
         </is>
       </c>
       <c r="D67" s="13" t="n">
-        <v>160.83</v>
+        <v>160.66</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0054</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>0.1581</v>
+        <v>0.1568</v>
       </c>
       <c r="G67" s="15" t="n">
         <v>46325</v>
@@ -5945,7 +5945,7 @@
         <v>185</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>0.1502829074177702</v>
+        <v>0.1515000622432466</v>
       </c>
       <c r="N67" s="12" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>185</v>
       </c>
       <c r="P67" s="18" t="n">
-        <v>0.1502829074177702</v>
+        <v>0.1515000622432466</v>
       </c>
       <c r="Q67" s="19" t="inlineStr">
         <is>
@@ -6001,13 +6001,13 @@
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>115.87</v>
+        <v>115.16</v>
       </c>
       <c r="E68" s="22" t="n">
-        <v>-0.0498</v>
+        <v>-0.0556</v>
       </c>
       <c r="F68" s="22" t="n">
-        <v>-0.0495</v>
+        <v>-0.0554</v>
       </c>
       <c r="G68" s="6" t="n"/>
       <c r="H68" s="7" t="inlineStr">
@@ -6026,7 +6026,7 @@
         <v>120</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>0.03564339345818586</v>
+        <v>0.04202848211184442</v>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>115</v>
       </c>
       <c r="P68" s="22" t="n">
-        <v>-0.007508414602571887</v>
+        <v>-0.00138937130948243</v>
       </c>
       <c r="Q68" s="9" t="inlineStr"/>
       <c r="R68" s="8" t="n"/>
@@ -6072,13 +6072,13 @@
         </is>
       </c>
       <c r="D69" s="13" t="n">
-        <v>319.55</v>
+        <v>315.79</v>
       </c>
       <c r="E69" s="14" t="n">
-        <v>-0.1048</v>
+        <v>-0.1154</v>
       </c>
       <c r="F69" s="14" t="n">
-        <v>-0.1048</v>
+        <v>-0.1153</v>
       </c>
       <c r="G69" s="15" t="n">
         <v>46325</v>
@@ -6107,7 +6107,7 @@
         <v>406</v>
       </c>
       <c r="M69" s="18" t="n">
-        <v>0.2705366922234392</v>
+        <v>0.2856645238924601</v>
       </c>
       <c r="N69" s="12" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>436</v>
       </c>
       <c r="P69" s="18" t="n">
-        <v>0.3644187138163041</v>
+        <v>0.3806643655593906</v>
       </c>
       <c r="Q69" s="19" t="inlineStr">
         <is>
@@ -6155,13 +6155,13 @@
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>325.47</v>
+        <v>326.1</v>
       </c>
       <c r="E70" s="22" t="n">
-        <v>-0.0395</v>
+        <v>-0.0377</v>
       </c>
       <c r="F70" s="22" t="n">
-        <v>-0.0716</v>
+        <v>-0.0698</v>
       </c>
       <c r="G70" s="6" t="n">
         <v>46311</v>
@@ -6190,7 +6190,7 @@
         <v>415</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>0.2750791163548099</v>
+        <v>0.2726157620361851</v>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>380</v>
       </c>
       <c r="P70" s="5" t="n">
-        <v>0.1675423234092235</v>
+        <v>0.1652867218644587</v>
       </c>
       <c r="Q70" s="9" t="inlineStr">
         <is>
@@ -6250,13 +6250,13 @@
         </is>
       </c>
       <c r="D71" s="13" t="n">
-        <v>62.17</v>
+        <v>62.39</v>
       </c>
       <c r="E71" s="14" t="n">
-        <v>-0.0265</v>
+        <v>-0.023</v>
       </c>
       <c r="F71" s="18" t="n">
-        <v>0.04190000000000001</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="G71" s="15" t="n">
         <v>46309</v>
@@ -6311,13 +6311,13 @@
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>1102.29</v>
+        <v>1095.37</v>
       </c>
       <c r="E72" s="22" t="n">
-        <v>-0.0257</v>
+        <v>-0.0318</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>0.0639</v>
+        <v>0.0572</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>46308</v>
@@ -6349,7 +6349,7 @@
         <v>1245</v>
       </c>
       <c r="P72" s="5" t="n">
-        <v>0.1294668372206951</v>
+        <v>0.1366022439906152</v>
       </c>
       <c r="Q72" s="9" t="inlineStr">
         <is>
@@ -6394,13 +6394,13 @@
         </is>
       </c>
       <c r="D73" s="13" t="n">
-        <v>35.78</v>
+        <v>35.53</v>
       </c>
       <c r="E73" s="18" t="n">
-        <v>0.4578</v>
+        <v>0.4478</v>
       </c>
       <c r="F73" s="18" t="n">
-        <v>0.4765</v>
+        <v>0.4664</v>
       </c>
       <c r="G73" s="15" t="n"/>
       <c r="H73" s="21" t="inlineStr">
@@ -6445,13 +6445,13 @@
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>24.96</v>
+        <v>24.77</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>0.379</v>
+        <v>0.3685</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>0.6662</v>
+        <v>0.6535</v>
       </c>
       <c r="G74" s="6" t="n">
         <v>46346</v>
@@ -6506,13 +6506,13 @@
         </is>
       </c>
       <c r="D75" s="13" t="n">
-        <v>504.45</v>
+        <v>505.83</v>
       </c>
       <c r="E75" s="14" t="n">
-        <v>-0.0472</v>
+        <v>-0.0446</v>
       </c>
       <c r="F75" s="18" t="n">
-        <v>0.0218</v>
+        <v>0.0245</v>
       </c>
       <c r="G75" s="15" t="n"/>
       <c r="H75" s="21" t="inlineStr">
@@ -6579,13 +6579,13 @@
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>68.76000000000001</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="E76" s="22" t="n">
-        <v>-0.0396</v>
+        <v>-0.0478</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>0.0163</v>
+        <v>0.0077</v>
       </c>
       <c r="G76" s="6" t="n">
         <v>46321</v>
@@ -6614,7 +6614,7 @@
         <v>68</v>
       </c>
       <c r="M76" s="22" t="n">
-        <v>-0.01105293775450851</v>
+        <v>-0.002640070401877483</v>
       </c>
       <c r="N76" s="3" t="inlineStr"/>
       <c r="O76" s="8" t="n"/>
@@ -6656,13 +6656,13 @@
         </is>
       </c>
       <c r="D77" s="13" t="n">
-        <v>135.59</v>
+        <v>133.97</v>
       </c>
       <c r="E77" s="14" t="n">
-        <v>-0.0429</v>
+        <v>-0.05429999999999999</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>0.1015</v>
+        <v>0.08839999999999999</v>
       </c>
       <c r="G77" s="15" t="n">
         <v>46310</v>
@@ -6721,13 +6721,13 @@
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>136.77</v>
+        <v>136.74</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>0.0115</v>
+        <v>0.0112</v>
       </c>
       <c r="F78" s="22" t="n">
-        <v>-0.0286</v>
+        <v>-0.0288</v>
       </c>
       <c r="G78" s="6" t="n">
         <v>46308</v>
@@ -6759,7 +6759,7 @@
         <v>140</v>
       </c>
       <c r="P78" s="5" t="n">
-        <v>0.02361629012210273</v>
+        <v>0.0238408658768465</v>
       </c>
       <c r="Q78" s="9" t="inlineStr">
         <is>
@@ -6808,13 +6808,13 @@
         </is>
       </c>
       <c r="D79" s="13" t="n">
-        <v>339.66</v>
+        <v>336.64</v>
       </c>
       <c r="E79" s="14" t="n">
-        <v>-0.0248</v>
+        <v>-0.0335</v>
       </c>
       <c r="F79" s="14" t="n">
-        <v>-0.0235</v>
+        <v>-0.0322</v>
       </c>
       <c r="G79" s="15" t="n">
         <v>46315</v>
@@ -6843,7 +6843,7 @@
         <v>358</v>
       </c>
       <c r="M79" s="18" t="n">
-        <v>0.05399517164223039</v>
+        <v>0.06345057034220537</v>
       </c>
       <c r="N79" s="12" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         <v>374</v>
       </c>
       <c r="P79" s="18" t="n">
-        <v>0.101101101101101</v>
+        <v>0.1109790874524715</v>
       </c>
       <c r="Q79" s="19" t="inlineStr">
         <is>
@@ -6899,13 +6899,13 @@
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>58.44</v>
+        <v>58.27</v>
       </c>
       <c r="E80" s="22" t="n">
-        <v>-0.0037</v>
-      </c>
-      <c r="F80" s="5" t="n">
-        <v>0.0011</v>
+        <v>-0.006500000000000001</v>
+      </c>
+      <c r="F80" s="22" t="n">
+        <v>-0.0017</v>
       </c>
       <c r="G80" s="6" t="n">
         <v>46310</v>
@@ -6934,7 +6934,7 @@
         <v>57</v>
       </c>
       <c r="M80" s="22" t="n">
-        <v>-0.02464065708418887</v>
+        <v>-0.02179509181396951</v>
       </c>
       <c r="N80" s="3" t="inlineStr"/>
       <c r="O80" s="8" t="n"/>
@@ -6976,13 +6976,13 @@
         </is>
       </c>
       <c r="D81" s="13" t="n">
-        <v>13.08</v>
+        <v>13.48</v>
       </c>
       <c r="E81" s="18" t="n">
-        <v>0.1286</v>
+        <v>0.1631</v>
       </c>
       <c r="F81" s="18" t="n">
-        <v>0.0179</v>
+        <v>0.049</v>
       </c>
       <c r="G81" s="15" t="n"/>
       <c r="H81" s="21" t="inlineStr">
@@ -7027,13 +7027,13 @@
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>409.86</v>
+        <v>407.05</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0.0224</v>
+        <v>0.0154</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>0.159</v>
+        <v>0.151</v>
       </c>
       <c r="G82" s="6" t="n"/>
       <c r="H82" s="7" t="inlineStr">
@@ -7090,13 +7090,13 @@
         </is>
       </c>
       <c r="D83" s="13" t="n">
-        <v>98.95999999999999</v>
+        <v>96.18000000000001</v>
       </c>
       <c r="E83" s="18" t="n">
-        <v>0.476</v>
+        <v>0.4345000000000001</v>
       </c>
       <c r="F83" s="18" t="n">
-        <v>0.4963</v>
+        <v>0.4542</v>
       </c>
       <c r="G83" s="15" t="n"/>
       <c r="H83" s="21" t="inlineStr">
@@ -7141,13 +7141,13 @@
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>42.47</v>
+        <v>42.29</v>
       </c>
       <c r="E84" s="22" t="n">
-        <v>-0.0161</v>
+        <v>-0.0202</v>
       </c>
       <c r="F84" s="22" t="n">
-        <v>-0.1642</v>
+        <v>-0.1677</v>
       </c>
       <c r="G84" s="6" t="n"/>
       <c r="H84" s="7" t="inlineStr">
@@ -7192,13 +7192,13 @@
         </is>
       </c>
       <c r="D85" s="13" t="n">
-        <v>1029.01</v>
-      </c>
-      <c r="E85" s="14" t="n">
-        <v>-0.0053</v>
+        <v>1036.53</v>
+      </c>
+      <c r="E85" s="18" t="n">
+        <v>0.002</v>
       </c>
       <c r="F85" s="14" t="n">
-        <v>-0.0248</v>
+        <v>-0.0177</v>
       </c>
       <c r="G85" s="15" t="n">
         <v>46308</v>
@@ -7227,7 +7227,7 @@
         <v>1325</v>
       </c>
       <c r="M85" s="18" t="n">
-        <v>0.2876454067501774</v>
+        <v>0.2783035705671809</v>
       </c>
       <c r="N85" s="12" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         <v>1210</v>
       </c>
       <c r="P85" s="18" t="n">
-        <v>0.1758875035228035</v>
+        <v>0.1673564682160671</v>
       </c>
       <c r="Q85" s="19" t="inlineStr">
         <is>
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>135.94</v>
+        <v>135.39</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>0.1017</v>
+        <v>0.0973</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>0.004500000000000001</v>
+        <v>0.0004</v>
       </c>
       <c r="G86" s="6" t="n">
         <v>46324</v>
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="D87" s="13" t="n">
-        <v>122.26</v>
+        <v>117.34</v>
       </c>
       <c r="E87" s="18" t="n">
-        <v>0.2935</v>
+        <v>0.2414</v>
       </c>
       <c r="F87" s="18" t="n">
-        <v>0.0919</v>
+        <v>0.048</v>
       </c>
       <c r="G87" s="15" t="n"/>
       <c r="H87" s="21" t="inlineStr">
@@ -7391,13 +7391,13 @@
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>94.68000000000001</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>0.1052</v>
+        <v>0.1615</v>
       </c>
       <c r="F88" s="22" t="n">
-        <v>-0.0738</v>
+        <v>-0.0267</v>
       </c>
       <c r="G88" s="6" t="n"/>
       <c r="H88" s="7" t="inlineStr">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="D89" s="13" t="n">
-        <v>158.93</v>
+        <v>157.76</v>
       </c>
       <c r="E89" s="18" t="n">
-        <v>0.0557</v>
+        <v>0.048</v>
       </c>
       <c r="F89" s="18" t="n">
-        <v>0.175</v>
+        <v>0.1663</v>
       </c>
       <c r="G89" s="15" t="n">
         <v>46324</v>
@@ -7503,13 +7503,13 @@
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>162.99</v>
+        <v>159.83</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>0.051</v>
+        <v>0.0306</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0.0843</v>
+        <v>0.0633</v>
       </c>
       <c r="G90" s="6" t="n"/>
       <c r="H90" s="7" t="inlineStr">
@@ -7568,13 +7568,13 @@
         </is>
       </c>
       <c r="D91" s="13" t="n">
-        <v>354.12</v>
+        <v>353.51</v>
       </c>
       <c r="E91" s="14" t="n">
-        <v>-0.0158</v>
+        <v>-0.0175</v>
       </c>
       <c r="F91" s="18" t="n">
-        <v>0.0525</v>
+        <v>0.0506</v>
       </c>
       <c r="G91" s="15" t="n">
         <v>46308</v>
@@ -7603,7 +7603,7 @@
         <v>196</v>
       </c>
       <c r="M91" s="14" t="n">
-        <v>-0.4465153055461425</v>
+        <v>-0.4455602387485502</v>
       </c>
       <c r="N91" s="12" t="inlineStr"/>
       <c r="O91" s="17" t="n"/>
@@ -7647,13 +7647,13 @@
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>107.32</v>
+        <v>105.73</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>0.0336</v>
+        <v>0.0183</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>0.1071</v>
+        <v>0.0907</v>
       </c>
       <c r="G92" s="6" t="n"/>
       <c r="H92" s="7" t="inlineStr">
@@ -7672,7 +7672,7 @@
         <v>375</v>
       </c>
       <c r="M92" s="5" t="n">
-        <v>2.494222884830414</v>
+        <v>2.546770074718623</v>
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>368</v>
       </c>
       <c r="P92" s="5" t="n">
-        <v>2.428997390980246</v>
+        <v>2.480563699990542</v>
       </c>
       <c r="Q92" s="9" t="inlineStr">
         <is>
@@ -7736,13 +7736,13 @@
         </is>
       </c>
       <c r="D93" s="13" t="n">
-        <v>368.95</v>
-      </c>
-      <c r="E93" s="18" t="n">
-        <v>0.0009</v>
+        <v>367.29</v>
+      </c>
+      <c r="E93" s="14" t="n">
+        <v>-0.0036</v>
       </c>
       <c r="F93" s="18" t="n">
-        <v>0.0833</v>
+        <v>0.0785</v>
       </c>
       <c r="G93" s="15" t="n">
         <v>46317</v>
@@ -7774,7 +7774,7 @@
         <v>115</v>
       </c>
       <c r="P93" s="14" t="n">
-        <v>-0.6883046483263314</v>
+        <v>-0.6868959133110076</v>
       </c>
       <c r="Q93" s="19" t="inlineStr">
         <is>
@@ -7823,13 +7823,13 @@
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>570.24</v>
+        <v>570.89</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0.0126</v>
+        <v>0.0137</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0.08259999999999999</v>
+        <v>0.08380000000000001</v>
       </c>
       <c r="G94" s="6" t="n">
         <v>46324</v>
@@ -7858,7 +7858,7 @@
         <v>366</v>
       </c>
       <c r="M94" s="22" t="n">
-        <v>-0.3581649831649832</v>
+        <v>-0.358895759253096</v>
       </c>
       <c r="N94" s="3" t="inlineStr"/>
       <c r="O94" s="8" t="n"/>
@@ -7900,13 +7900,13 @@
         </is>
       </c>
       <c r="D95" s="13" t="n">
-        <v>1794.32</v>
+        <v>1785.71</v>
       </c>
       <c r="E95" s="14" t="n">
-        <v>-0.0249</v>
+        <v>-0.0295</v>
       </c>
       <c r="F95" s="14" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-0.08410000000000001</v>
       </c>
       <c r="G95" s="15" t="n"/>
       <c r="H95" s="21" t="inlineStr">
@@ -7961,13 +7961,13 @@
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>215.42</v>
+        <v>216.24</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.0042</v>
       </c>
       <c r="F96" s="22" t="n">
-        <v>-0.0309</v>
+        <v>-0.0272</v>
       </c>
       <c r="G96" s="6" t="n">
         <v>46309</v>
@@ -7996,7 +7996,7 @@
         <v>668</v>
       </c>
       <c r="M96" s="5" t="n">
-        <v>2.100919134713583</v>
+        <v>2.089160192378838</v>
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>550</v>
       </c>
       <c r="P96" s="5" t="n">
-        <v>1.553151982174357</v>
+        <v>1.54347021827599</v>
       </c>
       <c r="Q96" s="9" t="inlineStr">
         <is>
@@ -8056,13 +8056,13 @@
         </is>
       </c>
       <c r="D97" s="13" t="n">
-        <v>115.05</v>
+        <v>115.04</v>
       </c>
       <c r="E97" s="18" t="n">
-        <v>0.0109</v>
+        <v>0.0108</v>
       </c>
       <c r="F97" s="18" t="n">
-        <v>0.0251</v>
+        <v>0.025</v>
       </c>
       <c r="G97" s="15" t="n">
         <v>46321</v>
@@ -8091,7 +8091,7 @@
         <v>240</v>
       </c>
       <c r="M97" s="18" t="n">
-        <v>1.086049543676662</v>
+        <v>1.086230876216968</v>
       </c>
       <c r="N97" s="12" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         <v>240</v>
       </c>
       <c r="P97" s="18" t="n">
-        <v>1.086049543676662</v>
+        <v>1.086230876216968</v>
       </c>
       <c r="Q97" s="19" t="inlineStr">
         <is>
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>243.88</v>
+        <v>242.91</v>
       </c>
       <c r="E98" s="22" t="n">
-        <v>-0.0313</v>
+        <v>-0.0352</v>
       </c>
       <c r="F98" s="22" t="n">
-        <v>-0.0319</v>
+        <v>-0.0357</v>
       </c>
       <c r="G98" s="6" t="n">
         <v>46310</v>
@@ -8186,7 +8186,7 @@
         <v>113</v>
       </c>
       <c r="M98" s="22" t="n">
-        <v>-0.5366573724782679</v>
+        <v>-0.534807130212836</v>
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>114</v>
       </c>
       <c r="P98" s="22" t="n">
-        <v>-0.5325569952435624</v>
+        <v>-0.5306903791527726</v>
       </c>
       <c r="Q98" s="9" t="inlineStr"/>
       <c r="R98" s="8" t="n"/>
@@ -8236,13 +8236,13 @@
         </is>
       </c>
       <c r="D99" s="13" t="n">
-        <v>22.18</v>
+        <v>22.26</v>
       </c>
       <c r="E99" s="18" t="n">
-        <v>0.1433</v>
+        <v>0.1474</v>
       </c>
       <c r="F99" s="18" t="n">
-        <v>0.058</v>
+        <v>0.06179999999999999</v>
       </c>
       <c r="G99" s="15" t="n">
         <v>46324</v>
@@ -8297,13 +8297,13 @@
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>14.92</v>
+        <v>14.86</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>0.0159</v>
+        <v>0.0116</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>0.076</v>
+        <v>0.07139999999999999</v>
       </c>
       <c r="G100" s="6" t="n">
         <v>46323</v>
@@ -8358,13 +8358,13 @@
         </is>
       </c>
       <c r="D101" s="13" t="n">
-        <v>109.88</v>
+        <v>108.6</v>
       </c>
       <c r="E101" s="18" t="n">
-        <v>0.0493</v>
+        <v>0.0371</v>
       </c>
       <c r="F101" s="18" t="n">
-        <v>0.1512</v>
+        <v>0.1378</v>
       </c>
       <c r="G101" s="15" t="n">
         <v>46323</v>
@@ -8393,7 +8393,7 @@
         <v>285</v>
       </c>
       <c r="M101" s="18" t="n">
-        <v>1.593738623953404</v>
+        <v>1.624309392265193</v>
       </c>
       <c r="N101" s="12" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>285</v>
       </c>
       <c r="P101" s="18" t="n">
-        <v>1.593738623953404</v>
+        <v>1.624309392265193</v>
       </c>
       <c r="Q101" s="19" t="inlineStr">
         <is>
@@ -8445,13 +8445,13 @@
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>432.86</v>
+        <v>429.31</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>0.0533</v>
-      </c>
-      <c r="F102" s="5" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.0447</v>
+      </c>
+      <c r="F102" s="22" t="n">
+        <v>-0.0028</v>
       </c>
       <c r="G102" s="6" t="n">
         <v>46324</v>
@@ -8520,13 +8520,13 @@
         </is>
       </c>
       <c r="D103" s="13" t="n">
-        <v>51.08</v>
+        <v>50.55</v>
       </c>
       <c r="E103" s="14" t="n">
-        <v>-0.0151</v>
+        <v>-0.0253</v>
       </c>
       <c r="F103" s="14" t="n">
-        <v>-0.0115</v>
+        <v>-0.0217</v>
       </c>
       <c r="G103" s="15" t="n">
         <v>46311</v>
@@ -8581,13 +8581,13 @@
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>370.35</v>
+        <v>368.64</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>0.025</v>
+        <v>0.0203</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>0.0613</v>
+        <v>0.0564</v>
       </c>
       <c r="G104" s="6" t="n">
         <v>46322</v>
@@ -8616,7 +8616,7 @@
         <v>525</v>
       </c>
       <c r="M104" s="5" t="n">
-        <v>0.4175779667881733</v>
+        <v>0.4241536458333334</v>
       </c>
       <c r="N104" s="3" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>543</v>
       </c>
       <c r="P104" s="5" t="n">
-        <v>0.4661806399351964</v>
+        <v>0.4729817708333334</v>
       </c>
       <c r="Q104" s="9" t="inlineStr">
         <is>
@@ -8672,13 +8672,13 @@
         </is>
       </c>
       <c r="D105" s="13" t="n">
-        <v>69.92</v>
+        <v>69.77</v>
       </c>
       <c r="E105" s="14" t="n">
-        <v>-0.0127</v>
+        <v>-0.0148</v>
       </c>
       <c r="F105" s="14" t="n">
-        <v>-0.0314</v>
+        <v>-0.0335</v>
       </c>
       <c r="G105" s="15" t="n">
         <v>46314</v>
@@ -8707,7 +8707,7 @@
         <v>412</v>
       </c>
       <c r="M105" s="18" t="n">
-        <v>4.892448512585812</v>
+        <v>4.905116812383547</v>
       </c>
       <c r="N105" s="12" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>350</v>
       </c>
       <c r="P105" s="18" t="n">
-        <v>4.005720823798627</v>
+        <v>4.016482728966605</v>
       </c>
       <c r="Q105" s="19" t="inlineStr">
         <is>
@@ -8763,13 +8763,13 @@
         </is>
       </c>
       <c r="D106" s="4" t="n">
-        <v>80.33</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.0142</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>0.0393</v>
+        <v>0.0362</v>
       </c>
       <c r="G106" s="6" t="n"/>
       <c r="H106" s="7" t="inlineStr">
@@ -8788,7 +8788,7 @@
         <v>68</v>
       </c>
       <c r="M106" s="22" t="n">
-        <v>-0.1534918461346944</v>
+        <v>-0.1510611735330836</v>
       </c>
       <c r="N106" s="3" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>68</v>
       </c>
       <c r="P106" s="22" t="n">
-        <v>-0.1534918461346944</v>
+        <v>-0.1510611735330836</v>
       </c>
       <c r="Q106" s="9" t="inlineStr">
         <is>
@@ -8844,13 +8844,13 @@
         </is>
       </c>
       <c r="D107" s="13" t="n">
-        <v>252.65</v>
+        <v>248.78</v>
       </c>
       <c r="E107" s="18" t="n">
-        <v>0.0189</v>
+        <v>0.0033</v>
       </c>
       <c r="F107" s="18" t="n">
-        <v>0.0184</v>
+        <v>0.0028</v>
       </c>
       <c r="G107" s="15" t="n">
         <v>46325</v>
@@ -8879,7 +8879,7 @@
         <v>295</v>
       </c>
       <c r="M107" s="18" t="n">
-        <v>0.1676231941420938</v>
+        <v>0.185786638797331</v>
       </c>
       <c r="N107" s="12" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>246</v>
       </c>
       <c r="P107" s="14" t="n">
-        <v>-0.02632099742727095</v>
+        <v>-0.01117453171476807</v>
       </c>
       <c r="Q107" s="19" t="inlineStr">
         <is>
@@ -8927,13 +8927,13 @@
         </is>
       </c>
       <c r="D108" s="4" t="n">
-        <v>105.65</v>
+        <v>105.52</v>
       </c>
       <c r="E108" s="22" t="n">
-        <v>-0.0273</v>
+        <v>-0.0285</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>0.1248</v>
+        <v>0.1234</v>
       </c>
       <c r="G108" s="6" t="n">
         <v>46316</v>
@@ -8962,7 +8962,7 @@
         <v>112</v>
       </c>
       <c r="M108" s="5" t="n">
-        <v>0.06010411736867008</v>
+        <v>0.06141015921152392</v>
       </c>
       <c r="N108" s="3" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>120</v>
       </c>
       <c r="P108" s="5" t="n">
-        <v>0.1358258400378608</v>
+        <v>0.1372251705837756</v>
       </c>
       <c r="Q108" s="9" t="inlineStr">
         <is>
@@ -9026,13 +9026,13 @@
         </is>
       </c>
       <c r="D109" s="13" t="n">
-        <v>397.84</v>
+        <v>393.17</v>
       </c>
       <c r="E109" s="14" t="n">
-        <v>-0.0464</v>
+        <v>-0.0576</v>
       </c>
       <c r="F109" s="18" t="n">
-        <v>0.09480000000000001</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="G109" s="15" t="n"/>
       <c r="H109" s="21" t="inlineStr">
@@ -9051,7 +9051,7 @@
         <v>390</v>
       </c>
       <c r="M109" s="14" t="n">
-        <v>-0.01970641463905081</v>
+        <v>-0.008062670091817829</v>
       </c>
       <c r="N109" s="12" t="inlineStr">
         <is>
@@ -9099,13 +9099,13 @@
         </is>
       </c>
       <c r="D110" s="4" t="n">
-        <v>179.96</v>
-      </c>
-      <c r="E110" s="5" t="n">
-        <v>0.0018</v>
+        <v>179.1</v>
+      </c>
+      <c r="E110" s="22" t="n">
+        <v>-0.003</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>0.1844</v>
+        <v>0.1788</v>
       </c>
       <c r="G110" s="6" t="n"/>
       <c r="H110" s="7" t="inlineStr">
@@ -9124,7 +9124,7 @@
         <v>161</v>
       </c>
       <c r="M110" s="22" t="n">
-        <v>-0.1053567459435431</v>
+        <v>-0.1010608598548297</v>
       </c>
       <c r="N110" s="3" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>180</v>
       </c>
       <c r="P110" s="5" t="n">
-        <v>0.0002222716159146035</v>
+        <v>0.005025125628140736</v>
       </c>
       <c r="Q110" s="9" t="inlineStr">
         <is>
@@ -9176,13 +9176,13 @@
         </is>
       </c>
       <c r="D111" s="13" t="n">
-        <v>45.92</v>
+        <v>44.98</v>
       </c>
       <c r="E111" s="14" t="n">
-        <v>-0.0901</v>
+        <v>-0.1086</v>
       </c>
       <c r="F111" s="18" t="n">
-        <v>0.0256</v>
+        <v>0.004699999999999999</v>
       </c>
       <c r="G111" s="15" t="n">
         <v>46323</v>
@@ -9211,7 +9211,7 @@
         <v>55</v>
       </c>
       <c r="M111" s="18" t="n">
-        <v>0.1977351916376306</v>
+        <v>0.2227656736327257</v>
       </c>
       <c r="N111" s="12" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>65</v>
       </c>
       <c r="P111" s="18" t="n">
-        <v>0.4155052264808362</v>
+        <v>0.4450867052023122</v>
       </c>
       <c r="Q111" s="19" t="inlineStr">
         <is>
@@ -9263,13 +9263,13 @@
         </is>
       </c>
       <c r="D112" s="4" t="n">
-        <v>326.49</v>
-      </c>
-      <c r="E112" s="5" t="n">
-        <v>0.0046</v>
+        <v>324.69</v>
+      </c>
+      <c r="E112" s="22" t="n">
+        <v>-0.001</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>0.076</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G112" s="6" t="n"/>
       <c r="H112" s="7" t="inlineStr">
@@ -9288,7 +9288,7 @@
         <v>331</v>
       </c>
       <c r="M112" s="5" t="n">
-        <v>0.01381359306563751</v>
+        <v>0.01943392158674428</v>
       </c>
       <c r="N112" s="3" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>330</v>
       </c>
       <c r="P112" s="5" t="n">
-        <v>0.01075071211981987</v>
+        <v>0.01635406079645201</v>
       </c>
       <c r="Q112" s="9" t="inlineStr">
         <is>
@@ -9348,13 +9348,13 @@
         </is>
       </c>
       <c r="D113" s="13" t="n">
-        <v>95.58</v>
-      </c>
-      <c r="E113" s="14" t="n">
-        <v>-0.0009</v>
+        <v>96.06999999999999</v>
+      </c>
+      <c r="E113" s="18" t="n">
+        <v>0.0042</v>
       </c>
       <c r="F113" s="14" t="n">
-        <v>-0.08220000000000001</v>
+        <v>-0.0776</v>
       </c>
       <c r="G113" s="15" t="n"/>
       <c r="H113" s="21" t="inlineStr">
@@ -9373,7 +9373,7 @@
         <v>123</v>
       </c>
       <c r="M113" s="18" t="n">
-        <v>0.2868801004394225</v>
+        <v>0.2803164359321329</v>
       </c>
       <c r="N113" s="12" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>130</v>
       </c>
       <c r="P113" s="18" t="n">
-        <v>0.3601171793262189</v>
+        <v>0.3531799729364006</v>
       </c>
       <c r="Q113" s="19" t="inlineStr">
         <is>
@@ -9425,13 +9425,13 @@
         </is>
       </c>
       <c r="D114" s="4" t="n">
-        <v>206.47</v>
+        <v>205.23</v>
       </c>
       <c r="E114" s="22" t="n">
-        <v>-0.0139</v>
+        <v>-0.0198</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>0.0373</v>
+        <v>0.031</v>
       </c>
       <c r="G114" s="6" t="n">
         <v>46315</v>
@@ -9460,7 +9460,7 @@
         <v>212</v>
       </c>
       <c r="M114" s="5" t="n">
-        <v>0.026783552089892</v>
+        <v>0.03298738001266877</v>
       </c>
       <c r="N114" s="3" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>205</v>
       </c>
       <c r="P114" s="22" t="n">
-        <v>-0.00711967840364217</v>
+        <v>-0.001120693855674072</v>
       </c>
       <c r="Q114" s="9" t="inlineStr">
         <is>
@@ -9516,13 +9516,13 @@
         </is>
       </c>
       <c r="D115" s="13" t="n">
-        <v>85.18000000000001</v>
+        <v>84.53</v>
       </c>
       <c r="E115" s="14" t="n">
-        <v>-0.0281</v>
+        <v>-0.0356</v>
       </c>
       <c r="F115" s="18" t="n">
-        <v>0.1364</v>
+        <v>0.1277</v>
       </c>
       <c r="G115" s="15" t="n">
         <v>46324</v>
@@ -9550,8 +9550,8 @@
       <c r="L115" s="17" t="n">
         <v>85</v>
       </c>
-      <c r="M115" s="14" t="n">
-        <v>-0.002113172106128279</v>
+      <c r="M115" s="18" t="n">
+        <v>0.005560156157577178</v>
       </c>
       <c r="N115" s="12" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>90</v>
       </c>
       <c r="P115" s="18" t="n">
-        <v>0.05658605306409947</v>
+        <v>0.06471075357861113</v>
       </c>
       <c r="Q115" s="19" t="inlineStr">
         <is>
@@ -9603,13 +9603,13 @@
         </is>
       </c>
       <c r="D116" s="4" t="n">
-        <v>146.98</v>
+        <v>146.64</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0.1046</v>
+        <v>0.1021</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>0.1321</v>
+        <v>0.1295</v>
       </c>
       <c r="G116" s="6" t="n">
         <v>46324</v>
@@ -9638,7 +9638,7 @@
         <v>165</v>
       </c>
       <c r="M116" s="5" t="n">
-        <v>0.1226017145189822</v>
+        <v>0.1252045826513913</v>
       </c>
       <c r="N116" s="3" t="inlineStr"/>
       <c r="O116" s="8" t="n"/>
@@ -9686,13 +9686,13 @@
         </is>
       </c>
       <c r="D117" s="13" t="n">
-        <v>522.48</v>
+        <v>520.21</v>
       </c>
       <c r="E117" s="14" t="n">
-        <v>-0.123</v>
+        <v>-0.1268</v>
       </c>
       <c r="F117" s="14" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.07690000000000001</v>
       </c>
       <c r="G117" s="15" t="n">
         <v>46328</v>
@@ -9757,13 +9757,13 @@
         </is>
       </c>
       <c r="D118" s="4" t="n">
-        <v>352.91</v>
+        <v>350.16</v>
       </c>
       <c r="E118" s="22" t="n">
-        <v>-0.1029</v>
+        <v>-0.1099</v>
       </c>
       <c r="F118" s="22" t="n">
-        <v>-0.1324</v>
+        <v>-0.1392</v>
       </c>
       <c r="G118" s="6" t="n">
         <v>46315</v>
@@ -9792,7 +9792,7 @@
         <v>487</v>
       </c>
       <c r="M118" s="5" t="n">
-        <v>0.379955229378595</v>
+        <v>0.3907927804432259</v>
       </c>
       <c r="N118" s="3" t="inlineStr">
         <is>
@@ -9803,7 +9803,7 @@
         <v>375</v>
       </c>
       <c r="P118" s="5" t="n">
-        <v>0.06259386245785037</v>
+        <v>0.07093899931459896</v>
       </c>
       <c r="Q118" s="9" t="inlineStr">
         <is>
@@ -9848,13 +9848,13 @@
         </is>
       </c>
       <c r="D119" s="13" t="n">
-        <v>270.1</v>
+        <v>269.12</v>
       </c>
       <c r="E119" s="18" t="n">
-        <v>0.0317</v>
+        <v>0.0279</v>
       </c>
       <c r="F119" s="18" t="n">
-        <v>0.05110000000000001</v>
+        <v>0.0472</v>
       </c>
       <c r="G119" s="15" t="n">
         <v>46308</v>
@@ -9883,7 +9883,7 @@
         <v>272</v>
       </c>
       <c r="M119" s="18" t="n">
-        <v>0.007034431691965853</v>
+        <v>0.0107015457788347</v>
       </c>
       <c r="N119" s="12" t="inlineStr"/>
       <c r="O119" s="17" t="n"/>
@@ -9935,13 +9935,13 @@
         </is>
       </c>
       <c r="D120" s="4" t="n">
-        <v>1133.03</v>
+        <v>1123.86</v>
       </c>
       <c r="E120" s="22" t="n">
-        <v>-0.0803</v>
+        <v>-0.0877</v>
       </c>
       <c r="F120" s="22" t="n">
-        <v>-0.0467</v>
+        <v>-0.0545</v>
       </c>
       <c r="G120" s="6" t="n">
         <v>46324</v>
@@ -9970,7 +9970,7 @@
         <v>1280</v>
       </c>
       <c r="M120" s="5" t="n">
-        <v>0.1297141293699196</v>
+        <v>0.1389318954318154</v>
       </c>
       <c r="N120" s="3" t="inlineStr">
         <is>
@@ -10030,13 +10030,13 @@
         </is>
       </c>
       <c r="D121" s="13" t="n">
-        <v>91.84</v>
+        <v>92.39</v>
       </c>
       <c r="E121" s="18" t="n">
-        <v>0.0272</v>
+        <v>0.0333</v>
       </c>
       <c r="F121" s="18" t="n">
-        <v>0.095</v>
+        <v>0.1016</v>
       </c>
       <c r="G121" s="15" t="n"/>
       <c r="H121" s="21" t="inlineStr">
@@ -10055,7 +10055,7 @@
         <v>102</v>
       </c>
       <c r="M121" s="18" t="n">
-        <v>0.1106271777003484</v>
+        <v>0.104015586102392</v>
       </c>
       <c r="N121" s="12" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>105</v>
       </c>
       <c r="P121" s="18" t="n">
-        <v>0.1432926829268292</v>
+        <v>0.1364866327524624</v>
       </c>
       <c r="Q121" s="19" t="inlineStr">
         <is>
@@ -10107,13 +10107,13 @@
         </is>
       </c>
       <c r="D122" s="4" t="n">
-        <v>149.54</v>
+        <v>148.46</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0.1422</v>
+        <v>0.134</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>0.2105</v>
+        <v>0.2017</v>
       </c>
       <c r="G122" s="6" t="n">
         <v>46324</v>
@@ -10142,7 +10142,7 @@
         <v>150</v>
       </c>
       <c r="M122" s="5" t="n">
-        <v>0.003076100040123098</v>
+        <v>0.01037316448875113</v>
       </c>
       <c r="N122" s="3" t="inlineStr"/>
       <c r="O122" s="8" t="n"/>
@@ -10186,13 +10186,13 @@
         </is>
       </c>
       <c r="D123" s="13" t="n">
-        <v>139.13</v>
+        <v>137.7</v>
       </c>
       <c r="E123" s="14" t="n">
-        <v>-0.1126</v>
+        <v>-0.1218</v>
       </c>
       <c r="F123" s="14" t="n">
-        <v>-0.0968</v>
+        <v>-0.1061</v>
       </c>
       <c r="G123" s="15" t="n">
         <v>46322</v>
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="D124" s="4" t="n">
-        <v>28.03</v>
+        <v>27.79</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0.0363</v>
+        <v>0.0274</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>0.1598</v>
+        <v>0.1498</v>
       </c>
       <c r="G124" s="6" t="n"/>
       <c r="H124" s="7" t="inlineStr">
@@ -10289,8 +10289,8 @@
       <c r="L124" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="M124" s="22" t="n">
-        <v>-0.001070281840884807</v>
+      <c r="M124" s="5" t="n">
+        <v>0.007556675062972323</v>
       </c>
       <c r="N124" s="3" t="inlineStr"/>
       <c r="O124" s="8" t="n"/>
@@ -10334,13 +10334,13 @@
         </is>
       </c>
       <c r="D125" s="13" t="n">
-        <v>281.52</v>
+        <v>276.43</v>
       </c>
       <c r="E125" s="14" t="n">
-        <v>-0.1859</v>
+        <v>-0.2006</v>
       </c>
       <c r="F125" s="14" t="n">
-        <v>-0.1464</v>
+        <v>-0.1618</v>
       </c>
       <c r="G125" s="15" t="n">
         <v>46324</v>
@@ -10369,7 +10369,7 @@
         <v>418</v>
       </c>
       <c r="M125" s="18" t="n">
-        <v>0.4847968172776358</v>
+        <v>0.5121368881814564</v>
       </c>
       <c r="N125" s="12" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>350</v>
       </c>
       <c r="P125" s="18" t="n">
-        <v>0.243250923557829</v>
+        <v>0.2661433274246645</v>
       </c>
       <c r="Q125" s="19" t="inlineStr">
         <is>
@@ -10425,13 +10425,13 @@
         </is>
       </c>
       <c r="D126" s="4" t="n">
-        <v>602.42</v>
+        <v>603.02</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>0.0046</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="F126" s="5" t="n">
-        <v>0.143</v>
+        <v>0.1441</v>
       </c>
       <c r="G126" s="6" t="n">
         <v>46323</v>
@@ -10460,7 +10460,7 @@
         <v>615</v>
       </c>
       <c r="M126" s="5" t="n">
-        <v>0.02088244082201793</v>
+        <v>0.01986667108885281</v>
       </c>
       <c r="N126" s="3" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>570</v>
       </c>
       <c r="P126" s="22" t="n">
-        <v>-0.05381627436008094</v>
+        <v>-0.05475771947862423</v>
       </c>
       <c r="Q126" s="9" t="inlineStr">
         <is>
@@ -10520,13 +10520,13 @@
         </is>
       </c>
       <c r="D127" s="13" t="n">
-        <v>392.95</v>
+        <v>400.84</v>
       </c>
       <c r="E127" s="14" t="n">
-        <v>-0.0386</v>
+        <v>-0.0193</v>
       </c>
       <c r="F127" s="14" t="n">
-        <v>-0.0746</v>
+        <v>-0.05599999999999999</v>
       </c>
       <c r="G127" s="15" t="n">
         <v>46322</v>
@@ -10555,7 +10555,7 @@
         <v>526</v>
       </c>
       <c r="M127" s="18" t="n">
-        <v>0.3385926962717903</v>
+        <v>0.3122442869973057</v>
       </c>
       <c r="N127" s="12" t="inlineStr">
         <is>
@@ -10566,7 +10566,7 @@
         <v>480</v>
       </c>
       <c r="P127" s="18" t="n">
-        <v>0.2215294566738771</v>
+        <v>0.1974852809100889</v>
       </c>
       <c r="Q127" s="19" t="inlineStr">
         <is>
@@ -10611,13 +10611,13 @@
         </is>
       </c>
       <c r="D128" s="4" t="n">
-        <v>74.84999999999999</v>
-      </c>
-      <c r="E128" s="5" t="n">
-        <v>0.0003</v>
+        <v>73.56</v>
+      </c>
+      <c r="E128" s="22" t="n">
+        <v>-0.017</v>
       </c>
       <c r="F128" s="22" t="n">
-        <v>-0.009399999999999999</v>
+        <v>-0.0265</v>
       </c>
       <c r="G128" s="6" t="n"/>
       <c r="H128" s="7" t="inlineStr">
@@ -10680,13 +10680,13 @@
         </is>
       </c>
       <c r="D129" s="13" t="n">
-        <v>270.4</v>
+        <v>267.96</v>
       </c>
       <c r="E129" s="14" t="n">
-        <v>-0.012</v>
+        <v>-0.0209</v>
       </c>
       <c r="F129" s="18" t="n">
-        <v>0.1177</v>
+        <v>0.1076</v>
       </c>
       <c r="G129" s="15" t="n"/>
       <c r="H129" s="21" t="inlineStr">
@@ -10705,7 +10705,7 @@
         <v>248</v>
       </c>
       <c r="M129" s="14" t="n">
-        <v>-0.08284023668639046</v>
+        <v>-0.07448872966114338</v>
       </c>
       <c r="N129" s="12" t="inlineStr"/>
       <c r="O129" s="17" t="n"/>
@@ -10761,13 +10761,13 @@
         </is>
       </c>
       <c r="D130" s="4" t="n">
-        <v>127.74</v>
+        <v>127.31</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>0.2664</v>
+        <v>0.2621</v>
       </c>
       <c r="F130" s="5" t="n">
-        <v>0.1174</v>
+        <v>0.1136</v>
       </c>
       <c r="G130" s="6" t="n">
         <v>46325</v>
@@ -10822,13 +10822,13 @@
         </is>
       </c>
       <c r="D131" s="13" t="n">
-        <v>237.73</v>
+        <v>237.76</v>
       </c>
       <c r="E131" s="14" t="n">
-        <v>-0.0599</v>
+        <v>-0.05980000000000001</v>
       </c>
       <c r="F131" s="18" t="n">
-        <v>0.016</v>
+        <v>0.0162</v>
       </c>
       <c r="G131" s="15" t="n">
         <v>46324</v>
@@ -10883,13 +10883,13 @@
         </is>
       </c>
       <c r="D132" s="4" t="n">
-        <v>213.79</v>
+        <v>210.73</v>
       </c>
       <c r="E132" s="22" t="n">
-        <v>-0.08160000000000001</v>
+        <v>-0.09480000000000001</v>
       </c>
       <c r="F132" s="22" t="n">
-        <v>-0.0382</v>
+        <v>-0.052</v>
       </c>
       <c r="G132" s="6" t="n"/>
       <c r="H132" s="7" t="inlineStr">
@@ -10908,7 +10908,7 @@
         <v>250</v>
       </c>
       <c r="M132" s="5" t="n">
-        <v>0.1693718134618084</v>
+        <v>0.1863522042423955</v>
       </c>
       <c r="N132" s="3" t="inlineStr"/>
       <c r="O132" s="8" t="n"/>
@@ -10952,13 +10952,13 @@
         </is>
       </c>
       <c r="D133" s="13" t="n">
-        <v>168.26</v>
+        <v>168.62</v>
       </c>
       <c r="E133" s="14" t="n">
-        <v>-0.0296</v>
+        <v>-0.0276</v>
       </c>
       <c r="F133" s="18" t="n">
-        <v>0.141</v>
+        <v>0.1434</v>
       </c>
       <c r="G133" s="15" t="n"/>
       <c r="H133" s="21" t="inlineStr">
@@ -11013,13 +11013,13 @@
         </is>
       </c>
       <c r="D134" s="4" t="n">
-        <v>821.58</v>
+        <v>822.48</v>
       </c>
       <c r="E134" s="22" t="n">
-        <v>-0.0191</v>
+        <v>-0.018</v>
       </c>
       <c r="F134" s="22" t="n">
-        <v>-0.1374</v>
+        <v>-0.1364</v>
       </c>
       <c r="G134" s="6" t="n"/>
       <c r="H134" s="7" t="inlineStr">
@@ -11038,7 +11038,7 @@
         <v>1155</v>
       </c>
       <c r="M134" s="5" t="n">
-        <v>0.4058277952238369</v>
+        <v>0.4042894660052524</v>
       </c>
       <c r="N134" s="3" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>1103</v>
       </c>
       <c r="P134" s="5" t="n">
-        <v>0.3425351152657075</v>
+        <v>0.3410660441591284</v>
       </c>
       <c r="Q134" s="9" t="inlineStr">
         <is>
@@ -11090,13 +11090,13 @@
         </is>
       </c>
       <c r="D135" s="13" t="n">
-        <v>561.21</v>
+        <v>561.55</v>
       </c>
       <c r="E135" s="14" t="n">
-        <v>-0.116</v>
+        <v>-0.1154</v>
       </c>
       <c r="F135" s="14" t="n">
-        <v>-0.1697</v>
+        <v>-0.1692</v>
       </c>
       <c r="G135" s="15" t="n"/>
       <c r="H135" s="21" t="inlineStr">
@@ -11115,7 +11115,7 @@
         <v>874</v>
       </c>
       <c r="M135" s="18" t="n">
-        <v>0.5573492988364426</v>
+        <v>0.5564063752114684</v>
       </c>
       <c r="N135" s="12" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>845</v>
       </c>
       <c r="P135" s="18" t="n">
-        <v>0.5056752374334027</v>
+        <v>0.5047636007479299</v>
       </c>
       <c r="Q135" s="19" t="inlineStr">
         <is>
@@ -11175,13 +11175,13 @@
         </is>
       </c>
       <c r="D136" s="4" t="n">
-        <v>200.4</v>
+        <v>200.5</v>
       </c>
       <c r="E136" s="22" t="n">
-        <v>-0.0114</v>
+        <v>-0.0109</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>0.1155</v>
+        <v>0.1161</v>
       </c>
       <c r="G136" s="6" t="n">
         <v>46288</v>
@@ -11210,7 +11210,7 @@
         <v>250</v>
       </c>
       <c r="M136" s="5" t="n">
-        <v>0.24750499001996</v>
+        <v>0.2468827930174564</v>
       </c>
       <c r="N136" s="3" t="inlineStr"/>
       <c r="O136" s="8" t="n"/>
@@ -11254,13 +11254,13 @@
         </is>
       </c>
       <c r="D137" s="13" t="n">
-        <v>682.77</v>
+        <v>680.73</v>
       </c>
       <c r="E137" s="18" t="n">
-        <v>0.1206</v>
+        <v>0.1173</v>
       </c>
       <c r="F137" s="18" t="n">
-        <v>0.1634</v>
+        <v>0.16</v>
       </c>
       <c r="G137" s="15" t="n"/>
       <c r="H137" s="21" t="inlineStr">
@@ -11279,7 +11279,7 @@
         <v>750</v>
       </c>
       <c r="M137" s="18" t="n">
-        <v>0.09846654070917003</v>
+        <v>0.1017584064166409</v>
       </c>
       <c r="N137" s="12" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>641.29</v>
       </c>
       <c r="P137" s="14" t="n">
-        <v>-0.06075252281148853</v>
+        <v>-0.05793780206542984</v>
       </c>
       <c r="Q137" s="19" t="inlineStr">
         <is>
@@ -11331,13 +11331,13 @@
         </is>
       </c>
       <c r="D138" s="4" t="n">
-        <v>152.09</v>
+        <v>152.15</v>
       </c>
       <c r="E138" s="22" t="n">
-        <v>-0.0417</v>
+        <v>-0.0413</v>
       </c>
       <c r="F138" s="5" t="n">
-        <v>0.0951</v>
+        <v>0.0956</v>
       </c>
       <c r="G138" s="6" t="n"/>
       <c r="H138" s="7" t="inlineStr">
@@ -11363,7 +11363,7 @@
         <v>185</v>
       </c>
       <c r="P138" s="5" t="n">
-        <v>0.2163850351765402</v>
+        <v>0.2159053565560302</v>
       </c>
       <c r="Q138" s="9" t="inlineStr">
         <is>
@@ -11402,13 +11402,13 @@
         </is>
       </c>
       <c r="D139" s="13" t="n">
-        <v>423.92</v>
+        <v>422.13</v>
       </c>
       <c r="E139" s="14" t="n">
-        <v>-0.0473</v>
+        <v>-0.0513</v>
       </c>
       <c r="F139" s="18" t="n">
-        <v>0.0409</v>
+        <v>0.0365</v>
       </c>
       <c r="G139" s="15" t="n"/>
       <c r="H139" s="21" t="inlineStr">
@@ -11434,7 +11434,7 @@
         <v>453</v>
       </c>
       <c r="P139" s="18" t="n">
-        <v>0.06859784865068877</v>
+        <v>0.07312913083647218</v>
       </c>
       <c r="Q139" s="19" t="inlineStr">
         <is>
@@ -11475,13 +11475,13 @@
         </is>
       </c>
       <c r="D140" s="4" t="n">
-        <v>49.35</v>
+        <v>49.38</v>
       </c>
       <c r="E140" s="22" t="n">
-        <v>-0.0537</v>
+        <v>-0.05309999999999999</v>
       </c>
       <c r="F140" s="5" t="n">
-        <v>0.06150000000000001</v>
+        <v>0.0622</v>
       </c>
       <c r="G140" s="6" t="n">
         <v>46309</v>
@@ -11554,13 +11554,13 @@
         </is>
       </c>
       <c r="D141" s="13" t="n">
-        <v>317.05</v>
+        <v>314.13</v>
       </c>
       <c r="E141" s="14" t="n">
-        <v>-0.0247</v>
-      </c>
-      <c r="F141" s="18" t="n">
-        <v>0.0075</v>
+        <v>-0.0337</v>
+      </c>
+      <c r="F141" s="14" t="n">
+        <v>-0.0018</v>
       </c>
       <c r="G141" s="15" t="n">
         <v>46282</v>
@@ -11589,7 +11589,7 @@
         <v>425</v>
       </c>
       <c r="M141" s="18" t="n">
-        <v>0.3404825737265415</v>
+        <v>0.3529430490561233</v>
       </c>
       <c r="N141" s="12" t="inlineStr">
         <is>
@@ -11600,7 +11600,7 @@
         <v>323</v>
       </c>
       <c r="P141" s="18" t="n">
-        <v>0.01876675603217155</v>
+        <v>0.02823671728265369</v>
       </c>
       <c r="Q141" s="19" t="inlineStr">
         <is>
@@ -11641,13 +11641,13 @@
         </is>
       </c>
       <c r="D142" s="4" t="n">
-        <v>229.68</v>
+        <v>226.3</v>
       </c>
       <c r="E142" s="22" t="n">
-        <v>-0.1293</v>
-      </c>
-      <c r="F142" s="5" t="n">
-        <v>0.0098</v>
+        <v>-0.1421</v>
+      </c>
+      <c r="F142" s="22" t="n">
+        <v>-0.0051</v>
       </c>
       <c r="G142" s="6" t="n"/>
       <c r="H142" s="7" t="inlineStr">
@@ -11666,7 +11666,7 @@
         <v>285</v>
       </c>
       <c r="M142" s="5" t="n">
-        <v>0.2408568443051201</v>
+        <v>0.2593901900132567</v>
       </c>
       <c r="N142" s="3" t="inlineStr"/>
       <c r="O142" s="8" t="n"/>
@@ -11714,13 +11714,13 @@
         </is>
       </c>
       <c r="D143" s="13" t="n">
-        <v>1631.87</v>
+        <v>1648.47</v>
       </c>
       <c r="E143" s="14" t="n">
-        <v>-0.0257</v>
+        <v>-0.0157</v>
       </c>
       <c r="F143" s="14" t="n">
-        <v>-0.0707</v>
+        <v>-0.0613</v>
       </c>
       <c r="G143" s="15" t="n">
         <v>46317</v>
@@ -11775,13 +11775,13 @@
         </is>
       </c>
       <c r="D144" s="4" t="n">
-        <v>56.56</v>
+        <v>56.62</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>0.0825</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="F144" s="5" t="n">
-        <v>0.1147</v>
+        <v>0.1159</v>
       </c>
       <c r="G144" s="6" t="n"/>
       <c r="H144" s="7" t="inlineStr">
@@ -11826,13 +11826,13 @@
         </is>
       </c>
       <c r="D145" s="13" t="n">
-        <v>356.86</v>
+        <v>356.58</v>
       </c>
       <c r="E145" s="14" t="n">
-        <v>-0.09880000000000001</v>
+        <v>-0.09949999999999999</v>
       </c>
       <c r="F145" s="14" t="n">
-        <v>-0.04849999999999999</v>
+        <v>-0.0493</v>
       </c>
       <c r="G145" s="15" t="n">
         <v>46318</v>
@@ -11861,7 +11861,7 @@
         <v>400</v>
       </c>
       <c r="M145" s="18" t="n">
-        <v>0.1208877430925292</v>
+        <v>0.1217679062202031</v>
       </c>
       <c r="N145" s="12" t="inlineStr"/>
       <c r="O145" s="17" t="n"/>
@@ -11913,13 +11913,13 @@
         </is>
       </c>
       <c r="D146" s="4" t="n">
-        <v>339.22</v>
+        <v>334.91</v>
       </c>
       <c r="E146" s="22" t="n">
-        <v>-0.07490000000000001</v>
+        <v>-0.0867</v>
       </c>
       <c r="F146" s="22" t="n">
-        <v>-0.0558</v>
+        <v>-0.0678</v>
       </c>
       <c r="G146" s="6" t="n">
         <v>46315</v>
@@ -11948,7 +11948,7 @@
         <v>390</v>
       </c>
       <c r="M146" s="5" t="n">
-        <v>0.1496963622427922</v>
+        <v>0.1644919530620166</v>
       </c>
       <c r="N146" s="3" t="inlineStr"/>
       <c r="O146" s="8" t="n"/>
@@ -12000,13 +12000,13 @@
         </is>
       </c>
       <c r="D147" s="13" t="n">
-        <v>963.95</v>
+        <v>971.3099999999999</v>
       </c>
       <c r="E147" s="14" t="n">
-        <v>-0.0272</v>
+        <v>-0.0197</v>
       </c>
       <c r="F147" s="14" t="n">
-        <v>-0.1169</v>
+        <v>-0.1102</v>
       </c>
       <c r="G147" s="15" t="n">
         <v>46316</v>
@@ -12035,7 +12035,7 @@
         <v>1259</v>
       </c>
       <c r="M147" s="18" t="n">
-        <v>0.3060843404740909</v>
+        <v>0.2961876229010306</v>
       </c>
       <c r="N147" s="12" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>1350</v>
       </c>
       <c r="P147" s="18" t="n">
-        <v>0.4004875771564915</v>
+        <v>0.3898755289248542</v>
       </c>
       <c r="Q147" s="19" t="inlineStr">
         <is>
@@ -12091,13 +12091,13 @@
         </is>
       </c>
       <c r="D148" s="4" t="n">
-        <v>1276.38</v>
+        <v>1289.17</v>
       </c>
       <c r="E148" s="22" t="n">
-        <v>-0.0162</v>
+        <v>-0.0064</v>
       </c>
       <c r="F148" s="22" t="n">
-        <v>-0.0722</v>
+        <v>-0.0629</v>
       </c>
       <c r="G148" s="6" t="n">
         <v>46325</v>
@@ -12166,13 +12166,13 @@
         </is>
       </c>
       <c r="D149" s="13" t="n">
-        <v>207.75</v>
+        <v>208.24</v>
       </c>
       <c r="E149" s="14" t="n">
-        <v>-0.1448</v>
+        <v>-0.1428</v>
       </c>
       <c r="F149" s="14" t="n">
-        <v>-0.0825</v>
+        <v>-0.0803</v>
       </c>
       <c r="G149" s="15" t="n">
         <v>46317</v>
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="D150" s="4" t="n">
-        <v>461.18</v>
+        <v>464.75</v>
       </c>
       <c r="E150" s="22" t="n">
-        <v>-0.0866</v>
+        <v>-0.0795</v>
       </c>
       <c r="F150" s="22" t="n">
-        <v>-0.06059999999999999</v>
+        <v>-0.0533</v>
       </c>
       <c r="G150" s="6" t="n">
         <v>46322</v>
@@ -12294,13 +12294,13 @@
         </is>
       </c>
       <c r="D151" s="13" t="n">
-        <v>267.37</v>
+        <v>268.69</v>
       </c>
       <c r="E151" s="14" t="n">
-        <v>-0.0922</v>
+        <v>-0.0877</v>
       </c>
       <c r="F151" s="14" t="n">
-        <v>-0.0054</v>
+        <v>-0.0004</v>
       </c>
       <c r="G151" s="15" t="n">
         <v>46318</v>
@@ -12332,7 +12332,7 @@
         <v>272</v>
       </c>
       <c r="P151" s="18" t="n">
-        <v>0.01731682686913264</v>
+        <v>0.01231902936469538</v>
       </c>
       <c r="Q151" s="19" t="inlineStr">
         <is>
@@ -12385,13 +12385,13 @@
         </is>
       </c>
       <c r="D152" s="4" t="n">
-        <v>255.78</v>
+        <v>255.74</v>
       </c>
       <c r="E152" s="22" t="n">
-        <v>-0.1171</v>
+        <v>-0.1173</v>
       </c>
       <c r="F152" s="22" t="n">
-        <v>-0.1203</v>
+        <v>-0.1205</v>
       </c>
       <c r="G152" s="6" t="n">
         <v>46324</v>
@@ -12456,13 +12456,13 @@
         </is>
       </c>
       <c r="D153" s="13" t="n">
-        <v>386.23</v>
+        <v>385.18</v>
       </c>
       <c r="E153" s="14" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-0.09</v>
       </c>
       <c r="F153" s="14" t="n">
-        <v>-0.3003</v>
+        <v>-0.3022</v>
       </c>
       <c r="G153" s="15" t="n">
         <v>46323</v>
@@ -12517,13 +12517,13 @@
         </is>
       </c>
       <c r="D154" s="4" t="n">
-        <v>540.5700000000001</v>
+        <v>536.15</v>
       </c>
       <c r="E154" s="22" t="n">
-        <v>-0.1038</v>
+        <v>-0.1111</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>0.0332</v>
+        <v>0.0247</v>
       </c>
       <c r="G154" s="6" t="n">
         <v>46315</v>
@@ -12584,13 +12584,13 @@
         </is>
       </c>
       <c r="D155" s="13" t="n">
-        <v>187.48</v>
+        <v>187.01</v>
       </c>
       <c r="E155" s="14" t="n">
-        <v>-0.1179</v>
+        <v>-0.1202</v>
       </c>
       <c r="F155" s="14" t="n">
-        <v>-0.1764</v>
+        <v>-0.1784</v>
       </c>
       <c r="G155" s="15" t="n"/>
       <c r="H155" s="21" t="inlineStr">
@@ -12609,7 +12609,7 @@
         <v>575</v>
       </c>
       <c r="M155" s="18" t="n">
-        <v>2.066993812673352</v>
+        <v>2.074701887599594</v>
       </c>
       <c r="N155" s="12" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>237</v>
       </c>
       <c r="P155" s="18" t="n">
-        <v>0.264134841049712</v>
+        <v>0.2673119084540934</v>
       </c>
       <c r="Q155" s="19" t="inlineStr">
         <is>
@@ -12669,13 +12669,13 @@
         </is>
       </c>
       <c r="D156" s="4" t="n">
-        <v>117.82</v>
+        <v>116.93</v>
       </c>
       <c r="E156" s="22" t="n">
-        <v>-0.0277</v>
+        <v>-0.0351</v>
       </c>
       <c r="F156" s="5" t="n">
-        <v>0.0956</v>
+        <v>0.0873</v>
       </c>
       <c r="G156" s="6" t="n">
         <v>46294</v>
@@ -12704,7 +12704,7 @@
         <v>250</v>
       </c>
       <c r="M156" s="5" t="n">
-        <v>1.121880835172297</v>
+        <v>1.138031300778243</v>
       </c>
       <c r="N156" s="3" t="inlineStr"/>
       <c r="O156" s="8" t="n"/>
@@ -12748,13 +12748,13 @@
         </is>
       </c>
       <c r="D157" s="13" t="n">
-        <v>122.74</v>
+        <v>122.5</v>
       </c>
       <c r="E157" s="14" t="n">
-        <v>-0.06480000000000001</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="F157" s="14" t="n">
-        <v>-0.0147</v>
+        <v>-0.0166</v>
       </c>
       <c r="G157" s="15" t="n">
         <v>46315</v>
@@ -12783,7 +12783,7 @@
         <v>95</v>
       </c>
       <c r="M157" s="14" t="n">
-        <v>-0.2260061919504644</v>
+        <v>-0.2244897959183673</v>
       </c>
       <c r="N157" s="12" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>139</v>
       </c>
       <c r="P157" s="18" t="n">
-        <v>0.13247515072511</v>
+        <v>0.1346938775510204</v>
       </c>
       <c r="Q157" s="19" t="inlineStr">
         <is>
@@ -12839,13 +12839,13 @@
         </is>
       </c>
       <c r="D158" s="4" t="n">
-        <v>957.77</v>
+        <v>955.87</v>
       </c>
       <c r="E158" s="22" t="n">
-        <v>-0.0969</v>
+        <v>-0.0987</v>
       </c>
       <c r="F158" s="22" t="n">
-        <v>-0.0036</v>
+        <v>-0.005600000000000001</v>
       </c>
       <c r="G158" s="6" t="n"/>
       <c r="H158" s="7" t="inlineStr">
@@ -12864,7 +12864,7 @@
         <v>125</v>
       </c>
       <c r="M158" s="22" t="n">
-        <v>-0.8694884993265607</v>
+        <v>-0.8692290792681013</v>
       </c>
       <c r="N158" s="3" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>1064</v>
       </c>
       <c r="P158" s="5" t="n">
-        <v>0.1109138937323157</v>
+        <v>0.1131220772699216</v>
       </c>
       <c r="Q158" s="9" t="inlineStr">
         <is>
@@ -12920,13 +12920,13 @@
         </is>
       </c>
       <c r="D159" s="13" t="n">
-        <v>488.92</v>
+        <v>492.23</v>
       </c>
       <c r="E159" s="14" t="n">
-        <v>-0.1214</v>
+        <v>-0.1155</v>
       </c>
       <c r="F159" s="14" t="n">
-        <v>-0.179</v>
+        <v>-0.1734</v>
       </c>
       <c r="G159" s="15" t="n">
         <v>46325</v>
@@ -13001,10 +13001,10 @@
         </is>
       </c>
       <c r="D160" s="4" t="n">
-        <v>429.09</v>
+        <v>429.13</v>
       </c>
       <c r="E160" s="22" t="n">
-        <v>-0.0141</v>
+        <v>-0.014</v>
       </c>
       <c r="F160" s="22" t="n">
         <v>-0.0911</v>
@@ -13052,13 +13052,13 @@
         </is>
       </c>
       <c r="D161" s="13" t="n">
-        <v>35.34</v>
+        <v>34.95</v>
       </c>
       <c r="E161" s="14" t="n">
-        <v>-0.0508</v>
+        <v>-0.0612</v>
       </c>
       <c r="F161" s="14" t="n">
-        <v>-0.2053</v>
+        <v>-0.2141</v>
       </c>
       <c r="G161" s="15" t="n">
         <v>46323</v>
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="D162" s="4" t="n">
-        <v>199.2</v>
+        <v>198.81</v>
       </c>
       <c r="E162" s="22" t="n">
-        <v>-0.1112</v>
+        <v>-0.1129</v>
       </c>
       <c r="F162" s="5" t="n">
-        <v>0.0167</v>
+        <v>0.0147</v>
       </c>
       <c r="G162" s="6" t="n">
         <v>46315</v>
@@ -13206,13 +13206,13 @@
         </is>
       </c>
       <c r="D163" s="13" t="n">
-        <v>43.22</v>
+        <v>43.3</v>
       </c>
       <c r="E163" s="18" t="n">
-        <v>0.0774</v>
+        <v>0.0795</v>
       </c>
       <c r="F163" s="14" t="n">
-        <v>-0.0097</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="G163" s="15" t="n"/>
       <c r="H163" s="21" t="inlineStr">
@@ -13257,13 +13257,13 @@
         </is>
       </c>
       <c r="D164" s="4" t="n">
-        <v>446.67</v>
+        <v>446</v>
       </c>
       <c r="E164" s="22" t="n">
-        <v>-0.0636</v>
+        <v>-0.065</v>
       </c>
       <c r="F164" s="22" t="n">
-        <v>-0.0689</v>
+        <v>-0.0703</v>
       </c>
       <c r="G164" s="6" t="n">
         <v>46324</v>
@@ -13295,7 +13295,7 @@
         <v>560</v>
       </c>
       <c r="P164" s="5" t="n">
-        <v>0.2537219871493496</v>
+        <v>0.2556053811659193</v>
       </c>
       <c r="Q164" s="9" t="inlineStr">
         <is>
@@ -13348,13 +13348,13 @@
         </is>
       </c>
       <c r="D165" s="13" t="n">
-        <v>289.96</v>
+        <v>288.45</v>
       </c>
       <c r="E165" s="14" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.013</v>
       </c>
       <c r="F165" s="18" t="n">
-        <v>0.0105</v>
+        <v>0.0052</v>
       </c>
       <c r="G165" s="15" t="n">
         <v>46317</v>
@@ -13386,7 +13386,7 @@
         <v>294</v>
       </c>
       <c r="P165" s="18" t="n">
-        <v>0.01393295626983039</v>
+        <v>0.01924076963078527</v>
       </c>
       <c r="Q165" s="19" t="inlineStr">
         <is>
@@ -13431,13 +13431,13 @@
         </is>
       </c>
       <c r="D166" s="4" t="n">
-        <v>288.64</v>
+        <v>290.83</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>0.06860000000000001</v>
+        <v>0.0767</v>
       </c>
       <c r="F166" s="22" t="n">
-        <v>-0.09480000000000001</v>
+        <v>-0.08789999999999999</v>
       </c>
       <c r="G166" s="6" t="n">
         <v>46323</v>
@@ -13469,7 +13469,7 @@
         <v>425</v>
       </c>
       <c r="P166" s="5" t="n">
-        <v>0.4724223946784923</v>
+        <v>0.4613348003988585</v>
       </c>
       <c r="Q166" s="9" t="inlineStr">
         <is>
@@ -13510,13 +13510,13 @@
         </is>
       </c>
       <c r="D167" s="13" t="n">
-        <v>218.21</v>
+        <v>217.78</v>
       </c>
       <c r="E167" s="14" t="n">
-        <v>-0.03700000000000001</v>
+        <v>-0.0389</v>
       </c>
       <c r="F167" s="14" t="n">
-        <v>-0.06480000000000001</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="G167" s="15" t="n">
         <v>46321</v>
@@ -13545,7 +13545,7 @@
         <v>268</v>
       </c>
       <c r="M167" s="18" t="n">
-        <v>0.2281746941020118</v>
+        <v>0.2305996877582882</v>
       </c>
       <c r="N167" s="12" t="inlineStr"/>
       <c r="O167" s="17" t="n"/>
@@ -13593,13 +13593,13 @@
         </is>
       </c>
       <c r="D168" s="4" t="n">
-        <v>316.86</v>
+        <v>316.02</v>
       </c>
       <c r="E168" s="22" t="n">
-        <v>-0.0301</v>
+        <v>-0.0327</v>
       </c>
       <c r="F168" s="22" t="n">
-        <v>-0.1745</v>
+        <v>-0.1767</v>
       </c>
       <c r="G168" s="6" t="n"/>
       <c r="H168" s="7" t="inlineStr">
@@ -13658,13 +13658,13 @@
         </is>
       </c>
       <c r="D169" s="13" t="n">
-        <v>344.14</v>
+        <v>339.27</v>
       </c>
       <c r="E169" s="14" t="n">
-        <v>-0.0336</v>
+        <v>-0.0473</v>
       </c>
       <c r="F169" s="14" t="n">
-        <v>-0.1532</v>
+        <v>-0.1652</v>
       </c>
       <c r="G169" s="15" t="n"/>
       <c r="H169" s="21" t="inlineStr">
@@ -13727,13 +13727,13 @@
         </is>
       </c>
       <c r="D170" s="4" t="n">
-        <v>109.28</v>
+        <v>108.81</v>
       </c>
       <c r="E170" s="22" t="n">
-        <v>-0.0983</v>
+        <v>-0.1022</v>
       </c>
       <c r="F170" s="22" t="n">
-        <v>-0.09849999999999999</v>
+        <v>-0.1024</v>
       </c>
       <c r="G170" s="6" t="n">
         <v>46322</v>
@@ -13806,13 +13806,13 @@
         </is>
       </c>
       <c r="D171" s="13" t="n">
-        <v>115.52</v>
+        <v>111.55</v>
       </c>
       <c r="E171" s="14" t="n">
-        <v>-0.1302</v>
+        <v>-0.1601</v>
       </c>
       <c r="F171" s="14" t="n">
-        <v>-0.0367</v>
+        <v>-0.0698</v>
       </c>
       <c r="G171" s="15" t="n"/>
       <c r="H171" s="21" t="inlineStr">
@@ -13857,13 +13857,13 @@
         </is>
       </c>
       <c r="D172" s="4" t="n">
-        <v>316.02</v>
+        <v>316.22</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>0.0252</v>
+        <v>0.0258</v>
       </c>
       <c r="F172" s="5" t="n">
-        <v>0.0022</v>
+        <v>0.0029</v>
       </c>
       <c r="G172" s="6" t="n">
         <v>46324</v>
@@ -13892,7 +13892,7 @@
         <v>310</v>
       </c>
       <c r="M172" s="22" t="n">
-        <v>-0.01904942725143973</v>
+        <v>-0.01966985010435781</v>
       </c>
       <c r="N172" s="3" t="inlineStr">
         <is>
@@ -13903,7 +13903,7 @@
         <v>365</v>
       </c>
       <c r="P172" s="5" t="n">
-        <v>0.1549901904942726</v>
+        <v>0.1542596926190626</v>
       </c>
       <c r="Q172" s="9" t="inlineStr">
         <is>
@@ -13960,13 +13960,13 @@
         </is>
       </c>
       <c r="D173" s="13" t="n">
-        <v>117.84</v>
+        <v>119.17</v>
       </c>
       <c r="E173" s="14" t="n">
-        <v>-0.1116</v>
+        <v>-0.1016</v>
       </c>
       <c r="F173" s="14" t="n">
-        <v>-0.178</v>
+        <v>-0.1687</v>
       </c>
       <c r="G173" s="15" t="n"/>
       <c r="H173" s="21" t="inlineStr">
@@ -14011,13 +14011,13 @@
         </is>
       </c>
       <c r="D174" s="4" t="n">
-        <v>179.28</v>
+        <v>179.03</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>0.0058</v>
+        <v>0.0044</v>
       </c>
       <c r="F174" s="5" t="n">
-        <v>0.3257</v>
+        <v>0.3239</v>
       </c>
       <c r="G174" s="6" t="n">
         <v>46296</v>
@@ -14072,13 +14072,13 @@
         </is>
       </c>
       <c r="D175" s="13" t="n">
-        <v>257.01</v>
+        <v>257.26</v>
       </c>
       <c r="E175" s="14" t="n">
-        <v>-0.0584</v>
+        <v>-0.0575</v>
       </c>
       <c r="F175" s="18" t="n">
-        <v>0.1492</v>
+        <v>0.1503</v>
       </c>
       <c r="G175" s="15" t="n">
         <v>46275</v>
@@ -14133,13 +14133,13 @@
         </is>
       </c>
       <c r="D176" s="4" t="n">
-        <v>364.45</v>
+        <v>363.2</v>
       </c>
       <c r="E176" s="22" t="n">
-        <v>-0.0507</v>
+        <v>-0.05400000000000001</v>
       </c>
       <c r="F176" s="22" t="n">
-        <v>-0.0789</v>
+        <v>-0.08199999999999999</v>
       </c>
       <c r="G176" s="6" t="n"/>
       <c r="H176" s="7" t="inlineStr">
@@ -14158,7 +14158,7 @@
         <v>515</v>
       </c>
       <c r="M176" s="5" t="n">
-        <v>0.413088215118672</v>
+        <v>0.4179515418502203</v>
       </c>
       <c r="N176" s="3" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>474</v>
       </c>
       <c r="P176" s="5" t="n">
-        <v>0.3005899300315544</v>
+        <v>0.3050660792951542</v>
       </c>
       <c r="Q176" s="9" t="inlineStr">
         <is>
@@ -14218,13 +14218,13 @@
         </is>
       </c>
       <c r="D177" s="13" t="n">
-        <v>212.1</v>
+        <v>212.21</v>
       </c>
       <c r="E177" s="14" t="n">
-        <v>-0.1717</v>
+        <v>-0.1713</v>
       </c>
       <c r="F177" s="18" t="n">
-        <v>0.0175</v>
+        <v>0.018</v>
       </c>
       <c r="G177" s="15" t="n"/>
       <c r="H177" s="21" t="inlineStr">
@@ -14269,13 +14269,13 @@
         </is>
       </c>
       <c r="D178" s="4" t="n">
-        <v>291.27</v>
+        <v>288.72</v>
       </c>
       <c r="E178" s="22" t="n">
-        <v>-0.0738</v>
+        <v>-0.0819</v>
       </c>
       <c r="F178" s="22" t="n">
-        <v>-0.0545</v>
+        <v>-0.06269999999999999</v>
       </c>
       <c r="G178" s="6" t="n"/>
       <c r="H178" s="7" t="inlineStr">
@@ -14320,13 +14320,13 @@
         </is>
       </c>
       <c r="D179" s="13" t="n">
-        <v>300.57</v>
+        <v>288.85</v>
       </c>
       <c r="E179" s="14" t="n">
-        <v>-0.0525</v>
+        <v>-0.0895</v>
       </c>
       <c r="F179" s="14" t="n">
-        <v>-0.2722</v>
+        <v>-0.3006</v>
       </c>
       <c r="G179" s="15" t="n"/>
       <c r="H179" s="21" t="inlineStr">
@@ -14371,13 +14371,13 @@
         </is>
       </c>
       <c r="D180" s="4" t="n">
-        <v>36.66</v>
+        <v>36.47</v>
       </c>
       <c r="E180" s="22" t="n">
-        <v>-0.1366</v>
+        <v>-0.1411</v>
       </c>
       <c r="F180" s="22" t="n">
-        <v>-0.3319</v>
+        <v>-0.3353</v>
       </c>
       <c r="G180" s="6" t="n">
         <v>46324</v>
@@ -14432,13 +14432,13 @@
         </is>
       </c>
       <c r="D181" s="13" t="n">
-        <v>466.5</v>
+        <v>472.79</v>
       </c>
       <c r="E181" s="14" t="n">
-        <v>-0.1065</v>
+        <v>-0.09449999999999999</v>
       </c>
       <c r="F181" s="14" t="n">
-        <v>-0.2257</v>
+        <v>-0.2153</v>
       </c>
       <c r="G181" s="15" t="n"/>
       <c r="H181" s="21" t="inlineStr">
@@ -14457,7 +14457,7 @@
         <v>740</v>
       </c>
       <c r="M181" s="18" t="n">
-        <v>0.5862808145766345</v>
+        <v>0.5651769284460331</v>
       </c>
       <c r="N181" s="12" t="inlineStr">
         <is>
@@ -14468,7 +14468,7 @@
         <v>700</v>
       </c>
       <c r="P181" s="18" t="n">
-        <v>0.5005359056806002</v>
+        <v>0.4805727701516529</v>
       </c>
       <c r="Q181" s="19" t="inlineStr">
         <is>
@@ -14509,13 +14509,13 @@
         </is>
       </c>
       <c r="D182" s="4" t="n">
-        <v>58.96</v>
+        <v>59.62</v>
       </c>
       <c r="E182" s="22" t="n">
-        <v>-0.0776</v>
+        <v>-0.0673</v>
       </c>
       <c r="F182" s="22" t="n">
-        <v>-0.3086</v>
+        <v>-0.3009</v>
       </c>
       <c r="G182" s="6" t="n"/>
       <c r="H182" s="7" t="inlineStr">
@@ -14564,13 +14564,13 @@
         </is>
       </c>
       <c r="D183" s="13" t="n">
-        <v>497.67</v>
+        <v>505.74</v>
       </c>
       <c r="E183" s="18" t="n">
-        <v>0.0599</v>
+        <v>0.0771</v>
       </c>
       <c r="F183" s="14" t="n">
-        <v>-0.1079</v>
+        <v>-0.0935</v>
       </c>
       <c r="G183" s="15" t="n"/>
       <c r="H183" s="21" t="inlineStr">
@@ -14589,7 +14589,7 @@
         <v>615</v>
       </c>
       <c r="M183" s="18" t="n">
-        <v>0.2357586352402194</v>
+        <v>0.216039862379879</v>
       </c>
       <c r="N183" s="12" t="inlineStr">
         <is>
@@ -14600,7 +14600,7 @@
         <v>579</v>
       </c>
       <c r="P183" s="18" t="n">
-        <v>0.1634215443968895</v>
+        <v>0.1448570411673983</v>
       </c>
       <c r="Q183" s="19" t="inlineStr">
         <is>
@@ -14641,13 +14641,13 @@
         </is>
       </c>
       <c r="D184" s="4" t="n">
-        <v>50.49</v>
+        <v>50.72</v>
       </c>
       <c r="E184" s="22" t="n">
-        <v>-0.0451</v>
+        <v>-0.0407</v>
       </c>
       <c r="F184" s="22" t="n">
-        <v>-0.2836</v>
+        <v>-0.2803</v>
       </c>
       <c r="G184" s="6" t="n">
         <v>46321</v>
@@ -14702,13 +14702,13 @@
         </is>
       </c>
       <c r="D185" s="13" t="n">
-        <v>197.24</v>
+        <v>194.96</v>
       </c>
       <c r="E185" s="18" t="n">
-        <v>0.0298</v>
+        <v>0.018</v>
       </c>
       <c r="F185" s="18" t="n">
-        <v>0.055</v>
+        <v>0.0428</v>
       </c>
       <c r="G185" s="15" t="n"/>
       <c r="H185" s="21" t="inlineStr">
@@ -14727,7 +14727,7 @@
         <v>200</v>
       </c>
       <c r="M185" s="18" t="n">
-        <v>0.01399310484688699</v>
+        <v>0.02585145670906849</v>
       </c>
       <c r="N185" s="12" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>200</v>
       </c>
       <c r="P185" s="18" t="n">
-        <v>0.01399310484688699</v>
+        <v>0.02585145670906849</v>
       </c>
       <c r="Q185" s="19" t="inlineStr">
         <is>
@@ -14783,13 +14783,13 @@
         </is>
       </c>
       <c r="D186" s="4" t="n">
-        <v>83.12</v>
+        <v>81.76000000000001</v>
       </c>
       <c r="E186" s="22" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-0.0249</v>
       </c>
       <c r="F186" s="5" t="n">
-        <v>0.0451</v>
+        <v>0.028</v>
       </c>
       <c r="G186" s="6" t="n">
         <v>46323</v>
@@ -14821,7 +14821,7 @@
         <v>180</v>
       </c>
       <c r="P186" s="5" t="n">
-        <v>1.165543792107796</v>
+        <v>1.201565557729941</v>
       </c>
       <c r="Q186" s="9" t="inlineStr">
         <is>
@@ -14874,13 +14874,13 @@
         </is>
       </c>
       <c r="D187" s="13" t="n">
-        <v>28.05</v>
+        <v>28.31</v>
       </c>
       <c r="E187" s="14" t="n">
-        <v>-0.0348</v>
+        <v>-0.0258</v>
       </c>
       <c r="F187" s="14" t="n">
-        <v>-0.09949999999999999</v>
+        <v>-0.09119999999999999</v>
       </c>
       <c r="G187" s="15" t="n">
         <v>46303</v>
@@ -14935,13 +14935,13 @@
         </is>
       </c>
       <c r="D188" s="4" t="n">
-        <v>256.27</v>
+        <v>261.53</v>
       </c>
       <c r="E188" s="22" t="n">
-        <v>-0.0432</v>
+        <v>-0.0236</v>
       </c>
       <c r="F188" s="22" t="n">
-        <v>-0.2076</v>
+        <v>-0.1913</v>
       </c>
       <c r="G188" s="6" t="n"/>
       <c r="H188" s="7" t="inlineStr">
@@ -14986,13 +14986,13 @@
         </is>
       </c>
       <c r="D189" s="13" t="n">
-        <v>1756.72</v>
+        <v>1764.85</v>
       </c>
       <c r="E189" s="18" t="n">
-        <v>0.0134</v>
+        <v>0.0181</v>
       </c>
       <c r="F189" s="14" t="n">
-        <v>-0.0226</v>
+        <v>-0.0181</v>
       </c>
       <c r="G189" s="15" t="n">
         <v>46309</v>
@@ -15065,13 +15065,13 @@
         </is>
       </c>
       <c r="D190" s="4" t="n">
-        <v>39.88</v>
+        <v>39.79</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>0.0611</v>
+        <v>0.0585</v>
       </c>
       <c r="F190" s="22" t="n">
-        <v>-0.065</v>
+        <v>-0.0673</v>
       </c>
       <c r="G190" s="6" t="n">
         <v>46324</v>
@@ -15126,13 +15126,13 @@
         </is>
       </c>
       <c r="D191" s="13" t="n">
-        <v>367.99</v>
+        <v>368.56</v>
       </c>
       <c r="E191" s="14" t="n">
-        <v>-0.1288</v>
+        <v>-0.1275</v>
       </c>
       <c r="F191" s="14" t="n">
-        <v>-0.08</v>
+        <v>-0.0785</v>
       </c>
       <c r="G191" s="15" t="n"/>
       <c r="H191" s="21" t="inlineStr">
@@ -15151,7 +15151,7 @@
         <v>545</v>
       </c>
       <c r="M191" s="18" t="n">
-        <v>0.4810185059376613</v>
+        <v>0.4787280225743434</v>
       </c>
       <c r="N191" s="12" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>582</v>
       </c>
       <c r="P191" s="18" t="n">
-        <v>0.5815647164325117</v>
+        <v>0.5791187323637942</v>
       </c>
       <c r="Q191" s="19" t="inlineStr">
         <is>
@@ -15215,13 +15215,13 @@
         </is>
       </c>
       <c r="D192" s="4" t="n">
-        <v>148.71</v>
+        <v>147.01</v>
       </c>
       <c r="E192" s="22" t="n">
-        <v>-0.0594</v>
+        <v>-0.0701</v>
       </c>
       <c r="F192" s="5" t="n">
-        <v>0.0343</v>
+        <v>0.0224</v>
       </c>
       <c r="G192" s="6" t="n"/>
       <c r="H192" s="7" t="inlineStr">
@@ -15266,13 +15266,13 @@
         </is>
       </c>
       <c r="D193" s="13" t="n">
-        <v>291.02</v>
+        <v>284.11</v>
       </c>
       <c r="E193" s="14" t="n">
-        <v>-0.1232</v>
+        <v>-0.144</v>
       </c>
       <c r="F193" s="14" t="n">
-        <v>-0.2425</v>
+        <v>-0.2605</v>
       </c>
       <c r="G193" s="15" t="n">
         <v>46321</v>
@@ -15301,7 +15301,7 @@
         <v>425</v>
       </c>
       <c r="M193" s="18" t="n">
-        <v>0.460380729846746</v>
+        <v>0.4958994755552426</v>
       </c>
       <c r="N193" s="12" t="inlineStr"/>
       <c r="O193" s="17" t="n"/>
@@ -15345,13 +15345,13 @@
         </is>
       </c>
       <c r="D194" s="4" t="n">
-        <v>132.72</v>
+        <v>132.9</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>0.012</v>
+        <v>0.0134</v>
       </c>
       <c r="F194" s="5" t="n">
-        <v>0.0077</v>
+        <v>0.0091</v>
       </c>
       <c r="G194" s="6" t="n">
         <v>46322</v>
@@ -15406,13 +15406,13 @@
         </is>
       </c>
       <c r="D195" s="13" t="n">
-        <v>338.81</v>
+        <v>341.29</v>
       </c>
       <c r="E195" s="14" t="n">
-        <v>-0.1261</v>
+        <v>-0.1197</v>
       </c>
       <c r="F195" s="14" t="n">
-        <v>-0.2646</v>
+        <v>-0.2592</v>
       </c>
       <c r="G195" s="15" t="n"/>
       <c r="H195" s="21" t="inlineStr">
@@ -15457,13 +15457,13 @@
         </is>
       </c>
       <c r="D196" s="4" t="n">
-        <v>11.48</v>
+        <v>11.45</v>
       </c>
       <c r="E196" s="22" t="n">
-        <v>-0.278</v>
+        <v>-0.2799</v>
       </c>
       <c r="F196" s="22" t="n">
-        <v>-0.2798</v>
+        <v>-0.2817</v>
       </c>
       <c r="G196" s="6" t="n"/>
       <c r="H196" s="7" t="inlineStr">
@@ -15508,13 +15508,13 @@
         </is>
       </c>
       <c r="D197" s="13" t="n">
-        <v>325.4</v>
+        <v>329.97</v>
       </c>
       <c r="E197" s="18" t="n">
-        <v>0.0344</v>
+        <v>0.0489</v>
       </c>
       <c r="F197" s="14" t="n">
-        <v>-0.09570000000000001</v>
+        <v>-0.083</v>
       </c>
       <c r="G197" s="15" t="n">
         <v>46321</v>
@@ -15569,13 +15569,13 @@
         </is>
       </c>
       <c r="D198" s="4" t="n">
-        <v>309.93</v>
+        <v>301.88</v>
       </c>
       <c r="E198" s="22" t="n">
-        <v>-0.04679999999999999</v>
+        <v>-0.0716</v>
       </c>
       <c r="F198" s="22" t="n">
-        <v>-0.0449</v>
+        <v>-0.0697</v>
       </c>
       <c r="G198" s="6" t="n"/>
       <c r="H198" s="7" t="inlineStr">
@@ -15620,13 +15620,13 @@
         </is>
       </c>
       <c r="D199" s="13" t="n">
-        <v>52.38</v>
+        <v>53.17</v>
       </c>
       <c r="E199" s="18" t="n">
-        <v>0.0588</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="F199" s="14" t="n">
-        <v>-0.0675</v>
+        <v>-0.0534</v>
       </c>
       <c r="G199" s="15" t="n"/>
       <c r="H199" s="21" t="inlineStr">
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="D200" s="4" t="n">
-        <v>18.33</v>
+        <v>18.73</v>
       </c>
       <c r="E200" s="22" t="n">
-        <v>-0.0568</v>
+        <v>-0.0365</v>
       </c>
       <c r="F200" s="22" t="n">
-        <v>-0.2195</v>
+        <v>-0.2026</v>
       </c>
       <c r="G200" s="6" t="n">
         <v>46318</v>
@@ -15732,13 +15732,13 @@
         </is>
       </c>
       <c r="D201" s="13" t="n">
-        <v>173.63</v>
+        <v>167.75</v>
       </c>
       <c r="E201" s="14" t="n">
-        <v>-0.2764</v>
+        <v>-0.3009</v>
       </c>
       <c r="F201" s="14" t="n">
-        <v>-0.3265</v>
+        <v>-0.3493</v>
       </c>
       <c r="G201" s="15" t="n"/>
       <c r="H201" s="21" t="inlineStr">
@@ -15783,13 +15783,13 @@
         </is>
       </c>
       <c r="D202" s="4" t="n">
-        <v>248.64</v>
+        <v>249.12</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>0.2589</v>
+        <v>0.2613</v>
       </c>
       <c r="F202" s="5" t="n">
-        <v>0.5224</v>
+        <v>0.5253</v>
       </c>
       <c r="G202" s="6" t="n"/>
       <c r="H202" s="7" t="inlineStr">
@@ -15808,7 +15808,7 @@
         <v>200</v>
       </c>
       <c r="M202" s="22" t="n">
-        <v>-0.1956241956241956</v>
+        <v>-0.1971740526653822</v>
       </c>
       <c r="N202" s="3" t="inlineStr">
         <is>
@@ -15819,7 +15819,7 @@
         <v>250</v>
       </c>
       <c r="P202" s="5" t="n">
-        <v>0.005469755469755525</v>
+        <v>0.0035324341682723</v>
       </c>
       <c r="Q202" s="9" t="inlineStr">
         <is>
@@ -15864,13 +15864,13 @@
         </is>
       </c>
       <c r="D203" s="13" t="n">
-        <v>208.39</v>
+        <v>210.02</v>
       </c>
       <c r="E203" s="14" t="n">
-        <v>-0.0745</v>
+        <v>-0.0672</v>
       </c>
       <c r="F203" s="18" t="n">
-        <v>0.1133</v>
+        <v>0.122</v>
       </c>
       <c r="G203" s="15" t="n"/>
       <c r="H203" s="21" t="inlineStr">
@@ -15889,7 +15889,7 @@
         <v>181.25</v>
       </c>
       <c r="M203" s="14" t="n">
-        <v>-0.1302365756514227</v>
+        <v>-0.1369869536234645</v>
       </c>
       <c r="N203" s="12" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>177.5</v>
       </c>
       <c r="P203" s="14" t="n">
-        <v>-0.1482316809827726</v>
+        <v>-0.1548423959622894</v>
       </c>
       <c r="Q203" s="19" t="inlineStr">
         <is>
@@ -15941,13 +15941,13 @@
         </is>
       </c>
       <c r="D204" s="4" t="n">
-        <v>96.86</v>
+        <v>99.83</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>0.0983</v>
+        <v>0.132</v>
       </c>
       <c r="F204" s="5" t="n">
-        <v>0.0898</v>
+        <v>0.1232</v>
       </c>
       <c r="G204" s="6" t="n"/>
       <c r="H204" s="7" t="inlineStr">
@@ -15992,13 +15992,13 @@
         </is>
       </c>
       <c r="D205" s="13" t="n">
-        <v>109.02</v>
+        <v>109.17</v>
       </c>
       <c r="E205" s="14" t="n">
-        <v>-0.1105</v>
+        <v>-0.1093</v>
       </c>
       <c r="F205" s="14" t="n">
-        <v>-0.1013</v>
+        <v>-0.1001</v>
       </c>
       <c r="G205" s="15" t="n"/>
       <c r="H205" s="21" t="inlineStr">
@@ -16017,7 +16017,7 @@
         <v>130</v>
       </c>
       <c r="M205" s="18" t="n">
-        <v>0.192441753806641</v>
+        <v>0.1908033342493359</v>
       </c>
       <c r="N205" s="12" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
         <v>150</v>
       </c>
       <c r="P205" s="18" t="n">
-        <v>0.375894331315355</v>
+        <v>0.3740038472107722</v>
       </c>
       <c r="Q205" s="19" t="inlineStr">
         <is>
@@ -16085,13 +16085,13 @@
         </is>
       </c>
       <c r="D206" s="4" t="n">
-        <v>207.78</v>
+        <v>210.23</v>
       </c>
       <c r="E206" s="22" t="n">
-        <v>-0.2032</v>
+        <v>-0.1938</v>
       </c>
       <c r="F206" s="22" t="n">
-        <v>-0.1932</v>
+        <v>-0.1837</v>
       </c>
       <c r="G206" s="6" t="n"/>
       <c r="H206" s="7" t="inlineStr">
@@ -16136,13 +16136,13 @@
         </is>
       </c>
       <c r="D207" s="13" t="n">
-        <v>521.71</v>
+        <v>533.88</v>
       </c>
       <c r="E207" s="18" t="n">
-        <v>0.1394</v>
+        <v>0.166</v>
       </c>
       <c r="F207" s="18" t="n">
-        <v>0.1994</v>
+        <v>0.2274</v>
       </c>
       <c r="G207" s="15" t="n"/>
       <c r="H207" s="21" t="inlineStr">
@@ -16187,13 +16187,13 @@
         </is>
       </c>
       <c r="D208" s="4" t="n">
-        <v>64.70999999999999</v>
+        <v>65.08</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>0.0851</v>
+        <v>0.09119999999999999</v>
       </c>
       <c r="F208" s="5" t="n">
-        <v>0.3159</v>
+        <v>0.3233</v>
       </c>
       <c r="G208" s="6" t="n"/>
       <c r="H208" s="7" t="inlineStr">
@@ -16238,13 +16238,13 @@
         </is>
       </c>
       <c r="D209" s="13" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="E209" s="18" t="n">
-        <v>0.0005999999999999999</v>
+        <v>50.29</v>
+      </c>
+      <c r="E209" s="14" t="n">
+        <v>-0.005500000000000001</v>
       </c>
       <c r="F209" s="18" t="n">
-        <v>0.1584</v>
+        <v>0.1513</v>
       </c>
       <c r="G209" s="15" t="n"/>
       <c r="H209" s="21" t="inlineStr">
@@ -16289,13 +16289,13 @@
         </is>
       </c>
       <c r="D210" s="4" t="n">
-        <v>425.04</v>
+        <v>416.31</v>
       </c>
       <c r="E210" s="22" t="n">
-        <v>-0.1936</v>
+        <v>-0.2101</v>
       </c>
       <c r="F210" s="22" t="n">
-        <v>-0.0978</v>
+        <v>-0.1164</v>
       </c>
       <c r="G210" s="6" t="n">
         <v>46328</v>
@@ -16350,13 +16350,13 @@
         </is>
       </c>
       <c r="D211" s="13" t="n">
-        <v>108.25</v>
+        <v>109.86</v>
       </c>
       <c r="E211" s="14" t="n">
-        <v>-0.03759999999999999</v>
+        <v>-0.0232</v>
       </c>
       <c r="F211" s="14" t="n">
-        <v>-0.0789</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="G211" s="15" t="n"/>
       <c r="H211" s="21" t="inlineStr">
@@ -16401,13 +16401,13 @@
         </is>
       </c>
       <c r="D212" s="4" t="n">
-        <v>153.97</v>
+        <v>157.47</v>
       </c>
       <c r="E212" s="22" t="n">
-        <v>-0.0624</v>
+        <v>-0.04099999999999999</v>
       </c>
       <c r="F212" s="22" t="n">
-        <v>-0.0225</v>
+        <v>-0.0003</v>
       </c>
       <c r="G212" s="6" t="n"/>
       <c r="H212" s="7" t="inlineStr">
@@ -16452,13 +16452,13 @@
         </is>
       </c>
       <c r="D213" s="13" t="n">
-        <v>45.98</v>
+        <v>45.09</v>
       </c>
       <c r="E213" s="14" t="n">
-        <v>-0.08130000000000001</v>
+        <v>-0.09910000000000001</v>
       </c>
       <c r="F213" s="14" t="n">
-        <v>-0.3333</v>
+        <v>-0.3462</v>
       </c>
       <c r="G213" s="15" t="n"/>
       <c r="H213" s="21" t="inlineStr">
@@ -16503,13 +16503,13 @@
         </is>
       </c>
       <c r="D214" s="4" t="n">
-        <v>166.07</v>
+        <v>165.96</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>0.0526</v>
+        <v>0.052</v>
       </c>
       <c r="F214" s="22" t="n">
-        <v>-0.13</v>
+        <v>-0.1306</v>
       </c>
       <c r="G214" s="6" t="n">
         <v>46322</v>
@@ -16564,13 +16564,13 @@
         </is>
       </c>
       <c r="D215" s="13" t="n">
-        <v>47.41</v>
+        <v>47.15</v>
       </c>
       <c r="E215" s="18" t="n">
-        <v>0.164</v>
+        <v>0.1576</v>
       </c>
       <c r="F215" s="18" t="n">
-        <v>0.4624</v>
+        <v>0.4543</v>
       </c>
       <c r="G215" s="15" t="n"/>
       <c r="H215" s="21" t="inlineStr">
@@ -16615,13 +16615,13 @@
         </is>
       </c>
       <c r="D216" s="4" t="n">
-        <v>151.65</v>
+        <v>149.71</v>
       </c>
       <c r="E216" s="22" t="n">
-        <v>-0.1231</v>
+        <v>-0.1343</v>
       </c>
       <c r="F216" s="5" t="n">
-        <v>0.114</v>
+        <v>0.0998</v>
       </c>
       <c r="G216" s="6" t="n"/>
       <c r="H216" s="7" t="inlineStr">
@@ -16640,7 +16640,7 @@
         <v>190</v>
       </c>
       <c r="M216" s="5" t="n">
-        <v>0.2528849324101549</v>
+        <v>0.2691202992452073</v>
       </c>
       <c r="N216" s="3" t="inlineStr"/>
       <c r="O216" s="8" t="n"/>
@@ -16684,13 +16684,13 @@
         </is>
       </c>
       <c r="D217" s="13" t="n">
-        <v>54.13</v>
-      </c>
-      <c r="E217" s="14" t="n">
-        <v>-0.0101</v>
+        <v>56.03</v>
+      </c>
+      <c r="E217" s="18" t="n">
+        <v>0.0247</v>
       </c>
       <c r="F217" s="18" t="n">
-        <v>0.1152</v>
+        <v>0.1543</v>
       </c>
       <c r="G217" s="15" t="n"/>
       <c r="H217" s="21" t="inlineStr">
@@ -16709,7 +16709,7 @@
         <v>67</v>
       </c>
       <c r="M217" s="18" t="n">
-        <v>0.2377609458710511</v>
+        <v>0.1957879707299661</v>
       </c>
       <c r="N217" s="12" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>70</v>
       </c>
       <c r="P217" s="18" t="n">
-        <v>0.2931830777757251</v>
+        <v>0.2493307156880243</v>
       </c>
       <c r="Q217" s="19" t="inlineStr">
         <is>
@@ -16761,13 +16761,13 @@
         </is>
       </c>
       <c r="D218" s="4" t="n">
-        <v>241.82</v>
+        <v>240.42</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>0.12</v>
+        <v>0.1135</v>
       </c>
       <c r="F218" s="5" t="n">
-        <v>0.1655</v>
+        <v>0.1588</v>
       </c>
       <c r="G218" s="6" t="n"/>
       <c r="H218" s="7" t="inlineStr">
@@ -16812,13 +16812,13 @@
         </is>
       </c>
       <c r="D219" s="13" t="n">
-        <v>231.85</v>
+        <v>232.09</v>
       </c>
       <c r="E219" s="14" t="n">
-        <v>-0.0189</v>
+        <v>-0.0179</v>
       </c>
       <c r="F219" s="14" t="n">
-        <v>-0.1937</v>
+        <v>-0.1929</v>
       </c>
       <c r="G219" s="15" t="n">
         <v>46316</v>
@@ -16854,7 +16854,7 @@
         <v>250</v>
       </c>
       <c r="P219" s="18" t="n">
-        <v>0.07828337287039036</v>
+        <v>0.07716833986815458</v>
       </c>
       <c r="Q219" s="19" t="inlineStr">
         <is>
@@ -16891,13 +16891,13 @@
         </is>
       </c>
       <c r="D220" s="4" t="n">
-        <v>14.14</v>
+        <v>13.66</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>0.2092</v>
+        <v>0.1685</v>
       </c>
       <c r="F220" s="5" t="n">
-        <v>0.2654</v>
+        <v>0.2229</v>
       </c>
       <c r="G220" s="6" t="n"/>
       <c r="H220" s="7" t="inlineStr">
@@ -16942,13 +16942,13 @@
         </is>
       </c>
       <c r="D221" s="13" t="n">
-        <v>103.08</v>
+        <v>104.47</v>
       </c>
       <c r="E221" s="18" t="n">
-        <v>0.057</v>
+        <v>0.0713</v>
       </c>
       <c r="F221" s="14" t="n">
-        <v>-0.06150000000000001</v>
+        <v>-0.0489</v>
       </c>
       <c r="G221" s="15" t="n">
         <v>46317</v>
@@ -17003,13 +17003,13 @@
         </is>
       </c>
       <c r="D222" s="4" t="n">
-        <v>315.47</v>
+        <v>318.93</v>
       </c>
       <c r="E222" s="22" t="n">
-        <v>-0.0567</v>
+        <v>-0.0463</v>
       </c>
       <c r="F222" s="5" t="n">
-        <v>0.1473</v>
+        <v>0.1599</v>
       </c>
       <c r="G222" s="6" t="n"/>
       <c r="H222" s="7" t="inlineStr">
@@ -17054,13 +17054,13 @@
         </is>
       </c>
       <c r="D223" s="13" t="n">
-        <v>42.69</v>
-      </c>
-      <c r="E223" s="18" t="n">
-        <v>0.0038</v>
+        <v>40.47</v>
+      </c>
+      <c r="E223" s="14" t="n">
+        <v>-0.0484</v>
       </c>
       <c r="F223" s="14" t="n">
-        <v>-0.004</v>
+        <v>-0.0558</v>
       </c>
       <c r="G223" s="15" t="n"/>
       <c r="H223" s="21" t="inlineStr">
@@ -17105,13 +17105,13 @@
         </is>
       </c>
       <c r="D224" s="4" t="n">
-        <v>47.54</v>
+        <v>46.93</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>0.2272</v>
+        <v>0.2114</v>
       </c>
       <c r="F224" s="5" t="n">
-        <v>0.1556</v>
+        <v>0.1407</v>
       </c>
       <c r="G224" s="6" t="n"/>
       <c r="H224" s="7" t="inlineStr">
@@ -17156,13 +17156,13 @@
         </is>
       </c>
       <c r="D225" s="13" t="n">
-        <v>312.19</v>
+        <v>312.33</v>
       </c>
       <c r="E225" s="14" t="n">
-        <v>-0.0726</v>
+        <v>-0.0722</v>
       </c>
       <c r="F225" s="14" t="n">
-        <v>-0.0548</v>
+        <v>-0.0544</v>
       </c>
       <c r="G225" s="15" t="n">
         <v>46289</v>
@@ -17221,13 +17221,13 @@
         </is>
       </c>
       <c r="D226" s="4" t="n">
-        <v>326.3</v>
+        <v>333.42</v>
       </c>
       <c r="E226" s="22" t="n">
-        <v>-0.0272</v>
+        <v>-0.0059</v>
       </c>
       <c r="F226" s="5" t="n">
-        <v>0.0132</v>
+        <v>0.0353</v>
       </c>
       <c r="G226" s="6" t="n"/>
       <c r="H226" s="7" t="inlineStr">
@@ -17246,7 +17246,7 @@
         <v>390</v>
       </c>
       <c r="M226" s="5" t="n">
-        <v>0.1952191235059761</v>
+        <v>0.1696958790714414</v>
       </c>
       <c r="N226" s="3" t="inlineStr"/>
       <c r="O226" s="8" t="n"/>
@@ -17302,13 +17302,13 @@
         </is>
       </c>
       <c r="D227" s="13" t="n">
-        <v>188.28</v>
+        <v>188.98</v>
       </c>
       <c r="E227" s="14" t="n">
-        <v>-0.0231</v>
+        <v>-0.0195</v>
       </c>
       <c r="F227" s="14" t="n">
-        <v>-0.1868</v>
+        <v>-0.1837</v>
       </c>
       <c r="G227" s="15" t="n"/>
       <c r="H227" s="21" t="inlineStr">
@@ -17327,7 +17327,7 @@
         <v>305</v>
       </c>
       <c r="M227" s="18" t="n">
-        <v>0.6199277671553006</v>
+        <v>0.6139273997248387</v>
       </c>
       <c r="N227" s="12" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>185</v>
       </c>
       <c r="P227" s="14" t="n">
-        <v>-0.01742086254514554</v>
+        <v>-0.02106042967509784</v>
       </c>
       <c r="Q227" s="19" t="inlineStr">
         <is>
@@ -17379,13 +17379,13 @@
         </is>
       </c>
       <c r="D228" s="4" t="n">
-        <v>82.95999999999999</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="E228" s="22" t="n">
-        <v>-0.0409</v>
+        <v>-0.0397</v>
       </c>
       <c r="F228" s="22" t="n">
-        <v>-0.2685</v>
+        <v>-0.2675</v>
       </c>
       <c r="G228" s="6" t="n"/>
       <c r="H228" s="7" t="inlineStr">
@@ -17430,13 +17430,13 @@
         </is>
       </c>
       <c r="D229" s="13" t="n">
-        <v>970.5</v>
+        <v>978.53</v>
       </c>
       <c r="E229" s="18" t="n">
-        <v>0.193</v>
+        <v>0.2029</v>
       </c>
       <c r="F229" s="18" t="n">
-        <v>0.2101</v>
+        <v>0.2201</v>
       </c>
       <c r="G229" s="15" t="n"/>
       <c r="H229" s="21" t="inlineStr">
@@ -17481,13 +17481,13 @@
         </is>
       </c>
       <c r="D230" s="4" t="n">
-        <v>97.78</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="E230" s="22" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.06059999999999999</v>
       </c>
       <c r="F230" s="22" t="n">
-        <v>-0.0409</v>
+        <v>-0.0337</v>
       </c>
       <c r="G230" s="6" t="n">
         <v>46322</v>
@@ -17542,13 +17542,13 @@
         </is>
       </c>
       <c r="D231" s="13" t="n">
-        <v>318.14</v>
+        <v>320.42</v>
       </c>
       <c r="E231" s="18" t="n">
-        <v>0.0383</v>
+        <v>0.0458</v>
       </c>
       <c r="F231" s="14" t="n">
-        <v>-0.0919</v>
+        <v>-0.08539999999999999</v>
       </c>
       <c r="G231" s="15" t="n">
         <v>46323</v>
@@ -17577,7 +17577,7 @@
         <v>450</v>
       </c>
       <c r="M231" s="18" t="n">
-        <v>0.4144716162695669</v>
+        <v>0.4044067161850071</v>
       </c>
       <c r="N231" s="12" t="inlineStr">
         <is>
@@ -17588,7 +17588,7 @@
         <v>355</v>
       </c>
       <c r="P231" s="18" t="n">
-        <v>0.1158609417237695</v>
+        <v>0.1079208538792834</v>
       </c>
       <c r="Q231" s="19" t="inlineStr">
         <is>
@@ -17633,13 +17633,13 @@
         </is>
       </c>
       <c r="D232" s="4" t="n">
-        <v>74.04000000000001</v>
+        <v>73.38</v>
       </c>
       <c r="E232" s="22" t="n">
-        <v>-0.09029999999999999</v>
+        <v>-0.0984</v>
       </c>
       <c r="F232" s="22" t="n">
-        <v>-0.1642</v>
+        <v>-0.1717</v>
       </c>
       <c r="G232" s="6" t="n"/>
       <c r="H232" s="7" t="inlineStr">
@@ -17684,13 +17684,13 @@
         </is>
       </c>
       <c r="D233" s="13" t="n">
-        <v>357.84</v>
+        <v>356</v>
       </c>
       <c r="E233" s="14" t="n">
-        <v>-0.1412</v>
+        <v>-0.1456</v>
       </c>
       <c r="F233" s="18" t="n">
-        <v>0.0461</v>
+        <v>0.0407</v>
       </c>
       <c r="G233" s="15" t="n"/>
       <c r="H233" s="21" t="inlineStr">
@@ -17735,13 +17735,13 @@
         </is>
       </c>
       <c r="D234" s="4" t="n">
-        <v>266.43</v>
+        <v>265.5</v>
       </c>
       <c r="E234" s="22" t="n">
-        <v>-0.0886</v>
+        <v>-0.09179999999999999</v>
       </c>
       <c r="F234" s="22" t="n">
-        <v>-0.2771</v>
+        <v>-0.2797</v>
       </c>
       <c r="G234" s="6" t="n"/>
       <c r="H234" s="7" t="inlineStr">
@@ -17786,13 +17786,13 @@
         </is>
       </c>
       <c r="D235" s="13" t="n">
-        <v>1228.64</v>
+        <v>1218.5</v>
       </c>
       <c r="E235" s="14" t="n">
-        <v>-0.1104</v>
+        <v>-0.1177</v>
       </c>
       <c r="F235" s="14" t="n">
-        <v>-0.0917</v>
+        <v>-0.0992</v>
       </c>
       <c r="G235" s="15" t="n">
         <v>46324</v>
@@ -17847,13 +17847,13 @@
         </is>
       </c>
       <c r="D236" s="4" t="n">
-        <v>226.65</v>
+        <v>225.41</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>0.0867</v>
+        <v>0.0808</v>
       </c>
       <c r="F236" s="22" t="n">
-        <v>-0.0388</v>
+        <v>-0.0441</v>
       </c>
       <c r="G236" s="6" t="n"/>
       <c r="H236" s="7" t="inlineStr">
@@ -17872,7 +17872,7 @@
         <v>240</v>
       </c>
       <c r="M236" s="5" t="n">
-        <v>0.0589013898080741</v>
+        <v>0.06472649838072847</v>
       </c>
       <c r="N236" s="3" t="inlineStr">
         <is>
@@ -17883,7 +17883,7 @@
         <v>251</v>
       </c>
       <c r="P236" s="5" t="n">
-        <v>0.1074343701742775</v>
+        <v>0.1135264628898452</v>
       </c>
       <c r="Q236" s="9" t="inlineStr">
         <is>
@@ -17924,13 +17924,13 @@
         </is>
       </c>
       <c r="D237" s="13" t="n">
-        <v>492.37</v>
+        <v>493.95</v>
       </c>
       <c r="E237" s="14" t="n">
-        <v>-0.0271</v>
+        <v>-0.0239</v>
       </c>
       <c r="F237" s="18" t="n">
-        <v>0.2786</v>
+        <v>0.2827</v>
       </c>
       <c r="G237" s="15" t="n"/>
       <c r="H237" s="21" t="inlineStr">
@@ -17949,7 +17949,7 @@
         <v>625</v>
       </c>
       <c r="M237" s="18" t="n">
-        <v>0.2693705952840343</v>
+        <v>0.265310254074299</v>
       </c>
       <c r="N237" s="12" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>525</v>
       </c>
       <c r="P237" s="18" t="n">
-        <v>0.06627130003858886</v>
+        <v>0.0628606134224112</v>
       </c>
       <c r="Q237" s="19" t="inlineStr">
         <is>
@@ -18013,13 +18013,13 @@
         </is>
       </c>
       <c r="D238" s="4" t="n">
-        <v>460.99</v>
-      </c>
-      <c r="E238" s="22" t="n">
-        <v>-0.0021</v>
+        <v>462.98</v>
+      </c>
+      <c r="E238" s="5" t="n">
+        <v>0.0022</v>
       </c>
       <c r="F238" s="5" t="n">
-        <v>0.0901</v>
+        <v>0.09480000000000001</v>
       </c>
       <c r="G238" s="6" t="n">
         <v>46324</v>
@@ -18051,7 +18051,7 @@
         <v>525</v>
       </c>
       <c r="P238" s="5" t="n">
-        <v>0.1388533373825896</v>
+        <v>0.1339582703356516</v>
       </c>
       <c r="Q238" s="9" t="inlineStr">
         <is>
@@ -18100,13 +18100,13 @@
         </is>
       </c>
       <c r="D239" s="13" t="n">
-        <v>138</v>
+        <v>136.52</v>
       </c>
       <c r="E239" s="18" t="n">
-        <v>0.4179</v>
+        <v>0.4027000000000001</v>
       </c>
       <c r="F239" s="18" t="n">
-        <v>0.4582</v>
+        <v>0.4425</v>
       </c>
       <c r="G239" s="15" t="n">
         <v>46324</v>
@@ -18161,13 +18161,13 @@
         </is>
       </c>
       <c r="D240" s="4" t="n">
-        <v>273.64</v>
+        <v>274.8</v>
       </c>
       <c r="E240" s="22" t="n">
-        <v>-0.0788</v>
+        <v>-0.07480000000000001</v>
       </c>
       <c r="F240" s="22" t="n">
-        <v>-0.1131</v>
+        <v>-0.1093</v>
       </c>
       <c r="G240" s="6" t="n"/>
       <c r="H240" s="7" t="inlineStr">
@@ -18212,13 +18212,13 @@
         </is>
       </c>
       <c r="D241" s="13" t="n">
-        <v>1017.44</v>
+        <v>1000.26</v>
       </c>
       <c r="E241" s="18" t="n">
-        <v>0.1817</v>
+        <v>0.1617</v>
       </c>
       <c r="F241" s="18" t="n">
-        <v>0.0389</v>
+        <v>0.0214</v>
       </c>
       <c r="G241" s="15" t="n">
         <v>46295</v>
@@ -18247,7 +18247,7 @@
         <v>1525</v>
       </c>
       <c r="M241" s="18" t="n">
-        <v>0.4988598836295014</v>
+        <v>0.5246036030632035</v>
       </c>
       <c r="N241" s="12" t="inlineStr">
         <is>
@@ -18295,13 +18295,13 @@
         </is>
       </c>
       <c r="D242" s="4" t="n">
-        <v>240.46</v>
+        <v>243.88</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>0.3061</v>
+        <v>0.3246</v>
       </c>
       <c r="F242" s="5" t="n">
-        <v>0.09480000000000001</v>
+        <v>0.1103</v>
       </c>
       <c r="G242" s="6" t="n"/>
       <c r="H242" s="7" t="inlineStr">
@@ -18346,13 +18346,13 @@
         </is>
       </c>
       <c r="D243" s="13" t="n">
-        <v>279.58</v>
+        <v>284.3</v>
       </c>
       <c r="E243" s="14" t="n">
-        <v>-0.0998</v>
+        <v>-0.08460000000000001</v>
       </c>
       <c r="F243" s="18" t="n">
-        <v>0.0417</v>
+        <v>0.0592</v>
       </c>
       <c r="G243" s="15" t="n">
         <v>46324</v>
@@ -18407,13 +18407,13 @@
         </is>
       </c>
       <c r="D244" s="4" t="n">
-        <v>134.09</v>
+        <v>134.21</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>0.0522</v>
+        <v>0.05309999999999999</v>
       </c>
       <c r="F244" s="5" t="n">
-        <v>0.2449</v>
+        <v>0.246</v>
       </c>
       <c r="G244" s="6" t="n">
         <v>46323</v>
@@ -18442,7 +18442,7 @@
         <v>160</v>
       </c>
       <c r="M244" s="5" t="n">
-        <v>0.193228428667313</v>
+        <v>0.1921615378883838</v>
       </c>
       <c r="N244" s="3" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>150</v>
       </c>
       <c r="P244" s="5" t="n">
-        <v>0.1186516518756059</v>
+        <v>0.1176514417703598</v>
       </c>
       <c r="Q244" s="9" t="inlineStr">
         <is>
@@ -18498,13 +18498,13 @@
         </is>
       </c>
       <c r="D245" s="13" t="n">
-        <v>67.34999999999999</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="E245" s="18" t="n">
-        <v>0.04480000000000001</v>
+        <v>0.047</v>
       </c>
       <c r="F245" s="18" t="n">
-        <v>0.2292</v>
+        <v>0.2318</v>
       </c>
       <c r="G245" s="15" t="n"/>
       <c r="H245" s="21" t="inlineStr">
@@ -18549,13 +18549,13 @@
         </is>
       </c>
       <c r="D246" s="4" t="n">
-        <v>227.17</v>
+        <v>225.73</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>0.0442</v>
+        <v>0.03759999999999999</v>
       </c>
       <c r="F246" s="5" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G246" s="6" t="n"/>
       <c r="H246" s="7" t="inlineStr">
@@ -18574,7 +18574,7 @@
         <v>315</v>
       </c>
       <c r="M246" s="5" t="n">
-        <v>0.3866267552933927</v>
+        <v>0.3954724671067205</v>
       </c>
       <c r="N246" s="3" t="inlineStr">
         <is>
@@ -18585,7 +18585,7 @@
         <v>413</v>
       </c>
       <c r="P246" s="5" t="n">
-        <v>0.8180217458291149</v>
+        <v>0.8296194568732558</v>
       </c>
       <c r="Q246" s="9" t="inlineStr">
         <is>
@@ -18634,13 +18634,13 @@
         </is>
       </c>
       <c r="D247" s="13" t="n">
-        <v>383.83</v>
+        <v>377.11</v>
       </c>
       <c r="E247" s="14" t="n">
-        <v>-0.0025</v>
+        <v>-0.02</v>
       </c>
       <c r="F247" s="14" t="n">
-        <v>-0.1935</v>
+        <v>-0.2076</v>
       </c>
       <c r="G247" s="15" t="n"/>
       <c r="H247" s="21" t="inlineStr">
@@ -18685,13 +18685,13 @@
         </is>
       </c>
       <c r="D248" s="4" t="n">
-        <v>226.96</v>
+        <v>223.87</v>
       </c>
       <c r="E248" s="22" t="n">
-        <v>-0.0277</v>
+        <v>-0.04099999999999999</v>
       </c>
       <c r="F248" s="22" t="n">
-        <v>-0.2234</v>
+        <v>-0.234</v>
       </c>
       <c r="G248" s="6" t="n">
         <v>46321</v>
@@ -18745,10 +18745,10 @@
         <v>10.98</v>
       </c>
       <c r="E249" s="14" t="n">
-        <v>-0.0575</v>
+        <v>-0.04269999999999999</v>
       </c>
       <c r="F249" s="14" t="n">
-        <v>-0.4193</v>
+        <v>-0.3708</v>
       </c>
       <c r="G249" s="15" t="n"/>
       <c r="H249" s="21" t="inlineStr">
@@ -18793,13 +18793,13 @@
         </is>
       </c>
       <c r="D250" s="4" t="n">
-        <v>166.86</v>
+        <v>167.6</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>0.1067</v>
+        <v>0.1116</v>
       </c>
       <c r="F250" s="5" t="n">
-        <v>0.2036</v>
+        <v>0.2089</v>
       </c>
       <c r="G250" s="6" t="n"/>
       <c r="H250" s="7" t="inlineStr">
@@ -18818,7 +18818,7 @@
         <v>150</v>
       </c>
       <c r="M250" s="22" t="n">
-        <v>-0.1010427903631788</v>
+        <v>-0.1050119331742243</v>
       </c>
       <c r="N250" s="3" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>130</v>
       </c>
       <c r="P250" s="22" t="n">
-        <v>-0.2209037516480883</v>
+        <v>-0.2243436754176611</v>
       </c>
       <c r="Q250" s="9" t="inlineStr">
         <is>
@@ -18870,13 +18870,13 @@
         </is>
       </c>
       <c r="D251" s="13" t="n">
-        <v>73.59999999999999</v>
+        <v>71.08</v>
       </c>
       <c r="E251" s="14" t="n">
-        <v>-0.0775</v>
+        <v>-0.109</v>
       </c>
       <c r="F251" s="14" t="n">
-        <v>-0.233</v>
+        <v>-0.2593</v>
       </c>
       <c r="G251" s="15" t="n">
         <v>46328</v>
@@ -18931,13 +18931,13 @@
         </is>
       </c>
       <c r="D252" s="4" t="n">
-        <v>281.27</v>
+        <v>281.11</v>
       </c>
       <c r="E252" s="22" t="n">
-        <v>-0.0346</v>
+        <v>-0.0351</v>
       </c>
       <c r="F252" s="22" t="n">
-        <v>-0.125</v>
+        <v>-0.1255</v>
       </c>
       <c r="G252" s="6" t="n"/>
       <c r="H252" s="7" t="inlineStr">
@@ -18982,13 +18982,13 @@
         </is>
       </c>
       <c r="D253" s="13" t="n">
-        <v>163.16</v>
+        <v>162.52</v>
       </c>
       <c r="E253" s="18" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.0759</v>
       </c>
       <c r="F253" s="18" t="n">
-        <v>0.1601</v>
+        <v>0.1556</v>
       </c>
       <c r="G253" s="15" t="n">
         <v>46275</v>
@@ -19017,7 +19017,7 @@
         <v>280</v>
       </c>
       <c r="M253" s="18" t="n">
-        <v>0.7161068889433685</v>
+        <v>0.7228648781688406</v>
       </c>
       <c r="N253" s="12" t="inlineStr">
         <is>
@@ -19028,7 +19028,7 @@
         <v>245</v>
       </c>
       <c r="P253" s="18" t="n">
-        <v>0.5015935278254474</v>
+        <v>0.5075067683977356</v>
       </c>
       <c r="Q253" s="19" t="inlineStr">
         <is>
@@ -19069,13 +19069,13 @@
         </is>
       </c>
       <c r="D254" s="4" t="n">
-        <v>331.21</v>
+        <v>336.98</v>
       </c>
       <c r="E254" s="22" t="n">
-        <v>-0.1398</v>
+        <v>-0.1248</v>
       </c>
       <c r="F254" s="5" t="n">
-        <v>0.0163</v>
+        <v>0.034</v>
       </c>
       <c r="G254" s="6" t="n"/>
       <c r="H254" s="7" t="inlineStr">
@@ -19094,7 +19094,7 @@
         <v>420</v>
       </c>
       <c r="M254" s="5" t="n">
-        <v>0.2680776546601855</v>
+        <v>0.2463647694225176</v>
       </c>
       <c r="N254" s="3" t="inlineStr">
         <is>
@@ -19105,7 +19105,7 @@
         <v>415</v>
       </c>
       <c r="P254" s="5" t="n">
-        <v>0.2529814921047071</v>
+        <v>0.2315270935960591</v>
       </c>
       <c r="Q254" s="9" t="inlineStr">
         <is>
@@ -19154,13 +19154,13 @@
         </is>
       </c>
       <c r="D255" s="13" t="n">
-        <v>14.28</v>
+        <v>14.01</v>
       </c>
       <c r="E255" s="14" t="n">
-        <v>-0.0837</v>
+        <v>-0.1013</v>
       </c>
       <c r="F255" s="18" t="n">
-        <v>0.223</v>
+        <v>0.1995</v>
       </c>
       <c r="G255" s="15" t="n"/>
       <c r="H255" s="21" t="inlineStr">
@@ -19205,13 +19205,13 @@
         </is>
       </c>
       <c r="D256" s="4" t="n">
-        <v>35.43</v>
+        <v>35.8</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>0.0733</v>
+        <v>0.08449999999999999</v>
       </c>
       <c r="F256" s="5" t="n">
-        <v>0.1341</v>
+        <v>0.146</v>
       </c>
       <c r="G256" s="6" t="n">
         <v>46315</v>
@@ -19266,13 +19266,13 @@
         </is>
       </c>
       <c r="D257" s="13" t="n">
-        <v>173.37</v>
+        <v>171.82</v>
       </c>
       <c r="E257" s="14" t="n">
-        <v>-0.0163</v>
+        <v>-0.0251</v>
       </c>
       <c r="F257" s="18" t="n">
-        <v>0.2037</v>
+        <v>0.1929</v>
       </c>
       <c r="G257" s="15" t="n"/>
       <c r="H257" s="21" t="inlineStr">
@@ -19317,13 +19317,13 @@
         </is>
       </c>
       <c r="D258" s="4" t="n">
-        <v>172.35</v>
+        <v>170.3</v>
       </c>
       <c r="E258" s="22" t="n">
-        <v>-0.0164</v>
+        <v>-0.0281</v>
       </c>
       <c r="F258" s="5" t="n">
-        <v>0.3593</v>
+        <v>0.3432</v>
       </c>
       <c r="G258" s="6" t="n">
         <v>46328</v>
@@ -19378,13 +19378,13 @@
         </is>
       </c>
       <c r="D259" s="13" t="n">
-        <v>122.74</v>
+        <v>123.28</v>
       </c>
       <c r="E259" s="14" t="n">
-        <v>-0.08650000000000001</v>
+        <v>-0.0825</v>
       </c>
       <c r="F259" s="14" t="n">
-        <v>-0.1465</v>
+        <v>-0.1427</v>
       </c>
       <c r="G259" s="15" t="n"/>
       <c r="H259" s="21" t="inlineStr">
@@ -19439,13 +19439,13 @@
         </is>
       </c>
       <c r="D260" s="4" t="n">
-        <v>18.14</v>
+        <v>17.67</v>
       </c>
       <c r="E260" s="22" t="n">
-        <v>-0.1015</v>
+        <v>-0.1248</v>
       </c>
       <c r="F260" s="22" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.1205</v>
       </c>
       <c r="G260" s="6" t="n"/>
       <c r="H260" s="7" t="inlineStr">
@@ -19490,13 +19490,13 @@
         </is>
       </c>
       <c r="D261" s="13" t="n">
-        <v>177.48</v>
+        <v>174.09</v>
       </c>
       <c r="E261" s="18" t="n">
-        <v>0.0944</v>
+        <v>0.0735</v>
       </c>
       <c r="F261" s="14" t="n">
-        <v>-0.06179999999999999</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="G261" s="15" t="n"/>
       <c r="H261" s="21" t="inlineStr">
@@ -19515,7 +19515,7 @@
         <v>265</v>
       </c>
       <c r="M261" s="18" t="n">
-        <v>0.4931259860265946</v>
+        <v>0.522201160319375</v>
       </c>
       <c r="N261" s="12" t="inlineStr">
         <is>
@@ -19526,7 +19526,7 @@
         <v>179</v>
       </c>
       <c r="P261" s="18" t="n">
-        <v>0.00856434527834128</v>
+        <v>0.02820380263082312</v>
       </c>
       <c r="Q261" s="19" t="inlineStr">
         <is>
@@ -19571,13 +19571,13 @@
         </is>
       </c>
       <c r="D262" s="4" t="n">
-        <v>102.93</v>
+        <v>104.07</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>0.0612</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="F262" s="5" t="n">
-        <v>0.1995</v>
+        <v>0.2128</v>
       </c>
       <c r="G262" s="6" t="n">
         <v>46322</v>
@@ -19632,13 +19632,13 @@
         </is>
       </c>
       <c r="D263" s="13" t="n">
-        <v>8.390000000000001</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="E263" s="14" t="n">
-        <v>-0.0605</v>
+        <v>-0.0795</v>
       </c>
       <c r="F263" s="14" t="n">
-        <v>-0.0312</v>
+        <v>-0.0508</v>
       </c>
       <c r="G263" s="15" t="n"/>
       <c r="H263" s="21" t="inlineStr">
@@ -19683,13 +19683,13 @@
         </is>
       </c>
       <c r="D264" s="4" t="n">
-        <v>91.23999999999999</v>
+        <v>91.63</v>
       </c>
       <c r="E264" s="22" t="n">
-        <v>-0.06809999999999999</v>
+        <v>-0.0641</v>
       </c>
       <c r="F264" s="5" t="n">
-        <v>0.08130000000000001</v>
+        <v>0.0859</v>
       </c>
       <c r="G264" s="6" t="n"/>
       <c r="H264" s="7" t="inlineStr">
@@ -19734,13 +19734,13 @@
         </is>
       </c>
       <c r="D265" s="13" t="n">
-        <v>16.16</v>
+        <v>15.81</v>
       </c>
       <c r="E265" s="14" t="n">
-        <v>-0.08439999999999999</v>
+        <v>-0.1042</v>
       </c>
       <c r="F265" s="14" t="n">
-        <v>-0.023</v>
+        <v>-0.0441</v>
       </c>
       <c r="G265" s="15" t="n"/>
       <c r="H265" s="21" t="inlineStr">
@@ -19785,13 +19785,13 @@
         </is>
       </c>
       <c r="D266" s="4" t="n">
-        <v>395.56</v>
+        <v>395.65</v>
       </c>
       <c r="E266" s="22" t="n">
-        <v>-0.0206</v>
+        <v>-0.0204</v>
       </c>
       <c r="F266" s="5" t="n">
-        <v>0.1114</v>
+        <v>0.1117</v>
       </c>
       <c r="G266" s="6" t="n">
         <v>46317</v>
@@ -19860,13 +19860,13 @@
         </is>
       </c>
       <c r="D267" s="13" t="n">
-        <v>3.16</v>
+        <v>3.23</v>
       </c>
       <c r="E267" s="14" t="n">
-        <v>-0.3319</v>
+        <v>-0.3171</v>
       </c>
       <c r="F267" s="14" t="n">
-        <v>-0.4082</v>
+        <v>-0.3951</v>
       </c>
       <c r="G267" s="15" t="n"/>
       <c r="H267" s="21" t="inlineStr">
@@ -19911,13 +19911,13 @@
         </is>
       </c>
       <c r="D268" s="4" t="n">
-        <v>19.3</v>
+        <v>19.43</v>
       </c>
       <c r="E268" s="22" t="n">
-        <v>-0.1318</v>
+        <v>-0.126</v>
       </c>
       <c r="F268" s="5" t="n">
-        <v>0.0794</v>
+        <v>0.0867</v>
       </c>
       <c r="G268" s="6" t="n"/>
       <c r="H268" s="7" t="inlineStr">
@@ -19962,13 +19962,13 @@
         </is>
       </c>
       <c r="D269" s="13" t="n">
-        <v>18.08</v>
+        <v>17.79</v>
       </c>
       <c r="E269" s="14" t="n">
-        <v>-0.0683</v>
+        <v>-0.08349999999999999</v>
       </c>
       <c r="F269" s="18" t="n">
-        <v>0.3191</v>
+        <v>0.2976</v>
       </c>
       <c r="G269" s="15" t="n">
         <v>46274</v>
@@ -20023,13 +20023,13 @@
         </is>
       </c>
       <c r="D270" s="4" t="n">
-        <v>206.99</v>
+        <v>205.41</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>0.0394</v>
+        <v>0.0314</v>
       </c>
       <c r="F270" s="22" t="n">
-        <v>-0.0086</v>
+        <v>-0.0162</v>
       </c>
       <c r="G270" s="6" t="n">
         <v>46328</v>
@@ -20084,13 +20084,13 @@
         </is>
       </c>
       <c r="D271" s="13" t="n">
-        <v>210.93</v>
+        <v>211.49</v>
       </c>
       <c r="E271" s="18" t="n">
-        <v>0.0114</v>
+        <v>0.0141</v>
       </c>
       <c r="F271" s="18" t="n">
-        <v>0.3362</v>
+        <v>0.3397</v>
       </c>
       <c r="G271" s="15" t="n">
         <v>46316</v>
@@ -20165,13 +20165,13 @@
         </is>
       </c>
       <c r="D272" s="4" t="n">
-        <v>40.98</v>
+        <v>40.26</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>0.3026</v>
+        <v>0.2797</v>
       </c>
       <c r="F272" s="5" t="n">
-        <v>0.4475</v>
+        <v>0.4221</v>
       </c>
       <c r="G272" s="6" t="n"/>
       <c r="H272" s="7" t="inlineStr">
@@ -20216,13 +20216,13 @@
         </is>
       </c>
       <c r="D273" s="13" t="n">
-        <v>339.11</v>
+        <v>335.5</v>
       </c>
       <c r="E273" s="18" t="n">
-        <v>0.0132</v>
+        <v>0.0024</v>
       </c>
       <c r="F273" s="18" t="n">
-        <v>0.297</v>
+        <v>0.2832</v>
       </c>
       <c r="G273" s="15" t="n"/>
       <c r="H273" s="21" t="inlineStr">
@@ -20241,7 +20241,7 @@
         <v>320</v>
       </c>
       <c r="M273" s="14" t="n">
-        <v>-0.05635339565332786</v>
+        <v>-0.04619970193740686</v>
       </c>
       <c r="N273" s="12" t="inlineStr">
         <is>
@@ -20252,7 +20252,7 @@
         <v>280</v>
       </c>
       <c r="P273" s="14" t="n">
-        <v>-0.1743092211966619</v>
+        <v>-0.165424739195231</v>
       </c>
       <c r="Q273" s="19" t="inlineStr">
         <is>
@@ -20293,13 +20293,13 @@
         </is>
       </c>
       <c r="D274" s="4" t="n">
-        <v>396.49</v>
+        <v>392.03</v>
       </c>
       <c r="E274" s="22" t="n">
-        <v>-0.0369</v>
+        <v>-0.04769999999999999</v>
       </c>
       <c r="F274" s="22" t="n">
-        <v>-0.11</v>
+        <v>-0.12</v>
       </c>
       <c r="G274" s="6" t="n"/>
       <c r="H274" s="7" t="inlineStr">
@@ -20318,7 +20318,7 @@
         <v>535</v>
       </c>
       <c r="M274" s="5" t="n">
-        <v>0.3493404625589548</v>
+        <v>0.3646914776930338</v>
       </c>
       <c r="N274" s="3" t="inlineStr"/>
       <c r="O274" s="8" t="n"/>
@@ -20362,13 +20362,13 @@
         </is>
       </c>
       <c r="D275" s="13" t="n">
-        <v>6.55</v>
+        <v>6.57</v>
       </c>
       <c r="E275" s="14" t="n">
-        <v>-0.1227</v>
+        <v>-0.1193</v>
       </c>
       <c r="F275" s="14" t="n">
-        <v>-0.0143</v>
+        <v>-0.0105</v>
       </c>
       <c r="G275" s="15" t="n"/>
       <c r="H275" s="21" t="inlineStr">
@@ -20413,13 +20413,13 @@
         </is>
       </c>
       <c r="D276" s="4" t="n">
-        <v>74.20999999999999</v>
+        <v>75.38</v>
       </c>
       <c r="E276" s="5" t="n">
-        <v>0.0789</v>
+        <v>0.0958</v>
       </c>
       <c r="F276" s="5" t="n">
-        <v>0.2291</v>
+        <v>0.2484</v>
       </c>
       <c r="G276" s="6" t="n">
         <v>46322</v>
@@ -20474,13 +20474,13 @@
         </is>
       </c>
       <c r="D277" s="13" t="n">
-        <v>97.77</v>
+        <v>94.72</v>
       </c>
       <c r="E277" s="14" t="n">
-        <v>-0.0663</v>
+        <v>-0.09539999999999998</v>
       </c>
       <c r="F277" s="14" t="n">
-        <v>-0.2287</v>
+        <v>-0.2528</v>
       </c>
       <c r="G277" s="15" t="n"/>
       <c r="H277" s="21" t="inlineStr">
@@ -20525,13 +20525,13 @@
         </is>
       </c>
       <c r="D278" s="4" t="n">
-        <v>209.59</v>
+        <v>204.99</v>
       </c>
       <c r="E278" s="22" t="n">
-        <v>-0.0219</v>
+        <v>-0.0434</v>
       </c>
       <c r="F278" s="5" t="n">
-        <v>0.0461</v>
+        <v>0.0231</v>
       </c>
       <c r="G278" s="6" t="n">
         <v>46330</v>
@@ -20586,13 +20586,13 @@
         </is>
       </c>
       <c r="D279" s="13" t="n">
-        <v>374.58</v>
+        <v>372.06</v>
       </c>
       <c r="E279" s="18" t="n">
-        <v>0.026</v>
+        <v>0.0191</v>
       </c>
       <c r="F279" s="18" t="n">
-        <v>0.0417</v>
+        <v>0.0346</v>
       </c>
       <c r="G279" s="15" t="n">
         <v>46322</v>
@@ -20647,13 +20647,13 @@
         </is>
       </c>
       <c r="D280" s="4" t="n">
-        <v>58.42</v>
-      </c>
-      <c r="E280" s="22" t="n">
-        <v>-0.0003</v>
+        <v>58.78</v>
+      </c>
+      <c r="E280" s="5" t="n">
+        <v>0.0058</v>
       </c>
       <c r="F280" s="5" t="n">
-        <v>0.106</v>
+        <v>0.1128</v>
       </c>
       <c r="G280" s="6" t="n"/>
       <c r="H280" s="7" t="inlineStr">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="D281" s="13" t="n">
-        <v>435.48</v>
+        <v>439</v>
       </c>
       <c r="E281" s="18" t="n">
-        <v>0.0406</v>
+        <v>0.0491</v>
       </c>
       <c r="F281" s="18" t="n">
-        <v>0.0032</v>
+        <v>0.0113</v>
       </c>
       <c r="G281" s="15" t="n">
         <v>46310</v>
@@ -20781,13 +20781,13 @@
         </is>
       </c>
       <c r="D282" s="4" t="n">
-        <v>131.1</v>
-      </c>
-      <c r="E282" s="5" t="n">
-        <v>0.007800000000000001</v>
+        <v>129.35</v>
+      </c>
+      <c r="E282" s="22" t="n">
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F282" s="22" t="n">
-        <v>-0.1048</v>
+        <v>-0.1167</v>
       </c>
       <c r="G282" s="6" t="n"/>
       <c r="H282" s="7" t="inlineStr">
@@ -20832,13 +20832,13 @@
         </is>
       </c>
       <c r="D283" s="13" t="n">
-        <v>223.2</v>
+        <v>225.89</v>
       </c>
       <c r="E283" s="14" t="n">
-        <v>-0.1074</v>
+        <v>-0.09669999999999999</v>
       </c>
       <c r="F283" s="18" t="n">
-        <v>0.0403</v>
+        <v>0.0528</v>
       </c>
       <c r="G283" s="15" t="n">
         <v>46324</v>
@@ -20893,13 +20893,13 @@
         </is>
       </c>
       <c r="D284" s="4" t="n">
-        <v>259.34</v>
+        <v>258.92</v>
       </c>
       <c r="E284" s="22" t="n">
-        <v>-0.07519999999999999</v>
+        <v>-0.0767</v>
       </c>
       <c r="F284" s="22" t="n">
-        <v>-0.1673</v>
+        <v>-0.1687</v>
       </c>
       <c r="G284" s="6" t="n">
         <v>46315</v>
@@ -20928,7 +20928,7 @@
         <v>300</v>
       </c>
       <c r="M284" s="5" t="n">
-        <v>0.1567826019896662</v>
+        <v>0.1586590452649466</v>
       </c>
       <c r="N284" s="3" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         <v>316</v>
       </c>
       <c r="P284" s="5" t="n">
-        <v>0.2184776740957817</v>
+        <v>0.2204541943457438</v>
       </c>
       <c r="Q284" s="9" t="inlineStr">
         <is>
@@ -20996,13 +20996,13 @@
         </is>
       </c>
       <c r="D285" s="13" t="n">
-        <v>348.37</v>
+        <v>347.82</v>
       </c>
       <c r="E285" s="18" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.0916</v>
       </c>
       <c r="F285" s="18" t="n">
-        <v>0.1257</v>
+        <v>0.1239</v>
       </c>
       <c r="G285" s="15" t="n"/>
       <c r="H285" s="21" t="inlineStr">
@@ -21021,7 +21021,7 @@
         <v>335</v>
       </c>
       <c r="M285" s="14" t="n">
-        <v>-0.03837873525274853</v>
+        <v>-0.03685814501753779</v>
       </c>
       <c r="N285" s="12" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>375</v>
       </c>
       <c r="P285" s="18" t="n">
-        <v>0.07644171426931134</v>
+        <v>0.07814386751768158</v>
       </c>
       <c r="Q285" s="19" t="inlineStr">
         <is>
@@ -21073,13 +21073,13 @@
         </is>
       </c>
       <c r="D286" s="4" t="n">
-        <v>41.37</v>
+        <v>42.75</v>
       </c>
       <c r="E286" s="22" t="n">
-        <v>-0.0401</v>
+        <v>-0.008100000000000001</v>
       </c>
       <c r="F286" s="5" t="n">
-        <v>0.3393</v>
+        <v>0.3839</v>
       </c>
       <c r="G286" s="6" t="n"/>
       <c r="H286" s="7" t="inlineStr">
@@ -21124,13 +21124,13 @@
         </is>
       </c>
       <c r="D287" s="13" t="n">
-        <v>6.8</v>
+        <v>6.75</v>
       </c>
       <c r="E287" s="14" t="n">
-        <v>-0.0916</v>
+        <v>-0.09759999999999999</v>
       </c>
       <c r="F287" s="14" t="n">
-        <v>-0.1517</v>
+        <v>-0.1573</v>
       </c>
       <c r="G287" s="15" t="n"/>
       <c r="H287" s="21" t="inlineStr">
@@ -21175,13 +21175,13 @@
         </is>
       </c>
       <c r="D288" s="4" t="n">
-        <v>186.05</v>
+        <v>186.28</v>
       </c>
       <c r="E288" s="5" t="n">
-        <v>0.0101</v>
+        <v>0.0113</v>
       </c>
       <c r="F288" s="5" t="n">
-        <v>0.339</v>
+        <v>0.3406</v>
       </c>
       <c r="G288" s="6" t="n"/>
       <c r="H288" s="7" t="inlineStr">
@@ -21226,13 +21226,13 @@
         </is>
       </c>
       <c r="D289" s="13" t="n">
-        <v>476.61</v>
+        <v>477.3</v>
       </c>
       <c r="E289" s="18" t="n">
-        <v>0.0873</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="F289" s="14" t="n">
-        <v>-0.1819</v>
+        <v>-0.1807</v>
       </c>
       <c r="G289" s="15" t="n">
         <v>46324</v>
@@ -21261,7 +21261,7 @@
         <v>730</v>
       </c>
       <c r="M289" s="18" t="n">
-        <v>0.5316506158074735</v>
+        <v>0.5294364131573434</v>
       </c>
       <c r="N289" s="12" t="inlineStr">
         <is>
@@ -21272,7 +21272,7 @@
         <v>575</v>
       </c>
       <c r="P289" s="18" t="n">
-        <v>0.2064371288894484</v>
+        <v>0.2046930651581814</v>
       </c>
       <c r="Q289" s="19" t="inlineStr">
         <is>
@@ -21313,13 +21313,13 @@
         </is>
       </c>
       <c r="D290" s="4" t="n">
-        <v>28.69</v>
+        <v>28.88</v>
       </c>
       <c r="E290" s="22" t="n">
-        <v>-0.0206</v>
+        <v>-0.0143</v>
       </c>
       <c r="F290" s="22" t="n">
-        <v>-0.1869</v>
+        <v>-0.1816</v>
       </c>
       <c r="G290" s="6" t="n"/>
       <c r="H290" s="7" t="inlineStr">
@@ -21364,13 +21364,13 @@
         </is>
       </c>
       <c r="D291" s="13" t="n">
-        <v>96.29000000000001</v>
+        <v>96.44</v>
       </c>
       <c r="E291" s="14" t="n">
-        <v>-0.1017</v>
+        <v>-0.1004</v>
       </c>
       <c r="F291" s="18" t="n">
-        <v>0.0728</v>
+        <v>0.07440000000000001</v>
       </c>
       <c r="G291" s="15" t="n"/>
       <c r="H291" s="21" t="inlineStr">
@@ -21415,13 +21415,13 @@
         </is>
       </c>
       <c r="D292" s="4" t="n">
-        <v>160.6</v>
+        <v>161.94</v>
       </c>
       <c r="E292" s="22" t="n">
-        <v>-0.091</v>
+        <v>-0.0834</v>
       </c>
       <c r="F292" s="5" t="n">
-        <v>0.1532</v>
+        <v>0.1628</v>
       </c>
       <c r="G292" s="6" t="n"/>
       <c r="H292" s="7" t="inlineStr">
@@ -21466,13 +21466,13 @@
         </is>
       </c>
       <c r="D293" s="13" t="n">
-        <v>302.54</v>
+        <v>297.71</v>
       </c>
       <c r="E293" s="14" t="n">
-        <v>-0.0183</v>
-      </c>
-      <c r="F293" s="18" t="n">
-        <v>0.01</v>
+        <v>-0.034</v>
+      </c>
+      <c r="F293" s="14" t="n">
+        <v>-0.0061</v>
       </c>
       <c r="G293" s="15" t="n"/>
       <c r="H293" s="21" t="inlineStr">
@@ -21517,13 +21517,13 @@
         </is>
       </c>
       <c r="D294" s="4" t="n">
-        <v>93.08</v>
+        <v>91.98999999999999</v>
       </c>
       <c r="E294" s="5" t="n">
-        <v>0.0273</v>
+        <v>0.0152</v>
       </c>
       <c r="F294" s="5" t="n">
-        <v>0.1396</v>
+        <v>0.1262</v>
       </c>
       <c r="G294" s="6" t="n"/>
       <c r="H294" s="7" t="inlineStr">
@@ -21568,13 +21568,13 @@
         </is>
       </c>
       <c r="D295" s="13" t="n">
-        <v>130.62</v>
+        <v>131.32</v>
       </c>
       <c r="E295" s="14" t="n">
-        <v>-0.07719999999999999</v>
+        <v>-0.0723</v>
       </c>
       <c r="F295" s="14" t="n">
-        <v>-0.0301</v>
+        <v>-0.0249</v>
       </c>
       <c r="G295" s="15" t="n"/>
       <c r="H295" s="21" t="inlineStr">
@@ -21593,7 +21593,7 @@
         <v>166</v>
       </c>
       <c r="M295" s="18" t="n">
-        <v>0.2708620425662226</v>
+        <v>0.2640877246420957</v>
       </c>
       <c r="N295" s="12" t="inlineStr"/>
       <c r="O295" s="17" t="n"/>
@@ -21641,13 +21641,13 @@
         </is>
       </c>
       <c r="D296" s="4" t="n">
-        <v>29.88</v>
+        <v>29.57</v>
       </c>
       <c r="E296" s="22" t="n">
-        <v>-0.0231</v>
+        <v>-0.033</v>
       </c>
       <c r="F296" s="5" t="n">
-        <v>0.0291</v>
+        <v>0.0186</v>
       </c>
       <c r="G296" s="6" t="n">
         <v>46317</v>
@@ -21702,13 +21702,13 @@
         </is>
       </c>
       <c r="D297" s="13" t="n">
-        <v>278.03</v>
+        <v>278.11</v>
       </c>
       <c r="E297" s="14" t="n">
-        <v>-0.0224</v>
+        <v>-0.0221</v>
       </c>
       <c r="F297" s="18" t="n">
-        <v>0.0136</v>
+        <v>0.0139</v>
       </c>
       <c r="G297" s="15" t="n">
         <v>46322</v>
@@ -21737,7 +21737,7 @@
         <v>275</v>
       </c>
       <c r="M297" s="14" t="n">
-        <v>-0.01089810452109475</v>
+        <v>-0.0111826255798066</v>
       </c>
       <c r="N297" s="12" t="inlineStr">
         <is>
@@ -21748,7 +21748,7 @@
         <v>312</v>
       </c>
       <c r="P297" s="18" t="n">
-        <v>0.1221810595978852</v>
+        <v>0.1218582575240012</v>
       </c>
       <c r="Q297" s="19" t="inlineStr">
         <is>
@@ -21801,13 +21801,13 @@
         </is>
       </c>
       <c r="D298" s="4" t="n">
-        <v>36.31</v>
+        <v>36.21</v>
       </c>
       <c r="E298" s="22" t="n">
-        <v>-0.0258</v>
+        <v>-0.0284</v>
       </c>
       <c r="F298" s="22" t="n">
-        <v>-0.08810000000000001</v>
+        <v>-0.0907</v>
       </c>
       <c r="G298" s="6" t="n">
         <v>46322</v>
@@ -21866,13 +21866,13 @@
         </is>
       </c>
       <c r="D299" s="13" t="n">
-        <v>77.93000000000001</v>
+        <v>76.62</v>
       </c>
       <c r="E299" s="18" t="n">
-        <v>0.1052</v>
+        <v>0.0867</v>
       </c>
       <c r="F299" s="18" t="n">
-        <v>0.2667</v>
+        <v>0.2454</v>
       </c>
       <c r="G299" s="15" t="n">
         <v>46310</v>
@@ -21927,13 +21927,13 @@
         </is>
       </c>
       <c r="D300" s="4" t="n">
-        <v>472.32</v>
+        <v>468.38</v>
       </c>
       <c r="E300" s="22" t="n">
-        <v>-0.0409</v>
+        <v>-0.0489</v>
       </c>
       <c r="F300" s="22" t="n">
-        <v>-0.1085</v>
+        <v>-0.1159</v>
       </c>
       <c r="G300" s="6" t="n">
         <v>46325</v>
@@ -21962,7 +21962,7 @@
         <v>570</v>
       </c>
       <c r="M300" s="5" t="n">
-        <v>0.2068089430894309</v>
+        <v>0.2169605875571118</v>
       </c>
       <c r="N300" s="3" t="inlineStr">
         <is>
@@ -21973,7 +21973,7 @@
         <v>525</v>
       </c>
       <c r="P300" s="5" t="n">
-        <v>0.1115345528455285</v>
+        <v>0.1208847516973398</v>
       </c>
       <c r="Q300" s="9" t="inlineStr">
         <is>
@@ -22026,13 +22026,13 @@
         </is>
       </c>
       <c r="D301" s="13" t="n">
-        <v>509.28</v>
+        <v>511.98</v>
       </c>
       <c r="E301" s="14" t="n">
-        <v>-0.0733</v>
+        <v>-0.0683</v>
       </c>
       <c r="F301" s="14" t="n">
-        <v>-0.1185</v>
+        <v>-0.1138</v>
       </c>
       <c r="G301" s="15" t="n"/>
       <c r="H301" s="21" t="inlineStr">
@@ -22051,7 +22051,7 @@
         <v>616</v>
       </c>
       <c r="M301" s="18" t="n">
-        <v>0.209550738297204</v>
+        <v>0.2031719989062072</v>
       </c>
       <c r="N301" s="12" t="inlineStr"/>
       <c r="O301" s="17" t="n"/>
@@ -22095,13 +22095,13 @@
         </is>
       </c>
       <c r="D302" s="4" t="n">
-        <v>255.15</v>
+        <v>256.4</v>
       </c>
       <c r="E302" s="22" t="n">
-        <v>-0.0709</v>
+        <v>-0.0663</v>
       </c>
       <c r="F302" s="5" t="n">
-        <v>0.1222</v>
+        <v>0.1277</v>
       </c>
       <c r="G302" s="6" t="n">
         <v>46321</v>
@@ -22130,7 +22130,7 @@
         <v>283</v>
       </c>
       <c r="M302" s="5" t="n">
-        <v>0.1091514795218499</v>
+        <v>0.1037441497659907</v>
       </c>
       <c r="N302" s="3" t="inlineStr"/>
       <c r="O302" s="8" t="n"/>
@@ -22176,13 +22176,13 @@
         </is>
       </c>
       <c r="D303" s="13" t="n">
-        <v>236.6</v>
+        <v>231.99</v>
       </c>
       <c r="E303" s="14" t="n">
-        <v>-0.0713</v>
+        <v>-0.08929999999999999</v>
       </c>
       <c r="F303" s="18" t="n">
-        <v>0.0342</v>
+        <v>0.0141</v>
       </c>
       <c r="G303" s="15" t="n">
         <v>46323</v>
@@ -22211,7 +22211,7 @@
         <v>246</v>
       </c>
       <c r="M303" s="18" t="n">
-        <v>0.03972950126796283</v>
+        <v>0.06039053407474456</v>
       </c>
       <c r="N303" s="12" t="inlineStr"/>
       <c r="O303" s="17" t="n"/>
@@ -22259,13 +22259,13 @@
         </is>
       </c>
       <c r="D304" s="4" t="n">
-        <v>110.51</v>
+        <v>109.72</v>
       </c>
       <c r="E304" s="22" t="n">
-        <v>-0.043</v>
+        <v>-0.0499</v>
       </c>
       <c r="F304" s="22" t="n">
-        <v>-0.0535</v>
+        <v>-0.0603</v>
       </c>
       <c r="G304" s="6" t="n">
         <v>46322</v>
@@ -22294,7 +22294,7 @@
         <v>130</v>
       </c>
       <c r="M304" s="5" t="n">
-        <v>0.1763641299429915</v>
+        <v>0.1848341232227488</v>
       </c>
       <c r="N304" s="3" t="inlineStr">
         <is>
@@ -22305,7 +22305,7 @@
         <v>128</v>
       </c>
       <c r="P304" s="5" t="n">
-        <v>0.1582662202515609</v>
+        <v>0.1666059059423989</v>
       </c>
       <c r="Q304" s="9" t="inlineStr">
         <is>
@@ -22354,13 +22354,13 @@
         </is>
       </c>
       <c r="D305" s="13" t="n">
-        <v>103.68</v>
+        <v>102.27</v>
       </c>
       <c r="E305" s="14" t="n">
-        <v>-0.1057</v>
+        <v>-0.1178</v>
       </c>
       <c r="F305" s="14" t="n">
-        <v>-0.0136</v>
+        <v>-0.0269</v>
       </c>
       <c r="G305" s="15" t="n">
         <v>46302</v>
@@ -22389,7 +22389,7 @@
         <v>135</v>
       </c>
       <c r="M305" s="18" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.3200352009386918</v>
       </c>
       <c r="N305" s="12" t="inlineStr">
         <is>
@@ -22400,7 +22400,7 @@
         <v>125</v>
       </c>
       <c r="P305" s="18" t="n">
-        <v>0.2056327160493826</v>
+        <v>0.2222548156839738</v>
       </c>
       <c r="Q305" s="19" t="inlineStr"/>
       <c r="R305" s="17" t="n"/>
@@ -22435,13 +22435,13 @@
         </is>
       </c>
       <c r="D306" s="4" t="n">
-        <v>328.37</v>
+        <v>326.09</v>
       </c>
       <c r="E306" s="22" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.101</v>
       </c>
       <c r="F306" s="22" t="n">
-        <v>-0.0168</v>
+        <v>-0.0237</v>
       </c>
       <c r="G306" s="6" t="n">
         <v>46322</v>
@@ -22470,7 +22470,7 @@
         <v>350</v>
       </c>
       <c r="M306" s="5" t="n">
-        <v>0.06587081645704539</v>
+        <v>0.07332331564905402</v>
       </c>
       <c r="N306" s="3" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         <v>400</v>
       </c>
       <c r="P306" s="5" t="n">
-        <v>0.218138075950909</v>
+        <v>0.2266552178846332</v>
       </c>
       <c r="Q306" s="9" t="inlineStr">
         <is>
@@ -22522,13 +22522,13 @@
         </is>
       </c>
       <c r="D307" s="13" t="n">
-        <v>99.54000000000001</v>
+        <v>101.14</v>
       </c>
       <c r="E307" s="18" t="n">
-        <v>0.0159</v>
+        <v>0.0323</v>
       </c>
       <c r="F307" s="18" t="n">
-        <v>0.2547</v>
+        <v>0.2749</v>
       </c>
       <c r="G307" s="15" t="n"/>
       <c r="H307" s="21" t="inlineStr">
@@ -22569,13 +22569,13 @@
         </is>
       </c>
       <c r="D308" s="4" t="n">
-        <v>51.11</v>
+        <v>50.47</v>
       </c>
       <c r="E308" s="22" t="n">
-        <v>-0.0968</v>
+        <v>-0.1081</v>
       </c>
       <c r="F308" s="22" t="n">
-        <v>-0.2745</v>
+        <v>-0.2836</v>
       </c>
       <c r="G308" s="6" t="n">
         <v>46267</v>
@@ -22630,13 +22630,13 @@
         </is>
       </c>
       <c r="D309" s="13" t="n">
-        <v>73.48</v>
+        <v>72.78</v>
       </c>
       <c r="E309" s="14" t="n">
-        <v>-0.0089</v>
+        <v>-0.0183</v>
       </c>
       <c r="F309" s="14" t="n">
-        <v>-0.0573</v>
+        <v>-0.0663</v>
       </c>
       <c r="G309" s="15" t="n">
         <v>46315</v>
@@ -22665,14 +22665,14 @@
         <v>83</v>
       </c>
       <c r="M309" s="18" t="n">
-        <v>0.1295590636908002</v>
+        <v>0.1404231931849409</v>
       </c>
       <c r="N309" s="12" t="inlineStr"/>
       <c r="O309" s="17" t="n">
         <v>87</v>
       </c>
       <c r="P309" s="18" t="n">
-        <v>0.1839956450734893</v>
+        <v>0.1953833470733718</v>
       </c>
       <c r="Q309" s="19" t="inlineStr"/>
       <c r="R309" s="17" t="n"/>
@@ -22707,13 +22707,13 @@
         </is>
       </c>
       <c r="D310" s="4" t="n">
-        <v>178.74</v>
+        <v>175.73</v>
       </c>
       <c r="E310" s="5" t="n">
-        <v>0.05690000000000001</v>
+        <v>0.0391</v>
       </c>
       <c r="F310" s="5" t="n">
-        <v>0.0602</v>
+        <v>0.0424</v>
       </c>
       <c r="G310" s="6" t="n">
         <v>46322</v>
@@ -22742,7 +22742,7 @@
         <v>200</v>
       </c>
       <c r="M310" s="5" t="n">
-        <v>0.1189437171310282</v>
+        <v>0.1381095999544757</v>
       </c>
       <c r="N310" s="3" t="inlineStr"/>
       <c r="O310" s="8" t="n"/>
@@ -22790,13 +22790,13 @@
         </is>
       </c>
       <c r="D311" s="13" t="n">
-        <v>144.32</v>
-      </c>
-      <c r="E311" s="18" t="n">
-        <v>0.0026</v>
+        <v>142.26</v>
+      </c>
+      <c r="E311" s="14" t="n">
+        <v>-0.0117</v>
       </c>
       <c r="F311" s="18" t="n">
-        <v>0.0343</v>
+        <v>0.0196</v>
       </c>
       <c r="G311" s="15" t="n">
         <v>46317</v>
@@ -22855,13 +22855,13 @@
         </is>
       </c>
       <c r="D312" s="4" t="n">
-        <v>191.27</v>
+        <v>189.5</v>
       </c>
       <c r="E312" s="22" t="n">
-        <v>-0.0002</v>
+        <v>-0.009399999999999999</v>
       </c>
       <c r="F312" s="5" t="n">
-        <v>0.0602</v>
+        <v>0.0504</v>
       </c>
       <c r="G312" s="6" t="n">
         <v>46317</v>
@@ -22890,7 +22890,7 @@
         <v>220</v>
       </c>
       <c r="M312" s="5" t="n">
-        <v>0.1502065143514403</v>
+        <v>0.1609498680738786</v>
       </c>
       <c r="N312" s="3" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>230</v>
       </c>
       <c r="P312" s="5" t="n">
-        <v>0.2024886286401421</v>
+        <v>0.2137203166226913</v>
       </c>
       <c r="Q312" s="9" t="inlineStr">
         <is>
@@ -22942,13 +22942,13 @@
         </is>
       </c>
       <c r="D313" s="13" t="n">
-        <v>1047.19</v>
-      </c>
-      <c r="E313" s="18" t="n">
-        <v>0.0037</v>
+        <v>1041.21</v>
+      </c>
+      <c r="E313" s="14" t="n">
+        <v>-0.0021</v>
       </c>
       <c r="F313" s="14" t="n">
-        <v>-0.0038</v>
+        <v>-0.0095</v>
       </c>
       <c r="G313" s="15" t="n"/>
       <c r="H313" s="21" t="inlineStr">
@@ -22967,7 +22967,7 @@
         <v>1200</v>
       </c>
       <c r="M313" s="18" t="n">
-        <v>0.1459238533599442</v>
+        <v>0.152505258305241</v>
       </c>
       <c r="N313" s="12" t="inlineStr">
         <is>
@@ -22978,7 +22978,7 @@
         <v>1240</v>
       </c>
       <c r="P313" s="18" t="n">
-        <v>0.184121315138609</v>
+        <v>0.190922100248749</v>
       </c>
       <c r="Q313" s="19" t="inlineStr">
         <is>
@@ -23023,13 +23023,13 @@
         </is>
       </c>
       <c r="D314" s="4" t="n">
-        <v>117.11</v>
-      </c>
-      <c r="E314" s="22" t="n">
-        <v>-0.0001</v>
+        <v>117.25</v>
+      </c>
+      <c r="E314" s="5" t="n">
+        <v>0.001</v>
       </c>
       <c r="F314" s="22" t="n">
-        <v>-0.0316</v>
+        <v>-0.0305</v>
       </c>
       <c r="G314" s="6" t="n">
         <v>46325</v>
@@ -23058,7 +23058,7 @@
         <v>129</v>
       </c>
       <c r="M314" s="5" t="n">
-        <v>0.1015284774997865</v>
+        <v>0.1002132196162047</v>
       </c>
       <c r="N314" s="3" t="inlineStr">
         <is>
@@ -23069,7 +23069,7 @@
         <v>122</v>
       </c>
       <c r="P314" s="5" t="n">
-        <v>0.04175561437964308</v>
+        <v>0.04051172707889126</v>
       </c>
       <c r="Q314" s="9" t="inlineStr">
         <is>
@@ -23110,13 +23110,13 @@
         </is>
       </c>
       <c r="D315" s="13" t="n">
-        <v>61.64</v>
+        <v>61.02</v>
       </c>
       <c r="E315" s="14" t="n">
-        <v>-0.004</v>
+        <v>-0.0141</v>
       </c>
       <c r="F315" s="14" t="n">
-        <v>-0.0264</v>
+        <v>-0.0362</v>
       </c>
       <c r="G315" s="15" t="n">
         <v>46328</v>
@@ -23145,14 +23145,14 @@
         <v>65</v>
       </c>
       <c r="M315" s="18" t="n">
-        <v>0.05451005840363399</v>
+        <v>0.06522451655195012</v>
       </c>
       <c r="N315" s="12" t="inlineStr"/>
       <c r="O315" s="17" t="n">
         <v>67</v>
       </c>
       <c r="P315" s="18" t="n">
-        <v>0.08695652173913042</v>
+        <v>0.09800065552277935</v>
       </c>
       <c r="Q315" s="19" t="inlineStr">
         <is>
@@ -23193,13 +23193,13 @@
         </is>
       </c>
       <c r="D316" s="4" t="n">
-        <v>138.02</v>
+        <v>138.48</v>
       </c>
       <c r="E316" s="22" t="n">
-        <v>-0.0053</v>
+        <v>-0.002</v>
       </c>
       <c r="F316" s="22" t="n">
-        <v>-0.0202</v>
+        <v>-0.017</v>
       </c>
       <c r="G316" s="6" t="n">
         <v>46310</v>
@@ -23228,7 +23228,7 @@
         <v>167</v>
       </c>
       <c r="M316" s="5" t="n">
-        <v>0.2099695696275901</v>
+        <v>0.2059503177354131</v>
       </c>
       <c r="N316" s="3" t="inlineStr"/>
       <c r="O316" s="8" t="n"/>
@@ -23272,13 +23272,13 @@
         </is>
       </c>
       <c r="D317" s="13" t="n">
-        <v>303.24</v>
+        <v>301.6</v>
       </c>
       <c r="E317" s="14" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.07400000000000001</v>
       </c>
       <c r="F317" s="14" t="n">
-        <v>-0.05400000000000001</v>
+        <v>-0.0591</v>
       </c>
       <c r="G317" s="15" t="n"/>
       <c r="H317" s="21" t="inlineStr">
@@ -23304,7 +23304,7 @@
         <v>316</v>
       </c>
       <c r="P317" s="18" t="n">
-        <v>0.04207888141406144</v>
+        <v>0.0477453580901856</v>
       </c>
       <c r="Q317" s="19" t="inlineStr">
         <is>
@@ -23345,13 +23345,13 @@
         </is>
       </c>
       <c r="D318" s="4" t="n">
-        <v>210.33</v>
+        <v>211.88</v>
       </c>
       <c r="E318" s="22" t="n">
-        <v>-0.0463</v>
+        <v>-0.0393</v>
       </c>
       <c r="F318" s="22" t="n">
-        <v>-0.0386</v>
+        <v>-0.0315</v>
       </c>
       <c r="G318" s="6" t="n">
         <v>46328</v>
@@ -23387,7 +23387,7 @@
         <v>215</v>
       </c>
       <c r="P318" s="5" t="n">
-        <v>0.02220320448818517</v>
+        <v>0.01472531621672647</v>
       </c>
       <c r="Q318" s="9" t="inlineStr">
         <is>
@@ -23428,13 +23428,13 @@
         </is>
       </c>
       <c r="D319" s="13" t="n">
-        <v>120.32</v>
-      </c>
-      <c r="E319" s="18" t="n">
-        <v>0.0147</v>
-      </c>
-      <c r="F319" s="18" t="n">
-        <v>0.0121</v>
+        <v>117.65</v>
+      </c>
+      <c r="E319" s="14" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F319" s="14" t="n">
+        <v>-0.0103</v>
       </c>
       <c r="G319" s="15" t="n"/>
       <c r="H319" s="21" t="inlineStr">
@@ -23453,7 +23453,7 @@
         <v>142</v>
       </c>
       <c r="M319" s="18" t="n">
-        <v>0.180186170212766</v>
+        <v>0.2069698257543561</v>
       </c>
       <c r="N319" s="12" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>137</v>
       </c>
       <c r="P319" s="18" t="n">
-        <v>0.1386303191489362</v>
+        <v>0.1644708882277942</v>
       </c>
       <c r="Q319" s="19" t="inlineStr">
         <is>
@@ -23513,13 +23513,13 @@
         </is>
       </c>
       <c r="D320" s="4" t="n">
-        <v>239.91</v>
+        <v>237.25</v>
       </c>
       <c r="E320" s="5" t="n">
-        <v>0.0207</v>
+        <v>0.009399999999999999</v>
       </c>
       <c r="F320" s="5" t="n">
-        <v>0.0359</v>
+        <v>0.0244</v>
       </c>
       <c r="G320" s="6" t="n">
         <v>46321</v>
@@ -23548,7 +23548,7 @@
         <v>237</v>
       </c>
       <c r="M320" s="22" t="n">
-        <v>-0.01212954858071776</v>
+        <v>-0.001053740779768177</v>
       </c>
       <c r="N320" s="3" t="inlineStr">
         <is>
@@ -23559,7 +23559,7 @@
         <v>236</v>
       </c>
       <c r="P320" s="22" t="n">
-        <v>-0.01629777833354173</v>
+        <v>-0.005268703898840885</v>
       </c>
       <c r="Q320" s="9" t="inlineStr">
         <is>
@@ -23600,13 +23600,13 @@
         </is>
       </c>
       <c r="D321" s="13" t="n">
-        <v>169</v>
+        <v>168.07</v>
       </c>
       <c r="E321" s="18" t="n">
-        <v>0.0064</v>
+        <v>0.0009</v>
       </c>
       <c r="F321" s="14" t="n">
-        <v>-0.0409</v>
+        <v>-0.0461</v>
       </c>
       <c r="G321" s="15" t="n"/>
       <c r="H321" s="21" t="inlineStr">
@@ -23625,7 +23625,7 @@
         <v>200</v>
       </c>
       <c r="M321" s="18" t="n">
-        <v>0.1834319526627219</v>
+        <v>0.1899803653239722</v>
       </c>
       <c r="N321" s="12" t="inlineStr"/>
       <c r="O321" s="17" t="n"/>
@@ -23669,13 +23669,13 @@
         </is>
       </c>
       <c r="D322" s="4" t="n">
-        <v>141.71</v>
+        <v>140.38</v>
       </c>
       <c r="E322" s="5" t="n">
-        <v>0.0463</v>
+        <v>0.0364</v>
       </c>
       <c r="F322" s="5" t="n">
-        <v>0.08439999999999999</v>
+        <v>0.0741</v>
       </c>
       <c r="G322" s="6" t="n"/>
       <c r="H322" s="7" t="inlineStr">
@@ -23694,7 +23694,7 @@
         <v>131</v>
       </c>
       <c r="M322" s="22" t="n">
-        <v>-0.07557688236539417</v>
+        <v>-0.06681863513320983</v>
       </c>
       <c r="N322" s="3" t="inlineStr"/>
       <c r="O322" s="8" t="n"/>
@@ -23738,13 +23738,13 @@
         </is>
       </c>
       <c r="D323" s="13" t="n">
-        <v>32.95</v>
+        <v>32.56</v>
       </c>
       <c r="E323" s="14" t="n">
-        <v>-0.008100000000000001</v>
+        <v>-0.0199</v>
       </c>
       <c r="F323" s="14" t="n">
-        <v>-0.0605</v>
+        <v>-0.0716</v>
       </c>
       <c r="G323" s="15" t="n"/>
       <c r="H323" s="21" t="inlineStr">
@@ -23807,13 +23807,13 @@
         </is>
       </c>
       <c r="D324" s="4" t="n">
-        <v>37.01</v>
+        <v>37.26</v>
       </c>
       <c r="E324" s="22" t="n">
-        <v>-0.0255</v>
+        <v>-0.019</v>
       </c>
       <c r="F324" s="22" t="n">
-        <v>-0.017</v>
+        <v>-0.0104</v>
       </c>
       <c r="G324" s="6" t="n"/>
       <c r="H324" s="7" t="inlineStr">
@@ -23858,13 +23858,13 @@
         </is>
       </c>
       <c r="D325" s="13" t="n">
-        <v>303.73</v>
+        <v>299.05</v>
       </c>
       <c r="E325" s="18" t="n">
-        <v>0.1232</v>
+        <v>0.1058</v>
       </c>
       <c r="F325" s="18" t="n">
-        <v>0.2083</v>
+        <v>0.1896</v>
       </c>
       <c r="G325" s="15" t="n"/>
       <c r="H325" s="21" t="inlineStr">
@@ -23883,7 +23883,7 @@
         <v>384</v>
       </c>
       <c r="M325" s="18" t="n">
-        <v>0.2642807756889342</v>
+        <v>0.2840662096639358</v>
       </c>
       <c r="N325" s="12" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>380</v>
       </c>
       <c r="P325" s="18" t="n">
-        <v>0.2511111842755078</v>
+        <v>0.2706905199799364</v>
       </c>
       <c r="Q325" s="19" t="inlineStr"/>
       <c r="R325" s="17" t="n"/>
@@ -23937,13 +23937,13 @@
         </is>
       </c>
       <c r="D326" s="4" t="n">
-        <v>69.31</v>
-      </c>
-      <c r="E326" s="5" t="n">
-        <v>0.0036</v>
+        <v>68.79000000000001</v>
+      </c>
+      <c r="E326" s="22" t="n">
+        <v>-0.0039</v>
       </c>
       <c r="F326" s="22" t="n">
-        <v>-0.0808</v>
+        <v>-0.0877</v>
       </c>
       <c r="G326" s="6" t="n">
         <v>46324</v>
@@ -23972,7 +23972,7 @@
         <v>79</v>
       </c>
       <c r="M326" s="5" t="n">
-        <v>0.1398066657048045</v>
+        <v>0.1484227358627707</v>
       </c>
       <c r="N326" s="3" t="inlineStr"/>
       <c r="O326" s="8" t="n"/>
@@ -24024,13 +24024,13 @@
         </is>
       </c>
       <c r="D327" s="13" t="n">
-        <v>121.37</v>
+        <v>121.24</v>
       </c>
       <c r="E327" s="18" t="n">
-        <v>0.0015</v>
+        <v>0.0004</v>
       </c>
       <c r="F327" s="14" t="n">
-        <v>-0.0328</v>
+        <v>-0.0338</v>
       </c>
       <c r="G327" s="15" t="n"/>
       <c r="H327" s="21" t="inlineStr">
@@ -24049,7 +24049,7 @@
         <v>136</v>
       </c>
       <c r="M327" s="18" t="n">
-        <v>0.1205404960039548</v>
+        <v>0.1217419993401518</v>
       </c>
       <c r="N327" s="12" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>140</v>
       </c>
       <c r="P327" s="18" t="n">
-        <v>0.1534975694158358</v>
+        <v>0.1547344110854504</v>
       </c>
       <c r="Q327" s="19" t="inlineStr">
         <is>
@@ -24101,13 +24101,13 @@
         </is>
       </c>
       <c r="D328" s="4" t="n">
-        <v>108.87</v>
+        <v>108.53</v>
       </c>
       <c r="E328" s="5" t="n">
-        <v>0.0305</v>
+        <v>0.0273</v>
       </c>
       <c r="F328" s="22" t="n">
-        <v>-0.0537</v>
+        <v>-0.0567</v>
       </c>
       <c r="G328" s="6" t="n"/>
       <c r="H328" s="7" t="inlineStr">
@@ -24126,7 +24126,7 @@
         <v>131</v>
       </c>
       <c r="M328" s="5" t="n">
-        <v>0.2032699549921925</v>
+        <v>0.2070395282410393</v>
       </c>
       <c r="N328" s="3" t="inlineStr">
         <is>
@@ -24137,7 +24137,7 @@
         <v>121</v>
       </c>
       <c r="P328" s="5" t="n">
-        <v>0.1114172866721778</v>
+        <v>0.1148991062379066</v>
       </c>
       <c r="Q328" s="9" t="inlineStr">
         <is>
@@ -24182,13 +24182,13 @@
         </is>
       </c>
       <c r="D329" s="13" t="n">
-        <v>84.31999999999999</v>
+        <v>83.83</v>
       </c>
       <c r="E329" s="14" t="n">
-        <v>-0.004500000000000001</v>
+        <v>-0.0103</v>
       </c>
       <c r="F329" s="14" t="n">
-        <v>-0.0414</v>
+        <v>-0.047</v>
       </c>
       <c r="G329" s="15" t="n">
         <v>46322</v>
@@ -24224,7 +24224,7 @@
         <v>107</v>
       </c>
       <c r="P329" s="18" t="n">
-        <v>0.2689753320683113</v>
+        <v>0.276392699510915</v>
       </c>
       <c r="Q329" s="19" t="inlineStr">
         <is>
@@ -24273,13 +24273,13 @@
         </is>
       </c>
       <c r="D330" s="4" t="n">
-        <v>53.99</v>
+        <v>54</v>
       </c>
       <c r="E330" s="5" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.006</v>
       </c>
       <c r="F330" s="22" t="n">
-        <v>-0.0751</v>
+        <v>-0.07490000000000001</v>
       </c>
       <c r="G330" s="6" t="n"/>
       <c r="H330" s="7" t="inlineStr">
@@ -24298,7 +24298,7 @@
         <v>63</v>
       </c>
       <c r="M330" s="5" t="n">
-        <v>0.1668827560659381</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="N330" s="3" t="inlineStr"/>
       <c r="O330" s="8" t="n"/>
@@ -24342,13 +24342,13 @@
         </is>
       </c>
       <c r="D331" s="13" t="n">
-        <v>44.12</v>
+        <v>43.31</v>
       </c>
       <c r="E331" s="14" t="n">
-        <v>-0.0083</v>
+        <v>-0.0265</v>
       </c>
       <c r="F331" s="14" t="n">
-        <v>-0.0968</v>
+        <v>-0.1134</v>
       </c>
       <c r="G331" s="15" t="n"/>
       <c r="H331" s="21" t="inlineStr">
@@ -24393,13 +24393,13 @@
         </is>
       </c>
       <c r="D332" s="4" t="n">
-        <v>10.89</v>
+        <v>11.18</v>
       </c>
       <c r="E332" s="5" t="n">
-        <v>0.1857</v>
+        <v>0.2179</v>
       </c>
       <c r="F332" s="5" t="n">
-        <v>0.2041</v>
+        <v>0.2367</v>
       </c>
       <c r="G332" s="6" t="n"/>
       <c r="H332" s="7" t="inlineStr">
@@ -24444,13 +24444,13 @@
         </is>
       </c>
       <c r="D333" s="13" t="n">
-        <v>89.2</v>
+        <v>88.98999999999999</v>
       </c>
       <c r="E333" s="14" t="n">
-        <v>-0.0234</v>
+        <v>-0.0257</v>
       </c>
       <c r="F333" s="14" t="n">
-        <v>-0.067</v>
+        <v>-0.0692</v>
       </c>
       <c r="G333" s="15" t="n">
         <v>46324</v>
@@ -24479,7 +24479,7 @@
         <v>99</v>
       </c>
       <c r="M333" s="18" t="n">
-        <v>0.1098654708520179</v>
+        <v>0.1124845488257108</v>
       </c>
       <c r="N333" s="12" t="inlineStr">
         <is>
@@ -24490,7 +24490,7 @@
         <v>112</v>
       </c>
       <c r="P333" s="18" t="n">
-        <v>0.2556053811659192</v>
+        <v>0.258568378469491</v>
       </c>
       <c r="Q333" s="19" t="inlineStr">
         <is>
@@ -24531,13 +24531,13 @@
         </is>
       </c>
       <c r="D334" s="4" t="n">
-        <v>107.24</v>
+        <v>107.06</v>
       </c>
       <c r="E334" s="5" t="n">
-        <v>0.0106</v>
+        <v>0.0089</v>
       </c>
       <c r="F334" s="22" t="n">
-        <v>-0.0672</v>
+        <v>-0.0687</v>
       </c>
       <c r="G334" s="6" t="n">
         <v>46324</v>
@@ -24566,7 +24566,7 @@
         <v>127</v>
       </c>
       <c r="M334" s="5" t="n">
-        <v>0.1842596046251399</v>
+        <v>0.1862507005417523</v>
       </c>
       <c r="N334" s="3" t="inlineStr"/>
       <c r="O334" s="8" t="n"/>
@@ -32738,7 +32738,7 @@
     <row r="2">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>Data as of September 08, 2026 at 14:47 UTC</t>
+          <t>Data as of September 08, 2026 at 20:21 UTC</t>
         </is>
       </c>
     </row>

--- a/earnings-data.xlsx
+++ b/earnings-data.xlsx
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>104.46</v>
+        <v>104.18</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.0124</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.0924</v>
+        <v>0.0895</v>
       </c>
       <c r="G2" s="6" t="n"/>
       <c r="H2" s="7" t="inlineStr">
@@ -868,7 +868,7 @@
         <v>125</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>0.1966302891058779</v>
+        <v>0.1998464196582837</v>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         <v>144</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>0.3785180930499714</v>
+        <v>0.3822230754463428</v>
       </c>
       <c r="Q2" s="9" t="inlineStr">
         <is>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="D3" s="13" t="n">
-        <v>330.23</v>
+        <v>330.65</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>-0.07629999999999999</v>
+        <v>-0.07519999999999999</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.07429999999999999</v>
       </c>
       <c r="G3" s="15" t="n">
         <v>46322</v>
@@ -963,7 +963,7 @@
         <v>438</v>
       </c>
       <c r="M3" s="18" t="n">
-        <v>0.3263483026981194</v>
+        <v>0.3246635415091487</v>
       </c>
       <c r="N3" s="12" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>420</v>
       </c>
       <c r="P3" s="18" t="n">
-        <v>0.2718408382036762</v>
+        <v>0.270225313775896</v>
       </c>
       <c r="Q3" s="19" t="inlineStr">
         <is>
@@ -1019,13 +1019,13 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>650.85</v>
+        <v>653.6900000000001</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.094</v>
+        <v>0.09880000000000001</v>
       </c>
       <c r="F4" s="22" t="n">
-        <v>-0.0274</v>
+        <v>-0.0232</v>
       </c>
       <c r="G4" s="6" t="n"/>
       <c r="H4" s="7" t="inlineStr">
@@ -1044,7 +1044,7 @@
         <v>835</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>0.2829376968579549</v>
+        <v>0.2773638880815064</v>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>930</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>0.4289006683567642</v>
+        <v>0.4226927136716179</v>
       </c>
       <c r="Q4" s="9" t="inlineStr">
         <is>
@@ -1104,13 +1104,13 @@
         </is>
       </c>
       <c r="D5" s="13" t="n">
-        <v>41.31</v>
+        <v>41.43</v>
       </c>
       <c r="E5" s="18" t="n">
-        <v>0.1248</v>
+        <v>0.128</v>
       </c>
       <c r="F5" s="18" t="n">
-        <v>0.0634</v>
+        <v>0.0664</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>46329</v>
@@ -1165,13 +1165,13 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>76.48</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>0.0025</v>
+        <v>76.03</v>
+      </c>
+      <c r="E6" s="22" t="n">
+        <v>-0.0034</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.0424</v>
+        <v>0.0363</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>46315</v>
@@ -1200,7 +1200,7 @@
         <v>80</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>0.04602510460251041</v>
+        <v>0.05221623043535445</v>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>100</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>0.307531380753138</v>
+        <v>0.315270288044193</v>
       </c>
       <c r="Q6" s="9" t="inlineStr">
         <is>
@@ -1252,13 +1252,13 @@
         </is>
       </c>
       <c r="D7" s="13" t="n">
-        <v>78.43000000000001</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>-0.07339999999999999</v>
+        <v>-0.0757</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>-0.04269999999999999</v>
+        <v>-0.045</v>
       </c>
       <c r="G7" s="15" t="n">
         <v>46315</v>
@@ -1287,7 +1287,7 @@
         <v>91</v>
       </c>
       <c r="M7" s="18" t="n">
-        <v>0.1602703047303327</v>
+        <v>0.1630879345603273</v>
       </c>
       <c r="N7" s="12" t="inlineStr"/>
       <c r="O7" s="17" t="n"/>
@@ -1331,13 +1331,13 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>531.83</v>
+        <v>523.01</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.0391</v>
+        <v>0.0219</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.1085</v>
+        <v>0.0901</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>46329</v>
@@ -1366,7 +1366,7 @@
         <v>569.9299999999999</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>0.07163943365361095</v>
+        <v>0.08971147779201155</v>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>648.04</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>0.2185096741439932</v>
+        <v>0.2390585266056098</v>
       </c>
       <c r="Q8" s="9" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         </is>
       </c>
       <c r="D9" s="13" t="n">
-        <v>192.08</v>
+        <v>191.09</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>0.014</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>0.0416</v>
+        <v>0.0363</v>
       </c>
       <c r="G9" s="15" t="n"/>
       <c r="H9" s="21" t="inlineStr">
@@ -1477,13 +1477,13 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>177.96</v>
+        <v>177.34</v>
       </c>
       <c r="E10" s="22" t="n">
-        <v>-0.0014</v>
+        <v>-0.0048</v>
       </c>
       <c r="F10" s="22" t="n">
-        <v>-0.0515</v>
+        <v>-0.0547</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>46317</v>
@@ -1512,7 +1512,7 @@
         <v>170</v>
       </c>
       <c r="M10" s="22" t="n">
-        <v>-0.04472915261856601</v>
+        <v>-0.04138942145032144</v>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>270</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>0.5171948752528658</v>
+        <v>0.5224991541671365</v>
       </c>
       <c r="Q10" s="9" t="inlineStr">
         <is>
@@ -1564,13 +1564,13 @@
         </is>
       </c>
       <c r="D11" s="13" t="n">
-        <v>49.44</v>
+        <v>49.76</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>0.0512</v>
+        <v>0.0579</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>0.1738</v>
+        <v>0.1813</v>
       </c>
       <c r="G11" s="15" t="n">
         <v>46316</v>
@@ -1599,7 +1599,7 @@
         <v>43</v>
       </c>
       <c r="M11" s="14" t="n">
-        <v>-0.1302588996763754</v>
+        <v>-0.1358520900321543</v>
       </c>
       <c r="N11" s="12" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>50</v>
       </c>
       <c r="P11" s="18" t="n">
-        <v>0.01132686084142399</v>
+        <v>0.00482315112540197</v>
       </c>
       <c r="Q11" s="19" t="inlineStr">
         <is>
@@ -1655,13 +1655,13 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>169.92</v>
+        <v>169.63</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>-0.08</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.1433</v>
+        <v>0.1414</v>
       </c>
       <c r="G12" s="6" t="n"/>
       <c r="H12" s="7" t="inlineStr">
@@ -1680,7 +1680,7 @@
         <v>181</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>0.06520715630885131</v>
+        <v>0.06702823792961153</v>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>155</v>
       </c>
       <c r="P12" s="22" t="n">
-        <v>-0.08780602636534833</v>
+        <v>-0.08624653657961442</v>
       </c>
       <c r="Q12" s="9" t="inlineStr">
         <is>
@@ -1732,13 +1732,13 @@
         </is>
       </c>
       <c r="D13" s="13" t="n">
-        <v>252.58</v>
+        <v>252.4</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>-0.0917</v>
+        <v>-0.0924</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>0.0295</v>
+        <v>0.0288</v>
       </c>
       <c r="G13" s="15" t="n">
         <v>46324</v>
@@ -1767,7 +1767,7 @@
         <v>322</v>
       </c>
       <c r="M13" s="18" t="n">
-        <v>0.2748436139045055</v>
+        <v>0.2757527733755943</v>
       </c>
       <c r="N13" s="12" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>285</v>
       </c>
       <c r="P13" s="18" t="n">
-        <v>0.12835537255523</v>
+        <v>0.1291600633914421</v>
       </c>
       <c r="Q13" s="19" t="inlineStr">
         <is>
@@ -1831,13 +1831,13 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2900.27</v>
+        <v>2910.28</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>-0.0547</v>
+        <v>-0.05139999999999999</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>-0.0561</v>
+        <v>-0.0528</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>46287</v>
@@ -1866,7 +1866,7 @@
         <v>4150</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>0.430901260917087</v>
+        <v>0.4259796308258998</v>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>3700</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>0.2757432928658367</v>
+        <v>0.2713553335074287</v>
       </c>
       <c r="Q14" s="9" t="inlineStr">
         <is>
@@ -1918,13 +1918,13 @@
         </is>
       </c>
       <c r="D15" s="13" t="n">
-        <v>90.08</v>
+        <v>88</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>0.08789999999999999</v>
+        <v>0.06280000000000001</v>
       </c>
       <c r="G15" s="15" t="n"/>
       <c r="H15" s="21" t="inlineStr">
@@ -1943,7 +1943,7 @@
         <v>65</v>
       </c>
       <c r="M15" s="14" t="n">
-        <v>-0.2784191829484902</v>
+        <v>-0.2613636363636364</v>
       </c>
       <c r="N15" s="12" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>85</v>
       </c>
       <c r="P15" s="14" t="n">
-        <v>-0.05639431616341029</v>
+        <v>-0.03409090909090909</v>
       </c>
       <c r="Q15" s="19" t="inlineStr"/>
       <c r="R15" s="17" t="n"/>
@@ -1989,13 +1989,13 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>172.29</v>
+        <v>173.43</v>
       </c>
       <c r="E16" s="22" t="n">
-        <v>-0.1907</v>
+        <v>-0.1853</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>-0.0342</v>
+        <v>-0.0278</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>46322</v>
@@ -2024,7 +2024,7 @@
         <v>214</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>0.2420918219281445</v>
+        <v>0.2339272328893501</v>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>245</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>0.4220210110859598</v>
+        <v>0.4126737012050971</v>
       </c>
       <c r="Q16" s="9" t="inlineStr">
         <is>
@@ -2084,13 +2084,13 @@
         </is>
       </c>
       <c r="D17" s="13" t="n">
-        <v>243.89</v>
+        <v>239.24</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>-0.3435</v>
+        <v>-0.356</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>-0.2558</v>
+        <v>-0.27</v>
       </c>
       <c r="G17" s="15" t="n"/>
       <c r="H17" s="21" t="inlineStr">
@@ -2109,7 +2109,7 @@
         <v>375</v>
       </c>
       <c r="M17" s="18" t="n">
-        <v>0.5375784164992415</v>
+        <v>0.5674636348436716</v>
       </c>
       <c r="N17" s="12" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>375</v>
       </c>
       <c r="P17" s="18" t="n">
-        <v>0.5375784164992415</v>
+        <v>0.5674636348436716</v>
       </c>
       <c r="Q17" s="19" t="inlineStr"/>
       <c r="R17" s="17" t="n"/>
@@ -2159,13 +2159,13 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>36.19</v>
+        <v>36.03</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.1262</v>
+        <v>0.1212</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.0268</v>
+        <v>0.0223</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>46323</v>
@@ -2194,7 +2194,7 @@
         <v>45</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>0.2434374136501797</v>
+        <v>0.2489592006661115</v>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>45</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>0.2434374136501797</v>
+        <v>0.2489592006661115</v>
       </c>
       <c r="Q18" s="9" t="inlineStr">
         <is>
@@ -2246,13 +2246,13 @@
         </is>
       </c>
       <c r="D19" s="13" t="n">
-        <v>139.24</v>
+        <v>138.94</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>-0.0506</v>
+        <v>-0.0526</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>-0.0814</v>
+        <v>-0.0834</v>
       </c>
       <c r="G19" s="15" t="n">
         <v>46322</v>
@@ -2281,7 +2281,7 @@
         <v>170</v>
       </c>
       <c r="M19" s="18" t="n">
-        <v>0.2209135305946566</v>
+        <v>0.2235497336979992</v>
       </c>
       <c r="N19" s="12" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>177</v>
       </c>
       <c r="P19" s="18" t="n">
-        <v>0.271186440677966</v>
+        <v>0.273931193320858</v>
       </c>
       <c r="Q19" s="19" t="inlineStr">
         <is>
@@ -2333,13 +2333,13 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>132.53</v>
+        <v>133.39</v>
       </c>
       <c r="E20" s="22" t="n">
-        <v>-0.381</v>
+        <v>-0.377</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>-0.392</v>
+        <v>-0.3881</v>
       </c>
       <c r="G20" s="6" t="n"/>
       <c r="H20" s="7" t="inlineStr">
@@ -2358,7 +2358,7 @@
         <v>220</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>0.6600015090922809</v>
+        <v>0.6492990479046407</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="8" t="n"/>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="D21" s="13" t="n">
-        <v>120.71</v>
+        <v>118.39</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>-0.0669</v>
+        <v>-0.0849</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>-0.0336</v>
+        <v>-0.0522</v>
       </c>
       <c r="G21" s="15" t="n"/>
       <c r="H21" s="21" t="inlineStr">
@@ -2453,13 +2453,13 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>85.84999999999999</v>
+        <v>83.78</v>
       </c>
       <c r="E22" s="22" t="n">
-        <v>-0.024</v>
+        <v>-0.0475</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.1028</v>
+        <v>0.0762</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>46315</v>
@@ -2488,7 +2488,7 @@
         <v>61</v>
       </c>
       <c r="M22" s="22" t="n">
-        <v>-0.2894583576004659</v>
+        <v>-0.2719026020529959</v>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>100</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0.1648223645894002</v>
+        <v>0.1936022917164001</v>
       </c>
       <c r="Q22" s="9" t="inlineStr">
         <is>
@@ -2540,13 +2540,13 @@
         </is>
       </c>
       <c r="D23" s="13" t="n">
-        <v>134.57</v>
+        <v>135.25</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>0.0003</v>
+        <v>0.0053</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>0.0713</v>
+        <v>0.0767</v>
       </c>
       <c r="G23" s="15" t="n">
         <v>46315</v>
@@ -2578,7 +2578,7 @@
         <v>145</v>
       </c>
       <c r="P23" s="18" t="n">
-        <v>0.07750613063832955</v>
+        <v>0.07208872458410351</v>
       </c>
       <c r="Q23" s="19" t="inlineStr"/>
       <c r="R23" s="17" t="n"/>
@@ -2613,13 +2613,13 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>311.27</v>
+        <v>310.49</v>
       </c>
       <c r="E24" s="22" t="n">
-        <v>-0.1126</v>
+        <v>-0.1149</v>
       </c>
       <c r="F24" s="22" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-0.0956</v>
       </c>
       <c r="G24" s="6" t="n"/>
       <c r="H24" s="7" t="inlineStr">
@@ -2638,7 +2638,7 @@
         <v>360</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>0.1565521894175475</v>
+        <v>0.1594576314857161</v>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>400</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0.2850579882417195</v>
+        <v>0.2882862572063512</v>
       </c>
       <c r="Q24" s="9" t="inlineStr">
         <is>
@@ -2698,13 +2698,13 @@
         </is>
       </c>
       <c r="D25" s="13" t="n">
-        <v>198.89</v>
+        <v>198.6</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.0926</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>-0.0602</v>
+        <v>-0.06150000000000001</v>
       </c>
       <c r="G25" s="15" t="n"/>
       <c r="H25" s="21" t="inlineStr">
@@ -2723,7 +2723,7 @@
         <v>255</v>
       </c>
       <c r="M25" s="18" t="n">
-        <v>0.2821157423701545</v>
+        <v>0.283987915407855</v>
       </c>
       <c r="N25" s="12" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>230</v>
       </c>
       <c r="P25" s="18" t="n">
-        <v>0.1564181205691589</v>
+        <v>0.1581067472306143</v>
       </c>
       <c r="Q25" s="19" t="inlineStr">
         <is>
@@ -2779,13 +2779,13 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>254.21</v>
+        <v>253.54</v>
       </c>
       <c r="E26" s="22" t="n">
-        <v>-0.0713</v>
+        <v>-0.0737</v>
       </c>
       <c r="F26" s="22" t="n">
-        <v>-0.07429999999999999</v>
+        <v>-0.0767</v>
       </c>
       <c r="G26" s="6" t="n"/>
       <c r="H26" s="7" t="inlineStr">
@@ -2804,7 +2804,7 @@
         <v>300</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>0.180126666928917</v>
+        <v>0.1832452472982567</v>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>350</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>0.3768144447504032</v>
+        <v>0.3804527885146328</v>
       </c>
       <c r="Q26" s="9" t="inlineStr">
         <is>
@@ -2856,13 +2856,13 @@
         </is>
       </c>
       <c r="D27" s="13" t="n">
-        <v>37.34</v>
+        <v>37.35</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>-0.1132</v>
+        <v>-0.1129</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>-0.1584</v>
+        <v>-0.1581</v>
       </c>
       <c r="G27" s="15" t="n">
         <v>46289</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>85.42</v>
+        <v>86.08</v>
       </c>
       <c r="E28" s="22" t="n">
-        <v>-0.0738</v>
+        <v>-0.0667</v>
       </c>
       <c r="F28" s="22" t="n">
-        <v>-0.01</v>
+        <v>-0.0023</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>46323</v>
@@ -2952,7 +2952,7 @@
         <v>110</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>0.2877546242097869</v>
+        <v>0.2778810408921933</v>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>115</v>
       </c>
       <c r="P28" s="5" t="n">
-        <v>0.3462889253102318</v>
+        <v>0.3359665427509294</v>
       </c>
       <c r="Q28" s="9" t="inlineStr">
         <is>
@@ -3008,13 +3008,13 @@
         </is>
       </c>
       <c r="D29" s="13" t="n">
-        <v>179.92</v>
+        <v>177.92</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>-0.1003</v>
+        <v>-0.1103</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>-0.145</v>
+        <v>-0.1545</v>
       </c>
       <c r="G29" s="15" t="n">
         <v>46317</v>
@@ -3069,13 +3069,13 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>227.17</v>
+        <v>225.27</v>
       </c>
       <c r="E30" s="22" t="n">
-        <v>-0.1085</v>
+        <v>-0.116</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.0192</v>
+        <v>0.0107</v>
       </c>
       <c r="G30" s="6" t="n"/>
       <c r="H30" s="7" t="inlineStr">
@@ -3094,7 +3094,7 @@
         <v>245</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>0.07848747633930543</v>
+        <v>0.08758378834287739</v>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         <v>265</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>0.1665272703261875</v>
+        <v>0.1763661384116837</v>
       </c>
       <c r="Q30" s="9" t="inlineStr">
         <is>
@@ -3146,13 +3146,13 @@
         </is>
       </c>
       <c r="D31" s="13" t="n">
-        <v>100.54</v>
+        <v>100.04</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>-0.0393</v>
+        <v>-0.0441</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>-0.0516</v>
+        <v>-0.0563</v>
       </c>
       <c r="G31" s="15" t="n"/>
       <c r="H31" s="21" t="inlineStr">
@@ -3171,7 +3171,7 @@
         <v>120</v>
       </c>
       <c r="M31" s="18" t="n">
-        <v>0.1935548040580863</v>
+        <v>0.1995201919232306</v>
       </c>
       <c r="N31" s="12" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>115</v>
       </c>
       <c r="P31" s="18" t="n">
-        <v>0.1438233538889993</v>
+        <v>0.1495401839264293</v>
       </c>
       <c r="Q31" s="19" t="inlineStr">
         <is>
@@ -3223,13 +3223,13 @@
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>12.5</v>
+        <v>12.83</v>
       </c>
       <c r="E32" s="22" t="n">
-        <v>-0.063</v>
+        <v>-0.0382</v>
       </c>
       <c r="F32" s="22" t="n">
-        <v>-0.1909</v>
+        <v>-0.1696</v>
       </c>
       <c r="G32" s="6" t="n"/>
       <c r="H32" s="7" t="inlineStr">
@@ -3274,13 +3274,13 @@
         </is>
       </c>
       <c r="D33" s="13" t="n">
-        <v>127.05</v>
+        <v>126.11</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>-0.2</v>
+        <v>-0.206</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>-0.1605</v>
+        <v>-0.1667</v>
       </c>
       <c r="G33" s="15" t="n"/>
       <c r="H33" s="21" t="inlineStr">
@@ -3299,7 +3299,7 @@
         <v>160</v>
       </c>
       <c r="M33" s="18" t="n">
-        <v>0.2593467138921685</v>
+        <v>0.2687336452303545</v>
       </c>
       <c r="N33" s="12" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>175</v>
       </c>
       <c r="P33" s="18" t="n">
-        <v>0.3774104683195593</v>
+        <v>0.3876774244707002</v>
       </c>
       <c r="Q33" s="19" t="inlineStr">
         <is>
@@ -3355,13 +3355,13 @@
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>33.56</v>
+        <v>34</v>
       </c>
       <c r="E34" s="22" t="n">
-        <v>-0.0308</v>
+        <v>-0.0179</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.1027</v>
+        <v>0.1173</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>46317</v>
@@ -3390,7 +3390,7 @@
         <v>35</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>0.04290822407628122</v>
+        <v>0.02941176470588235</v>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>40</v>
       </c>
       <c r="P34" s="5" t="n">
-        <v>0.1918951132300357</v>
+        <v>0.1764705882352941</v>
       </c>
       <c r="Q34" s="9" t="inlineStr">
         <is>
@@ -3442,13 +3442,13 @@
         </is>
       </c>
       <c r="D35" s="13" t="n">
-        <v>373.09</v>
+        <v>367.81</v>
       </c>
       <c r="E35" s="18" t="n">
-        <v>0.1276</v>
+        <v>0.1116</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.098</v>
       </c>
       <c r="G35" s="15" t="n">
         <v>46323</v>
@@ -3477,7 +3477,7 @@
         <v>130</v>
       </c>
       <c r="M35" s="14" t="n">
-        <v>-0.6515586051622932</v>
+        <v>-0.646556646094451</v>
       </c>
       <c r="N35" s="12" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>300</v>
       </c>
       <c r="P35" s="14" t="n">
-        <v>-0.195904473451446</v>
+        <v>-0.1843614909871945</v>
       </c>
       <c r="Q35" s="19" t="inlineStr">
         <is>
@@ -3529,13 +3529,13 @@
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>72.03</v>
+        <v>71.11</v>
       </c>
       <c r="E36" s="22" t="n">
-        <v>-0.07690000000000001</v>
+        <v>-0.08869999999999999</v>
       </c>
       <c r="F36" s="22" t="n">
-        <v>-0.0337</v>
+        <v>-0.0461</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>46329</v>
@@ -3590,13 +3590,13 @@
         </is>
       </c>
       <c r="D37" s="13" t="n">
-        <v>543.75</v>
+        <v>541.86</v>
       </c>
       <c r="E37" s="14" t="n">
-        <v>-0.0089</v>
+        <v>-0.0124</v>
       </c>
       <c r="F37" s="18" t="n">
-        <v>0.1589</v>
+        <v>0.1549</v>
       </c>
       <c r="G37" s="15" t="n"/>
       <c r="H37" s="21" t="inlineStr">
@@ -3615,7 +3615,7 @@
         <v>450</v>
       </c>
       <c r="M37" s="14" t="n">
-        <v>-0.1724137931034483</v>
+        <v>-0.1695271841435057</v>
       </c>
       <c r="N37" s="12" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>635</v>
       </c>
       <c r="P37" s="18" t="n">
-        <v>0.167816091954023</v>
+        <v>0.1718894179308308</v>
       </c>
       <c r="Q37" s="19" t="inlineStr">
         <is>
@@ -3671,13 +3671,13 @@
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>94.81999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="E38" s="22" t="n">
-        <v>-0.08210000000000001</v>
+        <v>-0.0784</v>
       </c>
       <c r="F38" s="22" t="n">
-        <v>-0.016</v>
+        <v>-0.012</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>46325</v>
@@ -3706,7 +3706,7 @@
         <v>110</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>0.1600928074245941</v>
+        <v>0.1554621848739496</v>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>105</v>
       </c>
       <c r="P38" s="5" t="n">
-        <v>0.1073613161780216</v>
+        <v>0.1029411764705882</v>
       </c>
       <c r="Q38" s="9" t="inlineStr">
         <is>
@@ -3762,13 +3762,13 @@
         </is>
       </c>
       <c r="D39" s="13" t="n">
-        <v>88.13</v>
+        <v>88.01000000000001</v>
       </c>
       <c r="E39" s="14" t="n">
-        <v>-0.0539</v>
+        <v>-0.0551</v>
       </c>
       <c r="F39" s="14" t="n">
-        <v>-0.0446</v>
+        <v>-0.0458</v>
       </c>
       <c r="G39" s="15" t="n">
         <v>46325</v>
@@ -3797,7 +3797,7 @@
         <v>95</v>
       </c>
       <c r="M39" s="18" t="n">
-        <v>0.07795302394190406</v>
+        <v>0.07942279286444716</v>
       </c>
       <c r="N39" s="12" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>100</v>
       </c>
       <c r="P39" s="18" t="n">
-        <v>0.1346873936230569</v>
+        <v>0.1362345188046812</v>
       </c>
       <c r="Q39" s="19" t="inlineStr">
         <is>
@@ -3853,13 +3853,13 @@
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>903.85</v>
+        <v>902.6</v>
       </c>
       <c r="E40" s="22" t="n">
-        <v>-0.0513</v>
+        <v>-0.0526</v>
       </c>
       <c r="F40" s="22" t="n">
-        <v>-0.0135</v>
+        <v>-0.0149</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>46289</v>
@@ -3888,7 +3888,7 @@
         <v>1000</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>0.1063782707307628</v>
+        <v>0.1079104808331487</v>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>1100</v>
       </c>
       <c r="P40" s="5" t="n">
-        <v>0.2170160978038391</v>
+        <v>0.2187015289164635</v>
       </c>
       <c r="Q40" s="9" t="inlineStr">
         <is>
@@ -3948,13 +3948,13 @@
         </is>
       </c>
       <c r="D41" s="13" t="n">
-        <v>126.47</v>
+        <v>124.51</v>
       </c>
       <c r="E41" s="18" t="n">
-        <v>0.033</v>
+        <v>0.0171</v>
       </c>
       <c r="F41" s="18" t="n">
-        <v>0.0634</v>
+        <v>0.047</v>
       </c>
       <c r="G41" s="15" t="n"/>
       <c r="H41" s="21" t="inlineStr">
@@ -3972,8 +3972,8 @@
       <c r="L41" s="17" t="n">
         <v>125</v>
       </c>
-      <c r="M41" s="14" t="n">
-        <v>-0.01162330987585988</v>
+      <c r="M41" s="18" t="n">
+        <v>0.003935426873343465</v>
       </c>
       <c r="N41" s="12" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>135</v>
       </c>
       <c r="P41" s="18" t="n">
-        <v>0.06744682533407133</v>
+        <v>0.08425026102321094</v>
       </c>
       <c r="Q41" s="19" t="inlineStr">
         <is>
@@ -4025,13 +4025,13 @@
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>24.83</v>
+        <v>24.61</v>
       </c>
       <c r="E42" s="22" t="n">
-        <v>-0.0038</v>
+        <v>-0.0128</v>
       </c>
       <c r="F42" s="22" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0097</v>
       </c>
       <c r="G42" s="6" t="n"/>
       <c r="H42" s="7" t="inlineStr">
@@ -4076,13 +4076,13 @@
         </is>
       </c>
       <c r="D43" s="13" t="n">
-        <v>87.98</v>
+        <v>87.58</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>0.0128</v>
+        <v>0.008199999999999999</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>0.0538</v>
+        <v>0.049</v>
       </c>
       <c r="G43" s="15" t="n">
         <v>46315</v>
@@ -4111,7 +4111,7 @@
         <v>90</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>0.02295976358263237</v>
+        <v>0.02763187942452617</v>
       </c>
       <c r="N43" s="12" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>88</v>
       </c>
       <c r="P43" s="18" t="n">
-        <v>0.0002273243919072064</v>
+        <v>0.004795615437314475</v>
       </c>
       <c r="Q43" s="19" t="inlineStr">
         <is>
@@ -4171,13 +4171,13 @@
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>56.92</v>
-      </c>
-      <c r="E44" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>56.46</v>
+      </c>
+      <c r="E44" s="22" t="n">
+        <v>-0.0004</v>
       </c>
       <c r="F44" s="22" t="n">
-        <v>-0.0597</v>
+        <v>-0.0674</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>46276</v>
@@ -4206,7 +4206,7 @@
         <v>58</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>0.01897399859451859</v>
+        <v>0.02727594757350335</v>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>78</v>
       </c>
       <c r="P44" s="5" t="n">
-        <v>0.3703443429374561</v>
+        <v>0.3815090329436769</v>
       </c>
       <c r="Q44" s="9" t="inlineStr">
         <is>
@@ -4258,13 +4258,13 @@
         </is>
       </c>
       <c r="D45" s="13" t="n">
-        <v>61.9</v>
+        <v>62.42</v>
       </c>
       <c r="E45" s="18" t="n">
-        <v>0.0059</v>
+        <v>0.0145</v>
       </c>
       <c r="F45" s="18" t="n">
-        <v>0.0521</v>
+        <v>0.061</v>
       </c>
       <c r="G45" s="15" t="n">
         <v>46322</v>
@@ -4293,7 +4293,7 @@
         <v>70</v>
       </c>
       <c r="M45" s="18" t="n">
-        <v>0.1308562197092084</v>
+        <v>0.1214354373598205</v>
       </c>
       <c r="N45" s="12" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>71</v>
       </c>
       <c r="P45" s="18" t="n">
-        <v>0.1470113085621971</v>
+        <v>0.137455943607818</v>
       </c>
       <c r="Q45" s="19" t="inlineStr">
         <is>
@@ -4353,13 +4353,13 @@
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>51.34</v>
+        <v>51.5</v>
       </c>
       <c r="E46" s="22" t="n">
-        <v>-0.0337</v>
+        <v>-0.0307</v>
       </c>
       <c r="F46" s="22" t="n">
-        <v>-0.0212</v>
+        <v>-0.0181</v>
       </c>
       <c r="G46" s="6" t="n">
         <v>46296</v>
@@ -4424,13 +4424,13 @@
         </is>
       </c>
       <c r="D47" s="13" t="n">
-        <v>42.26</v>
+        <v>42.84</v>
       </c>
       <c r="E47" s="14" t="n">
-        <v>-0.0755</v>
+        <v>-0.0629</v>
       </c>
       <c r="F47" s="14" t="n">
-        <v>-0.132</v>
+        <v>-0.1202</v>
       </c>
       <c r="G47" s="15" t="n"/>
       <c r="H47" s="21" t="inlineStr">
@@ -4475,13 +4475,13 @@
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>67.5</v>
+        <v>67.92</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0.0298</v>
+        <v>0.0362</v>
       </c>
       <c r="F48" s="22" t="n">
-        <v>-0.05980000000000001</v>
+        <v>-0.05400000000000001</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>46324</v>
@@ -4536,13 +4536,13 @@
         </is>
       </c>
       <c r="D49" s="13" t="n">
-        <v>136.74</v>
+        <v>136.69</v>
       </c>
       <c r="E49" s="14" t="n">
-        <v>-0.0072</v>
+        <v>-0.0076</v>
       </c>
       <c r="F49" s="14" t="n">
-        <v>-0.004699999999999999</v>
+        <v>-0.005</v>
       </c>
       <c r="G49" s="15" t="n">
         <v>46303</v>
@@ -4571,7 +4571,7 @@
         <v>140</v>
       </c>
       <c r="M49" s="18" t="n">
-        <v>0.0238408658768465</v>
+        <v>0.02421537786231621</v>
       </c>
       <c r="N49" s="12" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>150</v>
       </c>
       <c r="P49" s="18" t="n">
-        <v>0.09697235629662125</v>
+        <v>0.09737361913819594</v>
       </c>
       <c r="Q49" s="19" t="inlineStr">
         <is>
@@ -4631,13 +4631,13 @@
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>143.13</v>
+        <v>142.67</v>
       </c>
       <c r="E50" s="22" t="n">
-        <v>-0.0226</v>
+        <v>-0.0257</v>
       </c>
       <c r="F50" s="22" t="n">
-        <v>-0.0266</v>
+        <v>-0.0297</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>46318</v>
@@ -4666,7 +4666,7 @@
         <v>164</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>0.1458115000349333</v>
+        <v>0.1495058526669939</v>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>162</v>
       </c>
       <c r="P50" s="5" t="n">
-        <v>0.1318381890588975</v>
+        <v>0.1354874886100793</v>
       </c>
       <c r="Q50" s="9" t="inlineStr">
         <is>
@@ -4730,13 +4730,13 @@
         </is>
       </c>
       <c r="D51" s="13" t="n">
-        <v>80.95999999999999</v>
+        <v>81.56</v>
       </c>
       <c r="E51" s="14" t="n">
-        <v>-0.0348</v>
+        <v>-0.0275</v>
       </c>
       <c r="F51" s="14" t="n">
-        <v>-0.0343</v>
+        <v>-0.0271</v>
       </c>
       <c r="G51" s="15" t="n">
         <v>46322</v>
@@ -4765,7 +4765,7 @@
         <v>100</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>0.2351778656126483</v>
+        <v>0.2260912211868563</v>
       </c>
       <c r="N51" s="12" t="inlineStr"/>
       <c r="O51" s="17" t="n"/>
@@ -4809,13 +4809,13 @@
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>160.42</v>
+        <v>157.53</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0.0553</v>
+        <v>0.0362</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.1871</v>
+        <v>0.1657</v>
       </c>
       <c r="G52" s="6" t="n"/>
       <c r="H52" s="7" t="inlineStr">
@@ -4834,7 +4834,7 @@
         <v>140</v>
       </c>
       <c r="M52" s="22" t="n">
-        <v>-0.1272908614885924</v>
+        <v>-0.111280391036628</v>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>135</v>
       </c>
       <c r="P52" s="22" t="n">
-        <v>-0.1584590450068569</v>
+        <v>-0.1430203770710341</v>
       </c>
       <c r="Q52" s="9" t="inlineStr">
         <is>
@@ -4890,13 +4890,13 @@
         </is>
       </c>
       <c r="D53" s="13" t="n">
-        <v>105.96</v>
+        <v>105.83</v>
       </c>
       <c r="E53" s="14" t="n">
-        <v>-0.0595</v>
+        <v>-0.06059999999999999</v>
       </c>
       <c r="F53" s="14" t="n">
-        <v>-0.0697</v>
+        <v>-0.0709</v>
       </c>
       <c r="G53" s="15" t="n"/>
       <c r="H53" s="21" t="inlineStr">
@@ -4915,7 +4915,7 @@
         <v>140</v>
       </c>
       <c r="M53" s="18" t="n">
-        <v>0.3212533031332579</v>
+        <v>0.3228763110649154</v>
       </c>
       <c r="N53" s="12" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>140</v>
       </c>
       <c r="P53" s="18" t="n">
-        <v>0.3212533031332579</v>
+        <v>0.3228763110649154</v>
       </c>
       <c r="Q53" s="19" t="inlineStr">
         <is>
@@ -4975,13 +4975,13 @@
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>64.45</v>
-      </c>
-      <c r="E54" s="5" t="n">
-        <v>0.0059</v>
+        <v>63.64</v>
+      </c>
+      <c r="E54" s="22" t="n">
+        <v>-0.0067</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>0.1197</v>
+        <v>0.1056</v>
       </c>
       <c r="G54" s="6" t="n">
         <v>46317</v>
@@ -5017,7 +5017,7 @@
         <v>76</v>
       </c>
       <c r="P54" s="5" t="n">
-        <v>0.1792086889061287</v>
+        <v>0.1942174732872407</v>
       </c>
       <c r="Q54" s="9" t="inlineStr">
         <is>
@@ -5058,13 +5058,13 @@
         </is>
       </c>
       <c r="D55" s="13" t="n">
-        <v>137.3</v>
+        <v>136.61</v>
       </c>
       <c r="E55" s="18" t="n">
-        <v>0.116</v>
+        <v>0.1104</v>
       </c>
       <c r="F55" s="18" t="n">
-        <v>0.2592</v>
+        <v>0.2528</v>
       </c>
       <c r="G55" s="15" t="n"/>
       <c r="H55" s="21" t="inlineStr">
@@ -5083,7 +5083,7 @@
         <v>183</v>
       </c>
       <c r="M55" s="18" t="n">
-        <v>0.3328477785870356</v>
+        <v>0.3395798257814214</v>
       </c>
       <c r="N55" s="12" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>145</v>
       </c>
       <c r="P55" s="18" t="n">
-        <v>0.05608157319737792</v>
+        <v>0.06141570895249239</v>
       </c>
       <c r="Q55" s="19" t="inlineStr">
         <is>
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>212.89</v>
+        <v>213.82</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0.0922</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.2069</v>
+        <v>0.2121</v>
       </c>
       <c r="G56" s="6" t="n">
         <v>46325</v>
@@ -5170,7 +5170,7 @@
         <v>222</v>
       </c>
       <c r="M56" s="5" t="n">
-        <v>0.04279205223354791</v>
+        <v>0.0382564774109064</v>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>225</v>
       </c>
       <c r="P56" s="5" t="n">
-        <v>0.05688383672319045</v>
+        <v>0.05228697034889163</v>
       </c>
       <c r="Q56" s="9" t="inlineStr">
         <is>
@@ -5226,13 +5226,13 @@
         </is>
       </c>
       <c r="D57" s="13" t="n">
-        <v>146.9</v>
+        <v>147.04</v>
       </c>
       <c r="E57" s="18" t="n">
-        <v>0.0329</v>
+        <v>0.0339</v>
       </c>
       <c r="F57" s="18" t="n">
-        <v>0.0955</v>
+        <v>0.0965</v>
       </c>
       <c r="G57" s="15" t="n"/>
       <c r="H57" s="21" t="inlineStr">
@@ -5251,7 +5251,7 @@
         <v>196</v>
       </c>
       <c r="M57" s="18" t="n">
-        <v>0.3342409802586793</v>
+        <v>0.3329706202393907</v>
       </c>
       <c r="N57" s="12" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>170</v>
       </c>
       <c r="P57" s="18" t="n">
-        <v>0.1572498298162014</v>
+        <v>0.1561479869423287</v>
       </c>
       <c r="Q57" s="19" t="inlineStr">
         <is>
@@ -5307,13 +5307,13 @@
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>39.19</v>
+        <v>39.31</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0.0315</v>
+        <v>0.0348</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0.05139999999999999</v>
+        <v>0.0548</v>
       </c>
       <c r="G58" s="6" t="n">
         <v>46324</v>
@@ -5368,13 +5368,13 @@
         </is>
       </c>
       <c r="D59" s="13" t="n">
-        <v>21.55</v>
+        <v>21.67</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>0.0464</v>
+        <v>0.0527</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>0.0959</v>
+        <v>0.1025</v>
       </c>
       <c r="G59" s="15" t="n"/>
       <c r="H59" s="21" t="inlineStr">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>201.91</v>
+        <v>202.63</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0.0148</v>
+        <v>0.0184</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>0.101</v>
+        <v>0.1049</v>
       </c>
       <c r="G60" s="6" t="n">
         <v>46328</v>
@@ -5480,13 +5480,13 @@
         </is>
       </c>
       <c r="D61" s="13" t="n">
-        <v>37.04</v>
+        <v>37.14</v>
       </c>
       <c r="E61" s="18" t="n">
-        <v>0.1012</v>
+        <v>0.104</v>
       </c>
       <c r="F61" s="18" t="n">
-        <v>0.07719999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="G61" s="15" t="n">
         <v>46315</v>
@@ -5522,7 +5522,7 @@
         <v>43</v>
       </c>
       <c r="P61" s="18" t="n">
-        <v>0.1609071274298056</v>
+        <v>0.1577813677975229</v>
       </c>
       <c r="Q61" s="19" t="inlineStr">
         <is>
@@ -5567,13 +5567,13 @@
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>31.5</v>
+        <v>31.41</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="F62" s="22" t="n">
-        <v>-0.0191</v>
+        <v>-0.0221</v>
       </c>
       <c r="G62" s="6" t="n">
         <v>46316</v>
@@ -5602,7 +5602,7 @@
         <v>35</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1142948105698822</v>
       </c>
       <c r="N62" s="3" t="inlineStr"/>
       <c r="O62" s="8" t="n"/>
@@ -5646,13 +5646,13 @@
         </is>
       </c>
       <c r="D63" s="13" t="n">
-        <v>259.35</v>
+        <v>260.71</v>
       </c>
       <c r="E63" s="18" t="n">
-        <v>0.2033</v>
+        <v>0.2097</v>
       </c>
       <c r="F63" s="18" t="n">
-        <v>0.3769</v>
+        <v>0.3840999999999999</v>
       </c>
       <c r="G63" s="15" t="n"/>
       <c r="H63" s="21" t="inlineStr">
@@ -5697,13 +5697,13 @@
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>58.13</v>
+        <v>57.06</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0.0926</v>
+        <v>0.0726</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>0.217</v>
+        <v>0.1947</v>
       </c>
       <c r="G64" s="6" t="n">
         <v>46311</v>
@@ -5739,7 +5739,7 @@
         <v>63</v>
       </c>
       <c r="P64" s="5" t="n">
-        <v>0.08377773954928604</v>
+        <v>0.1041009463722397</v>
       </c>
       <c r="Q64" s="9" t="inlineStr">
         <is>
@@ -5788,13 +5788,13 @@
         </is>
       </c>
       <c r="D65" s="13" t="n">
-        <v>45.05</v>
+        <v>45.27</v>
       </c>
       <c r="E65" s="18" t="n">
-        <v>0.0633</v>
+        <v>0.0684</v>
       </c>
       <c r="F65" s="18" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0771</v>
       </c>
       <c r="G65" s="15" t="n">
         <v>46328</v>
@@ -5849,13 +5849,13 @@
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>74.90000000000001</v>
+        <v>75.16</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>0.0425</v>
-      </c>
-      <c r="F66" s="22" t="n">
-        <v>-0.0015</v>
+        <v>0.0461</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>0.0019</v>
       </c>
       <c r="G66" s="6" t="n">
         <v>46328</v>
@@ -5884,7 +5884,7 @@
         <v>89</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>0.1882510013351134</v>
+        <v>0.184140500266099</v>
       </c>
       <c r="N66" s="3" t="inlineStr"/>
       <c r="O66" s="8" t="n"/>
@@ -5940,13 +5940,13 @@
         </is>
       </c>
       <c r="D67" s="13" t="n">
-        <v>163.61</v>
+        <v>164.26</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>0.0239</v>
+        <v>0.028</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>0.1781</v>
+        <v>0.1827</v>
       </c>
       <c r="G67" s="15" t="n">
         <v>46325</v>
@@ -5975,7 +5975,7 @@
         <v>185</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>0.1307377299676058</v>
+        <v>0.126263241202971</v>
       </c>
       <c r="N67" s="12" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>185</v>
       </c>
       <c r="P67" s="18" t="n">
-        <v>0.1307377299676058</v>
+        <v>0.126263241202971</v>
       </c>
       <c r="Q67" s="19" t="inlineStr">
         <is>
@@ -6031,13 +6031,13 @@
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>114.96</v>
+        <v>114.75</v>
       </c>
       <c r="E68" s="22" t="n">
-        <v>-0.0572</v>
+        <v>-0.059</v>
       </c>
       <c r="F68" s="22" t="n">
-        <v>-0.057</v>
+        <v>-0.0587</v>
       </c>
       <c r="G68" s="6" t="n">
         <v>46329</v>
@@ -6066,7 +6066,7 @@
         <v>120</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>0.04384133611691029</v>
+        <v>0.0457516339869281</v>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>115</v>
       </c>
       <c r="P68" s="5" t="n">
-        <v>0.0003479471120390245</v>
+        <v>0.002178649237472767</v>
       </c>
       <c r="Q68" s="9" t="inlineStr"/>
       <c r="R68" s="8" t="n"/>
@@ -6112,13 +6112,13 @@
         </is>
       </c>
       <c r="D69" s="13" t="n">
-        <v>308.5</v>
+        <v>304.83</v>
       </c>
       <c r="E69" s="14" t="n">
-        <v>-0.1358</v>
+        <v>-0.1461</v>
       </c>
       <c r="F69" s="14" t="n">
-        <v>-0.1357</v>
+        <v>-0.146</v>
       </c>
       <c r="G69" s="15" t="n">
         <v>46325</v>
@@ -6147,7 +6147,7 @@
         <v>406</v>
       </c>
       <c r="M69" s="18" t="n">
-        <v>0.3160453808752026</v>
+        <v>0.3318899058491619</v>
       </c>
       <c r="N69" s="12" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         <v>436</v>
       </c>
       <c r="P69" s="18" t="n">
-        <v>0.413290113452188</v>
+        <v>0.4303054161335828</v>
       </c>
       <c r="Q69" s="19" t="inlineStr">
         <is>
@@ -6195,13 +6195,13 @@
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>322.68</v>
+        <v>321.8</v>
       </c>
       <c r="E70" s="22" t="n">
-        <v>-0.04769999999999999</v>
+        <v>-0.0503</v>
       </c>
       <c r="F70" s="22" t="n">
-        <v>-0.0796</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="G70" s="6" t="n">
         <v>46311</v>
@@ -6230,7 +6230,7 @@
         <v>415</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>0.2861038800049585</v>
+        <v>0.2896208825357364</v>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>380</v>
       </c>
       <c r="P70" s="5" t="n">
-        <v>0.1776372877153836</v>
+        <v>0.1808576755748912</v>
       </c>
       <c r="Q70" s="9" t="inlineStr">
         <is>
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="D71" s="13" t="n">
-        <v>62.9</v>
+        <v>62.69</v>
       </c>
       <c r="E71" s="14" t="n">
-        <v>-0.015</v>
+        <v>-0.0183</v>
       </c>
       <c r="F71" s="18" t="n">
-        <v>0.0541</v>
+        <v>0.0506</v>
       </c>
       <c r="G71" s="15" t="n">
         <v>46309</v>
@@ -6351,13 +6351,13 @@
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>1082.2</v>
+        <v>1072.51</v>
       </c>
       <c r="E72" s="22" t="n">
-        <v>-0.0435</v>
+        <v>-0.0521</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>0.0445</v>
+        <v>0.0351</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>46308</v>
@@ -6389,7 +6389,7 @@
         <v>1245</v>
       </c>
       <c r="P72" s="5" t="n">
-        <v>0.1504343004989835</v>
+        <v>0.1608283372649206</v>
       </c>
       <c r="Q72" s="9" t="inlineStr">
         <is>
@@ -6434,13 +6434,13 @@
         </is>
       </c>
       <c r="D73" s="13" t="n">
-        <v>35.18</v>
+        <v>34.37</v>
       </c>
       <c r="E73" s="18" t="n">
-        <v>0.4336</v>
+        <v>0.4004</v>
       </c>
       <c r="F73" s="18" t="n">
-        <v>0.4519</v>
+        <v>0.4183</v>
       </c>
       <c r="G73" s="15" t="n"/>
       <c r="H73" s="21" t="inlineStr">
@@ -6485,13 +6485,13 @@
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>24.88</v>
+        <v>24.21</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>0.3746</v>
+        <v>0.3376</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>0.6609</v>
+        <v>0.6162</v>
       </c>
       <c r="G74" s="6" t="n">
         <v>46346</v>
@@ -6546,13 +6546,13 @@
         </is>
       </c>
       <c r="D75" s="13" t="n">
-        <v>505.14</v>
+        <v>506.76</v>
       </c>
       <c r="E75" s="14" t="n">
-        <v>-0.0459</v>
+        <v>-0.0428</v>
       </c>
       <c r="F75" s="18" t="n">
-        <v>0.0231</v>
+        <v>0.0264</v>
       </c>
       <c r="G75" s="15" t="n"/>
       <c r="H75" s="21" t="inlineStr">
@@ -6619,13 +6619,13 @@
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>67.18000000000001</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="E76" s="22" t="n">
-        <v>-0.06179999999999999</v>
+        <v>-0.0707</v>
       </c>
       <c r="F76" s="22" t="n">
-        <v>-0.0072</v>
+        <v>-0.0166</v>
       </c>
       <c r="G76" s="6" t="n">
         <v>46321</v>
@@ -6654,7 +6654,7 @@
         <v>68</v>
       </c>
       <c r="M76" s="5" t="n">
-        <v>0.01220601369455185</v>
+        <v>0.02194168920949795</v>
       </c>
       <c r="N76" s="3" t="inlineStr"/>
       <c r="O76" s="8" t="n"/>
@@ -6696,13 +6696,13 @@
         </is>
       </c>
       <c r="D77" s="13" t="n">
-        <v>129.68</v>
+        <v>129.07</v>
       </c>
       <c r="E77" s="14" t="n">
-        <v>-0.08460000000000001</v>
+        <v>-0.0888</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>0.0535</v>
+        <v>0.0486</v>
       </c>
       <c r="G77" s="15" t="n">
         <v>46310</v>
@@ -6761,13 +6761,13 @@
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>137.63</v>
+        <v>137.81</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>0.0178</v>
+        <v>0.0192</v>
       </c>
       <c r="F78" s="22" t="n">
-        <v>-0.0224</v>
+        <v>-0.0212</v>
       </c>
       <c r="G78" s="6" t="n">
         <v>46308</v>
@@ -6799,7 +6799,7 @@
         <v>140</v>
       </c>
       <c r="P78" s="5" t="n">
-        <v>0.01722008283077821</v>
+        <v>0.01589144474276176</v>
       </c>
       <c r="Q78" s="9" t="inlineStr">
         <is>
@@ -6848,13 +6848,13 @@
         </is>
       </c>
       <c r="D79" s="13" t="n">
-        <v>336.74</v>
+        <v>337.61</v>
       </c>
       <c r="E79" s="14" t="n">
-        <v>-0.0332</v>
+        <v>-0.0307</v>
       </c>
       <c r="F79" s="14" t="n">
-        <v>-0.0319</v>
+        <v>-0.0294</v>
       </c>
       <c r="G79" s="15" t="n">
         <v>46315</v>
@@ -6883,7 +6883,7 @@
         <v>358</v>
       </c>
       <c r="M79" s="18" t="n">
-        <v>0.06313476272495097</v>
+        <v>0.06039513047599297</v>
       </c>
       <c r="N79" s="12" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>374</v>
       </c>
       <c r="P79" s="18" t="n">
-        <v>0.1106491655283007</v>
+        <v>0.1077870916145848</v>
       </c>
       <c r="Q79" s="19" t="inlineStr">
         <is>
@@ -6939,13 +6939,13 @@
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>58.08</v>
+        <v>58.09</v>
       </c>
       <c r="E80" s="22" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0095</v>
       </c>
       <c r="F80" s="22" t="n">
-        <v>-0.0049</v>
+        <v>-0.0048</v>
       </c>
       <c r="G80" s="6" t="n">
         <v>46310</v>
@@ -6974,7 +6974,7 @@
         <v>57</v>
       </c>
       <c r="M80" s="22" t="n">
-        <v>-0.01859504132231402</v>
+        <v>-0.01876398691685322</v>
       </c>
       <c r="N80" s="3" t="inlineStr"/>
       <c r="O80" s="8" t="n"/>
@@ -7016,13 +7016,13 @@
         </is>
       </c>
       <c r="D81" s="13" t="n">
-        <v>13.48</v>
+        <v>13.28</v>
       </c>
       <c r="E81" s="18" t="n">
-        <v>0.1635</v>
+        <v>0.1458</v>
       </c>
       <c r="F81" s="18" t="n">
-        <v>0.04940000000000001</v>
+        <v>0.0335</v>
       </c>
       <c r="G81" s="15" t="n"/>
       <c r="H81" s="21" t="inlineStr">
@@ -7067,13 +7067,13 @@
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>405.22</v>
+        <v>406.08</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0.0108</v>
+        <v>0.013</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>0.1459</v>
+        <v>0.1483</v>
       </c>
       <c r="G82" s="6" t="n"/>
       <c r="H82" s="7" t="inlineStr">
@@ -7130,13 +7130,13 @@
         </is>
       </c>
       <c r="D83" s="13" t="n">
-        <v>95.88</v>
+        <v>92.95</v>
       </c>
       <c r="E83" s="18" t="n">
-        <v>0.4299</v>
+        <v>0.3863</v>
       </c>
       <c r="F83" s="18" t="n">
-        <v>0.4496</v>
+        <v>0.4054</v>
       </c>
       <c r="G83" s="15" t="n"/>
       <c r="H83" s="21" t="inlineStr">
@@ -7181,13 +7181,13 @@
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>41.44</v>
+        <v>41.14</v>
       </c>
       <c r="E84" s="22" t="n">
-        <v>-0.0399</v>
+        <v>-0.04679999999999999</v>
       </c>
       <c r="F84" s="22" t="n">
-        <v>-0.1844</v>
+        <v>-0.1903</v>
       </c>
       <c r="G84" s="6" t="n"/>
       <c r="H84" s="7" t="inlineStr">
@@ -7232,13 +7232,13 @@
         </is>
       </c>
       <c r="D85" s="13" t="n">
-        <v>1032.24</v>
+        <v>1029.36</v>
       </c>
       <c r="E85" s="14" t="n">
-        <v>-0.0022</v>
+        <v>-0.005</v>
       </c>
       <c r="F85" s="14" t="n">
-        <v>-0.0217</v>
+        <v>-0.0245</v>
       </c>
       <c r="G85" s="15" t="n">
         <v>46308</v>
@@ -7267,7 +7267,7 @@
         <v>1325</v>
       </c>
       <c r="M85" s="18" t="n">
-        <v>0.2836162132837324</v>
+        <v>0.2872075852957178</v>
       </c>
       <c r="N85" s="12" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>1210</v>
       </c>
       <c r="P85" s="18" t="n">
-        <v>0.1722080136402387</v>
+        <v>0.1754876816662782</v>
       </c>
       <c r="Q85" s="19" t="inlineStr">
         <is>
@@ -7319,13 +7319,13 @@
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>134.34</v>
+        <v>135.23</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>0.08869999999999999</v>
+        <v>0.096</v>
       </c>
       <c r="F86" s="22" t="n">
-        <v>-0.0073</v>
+        <v>-0.0007000000000000001</v>
       </c>
       <c r="G86" s="6" t="n">
         <v>46324</v>
@@ -7380,13 +7380,13 @@
         </is>
       </c>
       <c r="D87" s="13" t="n">
-        <v>117.9</v>
+        <v>115.28</v>
       </c>
       <c r="E87" s="18" t="n">
-        <v>0.2474</v>
+        <v>0.2196</v>
       </c>
       <c r="F87" s="18" t="n">
-        <v>0.053</v>
+        <v>0.0296</v>
       </c>
       <c r="G87" s="15" t="n"/>
       <c r="H87" s="21" t="inlineStr">
@@ -7431,13 +7431,13 @@
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>97.01000000000001</v>
+        <v>95.92</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>0.1325</v>
+        <v>0.1198</v>
       </c>
       <c r="F88" s="22" t="n">
-        <v>-0.051</v>
+        <v>-0.0616</v>
       </c>
       <c r="G88" s="6" t="n">
         <v>46329</v>
@@ -7492,13 +7492,13 @@
         </is>
       </c>
       <c r="D89" s="13" t="n">
-        <v>157.66</v>
+        <v>156.51</v>
       </c>
       <c r="E89" s="18" t="n">
-        <v>0.0473</v>
+        <v>0.0396</v>
       </c>
       <c r="F89" s="18" t="n">
-        <v>0.1656</v>
+        <v>0.1571</v>
       </c>
       <c r="G89" s="15" t="n">
         <v>46324</v>
@@ -7553,13 +7553,13 @@
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>159.59</v>
+        <v>158.48</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>0.029</v>
+        <v>0.0219</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0.0616</v>
+        <v>0.05429999999999999</v>
       </c>
       <c r="G90" s="6" t="n">
         <v>46329</v>
@@ -7628,13 +7628,13 @@
         </is>
       </c>
       <c r="D91" s="13" t="n">
-        <v>354.8</v>
+        <v>354.69</v>
       </c>
       <c r="E91" s="14" t="n">
-        <v>-0.0139</v>
+        <v>-0.0142</v>
       </c>
       <c r="F91" s="18" t="n">
-        <v>0.0545</v>
+        <v>0.0542</v>
       </c>
       <c r="G91" s="15" t="n">
         <v>46308</v>
@@ -7663,7 +7663,7 @@
         <v>196</v>
       </c>
       <c r="M91" s="14" t="n">
-        <v>-0.447576099210823</v>
+        <v>-0.4474047760015789</v>
       </c>
       <c r="N91" s="12" t="inlineStr"/>
       <c r="O91" s="17" t="n"/>
@@ -7707,13 +7707,13 @@
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>103.76</v>
-      </c>
-      <c r="E92" s="22" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>104.1</v>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>0.0026</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>0.0704</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="G92" s="6" t="n"/>
       <c r="H92" s="7" t="inlineStr">
@@ -7732,7 +7732,7 @@
         <v>375</v>
       </c>
       <c r="M92" s="5" t="n">
-        <v>2.614109483423285</v>
+        <v>2.602305475504323</v>
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>368</v>
       </c>
       <c r="P92" s="5" t="n">
-        <v>2.546646106399383</v>
+        <v>2.535062439961576</v>
       </c>
       <c r="Q92" s="9" t="inlineStr">
         <is>
@@ -7796,13 +7796,13 @@
         </is>
       </c>
       <c r="D93" s="13" t="n">
-        <v>359.92</v>
+        <v>359.73</v>
       </c>
       <c r="E93" s="14" t="n">
-        <v>-0.0236</v>
+        <v>-0.0241</v>
       </c>
       <c r="F93" s="18" t="n">
-        <v>0.0568</v>
+        <v>0.0563</v>
       </c>
       <c r="G93" s="15" t="n">
         <v>46317</v>
@@ -7834,7 +7834,7 @@
         <v>115</v>
       </c>
       <c r="P93" s="14" t="n">
-        <v>-0.680484552122694</v>
+        <v>-0.6803157923998555</v>
       </c>
       <c r="Q93" s="19" t="inlineStr">
         <is>
@@ -7883,13 +7883,13 @@
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>566.86</v>
+        <v>567.62</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0.0066</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0.0762</v>
+        <v>0.0776</v>
       </c>
       <c r="G94" s="6" t="n">
         <v>46324</v>
@@ -7918,7 +7918,7 @@
         <v>366</v>
       </c>
       <c r="M94" s="22" t="n">
-        <v>-0.3543379317644568</v>
+        <v>-0.3552024241570065</v>
       </c>
       <c r="N94" s="3" t="inlineStr"/>
       <c r="O94" s="8" t="n"/>
@@ -7960,13 +7960,13 @@
         </is>
       </c>
       <c r="D95" s="13" t="n">
-        <v>1780.87</v>
+        <v>1785.54</v>
       </c>
       <c r="E95" s="14" t="n">
-        <v>-0.0322</v>
+        <v>-0.0296</v>
       </c>
       <c r="F95" s="14" t="n">
-        <v>-0.0866</v>
+        <v>-0.0842</v>
       </c>
       <c r="G95" s="15" t="n"/>
       <c r="H95" s="21" t="inlineStr">
@@ -8021,13 +8021,13 @@
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>216.18</v>
+        <v>215.35</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>0.004</v>
+        <v>0.0001</v>
       </c>
       <c r="F96" s="22" t="n">
-        <v>-0.0274</v>
+        <v>-0.0312</v>
       </c>
       <c r="G96" s="6" t="n">
         <v>46309</v>
@@ -8056,7 +8056,7 @@
         <v>668</v>
       </c>
       <c r="M96" s="5" t="n">
-        <v>2.090017577944306</v>
+        <v>2.10192709542605</v>
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>550</v>
       </c>
       <c r="P96" s="5" t="n">
-        <v>1.544176149505042</v>
+        <v>1.553981889946598</v>
       </c>
       <c r="Q96" s="9" t="inlineStr">
         <is>
@@ -8116,13 +8116,13 @@
         </is>
       </c>
       <c r="D97" s="13" t="n">
-        <v>113.65</v>
-      </c>
-      <c r="E97" s="14" t="n">
-        <v>-0.0014</v>
+        <v>114.02</v>
+      </c>
+      <c r="E97" s="18" t="n">
+        <v>0.0018</v>
       </c>
       <c r="F97" s="18" t="n">
-        <v>0.0127</v>
+        <v>0.0159</v>
       </c>
       <c r="G97" s="15" t="n">
         <v>46321</v>
@@ -8151,7 +8151,7 @@
         <v>240</v>
       </c>
       <c r="M97" s="18" t="n">
-        <v>1.111746590409151</v>
+        <v>1.104893878266971</v>
       </c>
       <c r="N97" s="12" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>240</v>
       </c>
       <c r="P97" s="18" t="n">
-        <v>1.111746590409151</v>
+        <v>1.104893878266971</v>
       </c>
       <c r="Q97" s="19" t="inlineStr">
         <is>
@@ -8211,13 +8211,13 @@
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>241.93</v>
+        <v>240.64</v>
       </c>
       <c r="E98" s="22" t="n">
-        <v>-0.0391</v>
+        <v>-0.0442</v>
       </c>
       <c r="F98" s="22" t="n">
-        <v>-0.0396</v>
+        <v>-0.0447</v>
       </c>
       <c r="G98" s="6" t="n">
         <v>46310</v>
@@ -8246,7 +8246,7 @@
         <v>113</v>
       </c>
       <c r="M98" s="22" t="n">
-        <v>-0.532922746248915</v>
+        <v>-0.5304188829787234</v>
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>114</v>
       </c>
       <c r="P98" s="22" t="n">
-        <v>-0.5287893192245691</v>
+        <v>-0.5262632978723404</v>
       </c>
       <c r="Q98" s="9" t="inlineStr"/>
       <c r="R98" s="8" t="n"/>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="D99" s="13" t="n">
-        <v>22.2</v>
+        <v>22.07</v>
       </c>
       <c r="E99" s="18" t="n">
-        <v>0.1443</v>
+        <v>0.1376</v>
       </c>
       <c r="F99" s="18" t="n">
-        <v>0.05889999999999999</v>
+        <v>0.0527</v>
       </c>
       <c r="G99" s="15" t="n">
         <v>46324</v>
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>14.65</v>
+        <v>14.68</v>
       </c>
       <c r="E100" s="22" t="n">
-        <v>-0.0024</v>
+        <v>-0.0007000000000000001</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>0.0566</v>
+        <v>0.0584</v>
       </c>
       <c r="G100" s="6" t="n">
         <v>46323</v>
@@ -8418,13 +8418,13 @@
         </is>
       </c>
       <c r="D101" s="13" t="n">
-        <v>107.31</v>
+        <v>107.17</v>
       </c>
       <c r="E101" s="18" t="n">
-        <v>0.0247</v>
+        <v>0.0234</v>
       </c>
       <c r="F101" s="18" t="n">
-        <v>0.1243</v>
+        <v>0.1228</v>
       </c>
       <c r="G101" s="15" t="n">
         <v>46323</v>
@@ -8453,7 +8453,7 @@
         <v>285</v>
       </c>
       <c r="M101" s="18" t="n">
-        <v>1.655856863293262</v>
+        <v>1.659326304002986</v>
       </c>
       <c r="N101" s="12" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>285</v>
       </c>
       <c r="P101" s="18" t="n">
-        <v>1.655856863293262</v>
+        <v>1.659326304002986</v>
       </c>
       <c r="Q101" s="19" t="inlineStr">
         <is>
@@ -8505,13 +8505,13 @@
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>424.53</v>
+        <v>418.37</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>0.0331</v>
+        <v>0.0181</v>
       </c>
       <c r="F102" s="22" t="n">
-        <v>-0.0139</v>
+        <v>-0.0282</v>
       </c>
       <c r="G102" s="6" t="n">
         <v>46324</v>
@@ -8580,13 +8580,13 @@
         </is>
       </c>
       <c r="D103" s="13" t="n">
-        <v>50.47</v>
+        <v>50.15</v>
       </c>
       <c r="E103" s="14" t="n">
-        <v>-0.0267</v>
+        <v>-0.0329</v>
       </c>
       <c r="F103" s="14" t="n">
-        <v>-0.0231</v>
+        <v>-0.0293</v>
       </c>
       <c r="G103" s="15" t="n">
         <v>46311</v>
@@ -8641,13 +8641,13 @@
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>367.35</v>
+        <v>367.58</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>0.0167</v>
+        <v>0.0173</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>0.0527</v>
+        <v>0.0533</v>
       </c>
       <c r="G104" s="6" t="n">
         <v>46322</v>
@@ -8676,7 +8676,7 @@
         <v>525</v>
       </c>
       <c r="M104" s="5" t="n">
-        <v>0.4291547570436912</v>
+        <v>0.4282605147178846</v>
       </c>
       <c r="N104" s="3" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         <v>543</v>
       </c>
       <c r="P104" s="5" t="n">
-        <v>0.4781543487137606</v>
+        <v>0.4772294466510692</v>
       </c>
       <c r="Q104" s="9" t="inlineStr">
         <is>
@@ -8732,13 +8732,13 @@
         </is>
       </c>
       <c r="D105" s="13" t="n">
-        <v>69.20999999999999</v>
+        <v>69.92</v>
       </c>
       <c r="E105" s="14" t="n">
-        <v>-0.0227</v>
+        <v>-0.0128</v>
       </c>
       <c r="F105" s="14" t="n">
-        <v>-0.0413</v>
+        <v>-0.0315</v>
       </c>
       <c r="G105" s="15" t="n">
         <v>46314</v>
@@ -8767,7 +8767,7 @@
         <v>412</v>
       </c>
       <c r="M105" s="18" t="n">
-        <v>4.952896980205173</v>
+        <v>4.892448512585812</v>
       </c>
       <c r="N105" s="12" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>350</v>
       </c>
       <c r="P105" s="18" t="n">
-        <v>4.057072677358764</v>
+        <v>4.005720823798627</v>
       </c>
       <c r="Q105" s="19" t="inlineStr">
         <is>
@@ -8823,13 +8823,13 @@
         </is>
       </c>
       <c r="D106" s="4" t="n">
-        <v>79.31999999999999</v>
+        <v>79.41</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0.0043</v>
+        <v>0.0054</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>0.0261</v>
+        <v>0.0273</v>
       </c>
       <c r="G106" s="6" t="n"/>
       <c r="H106" s="7" t="inlineStr">
@@ -8848,7 +8848,7 @@
         <v>68</v>
       </c>
       <c r="M106" s="22" t="n">
-        <v>-0.1427130610186585</v>
+        <v>-0.1436846744742475</v>
       </c>
       <c r="N106" s="3" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>68</v>
       </c>
       <c r="P106" s="22" t="n">
-        <v>-0.1427130610186585</v>
+        <v>-0.1436846744742475</v>
       </c>
       <c r="Q106" s="9" t="inlineStr">
         <is>
@@ -8904,13 +8904,13 @@
         </is>
       </c>
       <c r="D107" s="13" t="n">
-        <v>249.5</v>
+        <v>250.93</v>
       </c>
       <c r="E107" s="18" t="n">
-        <v>0.0062</v>
+        <v>0.0119</v>
       </c>
       <c r="F107" s="18" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.0115</v>
       </c>
       <c r="G107" s="15" t="n">
         <v>46325</v>
@@ -8939,7 +8939,7 @@
         <v>295</v>
       </c>
       <c r="M107" s="18" t="n">
-        <v>0.1823647294589178</v>
+        <v>0.1756266687920934</v>
       </c>
       <c r="N107" s="12" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>246</v>
       </c>
       <c r="P107" s="14" t="n">
-        <v>-0.01402805611222445</v>
+        <v>-0.01964691348184755</v>
       </c>
       <c r="Q107" s="19" t="inlineStr">
         <is>
@@ -8987,13 +8987,13 @@
         </is>
       </c>
       <c r="D108" s="4" t="n">
-        <v>106.21</v>
+        <v>105.25</v>
       </c>
       <c r="E108" s="22" t="n">
-        <v>-0.0222</v>
+        <v>-0.031</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>0.1307</v>
+        <v>0.1205</v>
       </c>
       <c r="G108" s="6" t="n">
         <v>46316</v>
@@ -9022,7 +9022,7 @@
         <v>112</v>
       </c>
       <c r="M108" s="5" t="n">
-        <v>0.05451464080595054</v>
+        <v>0.06413301662707839</v>
       </c>
       <c r="N108" s="3" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>120</v>
       </c>
       <c r="P108" s="5" t="n">
-        <v>0.1298371151492327</v>
+        <v>0.1401425178147268</v>
       </c>
       <c r="Q108" s="9" t="inlineStr">
         <is>
@@ -9086,13 +9086,13 @@
         </is>
       </c>
       <c r="D109" s="13" t="n">
-        <v>393.1</v>
+        <v>391.27</v>
       </c>
       <c r="E109" s="14" t="n">
-        <v>-0.0578</v>
+        <v>-0.0622</v>
       </c>
       <c r="F109" s="18" t="n">
-        <v>0.0818</v>
+        <v>0.0767</v>
       </c>
       <c r="G109" s="15" t="n">
         <v>46329</v>
@@ -9121,7 +9121,7 @@
         <v>390</v>
       </c>
       <c r="M109" s="14" t="n">
-        <v>-0.007886034088018374</v>
+        <v>-0.003245840468218831</v>
       </c>
       <c r="N109" s="12" t="inlineStr">
         <is>
@@ -9169,13 +9169,13 @@
         </is>
       </c>
       <c r="D110" s="4" t="n">
-        <v>180.03</v>
+        <v>179.76</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>0.0022</v>
+        <v>0.0008</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>0.1849</v>
+        <v>0.1831</v>
       </c>
       <c r="G110" s="6" t="n"/>
       <c r="H110" s="7" t="inlineStr">
@@ -9194,7 +9194,7 @@
         <v>161</v>
       </c>
       <c r="M110" s="22" t="n">
-        <v>-0.1057046047880909</v>
+        <v>-0.1043613707165109</v>
       </c>
       <c r="N110" s="3" t="inlineStr">
         <is>
@@ -9204,8 +9204,8 @@
       <c r="O110" s="8" t="n">
         <v>180</v>
       </c>
-      <c r="P110" s="22" t="n">
-        <v>-0.0001666388935177533</v>
+      <c r="P110" s="5" t="n">
+        <v>0.001335113484646246</v>
       </c>
       <c r="Q110" s="9" t="inlineStr">
         <is>
@@ -9246,13 +9246,13 @@
         </is>
       </c>
       <c r="D111" s="13" t="n">
-        <v>46.03</v>
+        <v>44.97</v>
       </c>
       <c r="E111" s="14" t="n">
-        <v>-0.08779999999999999</v>
+        <v>-0.1087</v>
       </c>
       <c r="F111" s="18" t="n">
-        <v>0.0281</v>
+        <v>0.0046</v>
       </c>
       <c r="G111" s="15" t="n">
         <v>46323</v>
@@ -9281,7 +9281,7 @@
         <v>55</v>
       </c>
       <c r="M111" s="18" t="n">
-        <v>0.1948729089724093</v>
+        <v>0.2230375806092951</v>
       </c>
       <c r="N111" s="12" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>65</v>
       </c>
       <c r="P111" s="18" t="n">
-        <v>0.4121225287855746</v>
+        <v>0.4454080498109851</v>
       </c>
       <c r="Q111" s="19" t="inlineStr">
         <is>
@@ -9333,13 +9333,13 @@
         </is>
       </c>
       <c r="D112" s="4" t="n">
-        <v>325.48</v>
-      </c>
-      <c r="E112" s="5" t="n">
-        <v>0.0015</v>
+        <v>323.41</v>
+      </c>
+      <c r="E112" s="22" t="n">
+        <v>-0.0049</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>0.0726</v>
+        <v>0.0658</v>
       </c>
       <c r="G112" s="6" t="n"/>
       <c r="H112" s="7" t="inlineStr">
@@ -9358,7 +9358,7 @@
         <v>331</v>
       </c>
       <c r="M112" s="5" t="n">
-        <v>0.01695956740813562</v>
+        <v>0.02346866206981842</v>
       </c>
       <c r="N112" s="3" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>330</v>
       </c>
       <c r="P112" s="5" t="n">
-        <v>0.01388718200811104</v>
+        <v>0.02037661173123891</v>
       </c>
       <c r="Q112" s="9" t="inlineStr">
         <is>
@@ -9418,13 +9418,13 @@
         </is>
       </c>
       <c r="D113" s="13" t="n">
-        <v>94.54000000000001</v>
+        <v>95.38</v>
       </c>
       <c r="E113" s="14" t="n">
-        <v>-0.0118</v>
+        <v>-0.003</v>
       </c>
       <c r="F113" s="14" t="n">
-        <v>-0.09230000000000001</v>
+        <v>-0.0842</v>
       </c>
       <c r="G113" s="15" t="n"/>
       <c r="H113" s="21" t="inlineStr">
@@ -9443,7 +9443,7 @@
         <v>123</v>
       </c>
       <c r="M113" s="18" t="n">
-        <v>0.3010365982652844</v>
+        <v>0.28957852799329</v>
       </c>
       <c r="N113" s="12" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>130</v>
       </c>
       <c r="P113" s="18" t="n">
-        <v>0.3750793314998941</v>
+        <v>0.3629691759278675</v>
       </c>
       <c r="Q113" s="19" t="inlineStr">
         <is>
@@ -9495,13 +9495,13 @@
         </is>
       </c>
       <c r="D114" s="4" t="n">
-        <v>203.71</v>
+        <v>204.99</v>
       </c>
       <c r="E114" s="22" t="n">
-        <v>-0.027</v>
+        <v>-0.0209</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>0.0234</v>
+        <v>0.0299</v>
       </c>
       <c r="G114" s="6" t="n">
         <v>46315</v>
@@ -9530,7 +9530,7 @@
         <v>212</v>
       </c>
       <c r="M114" s="5" t="n">
-        <v>0.04069510578763925</v>
+        <v>0.03419679008732129</v>
       </c>
       <c r="N114" s="3" t="inlineStr">
         <is>
@@ -9541,7 +9541,7 @@
         <v>205</v>
       </c>
       <c r="P114" s="5" t="n">
-        <v>0.006332531539934181</v>
+        <v>4.878286745690475e-05</v>
       </c>
       <c r="Q114" s="9" t="inlineStr">
         <is>
@@ -9586,13 +9586,13 @@
         </is>
       </c>
       <c r="D115" s="13" t="n">
-        <v>84.91</v>
+        <v>83.88</v>
       </c>
       <c r="E115" s="14" t="n">
-        <v>-0.0313</v>
+        <v>-0.043</v>
       </c>
       <c r="F115" s="18" t="n">
-        <v>0.1327</v>
+        <v>0.119</v>
       </c>
       <c r="G115" s="15" t="n">
         <v>46324</v>
@@ -9621,7 +9621,7 @@
         <v>85</v>
       </c>
       <c r="M115" s="18" t="n">
-        <v>0.001059945824991207</v>
+        <v>0.01335240820219366</v>
       </c>
       <c r="N115" s="12" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>90</v>
       </c>
       <c r="P115" s="18" t="n">
-        <v>0.05994582499116716</v>
+        <v>0.072961373390558</v>
       </c>
       <c r="Q115" s="19" t="inlineStr">
         <is>
@@ -9673,13 +9673,13 @@
         </is>
       </c>
       <c r="D116" s="4" t="n">
-        <v>145.54</v>
+        <v>145.65</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0.09380000000000001</v>
+        <v>0.0946</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>0.121</v>
+        <v>0.1219</v>
       </c>
       <c r="G116" s="6" t="n">
         <v>46324</v>
@@ -9708,7 +9708,7 @@
         <v>165</v>
       </c>
       <c r="M116" s="5" t="n">
-        <v>0.1337089459942284</v>
+        <v>0.1328527291452111</v>
       </c>
       <c r="N116" s="3" t="inlineStr"/>
       <c r="O116" s="8" t="n"/>
@@ -9756,13 +9756,13 @@
         </is>
       </c>
       <c r="D117" s="13" t="n">
-        <v>519.9299999999999</v>
+        <v>515.15</v>
       </c>
       <c r="E117" s="14" t="n">
-        <v>-0.1273</v>
+        <v>-0.1353</v>
       </c>
       <c r="F117" s="14" t="n">
-        <v>-0.0774</v>
+        <v>-0.0859</v>
       </c>
       <c r="G117" s="15" t="n">
         <v>46328</v>
@@ -9827,13 +9827,13 @@
         </is>
       </c>
       <c r="D118" s="4" t="n">
-        <v>352.67</v>
+        <v>353.24</v>
       </c>
       <c r="E118" s="22" t="n">
-        <v>-0.1035</v>
+        <v>-0.102</v>
       </c>
       <c r="F118" s="22" t="n">
-        <v>-0.133</v>
+        <v>-0.1316</v>
       </c>
       <c r="G118" s="6" t="n">
         <v>46315</v>
@@ -9862,7 +9862,7 @@
         <v>487</v>
       </c>
       <c r="M118" s="5" t="n">
-        <v>0.3808943204695607</v>
+        <v>0.3786660627335522</v>
       </c>
       <c r="N118" s="3" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>375</v>
       </c>
       <c r="P118" s="5" t="n">
-        <v>0.06331698188107858</v>
+        <v>0.06160117766957307</v>
       </c>
       <c r="Q118" s="9" t="inlineStr">
         <is>
@@ -9918,13 +9918,13 @@
         </is>
       </c>
       <c r="D119" s="13" t="n">
-        <v>268.77</v>
+        <v>267.19</v>
       </c>
       <c r="E119" s="18" t="n">
-        <v>0.0266</v>
+        <v>0.0205</v>
       </c>
       <c r="F119" s="18" t="n">
-        <v>0.0459</v>
+        <v>0.0397</v>
       </c>
       <c r="G119" s="15" t="n">
         <v>46308</v>
@@ -9953,7 +9953,7 @@
         <v>272</v>
       </c>
       <c r="M119" s="18" t="n">
-        <v>0.01201771030993049</v>
+        <v>0.01800217073992291</v>
       </c>
       <c r="N119" s="12" t="inlineStr"/>
       <c r="O119" s="17" t="n"/>
@@ -10005,13 +10005,13 @@
         </is>
       </c>
       <c r="D120" s="4" t="n">
-        <v>1126.61</v>
+        <v>1124.26</v>
       </c>
       <c r="E120" s="22" t="n">
-        <v>-0.08550000000000001</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="F120" s="22" t="n">
-        <v>-0.0521</v>
+        <v>-0.0541</v>
       </c>
       <c r="G120" s="6" t="n">
         <v>46324</v>
@@ -10040,7 +10040,7 @@
         <v>1280</v>
       </c>
       <c r="M120" s="5" t="n">
-        <v>0.1361518182867187</v>
+        <v>0.1385266753242133</v>
       </c>
       <c r="N120" s="3" t="inlineStr">
         <is>
@@ -10100,13 +10100,13 @@
         </is>
       </c>
       <c r="D121" s="13" t="n">
-        <v>92.72</v>
+        <v>91.91</v>
       </c>
       <c r="E121" s="18" t="n">
-        <v>0.0371</v>
+        <v>0.028</v>
       </c>
       <c r="F121" s="18" t="n">
-        <v>0.1056</v>
+        <v>0.0959</v>
       </c>
       <c r="G121" s="15" t="n"/>
       <c r="H121" s="21" t="inlineStr">
@@ -10125,7 +10125,7 @@
         <v>102</v>
       </c>
       <c r="M121" s="18" t="n">
-        <v>0.1000862812769629</v>
+        <v>0.1097813078011098</v>
       </c>
       <c r="N121" s="12" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>105</v>
       </c>
       <c r="P121" s="18" t="n">
-        <v>0.1324417601380501</v>
+        <v>0.1424219345011425</v>
       </c>
       <c r="Q121" s="19" t="inlineStr">
         <is>
@@ -10177,13 +10177,13 @@
         </is>
       </c>
       <c r="D122" s="4" t="n">
-        <v>147.38</v>
+        <v>147.59</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0.1258</v>
+        <v>0.1273</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>0.193</v>
+        <v>0.1947</v>
       </c>
       <c r="G122" s="6" t="n">
         <v>46324</v>
@@ -10212,7 +10212,7 @@
         <v>150</v>
       </c>
       <c r="M122" s="5" t="n">
-        <v>0.0177771746505632</v>
+        <v>0.01632901958127242</v>
       </c>
       <c r="N122" s="3" t="inlineStr"/>
       <c r="O122" s="8" t="n"/>
@@ -10256,13 +10256,13 @@
         </is>
       </c>
       <c r="D123" s="13" t="n">
-        <v>138.21</v>
+        <v>137.5</v>
       </c>
       <c r="E123" s="14" t="n">
-        <v>-0.1185</v>
+        <v>-0.123</v>
       </c>
       <c r="F123" s="14" t="n">
-        <v>-0.1028</v>
+        <v>-0.1074</v>
       </c>
       <c r="G123" s="15" t="n">
         <v>46322</v>
@@ -10335,13 +10335,13 @@
         </is>
       </c>
       <c r="D124" s="4" t="n">
-        <v>27.82</v>
+        <v>27.78</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0.0283</v>
+        <v>0.0272</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>0.1508</v>
+        <v>0.1496</v>
       </c>
       <c r="G124" s="6" t="n">
         <v>46329</v>
@@ -10370,7 +10370,7 @@
         <v>28</v>
       </c>
       <c r="M124" s="5" t="n">
-        <v>0.006470165348670011</v>
+        <v>0.007919366450683904</v>
       </c>
       <c r="N124" s="3" t="inlineStr"/>
       <c r="O124" s="8" t="n"/>
@@ -10414,13 +10414,13 @@
         </is>
       </c>
       <c r="D125" s="13" t="n">
-        <v>273.62</v>
+        <v>275.55</v>
       </c>
       <c r="E125" s="14" t="n">
-        <v>-0.2088</v>
+        <v>-0.2032</v>
       </c>
       <c r="F125" s="14" t="n">
-        <v>-0.1703</v>
+        <v>-0.1644</v>
       </c>
       <c r="G125" s="15" t="n">
         <v>46324</v>
@@ -10449,7 +10449,7 @@
         <v>418</v>
       </c>
       <c r="M125" s="18" t="n">
-        <v>0.5276661062787807</v>
+        <v>0.5169660678642714</v>
       </c>
       <c r="N125" s="12" t="inlineStr">
         <is>
@@ -10460,7 +10460,7 @@
         <v>350</v>
       </c>
       <c r="P125" s="18" t="n">
-        <v>0.2791462612382136</v>
+        <v>0.2701868989294138</v>
       </c>
       <c r="Q125" s="19" t="inlineStr">
         <is>
@@ -10505,13 +10505,13 @@
         </is>
       </c>
       <c r="D126" s="4" t="n">
-        <v>604.4400000000001</v>
+        <v>606.17</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0108</v>
       </c>
       <c r="F126" s="5" t="n">
-        <v>0.1468</v>
+        <v>0.1501</v>
       </c>
       <c r="G126" s="6" t="n">
         <v>46323</v>
@@ -10540,7 +10540,7 @@
         <v>615</v>
       </c>
       <c r="M126" s="5" t="n">
-        <v>0.01747071669644621</v>
+        <v>0.01456687067984236</v>
       </c>
       <c r="N126" s="3" t="inlineStr">
         <is>
@@ -10551,7 +10551,7 @@
         <v>570</v>
       </c>
       <c r="P126" s="22" t="n">
-        <v>-0.05697836013500108</v>
+        <v>-0.05966972961380464</v>
       </c>
       <c r="Q126" s="9" t="inlineStr">
         <is>
@@ -10600,13 +10600,13 @@
         </is>
       </c>
       <c r="D127" s="13" t="n">
-        <v>388.61</v>
+        <v>393.08</v>
       </c>
       <c r="E127" s="14" t="n">
-        <v>-0.0492</v>
+        <v>-0.0383</v>
       </c>
       <c r="F127" s="14" t="n">
-        <v>-0.0848</v>
+        <v>-0.07429999999999999</v>
       </c>
       <c r="G127" s="15" t="n">
         <v>46322</v>
@@ -10635,7 +10635,7 @@
         <v>526</v>
       </c>
       <c r="M127" s="18" t="n">
-        <v>0.353542111628625</v>
+        <v>0.3381499949119773</v>
       </c>
       <c r="N127" s="12" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>480</v>
       </c>
       <c r="P127" s="18" t="n">
-        <v>0.2351715087105324</v>
+        <v>0.2211254706421085</v>
       </c>
       <c r="Q127" s="19" t="inlineStr">
         <is>
@@ -10691,13 +10691,13 @@
         </is>
       </c>
       <c r="D128" s="4" t="n">
-        <v>73.3</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="E128" s="22" t="n">
-        <v>-0.0204</v>
+        <v>-0.0202</v>
       </c>
       <c r="F128" s="22" t="n">
-        <v>-0.0299</v>
+        <v>-0.0296</v>
       </c>
       <c r="G128" s="6" t="n">
         <v>46329</v>
@@ -10770,13 +10770,13 @@
         </is>
       </c>
       <c r="D129" s="13" t="n">
-        <v>266.53</v>
+        <v>265.22</v>
       </c>
       <c r="E129" s="14" t="n">
-        <v>-0.0261</v>
+        <v>-0.0309</v>
       </c>
       <c r="F129" s="18" t="n">
-        <v>0.1017</v>
+        <v>0.09630000000000001</v>
       </c>
       <c r="G129" s="15" t="n"/>
       <c r="H129" s="21" t="inlineStr">
@@ -10795,7 +10795,7 @@
         <v>248</v>
       </c>
       <c r="M129" s="14" t="n">
-        <v>-0.06952313060443467</v>
+        <v>-0.06492723022396511</v>
       </c>
       <c r="N129" s="12" t="inlineStr"/>
       <c r="O129" s="17" t="n"/>
@@ -10851,13 +10851,13 @@
         </is>
       </c>
       <c r="D130" s="4" t="n">
-        <v>126.5</v>
+        <v>126.92</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>0.2541</v>
+        <v>0.2583</v>
       </c>
       <c r="F130" s="5" t="n">
-        <v>0.1065</v>
+        <v>0.1102</v>
       </c>
       <c r="G130" s="6" t="n">
         <v>46325</v>
@@ -10912,13 +10912,13 @@
         </is>
       </c>
       <c r="D131" s="13" t="n">
-        <v>236.32</v>
+        <v>236.34</v>
       </c>
       <c r="E131" s="14" t="n">
-        <v>-0.0655</v>
+        <v>-0.0654</v>
       </c>
       <c r="F131" s="18" t="n">
-        <v>0.01</v>
+        <v>0.0101</v>
       </c>
       <c r="G131" s="15" t="n">
         <v>46324</v>
@@ -10973,13 +10973,13 @@
         </is>
       </c>
       <c r="D132" s="4" t="n">
-        <v>211.07</v>
+        <v>206.48</v>
       </c>
       <c r="E132" s="22" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-0.113</v>
       </c>
       <c r="F132" s="22" t="n">
-        <v>-0.0504</v>
+        <v>-0.0711</v>
       </c>
       <c r="G132" s="6" t="n"/>
       <c r="H132" s="7" t="inlineStr">
@@ -10998,7 +10998,7 @@
         <v>250</v>
       </c>
       <c r="M132" s="5" t="n">
-        <v>0.1844411806509689</v>
+        <v>0.2107710189848896</v>
       </c>
       <c r="N132" s="3" t="inlineStr"/>
       <c r="O132" s="8" t="n"/>
@@ -11042,13 +11042,13 @@
         </is>
       </c>
       <c r="D133" s="13" t="n">
-        <v>168.48</v>
+        <v>168.04</v>
       </c>
       <c r="E133" s="14" t="n">
-        <v>-0.0284</v>
+        <v>-0.0309</v>
       </c>
       <c r="F133" s="18" t="n">
-        <v>0.1425</v>
+        <v>0.1395</v>
       </c>
       <c r="G133" s="15" t="n">
         <v>46329</v>
@@ -11113,13 +11113,13 @@
         </is>
       </c>
       <c r="D134" s="4" t="n">
-        <v>818.5599999999999</v>
+        <v>816.05</v>
       </c>
       <c r="E134" s="22" t="n">
-        <v>-0.0227</v>
+        <v>-0.0257</v>
       </c>
       <c r="F134" s="22" t="n">
-        <v>-0.1405</v>
+        <v>-0.1432</v>
       </c>
       <c r="G134" s="6" t="n"/>
       <c r="H134" s="7" t="inlineStr">
@@ -11138,7 +11138,7 @@
         <v>1155</v>
       </c>
       <c r="M134" s="5" t="n">
-        <v>0.4110144644253324</v>
+        <v>0.4153544513203848</v>
       </c>
       <c r="N134" s="3" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>1103</v>
       </c>
       <c r="P134" s="5" t="n">
-        <v>0.3474882720875685</v>
+        <v>0.3516328656332333</v>
       </c>
       <c r="Q134" s="9" t="inlineStr">
         <is>
@@ -11190,13 +11190,13 @@
         </is>
       </c>
       <c r="D135" s="13" t="n">
-        <v>553.92</v>
+        <v>554.87</v>
       </c>
       <c r="E135" s="14" t="n">
-        <v>-0.1274</v>
+        <v>-0.1259</v>
       </c>
       <c r="F135" s="14" t="n">
-        <v>-0.1805</v>
+        <v>-0.1791</v>
       </c>
       <c r="G135" s="15" t="n"/>
       <c r="H135" s="21" t="inlineStr">
@@ -11215,7 +11215,7 @@
         <v>874</v>
       </c>
       <c r="M135" s="18" t="n">
-        <v>0.5778451761987292</v>
+        <v>0.5751437273595617</v>
       </c>
       <c r="N135" s="12" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>845</v>
       </c>
       <c r="P135" s="18" t="n">
-        <v>0.5254910456383595</v>
+        <v>0.5228792329734893</v>
       </c>
       <c r="Q135" s="19" t="inlineStr">
         <is>
@@ -11275,13 +11275,13 @@
         </is>
       </c>
       <c r="D136" s="4" t="n">
-        <v>198.29</v>
+        <v>200.04</v>
       </c>
       <c r="E136" s="22" t="n">
-        <v>-0.0218</v>
+        <v>-0.0132</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>0.1038</v>
+        <v>0.1136</v>
       </c>
       <c r="G136" s="6" t="n">
         <v>46288</v>
@@ -11310,7 +11310,7 @@
         <v>250</v>
       </c>
       <c r="M136" s="5" t="n">
-        <v>0.2607796661455444</v>
+        <v>0.2497500499900021</v>
       </c>
       <c r="N136" s="3" t="inlineStr"/>
       <c r="O136" s="8" t="n"/>
@@ -11354,13 +11354,13 @@
         </is>
       </c>
       <c r="D137" s="13" t="n">
-        <v>676.38</v>
+        <v>677.28</v>
       </c>
       <c r="E137" s="18" t="n">
-        <v>0.1101</v>
+        <v>0.1116</v>
       </c>
       <c r="F137" s="18" t="n">
-        <v>0.1525</v>
+        <v>0.1541</v>
       </c>
       <c r="G137" s="15" t="n"/>
       <c r="H137" s="21" t="inlineStr">
@@ -11379,7 +11379,7 @@
         <v>750</v>
       </c>
       <c r="M137" s="18" t="n">
-        <v>0.1088441408675597</v>
+        <v>0.1073706591070163</v>
       </c>
       <c r="N137" s="12" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>641.29</v>
       </c>
       <c r="P137" s="14" t="n">
-        <v>-0.05187912120405694</v>
+        <v>-0.05313902669501537</v>
       </c>
       <c r="Q137" s="19" t="inlineStr">
         <is>
@@ -11431,13 +11431,13 @@
         </is>
       </c>
       <c r="D138" s="4" t="n">
-        <v>151.69</v>
+        <v>150.4</v>
       </c>
       <c r="E138" s="22" t="n">
-        <v>-0.0442</v>
+        <v>-0.0524</v>
       </c>
       <c r="F138" s="5" t="n">
-        <v>0.0922</v>
+        <v>0.08289999999999999</v>
       </c>
       <c r="G138" s="6" t="n"/>
       <c r="H138" s="7" t="inlineStr">
@@ -11463,7 +11463,7 @@
         <v>185</v>
       </c>
       <c r="P138" s="5" t="n">
-        <v>0.2195925901509658</v>
+        <v>0.2300531914893617</v>
       </c>
       <c r="Q138" s="9" t="inlineStr">
         <is>
@@ -11502,13 +11502,13 @@
         </is>
       </c>
       <c r="D139" s="13" t="n">
-        <v>417.71</v>
+        <v>415.32</v>
       </c>
       <c r="E139" s="14" t="n">
-        <v>-0.0612</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="F139" s="18" t="n">
-        <v>0.0256</v>
+        <v>0.0197</v>
       </c>
       <c r="G139" s="15" t="n">
         <v>46329</v>
@@ -11544,7 +11544,7 @@
         <v>453</v>
       </c>
       <c r="P139" s="18" t="n">
-        <v>0.08448445093485916</v>
+        <v>0.09072522392372148</v>
       </c>
       <c r="Q139" s="19" t="inlineStr">
         <is>
@@ -11585,13 +11585,13 @@
         </is>
       </c>
       <c r="D140" s="4" t="n">
-        <v>48.92</v>
+        <v>48.79</v>
       </c>
       <c r="E140" s="22" t="n">
-        <v>-0.0619</v>
+        <v>-0.0644</v>
       </c>
       <c r="F140" s="5" t="n">
-        <v>0.05230000000000001</v>
+        <v>0.0495</v>
       </c>
       <c r="G140" s="6" t="n">
         <v>46309</v>
@@ -11664,13 +11664,13 @@
         </is>
       </c>
       <c r="D141" s="13" t="n">
-        <v>311.83</v>
+        <v>309.22</v>
       </c>
       <c r="E141" s="14" t="n">
-        <v>-0.0408</v>
+        <v>-0.0488</v>
       </c>
       <c r="F141" s="14" t="n">
-        <v>-0.0091</v>
+        <v>-0.0174</v>
       </c>
       <c r="G141" s="15" t="n">
         <v>46282</v>
@@ -11699,7 +11699,7 @@
         <v>425</v>
       </c>
       <c r="M141" s="18" t="n">
-        <v>0.3629221049931053</v>
+        <v>0.3744259750339563</v>
       </c>
       <c r="N141" s="12" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>323</v>
       </c>
       <c r="P141" s="18" t="n">
-        <v>0.03582079979476002</v>
+        <v>0.04456374102580678</v>
       </c>
       <c r="Q141" s="19" t="inlineStr">
         <is>
@@ -11751,13 +11751,13 @@
         </is>
       </c>
       <c r="D142" s="4" t="n">
-        <v>222.98</v>
+        <v>223.2</v>
       </c>
       <c r="E142" s="22" t="n">
-        <v>-0.1547</v>
+        <v>-0.1539</v>
       </c>
       <c r="F142" s="22" t="n">
-        <v>-0.0197</v>
+        <v>-0.0188</v>
       </c>
       <c r="G142" s="6" t="n"/>
       <c r="H142" s="7" t="inlineStr">
@@ -11776,7 +11776,7 @@
         <v>285</v>
       </c>
       <c r="M142" s="5" t="n">
-        <v>0.2781415373576106</v>
+        <v>0.2768817204301076</v>
       </c>
       <c r="N142" s="3" t="inlineStr"/>
       <c r="O142" s="8" t="n"/>
@@ -11824,13 +11824,13 @@
         </is>
       </c>
       <c r="D143" s="13" t="n">
-        <v>1630.51</v>
+        <v>1614.08</v>
       </c>
       <c r="E143" s="14" t="n">
-        <v>-0.0265</v>
+        <v>-0.0363</v>
       </c>
       <c r="F143" s="14" t="n">
-        <v>-0.07150000000000001</v>
+        <v>-0.0809</v>
       </c>
       <c r="G143" s="15" t="n">
         <v>46317</v>
@@ -11885,13 +11885,13 @@
         </is>
       </c>
       <c r="D144" s="4" t="n">
-        <v>55.67</v>
+        <v>54.84</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>0.06559999999999999</v>
+        <v>0.0496</v>
       </c>
       <c r="F144" s="5" t="n">
-        <v>0.0973</v>
+        <v>0.0808</v>
       </c>
       <c r="G144" s="6" t="n"/>
       <c r="H144" s="7" t="inlineStr">
@@ -11936,13 +11936,13 @@
         </is>
       </c>
       <c r="D145" s="13" t="n">
-        <v>353.79</v>
+        <v>352.68</v>
       </c>
       <c r="E145" s="14" t="n">
-        <v>-0.1065</v>
+        <v>-0.1093</v>
       </c>
       <c r="F145" s="14" t="n">
-        <v>-0.0567</v>
+        <v>-0.0597</v>
       </c>
       <c r="G145" s="15" t="n">
         <v>46318</v>
@@ -11971,7 +11971,7 @@
         <v>400</v>
       </c>
       <c r="M145" s="18" t="n">
-        <v>0.1306142061675004</v>
+        <v>0.1341726210729273</v>
       </c>
       <c r="N145" s="12" t="inlineStr"/>
       <c r="O145" s="17" t="n"/>
@@ -12023,13 +12023,13 @@
         </is>
       </c>
       <c r="D146" s="4" t="n">
-        <v>326.85</v>
+        <v>325.44</v>
       </c>
       <c r="E146" s="22" t="n">
-        <v>-0.1087</v>
+        <v>-0.1125</v>
       </c>
       <c r="F146" s="22" t="n">
-        <v>-0.09029999999999999</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="G146" s="6" t="n">
         <v>46315</v>
@@ -12058,7 +12058,7 @@
         <v>390</v>
       </c>
       <c r="M146" s="5" t="n">
-        <v>0.1932078935291417</v>
+        <v>0.198377581120944</v>
       </c>
       <c r="N146" s="3" t="inlineStr"/>
       <c r="O146" s="8" t="n"/>
@@ -12110,13 +12110,13 @@
         </is>
       </c>
       <c r="D147" s="13" t="n">
-        <v>952.26</v>
+        <v>950.61</v>
       </c>
       <c r="E147" s="14" t="n">
-        <v>-0.0389</v>
+        <v>-0.0406</v>
       </c>
       <c r="F147" s="14" t="n">
-        <v>-0.1276</v>
+        <v>-0.1291</v>
       </c>
       <c r="G147" s="15" t="n">
         <v>46316</v>
@@ -12145,7 +12145,7 @@
         <v>1259</v>
       </c>
       <c r="M147" s="18" t="n">
-        <v>0.3221179089744398</v>
+        <v>0.3244127455002577</v>
       </c>
       <c r="N147" s="12" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>1350</v>
       </c>
       <c r="P147" s="18" t="n">
-        <v>0.4176800453657615</v>
+        <v>0.4201407517278379</v>
       </c>
       <c r="Q147" s="19" t="inlineStr">
         <is>
@@ -12201,13 +12201,13 @@
         </is>
       </c>
       <c r="D148" s="4" t="n">
-        <v>1278.07</v>
+        <v>1279.1</v>
       </c>
       <c r="E148" s="22" t="n">
-        <v>-0.0149</v>
+        <v>-0.0141</v>
       </c>
       <c r="F148" s="22" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.0703</v>
       </c>
       <c r="G148" s="6" t="n">
         <v>46325</v>
@@ -12276,13 +12276,13 @@
         </is>
       </c>
       <c r="D149" s="13" t="n">
-        <v>206.51</v>
+        <v>204.93</v>
       </c>
       <c r="E149" s="14" t="n">
-        <v>-0.1499</v>
+        <v>-0.1564</v>
       </c>
       <c r="F149" s="14" t="n">
-        <v>-0.08789999999999999</v>
+        <v>-0.0949</v>
       </c>
       <c r="G149" s="15" t="n">
         <v>46317</v>
@@ -12337,13 +12337,13 @@
         </is>
       </c>
       <c r="D150" s="4" t="n">
-        <v>457.41</v>
+        <v>455.08</v>
       </c>
       <c r="E150" s="22" t="n">
-        <v>-0.0941</v>
+        <v>-0.0987</v>
       </c>
       <c r="F150" s="22" t="n">
-        <v>-0.0683</v>
+        <v>-0.0731</v>
       </c>
       <c r="G150" s="6" t="n">
         <v>46322</v>
@@ -12404,13 +12404,13 @@
         </is>
       </c>
       <c r="D151" s="13" t="n">
-        <v>265.51</v>
+        <v>263.98</v>
       </c>
       <c r="E151" s="14" t="n">
-        <v>-0.09849999999999999</v>
+        <v>-0.1037</v>
       </c>
       <c r="F151" s="14" t="n">
-        <v>-0.0123</v>
+        <v>-0.018</v>
       </c>
       <c r="G151" s="15" t="n">
         <v>46318</v>
@@ -12442,7 +12442,7 @@
         <v>272</v>
       </c>
       <c r="P151" s="18" t="n">
-        <v>0.02444352378441493</v>
+        <v>0.03038108947647542</v>
       </c>
       <c r="Q151" s="19" t="inlineStr">
         <is>
@@ -12495,13 +12495,13 @@
         </is>
       </c>
       <c r="D152" s="4" t="n">
-        <v>254.87</v>
+        <v>250.48</v>
       </c>
       <c r="E152" s="22" t="n">
-        <v>-0.1203</v>
+        <v>-0.1354</v>
       </c>
       <c r="F152" s="22" t="n">
-        <v>-0.1235</v>
+        <v>-0.1386</v>
       </c>
       <c r="G152" s="6" t="n">
         <v>46324</v>
@@ -12566,13 +12566,13 @@
         </is>
       </c>
       <c r="D153" s="13" t="n">
-        <v>381.33</v>
+        <v>375.83</v>
       </c>
       <c r="E153" s="14" t="n">
-        <v>-0.09910000000000001</v>
+        <v>-0.1121</v>
       </c>
       <c r="F153" s="14" t="n">
-        <v>-0.3092</v>
+        <v>-0.3192</v>
       </c>
       <c r="G153" s="15" t="n">
         <v>46323</v>
@@ -12627,13 +12627,13 @@
         </is>
       </c>
       <c r="D154" s="4" t="n">
-        <v>528.45</v>
+        <v>524.49</v>
       </c>
       <c r="E154" s="22" t="n">
-        <v>-0.1239</v>
+        <v>-0.1304</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>0.01</v>
+        <v>0.0024</v>
       </c>
       <c r="G154" s="6" t="n">
         <v>46315</v>
@@ -12694,13 +12694,13 @@
         </is>
       </c>
       <c r="D155" s="13" t="n">
-        <v>184.02</v>
+        <v>181.96</v>
       </c>
       <c r="E155" s="14" t="n">
-        <v>-0.1342</v>
+        <v>-0.1439</v>
       </c>
       <c r="F155" s="14" t="n">
-        <v>-0.1916</v>
+        <v>-0.2006</v>
       </c>
       <c r="G155" s="15" t="n"/>
       <c r="H155" s="21" t="inlineStr">
@@ -12719,7 +12719,7 @@
         <v>575</v>
       </c>
       <c r="M155" s="18" t="n">
-        <v>2.124660363004022</v>
+        <v>2.160035172565399</v>
       </c>
       <c r="N155" s="12" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>237</v>
       </c>
       <c r="P155" s="18" t="n">
-        <v>0.2879034887512226</v>
+        <v>0.3024840624313035</v>
       </c>
       <c r="Q155" s="19" t="inlineStr">
         <is>
@@ -12779,13 +12779,13 @@
         </is>
       </c>
       <c r="D156" s="4" t="n">
-        <v>115.35</v>
+        <v>114.75</v>
       </c>
       <c r="E156" s="22" t="n">
-        <v>-0.0482</v>
+        <v>-0.05309999999999999</v>
       </c>
       <c r="F156" s="5" t="n">
-        <v>0.0726</v>
+        <v>0.067</v>
       </c>
       <c r="G156" s="6" t="n">
         <v>46294</v>
@@ -12814,7 +12814,7 @@
         <v>250</v>
       </c>
       <c r="M156" s="5" t="n">
-        <v>1.167316861725184</v>
+        <v>1.178649237472767</v>
       </c>
       <c r="N156" s="3" t="inlineStr"/>
       <c r="O156" s="8" t="n"/>
@@ -12858,13 +12858,13 @@
         </is>
       </c>
       <c r="D157" s="13" t="n">
-        <v>121.27</v>
+        <v>121.88</v>
       </c>
       <c r="E157" s="14" t="n">
-        <v>-0.076</v>
+        <v>-0.0713</v>
       </c>
       <c r="F157" s="14" t="n">
-        <v>-0.0265</v>
+        <v>-0.0216</v>
       </c>
       <c r="G157" s="15" t="n">
         <v>46315</v>
@@ -12893,7 +12893,7 @@
         <v>95</v>
       </c>
       <c r="M157" s="14" t="n">
-        <v>-0.21662406201039</v>
+        <v>-0.2205447981621267</v>
       </c>
       <c r="N157" s="12" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>139</v>
       </c>
       <c r="P157" s="18" t="n">
-        <v>0.1462026882163767</v>
+        <v>0.1404660321627831</v>
       </c>
       <c r="Q157" s="19" t="inlineStr">
         <is>
@@ -12949,13 +12949,13 @@
         </is>
       </c>
       <c r="D158" s="4" t="n">
-        <v>950.8200000000001</v>
+        <v>949.9</v>
       </c>
       <c r="E158" s="22" t="n">
-        <v>-0.1034</v>
+        <v>-0.1043</v>
       </c>
       <c r="F158" s="22" t="n">
-        <v>-0.0109</v>
+        <v>-0.0118</v>
       </c>
       <c r="G158" s="6" t="n"/>
       <c r="H158" s="7" t="inlineStr">
@@ -12974,7 +12974,7 @@
         <v>125</v>
       </c>
       <c r="M158" s="22" t="n">
-        <v>-0.8685345280915421</v>
+        <v>-0.8684072007579745</v>
       </c>
       <c r="N158" s="3" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>1064</v>
       </c>
       <c r="P158" s="5" t="n">
-        <v>0.1190340968847941</v>
+        <v>0.1201179071481209</v>
       </c>
       <c r="Q158" s="9" t="inlineStr">
         <is>
@@ -13030,13 +13030,13 @@
         </is>
       </c>
       <c r="D159" s="13" t="n">
-        <v>484.41</v>
+        <v>485.93</v>
       </c>
       <c r="E159" s="14" t="n">
-        <v>-0.1295</v>
+        <v>-0.1268</v>
       </c>
       <c r="F159" s="14" t="n">
-        <v>-0.1865</v>
+        <v>-0.184</v>
       </c>
       <c r="G159" s="15" t="n">
         <v>46325</v>
@@ -13111,13 +13111,13 @@
         </is>
       </c>
       <c r="D160" s="4" t="n">
-        <v>427.2</v>
+        <v>426.14</v>
       </c>
       <c r="E160" s="22" t="n">
-        <v>-0.0184</v>
+        <v>-0.0209</v>
       </c>
       <c r="F160" s="22" t="n">
-        <v>-0.0951</v>
+        <v>-0.0974</v>
       </c>
       <c r="G160" s="6" t="n"/>
       <c r="H160" s="7" t="inlineStr">
@@ -13162,13 +13162,13 @@
         </is>
       </c>
       <c r="D161" s="13" t="n">
-        <v>34.49</v>
+        <v>34.53</v>
       </c>
       <c r="E161" s="14" t="n">
-        <v>-0.0736</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="F161" s="14" t="n">
-        <v>-0.2244</v>
+        <v>-0.2234</v>
       </c>
       <c r="G161" s="15" t="n">
         <v>46323</v>
@@ -13237,13 +13237,13 @@
         </is>
       </c>
       <c r="D162" s="4" t="n">
-        <v>198.46</v>
+        <v>197.58</v>
       </c>
       <c r="E162" s="22" t="n">
-        <v>-0.1145</v>
+        <v>-0.1184</v>
       </c>
       <c r="F162" s="5" t="n">
-        <v>0.0129</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="G162" s="6" t="n">
         <v>46315</v>
@@ -13316,13 +13316,13 @@
         </is>
       </c>
       <c r="D163" s="13" t="n">
-        <v>43.32</v>
+        <v>42.62</v>
       </c>
       <c r="E163" s="18" t="n">
-        <v>0.08</v>
+        <v>0.0626</v>
       </c>
       <c r="F163" s="14" t="n">
-        <v>-0.0073</v>
+        <v>-0.0234</v>
       </c>
       <c r="G163" s="15" t="n"/>
       <c r="H163" s="21" t="inlineStr">
@@ -13367,13 +13367,13 @@
         </is>
       </c>
       <c r="D164" s="4" t="n">
-        <v>444.7</v>
+        <v>444.2</v>
       </c>
       <c r="E164" s="22" t="n">
-        <v>-0.0677</v>
+        <v>-0.0687</v>
       </c>
       <c r="F164" s="22" t="n">
-        <v>-0.073</v>
+        <v>-0.07400000000000001</v>
       </c>
       <c r="G164" s="6" t="n">
         <v>46324</v>
@@ -13405,7 +13405,7 @@
         <v>560</v>
       </c>
       <c r="P164" s="5" t="n">
-        <v>0.2592759163480999</v>
+        <v>0.2606933813597479</v>
       </c>
       <c r="Q164" s="9" t="inlineStr">
         <is>
@@ -13458,13 +13458,13 @@
         </is>
       </c>
       <c r="D165" s="13" t="n">
-        <v>285.08</v>
+        <v>284.79</v>
       </c>
       <c r="E165" s="14" t="n">
-        <v>-0.0245</v>
+        <v>-0.0255</v>
       </c>
       <c r="F165" s="14" t="n">
-        <v>-0.0066</v>
+        <v>-0.0076</v>
       </c>
       <c r="G165" s="15" t="n">
         <v>46317</v>
@@ -13496,7 +13496,7 @@
         <v>294</v>
       </c>
       <c r="P165" s="18" t="n">
-        <v>0.03128946260698757</v>
+        <v>0.03233961866638568</v>
       </c>
       <c r="Q165" s="19" t="inlineStr">
         <is>
@@ -13541,13 +13541,13 @@
         </is>
       </c>
       <c r="D166" s="4" t="n">
-        <v>273.85</v>
-      </c>
-      <c r="E166" s="5" t="n">
-        <v>0.0139</v>
+        <v>262.77</v>
+      </c>
+      <c r="E166" s="22" t="n">
+        <v>-0.0271</v>
       </c>
       <c r="F166" s="22" t="n">
-        <v>-0.1412</v>
+        <v>-0.1759</v>
       </c>
       <c r="G166" s="6" t="n">
         <v>46323</v>
@@ -13579,7 +13579,7 @@
         <v>425</v>
       </c>
       <c r="P166" s="5" t="n">
-        <v>0.5519444951615847</v>
+        <v>0.617384024051452</v>
       </c>
       <c r="Q166" s="9" t="inlineStr">
         <is>
@@ -13620,13 +13620,13 @@
         </is>
       </c>
       <c r="D167" s="13" t="n">
-        <v>215.73</v>
+        <v>216.43</v>
       </c>
       <c r="E167" s="14" t="n">
-        <v>-0.048</v>
+        <v>-0.0449</v>
       </c>
       <c r="F167" s="14" t="n">
-        <v>-0.0755</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="G167" s="15" t="n">
         <v>46321</v>
@@ -13655,7 +13655,7 @@
         <v>268</v>
       </c>
       <c r="M167" s="18" t="n">
-        <v>0.2422936077504288</v>
+        <v>0.2382756549461719</v>
       </c>
       <c r="N167" s="12" t="inlineStr"/>
       <c r="O167" s="17" t="n"/>
@@ -13703,13 +13703,13 @@
         </is>
       </c>
       <c r="D168" s="4" t="n">
-        <v>310.5</v>
+        <v>309.59</v>
       </c>
       <c r="E168" s="22" t="n">
-        <v>-0.0496</v>
+        <v>-0.0524</v>
       </c>
       <c r="F168" s="22" t="n">
-        <v>-0.1911</v>
+        <v>-0.1935</v>
       </c>
       <c r="G168" s="6" t="n"/>
       <c r="H168" s="7" t="inlineStr">
@@ -13768,13 +13768,13 @@
         </is>
       </c>
       <c r="D169" s="13" t="n">
-        <v>337.21</v>
+        <v>337.66</v>
       </c>
       <c r="E169" s="14" t="n">
-        <v>-0.05309999999999999</v>
+        <v>-0.0518</v>
       </c>
       <c r="F169" s="14" t="n">
-        <v>-0.1703</v>
+        <v>-0.1691</v>
       </c>
       <c r="G169" s="15" t="n"/>
       <c r="H169" s="21" t="inlineStr">
@@ -13837,13 +13837,13 @@
         </is>
       </c>
       <c r="D170" s="4" t="n">
-        <v>106.86</v>
+        <v>107.66</v>
       </c>
       <c r="E170" s="22" t="n">
-        <v>-0.1183</v>
+        <v>-0.1116</v>
       </c>
       <c r="F170" s="22" t="n">
-        <v>-0.1185</v>
+        <v>-0.1119</v>
       </c>
       <c r="G170" s="6" t="n">
         <v>46322</v>
@@ -13916,13 +13916,13 @@
         </is>
       </c>
       <c r="D171" s="13" t="n">
-        <v>111.16</v>
+        <v>107.93</v>
       </c>
       <c r="E171" s="14" t="n">
-        <v>-0.163</v>
+        <v>-0.1873</v>
       </c>
       <c r="F171" s="14" t="n">
-        <v>-0.073</v>
+        <v>-0.1</v>
       </c>
       <c r="G171" s="15" t="n"/>
       <c r="H171" s="21" t="inlineStr">
@@ -13967,13 +13967,13 @@
         </is>
       </c>
       <c r="D172" s="4" t="n">
-        <v>313.32</v>
+        <v>315.34</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>0.0164</v>
-      </c>
-      <c r="F172" s="22" t="n">
-        <v>-0.0064</v>
+        <v>0.023</v>
+      </c>
+      <c r="F172" s="5" t="n">
+        <v>0.0001</v>
       </c>
       <c r="G172" s="6" t="n">
         <v>46324</v>
@@ -14002,7 +14002,7 @@
         <v>310</v>
       </c>
       <c r="M172" s="22" t="n">
-        <v>-0.01059619558279074</v>
+        <v>-0.01693410287308928</v>
       </c>
       <c r="N172" s="3" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         <v>365</v>
       </c>
       <c r="P172" s="5" t="n">
-        <v>0.1649431890718754</v>
+        <v>0.1574808143591045</v>
       </c>
       <c r="Q172" s="9" t="inlineStr">
         <is>
@@ -14070,13 +14070,13 @@
         </is>
       </c>
       <c r="D173" s="13" t="n">
-        <v>116.78</v>
+        <v>115.56</v>
       </c>
       <c r="E173" s="14" t="n">
-        <v>-0.1197</v>
+        <v>-0.1288</v>
       </c>
       <c r="F173" s="14" t="n">
-        <v>-0.1854</v>
+        <v>-0.1939</v>
       </c>
       <c r="G173" s="15" t="n">
         <v>46329</v>
@@ -14131,13 +14131,13 @@
         </is>
       </c>
       <c r="D174" s="4" t="n">
-        <v>177.82</v>
+        <v>175.84</v>
       </c>
       <c r="E174" s="22" t="n">
-        <v>-0.0024</v>
+        <v>-0.0135</v>
       </c>
       <c r="F174" s="5" t="n">
-        <v>0.3149</v>
+        <v>0.3003</v>
       </c>
       <c r="G174" s="6" t="n">
         <v>46296</v>
@@ -14192,13 +14192,13 @@
         </is>
       </c>
       <c r="D175" s="13" t="n">
-        <v>257.53</v>
+        <v>254.86</v>
       </c>
       <c r="E175" s="14" t="n">
-        <v>-0.0565</v>
+        <v>-0.0663</v>
       </c>
       <c r="F175" s="18" t="n">
-        <v>0.1515</v>
+        <v>0.1396</v>
       </c>
       <c r="G175" s="15" t="n">
         <v>46275</v>
@@ -14253,13 +14253,13 @@
         </is>
       </c>
       <c r="D176" s="4" t="n">
-        <v>364.11</v>
+        <v>365.07</v>
       </c>
       <c r="E176" s="22" t="n">
-        <v>-0.0516</v>
+        <v>-0.0491</v>
       </c>
       <c r="F176" s="22" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-0.07730000000000001</v>
       </c>
       <c r="G176" s="6" t="n"/>
       <c r="H176" s="7" t="inlineStr">
@@ -14278,7 +14278,7 @@
         <v>515</v>
       </c>
       <c r="M176" s="5" t="n">
-        <v>0.4144077339265606</v>
+        <v>0.4106883611362205</v>
       </c>
       <c r="N176" s="3" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>474</v>
       </c>
       <c r="P176" s="5" t="n">
-        <v>0.3018043997693005</v>
+        <v>0.2983811323855699</v>
       </c>
       <c r="Q176" s="9" t="inlineStr">
         <is>
@@ -14338,13 +14338,13 @@
         </is>
       </c>
       <c r="D177" s="13" t="n">
-        <v>208.38</v>
+        <v>206.62</v>
       </c>
       <c r="E177" s="14" t="n">
-        <v>-0.1862</v>
+        <v>-0.1931</v>
       </c>
       <c r="F177" s="14" t="n">
-        <v>-0.0003</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="G177" s="15" t="n"/>
       <c r="H177" s="21" t="inlineStr">
@@ -14389,13 +14389,13 @@
         </is>
       </c>
       <c r="D178" s="4" t="n">
-        <v>288.5</v>
+        <v>285.52</v>
       </c>
       <c r="E178" s="22" t="n">
-        <v>-0.08259999999999999</v>
+        <v>-0.09210000000000002</v>
       </c>
       <c r="F178" s="22" t="n">
-        <v>-0.0635</v>
+        <v>-0.0731</v>
       </c>
       <c r="G178" s="6" t="n">
         <v>46329</v>
@@ -14450,13 +14450,13 @@
         </is>
       </c>
       <c r="D179" s="13" t="n">
-        <v>301.39</v>
+        <v>300.54</v>
       </c>
       <c r="E179" s="14" t="n">
-        <v>-0.0499</v>
+        <v>-0.0526</v>
       </c>
       <c r="F179" s="14" t="n">
-        <v>-0.2702</v>
+        <v>-0.2722</v>
       </c>
       <c r="G179" s="15" t="n">
         <v>46329</v>
@@ -14511,13 +14511,13 @@
         </is>
       </c>
       <c r="D180" s="4" t="n">
-        <v>36.17</v>
+        <v>35.84</v>
       </c>
       <c r="E180" s="22" t="n">
-        <v>-0.1481</v>
+        <v>-0.1559</v>
       </c>
       <c r="F180" s="22" t="n">
-        <v>-0.3408</v>
+        <v>-0.3468</v>
       </c>
       <c r="G180" s="6" t="n">
         <v>46324</v>
@@ -14572,13 +14572,13 @@
         </is>
       </c>
       <c r="D181" s="13" t="n">
-        <v>467.79</v>
+        <v>468.85</v>
       </c>
       <c r="E181" s="14" t="n">
-        <v>-0.1041</v>
+        <v>-0.102</v>
       </c>
       <c r="F181" s="14" t="n">
-        <v>-0.2236</v>
+        <v>-0.2218</v>
       </c>
       <c r="G181" s="15" t="n"/>
       <c r="H181" s="21" t="inlineStr">
@@ -14597,7 +14597,7 @@
         <v>740</v>
       </c>
       <c r="M181" s="18" t="n">
-        <v>0.5819064109963872</v>
+        <v>0.5783299562759944</v>
       </c>
       <c r="N181" s="12" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
         <v>700</v>
       </c>
       <c r="P181" s="18" t="n">
-        <v>0.4963979563479338</v>
+        <v>0.493014823504319</v>
       </c>
       <c r="Q181" s="19" t="inlineStr">
         <is>
@@ -14649,13 +14649,13 @@
         </is>
       </c>
       <c r="D182" s="4" t="n">
-        <v>61.07</v>
+        <v>63.78</v>
       </c>
       <c r="E182" s="22" t="n">
-        <v>-0.0446</v>
+        <v>-0.0021</v>
       </c>
       <c r="F182" s="22" t="n">
-        <v>-0.2839</v>
+        <v>-0.2521</v>
       </c>
       <c r="G182" s="6" t="n"/>
       <c r="H182" s="7" t="inlineStr">
@@ -14704,13 +14704,13 @@
         </is>
       </c>
       <c r="D183" s="13" t="n">
-        <v>521.14</v>
+        <v>521.09</v>
       </c>
       <c r="E183" s="18" t="n">
         <v>0.1098</v>
       </c>
       <c r="F183" s="14" t="n">
-        <v>-0.0659</v>
+        <v>-0.066</v>
       </c>
       <c r="G183" s="15" t="n">
         <v>46329</v>
@@ -14739,7 +14739,7 @@
         <v>615</v>
       </c>
       <c r="M183" s="18" t="n">
-        <v>0.1801051540852746</v>
+        <v>0.1802183883782071</v>
       </c>
       <c r="N183" s="12" t="inlineStr">
         <is>
@@ -14750,7 +14750,7 @@
         <v>579</v>
       </c>
       <c r="P183" s="18" t="n">
-        <v>0.1110258279924781</v>
+        <v>0.111132433936556</v>
       </c>
       <c r="Q183" s="19" t="inlineStr">
         <is>
@@ -14791,13 +14791,13 @@
         </is>
       </c>
       <c r="D184" s="4" t="n">
-        <v>50.82</v>
+        <v>51.35</v>
       </c>
       <c r="E184" s="22" t="n">
-        <v>-0.0388</v>
+        <v>-0.0287</v>
       </c>
       <c r="F184" s="22" t="n">
-        <v>-0.2788</v>
+        <v>-0.2713</v>
       </c>
       <c r="G184" s="6" t="n">
         <v>46321</v>
@@ -14852,13 +14852,13 @@
         </is>
       </c>
       <c r="D185" s="13" t="n">
-        <v>194.91</v>
+        <v>192.84</v>
       </c>
       <c r="E185" s="18" t="n">
-        <v>0.0177</v>
+        <v>0.0069</v>
       </c>
       <c r="F185" s="18" t="n">
-        <v>0.0425</v>
+        <v>0.0315</v>
       </c>
       <c r="G185" s="15" t="n">
         <v>46329</v>
@@ -14887,7 +14887,7 @@
         <v>200</v>
       </c>
       <c r="M185" s="18" t="n">
-        <v>0.02611461700271922</v>
+        <v>0.03712922630159716</v>
       </c>
       <c r="N185" s="12" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
         <v>200</v>
       </c>
       <c r="P185" s="18" t="n">
-        <v>0.02611461700271922</v>
+        <v>0.03712922630159716</v>
       </c>
       <c r="Q185" s="19" t="inlineStr">
         <is>
@@ -14943,13 +14943,13 @@
         </is>
       </c>
       <c r="D186" s="4" t="n">
-        <v>81.8</v>
+        <v>81.37</v>
       </c>
       <c r="E186" s="22" t="n">
-        <v>-0.0244</v>
+        <v>-0.0296</v>
       </c>
       <c r="F186" s="5" t="n">
-        <v>0.0285</v>
+        <v>0.0231</v>
       </c>
       <c r="G186" s="6" t="n">
         <v>46323</v>
@@ -14981,7 +14981,7 @@
         <v>180</v>
       </c>
       <c r="P186" s="5" t="n">
-        <v>1.200488997555012</v>
+        <v>1.212117488017697</v>
       </c>
       <c r="Q186" s="9" t="inlineStr">
         <is>
@@ -15034,13 +15034,13 @@
         </is>
       </c>
       <c r="D187" s="13" t="n">
-        <v>27.93</v>
+        <v>27.14</v>
       </c>
       <c r="E187" s="14" t="n">
-        <v>-0.0389</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="F187" s="14" t="n">
-        <v>-0.1034</v>
+        <v>-0.1287</v>
       </c>
       <c r="G187" s="15" t="n">
         <v>46303</v>
@@ -15095,13 +15095,13 @@
         </is>
       </c>
       <c r="D188" s="4" t="n">
-        <v>268.4</v>
-      </c>
-      <c r="E188" s="5" t="n">
-        <v>0.0021</v>
+        <v>264.23</v>
+      </c>
+      <c r="E188" s="22" t="n">
+        <v>-0.0135</v>
       </c>
       <c r="F188" s="22" t="n">
-        <v>-0.17</v>
+        <v>-0.1829</v>
       </c>
       <c r="G188" s="6" t="n"/>
       <c r="H188" s="7" t="inlineStr">
@@ -15146,13 +15146,13 @@
         </is>
       </c>
       <c r="D189" s="13" t="n">
-        <v>1743.67</v>
-      </c>
-      <c r="E189" s="18" t="n">
-        <v>0.0059</v>
+        <v>1729.52</v>
+      </c>
+      <c r="E189" s="14" t="n">
+        <v>-0.0023</v>
       </c>
       <c r="F189" s="14" t="n">
-        <v>-0.0298</v>
+        <v>-0.0377</v>
       </c>
       <c r="G189" s="15" t="n">
         <v>46309</v>
@@ -15225,13 +15225,13 @@
         </is>
       </c>
       <c r="D190" s="4" t="n">
-        <v>40.59</v>
+        <v>41.25</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>0.07980000000000001</v>
+        <v>0.0974</v>
       </c>
       <c r="F190" s="22" t="n">
-        <v>-0.04849999999999999</v>
+        <v>-0.0331</v>
       </c>
       <c r="G190" s="6" t="n">
         <v>46324</v>
@@ -15286,13 +15286,13 @@
         </is>
       </c>
       <c r="D191" s="13" t="n">
-        <v>363</v>
+        <v>364.38</v>
       </c>
       <c r="E191" s="14" t="n">
-        <v>-0.1406</v>
+        <v>-0.1374</v>
       </c>
       <c r="F191" s="14" t="n">
-        <v>-0.0924</v>
+        <v>-0.08900000000000001</v>
       </c>
       <c r="G191" s="15" t="n"/>
       <c r="H191" s="21" t="inlineStr">
@@ -15311,7 +15311,7 @@
         <v>545</v>
       </c>
       <c r="M191" s="18" t="n">
-        <v>0.5013774104683195</v>
+        <v>0.495691311268456</v>
       </c>
       <c r="N191" s="12" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>582</v>
       </c>
       <c r="P191" s="18" t="n">
-        <v>0.6033057851239669</v>
+        <v>0.5972336571710851</v>
       </c>
       <c r="Q191" s="19" t="inlineStr">
         <is>
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="D192" s="4" t="n">
-        <v>146.63</v>
+        <v>148.66</v>
       </c>
       <c r="E192" s="22" t="n">
-        <v>-0.0725</v>
+        <v>-0.0597</v>
       </c>
       <c r="F192" s="5" t="n">
-        <v>0.0198</v>
+        <v>0.0339</v>
       </c>
       <c r="G192" s="6" t="n"/>
       <c r="H192" s="7" t="inlineStr">
@@ -15426,13 +15426,13 @@
         </is>
       </c>
       <c r="D193" s="13" t="n">
-        <v>285.4</v>
+        <v>284.6</v>
       </c>
       <c r="E193" s="14" t="n">
-        <v>-0.1401</v>
+        <v>-0.1425</v>
       </c>
       <c r="F193" s="14" t="n">
-        <v>-0.2571</v>
+        <v>-0.2592</v>
       </c>
       <c r="G193" s="15" t="n">
         <v>46321</v>
@@ -15461,7 +15461,7 @@
         <v>425</v>
       </c>
       <c r="M193" s="18" t="n">
-        <v>0.4891380518570428</v>
+        <v>0.4933239634574841</v>
       </c>
       <c r="N193" s="12" t="inlineStr"/>
       <c r="O193" s="17" t="n"/>
@@ -15505,13 +15505,13 @@
         </is>
       </c>
       <c r="D194" s="4" t="n">
-        <v>135.1</v>
+        <v>135.06</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>0.0302</v>
+        <v>0.0299</v>
       </c>
       <c r="F194" s="5" t="n">
-        <v>0.0258</v>
+        <v>0.0255</v>
       </c>
       <c r="G194" s="6" t="n">
         <v>46322</v>
@@ -15566,13 +15566,13 @@
         </is>
       </c>
       <c r="D195" s="13" t="n">
-        <v>339.61</v>
+        <v>337.83</v>
       </c>
       <c r="E195" s="14" t="n">
-        <v>-0.1241</v>
+        <v>-0.1286</v>
       </c>
       <c r="F195" s="14" t="n">
-        <v>-0.2629</v>
+        <v>-0.2667</v>
       </c>
       <c r="G195" s="15" t="n"/>
       <c r="H195" s="21" t="inlineStr">
@@ -15617,13 +15617,13 @@
         </is>
       </c>
       <c r="D196" s="4" t="n">
-        <v>11.34</v>
+        <v>11.43</v>
       </c>
       <c r="E196" s="22" t="n">
-        <v>-0.2868</v>
+        <v>-0.2811</v>
       </c>
       <c r="F196" s="22" t="n">
-        <v>-0.2886</v>
+        <v>-0.2829</v>
       </c>
       <c r="G196" s="6" t="n"/>
       <c r="H196" s="7" t="inlineStr">
@@ -15668,13 +15668,13 @@
         </is>
       </c>
       <c r="D197" s="13" t="n">
-        <v>341.64</v>
+        <v>333.57</v>
       </c>
       <c r="E197" s="18" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0603</v>
       </c>
       <c r="F197" s="14" t="n">
-        <v>-0.0506</v>
+        <v>-0.073</v>
       </c>
       <c r="G197" s="15" t="n">
         <v>46321</v>
@@ -15729,13 +15729,13 @@
         </is>
       </c>
       <c r="D198" s="4" t="n">
-        <v>306.78</v>
+        <v>303.54</v>
       </c>
       <c r="E198" s="22" t="n">
-        <v>-0.0565</v>
+        <v>-0.0665</v>
       </c>
       <c r="F198" s="22" t="n">
-        <v>-0.0546</v>
+        <v>-0.0646</v>
       </c>
       <c r="G198" s="6" t="n"/>
       <c r="H198" s="7" t="inlineStr">
@@ -15780,13 +15780,13 @@
         </is>
       </c>
       <c r="D199" s="13" t="n">
-        <v>53.87</v>
+        <v>56.68</v>
       </c>
       <c r="E199" s="18" t="n">
-        <v>0.08890000000000001</v>
-      </c>
-      <c r="F199" s="14" t="n">
-        <v>-0.0409</v>
+        <v>0.1457</v>
+      </c>
+      <c r="F199" s="18" t="n">
+        <v>0.0091</v>
       </c>
       <c r="G199" s="15" t="n"/>
       <c r="H199" s="21" t="inlineStr">
@@ -15831,13 +15831,13 @@
         </is>
       </c>
       <c r="D200" s="4" t="n">
-        <v>18.42</v>
+        <v>18.09</v>
       </c>
       <c r="E200" s="22" t="n">
-        <v>-0.0525</v>
+        <v>-0.0694</v>
       </c>
       <c r="F200" s="22" t="n">
-        <v>-0.2158</v>
+        <v>-0.2299</v>
       </c>
       <c r="G200" s="6" t="n">
         <v>46318</v>
@@ -15892,13 +15892,13 @@
         </is>
       </c>
       <c r="D201" s="13" t="n">
-        <v>171.62</v>
+        <v>167.92</v>
       </c>
       <c r="E201" s="14" t="n">
-        <v>-0.2847</v>
+        <v>-0.3001</v>
       </c>
       <c r="F201" s="14" t="n">
-        <v>-0.3343</v>
+        <v>-0.3486</v>
       </c>
       <c r="G201" s="15" t="n"/>
       <c r="H201" s="21" t="inlineStr">
@@ -15943,13 +15943,13 @@
         </is>
       </c>
       <c r="D202" s="4" t="n">
-        <v>249.93</v>
+        <v>244.2</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>0.2654</v>
+        <v>0.2364</v>
       </c>
       <c r="F202" s="5" t="n">
-        <v>0.5303</v>
+        <v>0.4952</v>
       </c>
       <c r="G202" s="6" t="n"/>
       <c r="H202" s="7" t="inlineStr">
@@ -15968,7 +15968,7 @@
         <v>200</v>
       </c>
       <c r="M202" s="22" t="n">
-        <v>-0.1997759372624335</v>
+        <v>-0.180999180999181</v>
       </c>
       <c r="N202" s="3" t="inlineStr">
         <is>
@@ -15979,7 +15979,7 @@
         <v>250</v>
       </c>
       <c r="P202" s="5" t="n">
-        <v>0.000280078421958121</v>
+        <v>0.0237510237510238</v>
       </c>
       <c r="Q202" s="9" t="inlineStr">
         <is>
@@ -16024,13 +16024,13 @@
         </is>
       </c>
       <c r="D203" s="13" t="n">
-        <v>210.8</v>
+        <v>207.8</v>
       </c>
       <c r="E203" s="14" t="n">
-        <v>-0.0638</v>
+        <v>-0.0771</v>
       </c>
       <c r="F203" s="18" t="n">
-        <v>0.1262</v>
+        <v>0.1102</v>
       </c>
       <c r="G203" s="15" t="n"/>
       <c r="H203" s="21" t="inlineStr">
@@ -16049,7 +16049,7 @@
         <v>181.25</v>
       </c>
       <c r="M203" s="14" t="n">
-        <v>-0.140180265654649</v>
+        <v>-0.12776708373436</v>
       </c>
       <c r="N203" s="12" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>177.5</v>
       </c>
       <c r="P203" s="14" t="n">
-        <v>-0.1579696394686907</v>
+        <v>-0.145813282001925</v>
       </c>
       <c r="Q203" s="19" t="inlineStr">
         <is>
@@ -16101,13 +16101,13 @@
         </is>
       </c>
       <c r="D204" s="4" t="n">
-        <v>98.45999999999999</v>
+        <v>94.94</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>0.1164</v>
+        <v>0.0765</v>
       </c>
       <c r="F204" s="5" t="n">
-        <v>0.1078</v>
+        <v>0.0682</v>
       </c>
       <c r="G204" s="6" t="n"/>
       <c r="H204" s="7" t="inlineStr">
@@ -16152,13 +16152,13 @@
         </is>
       </c>
       <c r="D205" s="13" t="n">
-        <v>109.82</v>
+        <v>109.43</v>
       </c>
       <c r="E205" s="14" t="n">
-        <v>-0.104</v>
+        <v>-0.1072</v>
       </c>
       <c r="F205" s="14" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.09789999999999999</v>
       </c>
       <c r="G205" s="15" t="n"/>
       <c r="H205" s="21" t="inlineStr">
@@ -16177,7 +16177,7 @@
         <v>130</v>
       </c>
       <c r="M205" s="18" t="n">
-        <v>0.1837552358404663</v>
+        <v>0.1879740473361966</v>
       </c>
       <c r="N205" s="12" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>150</v>
       </c>
       <c r="P205" s="18" t="n">
-        <v>0.3658714259697688</v>
+        <v>0.3707392853879191</v>
       </c>
       <c r="Q205" s="19" t="inlineStr">
         <is>
@@ -16245,13 +16245,13 @@
         </is>
       </c>
       <c r="D206" s="4" t="n">
-        <v>223.45</v>
+        <v>225.27</v>
       </c>
       <c r="E206" s="22" t="n">
-        <v>-0.1432</v>
+        <v>-0.1362</v>
       </c>
       <c r="F206" s="22" t="n">
-        <v>-0.1324</v>
+        <v>-0.1253</v>
       </c>
       <c r="G206" s="6" t="n"/>
       <c r="H206" s="7" t="inlineStr">
@@ -16296,13 +16296,13 @@
         </is>
       </c>
       <c r="D207" s="13" t="n">
-        <v>551.42</v>
+        <v>535.47</v>
       </c>
       <c r="E207" s="18" t="n">
-        <v>0.2043</v>
+        <v>0.1695</v>
       </c>
       <c r="F207" s="18" t="n">
-        <v>0.2677</v>
+        <v>0.2311</v>
       </c>
       <c r="G207" s="15" t="n"/>
       <c r="H207" s="21" t="inlineStr">
@@ -16347,13 +16347,13 @@
         </is>
       </c>
       <c r="D208" s="4" t="n">
-        <v>64.31</v>
+        <v>64.45</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.08070000000000001</v>
       </c>
       <c r="F208" s="5" t="n">
-        <v>0.3076</v>
+        <v>0.3105</v>
       </c>
       <c r="G208" s="6" t="n"/>
       <c r="H208" s="7" t="inlineStr">
@@ -16398,13 +16398,13 @@
         </is>
       </c>
       <c r="D209" s="13" t="n">
-        <v>50.45</v>
-      </c>
-      <c r="E209" s="14" t="n">
-        <v>-0.0024</v>
+        <v>50.6</v>
+      </c>
+      <c r="E209" s="18" t="n">
+        <v>0.0005</v>
       </c>
       <c r="F209" s="18" t="n">
-        <v>0.155</v>
+        <v>0.1583</v>
       </c>
       <c r="G209" s="15" t="n"/>
       <c r="H209" s="21" t="inlineStr">
@@ -16449,13 +16449,13 @@
         </is>
       </c>
       <c r="D210" s="4" t="n">
-        <v>421.85</v>
+        <v>418.29</v>
       </c>
       <c r="E210" s="22" t="n">
-        <v>-0.1996</v>
+        <v>-0.2064</v>
       </c>
       <c r="F210" s="22" t="n">
-        <v>-0.1046</v>
+        <v>-0.1122</v>
       </c>
       <c r="G210" s="6" t="n">
         <v>46328</v>
@@ -16510,13 +16510,13 @@
         </is>
       </c>
       <c r="D211" s="13" t="n">
-        <v>112.65</v>
+        <v>114.18</v>
       </c>
       <c r="E211" s="18" t="n">
-        <v>0.0016</v>
+        <v>0.0152</v>
       </c>
       <c r="F211" s="14" t="n">
-        <v>-0.0414</v>
+        <v>-0.0284</v>
       </c>
       <c r="G211" s="15" t="n"/>
       <c r="H211" s="21" t="inlineStr">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="D212" s="4" t="n">
-        <v>158.26</v>
+        <v>157.22</v>
       </c>
       <c r="E212" s="22" t="n">
-        <v>-0.0362</v>
-      </c>
-      <c r="F212" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.0426</v>
+      </c>
+      <c r="F212" s="22" t="n">
+        <v>-0.0018</v>
       </c>
       <c r="G212" s="6" t="n"/>
       <c r="H212" s="7" t="inlineStr">
@@ -16612,13 +16612,13 @@
         </is>
       </c>
       <c r="D213" s="13" t="n">
-        <v>45.74</v>
+        <v>45.95</v>
       </c>
       <c r="E213" s="14" t="n">
-        <v>-0.0862</v>
+        <v>-0.0819</v>
       </c>
       <c r="F213" s="14" t="n">
-        <v>-0.3369</v>
+        <v>-0.3338</v>
       </c>
       <c r="G213" s="15" t="n"/>
       <c r="H213" s="21" t="inlineStr">
@@ -16663,13 +16663,13 @@
         </is>
       </c>
       <c r="D214" s="4" t="n">
-        <v>169.21</v>
+        <v>168.52</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>0.0726</v>
+        <v>0.0682</v>
       </c>
       <c r="F214" s="22" t="n">
-        <v>-0.1136</v>
+        <v>-0.1172</v>
       </c>
       <c r="G214" s="6" t="n">
         <v>46322</v>
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="D215" s="13" t="n">
-        <v>47.32</v>
+        <v>46.33</v>
       </c>
       <c r="E215" s="18" t="n">
-        <v>0.1618</v>
+        <v>0.1375</v>
       </c>
       <c r="F215" s="18" t="n">
-        <v>0.4596</v>
+        <v>0.4291</v>
       </c>
       <c r="G215" s="15" t="n"/>
       <c r="H215" s="21" t="inlineStr">
@@ -16775,13 +16775,13 @@
         </is>
       </c>
       <c r="D216" s="4" t="n">
-        <v>146.96</v>
+        <v>142.2</v>
       </c>
       <c r="E216" s="22" t="n">
-        <v>-0.1502</v>
+        <v>-0.1777</v>
       </c>
       <c r="F216" s="5" t="n">
-        <v>0.0796</v>
+        <v>0.0446</v>
       </c>
       <c r="G216" s="6" t="n"/>
       <c r="H216" s="7" t="inlineStr">
@@ -16800,7 +16800,7 @@
         <v>190</v>
       </c>
       <c r="M216" s="5" t="n">
-        <v>0.2928688078388677</v>
+        <v>0.3361462728551337</v>
       </c>
       <c r="N216" s="3" t="inlineStr"/>
       <c r="O216" s="8" t="n"/>
@@ -16844,13 +16844,13 @@
         </is>
       </c>
       <c r="D217" s="13" t="n">
-        <v>57.47</v>
+        <v>58.91</v>
       </c>
       <c r="E217" s="18" t="n">
-        <v>0.051</v>
+        <v>0.0774</v>
       </c>
       <c r="F217" s="18" t="n">
-        <v>0.184</v>
+        <v>0.2136</v>
       </c>
       <c r="G217" s="15" t="n"/>
       <c r="H217" s="21" t="inlineStr">
@@ -16869,7 +16869,7 @@
         <v>67</v>
       </c>
       <c r="M217" s="18" t="n">
-        <v>0.1658256481642596</v>
+        <v>0.1373281276523511</v>
       </c>
       <c r="N217" s="12" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>70</v>
       </c>
       <c r="P217" s="18" t="n">
-        <v>0.218026796589525</v>
+        <v>0.1882532676964862</v>
       </c>
       <c r="Q217" s="19" t="inlineStr">
         <is>
@@ -16921,13 +16921,13 @@
         </is>
       </c>
       <c r="D218" s="4" t="n">
-        <v>235.8</v>
+        <v>230.27</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>0.09210000000000002</v>
+        <v>0.0665</v>
       </c>
       <c r="F218" s="5" t="n">
-        <v>0.1365</v>
+        <v>0.1098</v>
       </c>
       <c r="G218" s="6" t="n"/>
       <c r="H218" s="7" t="inlineStr">
@@ -16972,13 +16972,13 @@
         </is>
       </c>
       <c r="D219" s="13" t="n">
-        <v>231.85</v>
-      </c>
-      <c r="E219" s="14" t="n">
-        <v>-0.0189</v>
+        <v>239.96</v>
+      </c>
+      <c r="E219" s="18" t="n">
+        <v>0.0155</v>
       </c>
       <c r="F219" s="14" t="n">
-        <v>-0.1937</v>
+        <v>-0.1655</v>
       </c>
       <c r="G219" s="15" t="n">
         <v>46316</v>
@@ -17014,7 +17014,7 @@
         <v>250</v>
       </c>
       <c r="P219" s="18" t="n">
-        <v>0.07828337287039036</v>
+        <v>0.04184030671778626</v>
       </c>
       <c r="Q219" s="19" t="inlineStr">
         <is>
@@ -17051,13 +17051,13 @@
         </is>
       </c>
       <c r="D220" s="4" t="n">
-        <v>13.48</v>
+        <v>13.27</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>0.1527</v>
+        <v>0.1347</v>
       </c>
       <c r="F220" s="5" t="n">
-        <v>0.2064</v>
+        <v>0.1876</v>
       </c>
       <c r="G220" s="6" t="n"/>
       <c r="H220" s="7" t="inlineStr">
@@ -17102,13 +17102,13 @@
         </is>
       </c>
       <c r="D221" s="13" t="n">
-        <v>105.81</v>
+        <v>106.24</v>
       </c>
       <c r="E221" s="18" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="F221" s="14" t="n">
-        <v>-0.0367</v>
+        <v>-0.0328</v>
       </c>
       <c r="G221" s="15" t="n">
         <v>46317</v>
@@ -17163,13 +17163,13 @@
         </is>
       </c>
       <c r="D222" s="4" t="n">
-        <v>318.46</v>
+        <v>313.94</v>
       </c>
       <c r="E222" s="22" t="n">
-        <v>-0.0478</v>
+        <v>-0.0613</v>
       </c>
       <c r="F222" s="5" t="n">
-        <v>0.1582</v>
+        <v>0.1418</v>
       </c>
       <c r="G222" s="6" t="n"/>
       <c r="H222" s="7" t="inlineStr">
@@ -17214,13 +17214,13 @@
         </is>
       </c>
       <c r="D223" s="13" t="n">
-        <v>38.43</v>
+        <v>38.13</v>
       </c>
       <c r="E223" s="14" t="n">
-        <v>-0.0964</v>
+        <v>-0.1035</v>
       </c>
       <c r="F223" s="14" t="n">
-        <v>-0.1034</v>
+        <v>-0.1104</v>
       </c>
       <c r="G223" s="15" t="n"/>
       <c r="H223" s="21" t="inlineStr">
@@ -17265,13 +17265,13 @@
         </is>
       </c>
       <c r="D224" s="4" t="n">
-        <v>46.24</v>
+        <v>45.37</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>0.1937</v>
+        <v>0.1711</v>
       </c>
       <c r="F224" s="5" t="n">
-        <v>0.1241</v>
+        <v>0.1028</v>
       </c>
       <c r="G224" s="6" t="n"/>
       <c r="H224" s="7" t="inlineStr">
@@ -17316,13 +17316,13 @@
         </is>
       </c>
       <c r="D225" s="13" t="n">
-        <v>313.97</v>
+        <v>311.26</v>
       </c>
       <c r="E225" s="14" t="n">
-        <v>-0.0673</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="F225" s="14" t="n">
-        <v>-0.04940000000000001</v>
+        <v>-0.0576</v>
       </c>
       <c r="G225" s="15" t="n">
         <v>46289</v>
@@ -17381,13 +17381,13 @@
         </is>
       </c>
       <c r="D226" s="4" t="n">
-        <v>330.23</v>
+        <v>331.15</v>
       </c>
       <c r="E226" s="22" t="n">
-        <v>-0.0154</v>
+        <v>-0.0127</v>
       </c>
       <c r="F226" s="5" t="n">
-        <v>0.0254</v>
+        <v>0.0283</v>
       </c>
       <c r="G226" s="6" t="n"/>
       <c r="H226" s="7" t="inlineStr">
@@ -17406,7 +17406,7 @@
         <v>390</v>
       </c>
       <c r="M226" s="5" t="n">
-        <v>0.1809950640462707</v>
+        <v>0.1777140268760381</v>
       </c>
       <c r="N226" s="3" t="inlineStr"/>
       <c r="O226" s="8" t="n"/>
@@ -17462,13 +17462,13 @@
         </is>
       </c>
       <c r="D227" s="13" t="n">
-        <v>183.42</v>
+        <v>182.91</v>
       </c>
       <c r="E227" s="14" t="n">
-        <v>-0.0484</v>
+        <v>-0.051</v>
       </c>
       <c r="F227" s="14" t="n">
-        <v>-0.2078</v>
+        <v>-0.21</v>
       </c>
       <c r="G227" s="15" t="n"/>
       <c r="H227" s="21" t="inlineStr">
@@ -17487,7 +17487,7 @@
         <v>305</v>
       </c>
       <c r="M227" s="18" t="n">
-        <v>0.6628502889543126</v>
+        <v>0.6674867421136078</v>
       </c>
       <c r="N227" s="12" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>185</v>
       </c>
       <c r="P227" s="18" t="n">
-        <v>0.008614109693599457</v>
+        <v>0.01142638456071294</v>
       </c>
       <c r="Q227" s="19" t="inlineStr">
         <is>
@@ -17539,13 +17539,13 @@
         </is>
       </c>
       <c r="D228" s="4" t="n">
-        <v>82.84999999999999</v>
+        <v>83.78</v>
       </c>
       <c r="E228" s="22" t="n">
-        <v>-0.04219999999999999</v>
+        <v>-0.0314</v>
       </c>
       <c r="F228" s="22" t="n">
-        <v>-0.2695</v>
+        <v>-0.2613</v>
       </c>
       <c r="G228" s="6" t="n"/>
       <c r="H228" s="7" t="inlineStr">
@@ -17590,13 +17590,13 @@
         </is>
       </c>
       <c r="D229" s="13" t="n">
-        <v>1008.23</v>
+        <v>988.98</v>
       </c>
       <c r="E229" s="18" t="n">
-        <v>0.2394</v>
+        <v>0.2157</v>
       </c>
       <c r="F229" s="18" t="n">
-        <v>0.2571</v>
+        <v>0.2331</v>
       </c>
       <c r="G229" s="15" t="n">
         <v>46329</v>
@@ -17651,13 +17651,13 @@
         </is>
       </c>
       <c r="D230" s="4" t="n">
-        <v>99.08</v>
+        <v>98.69</v>
       </c>
       <c r="E230" s="22" t="n">
-        <v>-0.0552</v>
+        <v>-0.05889999999999999</v>
       </c>
       <c r="F230" s="22" t="n">
-        <v>-0.0282</v>
+        <v>-0.032</v>
       </c>
       <c r="G230" s="6" t="n">
         <v>46322</v>
@@ -17712,13 +17712,13 @@
         </is>
       </c>
       <c r="D231" s="13" t="n">
-        <v>315.69</v>
+        <v>315.84</v>
       </c>
       <c r="E231" s="18" t="n">
-        <v>0.0303</v>
+        <v>0.0308</v>
       </c>
       <c r="F231" s="14" t="n">
-        <v>-0.0989</v>
+        <v>-0.09849999999999999</v>
       </c>
       <c r="G231" s="15" t="n">
         <v>46323</v>
@@ -17747,7 +17747,7 @@
         <v>450</v>
       </c>
       <c r="M231" s="18" t="n">
-        <v>0.4254490164401787</v>
+        <v>0.4247720364741642</v>
       </c>
       <c r="N231" s="12" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>355</v>
       </c>
       <c r="P231" s="18" t="n">
-        <v>0.1245208907472521</v>
+        <v>0.1239868287740629</v>
       </c>
       <c r="Q231" s="19" t="inlineStr">
         <is>
@@ -17803,13 +17803,13 @@
         </is>
       </c>
       <c r="D232" s="4" t="n">
-        <v>73.54000000000001</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="E232" s="22" t="n">
-        <v>-0.0964</v>
+        <v>-0.103</v>
       </c>
       <c r="F232" s="22" t="n">
-        <v>-0.1699</v>
+        <v>-0.1759</v>
       </c>
       <c r="G232" s="6" t="n"/>
       <c r="H232" s="7" t="inlineStr">
@@ -17854,13 +17854,13 @@
         </is>
       </c>
       <c r="D233" s="13" t="n">
-        <v>363.58</v>
+        <v>358.38</v>
       </c>
       <c r="E233" s="14" t="n">
-        <v>-0.1274</v>
+        <v>-0.1399</v>
       </c>
       <c r="F233" s="18" t="n">
-        <v>0.06280000000000001</v>
+        <v>0.0476</v>
       </c>
       <c r="G233" s="15" t="n"/>
       <c r="H233" s="21" t="inlineStr">
@@ -17905,13 +17905,13 @@
         </is>
       </c>
       <c r="D234" s="4" t="n">
-        <v>266.08</v>
+        <v>268.05</v>
       </c>
       <c r="E234" s="22" t="n">
-        <v>-0.08990000000000001</v>
+        <v>-0.08310000000000001</v>
       </c>
       <c r="F234" s="22" t="n">
-        <v>-0.2781</v>
+        <v>-0.2727</v>
       </c>
       <c r="G234" s="6" t="n"/>
       <c r="H234" s="7" t="inlineStr">
@@ -17956,13 +17956,13 @@
         </is>
       </c>
       <c r="D235" s="13" t="n">
-        <v>1208.75</v>
+        <v>1203.75</v>
       </c>
       <c r="E235" s="14" t="n">
-        <v>-0.1248</v>
+        <v>-0.1284</v>
       </c>
       <c r="F235" s="14" t="n">
-        <v>-0.1064</v>
+        <v>-0.1101</v>
       </c>
       <c r="G235" s="15" t="n">
         <v>46324</v>
@@ -18017,13 +18017,13 @@
         </is>
       </c>
       <c r="D236" s="4" t="n">
-        <v>238.08</v>
+        <v>235.01</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>0.1415</v>
-      </c>
-      <c r="F236" s="5" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.1268</v>
+      </c>
+      <c r="F236" s="22" t="n">
+        <v>-0.0034</v>
       </c>
       <c r="G236" s="6" t="n"/>
       <c r="H236" s="7" t="inlineStr">
@@ -18042,7 +18042,7 @@
         <v>240</v>
       </c>
       <c r="M236" s="5" t="n">
-        <v>0.008064516129032206</v>
+        <v>0.02123313901536109</v>
       </c>
       <c r="N236" s="3" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         <v>251</v>
       </c>
       <c r="P236" s="5" t="n">
-        <v>0.05426747311827951</v>
+        <v>0.06803965788689847</v>
       </c>
       <c r="Q236" s="9" t="inlineStr">
         <is>
@@ -18094,13 +18094,13 @@
         </is>
       </c>
       <c r="D237" s="13" t="n">
-        <v>493.43</v>
+        <v>491.65</v>
       </c>
       <c r="E237" s="14" t="n">
-        <v>-0.025</v>
+        <v>-0.0285</v>
       </c>
       <c r="F237" s="18" t="n">
-        <v>0.2813</v>
+        <v>0.2767</v>
       </c>
       <c r="G237" s="15" t="n"/>
       <c r="H237" s="21" t="inlineStr">
@@ -18119,7 +18119,7 @@
         <v>625</v>
       </c>
       <c r="M237" s="18" t="n">
-        <v>0.2666436981942727</v>
+        <v>0.2712295332045155</v>
       </c>
       <c r="N237" s="12" t="inlineStr">
         <is>
@@ -18130,7 +18130,7 @@
         <v>525</v>
       </c>
       <c r="P237" s="18" t="n">
-        <v>0.06398070648318908</v>
+        <v>0.067832807891793</v>
       </c>
       <c r="Q237" s="19" t="inlineStr">
         <is>
@@ -18183,13 +18183,13 @@
         </is>
       </c>
       <c r="D238" s="4" t="n">
-        <v>463</v>
-      </c>
-      <c r="E238" s="5" t="n">
-        <v>0.0022</v>
+        <v>459.91</v>
+      </c>
+      <c r="E238" s="22" t="n">
+        <v>-0.004500000000000001</v>
       </c>
       <c r="F238" s="5" t="n">
-        <v>0.0949</v>
+        <v>0.0876</v>
       </c>
       <c r="G238" s="6" t="n">
         <v>46324</v>
@@ -18221,7 +18221,7 @@
         <v>525</v>
       </c>
       <c r="P238" s="5" t="n">
-        <v>0.1339092872570194</v>
+        <v>0.1415276902002565</v>
       </c>
       <c r="Q238" s="9" t="inlineStr">
         <is>
@@ -18270,13 +18270,13 @@
         </is>
       </c>
       <c r="D239" s="13" t="n">
-        <v>136.27</v>
+        <v>132.7</v>
       </c>
       <c r="E239" s="18" t="n">
-        <v>0.4001</v>
+        <v>0.3634000000000001</v>
       </c>
       <c r="F239" s="18" t="n">
-        <v>0.4399</v>
+        <v>0.4022</v>
       </c>
       <c r="G239" s="15" t="n">
         <v>46324</v>
@@ -18331,13 +18331,13 @@
         </is>
       </c>
       <c r="D240" s="4" t="n">
-        <v>280.55</v>
+        <v>286.12</v>
       </c>
       <c r="E240" s="22" t="n">
-        <v>-0.0555</v>
+        <v>-0.0367</v>
       </c>
       <c r="F240" s="22" t="n">
-        <v>-0.0907</v>
+        <v>-0.0726</v>
       </c>
       <c r="G240" s="6" t="n"/>
       <c r="H240" s="7" t="inlineStr">
@@ -18382,13 +18382,13 @@
         </is>
       </c>
       <c r="D241" s="13" t="n">
-        <v>1037.01</v>
+        <v>1027.77</v>
       </c>
       <c r="E241" s="18" t="n">
-        <v>0.2044</v>
+        <v>0.1937</v>
       </c>
       <c r="F241" s="18" t="n">
-        <v>0.05889999999999999</v>
+        <v>0.0495</v>
       </c>
       <c r="G241" s="15" t="n">
         <v>46295</v>
@@ -18417,7 +18417,7 @@
         <v>1525</v>
       </c>
       <c r="M241" s="18" t="n">
-        <v>0.4705740542521287</v>
+        <v>0.4837950125027973</v>
       </c>
       <c r="N241" s="12" t="inlineStr">
         <is>
@@ -18465,13 +18465,13 @@
         </is>
       </c>
       <c r="D242" s="4" t="n">
-        <v>244.77</v>
+        <v>240.35</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>0.3295</v>
+        <v>0.3055</v>
       </c>
       <c r="F242" s="5" t="n">
-        <v>0.1144</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="G242" s="6" t="n"/>
       <c r="H242" s="7" t="inlineStr">
@@ -18516,13 +18516,13 @@
         </is>
       </c>
       <c r="D243" s="13" t="n">
-        <v>308.48</v>
-      </c>
-      <c r="E243" s="14" t="n">
-        <v>-0.0068</v>
+        <v>314.13</v>
+      </c>
+      <c r="E243" s="18" t="n">
+        <v>0.0114</v>
       </c>
       <c r="F243" s="18" t="n">
-        <v>0.1493</v>
+        <v>0.1704</v>
       </c>
       <c r="G243" s="15" t="n">
         <v>46324</v>
@@ -18577,13 +18577,13 @@
         </is>
       </c>
       <c r="D244" s="4" t="n">
-        <v>133.24</v>
+        <v>131.11</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>0.0455</v>
+        <v>0.0288</v>
       </c>
       <c r="F244" s="5" t="n">
-        <v>0.237</v>
+        <v>0.2173</v>
       </c>
       <c r="G244" s="6" t="n">
         <v>46323</v>
@@ -18612,7 +18612,7 @@
         <v>160</v>
       </c>
       <c r="M244" s="5" t="n">
-        <v>0.2008405884118882</v>
+        <v>0.2203493249942795</v>
       </c>
       <c r="N244" s="3" t="inlineStr">
         <is>
@@ -18623,7 +18623,7 @@
         <v>150</v>
       </c>
       <c r="P244" s="5" t="n">
-        <v>0.1257880516361452</v>
+        <v>0.144077492182137</v>
       </c>
       <c r="Q244" s="9" t="inlineStr">
         <is>
@@ -18668,13 +18668,13 @@
         </is>
       </c>
       <c r="D245" s="13" t="n">
-        <v>67.64</v>
+        <v>66.94</v>
       </c>
       <c r="E245" s="18" t="n">
-        <v>0.0493</v>
+        <v>0.0385</v>
       </c>
       <c r="F245" s="18" t="n">
-        <v>0.2345</v>
+        <v>0.2218</v>
       </c>
       <c r="G245" s="15" t="n"/>
       <c r="H245" s="21" t="inlineStr">
@@ -18719,13 +18719,13 @@
         </is>
       </c>
       <c r="D246" s="4" t="n">
-        <v>224.59</v>
+        <v>223.67</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>0.03240000000000001</v>
+        <v>0.0281</v>
       </c>
       <c r="F246" s="5" t="n">
-        <v>0.0646</v>
+        <v>0.0602</v>
       </c>
       <c r="G246" s="6" t="n"/>
       <c r="H246" s="7" t="inlineStr">
@@ -18744,7 +18744,7 @@
         <v>315</v>
       </c>
       <c r="M246" s="5" t="n">
-        <v>0.402555768288882</v>
+        <v>0.408324764161488</v>
       </c>
       <c r="N246" s="3" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>413</v>
       </c>
       <c r="P246" s="5" t="n">
-        <v>0.8389064517565341</v>
+        <v>0.8464702463450621</v>
       </c>
       <c r="Q246" s="9" t="inlineStr">
         <is>
@@ -18804,13 +18804,13 @@
         </is>
       </c>
       <c r="D247" s="13" t="n">
-        <v>374.39</v>
+        <v>373.85</v>
       </c>
       <c r="E247" s="14" t="n">
-        <v>-0.0271</v>
+        <v>-0.0285</v>
       </c>
       <c r="F247" s="14" t="n">
-        <v>-0.2133</v>
+        <v>-0.2144</v>
       </c>
       <c r="G247" s="15" t="n"/>
       <c r="H247" s="21" t="inlineStr">
@@ -18855,13 +18855,13 @@
         </is>
       </c>
       <c r="D248" s="4" t="n">
-        <v>223.51</v>
+        <v>223.32</v>
       </c>
       <c r="E248" s="22" t="n">
-        <v>-0.0425</v>
+        <v>-0.0433</v>
       </c>
       <c r="F248" s="22" t="n">
-        <v>-0.2352</v>
+        <v>-0.2359</v>
       </c>
       <c r="G248" s="6" t="n">
         <v>46321</v>
@@ -18912,13 +18912,13 @@
         </is>
       </c>
       <c r="D249" s="13" t="n">
-        <v>10.54</v>
+        <v>10.83</v>
       </c>
       <c r="E249" s="14" t="n">
-        <v>-0.0949</v>
+        <v>-0.0704</v>
       </c>
       <c r="F249" s="14" t="n">
-        <v>-0.4424</v>
+        <v>-0.4273</v>
       </c>
       <c r="G249" s="15" t="n"/>
       <c r="H249" s="21" t="inlineStr">
@@ -18963,13 +18963,13 @@
         </is>
       </c>
       <c r="D250" s="4" t="n">
-        <v>169.68</v>
+        <v>172.74</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>0.1254</v>
+        <v>0.1457</v>
       </c>
       <c r="F250" s="5" t="n">
-        <v>0.224</v>
+        <v>0.2461</v>
       </c>
       <c r="G250" s="6" t="n"/>
       <c r="H250" s="7" t="inlineStr">
@@ -18988,7 +18988,7 @@
         <v>150</v>
       </c>
       <c r="M250" s="22" t="n">
-        <v>-0.115983026874116</v>
+        <v>-0.131642931573463</v>
       </c>
       <c r="N250" s="3" t="inlineStr">
         <is>
@@ -18999,7 +18999,7 @@
         <v>130</v>
       </c>
       <c r="P250" s="22" t="n">
-        <v>-0.2338519566242339</v>
+        <v>-0.2474238740303346</v>
       </c>
       <c r="Q250" s="9" t="inlineStr">
         <is>
@@ -19040,13 +19040,13 @@
         </is>
       </c>
       <c r="D251" s="13" t="n">
-        <v>71.7</v>
+        <v>70.98</v>
       </c>
       <c r="E251" s="14" t="n">
-        <v>-0.1013</v>
+        <v>-0.1103</v>
       </c>
       <c r="F251" s="14" t="n">
-        <v>-0.2528</v>
+        <v>-0.2603</v>
       </c>
       <c r="G251" s="15" t="n">
         <v>46328</v>
@@ -19101,13 +19101,13 @@
         </is>
       </c>
       <c r="D252" s="4" t="n">
-        <v>280.64</v>
+        <v>278.48</v>
       </c>
       <c r="E252" s="22" t="n">
-        <v>-0.0367</v>
+        <v>-0.0442</v>
       </c>
       <c r="F252" s="22" t="n">
-        <v>-0.1269</v>
+        <v>-0.1336</v>
       </c>
       <c r="G252" s="6" t="n"/>
       <c r="H252" s="7" t="inlineStr">
@@ -19152,13 +19152,13 @@
         </is>
       </c>
       <c r="D253" s="13" t="n">
-        <v>161.85</v>
+        <v>161.72</v>
       </c>
       <c r="E253" s="18" t="n">
-        <v>0.07150000000000001</v>
+        <v>0.0706</v>
       </c>
       <c r="F253" s="18" t="n">
-        <v>0.1508</v>
+        <v>0.1499</v>
       </c>
       <c r="G253" s="15" t="n">
         <v>46275</v>
@@ -19187,7 +19187,7 @@
         <v>280</v>
       </c>
       <c r="M253" s="18" t="n">
-        <v>0.7299969107198023</v>
+        <v>0.7313875834776157</v>
       </c>
       <c r="N253" s="12" t="inlineStr">
         <is>
@@ -19198,7 +19198,7 @@
         <v>245</v>
       </c>
       <c r="P253" s="18" t="n">
-        <v>0.513747296879827</v>
+        <v>0.5149641355429136</v>
       </c>
       <c r="Q253" s="19" t="inlineStr">
         <is>
@@ -19239,13 +19239,13 @@
         </is>
       </c>
       <c r="D254" s="4" t="n">
-        <v>335.57</v>
+        <v>335.1</v>
       </c>
       <c r="E254" s="22" t="n">
-        <v>-0.1285</v>
+        <v>-0.1297</v>
       </c>
       <c r="F254" s="5" t="n">
-        <v>0.0296</v>
+        <v>0.0282</v>
       </c>
       <c r="G254" s="6" t="n"/>
       <c r="H254" s="7" t="inlineStr">
@@ -19264,7 +19264,7 @@
         <v>420</v>
       </c>
       <c r="M254" s="5" t="n">
-        <v>0.2516017522424532</v>
+        <v>0.253357206803939</v>
       </c>
       <c r="N254" s="3" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>415</v>
       </c>
       <c r="P254" s="5" t="n">
-        <v>0.236701731382424</v>
+        <v>0.2384362876753207</v>
       </c>
       <c r="Q254" s="9" t="inlineStr">
         <is>
@@ -19324,13 +19324,13 @@
         </is>
       </c>
       <c r="D255" s="13" t="n">
-        <v>14.02</v>
+        <v>13.56</v>
       </c>
       <c r="E255" s="14" t="n">
-        <v>-0.1004</v>
+        <v>-0.1299</v>
       </c>
       <c r="F255" s="18" t="n">
-        <v>0.2008</v>
+        <v>0.1614</v>
       </c>
       <c r="G255" s="15" t="n"/>
       <c r="H255" s="21" t="inlineStr">
@@ -19375,13 +19375,13 @@
         </is>
       </c>
       <c r="D256" s="4" t="n">
-        <v>35.25</v>
+        <v>35.03</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>0.0679</v>
+        <v>0.0612</v>
       </c>
       <c r="F256" s="5" t="n">
-        <v>0.1284</v>
+        <v>0.1213</v>
       </c>
       <c r="G256" s="6" t="n">
         <v>46315</v>
@@ -19436,13 +19436,13 @@
         </is>
       </c>
       <c r="D257" s="13" t="n">
-        <v>170.47</v>
+        <v>164.7</v>
       </c>
       <c r="E257" s="14" t="n">
-        <v>-0.0328</v>
+        <v>-0.0655</v>
       </c>
       <c r="F257" s="18" t="n">
-        <v>0.1836</v>
+        <v>0.1435</v>
       </c>
       <c r="G257" s="15" t="n"/>
       <c r="H257" s="21" t="inlineStr">
@@ -19487,13 +19487,13 @@
         </is>
       </c>
       <c r="D258" s="4" t="n">
-        <v>170.84</v>
+        <v>169.53</v>
       </c>
       <c r="E258" s="22" t="n">
-        <v>-0.0251</v>
+        <v>-0.0325</v>
       </c>
       <c r="F258" s="5" t="n">
-        <v>0.3474</v>
+        <v>0.3371</v>
       </c>
       <c r="G258" s="6" t="n">
         <v>46328</v>
@@ -19548,13 +19548,13 @@
         </is>
       </c>
       <c r="D259" s="13" t="n">
-        <v>122.64</v>
+        <v>125.57</v>
       </c>
       <c r="E259" s="14" t="n">
-        <v>-0.0873</v>
+        <v>-0.0655</v>
       </c>
       <c r="F259" s="14" t="n">
-        <v>-0.1471</v>
+        <v>-0.1268</v>
       </c>
       <c r="G259" s="15" t="n"/>
       <c r="H259" s="21" t="inlineStr">
@@ -19609,13 +19609,13 @@
         </is>
       </c>
       <c r="D260" s="4" t="n">
-        <v>17.02</v>
+        <v>17.12</v>
       </c>
       <c r="E260" s="22" t="n">
-        <v>-0.1571</v>
+        <v>-0.1521</v>
       </c>
       <c r="F260" s="22" t="n">
-        <v>-0.1529</v>
+        <v>-0.1478</v>
       </c>
       <c r="G260" s="6" t="n"/>
       <c r="H260" s="7" t="inlineStr">
@@ -19660,13 +19660,13 @@
         </is>
       </c>
       <c r="D261" s="13" t="n">
-        <v>176.11</v>
+        <v>176.4</v>
       </c>
       <c r="E261" s="18" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0877</v>
       </c>
       <c r="F261" s="14" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.0675</v>
       </c>
       <c r="G261" s="15" t="n"/>
       <c r="H261" s="21" t="inlineStr">
@@ -19685,7 +19685,7 @@
         <v>265</v>
       </c>
       <c r="M261" s="18" t="n">
-        <v>0.5047413548350461</v>
+        <v>0.5022675736961451</v>
       </c>
       <c r="N261" s="12" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>179</v>
       </c>
       <c r="P261" s="18" t="n">
-        <v>0.01641019817159722</v>
+        <v>0.01473922902494328</v>
       </c>
       <c r="Q261" s="19" t="inlineStr">
         <is>
@@ -19741,13 +19741,13 @@
         </is>
       </c>
       <c r="D262" s="4" t="n">
-        <v>104.17</v>
+        <v>105.24</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>0.07400000000000001</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="F262" s="5" t="n">
-        <v>0.214</v>
+        <v>0.2264</v>
       </c>
       <c r="G262" s="6" t="n">
         <v>46322</v>
@@ -19802,13 +19802,13 @@
         </is>
       </c>
       <c r="D263" s="13" t="n">
-        <v>8.1</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="E263" s="14" t="n">
-        <v>-0.0934</v>
+        <v>-0.09970000000000001</v>
       </c>
       <c r="F263" s="14" t="n">
-        <v>-0.06509999999999999</v>
+        <v>-0.0716</v>
       </c>
       <c r="G263" s="15" t="n"/>
       <c r="H263" s="21" t="inlineStr">
@@ -19853,13 +19853,13 @@
         </is>
       </c>
       <c r="D264" s="4" t="n">
-        <v>91.12</v>
+        <v>88.83</v>
       </c>
       <c r="E264" s="22" t="n">
-        <v>-0.0693</v>
+        <v>-0.09269999999999999</v>
       </c>
       <c r="F264" s="5" t="n">
-        <v>0.0799</v>
+        <v>0.0528</v>
       </c>
       <c r="G264" s="6" t="n"/>
       <c r="H264" s="7" t="inlineStr">
@@ -19904,13 +19904,13 @@
         </is>
       </c>
       <c r="D265" s="13" t="n">
-        <v>15.3</v>
+        <v>15.24</v>
       </c>
       <c r="E265" s="14" t="n">
-        <v>-0.1334</v>
+        <v>-0.1365</v>
       </c>
       <c r="F265" s="14" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.0786</v>
       </c>
       <c r="G265" s="15" t="n"/>
       <c r="H265" s="21" t="inlineStr">
@@ -19955,13 +19955,13 @@
         </is>
       </c>
       <c r="D266" s="4" t="n">
-        <v>391.84</v>
+        <v>390.35</v>
       </c>
       <c r="E266" s="22" t="n">
-        <v>-0.0298</v>
+        <v>-0.0335</v>
       </c>
       <c r="F266" s="5" t="n">
-        <v>0.101</v>
+        <v>0.0968</v>
       </c>
       <c r="G266" s="6" t="n">
         <v>46317</v>
@@ -20030,13 +20030,13 @@
         </is>
       </c>
       <c r="D267" s="13" t="n">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="E267" s="14" t="n">
-        <v>-0.3265999999999999</v>
+        <v>-0.315</v>
       </c>
       <c r="F267" s="14" t="n">
-        <v>-0.4036</v>
+        <v>-0.3933</v>
       </c>
       <c r="G267" s="15" t="n"/>
       <c r="H267" s="21" t="inlineStr">
@@ -20081,13 +20081,13 @@
         </is>
       </c>
       <c r="D268" s="4" t="n">
-        <v>19.64</v>
+        <v>19.45</v>
       </c>
       <c r="E268" s="22" t="n">
-        <v>-0.1165</v>
+        <v>-0.1251</v>
       </c>
       <c r="F268" s="5" t="n">
-        <v>0.0984</v>
+        <v>0.08779999999999999</v>
       </c>
       <c r="G268" s="6" t="n"/>
       <c r="H268" s="7" t="inlineStr">
@@ -20132,13 +20132,13 @@
         </is>
       </c>
       <c r="D269" s="13" t="n">
-        <v>17.76</v>
+        <v>17.58</v>
       </c>
       <c r="E269" s="14" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="F269" s="18" t="n">
-        <v>0.2954</v>
+        <v>0.2823</v>
       </c>
       <c r="G269" s="15" t="n">
         <v>46274</v>
@@ -20193,13 +20193,13 @@
         </is>
       </c>
       <c r="D270" s="4" t="n">
-        <v>204.51</v>
+        <v>206.15</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>0.0269</v>
+        <v>0.0351</v>
       </c>
       <c r="F270" s="22" t="n">
-        <v>-0.0205</v>
+        <v>-0.0126</v>
       </c>
       <c r="G270" s="6" t="n">
         <v>46328</v>
@@ -20254,13 +20254,13 @@
         </is>
       </c>
       <c r="D271" s="13" t="n">
-        <v>214.34</v>
+        <v>209.13</v>
       </c>
       <c r="E271" s="18" t="n">
-        <v>0.0277</v>
+        <v>0.0028</v>
       </c>
       <c r="F271" s="18" t="n">
-        <v>0.3578</v>
+        <v>0.3248</v>
       </c>
       <c r="G271" s="15" t="n">
         <v>46316</v>
@@ -20335,13 +20335,13 @@
         </is>
       </c>
       <c r="D272" s="4" t="n">
-        <v>39.82</v>
+        <v>38.93</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>0.2657</v>
+        <v>0.2374</v>
       </c>
       <c r="F272" s="5" t="n">
-        <v>0.4066</v>
+        <v>0.3751</v>
       </c>
       <c r="G272" s="6" t="n">
         <v>46329</v>
@@ -20396,13 +20396,13 @@
         </is>
       </c>
       <c r="D273" s="13" t="n">
-        <v>336.32</v>
-      </c>
-      <c r="E273" s="18" t="n">
-        <v>0.0048</v>
+        <v>331.6</v>
+      </c>
+      <c r="E273" s="14" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F273" s="18" t="n">
-        <v>0.2864</v>
+        <v>0.2683</v>
       </c>
       <c r="G273" s="15" t="n"/>
       <c r="H273" s="21" t="inlineStr">
@@ -20421,7 +20421,7 @@
         <v>320</v>
       </c>
       <c r="M273" s="14" t="n">
-        <v>-0.04852521408182681</v>
+        <v>-0.03498190591073589</v>
       </c>
       <c r="N273" s="12" t="inlineStr">
         <is>
@@ -20432,7 +20432,7 @@
         <v>280</v>
       </c>
       <c r="P273" s="14" t="n">
-        <v>-0.1674595623215984</v>
+        <v>-0.1556091676718939</v>
       </c>
       <c r="Q273" s="19" t="inlineStr">
         <is>
@@ -20473,13 +20473,13 @@
         </is>
       </c>
       <c r="D274" s="4" t="n">
-        <v>392</v>
+        <v>393.22</v>
       </c>
       <c r="E274" s="22" t="n">
-        <v>-0.0478</v>
+        <v>-0.04480000000000001</v>
       </c>
       <c r="F274" s="22" t="n">
-        <v>-0.1201</v>
+        <v>-0.1174</v>
       </c>
       <c r="G274" s="6" t="n"/>
       <c r="H274" s="7" t="inlineStr">
@@ -20498,7 +20498,7 @@
         <v>535</v>
       </c>
       <c r="M274" s="5" t="n">
-        <v>0.3647959183673469</v>
+        <v>0.3605615177254462</v>
       </c>
       <c r="N274" s="3" t="inlineStr"/>
       <c r="O274" s="8" t="n"/>
@@ -20542,13 +20542,13 @@
         </is>
       </c>
       <c r="D275" s="13" t="n">
-        <v>6.55</v>
+        <v>6.48</v>
       </c>
       <c r="E275" s="14" t="n">
-        <v>-0.122</v>
+        <v>-0.1314</v>
       </c>
       <c r="F275" s="14" t="n">
-        <v>-0.0136</v>
+        <v>-0.0241</v>
       </c>
       <c r="G275" s="15" t="n"/>
       <c r="H275" s="21" t="inlineStr">
@@ -20593,13 +20593,13 @@
         </is>
       </c>
       <c r="D276" s="4" t="n">
-        <v>75.44</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="E276" s="5" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.1127</v>
       </c>
       <c r="F276" s="5" t="n">
-        <v>0.2494</v>
+        <v>0.2676</v>
       </c>
       <c r="G276" s="6" t="n">
         <v>46322</v>
@@ -20654,13 +20654,13 @@
         </is>
       </c>
       <c r="D277" s="13" t="n">
-        <v>95.56</v>
+        <v>93.93000000000001</v>
       </c>
       <c r="E277" s="14" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.103</v>
       </c>
       <c r="F277" s="14" t="n">
-        <v>-0.2461</v>
+        <v>-0.259</v>
       </c>
       <c r="G277" s="15" t="n"/>
       <c r="H277" s="21" t="inlineStr">
@@ -20705,13 +20705,13 @@
         </is>
       </c>
       <c r="D278" s="4" t="n">
-        <v>205.18</v>
+        <v>204.64</v>
       </c>
       <c r="E278" s="22" t="n">
-        <v>-0.0425</v>
+        <v>-0.045</v>
       </c>
       <c r="F278" s="5" t="n">
-        <v>0.024</v>
+        <v>0.0214</v>
       </c>
       <c r="G278" s="6" t="n">
         <v>46330</v>
@@ -20766,13 +20766,13 @@
         </is>
       </c>
       <c r="D279" s="13" t="n">
-        <v>379.08</v>
+        <v>383.69</v>
       </c>
       <c r="E279" s="18" t="n">
-        <v>0.0383</v>
+        <v>0.0509</v>
       </c>
       <c r="F279" s="18" t="n">
-        <v>0.0542</v>
+        <v>0.067</v>
       </c>
       <c r="G279" s="15" t="n">
         <v>46322</v>
@@ -20827,13 +20827,13 @@
         </is>
       </c>
       <c r="D280" s="4" t="n">
-        <v>57.92</v>
+        <v>57.4</v>
       </c>
       <c r="E280" s="22" t="n">
-        <v>-0.0089</v>
+        <v>-0.0178</v>
       </c>
       <c r="F280" s="5" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.0867</v>
       </c>
       <c r="G280" s="6" t="n"/>
       <c r="H280" s="7" t="inlineStr">
@@ -20878,13 +20878,13 @@
         </is>
       </c>
       <c r="D281" s="13" t="n">
-        <v>435.94</v>
+        <v>435.56</v>
       </c>
       <c r="E281" s="18" t="n">
-        <v>0.0417</v>
+        <v>0.0408</v>
       </c>
       <c r="F281" s="18" t="n">
-        <v>0.0042</v>
+        <v>0.0033</v>
       </c>
       <c r="G281" s="15" t="n">
         <v>46310</v>
@@ -20961,13 +20961,13 @@
         </is>
       </c>
       <c r="D282" s="4" t="n">
-        <v>127.2</v>
+        <v>124.25</v>
       </c>
       <c r="E282" s="22" t="n">
-        <v>-0.0221</v>
+        <v>-0.04480000000000001</v>
       </c>
       <c r="F282" s="22" t="n">
-        <v>-0.1314</v>
+        <v>-0.1515</v>
       </c>
       <c r="G282" s="6" t="n"/>
       <c r="H282" s="7" t="inlineStr">
@@ -21012,13 +21012,13 @@
         </is>
       </c>
       <c r="D283" s="13" t="n">
-        <v>226.85</v>
+        <v>227.24</v>
       </c>
       <c r="E283" s="14" t="n">
-        <v>-0.09279999999999999</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="F283" s="18" t="n">
-        <v>0.0573</v>
+        <v>0.0591</v>
       </c>
       <c r="G283" s="15" t="n">
         <v>46324</v>
@@ -21073,13 +21073,13 @@
         </is>
       </c>
       <c r="D284" s="4" t="n">
-        <v>260.27</v>
+        <v>261.59</v>
       </c>
       <c r="E284" s="22" t="n">
-        <v>-0.07190000000000001</v>
+        <v>-0.0672</v>
       </c>
       <c r="F284" s="22" t="n">
-        <v>-0.1644</v>
+        <v>-0.1601</v>
       </c>
       <c r="G284" s="6" t="n">
         <v>46315</v>
@@ -21108,7 +21108,7 @@
         <v>300</v>
       </c>
       <c r="M284" s="5" t="n">
-        <v>0.1526491720136782</v>
+        <v>0.1468328300011469</v>
       </c>
       <c r="N284" s="3" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>316</v>
       </c>
       <c r="P284" s="5" t="n">
-        <v>0.2141237945210744</v>
+        <v>0.2079972476012081</v>
       </c>
       <c r="Q284" s="9" t="inlineStr">
         <is>
@@ -21176,13 +21176,13 @@
         </is>
       </c>
       <c r="D285" s="13" t="n">
-        <v>343.44</v>
+        <v>342.62</v>
       </c>
       <c r="E285" s="18" t="n">
-        <v>0.0779</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="F285" s="18" t="n">
-        <v>0.1097</v>
+        <v>0.1071</v>
       </c>
       <c r="G285" s="15" t="n"/>
       <c r="H285" s="21" t="inlineStr">
@@ -21201,7 +21201,7 @@
         <v>335</v>
       </c>
       <c r="M285" s="14" t="n">
-        <v>-0.02457488935476356</v>
+        <v>-0.02224038293152765</v>
       </c>
       <c r="N285" s="12" t="inlineStr">
         <is>
@@ -21212,7 +21212,7 @@
         <v>375</v>
       </c>
       <c r="P285" s="18" t="n">
-        <v>0.09189378057302586</v>
+        <v>0.09450703403187204</v>
       </c>
       <c r="Q285" s="19" t="inlineStr">
         <is>
@@ -21253,13 +21253,13 @@
         </is>
       </c>
       <c r="D286" s="4" t="n">
-        <v>42.6</v>
+        <v>42.54</v>
       </c>
       <c r="E286" s="22" t="n">
-        <v>-0.0116</v>
+        <v>-0.0129</v>
       </c>
       <c r="F286" s="5" t="n">
-        <v>0.3791</v>
+        <v>0.3773</v>
       </c>
       <c r="G286" s="6" t="n"/>
       <c r="H286" s="7" t="inlineStr">
@@ -21304,13 +21304,13 @@
         </is>
       </c>
       <c r="D287" s="13" t="n">
-        <v>6.36</v>
+        <v>6.52</v>
       </c>
       <c r="E287" s="14" t="n">
-        <v>-0.1491</v>
+        <v>-0.1283</v>
       </c>
       <c r="F287" s="14" t="n">
-        <v>-0.2054</v>
+        <v>-0.186</v>
       </c>
       <c r="G287" s="15" t="n"/>
       <c r="H287" s="21" t="inlineStr">
@@ -21355,13 +21355,13 @@
         </is>
       </c>
       <c r="D288" s="4" t="n">
-        <v>185.06</v>
+        <v>186.05</v>
       </c>
       <c r="E288" s="5" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.0101</v>
       </c>
       <c r="F288" s="5" t="n">
-        <v>0.3318</v>
+        <v>0.339</v>
       </c>
       <c r="G288" s="6" t="n"/>
       <c r="H288" s="7" t="inlineStr">
@@ -21406,13 +21406,13 @@
         </is>
       </c>
       <c r="D289" s="13" t="n">
-        <v>487.09</v>
+        <v>482.28</v>
       </c>
       <c r="E289" s="18" t="n">
-        <v>0.1112</v>
+        <v>0.1002</v>
       </c>
       <c r="F289" s="14" t="n">
-        <v>-0.1639</v>
+        <v>-0.1722</v>
       </c>
       <c r="G289" s="15" t="n">
         <v>46324</v>
@@ -21441,7 +21441,7 @@
         <v>730</v>
       </c>
       <c r="M289" s="18" t="n">
-        <v>0.4986963394855161</v>
+        <v>0.5136435265820686</v>
       </c>
       <c r="N289" s="12" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>575</v>
       </c>
       <c r="P289" s="18" t="n">
-        <v>0.1804799934303723</v>
+        <v>0.1922534627187527</v>
       </c>
       <c r="Q289" s="19" t="inlineStr">
         <is>
@@ -21493,13 +21493,13 @@
         </is>
       </c>
       <c r="D290" s="4" t="n">
-        <v>28.52</v>
+        <v>27.25</v>
       </c>
       <c r="E290" s="22" t="n">
-        <v>-0.0266</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F290" s="22" t="n">
-        <v>-0.1918</v>
+        <v>-0.2278</v>
       </c>
       <c r="G290" s="6" t="n"/>
       <c r="H290" s="7" t="inlineStr">
@@ -21544,13 +21544,13 @@
         </is>
       </c>
       <c r="D291" s="13" t="n">
-        <v>95.84999999999999</v>
+        <v>96.18000000000001</v>
       </c>
       <c r="E291" s="14" t="n">
-        <v>-0.1059</v>
+        <v>-0.1028</v>
       </c>
       <c r="F291" s="18" t="n">
-        <v>0.0678</v>
+        <v>0.07150000000000001</v>
       </c>
       <c r="G291" s="15" t="n"/>
       <c r="H291" s="21" t="inlineStr">
@@ -21595,13 +21595,13 @@
         </is>
       </c>
       <c r="D292" s="4" t="n">
-        <v>168.15</v>
+        <v>166.1</v>
       </c>
       <c r="E292" s="22" t="n">
-        <v>-0.0483</v>
+        <v>-0.0599</v>
       </c>
       <c r="F292" s="5" t="n">
-        <v>0.2073</v>
+        <v>0.1926</v>
       </c>
       <c r="G292" s="6" t="n"/>
       <c r="H292" s="7" t="inlineStr">
@@ -21646,13 +21646,13 @@
         </is>
       </c>
       <c r="D293" s="13" t="n">
-        <v>296.49</v>
+        <v>295.27</v>
       </c>
       <c r="E293" s="14" t="n">
-        <v>-0.0379</v>
+        <v>-0.04190000000000001</v>
       </c>
       <c r="F293" s="14" t="n">
-        <v>-0.0101</v>
+        <v>-0.0142</v>
       </c>
       <c r="G293" s="15" t="n"/>
       <c r="H293" s="21" t="inlineStr">
@@ -21697,13 +21697,13 @@
         </is>
       </c>
       <c r="D294" s="4" t="n">
-        <v>92.33</v>
+        <v>92.25</v>
       </c>
       <c r="E294" s="5" t="n">
-        <v>0.019</v>
+        <v>0.0181</v>
       </c>
       <c r="F294" s="5" t="n">
-        <v>0.1304</v>
+        <v>0.1294</v>
       </c>
       <c r="G294" s="6" t="n"/>
       <c r="H294" s="7" t="inlineStr">
@@ -21748,13 +21748,13 @@
         </is>
       </c>
       <c r="D295" s="13" t="n">
-        <v>130.25</v>
+        <v>128</v>
       </c>
       <c r="E295" s="14" t="n">
-        <v>-0.07980000000000001</v>
+        <v>-0.09570000000000001</v>
       </c>
       <c r="F295" s="14" t="n">
-        <v>-0.0329</v>
+        <v>-0.0496</v>
       </c>
       <c r="G295" s="15" t="n"/>
       <c r="H295" s="21" t="inlineStr">
@@ -21773,7 +21773,7 @@
         <v>166</v>
       </c>
       <c r="M295" s="18" t="n">
-        <v>0.2744721689059501</v>
+        <v>0.296875</v>
       </c>
       <c r="N295" s="12" t="inlineStr"/>
       <c r="O295" s="17" t="n"/>
@@ -21821,13 +21821,13 @@
         </is>
       </c>
       <c r="D296" s="4" t="n">
-        <v>29.26</v>
+        <v>29.4</v>
       </c>
       <c r="E296" s="22" t="n">
-        <v>-0.0432</v>
+        <v>-0.0386</v>
       </c>
       <c r="F296" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0127</v>
       </c>
       <c r="G296" s="6" t="n">
         <v>46317</v>
@@ -21882,13 +21882,13 @@
         </is>
       </c>
       <c r="D297" s="13" t="n">
-        <v>274.35</v>
+        <v>272.3</v>
       </c>
       <c r="E297" s="14" t="n">
-        <v>-0.0354</v>
-      </c>
-      <c r="F297" s="18" t="n">
-        <v>0.0001</v>
+        <v>-0.0426</v>
+      </c>
+      <c r="F297" s="14" t="n">
+        <v>-0.0073</v>
       </c>
       <c r="G297" s="15" t="n">
         <v>46322</v>
@@ -21917,7 +21917,7 @@
         <v>275</v>
       </c>
       <c r="M297" s="18" t="n">
-        <v>0.00236923637689075</v>
+        <v>0.009915534337128126</v>
       </c>
       <c r="N297" s="12" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>312</v>
       </c>
       <c r="P297" s="18" t="n">
-        <v>0.1372334609075997</v>
+        <v>0.1457950789570326</v>
       </c>
       <c r="Q297" s="19" t="inlineStr">
         <is>
@@ -21981,13 +21981,13 @@
         </is>
       </c>
       <c r="D298" s="4" t="n">
-        <v>36.23</v>
+        <v>35.77</v>
       </c>
       <c r="E298" s="22" t="n">
-        <v>-0.0279</v>
+        <v>-0.04019999999999999</v>
       </c>
       <c r="F298" s="22" t="n">
-        <v>-0.0902</v>
+        <v>-0.1017</v>
       </c>
       <c r="G298" s="6" t="n">
         <v>46322</v>
@@ -22046,13 +22046,13 @@
         </is>
       </c>
       <c r="D299" s="13" t="n">
-        <v>76.48999999999999</v>
+        <v>76.23</v>
       </c>
       <c r="E299" s="18" t="n">
-        <v>0.0848</v>
+        <v>0.08109999999999999</v>
       </c>
       <c r="F299" s="18" t="n">
-        <v>0.2433</v>
+        <v>0.2391</v>
       </c>
       <c r="G299" s="15" t="n">
         <v>46310</v>
@@ -22107,13 +22107,13 @@
         </is>
       </c>
       <c r="D300" s="4" t="n">
-        <v>464.93</v>
+        <v>466.65</v>
       </c>
       <c r="E300" s="22" t="n">
-        <v>-0.0559</v>
+        <v>-0.0524</v>
       </c>
       <c r="F300" s="22" t="n">
-        <v>-0.1224</v>
+        <v>-0.1192</v>
       </c>
       <c r="G300" s="6" t="n">
         <v>46325</v>
@@ -22142,7 +22142,7 @@
         <v>570</v>
       </c>
       <c r="M300" s="5" t="n">
-        <v>0.2259910093992644</v>
+        <v>0.2214721954355513</v>
       </c>
       <c r="N300" s="3" t="inlineStr">
         <is>
@@ -22153,7 +22153,7 @@
         <v>525</v>
       </c>
       <c r="P300" s="5" t="n">
-        <v>0.1292022454993225</v>
+        <v>0.1250401800064289</v>
       </c>
       <c r="Q300" s="9" t="inlineStr">
         <is>
@@ -22206,13 +22206,13 @@
         </is>
       </c>
       <c r="D301" s="13" t="n">
-        <v>510.96</v>
+        <v>502.98</v>
       </c>
       <c r="E301" s="14" t="n">
-        <v>-0.0702</v>
+        <v>-0.08470000000000001</v>
       </c>
       <c r="F301" s="14" t="n">
-        <v>-0.1155</v>
+        <v>-0.1294</v>
       </c>
       <c r="G301" s="15" t="n">
         <v>46329</v>
@@ -22241,7 +22241,7 @@
         <v>616</v>
       </c>
       <c r="M301" s="18" t="n">
-        <v>0.2055738218255833</v>
+        <v>0.2247007833313451</v>
       </c>
       <c r="N301" s="12" t="inlineStr"/>
       <c r="O301" s="17" t="n"/>
@@ -22285,13 +22285,13 @@
         </is>
       </c>
       <c r="D302" s="4" t="n">
-        <v>260.3</v>
+        <v>257.87</v>
       </c>
       <c r="E302" s="22" t="n">
-        <v>-0.0521</v>
+        <v>-0.061</v>
       </c>
       <c r="F302" s="5" t="n">
-        <v>0.1448</v>
+        <v>0.1341</v>
       </c>
       <c r="G302" s="6" t="n">
         <v>46321</v>
@@ -22320,7 +22320,7 @@
         <v>283</v>
       </c>
       <c r="M302" s="5" t="n">
-        <v>0.08720706876680748</v>
+        <v>0.09745220459921664</v>
       </c>
       <c r="N302" s="3" t="inlineStr"/>
       <c r="O302" s="8" t="n"/>
@@ -22366,13 +22366,13 @@
         </is>
       </c>
       <c r="D303" s="13" t="n">
-        <v>231.59</v>
+        <v>227.36</v>
       </c>
       <c r="E303" s="14" t="n">
-        <v>-0.09089999999999999</v>
-      </c>
-      <c r="F303" s="18" t="n">
-        <v>0.0123</v>
+        <v>-0.1075</v>
+      </c>
+      <c r="F303" s="14" t="n">
+        <v>-0.0062</v>
       </c>
       <c r="G303" s="15" t="n">
         <v>46323</v>
@@ -22401,7 +22401,7 @@
         <v>246</v>
       </c>
       <c r="M303" s="18" t="n">
-        <v>0.06222203031218963</v>
+        <v>0.08198451794510901</v>
       </c>
       <c r="N303" s="12" t="inlineStr"/>
       <c r="O303" s="17" t="n"/>
@@ -22449,13 +22449,13 @@
         </is>
       </c>
       <c r="D304" s="4" t="n">
-        <v>108.61</v>
+        <v>107.15</v>
       </c>
       <c r="E304" s="22" t="n">
-        <v>-0.0594</v>
+        <v>-0.0721</v>
       </c>
       <c r="F304" s="22" t="n">
-        <v>-0.0698</v>
+        <v>-0.0823</v>
       </c>
       <c r="G304" s="6" t="n">
         <v>46322</v>
@@ -22484,7 +22484,7 @@
         <v>130</v>
       </c>
       <c r="M304" s="5" t="n">
-        <v>0.1969431912346929</v>
+        <v>0.2132524498366775</v>
       </c>
       <c r="N304" s="3" t="inlineStr">
         <is>
@@ -22495,7 +22495,7 @@
         <v>128</v>
       </c>
       <c r="P304" s="5" t="n">
-        <v>0.178528680600313</v>
+        <v>0.1945870275314978</v>
       </c>
       <c r="Q304" s="9" t="inlineStr">
         <is>
@@ -22544,13 +22544,13 @@
         </is>
       </c>
       <c r="D305" s="13" t="n">
-        <v>101.13</v>
+        <v>99.70999999999999</v>
       </c>
       <c r="E305" s="14" t="n">
-        <v>-0.1277</v>
+        <v>-0.1399</v>
       </c>
       <c r="F305" s="14" t="n">
-        <v>-0.0378</v>
+        <v>-0.0512</v>
       </c>
       <c r="G305" s="15" t="n">
         <v>46301</v>
@@ -22579,7 +22579,7 @@
         <v>135</v>
       </c>
       <c r="M305" s="18" t="n">
-        <v>0.3349154553544943</v>
+        <v>0.3539263865209107</v>
       </c>
       <c r="N305" s="12" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>125</v>
       </c>
       <c r="P305" s="18" t="n">
-        <v>0.2360328290319391</v>
+        <v>0.2536355430749173</v>
       </c>
       <c r="Q305" s="19" t="inlineStr"/>
       <c r="R305" s="17" t="n"/>
@@ -22625,13 +22625,13 @@
         </is>
       </c>
       <c r="D306" s="4" t="n">
-        <v>322.74</v>
+        <v>320.7</v>
       </c>
       <c r="E306" s="22" t="n">
-        <v>-0.1102</v>
+        <v>-0.1158</v>
       </c>
       <c r="F306" s="22" t="n">
-        <v>-0.0337</v>
+        <v>-0.0398</v>
       </c>
       <c r="G306" s="6" t="n">
         <v>46322</v>
@@ -22660,7 +22660,7 @@
         <v>350</v>
       </c>
       <c r="M306" s="5" t="n">
-        <v>0.08446427464832369</v>
+        <v>0.09136264421577803</v>
       </c>
       <c r="N306" s="3" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>400</v>
       </c>
       <c r="P306" s="5" t="n">
-        <v>0.2393877424552271</v>
+        <v>0.2472715933894606</v>
       </c>
       <c r="Q306" s="9" t="inlineStr">
         <is>
@@ -22712,13 +22712,13 @@
         </is>
       </c>
       <c r="D307" s="13" t="n">
-        <v>99.48</v>
-      </c>
-      <c r="E307" s="18" t="n">
-        <v>0.0153</v>
+        <v>97.06</v>
+      </c>
+      <c r="E307" s="14" t="n">
+        <v>-0.009399999999999999</v>
       </c>
       <c r="F307" s="18" t="n">
-        <v>0.254</v>
+        <v>0.2235</v>
       </c>
       <c r="G307" s="15" t="n"/>
       <c r="H307" s="21" t="inlineStr">
@@ -22759,13 +22759,13 @@
         </is>
       </c>
       <c r="D308" s="4" t="n">
-        <v>49.59</v>
+        <v>48.89</v>
       </c>
       <c r="E308" s="22" t="n">
-        <v>-0.1236</v>
+        <v>-0.1361</v>
       </c>
       <c r="F308" s="22" t="n">
-        <v>-0.2961</v>
+        <v>-0.306</v>
       </c>
       <c r="G308" s="6" t="n">
         <v>46267</v>
@@ -22820,13 +22820,13 @@
         </is>
       </c>
       <c r="D309" s="13" t="n">
-        <v>72.40000000000001</v>
+        <v>72.61</v>
       </c>
       <c r="E309" s="14" t="n">
-        <v>-0.0234</v>
+        <v>-0.0206</v>
       </c>
       <c r="F309" s="14" t="n">
-        <v>-0.0711</v>
+        <v>-0.06849999999999999</v>
       </c>
       <c r="G309" s="15" t="n">
         <v>46315</v>
@@ -22855,14 +22855,14 @@
         <v>83</v>
       </c>
       <c r="M309" s="18" t="n">
-        <v>0.1464088397790054</v>
+        <v>0.1430932378460267</v>
       </c>
       <c r="N309" s="12" t="inlineStr"/>
       <c r="O309" s="17" t="n">
         <v>87</v>
       </c>
       <c r="P309" s="18" t="n">
-        <v>0.2016574585635358</v>
+        <v>0.1981820685855943</v>
       </c>
       <c r="Q309" s="19" t="inlineStr"/>
       <c r="R309" s="17" t="n"/>
@@ -22897,13 +22897,13 @@
         </is>
       </c>
       <c r="D310" s="4" t="n">
-        <v>175.06</v>
+        <v>175.58</v>
       </c>
       <c r="E310" s="5" t="n">
-        <v>0.0352</v>
+        <v>0.0383</v>
       </c>
       <c r="F310" s="5" t="n">
-        <v>0.0384</v>
+        <v>0.0415</v>
       </c>
       <c r="G310" s="6" t="n">
         <v>46322</v>
@@ -22932,7 +22932,7 @@
         <v>200</v>
       </c>
       <c r="M310" s="5" t="n">
-        <v>0.1424654404204273</v>
+        <v>0.1390818999886091</v>
       </c>
       <c r="N310" s="3" t="inlineStr"/>
       <c r="O310" s="8" t="n"/>
@@ -22980,13 +22980,13 @@
         </is>
       </c>
       <c r="D311" s="13" t="n">
-        <v>142.54</v>
+        <v>139.69</v>
       </c>
       <c r="E311" s="14" t="n">
-        <v>-0.0097</v>
+        <v>-0.0295</v>
       </c>
       <c r="F311" s="18" t="n">
-        <v>0.0216</v>
+        <v>0.0011</v>
       </c>
       <c r="G311" s="15" t="n">
         <v>46317</v>
@@ -23045,13 +23045,13 @@
         </is>
       </c>
       <c r="D312" s="4" t="n">
-        <v>189.04</v>
+        <v>189.13</v>
       </c>
       <c r="E312" s="22" t="n">
-        <v>-0.0118</v>
+        <v>-0.0113</v>
       </c>
       <c r="F312" s="5" t="n">
-        <v>0.0479</v>
+        <v>0.0483</v>
       </c>
       <c r="G312" s="6" t="n">
         <v>46317</v>
@@ -23080,7 +23080,7 @@
         <v>220</v>
       </c>
       <c r="M312" s="5" t="n">
-        <v>0.1637748624629708</v>
+        <v>0.1632210648760112</v>
       </c>
       <c r="N312" s="3" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>230</v>
       </c>
       <c r="P312" s="5" t="n">
-        <v>0.2166737198476514</v>
+        <v>0.2160947496431027</v>
       </c>
       <c r="Q312" s="9" t="inlineStr">
         <is>
@@ -23132,13 +23132,13 @@
         </is>
       </c>
       <c r="D313" s="13" t="n">
-        <v>1037.54</v>
+        <v>1043.06</v>
       </c>
       <c r="E313" s="14" t="n">
-        <v>-0.005600000000000001</v>
+        <v>-0.0003</v>
       </c>
       <c r="F313" s="14" t="n">
-        <v>-0.013</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="G313" s="15" t="n"/>
       <c r="H313" s="21" t="inlineStr">
@@ -23157,7 +23157,7 @@
         <v>1200</v>
       </c>
       <c r="M313" s="18" t="n">
-        <v>0.1565819149141238</v>
+        <v>0.1504611431748893</v>
       </c>
       <c r="N313" s="12" t="inlineStr">
         <is>
@@ -23168,7 +23168,7 @@
         <v>1240</v>
       </c>
       <c r="P313" s="18" t="n">
-        <v>0.1951346454112613</v>
+        <v>0.1888098479473856</v>
       </c>
       <c r="Q313" s="19" t="inlineStr">
         <is>
@@ -23213,13 +23213,13 @@
         </is>
       </c>
       <c r="D314" s="4" t="n">
-        <v>115.65</v>
+        <v>115.19</v>
       </c>
       <c r="E314" s="22" t="n">
-        <v>-0.0126</v>
+        <v>-0.0166</v>
       </c>
       <c r="F314" s="22" t="n">
-        <v>-0.0437</v>
+        <v>-0.0475</v>
       </c>
       <c r="G314" s="6" t="n">
         <v>46325</v>
@@ -23248,7 +23248,7 @@
         <v>129</v>
       </c>
       <c r="M314" s="5" t="n">
-        <v>0.1154345006485084</v>
+        <v>0.1198888792429899</v>
       </c>
       <c r="N314" s="3" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>122</v>
       </c>
       <c r="P314" s="5" t="n">
-        <v>0.05490704712494591</v>
+        <v>0.05911971525306018</v>
       </c>
       <c r="Q314" s="9" t="inlineStr">
         <is>
@@ -23300,13 +23300,13 @@
         </is>
       </c>
       <c r="D315" s="13" t="n">
-        <v>60.53</v>
+        <v>60.12</v>
       </c>
       <c r="E315" s="14" t="n">
-        <v>-0.0219</v>
+        <v>-0.0287</v>
       </c>
       <c r="F315" s="14" t="n">
-        <v>-0.0438</v>
+        <v>-0.0505</v>
       </c>
       <c r="G315" s="15" t="n">
         <v>46328</v>
@@ -23335,14 +23335,14 @@
         <v>65</v>
       </c>
       <c r="M315" s="18" t="n">
-        <v>0.07384767883694034</v>
+        <v>0.08117099135063212</v>
       </c>
       <c r="N315" s="12" t="inlineStr"/>
       <c r="O315" s="17" t="n">
         <v>67</v>
       </c>
       <c r="P315" s="18" t="n">
-        <v>0.106889145878077</v>
+        <v>0.1144377910844977</v>
       </c>
       <c r="Q315" s="19" t="inlineStr">
         <is>
@@ -23383,13 +23383,13 @@
         </is>
       </c>
       <c r="D316" s="4" t="n">
-        <v>135.96</v>
+        <v>135.7</v>
       </c>
       <c r="E316" s="22" t="n">
-        <v>-0.0202</v>
+        <v>-0.0221</v>
       </c>
       <c r="F316" s="22" t="n">
-        <v>-0.0349</v>
+        <v>-0.0367</v>
       </c>
       <c r="G316" s="6" t="n">
         <v>46310</v>
@@ -23418,7 +23418,7 @@
         <v>167</v>
       </c>
       <c r="M316" s="5" t="n">
-        <v>0.2283024418946748</v>
+        <v>0.2306558585114224</v>
       </c>
       <c r="N316" s="3" t="inlineStr"/>
       <c r="O316" s="8" t="n"/>
@@ -23462,13 +23462,13 @@
         </is>
       </c>
       <c r="D317" s="13" t="n">
-        <v>296.61</v>
+        <v>294.58</v>
       </c>
       <c r="E317" s="14" t="n">
-        <v>-0.08929999999999999</v>
+        <v>-0.0956</v>
       </c>
       <c r="F317" s="14" t="n">
-        <v>-0.0747</v>
+        <v>-0.081</v>
       </c>
       <c r="G317" s="15" t="n"/>
       <c r="H317" s="21" t="inlineStr">
@@ -23494,7 +23494,7 @@
         <v>316</v>
       </c>
       <c r="P317" s="18" t="n">
-        <v>0.06537203735544987</v>
+        <v>0.07271369407291743</v>
       </c>
       <c r="Q317" s="19" t="inlineStr">
         <is>
@@ -23535,13 +23535,13 @@
         </is>
       </c>
       <c r="D318" s="4" t="n">
-        <v>207.54</v>
+        <v>204.63</v>
       </c>
       <c r="E318" s="22" t="n">
-        <v>-0.059</v>
+        <v>-0.0722</v>
       </c>
       <c r="F318" s="22" t="n">
-        <v>-0.05139999999999999</v>
+        <v>-0.0646</v>
       </c>
       <c r="G318" s="6" t="n">
         <v>46328</v>
@@ -23577,7 +23577,7 @@
         <v>215</v>
       </c>
       <c r="P318" s="5" t="n">
-        <v>0.0359448780957888</v>
+        <v>0.05067683135415142</v>
       </c>
       <c r="Q318" s="9" t="inlineStr">
         <is>
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="D319" s="13" t="n">
-        <v>116.19</v>
+        <v>116.06</v>
       </c>
       <c r="E319" s="14" t="n">
-        <v>-0.0201</v>
+        <v>-0.0212</v>
       </c>
       <c r="F319" s="14" t="n">
-        <v>-0.0226</v>
+        <v>-0.0237</v>
       </c>
       <c r="G319" s="15" t="n"/>
       <c r="H319" s="21" t="inlineStr">
@@ -23643,7 +23643,7 @@
         <v>142</v>
       </c>
       <c r="M319" s="18" t="n">
-        <v>0.2221361562957226</v>
+        <v>0.2235050835774599</v>
       </c>
       <c r="N319" s="12" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>137</v>
       </c>
       <c r="P319" s="18" t="n">
-        <v>0.1791031930458732</v>
+        <v>0.1804239186627606</v>
       </c>
       <c r="Q319" s="19" t="inlineStr">
         <is>
@@ -23703,13 +23703,13 @@
         </is>
       </c>
       <c r="D320" s="4" t="n">
-        <v>235.03</v>
+        <v>235.97</v>
       </c>
       <c r="E320" s="5" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="F320" s="5" t="n">
-        <v>0.0149</v>
+        <v>0.0189</v>
       </c>
       <c r="G320" s="6" t="n">
         <v>46321</v>
@@ -23738,7 +23738,7 @@
         <v>237</v>
       </c>
       <c r="M320" s="5" t="n">
-        <v>0.008381908692507335</v>
+        <v>0.004364961647667081</v>
       </c>
       <c r="N320" s="3" t="inlineStr">
         <is>
@@ -23749,7 +23749,7 @@
         <v>236</v>
       </c>
       <c r="P320" s="5" t="n">
-        <v>0.004127132706463</v>
+        <v>0.0001271348052718614</v>
       </c>
       <c r="Q320" s="9" t="inlineStr">
         <is>
@@ -23790,13 +23790,13 @@
         </is>
       </c>
       <c r="D321" s="13" t="n">
-        <v>166.95</v>
+        <v>166.55</v>
       </c>
       <c r="E321" s="14" t="n">
-        <v>-0.0058</v>
+        <v>-0.008100000000000001</v>
       </c>
       <c r="F321" s="14" t="n">
-        <v>-0.0525</v>
+        <v>-0.0547</v>
       </c>
       <c r="G321" s="15" t="n"/>
       <c r="H321" s="21" t="inlineStr">
@@ -23815,7 +23815,7 @@
         <v>200</v>
       </c>
       <c r="M321" s="18" t="n">
-        <v>0.1979634621144056</v>
+        <v>0.2008405884118882</v>
       </c>
       <c r="N321" s="12" t="inlineStr"/>
       <c r="O321" s="17" t="n"/>
@@ -23859,13 +23859,13 @@
         </is>
       </c>
       <c r="D322" s="4" t="n">
-        <v>140.28</v>
+        <v>140.33</v>
       </c>
       <c r="E322" s="5" t="n">
-        <v>0.0357</v>
+        <v>0.036</v>
       </c>
       <c r="F322" s="5" t="n">
-        <v>0.07339999999999999</v>
+        <v>0.0738</v>
       </c>
       <c r="G322" s="6" t="n"/>
       <c r="H322" s="7" t="inlineStr">
@@ -23884,7 +23884,7 @@
         <v>131</v>
       </c>
       <c r="M322" s="22" t="n">
-        <v>-0.06615340747077275</v>
+        <v>-0.06648613981329732</v>
       </c>
       <c r="N322" s="3" t="inlineStr"/>
       <c r="O322" s="8" t="n"/>
@@ -23928,13 +23928,13 @@
         </is>
       </c>
       <c r="D323" s="13" t="n">
-        <v>31.83</v>
+        <v>31.59</v>
       </c>
       <c r="E323" s="14" t="n">
-        <v>-0.0418</v>
+        <v>-0.0491</v>
       </c>
       <c r="F323" s="14" t="n">
-        <v>-0.0924</v>
+        <v>-0.0992</v>
       </c>
       <c r="G323" s="15" t="n"/>
       <c r="H323" s="21" t="inlineStr">
@@ -24048,13 +24048,13 @@
         </is>
       </c>
       <c r="D325" s="13" t="n">
-        <v>295.05</v>
+        <v>293.9</v>
       </c>
       <c r="E325" s="18" t="n">
-        <v>0.091</v>
+        <v>0.0868</v>
       </c>
       <c r="F325" s="18" t="n">
-        <v>0.1737</v>
+        <v>0.1692</v>
       </c>
       <c r="G325" s="15" t="n"/>
       <c r="H325" s="21" t="inlineStr">
@@ -24073,7 +24073,7 @@
         <v>384</v>
       </c>
       <c r="M325" s="18" t="n">
-        <v>0.3014743263853584</v>
+        <v>0.3065668594760124</v>
       </c>
       <c r="N325" s="12" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>380</v>
       </c>
       <c r="P325" s="18" t="n">
-        <v>0.2879173021521775</v>
+        <v>0.2929567880231372</v>
       </c>
       <c r="Q325" s="19" t="inlineStr"/>
       <c r="R325" s="17" t="n"/>
@@ -24127,13 +24127,13 @@
         </is>
       </c>
       <c r="D326" s="4" t="n">
-        <v>68.3</v>
+        <v>68.17</v>
       </c>
       <c r="E326" s="22" t="n">
-        <v>-0.011</v>
+        <v>-0.0129</v>
       </c>
       <c r="F326" s="22" t="n">
-        <v>-0.09420000000000001</v>
+        <v>-0.0959</v>
       </c>
       <c r="G326" s="6" t="n">
         <v>46324</v>
@@ -24162,7 +24162,7 @@
         <v>79</v>
       </c>
       <c r="M326" s="5" t="n">
-        <v>0.1566617862371889</v>
+        <v>0.1588675370397535</v>
       </c>
       <c r="N326" s="3" t="inlineStr"/>
       <c r="O326" s="8" t="n"/>
@@ -24214,13 +24214,13 @@
         </is>
       </c>
       <c r="D327" s="13" t="n">
-        <v>120.32</v>
+        <v>120.44</v>
       </c>
       <c r="E327" s="14" t="n">
-        <v>-0.0072</v>
+        <v>-0.0062</v>
       </c>
       <c r="F327" s="14" t="n">
-        <v>-0.0412</v>
+        <v>-0.04019999999999999</v>
       </c>
       <c r="G327" s="15" t="n"/>
       <c r="H327" s="21" t="inlineStr">
@@ -24239,7 +24239,7 @@
         <v>136</v>
       </c>
       <c r="M327" s="18" t="n">
-        <v>0.1303191489361703</v>
+        <v>0.1291929591497842</v>
       </c>
       <c r="N327" s="12" t="inlineStr">
         <is>
@@ -24250,7 +24250,7 @@
         <v>140</v>
       </c>
       <c r="P327" s="18" t="n">
-        <v>0.1635638297872341</v>
+        <v>0.1624045167718366</v>
       </c>
       <c r="Q327" s="19" t="inlineStr">
         <is>
@@ -24291,13 +24291,13 @@
         </is>
       </c>
       <c r="D328" s="4" t="n">
-        <v>107.79</v>
+        <v>107.21</v>
       </c>
       <c r="E328" s="5" t="n">
-        <v>0.0203</v>
+        <v>0.0148</v>
       </c>
       <c r="F328" s="22" t="n">
-        <v>-0.06309999999999999</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="G328" s="6" t="n"/>
       <c r="H328" s="7" t="inlineStr">
@@ -24316,7 +24316,7 @@
         <v>131</v>
       </c>
       <c r="M328" s="5" t="n">
-        <v>0.2153260970405417</v>
+        <v>0.2219009420762989</v>
       </c>
       <c r="N328" s="3" t="inlineStr">
         <is>
@@ -24327,7 +24327,7 @@
         <v>121</v>
       </c>
       <c r="P328" s="5" t="n">
-        <v>0.1225531125336301</v>
+        <v>0.1286260610017723</v>
       </c>
       <c r="Q328" s="9" t="inlineStr">
         <is>
@@ -24372,13 +24372,13 @@
         </is>
       </c>
       <c r="D329" s="13" t="n">
-        <v>83.23</v>
+        <v>82.67</v>
       </c>
       <c r="E329" s="14" t="n">
-        <v>-0.0174</v>
+        <v>-0.024</v>
       </c>
       <c r="F329" s="14" t="n">
-        <v>-0.0538</v>
+        <v>-0.0602</v>
       </c>
       <c r="G329" s="15" t="n">
         <v>46322</v>
@@ -24414,7 +24414,7 @@
         <v>107</v>
       </c>
       <c r="P329" s="18" t="n">
-        <v>0.2855941367295446</v>
+        <v>0.2943026490867304</v>
       </c>
       <c r="Q329" s="19" t="inlineStr">
         <is>
@@ -24463,13 +24463,13 @@
         </is>
       </c>
       <c r="D330" s="4" t="n">
-        <v>53.51</v>
+        <v>53.48</v>
       </c>
       <c r="E330" s="22" t="n">
-        <v>-0.0032</v>
+        <v>-0.0037</v>
       </c>
       <c r="F330" s="22" t="n">
-        <v>-0.0833</v>
+        <v>-0.08380000000000001</v>
       </c>
       <c r="G330" s="6" t="n"/>
       <c r="H330" s="7" t="inlineStr">
@@ -24488,7 +24488,7 @@
         <v>63</v>
       </c>
       <c r="M330" s="5" t="n">
-        <v>0.1773500280321436</v>
+        <v>0.1780104712041886</v>
       </c>
       <c r="N330" s="3" t="inlineStr"/>
       <c r="O330" s="8" t="n"/>
@@ -24532,13 +24532,13 @@
         </is>
       </c>
       <c r="D331" s="13" t="n">
-        <v>43.34</v>
+        <v>42.58</v>
       </c>
       <c r="E331" s="14" t="n">
-        <v>-0.0258</v>
+        <v>-0.0429</v>
       </c>
       <c r="F331" s="14" t="n">
-        <v>-0.1128</v>
+        <v>-0.1284</v>
       </c>
       <c r="G331" s="15" t="n"/>
       <c r="H331" s="21" t="inlineStr">
@@ -24583,13 +24583,13 @@
         </is>
       </c>
       <c r="D332" s="4" t="n">
-        <v>10.91</v>
+        <v>10.78</v>
       </c>
       <c r="E332" s="5" t="n">
-        <v>0.189</v>
+        <v>0.1743</v>
       </c>
       <c r="F332" s="5" t="n">
-        <v>0.2074</v>
+        <v>0.1925</v>
       </c>
       <c r="G332" s="6" t="n"/>
       <c r="H332" s="7" t="inlineStr">
@@ -24634,13 +24634,13 @@
         </is>
       </c>
       <c r="D333" s="13" t="n">
-        <v>88.54000000000001</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="E333" s="14" t="n">
-        <v>-0.0307</v>
+        <v>-0.0327</v>
       </c>
       <c r="F333" s="14" t="n">
-        <v>-0.07389999999999999</v>
+        <v>-0.0759</v>
       </c>
       <c r="G333" s="15" t="n">
         <v>46324</v>
@@ -24669,7 +24669,7 @@
         <v>99</v>
       </c>
       <c r="M333" s="18" t="n">
-        <v>0.1181386943754235</v>
+        <v>0.1205432937181665</v>
       </c>
       <c r="N333" s="12" t="inlineStr">
         <is>
@@ -24680,7 +24680,7 @@
         <v>112</v>
       </c>
       <c r="P333" s="18" t="n">
-        <v>0.2649649875762367</v>
+        <v>0.2676853423882287</v>
       </c>
       <c r="Q333" s="19" t="inlineStr">
         <is>
@@ -24721,13 +24721,13 @@
         </is>
       </c>
       <c r="D334" s="4" t="n">
-        <v>106.17</v>
+        <v>106.18</v>
       </c>
       <c r="E334" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="F334" s="22" t="n">
-        <v>-0.0765</v>
+        <v>-0.0764</v>
       </c>
       <c r="G334" s="6" t="n">
         <v>46324</v>
@@ -24756,7 +24756,7 @@
         <v>127</v>
       </c>
       <c r="M334" s="5" t="n">
-        <v>0.1961947819534708</v>
+        <v>0.1960821246939159</v>
       </c>
       <c r="N334" s="3" t="inlineStr"/>
       <c r="O334" s="8" t="n"/>
@@ -33617,7 +33617,7 @@
     <row r="2">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>Data as of September 09, 2026 at 14:49 UTC</t>
+          <t>Data as of September 09, 2026 at 20:04 UTC</t>
         </is>
       </c>
     </row>

--- a/earnings-data.xlsx
+++ b/earnings-data.xlsx
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>106.89</v>
+        <v>106.54</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.0356</v>
+        <v>0.0321</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.1135</v>
+        <v>0.1097</v>
       </c>
       <c r="G2" s="6" t="n"/>
       <c r="H2" s="7" t="inlineStr">
@@ -868,7 +868,7 @@
         <v>125</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>0.1694265132379081</v>
+        <v>0.1732682560540641</v>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         <v>144</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>0.3471793432500702</v>
+        <v>0.3516050309742819</v>
       </c>
       <c r="Q2" s="9" t="inlineStr">
         <is>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="D3" s="13" t="n">
-        <v>339.83</v>
+        <v>338.5</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>-0.0108</v>
+        <v>-0.0147</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>-0.036</v>
+        <v>-0.0397</v>
       </c>
       <c r="G3" s="15" t="n">
         <v>46322</v>
@@ -963,7 +963,7 @@
         <v>438</v>
       </c>
       <c r="M3" s="18" t="n">
-        <v>0.2888797339846395</v>
+        <v>0.2939438700147711</v>
       </c>
       <c r="N3" s="12" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>420</v>
       </c>
       <c r="P3" s="18" t="n">
-        <v>0.2359120736839008</v>
+        <v>0.240768094534712</v>
       </c>
       <c r="Q3" s="19" t="inlineStr">
         <is>
@@ -1019,13 +1019,13 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>651.54</v>
+        <v>648.03</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.1256</v>
+        <v>0.1195</v>
       </c>
       <c r="F4" s="22" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0132</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>46330</v>
@@ -1054,7 +1054,7 @@
         <v>835</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>0.281579028148694</v>
+        <v>0.2885205931824145</v>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>930</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>0.4273874205727968</v>
+        <v>0.4351187445025694</v>
       </c>
       <c r="Q4" s="9" t="inlineStr">
         <is>
@@ -1114,13 +1114,13 @@
         </is>
       </c>
       <c r="D5" s="13" t="n">
-        <v>42.28</v>
+        <v>42.39</v>
       </c>
       <c r="E5" s="18" t="n">
-        <v>0.1557</v>
+        <v>0.1588</v>
       </c>
       <c r="F5" s="18" t="n">
-        <v>0.0969</v>
+        <v>0.0999</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>46329</v>
@@ -1175,13 +1175,13 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>76.45</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.0302</v>
+        <v>0.043</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.0355</v>
+        <v>0.0484</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>46315</v>
@@ -1210,7 +1210,7 @@
         <v>80</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>0.04643557880967949</v>
+        <v>0.0335917312661498</v>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>100</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>0.3080444735120993</v>
+        <v>0.2919896640826872</v>
       </c>
       <c r="Q6" s="9" t="inlineStr">
         <is>
@@ -1262,13 +1262,13 @@
         </is>
       </c>
       <c r="D7" s="13" t="n">
-        <v>78.54000000000001</v>
+        <v>79</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>-0.0815</v>
+        <v>-0.0761</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>-0.0486</v>
+        <v>-0.043</v>
       </c>
       <c r="G7" s="15" t="n">
         <v>46315</v>
@@ -1297,7 +1297,7 @@
         <v>91</v>
       </c>
       <c r="M7" s="18" t="n">
-        <v>0.158645276292335</v>
+        <v>0.1518987341772152</v>
       </c>
       <c r="N7" s="12" t="inlineStr"/>
       <c r="O7" s="17" t="n"/>
@@ -1341,13 +1341,13 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>527.25</v>
+        <v>525.76</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.07690000000000001</v>
+        <v>0.0738</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.09880000000000001</v>
+        <v>0.09570000000000001</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>46329</v>
@@ -1376,7 +1376,7 @@
         <v>569.9299999999999</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>0.08094831673779032</v>
+        <v>0.08401171637248928</v>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>648.04</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>0.2290943575154101</v>
+        <v>0.2325776019476567</v>
       </c>
       <c r="Q8" s="9" t="inlineStr">
         <is>
@@ -1428,13 +1428,13 @@
         </is>
       </c>
       <c r="D9" s="13" t="n">
-        <v>187.86</v>
+        <v>190.38</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>-0.0373</v>
+        <v>-0.0244</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>0.0381</v>
+        <v>0.052</v>
       </c>
       <c r="G9" s="15" t="n">
         <v>46330</v>
@@ -1497,13 +1497,13 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>183.53</v>
+        <v>182.33</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.0361</v>
+        <v>0.0294</v>
       </c>
       <c r="F10" s="22" t="n">
-        <v>-0.0259</v>
+        <v>-0.0323</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>46317</v>
@@ -1532,7 +1532,7 @@
         <v>170</v>
       </c>
       <c r="M10" s="22" t="n">
-        <v>-0.07372091756116167</v>
+        <v>-0.06762463664783641</v>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>270</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>0.4711491309322726</v>
+        <v>0.4808314594416716</v>
       </c>
       <c r="Q10" s="9" t="inlineStr">
         <is>
@@ -1584,13 +1584,13 @@
         </is>
       </c>
       <c r="D11" s="13" t="n">
-        <v>50.71</v>
+        <v>50.6</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>0.0795</v>
+        <v>0.07690000000000001</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>0.1882</v>
+        <v>0.1854</v>
       </c>
       <c r="G11" s="15" t="n">
         <v>46316</v>
@@ -1619,7 +1619,7 @@
         <v>43</v>
       </c>
       <c r="M11" s="14" t="n">
-        <v>-0.152041017550779</v>
+        <v>-0.150197628458498</v>
       </c>
       <c r="N11" s="12" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>50</v>
       </c>
       <c r="P11" s="14" t="n">
-        <v>-0.01400118319858018</v>
+        <v>-0.01185770750988145</v>
       </c>
       <c r="Q11" s="19" t="inlineStr">
         <is>
@@ -1675,13 +1675,13 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>168.76</v>
+        <v>170.19</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>-0.0629</v>
+        <v>-0.055</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.1533</v>
+        <v>0.1631</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>46331</v>
@@ -1710,7 +1710,7 @@
         <v>181</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>0.07252903531642575</v>
+        <v>0.06351724543157648</v>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>155</v>
       </c>
       <c r="P12" s="22" t="n">
-        <v>-0.08153590898317131</v>
+        <v>-0.08925318761384333</v>
       </c>
       <c r="Q12" s="9" t="inlineStr">
         <is>
@@ -1762,13 +1762,13 @@
         </is>
       </c>
       <c r="D13" s="13" t="n">
-        <v>255.2</v>
+        <v>256.78</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>-0.0452</v>
+        <v>-0.0393</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>0.0319</v>
+        <v>0.0383</v>
       </c>
       <c r="G13" s="15" t="n">
         <v>46324</v>
@@ -1797,7 +1797,7 @@
         <v>322</v>
       </c>
       <c r="M13" s="18" t="n">
-        <v>0.261755485893417</v>
+        <v>0.2539917439052887</v>
       </c>
       <c r="N13" s="12" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>285</v>
       </c>
       <c r="P13" s="18" t="n">
-        <v>0.1167711598746082</v>
+        <v>0.1098995248851158</v>
       </c>
       <c r="Q13" s="19" t="inlineStr">
         <is>
@@ -1861,13 +1861,13 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2921.79</v>
+        <v>2880</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>-0.0407</v>
+        <v>-0.0545</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>-0.05110000000000001</v>
+        <v>-0.0646</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>46287</v>
@@ -1896,7 +1896,7 @@
         <v>4150</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>0.4203621752418894</v>
+        <v>0.4409722222222222</v>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>3700</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>0.2663469996132508</v>
+        <v>0.2847222222222222</v>
       </c>
       <c r="Q14" s="9" t="inlineStr">
         <is>
@@ -1948,13 +1948,13 @@
         </is>
       </c>
       <c r="D15" s="13" t="n">
-        <v>89.98</v>
+        <v>90.8</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>0.08410000000000001</v>
+        <v>0.094</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>0.102</v>
+        <v>0.1121</v>
       </c>
       <c r="G15" s="15" t="n"/>
       <c r="H15" s="21" t="inlineStr">
@@ -1973,7 +1973,7 @@
         <v>65</v>
       </c>
       <c r="M15" s="14" t="n">
-        <v>-0.277617248277395</v>
+        <v>-0.2841409691629956</v>
       </c>
       <c r="N15" s="12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>85</v>
       </c>
       <c r="P15" s="14" t="n">
-        <v>-0.05534563236274732</v>
+        <v>-0.06387665198237882</v>
       </c>
       <c r="Q15" s="19" t="inlineStr"/>
       <c r="R15" s="17" t="n"/>
@@ -2019,13 +2019,13 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>173.16</v>
+        <v>173.92</v>
       </c>
       <c r="E16" s="22" t="n">
-        <v>-0.1842</v>
+        <v>-0.1806</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>-0.015</v>
+        <v>-0.0107</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>46322</v>
@@ -2054,7 +2054,7 @@
         <v>214</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>0.2358512358512359</v>
+        <v>0.2304507819687213</v>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>245</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>0.4148764148764149</v>
+        <v>0.40869365225391</v>
       </c>
       <c r="Q16" s="9" t="inlineStr">
         <is>
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="D17" s="13" t="n">
-        <v>238.41</v>
+        <v>239.07</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>-0.3258</v>
+        <v>-0.324</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>-0.2722</v>
+        <v>-0.2702</v>
       </c>
       <c r="G17" s="15" t="n"/>
       <c r="H17" s="21" t="inlineStr">
@@ -2139,7 +2139,7 @@
         <v>375</v>
       </c>
       <c r="M17" s="18" t="n">
-        <v>0.5729205989681642</v>
+        <v>0.5685782406826453</v>
       </c>
       <c r="N17" s="12" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>375</v>
       </c>
       <c r="P17" s="18" t="n">
-        <v>0.5729205989681642</v>
+        <v>0.5685782406826453</v>
       </c>
       <c r="Q17" s="19" t="inlineStr"/>
       <c r="R17" s="17" t="n"/>
@@ -2189,13 +2189,13 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>36.01</v>
+        <v>36.2</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.1034</v>
+        <v>0.1091</v>
       </c>
       <c r="F18" s="22" t="n">
-        <v>-0.0168</v>
+        <v>-0.0117</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>46323</v>
@@ -2224,7 +2224,7 @@
         <v>45</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>0.2496528742016107</v>
+        <v>0.2430939226519336</v>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>45</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>0.2496528742016107</v>
+        <v>0.2430939226519336</v>
       </c>
       <c r="Q18" s="9" t="inlineStr">
         <is>
@@ -2276,13 +2276,13 @@
         </is>
       </c>
       <c r="D19" s="13" t="n">
-        <v>136.33</v>
+        <v>137.93</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>-0.06509999999999999</v>
+        <v>-0.0541</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>-0.08410000000000001</v>
+        <v>-0.07339999999999999</v>
       </c>
       <c r="G19" s="15" t="n">
         <v>46322</v>
@@ -2311,7 +2311,7 @@
         <v>170</v>
       </c>
       <c r="M19" s="18" t="n">
-        <v>0.2469742536492334</v>
+        <v>0.2325092438193286</v>
       </c>
       <c r="N19" s="12" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>177</v>
       </c>
       <c r="P19" s="18" t="n">
-        <v>0.2983202523289077</v>
+        <v>0.2832596244471833</v>
       </c>
       <c r="Q19" s="19" t="inlineStr">
         <is>
@@ -2363,13 +2363,13 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>133.62</v>
+        <v>135.03</v>
       </c>
       <c r="E20" s="22" t="n">
-        <v>-0.3407</v>
+        <v>-0.3337</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>-0.3817</v>
+        <v>-0.3752</v>
       </c>
       <c r="G20" s="6" t="n"/>
       <c r="H20" s="7" t="inlineStr">
@@ -2388,7 +2388,7 @@
         <v>220</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>0.6464601107618619</v>
+        <v>0.6292675701695919</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="8" t="n"/>
@@ -2432,13 +2432,13 @@
         </is>
       </c>
       <c r="D21" s="13" t="n">
-        <v>118.22</v>
+        <v>118.17</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>-0.08070000000000001</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>-0.0645</v>
+        <v>-0.065</v>
       </c>
       <c r="G21" s="15" t="n"/>
       <c r="H21" s="21" t="inlineStr">
@@ -2483,13 +2483,13 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>86.56999999999999</v>
+        <v>85.61</v>
       </c>
       <c r="E22" s="22" t="n">
-        <v>-0.0021</v>
+        <v>-0.0132</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.1285</v>
+        <v>0.1159</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>46315</v>
@@ -2518,7 +2518,7 @@
         <v>61</v>
       </c>
       <c r="M22" s="22" t="n">
-        <v>-0.2953679103615571</v>
+        <v>-0.2874664174745941</v>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>100</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0.1551345731777753</v>
+        <v>0.1680878402055835</v>
       </c>
       <c r="Q22" s="9" t="inlineStr">
         <is>
@@ -2570,13 +2570,13 @@
         </is>
       </c>
       <c r="D23" s="13" t="n">
-        <v>134.76</v>
-      </c>
-      <c r="E23" s="18" t="n">
-        <v>0.005600000000000001</v>
+        <v>133.72</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>-0.0022</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>0.091</v>
+        <v>0.08259999999999999</v>
       </c>
       <c r="G23" s="15" t="n">
         <v>46315</v>
@@ -2608,7 +2608,7 @@
         <v>145</v>
       </c>
       <c r="P23" s="18" t="n">
-        <v>0.07598693974473145</v>
+        <v>0.0843553694286569</v>
       </c>
       <c r="Q23" s="19" t="inlineStr"/>
       <c r="R23" s="17" t="n"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>308.06</v>
+        <v>308.73</v>
       </c>
       <c r="E24" s="22" t="n">
-        <v>-0.103</v>
+        <v>-0.1011</v>
       </c>
       <c r="F24" s="22" t="n">
-        <v>-0.0862</v>
+        <v>-0.0842</v>
       </c>
       <c r="G24" s="6" t="n"/>
       <c r="H24" s="7" t="inlineStr">
@@ -2668,7 +2668,7 @@
         <v>360</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>0.1686035187950399</v>
+        <v>0.1660674375668059</v>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>400</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0.298448354216711</v>
+        <v>0.2956304861853399</v>
       </c>
       <c r="Q24" s="9" t="inlineStr">
         <is>
@@ -2728,13 +2728,13 @@
         </is>
       </c>
       <c r="D25" s="13" t="n">
-        <v>197.23</v>
+        <v>196.81</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>-0.0868</v>
+        <v>-0.08869999999999999</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>-0.0504</v>
+        <v>-0.0524</v>
       </c>
       <c r="G25" s="15" t="n"/>
       <c r="H25" s="21" t="inlineStr">
@@ -2753,7 +2753,7 @@
         <v>255</v>
       </c>
       <c r="M25" s="18" t="n">
-        <v>0.2929067586067029</v>
+        <v>0.2956658706366546</v>
       </c>
       <c r="N25" s="12" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>230</v>
       </c>
       <c r="P25" s="18" t="n">
-        <v>0.1661511940374183</v>
+        <v>0.168639804887963</v>
       </c>
       <c r="Q25" s="19" t="inlineStr">
         <is>
@@ -2809,13 +2809,13 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>252.4</v>
+        <v>252.52</v>
       </c>
       <c r="E26" s="22" t="n">
-        <v>-0.08449999999999999</v>
+        <v>-0.08410000000000001</v>
       </c>
       <c r="F26" s="22" t="n">
-        <v>-0.0741</v>
+        <v>-0.0737</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>46330</v>
@@ -2844,7 +2844,7 @@
         <v>300</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>0.1885895404120443</v>
+        <v>0.188024710913987</v>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>350</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>0.386687797147385</v>
+        <v>0.3860288293996514</v>
       </c>
       <c r="Q26" s="9" t="inlineStr">
         <is>
@@ -2896,13 +2896,13 @@
         </is>
       </c>
       <c r="D27" s="13" t="n">
-        <v>36.72</v>
+        <v>36.81</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>-0.09359999999999999</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>-0.1609</v>
+        <v>-0.1588</v>
       </c>
       <c r="G27" s="15" t="n">
         <v>46289</v>
@@ -2957,13 +2957,13 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>86.03</v>
+        <v>85.81999999999999</v>
       </c>
       <c r="E28" s="22" t="n">
-        <v>-0.0654</v>
+        <v>-0.0677</v>
       </c>
       <c r="F28" s="22" t="n">
-        <v>-0.0143</v>
+        <v>-0.0167</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>46323</v>
@@ -2992,7 +2992,7 @@
         <v>110</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>0.2786237359060793</v>
+        <v>0.2817525052435331</v>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>115</v>
       </c>
       <c r="P28" s="5" t="n">
-        <v>0.3367429966290829</v>
+        <v>0.3400139827546028</v>
       </c>
       <c r="Q28" s="9" t="inlineStr">
         <is>
@@ -3048,13 +3048,13 @@
         </is>
       </c>
       <c r="D29" s="13" t="n">
-        <v>174.39</v>
+        <v>173.04</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>-0.1255</v>
+        <v>-0.1322</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>-0.1728</v>
+        <v>-0.1792</v>
       </c>
       <c r="G29" s="15" t="n">
         <v>46317</v>
@@ -3109,13 +3109,13 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>226.39</v>
+        <v>230.74</v>
       </c>
       <c r="E30" s="22" t="n">
-        <v>-0.08810000000000001</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.0316</v>
+        <v>0.05139999999999999</v>
       </c>
       <c r="G30" s="6" t="n"/>
       <c r="H30" s="7" t="inlineStr">
@@ -3134,7 +3134,7 @@
         <v>245</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>0.0822032775299263</v>
+        <v>0.06180116148045415</v>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>265</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>0.1705464022262468</v>
+        <v>0.1484788073155933</v>
       </c>
       <c r="Q30" s="9" t="inlineStr">
         <is>
@@ -3186,13 +3186,13 @@
         </is>
       </c>
       <c r="D31" s="13" t="n">
-        <v>98.72</v>
+        <v>98.73999999999999</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>-0.0901</v>
+        <v>-0.08990000000000001</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>-0.0803</v>
+        <v>-0.0801</v>
       </c>
       <c r="G31" s="15" t="n">
         <v>46330</v>
@@ -3221,7 +3221,7 @@
         <v>120</v>
       </c>
       <c r="M31" s="18" t="n">
-        <v>0.2155591572123177</v>
+        <v>0.2153129430828439</v>
       </c>
       <c r="N31" s="12" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>115</v>
       </c>
       <c r="P31" s="18" t="n">
-        <v>0.1649108589951378</v>
+        <v>0.1646749037877254</v>
       </c>
       <c r="Q31" s="19" t="inlineStr">
         <is>
@@ -3273,13 +3273,13 @@
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>12.81</v>
+        <v>12.91</v>
       </c>
       <c r="E32" s="22" t="n">
-        <v>-0.0142</v>
+        <v>-0.0062</v>
       </c>
       <c r="F32" s="22" t="n">
-        <v>-0.1786</v>
+        <v>-0.1719</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>46330</v>
@@ -3334,13 +3334,13 @@
         </is>
       </c>
       <c r="D33" s="13" t="n">
-        <v>125.24</v>
+        <v>126.07</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>-0.1793</v>
+        <v>-0.1739</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>-0.168</v>
+        <v>-0.1625</v>
       </c>
       <c r="G33" s="15" t="n"/>
       <c r="H33" s="21" t="inlineStr">
@@ -3359,7 +3359,7 @@
         <v>160</v>
       </c>
       <c r="M33" s="18" t="n">
-        <v>0.2775471095496647</v>
+        <v>0.2691361941778378</v>
       </c>
       <c r="N33" s="12" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>175</v>
       </c>
       <c r="P33" s="18" t="n">
-        <v>0.3973171510699458</v>
+        <v>0.3881177123820101</v>
       </c>
       <c r="Q33" s="19" t="inlineStr">
         <is>
@@ -3415,13 +3415,13 @@
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>33.49</v>
+        <v>33.01</v>
       </c>
       <c r="E34" s="22" t="n">
-        <v>-0.0806</v>
+        <v>-0.09390000000000001</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.1076</v>
+        <v>0.0916</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>46317</v>
@@ -3450,7 +3450,7 @@
         <v>35</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>0.04508808599581959</v>
+        <v>0.06028476219327483</v>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>40</v>
       </c>
       <c r="P34" s="5" t="n">
-        <v>0.1943863839952224</v>
+        <v>0.2117540139351712</v>
       </c>
       <c r="Q34" s="9" t="inlineStr">
         <is>
@@ -3502,13 +3502,13 @@
         </is>
       </c>
       <c r="D35" s="13" t="n">
-        <v>365.74</v>
+        <v>365.44</v>
       </c>
       <c r="E35" s="18" t="n">
-        <v>0.1167</v>
+        <v>0.1158</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>-0.0735</v>
+        <v>-0.07429999999999999</v>
       </c>
       <c r="G35" s="15" t="n">
         <v>46323</v>
@@ -3537,7 +3537,7 @@
         <v>130</v>
       </c>
       <c r="M35" s="14" t="n">
-        <v>-0.6445562421392246</v>
+        <v>-0.6442644483362522</v>
       </c>
       <c r="N35" s="12" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>300</v>
       </c>
       <c r="P35" s="14" t="n">
-        <v>-0.1797451741674414</v>
+        <v>-0.1790718038528896</v>
       </c>
       <c r="Q35" s="19" t="inlineStr">
         <is>
@@ -3589,13 +3589,13 @@
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>71.3</v>
+        <v>71.66</v>
       </c>
       <c r="E36" s="22" t="n">
-        <v>-0.0539</v>
+        <v>-0.0492</v>
       </c>
       <c r="F36" s="22" t="n">
-        <v>-0.0399</v>
+        <v>-0.0351</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>46329</v>
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="D37" s="13" t="n">
-        <v>536.1</v>
+        <v>546.78</v>
       </c>
       <c r="E37" s="18" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.028</v>
       </c>
       <c r="F37" s="18" t="n">
-        <v>0.1326</v>
+        <v>0.1552</v>
       </c>
       <c r="G37" s="15" t="n"/>
       <c r="H37" s="21" t="inlineStr">
@@ -3675,7 +3675,7 @@
         <v>450</v>
       </c>
       <c r="M37" s="14" t="n">
-        <v>-0.1606043648573028</v>
+        <v>-0.176999890266652</v>
       </c>
       <c r="N37" s="12" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>635</v>
       </c>
       <c r="P37" s="18" t="n">
-        <v>0.1844805073680283</v>
+        <v>0.1613445992903911</v>
       </c>
       <c r="Q37" s="19" t="inlineStr">
         <is>
@@ -3731,13 +3731,13 @@
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>93.39</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="E38" s="22" t="n">
-        <v>-0.0776</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F38" s="22" t="n">
-        <v>-0.0389</v>
+        <v>-0.031</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>46325</v>
@@ -3766,7 +3766,7 @@
         <v>110</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>0.1778563015312132</v>
+        <v>0.168348380244291</v>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>105</v>
       </c>
       <c r="P38" s="5" t="n">
-        <v>0.1243173787343399</v>
+        <v>0.1152416356877323</v>
       </c>
       <c r="Q38" s="9" t="inlineStr">
         <is>
@@ -3822,13 +3822,13 @@
         </is>
       </c>
       <c r="D39" s="13" t="n">
-        <v>87.66</v>
+        <v>86.78</v>
       </c>
       <c r="E39" s="14" t="n">
-        <v>-0.0505</v>
+        <v>-0.06</v>
       </c>
       <c r="F39" s="14" t="n">
-        <v>-0.0595</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="G39" s="15" t="n">
         <v>46325</v>
@@ -3857,7 +3857,7 @@
         <v>95</v>
       </c>
       <c r="M39" s="18" t="n">
-        <v>0.08373260323979013</v>
+        <v>0.09472228624106936</v>
       </c>
       <c r="N39" s="12" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>100</v>
       </c>
       <c r="P39" s="18" t="n">
-        <v>0.1407711613050422</v>
+        <v>0.1523392486748099</v>
       </c>
       <c r="Q39" s="19" t="inlineStr">
         <is>
@@ -3913,13 +3913,13 @@
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>902.25</v>
+        <v>904.77</v>
       </c>
       <c r="E40" s="22" t="n">
-        <v>-0.0498</v>
+        <v>-0.0472</v>
       </c>
       <c r="F40" s="22" t="n">
-        <v>-0.0261</v>
+        <v>-0.0234</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>46289</v>
@@ -3948,7 +3948,7 @@
         <v>1000</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>0.1083402604599612</v>
+        <v>0.1052532687865425</v>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>1100</v>
       </c>
       <c r="P40" s="5" t="n">
-        <v>0.2191742865059573</v>
+        <v>0.2157785956651967</v>
       </c>
       <c r="Q40" s="9" t="inlineStr">
         <is>
@@ -4008,13 +4008,13 @@
         </is>
       </c>
       <c r="D41" s="13" t="n">
-        <v>123.92</v>
+        <v>124.57</v>
       </c>
       <c r="E41" s="18" t="n">
-        <v>0.0361</v>
+        <v>0.0416</v>
       </c>
       <c r="F41" s="18" t="n">
-        <v>0.0039</v>
+        <v>0.0092</v>
       </c>
       <c r="G41" s="15" t="n"/>
       <c r="H41" s="21" t="inlineStr">
@@ -4033,7 +4033,7 @@
         <v>125</v>
       </c>
       <c r="M41" s="18" t="n">
-        <v>0.008715300193673324</v>
+        <v>0.003451874448101524</v>
       </c>
       <c r="N41" s="12" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>135</v>
       </c>
       <c r="P41" s="18" t="n">
-        <v>0.08941252420916719</v>
+        <v>0.08372802440394965</v>
       </c>
       <c r="Q41" s="19" t="inlineStr">
         <is>
@@ -4085,13 +4085,13 @@
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>24.32</v>
-      </c>
-      <c r="E42" s="22" t="n">
-        <v>-0.008699999999999999</v>
+        <v>24.6</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>0.0029</v>
       </c>
       <c r="F42" s="22" t="n">
-        <v>-0.0362</v>
+        <v>-0.025</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>46330</v>
@@ -4146,13 +4146,13 @@
         </is>
       </c>
       <c r="D43" s="13" t="n">
-        <v>88.13</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>0.0163</v>
+        <v>0.0179</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>0.046</v>
+        <v>0.04769999999999999</v>
       </c>
       <c r="G43" s="15" t="n">
         <v>46315</v>
@@ -4181,7 +4181,7 @@
         <v>90</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>0.02121865426075122</v>
+        <v>0.01971447994561517</v>
       </c>
       <c r="N43" s="12" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>88</v>
       </c>
       <c r="P43" s="14" t="n">
-        <v>-0.001475093611709922</v>
+        <v>-0.002945841830954058</v>
       </c>
       <c r="Q43" s="19" t="inlineStr">
         <is>
@@ -4241,13 +4241,13 @@
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>58.92</v>
+        <v>58.46</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0.0509</v>
+        <v>0.0428</v>
       </c>
       <c r="F44" s="22" t="n">
-        <v>-0.0067</v>
+        <v>-0.0143</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>46276</v>
@@ -4276,7 +4276,7 @@
         <v>58</v>
       </c>
       <c r="M44" s="22" t="n">
-        <v>-0.01561439239646982</v>
+        <v>-0.007868628121792693</v>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>78</v>
       </c>
       <c r="P44" s="5" t="n">
-        <v>0.3238289205702647</v>
+        <v>0.3342456380431064</v>
       </c>
       <c r="Q44" s="9" t="inlineStr">
         <is>
@@ -4328,13 +4328,13 @@
         </is>
       </c>
       <c r="D45" s="13" t="n">
-        <v>62.33</v>
+        <v>62.44</v>
       </c>
       <c r="E45" s="18" t="n">
-        <v>0.0023</v>
+        <v>0.0042</v>
       </c>
       <c r="F45" s="18" t="n">
-        <v>0.0412</v>
+        <v>0.0431</v>
       </c>
       <c r="G45" s="15" t="n">
         <v>46322</v>
@@ -4363,7 +4363,7 @@
         <v>70</v>
       </c>
       <c r="M45" s="18" t="n">
-        <v>0.1230547088079577</v>
+        <v>0.1210762331838565</v>
       </c>
       <c r="N45" s="12" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>71</v>
       </c>
       <c r="P45" s="18" t="n">
-        <v>0.1390983475052142</v>
+        <v>0.1370916079436259</v>
       </c>
       <c r="Q45" s="19" t="inlineStr">
         <is>
@@ -4423,13 +4423,13 @@
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>51.45</v>
+        <v>51.34</v>
       </c>
       <c r="E46" s="22" t="n">
-        <v>-0.0287</v>
+        <v>-0.0308</v>
       </c>
       <c r="F46" s="22" t="n">
-        <v>-0.0428</v>
+        <v>-0.04480000000000001</v>
       </c>
       <c r="G46" s="6" t="n">
         <v>46296</v>
@@ -4494,13 +4494,13 @@
         </is>
       </c>
       <c r="D47" s="13" t="n">
-        <v>43.1</v>
+        <v>43.4</v>
       </c>
       <c r="E47" s="14" t="n">
-        <v>-0.0625</v>
+        <v>-0.0561</v>
       </c>
       <c r="F47" s="14" t="n">
-        <v>-0.1119</v>
+        <v>-0.1058</v>
       </c>
       <c r="G47" s="15" t="n">
         <v>46331</v>
@@ -4555,13 +4555,13 @@
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>69.03</v>
+        <v>68.97</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0.0722</v>
+        <v>0.0713</v>
       </c>
       <c r="F48" s="22" t="n">
-        <v>-0.0395</v>
+        <v>-0.0404</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>46324</v>
@@ -4616,13 +4616,13 @@
         </is>
       </c>
       <c r="D49" s="13" t="n">
-        <v>136.42</v>
+        <v>136.32</v>
       </c>
       <c r="E49" s="14" t="n">
-        <v>-0.0164</v>
+        <v>-0.0172</v>
       </c>
       <c r="F49" s="14" t="n">
-        <v>-0.0149</v>
+        <v>-0.0157</v>
       </c>
       <c r="G49" s="15" t="n">
         <v>46303</v>
@@ -4651,7 +4651,7 @@
         <v>140</v>
       </c>
       <c r="M49" s="18" t="n">
-        <v>0.02624248643893867</v>
+        <v>0.0269953051643193</v>
       </c>
       <c r="N49" s="12" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>150</v>
       </c>
       <c r="P49" s="18" t="n">
-        <v>0.09954552118457714</v>
+        <v>0.1003521126760564</v>
       </c>
       <c r="Q49" s="19" t="inlineStr">
         <is>
@@ -4711,13 +4711,13 @@
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>143.95</v>
-      </c>
-      <c r="E50" s="22" t="n">
-        <v>-0.0009</v>
+        <v>145.22</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>0.007900000000000001</v>
       </c>
       <c r="F50" s="22" t="n">
-        <v>-0.0298</v>
+        <v>-0.0212</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>46318</v>
@@ -4746,7 +4746,7 @@
         <v>164</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>0.1392844737756166</v>
+        <v>0.1293210301611348</v>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>162</v>
       </c>
       <c r="P50" s="5" t="n">
-        <v>0.125390760680792</v>
+        <v>0.115548822476243</v>
       </c>
       <c r="Q50" s="9" t="inlineStr">
         <is>
@@ -4810,13 +4810,13 @@
         </is>
       </c>
       <c r="D51" s="13" t="n">
-        <v>83.63</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="E51" s="14" t="n">
-        <v>-0.0125</v>
-      </c>
-      <c r="F51" s="18" t="n">
-        <v>0.002</v>
+        <v>-0.0175</v>
+      </c>
+      <c r="F51" s="14" t="n">
+        <v>-0.003</v>
       </c>
       <c r="G51" s="15" t="n">
         <v>46322</v>
@@ -4845,7 +4845,7 @@
         <v>100</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>0.1957431543704413</v>
+        <v>0.2017786323759165</v>
       </c>
       <c r="N51" s="12" t="inlineStr"/>
       <c r="O51" s="17" t="n"/>
@@ -4889,13 +4889,13 @@
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>155.73</v>
+        <v>155.85</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0.0112</v>
+        <v>0.012</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.1555</v>
+        <v>0.1564</v>
       </c>
       <c r="G52" s="6" t="n"/>
       <c r="H52" s="7" t="inlineStr">
@@ -4914,7 +4914,7 @@
         <v>140</v>
       </c>
       <c r="M52" s="22" t="n">
-        <v>-0.1010081551403069</v>
+        <v>-0.1017003529034328</v>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>135</v>
       </c>
       <c r="P52" s="22" t="n">
-        <v>-0.1331150067424388</v>
+        <v>-0.1337824831568816</v>
       </c>
       <c r="Q52" s="9" t="inlineStr">
         <is>
@@ -4970,13 +4970,13 @@
         </is>
       </c>
       <c r="D53" s="13" t="n">
-        <v>105.88</v>
+        <v>107.15</v>
       </c>
       <c r="E53" s="14" t="n">
-        <v>-0.0873</v>
+        <v>-0.0764</v>
       </c>
       <c r="F53" s="14" t="n">
-        <v>-0.0775</v>
+        <v>-0.0665</v>
       </c>
       <c r="G53" s="15" t="n"/>
       <c r="H53" s="21" t="inlineStr">
@@ -4995,7 +4995,7 @@
         <v>140</v>
       </c>
       <c r="M53" s="18" t="n">
-        <v>0.3222516055912354</v>
+        <v>0.3065795613625757</v>
       </c>
       <c r="N53" s="12" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>140</v>
       </c>
       <c r="P53" s="18" t="n">
-        <v>0.3222516055912354</v>
+        <v>0.3065795613625757</v>
       </c>
       <c r="Q53" s="19" t="inlineStr">
         <is>
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>58.15</v>
+        <v>59.06</v>
       </c>
       <c r="E54" s="22" t="n">
-        <v>-0.09539999999999998</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0243</v>
       </c>
       <c r="G54" s="6" t="n">
         <v>46317</v>
@@ -5097,7 +5097,7 @@
         <v>76</v>
       </c>
       <c r="P54" s="5" t="n">
-        <v>0.3069647463456578</v>
+        <v>0.2868269556383338</v>
       </c>
       <c r="Q54" s="9" t="inlineStr">
         <is>
@@ -5138,13 +5138,13 @@
         </is>
       </c>
       <c r="D55" s="13" t="n">
-        <v>136.5</v>
+        <v>137.37</v>
       </c>
       <c r="E55" s="18" t="n">
-        <v>0.0723</v>
+        <v>0.0791</v>
       </c>
       <c r="F55" s="18" t="n">
-        <v>0.2096</v>
+        <v>0.2173</v>
       </c>
       <c r="G55" s="15" t="n">
         <v>46331</v>
@@ -5173,7 +5173,7 @@
         <v>183</v>
       </c>
       <c r="M55" s="18" t="n">
-        <v>0.3406593406593407</v>
+        <v>0.3321685957632671</v>
       </c>
       <c r="N55" s="12" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>145</v>
       </c>
       <c r="P55" s="18" t="n">
-        <v>0.06227106227106227</v>
+        <v>0.055543422872534</v>
       </c>
       <c r="Q55" s="19" t="inlineStr">
         <is>
@@ -5225,13 +5225,13 @@
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>214.24</v>
+        <v>214.04</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0.0897</v>
+        <v>0.08869999999999999</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.1759</v>
+        <v>0.1748</v>
       </c>
       <c r="G56" s="6" t="n">
         <v>46325</v>
@@ -5260,7 +5260,7 @@
         <v>222</v>
       </c>
       <c r="M56" s="5" t="n">
-        <v>0.03622106049290511</v>
+        <v>0.03718931040926934</v>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>225</v>
       </c>
       <c r="P56" s="5" t="n">
-        <v>0.05022404779686328</v>
+        <v>0.05120538217155676</v>
       </c>
       <c r="Q56" s="9" t="inlineStr">
         <is>
@@ -5316,13 +5316,13 @@
         </is>
       </c>
       <c r="D57" s="13" t="n">
-        <v>146.62</v>
+        <v>147.35</v>
       </c>
       <c r="E57" s="18" t="n">
-        <v>0.0243</v>
+        <v>0.0294</v>
       </c>
       <c r="F57" s="18" t="n">
-        <v>0.05019999999999999</v>
+        <v>0.0555</v>
       </c>
       <c r="G57" s="15" t="n">
         <v>46331</v>
@@ -5351,7 +5351,7 @@
         <v>196</v>
       </c>
       <c r="M57" s="18" t="n">
-        <v>0.3367889783112808</v>
+        <v>0.330166270783848</v>
       </c>
       <c r="N57" s="12" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>170</v>
       </c>
       <c r="P57" s="18" t="n">
-        <v>0.1594598281271313</v>
+        <v>0.153715643026807</v>
       </c>
       <c r="Q57" s="19" t="inlineStr">
         <is>
@@ -5407,13 +5407,13 @@
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>39.17</v>
+        <v>38.91</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0.033</v>
+        <v>0.0261</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0.0224</v>
+        <v>0.0157</v>
       </c>
       <c r="G58" s="6" t="n">
         <v>46324</v>
@@ -5468,13 +5468,13 @@
         </is>
       </c>
       <c r="D59" s="13" t="n">
-        <v>21.45</v>
+        <v>21.54</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>0.0239</v>
+        <v>0.0282</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>0.063</v>
+        <v>0.0674</v>
       </c>
       <c r="G59" s="15" t="n">
         <v>46330</v>
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>202.1</v>
+        <v>204.97</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0206</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>0.0548</v>
+        <v>0.0698</v>
       </c>
       <c r="G60" s="6" t="n">
         <v>46328</v>
@@ -5590,13 +5590,13 @@
         </is>
       </c>
       <c r="D61" s="13" t="n">
-        <v>35.9</v>
+        <v>35.83</v>
       </c>
       <c r="E61" s="18" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.0764</v>
       </c>
       <c r="F61" s="18" t="n">
-        <v>0.0195</v>
+        <v>0.0178</v>
       </c>
       <c r="G61" s="15" t="n">
         <v>46315</v>
@@ -5632,7 +5632,7 @@
         <v>43</v>
       </c>
       <c r="P61" s="18" t="n">
-        <v>0.1977715877437326</v>
+        <v>0.2001116382919342</v>
       </c>
       <c r="Q61" s="19" t="inlineStr">
         <is>
@@ -5677,13 +5677,13 @@
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>30.97</v>
+        <v>30.86</v>
       </c>
       <c r="E62" s="22" t="n">
-        <v>-0.024</v>
+        <v>-0.0274</v>
       </c>
       <c r="F62" s="22" t="n">
-        <v>-0.0394</v>
+        <v>-0.0428</v>
       </c>
       <c r="G62" s="6" t="n">
         <v>46316</v>
@@ -5712,7 +5712,7 @@
         <v>35</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>0.1301259283177269</v>
+        <v>0.1341542449773169</v>
       </c>
       <c r="N62" s="3" t="inlineStr"/>
       <c r="O62" s="8" t="n"/>
@@ -5756,13 +5756,13 @@
         </is>
       </c>
       <c r="D63" s="13" t="n">
-        <v>262.33</v>
+        <v>259.49</v>
       </c>
       <c r="E63" s="18" t="n">
-        <v>0.1629</v>
+        <v>0.1503</v>
       </c>
       <c r="F63" s="18" t="n">
-        <v>0.323</v>
+        <v>0.3086</v>
       </c>
       <c r="G63" s="15" t="n">
         <v>46330</v>
@@ -5817,13 +5817,13 @@
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>56.09</v>
+        <v>56.06</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.06559999999999999</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>0.1843</v>
+        <v>0.1837</v>
       </c>
       <c r="G64" s="6" t="n">
         <v>46311</v>
@@ -5859,7 +5859,7 @@
         <v>63</v>
       </c>
       <c r="P64" s="5" t="n">
-        <v>0.123194865394901</v>
+        <v>0.1237959329290046</v>
       </c>
       <c r="Q64" s="9" t="inlineStr">
         <is>
@@ -5908,13 +5908,13 @@
         </is>
       </c>
       <c r="D65" s="13" t="n">
-        <v>44.56</v>
+        <v>44.71</v>
       </c>
       <c r="E65" s="18" t="n">
-        <v>0.0552</v>
+        <v>0.0587</v>
       </c>
       <c r="F65" s="18" t="n">
-        <v>0.0312</v>
+        <v>0.0347</v>
       </c>
       <c r="G65" s="15" t="n">
         <v>46328</v>
@@ -5969,13 +5969,13 @@
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>73.14</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="E66" s="22" t="n">
-        <v>-0.0077</v>
+        <v>-0.0115</v>
       </c>
       <c r="F66" s="22" t="n">
-        <v>-0.0178</v>
+        <v>-0.0216</v>
       </c>
       <c r="G66" s="6" t="n">
         <v>46328</v>
@@ -6004,7 +6004,7 @@
         <v>89</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>0.2168444079846869</v>
+        <v>0.2216884008236102</v>
       </c>
       <c r="N66" s="3" t="inlineStr"/>
       <c r="O66" s="8" t="n"/>
@@ -6060,13 +6060,13 @@
         </is>
       </c>
       <c r="D67" s="13" t="n">
-        <v>165.49</v>
+        <v>165.99</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>0.0359</v>
+        <v>0.039</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>0.1452</v>
+        <v>0.1486</v>
       </c>
       <c r="G67" s="15" t="n">
         <v>46325</v>
@@ -6095,7 +6095,7 @@
         <v>185</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>0.11789231977763</v>
+        <v>0.1145249713838182</v>
       </c>
       <c r="N67" s="12" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>185</v>
       </c>
       <c r="P67" s="18" t="n">
-        <v>0.11789231977763</v>
+        <v>0.1145249713838182</v>
       </c>
       <c r="Q67" s="19" t="inlineStr">
         <is>
@@ -6151,13 +6151,13 @@
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>114.6</v>
+        <v>115.27</v>
       </c>
       <c r="E68" s="22" t="n">
-        <v>-0.0508</v>
+        <v>-0.0452</v>
       </c>
       <c r="F68" s="22" t="n">
-        <v>-0.0706</v>
+        <v>-0.06509999999999999</v>
       </c>
       <c r="G68" s="6" t="n">
         <v>46329</v>
@@ -6186,7 +6186,7 @@
         <v>120</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>0.04712041884816759</v>
+        <v>0.04103409386657417</v>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
@@ -6196,8 +6196,8 @@
       <c r="O68" s="8" t="n">
         <v>115</v>
       </c>
-      <c r="P68" s="5" t="n">
-        <v>0.003490401396160608</v>
+      <c r="P68" s="22" t="n">
+        <v>-0.002342326711199758</v>
       </c>
       <c r="Q68" s="9" t="inlineStr"/>
       <c r="R68" s="8" t="n"/>
@@ -6232,13 +6232,13 @@
         </is>
       </c>
       <c r="D69" s="13" t="n">
-        <v>303.85</v>
+        <v>302.64</v>
       </c>
       <c r="E69" s="14" t="n">
-        <v>-0.1377</v>
+        <v>-0.1411</v>
       </c>
       <c r="F69" s="14" t="n">
-        <v>-0.1729</v>
+        <v>-0.1762</v>
       </c>
       <c r="G69" s="15" t="n">
         <v>46325</v>
@@ -6267,7 +6267,7 @@
         <v>406</v>
       </c>
       <c r="M69" s="18" t="n">
-        <v>0.3361856179035708</v>
+        <v>0.3415278879196406</v>
       </c>
       <c r="N69" s="12" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         <v>436</v>
       </c>
       <c r="P69" s="18" t="n">
-        <v>0.4349185453348691</v>
+        <v>0.4406555643669046</v>
       </c>
       <c r="Q69" s="19" t="inlineStr">
         <is>
@@ -6315,13 +6315,13 @@
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>323.02</v>
+        <v>324.68</v>
       </c>
       <c r="E70" s="22" t="n">
-        <v>-0.0612</v>
+        <v>-0.0564</v>
       </c>
       <c r="F70" s="22" t="n">
-        <v>-0.0886</v>
+        <v>-0.0839</v>
       </c>
       <c r="G70" s="6" t="n">
         <v>46311</v>
@@ -6350,7 +6350,7 @@
         <v>415</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>0.2847501702680949</v>
+        <v>0.2781815941850437</v>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>380</v>
       </c>
       <c r="P70" s="5" t="n">
-        <v>0.1763977462695809</v>
+        <v>0.1703831464826906</v>
       </c>
       <c r="Q70" s="9" t="inlineStr">
         <is>
@@ -6410,13 +6410,13 @@
         </is>
       </c>
       <c r="D71" s="13" t="n">
-        <v>62.55</v>
+        <v>62.69</v>
       </c>
       <c r="E71" s="14" t="n">
-        <v>-0.0349</v>
+        <v>-0.0328</v>
       </c>
       <c r="F71" s="18" t="n">
-        <v>0.0513</v>
+        <v>0.0535</v>
       </c>
       <c r="G71" s="15" t="n">
         <v>46309</v>
@@ -6471,13 +6471,13 @@
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>1085.3</v>
+        <v>1079.59</v>
       </c>
       <c r="E72" s="22" t="n">
-        <v>-0.06509999999999999</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>0.0521</v>
+        <v>0.0466</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>46308</v>
@@ -6509,7 +6509,7 @@
         <v>1245</v>
       </c>
       <c r="P72" s="5" t="n">
-        <v>0.1471482539390031</v>
+        <v>0.153215572578479</v>
       </c>
       <c r="Q72" s="9" t="inlineStr">
         <is>
@@ -6554,13 +6554,13 @@
         </is>
       </c>
       <c r="D73" s="13" t="n">
-        <v>35.01</v>
+        <v>35.18</v>
       </c>
       <c r="E73" s="18" t="n">
-        <v>0.4216</v>
+        <v>0.4283</v>
       </c>
       <c r="F73" s="18" t="n">
-        <v>0.531</v>
+        <v>0.5383</v>
       </c>
       <c r="G73" s="15" t="n"/>
       <c r="H73" s="21" t="inlineStr">
@@ -6605,13 +6605,13 @@
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>26.17</v>
+        <v>25.05</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>0.4625</v>
+        <v>0.4002000000000001</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>0.7909</v>
+        <v>0.7145999999999999</v>
       </c>
       <c r="G74" s="6" t="n">
         <v>46346</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="D75" s="13" t="n">
-        <v>506.72</v>
-      </c>
-      <c r="E75" s="14" t="n">
-        <v>-0.0064</v>
+        <v>510.34</v>
+      </c>
+      <c r="E75" s="18" t="n">
+        <v>0.0007000000000000001</v>
       </c>
       <c r="F75" s="18" t="n">
-        <v>0.0199</v>
+        <v>0.0272</v>
       </c>
       <c r="G75" s="15" t="n"/>
       <c r="H75" s="21" t="inlineStr">
@@ -6739,13 +6739,13 @@
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>65.59999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="E76" s="22" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.0684</v>
       </c>
       <c r="F76" s="22" t="n">
-        <v>-0.0522</v>
+        <v>-0.0435</v>
       </c>
       <c r="G76" s="6" t="n">
         <v>46321</v>
@@ -6774,7 +6774,7 @@
         <v>68</v>
       </c>
       <c r="M76" s="5" t="n">
-        <v>0.03658536585365862</v>
+        <v>0.02719033232628395</v>
       </c>
       <c r="N76" s="3" t="inlineStr"/>
       <c r="O76" s="8" t="n"/>
@@ -6816,13 +6816,13 @@
         </is>
       </c>
       <c r="D77" s="13" t="n">
-        <v>129.43</v>
+        <v>128.51</v>
       </c>
       <c r="E77" s="14" t="n">
-        <v>-0.1159</v>
+        <v>-0.1223</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>0.06059999999999999</v>
+        <v>0.053</v>
       </c>
       <c r="G77" s="15" t="n">
         <v>46310</v>
@@ -6881,13 +6881,13 @@
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>138.1</v>
+        <v>138.79</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="F78" s="22" t="n">
-        <v>-0.0185</v>
+        <v>-0.0136</v>
       </c>
       <c r="G78" s="6" t="n">
         <v>46308</v>
@@ -6919,7 +6919,7 @@
         <v>140</v>
       </c>
       <c r="P78" s="5" t="n">
-        <v>0.01375814627081829</v>
+        <v>0.008718207363642972</v>
       </c>
       <c r="Q78" s="9" t="inlineStr">
         <is>
@@ -6968,13 +6968,13 @@
         </is>
       </c>
       <c r="D79" s="13" t="n">
-        <v>336.37</v>
+        <v>338.19</v>
       </c>
       <c r="E79" s="14" t="n">
-        <v>-0.0203</v>
+        <v>-0.015</v>
       </c>
       <c r="F79" s="14" t="n">
-        <v>-0.0518</v>
+        <v>-0.0467</v>
       </c>
       <c r="G79" s="15" t="n">
         <v>46315</v>
@@ -7003,7 +7003,7 @@
         <v>358</v>
       </c>
       <c r="M79" s="18" t="n">
-        <v>0.06430418883967058</v>
+        <v>0.05857653981489696</v>
       </c>
       <c r="N79" s="12" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>374</v>
       </c>
       <c r="P79" s="18" t="n">
-        <v>0.1118708564973095</v>
+        <v>0.1058872231585795</v>
       </c>
       <c r="Q79" s="19" t="inlineStr">
         <is>
@@ -7059,13 +7059,13 @@
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>58.06</v>
+        <v>58.25</v>
       </c>
       <c r="E80" s="22" t="n">
-        <v>-0.0276</v>
+        <v>-0.0245</v>
       </c>
       <c r="F80" s="22" t="n">
-        <v>-0.0074</v>
+        <v>-0.004099999999999999</v>
       </c>
       <c r="G80" s="6" t="n">
         <v>46310</v>
@@ -7094,7 +7094,7 @@
         <v>57</v>
       </c>
       <c r="M80" s="22" t="n">
-        <v>-0.01825697554254224</v>
+        <v>-0.02145922746781116</v>
       </c>
       <c r="N80" s="3" t="inlineStr"/>
       <c r="O80" s="8" t="n"/>
@@ -7136,13 +7136,13 @@
         </is>
       </c>
       <c r="D81" s="13" t="n">
-        <v>13.77</v>
+        <v>13.67</v>
       </c>
       <c r="E81" s="18" t="n">
-        <v>0.131</v>
+        <v>0.1223</v>
       </c>
       <c r="F81" s="18" t="n">
-        <v>0.1145</v>
+        <v>0.106</v>
       </c>
       <c r="G81" s="15" t="n"/>
       <c r="H81" s="21" t="inlineStr">
@@ -7187,13 +7187,13 @@
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>410.38</v>
-      </c>
-      <c r="E82" s="5" t="n">
-        <v>0.0017</v>
+        <v>408.61</v>
+      </c>
+      <c r="E82" s="22" t="n">
+        <v>-0.0026</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>0.1335</v>
+        <v>0.1286</v>
       </c>
       <c r="G82" s="6" t="n">
         <v>46330</v>
@@ -7260,13 +7260,13 @@
         </is>
       </c>
       <c r="D83" s="13" t="n">
-        <v>93.68000000000001</v>
+        <v>90.63</v>
       </c>
       <c r="E83" s="18" t="n">
-        <v>0.3142</v>
+        <v>0.2715</v>
       </c>
       <c r="F83" s="18" t="n">
-        <v>0.487</v>
+        <v>0.4386</v>
       </c>
       <c r="G83" s="15" t="n"/>
       <c r="H83" s="21" t="inlineStr">
@@ -7311,13 +7311,13 @@
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>44.8</v>
+        <v>45.03</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>0.02</v>
+        <v>0.0253</v>
       </c>
       <c r="F84" s="22" t="n">
-        <v>-0.09</v>
+        <v>-0.08529999999999999</v>
       </c>
       <c r="G84" s="6" t="n">
         <v>46331</v>
@@ -7372,13 +7372,13 @@
         </is>
       </c>
       <c r="D85" s="13" t="n">
-        <v>1025.81</v>
+        <v>1029.1</v>
       </c>
       <c r="E85" s="14" t="n">
-        <v>-0.011</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F85" s="14" t="n">
-        <v>-0.0192</v>
+        <v>-0.0161</v>
       </c>
       <c r="G85" s="15" t="n">
         <v>46308</v>
@@ -7407,7 +7407,7 @@
         <v>1325</v>
       </c>
       <c r="M85" s="18" t="n">
-        <v>0.291662198652772</v>
+        <v>0.2875327956466817</v>
       </c>
       <c r="N85" s="12" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>1210</v>
       </c>
       <c r="P85" s="18" t="n">
-        <v>0.1795556682036635</v>
+        <v>0.1757846662131961</v>
       </c>
       <c r="Q85" s="19" t="inlineStr">
         <is>
@@ -7459,13 +7459,13 @@
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>136.64</v>
+        <v>136.66</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>0.1071</v>
+        <v>0.1073</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>0.0311</v>
+        <v>0.0312</v>
       </c>
       <c r="G86" s="6" t="n">
         <v>46324</v>
@@ -7520,13 +7520,13 @@
         </is>
       </c>
       <c r="D87" s="13" t="n">
-        <v>113.81</v>
+        <v>112.57</v>
       </c>
       <c r="E87" s="18" t="n">
-        <v>0.1991</v>
+        <v>0.1861</v>
       </c>
       <c r="F87" s="18" t="n">
-        <v>0.036</v>
+        <v>0.0247</v>
       </c>
       <c r="G87" s="15" t="n">
         <v>46330</v>
@@ -7581,13 +7581,13 @@
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>98.06999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>0.08039999999999999</v>
+        <v>0.0863</v>
       </c>
       <c r="F88" s="22" t="n">
-        <v>-0.0111</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="G88" s="6" t="n">
         <v>46329</v>
@@ -7642,13 +7642,13 @@
         </is>
       </c>
       <c r="D89" s="13" t="n">
-        <v>157.37</v>
+        <v>157.38</v>
       </c>
       <c r="E89" s="18" t="n">
-        <v>0.0399</v>
+        <v>0.04</v>
       </c>
       <c r="F89" s="18" t="n">
-        <v>0.1431</v>
+        <v>0.1432</v>
       </c>
       <c r="G89" s="15" t="n">
         <v>46324</v>
@@ -7703,13 +7703,13 @@
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>160.83</v>
+        <v>161.12</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>0.0559</v>
+        <v>0.0578</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0.067</v>
+        <v>0.0689</v>
       </c>
       <c r="G90" s="6" t="n">
         <v>46329</v>
@@ -7778,13 +7778,13 @@
         </is>
       </c>
       <c r="D91" s="13" t="n">
-        <v>356.6</v>
+        <v>356.28</v>
       </c>
       <c r="E91" s="14" t="n">
-        <v>-0.0235</v>
+        <v>-0.0244</v>
       </c>
       <c r="F91" s="18" t="n">
-        <v>0.066</v>
+        <v>0.065</v>
       </c>
       <c r="G91" s="15" t="n">
         <v>46308</v>
@@ -7813,7 +7813,7 @@
         <v>196</v>
       </c>
       <c r="M91" s="14" t="n">
-        <v>-0.4503645541222659</v>
+        <v>-0.4498708880655664</v>
       </c>
       <c r="N91" s="12" t="inlineStr"/>
       <c r="O91" s="17" t="n"/>
@@ -7857,13 +7857,13 @@
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>101.68</v>
+        <v>101.01</v>
       </c>
       <c r="E92" s="22" t="n">
-        <v>-0.0832</v>
+        <v>-0.0892</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>0.0492</v>
+        <v>0.0423</v>
       </c>
       <c r="G92" s="6" t="n"/>
       <c r="H92" s="7" t="inlineStr">
@@ -7882,7 +7882,7 @@
         <v>375</v>
       </c>
       <c r="M92" s="5" t="n">
-        <v>2.688040912667191</v>
+        <v>2.712503712503712</v>
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>368</v>
       </c>
       <c r="P92" s="5" t="n">
-        <v>2.619197482297404</v>
+        <v>2.643203643203643</v>
       </c>
       <c r="Q92" s="9" t="inlineStr">
         <is>
@@ -7946,13 +7946,13 @@
         </is>
       </c>
       <c r="D93" s="13" t="n">
-        <v>358.35</v>
+        <v>360.32</v>
       </c>
       <c r="E93" s="14" t="n">
-        <v>-0.0406</v>
+        <v>-0.0353</v>
       </c>
       <c r="F93" s="18" t="n">
-        <v>0.0388</v>
+        <v>0.0445</v>
       </c>
       <c r="G93" s="15" t="n">
         <v>46317</v>
@@ -7984,7 +7984,7 @@
         <v>115</v>
       </c>
       <c r="P93" s="14" t="n">
-        <v>-0.6790846937351751</v>
+        <v>-0.6808392539964476</v>
       </c>
       <c r="Q93" s="19" t="inlineStr">
         <is>
@@ -8033,13 +8033,13 @@
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>566.24</v>
+        <v>569.15</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0168</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0.05309999999999999</v>
+        <v>0.0585</v>
       </c>
       <c r="G94" s="6" t="n">
         <v>46324</v>
@@ -8068,7 +8068,7 @@
         <v>366</v>
       </c>
       <c r="M94" s="22" t="n">
-        <v>-0.3536309692003391</v>
+        <v>-0.3569357814284459</v>
       </c>
       <c r="N94" s="3" t="inlineStr"/>
       <c r="O94" s="8" t="n"/>
@@ -8110,13 +8110,13 @@
         </is>
       </c>
       <c r="D95" s="13" t="n">
-        <v>1773</v>
+        <v>1786.04</v>
       </c>
       <c r="E95" s="14" t="n">
-        <v>-0.0377</v>
+        <v>-0.0306</v>
       </c>
       <c r="F95" s="14" t="n">
-        <v>-0.0965</v>
+        <v>-0.0898</v>
       </c>
       <c r="G95" s="15" t="n">
         <v>46330</v>
@@ -8181,13 +8181,13 @@
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>212.57</v>
+        <v>214.38</v>
       </c>
       <c r="E96" s="22" t="n">
-        <v>-0.0233</v>
+        <v>-0.015</v>
       </c>
       <c r="F96" s="22" t="n">
-        <v>-0.0385</v>
+        <v>-0.0303</v>
       </c>
       <c r="G96" s="6" t="n">
         <v>46309</v>
@@ -8216,7 +8216,7 @@
         <v>668</v>
       </c>
       <c r="M96" s="5" t="n">
-        <v>2.142494237192454</v>
+        <v>2.11596230991697</v>
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>550</v>
       </c>
       <c r="P96" s="5" t="n">
-        <v>1.587382979724326</v>
+        <v>1.565537830021457</v>
       </c>
       <c r="Q96" s="9" t="inlineStr">
         <is>
@@ -8276,13 +8276,13 @@
         </is>
       </c>
       <c r="D97" s="13" t="n">
-        <v>114.76</v>
+        <v>116.17</v>
       </c>
       <c r="E97" s="18" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0211</v>
       </c>
       <c r="F97" s="18" t="n">
-        <v>0.0101</v>
+        <v>0.0225</v>
       </c>
       <c r="G97" s="15" t="n">
         <v>46321</v>
@@ -8311,7 +8311,7 @@
         <v>240</v>
       </c>
       <c r="M97" s="18" t="n">
-        <v>1.091321017776228</v>
+        <v>1.065937849703021</v>
       </c>
       <c r="N97" s="12" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>240</v>
       </c>
       <c r="P97" s="18" t="n">
-        <v>1.091321017776228</v>
+        <v>1.065937849703021</v>
       </c>
       <c r="Q97" s="19" t="inlineStr">
         <is>
@@ -8371,13 +8371,13 @@
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>242.17</v>
+        <v>244.3</v>
       </c>
       <c r="E98" s="22" t="n">
-        <v>-0.052</v>
+        <v>-0.0437</v>
       </c>
       <c r="F98" s="22" t="n">
-        <v>-0.04219999999999999</v>
+        <v>-0.0338</v>
       </c>
       <c r="G98" s="6" t="n">
         <v>46310</v>
@@ -8406,7 +8406,7 @@
         <v>113</v>
       </c>
       <c r="M98" s="22" t="n">
-        <v>-0.5333856381880497</v>
+        <v>-0.5374539500614</v>
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>114</v>
       </c>
       <c r="P98" s="22" t="n">
-        <v>-0.5292563075525457</v>
+        <v>-0.5333606221858371</v>
       </c>
       <c r="Q98" s="9" t="inlineStr"/>
       <c r="R98" s="8" t="n"/>
@@ -8456,13 +8456,13 @@
         </is>
       </c>
       <c r="D99" s="13" t="n">
-        <v>21.52</v>
+        <v>21.47</v>
       </c>
       <c r="E99" s="18" t="n">
-        <v>0.0591</v>
+        <v>0.0566</v>
       </c>
       <c r="F99" s="18" t="n">
-        <v>0.0659</v>
+        <v>0.0634</v>
       </c>
       <c r="G99" s="15" t="n">
         <v>46324</v>
@@ -8517,13 +8517,13 @@
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>14.81</v>
-      </c>
-      <c r="E100" s="22" t="n">
-        <v>-0.001</v>
+        <v>14.95</v>
+      </c>
+      <c r="E100" s="5" t="n">
+        <v>0.008800000000000001</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>0.08380000000000001</v>
+        <v>0.0944</v>
       </c>
       <c r="G100" s="6" t="n">
         <v>46323</v>
@@ -8578,13 +8578,13 @@
         </is>
       </c>
       <c r="D101" s="13" t="n">
-        <v>106.57</v>
+        <v>106.93</v>
       </c>
       <c r="E101" s="18" t="n">
-        <v>0.0098</v>
+        <v>0.0132</v>
       </c>
       <c r="F101" s="18" t="n">
-        <v>0.108</v>
+        <v>0.1118</v>
       </c>
       <c r="G101" s="15" t="n">
         <v>46323</v>
@@ -8613,7 +8613,7 @@
         <v>285</v>
       </c>
       <c r="M101" s="18" t="n">
-        <v>1.674298583090926</v>
+        <v>1.665295052838305</v>
       </c>
       <c r="N101" s="12" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>285</v>
       </c>
       <c r="P101" s="18" t="n">
-        <v>1.674298583090926</v>
+        <v>1.665295052838305</v>
       </c>
       <c r="Q101" s="19" t="inlineStr">
         <is>
@@ -8665,13 +8665,13 @@
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>411.71</v>
+        <v>410.7</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>0.0039</v>
+        <v>0.0015</v>
       </c>
       <c r="F102" s="22" t="n">
-        <v>-0.0597</v>
+        <v>-0.062</v>
       </c>
       <c r="G102" s="6" t="n">
         <v>46324</v>
@@ -8740,13 +8740,13 @@
         </is>
       </c>
       <c r="D103" s="13" t="n">
-        <v>50.21</v>
+        <v>50.39</v>
       </c>
       <c r="E103" s="14" t="n">
-        <v>-0.0467</v>
+        <v>-0.0433</v>
       </c>
       <c r="F103" s="14" t="n">
-        <v>-0.0335</v>
+        <v>-0.03</v>
       </c>
       <c r="G103" s="15" t="n">
         <v>46311</v>
@@ -8801,13 +8801,13 @@
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>369.01</v>
+        <v>370.46</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>0.0267</v>
+        <v>0.0307</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>0.0315</v>
+        <v>0.0355</v>
       </c>
       <c r="G104" s="6" t="n">
         <v>46322</v>
@@ -8836,7 +8836,7 @@
         <v>525</v>
       </c>
       <c r="M104" s="5" t="n">
-        <v>0.4227256713910192</v>
+        <v>0.4171570479943854</v>
       </c>
       <c r="N104" s="3" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         <v>543</v>
       </c>
       <c r="P104" s="5" t="n">
-        <v>0.4715048372672828</v>
+        <v>0.4657452896399072</v>
       </c>
       <c r="Q104" s="9" t="inlineStr">
         <is>
@@ -8892,13 +8892,13 @@
         </is>
       </c>
       <c r="D105" s="13" t="n">
-        <v>69.92</v>
+        <v>69.89</v>
       </c>
       <c r="E105" s="18" t="n">
-        <v>0.0027</v>
+        <v>0.0023</v>
       </c>
       <c r="F105" s="14" t="n">
-        <v>-0.05309999999999999</v>
+        <v>-0.0535</v>
       </c>
       <c r="G105" s="15" t="n">
         <v>46314</v>
@@ -8927,7 +8927,7 @@
         <v>412</v>
       </c>
       <c r="M105" s="18" t="n">
-        <v>4.892448512585812</v>
+        <v>4.894977822292174</v>
       </c>
       <c r="N105" s="12" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>350</v>
       </c>
       <c r="P105" s="18" t="n">
-        <v>4.005720823798627</v>
+        <v>4.007869509228788</v>
       </c>
       <c r="Q105" s="19" t="inlineStr">
         <is>
@@ -8983,13 +8983,13 @@
         </is>
       </c>
       <c r="D106" s="4" t="n">
-        <v>79.06999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0.0101</v>
+        <v>0.0118</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0061</v>
       </c>
       <c r="G106" s="6" t="n">
         <v>46331</v>
@@ -9018,7 +9018,7 @@
         <v>68</v>
       </c>
       <c r="M106" s="22" t="n">
-        <v>-0.1400025294043252</v>
+        <v>-0.1414141414141414</v>
       </c>
       <c r="N106" s="3" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>68</v>
       </c>
       <c r="P106" s="22" t="n">
-        <v>-0.1400025294043252</v>
+        <v>-0.1414141414141414</v>
       </c>
       <c r="Q106" s="9" t="inlineStr">
         <is>
@@ -9074,13 +9074,13 @@
         </is>
       </c>
       <c r="D107" s="13" t="n">
-        <v>256.5</v>
+        <v>257.05</v>
       </c>
       <c r="E107" s="18" t="n">
-        <v>0.0311</v>
+        <v>0.0333</v>
       </c>
       <c r="F107" s="18" t="n">
-        <v>0.0343</v>
+        <v>0.0365</v>
       </c>
       <c r="G107" s="15" t="n">
         <v>46325</v>
@@ -9109,7 +9109,7 @@
         <v>295</v>
       </c>
       <c r="M107" s="18" t="n">
-        <v>0.1500974658869396</v>
+        <v>0.1476366465668157</v>
       </c>
       <c r="N107" s="12" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         <v>246</v>
       </c>
       <c r="P107" s="14" t="n">
-        <v>-0.04093567251461988</v>
+        <v>-0.04298774557479094</v>
       </c>
       <c r="Q107" s="19" t="inlineStr">
         <is>
@@ -9157,13 +9157,13 @@
         </is>
       </c>
       <c r="D108" s="4" t="n">
-        <v>101.82</v>
+        <v>102</v>
       </c>
       <c r="E108" s="22" t="n">
-        <v>-0.0819</v>
+        <v>-0.0803</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>0.1055</v>
+        <v>0.1074</v>
       </c>
       <c r="G108" s="6" t="n">
         <v>46316</v>
@@ -9192,7 +9192,7 @@
         <v>112</v>
       </c>
       <c r="M108" s="5" t="n">
-        <v>0.09998035749361626</v>
+        <v>0.09803921568627451</v>
       </c>
       <c r="N108" s="3" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>120</v>
       </c>
       <c r="P108" s="5" t="n">
-        <v>0.1785503830288746</v>
+        <v>0.1764705882352941</v>
       </c>
       <c r="Q108" s="9" t="inlineStr">
         <is>
@@ -9256,13 +9256,13 @@
         </is>
       </c>
       <c r="D109" s="13" t="n">
-        <v>378.79</v>
+        <v>377.35</v>
       </c>
       <c r="E109" s="14" t="n">
-        <v>-0.08990000000000001</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="F109" s="18" t="n">
-        <v>0.0509</v>
+        <v>0.0469</v>
       </c>
       <c r="G109" s="15" t="n">
         <v>46329</v>
@@ -9291,7 +9291,7 @@
         <v>390</v>
       </c>
       <c r="M109" s="18" t="n">
-        <v>0.02959423427228802</v>
+        <v>0.03352325427322109</v>
       </c>
       <c r="N109" s="12" t="inlineStr">
         <is>
@@ -9339,13 +9339,13 @@
         </is>
       </c>
       <c r="D110" s="4" t="n">
-        <v>175.89</v>
+        <v>177.82</v>
       </c>
       <c r="E110" s="22" t="n">
-        <v>-0.04190000000000001</v>
+        <v>-0.0314</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>0.1434</v>
+        <v>0.156</v>
       </c>
       <c r="G110" s="6" t="n">
         <v>46331</v>
@@ -9374,7 +9374,7 @@
         <v>161</v>
       </c>
       <c r="M110" s="22" t="n">
-        <v>-0.08465518221615775</v>
+        <v>-0.09459003486671912</v>
       </c>
       <c r="N110" s="3" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>180</v>
       </c>
       <c r="P110" s="5" t="n">
-        <v>0.02336687702541369</v>
+        <v>0.01225958834776744</v>
       </c>
       <c r="Q110" s="9" t="inlineStr">
         <is>
@@ -9426,13 +9426,13 @@
         </is>
       </c>
       <c r="D111" s="13" t="n">
-        <v>42.97</v>
+        <v>42.96</v>
       </c>
       <c r="E111" s="14" t="n">
-        <v>-0.1644</v>
+        <v>-0.1645</v>
       </c>
       <c r="F111" s="14" t="n">
-        <v>-0.0377</v>
+        <v>-0.0378</v>
       </c>
       <c r="G111" s="15" t="n">
         <v>46323</v>
@@ -9461,7 +9461,7 @@
         <v>55</v>
       </c>
       <c r="M111" s="18" t="n">
-        <v>0.2799627647195718</v>
+        <v>0.2802607076350093</v>
       </c>
       <c r="N111" s="12" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         <v>65</v>
       </c>
       <c r="P111" s="18" t="n">
-        <v>0.5126832673958576</v>
+        <v>0.5130353817504655</v>
       </c>
       <c r="Q111" s="19" t="inlineStr">
         <is>
@@ -9513,13 +9513,13 @@
         </is>
       </c>
       <c r="D112" s="4" t="n">
-        <v>319.81</v>
+        <v>321.5</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0.018</v>
+        <v>0.0233</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>0.0447</v>
+        <v>0.05019999999999999</v>
       </c>
       <c r="G112" s="6" t="n">
         <v>46330</v>
@@ -9548,7 +9548,7 @@
         <v>331</v>
       </c>
       <c r="M112" s="5" t="n">
-        <v>0.03498952503048684</v>
+        <v>0.02954898911353033</v>
       </c>
       <c r="N112" s="3" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>330</v>
       </c>
       <c r="P112" s="5" t="n">
-        <v>0.03186266845939776</v>
+        <v>0.02643856920684292</v>
       </c>
       <c r="Q112" s="9" t="inlineStr">
         <is>
@@ -9608,13 +9608,13 @@
         </is>
       </c>
       <c r="D113" s="13" t="n">
-        <v>94.59999999999999</v>
+        <v>94.67</v>
       </c>
       <c r="E113" s="14" t="n">
-        <v>-0.0013</v>
+        <v>-0.0005</v>
       </c>
       <c r="F113" s="14" t="n">
-        <v>-0.1067</v>
+        <v>-0.106</v>
       </c>
       <c r="G113" s="15" t="n">
         <v>46330</v>
@@ -9643,7 +9643,7 @@
         <v>123</v>
       </c>
       <c r="M113" s="18" t="n">
-        <v>0.3002114164904863</v>
+        <v>0.2992500264075209</v>
       </c>
       <c r="N113" s="12" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>130</v>
       </c>
       <c r="P113" s="18" t="n">
-        <v>0.3742071881606766</v>
+        <v>0.373191084820957</v>
       </c>
       <c r="Q113" s="19" t="inlineStr">
         <is>
@@ -9695,13 +9695,13 @@
         </is>
       </c>
       <c r="D114" s="4" t="n">
-        <v>200.52</v>
+        <v>200.09</v>
       </c>
       <c r="E114" s="22" t="n">
-        <v>-0.0256</v>
-      </c>
-      <c r="F114" s="5" t="n">
-        <v>0.0018</v>
+        <v>-0.0277</v>
+      </c>
+      <c r="F114" s="22" t="n">
+        <v>-0.0003</v>
       </c>
       <c r="G114" s="6" t="n">
         <v>46315</v>
@@ -9730,7 +9730,7 @@
         <v>212</v>
       </c>
       <c r="M114" s="5" t="n">
-        <v>0.05725114701775379</v>
+        <v>0.05952321455345093</v>
       </c>
       <c r="N114" s="3" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>205</v>
       </c>
       <c r="P114" s="5" t="n">
-        <v>0.02234191103131852</v>
+        <v>0.02453895746913887</v>
       </c>
       <c r="Q114" s="9" t="inlineStr">
         <is>
@@ -9786,13 +9786,13 @@
         </is>
       </c>
       <c r="D115" s="13" t="n">
-        <v>83.29000000000001</v>
+        <v>83.03</v>
       </c>
       <c r="E115" s="14" t="n">
-        <v>-0.0827</v>
+        <v>-0.08560000000000001</v>
       </c>
       <c r="F115" s="18" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="G115" s="15" t="n">
         <v>46324</v>
@@ -9821,7 +9821,7 @@
         <v>85</v>
       </c>
       <c r="M115" s="18" t="n">
-        <v>0.0205306759514947</v>
+        <v>0.02372636396483198</v>
       </c>
       <c r="N115" s="12" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>90</v>
       </c>
       <c r="P115" s="18" t="n">
-        <v>0.08056189218393557</v>
+        <v>0.08394556184511621</v>
       </c>
       <c r="Q115" s="19" t="inlineStr">
         <is>
@@ -9873,13 +9873,13 @@
         </is>
       </c>
       <c r="D116" s="4" t="n">
-        <v>144.15</v>
+        <v>143.72</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0.0609</v>
+        <v>0.0578</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>0.09699999999999999</v>
+        <v>0.09380000000000001</v>
       </c>
       <c r="G116" s="6" t="n">
         <v>46324</v>
@@ -9908,7 +9908,7 @@
         <v>165</v>
       </c>
       <c r="M116" s="5" t="n">
-        <v>0.1446409989594172</v>
+        <v>0.1480656832730309</v>
       </c>
       <c r="N116" s="3" t="inlineStr"/>
       <c r="O116" s="8" t="n"/>
@@ -9956,13 +9956,13 @@
         </is>
       </c>
       <c r="D117" s="13" t="n">
-        <v>501.96</v>
+        <v>504.7</v>
       </c>
       <c r="E117" s="14" t="n">
-        <v>-0.1203</v>
+        <v>-0.1155</v>
       </c>
       <c r="F117" s="14" t="n">
-        <v>-0.1103</v>
+        <v>-0.1055</v>
       </c>
       <c r="G117" s="15" t="n">
         <v>46328</v>
@@ -10027,13 +10027,13 @@
         </is>
       </c>
       <c r="D118" s="4" t="n">
-        <v>370.08</v>
+        <v>369.15</v>
       </c>
       <c r="E118" s="22" t="n">
-        <v>-0.07769999999999999</v>
+        <v>-0.08</v>
       </c>
       <c r="F118" s="22" t="n">
-        <v>-0.091</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="G118" s="6" t="n">
         <v>46315</v>
@@ -10062,7 +10062,7 @@
         <v>487</v>
       </c>
       <c r="M118" s="5" t="n">
-        <v>0.3159316904453092</v>
+        <v>0.3192469185967765</v>
       </c>
       <c r="N118" s="3" t="inlineStr">
         <is>
@@ -10073,7 +10073,7 @@
         <v>375</v>
       </c>
       <c r="P118" s="5" t="n">
-        <v>0.0132944228274968</v>
+        <v>0.01584721657862664</v>
       </c>
       <c r="Q118" s="9" t="inlineStr">
         <is>
@@ -10118,13 +10118,13 @@
         </is>
       </c>
       <c r="D119" s="13" t="n">
-        <v>268.79</v>
+        <v>265.62</v>
       </c>
       <c r="E119" s="18" t="n">
-        <v>0.0304</v>
+        <v>0.0182</v>
       </c>
       <c r="F119" s="18" t="n">
-        <v>0.0428</v>
+        <v>0.0305</v>
       </c>
       <c r="G119" s="15" t="n">
         <v>46308</v>
@@ -10153,7 +10153,7 @@
         <v>272</v>
       </c>
       <c r="M119" s="18" t="n">
-        <v>0.01194240857174738</v>
+        <v>0.02401927565695353</v>
       </c>
       <c r="N119" s="12" t="inlineStr"/>
       <c r="O119" s="17" t="n"/>
@@ -10205,13 +10205,13 @@
         </is>
       </c>
       <c r="D120" s="4" t="n">
-        <v>1118.09</v>
+        <v>1115.23</v>
       </c>
       <c r="E120" s="22" t="n">
-        <v>-0.0837</v>
+        <v>-0.0861</v>
       </c>
       <c r="F120" s="22" t="n">
-        <v>-0.05400000000000001</v>
+        <v>-0.0564</v>
       </c>
       <c r="G120" s="6" t="n">
         <v>46324</v>
@@ -10240,7 +10240,7 @@
         <v>1280</v>
       </c>
       <c r="M120" s="5" t="n">
-        <v>0.1448094518330368</v>
+        <v>0.1477453081427149</v>
       </c>
       <c r="N120" s="3" t="inlineStr">
         <is>
@@ -10300,13 +10300,13 @@
         </is>
       </c>
       <c r="D121" s="13" t="n">
-        <v>90.78</v>
+        <v>90.98</v>
       </c>
       <c r="E121" s="18" t="n">
-        <v>0.0002</v>
+        <v>0.0024</v>
       </c>
       <c r="F121" s="18" t="n">
-        <v>0.0863</v>
+        <v>0.08869999999999999</v>
       </c>
       <c r="G121" s="15" t="n"/>
       <c r="H121" s="21" t="inlineStr">
@@ -10325,7 +10325,7 @@
         <v>102</v>
       </c>
       <c r="M121" s="18" t="n">
-        <v>0.1235955056179775</v>
+        <v>0.1211255220927676</v>
       </c>
       <c r="N121" s="12" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>105</v>
       </c>
       <c r="P121" s="18" t="n">
-        <v>0.1566424322538004</v>
+        <v>0.1540998021543196</v>
       </c>
       <c r="Q121" s="19" t="inlineStr">
         <is>
@@ -10377,13 +10377,13 @@
         </is>
       </c>
       <c r="D122" s="4" t="n">
-        <v>144.23</v>
+        <v>143.93</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0.0851</v>
+        <v>0.08289999999999999</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>0.1628</v>
+        <v>0.1605</v>
       </c>
       <c r="G122" s="6" t="n">
         <v>46324</v>
@@ -10412,7 +10412,7 @@
         <v>150</v>
       </c>
       <c r="M122" s="5" t="n">
-        <v>0.04000554669624912</v>
+        <v>0.04217327867713467</v>
       </c>
       <c r="N122" s="3" t="inlineStr"/>
       <c r="O122" s="8" t="n"/>
@@ -10456,13 +10456,13 @@
         </is>
       </c>
       <c r="D123" s="13" t="n">
-        <v>137.66</v>
+        <v>137.19</v>
       </c>
       <c r="E123" s="14" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.0993</v>
       </c>
       <c r="F123" s="14" t="n">
-        <v>-0.1024</v>
+        <v>-0.1055</v>
       </c>
       <c r="G123" s="15" t="n">
         <v>46322</v>
@@ -10535,13 +10535,13 @@
         </is>
       </c>
       <c r="D124" s="4" t="n">
-        <v>27.49</v>
+        <v>27.69</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0.04480000000000001</v>
+        <v>0.0525</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>0.123</v>
+        <v>0.1311</v>
       </c>
       <c r="G124" s="6" t="n">
         <v>46329</v>
@@ -10570,7 +10570,7 @@
         <v>28</v>
       </c>
       <c r="M124" s="5" t="n">
-        <v>0.01855220080029107</v>
+        <v>0.01119537739256044</v>
       </c>
       <c r="N124" s="3" t="inlineStr"/>
       <c r="O124" s="8" t="n"/>
@@ -10614,13 +10614,13 @@
         </is>
       </c>
       <c r="D125" s="13" t="n">
-        <v>269.86</v>
+        <v>275.57</v>
       </c>
       <c r="E125" s="14" t="n">
-        <v>-0.2228</v>
+        <v>-0.2063</v>
       </c>
       <c r="F125" s="14" t="n">
-        <v>-0.1858</v>
+        <v>-0.1686</v>
       </c>
       <c r="G125" s="15" t="n">
         <v>46324</v>
@@ -10649,7 +10649,7 @@
         <v>418</v>
       </c>
       <c r="M125" s="18" t="n">
-        <v>0.5489513080856739</v>
+        <v>0.5168559712595711</v>
       </c>
       <c r="N125" s="12" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>350</v>
       </c>
       <c r="P125" s="18" t="n">
-        <v>0.2969687986363299</v>
+        <v>0.2700947127771529</v>
       </c>
       <c r="Q125" s="19" t="inlineStr">
         <is>
@@ -10705,13 +10705,13 @@
         </is>
       </c>
       <c r="D126" s="4" t="n">
-        <v>608.33</v>
+        <v>610</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0116</v>
       </c>
       <c r="F126" s="5" t="n">
-        <v>0.151</v>
+        <v>0.1542</v>
       </c>
       <c r="G126" s="6" t="n">
         <v>46323</v>
@@ -10740,7 +10740,7 @@
         <v>615</v>
       </c>
       <c r="M126" s="5" t="n">
-        <v>0.010964443640787</v>
+        <v>0.00819672131147541</v>
       </c>
       <c r="N126" s="3" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         <v>570</v>
       </c>
       <c r="P126" s="22" t="n">
-        <v>-0.06300856443049009</v>
+        <v>-0.06557377049180328</v>
       </c>
       <c r="Q126" s="9" t="inlineStr">
         <is>
@@ -10800,13 +10800,13 @@
         </is>
       </c>
       <c r="D127" s="13" t="n">
-        <v>379.15</v>
+        <v>379.05</v>
       </c>
       <c r="E127" s="14" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.0654</v>
       </c>
       <c r="F127" s="14" t="n">
-        <v>-0.1164</v>
+        <v>-0.1166</v>
       </c>
       <c r="G127" s="15" t="n">
         <v>46322</v>
@@ -10835,7 +10835,7 @@
         <v>526</v>
       </c>
       <c r="M127" s="18" t="n">
-        <v>0.3873137280759595</v>
+        <v>0.3876797256298641</v>
       </c>
       <c r="N127" s="12" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>480</v>
       </c>
       <c r="P127" s="18" t="n">
-        <v>0.2659897138335752</v>
+        <v>0.2663237039968341</v>
       </c>
       <c r="Q127" s="19" t="inlineStr">
         <is>
@@ -10891,13 +10891,13 @@
         </is>
       </c>
       <c r="D128" s="4" t="n">
-        <v>72.33</v>
+        <v>72.97</v>
       </c>
       <c r="E128" s="22" t="n">
-        <v>-0.0164</v>
+        <v>-0.0077</v>
       </c>
       <c r="F128" s="22" t="n">
-        <v>-0.0405</v>
+        <v>-0.032</v>
       </c>
       <c r="G128" s="6" t="n">
         <v>46329</v>
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="D129" s="13" t="n">
-        <v>266.37</v>
+        <v>268.26</v>
       </c>
       <c r="E129" s="14" t="n">
-        <v>-0.011</v>
+        <v>-0.004</v>
       </c>
       <c r="F129" s="18" t="n">
-        <v>0.061</v>
+        <v>0.06860000000000001</v>
       </c>
       <c r="G129" s="15" t="n">
         <v>46330</v>
@@ -11005,7 +11005,7 @@
         <v>248</v>
       </c>
       <c r="M129" s="14" t="n">
-        <v>-0.06896422269775127</v>
+        <v>-0.07552374561992094</v>
       </c>
       <c r="N129" s="12" t="inlineStr"/>
       <c r="O129" s="17" t="n"/>
@@ -11061,13 +11061,13 @@
         </is>
       </c>
       <c r="D130" s="4" t="n">
-        <v>125.01</v>
+        <v>121.09</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>0.231</v>
+        <v>0.1924</v>
       </c>
       <c r="F130" s="5" t="n">
-        <v>0.0958</v>
+        <v>0.0614</v>
       </c>
       <c r="G130" s="6" t="n">
         <v>46325</v>
@@ -11122,13 +11122,13 @@
         </is>
       </c>
       <c r="D131" s="13" t="n">
-        <v>240.11</v>
+        <v>241.85</v>
       </c>
       <c r="E131" s="14" t="n">
-        <v>-0.0712</v>
+        <v>-0.0645</v>
       </c>
       <c r="F131" s="18" t="n">
-        <v>0.0345</v>
+        <v>0.042</v>
       </c>
       <c r="G131" s="15" t="n">
         <v>46324</v>
@@ -11183,13 +11183,13 @@
         </is>
       </c>
       <c r="D132" s="4" t="n">
-        <v>208.28</v>
+        <v>210.33</v>
       </c>
       <c r="E132" s="22" t="n">
-        <v>-0.09910000000000001</v>
+        <v>-0.09029999999999999</v>
       </c>
       <c r="F132" s="22" t="n">
-        <v>-0.0335</v>
+        <v>-0.024</v>
       </c>
       <c r="G132" s="6" t="n">
         <v>46330</v>
@@ -11218,7 +11218,7 @@
         <v>250</v>
       </c>
       <c r="M132" s="5" t="n">
-        <v>0.2003072786633378</v>
+        <v>0.1886083773118432</v>
       </c>
       <c r="N132" s="3" t="inlineStr"/>
       <c r="O132" s="8" t="n"/>
@@ -11262,13 +11262,13 @@
         </is>
       </c>
       <c r="D133" s="13" t="n">
-        <v>167.8</v>
+        <v>167.77</v>
       </c>
       <c r="E133" s="14" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-0.0089</v>
       </c>
       <c r="F133" s="18" t="n">
-        <v>0.111</v>
+        <v>0.1108</v>
       </c>
       <c r="G133" s="15" t="n">
         <v>46329</v>
@@ -11333,13 +11333,13 @@
         </is>
       </c>
       <c r="D134" s="4" t="n">
-        <v>818.87</v>
+        <v>818.54</v>
       </c>
       <c r="E134" s="22" t="n">
-        <v>-0.0429</v>
+        <v>-0.0433</v>
       </c>
       <c r="F134" s="22" t="n">
-        <v>-0.1209</v>
+        <v>-0.1212</v>
       </c>
       <c r="G134" s="6" t="n">
         <v>46330</v>
@@ -11368,7 +11368,7 @@
         <v>1155</v>
       </c>
       <c r="M134" s="5" t="n">
-        <v>0.4104802960176829</v>
+        <v>0.4110489407970289</v>
       </c>
       <c r="N134" s="3" t="inlineStr">
         <is>
@@ -11379,7 +11379,7 @@
         <v>1103</v>
       </c>
       <c r="P134" s="5" t="n">
-        <v>0.34697815282035</v>
+        <v>0.3475211962762969</v>
       </c>
       <c r="Q134" s="9" t="inlineStr">
         <is>
@@ -11420,13 +11420,13 @@
         </is>
       </c>
       <c r="D135" s="13" t="n">
-        <v>556.62</v>
+        <v>556.6799999999999</v>
       </c>
       <c r="E135" s="14" t="n">
-        <v>-0.1273</v>
+        <v>-0.1272</v>
       </c>
       <c r="F135" s="14" t="n">
-        <v>-0.1622</v>
+        <v>-0.1621</v>
       </c>
       <c r="G135" s="15" t="n">
         <v>46331</v>
@@ -11455,7 +11455,7 @@
         <v>874</v>
       </c>
       <c r="M135" s="18" t="n">
-        <v>0.5701915130609752</v>
+        <v>0.570022274915571</v>
       </c>
       <c r="N135" s="12" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>845</v>
       </c>
       <c r="P135" s="18" t="n">
-        <v>0.5180913369983112</v>
+        <v>0.5179277143062443</v>
       </c>
       <c r="Q135" s="19" t="inlineStr">
         <is>
@@ -11515,13 +11515,13 @@
         </is>
       </c>
       <c r="D136" s="4" t="n">
-        <v>201.67</v>
+        <v>201.5</v>
       </c>
       <c r="E136" s="22" t="n">
-        <v>-0.009000000000000001</v>
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>0.0975</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="G136" s="6" t="n">
         <v>46288</v>
@@ -11550,7 +11550,7 @@
         <v>250</v>
       </c>
       <c r="M136" s="5" t="n">
-        <v>0.2396489314226212</v>
+        <v>0.2406947890818859</v>
       </c>
       <c r="N136" s="3" t="inlineStr"/>
       <c r="O136" s="8" t="n"/>
@@ -11594,13 +11594,13 @@
         </is>
       </c>
       <c r="D137" s="13" t="n">
-        <v>687.04</v>
+        <v>676.29</v>
       </c>
       <c r="E137" s="18" t="n">
-        <v>0.1085</v>
+        <v>0.09119999999999999</v>
       </c>
       <c r="F137" s="18" t="n">
-        <v>0.1731</v>
+        <v>0.1548</v>
       </c>
       <c r="G137" s="15" t="n"/>
       <c r="H137" s="21" t="inlineStr">
@@ -11619,7 +11619,7 @@
         <v>750</v>
       </c>
       <c r="M137" s="18" t="n">
-        <v>0.09163949697251986</v>
+        <v>0.1089917047420486</v>
       </c>
       <c r="N137" s="12" t="inlineStr">
         <is>
@@ -11630,7 +11630,7 @@
         <v>641.29</v>
       </c>
       <c r="P137" s="14" t="n">
-        <v>-0.06659000931532372</v>
+        <v>-0.0517529462212956</v>
       </c>
       <c r="Q137" s="19" t="inlineStr">
         <is>
@@ -11671,13 +11671,13 @@
         </is>
       </c>
       <c r="D138" s="4" t="n">
-        <v>150.63</v>
+        <v>152.16</v>
       </c>
       <c r="E138" s="22" t="n">
-        <v>-0.08039999999999999</v>
+        <v>-0.0711</v>
       </c>
       <c r="F138" s="5" t="n">
-        <v>0.1126</v>
+        <v>0.1239</v>
       </c>
       <c r="G138" s="6" t="n">
         <v>46330</v>
@@ -11713,7 +11713,7 @@
         <v>185</v>
       </c>
       <c r="P138" s="5" t="n">
-        <v>0.2281749983403041</v>
+        <v>0.2158254468980021</v>
       </c>
       <c r="Q138" s="9" t="inlineStr">
         <is>
@@ -11752,13 +11752,13 @@
         </is>
       </c>
       <c r="D139" s="13" t="n">
-        <v>423.68</v>
+        <v>425.3</v>
       </c>
       <c r="E139" s="14" t="n">
-        <v>-0.0789</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="F139" s="18" t="n">
-        <v>0.0517</v>
+        <v>0.0557</v>
       </c>
       <c r="G139" s="15" t="n">
         <v>46329</v>
@@ -11794,7 +11794,7 @@
         <v>453</v>
       </c>
       <c r="P139" s="18" t="n">
-        <v>0.06920317220543805</v>
+        <v>0.06513049612038559</v>
       </c>
       <c r="Q139" s="19" t="inlineStr">
         <is>
@@ -11835,13 +11835,13 @@
         </is>
       </c>
       <c r="D140" s="4" t="n">
-        <v>49.41</v>
+        <v>49.32</v>
       </c>
       <c r="E140" s="22" t="n">
-        <v>-0.0538</v>
+        <v>-0.0555</v>
       </c>
       <c r="F140" s="5" t="n">
-        <v>0.05019999999999999</v>
+        <v>0.0482</v>
       </c>
       <c r="G140" s="6" t="n">
         <v>46309</v>
@@ -11914,13 +11914,13 @@
         </is>
       </c>
       <c r="D141" s="13" t="n">
-        <v>309.01</v>
+        <v>312</v>
       </c>
       <c r="E141" s="14" t="n">
-        <v>-0.0544</v>
+        <v>-0.0452</v>
       </c>
       <c r="F141" s="14" t="n">
-        <v>-0.0151</v>
+        <v>-0.005500000000000001</v>
       </c>
       <c r="G141" s="15" t="n">
         <v>46282</v>
@@ -11949,7 +11949,7 @@
         <v>425</v>
       </c>
       <c r="M141" s="18" t="n">
-        <v>0.3753600207113039</v>
+        <v>0.3621794871794872</v>
       </c>
       <c r="N141" s="12" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>323</v>
       </c>
       <c r="P141" s="18" t="n">
-        <v>0.04527361574059095</v>
+        <v>0.03525641025641026</v>
       </c>
       <c r="Q141" s="19" t="inlineStr">
         <is>
@@ -12001,13 +12001,13 @@
         </is>
       </c>
       <c r="D142" s="4" t="n">
-        <v>223.47</v>
+        <v>222.51</v>
       </c>
       <c r="E142" s="22" t="n">
-        <v>-0.0885</v>
+        <v>-0.0925</v>
       </c>
       <c r="F142" s="22" t="n">
-        <v>-0.0417</v>
+        <v>-0.0458</v>
       </c>
       <c r="G142" s="6" t="n"/>
       <c r="H142" s="7" t="inlineStr">
@@ -12026,7 +12026,7 @@
         <v>285</v>
       </c>
       <c r="M142" s="5" t="n">
-        <v>0.2753389716740502</v>
+        <v>0.2808413105028988</v>
       </c>
       <c r="N142" s="3" t="inlineStr"/>
       <c r="O142" s="8" t="n"/>
@@ -12074,7 +12074,7 @@
         </is>
       </c>
       <c r="D143" s="13" t="n">
-        <v>1690.98</v>
+        <v>1690.96</v>
       </c>
       <c r="E143" s="14" t="n">
         <v>-0.0275</v>
@@ -12135,13 +12135,13 @@
         </is>
       </c>
       <c r="D144" s="4" t="n">
-        <v>53.56</v>
+        <v>54.21</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>0.0293</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="F144" s="5" t="n">
-        <v>0.0791</v>
+        <v>0.09230000000000001</v>
       </c>
       <c r="G144" s="6" t="n"/>
       <c r="H144" s="7" t="inlineStr">
@@ -12186,13 +12186,13 @@
         </is>
       </c>
       <c r="D145" s="13" t="n">
-        <v>353.26</v>
+        <v>355.91</v>
       </c>
       <c r="E145" s="14" t="n">
-        <v>-0.1039</v>
+        <v>-0.09720000000000001</v>
       </c>
       <c r="F145" s="14" t="n">
-        <v>-0.0524</v>
+        <v>-0.0453</v>
       </c>
       <c r="G145" s="15" t="n">
         <v>46318</v>
@@ -12221,7 +12221,7 @@
         <v>400</v>
       </c>
       <c r="M145" s="18" t="n">
-        <v>0.1323104795334881</v>
+        <v>0.1238796324913601</v>
       </c>
       <c r="N145" s="12" t="inlineStr"/>
       <c r="O145" s="17" t="n"/>
@@ -12273,13 +12273,13 @@
         </is>
       </c>
       <c r="D146" s="4" t="n">
-        <v>323.28</v>
+        <v>323.61</v>
       </c>
       <c r="E146" s="22" t="n">
-        <v>-0.1151</v>
+        <v>-0.1142</v>
       </c>
       <c r="F146" s="22" t="n">
-        <v>-0.08529999999999999</v>
+        <v>-0.0843</v>
       </c>
       <c r="G146" s="6" t="n">
         <v>46315</v>
@@ -12308,7 +12308,7 @@
         <v>390</v>
       </c>
       <c r="M146" s="5" t="n">
-        <v>0.2063845582776541</v>
+        <v>0.205154352461296</v>
       </c>
       <c r="N146" s="3" t="inlineStr"/>
       <c r="O146" s="8" t="n"/>
@@ -12360,13 +12360,13 @@
         </is>
       </c>
       <c r="D147" s="13" t="n">
-        <v>956.76</v>
+        <v>956.5700000000001</v>
       </c>
       <c r="E147" s="14" t="n">
-        <v>-0.08</v>
+        <v>-0.0801</v>
       </c>
       <c r="F147" s="14" t="n">
-        <v>-0.0823</v>
+        <v>-0.0825</v>
       </c>
       <c r="G147" s="15" t="n">
         <v>46316</v>
@@ -12395,7 +12395,7 @@
         <v>1259</v>
       </c>
       <c r="M147" s="18" t="n">
-        <v>0.3158994941260087</v>
+        <v>0.3161608664290119</v>
       </c>
       <c r="N147" s="12" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         <v>1350</v>
       </c>
       <c r="P147" s="18" t="n">
-        <v>0.411012166060454</v>
+        <v>0.4112924302455648</v>
       </c>
       <c r="Q147" s="19" t="inlineStr">
         <is>
@@ -12451,13 +12451,13 @@
         </is>
       </c>
       <c r="D148" s="4" t="n">
-        <v>1287.23</v>
+        <v>1280.92</v>
       </c>
       <c r="E148" s="22" t="n">
-        <v>-0.0135</v>
+        <v>-0.0184</v>
       </c>
       <c r="F148" s="22" t="n">
-        <v>-0.075</v>
+        <v>-0.0796</v>
       </c>
       <c r="G148" s="6" t="n">
         <v>46325</v>
@@ -12526,13 +12526,13 @@
         </is>
       </c>
       <c r="D149" s="13" t="n">
-        <v>202.14</v>
+        <v>202.36</v>
       </c>
       <c r="E149" s="14" t="n">
-        <v>-0.1411</v>
+        <v>-0.1401</v>
       </c>
       <c r="F149" s="14" t="n">
-        <v>-0.09050000000000001</v>
+        <v>-0.0895</v>
       </c>
       <c r="G149" s="15" t="n">
         <v>46317</v>
@@ -12587,13 +12587,13 @@
         </is>
       </c>
       <c r="D150" s="4" t="n">
-        <v>464.22</v>
+        <v>460.34</v>
       </c>
       <c r="E150" s="22" t="n">
-        <v>-0.0949</v>
+        <v>-0.1025</v>
       </c>
       <c r="F150" s="22" t="n">
-        <v>-0.0269</v>
+        <v>-0.035</v>
       </c>
       <c r="G150" s="6" t="n">
         <v>46322</v>
@@ -12654,13 +12654,13 @@
         </is>
       </c>
       <c r="D151" s="13" t="n">
-        <v>267.05</v>
+        <v>268.24</v>
       </c>
       <c r="E151" s="14" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.083</v>
       </c>
       <c r="F151" s="14" t="n">
-        <v>-0.0164</v>
+        <v>-0.012</v>
       </c>
       <c r="G151" s="15" t="n">
         <v>46318</v>
@@ -12692,7 +12692,7 @@
         <v>272</v>
       </c>
       <c r="P151" s="18" t="n">
-        <v>0.01853585470885597</v>
+        <v>0.01401729794214133</v>
       </c>
       <c r="Q151" s="19" t="inlineStr">
         <is>
@@ -12745,13 +12745,13 @@
         </is>
       </c>
       <c r="D152" s="4" t="n">
-        <v>246.76</v>
+        <v>245.55</v>
       </c>
       <c r="E152" s="22" t="n">
-        <v>-0.1513</v>
+        <v>-0.1554</v>
       </c>
       <c r="F152" s="22" t="n">
-        <v>-0.1452</v>
+        <v>-0.1494</v>
       </c>
       <c r="G152" s="6" t="n">
         <v>46324</v>
@@ -12816,13 +12816,13 @@
         </is>
       </c>
       <c r="D153" s="13" t="n">
-        <v>372.14</v>
+        <v>365.86</v>
       </c>
       <c r="E153" s="14" t="n">
-        <v>-0.1159</v>
+        <v>-0.1308</v>
       </c>
       <c r="F153" s="14" t="n">
-        <v>-0.3248</v>
+        <v>-0.3362</v>
       </c>
       <c r="G153" s="15" t="n">
         <v>46323</v>
@@ -12877,13 +12877,13 @@
         </is>
       </c>
       <c r="D154" s="4" t="n">
-        <v>523.37</v>
+        <v>523.92</v>
       </c>
       <c r="E154" s="22" t="n">
-        <v>-0.1374</v>
+        <v>-0.1365</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.0062</v>
       </c>
       <c r="G154" s="6" t="n">
         <v>46315</v>
@@ -12944,13 +12944,13 @@
         </is>
       </c>
       <c r="D155" s="13" t="n">
-        <v>178.17</v>
+        <v>179.79</v>
       </c>
       <c r="E155" s="14" t="n">
-        <v>-0.1618</v>
+        <v>-0.1541</v>
       </c>
       <c r="F155" s="14" t="n">
-        <v>-0.235</v>
+        <v>-0.228</v>
       </c>
       <c r="G155" s="15" t="n">
         <v>46330</v>
@@ -12979,7 +12979,7 @@
         <v>575</v>
       </c>
       <c r="M155" s="18" t="n">
-        <v>2.22725486894539</v>
+        <v>2.198175649368708</v>
       </c>
       <c r="N155" s="12" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>237</v>
       </c>
       <c r="P155" s="18" t="n">
-        <v>0.3301902677218388</v>
+        <v>0.3182045720006675</v>
       </c>
       <c r="Q155" s="19" t="inlineStr">
         <is>
@@ -13039,13 +13039,13 @@
         </is>
       </c>
       <c r="D156" s="4" t="n">
-        <v>114.92</v>
+        <v>115.8</v>
       </c>
       <c r="E156" s="22" t="n">
-        <v>-0.0453</v>
+        <v>-0.038</v>
       </c>
       <c r="F156" s="5" t="n">
-        <v>0.03759999999999999</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="G156" s="6" t="n">
         <v>46288</v>
@@ -13074,7 +13074,7 @@
         <v>250</v>
       </c>
       <c r="M156" s="5" t="n">
-        <v>1.17542638357118</v>
+        <v>1.158894645941278</v>
       </c>
       <c r="N156" s="3" t="inlineStr"/>
       <c r="O156" s="8" t="n"/>
@@ -13118,13 +13118,13 @@
         </is>
       </c>
       <c r="D157" s="13" t="n">
-        <v>123.25</v>
+        <v>122.73</v>
       </c>
       <c r="E157" s="14" t="n">
-        <v>-0.0596</v>
+        <v>-0.0636</v>
       </c>
       <c r="F157" s="14" t="n">
-        <v>-0.008100000000000001</v>
+        <v>-0.0123</v>
       </c>
       <c r="G157" s="15" t="n">
         <v>46315</v>
@@ -13153,7 +13153,7 @@
         <v>95</v>
       </c>
       <c r="M157" s="14" t="n">
-        <v>-0.2292089249492901</v>
+        <v>-0.2259431271897662</v>
       </c>
       <c r="N157" s="12" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
         <v>139</v>
       </c>
       <c r="P157" s="18" t="n">
-        <v>0.127789046653144</v>
+        <v>0.1325674244276053</v>
       </c>
       <c r="Q157" s="19" t="inlineStr">
         <is>
@@ -13209,13 +13209,13 @@
         </is>
       </c>
       <c r="D158" s="4" t="n">
-        <v>944.49</v>
+        <v>950.17</v>
       </c>
       <c r="E158" s="22" t="n">
-        <v>-0.1169</v>
+        <v>-0.1116</v>
       </c>
       <c r="F158" s="22" t="n">
-        <v>-0.0071</v>
+        <v>-0.0011</v>
       </c>
       <c r="G158" s="6" t="n">
         <v>46331</v>
@@ -13244,7 +13244,7 @@
         <v>125</v>
       </c>
       <c r="M158" s="22" t="n">
-        <v>-0.8676534425986511</v>
+        <v>-0.8684445941252618</v>
       </c>
       <c r="N158" s="3" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>1064</v>
       </c>
       <c r="P158" s="5" t="n">
-        <v>0.1265338966002816</v>
+        <v>0.1197996148057716</v>
       </c>
       <c r="Q158" s="9" t="inlineStr">
         <is>
@@ -13300,13 +13300,13 @@
         </is>
       </c>
       <c r="D159" s="13" t="n">
-        <v>482.64</v>
+        <v>495.07</v>
       </c>
       <c r="E159" s="14" t="n">
-        <v>-0.1314</v>
+        <v>-0.109</v>
       </c>
       <c r="F159" s="14" t="n">
-        <v>-0.1744</v>
+        <v>-0.1531</v>
       </c>
       <c r="G159" s="15" t="n">
         <v>46325</v>
@@ -13381,13 +13381,13 @@
         </is>
       </c>
       <c r="D160" s="4" t="n">
-        <v>431.54</v>
+        <v>428.54</v>
       </c>
       <c r="E160" s="22" t="n">
-        <v>-0.044</v>
+        <v>-0.0506</v>
       </c>
       <c r="F160" s="22" t="n">
-        <v>-0.06280000000000001</v>
+        <v>-0.0693</v>
       </c>
       <c r="G160" s="6" t="n">
         <v>46331</v>
@@ -13442,13 +13442,13 @@
         </is>
       </c>
       <c r="D161" s="13" t="n">
-        <v>34.64</v>
+        <v>34.75</v>
       </c>
       <c r="E161" s="14" t="n">
-        <v>-0.0515</v>
+        <v>-0.04849999999999999</v>
       </c>
       <c r="F161" s="14" t="n">
-        <v>-0.2289</v>
+        <v>-0.2264</v>
       </c>
       <c r="G161" s="15" t="n">
         <v>46323</v>
@@ -13517,13 +13517,13 @@
         </is>
       </c>
       <c r="D162" s="4" t="n">
-        <v>197</v>
+        <v>197.67</v>
       </c>
       <c r="E162" s="22" t="n">
-        <v>-0.1156</v>
+        <v>-0.1126</v>
       </c>
       <c r="F162" s="5" t="n">
-        <v>0.0031</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="G162" s="6" t="n">
         <v>46315</v>
@@ -13596,13 +13596,13 @@
         </is>
       </c>
       <c r="D163" s="13" t="n">
-        <v>42.6</v>
+        <v>42.13</v>
       </c>
       <c r="E163" s="18" t="n">
-        <v>0.0342</v>
-      </c>
-      <c r="F163" s="18" t="n">
-        <v>0.004</v>
+        <v>0.0228</v>
+      </c>
+      <c r="F163" s="14" t="n">
+        <v>-0.0071</v>
       </c>
       <c r="G163" s="15" t="n"/>
       <c r="H163" s="21" t="inlineStr">
@@ -13647,13 +13647,13 @@
         </is>
       </c>
       <c r="D164" s="4" t="n">
-        <v>444.75</v>
+        <v>442.31</v>
       </c>
       <c r="E164" s="22" t="n">
-        <v>-0.0706</v>
+        <v>-0.0757</v>
       </c>
       <c r="F164" s="22" t="n">
-        <v>-0.0732</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="G164" s="6" t="n">
         <v>46324</v>
@@ -13685,7 +13685,7 @@
         <v>560</v>
       </c>
       <c r="P164" s="5" t="n">
-        <v>0.2591343451377178</v>
+        <v>0.2660803508851258</v>
       </c>
       <c r="Q164" s="9" t="inlineStr">
         <is>
@@ -13738,13 +13738,13 @@
         </is>
       </c>
       <c r="D165" s="13" t="n">
-        <v>283.81</v>
+        <v>284.4</v>
       </c>
       <c r="E165" s="14" t="n">
-        <v>-0.0338</v>
+        <v>-0.0318</v>
       </c>
       <c r="F165" s="14" t="n">
-        <v>-0.0184</v>
+        <v>-0.0164</v>
       </c>
       <c r="G165" s="15" t="n">
         <v>46317</v>
@@ -13776,7 +13776,7 @@
         <v>294</v>
       </c>
       <c r="P165" s="18" t="n">
-        <v>0.03590430217398963</v>
+        <v>0.03375527426160346</v>
       </c>
       <c r="Q165" s="19" t="inlineStr">
         <is>
@@ -13821,13 +13821,13 @@
         </is>
       </c>
       <c r="D166" s="4" t="n">
-        <v>256.86</v>
+        <v>257.06</v>
       </c>
       <c r="E166" s="22" t="n">
-        <v>-0.1092</v>
+        <v>-0.1085</v>
       </c>
       <c r="F166" s="22" t="n">
-        <v>-0.1602</v>
+        <v>-0.1596</v>
       </c>
       <c r="G166" s="6" t="n">
         <v>46323</v>
@@ -13859,7 +13859,7 @@
         <v>425</v>
       </c>
       <c r="P166" s="5" t="n">
-        <v>0.6545978353967141</v>
+        <v>0.6533105111647086</v>
       </c>
       <c r="Q166" s="9" t="inlineStr">
         <is>
@@ -13900,13 +13900,13 @@
         </is>
       </c>
       <c r="D167" s="13" t="n">
-        <v>213.04</v>
+        <v>213.44</v>
       </c>
       <c r="E167" s="14" t="n">
-        <v>-0.0587</v>
+        <v>-0.05690000000000001</v>
       </c>
       <c r="F167" s="14" t="n">
-        <v>-0.1</v>
+        <v>-0.0983</v>
       </c>
       <c r="G167" s="15" t="n">
         <v>46321</v>
@@ -13935,7 +13935,7 @@
         <v>268</v>
       </c>
       <c r="M167" s="18" t="n">
-        <v>0.2579797221179122</v>
+        <v>0.2556221889055472</v>
       </c>
       <c r="N167" s="12" t="inlineStr"/>
       <c r="O167" s="17" t="n"/>
@@ -13983,13 +13983,13 @@
         </is>
       </c>
       <c r="D168" s="4" t="n">
-        <v>316.05</v>
+        <v>314.1</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>0.0214</v>
+        <v>0.0152</v>
       </c>
       <c r="F168" s="22" t="n">
-        <v>-0.1973</v>
+        <v>-0.2022</v>
       </c>
       <c r="G168" s="6" t="n">
         <v>46330</v>
@@ -14058,13 +14058,13 @@
         </is>
       </c>
       <c r="D169" s="13" t="n">
-        <v>338.2</v>
+        <v>337.26</v>
       </c>
       <c r="E169" s="14" t="n">
-        <v>-0.0675</v>
+        <v>-0.0701</v>
       </c>
       <c r="F169" s="14" t="n">
-        <v>-0.1479</v>
+        <v>-0.1503</v>
       </c>
       <c r="G169" s="15" t="n"/>
       <c r="H169" s="21" t="inlineStr">
@@ -14127,13 +14127,13 @@
         </is>
       </c>
       <c r="D170" s="4" t="n">
-        <v>106.92</v>
+        <v>106.94</v>
       </c>
       <c r="E170" s="22" t="n">
-        <v>-0.1231</v>
+        <v>-0.1229</v>
       </c>
       <c r="F170" s="22" t="n">
-        <v>-0.1179</v>
+        <v>-0.1177</v>
       </c>
       <c r="G170" s="6" t="n">
         <v>46322</v>
@@ -14206,13 +14206,13 @@
         </is>
       </c>
       <c r="D171" s="13" t="n">
-        <v>106.12</v>
+        <v>105.36</v>
       </c>
       <c r="E171" s="14" t="n">
-        <v>-0.2315</v>
+        <v>-0.237</v>
       </c>
       <c r="F171" s="14" t="n">
-        <v>-0.0515</v>
+        <v>-0.0583</v>
       </c>
       <c r="G171" s="15" t="n">
         <v>46331</v>
@@ -14267,13 +14267,13 @@
         </is>
       </c>
       <c r="D172" s="4" t="n">
-        <v>334.11</v>
+        <v>332.27</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>0.1054</v>
+        <v>0.0993</v>
       </c>
       <c r="F172" s="5" t="n">
-        <v>0.0529</v>
+        <v>0.0471</v>
       </c>
       <c r="G172" s="6" t="n">
         <v>46324</v>
@@ -14302,7 +14302,7 @@
         <v>310</v>
       </c>
       <c r="M172" s="22" t="n">
-        <v>-0.07216186285953731</v>
+        <v>-0.06702380594095159</v>
       </c>
       <c r="N172" s="3" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         <v>365</v>
       </c>
       <c r="P172" s="5" t="n">
-        <v>0.09245458082667381</v>
+        <v>0.09850422848887959</v>
       </c>
       <c r="Q172" s="9" t="inlineStr">
         <is>
@@ -14370,13 +14370,13 @@
         </is>
       </c>
       <c r="D173" s="13" t="n">
-        <v>116.77</v>
+        <v>113.43</v>
       </c>
       <c r="E173" s="14" t="n">
-        <v>-0.1785</v>
+        <v>-0.202</v>
       </c>
       <c r="F173" s="14" t="n">
-        <v>-0.1449</v>
+        <v>-0.1694</v>
       </c>
       <c r="G173" s="15" t="n">
         <v>46329</v>
@@ -14431,13 +14431,13 @@
         </is>
       </c>
       <c r="D174" s="4" t="n">
-        <v>179.67</v>
-      </c>
-      <c r="E174" s="22" t="n">
-        <v>-0.0026</v>
+        <v>183.86</v>
+      </c>
+      <c r="E174" s="5" t="n">
+        <v>0.0207</v>
       </c>
       <c r="F174" s="5" t="n">
-        <v>0.2971</v>
+        <v>0.3273</v>
       </c>
       <c r="G174" s="6" t="n">
         <v>46296</v>
@@ -14492,13 +14492,13 @@
         </is>
       </c>
       <c r="D175" s="13" t="n">
-        <v>248.61</v>
+        <v>252.23</v>
       </c>
       <c r="E175" s="14" t="n">
-        <v>-0.0392</v>
+        <v>-0.0252</v>
       </c>
       <c r="F175" s="18" t="n">
-        <v>0.0781</v>
+        <v>0.09380000000000001</v>
       </c>
       <c r="G175" s="15" t="n"/>
       <c r="H175" s="21" t="inlineStr">
@@ -14543,13 +14543,13 @@
         </is>
       </c>
       <c r="D176" s="4" t="n">
-        <v>372.54</v>
+        <v>378.78</v>
       </c>
       <c r="E176" s="22" t="n">
-        <v>-0.0309</v>
+        <v>-0.0147</v>
       </c>
       <c r="F176" s="22" t="n">
-        <v>-0.0349</v>
+        <v>-0.0187</v>
       </c>
       <c r="G176" s="6" t="n"/>
       <c r="H176" s="7" t="inlineStr">
@@ -14568,7 +14568,7 @@
         <v>515</v>
       </c>
       <c r="M176" s="5" t="n">
-        <v>0.3824018897299618</v>
+        <v>0.3596282802682297</v>
       </c>
       <c r="N176" s="3" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>474</v>
       </c>
       <c r="P176" s="5" t="n">
-        <v>0.2723465936543726</v>
+        <v>0.2513860288293998</v>
       </c>
       <c r="Q176" s="9" t="inlineStr">
         <is>
@@ -14628,13 +14628,13 @@
         </is>
       </c>
       <c r="D177" s="13" t="n">
-        <v>211</v>
+        <v>212.4</v>
       </c>
       <c r="E177" s="14" t="n">
-        <v>-0.1543</v>
-      </c>
-      <c r="F177" s="14" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.1487</v>
+      </c>
+      <c r="F177" s="18" t="n">
+        <v>0.0008</v>
       </c>
       <c r="G177" s="15" t="n"/>
       <c r="H177" s="21" t="inlineStr">
@@ -14679,13 +14679,13 @@
         </is>
       </c>
       <c r="D178" s="4" t="n">
-        <v>282.66</v>
+        <v>287.25</v>
       </c>
       <c r="E178" s="22" t="n">
-        <v>-0.162</v>
+        <v>-0.1484</v>
       </c>
       <c r="F178" s="22" t="n">
-        <v>-0.05309999999999999</v>
+        <v>-0.0378</v>
       </c>
       <c r="G178" s="6" t="n">
         <v>46329</v>
@@ -14740,13 +14740,13 @@
         </is>
       </c>
       <c r="D179" s="13" t="n">
-        <v>292.61</v>
+        <v>291.22</v>
       </c>
       <c r="E179" s="14" t="n">
-        <v>-0.08220000000000001</v>
+        <v>-0.08650000000000001</v>
       </c>
       <c r="F179" s="14" t="n">
-        <v>-0.1918</v>
+        <v>-0.1956</v>
       </c>
       <c r="G179" s="15" t="n">
         <v>46329</v>
@@ -14801,13 +14801,13 @@
         </is>
       </c>
       <c r="D180" s="4" t="n">
-        <v>35.88</v>
+        <v>36.31</v>
       </c>
       <c r="E180" s="22" t="n">
-        <v>-0.1552</v>
+        <v>-0.145</v>
       </c>
       <c r="F180" s="22" t="n">
-        <v>-0.2945</v>
+        <v>-0.286</v>
       </c>
       <c r="G180" s="6" t="n">
         <v>46324</v>
@@ -14862,13 +14862,13 @@
         </is>
       </c>
       <c r="D181" s="13" t="n">
-        <v>458.79</v>
+        <v>456.49</v>
       </c>
       <c r="E181" s="14" t="n">
-        <v>-0.163</v>
+        <v>-0.1672</v>
       </c>
       <c r="F181" s="14" t="n">
-        <v>-0.2026</v>
+        <v>-0.2066</v>
       </c>
       <c r="G181" s="15" t="n"/>
       <c r="H181" s="21" t="inlineStr">
@@ -14887,7 +14887,7 @@
         <v>740</v>
       </c>
       <c r="M181" s="18" t="n">
-        <v>0.6129383813945377</v>
+        <v>0.6210650835724769</v>
       </c>
       <c r="N181" s="12" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
         <v>700</v>
       </c>
       <c r="P181" s="18" t="n">
-        <v>0.5257525229407789</v>
+        <v>0.5334399439199106</v>
       </c>
       <c r="Q181" s="19" t="inlineStr">
         <is>
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="D182" s="4" t="n">
-        <v>63.48</v>
+        <v>63.5</v>
       </c>
       <c r="E182" s="22" t="n">
-        <v>-0.0322</v>
+        <v>-0.0319</v>
       </c>
       <c r="F182" s="22" t="n">
-        <v>-0.2197</v>
+        <v>-0.2194</v>
       </c>
       <c r="G182" s="6" t="n">
         <v>46331</v>
@@ -15004,13 +15004,13 @@
         </is>
       </c>
       <c r="D183" s="13" t="n">
-        <v>517.7</v>
+        <v>516.13</v>
       </c>
       <c r="E183" s="18" t="n">
-        <v>0.07200000000000001</v>
+        <v>0.0687</v>
       </c>
       <c r="F183" s="14" t="n">
-        <v>-0.0312</v>
+        <v>-0.0342</v>
       </c>
       <c r="G183" s="15" t="n">
         <v>46329</v>
@@ -15039,7 +15039,7 @@
         <v>615</v>
       </c>
       <c r="M183" s="18" t="n">
-        <v>0.1879466872706199</v>
+        <v>0.1915602658245016</v>
       </c>
       <c r="N183" s="12" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>579</v>
       </c>
       <c r="P183" s="18" t="n">
-        <v>0.1184083446011202</v>
+        <v>0.1218103966055064</v>
       </c>
       <c r="Q183" s="19" t="inlineStr">
         <is>
@@ -15091,13 +15091,13 @@
         </is>
       </c>
       <c r="D184" s="4" t="n">
-        <v>50.9</v>
+        <v>51.73</v>
       </c>
       <c r="E184" s="22" t="n">
-        <v>-0.08439999999999999</v>
+        <v>-0.0694</v>
       </c>
       <c r="F184" s="22" t="n">
-        <v>-0.2295</v>
+        <v>-0.2169</v>
       </c>
       <c r="G184" s="6" t="n">
         <v>46321</v>
@@ -15152,13 +15152,13 @@
         </is>
       </c>
       <c r="D185" s="13" t="n">
-        <v>199.71</v>
+        <v>199.45</v>
       </c>
       <c r="E185" s="14" t="n">
-        <v>-0.0513</v>
+        <v>-0.0525</v>
       </c>
       <c r="F185" s="18" t="n">
-        <v>0.1025</v>
+        <v>0.101</v>
       </c>
       <c r="G185" s="15" t="n">
         <v>46329</v>
@@ -15187,7 +15187,7 @@
         <v>200</v>
       </c>
       <c r="M185" s="18" t="n">
-        <v>0.001452105553051885</v>
+        <v>0.002757583354224174</v>
       </c>
       <c r="N185" s="12" t="inlineStr">
         <is>
@@ -15198,7 +15198,7 @@
         <v>200</v>
       </c>
       <c r="P185" s="18" t="n">
-        <v>0.001452105553051885</v>
+        <v>0.002757583354224174</v>
       </c>
       <c r="Q185" s="19" t="inlineStr">
         <is>
@@ -15243,13 +15243,13 @@
         </is>
       </c>
       <c r="D186" s="4" t="n">
-        <v>83.19</v>
+        <v>83.92</v>
       </c>
       <c r="E186" s="22" t="n">
-        <v>-0.021</v>
+        <v>-0.0125</v>
       </c>
       <c r="F186" s="5" t="n">
-        <v>0.0667</v>
+        <v>0.076</v>
       </c>
       <c r="G186" s="6" t="n">
         <v>46323</v>
@@ -15281,7 +15281,7 @@
         <v>180</v>
       </c>
       <c r="P186" s="5" t="n">
-        <v>1.163721601153985</v>
+        <v>1.144899904671115</v>
       </c>
       <c r="Q186" s="9" t="inlineStr">
         <is>
@@ -15334,13 +15334,13 @@
         </is>
       </c>
       <c r="D187" s="13" t="n">
-        <v>26.46</v>
+        <v>26.42</v>
       </c>
       <c r="E187" s="14" t="n">
-        <v>-0.1507</v>
+        <v>-0.1518</v>
       </c>
       <c r="F187" s="14" t="n">
-        <v>-0.08259999999999999</v>
+        <v>-0.0839</v>
       </c>
       <c r="G187" s="15" t="n">
         <v>46303</v>
@@ -15395,13 +15395,13 @@
         </is>
       </c>
       <c r="D188" s="4" t="n">
-        <v>255.21</v>
+        <v>264.79</v>
       </c>
       <c r="E188" s="22" t="n">
-        <v>-0.0613</v>
+        <v>-0.026</v>
       </c>
       <c r="F188" s="22" t="n">
-        <v>-0.1464</v>
+        <v>-0.1144</v>
       </c>
       <c r="G188" s="6" t="n">
         <v>46330</v>
@@ -15456,13 +15456,13 @@
         </is>
       </c>
       <c r="D189" s="13" t="n">
-        <v>1703.62</v>
+        <v>1698.3</v>
       </c>
       <c r="E189" s="14" t="n">
-        <v>-0.0588</v>
+        <v>-0.0617</v>
       </c>
       <c r="F189" s="14" t="n">
-        <v>-0.013</v>
+        <v>-0.0161</v>
       </c>
       <c r="G189" s="15" t="n">
         <v>46309</v>
@@ -15535,13 +15535,13 @@
         </is>
       </c>
       <c r="D190" s="4" t="n">
-        <v>39.42</v>
+        <v>39.47</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>0.0034</v>
+        <v>0.004699999999999999</v>
       </c>
       <c r="F190" s="22" t="n">
-        <v>-0.0282</v>
+        <v>-0.027</v>
       </c>
       <c r="G190" s="6" t="n">
         <v>46324</v>
@@ -15596,13 +15596,13 @@
         </is>
       </c>
       <c r="D191" s="13" t="n">
-        <v>364.52</v>
+        <v>361.99</v>
       </c>
       <c r="E191" s="14" t="n">
-        <v>-0.1239</v>
+        <v>-0.1299</v>
       </c>
       <c r="F191" s="14" t="n">
-        <v>-0.0509</v>
+        <v>-0.0574</v>
       </c>
       <c r="G191" s="15" t="n"/>
       <c r="H191" s="21" t="inlineStr">
@@ -15621,7 +15621,7 @@
         <v>545</v>
       </c>
       <c r="M191" s="18" t="n">
-        <v>0.4951168660155822</v>
+        <v>0.5055664521119367</v>
       </c>
       <c r="N191" s="12" t="inlineStr">
         <is>
@@ -15632,7 +15632,7 @@
         <v>582</v>
       </c>
       <c r="P191" s="18" t="n">
-        <v>0.5966202128826952</v>
+        <v>0.6077792204204535</v>
       </c>
       <c r="Q191" s="19" t="inlineStr">
         <is>
@@ -15685,13 +15685,13 @@
         </is>
       </c>
       <c r="D192" s="4" t="n">
-        <v>147.26</v>
+        <v>147.97</v>
       </c>
       <c r="E192" s="22" t="n">
-        <v>-0.1546</v>
+        <v>-0.1506</v>
       </c>
       <c r="F192" s="5" t="n">
-        <v>0.0766</v>
+        <v>0.0818</v>
       </c>
       <c r="G192" s="6" t="n"/>
       <c r="H192" s="7" t="inlineStr">
@@ -15736,13 +15736,13 @@
         </is>
       </c>
       <c r="D193" s="13" t="n">
-        <v>287.33</v>
+        <v>289.37</v>
       </c>
       <c r="E193" s="14" t="n">
-        <v>-0.1108</v>
+        <v>-0.1045</v>
       </c>
       <c r="F193" s="14" t="n">
-        <v>-0.2397</v>
+        <v>-0.2343</v>
       </c>
       <c r="G193" s="15" t="n">
         <v>46321</v>
@@ -15771,7 +15771,7 @@
         <v>425</v>
       </c>
       <c r="M193" s="18" t="n">
-        <v>0.4791354888107752</v>
+        <v>0.4687078826416007</v>
       </c>
       <c r="N193" s="12" t="inlineStr"/>
       <c r="O193" s="17" t="n"/>
@@ -15815,13 +15815,13 @@
         </is>
       </c>
       <c r="D194" s="4" t="n">
-        <v>130.8</v>
+        <v>131.64</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>0.0117</v>
+        <v>0.0182</v>
       </c>
       <c r="F194" s="22" t="n">
-        <v>-0.0262</v>
+        <v>-0.02</v>
       </c>
       <c r="G194" s="6" t="n">
         <v>46322</v>
@@ -15876,13 +15876,13 @@
         </is>
       </c>
       <c r="D195" s="13" t="n">
-        <v>349.61</v>
+        <v>349.45</v>
       </c>
       <c r="E195" s="14" t="n">
-        <v>-0.1908</v>
+        <v>-0.1912</v>
       </c>
       <c r="F195" s="14" t="n">
-        <v>-0.2151</v>
+        <v>-0.2155</v>
       </c>
       <c r="G195" s="15" t="n"/>
       <c r="H195" s="21" t="inlineStr">
@@ -15927,13 +15927,13 @@
         </is>
       </c>
       <c r="D196" s="4" t="n">
-        <v>11.13</v>
+        <v>11.23</v>
       </c>
       <c r="E196" s="22" t="n">
-        <v>-0.2702</v>
+        <v>-0.2636</v>
       </c>
       <c r="F196" s="22" t="n">
-        <v>-0.31</v>
+        <v>-0.3038</v>
       </c>
       <c r="G196" s="6" t="n"/>
       <c r="H196" s="7" t="inlineStr">
@@ -15978,13 +15978,13 @@
         </is>
       </c>
       <c r="D197" s="13" t="n">
-        <v>349.7</v>
+        <v>346.64</v>
       </c>
       <c r="E197" s="18" t="n">
-        <v>0.0302</v>
+        <v>0.0212</v>
       </c>
       <c r="F197" s="18" t="n">
-        <v>0.0131</v>
+        <v>0.0042</v>
       </c>
       <c r="G197" s="15" t="n">
         <v>46321</v>
@@ -16039,13 +16039,13 @@
         </is>
       </c>
       <c r="D198" s="4" t="n">
-        <v>301.94</v>
+        <v>305.28</v>
       </c>
       <c r="E198" s="22" t="n">
-        <v>-0.151</v>
+        <v>-0.1416</v>
       </c>
       <c r="F198" s="22" t="n">
-        <v>-0.0177</v>
+        <v>-0.0069</v>
       </c>
       <c r="G198" s="6" t="n">
         <v>46330</v>
@@ -16100,13 +16100,13 @@
         </is>
       </c>
       <c r="D199" s="13" t="n">
-        <v>58.29</v>
+        <v>57.08</v>
       </c>
       <c r="E199" s="18" t="n">
-        <v>0.0382</v>
+        <v>0.0167</v>
       </c>
       <c r="F199" s="18" t="n">
-        <v>0.1037</v>
+        <v>0.0809</v>
       </c>
       <c r="G199" s="15" t="n">
         <v>46330</v>
@@ -16161,13 +16161,13 @@
         </is>
       </c>
       <c r="D200" s="4" t="n">
-        <v>17.96</v>
+        <v>17.94</v>
       </c>
       <c r="E200" s="22" t="n">
-        <v>-0.1394</v>
+        <v>-0.1404</v>
       </c>
       <c r="F200" s="22" t="n">
-        <v>-0.2092</v>
+        <v>-0.21</v>
       </c>
       <c r="G200" s="6" t="n">
         <v>46318</v>
@@ -16222,13 +16222,13 @@
         </is>
       </c>
       <c r="D201" s="13" t="n">
-        <v>162.85</v>
+        <v>162.95</v>
       </c>
       <c r="E201" s="14" t="n">
-        <v>-0.3927</v>
+        <v>-0.3923</v>
       </c>
       <c r="F201" s="14" t="n">
-        <v>-0.3125</v>
+        <v>-0.3121</v>
       </c>
       <c r="G201" s="15" t="n"/>
       <c r="H201" s="21" t="inlineStr">
@@ -16273,13 +16273,13 @@
         </is>
       </c>
       <c r="D202" s="4" t="n">
-        <v>248.01</v>
+        <v>247.65</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>0.2829</v>
+        <v>0.281</v>
       </c>
       <c r="F202" s="5" t="n">
-        <v>0.4485</v>
+        <v>0.4464</v>
       </c>
       <c r="G202" s="6" t="n"/>
       <c r="H202" s="7" t="inlineStr">
@@ -16298,7 +16298,7 @@
         <v>200</v>
       </c>
       <c r="M202" s="22" t="n">
-        <v>-0.1935809039958066</v>
+        <v>-0.1924086412275389</v>
       </c>
       <c r="N202" s="3" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>250</v>
       </c>
       <c r="P202" s="5" t="n">
-        <v>0.008023870005241761</v>
+        <v>0.009489198465576396</v>
       </c>
       <c r="Q202" s="9" t="inlineStr">
         <is>
@@ -16354,13 +16354,13 @@
         </is>
       </c>
       <c r="D203" s="13" t="n">
-        <v>206.7</v>
+        <v>206.74</v>
       </c>
       <c r="E203" s="14" t="n">
-        <v>-0.068</v>
+        <v>-0.0678</v>
       </c>
       <c r="F203" s="18" t="n">
-        <v>0.1</v>
+        <v>0.1002</v>
       </c>
       <c r="G203" s="15" t="n"/>
       <c r="H203" s="21" t="inlineStr">
@@ -16379,7 +16379,7 @@
         <v>181.25</v>
       </c>
       <c r="M203" s="14" t="n">
-        <v>-0.1231253023705853</v>
+        <v>-0.1232949598529554</v>
       </c>
       <c r="N203" s="12" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>177.5</v>
       </c>
       <c r="P203" s="14" t="n">
-        <v>-0.1412675374939525</v>
+        <v>-0.141433684821515</v>
       </c>
       <c r="Q203" s="19" t="inlineStr">
         <is>
@@ -16431,13 +16431,13 @@
         </is>
       </c>
       <c r="D204" s="4" t="n">
-        <v>90.51000000000001</v>
+        <v>88.98999999999999</v>
       </c>
       <c r="E204" s="22" t="n">
-        <v>-0.1599</v>
+        <v>-0.174</v>
       </c>
       <c r="F204" s="5" t="n">
-        <v>0.0864</v>
+        <v>0.0682</v>
       </c>
       <c r="G204" s="6" t="n"/>
       <c r="H204" s="7" t="inlineStr">
@@ -16482,13 +16482,13 @@
         </is>
       </c>
       <c r="D205" s="13" t="n">
-        <v>110.94</v>
+        <v>112.13</v>
       </c>
       <c r="E205" s="14" t="n">
-        <v>-0.1045</v>
+        <v>-0.09480000000000001</v>
       </c>
       <c r="F205" s="14" t="n">
-        <v>-0.0697</v>
+        <v>-0.0597</v>
       </c>
       <c r="G205" s="15" t="n"/>
       <c r="H205" s="21" t="inlineStr">
@@ -16507,7 +16507,7 @@
         <v>130</v>
       </c>
       <c r="M205" s="18" t="n">
-        <v>0.1718045790517397</v>
+        <v>0.1593685900294302</v>
       </c>
       <c r="N205" s="12" t="inlineStr">
         <is>
@@ -16518,7 +16518,7 @@
         <v>150</v>
       </c>
       <c r="P205" s="18" t="n">
-        <v>0.3520822065981612</v>
+        <v>0.3377329884954964</v>
       </c>
       <c r="Q205" s="19" t="inlineStr">
         <is>
@@ -16575,13 +16575,13 @@
         </is>
       </c>
       <c r="D206" s="4" t="n">
-        <v>221.45</v>
+        <v>221.21</v>
       </c>
       <c r="E206" s="22" t="n">
-        <v>-0.0808</v>
+        <v>-0.0818</v>
       </c>
       <c r="F206" s="22" t="n">
-        <v>-0.1491</v>
+        <v>-0.15</v>
       </c>
       <c r="G206" s="6" t="n">
         <v>46331</v>
@@ -16636,13 +16636,13 @@
         </is>
       </c>
       <c r="D207" s="13" t="n">
-        <v>566.08</v>
+        <v>567.14</v>
       </c>
       <c r="E207" s="18" t="n">
-        <v>0.1684</v>
+        <v>0.1706</v>
       </c>
       <c r="F207" s="18" t="n">
-        <v>0.3254</v>
+        <v>0.3279</v>
       </c>
       <c r="G207" s="15" t="n"/>
       <c r="H207" s="21" t="inlineStr">
@@ -16687,13 +16687,13 @@
         </is>
       </c>
       <c r="D208" s="4" t="n">
-        <v>66.06</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>0.1369</v>
+        <v>0.1299</v>
       </c>
       <c r="F208" s="5" t="n">
-        <v>0.3245</v>
+        <v>0.3164</v>
       </c>
       <c r="G208" s="6" t="n"/>
       <c r="H208" s="7" t="inlineStr">
@@ -16738,13 +16738,13 @@
         </is>
       </c>
       <c r="D209" s="13" t="n">
-        <v>51.29</v>
+        <v>51.07</v>
       </c>
       <c r="E209" s="18" t="n">
-        <v>0.0349</v>
+        <v>0.0305</v>
       </c>
       <c r="F209" s="18" t="n">
-        <v>0.1503</v>
+        <v>0.1453</v>
       </c>
       <c r="G209" s="15" t="n">
         <v>46330</v>
@@ -16799,13 +16799,13 @@
         </is>
       </c>
       <c r="D210" s="4" t="n">
-        <v>413.27</v>
+        <v>414.61</v>
       </c>
       <c r="E210" s="22" t="n">
-        <v>-0.2773</v>
+        <v>-0.275</v>
       </c>
       <c r="F210" s="22" t="n">
-        <v>-0.1293</v>
+        <v>-0.1265</v>
       </c>
       <c r="G210" s="6" t="n">
         <v>46328</v>
@@ -16860,13 +16860,13 @@
         </is>
       </c>
       <c r="D211" s="13" t="n">
-        <v>113.82</v>
+        <v>114.95</v>
       </c>
       <c r="E211" s="14" t="n">
-        <v>-0.1161</v>
+        <v>-0.1073</v>
       </c>
       <c r="F211" s="18" t="n">
-        <v>0.0319</v>
+        <v>0.04219999999999999</v>
       </c>
       <c r="G211" s="15" t="n">
         <v>46330</v>
@@ -16921,13 +16921,13 @@
         </is>
       </c>
       <c r="D212" s="4" t="n">
-        <v>156.77</v>
+        <v>156.07</v>
       </c>
       <c r="E212" s="22" t="n">
-        <v>-0.0253</v>
+        <v>-0.0297</v>
       </c>
       <c r="F212" s="22" t="n">
-        <v>-0.0239</v>
+        <v>-0.0283</v>
       </c>
       <c r="G212" s="6" t="n">
         <v>46330</v>
@@ -16982,13 +16982,13 @@
         </is>
       </c>
       <c r="D213" s="13" t="n">
-        <v>46.6</v>
+        <v>46.95</v>
       </c>
       <c r="E213" s="14" t="n">
-        <v>-0.1237</v>
+        <v>-0.1171</v>
       </c>
       <c r="F213" s="14" t="n">
-        <v>-0.2712</v>
+        <v>-0.2657</v>
       </c>
       <c r="G213" s="15" t="n"/>
       <c r="H213" s="21" t="inlineStr">
@@ -17033,13 +17033,13 @@
         </is>
       </c>
       <c r="D214" s="4" t="n">
-        <v>166.43</v>
+        <v>166.35</v>
       </c>
       <c r="E214" s="22" t="n">
-        <v>-0.0061</v>
+        <v>-0.006500000000000001</v>
       </c>
       <c r="F214" s="22" t="n">
-        <v>-0.0911</v>
+        <v>-0.0915</v>
       </c>
       <c r="G214" s="6" t="n">
         <v>46322</v>
@@ -17094,13 +17094,13 @@
         </is>
       </c>
       <c r="D215" s="13" t="n">
-        <v>46.53</v>
+        <v>46.99</v>
       </c>
       <c r="E215" s="18" t="n">
-        <v>0.14</v>
+        <v>0.1514</v>
       </c>
       <c r="F215" s="18" t="n">
-        <v>0.3901</v>
+        <v>0.4039</v>
       </c>
       <c r="G215" s="15" t="n"/>
       <c r="H215" s="21" t="inlineStr">
@@ -17145,13 +17145,13 @@
         </is>
       </c>
       <c r="D216" s="4" t="n">
-        <v>139.1</v>
+        <v>140.95</v>
       </c>
       <c r="E216" s="22" t="n">
-        <v>-0.1964</v>
-      </c>
-      <c r="F216" s="22" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-0.1856</v>
+      </c>
+      <c r="F216" s="5" t="n">
+        <v>0.0046</v>
       </c>
       <c r="G216" s="6" t="n"/>
       <c r="H216" s="7" t="inlineStr">
@@ -17170,7 +17170,7 @@
         <v>190</v>
       </c>
       <c r="M216" s="5" t="n">
-        <v>0.365923795830338</v>
+        <v>0.3479957431713375</v>
       </c>
       <c r="N216" s="3" t="inlineStr"/>
       <c r="O216" s="8" t="n"/>
@@ -17214,13 +17214,13 @@
         </is>
       </c>
       <c r="D217" s="13" t="n">
-        <v>61.26</v>
+        <v>62.08</v>
       </c>
       <c r="E217" s="18" t="n">
-        <v>0.042</v>
+        <v>0.05599999999999999</v>
       </c>
       <c r="F217" s="18" t="n">
-        <v>0.2968</v>
+        <v>0.3141</v>
       </c>
       <c r="G217" s="15" t="n"/>
       <c r="H217" s="21" t="inlineStr">
@@ -17239,7 +17239,7 @@
         <v>67</v>
       </c>
       <c r="M217" s="18" t="n">
-        <v>0.09369898792033957</v>
+        <v>0.07925257731958765</v>
       </c>
       <c r="N217" s="12" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>70</v>
       </c>
       <c r="P217" s="18" t="n">
-        <v>0.1426705843943846</v>
+        <v>0.1275773195876289</v>
       </c>
       <c r="Q217" s="19" t="inlineStr">
         <is>
@@ -17291,13 +17291,13 @@
         </is>
       </c>
       <c r="D218" s="4" t="n">
-        <v>227.06</v>
+        <v>225.35</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>0.0806</v>
+        <v>0.0725</v>
       </c>
       <c r="F218" s="5" t="n">
-        <v>0.0435</v>
+        <v>0.0357</v>
       </c>
       <c r="G218" s="6" t="n">
         <v>46330</v>
@@ -17352,13 +17352,13 @@
         </is>
       </c>
       <c r="D219" s="13" t="n">
-        <v>240.59</v>
+        <v>243.24</v>
       </c>
       <c r="E219" s="18" t="n">
-        <v>0.0195</v>
+        <v>0.0307</v>
       </c>
       <c r="F219" s="14" t="n">
-        <v>-0.171</v>
+        <v>-0.1619</v>
       </c>
       <c r="G219" s="15" t="n">
         <v>46316</v>
@@ -17394,7 +17394,7 @@
         <v>250</v>
       </c>
       <c r="P219" s="18" t="n">
-        <v>0.03911218255122822</v>
+        <v>0.02779148166419993</v>
       </c>
       <c r="Q219" s="19" t="inlineStr">
         <is>
@@ -17431,13 +17431,13 @@
         </is>
       </c>
       <c r="D220" s="4" t="n">
-        <v>13.18</v>
+        <v>13.12</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>0.0663</v>
+        <v>0.06150000000000001</v>
       </c>
       <c r="F220" s="5" t="n">
-        <v>0.3011</v>
+        <v>0.2952</v>
       </c>
       <c r="G220" s="6" t="n"/>
       <c r="H220" s="7" t="inlineStr">
@@ -17482,13 +17482,13 @@
         </is>
       </c>
       <c r="D221" s="13" t="n">
-        <v>103.32</v>
+        <v>102.94</v>
       </c>
       <c r="E221" s="18" t="n">
-        <v>0.0235</v>
-      </c>
-      <c r="F221" s="18" t="n">
-        <v>0.0019</v>
+        <v>0.0197</v>
+      </c>
+      <c r="F221" s="14" t="n">
+        <v>-0.0017</v>
       </c>
       <c r="G221" s="15" t="n">
         <v>46317</v>
@@ -17543,13 +17543,13 @@
         </is>
       </c>
       <c r="D222" s="4" t="n">
-        <v>317.99</v>
+        <v>321.57</v>
       </c>
       <c r="E222" s="22" t="n">
-        <v>-0.05</v>
+        <v>-0.0393</v>
       </c>
       <c r="F222" s="5" t="n">
-        <v>0.0974</v>
+        <v>0.1098</v>
       </c>
       <c r="G222" s="6" t="n"/>
       <c r="H222" s="7" t="inlineStr">
@@ -17594,13 +17594,13 @@
         </is>
       </c>
       <c r="D223" s="13" t="n">
-        <v>37.08</v>
+        <v>36.76</v>
       </c>
       <c r="E223" s="14" t="n">
-        <v>-0.1795</v>
+        <v>-0.1868</v>
       </c>
       <c r="F223" s="14" t="n">
-        <v>-0.0462</v>
+        <v>-0.0547</v>
       </c>
       <c r="G223" s="15" t="n">
         <v>46330</v>
@@ -17655,13 +17655,13 @@
         </is>
       </c>
       <c r="D224" s="4" t="n">
-        <v>44.04</v>
+        <v>43.83</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0037</v>
       </c>
       <c r="F224" s="5" t="n">
-        <v>0.1298</v>
+        <v>0.1244</v>
       </c>
       <c r="G224" s="6" t="n">
         <v>46331</v>
@@ -17716,13 +17716,13 @@
         </is>
       </c>
       <c r="D225" s="13" t="n">
-        <v>317.7</v>
+        <v>318.05</v>
       </c>
       <c r="E225" s="14" t="n">
-        <v>-0.1324</v>
+        <v>-0.1314</v>
       </c>
       <c r="F225" s="14" t="n">
-        <v>-0.0132</v>
+        <v>-0.0121</v>
       </c>
       <c r="G225" s="15" t="n">
         <v>46289</v>
@@ -17781,13 +17781,13 @@
         </is>
       </c>
       <c r="D226" s="4" t="n">
-        <v>336.15</v>
+        <v>338.72</v>
       </c>
       <c r="E226" s="22" t="n">
-        <v>-0.0518</v>
+        <v>-0.0445</v>
       </c>
       <c r="F226" s="5" t="n">
-        <v>0.0478</v>
+        <v>0.0558</v>
       </c>
       <c r="G226" s="6" t="n"/>
       <c r="H226" s="7" t="inlineStr">
@@ -17806,7 +17806,7 @@
         <v>390</v>
       </c>
       <c r="M226" s="5" t="n">
-        <v>0.1601963409192326</v>
+        <v>0.1513934813415209</v>
       </c>
       <c r="N226" s="3" t="inlineStr"/>
       <c r="O226" s="8" t="n"/>
@@ -17862,13 +17862,13 @@
         </is>
       </c>
       <c r="D227" s="13" t="n">
-        <v>179.25</v>
+        <v>180.64</v>
       </c>
       <c r="E227" s="14" t="n">
-        <v>-0.1393</v>
+        <v>-0.1326</v>
       </c>
       <c r="F227" s="14" t="n">
-        <v>-0.1935</v>
+        <v>-0.1872</v>
       </c>
       <c r="G227" s="15" t="n">
         <v>46330</v>
@@ -17897,7 +17897,7 @@
         <v>305</v>
       </c>
       <c r="M227" s="18" t="n">
-        <v>0.701534170153417</v>
+        <v>0.6884410983170949</v>
       </c>
       <c r="N227" s="12" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>185</v>
       </c>
       <c r="P227" s="18" t="n">
-        <v>0.03207810320781032</v>
+        <v>0.02413640389725429</v>
       </c>
       <c r="Q227" s="19" t="inlineStr">
         <is>
@@ -17949,13 +17949,13 @@
         </is>
       </c>
       <c r="D228" s="4" t="n">
-        <v>85.39</v>
+        <v>86.13</v>
       </c>
       <c r="E228" s="22" t="n">
-        <v>-0.1026</v>
+        <v>-0.09480000000000001</v>
       </c>
       <c r="F228" s="22" t="n">
-        <v>-0.1982</v>
+        <v>-0.1912</v>
       </c>
       <c r="G228" s="6" t="n"/>
       <c r="H228" s="7" t="inlineStr">
@@ -18000,13 +18000,13 @@
         </is>
       </c>
       <c r="D229" s="13" t="n">
-        <v>939.72</v>
-      </c>
-      <c r="E229" s="18" t="n">
-        <v>0.007800000000000001</v>
+        <v>927.03</v>
+      </c>
+      <c r="E229" s="14" t="n">
+        <v>-0.0058</v>
       </c>
       <c r="F229" s="18" t="n">
-        <v>0.2233</v>
+        <v>0.2068</v>
       </c>
       <c r="G229" s="15" t="n">
         <v>46329</v>
@@ -18061,13 +18061,13 @@
         </is>
       </c>
       <c r="D230" s="4" t="n">
-        <v>102.77</v>
+        <v>102.7</v>
       </c>
       <c r="E230" s="22" t="n">
-        <v>-0.0049</v>
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F230" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.004699999999999999</v>
       </c>
       <c r="G230" s="6" t="n">
         <v>46322</v>
@@ -18122,13 +18122,13 @@
         </is>
       </c>
       <c r="D231" s="13" t="n">
-        <v>297.76</v>
+        <v>298.22</v>
       </c>
       <c r="E231" s="14" t="n">
-        <v>-0.08689999999999999</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="F231" s="14" t="n">
-        <v>-0.0975</v>
+        <v>-0.09609999999999999</v>
       </c>
       <c r="G231" s="15" t="n">
         <v>46323</v>
@@ -18157,7 +18157,7 @@
         <v>450</v>
       </c>
       <c r="M231" s="18" t="n">
-        <v>0.5112842557764643</v>
+        <v>0.5089531218563476</v>
       </c>
       <c r="N231" s="12" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         <v>355</v>
       </c>
       <c r="P231" s="18" t="n">
-        <v>0.1922353573347663</v>
+        <v>0.1903963516866742</v>
       </c>
       <c r="Q231" s="19" t="inlineStr">
         <is>
@@ -18213,13 +18213,13 @@
         </is>
       </c>
       <c r="D232" s="4" t="n">
-        <v>72.87</v>
+        <v>74.2</v>
       </c>
       <c r="E232" s="22" t="n">
-        <v>-0.0827</v>
+        <v>-0.066</v>
       </c>
       <c r="F232" s="22" t="n">
-        <v>-0.1349</v>
+        <v>-0.1191</v>
       </c>
       <c r="G232" s="6" t="n">
         <v>46331</v>
@@ -18274,13 +18274,13 @@
         </is>
       </c>
       <c r="D233" s="13" t="n">
-        <v>369.1</v>
+        <v>362.21</v>
       </c>
       <c r="E233" s="14" t="n">
-        <v>-0.157</v>
+        <v>-0.1727</v>
       </c>
       <c r="F233" s="18" t="n">
-        <v>0.09210000000000002</v>
+        <v>0.0717</v>
       </c>
       <c r="G233" s="15" t="n"/>
       <c r="H233" s="21" t="inlineStr">
@@ -18325,13 +18325,13 @@
         </is>
       </c>
       <c r="D234" s="4" t="n">
-        <v>267.16</v>
+        <v>267.31</v>
       </c>
       <c r="E234" s="22" t="n">
-        <v>-0.1293</v>
+        <v>-0.1288</v>
       </c>
       <c r="F234" s="22" t="n">
-        <v>-0.2411</v>
+        <v>-0.2407</v>
       </c>
       <c r="G234" s="6" t="n">
         <v>46330</v>
@@ -18386,13 +18386,13 @@
         </is>
       </c>
       <c r="D235" s="13" t="n">
-        <v>1210.55</v>
+        <v>1234.46</v>
       </c>
       <c r="E235" s="14" t="n">
-        <v>-0.1505</v>
+        <v>-0.1337</v>
       </c>
       <c r="F235" s="14" t="n">
-        <v>-0.0626</v>
+        <v>-0.0441</v>
       </c>
       <c r="G235" s="15" t="n">
         <v>46324</v>
@@ -18447,13 +18447,13 @@
         </is>
       </c>
       <c r="D236" s="4" t="n">
-        <v>234.74</v>
+        <v>236.1</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>0.0814</v>
+        <v>0.0876</v>
       </c>
       <c r="F236" s="5" t="n">
-        <v>0.0791</v>
+        <v>0.08539999999999999</v>
       </c>
       <c r="G236" s="6" t="n"/>
       <c r="H236" s="7" t="inlineStr">
@@ -18472,7 +18472,7 @@
         <v>240</v>
       </c>
       <c r="M236" s="5" t="n">
-        <v>0.02240777029905423</v>
+        <v>0.01651842439644221</v>
       </c>
       <c r="N236" s="3" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>251</v>
       </c>
       <c r="P236" s="5" t="n">
-        <v>0.06926812643776088</v>
+        <v>0.06310885218127915</v>
       </c>
       <c r="Q236" s="9" t="inlineStr">
         <is>
@@ -18524,13 +18524,13 @@
         </is>
       </c>
       <c r="D237" s="13" t="n">
-        <v>495.03</v>
+        <v>495.63</v>
       </c>
       <c r="E237" s="18" t="n">
-        <v>0.0053</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F237" s="18" t="n">
-        <v>0.2661</v>
+        <v>0.2676</v>
       </c>
       <c r="G237" s="15" t="n">
         <v>46330</v>
@@ -18559,7 +18559,7 @@
         <v>625</v>
       </c>
       <c r="M237" s="18" t="n">
-        <v>0.2625497444599318</v>
+        <v>0.2610213263926719</v>
       </c>
       <c r="N237" s="12" t="inlineStr">
         <is>
@@ -18570,7 +18570,7 @@
         <v>525</v>
       </c>
       <c r="P237" s="18" t="n">
-        <v>0.06054178534634271</v>
+        <v>0.05925791416984445</v>
       </c>
       <c r="Q237" s="19" t="inlineStr">
         <is>
@@ -18623,13 +18623,13 @@
         </is>
       </c>
       <c r="D238" s="4" t="n">
-        <v>467.54</v>
+        <v>466.02</v>
       </c>
       <c r="E238" s="22" t="n">
-        <v>-0.004699999999999999</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F238" s="5" t="n">
-        <v>0.1184</v>
+        <v>0.1147</v>
       </c>
       <c r="G238" s="6" t="n">
         <v>46324</v>
@@ -18661,7 +18661,7 @@
         <v>525</v>
       </c>
       <c r="P238" s="5" t="n">
-        <v>0.1228985755229499</v>
+        <v>0.1265610917986353</v>
       </c>
       <c r="Q238" s="9" t="inlineStr">
         <is>
@@ -18710,13 +18710,13 @@
         </is>
       </c>
       <c r="D239" s="13" t="n">
-        <v>134.96</v>
+        <v>130.97</v>
       </c>
       <c r="E239" s="18" t="n">
-        <v>0.4232</v>
+        <v>0.3811</v>
       </c>
       <c r="F239" s="18" t="n">
-        <v>0.4654</v>
+        <v>0.422</v>
       </c>
       <c r="G239" s="15" t="n">
         <v>46324</v>
@@ -18771,13 +18771,13 @@
         </is>
       </c>
       <c r="D240" s="4" t="n">
-        <v>274.55</v>
+        <v>274.9</v>
       </c>
       <c r="E240" s="22" t="n">
-        <v>-0.1165</v>
+        <v>-0.1154</v>
       </c>
       <c r="F240" s="22" t="n">
-        <v>-0.0669</v>
+        <v>-0.06570000000000001</v>
       </c>
       <c r="G240" s="6" t="n">
         <v>46331</v>
@@ -18832,13 +18832,13 @@
         </is>
       </c>
       <c r="D241" s="13" t="n">
-        <v>977.88</v>
+        <v>975.26</v>
       </c>
       <c r="E241" s="18" t="n">
-        <v>0.0731</v>
+        <v>0.0702</v>
       </c>
       <c r="F241" s="18" t="n">
-        <v>0.0436</v>
+        <v>0.0408</v>
       </c>
       <c r="G241" s="15" t="n">
         <v>46295</v>
@@ -18867,7 +18867,7 @@
         <v>1525</v>
       </c>
       <c r="M241" s="18" t="n">
-        <v>0.559496052685401</v>
+        <v>0.5636855812808892</v>
       </c>
       <c r="N241" s="12" t="inlineStr">
         <is>
@@ -18915,13 +18915,13 @@
         </is>
       </c>
       <c r="D242" s="4" t="n">
-        <v>230.02</v>
+        <v>224.55</v>
       </c>
       <c r="E242" s="22" t="n">
-        <v>-0.1126</v>
+        <v>-0.1337</v>
       </c>
       <c r="F242" s="5" t="n">
-        <v>0.09269999999999999</v>
+        <v>0.0667</v>
       </c>
       <c r="G242" s="6" t="n"/>
       <c r="H242" s="7" t="inlineStr">
@@ -18966,13 +18966,13 @@
         </is>
       </c>
       <c r="D243" s="13" t="n">
-        <v>308.74</v>
+        <v>306.54</v>
       </c>
       <c r="E243" s="14" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-0.0158</v>
       </c>
       <c r="F243" s="18" t="n">
-        <v>0.1455</v>
+        <v>0.1373</v>
       </c>
       <c r="G243" s="15" t="n">
         <v>46324</v>
@@ -19027,13 +19027,13 @@
         </is>
       </c>
       <c r="D244" s="4" t="n">
-        <v>132.14</v>
+        <v>132.53</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>0.0576</v>
+        <v>0.0607</v>
       </c>
       <c r="F244" s="5" t="n">
-        <v>0.1877</v>
+        <v>0.1912</v>
       </c>
       <c r="G244" s="6" t="n">
         <v>46323</v>
@@ -19062,7 +19062,7 @@
         <v>160</v>
       </c>
       <c r="M244" s="5" t="n">
-        <v>0.2108369910700773</v>
+        <v>0.2072738247943862</v>
       </c>
       <c r="N244" s="3" t="inlineStr">
         <is>
@@ -19073,7 +19073,7 @@
         <v>150</v>
       </c>
       <c r="P244" s="5" t="n">
-        <v>0.1351596791281975</v>
+        <v>0.131819210744737</v>
       </c>
       <c r="Q244" s="9" t="inlineStr">
         <is>
@@ -19118,13 +19118,13 @@
         </is>
       </c>
       <c r="D245" s="13" t="n">
-        <v>66.73</v>
+        <v>65.92</v>
       </c>
       <c r="E245" s="18" t="n">
-        <v>0.0322</v>
+        <v>0.0196</v>
       </c>
       <c r="F245" s="18" t="n">
-        <v>0.2084</v>
+        <v>0.1938</v>
       </c>
       <c r="G245" s="15" t="n"/>
       <c r="H245" s="21" t="inlineStr">
@@ -19169,13 +19169,13 @@
         </is>
       </c>
       <c r="D246" s="4" t="n">
-        <v>219.92</v>
+        <v>218.29</v>
       </c>
       <c r="E246" s="22" t="n">
-        <v>-0.0186</v>
+        <v>-0.0259</v>
       </c>
       <c r="F246" s="5" t="n">
-        <v>0.0805</v>
+        <v>0.0725</v>
       </c>
       <c r="G246" s="6" t="n"/>
       <c r="H246" s="7" t="inlineStr">
@@ -19194,7 +19194,7 @@
         <v>315</v>
       </c>
       <c r="M246" s="5" t="n">
-        <v>0.4323390323754093</v>
+        <v>0.4430344953960328</v>
       </c>
       <c r="N246" s="3" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>413</v>
       </c>
       <c r="P246" s="5" t="n">
-        <v>0.8779556202255366</v>
+        <v>0.8919785606303542</v>
       </c>
       <c r="Q246" s="9" t="inlineStr">
         <is>
@@ -19254,13 +19254,13 @@
         </is>
       </c>
       <c r="D247" s="13" t="n">
-        <v>367.16</v>
+        <v>371.81</v>
       </c>
       <c r="E247" s="14" t="n">
-        <v>-0.09539999999999998</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="F247" s="14" t="n">
-        <v>-0.189</v>
+        <v>-0.1787</v>
       </c>
       <c r="G247" s="15" t="n">
         <v>46331</v>
@@ -19315,13 +19315,13 @@
         </is>
       </c>
       <c r="D248" s="4" t="n">
-        <v>232.72</v>
-      </c>
-      <c r="E248" s="22" t="n">
-        <v>-0.003</v>
+        <v>236.62</v>
+      </c>
+      <c r="E248" s="5" t="n">
+        <v>0.0138</v>
       </c>
       <c r="F248" s="22" t="n">
-        <v>-0.1641</v>
+        <v>-0.15</v>
       </c>
       <c r="G248" s="6" t="n">
         <v>46322</v>
@@ -19423,13 +19423,13 @@
         </is>
       </c>
       <c r="D250" s="4" t="n">
-        <v>168.59</v>
+        <v>166.5</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>0.1445</v>
+        <v>0.1303</v>
       </c>
       <c r="F250" s="5" t="n">
-        <v>0.2083</v>
+        <v>0.1933</v>
       </c>
       <c r="G250" s="6" t="n"/>
       <c r="H250" s="7" t="inlineStr">
@@ -19448,7 +19448,7 @@
         <v>150</v>
       </c>
       <c r="M250" s="22" t="n">
-        <v>-0.1102675129011211</v>
+        <v>-0.0990990990990991</v>
       </c>
       <c r="N250" s="3" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>130</v>
       </c>
       <c r="P250" s="22" t="n">
-        <v>-0.2288985111809716</v>
+        <v>-0.2192192192192192</v>
       </c>
       <c r="Q250" s="9" t="inlineStr">
         <is>
@@ -19500,13 +19500,13 @@
         </is>
       </c>
       <c r="D251" s="13" t="n">
-        <v>72.13</v>
+        <v>76.14</v>
       </c>
       <c r="E251" s="14" t="n">
-        <v>-0.1344</v>
+        <v>-0.0862</v>
       </c>
       <c r="F251" s="14" t="n">
-        <v>-0.2019</v>
+        <v>-0.1575</v>
       </c>
       <c r="G251" s="15" t="n">
         <v>46328</v>
@@ -19561,13 +19561,13 @@
         </is>
       </c>
       <c r="D252" s="4" t="n">
-        <v>275.59</v>
+        <v>281.19</v>
       </c>
       <c r="E252" s="22" t="n">
-        <v>-0.1831</v>
+        <v>-0.1665</v>
       </c>
       <c r="F252" s="22" t="n">
-        <v>-0.0941</v>
+        <v>-0.0757</v>
       </c>
       <c r="G252" s="6" t="n">
         <v>46331</v>
@@ -19622,13 +19622,13 @@
         </is>
       </c>
       <c r="D253" s="13" t="n">
-        <v>153.72</v>
-      </c>
-      <c r="E253" s="18" t="n">
-        <v>0.0029</v>
+        <v>150.15</v>
+      </c>
+      <c r="E253" s="14" t="n">
+        <v>-0.0204</v>
       </c>
       <c r="F253" s="18" t="n">
-        <v>0.1686</v>
+        <v>0.1415</v>
       </c>
       <c r="G253" s="15" t="n"/>
       <c r="H253" s="21" t="inlineStr">
@@ -19647,7 +19647,7 @@
         <v>280</v>
       </c>
       <c r="M253" s="18" t="n">
-        <v>0.8214936247723134</v>
+        <v>0.8648018648018647</v>
       </c>
       <c r="N253" s="12" t="inlineStr">
         <is>
@@ -19658,7 +19658,7 @@
         <v>245</v>
       </c>
       <c r="P253" s="18" t="n">
-        <v>0.5938069216757742</v>
+        <v>0.6317016317016316</v>
       </c>
       <c r="Q253" s="19" t="inlineStr">
         <is>
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="D254" s="4" t="n">
-        <v>332.4</v>
+        <v>330.65</v>
       </c>
       <c r="E254" s="22" t="n">
-        <v>-0.1411</v>
+        <v>-0.1456</v>
       </c>
       <c r="F254" s="5" t="n">
-        <v>0.0064</v>
+        <v>0.0011</v>
       </c>
       <c r="G254" s="6" t="n"/>
       <c r="H254" s="7" t="inlineStr">
@@ -19724,7 +19724,7 @@
         <v>420</v>
       </c>
       <c r="M254" s="5" t="n">
-        <v>0.2635379061371842</v>
+        <v>0.270225313775896</v>
       </c>
       <c r="N254" s="3" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>415</v>
       </c>
       <c r="P254" s="5" t="n">
-        <v>0.2484957882069796</v>
+        <v>0.2551035838499925</v>
       </c>
       <c r="Q254" s="9" t="inlineStr">
         <is>
@@ -19784,13 +19784,13 @@
         </is>
       </c>
       <c r="D255" s="13" t="n">
-        <v>13.91</v>
+        <v>13.74</v>
       </c>
       <c r="E255" s="14" t="n">
-        <v>-0.08810000000000001</v>
+        <v>-0.0993</v>
       </c>
       <c r="F255" s="18" t="n">
-        <v>0.1743</v>
+        <v>0.1599</v>
       </c>
       <c r="G255" s="15" t="n"/>
       <c r="H255" s="21" t="inlineStr">
@@ -19835,13 +19835,13 @@
         </is>
       </c>
       <c r="D256" s="4" t="n">
-        <v>36</v>
+        <v>36.24</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>0.1483</v>
+        <v>0.156</v>
       </c>
       <c r="F256" s="5" t="n">
-        <v>0.1271</v>
+        <v>0.1346</v>
       </c>
       <c r="G256" s="6" t="n">
         <v>46315</v>
@@ -19896,13 +19896,13 @@
         </is>
       </c>
       <c r="D257" s="13" t="n">
-        <v>179.51</v>
+        <v>176.82</v>
       </c>
       <c r="E257" s="14" t="n">
-        <v>-0.0004</v>
+        <v>-0.0154</v>
       </c>
       <c r="F257" s="18" t="n">
-        <v>0.2294</v>
+        <v>0.2109</v>
       </c>
       <c r="G257" s="15" t="n">
         <v>46330</v>
@@ -19957,13 +19957,13 @@
         </is>
       </c>
       <c r="D258" s="4" t="n">
-        <v>166.7</v>
+        <v>167.23</v>
       </c>
       <c r="E258" s="22" t="n">
-        <v>-0.0254</v>
+        <v>-0.0223</v>
       </c>
       <c r="F258" s="5" t="n">
-        <v>0.2819</v>
+        <v>0.286</v>
       </c>
       <c r="G258" s="6" t="n">
         <v>46328</v>
@@ -20018,13 +20018,13 @@
         </is>
       </c>
       <c r="D259" s="13" t="n">
-        <v>126.58</v>
+        <v>126.45</v>
       </c>
       <c r="E259" s="14" t="n">
-        <v>-0.1091</v>
+        <v>-0.11</v>
       </c>
       <c r="F259" s="14" t="n">
-        <v>-0.1021</v>
+        <v>-0.1031</v>
       </c>
       <c r="G259" s="15" t="n"/>
       <c r="H259" s="21" t="inlineStr">
@@ -20079,13 +20079,13 @@
         </is>
       </c>
       <c r="D260" s="4" t="n">
-        <v>16.83</v>
+        <v>16.8</v>
       </c>
       <c r="E260" s="22" t="n">
-        <v>-0.1885</v>
+        <v>-0.19</v>
       </c>
       <c r="F260" s="22" t="n">
-        <v>-0.09810000000000001</v>
+        <v>-0.09970000000000001</v>
       </c>
       <c r="G260" s="6" t="n">
         <v>46331</v>
@@ -20140,13 +20140,13 @@
         </is>
       </c>
       <c r="D261" s="13" t="n">
-        <v>182.09</v>
+        <v>181.97</v>
       </c>
       <c r="E261" s="18" t="n">
-        <v>0.1166</v>
+        <v>0.1159</v>
       </c>
       <c r="F261" s="14" t="n">
-        <v>-0.0103</v>
+        <v>-0.0109</v>
       </c>
       <c r="G261" s="15" t="n">
         <v>46330</v>
@@ -20175,7 +20175,7 @@
         <v>265</v>
       </c>
       <c r="M261" s="18" t="n">
-        <v>0.4553242901861717</v>
+        <v>0.4562840028576139</v>
       </c>
       <c r="N261" s="12" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>179</v>
       </c>
       <c r="P261" s="14" t="n">
-        <v>-0.01696963040254821</v>
+        <v>-0.01632137165466835</v>
       </c>
       <c r="Q261" s="19" t="inlineStr">
         <is>
@@ -20231,13 +20231,13 @@
         </is>
       </c>
       <c r="D262" s="4" t="n">
-        <v>119.74</v>
+        <v>116.65</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>0.2188</v>
+        <v>0.1874</v>
       </c>
       <c r="F262" s="5" t="n">
-        <v>0.4195</v>
+        <v>0.3829</v>
       </c>
       <c r="G262" s="6" t="n">
         <v>46322</v>
@@ -20292,13 +20292,13 @@
         </is>
       </c>
       <c r="D263" s="13" t="n">
-        <v>7.95</v>
+        <v>7.99</v>
       </c>
       <c r="E263" s="14" t="n">
-        <v>-0.1093</v>
+        <v>-0.1043</v>
       </c>
       <c r="F263" s="14" t="n">
-        <v>-0.0069</v>
+        <v>-0.0013</v>
       </c>
       <c r="G263" s="15" t="n"/>
       <c r="H263" s="21" t="inlineStr">
@@ -20343,13 +20343,13 @@
         </is>
       </c>
       <c r="D264" s="4" t="n">
-        <v>86.98</v>
+        <v>86.67</v>
       </c>
       <c r="E264" s="22" t="n">
-        <v>-0.1008</v>
+        <v>-0.1041</v>
       </c>
       <c r="F264" s="5" t="n">
-        <v>0.0375</v>
+        <v>0.0337</v>
       </c>
       <c r="G264" s="6" t="n"/>
       <c r="H264" s="7" t="inlineStr">
@@ -20394,13 +20394,13 @@
         </is>
       </c>
       <c r="D265" s="13" t="n">
-        <v>15.4</v>
+        <v>15.27</v>
       </c>
       <c r="E265" s="14" t="n">
-        <v>-0.1637</v>
-      </c>
-      <c r="F265" s="18" t="n">
-        <v>0.0029</v>
+        <v>-0.171</v>
+      </c>
+      <c r="F265" s="14" t="n">
+        <v>-0.0059</v>
       </c>
       <c r="G265" s="15" t="n"/>
       <c r="H265" s="21" t="inlineStr">
@@ -20445,13 +20445,13 @@
         </is>
       </c>
       <c r="D266" s="4" t="n">
-        <v>385.35</v>
+        <v>388.52</v>
       </c>
       <c r="E266" s="22" t="n">
-        <v>-0.025</v>
+        <v>-0.017</v>
       </c>
       <c r="F266" s="5" t="n">
-        <v>0.0687</v>
+        <v>0.0775</v>
       </c>
       <c r="G266" s="6" t="n">
         <v>46317</v>
@@ -20520,13 +20520,13 @@
         </is>
       </c>
       <c r="D267" s="13" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="E267" s="14" t="n">
-        <v>-0.2934</v>
+        <v>-0.306</v>
       </c>
       <c r="F267" s="14" t="n">
-        <v>-0.2747</v>
+        <v>-0.2876</v>
       </c>
       <c r="G267" s="15" t="n">
         <v>46331</v>
@@ -20581,13 +20581,13 @@
         </is>
       </c>
       <c r="D268" s="4" t="n">
-        <v>19.95</v>
+        <v>19.75</v>
       </c>
       <c r="E268" s="22" t="n">
-        <v>-0.1054</v>
+        <v>-0.1143</v>
       </c>
       <c r="F268" s="5" t="n">
-        <v>0.0755</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="G268" s="6" t="n"/>
       <c r="H268" s="7" t="inlineStr">
@@ -20632,13 +20632,13 @@
         </is>
       </c>
       <c r="D269" s="13" t="n">
-        <v>16.83</v>
+        <v>17.24</v>
       </c>
       <c r="E269" s="14" t="n">
-        <v>-0.1012</v>
+        <v>-0.0796</v>
       </c>
       <c r="F269" s="18" t="n">
-        <v>0.2016</v>
+        <v>0.2305</v>
       </c>
       <c r="G269" s="15" t="n"/>
       <c r="H269" s="21" t="inlineStr">
@@ -20683,13 +20683,13 @@
         </is>
       </c>
       <c r="D270" s="4" t="n">
-        <v>215.02</v>
+        <v>216</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>0.0293</v>
+        <v>0.034</v>
       </c>
       <c r="F270" s="5" t="n">
-        <v>0.0655</v>
+        <v>0.0704</v>
       </c>
       <c r="G270" s="6" t="n">
         <v>46328</v>
@@ -20744,13 +20744,13 @@
         </is>
       </c>
       <c r="D271" s="13" t="n">
-        <v>206.62</v>
+        <v>206.38</v>
       </c>
       <c r="E271" s="18" t="n">
-        <v>0.0121</v>
+        <v>0.0109</v>
       </c>
       <c r="F271" s="18" t="n">
-        <v>0.2916</v>
+        <v>0.2901</v>
       </c>
       <c r="G271" s="15" t="n">
         <v>46316</v>
@@ -20825,13 +20825,13 @@
         </is>
       </c>
       <c r="D272" s="4" t="n">
-        <v>40.03</v>
+        <v>40.1</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>0.0643</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="F272" s="5" t="n">
-        <v>0.4472</v>
+        <v>0.4497</v>
       </c>
       <c r="G272" s="6" t="n">
         <v>46329</v>
@@ -20886,13 +20886,13 @@
         </is>
       </c>
       <c r="D273" s="13" t="n">
-        <v>328.04</v>
+        <v>329.1</v>
       </c>
       <c r="E273" s="14" t="n">
-        <v>-0.0127</v>
+        <v>-0.0095</v>
       </c>
       <c r="F273" s="18" t="n">
-        <v>0.2211</v>
+        <v>0.225</v>
       </c>
       <c r="G273" s="15" t="n"/>
       <c r="H273" s="21" t="inlineStr">
@@ -20911,7 +20911,7 @@
         <v>320</v>
       </c>
       <c r="M273" s="14" t="n">
-        <v>-0.0245092061943666</v>
+        <v>-0.02765116985718633</v>
       </c>
       <c r="N273" s="12" t="inlineStr">
         <is>
@@ -20922,7 +20922,7 @@
         <v>280</v>
       </c>
       <c r="P273" s="14" t="n">
-        <v>-0.1464455554200708</v>
+        <v>-0.1491947736250381</v>
       </c>
       <c r="Q273" s="19" t="inlineStr">
         <is>
@@ -20963,13 +20963,13 @@
         </is>
       </c>
       <c r="D274" s="4" t="n">
-        <v>398.1</v>
+        <v>397.38</v>
       </c>
       <c r="E274" s="22" t="n">
-        <v>-0.0345</v>
+        <v>-0.0362</v>
       </c>
       <c r="F274" s="22" t="n">
-        <v>-0.0823</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="G274" s="6" t="n"/>
       <c r="H274" s="7" t="inlineStr">
@@ -20988,7 +20988,7 @@
         <v>535</v>
       </c>
       <c r="M274" s="5" t="n">
-        <v>0.3438834463702586</v>
+        <v>0.3463183854245307</v>
       </c>
       <c r="N274" s="3" t="inlineStr"/>
       <c r="O274" s="8" t="n"/>
@@ -21032,13 +21032,13 @@
         </is>
       </c>
       <c r="D275" s="13" t="n">
-        <v>6.3</v>
+        <v>6.26</v>
       </c>
       <c r="E275" s="14" t="n">
-        <v>-0.148</v>
+        <v>-0.1541</v>
       </c>
       <c r="F275" s="14" t="n">
-        <v>-0.0285</v>
+        <v>-0.0354</v>
       </c>
       <c r="G275" s="15" t="n">
         <v>46331</v>
@@ -21093,13 +21093,13 @@
         </is>
       </c>
       <c r="D276" s="4" t="n">
-        <v>91.47</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="E276" s="5" t="n">
-        <v>0.3127</v>
+        <v>0.2679</v>
       </c>
       <c r="F276" s="5" t="n">
-        <v>0.5706</v>
+        <v>0.517</v>
       </c>
       <c r="G276" s="6" t="n">
         <v>46322</v>
@@ -21154,13 +21154,13 @@
         </is>
       </c>
       <c r="D277" s="13" t="n">
-        <v>95.95</v>
+        <v>101.03</v>
       </c>
       <c r="E277" s="14" t="n">
-        <v>-0.128</v>
+        <v>-0.0819</v>
       </c>
       <c r="F277" s="14" t="n">
-        <v>-0.1947</v>
+        <v>-0.1521</v>
       </c>
       <c r="G277" s="15" t="n">
         <v>46331</v>
@@ -21215,13 +21215,13 @@
         </is>
       </c>
       <c r="D278" s="4" t="n">
-        <v>211.42</v>
+        <v>211.97</v>
       </c>
       <c r="E278" s="22" t="n">
-        <v>-0.013</v>
+        <v>-0.0104</v>
       </c>
       <c r="F278" s="5" t="n">
-        <v>0.0668</v>
+        <v>0.0696</v>
       </c>
       <c r="G278" s="6" t="n">
         <v>46330</v>
@@ -21276,13 +21276,13 @@
         </is>
       </c>
       <c r="D279" s="13" t="n">
-        <v>381.21</v>
+        <v>379.72</v>
       </c>
       <c r="E279" s="14" t="n">
-        <v>-0.0534</v>
+        <v>-0.0572</v>
       </c>
       <c r="F279" s="18" t="n">
-        <v>0.1176</v>
+        <v>0.1132</v>
       </c>
       <c r="G279" s="15" t="n">
         <v>46322</v>
@@ -21337,13 +21337,13 @@
         </is>
       </c>
       <c r="D280" s="4" t="n">
-        <v>57.86</v>
+        <v>57.66</v>
       </c>
       <c r="E280" s="5" t="n">
-        <v>0.0268</v>
+        <v>0.0232</v>
       </c>
       <c r="F280" s="5" t="n">
-        <v>0.1065</v>
+        <v>0.1027</v>
       </c>
       <c r="G280" s="6" t="n">
         <v>46330</v>
@@ -21398,13 +21398,13 @@
         </is>
       </c>
       <c r="D281" s="13" t="n">
-        <v>431.23</v>
+        <v>433.19</v>
       </c>
       <c r="E281" s="18" t="n">
-        <v>0.0048</v>
+        <v>0.009399999999999999</v>
       </c>
       <c r="F281" s="18" t="n">
-        <v>0.0229</v>
+        <v>0.0275</v>
       </c>
       <c r="G281" s="15" t="n">
         <v>46310</v>
@@ -21481,13 +21481,13 @@
         </is>
       </c>
       <c r="D282" s="4" t="n">
-        <v>126.88</v>
+        <v>126.44</v>
       </c>
       <c r="E282" s="22" t="n">
-        <v>-0.08130000000000001</v>
+        <v>-0.08439999999999999</v>
       </c>
       <c r="F282" s="22" t="n">
-        <v>-0.0694</v>
+        <v>-0.0726</v>
       </c>
       <c r="G282" s="6" t="n">
         <v>46330</v>
@@ -21542,13 +21542,13 @@
         </is>
       </c>
       <c r="D283" s="13" t="n">
-        <v>230.15</v>
+        <v>227.29</v>
       </c>
       <c r="E283" s="14" t="n">
-        <v>-0.0668</v>
+        <v>-0.0784</v>
       </c>
       <c r="F283" s="18" t="n">
-        <v>0.0546</v>
+        <v>0.0415</v>
       </c>
       <c r="G283" s="15" t="n">
         <v>46324</v>
@@ -21603,13 +21603,13 @@
         </is>
       </c>
       <c r="D284" s="4" t="n">
-        <v>268.58</v>
+        <v>268.7</v>
       </c>
       <c r="E284" s="22" t="n">
-        <v>-0.0289</v>
+        <v>-0.0285</v>
       </c>
       <c r="F284" s="22" t="n">
-        <v>-0.1004</v>
+        <v>-0.1</v>
       </c>
       <c r="G284" s="6" t="n">
         <v>46315</v>
@@ -21638,7 +21638,7 @@
         <v>300</v>
       </c>
       <c r="M284" s="5" t="n">
-        <v>0.1169856281182516</v>
+        <v>0.1164867882396725</v>
       </c>
       <c r="N284" s="3" t="inlineStr">
         <is>
@@ -21649,7 +21649,7 @@
         <v>316</v>
       </c>
       <c r="P284" s="5" t="n">
-        <v>0.176558194951225</v>
+        <v>0.1760327502791217</v>
       </c>
       <c r="Q284" s="9" t="inlineStr">
         <is>
@@ -21706,13 +21706,13 @@
         </is>
       </c>
       <c r="D285" s="13" t="n">
-        <v>337.4</v>
+        <v>336.79</v>
       </c>
       <c r="E285" s="18" t="n">
-        <v>0.0622</v>
+        <v>0.0603</v>
       </c>
       <c r="F285" s="18" t="n">
-        <v>0.0738</v>
+        <v>0.0718</v>
       </c>
       <c r="G285" s="15" t="n">
         <v>46330</v>
@@ -21741,7 +21741,7 @@
         <v>335</v>
       </c>
       <c r="M285" s="14" t="n">
-        <v>-0.007113218731475926</v>
+        <v>-0.005314884646218773</v>
       </c>
       <c r="N285" s="12" t="inlineStr">
         <is>
@@ -21752,7 +21752,7 @@
         <v>375</v>
       </c>
       <c r="P285" s="18" t="n">
-        <v>0.111440426793124</v>
+        <v>0.1134534873363223</v>
       </c>
       <c r="Q285" s="19" t="inlineStr">
         <is>
@@ -21793,13 +21793,13 @@
         </is>
       </c>
       <c r="D286" s="4" t="n">
-        <v>43.35</v>
+        <v>43.97</v>
       </c>
       <c r="E286" s="22" t="n">
-        <v>-0.0265</v>
+        <v>-0.0126</v>
       </c>
       <c r="F286" s="5" t="n">
-        <v>0.413</v>
+        <v>0.4332</v>
       </c>
       <c r="G286" s="6" t="n">
         <v>46330</v>
@@ -21854,13 +21854,13 @@
         </is>
       </c>
       <c r="D287" s="13" t="n">
-        <v>6.34</v>
+        <v>6.33</v>
       </c>
       <c r="E287" s="14" t="n">
-        <v>-0.146</v>
+        <v>-0.148</v>
       </c>
       <c r="F287" s="14" t="n">
-        <v>-0.1781</v>
+        <v>-0.1801</v>
       </c>
       <c r="G287" s="15" t="n"/>
       <c r="H287" s="21" t="inlineStr">
@@ -21905,13 +21905,13 @@
         </is>
       </c>
       <c r="D288" s="4" t="n">
-        <v>185.63</v>
+        <v>185.7</v>
       </c>
       <c r="E288" s="5" t="n">
-        <v>0.059</v>
+        <v>0.0594</v>
       </c>
       <c r="F288" s="5" t="n">
-        <v>0.2814</v>
+        <v>0.2818</v>
       </c>
       <c r="G288" s="6" t="n"/>
       <c r="H288" s="7" t="inlineStr">
@@ -21956,13 +21956,13 @@
         </is>
       </c>
       <c r="D289" s="13" t="n">
-        <v>453.05</v>
+        <v>447.18</v>
       </c>
       <c r="E289" s="14" t="n">
-        <v>-0.0023</v>
+        <v>-0.0152</v>
       </c>
       <c r="F289" s="14" t="n">
-        <v>-0.1845</v>
+        <v>-0.1951</v>
       </c>
       <c r="G289" s="15" t="n">
         <v>46324</v>
@@ -21991,7 +21991,7 @@
         <v>730</v>
       </c>
       <c r="M289" s="18" t="n">
-        <v>0.611301180885112</v>
+        <v>0.6324522563620913</v>
       </c>
       <c r="N289" s="12" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>575</v>
       </c>
       <c r="P289" s="18" t="n">
-        <v>0.2691755876834786</v>
+        <v>0.2858356813810993</v>
       </c>
       <c r="Q289" s="19" t="inlineStr">
         <is>
@@ -22043,13 +22043,13 @@
         </is>
       </c>
       <c r="D290" s="4" t="n">
-        <v>26.47</v>
+        <v>25.91</v>
       </c>
       <c r="E290" s="22" t="n">
-        <v>-0.1652</v>
+        <v>-0.1829</v>
       </c>
       <c r="F290" s="22" t="n">
-        <v>-0.2134</v>
+        <v>-0.23</v>
       </c>
       <c r="G290" s="6" t="n">
         <v>46330</v>
@@ -22104,13 +22104,13 @@
         </is>
       </c>
       <c r="D291" s="13" t="n">
-        <v>95.02</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="E291" s="14" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F291" s="18" t="n">
-        <v>0.0342</v>
+        <v>0.04019999999999999</v>
       </c>
       <c r="G291" s="15" t="n"/>
       <c r="H291" s="21" t="inlineStr">
@@ -22155,13 +22155,13 @@
         </is>
       </c>
       <c r="D292" s="4" t="n">
-        <v>164.26</v>
+        <v>164.54</v>
       </c>
       <c r="E292" s="22" t="n">
-        <v>-0.0737</v>
+        <v>-0.0721</v>
       </c>
       <c r="F292" s="5" t="n">
-        <v>0.1582</v>
+        <v>0.1602</v>
       </c>
       <c r="G292" s="6" t="n"/>
       <c r="H292" s="7" t="inlineStr">
@@ -22206,13 +22206,13 @@
         </is>
       </c>
       <c r="D293" s="13" t="n">
-        <v>293.3</v>
+        <v>291.54</v>
       </c>
       <c r="E293" s="14" t="n">
-        <v>-0.0354</v>
+        <v>-0.0412</v>
       </c>
       <c r="F293" s="14" t="n">
-        <v>-0.0287</v>
+        <v>-0.0345</v>
       </c>
       <c r="G293" s="15" t="n">
         <v>46331</v>
@@ -22267,13 +22267,13 @@
         </is>
       </c>
       <c r="D294" s="4" t="n">
-        <v>87.20999999999999</v>
+        <v>87.17</v>
       </c>
       <c r="E294" s="22" t="n">
-        <v>-0.0323</v>
+        <v>-0.0327</v>
       </c>
       <c r="F294" s="5" t="n">
-        <v>0.0718</v>
+        <v>0.0713</v>
       </c>
       <c r="G294" s="6" t="n"/>
       <c r="H294" s="7" t="inlineStr">
@@ -22318,13 +22318,13 @@
         </is>
       </c>
       <c r="D295" s="13" t="n">
-        <v>127.02</v>
+        <v>127.01</v>
       </c>
       <c r="E295" s="14" t="n">
         <v>-0.1202</v>
       </c>
       <c r="F295" s="14" t="n">
-        <v>-0.0425</v>
+        <v>-0.0426</v>
       </c>
       <c r="G295" s="15" t="n">
         <v>46331</v>
@@ -22353,7 +22353,7 @@
         <v>166</v>
       </c>
       <c r="M295" s="18" t="n">
-        <v>0.3068808061722564</v>
+        <v>0.306983702070703</v>
       </c>
       <c r="N295" s="12" t="inlineStr"/>
       <c r="O295" s="17" t="n"/>
@@ -22401,13 +22401,13 @@
         </is>
       </c>
       <c r="D296" s="4" t="n">
-        <v>29.25</v>
+        <v>29.02</v>
       </c>
       <c r="E296" s="22" t="n">
-        <v>-0.043</v>
+        <v>-0.0507</v>
       </c>
       <c r="F296" s="22" t="n">
-        <v>-0.0367</v>
+        <v>-0.0445</v>
       </c>
       <c r="G296" s="6" t="n">
         <v>46317</v>
@@ -22462,13 +22462,13 @@
         </is>
       </c>
       <c r="D297" s="13" t="n">
-        <v>274.93</v>
+        <v>276.29</v>
       </c>
       <c r="E297" s="14" t="n">
-        <v>-0.0126</v>
+        <v>-0.0077</v>
       </c>
       <c r="F297" s="18" t="n">
-        <v>0.0113</v>
+        <v>0.0163</v>
       </c>
       <c r="G297" s="15" t="n">
         <v>46322</v>
@@ -22496,8 +22496,8 @@
       <c r="L297" s="17" t="n">
         <v>275</v>
       </c>
-      <c r="M297" s="18" t="n">
-        <v>0.0002546102644309212</v>
+      <c r="M297" s="14" t="n">
+        <v>-0.004669007202577076</v>
       </c>
       <c r="N297" s="12" t="inlineStr">
         <is>
@@ -22508,7 +22508,7 @@
         <v>312</v>
       </c>
       <c r="P297" s="18" t="n">
-        <v>0.1348343214636453</v>
+        <v>0.1292482536465307</v>
       </c>
       <c r="Q297" s="19" t="inlineStr">
         <is>
@@ -22561,13 +22561,13 @@
         </is>
       </c>
       <c r="D298" s="4" t="n">
-        <v>34.37</v>
+        <v>34.33</v>
       </c>
       <c r="E298" s="22" t="n">
-        <v>-0.1063</v>
+        <v>-0.1074</v>
       </c>
       <c r="F298" s="22" t="n">
-        <v>-0.1321</v>
+        <v>-0.1331</v>
       </c>
       <c r="G298" s="6" t="n">
         <v>46322</v>
@@ -22626,13 +22626,13 @@
         </is>
       </c>
       <c r="D299" s="13" t="n">
-        <v>71.76000000000001</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="E299" s="18" t="n">
-        <v>0.0367</v>
+        <v>0.0267</v>
       </c>
       <c r="F299" s="18" t="n">
-        <v>0.1966</v>
+        <v>0.1851</v>
       </c>
       <c r="G299" s="15" t="n">
         <v>46310</v>
@@ -22687,13 +22687,13 @@
         </is>
       </c>
       <c r="D300" s="4" t="n">
-        <v>464.4</v>
+        <v>466.22</v>
       </c>
       <c r="E300" s="22" t="n">
-        <v>-0.0314</v>
+        <v>-0.0276</v>
       </c>
       <c r="F300" s="22" t="n">
-        <v>-0.1138</v>
+        <v>-0.1104</v>
       </c>
       <c r="G300" s="6" t="n">
         <v>46325</v>
@@ -22722,7 +22722,7 @@
         <v>570</v>
       </c>
       <c r="M300" s="5" t="n">
-        <v>0.227390180878553</v>
+        <v>0.2225987731114066</v>
       </c>
       <c r="N300" s="3" t="inlineStr">
         <is>
@@ -22733,7 +22733,7 @@
         <v>525</v>
       </c>
       <c r="P300" s="5" t="n">
-        <v>0.1304909560723515</v>
+        <v>0.1260778173394534</v>
       </c>
       <c r="Q300" s="9" t="inlineStr">
         <is>
@@ -22786,13 +22786,13 @@
         </is>
       </c>
       <c r="D301" s="13" t="n">
-        <v>507.59</v>
+        <v>510.19</v>
       </c>
       <c r="E301" s="14" t="n">
-        <v>-0.0668</v>
+        <v>-0.062</v>
       </c>
       <c r="F301" s="14" t="n">
-        <v>-0.1085</v>
+        <v>-0.1039</v>
       </c>
       <c r="G301" s="15" t="n">
         <v>46329</v>
@@ -22821,7 +22821,7 @@
         <v>616</v>
       </c>
       <c r="M301" s="18" t="n">
-        <v>0.2135778876652417</v>
+        <v>0.207393324055744</v>
       </c>
       <c r="N301" s="12" t="inlineStr"/>
       <c r="O301" s="17" t="n"/>
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="D302" s="4" t="n">
-        <v>254.07</v>
+        <v>259.59</v>
       </c>
       <c r="E302" s="22" t="n">
-        <v>-0.0653</v>
+        <v>-0.045</v>
       </c>
       <c r="F302" s="5" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.1141</v>
       </c>
       <c r="G302" s="6" t="n">
         <v>46321</v>
@@ -22900,7 +22900,7 @@
         <v>283</v>
       </c>
       <c r="M302" s="5" t="n">
-        <v>0.1138662573306569</v>
+        <v>0.09018066951731588</v>
       </c>
       <c r="N302" s="3" t="inlineStr"/>
       <c r="O302" s="8" t="n"/>
@@ -22946,13 +22946,13 @@
         </is>
       </c>
       <c r="D303" s="13" t="n">
-        <v>235.46</v>
+        <v>234.42</v>
       </c>
       <c r="E303" s="14" t="n">
-        <v>-0.08130000000000001</v>
+        <v>-0.08539999999999999</v>
       </c>
       <c r="F303" s="18" t="n">
-        <v>0.0425</v>
+        <v>0.0379</v>
       </c>
       <c r="G303" s="15" t="n">
         <v>46323</v>
@@ -22981,7 +22981,7 @@
         <v>246</v>
       </c>
       <c r="M303" s="18" t="n">
-        <v>0.04476344177354961</v>
+        <v>0.04939851548502693</v>
       </c>
       <c r="N303" s="12" t="inlineStr"/>
       <c r="O303" s="17" t="n"/>
@@ -23029,13 +23029,13 @@
         </is>
       </c>
       <c r="D304" s="4" t="n">
-        <v>105.67</v>
+        <v>105.53</v>
       </c>
       <c r="E304" s="22" t="n">
-        <v>-0.0779</v>
+        <v>-0.07919999999999999</v>
       </c>
       <c r="F304" s="22" t="n">
-        <v>-0.0718</v>
+        <v>-0.073</v>
       </c>
       <c r="G304" s="6" t="n">
         <v>46322</v>
@@ -23064,7 +23064,7 @@
         <v>130</v>
       </c>
       <c r="M304" s="5" t="n">
-        <v>0.2302451026781489</v>
+        <v>0.2318771913200038</v>
       </c>
       <c r="N304" s="3" t="inlineStr">
         <is>
@@ -23075,7 +23075,7 @@
         <v>128</v>
       </c>
       <c r="P304" s="5" t="n">
-        <v>0.211318254944639</v>
+        <v>0.2129252345304652</v>
       </c>
       <c r="Q304" s="9" t="inlineStr">
         <is>
@@ -23124,13 +23124,13 @@
         </is>
       </c>
       <c r="D305" s="13" t="n">
-        <v>100.25</v>
+        <v>100.2</v>
       </c>
       <c r="E305" s="14" t="n">
-        <v>-0.1288</v>
+        <v>-0.1292</v>
       </c>
       <c r="F305" s="14" t="n">
-        <v>-0.022</v>
+        <v>-0.0225</v>
       </c>
       <c r="G305" s="15" t="n">
         <v>46301</v>
@@ -23159,7 +23159,7 @@
         <v>135</v>
       </c>
       <c r="M305" s="18" t="n">
-        <v>0.3466334164588529</v>
+        <v>0.3473053892215568</v>
       </c>
       <c r="N305" s="12" t="inlineStr">
         <is>
@@ -23170,7 +23170,7 @@
         <v>125</v>
       </c>
       <c r="P305" s="18" t="n">
-        <v>0.2468827930174564</v>
+        <v>0.24750499001996</v>
       </c>
       <c r="Q305" s="19" t="inlineStr"/>
       <c r="R305" s="17" t="n"/>
@@ -23205,13 +23205,13 @@
         </is>
       </c>
       <c r="D306" s="4" t="n">
-        <v>322.95</v>
+        <v>323.29</v>
       </c>
       <c r="E306" s="22" t="n">
-        <v>-0.1034</v>
+        <v>-0.1025</v>
       </c>
       <c r="F306" s="22" t="n">
-        <v>-0.0183</v>
+        <v>-0.0173</v>
       </c>
       <c r="G306" s="6" t="n">
         <v>46322</v>
@@ -23240,7 +23240,7 @@
         <v>350</v>
       </c>
       <c r="M306" s="5" t="n">
-        <v>0.08375909583526865</v>
+        <v>0.0826193201150669</v>
       </c>
       <c r="N306" s="3" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>400</v>
       </c>
       <c r="P306" s="5" t="n">
-        <v>0.2385818238117356</v>
+        <v>0.2372792229886479</v>
       </c>
       <c r="Q306" s="9" t="inlineStr">
         <is>
@@ -23292,13 +23292,13 @@
         </is>
       </c>
       <c r="D307" s="13" t="n">
-        <v>97.59</v>
+        <v>98.17</v>
       </c>
       <c r="E307" s="14" t="n">
-        <v>-0.124</v>
+        <v>-0.1188</v>
       </c>
       <c r="F307" s="18" t="n">
-        <v>0.295</v>
+        <v>0.3027</v>
       </c>
       <c r="G307" s="15" t="n"/>
       <c r="H307" s="21" t="inlineStr">
@@ -23339,13 +23339,13 @@
         </is>
       </c>
       <c r="D308" s="4" t="n">
-        <v>49.07</v>
+        <v>49.03</v>
       </c>
       <c r="E308" s="22" t="n">
-        <v>-0.316</v>
+        <v>-0.3166</v>
       </c>
       <c r="F308" s="22" t="n">
-        <v>-0.2344</v>
+        <v>-0.235</v>
       </c>
       <c r="G308" s="6" t="n">
         <v>46267</v>
@@ -23400,13 +23400,13 @@
         </is>
       </c>
       <c r="D309" s="13" t="n">
-        <v>71.08</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="E309" s="14" t="n">
-        <v>-0.044</v>
+        <v>-0.0423</v>
       </c>
       <c r="F309" s="14" t="n">
-        <v>-0.0958</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="G309" s="15" t="n">
         <v>46315</v>
@@ -23435,14 +23435,14 @@
         <v>83</v>
       </c>
       <c r="M309" s="18" t="n">
-        <v>0.1676983680360158</v>
+        <v>0.1655666338997333</v>
       </c>
       <c r="N309" s="12" t="inlineStr"/>
       <c r="O309" s="17" t="n">
         <v>87</v>
       </c>
       <c r="P309" s="18" t="n">
-        <v>0.2239729881823298</v>
+        <v>0.2217385198708048</v>
       </c>
       <c r="Q309" s="19" t="inlineStr"/>
       <c r="R309" s="17" t="n"/>
@@ -23477,13 +23477,13 @@
         </is>
       </c>
       <c r="D310" s="4" t="n">
-        <v>177.76</v>
+        <v>177.87</v>
       </c>
       <c r="E310" s="5" t="n">
-        <v>0.043</v>
+        <v>0.0437</v>
       </c>
       <c r="F310" s="5" t="n">
-        <v>0.0487</v>
+        <v>0.04940000000000001</v>
       </c>
       <c r="G310" s="6" t="n">
         <v>46322</v>
@@ -23512,7 +23512,7 @@
         <v>200</v>
       </c>
       <c r="M310" s="5" t="n">
-        <v>0.1251125112511252</v>
+        <v>0.1244167088322932</v>
       </c>
       <c r="N310" s="3" t="inlineStr"/>
       <c r="O310" s="8" t="n"/>
@@ -23560,13 +23560,13 @@
         </is>
       </c>
       <c r="D311" s="13" t="n">
-        <v>140.56</v>
+        <v>140.51</v>
       </c>
       <c r="E311" s="14" t="n">
-        <v>-0.0464</v>
+        <v>-0.0467</v>
       </c>
       <c r="F311" s="18" t="n">
-        <v>0.0183</v>
+        <v>0.018</v>
       </c>
       <c r="G311" s="15" t="n">
         <v>46317</v>
@@ -23625,13 +23625,13 @@
         </is>
       </c>
       <c r="D312" s="4" t="n">
-        <v>187.63</v>
+        <v>188.66</v>
       </c>
       <c r="E312" s="22" t="n">
-        <v>-0.0479</v>
+        <v>-0.0426</v>
       </c>
       <c r="F312" s="5" t="n">
-        <v>0.0546</v>
+        <v>0.0604</v>
       </c>
       <c r="G312" s="6" t="n">
         <v>46317</v>
@@ -23660,7 +23660,7 @@
         <v>220</v>
       </c>
       <c r="M312" s="5" t="n">
-        <v>0.1725203858657997</v>
+        <v>0.1661189441323015</v>
       </c>
       <c r="N312" s="3" t="inlineStr">
         <is>
@@ -23671,7 +23671,7 @@
         <v>230</v>
       </c>
       <c r="P312" s="5" t="n">
-        <v>0.2258167670415179</v>
+        <v>0.2191243506837698</v>
       </c>
       <c r="Q312" s="9" t="inlineStr">
         <is>
@@ -23712,13 +23712,13 @@
         </is>
       </c>
       <c r="D313" s="13" t="n">
-        <v>1037.34</v>
+        <v>1037.72</v>
       </c>
       <c r="E313" s="14" t="n">
-        <v>-0.0298</v>
+        <v>-0.0294</v>
       </c>
       <c r="F313" s="14" t="n">
-        <v>-0.0021</v>
+        <v>-0.0017</v>
       </c>
       <c r="G313" s="15" t="n">
         <v>46330</v>
@@ -23747,7 +23747,7 @@
         <v>1200</v>
       </c>
       <c r="M313" s="18" t="n">
-        <v>0.1568049048527967</v>
+        <v>0.1563812974598157</v>
       </c>
       <c r="N313" s="12" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         <v>1240</v>
       </c>
       <c r="P313" s="18" t="n">
-        <v>0.1953650683478899</v>
+        <v>0.1949273407084763</v>
       </c>
       <c r="Q313" s="19" t="inlineStr">
         <is>
@@ -23803,13 +23803,13 @@
         </is>
       </c>
       <c r="D314" s="4" t="n">
-        <v>114.31</v>
+        <v>114.29</v>
       </c>
       <c r="E314" s="22" t="n">
-        <v>-0.0247</v>
+        <v>-0.0249</v>
       </c>
       <c r="F314" s="22" t="n">
-        <v>-0.06179999999999999</v>
+        <v>-0.0619</v>
       </c>
       <c r="G314" s="6" t="n">
         <v>46325</v>
@@ -23838,7 +23838,7 @@
         <v>129</v>
       </c>
       <c r="M314" s="5" t="n">
-        <v>0.1285101915842883</v>
+        <v>0.1287076734622451</v>
       </c>
       <c r="N314" s="3" t="inlineStr">
         <is>
@@ -23849,7 +23849,7 @@
         <v>122</v>
       </c>
       <c r="P314" s="5" t="n">
-        <v>0.06727320444405561</v>
+        <v>0.06745997025111553</v>
       </c>
       <c r="Q314" s="9" t="inlineStr">
         <is>
@@ -23890,13 +23890,13 @@
         </is>
       </c>
       <c r="D315" s="13" t="n">
-        <v>59.35</v>
+        <v>59.51</v>
       </c>
       <c r="E315" s="14" t="n">
-        <v>-0.0518</v>
+        <v>-0.0493</v>
       </c>
       <c r="F315" s="14" t="n">
-        <v>-0.07519999999999999</v>
+        <v>-0.0727</v>
       </c>
       <c r="G315" s="15" t="n">
         <v>46328</v>
@@ -23925,14 +23925,14 @@
         <v>65</v>
       </c>
       <c r="M315" s="18" t="n">
-        <v>0.09519797809604041</v>
+        <v>0.09225340278944719</v>
       </c>
       <c r="N315" s="12" t="inlineStr"/>
       <c r="O315" s="17" t="n">
         <v>67</v>
       </c>
       <c r="P315" s="18" t="n">
-        <v>0.1288963774220724</v>
+        <v>0.1258611997983533</v>
       </c>
       <c r="Q315" s="19" t="inlineStr">
         <is>
@@ -23973,13 +23973,13 @@
         </is>
       </c>
       <c r="D316" s="4" t="n">
-        <v>134.9</v>
+        <v>135.76</v>
       </c>
       <c r="E316" s="22" t="n">
-        <v>-0.0414</v>
+        <v>-0.0353</v>
       </c>
       <c r="F316" s="22" t="n">
-        <v>-0.05110000000000001</v>
+        <v>-0.045</v>
       </c>
       <c r="G316" s="6" t="n">
         <v>46310</v>
@@ -24008,7 +24008,7 @@
         <v>167</v>
       </c>
       <c r="M316" s="5" t="n">
-        <v>0.2379540400296515</v>
+        <v>0.2301119622863878</v>
       </c>
       <c r="N316" s="3" t="inlineStr"/>
       <c r="O316" s="8" t="n"/>
@@ -24052,13 +24052,13 @@
         </is>
       </c>
       <c r="D317" s="13" t="n">
-        <v>293.27</v>
+        <v>296.54</v>
       </c>
       <c r="E317" s="14" t="n">
-        <v>-0.09369999999999999</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="F317" s="14" t="n">
-        <v>-0.0888</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="G317" s="15" t="n">
         <v>46330</v>
@@ -24094,7 +24094,7 @@
         <v>316</v>
       </c>
       <c r="P317" s="18" t="n">
-        <v>0.07750537047771684</v>
+        <v>0.0656235246509745</v>
       </c>
       <c r="Q317" s="19" t="inlineStr">
         <is>
@@ -24135,13 +24135,13 @@
         </is>
       </c>
       <c r="D318" s="4" t="n">
-        <v>204.07</v>
+        <v>204.71</v>
       </c>
       <c r="E318" s="22" t="n">
-        <v>-0.07480000000000001</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="F318" s="22" t="n">
-        <v>-0.0703</v>
+        <v>-0.0673</v>
       </c>
       <c r="G318" s="6" t="n">
         <v>46328</v>
@@ -24177,7 +24177,7 @@
         <v>215</v>
       </c>
       <c r="P318" s="5" t="n">
-        <v>0.05356005292301665</v>
+        <v>0.05026623027697714</v>
       </c>
       <c r="Q318" s="9" t="inlineStr">
         <is>
@@ -24218,13 +24218,13 @@
         </is>
       </c>
       <c r="D319" s="13" t="n">
-        <v>114.07</v>
+        <v>114.5</v>
       </c>
       <c r="E319" s="14" t="n">
-        <v>-0.0361</v>
+        <v>-0.03240000000000001</v>
       </c>
       <c r="F319" s="14" t="n">
-        <v>-0.0558</v>
+        <v>-0.0522</v>
       </c>
       <c r="G319" s="15" t="n">
         <v>46330</v>
@@ -24253,7 +24253,7 @@
         <v>142</v>
       </c>
       <c r="M319" s="18" t="n">
-        <v>0.2448496537213992</v>
+        <v>0.240174672489083</v>
       </c>
       <c r="N319" s="12" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>137</v>
       </c>
       <c r="P319" s="18" t="n">
-        <v>0.2010169194354345</v>
+        <v>0.1965065502183406</v>
       </c>
       <c r="Q319" s="19" t="inlineStr">
         <is>
@@ -24313,13 +24313,13 @@
         </is>
       </c>
       <c r="D320" s="4" t="n">
-        <v>235.8</v>
+        <v>235.55</v>
       </c>
       <c r="E320" s="5" t="n">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
       <c r="F320" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0043</v>
       </c>
       <c r="G320" s="6" t="n">
         <v>46321</v>
@@ -24348,7 +24348,7 @@
         <v>237</v>
       </c>
       <c r="M320" s="5" t="n">
-        <v>0.00508905852417298</v>
+        <v>0.006155805561451872</v>
       </c>
       <c r="N320" s="3" t="inlineStr">
         <is>
@@ -24359,7 +24359,7 @@
         <v>236</v>
       </c>
       <c r="P320" s="5" t="n">
-        <v>0.0008481764206954564</v>
+        <v>0.001910422415622962</v>
       </c>
       <c r="Q320" s="9" t="inlineStr">
         <is>
@@ -24400,13 +24400,13 @@
         </is>
       </c>
       <c r="D321" s="13" t="n">
-        <v>164.13</v>
+        <v>163.18</v>
       </c>
       <c r="E321" s="14" t="n">
-        <v>-0.0322</v>
+        <v>-0.0378</v>
       </c>
       <c r="F321" s="14" t="n">
-        <v>-0.08560000000000001</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="G321" s="15" t="n">
         <v>46330</v>
@@ -24435,7 +24435,7 @@
         <v>200</v>
       </c>
       <c r="M321" s="18" t="n">
-        <v>0.2185462742947664</v>
+        <v>0.2256403971074886</v>
       </c>
       <c r="N321" s="12" t="inlineStr"/>
       <c r="O321" s="17" t="n"/>
@@ -24479,13 +24479,13 @@
         </is>
       </c>
       <c r="D322" s="4" t="n">
-        <v>138.66</v>
+        <v>137.68</v>
       </c>
       <c r="E322" s="5" t="n">
-        <v>0.0278</v>
+        <v>0.0205</v>
       </c>
       <c r="F322" s="5" t="n">
-        <v>0.0542</v>
+        <v>0.04679999999999999</v>
       </c>
       <c r="G322" s="6" t="n">
         <v>46330</v>
@@ -24514,7 +24514,7 @@
         <v>131</v>
       </c>
       <c r="M322" s="22" t="n">
-        <v>-0.05524304053079473</v>
+        <v>-0.04851830331202794</v>
       </c>
       <c r="N322" s="3" t="inlineStr"/>
       <c r="O322" s="8" t="n"/>
@@ -24558,13 +24558,13 @@
         </is>
       </c>
       <c r="D323" s="13" t="n">
-        <v>30.92</v>
+        <v>30.77</v>
       </c>
       <c r="E323" s="14" t="n">
-        <v>-0.1166</v>
+        <v>-0.1207</v>
       </c>
       <c r="F323" s="14" t="n">
-        <v>-0.09539999999999998</v>
+        <v>-0.09960000000000001</v>
       </c>
       <c r="G323" s="15" t="n">
         <v>46330</v>
@@ -24637,13 +24637,13 @@
         </is>
       </c>
       <c r="D324" s="4" t="n">
-        <v>36.76</v>
+        <v>36.88</v>
       </c>
       <c r="E324" s="22" t="n">
-        <v>-0.0683</v>
+        <v>-0.06509999999999999</v>
       </c>
       <c r="F324" s="22" t="n">
-        <v>-0.0227</v>
+        <v>-0.0194</v>
       </c>
       <c r="G324" s="6" t="n"/>
       <c r="H324" s="7" t="inlineStr">
@@ -24688,13 +24688,13 @@
         </is>
       </c>
       <c r="D325" s="13" t="n">
-        <v>290.14</v>
+        <v>284.75</v>
       </c>
       <c r="E325" s="18" t="n">
-        <v>0.0411</v>
+        <v>0.0218</v>
       </c>
       <c r="F325" s="18" t="n">
-        <v>0.1265</v>
+        <v>0.1055</v>
       </c>
       <c r="G325" s="15" t="n"/>
       <c r="H325" s="21" t="inlineStr">
@@ -24713,7 +24713,7 @@
         <v>384</v>
       </c>
       <c r="M325" s="18" t="n">
-        <v>0.3234990004825257</v>
+        <v>0.3485513608428446</v>
       </c>
       <c r="N325" s="12" t="inlineStr">
         <is>
@@ -24724,7 +24724,7 @@
         <v>380</v>
       </c>
       <c r="P325" s="18" t="n">
-        <v>0.3097125525608327</v>
+        <v>0.334503950834065</v>
       </c>
       <c r="Q325" s="19" t="inlineStr"/>
       <c r="R325" s="17" t="n"/>
@@ -24767,13 +24767,13 @@
         </is>
       </c>
       <c r="D326" s="4" t="n">
-        <v>67.34999999999999</v>
+        <v>67.16</v>
       </c>
       <c r="E326" s="22" t="n">
-        <v>-0.0381</v>
+        <v>-0.0408</v>
       </c>
       <c r="F326" s="22" t="n">
-        <v>-0.1109</v>
+        <v>-0.1134</v>
       </c>
       <c r="G326" s="6" t="n">
         <v>46324</v>
@@ -24802,7 +24802,7 @@
         <v>79</v>
       </c>
       <c r="M326" s="5" t="n">
-        <v>0.1729769858945807</v>
+        <v>0.1762954139368672</v>
       </c>
       <c r="N326" s="3" t="inlineStr"/>
       <c r="O326" s="8" t="n"/>
@@ -24854,13 +24854,13 @@
         </is>
       </c>
       <c r="D327" s="13" t="n">
-        <v>119.22</v>
+        <v>119.42</v>
       </c>
       <c r="E327" s="14" t="n">
-        <v>-0.0346</v>
+        <v>-0.033</v>
       </c>
       <c r="F327" s="14" t="n">
-        <v>-0.0602</v>
+        <v>-0.05860000000000001</v>
       </c>
       <c r="G327" s="15" t="n">
         <v>46331</v>
@@ -24889,7 +24889,7 @@
         <v>136</v>
       </c>
       <c r="M327" s="18" t="n">
-        <v>0.1407481966113068</v>
+        <v>0.1388377156255234</v>
       </c>
       <c r="N327" s="12" t="inlineStr">
         <is>
@@ -24900,7 +24900,7 @@
         <v>140</v>
       </c>
       <c r="P327" s="18" t="n">
-        <v>0.1742996141586982</v>
+        <v>0.1723329425556858</v>
       </c>
       <c r="Q327" s="19" t="inlineStr">
         <is>
@@ -24941,13 +24941,13 @@
         </is>
       </c>
       <c r="D328" s="4" t="n">
-        <v>105.72</v>
+        <v>105.31</v>
       </c>
       <c r="E328" s="22" t="n">
-        <v>-0.0197</v>
+        <v>-0.0236</v>
       </c>
       <c r="F328" s="22" t="n">
-        <v>-0.0794</v>
+        <v>-0.083</v>
       </c>
       <c r="G328" s="6" t="n">
         <v>46330</v>
@@ -24976,7 +24976,7 @@
         <v>131</v>
       </c>
       <c r="M328" s="5" t="n">
-        <v>0.2391222096102913</v>
+        <v>0.2439464438324945</v>
       </c>
       <c r="N328" s="3" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>121</v>
       </c>
       <c r="P328" s="5" t="n">
-        <v>0.1445327279606508</v>
+        <v>0.1489887000284873</v>
       </c>
       <c r="Q328" s="9" t="inlineStr">
         <is>
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="D329" s="13" t="n">
-        <v>82.61</v>
+        <v>82.31</v>
       </c>
       <c r="E329" s="14" t="n">
-        <v>-0.0369</v>
+        <v>-0.0405</v>
       </c>
       <c r="F329" s="14" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.0687</v>
       </c>
       <c r="G329" s="15" t="n">
         <v>46322</v>
@@ -25074,7 +25074,7 @@
         <v>107</v>
       </c>
       <c r="P329" s="18" t="n">
-        <v>0.2952427066941049</v>
+        <v>0.2999635524237638</v>
       </c>
       <c r="Q329" s="19" t="inlineStr">
         <is>
@@ -25123,13 +25123,13 @@
         </is>
       </c>
       <c r="D330" s="4" t="n">
-        <v>53.56</v>
+        <v>53.15</v>
       </c>
       <c r="E330" s="22" t="n">
-        <v>-0.03240000000000001</v>
+        <v>-0.0399</v>
       </c>
       <c r="F330" s="22" t="n">
-        <v>-0.0953</v>
+        <v>-0.1023</v>
       </c>
       <c r="G330" s="6" t="n"/>
       <c r="H330" s="7" t="inlineStr">
@@ -25148,7 +25148,7 @@
         <v>63</v>
       </c>
       <c r="M330" s="5" t="n">
-        <v>0.1762509335324869</v>
+        <v>0.1853245531514582</v>
       </c>
       <c r="N330" s="3" t="inlineStr"/>
       <c r="O330" s="8" t="n"/>
@@ -25192,13 +25192,13 @@
         </is>
       </c>
       <c r="D331" s="13" t="n">
-        <v>37.37</v>
+        <v>36.25</v>
       </c>
       <c r="E331" s="14" t="n">
-        <v>-0.1721</v>
+        <v>-0.1968</v>
       </c>
       <c r="F331" s="14" t="n">
-        <v>-0.1843</v>
+        <v>-0.2087</v>
       </c>
       <c r="G331" s="15" t="n"/>
       <c r="H331" s="21" t="inlineStr">
@@ -25243,13 +25243,13 @@
         </is>
       </c>
       <c r="D332" s="4" t="n">
-        <v>9.109999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="E332" s="22" t="n">
-        <v>-0.05</v>
+        <v>-0.1027</v>
       </c>
       <c r="F332" s="5" t="n">
-        <v>0.091</v>
+        <v>0.0305</v>
       </c>
       <c r="G332" s="6" t="n">
         <v>46331</v>
@@ -25304,13 +25304,13 @@
         </is>
       </c>
       <c r="D333" s="13" t="n">
-        <v>87.63</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="E333" s="14" t="n">
-        <v>-0.0529</v>
+        <v>-0.058</v>
       </c>
       <c r="F333" s="14" t="n">
-        <v>-0.0916</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="G333" s="15" t="n">
         <v>46324</v>
@@ -25339,7 +25339,7 @@
         <v>99</v>
       </c>
       <c r="M333" s="18" t="n">
-        <v>0.1297500855871278</v>
+        <v>0.135972461273666</v>
       </c>
       <c r="N333" s="12" t="inlineStr">
         <is>
@@ -25350,7 +25350,7 @@
         <v>112</v>
       </c>
       <c r="P333" s="18" t="n">
-        <v>0.2781011069268516</v>
+        <v>0.2851405622489959</v>
       </c>
       <c r="Q333" s="19" t="inlineStr">
         <is>
@@ -25391,13 +25391,13 @@
         </is>
       </c>
       <c r="D334" s="4" t="n">
-        <v>105.6</v>
+        <v>105.34</v>
       </c>
       <c r="E334" s="22" t="n">
-        <v>-0.0322</v>
+        <v>-0.0346</v>
       </c>
       <c r="F334" s="22" t="n">
-        <v>-0.0886</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="G334" s="6" t="n">
         <v>46324</v>
@@ -25426,7 +25426,7 @@
         <v>127</v>
       </c>
       <c r="M334" s="5" t="n">
-        <v>0.2026515151515152</v>
+        <v>0.2056198974748433</v>
       </c>
       <c r="N334" s="3" t="inlineStr"/>
       <c r="O334" s="8" t="n"/>
@@ -36922,7 +36922,7 @@
     <row r="2">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>Data as of September 11, 2026 at 14:38 UTC</t>
+          <t>Data as of September 11, 2026 at 20:05 UTC</t>
         </is>
       </c>
     </row>

--- a/earnings-data.xlsx
+++ b/earnings-data.xlsx
@@ -13,7 +13,7 @@
     <sheet name="About" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Earnings Schedule'!$A$1:$H$278</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Earnings Schedule'!$A$1:$H$281</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>108.59</v>
+        <v>107.58</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.0163</v>
+        <v>0.0395</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.0891</v>
+        <v>0.1015</v>
       </c>
       <c r="G2" s="6" t="n"/>
       <c r="H2" s="7" t="inlineStr">
@@ -868,7 +868,7 @@
         <v>125</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>0.151118887558707</v>
+        <v>0.1619260085517754</v>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         <v>144</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>0.3260889584676305</v>
+        <v>0.3385387618516453</v>
       </c>
       <c r="Q2" s="9" t="inlineStr">
         <is>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="D3" s="13" t="n">
-        <v>349.39</v>
+        <v>344.22</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>0.0101</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>-0.0143</v>
+        <v>-0.0074</v>
       </c>
       <c r="G3" s="16" t="n">
         <v>46322</v>
@@ -963,7 +963,7 @@
         <v>438</v>
       </c>
       <c r="M3" s="14" t="n">
-        <v>0.2536134405678468</v>
+        <v>0.2724420428795536</v>
       </c>
       <c r="N3" s="12" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>420</v>
       </c>
       <c r="P3" s="14" t="n">
-        <v>0.2020950799965655</v>
+        <v>0.2201499041310789</v>
       </c>
       <c r="Q3" s="19" t="inlineStr">
         <is>
@@ -1019,13 +1019,13 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>665.6</v>
+        <v>670.35</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.1284</v>
+        <v>0.1782</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0377</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>46330</v>
@@ -1054,7 +1054,7 @@
         <v>835</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>0.2545072115384615</v>
+        <v>0.2456179607667636</v>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>930</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>0.3972355769230769</v>
+        <v>0.3873349742671738</v>
       </c>
       <c r="Q4" s="9" t="inlineStr">
         <is>
@@ -1114,13 +1114,13 @@
         </is>
       </c>
       <c r="D5" s="13" t="n">
-        <v>43.15</v>
+        <v>42.67</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>0.137</v>
+        <v>0.1466</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="G5" s="16" t="n">
         <v>46329</v>
@@ -1175,13 +1175,13 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>80.31999999999999</v>
+        <v>78.14</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.0276</v>
+        <v>0.028</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.0803</v>
+        <v>0.1334</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>46315</v>
@@ -1209,8 +1209,8 @@
       <c r="L6" s="8" t="n">
         <v>80</v>
       </c>
-      <c r="M6" s="25" t="n">
-        <v>-0.003984063745019836</v>
+      <c r="M6" s="5" t="n">
+        <v>0.02380342974148963</v>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>100</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>0.2450199203187252</v>
+        <v>0.279754287176862</v>
       </c>
       <c r="Q6" s="9" t="inlineStr">
         <is>
@@ -1262,13 +1262,13 @@
         </is>
       </c>
       <c r="D7" s="13" t="n">
-        <v>81.06999999999999</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>-0.0742</v>
+        <v>-0.0582</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>-0.0368</v>
+        <v>-0.0152</v>
       </c>
       <c r="G7" s="16" t="n">
         <v>46315</v>
@@ -1297,7 +1297,7 @@
         <v>91</v>
       </c>
       <c r="M7" s="14" t="n">
-        <v>0.1224867398544469</v>
+        <v>0.1305752267362406</v>
       </c>
       <c r="N7" s="12" t="inlineStr"/>
       <c r="O7" s="18" t="n"/>
@@ -1341,13 +1341,13 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>556.3099999999999</v>
+        <v>557.1799999999999</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.0848</v>
+        <v>0.1314</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.1685</v>
+        <v>0.1653</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>46329</v>
@@ -1376,7 +1376,7 @@
         <v>569.9299999999999</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>0.02448275242221065</v>
+        <v>0.02288308984529237</v>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>648.04</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>0.1648900792723482</v>
+        <v>0.16307117987006</v>
       </c>
       <c r="Q8" s="9" t="inlineStr">
         <is>
@@ -1428,13 +1428,13 @@
         </is>
       </c>
       <c r="D9" s="13" t="n">
-        <v>193.72</v>
+        <v>192.43</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>-0.03759999999999999</v>
+        <v>-0.0139</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>0.0484</v>
+        <v>0.0394</v>
       </c>
       <c r="G9" s="16" t="n">
         <v>46330</v>
@@ -1497,13 +1497,13 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>182.9</v>
+        <v>182.15</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0113</v>
       </c>
       <c r="F10" s="25" t="n">
-        <v>-0.0516</v>
+        <v>-0.0534</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>46317</v>
@@ -1532,7 +1532,7 @@
         <v>170</v>
       </c>
       <c r="M10" s="25" t="n">
-        <v>-0.07053034445051944</v>
+        <v>-0.06670326653856715</v>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>270</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>0.4762165117550574</v>
+        <v>0.482294811968158</v>
       </c>
       <c r="Q10" s="9" t="inlineStr">
         <is>
@@ -1584,13 +1584,13 @@
         </is>
       </c>
       <c r="D11" s="13" t="n">
-        <v>51.29</v>
+        <v>51.48</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>0.058</v>
+        <v>0.0712</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>0.1689</v>
+        <v>0.181</v>
       </c>
       <c r="G11" s="16" t="n">
         <v>46316</v>
@@ -1619,7 +1619,7 @@
         <v>43</v>
       </c>
       <c r="M11" s="15" t="n">
-        <v>-0.1616299473581595</v>
+        <v>-0.1647241647241647</v>
       </c>
       <c r="N11" s="12" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>50</v>
       </c>
       <c r="P11" s="15" t="n">
-        <v>-0.0251511015792552</v>
+        <v>-0.02874902874902869</v>
       </c>
       <c r="Q11" s="19" t="inlineStr">
         <is>
@@ -1675,13 +1675,13 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>170.65</v>
+        <v>167.4</v>
       </c>
       <c r="E12" s="25" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.0663</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.1546</v>
+        <v>0.1467</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>46331</v>
@@ -1710,7 +1710,7 @@
         <v>181</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>0.06065045414591265</v>
+        <v>0.08124253285543605</v>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>155</v>
       </c>
       <c r="P12" s="25" t="n">
-        <v>-0.0917081746264284</v>
+        <v>-0.07407407407407411</v>
       </c>
       <c r="Q12" s="9" t="inlineStr">
         <is>
@@ -1762,13 +1762,13 @@
         </is>
       </c>
       <c r="D13" s="13" t="n">
-        <v>253.54</v>
+        <v>248.92</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>-0.0347</v>
+        <v>-0.0474</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>0.0146</v>
+        <v>0.0068</v>
       </c>
       <c r="G13" s="16" t="n">
         <v>46324</v>
@@ -1797,7 +1797,7 @@
         <v>322</v>
       </c>
       <c r="M13" s="14" t="n">
-        <v>0.2700165654334622</v>
+        <v>0.2935883014623173</v>
       </c>
       <c r="N13" s="12" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>285</v>
       </c>
       <c r="P13" s="14" t="n">
-        <v>0.1240829849333439</v>
+        <v>0.1449461674433553</v>
       </c>
       <c r="Q13" s="19" t="inlineStr">
         <is>
@@ -1861,13 +1861,13 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2965.52</v>
+        <v>2902.24</v>
       </c>
       <c r="E14" s="25" t="n">
-        <v>-0.0197</v>
+        <v>-0.0388</v>
       </c>
       <c r="F14" s="25" t="n">
-        <v>-0.0316</v>
+        <v>-0.0473</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>46287</v>
@@ -1896,7 +1896,7 @@
         <v>4150</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>0.3994173028676252</v>
+        <v>0.4299299851149458</v>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>3700</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>0.2476732579783647</v>
+        <v>0.2748773361265782</v>
       </c>
       <c r="Q14" s="9" t="inlineStr">
         <is>
@@ -1948,13 +1948,13 @@
         </is>
       </c>
       <c r="D15" s="13" t="n">
-        <v>94.83</v>
+        <v>93.59</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>0.0973</v>
+        <v>0.09539999999999998</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>0.1119</v>
+        <v>0.0958</v>
       </c>
       <c r="G15" s="16" t="n"/>
       <c r="H15" s="21" t="inlineStr">
@@ -1973,7 +1973,7 @@
         <v>65</v>
       </c>
       <c r="M15" s="15" t="n">
-        <v>-0.3145629020352209</v>
+        <v>-0.3054813548456032</v>
       </c>
       <c r="N15" s="12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>85</v>
       </c>
       <c r="P15" s="15" t="n">
-        <v>-0.1036591795845196</v>
+        <v>-0.09178331018271187</v>
       </c>
       <c r="Q15" s="19" t="inlineStr"/>
       <c r="R15" s="18" t="n"/>
@@ -2019,13 +2019,13 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>175.35</v>
+        <v>170.88</v>
       </c>
       <c r="E16" s="25" t="n">
-        <v>-0.1731</v>
+        <v>-0.1655</v>
       </c>
       <c r="F16" s="25" t="n">
-        <v>-0.05019999999999999</v>
+        <v>-0.0594</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>46322</v>
@@ -2054,7 +2054,7 @@
         <v>214</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>0.2204163102366695</v>
+        <v>0.2523408239700375</v>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>245</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>0.3972055888223553</v>
+        <v>0.4337546816479401</v>
       </c>
       <c r="Q16" s="9" t="inlineStr">
         <is>
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="D17" s="13" t="n">
-        <v>232.24</v>
+        <v>229.56</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>-0.332</v>
+        <v>-0.3185</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>-0.348</v>
+        <v>-0.3352000000000001</v>
       </c>
       <c r="G17" s="16" t="n"/>
       <c r="H17" s="21" t="inlineStr">
@@ -2139,7 +2139,7 @@
         <v>375</v>
       </c>
       <c r="M17" s="14" t="n">
-        <v>0.6147089218050292</v>
+        <v>0.6335598536330371</v>
       </c>
       <c r="N17" s="12" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>375</v>
       </c>
       <c r="P17" s="14" t="n">
-        <v>0.6147089218050292</v>
+        <v>0.6335598536330371</v>
       </c>
       <c r="Q17" s="19" t="inlineStr"/>
       <c r="R17" s="18" t="n"/>
@@ -2189,13 +2189,13 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>37.03</v>
+        <v>35.17</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.1054</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.0827</v>
+        <v>0.0213</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>46323</v>
@@ -2224,7 +2224,7 @@
         <v>45</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>0.2152308938698352</v>
+        <v>0.2794995735001421</v>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>45</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>0.2152308938698352</v>
+        <v>0.2794995735001421</v>
       </c>
       <c r="Q18" s="9" t="inlineStr">
         <is>
@@ -2276,13 +2276,13 @@
         </is>
       </c>
       <c r="D19" s="13" t="n">
-        <v>139.41</v>
+        <v>138.88</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-0.0638</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>-0.09720000000000001</v>
+        <v>-0.0704</v>
       </c>
       <c r="G19" s="16" t="n">
         <v>46324</v>
@@ -2311,7 +2311,7 @@
         <v>170</v>
       </c>
       <c r="M19" s="14" t="n">
-        <v>0.2194247184563518</v>
+        <v>0.2240783410138249</v>
       </c>
       <c r="N19" s="12" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>177</v>
       </c>
       <c r="P19" s="14" t="n">
-        <v>0.2696363245104369</v>
+        <v>0.2744815668202765</v>
       </c>
       <c r="Q19" s="19" t="inlineStr">
         <is>
@@ -2363,13 +2363,13 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>130.77</v>
+        <v>126.43</v>
       </c>
       <c r="E20" s="25" t="n">
-        <v>-0.3525</v>
+        <v>-0.3557</v>
       </c>
       <c r="F20" s="25" t="n">
-        <v>-0.397</v>
+        <v>-0.4183</v>
       </c>
       <c r="G20" s="6" t="n"/>
       <c r="H20" s="7" t="inlineStr">
@@ -2388,7 +2388,7 @@
         <v>220</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>0.6823430450409114</v>
+        <v>0.7400933322787312</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="8" t="n"/>
@@ -2432,13 +2432,13 @@
         </is>
       </c>
       <c r="D21" s="13" t="n">
-        <v>119.17</v>
+        <v>114.26</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>-0.079</v>
+        <v>-0.118</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>-0.0722</v>
+        <v>-0.09269999999999999</v>
       </c>
       <c r="G21" s="16" t="n"/>
       <c r="H21" s="21" t="inlineStr">
@@ -2483,13 +2483,13 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>87.16</v>
+        <v>85.36</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.004500000000000001</v>
+        <v>0.0117</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.1215</v>
+        <v>0.1221</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>46315</v>
@@ -2518,7 +2518,7 @@
         <v>61</v>
       </c>
       <c r="M22" s="25" t="n">
-        <v>-0.3001376778338687</v>
+        <v>-0.2853795688847235</v>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>100</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0.1473152822395595</v>
+        <v>0.1715089034676664</v>
       </c>
       <c r="Q22" s="9" t="inlineStr">
         <is>
@@ -2570,13 +2570,13 @@
         </is>
       </c>
       <c r="D23" s="13" t="n">
-        <v>133.21</v>
+        <v>132.15</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>-0.0135</v>
+        <v>-0.0028</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0.0601</v>
+        <v>0.0587</v>
       </c>
       <c r="G23" s="16" t="n">
         <v>46315</v>
@@ -2608,7 +2608,7 @@
         <v>145</v>
       </c>
       <c r="P23" s="14" t="n">
-        <v>0.08850686885368959</v>
+        <v>0.09723798713583044</v>
       </c>
       <c r="Q23" s="19" t="inlineStr"/>
       <c r="R23" s="18" t="n"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>310.87</v>
+        <v>305.8</v>
       </c>
       <c r="E24" s="25" t="n">
-        <v>-0.08259999999999999</v>
+        <v>-0.0949</v>
       </c>
       <c r="F24" s="25" t="n">
-        <v>-0.1067</v>
+        <v>-0.09759999999999999</v>
       </c>
       <c r="G24" s="6" t="n"/>
       <c r="H24" s="7" t="inlineStr">
@@ -2668,7 +2668,7 @@
         <v>360</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>0.1580403384051211</v>
+        <v>0.1772400261608894</v>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>400</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0.2867114871168012</v>
+        <v>0.3080444735120993</v>
       </c>
       <c r="Q24" s="9" t="inlineStr">
         <is>
@@ -2728,13 +2728,13 @@
         </is>
       </c>
       <c r="D25" s="13" t="n">
-        <v>198.17</v>
+        <v>195.17</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>-0.0929</v>
+        <v>-0.0956</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>-0.0832</v>
+        <v>-0.065</v>
       </c>
       <c r="G25" s="16" t="n"/>
       <c r="H25" s="21" t="inlineStr">
@@ -2753,7 +2753,7 @@
         <v>255</v>
       </c>
       <c r="M25" s="14" t="n">
-        <v>0.2867739819347026</v>
+        <v>0.306553261259415</v>
       </c>
       <c r="N25" s="12" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>230</v>
       </c>
       <c r="P25" s="14" t="n">
-        <v>0.16061966998032</v>
+        <v>0.1784598042731978</v>
       </c>
       <c r="Q25" s="19" t="inlineStr">
         <is>
@@ -2809,13 +2809,13 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>257.49</v>
+        <v>255.36</v>
       </c>
       <c r="E26" s="25" t="n">
-        <v>-0.0562</v>
+        <v>-0.0383</v>
       </c>
       <c r="F26" s="25" t="n">
-        <v>-0.0584</v>
+        <v>-0.0461</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>46330</v>
@@ -2844,7 +2844,7 @@
         <v>300</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>0.165093790050099</v>
+        <v>0.1748120300751879</v>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>350</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>0.3592760883917822</v>
+        <v>0.3706140350877192</v>
       </c>
       <c r="Q26" s="9" t="inlineStr">
         <is>
@@ -2896,13 +2896,13 @@
         </is>
       </c>
       <c r="D27" s="13" t="n">
-        <v>37.05</v>
+        <v>36.32</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-0.0709</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>-0.1687</v>
+        <v>-0.17</v>
       </c>
       <c r="G27" s="16" t="n">
         <v>46289</v>
@@ -2957,13 +2957,13 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>87.22</v>
+        <v>86.06</v>
       </c>
       <c r="E28" s="25" t="n">
-        <v>-0.0421</v>
+        <v>-0.0462</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.0112</v>
+        <v>0.0001</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>46323</v>
@@ -2992,7 +2992,7 @@
         <v>110</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>0.2611786287548727</v>
+        <v>0.2781780153381361</v>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>115</v>
       </c>
       <c r="P28" s="5" t="n">
-        <v>0.3185049300619124</v>
+        <v>0.3362770160353242</v>
       </c>
       <c r="Q28" s="9" t="inlineStr">
         <is>
@@ -3048,13 +3048,13 @@
         </is>
       </c>
       <c r="D29" s="13" t="n">
-        <v>171.76</v>
+        <v>167.63</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>-0.1185</v>
+        <v>-0.1199</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>-0.1739</v>
+        <v>-0.1667</v>
       </c>
       <c r="G29" s="16" t="n">
         <v>46317</v>
@@ -3109,13 +3109,13 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>230.04</v>
+        <v>226.34</v>
       </c>
       <c r="E30" s="25" t="n">
-        <v>-0.0624</v>
+        <v>-0.038</v>
       </c>
       <c r="F30" s="25" t="n">
-        <v>-0.0115</v>
+        <v>-0.0305</v>
       </c>
       <c r="G30" s="6" t="n"/>
       <c r="H30" s="7" t="inlineStr">
@@ -3134,7 +3134,7 @@
         <v>245</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>0.06503216831855334</v>
+        <v>0.08244234337722009</v>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>265</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>0.1519735698139454</v>
+        <v>0.1708049836529115</v>
       </c>
       <c r="Q30" s="9" t="inlineStr">
         <is>
@@ -3186,13 +3186,13 @@
         </is>
       </c>
       <c r="D31" s="13" t="n">
-        <v>99.06999999999999</v>
+        <v>96.56999999999999</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>-0.08</v>
+        <v>-0.1052</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>-0.0858</v>
+        <v>-0.08460000000000001</v>
       </c>
       <c r="G31" s="16" t="n">
         <v>46330</v>
@@ -3221,7 +3221,7 @@
         <v>120</v>
       </c>
       <c r="M31" s="14" t="n">
-        <v>0.2112647622892905</v>
+        <v>0.2426219322771048</v>
       </c>
       <c r="N31" s="12" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>115</v>
       </c>
       <c r="P31" s="14" t="n">
-        <v>0.1607953971939034</v>
+        <v>0.1908460184322254</v>
       </c>
       <c r="Q31" s="19" t="inlineStr">
         <is>
@@ -3273,13 +3273,13 @@
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E32" s="25" t="n">
-        <v>-0.0449</v>
+        <v>13.32</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>0.0149</v>
       </c>
       <c r="F32" s="25" t="n">
-        <v>-0.1105</v>
+        <v>-0.07339999999999999</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>46330</v>
@@ -3334,13 +3334,13 @@
         </is>
       </c>
       <c r="D33" s="13" t="n">
-        <v>125.99</v>
+        <v>124.76</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>-0.1717</v>
+        <v>-0.173</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>-0.1861</v>
+        <v>-0.1923</v>
       </c>
       <c r="G33" s="16" t="n"/>
       <c r="H33" s="21" t="inlineStr">
@@ -3359,7 +3359,7 @@
         <v>160</v>
       </c>
       <c r="M33" s="14" t="n">
-        <v>0.269942058893563</v>
+        <v>0.2824623276691247</v>
       </c>
       <c r="N33" s="12" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>175</v>
       </c>
       <c r="P33" s="14" t="n">
-        <v>0.3889991269148346</v>
+        <v>0.4026931708881051</v>
       </c>
       <c r="Q33" s="19" t="inlineStr">
         <is>
@@ -3415,13 +3415,13 @@
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>33.83</v>
+        <v>32.87</v>
       </c>
       <c r="E34" s="25" t="n">
-        <v>-0.0558</v>
+        <v>-0.0522</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.0774</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>46317</v>
@@ -3450,7 +3450,7 @@
         <v>35</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>0.03458468814661548</v>
+        <v>0.06480073014907219</v>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>40</v>
       </c>
       <c r="P34" s="5" t="n">
-        <v>0.1823825007389891</v>
+        <v>0.2169151201703682</v>
       </c>
       <c r="Q34" s="9" t="inlineStr">
         <is>
@@ -3502,13 +3502,13 @@
         </is>
       </c>
       <c r="D35" s="13" t="n">
-        <v>358.97</v>
+        <v>358.96</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>0.0488</v>
+        <v>0.058</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>-0.08210000000000001</v>
+        <v>-0.0574</v>
       </c>
       <c r="G35" s="16" t="n">
         <v>46323</v>
@@ -3537,7 +3537,7 @@
         <v>130</v>
       </c>
       <c r="M35" s="15" t="n">
-        <v>-0.6378527453547651</v>
+        <v>-0.6378426565634053</v>
       </c>
       <c r="N35" s="12" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>300</v>
       </c>
       <c r="P35" s="15" t="n">
-        <v>-0.164275566203304</v>
+        <v>-0.1642522843770893</v>
       </c>
       <c r="Q35" s="19" t="inlineStr">
         <is>
@@ -3589,13 +3589,13 @@
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>72.63</v>
+        <v>71.5</v>
       </c>
       <c r="E36" s="25" t="n">
-        <v>-0.0437</v>
+        <v>-0.04650000000000001</v>
       </c>
       <c r="F36" s="25" t="n">
-        <v>-0.019</v>
+        <v>-0.0132</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>46329</v>
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="D37" s="13" t="n">
-        <v>548.65</v>
+        <v>543.34</v>
       </c>
       <c r="E37" s="14" t="n">
-        <v>0.0742</v>
+        <v>0.1014</v>
       </c>
       <c r="F37" s="14" t="n">
-        <v>0.1457</v>
+        <v>0.133</v>
       </c>
       <c r="G37" s="16" t="n"/>
       <c r="H37" s="21" t="inlineStr">
@@ -3675,7 +3675,7 @@
         <v>450</v>
       </c>
       <c r="M37" s="15" t="n">
-        <v>-0.1798049758498131</v>
+        <v>-0.1717893031987338</v>
       </c>
       <c r="N37" s="12" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>635</v>
       </c>
       <c r="P37" s="14" t="n">
-        <v>0.1573863118563748</v>
+        <v>0.1686973165973423</v>
       </c>
       <c r="Q37" s="19" t="inlineStr">
         <is>
@@ -3731,13 +3731,13 @@
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>94.58</v>
+        <v>94.11</v>
       </c>
       <c r="E38" s="25" t="n">
-        <v>-0.0663</v>
+        <v>-0.0395</v>
       </c>
       <c r="F38" s="25" t="n">
-        <v>-0.0458</v>
+        <v>-0.0404</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>46325</v>
@@ -3766,7 +3766,7 @@
         <v>110</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>0.1630365827870586</v>
+        <v>0.1688449686537031</v>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>105</v>
       </c>
       <c r="P38" s="5" t="n">
-        <v>0.110171283569465</v>
+        <v>0.1157156518967166</v>
       </c>
       <c r="Q38" s="9" t="inlineStr">
         <is>
@@ -3822,13 +3822,13 @@
         </is>
       </c>
       <c r="D39" s="13" t="n">
-        <v>87.89</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="E39" s="15" t="n">
-        <v>-0.0442</v>
+        <v>-0.0339</v>
       </c>
       <c r="F39" s="15" t="n">
-        <v>-0.06570000000000001</v>
+        <v>-0.06269999999999999</v>
       </c>
       <c r="G39" s="16" t="n">
         <v>46325</v>
@@ -3857,7 +3857,7 @@
         <v>95</v>
       </c>
       <c r="M39" s="14" t="n">
-        <v>0.08089657526453521</v>
+        <v>0.0900745840504876</v>
       </c>
       <c r="N39" s="12" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>100</v>
       </c>
       <c r="P39" s="14" t="n">
-        <v>0.1377858686995107</v>
+        <v>0.1474469305794606</v>
       </c>
       <c r="Q39" s="19" t="inlineStr">
         <is>
@@ -3913,13 +3913,13 @@
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>918.91</v>
+        <v>907.74</v>
       </c>
       <c r="E40" s="25" t="n">
-        <v>-0.04389999999999999</v>
+        <v>-0.048</v>
       </c>
       <c r="F40" s="25" t="n">
-        <v>-0.0282</v>
+        <v>-0.0352</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>46289</v>
@@ -3948,7 +3948,7 @@
         <v>1000</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>0.0882458565039014</v>
+        <v>0.1016370326304889</v>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>1100</v>
       </c>
       <c r="P40" s="5" t="n">
-        <v>0.1970704421542915</v>
+        <v>0.2118007358935378</v>
       </c>
       <c r="Q40" s="9" t="inlineStr">
         <is>
@@ -4008,13 +4008,13 @@
         </is>
       </c>
       <c r="D41" s="13" t="n">
-        <v>129.17</v>
+        <v>125.5</v>
       </c>
       <c r="E41" s="14" t="n">
-        <v>0.0478</v>
-      </c>
-      <c r="F41" s="14" t="n">
-        <v>0.0158</v>
+        <v>0.0451</v>
+      </c>
+      <c r="F41" s="15" t="n">
+        <v>-0.002</v>
       </c>
       <c r="G41" s="16" t="n"/>
       <c r="H41" s="21" t="inlineStr">
@@ -4033,7 +4033,7 @@
         <v>125</v>
       </c>
       <c r="M41" s="15" t="n">
-        <v>-0.03228303785708746</v>
+        <v>-0.00398406374501992</v>
       </c>
       <c r="N41" s="12" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>135</v>
       </c>
       <c r="P41" s="14" t="n">
-        <v>0.04513431911434554</v>
+        <v>0.07569721115537849</v>
       </c>
       <c r="Q41" s="19" t="inlineStr">
         <is>
@@ -4085,13 +4085,13 @@
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>24.27</v>
+        <v>24.32</v>
       </c>
       <c r="E42" s="25" t="n">
-        <v>-0.0486</v>
+        <v>-0.0176</v>
       </c>
       <c r="F42" s="25" t="n">
-        <v>-0.0747</v>
+        <v>-0.0605</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>46330</v>
@@ -4146,13 +4146,13 @@
         </is>
       </c>
       <c r="D43" s="13" t="n">
-        <v>89.34999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="E43" s="14" t="n">
-        <v>0.0187</v>
+        <v>0.0175</v>
       </c>
       <c r="F43" s="14" t="n">
-        <v>0.0522</v>
+        <v>0.0851</v>
       </c>
       <c r="G43" s="16" t="n">
         <v>46315</v>
@@ -4181,7 +4181,7 @@
         <v>90</v>
       </c>
       <c r="M43" s="14" t="n">
-        <v>0.007274762171236774</v>
+        <v>0.01694915254237288</v>
       </c>
       <c r="N43" s="12" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>88</v>
       </c>
       <c r="P43" s="15" t="n">
-        <v>-0.01510912143256849</v>
+        <v>-0.005649717514124294</v>
       </c>
       <c r="Q43" s="19" t="inlineStr">
         <is>
@@ -4241,13 +4241,13 @@
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>60.91</v>
+        <v>61.39</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0.07440000000000001</v>
+        <v>0.0949</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.0392</v>
+        <v>0.0437</v>
       </c>
       <c r="G44" s="6" t="n"/>
       <c r="H44" s="7" t="inlineStr">
@@ -4266,7 +4266,7 @@
         <v>58</v>
       </c>
       <c r="M44" s="25" t="n">
-        <v>-0.04777540633721879</v>
+        <v>-0.05522071998696857</v>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>78</v>
       </c>
       <c r="P44" s="5" t="n">
-        <v>0.2805779018223609</v>
+        <v>0.2705652386382147</v>
       </c>
       <c r="Q44" s="9" t="inlineStr">
         <is>
@@ -4318,13 +4318,13 @@
         </is>
       </c>
       <c r="D45" s="13" t="n">
-        <v>62.39</v>
+        <v>62.08</v>
       </c>
       <c r="E45" s="15" t="n">
-        <v>-0.0192</v>
+        <v>-0.0017</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0.0158</v>
+        <v>0.0176</v>
       </c>
       <c r="G45" s="16" t="n">
         <v>46322</v>
@@ -4353,7 +4353,7 @@
         <v>70</v>
       </c>
       <c r="M45" s="14" t="n">
-        <v>0.1219746754287546</v>
+        <v>0.1275773195876289</v>
       </c>
       <c r="N45" s="12" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>71</v>
       </c>
       <c r="P45" s="14" t="n">
-        <v>0.1380028850777368</v>
+        <v>0.1436855670103093</v>
       </c>
       <c r="Q45" s="19" t="inlineStr">
         <is>
@@ -4413,13 +4413,13 @@
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>50.39</v>
+        <v>49.67</v>
       </c>
       <c r="E46" s="25" t="n">
-        <v>-0.07829999999999999</v>
+        <v>-0.07919999999999999</v>
       </c>
       <c r="F46" s="25" t="n">
-        <v>-0.0474</v>
+        <v>-0.0393</v>
       </c>
       <c r="G46" s="6" t="n">
         <v>46296</v>
@@ -4484,13 +4484,13 @@
         </is>
       </c>
       <c r="D47" s="13" t="n">
-        <v>44.2</v>
+        <v>44.51</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>-0.05599999999999999</v>
+        <v>-0.0222</v>
       </c>
       <c r="F47" s="15" t="n">
-        <v>-0.1155</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="G47" s="16" t="n">
         <v>46331</v>
@@ -4545,13 +4545,13 @@
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>70.61</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0.0747</v>
+        <v>0.0956</v>
       </c>
       <c r="F48" s="25" t="n">
-        <v>-0.0331</v>
+        <v>-0.0557</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>46324</v>
@@ -4606,13 +4606,13 @@
         </is>
       </c>
       <c r="D49" s="13" t="n">
-        <v>136.34</v>
+        <v>135.49</v>
       </c>
       <c r="E49" s="15" t="n">
-        <v>-0.0316</v>
+        <v>-0.0199</v>
       </c>
       <c r="F49" s="15" t="n">
-        <v>-0.0222</v>
+        <v>-0.0119</v>
       </c>
       <c r="G49" s="16" t="n">
         <v>46303</v>
@@ -4641,7 +4641,7 @@
         <v>140</v>
       </c>
       <c r="M49" s="14" t="n">
-        <v>0.02684465307319933</v>
+        <v>0.03328658941619301</v>
       </c>
       <c r="N49" s="12" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>150</v>
       </c>
       <c r="P49" s="14" t="n">
-        <v>0.100190699721285</v>
+        <v>0.1070927743744925</v>
       </c>
       <c r="Q49" s="19" t="inlineStr">
         <is>
@@ -4701,13 +4701,13 @@
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>146.13</v>
+        <v>146.54</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0.0109</v>
+        <v>0.0239</v>
       </c>
       <c r="F50" s="25" t="n">
-        <v>-0.0354</v>
+        <v>-0.023</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>46318</v>
@@ -4736,7 +4736,7 @@
         <v>164</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>0.1222883733661808</v>
+        <v>0.1191483553978437</v>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>162</v>
       </c>
       <c r="P50" s="5" t="n">
-        <v>0.1086019297885445</v>
+        <v>0.1055002047222602</v>
       </c>
       <c r="Q50" s="9" t="inlineStr">
         <is>
@@ -4800,13 +4800,13 @@
         </is>
       </c>
       <c r="D51" s="13" t="n">
-        <v>83.54000000000001</v>
-      </c>
-      <c r="E51" s="14" t="n">
-        <v>0.0066</v>
-      </c>
-      <c r="F51" s="14" t="n">
-        <v>0.0157</v>
+        <v>80.86</v>
+      </c>
+      <c r="E51" s="15" t="n">
+        <v>-0.0122</v>
+      </c>
+      <c r="F51" s="15" t="n">
+        <v>-0.0102</v>
       </c>
       <c r="G51" s="16" t="n">
         <v>46322</v>
@@ -4835,7 +4835,7 @@
         <v>100</v>
       </c>
       <c r="M51" s="14" t="n">
-        <v>0.1970313622216901</v>
+        <v>0.2367054167697255</v>
       </c>
       <c r="N51" s="12" t="inlineStr"/>
       <c r="O51" s="18" t="n"/>
@@ -4879,13 +4879,13 @@
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>158.7</v>
+        <v>154.66</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0.0273</v>
+        <v>0.0242</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.1319</v>
+        <v>0.1079</v>
       </c>
       <c r="G52" s="6" t="n"/>
       <c r="H52" s="7" t="inlineStr">
@@ -4904,7 +4904,7 @@
         <v>140</v>
       </c>
       <c r="M52" s="25" t="n">
-        <v>-0.1178323881537491</v>
+        <v>-0.09478856847277897</v>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>135</v>
       </c>
       <c r="P52" s="25" t="n">
-        <v>-0.1493383742911152</v>
+        <v>-0.1271175481701797</v>
       </c>
       <c r="Q52" s="9" t="inlineStr">
         <is>
@@ -4960,13 +4960,13 @@
         </is>
       </c>
       <c r="D53" s="13" t="n">
-        <v>109.08</v>
+        <v>108.8</v>
       </c>
       <c r="E53" s="15" t="n">
-        <v>-0.0537</v>
+        <v>-0.0484</v>
       </c>
       <c r="F53" s="15" t="n">
-        <v>-0.05110000000000001</v>
+        <v>-0.0476</v>
       </c>
       <c r="G53" s="16" t="n"/>
       <c r="H53" s="21" t="inlineStr">
@@ -4985,7 +4985,7 @@
         <v>140</v>
       </c>
       <c r="M53" s="14" t="n">
-        <v>0.2834616795012835</v>
+        <v>0.286764705882353</v>
       </c>
       <c r="N53" s="12" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>140</v>
       </c>
       <c r="P53" s="14" t="n">
-        <v>0.2834616795012835</v>
+        <v>0.286764705882353</v>
       </c>
       <c r="Q53" s="19" t="inlineStr">
         <is>
@@ -5045,13 +5045,13 @@
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>56.78</v>
+        <v>56.21</v>
       </c>
       <c r="E54" s="25" t="n">
-        <v>-0.124</v>
+        <v>-0.134</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0046</v>
       </c>
       <c r="G54" s="6" t="n">
         <v>46317</v>
@@ -5087,7 +5087,7 @@
         <v>76</v>
       </c>
       <c r="P54" s="5" t="n">
-        <v>0.3384994716449454</v>
+        <v>0.3520725849492973</v>
       </c>
       <c r="Q54" s="9" t="inlineStr">
         <is>
@@ -5128,13 +5128,13 @@
         </is>
       </c>
       <c r="D55" s="13" t="n">
-        <v>136.67</v>
+        <v>139.74</v>
       </c>
       <c r="E55" s="14" t="n">
-        <v>0.078</v>
+        <v>0.09539999999999998</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0.2112</v>
+        <v>0.2182</v>
       </c>
       <c r="G55" s="16" t="n">
         <v>46331</v>
@@ -5163,7 +5163,7 @@
         <v>183</v>
       </c>
       <c r="M55" s="14" t="n">
-        <v>0.338991731908978</v>
+        <v>0.3095749248604551</v>
       </c>
       <c r="N55" s="12" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>145</v>
       </c>
       <c r="P55" s="14" t="n">
-        <v>0.06094973293334319</v>
+        <v>0.03764133390582504</v>
       </c>
       <c r="Q55" s="19" t="inlineStr">
         <is>
@@ -5215,13 +5215,13 @@
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>212.17</v>
+        <v>215.73</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0.0608</v>
+        <v>0.0643</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.154</v>
+        <v>0.1513</v>
       </c>
       <c r="G56" s="6" t="n">
         <v>46325</v>
@@ -5250,7 +5250,7 @@
         <v>222</v>
       </c>
       <c r="M56" s="5" t="n">
-        <v>0.04633077249375507</v>
+        <v>0.02906410791266866</v>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>225</v>
       </c>
       <c r="P56" s="5" t="n">
-        <v>0.06047037752745446</v>
+        <v>0.04297037964121824</v>
       </c>
       <c r="Q56" s="9" t="inlineStr">
         <is>
@@ -5306,13 +5306,13 @@
         </is>
       </c>
       <c r="D57" s="13" t="n">
-        <v>148.54</v>
+        <v>152.43</v>
       </c>
       <c r="E57" s="14" t="n">
-        <v>0.0416</v>
+        <v>0.0429</v>
       </c>
       <c r="F57" s="14" t="n">
-        <v>0.0728</v>
+        <v>0.08960000000000001</v>
       </c>
       <c r="G57" s="16" t="n">
         <v>46331</v>
@@ -5341,7 +5341,7 @@
         <v>196</v>
       </c>
       <c r="M57" s="14" t="n">
-        <v>0.3195098963242225</v>
+        <v>0.2858361214983927</v>
       </c>
       <c r="N57" s="12" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>170</v>
       </c>
       <c r="P57" s="14" t="n">
-        <v>0.1444728692608052</v>
+        <v>0.1152660237486059</v>
       </c>
       <c r="Q57" s="19" t="inlineStr">
         <is>
@@ -5397,13 +5397,13 @@
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="E58" s="25" t="n">
-        <v>-0.0051</v>
+        <v>38.81</v>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>0.0051</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0.0184</v>
+        <v>0.0158</v>
       </c>
       <c r="G58" s="6" t="n">
         <v>46324</v>
@@ -5458,13 +5458,13 @@
         </is>
       </c>
       <c r="D59" s="13" t="n">
-        <v>21.49</v>
+        <v>21.35</v>
       </c>
       <c r="E59" s="14" t="n">
-        <v>0.0209</v>
+        <v>0.0198</v>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0.0639</v>
+        <v>0.0509</v>
       </c>
       <c r="G59" s="16" t="n">
         <v>46330</v>
@@ -5519,13 +5519,13 @@
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>205.72</v>
+        <v>210.7</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0.0161</v>
+        <v>0.0214</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>0.08199999999999999</v>
+        <v>0.0775</v>
       </c>
       <c r="G60" s="6" t="n">
         <v>46328</v>
@@ -5580,13 +5580,13 @@
         </is>
       </c>
       <c r="D61" s="13" t="n">
-        <v>35.01</v>
+        <v>35.31</v>
       </c>
       <c r="E61" s="14" t="n">
-        <v>0.0171</v>
-      </c>
-      <c r="F61" s="15" t="n">
-        <v>-0.0009</v>
+        <v>0.0167</v>
+      </c>
+      <c r="F61" s="14" t="n">
+        <v>0.0026</v>
       </c>
       <c r="G61" s="16" t="n">
         <v>46315</v>
@@ -5622,7 +5622,7 @@
         <v>43</v>
       </c>
       <c r="P61" s="14" t="n">
-        <v>0.228220508426164</v>
+        <v>0.2177853299348626</v>
       </c>
       <c r="Q61" s="19" t="inlineStr">
         <is>
@@ -5667,13 +5667,13 @@
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>30.96</v>
+        <v>30.67</v>
       </c>
       <c r="E62" s="25" t="n">
-        <v>-0.0567</v>
+        <v>-0.0512</v>
       </c>
       <c r="F62" s="25" t="n">
-        <v>-0.0486</v>
+        <v>-0.0503</v>
       </c>
       <c r="G62" s="6" t="n">
         <v>46316</v>
@@ -5702,7 +5702,7 @@
         <v>35</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>0.1304909560723514</v>
+        <v>0.1411803064884251</v>
       </c>
       <c r="N62" s="3" t="inlineStr"/>
       <c r="O62" s="8" t="n"/>
@@ -5746,13 +5746,13 @@
         </is>
       </c>
       <c r="D63" s="13" t="n">
-        <v>257.06</v>
+        <v>262.58</v>
       </c>
       <c r="E63" s="14" t="n">
-        <v>0.1004</v>
+        <v>0.0916</v>
       </c>
       <c r="F63" s="14" t="n">
-        <v>0.2769</v>
+        <v>0.2694</v>
       </c>
       <c r="G63" s="16" t="n">
         <v>46330</v>
@@ -5807,13 +5807,13 @@
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>53.32</v>
+        <v>53.64</v>
       </c>
       <c r="E64" s="25" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>0.1325</v>
+        <v>0.1415</v>
       </c>
       <c r="G64" s="6" t="n">
         <v>46311</v>
@@ -5849,7 +5849,7 @@
         <v>63</v>
       </c>
       <c r="P64" s="5" t="n">
-        <v>0.1815453863465867</v>
+        <v>0.174496644295302</v>
       </c>
       <c r="Q64" s="9" t="inlineStr">
         <is>
@@ -5898,13 +5898,13 @@
         </is>
       </c>
       <c r="D65" s="13" t="n">
-        <v>44.64</v>
+        <v>45.7</v>
       </c>
       <c r="E65" s="14" t="n">
-        <v>0.0556</v>
+        <v>0.0616</v>
       </c>
       <c r="F65" s="14" t="n">
-        <v>0.0132</v>
+        <v>0.0297</v>
       </c>
       <c r="G65" s="16" t="n">
         <v>46328</v>
@@ -5959,13 +5959,13 @@
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>71.95</v>
+        <v>71.42</v>
       </c>
       <c r="E66" s="25" t="n">
-        <v>-0.0432</v>
+        <v>-0.0277</v>
       </c>
       <c r="F66" s="25" t="n">
-        <v>-0.0372</v>
+        <v>-0.0268</v>
       </c>
       <c r="G66" s="6" t="n">
         <v>46328</v>
@@ -5994,7 +5994,7 @@
         <v>89</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>0.2369701181375955</v>
+        <v>0.2461495379445533</v>
       </c>
       <c r="N66" s="3" t="inlineStr"/>
       <c r="O66" s="8" t="n"/>
@@ -6050,13 +6050,13 @@
         </is>
       </c>
       <c r="D67" s="13" t="n">
-        <v>165.08</v>
+        <v>168.45</v>
       </c>
       <c r="E67" s="14" t="n">
-        <v>0.0311</v>
+        <v>0.0433</v>
       </c>
       <c r="F67" s="14" t="n">
-        <v>0.1311</v>
+        <v>0.1431</v>
       </c>
       <c r="G67" s="16" t="n">
         <v>46325</v>
@@ -6085,7 +6085,7 @@
         <v>185</v>
       </c>
       <c r="M67" s="14" t="n">
-        <v>0.1206687666585897</v>
+        <v>0.09824873849807071</v>
       </c>
       <c r="N67" s="12" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>185</v>
       </c>
       <c r="P67" s="14" t="n">
-        <v>0.1206687666585897</v>
+        <v>0.09824873849807071</v>
       </c>
       <c r="Q67" s="19" t="inlineStr">
         <is>
@@ -6141,13 +6141,13 @@
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>117.01</v>
+        <v>116.68</v>
       </c>
       <c r="E68" s="25" t="n">
-        <v>-0.0366</v>
+        <v>-0.0356</v>
       </c>
       <c r="F68" s="25" t="n">
-        <v>-0.0489</v>
+        <v>-0.0645</v>
       </c>
       <c r="G68" s="6" t="n">
         <v>46329</v>
@@ -6176,7 +6176,7 @@
         <v>120</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>0.02555337150670878</v>
+        <v>0.02845389098388749</v>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>115</v>
       </c>
       <c r="P68" s="25" t="n">
-        <v>-0.01717801897273741</v>
+        <v>-0.01439835447377448</v>
       </c>
       <c r="Q68" s="9" t="inlineStr"/>
       <c r="R68" s="8" t="n"/>
@@ -6222,13 +6222,13 @@
         </is>
       </c>
       <c r="D69" s="13" t="n">
-        <v>311.54</v>
+        <v>309.95</v>
       </c>
       <c r="E69" s="15" t="n">
-        <v>-0.1245</v>
+        <v>-0.1073</v>
       </c>
       <c r="F69" s="15" t="n">
-        <v>-0.1549</v>
+        <v>-0.1559</v>
       </c>
       <c r="G69" s="16" t="n">
         <v>46325</v>
@@ -6257,7 +6257,7 @@
         <v>406</v>
       </c>
       <c r="M69" s="14" t="n">
-        <v>0.3032034409706618</v>
+        <v>0.3098886917244718</v>
       </c>
       <c r="N69" s="12" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>436</v>
       </c>
       <c r="P69" s="14" t="n">
-        <v>0.3994992617320408</v>
+        <v>0.4066784965316987</v>
       </c>
       <c r="Q69" s="19" t="inlineStr">
         <is>
@@ -6305,13 +6305,13 @@
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>327.78</v>
+        <v>322.68</v>
       </c>
       <c r="E70" s="25" t="n">
-        <v>-0.0429</v>
+        <v>-0.04019999999999999</v>
       </c>
       <c r="F70" s="25" t="n">
-        <v>-0.0935</v>
+        <v>-0.0919</v>
       </c>
       <c r="G70" s="6" t="n">
         <v>46311</v>
@@ -6340,7 +6340,7 @@
         <v>415</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>0.2660931112331443</v>
+        <v>0.2861038800049585</v>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
         <v>380</v>
       </c>
       <c r="P70" s="5" t="n">
-        <v>0.1593141741411924</v>
+        <v>0.1776372877153836</v>
       </c>
       <c r="Q70" s="9" t="inlineStr">
         <is>
@@ -6400,13 +6400,13 @@
         </is>
       </c>
       <c r="D71" s="13" t="n">
-        <v>59.47</v>
+        <v>59.2</v>
       </c>
       <c r="E71" s="15" t="n">
-        <v>-0.07780000000000001</v>
+        <v>-0.0733</v>
       </c>
       <c r="F71" s="15" t="n">
-        <v>-0.0329</v>
+        <v>-0.0337</v>
       </c>
       <c r="G71" s="16" t="n">
         <v>46309</v>
@@ -6461,13 +6461,13 @@
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>1065.6</v>
+        <v>1050.24</v>
       </c>
       <c r="E72" s="25" t="n">
-        <v>-0.09210000000000002</v>
+        <v>-0.08439999999999999</v>
       </c>
       <c r="F72" s="25" t="n">
-        <v>-0.0197</v>
+        <v>-0.0205</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>46308</v>
@@ -6499,7 +6499,7 @@
         <v>1245</v>
       </c>
       <c r="P72" s="5" t="n">
-        <v>0.168355855855856</v>
+        <v>0.1854433272394881</v>
       </c>
       <c r="Q72" s="9" t="inlineStr">
         <is>
@@ -6544,13 +6544,13 @@
         </is>
       </c>
       <c r="D73" s="13" t="n">
-        <v>37.62</v>
+        <v>35.81</v>
       </c>
       <c r="E73" s="14" t="n">
-        <v>0.5424</v>
+        <v>0.4349</v>
       </c>
       <c r="F73" s="14" t="n">
-        <v>0.6111</v>
+        <v>0.5982</v>
       </c>
       <c r="G73" s="16" t="n"/>
       <c r="H73" s="21" t="inlineStr">
@@ -6595,13 +6595,13 @@
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>25.76</v>
+        <v>23.95</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>0.4248</v>
+        <v>0.279</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>0.6684</v>
+        <v>0.5268</v>
       </c>
       <c r="G74" s="6" t="n">
         <v>46346</v>
@@ -6656,13 +6656,13 @@
         </is>
       </c>
       <c r="D75" s="13" t="n">
-        <v>514.95</v>
+        <v>515.03</v>
       </c>
       <c r="E75" s="14" t="n">
-        <v>0.0217</v>
+        <v>0.0337</v>
       </c>
       <c r="F75" s="14" t="n">
-        <v>0.0443</v>
+        <v>0.0491</v>
       </c>
       <c r="G75" s="16" t="n">
         <v>46332</v>
@@ -6739,13 +6739,13 @@
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>68.33</v>
+        <v>68.11</v>
       </c>
       <c r="E76" s="25" t="n">
-        <v>-0.0313</v>
+        <v>-0.011</v>
       </c>
       <c r="F76" s="25" t="n">
-        <v>-0.016</v>
+        <v>-0.018</v>
       </c>
       <c r="G76" s="6" t="n">
         <v>46321</v>
@@ -6774,7 +6774,7 @@
         <v>68</v>
       </c>
       <c r="M76" s="25" t="n">
-        <v>-0.004829503878237938</v>
+        <v>-0.001615034503009829</v>
       </c>
       <c r="N76" s="3" t="inlineStr"/>
       <c r="O76" s="8" t="n"/>
@@ -6816,13 +6816,13 @@
         </is>
       </c>
       <c r="D77" s="13" t="n">
-        <v>128.29</v>
+        <v>127.06</v>
       </c>
       <c r="E77" s="15" t="n">
-        <v>-0.1087</v>
-      </c>
-      <c r="F77" s="15" t="n">
-        <v>-0.0053</v>
+        <v>-0.09609999999999999</v>
+      </c>
+      <c r="F77" s="14" t="n">
+        <v>0.0012</v>
       </c>
       <c r="G77" s="16" t="n">
         <v>46310</v>
@@ -6881,13 +6881,13 @@
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>136.18</v>
+        <v>135.4</v>
       </c>
       <c r="E78" s="25" t="n">
-        <v>-0.0226</v>
+        <v>-0.0225</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>0.0339</v>
+        <v>0.0467</v>
       </c>
       <c r="G78" s="6" t="n">
         <v>46308</v>
@@ -6919,7 +6919,7 @@
         <v>140</v>
       </c>
       <c r="P78" s="5" t="n">
-        <v>0.02805110882655304</v>
+        <v>0.03397341211225993</v>
       </c>
       <c r="Q78" s="9" t="inlineStr">
         <is>
@@ -6968,13 +6968,13 @@
         </is>
       </c>
       <c r="D79" s="13" t="n">
-        <v>341.85</v>
-      </c>
-      <c r="E79" s="15" t="n">
-        <v>-0.0052</v>
+        <v>341.21</v>
+      </c>
+      <c r="E79" s="14" t="n">
+        <v>0.001</v>
       </c>
       <c r="F79" s="15" t="n">
-        <v>-0.0054</v>
+        <v>-0.0311</v>
       </c>
       <c r="G79" s="16" t="n">
         <v>46315</v>
@@ -7003,7 +7003,7 @@
         <v>358</v>
       </c>
       <c r="M79" s="14" t="n">
-        <v>0.04724294281117442</v>
+        <v>0.04920723308226611</v>
       </c>
       <c r="N79" s="12" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>374</v>
       </c>
       <c r="P79" s="14" t="n">
-        <v>0.09404709667983026</v>
+        <v>0.09609917646024449</v>
       </c>
       <c r="Q79" s="19" t="inlineStr">
         <is>
@@ -7059,13 +7059,13 @@
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>58.65</v>
+        <v>58.67</v>
       </c>
       <c r="E80" s="25" t="n">
-        <v>-0.0269</v>
+        <v>-0.0174</v>
       </c>
       <c r="F80" s="25" t="n">
-        <v>-0.0126</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="G80" s="6" t="n">
         <v>46310</v>
@@ -7094,7 +7094,7 @@
         <v>57</v>
       </c>
       <c r="M80" s="25" t="n">
-        <v>-0.02813299232736571</v>
+        <v>-0.02846429180160221</v>
       </c>
       <c r="N80" s="3" t="inlineStr"/>
       <c r="O80" s="8" t="n"/>
@@ -7136,13 +7136,13 @@
         </is>
       </c>
       <c r="D81" s="13" t="n">
-        <v>13.27</v>
+        <v>12.77</v>
       </c>
       <c r="E81" s="14" t="n">
-        <v>0.09759999999999999</v>
-      </c>
-      <c r="F81" s="14" t="n">
-        <v>0.0287</v>
+        <v>0.0302</v>
+      </c>
+      <c r="F81" s="15" t="n">
+        <v>-0.0196</v>
       </c>
       <c r="G81" s="16" t="n"/>
       <c r="H81" s="21" t="inlineStr">
@@ -7187,13 +7187,13 @@
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>412.56</v>
-      </c>
-      <c r="E82" s="25" t="n">
-        <v>-0.0121</v>
+        <v>410.42</v>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>0.0069</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>0.1096</v>
+        <v>0.122</v>
       </c>
       <c r="G82" s="6" t="n">
         <v>46330</v>
@@ -7260,13 +7260,13 @@
         </is>
       </c>
       <c r="D83" s="13" t="n">
-        <v>97.42</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="E83" s="14" t="n">
-        <v>0.3606</v>
+        <v>0.1979</v>
       </c>
       <c r="F83" s="14" t="n">
-        <v>0.6065</v>
+        <v>0.4778</v>
       </c>
       <c r="G83" s="16" t="n"/>
       <c r="H83" s="21" t="inlineStr">
@@ -7311,13 +7311,13 @@
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>45.32</v>
+        <v>44.13</v>
       </c>
       <c r="E84" s="25" t="n">
-        <v>-0.0011</v>
+        <v>-0.0048</v>
       </c>
       <c r="F84" s="25" t="n">
-        <v>-0.1226</v>
+        <v>-0.1227</v>
       </c>
       <c r="G84" s="6" t="n">
         <v>46331</v>
@@ -7372,13 +7372,13 @@
         </is>
       </c>
       <c r="D85" s="13" t="n">
-        <v>988.45</v>
+        <v>957.91</v>
       </c>
       <c r="E85" s="15" t="n">
-        <v>-0.049</v>
+        <v>-0.0888</v>
       </c>
       <c r="F85" s="15" t="n">
-        <v>-0.0977</v>
+        <v>-0.1007</v>
       </c>
       <c r="G85" s="16" t="n">
         <v>46308</v>
@@ -7407,7 +7407,7 @@
         <v>1325</v>
       </c>
       <c r="M85" s="14" t="n">
-        <v>0.3404825737265415</v>
+        <v>0.3832197179275715</v>
       </c>
       <c r="N85" s="12" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>1210</v>
       </c>
       <c r="P85" s="14" t="n">
-        <v>0.2241388031766907</v>
+        <v>0.2631666858055559</v>
       </c>
       <c r="Q85" s="19" t="inlineStr">
         <is>
@@ -7459,13 +7459,13 @@
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>137.82</v>
+        <v>137.46</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.0978</v>
       </c>
       <c r="F86" s="25" t="n">
-        <v>-0.0382</v>
+        <v>-0.0182</v>
       </c>
       <c r="G86" s="6" t="n">
         <v>46324</v>
@@ -7520,13 +7520,13 @@
         </is>
       </c>
       <c r="D87" s="13" t="n">
-        <v>114.33</v>
+        <v>111.09</v>
       </c>
       <c r="E87" s="14" t="n">
-        <v>0.1964</v>
+        <v>0.1542</v>
       </c>
       <c r="F87" s="14" t="n">
-        <v>0.0784</v>
+        <v>0.1113</v>
       </c>
       <c r="G87" s="16" t="n">
         <v>46330</v>
@@ -7581,13 +7581,13 @@
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>91.13</v>
+        <v>88.19</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.0017</v>
       </c>
       <c r="F88" s="25" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0356</v>
       </c>
       <c r="G88" s="6" t="n">
         <v>46329</v>
@@ -7642,13 +7642,13 @@
         </is>
       </c>
       <c r="D89" s="13" t="n">
-        <v>157.75</v>
+        <v>156.42</v>
       </c>
       <c r="E89" s="14" t="n">
-        <v>0.0195</v>
+        <v>0.0137</v>
       </c>
       <c r="F89" s="14" t="n">
-        <v>0.1128</v>
+        <v>0.1201</v>
       </c>
       <c r="G89" s="16" t="n">
         <v>46324</v>
@@ -7703,13 +7703,13 @@
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>164.55</v>
+        <v>165.09</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>0.0733</v>
+        <v>0.1016</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0.0696</v>
+        <v>0.0885</v>
       </c>
       <c r="G90" s="6" t="n">
         <v>46329</v>
@@ -7778,13 +7778,13 @@
         </is>
       </c>
       <c r="D91" s="13" t="n">
-        <v>350.13</v>
+        <v>345.08</v>
       </c>
       <c r="E91" s="15" t="n">
-        <v>-0.035</v>
+        <v>-0.044</v>
       </c>
       <c r="F91" s="14" t="n">
-        <v>0.0203</v>
+        <v>0.0117</v>
       </c>
       <c r="G91" s="16" t="n">
         <v>46308</v>
@@ -7813,7 +7813,7 @@
         <v>196</v>
       </c>
       <c r="M91" s="15" t="n">
-        <v>-0.440207922771542</v>
+        <v>-0.432015764460415</v>
       </c>
       <c r="N91" s="12" t="inlineStr"/>
       <c r="O91" s="18" t="n"/>
@@ -7857,13 +7857,13 @@
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>102.27</v>
+        <v>101.22</v>
       </c>
       <c r="E92" s="25" t="n">
-        <v>-0.103</v>
-      </c>
-      <c r="F92" s="25" t="n">
-        <v>-0.004699999999999999</v>
+        <v>-0.0699</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>0.0028</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>46332</v>
@@ -7892,7 +7892,7 @@
         <v>375</v>
       </c>
       <c r="M92" s="5" t="n">
-        <v>2.666764447051922</v>
+        <v>2.704801422643746</v>
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>368</v>
       </c>
       <c r="P92" s="5" t="n">
-        <v>2.598318177373619</v>
+        <v>2.635645129421063</v>
       </c>
       <c r="Q92" s="9" t="inlineStr">
         <is>
@@ -7956,13 +7956,13 @@
         </is>
       </c>
       <c r="D93" s="13" t="n">
-        <v>363.89</v>
+        <v>364.35</v>
       </c>
       <c r="E93" s="15" t="n">
-        <v>-0.0403</v>
+        <v>-0.0077</v>
       </c>
       <c r="F93" s="14" t="n">
-        <v>0.08460000000000001</v>
+        <v>0.0592</v>
       </c>
       <c r="G93" s="16" t="n">
         <v>46317</v>
@@ -7994,7 +7994,7 @@
         <v>115</v>
       </c>
       <c r="P93" s="15" t="n">
-        <v>-0.6839704306246392</v>
+        <v>-0.6843694250034308</v>
       </c>
       <c r="Q93" s="19" t="inlineStr">
         <is>
@@ -8043,13 +8043,13 @@
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>574.42</v>
+        <v>571.36</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.0162</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0.0415</v>
+        <v>0.05110000000000001</v>
       </c>
       <c r="G94" s="6" t="n">
         <v>46324</v>
@@ -8078,7 +8078,7 @@
         <v>366</v>
       </c>
       <c r="M94" s="25" t="n">
-        <v>-0.3628355558650465</v>
+        <v>-0.3594231307756931</v>
       </c>
       <c r="N94" s="3" t="inlineStr"/>
       <c r="O94" s="8" t="n"/>
@@ -8120,13 +8120,13 @@
         </is>
       </c>
       <c r="D95" s="13" t="n">
-        <v>1798.46</v>
+        <v>1784.35</v>
       </c>
       <c r="E95" s="15" t="n">
-        <v>-0.0264</v>
+        <v>-0.0083</v>
       </c>
       <c r="F95" s="15" t="n">
-        <v>-0.083</v>
+        <v>-0.09539999999999998</v>
       </c>
       <c r="G95" s="16" t="n">
         <v>46330</v>
@@ -8191,13 +8191,13 @@
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>206.58</v>
+        <v>201.02</v>
       </c>
       <c r="E96" s="25" t="n">
-        <v>-0.0496</v>
+        <v>-0.0788</v>
       </c>
       <c r="F96" s="25" t="n">
-        <v>-0.05400000000000001</v>
+        <v>-0.0672</v>
       </c>
       <c r="G96" s="6" t="n">
         <v>46309</v>
@@ -8226,7 +8226,7 @@
         <v>668</v>
       </c>
       <c r="M96" s="5" t="n">
-        <v>2.233614096233904</v>
+        <v>2.323052432593772</v>
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         <v>550</v>
       </c>
       <c r="P96" s="5" t="n">
-        <v>1.662406815761448</v>
+        <v>1.73604616456074</v>
       </c>
       <c r="Q96" s="9" t="inlineStr">
         <is>
@@ -8286,13 +8286,13 @@
         </is>
       </c>
       <c r="D97" s="13" t="n">
-        <v>116.9</v>
+        <v>117.11</v>
       </c>
       <c r="E97" s="14" t="n">
-        <v>0.0256</v>
+        <v>0.0366</v>
       </c>
       <c r="F97" s="14" t="n">
-        <v>0.0334</v>
+        <v>0.0277</v>
       </c>
       <c r="G97" s="16" t="n">
         <v>46321</v>
@@ -8321,7 +8321,7 @@
         <v>240</v>
       </c>
       <c r="M97" s="14" t="n">
-        <v>1.053036783575706</v>
+        <v>1.049355306976347</v>
       </c>
       <c r="N97" s="12" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>240</v>
       </c>
       <c r="P97" s="14" t="n">
-        <v>1.053036783575706</v>
+        <v>1.049355306976347</v>
       </c>
       <c r="Q97" s="19" t="inlineStr">
         <is>
@@ -8381,13 +8381,13 @@
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>242.72</v>
+        <v>240.3</v>
       </c>
       <c r="E98" s="25" t="n">
-        <v>-0.0555</v>
+        <v>-0.05599999999999999</v>
       </c>
       <c r="F98" s="25" t="n">
-        <v>-0.0489</v>
+        <v>-0.04969999999999999</v>
       </c>
       <c r="G98" s="6" t="n">
         <v>46310</v>
@@ -8416,7 +8416,7 @@
         <v>113</v>
       </c>
       <c r="M98" s="25" t="n">
-        <v>-0.5344429795649308</v>
+        <v>-0.5297544735746983</v>
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>114</v>
       </c>
       <c r="P98" s="25" t="n">
-        <v>-0.530323005932762</v>
+        <v>-0.5255930087390762</v>
       </c>
       <c r="Q98" s="9" t="inlineStr"/>
       <c r="R98" s="8" t="n"/>
@@ -8466,13 +8466,13 @@
         </is>
       </c>
       <c r="D99" s="13" t="n">
-        <v>20.95</v>
+        <v>20.11</v>
       </c>
       <c r="E99" s="14" t="n">
-        <v>0.1018</v>
+        <v>0.0037</v>
       </c>
       <c r="F99" s="14" t="n">
-        <v>0.1132</v>
+        <v>0.1016</v>
       </c>
       <c r="G99" s="16" t="n">
         <v>46324</v>
@@ -8527,13 +8527,13 @@
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>14.74</v>
+        <v>14.56</v>
       </c>
       <c r="E100" s="25" t="n">
-        <v>-0.0014</v>
+        <v>-0.0024</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>0.08220000000000001</v>
+        <v>0.0742</v>
       </c>
       <c r="G100" s="6" t="n">
         <v>46323</v>
@@ -8588,13 +8588,13 @@
         </is>
       </c>
       <c r="D101" s="13" t="n">
-        <v>105.51</v>
-      </c>
-      <c r="E101" s="15" t="n">
-        <v>-0.008199999999999999</v>
+        <v>105.5</v>
+      </c>
+      <c r="E101" s="14" t="n">
+        <v>0.0003</v>
       </c>
       <c r="F101" s="14" t="n">
-        <v>0.0524</v>
+        <v>0.063</v>
       </c>
       <c r="G101" s="16" t="n">
         <v>46323</v>
@@ -8623,7 +8623,7 @@
         <v>285</v>
       </c>
       <c r="M101" s="14" t="n">
-        <v>1.701165766278078</v>
+        <v>1.701421800947867</v>
       </c>
       <c r="N101" s="12" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>285</v>
       </c>
       <c r="P101" s="14" t="n">
-        <v>1.701165766278078</v>
+        <v>1.701421800947867</v>
       </c>
       <c r="Q101" s="19" t="inlineStr">
         <is>
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>418.54</v>
-      </c>
-      <c r="E102" s="25" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>413.79</v>
+      </c>
+      <c r="E102" s="5" t="n">
+        <v>0.007900000000000001</v>
       </c>
       <c r="F102" s="25" t="n">
-        <v>-0.0849</v>
+        <v>-0.08220000000000001</v>
       </c>
       <c r="G102" s="6" t="n">
         <v>46324</v>
@@ -8750,13 +8750,13 @@
         </is>
       </c>
       <c r="D103" s="13" t="n">
-        <v>50.1</v>
+        <v>50.66</v>
       </c>
       <c r="E103" s="15" t="n">
-        <v>-0.0565</v>
+        <v>-0.0356</v>
       </c>
       <c r="F103" s="15" t="n">
-        <v>-0.0592</v>
+        <v>-0.035</v>
       </c>
       <c r="G103" s="16" t="n">
         <v>46311</v>
@@ -8811,13 +8811,13 @@
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>375.28</v>
+        <v>374.17</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>0.0306</v>
+        <v>0.04269999999999999</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>0.0278</v>
+        <v>0.0435</v>
       </c>
       <c r="G104" s="6" t="n">
         <v>46322</v>
@@ -8846,7 +8846,7 @@
         <v>525</v>
       </c>
       <c r="M104" s="5" t="n">
-        <v>0.3989554465998722</v>
+        <v>0.4031055402624475</v>
       </c>
       <c r="N104" s="3" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         <v>543</v>
       </c>
       <c r="P104" s="5" t="n">
-        <v>0.4469196333404393</v>
+        <v>0.4512120159285886</v>
       </c>
       <c r="Q104" s="9" t="inlineStr">
         <is>
@@ -8902,13 +8902,13 @@
         </is>
       </c>
       <c r="D105" s="13" t="n">
-        <v>70.87</v>
+        <v>70.77</v>
       </c>
       <c r="E105" s="14" t="n">
-        <v>0.0051</v>
-      </c>
-      <c r="F105" s="14" t="n">
-        <v>0.0139</v>
+        <v>0.0146</v>
+      </c>
+      <c r="F105" s="15" t="n">
+        <v>-0.0117</v>
       </c>
       <c r="G105" s="16" t="n">
         <v>46314</v>
@@ -8937,7 +8937,7 @@
         <v>412</v>
       </c>
       <c r="M105" s="14" t="n">
-        <v>4.81346126710879</v>
+        <v>4.821675851349442</v>
       </c>
       <c r="N105" s="12" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         <v>350</v>
       </c>
       <c r="P105" s="14" t="n">
-        <v>3.938620008466205</v>
+        <v>3.945598417408507</v>
       </c>
       <c r="Q105" s="19" t="inlineStr">
         <is>
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="D106" s="4" t="n">
-        <v>79.48999999999999</v>
+        <v>78.31</v>
       </c>
       <c r="E106" s="25" t="n">
-        <v>-0.0409</v>
+        <v>-0.0236</v>
       </c>
       <c r="F106" s="25" t="n">
-        <v>-0.0249</v>
+        <v>-0.0204</v>
       </c>
       <c r="G106" s="6" t="n">
         <v>46331</v>
@@ -9028,7 +9028,7 @@
         <v>68</v>
       </c>
       <c r="M106" s="25" t="n">
-        <v>-0.1445464838344445</v>
+        <v>-0.1316562380283489</v>
       </c>
       <c r="N106" s="3" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>68</v>
       </c>
       <c r="P106" s="25" t="n">
-        <v>-0.1445464838344445</v>
+        <v>-0.1316562380283489</v>
       </c>
       <c r="Q106" s="9" t="inlineStr">
         <is>
@@ -9084,13 +9084,13 @@
         </is>
       </c>
       <c r="D107" s="13" t="n">
-        <v>261.77</v>
+        <v>261.73</v>
       </c>
       <c r="E107" s="14" t="n">
-        <v>0.0493</v>
+        <v>0.0455</v>
       </c>
       <c r="F107" s="14" t="n">
-        <v>0.029</v>
+        <v>0.0284</v>
       </c>
       <c r="G107" s="16" t="n">
         <v>46325</v>
@@ -9119,7 +9119,7 @@
         <v>295</v>
       </c>
       <c r="M107" s="14" t="n">
-        <v>0.1269435000191008</v>
+        <v>0.1271157299507125</v>
       </c>
       <c r="N107" s="12" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>246</v>
       </c>
       <c r="P107" s="15" t="n">
-        <v>-0.06024372540780067</v>
+        <v>-0.06010010315974484</v>
       </c>
       <c r="Q107" s="19" t="inlineStr">
         <is>
@@ -9167,13 +9167,13 @@
         </is>
       </c>
       <c r="D108" s="4" t="n">
-        <v>103.09</v>
+        <v>101.75</v>
       </c>
       <c r="E108" s="25" t="n">
-        <v>-0.0733</v>
+        <v>-0.0781</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>0.0431</v>
+        <v>0.0106</v>
       </c>
       <c r="G108" s="6" t="n">
         <v>46316</v>
@@ -9202,7 +9202,7 @@
         <v>112</v>
       </c>
       <c r="M108" s="5" t="n">
-        <v>0.08642933359200695</v>
+        <v>0.1007371007371007</v>
       </c>
       <c r="N108" s="3" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         <v>120</v>
       </c>
       <c r="P108" s="5" t="n">
-        <v>0.1640314288485789</v>
+        <v>0.1793611793611794</v>
       </c>
       <c r="Q108" s="9" t="inlineStr">
         <is>
@@ -9266,13 +9266,13 @@
         </is>
       </c>
       <c r="D109" s="13" t="n">
-        <v>381.5</v>
+        <v>376.43</v>
       </c>
       <c r="E109" s="15" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.1024</v>
       </c>
       <c r="F109" s="14" t="n">
-        <v>0.0267</v>
+        <v>0.0277</v>
       </c>
       <c r="G109" s="16" t="n">
         <v>46329</v>
@@ -9301,7 +9301,7 @@
         <v>390</v>
       </c>
       <c r="M109" s="14" t="n">
-        <v>0.02228047182175623</v>
+        <v>0.03604919905427302</v>
       </c>
       <c r="N109" s="12" t="inlineStr">
         <is>
@@ -9349,13 +9349,13 @@
         </is>
       </c>
       <c r="D110" s="4" t="n">
-        <v>182.91</v>
-      </c>
-      <c r="E110" s="25" t="n">
-        <v>-0.0027</v>
+        <v>183.76</v>
+      </c>
+      <c r="E110" s="5" t="n">
+        <v>0.0092</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>0.1437</v>
+        <v>0.1618</v>
       </c>
       <c r="G110" s="6" t="n">
         <v>46331</v>
@@ -9384,7 +9384,7 @@
         <v>161</v>
       </c>
       <c r="M110" s="25" t="n">
-        <v>-0.119785686949866</v>
+        <v>-0.1238572050500653</v>
       </c>
       <c r="N110" s="3" t="inlineStr">
         <is>
@@ -9395,7 +9395,7 @@
         <v>180</v>
       </c>
       <c r="P110" s="25" t="n">
-        <v>-0.01590946367065768</v>
+        <v>-0.02046147148454501</v>
       </c>
       <c r="Q110" s="9" t="inlineStr">
         <is>
@@ -9436,13 +9436,13 @@
         </is>
       </c>
       <c r="D111" s="13" t="n">
-        <v>45.05</v>
+        <v>43.82</v>
       </c>
       <c r="E111" s="15" t="n">
-        <v>-0.1308</v>
-      </c>
-      <c r="F111" s="14" t="n">
-        <v>0.009599999999999999</v>
+        <v>-0.148</v>
+      </c>
+      <c r="F111" s="15" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="G111" s="16" t="n">
         <v>46323</v>
@@ -9471,7 +9471,7 @@
         <v>55</v>
       </c>
       <c r="M111" s="14" t="n">
-        <v>0.2208657047724751</v>
+        <v>0.2551346417161113</v>
       </c>
       <c r="N111" s="12" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>65</v>
       </c>
       <c r="P111" s="14" t="n">
-        <v>0.4428412874583797</v>
+        <v>0.4833409402099498</v>
       </c>
       <c r="Q111" s="19" t="inlineStr">
         <is>
@@ -9523,13 +9523,13 @@
         </is>
       </c>
       <c r="D112" s="4" t="n">
-        <v>326.23</v>
+        <v>322.39</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0.0395</v>
+        <v>0.0316</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>0.0592</v>
+        <v>0.0471</v>
       </c>
       <c r="G112" s="6" t="n">
         <v>46330</v>
@@ -9558,7 +9558,7 @@
         <v>331</v>
       </c>
       <c r="M112" s="5" t="n">
-        <v>0.01462158599760899</v>
+        <v>0.02670678370917216</v>
       </c>
       <c r="N112" s="3" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>330</v>
       </c>
       <c r="P112" s="5" t="n">
-        <v>0.01155626398553162</v>
+        <v>0.02360495052576077</v>
       </c>
       <c r="Q112" s="9" t="inlineStr">
         <is>
@@ -9618,13 +9618,13 @@
         </is>
       </c>
       <c r="D113" s="13" t="n">
-        <v>95.55</v>
-      </c>
-      <c r="E113" s="15" t="n">
-        <v>-0.0166</v>
+        <v>94.25</v>
+      </c>
+      <c r="E113" s="14" t="n">
+        <v>0.0026</v>
       </c>
       <c r="F113" s="15" t="n">
-        <v>-0.1028</v>
+        <v>-0.123</v>
       </c>
       <c r="G113" s="16" t="n">
         <v>46330</v>
@@ -9653,7 +9653,7 @@
         <v>123</v>
       </c>
       <c r="M113" s="14" t="n">
-        <v>0.2872841444270016</v>
+        <v>0.3050397877984085</v>
       </c>
       <c r="N113" s="12" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>130</v>
       </c>
       <c r="P113" s="14" t="n">
-        <v>0.3605442176870749</v>
+        <v>0.3793103448275862</v>
       </c>
       <c r="Q113" s="19" t="inlineStr">
         <is>
@@ -9705,13 +9705,13 @@
         </is>
       </c>
       <c r="D114" s="4" t="n">
-        <v>203.25</v>
+        <v>207.38</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="F114" s="25" t="n">
-        <v>-0.0086</v>
+        <v>0.0234</v>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>0.0174</v>
       </c>
       <c r="G114" s="6" t="n">
         <v>46315</v>
@@ -9740,7 +9740,7 @@
         <v>212</v>
       </c>
       <c r="M114" s="5" t="n">
-        <v>0.04305043050430504</v>
+        <v>0.02227794387115442</v>
       </c>
       <c r="N114" s="3" t="inlineStr">
         <is>
@@ -9750,8 +9750,8 @@
       <c r="O114" s="8" t="n">
         <v>205</v>
       </c>
-      <c r="P114" s="5" t="n">
-        <v>0.008610086100861008</v>
+      <c r="P114" s="25" t="n">
+        <v>-0.01147651653968558</v>
       </c>
       <c r="Q114" s="9" t="inlineStr">
         <is>
@@ -9796,13 +9796,13 @@
         </is>
       </c>
       <c r="D115" s="13" t="n">
-        <v>84.68000000000001</v>
+        <v>85.33</v>
       </c>
       <c r="E115" s="15" t="n">
-        <v>-0.0565</v>
+        <v>-0.0386</v>
       </c>
       <c r="F115" s="14" t="n">
-        <v>0.0859</v>
+        <v>0.1132</v>
       </c>
       <c r="G115" s="16" t="n">
         <v>46324</v>
@@ -9830,8 +9830,8 @@
       <c r="L115" s="18" t="n">
         <v>85</v>
       </c>
-      <c r="M115" s="14" t="n">
-        <v>0.003778932451582347</v>
+      <c r="M115" s="15" t="n">
+        <v>-0.003867338567912789</v>
       </c>
       <c r="N115" s="12" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>90</v>
       </c>
       <c r="P115" s="14" t="n">
-        <v>0.06282475200755779</v>
+        <v>0.05472870033985704</v>
       </c>
       <c r="Q115" s="19" t="inlineStr">
         <is>
@@ -9883,13 +9883,13 @@
         </is>
       </c>
       <c r="D116" s="4" t="n">
-        <v>146.41</v>
+        <v>144.54</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0.0582</v>
+        <v>0.0405</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>0.0742</v>
+        <v>0.0764</v>
       </c>
       <c r="G116" s="6" t="n">
         <v>46324</v>
@@ -9918,7 +9918,7 @@
         <v>165</v>
       </c>
       <c r="M116" s="5" t="n">
-        <v>0.1269722013523667</v>
+        <v>0.1415525114155252</v>
       </c>
       <c r="N116" s="3" t="inlineStr"/>
       <c r="O116" s="8" t="n"/>
@@ -9966,13 +9966,13 @@
         </is>
       </c>
       <c r="D117" s="13" t="n">
-        <v>509.56</v>
+        <v>508.26</v>
       </c>
       <c r="E117" s="15" t="n">
-        <v>-0.0751</v>
+        <v>-0.0693</v>
       </c>
       <c r="F117" s="15" t="n">
-        <v>-0.1155</v>
+        <v>-0.1043</v>
       </c>
       <c r="G117" s="16" t="n">
         <v>46328</v>
@@ -10037,13 +10037,13 @@
         </is>
       </c>
       <c r="D118" s="4" t="n">
-        <v>377.94</v>
+        <v>371.98</v>
       </c>
       <c r="E118" s="25" t="n">
-        <v>-0.042</v>
-      </c>
-      <c r="F118" s="25" t="n">
-        <v>-0.06059999999999999</v>
+        <v>-0.047</v>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>0.07690000000000001</v>
       </c>
       <c r="G118" s="6" t="n">
         <v>46315</v>
@@ -10072,7 +10072,7 @@
         <v>487</v>
       </c>
       <c r="M118" s="5" t="n">
-        <v>0.2885643223792136</v>
+        <v>0.3092101725899241</v>
       </c>
       <c r="N118" s="3" t="inlineStr">
         <is>
@@ -10082,8 +10082,8 @@
       <c r="O118" s="8" t="n">
         <v>375</v>
       </c>
-      <c r="P118" s="25" t="n">
-        <v>-0.007779012541673276</v>
+      <c r="P118" s="5" t="n">
+        <v>0.008118716060003176</v>
       </c>
       <c r="Q118" s="9" t="inlineStr">
         <is>
@@ -10128,13 +10128,13 @@
         </is>
       </c>
       <c r="D119" s="13" t="n">
-        <v>266.32</v>
+        <v>263.48</v>
       </c>
       <c r="E119" s="14" t="n">
-        <v>0.0229</v>
+        <v>0.0042</v>
       </c>
       <c r="F119" s="14" t="n">
-        <v>0.0654</v>
+        <v>0.0412</v>
       </c>
       <c r="G119" s="16" t="n">
         <v>46308</v>
@@ -10163,7 +10163,7 @@
         <v>272</v>
       </c>
       <c r="M119" s="14" t="n">
-        <v>0.02132772604385704</v>
+        <v>0.03233642022164863</v>
       </c>
       <c r="N119" s="12" t="inlineStr"/>
       <c r="O119" s="18" t="n"/>
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="D120" s="4" t="n">
-        <v>1138.28</v>
+        <v>1143.4</v>
       </c>
       <c r="E120" s="25" t="n">
-        <v>-0.0355</v>
+        <v>-0.0336</v>
       </c>
       <c r="F120" s="25" t="n">
-        <v>-0.0264</v>
+        <v>-0.0303</v>
       </c>
       <c r="G120" s="6" t="n">
         <v>46324</v>
@@ -10250,7 +10250,7 @@
         <v>1280</v>
       </c>
       <c r="M120" s="5" t="n">
-        <v>0.1245036370664512</v>
+        <v>0.1194682525800244</v>
       </c>
       <c r="N120" s="3" t="inlineStr">
         <is>
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="D121" s="13" t="n">
-        <v>93.8</v>
+        <v>93.61</v>
       </c>
       <c r="E121" s="14" t="n">
-        <v>0.0277</v>
+        <v>0.0332</v>
       </c>
       <c r="F121" s="14" t="n">
-        <v>0.1225</v>
+        <v>0.1251</v>
       </c>
       <c r="G121" s="16" t="n"/>
       <c r="H121" s="21" t="inlineStr">
@@ -10335,7 +10335,7 @@
         <v>102</v>
       </c>
       <c r="M121" s="14" t="n">
-        <v>0.08742004264392328</v>
+        <v>0.08962717658369833</v>
       </c>
       <c r="N121" s="12" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         <v>105</v>
       </c>
       <c r="P121" s="14" t="n">
-        <v>0.1194029850746269</v>
+        <v>0.121675034718513</v>
       </c>
       <c r="Q121" s="19" t="inlineStr">
         <is>
@@ -10387,13 +10387,13 @@
         </is>
       </c>
       <c r="D122" s="4" t="n">
-        <v>144.85</v>
+        <v>143.29</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0.0663</v>
+        <v>0.0538</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>0.1349</v>
+        <v>0.1238</v>
       </c>
       <c r="G122" s="6" t="n">
         <v>46324</v>
@@ -10422,7 +10422,7 @@
         <v>150</v>
       </c>
       <c r="M122" s="5" t="n">
-        <v>0.03555402140144982</v>
+        <v>0.04682811082420273</v>
       </c>
       <c r="N122" s="3" t="inlineStr"/>
       <c r="O122" s="8" t="n"/>
@@ -10466,13 +10466,13 @@
         </is>
       </c>
       <c r="D123" s="13" t="n">
-        <v>138.99</v>
+        <v>138.56</v>
       </c>
       <c r="E123" s="15" t="n">
-        <v>-0.0788</v>
+        <v>-0.0882</v>
       </c>
       <c r="F123" s="15" t="n">
-        <v>-0.09</v>
+        <v>-0.0989</v>
       </c>
       <c r="G123" s="16" t="n">
         <v>46322</v>
@@ -10545,13 +10545,13 @@
         </is>
       </c>
       <c r="D124" s="4" t="n">
-        <v>27.72</v>
+        <v>27.51</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0.0347</v>
+        <v>0.0238</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>0.1026</v>
+        <v>0.09820000000000001</v>
       </c>
       <c r="G124" s="6" t="n">
         <v>46329</v>
@@ -10580,7 +10580,7 @@
         <v>28</v>
       </c>
       <c r="M124" s="5" t="n">
-        <v>0.01010101010101014</v>
+        <v>0.01781170483460554</v>
       </c>
       <c r="N124" s="3" t="inlineStr"/>
       <c r="O124" s="8" t="n"/>
@@ -10624,13 +10624,13 @@
         </is>
       </c>
       <c r="D125" s="13" t="n">
-        <v>281.87</v>
+        <v>280.2</v>
       </c>
       <c r="E125" s="15" t="n">
-        <v>-0.169</v>
+        <v>-0.1552</v>
       </c>
       <c r="F125" s="15" t="n">
-        <v>-0.1489</v>
+        <v>-0.124</v>
       </c>
       <c r="G125" s="16" t="n">
         <v>46324</v>
@@ -10659,7 +10659,7 @@
         <v>418</v>
       </c>
       <c r="M125" s="14" t="n">
-        <v>0.4829531344236704</v>
+        <v>0.4917915774446824</v>
       </c>
       <c r="N125" s="12" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>350</v>
       </c>
       <c r="P125" s="14" t="n">
-        <v>0.2417071699719729</v>
+        <v>0.2491077801570308</v>
       </c>
       <c r="Q125" s="19" t="inlineStr">
         <is>
@@ -10715,13 +10715,13 @@
         </is>
       </c>
       <c r="D126" s="4" t="n">
-        <v>613.62</v>
+        <v>633.84</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>0.0431</v>
+        <v>0.0825</v>
       </c>
       <c r="F126" s="5" t="n">
-        <v>0.1297</v>
+        <v>0.1904</v>
       </c>
       <c r="G126" s="6" t="n">
         <v>46323</v>
@@ -10749,8 +10749,8 @@
       <c r="L126" s="8" t="n">
         <v>615</v>
       </c>
-      <c r="M126" s="5" t="n">
-        <v>0.002248948860858504</v>
+      <c r="M126" s="25" t="n">
+        <v>-0.02972358954941315</v>
       </c>
       <c r="N126" s="3" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>570</v>
       </c>
       <c r="P126" s="25" t="n">
-        <v>-0.07108634008017992</v>
+        <v>-0.1007194244604317</v>
       </c>
       <c r="Q126" s="9" t="inlineStr">
         <is>
@@ -10810,13 +10810,13 @@
         </is>
       </c>
       <c r="D127" s="13" t="n">
-        <v>383.55</v>
+        <v>377.61</v>
       </c>
       <c r="E127" s="15" t="n">
-        <v>-0.0453</v>
+        <v>-0.0455</v>
       </c>
       <c r="F127" s="15" t="n">
-        <v>-0.0941</v>
+        <v>-0.1138</v>
       </c>
       <c r="G127" s="16" t="n">
         <v>46322</v>
@@ -10845,7 +10845,7 @@
         <v>526</v>
       </c>
       <c r="M127" s="14" t="n">
-        <v>0.3713987746056576</v>
+        <v>0.3929715844389714</v>
       </c>
       <c r="N127" s="12" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>480</v>
       </c>
       <c r="P127" s="14" t="n">
-        <v>0.2514665623777864</v>
+        <v>0.2711527766743465</v>
       </c>
       <c r="Q127" s="19" t="inlineStr">
         <is>
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="D128" s="4" t="n">
-        <v>73.67</v>
-      </c>
-      <c r="E128" s="25" t="n">
-        <v>-0.0016</v>
+        <v>73.51000000000001</v>
+      </c>
+      <c r="E128" s="5" t="n">
+        <v>0.0074</v>
       </c>
       <c r="F128" s="25" t="n">
-        <v>-0.0421</v>
+        <v>-0.0398</v>
       </c>
       <c r="G128" s="6" t="n">
         <v>46329</v>
@@ -10980,13 +10980,13 @@
         </is>
       </c>
       <c r="D129" s="13" t="n">
-        <v>276.63</v>
+        <v>276.54</v>
       </c>
       <c r="E129" s="14" t="n">
-        <v>0.0134</v>
+        <v>0.0394</v>
       </c>
       <c r="F129" s="14" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.0833</v>
       </c>
       <c r="G129" s="16" t="n">
         <v>46330</v>
@@ -11015,7 +11015,7 @@
         <v>248</v>
       </c>
       <c r="M129" s="15" t="n">
-        <v>-0.1034956440010122</v>
+        <v>-0.1032038764735663</v>
       </c>
       <c r="N129" s="12" t="inlineStr"/>
       <c r="O129" s="18" t="n"/>
@@ -11071,13 +11071,13 @@
         </is>
       </c>
       <c r="D130" s="4" t="n">
-        <v>122.3</v>
+        <v>124.43</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>0.2069</v>
+        <v>0.2474</v>
       </c>
       <c r="F130" s="5" t="n">
-        <v>0.0603</v>
+        <v>0.0789</v>
       </c>
       <c r="G130" s="6" t="n">
         <v>46325</v>
@@ -11132,13 +11132,13 @@
         </is>
       </c>
       <c r="D131" s="13" t="n">
-        <v>233.65</v>
+        <v>232.38</v>
       </c>
       <c r="E131" s="15" t="n">
-        <v>-0.083</v>
+        <v>-0.0857</v>
       </c>
       <c r="F131" s="15" t="n">
-        <v>-0.0154</v>
+        <v>-0.0195</v>
       </c>
       <c r="G131" s="16" t="n">
         <v>46324</v>
@@ -11193,13 +11193,13 @@
         </is>
       </c>
       <c r="D132" s="4" t="n">
-        <v>210.27</v>
+        <v>209.09</v>
       </c>
       <c r="E132" s="25" t="n">
-        <v>-0.0924</v>
+        <v>-0.0746</v>
       </c>
       <c r="F132" s="25" t="n">
-        <v>-0.019</v>
+        <v>-0.0231</v>
       </c>
       <c r="G132" s="6" t="n">
         <v>46330</v>
@@ -11228,7 +11228,7 @@
         <v>250</v>
       </c>
       <c r="M132" s="5" t="n">
-        <v>0.1889475436343748</v>
+        <v>0.1956573724233583</v>
       </c>
       <c r="N132" s="3" t="inlineStr"/>
       <c r="O132" s="8" t="n"/>
@@ -11272,13 +11272,13 @@
         </is>
       </c>
       <c r="D133" s="13" t="n">
-        <v>174.39</v>
+        <v>171.38</v>
       </c>
       <c r="E133" s="14" t="n">
-        <v>0.0198</v>
+        <v>0.0211</v>
       </c>
       <c r="F133" s="14" t="n">
-        <v>0.1394</v>
+        <v>0.1432</v>
       </c>
       <c r="G133" s="16" t="n">
         <v>46329</v>
@@ -11343,13 +11343,13 @@
         </is>
       </c>
       <c r="D134" s="4" t="n">
-        <v>784</v>
+        <v>780.73</v>
       </c>
       <c r="E134" s="25" t="n">
-        <v>-0.08470000000000001</v>
+        <v>-0.1145</v>
       </c>
       <c r="F134" s="25" t="n">
-        <v>-0.1062</v>
+        <v>-0.1131</v>
       </c>
       <c r="G134" s="6" t="n">
         <v>46330</v>
@@ -11378,7 +11378,7 @@
         <v>1155</v>
       </c>
       <c r="M134" s="5" t="n">
-        <v>0.4732142857142857</v>
+        <v>0.479384678441971</v>
       </c>
       <c r="N134" s="3" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>1103</v>
       </c>
       <c r="P134" s="5" t="n">
-        <v>0.4068877551020408</v>
+        <v>0.4127803465986961</v>
       </c>
       <c r="Q134" s="9" t="inlineStr">
         <is>
@@ -11430,13 +11430,13 @@
         </is>
       </c>
       <c r="D135" s="13" t="n">
-        <v>541.1</v>
+        <v>533.8099999999999</v>
       </c>
       <c r="E135" s="15" t="n">
-        <v>-0.1428</v>
+        <v>-0.1674</v>
       </c>
       <c r="F135" s="15" t="n">
-        <v>-0.1648</v>
+        <v>-0.1768</v>
       </c>
       <c r="G135" s="16" t="n">
         <v>46331</v>
@@ -11465,7 +11465,7 @@
         <v>874</v>
       </c>
       <c r="M135" s="14" t="n">
-        <v>0.61522823877287</v>
+        <v>0.6372866750341883</v>
       </c>
       <c r="N135" s="12" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>845</v>
       </c>
       <c r="P135" s="14" t="n">
-        <v>0.56163370911107</v>
+        <v>0.5829602292950677</v>
       </c>
       <c r="Q135" s="19" t="inlineStr">
         <is>
@@ -11525,13 +11525,13 @@
         </is>
       </c>
       <c r="D136" s="4" t="n">
-        <v>200.82</v>
+        <v>201.15</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0169</v>
       </c>
       <c r="F136" s="25" t="n">
-        <v>-0.0263</v>
+        <v>-0.0161</v>
       </c>
       <c r="G136" s="6" t="n">
         <v>46288</v>
@@ -11560,7 +11560,7 @@
         <v>250</v>
       </c>
       <c r="M136" s="5" t="n">
-        <v>0.2448959267005279</v>
+        <v>0.2428535918468804</v>
       </c>
       <c r="N136" s="3" t="inlineStr"/>
       <c r="O136" s="8" t="n"/>
@@ -11604,13 +11604,13 @@
         </is>
       </c>
       <c r="D137" s="13" t="n">
-        <v>681.46</v>
+        <v>685.16</v>
       </c>
       <c r="E137" s="14" t="n">
-        <v>0.1193</v>
+        <v>0.1421</v>
       </c>
       <c r="F137" s="14" t="n">
-        <v>0.1377</v>
+        <v>0.1472</v>
       </c>
       <c r="G137" s="16" t="n"/>
       <c r="H137" s="21" t="inlineStr">
@@ -11629,7 +11629,7 @@
         <v>750</v>
       </c>
       <c r="M137" s="14" t="n">
-        <v>0.1005781703988495</v>
+        <v>0.09463482982077184</v>
       </c>
       <c r="N137" s="12" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>641.29</v>
       </c>
       <c r="P137" s="15" t="n">
-        <v>-0.05894696680656249</v>
+        <v>-0.06402883997898302</v>
       </c>
       <c r="Q137" s="19" t="inlineStr">
         <is>
@@ -11681,13 +11681,13 @@
         </is>
       </c>
       <c r="D138" s="4" t="n">
-        <v>148.3</v>
+        <v>146.04</v>
       </c>
       <c r="E138" s="25" t="n">
-        <v>-0.0911</v>
+        <v>-0.09880000000000001</v>
       </c>
       <c r="F138" s="5" t="n">
-        <v>0.0663</v>
+        <v>0.0466</v>
       </c>
       <c r="G138" s="6" t="n">
         <v>46330</v>
@@ -11723,7 +11723,7 @@
         <v>185</v>
       </c>
       <c r="P138" s="5" t="n">
-        <v>0.2474713418745784</v>
+        <v>0.2667762256915914</v>
       </c>
       <c r="Q138" s="9" t="inlineStr">
         <is>
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="D139" s="13" t="n">
-        <v>393.16</v>
+        <v>390.58</v>
       </c>
       <c r="E139" s="15" t="n">
-        <v>-0.1292</v>
+        <v>-0.1423</v>
       </c>
       <c r="F139" s="15" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0235</v>
       </c>
       <c r="G139" s="16" t="n">
         <v>46329</v>
@@ -11804,7 +11804,7 @@
         <v>453</v>
       </c>
       <c r="P139" s="14" t="n">
-        <v>0.1522026655814426</v>
+        <v>0.1598136105279329</v>
       </c>
       <c r="Q139" s="19" t="inlineStr">
         <is>
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="D140" s="4" t="n">
-        <v>49.44</v>
+        <v>48.97</v>
       </c>
       <c r="E140" s="25" t="n">
-        <v>-0.031</v>
+        <v>-0.0441</v>
       </c>
       <c r="F140" s="5" t="n">
-        <v>0.0594</v>
+        <v>0.0765</v>
       </c>
       <c r="G140" s="6" t="n">
         <v>46309</v>
@@ -11924,13 +11924,13 @@
         </is>
       </c>
       <c r="D141" s="13" t="n">
-        <v>312.57</v>
+        <v>308.39</v>
       </c>
       <c r="E141" s="15" t="n">
-        <v>-0.066</v>
+        <v>-0.0697</v>
       </c>
       <c r="F141" s="15" t="n">
-        <v>-0.0177</v>
+        <v>-0.0147</v>
       </c>
       <c r="G141" s="16" t="n">
         <v>46282</v>
@@ -11959,7 +11959,7 @@
         <v>425</v>
       </c>
       <c r="M141" s="14" t="n">
-        <v>0.3596954282240779</v>
+        <v>0.3781251013327281</v>
       </c>
       <c r="N141" s="12" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>323</v>
       </c>
       <c r="P141" s="14" t="n">
-        <v>0.03336852545029916</v>
+        <v>0.04737507701287336</v>
       </c>
       <c r="Q141" s="19" t="inlineStr">
         <is>
@@ -12011,13 +12011,13 @@
         </is>
       </c>
       <c r="D142" s="4" t="n">
-        <v>222.31</v>
+        <v>215.8</v>
       </c>
       <c r="E142" s="25" t="n">
-        <v>-0.0924</v>
+        <v>-0.1191</v>
       </c>
       <c r="F142" s="25" t="n">
-        <v>-0.0504</v>
+        <v>-0.0699</v>
       </c>
       <c r="G142" s="6" t="n"/>
       <c r="H142" s="7" t="inlineStr">
@@ -12036,7 +12036,7 @@
         <v>285</v>
       </c>
       <c r="M142" s="5" t="n">
-        <v>0.2819936125230534</v>
+        <v>0.3206672845227062</v>
       </c>
       <c r="N142" s="3" t="inlineStr"/>
       <c r="O142" s="8" t="n"/>
@@ -12084,13 +12084,13 @@
         </is>
       </c>
       <c r="D143" s="13" t="n">
-        <v>1582.8</v>
+        <v>1590.55</v>
       </c>
       <c r="E143" s="15" t="n">
-        <v>-0.1078</v>
+        <v>-0.1545</v>
       </c>
       <c r="F143" s="15" t="n">
-        <v>-0.0582</v>
+        <v>-0.0499</v>
       </c>
       <c r="G143" s="16" t="n">
         <v>46317</v>
@@ -12145,13 +12145,13 @@
         </is>
       </c>
       <c r="D144" s="4" t="n">
-        <v>53.51</v>
-      </c>
-      <c r="E144" s="5" t="n">
-        <v>0.0218</v>
+        <v>53.72</v>
+      </c>
+      <c r="E144" s="25" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F144" s="5" t="n">
-        <v>0.0808</v>
+        <v>0.0946</v>
       </c>
       <c r="G144" s="6" t="n">
         <v>46332</v>
@@ -12206,13 +12206,13 @@
         </is>
       </c>
       <c r="D145" s="13" t="n">
-        <v>356.81</v>
+        <v>356.48</v>
       </c>
       <c r="E145" s="15" t="n">
-        <v>-0.09849999999999999</v>
+        <v>-0.0886</v>
       </c>
       <c r="F145" s="15" t="n">
-        <v>-0.0326</v>
+        <v>-0.0328</v>
       </c>
       <c r="G145" s="16" t="n">
         <v>46318</v>
@@ -12241,7 +12241,7 @@
         <v>400</v>
       </c>
       <c r="M145" s="14" t="n">
-        <v>0.1210448137664303</v>
+        <v>0.1220825852782764</v>
       </c>
       <c r="N145" s="12" t="inlineStr"/>
       <c r="O145" s="18" t="n"/>
@@ -12293,13 +12293,13 @@
         </is>
       </c>
       <c r="D146" s="4" t="n">
-        <v>317.56</v>
+        <v>309.03</v>
       </c>
       <c r="E146" s="25" t="n">
-        <v>-0.138</v>
+        <v>-0.1635</v>
       </c>
       <c r="F146" s="25" t="n">
-        <v>-0.0815</v>
+        <v>-0.1141</v>
       </c>
       <c r="G146" s="6" t="n">
         <v>46315</v>
@@ -12328,7 +12328,7 @@
         <v>390</v>
       </c>
       <c r="M146" s="5" t="n">
-        <v>0.2281143720871646</v>
+        <v>0.2620133967575964</v>
       </c>
       <c r="N146" s="3" t="inlineStr"/>
       <c r="O146" s="8" t="n"/>
@@ -12380,13 +12380,13 @@
         </is>
       </c>
       <c r="D147" s="13" t="n">
-        <v>874.76</v>
+        <v>878.21</v>
       </c>
       <c r="E147" s="15" t="n">
-        <v>-0.1773</v>
+        <v>-0.1861</v>
       </c>
       <c r="F147" s="15" t="n">
-        <v>-0.1558</v>
+        <v>-0.1698</v>
       </c>
       <c r="G147" s="16" t="n">
         <v>46316</v>
@@ -12415,7 +12415,7 @@
         <v>1259</v>
       </c>
       <c r="M147" s="14" t="n">
-        <v>0.4392519090950661</v>
+        <v>0.433597886610264</v>
       </c>
       <c r="N147" s="12" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>1350</v>
       </c>
       <c r="P147" s="14" t="n">
-        <v>0.5432804426356944</v>
+        <v>0.5372177497409503</v>
       </c>
       <c r="Q147" s="19" t="inlineStr">
         <is>
@@ -12471,13 +12471,13 @@
         </is>
       </c>
       <c r="D148" s="4" t="n">
-        <v>1277.51</v>
+        <v>1270.92</v>
       </c>
       <c r="E148" s="25" t="n">
-        <v>-0.0341</v>
+        <v>-0.0355</v>
       </c>
       <c r="F148" s="25" t="n">
-        <v>-0.0888</v>
+        <v>-0.08900000000000001</v>
       </c>
       <c r="G148" s="6" t="n">
         <v>46325</v>
@@ -12546,13 +12546,13 @@
         </is>
       </c>
       <c r="D149" s="13" t="n">
-        <v>201.38</v>
+        <v>200.59</v>
       </c>
       <c r="E149" s="15" t="n">
-        <v>-0.1393</v>
+        <v>-0.1258</v>
       </c>
       <c r="F149" s="15" t="n">
-        <v>-0.1102</v>
+        <v>-0.1086</v>
       </c>
       <c r="G149" s="16" t="n">
         <v>46317</v>
@@ -12607,13 +12607,13 @@
         </is>
       </c>
       <c r="D150" s="4" t="n">
-        <v>442.38</v>
+        <v>438.42</v>
       </c>
       <c r="E150" s="25" t="n">
-        <v>-0.1349</v>
+        <v>-0.1306</v>
       </c>
       <c r="F150" s="25" t="n">
-        <v>-0.0823</v>
+        <v>-0.1028</v>
       </c>
       <c r="G150" s="6" t="n">
         <v>46322</v>
@@ -12674,13 +12674,13 @@
         </is>
       </c>
       <c r="D151" s="13" t="n">
-        <v>269.04</v>
+        <v>266.79</v>
       </c>
       <c r="E151" s="15" t="n">
-        <v>-0.07490000000000001</v>
+        <v>-0.0713</v>
       </c>
       <c r="F151" s="15" t="n">
-        <v>-0.0492</v>
+        <v>-0.0335</v>
       </c>
       <c r="G151" s="16" t="n">
         <v>46318</v>
@@ -12712,7 +12712,7 @@
         <v>272</v>
       </c>
       <c r="P151" s="14" t="n">
-        <v>0.01100208147487355</v>
+        <v>0.0195284680835113</v>
       </c>
       <c r="Q151" s="19" t="inlineStr">
         <is>
@@ -12765,13 +12765,13 @@
         </is>
       </c>
       <c r="D152" s="4" t="n">
-        <v>248.93</v>
+        <v>249.71</v>
       </c>
       <c r="E152" s="25" t="n">
-        <v>-0.147</v>
+        <v>-0.103</v>
       </c>
       <c r="F152" s="25" t="n">
-        <v>-0.1248</v>
+        <v>-0.1145</v>
       </c>
       <c r="G152" s="6" t="n">
         <v>46324</v>
@@ -12836,13 +12836,13 @@
         </is>
       </c>
       <c r="D153" s="13" t="n">
-        <v>365.51</v>
+        <v>359.25</v>
       </c>
       <c r="E153" s="15" t="n">
-        <v>-0.1339</v>
+        <v>-0.1367</v>
       </c>
       <c r="F153" s="15" t="n">
-        <v>-0.3456</v>
+        <v>-0.3395</v>
       </c>
       <c r="G153" s="16" t="n">
         <v>46323</v>
@@ -12897,13 +12897,13 @@
         </is>
       </c>
       <c r="D154" s="4" t="n">
-        <v>529.38</v>
+        <v>530.61</v>
       </c>
       <c r="E154" s="25" t="n">
-        <v>-0.1303</v>
+        <v>-0.1063</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>0.0309</v>
+        <v>0.0429</v>
       </c>
       <c r="G154" s="6" t="n">
         <v>46315</v>
@@ -12964,13 +12964,13 @@
         </is>
       </c>
       <c r="D155" s="13" t="n">
-        <v>181.91</v>
+        <v>179.8</v>
       </c>
       <c r="E155" s="15" t="n">
-        <v>-0.1377</v>
+        <v>-0.1517</v>
       </c>
       <c r="F155" s="15" t="n">
-        <v>-0.2329</v>
+        <v>-0.2311</v>
       </c>
       <c r="G155" s="16" t="n">
         <v>46330</v>
@@ -12999,7 +12999,7 @@
         <v>575</v>
       </c>
       <c r="M155" s="14" t="n">
-        <v>2.160903743609477</v>
+        <v>2.197997775305895</v>
       </c>
       <c r="N155" s="12" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>237</v>
       </c>
       <c r="P155" s="14" t="n">
-        <v>0.3028420647572976</v>
+        <v>0.318131256952169</v>
       </c>
       <c r="Q155" s="19" t="inlineStr">
         <is>
@@ -13059,13 +13059,13 @@
         </is>
       </c>
       <c r="D156" s="4" t="n">
-        <v>118.51</v>
+        <v>118.46</v>
       </c>
       <c r="E156" s="25" t="n">
-        <v>-0.0288</v>
+        <v>-0.0007000000000000001</v>
       </c>
       <c r="F156" s="5" t="n">
-        <v>0.0332</v>
+        <v>0.0356</v>
       </c>
       <c r="G156" s="6" t="n">
         <v>46288</v>
@@ -13094,7 +13094,7 @@
         <v>250</v>
       </c>
       <c r="M156" s="5" t="n">
-        <v>1.109526622225973</v>
+        <v>1.110417018402837</v>
       </c>
       <c r="N156" s="3" t="inlineStr"/>
       <c r="O156" s="8" t="n"/>
@@ -13138,13 +13138,13 @@
         </is>
       </c>
       <c r="D157" s="13" t="n">
-        <v>122.86</v>
+        <v>121.64</v>
       </c>
       <c r="E157" s="15" t="n">
-        <v>-0.06059999999999999</v>
+        <v>-0.0703</v>
       </c>
       <c r="F157" s="15" t="n">
-        <v>-0.0301</v>
+        <v>-0.0361</v>
       </c>
       <c r="G157" s="16" t="n">
         <v>46315</v>
@@ -13173,7 +13173,7 @@
         <v>95</v>
       </c>
       <c r="M157" s="15" t="n">
-        <v>-0.2267621683216669</v>
+        <v>-0.2190069056231503</v>
       </c>
       <c r="N157" s="12" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>139</v>
       </c>
       <c r="P157" s="14" t="n">
-        <v>0.1313690379293505</v>
+        <v>0.1427162117724433</v>
       </c>
       <c r="Q157" s="19" t="inlineStr">
         <is>
@@ -13229,13 +13229,13 @@
         </is>
       </c>
       <c r="D158" s="4" t="n">
-        <v>928.83</v>
+        <v>923.0700000000001</v>
       </c>
       <c r="E158" s="25" t="n">
-        <v>-0.1203</v>
+        <v>-0.124</v>
       </c>
       <c r="F158" s="25" t="n">
-        <v>-0.0308</v>
+        <v>-0.0316</v>
       </c>
       <c r="G158" s="6" t="n">
         <v>46331</v>
@@ -13264,7 +13264,7 @@
         <v>125</v>
       </c>
       <c r="M158" s="25" t="n">
-        <v>-0.8654220901564333</v>
+        <v>-0.8645823177007161</v>
       </c>
       <c r="N158" s="3" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>1064</v>
       </c>
       <c r="P158" s="5" t="n">
-        <v>0.1455271685884392</v>
+        <v>0.1526753117315046</v>
       </c>
       <c r="Q158" s="9" t="inlineStr">
         <is>
@@ -13320,13 +13320,13 @@
         </is>
       </c>
       <c r="D159" s="13" t="n">
-        <v>478.81</v>
+        <v>477.55</v>
       </c>
       <c r="E159" s="15" t="n">
-        <v>-0.1457</v>
+        <v>-0.1436</v>
       </c>
       <c r="F159" s="15" t="n">
-        <v>-0.1748</v>
+        <v>-0.1698</v>
       </c>
       <c r="G159" s="16" t="n">
         <v>46325</v>
@@ -13401,13 +13401,13 @@
         </is>
       </c>
       <c r="D160" s="4" t="n">
-        <v>418.85</v>
+        <v>416.56</v>
       </c>
       <c r="E160" s="25" t="n">
-        <v>-0.0679</v>
+        <v>-0.06309999999999999</v>
       </c>
       <c r="F160" s="25" t="n">
-        <v>-0.1063</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="G160" s="6" t="n">
         <v>46331</v>
@@ -13462,13 +13462,13 @@
         </is>
       </c>
       <c r="D161" s="13" t="n">
-        <v>35.31</v>
+        <v>34.44</v>
       </c>
       <c r="E161" s="15" t="n">
-        <v>-0.0246</v>
+        <v>-0.0437</v>
       </c>
       <c r="F161" s="15" t="n">
-        <v>-0.2233</v>
+        <v>-0.2364</v>
       </c>
       <c r="G161" s="16" t="n">
         <v>46323</v>
@@ -13537,13 +13537,13 @@
         </is>
       </c>
       <c r="D162" s="4" t="n">
-        <v>195.34</v>
+        <v>193.97</v>
       </c>
       <c r="E162" s="25" t="n">
-        <v>-0.1239</v>
+        <v>-0.1248</v>
       </c>
       <c r="F162" s="5" t="n">
-        <v>0.005</v>
+        <v>0.0024</v>
       </c>
       <c r="G162" s="6" t="n">
         <v>46315</v>
@@ -13616,13 +13616,13 @@
         </is>
       </c>
       <c r="D163" s="13" t="n">
-        <v>41.6</v>
+        <v>41.8</v>
       </c>
       <c r="E163" s="15" t="n">
-        <v>-0.0258</v>
-      </c>
-      <c r="F163" s="15" t="n">
-        <v>-0.0091</v>
+        <v>-0.013</v>
+      </c>
+      <c r="F163" s="14" t="n">
+        <v>0.0133</v>
       </c>
       <c r="G163" s="16" t="n"/>
       <c r="H163" s="21" t="inlineStr">
@@ -13667,13 +13667,13 @@
         </is>
       </c>
       <c r="D164" s="4" t="n">
-        <v>426.01</v>
+        <v>419.5</v>
       </c>
       <c r="E164" s="25" t="n">
-        <v>-0.1128</v>
+        <v>-0.1174</v>
       </c>
       <c r="F164" s="25" t="n">
-        <v>-0.1031</v>
+        <v>-0.1074</v>
       </c>
       <c r="G164" s="6" t="n">
         <v>46324</v>
@@ -13705,7 +13705,7 @@
         <v>560</v>
       </c>
       <c r="P164" s="5" t="n">
-        <v>0.3145231332597827</v>
+        <v>0.3349225268176401</v>
       </c>
       <c r="Q164" s="9" t="inlineStr">
         <is>
@@ -13758,13 +13758,13 @@
         </is>
       </c>
       <c r="D165" s="13" t="n">
-        <v>285.08</v>
+        <v>283.57</v>
       </c>
       <c r="E165" s="15" t="n">
-        <v>-0.0293</v>
+        <v>-0.0545</v>
       </c>
       <c r="F165" s="15" t="n">
-        <v>-0.0479</v>
+        <v>-0.0603</v>
       </c>
       <c r="G165" s="16" t="n">
         <v>46317</v>
@@ -13796,7 +13796,7 @@
         <v>294</v>
       </c>
       <c r="P165" s="14" t="n">
-        <v>0.03128946260698757</v>
+        <v>0.03678104171809432</v>
       </c>
       <c r="Q165" s="19" t="inlineStr">
         <is>
@@ -13841,13 +13841,13 @@
         </is>
       </c>
       <c r="D166" s="4" t="n">
-        <v>237.39</v>
+        <v>238.88</v>
       </c>
       <c r="E166" s="25" t="n">
-        <v>-0.1921</v>
+        <v>-0.1831</v>
       </c>
       <c r="F166" s="25" t="n">
-        <v>-0.1929</v>
+        <v>-0.175</v>
       </c>
       <c r="G166" s="6" t="n">
         <v>46323</v>
@@ -13879,7 +13879,7 @@
         <v>425</v>
       </c>
       <c r="P166" s="5" t="n">
-        <v>0.7903028771220356</v>
+        <v>0.7791359678499665</v>
       </c>
       <c r="Q166" s="9" t="inlineStr">
         <is>
@@ -13920,13 +13920,13 @@
         </is>
       </c>
       <c r="D167" s="13" t="n">
-        <v>218.09</v>
+        <v>217.46</v>
       </c>
       <c r="E167" s="15" t="n">
-        <v>-0.0288</v>
+        <v>-0.0293</v>
       </c>
       <c r="F167" s="15" t="n">
-        <v>-0.09970000000000001</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="G167" s="16" t="n">
         <v>46321</v>
@@ -13955,7 +13955,7 @@
         <v>268</v>
       </c>
       <c r="M167" s="14" t="n">
-        <v>0.2288504745747168</v>
+        <v>0.2324105582635887</v>
       </c>
       <c r="N167" s="12" t="inlineStr"/>
       <c r="O167" s="18" t="n"/>
@@ -14003,13 +14003,13 @@
         </is>
       </c>
       <c r="D168" s="4" t="n">
-        <v>311.58</v>
+        <v>305.8</v>
       </c>
       <c r="E168" s="25" t="n">
-        <v>-0.004699999999999999</v>
+        <v>-0.0194</v>
       </c>
       <c r="F168" s="25" t="n">
-        <v>-0.191</v>
+        <v>-0.1778</v>
       </c>
       <c r="G168" s="6" t="n">
         <v>46330</v>
@@ -14078,13 +14078,13 @@
         </is>
       </c>
       <c r="D169" s="13" t="n">
-        <v>324.67</v>
+        <v>317.58</v>
       </c>
       <c r="E169" s="15" t="n">
-        <v>-0.1238</v>
+        <v>-0.1426</v>
       </c>
       <c r="F169" s="15" t="n">
-        <v>-0.1762</v>
+        <v>-0.1917</v>
       </c>
       <c r="G169" s="16" t="n"/>
       <c r="H169" s="21" t="inlineStr">
@@ -14147,13 +14147,13 @@
         </is>
       </c>
       <c r="D170" s="4" t="n">
-        <v>107.49</v>
+        <v>106.82</v>
       </c>
       <c r="E170" s="25" t="n">
-        <v>-0.1019</v>
+        <v>-0.0907</v>
       </c>
       <c r="F170" s="25" t="n">
-        <v>-0.1421</v>
+        <v>-0.13</v>
       </c>
       <c r="G170" s="6" t="n">
         <v>46322</v>
@@ -14226,13 +14226,13 @@
         </is>
       </c>
       <c r="D171" s="13" t="n">
-        <v>95.76000000000001</v>
+        <v>96.34999999999999</v>
       </c>
       <c r="E171" s="15" t="n">
-        <v>-0.3628</v>
+        <v>-0.3779</v>
       </c>
       <c r="F171" s="15" t="n">
-        <v>-0.0447</v>
+        <v>-0.0592</v>
       </c>
       <c r="G171" s="16" t="n">
         <v>46331</v>
@@ -14287,13 +14287,13 @@
         </is>
       </c>
       <c r="D172" s="4" t="n">
-        <v>333.08</v>
+        <v>329.38</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>0.08869999999999999</v>
+        <v>0.07780000000000001</v>
       </c>
       <c r="F172" s="25" t="n">
-        <v>-0.0005</v>
+        <v>-0.0131</v>
       </c>
       <c r="G172" s="6" t="n">
         <v>46324</v>
@@ -14322,7 +14322,7 @@
         <v>310</v>
       </c>
       <c r="M172" s="25" t="n">
-        <v>-0.06929266242344177</v>
+        <v>-0.05883781650373428</v>
       </c>
       <c r="N172" s="3" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>365</v>
       </c>
       <c r="P172" s="5" t="n">
-        <v>0.09583283295304437</v>
+        <v>0.1081425708907645</v>
       </c>
       <c r="Q172" s="9" t="inlineStr">
         <is>
@@ -14390,13 +14390,13 @@
         </is>
       </c>
       <c r="D173" s="13" t="n">
-        <v>105.31</v>
+        <v>103.53</v>
       </c>
       <c r="E173" s="15" t="n">
-        <v>-0.2486</v>
+        <v>-0.2816</v>
       </c>
       <c r="F173" s="15" t="n">
-        <v>-0.2442</v>
+        <v>-0.2411</v>
       </c>
       <c r="G173" s="16" t="n">
         <v>46329</v>
@@ -14451,13 +14451,13 @@
         </is>
       </c>
       <c r="D174" s="4" t="n">
-        <v>195</v>
+        <v>195.59</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>0.1024</v>
+        <v>0.1507</v>
       </c>
       <c r="F174" s="5" t="n">
-        <v>0.3485</v>
+        <v>0.3623</v>
       </c>
       <c r="G174" s="6" t="n">
         <v>46296</v>
@@ -14512,13 +14512,13 @@
         </is>
       </c>
       <c r="D175" s="13" t="n">
-        <v>265.6</v>
+        <v>260.46</v>
       </c>
       <c r="E175" s="14" t="n">
-        <v>0.006</v>
+        <v>0.0253</v>
       </c>
       <c r="F175" s="14" t="n">
-        <v>0.1287</v>
+        <v>0.09789999999999999</v>
       </c>
       <c r="G175" s="16" t="n"/>
       <c r="H175" s="21" t="inlineStr">
@@ -14563,13 +14563,13 @@
         </is>
       </c>
       <c r="D176" s="4" t="n">
-        <v>361.02</v>
+        <v>362.17</v>
       </c>
       <c r="E176" s="25" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.07200000000000001</v>
       </c>
       <c r="F176" s="25" t="n">
-        <v>-0.0513</v>
+        <v>-0.0351</v>
       </c>
       <c r="G176" s="6" t="n"/>
       <c r="H176" s="7" t="inlineStr">
@@ -14588,7 +14588,7 @@
         <v>515</v>
       </c>
       <c r="M176" s="5" t="n">
-        <v>0.4265137665503297</v>
+        <v>0.4219841510892674</v>
       </c>
       <c r="N176" s="3" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>474</v>
       </c>
       <c r="P176" s="5" t="n">
-        <v>0.3129466511550607</v>
+        <v>0.308777645856918</v>
       </c>
       <c r="Q176" s="9" t="inlineStr">
         <is>
@@ -14648,13 +14648,13 @@
         </is>
       </c>
       <c r="D177" s="13" t="n">
-        <v>228.93</v>
+        <v>229.25</v>
       </c>
       <c r="E177" s="15" t="n">
-        <v>-0.09029999999999999</v>
+        <v>-0.0513</v>
       </c>
       <c r="F177" s="14" t="n">
-        <v>0.0547</v>
+        <v>0.0499</v>
       </c>
       <c r="G177" s="16" t="n"/>
       <c r="H177" s="21" t="inlineStr">
@@ -14699,13 +14699,13 @@
         </is>
       </c>
       <c r="D178" s="4" t="n">
-        <v>254.35</v>
+        <v>250.41</v>
       </c>
       <c r="E178" s="25" t="n">
-        <v>-0.2298</v>
+        <v>-0.2817</v>
       </c>
       <c r="F178" s="25" t="n">
-        <v>-0.1103</v>
+        <v>-0.1184</v>
       </c>
       <c r="G178" s="6" t="n">
         <v>46329</v>
@@ -14760,13 +14760,13 @@
         </is>
       </c>
       <c r="D179" s="13" t="n">
-        <v>257.04</v>
+        <v>259.12</v>
       </c>
       <c r="E179" s="15" t="n">
-        <v>-0.2008</v>
+        <v>-0.1907</v>
       </c>
       <c r="F179" s="15" t="n">
-        <v>-0.1961</v>
+        <v>-0.1466</v>
       </c>
       <c r="G179" s="16" t="n">
         <v>46329</v>
@@ -14821,13 +14821,13 @@
         </is>
       </c>
       <c r="D180" s="4" t="n">
-        <v>33.85</v>
+        <v>33.16</v>
       </c>
       <c r="E180" s="25" t="n">
-        <v>-0.2374</v>
+        <v>-0.2506</v>
       </c>
       <c r="F180" s="25" t="n">
-        <v>-0.2816</v>
+        <v>-0.2866</v>
       </c>
       <c r="G180" s="6" t="n">
         <v>46324</v>
@@ -14882,13 +14882,13 @@
         </is>
       </c>
       <c r="D181" s="13" t="n">
-        <v>424.21</v>
+        <v>419.3</v>
       </c>
       <c r="E181" s="15" t="n">
-        <v>-0.1636</v>
+        <v>-0.2167</v>
       </c>
       <c r="F181" s="15" t="n">
-        <v>-0.2437</v>
+        <v>-0.2084</v>
       </c>
       <c r="G181" s="16" t="n"/>
       <c r="H181" s="21" t="inlineStr">
@@ -14907,7 +14907,7 @@
         <v>740</v>
       </c>
       <c r="M181" s="14" t="n">
-        <v>0.7444190377407417</v>
+        <v>0.7648461721917481</v>
       </c>
       <c r="N181" s="12" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>700</v>
       </c>
       <c r="P181" s="14" t="n">
-        <v>0.6501261167817827</v>
+        <v>0.669449081803005</v>
       </c>
       <c r="Q181" s="19" t="inlineStr">
         <is>
@@ -14959,13 +14959,13 @@
         </is>
       </c>
       <c r="D182" s="4" t="n">
-        <v>59.61</v>
+        <v>59.92</v>
       </c>
       <c r="E182" s="25" t="n">
-        <v>-0.076</v>
+        <v>-0.117</v>
       </c>
       <c r="F182" s="25" t="n">
-        <v>-0.1994</v>
+        <v>-0.1727</v>
       </c>
       <c r="G182" s="6" t="n">
         <v>46331</v>
@@ -15024,13 +15024,13 @@
         </is>
       </c>
       <c r="D183" s="13" t="n">
-        <v>493.41</v>
+        <v>503.34</v>
       </c>
       <c r="E183" s="15" t="n">
-        <v>-0.0408</v>
-      </c>
-      <c r="F183" s="15" t="n">
-        <v>-0.015</v>
+        <v>-0.0053</v>
+      </c>
+      <c r="F183" s="14" t="n">
+        <v>0.0153</v>
       </c>
       <c r="G183" s="16" t="n">
         <v>46329</v>
@@ -15059,7 +15059,7 @@
         <v>615</v>
       </c>
       <c r="M183" s="14" t="n">
-        <v>0.2464279199854076</v>
+        <v>0.2218381213493862</v>
       </c>
       <c r="N183" s="12" t="inlineStr">
         <is>
@@ -15070,7 +15070,7 @@
         <v>579</v>
       </c>
       <c r="P183" s="14" t="n">
-        <v>0.1734662856447984</v>
+        <v>0.1503158898557636</v>
       </c>
       <c r="Q183" s="19" t="inlineStr">
         <is>
@@ -15111,13 +15111,13 @@
         </is>
       </c>
       <c r="D184" s="4" t="n">
-        <v>47.12</v>
+        <v>46.14</v>
       </c>
       <c r="E184" s="25" t="n">
-        <v>-0.2012</v>
+        <v>-0.2473</v>
       </c>
       <c r="F184" s="25" t="n">
-        <v>-0.2523</v>
+        <v>-0.2669</v>
       </c>
       <c r="G184" s="6" t="n">
         <v>46321</v>
@@ -15172,13 +15172,13 @@
         </is>
       </c>
       <c r="D185" s="13" t="n">
-        <v>187.81</v>
+        <v>193.16</v>
       </c>
       <c r="E185" s="15" t="n">
-        <v>-0.0554</v>
+        <v>-0.0428</v>
       </c>
       <c r="F185" s="14" t="n">
-        <v>0.1142</v>
+        <v>0.1456</v>
       </c>
       <c r="G185" s="16" t="n">
         <v>46329</v>
@@ -15207,7 +15207,7 @@
         <v>200</v>
       </c>
       <c r="M185" s="14" t="n">
-        <v>0.06490602204355464</v>
+        <v>0.03541105819010149</v>
       </c>
       <c r="N185" s="12" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>200</v>
       </c>
       <c r="P185" s="14" t="n">
-        <v>0.06490602204355464</v>
+        <v>0.03541105819010149</v>
       </c>
       <c r="Q185" s="19" t="inlineStr">
         <is>
@@ -15263,13 +15263,13 @@
         </is>
       </c>
       <c r="D186" s="4" t="n">
-        <v>78.55</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="E186" s="25" t="n">
-        <v>-0.0599</v>
+        <v>-0.0953</v>
       </c>
       <c r="F186" s="5" t="n">
-        <v>0.0259</v>
+        <v>0.0224</v>
       </c>
       <c r="G186" s="6" t="n">
         <v>46323</v>
@@ -15301,7 +15301,7 @@
         <v>180</v>
       </c>
       <c r="P186" s="5" t="n">
-        <v>1.291534054742203</v>
+        <v>1.328891189028335</v>
       </c>
       <c r="Q186" s="9" t="inlineStr">
         <is>
@@ -15354,13 +15354,13 @@
         </is>
       </c>
       <c r="D187" s="13" t="n">
-        <v>24.58</v>
+        <v>23.83</v>
       </c>
       <c r="E187" s="15" t="n">
-        <v>-0.2122</v>
+        <v>-0.2356</v>
       </c>
       <c r="F187" s="15" t="n">
-        <v>-0.0703</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="G187" s="16" t="n">
         <v>46303</v>
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="D188" s="4" t="n">
-        <v>239.01</v>
+        <v>246.68</v>
       </c>
       <c r="E188" s="25" t="n">
-        <v>-0.1447</v>
+        <v>-0.09119999999999999</v>
       </c>
       <c r="F188" s="25" t="n">
-        <v>-0.08779999999999999</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="G188" s="6" t="n">
         <v>46330</v>
@@ -15476,13 +15476,13 @@
         </is>
       </c>
       <c r="D189" s="13" t="n">
-        <v>1575.15</v>
+        <v>1582.66</v>
       </c>
       <c r="E189" s="15" t="n">
-        <v>-0.1458</v>
+        <v>-0.1596</v>
       </c>
       <c r="F189" s="15" t="n">
-        <v>-0.1175</v>
+        <v>-0.0944</v>
       </c>
       <c r="G189" s="16" t="n">
         <v>46309</v>
@@ -15555,13 +15555,13 @@
         </is>
       </c>
       <c r="D190" s="4" t="n">
-        <v>37.08</v>
+        <v>37.31</v>
       </c>
       <c r="E190" s="25" t="n">
-        <v>-0.0622</v>
+        <v>-0.065</v>
       </c>
       <c r="F190" s="25" t="n">
-        <v>-0.06150000000000001</v>
+        <v>-0.0285</v>
       </c>
       <c r="G190" s="6" t="n">
         <v>46324</v>
@@ -15616,13 +15616,13 @@
         </is>
       </c>
       <c r="D191" s="13" t="n">
-        <v>344.72</v>
+        <v>341.7</v>
       </c>
       <c r="E191" s="15" t="n">
-        <v>-0.1228</v>
+        <v>-0.1293</v>
       </c>
       <c r="F191" s="15" t="n">
-        <v>-0.0794</v>
+        <v>-0.0786</v>
       </c>
       <c r="G191" s="16" t="n"/>
       <c r="H191" s="21" t="inlineStr">
@@ -15641,7 +15641,7 @@
         <v>545</v>
       </c>
       <c r="M191" s="14" t="n">
-        <v>0.5809932699002087</v>
+        <v>0.5949663447468541</v>
       </c>
       <c r="N191" s="12" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>582</v>
       </c>
       <c r="P191" s="14" t="n">
-        <v>0.6883267579484798</v>
+        <v>0.7032484635645303</v>
       </c>
       <c r="Q191" s="19" t="inlineStr">
         <is>
@@ -15705,22 +15705,32 @@
         </is>
       </c>
       <c r="D192" s="4" t="n">
-        <v>133.84</v>
+        <v>131.98</v>
       </c>
       <c r="E192" s="25" t="n">
-        <v>-0.1907</v>
+        <v>-0.2318</v>
       </c>
       <c r="F192" s="25" t="n">
-        <v>-0.09519999999999999</v>
-      </c>
-      <c r="G192" s="6" t="n"/>
-      <c r="H192" s="7" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="I192" s="3" t="inlineStr"/>
-      <c r="J192" s="3" t="inlineStr"/>
+        <v>-0.09699999999999999</v>
+      </c>
+      <c r="G192" s="6" t="n">
+        <v>46335</v>
+      </c>
+      <c r="H192" s="22" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I192" s="3" t="inlineStr">
+        <is>
+          <t>Nasdaq</t>
+        </is>
+      </c>
+      <c r="J192" s="3" t="inlineStr">
+        <is>
+          <t>Nov 09</t>
+        </is>
+      </c>
       <c r="K192" s="3" t="inlineStr"/>
       <c r="L192" s="8" t="n"/>
       <c r="M192" s="26" t="n"/>
@@ -15756,13 +15766,13 @@
         </is>
       </c>
       <c r="D193" s="13" t="n">
-        <v>279.06</v>
+        <v>274.06</v>
       </c>
       <c r="E193" s="15" t="n">
-        <v>-0.1409</v>
+        <v>-0.1527</v>
       </c>
       <c r="F193" s="15" t="n">
-        <v>-0.2347</v>
+        <v>-0.1698</v>
       </c>
       <c r="G193" s="16" t="n">
         <v>46321</v>
@@ -15791,7 +15801,7 @@
         <v>425</v>
       </c>
       <c r="M193" s="14" t="n">
-        <v>0.5229699706156382</v>
+        <v>0.550755309056411</v>
       </c>
       <c r="N193" s="12" t="inlineStr"/>
       <c r="O193" s="18" t="n"/>
@@ -15835,13 +15845,13 @@
         </is>
       </c>
       <c r="D194" s="4" t="n">
-        <v>138.49</v>
+        <v>136.45</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>0.05139999999999999</v>
-      </c>
-      <c r="F194" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.07429999999999999</v>
+      </c>
+      <c r="F194" s="25" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="G194" s="6" t="n">
         <v>46322</v>
@@ -15896,13 +15906,13 @@
         </is>
       </c>
       <c r="D195" s="13" t="n">
-        <v>319.64</v>
+        <v>329.33</v>
       </c>
       <c r="E195" s="15" t="n">
-        <v>-0.2545</v>
+        <v>-0.2602</v>
       </c>
       <c r="F195" s="15" t="n">
-        <v>-0.1779</v>
+        <v>-0.1204</v>
       </c>
       <c r="G195" s="16" t="n"/>
       <c r="H195" s="21" t="inlineStr">
@@ -15947,13 +15957,13 @@
         </is>
       </c>
       <c r="D196" s="4" t="n">
-        <v>11.67</v>
+        <v>11.37</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>0.0476</v>
+        <v>0.0891</v>
       </c>
       <c r="F196" s="25" t="n">
-        <v>-0.2628</v>
+        <v>-0.2636</v>
       </c>
       <c r="G196" s="6" t="n"/>
       <c r="H196" s="7" t="inlineStr">
@@ -15998,13 +16008,13 @@
         </is>
       </c>
       <c r="D197" s="13" t="n">
-        <v>316.08</v>
+        <v>319.14</v>
       </c>
       <c r="E197" s="15" t="n">
-        <v>-0.0566</v>
+        <v>-0.0624</v>
       </c>
       <c r="F197" s="14" t="n">
-        <v>0.04019999999999999</v>
+        <v>0.0591</v>
       </c>
       <c r="G197" s="16" t="n">
         <v>46321</v>
@@ -16059,13 +16069,13 @@
         </is>
       </c>
       <c r="D198" s="4" t="n">
-        <v>266.5</v>
+        <v>273.78</v>
       </c>
       <c r="E198" s="25" t="n">
-        <v>-0.1821</v>
+        <v>-0.2205</v>
       </c>
       <c r="F198" s="25" t="n">
-        <v>-0.0378</v>
+        <v>-0.0138</v>
       </c>
       <c r="G198" s="6" t="n">
         <v>46330</v>
@@ -16120,13 +16130,13 @@
         </is>
       </c>
       <c r="D199" s="13" t="n">
-        <v>49.97</v>
+        <v>49.29</v>
       </c>
       <c r="E199" s="15" t="n">
-        <v>-0.1573</v>
+        <v>-0.2129</v>
       </c>
       <c r="F199" s="15" t="n">
-        <v>-0.0299</v>
+        <v>-0.0371</v>
       </c>
       <c r="G199" s="16" t="n">
         <v>46330</v>
@@ -16181,13 +16191,13 @@
         </is>
       </c>
       <c r="D200" s="4" t="n">
-        <v>16.96</v>
+        <v>16.36</v>
       </c>
       <c r="E200" s="25" t="n">
-        <v>-0.1596</v>
+        <v>-0.187</v>
       </c>
       <c r="F200" s="25" t="n">
-        <v>-0.1931</v>
+        <v>-0.2185</v>
       </c>
       <c r="G200" s="6" t="n">
         <v>46318</v>
@@ -16242,13 +16252,13 @@
         </is>
       </c>
       <c r="D201" s="13" t="n">
-        <v>150.09</v>
+        <v>150.68</v>
       </c>
       <c r="E201" s="15" t="n">
-        <v>-0.4225</v>
+        <v>-0.4672</v>
       </c>
       <c r="F201" s="15" t="n">
-        <v>-0.2783</v>
+        <v>-0.2566</v>
       </c>
       <c r="G201" s="16" t="n"/>
       <c r="H201" s="21" t="inlineStr">
@@ -16293,13 +16303,13 @@
         </is>
       </c>
       <c r="D202" s="4" t="n">
-        <v>259.43</v>
+        <v>258.86</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>0.3222</v>
+        <v>0.3555</v>
       </c>
       <c r="F202" s="5" t="n">
-        <v>0.5024000000000001</v>
+        <v>0.5159</v>
       </c>
       <c r="G202" s="6" t="n"/>
       <c r="H202" s="7" t="inlineStr">
@@ -16318,7 +16328,7 @@
         <v>200</v>
       </c>
       <c r="M202" s="25" t="n">
-        <v>-0.2290791350267895</v>
+        <v>-0.2273815962296222</v>
       </c>
       <c r="N202" s="3" t="inlineStr">
         <is>
@@ -16329,7 +16339,7 @@
         <v>250</v>
       </c>
       <c r="P202" s="25" t="n">
-        <v>-0.0363489187834869</v>
+        <v>-0.03422699528702779</v>
       </c>
       <c r="Q202" s="9" t="inlineStr">
         <is>
@@ -16374,13 +16384,13 @@
         </is>
       </c>
       <c r="D203" s="13" t="n">
-        <v>235.38</v>
+        <v>238.22</v>
       </c>
       <c r="E203" s="14" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.1137</v>
       </c>
       <c r="F203" s="14" t="n">
-        <v>0.1552</v>
+        <v>0.173</v>
       </c>
       <c r="G203" s="16" t="n"/>
       <c r="H203" s="21" t="inlineStr">
@@ -16399,7 +16409,7 @@
         <v>181.25</v>
       </c>
       <c r="M203" s="15" t="n">
-        <v>-0.2299685614750616</v>
+        <v>-0.2391486860884896</v>
       </c>
       <c r="N203" s="12" t="inlineStr">
         <is>
@@ -16410,7 +16420,7 @@
         <v>177.5</v>
       </c>
       <c r="P203" s="15" t="n">
-        <v>-0.2459002464100603</v>
+        <v>-0.2548904374107968</v>
       </c>
       <c r="Q203" s="19" t="inlineStr">
         <is>
@@ -16451,22 +16461,32 @@
         </is>
       </c>
       <c r="D204" s="4" t="n">
-        <v>82.98</v>
+        <v>82.06999999999999</v>
       </c>
       <c r="E204" s="25" t="n">
-        <v>-0.2117</v>
+        <v>-0.2258</v>
       </c>
       <c r="F204" s="5" t="n">
-        <v>0.1381</v>
-      </c>
-      <c r="G204" s="6" t="n"/>
-      <c r="H204" s="7" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="I204" s="3" t="inlineStr"/>
-      <c r="J204" s="3" t="inlineStr"/>
+        <v>0.121</v>
+      </c>
+      <c r="G204" s="6" t="n">
+        <v>46335</v>
+      </c>
+      <c r="H204" s="22" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I204" s="3" t="inlineStr">
+        <is>
+          <t>Nasdaq</t>
+        </is>
+      </c>
+      <c r="J204" s="3" t="inlineStr">
+        <is>
+          <t>Nov 09</t>
+        </is>
+      </c>
       <c r="K204" s="3" t="inlineStr"/>
       <c r="L204" s="8" t="n"/>
       <c r="M204" s="26" t="n"/>
@@ -16502,13 +16522,13 @@
         </is>
       </c>
       <c r="D205" s="13" t="n">
-        <v>110.06</v>
+        <v>110.7</v>
       </c>
       <c r="E205" s="15" t="n">
-        <v>-0.0145</v>
-      </c>
-      <c r="F205" s="14" t="n">
-        <v>0.0036</v>
+        <v>-0.0195</v>
+      </c>
+      <c r="F205" s="15" t="n">
+        <v>-0.0111</v>
       </c>
       <c r="G205" s="16" t="n"/>
       <c r="H205" s="21" t="inlineStr">
@@ -16527,7 +16547,7 @@
         <v>130</v>
       </c>
       <c r="M205" s="14" t="n">
-        <v>0.1811739051426494</v>
+        <v>0.1743450767841011</v>
       </c>
       <c r="N205" s="12" t="inlineStr">
         <is>
@@ -16538,7 +16558,7 @@
         <v>150</v>
       </c>
       <c r="P205" s="14" t="n">
-        <v>0.3628929674722878</v>
+        <v>0.3550135501355013</v>
       </c>
       <c r="Q205" s="19" t="inlineStr">
         <is>
@@ -16595,13 +16615,13 @@
         </is>
       </c>
       <c r="D206" s="4" t="n">
-        <v>230.05</v>
+        <v>230.1</v>
       </c>
       <c r="E206" s="25" t="n">
-        <v>-0.09949999999999999</v>
+        <v>-0.0696</v>
       </c>
       <c r="F206" s="25" t="n">
-        <v>-0.123</v>
+        <v>-0.1105</v>
       </c>
       <c r="G206" s="6" t="n">
         <v>46331</v>
@@ -16656,13 +16676,13 @@
         </is>
       </c>
       <c r="D207" s="13" t="n">
-        <v>534.28</v>
+        <v>554.91</v>
       </c>
       <c r="E207" s="14" t="n">
-        <v>0.0886</v>
+        <v>0.1565</v>
       </c>
       <c r="F207" s="14" t="n">
-        <v>0.3651</v>
+        <v>0.4001</v>
       </c>
       <c r="G207" s="16" t="n"/>
       <c r="H207" s="21" t="inlineStr">
@@ -16707,13 +16727,13 @@
         </is>
       </c>
       <c r="D208" s="4" t="n">
-        <v>69.76000000000001</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>0.1244</v>
+        <v>0.1927</v>
       </c>
       <c r="F208" s="5" t="n">
-        <v>0.3069</v>
+        <v>0.3529</v>
       </c>
       <c r="G208" s="6" t="n"/>
       <c r="H208" s="7" t="inlineStr">
@@ -16758,13 +16778,13 @@
         </is>
       </c>
       <c r="D209" s="13" t="n">
-        <v>53.34</v>
+        <v>54.29</v>
       </c>
       <c r="E209" s="14" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.1404</v>
       </c>
       <c r="F209" s="14" t="n">
-        <v>0.1898</v>
+        <v>0.2226</v>
       </c>
       <c r="G209" s="16" t="n">
         <v>46330</v>
@@ -16819,13 +16839,13 @@
         </is>
       </c>
       <c r="D210" s="4" t="n">
-        <v>382.55</v>
+        <v>379.98</v>
       </c>
       <c r="E210" s="25" t="n">
-        <v>-0.3290999999999999</v>
+        <v>-0.3652</v>
       </c>
       <c r="F210" s="25" t="n">
-        <v>-0.1687</v>
+        <v>-0.2057</v>
       </c>
       <c r="G210" s="6" t="n">
         <v>46328</v>
@@ -16880,13 +16900,13 @@
         </is>
       </c>
       <c r="D211" s="13" t="n">
-        <v>102.94</v>
+        <v>101.98</v>
       </c>
       <c r="E211" s="15" t="n">
-        <v>-0.2178</v>
+        <v>-0.2619</v>
       </c>
       <c r="F211" s="15" t="n">
-        <v>-0.0389</v>
+        <v>-0.034</v>
       </c>
       <c r="G211" s="16" t="n">
         <v>46330</v>
@@ -16941,13 +16961,13 @@
         </is>
       </c>
       <c r="D212" s="4" t="n">
-        <v>170.18</v>
+        <v>169.9</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>0.0636</v>
+        <v>0.0902</v>
       </c>
       <c r="F212" s="5" t="n">
-        <v>0.0585</v>
+        <v>0.0513</v>
       </c>
       <c r="G212" s="6" t="n">
         <v>46330</v>
@@ -17002,13 +17022,13 @@
         </is>
       </c>
       <c r="D213" s="13" t="n">
-        <v>43.54</v>
+        <v>42.71</v>
       </c>
       <c r="E213" s="15" t="n">
-        <v>-0.2023</v>
+        <v>-0.2008</v>
       </c>
       <c r="F213" s="15" t="n">
-        <v>-0.2524</v>
+        <v>-0.257</v>
       </c>
       <c r="G213" s="16" t="n"/>
       <c r="H213" s="21" t="inlineStr">
@@ -17053,13 +17073,13 @@
         </is>
       </c>
       <c r="D214" s="4" t="n">
-        <v>143.6</v>
+        <v>143.69</v>
       </c>
       <c r="E214" s="25" t="n">
-        <v>-0.1349</v>
+        <v>-0.1704</v>
       </c>
       <c r="F214" s="25" t="n">
-        <v>-0.0934</v>
+        <v>-0.0706</v>
       </c>
       <c r="G214" s="6" t="n">
         <v>46322</v>
@@ -17114,13 +17134,13 @@
         </is>
       </c>
       <c r="D215" s="13" t="n">
-        <v>49.25</v>
+        <v>49.18</v>
       </c>
       <c r="E215" s="14" t="n">
-        <v>0.1556</v>
+        <v>0.2137</v>
       </c>
       <c r="F215" s="14" t="n">
-        <v>0.5509000000000001</v>
+        <v>0.5031</v>
       </c>
       <c r="G215" s="16" t="n"/>
       <c r="H215" s="21" t="inlineStr">
@@ -17165,13 +17185,13 @@
         </is>
       </c>
       <c r="D216" s="4" t="n">
-        <v>153</v>
+        <v>148.61</v>
       </c>
       <c r="E216" s="25" t="n">
-        <v>-0.1287</v>
-      </c>
-      <c r="F216" s="5" t="n">
-        <v>0.0275</v>
+        <v>-0.1359</v>
+      </c>
+      <c r="F216" s="25" t="n">
+        <v>-0.009399999999999999</v>
       </c>
       <c r="G216" s="6" t="n"/>
       <c r="H216" s="7" t="inlineStr">
@@ -17190,7 +17210,7 @@
         <v>190</v>
       </c>
       <c r="M216" s="5" t="n">
-        <v>0.2418300653594771</v>
+        <v>0.2785142318821074</v>
       </c>
       <c r="N216" s="3" t="inlineStr"/>
       <c r="O216" s="8" t="n"/>
@@ -17234,13 +17254,13 @@
         </is>
       </c>
       <c r="D217" s="13" t="n">
-        <v>55.41</v>
+        <v>57.45</v>
       </c>
       <c r="E217" s="15" t="n">
-        <v>-0.0562</v>
+        <v>-0.0028</v>
       </c>
       <c r="F217" s="14" t="n">
-        <v>0.2278</v>
+        <v>0.2538</v>
       </c>
       <c r="G217" s="16" t="n"/>
       <c r="H217" s="21" t="inlineStr">
@@ -17259,7 +17279,7 @@
         <v>67</v>
       </c>
       <c r="M217" s="14" t="n">
-        <v>0.209168020212958</v>
+        <v>0.1662315056570931</v>
       </c>
       <c r="N217" s="12" t="inlineStr">
         <is>
@@ -17270,7 +17290,7 @@
         <v>70</v>
       </c>
       <c r="P217" s="14" t="n">
-        <v>0.2633098718642845</v>
+        <v>0.2184508268059181</v>
       </c>
       <c r="Q217" s="19" t="inlineStr">
         <is>
@@ -17311,13 +17331,13 @@
         </is>
       </c>
       <c r="D218" s="4" t="n">
-        <v>250.61</v>
+        <v>246.63</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>0.1181</v>
+        <v>0.1462</v>
       </c>
       <c r="F218" s="5" t="n">
-        <v>0.116</v>
+        <v>0.0998</v>
       </c>
       <c r="G218" s="6" t="n">
         <v>46330</v>
@@ -17372,13 +17392,13 @@
         </is>
       </c>
       <c r="D219" s="13" t="n">
-        <v>249.09</v>
+        <v>249</v>
       </c>
       <c r="E219" s="14" t="n">
-        <v>0.063</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="F219" s="14" t="n">
-        <v>0.1371</v>
+        <v>0.1708</v>
       </c>
       <c r="G219" s="16" t="n">
         <v>46316</v>
@@ -17414,7 +17434,7 @@
         <v>250</v>
       </c>
       <c r="P219" s="14" t="n">
-        <v>0.00365329800473723</v>
+        <v>0.004016064257028112</v>
       </c>
       <c r="Q219" s="19" t="inlineStr">
         <is>
@@ -17451,13 +17471,13 @@
         </is>
       </c>
       <c r="D220" s="4" t="n">
-        <v>12.6</v>
+        <v>12.36</v>
       </c>
       <c r="E220" s="25" t="n">
-        <v>-0.0202</v>
+        <v>-0.0779</v>
       </c>
       <c r="F220" s="5" t="n">
-        <v>0.3907</v>
+        <v>0.3603</v>
       </c>
       <c r="G220" s="6" t="n"/>
       <c r="H220" s="7" t="inlineStr">
@@ -17502,13 +17522,13 @@
         </is>
       </c>
       <c r="D221" s="13" t="n">
-        <v>97.19</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="E221" s="15" t="n">
-        <v>-0.0518</v>
+        <v>-0.05019999999999999</v>
       </c>
       <c r="F221" s="14" t="n">
-        <v>0.0022</v>
+        <v>0.0342</v>
       </c>
       <c r="G221" s="16" t="n">
         <v>46317</v>
@@ -17563,13 +17583,13 @@
         </is>
       </c>
       <c r="D222" s="4" t="n">
-        <v>339.15</v>
+        <v>331.88</v>
       </c>
       <c r="E222" s="25" t="n">
-        <v>-0.0188</v>
+        <v>-0.0111</v>
       </c>
       <c r="F222" s="5" t="n">
-        <v>0.1505</v>
+        <v>0.1401</v>
       </c>
       <c r="G222" s="6" t="n"/>
       <c r="H222" s="7" t="inlineStr">
@@ -17614,13 +17634,13 @@
         </is>
       </c>
       <c r="D223" s="13" t="n">
-        <v>37.5</v>
+        <v>37.03</v>
       </c>
       <c r="E223" s="15" t="n">
-        <v>-0.1894</v>
+        <v>-0.2094</v>
       </c>
       <c r="F223" s="14" t="n">
-        <v>0.0684</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="G223" s="16" t="n">
         <v>46330</v>
@@ -17675,13 +17695,13 @@
         </is>
       </c>
       <c r="D224" s="4" t="n">
-        <v>43.17</v>
+        <v>41.36</v>
       </c>
       <c r="E224" s="25" t="n">
-        <v>-0.0202</v>
+        <v>-0.0789</v>
       </c>
       <c r="F224" s="5" t="n">
-        <v>0.2394</v>
+        <v>0.2301</v>
       </c>
       <c r="G224" s="6" t="n">
         <v>46331</v>
@@ -17736,13 +17756,13 @@
         </is>
       </c>
       <c r="D225" s="13" t="n">
-        <v>298.72</v>
+        <v>295.6</v>
       </c>
       <c r="E225" s="15" t="n">
-        <v>-0.1773</v>
+        <v>-0.2008</v>
       </c>
       <c r="F225" s="15" t="n">
-        <v>-0.0272</v>
+        <v>-0.018</v>
       </c>
       <c r="G225" s="16" t="n">
         <v>46289</v>
@@ -17801,13 +17821,13 @@
         </is>
       </c>
       <c r="D226" s="4" t="n">
-        <v>314.96</v>
+        <v>313.8</v>
       </c>
       <c r="E226" s="25" t="n">
-        <v>-0.1198</v>
-      </c>
-      <c r="F226" s="5" t="n">
-        <v>0.006999999999999999</v>
+        <v>-0.1311</v>
+      </c>
+      <c r="F226" s="25" t="n">
+        <v>-0.0066</v>
       </c>
       <c r="G226" s="6" t="n"/>
       <c r="H226" s="7" t="inlineStr">
@@ -17826,7 +17846,7 @@
         <v>390</v>
       </c>
       <c r="M226" s="5" t="n">
-        <v>0.2382524765049531</v>
+        <v>0.2428298279158699</v>
       </c>
       <c r="N226" s="3" t="inlineStr"/>
       <c r="O226" s="8" t="n"/>
@@ -17882,13 +17902,13 @@
         </is>
       </c>
       <c r="D227" s="13" t="n">
-        <v>169.09</v>
+        <v>166.63</v>
       </c>
       <c r="E227" s="15" t="n">
-        <v>-0.17</v>
+        <v>-0.1902</v>
       </c>
       <c r="F227" s="15" t="n">
-        <v>-0.2292</v>
+        <v>-0.2168</v>
       </c>
       <c r="G227" s="16" t="n">
         <v>46330</v>
@@ -17917,7 +17937,7 @@
         <v>305</v>
       </c>
       <c r="M227" s="14" t="n">
-        <v>0.8037731385652611</v>
+        <v>0.8304026885914901</v>
       </c>
       <c r="N227" s="12" t="inlineStr">
         <is>
@@ -17928,7 +17948,7 @@
         <v>185</v>
       </c>
       <c r="P227" s="14" t="n">
-        <v>0.09409190371991245</v>
+        <v>0.1102442537358219</v>
       </c>
       <c r="Q227" s="19" t="inlineStr">
         <is>
@@ -17969,13 +17989,13 @@
         </is>
       </c>
       <c r="D228" s="4" t="n">
-        <v>79.45</v>
+        <v>78.78</v>
       </c>
       <c r="E228" s="25" t="n">
-        <v>-0.1982</v>
+        <v>-0.2259</v>
       </c>
       <c r="F228" s="25" t="n">
-        <v>-0.1976</v>
+        <v>-0.1897</v>
       </c>
       <c r="G228" s="6" t="n"/>
       <c r="H228" s="7" t="inlineStr">
@@ -18020,13 +18040,13 @@
         </is>
       </c>
       <c r="D229" s="13" t="n">
-        <v>835.03</v>
+        <v>840.51</v>
       </c>
       <c r="E229" s="15" t="n">
-        <v>-0.0984</v>
+        <v>-0.1325</v>
       </c>
       <c r="F229" s="14" t="n">
-        <v>0.1824</v>
+        <v>0.147</v>
       </c>
       <c r="G229" s="16" t="n">
         <v>46329</v>
@@ -18081,13 +18101,13 @@
         </is>
       </c>
       <c r="D230" s="4" t="n">
-        <v>100.36</v>
+        <v>101.07</v>
       </c>
       <c r="E230" s="25" t="n">
-        <v>-0.0265</v>
-      </c>
-      <c r="F230" s="5" t="n">
-        <v>0.0007000000000000001</v>
+        <v>-0.0005</v>
+      </c>
+      <c r="F230" s="25" t="n">
+        <v>-0.0172</v>
       </c>
       <c r="G230" s="6" t="n">
         <v>46322</v>
@@ -18142,13 +18162,13 @@
         </is>
       </c>
       <c r="D231" s="13" t="n">
-        <v>273.49</v>
+        <v>267</v>
       </c>
       <c r="E231" s="15" t="n">
-        <v>-0.1771</v>
+        <v>-0.2235</v>
       </c>
       <c r="F231" s="15" t="n">
-        <v>-0.1479</v>
+        <v>-0.1478</v>
       </c>
       <c r="G231" s="16" t="n">
         <v>46323</v>
@@ -18177,7 +18197,7 @@
         <v>450</v>
       </c>
       <c r="M231" s="14" t="n">
-        <v>0.645398369227394</v>
+        <v>0.6853932584269663</v>
       </c>
       <c r="N231" s="12" t="inlineStr">
         <is>
@@ -18188,7 +18208,7 @@
         <v>355</v>
       </c>
       <c r="P231" s="14" t="n">
-        <v>0.2980364912793886</v>
+        <v>0.3295880149812734</v>
       </c>
       <c r="Q231" s="19" t="inlineStr">
         <is>
@@ -18233,13 +18253,13 @@
         </is>
       </c>
       <c r="D232" s="4" t="n">
-        <v>71.48</v>
+        <v>71.02</v>
       </c>
       <c r="E232" s="25" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.1151</v>
       </c>
       <c r="F232" s="25" t="n">
-        <v>-0.1249</v>
+        <v>-0.1228</v>
       </c>
       <c r="G232" s="6" t="n">
         <v>46331</v>
@@ -18294,13 +18314,13 @@
         </is>
       </c>
       <c r="D233" s="13" t="n">
-        <v>382.29</v>
+        <v>381.27</v>
       </c>
       <c r="E233" s="15" t="n">
-        <v>-0.1695</v>
+        <v>-0.1309</v>
       </c>
       <c r="F233" s="14" t="n">
-        <v>0.1634</v>
+        <v>0.2207</v>
       </c>
       <c r="G233" s="16" t="n"/>
       <c r="H233" s="21" t="inlineStr">
@@ -18345,13 +18365,13 @@
         </is>
       </c>
       <c r="D234" s="4" t="n">
-        <v>239.27</v>
+        <v>231.5</v>
       </c>
       <c r="E234" s="25" t="n">
-        <v>-0.23</v>
+        <v>-0.2782</v>
       </c>
       <c r="F234" s="25" t="n">
-        <v>-0.2793</v>
+        <v>-0.287</v>
       </c>
       <c r="G234" s="6" t="n">
         <v>46330</v>
@@ -18406,13 +18426,13 @@
         </is>
       </c>
       <c r="D235" s="13" t="n">
-        <v>1143.24</v>
+        <v>1151.56</v>
       </c>
       <c r="E235" s="15" t="n">
-        <v>-0.1846</v>
+        <v>-0.1867</v>
       </c>
       <c r="F235" s="15" t="n">
-        <v>-0.1244</v>
+        <v>-0.1223</v>
       </c>
       <c r="G235" s="16" t="n">
         <v>46324</v>
@@ -18467,13 +18487,13 @@
         </is>
       </c>
       <c r="D236" s="4" t="n">
-        <v>218.82</v>
+        <v>224.2</v>
       </c>
       <c r="E236" s="25" t="n">
-        <v>-0.0144</v>
+        <v>-0.0432</v>
       </c>
       <c r="F236" s="5" t="n">
-        <v>0.1621</v>
+        <v>0.1882</v>
       </c>
       <c r="G236" s="6" t="n"/>
       <c r="H236" s="7" t="inlineStr">
@@ -18492,7 +18512,7 @@
         <v>240</v>
       </c>
       <c r="M236" s="5" t="n">
-        <v>0.09679188374006036</v>
+        <v>0.07047279214986625</v>
       </c>
       <c r="N236" s="3" t="inlineStr">
         <is>
@@ -18503,7 +18523,7 @@
         <v>251</v>
       </c>
       <c r="P236" s="5" t="n">
-        <v>0.1470615117448131</v>
+        <v>0.1195361284567351</v>
       </c>
       <c r="Q236" s="9" t="inlineStr">
         <is>
@@ -18544,13 +18564,13 @@
         </is>
       </c>
       <c r="D237" s="13" t="n">
-        <v>505.41</v>
+        <v>500.79</v>
       </c>
       <c r="E237" s="14" t="n">
-        <v>0.0202</v>
+        <v>0.0426</v>
       </c>
       <c r="F237" s="14" t="n">
-        <v>0.2601</v>
+        <v>0.2716</v>
       </c>
       <c r="G237" s="16" t="n">
         <v>46330</v>
@@ -18579,7 +18599,7 @@
         <v>625</v>
       </c>
       <c r="M237" s="14" t="n">
-        <v>0.2366197740448348</v>
+        <v>0.2480281155773877</v>
       </c>
       <c r="N237" s="12" t="inlineStr">
         <is>
@@ -18590,7 +18610,7 @@
         <v>525</v>
       </c>
       <c r="P237" s="14" t="n">
-        <v>0.03876061019766126</v>
+        <v>0.04834361708500565</v>
       </c>
       <c r="Q237" s="19" t="inlineStr">
         <is>
@@ -18643,13 +18663,13 @@
         </is>
       </c>
       <c r="D238" s="4" t="n">
-        <v>474.13</v>
+        <v>472.99</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>0.0163</v>
+        <v>0.0348</v>
       </c>
       <c r="F238" s="5" t="n">
-        <v>0.1447</v>
+        <v>0.1444</v>
       </c>
       <c r="G238" s="6" t="n">
         <v>46324</v>
@@ -18681,7 +18701,7 @@
         <v>525</v>
       </c>
       <c r="P238" s="5" t="n">
-        <v>0.1072912492354418</v>
+        <v>0.1099600414385082</v>
       </c>
       <c r="Q238" s="9" t="inlineStr">
         <is>
@@ -18730,13 +18750,13 @@
         </is>
       </c>
       <c r="D239" s="13" t="n">
-        <v>136.94</v>
+        <v>131.33</v>
       </c>
       <c r="E239" s="14" t="n">
-        <v>0.4718</v>
+        <v>0.3445</v>
       </c>
       <c r="F239" s="14" t="n">
-        <v>0.4563</v>
+        <v>0.3846</v>
       </c>
       <c r="G239" s="16" t="n">
         <v>46324</v>
@@ -18791,13 +18811,13 @@
         </is>
       </c>
       <c r="D240" s="4" t="n">
-        <v>239.62</v>
+        <v>239.55</v>
       </c>
       <c r="E240" s="25" t="n">
-        <v>-0.2428</v>
+        <v>-0.2686</v>
       </c>
       <c r="F240" s="25" t="n">
-        <v>-0.1302</v>
+        <v>-0.104</v>
       </c>
       <c r="G240" s="6" t="n">
         <v>46331</v>
@@ -18852,13 +18872,13 @@
         </is>
       </c>
       <c r="D241" s="13" t="n">
-        <v>924.03</v>
+        <v>932.5700000000001</v>
       </c>
       <c r="E241" s="15" t="n">
-        <v>-0.049</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="F241" s="14" t="n">
-        <v>0.083</v>
+        <v>0.09849999999999999</v>
       </c>
       <c r="G241" s="16" t="n">
         <v>46295</v>
@@ -18887,7 +18907,7 @@
         <v>1525</v>
       </c>
       <c r="M241" s="14" t="n">
-        <v>0.6503793166888522</v>
+        <v>0.6352659853951981</v>
       </c>
       <c r="N241" s="12" t="inlineStr">
         <is>
@@ -18935,13 +18955,13 @@
         </is>
       </c>
       <c r="D242" s="4" t="n">
-        <v>212.19</v>
+        <v>209.43</v>
       </c>
       <c r="E242" s="25" t="n">
-        <v>-0.2358</v>
+        <v>-0.221</v>
       </c>
       <c r="F242" s="5" t="n">
-        <v>0.2353</v>
+        <v>0.1785</v>
       </c>
       <c r="G242" s="6" t="n"/>
       <c r="H242" s="7" t="inlineStr">
@@ -18986,13 +19006,13 @@
         </is>
       </c>
       <c r="D243" s="13" t="n">
-        <v>330.36</v>
+        <v>327.48</v>
       </c>
       <c r="E243" s="14" t="n">
-        <v>0.0462</v>
+        <v>0.0667</v>
       </c>
       <c r="F243" s="14" t="n">
-        <v>0.2125</v>
+        <v>0.1794</v>
       </c>
       <c r="G243" s="16" t="n">
         <v>46324</v>
@@ -19047,13 +19067,13 @@
         </is>
       </c>
       <c r="D244" s="4" t="n">
-        <v>142.35</v>
+        <v>144.1</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>0.148</v>
+        <v>0.2243</v>
       </c>
       <c r="F244" s="5" t="n">
-        <v>0.3686</v>
+        <v>0.3957</v>
       </c>
       <c r="G244" s="6" t="n">
         <v>46323</v>
@@ -19082,7 +19102,7 @@
         <v>160</v>
       </c>
       <c r="M244" s="5" t="n">
-        <v>0.1239901650860555</v>
+        <v>0.1103400416377516</v>
       </c>
       <c r="N244" s="3" t="inlineStr">
         <is>
@@ -19093,7 +19113,7 @@
         <v>150</v>
       </c>
       <c r="P244" s="5" t="n">
-        <v>0.05374077976817707</v>
+        <v>0.04094378903539213</v>
       </c>
       <c r="Q244" s="9" t="inlineStr">
         <is>
@@ -19138,13 +19158,13 @@
         </is>
       </c>
       <c r="D245" s="13" t="n">
-        <v>67.69</v>
+        <v>68.36</v>
       </c>
       <c r="E245" s="14" t="n">
-        <v>0.0163</v>
+        <v>0.0411</v>
       </c>
       <c r="F245" s="14" t="n">
-        <v>0.212</v>
+        <v>0.2411</v>
       </c>
       <c r="G245" s="16" t="n"/>
       <c r="H245" s="21" t="inlineStr">
@@ -19189,13 +19209,13 @@
         </is>
       </c>
       <c r="D246" s="4" t="n">
-        <v>210.96</v>
+        <v>212.3</v>
       </c>
       <c r="E246" s="25" t="n">
-        <v>-0.06309999999999999</v>
+        <v>-0.0565</v>
       </c>
       <c r="F246" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.04679999999999999</v>
       </c>
       <c r="G246" s="6" t="n"/>
       <c r="H246" s="7" t="inlineStr">
@@ -19214,7 +19234,7 @@
         <v>315</v>
       </c>
       <c r="M246" s="5" t="n">
-        <v>0.4931740614334471</v>
+        <v>0.483749411210551</v>
       </c>
       <c r="N246" s="3" t="inlineStr">
         <is>
@@ -19225,7 +19245,7 @@
         <v>413</v>
       </c>
       <c r="P246" s="5" t="n">
-        <v>0.9577171027682972</v>
+        <v>0.9453603391427224</v>
       </c>
       <c r="Q246" s="9" t="inlineStr">
         <is>
@@ -19274,13 +19294,13 @@
         </is>
       </c>
       <c r="D247" s="13" t="n">
-        <v>334.65</v>
+        <v>330.9</v>
       </c>
       <c r="E247" s="15" t="n">
-        <v>-0.1996</v>
+        <v>-0.2136</v>
       </c>
       <c r="F247" s="15" t="n">
-        <v>-0.2582</v>
+        <v>-0.2436</v>
       </c>
       <c r="G247" s="16" t="n">
         <v>46331</v>
@@ -19335,13 +19355,13 @@
         </is>
       </c>
       <c r="D248" s="4" t="n">
-        <v>224.23</v>
+        <v>226.15</v>
       </c>
       <c r="E248" s="25" t="n">
-        <v>-0.0447</v>
+        <v>-0.0282</v>
       </c>
       <c r="F248" s="25" t="n">
-        <v>-0.1715</v>
+        <v>-0.1515</v>
       </c>
       <c r="G248" s="6" t="n">
         <v>46322</v>
@@ -19395,10 +19415,10 @@
         <v>10.57</v>
       </c>
       <c r="E249" s="15" t="n">
-        <v>-0.09660000000000001</v>
+        <v>-0.08410000000000001</v>
       </c>
       <c r="F249" s="15" t="n">
-        <v>-0.339</v>
+        <v>-0.3264</v>
       </c>
       <c r="G249" s="16" t="n"/>
       <c r="H249" s="21" t="inlineStr">
@@ -19443,13 +19463,13 @@
         </is>
       </c>
       <c r="D250" s="4" t="n">
-        <v>186.45</v>
+        <v>187.76</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>0.2647</v>
+        <v>0.3108</v>
       </c>
       <c r="F250" s="5" t="n">
-        <v>0.262</v>
+        <v>0.2571</v>
       </c>
       <c r="G250" s="6" t="n"/>
       <c r="H250" s="7" t="inlineStr">
@@ -19468,7 +19488,7 @@
         <v>150</v>
       </c>
       <c r="M250" s="25" t="n">
-        <v>-0.1954947707160096</v>
+        <v>-0.2011077971878994</v>
       </c>
       <c r="N250" s="3" t="inlineStr">
         <is>
@@ -19479,7 +19499,7 @@
         <v>130</v>
       </c>
       <c r="P250" s="25" t="n">
-        <v>-0.3027621346205416</v>
+        <v>-0.3076267575628461</v>
       </c>
       <c r="Q250" s="9" t="inlineStr">
         <is>
@@ -19520,13 +19540,13 @@
         </is>
       </c>
       <c r="D251" s="13" t="n">
-        <v>71.65000000000001</v>
+        <v>72.47</v>
       </c>
       <c r="E251" s="15" t="n">
-        <v>-0.1332</v>
+        <v>-0.1308</v>
       </c>
       <c r="F251" s="15" t="n">
-        <v>-0.1869</v>
+        <v>-0.1705</v>
       </c>
       <c r="G251" s="16" t="n">
         <v>46328</v>
@@ -19581,13 +19601,13 @@
         </is>
       </c>
       <c r="D252" s="4" t="n">
-        <v>250.13</v>
+        <v>243.46</v>
       </c>
       <c r="E252" s="25" t="n">
-        <v>-0.2459</v>
+        <v>-0.3067</v>
       </c>
       <c r="F252" s="25" t="n">
-        <v>-0.1118</v>
+        <v>-0.13</v>
       </c>
       <c r="G252" s="6" t="n">
         <v>46331</v>
@@ -19642,13 +19662,13 @@
         </is>
       </c>
       <c r="D253" s="13" t="n">
-        <v>144.79</v>
+        <v>143.66</v>
       </c>
       <c r="E253" s="15" t="n">
-        <v>-0.0381</v>
+        <v>-0.0204</v>
       </c>
       <c r="F253" s="14" t="n">
-        <v>0.1657</v>
+        <v>0.1365</v>
       </c>
       <c r="G253" s="16" t="n"/>
       <c r="H253" s="21" t="inlineStr">
@@ -19667,7 +19687,7 @@
         <v>280</v>
       </c>
       <c r="M253" s="14" t="n">
-        <v>0.9338352096139237</v>
+        <v>0.9490463594598357</v>
       </c>
       <c r="N253" s="12" t="inlineStr">
         <is>
@@ -19678,7 +19698,7 @@
         <v>245</v>
       </c>
       <c r="P253" s="14" t="n">
-        <v>0.6921058084121833</v>
+        <v>0.7054155645273563</v>
       </c>
       <c r="Q253" s="19" t="inlineStr">
         <is>
@@ -19719,13 +19739,13 @@
         </is>
       </c>
       <c r="D254" s="4" t="n">
-        <v>373.94</v>
+        <v>373.23</v>
       </c>
       <c r="E254" s="25" t="n">
-        <v>-0.0269</v>
+        <v>-0.0067</v>
       </c>
       <c r="F254" s="5" t="n">
-        <v>0.0564</v>
+        <v>0.0406</v>
       </c>
       <c r="G254" s="6" t="n"/>
       <c r="H254" s="7" t="inlineStr">
@@ -19744,7 +19764,7 @@
         <v>420</v>
       </c>
       <c r="M254" s="5" t="n">
-        <v>0.1231748408835642</v>
+        <v>0.1253114701390563</v>
       </c>
       <c r="N254" s="3" t="inlineStr">
         <is>
@@ -19755,7 +19775,7 @@
         <v>415</v>
       </c>
       <c r="P254" s="5" t="n">
-        <v>0.1098037118254265</v>
+        <v>0.1119149050183532</v>
       </c>
       <c r="Q254" s="9" t="inlineStr">
         <is>
@@ -19804,13 +19824,13 @@
         </is>
       </c>
       <c r="D255" s="13" t="n">
-        <v>14.66</v>
+        <v>14.31</v>
       </c>
       <c r="E255" s="15" t="n">
-        <v>-0.0843</v>
+        <v>-0.1054</v>
       </c>
       <c r="F255" s="14" t="n">
-        <v>0.2186</v>
+        <v>0.1774</v>
       </c>
       <c r="G255" s="16" t="n"/>
       <c r="H255" s="21" t="inlineStr">
@@ -19855,13 +19875,13 @@
         </is>
       </c>
       <c r="D256" s="4" t="n">
-        <v>38.71</v>
+        <v>38.34</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>0.1977</v>
+        <v>0.2026</v>
       </c>
       <c r="F256" s="5" t="n">
-        <v>0.1759</v>
+        <v>0.1922</v>
       </c>
       <c r="G256" s="6" t="n">
         <v>46315</v>
@@ -19916,13 +19936,13 @@
         </is>
       </c>
       <c r="D257" s="13" t="n">
-        <v>173.09</v>
-      </c>
-      <c r="E257" s="14" t="n">
-        <v>0.0025</v>
+        <v>171.59</v>
+      </c>
+      <c r="E257" s="15" t="n">
+        <v>-0.0007000000000000001</v>
       </c>
       <c r="F257" s="14" t="n">
-        <v>0.2297</v>
+        <v>0.24</v>
       </c>
       <c r="G257" s="16" t="n">
         <v>46330</v>
@@ -19977,13 +19997,13 @@
         </is>
       </c>
       <c r="D258" s="4" t="n">
-        <v>173.31</v>
+        <v>171.92</v>
       </c>
       <c r="E258" s="25" t="n">
-        <v>-0.0042</v>
+        <v>-0.0037</v>
       </c>
       <c r="F258" s="5" t="n">
-        <v>0.2891</v>
+        <v>0.2987</v>
       </c>
       <c r="G258" s="6" t="n">
         <v>46328</v>
@@ -20038,13 +20058,13 @@
         </is>
       </c>
       <c r="D259" s="13" t="n">
-        <v>117.23</v>
+        <v>114.28</v>
       </c>
       <c r="E259" s="15" t="n">
-        <v>-0.1762</v>
+        <v>-0.1882</v>
       </c>
       <c r="F259" s="15" t="n">
-        <v>-0.1346</v>
+        <v>-0.1619</v>
       </c>
       <c r="G259" s="16" t="n"/>
       <c r="H259" s="21" t="inlineStr">
@@ -20099,13 +20119,13 @@
         </is>
       </c>
       <c r="D260" s="4" t="n">
-        <v>16.83</v>
+        <v>16.33</v>
       </c>
       <c r="E260" s="25" t="n">
-        <v>-0.205</v>
+        <v>-0.2178</v>
       </c>
       <c r="F260" s="25" t="n">
-        <v>-0.0053</v>
+        <v>-0.0242</v>
       </c>
       <c r="G260" s="6" t="n">
         <v>46331</v>
@@ -20160,13 +20180,13 @@
         </is>
       </c>
       <c r="D261" s="13" t="n">
-        <v>180.15</v>
+        <v>187.11</v>
       </c>
       <c r="E261" s="14" t="n">
-        <v>0.0866</v>
+        <v>0.1537</v>
       </c>
       <c r="F261" s="14" t="n">
-        <v>0.0559</v>
+        <v>0.0892</v>
       </c>
       <c r="G261" s="16" t="n">
         <v>46330</v>
@@ -20195,7 +20215,7 @@
         <v>265</v>
       </c>
       <c r="M261" s="14" t="n">
-        <v>0.4709963918956425</v>
+        <v>0.4162791940569717</v>
       </c>
       <c r="N261" s="12" t="inlineStr">
         <is>
@@ -20206,7 +20226,7 @@
         <v>179</v>
       </c>
       <c r="P261" s="15" t="n">
-        <v>-0.006383569247849046</v>
+        <v>-0.0433434877879323</v>
       </c>
       <c r="Q261" s="19" t="inlineStr">
         <is>
@@ -20251,13 +20271,13 @@
         </is>
       </c>
       <c r="D262" s="4" t="n">
-        <v>107.98</v>
+        <v>116.24</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>0.1006</v>
+        <v>0.2103</v>
       </c>
       <c r="F262" s="5" t="n">
-        <v>0.2932</v>
+        <v>0.3595</v>
       </c>
       <c r="G262" s="6" t="n">
         <v>46322</v>
@@ -20312,13 +20332,13 @@
         </is>
       </c>
       <c r="D263" s="13" t="n">
-        <v>7.97</v>
+        <v>7.86</v>
       </c>
       <c r="E263" s="15" t="n">
-        <v>-0.1154</v>
+        <v>-0.1314</v>
       </c>
       <c r="F263" s="14" t="n">
-        <v>0.0432</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="G263" s="16" t="n"/>
       <c r="H263" s="21" t="inlineStr">
@@ -20363,13 +20383,13 @@
         </is>
       </c>
       <c r="D264" s="4" t="n">
-        <v>100.2</v>
+        <v>98.77</v>
       </c>
       <c r="E264" s="25" t="n">
-        <v>-0.0199</v>
+        <v>-0.0223</v>
       </c>
       <c r="F264" s="5" t="n">
-        <v>0.2553</v>
+        <v>0.2507</v>
       </c>
       <c r="G264" s="6" t="n"/>
       <c r="H264" s="7" t="inlineStr">
@@ -20414,22 +20434,32 @@
         </is>
       </c>
       <c r="D265" s="13" t="n">
-        <v>15.27</v>
+        <v>15.02</v>
       </c>
       <c r="E265" s="15" t="n">
-        <v>-0.1886</v>
+        <v>-0.1952</v>
       </c>
       <c r="F265" s="14" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="G265" s="16" t="n"/>
-      <c r="H265" s="21" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="I265" s="12" t="inlineStr"/>
-      <c r="J265" s="12" t="inlineStr"/>
+        <v>0.06480000000000001</v>
+      </c>
+      <c r="G265" s="16" t="n">
+        <v>46335</v>
+      </c>
+      <c r="H265" s="23" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I265" s="12" t="inlineStr">
+        <is>
+          <t>Nasdaq</t>
+        </is>
+      </c>
+      <c r="J265" s="12" t="inlineStr">
+        <is>
+          <t>Nov 09</t>
+        </is>
+      </c>
       <c r="K265" s="12" t="inlineStr"/>
       <c r="L265" s="18" t="n"/>
       <c r="M265" s="24" t="n"/>
@@ -20465,13 +20495,13 @@
         </is>
       </c>
       <c r="D266" s="4" t="n">
-        <v>394.61</v>
+        <v>383.4</v>
       </c>
       <c r="E266" s="25" t="n">
-        <v>-0.0118</v>
+        <v>-0.0162</v>
       </c>
       <c r="F266" s="5" t="n">
-        <v>0.08349999999999999</v>
+        <v>0.0558</v>
       </c>
       <c r="G266" s="6" t="n">
         <v>46317</v>
@@ -20540,13 +20570,13 @@
         </is>
       </c>
       <c r="D267" s="13" t="n">
-        <v>3.49</v>
+        <v>3.38</v>
       </c>
       <c r="E267" s="15" t="n">
-        <v>-0.171</v>
+        <v>-0.1456</v>
       </c>
       <c r="F267" s="15" t="n">
-        <v>-0.171</v>
+        <v>-0.1867</v>
       </c>
       <c r="G267" s="16" t="n">
         <v>46331</v>
@@ -20601,13 +20631,13 @@
         </is>
       </c>
       <c r="D268" s="4" t="n">
-        <v>22.61</v>
-      </c>
-      <c r="E268" s="25" t="n">
-        <v>-0.0216</v>
+        <v>22.66</v>
+      </c>
+      <c r="E268" s="5" t="n">
+        <v>0.0385</v>
       </c>
       <c r="F268" s="5" t="n">
-        <v>0.1518</v>
+        <v>0.1579</v>
       </c>
       <c r="G268" s="6" t="n"/>
       <c r="H268" s="7" t="inlineStr">
@@ -20652,13 +20682,13 @@
         </is>
       </c>
       <c r="D269" s="13" t="n">
-        <v>19.88</v>
+        <v>19.9</v>
       </c>
       <c r="E269" s="14" t="n">
-        <v>0.0179</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="F269" s="14" t="n">
-        <v>0.2535</v>
+        <v>0.2691</v>
       </c>
       <c r="G269" s="16" t="n"/>
       <c r="H269" s="21" t="inlineStr">
@@ -20703,13 +20733,13 @@
         </is>
       </c>
       <c r="D270" s="4" t="n">
-        <v>196.04</v>
+        <v>193.77</v>
       </c>
       <c r="E270" s="25" t="n">
-        <v>-0.0702</v>
+        <v>-0.1072</v>
       </c>
       <c r="F270" s="25" t="n">
-        <v>-0.0101</v>
+        <v>-0.0176</v>
       </c>
       <c r="G270" s="6" t="n">
         <v>46328</v>
@@ -20764,13 +20794,13 @@
         </is>
       </c>
       <c r="D271" s="13" t="n">
-        <v>218.28</v>
+        <v>215.93</v>
       </c>
       <c r="E271" s="14" t="n">
-        <v>0.0496</v>
+        <v>0.0389</v>
       </c>
       <c r="F271" s="14" t="n">
-        <v>0.3504</v>
+        <v>0.3577</v>
       </c>
       <c r="G271" s="16" t="n">
         <v>46316</v>
@@ -20845,13 +20875,13 @@
         </is>
       </c>
       <c r="D272" s="4" t="n">
-        <v>36.74</v>
+        <v>36.44</v>
       </c>
       <c r="E272" s="25" t="n">
-        <v>-0.07780000000000001</v>
+        <v>-0.0479</v>
       </c>
       <c r="F272" s="5" t="n">
-        <v>0.4887</v>
+        <v>0.5072</v>
       </c>
       <c r="G272" s="6" t="n">
         <v>46329</v>
@@ -20906,13 +20936,13 @@
         </is>
       </c>
       <c r="D273" s="13" t="n">
-        <v>332.35</v>
-      </c>
-      <c r="E273" s="14" t="n">
-        <v>0.0104</v>
+        <v>324.13</v>
+      </c>
+      <c r="E273" s="15" t="n">
+        <v>-0.0181</v>
       </c>
       <c r="F273" s="14" t="n">
-        <v>0.2308</v>
+        <v>0.2054</v>
       </c>
       <c r="G273" s="16" t="n"/>
       <c r="H273" s="21" t="inlineStr">
@@ -20931,7 +20961,7 @@
         <v>320</v>
       </c>
       <c r="M273" s="15" t="n">
-        <v>-0.03715962088160079</v>
+        <v>-0.01274180112917655</v>
       </c>
       <c r="N273" s="12" t="inlineStr">
         <is>
@@ -20942,7 +20972,7 @@
         <v>280</v>
       </c>
       <c r="P273" s="15" t="n">
-        <v>-0.1575146682714007</v>
+        <v>-0.1361490759880295</v>
       </c>
       <c r="Q273" s="19" t="inlineStr">
         <is>
@@ -20983,13 +21013,13 @@
         </is>
       </c>
       <c r="D274" s="4" t="n">
-        <v>381.43</v>
+        <v>369.31</v>
       </c>
       <c r="E274" s="25" t="n">
-        <v>-0.0951</v>
+        <v>-0.1063</v>
       </c>
       <c r="F274" s="25" t="n">
-        <v>-0.08539999999999999</v>
+        <v>-0.039</v>
       </c>
       <c r="G274" s="6" t="n"/>
       <c r="H274" s="7" t="inlineStr">
@@ -21008,7 +21038,7 @@
         <v>535</v>
       </c>
       <c r="M274" s="5" t="n">
-        <v>0.4026164696012374</v>
+        <v>0.4486474777287374</v>
       </c>
       <c r="N274" s="3" t="inlineStr"/>
       <c r="O274" s="8" t="n"/>
@@ -21052,13 +21082,13 @@
         </is>
       </c>
       <c r="D275" s="13" t="n">
-        <v>6.47</v>
+        <v>6.26</v>
       </c>
       <c r="E275" s="15" t="n">
-        <v>-0.1292</v>
-      </c>
-      <c r="F275" s="14" t="n">
-        <v>0.0254</v>
+        <v>-0.1108</v>
+      </c>
+      <c r="F275" s="15" t="n">
+        <v>-0.0016</v>
       </c>
       <c r="G275" s="16" t="n">
         <v>46331</v>
@@ -21113,13 +21143,13 @@
         </is>
       </c>
       <c r="D276" s="4" t="n">
-        <v>79.26000000000001</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="E276" s="5" t="n">
-        <v>0.1385</v>
+        <v>0.2987</v>
       </c>
       <c r="F276" s="5" t="n">
-        <v>0.3753</v>
+        <v>0.4821</v>
       </c>
       <c r="G276" s="6" t="n">
         <v>46322</v>
@@ -21174,13 +21204,13 @@
         </is>
       </c>
       <c r="D277" s="13" t="n">
-        <v>95.06</v>
+        <v>96.66</v>
       </c>
       <c r="E277" s="15" t="n">
-        <v>-0.1249</v>
+        <v>-0.1259</v>
       </c>
       <c r="F277" s="15" t="n">
-        <v>-0.1773</v>
+        <v>-0.1525</v>
       </c>
       <c r="G277" s="16" t="n">
         <v>46331</v>
@@ -21235,13 +21265,13 @@
         </is>
       </c>
       <c r="D278" s="4" t="n">
-        <v>203.37</v>
+        <v>202.38</v>
       </c>
       <c r="E278" s="25" t="n">
-        <v>-0.0595</v>
-      </c>
-      <c r="F278" s="5" t="n">
-        <v>0.0039</v>
+        <v>-0.06900000000000001</v>
+      </c>
+      <c r="F278" s="25" t="n">
+        <v>-0.004500000000000001</v>
       </c>
       <c r="G278" s="6" t="n">
         <v>46330</v>
@@ -21296,13 +21326,13 @@
         </is>
       </c>
       <c r="D279" s="13" t="n">
-        <v>329.2</v>
+        <v>328.08</v>
       </c>
       <c r="E279" s="15" t="n">
-        <v>-0.2139</v>
+        <v>-0.2596</v>
       </c>
       <c r="F279" s="14" t="n">
-        <v>0.0214</v>
+        <v>0.0177</v>
       </c>
       <c r="G279" s="16" t="n">
         <v>46322</v>
@@ -21357,13 +21387,13 @@
         </is>
       </c>
       <c r="D280" s="4" t="n">
-        <v>58.74</v>
+        <v>58.64</v>
       </c>
       <c r="E280" s="5" t="n">
-        <v>0.0198</v>
+        <v>0.053</v>
       </c>
       <c r="F280" s="5" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.1123</v>
       </c>
       <c r="G280" s="6" t="n">
         <v>46330</v>
@@ -21418,13 +21448,13 @@
         </is>
       </c>
       <c r="D281" s="13" t="n">
-        <v>418.01</v>
+        <v>414.02</v>
       </c>
       <c r="E281" s="15" t="n">
-        <v>-0.0196</v>
+        <v>-0.0393</v>
       </c>
       <c r="F281" s="14" t="n">
-        <v>0.0202</v>
+        <v>0.0393</v>
       </c>
       <c r="G281" s="16" t="n">
         <v>46310</v>
@@ -21501,13 +21531,13 @@
         </is>
       </c>
       <c r="D282" s="4" t="n">
-        <v>113.22</v>
+        <v>112.1</v>
       </c>
       <c r="E282" s="25" t="n">
-        <v>-0.1913</v>
+        <v>-0.2049</v>
       </c>
       <c r="F282" s="25" t="n">
-        <v>-0.13</v>
+        <v>-0.1508</v>
       </c>
       <c r="G282" s="6" t="n">
         <v>46330</v>
@@ -21562,13 +21592,13 @@
         </is>
       </c>
       <c r="D283" s="13" t="n">
-        <v>231.88</v>
-      </c>
-      <c r="E283" s="15" t="n">
-        <v>-0.0265</v>
+        <v>235.85</v>
+      </c>
+      <c r="E283" s="14" t="n">
+        <v>0.0317</v>
       </c>
       <c r="F283" s="14" t="n">
-        <v>0.1218</v>
+        <v>0.1406</v>
       </c>
       <c r="G283" s="16" t="n">
         <v>46324</v>
@@ -21623,13 +21653,13 @@
         </is>
       </c>
       <c r="D284" s="4" t="n">
-        <v>263.42</v>
+        <v>264.43</v>
       </c>
       <c r="E284" s="25" t="n">
-        <v>-0.0578</v>
+        <v>-0.0653</v>
       </c>
       <c r="F284" s="25" t="n">
-        <v>-0.0955</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="G284" s="6" t="n">
         <v>46315</v>
@@ -21658,7 +21688,7 @@
         <v>300</v>
       </c>
       <c r="M284" s="5" t="n">
-        <v>0.1388656897729861</v>
+        <v>0.1345157508603411</v>
       </c>
       <c r="N284" s="3" t="inlineStr">
         <is>
@@ -21669,7 +21699,7 @@
         <v>316</v>
       </c>
       <c r="P284" s="5" t="n">
-        <v>0.1996051932275453</v>
+        <v>0.1950232575728926</v>
       </c>
       <c r="Q284" s="9" t="inlineStr">
         <is>
@@ -21726,13 +21756,13 @@
         </is>
       </c>
       <c r="D285" s="13" t="n">
-        <v>359.54</v>
+        <v>348.73</v>
       </c>
       <c r="E285" s="14" t="n">
-        <v>0.094</v>
+        <v>0.08810000000000001</v>
       </c>
       <c r="F285" s="14" t="n">
-        <v>0.137</v>
+        <v>0.0915</v>
       </c>
       <c r="G285" s="16" t="n">
         <v>46330</v>
@@ -21761,7 +21791,7 @@
         <v>335</v>
       </c>
       <c r="M285" s="15" t="n">
-        <v>-0.06825387995772381</v>
+        <v>-0.03937143348722513</v>
       </c>
       <c r="N285" s="12" t="inlineStr">
         <is>
@@ -21772,7 +21802,7 @@
         <v>375</v>
       </c>
       <c r="P285" s="14" t="n">
-        <v>0.04299938810702558</v>
+        <v>0.07533048490235994</v>
       </c>
       <c r="Q285" s="19" t="inlineStr">
         <is>
@@ -21813,13 +21843,13 @@
         </is>
       </c>
       <c r="D286" s="4" t="n">
-        <v>43.45</v>
+        <v>42.89</v>
       </c>
       <c r="E286" s="25" t="n">
-        <v>-0.0605</v>
+        <v>-0.0563</v>
       </c>
       <c r="F286" s="5" t="n">
-        <v>0.4392</v>
+        <v>0.4795</v>
       </c>
       <c r="G286" s="6" t="n">
         <v>46330</v>
@@ -21874,13 +21904,13 @@
         </is>
       </c>
       <c r="D287" s="13" t="n">
-        <v>6.16</v>
+        <v>6.01</v>
       </c>
       <c r="E287" s="15" t="n">
-        <v>-0.1895</v>
+        <v>-0.2405</v>
       </c>
       <c r="F287" s="15" t="n">
-        <v>-0.2021</v>
+        <v>-0.1861</v>
       </c>
       <c r="G287" s="16" t="n"/>
       <c r="H287" s="21" t="inlineStr">
@@ -21925,13 +21955,13 @@
         </is>
       </c>
       <c r="D288" s="4" t="n">
-        <v>194.21</v>
-      </c>
-      <c r="E288" s="25" t="n">
-        <v>-0.0225</v>
+        <v>191.92</v>
+      </c>
+      <c r="E288" s="5" t="n">
+        <v>0.0039</v>
       </c>
       <c r="F288" s="5" t="n">
-        <v>0.3354</v>
+        <v>0.3256</v>
       </c>
       <c r="G288" s="6" t="n"/>
       <c r="H288" s="7" t="inlineStr">
@@ -21976,13 +22006,13 @@
         </is>
       </c>
       <c r="D289" s="13" t="n">
-        <v>426.94</v>
+        <v>416.68</v>
       </c>
       <c r="E289" s="15" t="n">
-        <v>-0.1609</v>
+        <v>-0.2226</v>
       </c>
       <c r="F289" s="15" t="n">
-        <v>-0.08539999999999999</v>
+        <v>-0.1269</v>
       </c>
       <c r="G289" s="16" t="n">
         <v>46324</v>
@@ -22011,7 +22041,7 @@
         <v>730</v>
       </c>
       <c r="M289" s="14" t="n">
-        <v>0.7098421323839416</v>
+        <v>0.7519439377939906</v>
       </c>
       <c r="N289" s="12" t="inlineStr">
         <is>
@@ -22022,7 +22052,7 @@
         <v>575</v>
       </c>
       <c r="P289" s="14" t="n">
-        <v>0.346793460439406</v>
+        <v>0.3799558414130748</v>
       </c>
       <c r="Q289" s="19" t="inlineStr">
         <is>
@@ -22063,13 +22093,13 @@
         </is>
       </c>
       <c r="D290" s="4" t="n">
-        <v>23.96</v>
+        <v>23.6</v>
       </c>
       <c r="E290" s="25" t="n">
-        <v>-0.2463</v>
+        <v>-0.3249</v>
       </c>
       <c r="F290" s="25" t="n">
-        <v>-0.2316</v>
+        <v>-0.2104</v>
       </c>
       <c r="G290" s="6" t="n">
         <v>46330</v>
@@ -22124,13 +22154,13 @@
         </is>
       </c>
       <c r="D291" s="13" t="n">
-        <v>95.36</v>
+        <v>93.3</v>
       </c>
       <c r="E291" s="15" t="n">
-        <v>-0.1</v>
+        <v>-0.1161</v>
       </c>
       <c r="F291" s="14" t="n">
-        <v>0.0263</v>
+        <v>0.0238</v>
       </c>
       <c r="G291" s="16" t="n"/>
       <c r="H291" s="21" t="inlineStr">
@@ -22175,13 +22205,13 @@
         </is>
       </c>
       <c r="D292" s="4" t="n">
-        <v>191.73</v>
+        <v>190.84</v>
       </c>
       <c r="E292" s="5" t="n">
-        <v>0.0443</v>
+        <v>0.0347</v>
       </c>
       <c r="F292" s="5" t="n">
-        <v>0.3094</v>
+        <v>0.2728</v>
       </c>
       <c r="G292" s="6" t="n"/>
       <c r="H292" s="7" t="inlineStr">
@@ -22226,13 +22256,13 @@
         </is>
       </c>
       <c r="D293" s="13" t="n">
-        <v>287.13</v>
+        <v>286.99</v>
       </c>
       <c r="E293" s="15" t="n">
-        <v>-0.0707</v>
+        <v>-0.0461</v>
       </c>
       <c r="F293" s="15" t="n">
-        <v>-0.0342</v>
+        <v>-0.0292</v>
       </c>
       <c r="G293" s="16" t="n">
         <v>46331</v>
@@ -22287,13 +22317,13 @@
         </is>
       </c>
       <c r="D294" s="4" t="n">
-        <v>84.73999999999999</v>
+        <v>84.22</v>
       </c>
       <c r="E294" s="25" t="n">
-        <v>-0.0235</v>
+        <v>-0.047</v>
       </c>
       <c r="F294" s="5" t="n">
-        <v>0.0499</v>
+        <v>0.0444</v>
       </c>
       <c r="G294" s="6" t="n"/>
       <c r="H294" s="7" t="inlineStr">
@@ -22338,13 +22368,13 @@
         </is>
       </c>
       <c r="D295" s="13" t="n">
-        <v>124.29</v>
+        <v>123.52</v>
       </c>
       <c r="E295" s="15" t="n">
-        <v>-0.1502</v>
+        <v>-0.1366</v>
       </c>
       <c r="F295" s="15" t="n">
-        <v>-0.0745</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="G295" s="16" t="n">
         <v>46331</v>
@@ -22373,7 +22403,7 @@
         <v>166</v>
       </c>
       <c r="M295" s="14" t="n">
-        <v>0.3355861292139351</v>
+        <v>0.3439119170984457</v>
       </c>
       <c r="N295" s="12" t="inlineStr"/>
       <c r="O295" s="18" t="n"/>
@@ -22421,13 +22451,13 @@
         </is>
       </c>
       <c r="D296" s="4" t="n">
-        <v>28.9</v>
+        <v>29.69</v>
       </c>
       <c r="E296" s="25" t="n">
-        <v>-0.0698</v>
+        <v>-0.0527</v>
       </c>
       <c r="F296" s="25" t="n">
-        <v>-0.0137</v>
+        <v>-0.0077</v>
       </c>
       <c r="G296" s="6" t="n">
         <v>46317</v>
@@ -22482,13 +22512,13 @@
         </is>
       </c>
       <c r="D297" s="13" t="n">
-        <v>275.51</v>
+        <v>273.81</v>
       </c>
       <c r="E297" s="15" t="n">
-        <v>-0.0022</v>
-      </c>
-      <c r="F297" s="15" t="n">
-        <v>-0.0007000000000000001</v>
+        <v>-0.0074</v>
+      </c>
+      <c r="F297" s="14" t="n">
+        <v>0.0036</v>
       </c>
       <c r="G297" s="16" t="n">
         <v>46322</v>
@@ -22516,8 +22546,8 @@
       <c r="L297" s="18" t="n">
         <v>275</v>
       </c>
-      <c r="M297" s="15" t="n">
-        <v>-0.00185111248230551</v>
+      <c r="M297" s="14" t="n">
+        <v>0.004346079398122778</v>
       </c>
       <c r="N297" s="12" t="inlineStr">
         <is>
@@ -22528,7 +22558,7 @@
         <v>312</v>
       </c>
       <c r="P297" s="14" t="n">
-        <v>0.1324452832928025</v>
+        <v>0.1394762791716884</v>
       </c>
       <c r="Q297" s="19" t="inlineStr">
         <is>
@@ -22581,13 +22611,13 @@
         </is>
       </c>
       <c r="D298" s="4" t="n">
-        <v>32.13</v>
+        <v>31.72</v>
       </c>
       <c r="E298" s="25" t="n">
-        <v>-0.1721</v>
+        <v>-0.1912</v>
       </c>
       <c r="F298" s="25" t="n">
-        <v>-0.1462</v>
+        <v>-0.1519</v>
       </c>
       <c r="G298" s="6" t="n">
         <v>46322</v>
@@ -22646,13 +22676,13 @@
         </is>
       </c>
       <c r="D299" s="13" t="n">
-        <v>69.34</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="E299" s="14" t="n">
-        <v>0.0429</v>
+        <v>0.0019</v>
       </c>
       <c r="F299" s="14" t="n">
-        <v>0.1841</v>
+        <v>0.1735</v>
       </c>
       <c r="G299" s="16" t="n">
         <v>46310</v>
@@ -22707,13 +22737,13 @@
         </is>
       </c>
       <c r="D300" s="4" t="n">
-        <v>464.41</v>
+        <v>460.35</v>
       </c>
       <c r="E300" s="25" t="n">
-        <v>-0.038</v>
+        <v>-0.0295</v>
       </c>
       <c r="F300" s="25" t="n">
-        <v>-0.1082</v>
+        <v>-0.103</v>
       </c>
       <c r="G300" s="6" t="n">
         <v>46325</v>
@@ -22742,7 +22772,7 @@
         <v>570</v>
       </c>
       <c r="M300" s="5" t="n">
-        <v>0.2273637518571951</v>
+        <v>0.2381883349625284</v>
       </c>
       <c r="N300" s="3" t="inlineStr">
         <is>
@@ -22753,7 +22783,7 @@
         <v>525</v>
       </c>
       <c r="P300" s="5" t="n">
-        <v>0.1304666135526797</v>
+        <v>0.140436624307592</v>
       </c>
       <c r="Q300" s="9" t="inlineStr">
         <is>
@@ -22806,13 +22836,13 @@
         </is>
       </c>
       <c r="D301" s="13" t="n">
-        <v>500.92</v>
+        <v>496.03</v>
       </c>
       <c r="E301" s="15" t="n">
-        <v>-0.0858</v>
+        <v>-0.0791</v>
       </c>
       <c r="F301" s="15" t="n">
-        <v>-0.1317</v>
+        <v>-0.1183</v>
       </c>
       <c r="G301" s="16" t="n">
         <v>46329</v>
@@ -22841,7 +22871,7 @@
         <v>616</v>
       </c>
       <c r="M301" s="14" t="n">
-        <v>0.2297372833985466</v>
+        <v>0.2418603713485072</v>
       </c>
       <c r="N301" s="12" t="inlineStr"/>
       <c r="O301" s="18" t="n"/>
@@ -22885,13 +22915,13 @@
         </is>
       </c>
       <c r="D302" s="4" t="n">
-        <v>254.63</v>
+        <v>256.82</v>
       </c>
       <c r="E302" s="25" t="n">
-        <v>-0.05309999999999999</v>
+        <v>-0.0582</v>
       </c>
       <c r="F302" s="5" t="n">
-        <v>0.0805</v>
+        <v>0.08539999999999999</v>
       </c>
       <c r="G302" s="6" t="n">
         <v>46321</v>
@@ -22920,7 +22950,7 @@
         <v>283</v>
       </c>
       <c r="M302" s="5" t="n">
-        <v>0.1114165652122688</v>
+        <v>0.1019391013160969</v>
       </c>
       <c r="N302" s="3" t="inlineStr"/>
       <c r="O302" s="8" t="n"/>
@@ -22966,13 +22996,13 @@
         </is>
       </c>
       <c r="D303" s="13" t="n">
-        <v>233.26</v>
+        <v>229.7</v>
       </c>
       <c r="E303" s="15" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.092</v>
       </c>
       <c r="F303" s="15" t="n">
-        <v>-0.0033</v>
+        <v>-0.0145</v>
       </c>
       <c r="G303" s="16" t="n">
         <v>46323</v>
@@ -23001,7 +23031,7 @@
         <v>246</v>
       </c>
       <c r="M303" s="14" t="n">
-        <v>0.05461716539483842</v>
+        <v>0.07096212451023079</v>
       </c>
       <c r="N303" s="12" t="inlineStr"/>
       <c r="O303" s="18" t="n"/>
@@ -23049,13 +23079,13 @@
         </is>
       </c>
       <c r="D304" s="4" t="n">
-        <v>105.25</v>
+        <v>104.64</v>
       </c>
       <c r="E304" s="25" t="n">
         <v>-0.0776</v>
       </c>
       <c r="F304" s="25" t="n">
-        <v>-0.1132</v>
+        <v>-0.1084</v>
       </c>
       <c r="G304" s="6" t="n">
         <v>46322</v>
@@ -23084,7 +23114,7 @@
         <v>130</v>
       </c>
       <c r="M304" s="5" t="n">
-        <v>0.2351543942992874</v>
+        <v>0.2423547400611621</v>
       </c>
       <c r="N304" s="3" t="inlineStr">
         <is>
@@ -23095,7 +23125,7 @@
         <v>128</v>
       </c>
       <c r="P304" s="5" t="n">
-        <v>0.2161520190023753</v>
+        <v>0.2232415902140673</v>
       </c>
       <c r="Q304" s="9" t="inlineStr">
         <is>
@@ -23144,13 +23174,13 @@
         </is>
       </c>
       <c r="D305" s="13" t="n">
-        <v>100.81</v>
+        <v>100.15</v>
       </c>
       <c r="E305" s="15" t="n">
-        <v>-0.1143</v>
+        <v>-0.1076</v>
       </c>
       <c r="F305" s="15" t="n">
-        <v>-0.0517</v>
+        <v>-0.0469</v>
       </c>
       <c r="G305" s="16" t="n">
         <v>46301</v>
@@ -23179,7 +23209,7 @@
         <v>135</v>
       </c>
       <c r="M305" s="14" t="n">
-        <v>0.3391528618192639</v>
+        <v>0.3479780329505741</v>
       </c>
       <c r="N305" s="12" t="inlineStr">
         <is>
@@ -23190,7 +23220,7 @@
         <v>125</v>
       </c>
       <c r="P305" s="14" t="n">
-        <v>0.2399563535363555</v>
+        <v>0.2481278082875686</v>
       </c>
       <c r="Q305" s="19" t="inlineStr"/>
       <c r="R305" s="18" t="n"/>
@@ -23225,13 +23255,13 @@
         </is>
       </c>
       <c r="D306" s="4" t="n">
-        <v>324.5</v>
+        <v>320.7</v>
       </c>
       <c r="E306" s="25" t="n">
-        <v>-0.0964</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="F306" s="25" t="n">
-        <v>-0.0403</v>
+        <v>-0.0321</v>
       </c>
       <c r="G306" s="6" t="n">
         <v>46322</v>
@@ -23260,7 +23290,7 @@
         <v>350</v>
       </c>
       <c r="M306" s="5" t="n">
-        <v>0.07858243451463791</v>
+        <v>0.09136264421577803</v>
       </c>
       <c r="N306" s="3" t="inlineStr">
         <is>
@@ -23271,7 +23301,7 @@
         <v>400</v>
       </c>
       <c r="P306" s="5" t="n">
-        <v>0.2326656394453005</v>
+        <v>0.2472715933894606</v>
       </c>
       <c r="Q306" s="9" t="inlineStr">
         <is>
@@ -23312,13 +23342,13 @@
         </is>
       </c>
       <c r="D307" s="13" t="n">
-        <v>93.78</v>
+        <v>97.13</v>
       </c>
       <c r="E307" s="15" t="n">
-        <v>-0.2063</v>
+        <v>-0.1698</v>
       </c>
       <c r="F307" s="14" t="n">
-        <v>0.3717</v>
+        <v>0.4</v>
       </c>
       <c r="G307" s="16" t="n"/>
       <c r="H307" s="21" t="inlineStr">
@@ -23359,13 +23389,13 @@
         </is>
       </c>
       <c r="D308" s="4" t="n">
-        <v>49.1</v>
+        <v>48.78</v>
       </c>
       <c r="E308" s="25" t="n">
-        <v>-0.2279</v>
+        <v>-0.261</v>
       </c>
       <c r="F308" s="25" t="n">
-        <v>-0.1313</v>
+        <v>-0.13</v>
       </c>
       <c r="G308" s="6" t="n">
         <v>46267</v>
@@ -23420,13 +23450,13 @@
         </is>
       </c>
       <c r="D309" s="13" t="n">
-        <v>70.78</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="E309" s="15" t="n">
-        <v>-0.053</v>
+        <v>-0.0547</v>
       </c>
       <c r="F309" s="15" t="n">
-        <v>-0.1235</v>
+        <v>-0.1313</v>
       </c>
       <c r="G309" s="16" t="n">
         <v>46315</v>
@@ -23455,14 +23485,14 @@
         <v>83</v>
       </c>
       <c r="M309" s="14" t="n">
-        <v>0.172647640576434</v>
+        <v>0.1779733181947205</v>
       </c>
       <c r="N309" s="12" t="inlineStr"/>
       <c r="O309" s="18" t="n">
         <v>87</v>
       </c>
       <c r="P309" s="14" t="n">
-        <v>0.2291607798813224</v>
+        <v>0.234743116661936</v>
       </c>
       <c r="Q309" s="19" t="inlineStr"/>
       <c r="R309" s="18" t="n"/>
@@ -23497,13 +23527,13 @@
         </is>
       </c>
       <c r="D310" s="4" t="n">
-        <v>176.94</v>
+        <v>178.4</v>
       </c>
       <c r="E310" s="5" t="n">
-        <v>0.0077</v>
+        <v>0.0358</v>
       </c>
       <c r="F310" s="5" t="n">
-        <v>0.0475</v>
+        <v>0.049</v>
       </c>
       <c r="G310" s="6" t="n">
         <v>46322</v>
@@ -23532,7 +23562,7 @@
         <v>200</v>
       </c>
       <c r="M310" s="5" t="n">
-        <v>0.1303266644060133</v>
+        <v>0.1210762331838565</v>
       </c>
       <c r="N310" s="3" t="inlineStr"/>
       <c r="O310" s="8" t="n"/>
@@ -23580,13 +23610,13 @@
         </is>
       </c>
       <c r="D311" s="13" t="n">
-        <v>140.9</v>
+        <v>139.5</v>
       </c>
       <c r="E311" s="15" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.0572</v>
       </c>
       <c r="F311" s="15" t="n">
-        <v>-0.0194</v>
+        <v>-0.0104</v>
       </c>
       <c r="G311" s="16" t="n">
         <v>46317</v>
@@ -23645,13 +23675,13 @@
         </is>
       </c>
       <c r="D312" s="4" t="n">
-        <v>179.14</v>
+        <v>179.09</v>
       </c>
       <c r="E312" s="25" t="n">
-        <v>-0.105</v>
+        <v>-0.0951</v>
       </c>
       <c r="F312" s="5" t="n">
-        <v>0.0319</v>
+        <v>0.03</v>
       </c>
       <c r="G312" s="6" t="n">
         <v>46317</v>
@@ -23680,7 +23710,7 @@
         <v>220</v>
       </c>
       <c r="M312" s="5" t="n">
-        <v>0.2280897621971643</v>
+        <v>0.228432631637724</v>
       </c>
       <c r="N312" s="3" t="inlineStr">
         <is>
@@ -23691,7 +23721,7 @@
         <v>230</v>
       </c>
       <c r="P312" s="5" t="n">
-        <v>0.2839120241152173</v>
+        <v>0.2842704785303479</v>
       </c>
       <c r="Q312" s="9" t="inlineStr">
         <is>
@@ -23732,13 +23762,13 @@
         </is>
       </c>
       <c r="D313" s="13" t="n">
-        <v>998.72</v>
+        <v>1006.34</v>
       </c>
       <c r="E313" s="15" t="n">
-        <v>-0.09380000000000001</v>
+        <v>-0.0832</v>
       </c>
       <c r="F313" s="15" t="n">
-        <v>-0.0103</v>
+        <v>-0.0134</v>
       </c>
       <c r="G313" s="16" t="n">
         <v>46330</v>
@@ -23767,7 +23797,7 @@
         <v>1200</v>
       </c>
       <c r="M313" s="14" t="n">
-        <v>0.2015379685998077</v>
+        <v>0.192439930838484</v>
       </c>
       <c r="N313" s="12" t="inlineStr">
         <is>
@@ -23778,7 +23808,7 @@
         <v>1240</v>
       </c>
       <c r="P313" s="14" t="n">
-        <v>0.2415892342198013</v>
+        <v>0.2321879285331001</v>
       </c>
       <c r="Q313" s="19" t="inlineStr">
         <is>
@@ -23823,13 +23853,13 @@
         </is>
       </c>
       <c r="D314" s="4" t="n">
-        <v>114.53</v>
+        <v>113.9</v>
       </c>
       <c r="E314" s="25" t="n">
-        <v>-0.0326</v>
+        <v>-0.0349</v>
       </c>
       <c r="F314" s="25" t="n">
-        <v>-0.0864</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="G314" s="6" t="n">
         <v>46325</v>
@@ -23858,7 +23888,7 @@
         <v>129</v>
       </c>
       <c r="M314" s="5" t="n">
-        <v>0.1263424430280276</v>
+        <v>0.1325724319578577</v>
       </c>
       <c r="N314" s="3" t="inlineStr">
         <is>
@@ -23869,7 +23899,7 @@
         <v>122</v>
       </c>
       <c r="P314" s="5" t="n">
-        <v>0.06522308565441368</v>
+        <v>0.07111501316944684</v>
       </c>
       <c r="Q314" s="9" t="inlineStr">
         <is>
@@ -23910,13 +23940,13 @@
         </is>
       </c>
       <c r="D315" s="13" t="n">
-        <v>59.27</v>
+        <v>59.06</v>
       </c>
       <c r="E315" s="15" t="n">
-        <v>-0.0553</v>
+        <v>-0.0536</v>
       </c>
       <c r="F315" s="15" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.1013</v>
       </c>
       <c r="G315" s="16" t="n">
         <v>46328</v>
@@ -23945,14 +23975,14 @@
         <v>65</v>
       </c>
       <c r="M315" s="14" t="n">
-        <v>0.09667622743377757</v>
+        <v>0.1005756857433118</v>
       </c>
       <c r="N315" s="12" t="inlineStr"/>
       <c r="O315" s="18" t="n">
         <v>67</v>
       </c>
       <c r="P315" s="14" t="n">
-        <v>0.1304201113548169</v>
+        <v>0.1344395529969522</v>
       </c>
       <c r="Q315" s="19" t="inlineStr">
         <is>
@@ -23993,13 +24023,13 @@
         </is>
       </c>
       <c r="D316" s="4" t="n">
-        <v>135.19</v>
+        <v>135.05</v>
       </c>
       <c r="E316" s="25" t="n">
-        <v>-0.0414</v>
+        <v>-0.0396</v>
       </c>
       <c r="F316" s="25" t="n">
-        <v>-0.09910000000000001</v>
+        <v>-0.0984</v>
       </c>
       <c r="G316" s="6" t="n">
         <v>46310</v>
@@ -24028,7 +24058,7 @@
         <v>167</v>
       </c>
       <c r="M316" s="5" t="n">
-        <v>0.2352984688216584</v>
+        <v>0.2365790447982228</v>
       </c>
       <c r="N316" s="3" t="inlineStr"/>
       <c r="O316" s="8" t="n"/>
@@ -24072,13 +24102,13 @@
         </is>
       </c>
       <c r="D317" s="13" t="n">
-        <v>295.4</v>
+        <v>295.55</v>
       </c>
       <c r="E317" s="15" t="n">
-        <v>-0.09369999999999999</v>
+        <v>-0.08869999999999999</v>
       </c>
       <c r="F317" s="15" t="n">
-        <v>-0.0897</v>
+        <v>-0.0707</v>
       </c>
       <c r="G317" s="16" t="n">
         <v>46330</v>
@@ -24114,7 +24144,7 @@
         <v>316</v>
       </c>
       <c r="P317" s="14" t="n">
-        <v>0.06973595125253901</v>
+        <v>0.06919302994417184</v>
       </c>
       <c r="Q317" s="19" t="inlineStr">
         <is>
@@ -24155,13 +24185,13 @@
         </is>
       </c>
       <c r="D318" s="4" t="n">
-        <v>204.97</v>
+        <v>204.16</v>
       </c>
       <c r="E318" s="25" t="n">
-        <v>-0.0665</v>
+        <v>-0.079</v>
       </c>
       <c r="F318" s="25" t="n">
-        <v>-0.1029</v>
+        <v>-0.1073</v>
       </c>
       <c r="G318" s="6" t="n">
         <v>46328</v>
@@ -24197,7 +24227,7 @@
         <v>215</v>
       </c>
       <c r="P318" s="5" t="n">
-        <v>0.04893399034004977</v>
+        <v>0.05309561128526648</v>
       </c>
       <c r="Q318" s="9" t="inlineStr">
         <is>
@@ -24238,13 +24268,13 @@
         </is>
       </c>
       <c r="D319" s="13" t="n">
-        <v>118.04</v>
+        <v>117.63</v>
       </c>
       <c r="E319" s="15" t="n">
-        <v>-0.0426</v>
+        <v>-0.0308</v>
       </c>
       <c r="F319" s="15" t="n">
-        <v>-0.0322</v>
+        <v>-0.0316</v>
       </c>
       <c r="G319" s="16" t="n">
         <v>46330</v>
@@ -24273,7 +24303,7 @@
         <v>142</v>
       </c>
       <c r="M319" s="14" t="n">
-        <v>0.2029820399864452</v>
+        <v>0.2071750403808553</v>
       </c>
       <c r="N319" s="12" t="inlineStr">
         <is>
@@ -24284,7 +24314,7 @@
         <v>137</v>
       </c>
       <c r="P319" s="14" t="n">
-        <v>0.1606235174517112</v>
+        <v>0.1646688769871632</v>
       </c>
       <c r="Q319" s="19" t="inlineStr">
         <is>
@@ -24333,13 +24363,13 @@
         </is>
       </c>
       <c r="D320" s="4" t="n">
-        <v>234.21</v>
+        <v>233.14</v>
       </c>
       <c r="E320" s="25" t="n">
-        <v>-0.005600000000000001</v>
+        <v>-0.0092</v>
       </c>
       <c r="F320" s="25" t="n">
-        <v>-0.0301</v>
+        <v>-0.0416</v>
       </c>
       <c r="G320" s="6" t="n">
         <v>46321</v>
@@ -24368,7 +24398,7 @@
         <v>237</v>
       </c>
       <c r="M320" s="5" t="n">
-        <v>0.01191238631996922</v>
+        <v>0.01655657544822859</v>
       </c>
       <c r="N320" s="3" t="inlineStr">
         <is>
@@ -24379,7 +24409,7 @@
         <v>236</v>
       </c>
       <c r="P320" s="5" t="n">
-        <v>0.00764271380385121</v>
+        <v>0.01226730719739218</v>
       </c>
       <c r="Q320" s="9" t="inlineStr">
         <is>
@@ -24420,13 +24450,13 @@
         </is>
       </c>
       <c r="D321" s="13" t="n">
-        <v>163.84</v>
+        <v>163.47</v>
       </c>
       <c r="E321" s="15" t="n">
-        <v>-0.0358</v>
+        <v>-0.0378</v>
       </c>
       <c r="F321" s="15" t="n">
-        <v>-0.07980000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="G321" s="16" t="n">
         <v>46330</v>
@@ -24455,7 +24485,7 @@
         <v>200</v>
       </c>
       <c r="M321" s="14" t="n">
-        <v>0.220703125</v>
+        <v>0.2234660794029486</v>
       </c>
       <c r="N321" s="12" t="inlineStr"/>
       <c r="O321" s="18" t="n"/>
@@ -24499,13 +24529,13 @@
         </is>
       </c>
       <c r="D322" s="4" t="n">
-        <v>138.92</v>
+        <v>139.18</v>
       </c>
       <c r="E322" s="5" t="n">
-        <v>0.02</v>
+        <v>0.036</v>
       </c>
       <c r="F322" s="5" t="n">
-        <v>0.0342</v>
+        <v>0.0302</v>
       </c>
       <c r="G322" s="6" t="n">
         <v>46330</v>
@@ -24534,7 +24564,7 @@
         <v>131</v>
       </c>
       <c r="M322" s="25" t="n">
-        <v>-0.05701122948459537</v>
+        <v>-0.05877281218565891</v>
       </c>
       <c r="N322" s="3" t="inlineStr"/>
       <c r="O322" s="8" t="n"/>
@@ -24578,13 +24608,13 @@
         </is>
       </c>
       <c r="D323" s="13" t="n">
-        <v>29.71</v>
+        <v>29.62</v>
       </c>
       <c r="E323" s="15" t="n">
-        <v>-0.1631</v>
+        <v>-0.1561</v>
       </c>
       <c r="F323" s="15" t="n">
-        <v>-0.1282</v>
+        <v>-0.1265</v>
       </c>
       <c r="G323" s="16" t="n">
         <v>46330</v>
@@ -24657,13 +24687,13 @@
         </is>
       </c>
       <c r="D324" s="4" t="n">
-        <v>35.65</v>
+        <v>35.85</v>
       </c>
       <c r="E324" s="25" t="n">
-        <v>-0.1029</v>
+        <v>-0.0786</v>
       </c>
       <c r="F324" s="25" t="n">
-        <v>-0.08960000000000001</v>
+        <v>-0.08689999999999999</v>
       </c>
       <c r="G324" s="6" t="n">
         <v>46332</v>
@@ -24718,13 +24748,13 @@
         </is>
       </c>
       <c r="D325" s="13" t="n">
-        <v>264.57</v>
+        <v>261.22</v>
       </c>
       <c r="E325" s="15" t="n">
-        <v>-0.0635</v>
+        <v>-0.061</v>
       </c>
       <c r="F325" s="14" t="n">
-        <v>0.0508</v>
+        <v>0.035</v>
       </c>
       <c r="G325" s="16" t="n">
         <v>46332</v>
@@ -24753,7 +24783,7 @@
         <v>384</v>
       </c>
       <c r="M325" s="14" t="n">
-        <v>0.4514117246853385</v>
+        <v>0.4700252660592603</v>
       </c>
       <c r="N325" s="12" t="inlineStr">
         <is>
@@ -24764,7 +24794,7 @@
         <v>380</v>
       </c>
       <c r="P325" s="14" t="n">
-        <v>0.4362928525531996</v>
+        <v>0.454712502871143</v>
       </c>
       <c r="Q325" s="19" t="inlineStr"/>
       <c r="R325" s="18" t="n"/>
@@ -24807,13 +24837,13 @@
         </is>
       </c>
       <c r="D326" s="4" t="n">
-        <v>66.81999999999999</v>
+        <v>66.36</v>
       </c>
       <c r="E326" s="25" t="n">
-        <v>-0.0603</v>
+        <v>-0.0706</v>
       </c>
       <c r="F326" s="25" t="n">
-        <v>-0.1018</v>
+        <v>-0.099</v>
       </c>
       <c r="G326" s="6" t="n">
         <v>46324</v>
@@ -24842,7 +24872,7 @@
         <v>79</v>
       </c>
       <c r="M326" s="5" t="n">
-        <v>0.1822807542651902</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="N326" s="3" t="inlineStr"/>
       <c r="O326" s="8" t="n"/>
@@ -24894,13 +24924,13 @@
         </is>
       </c>
       <c r="D327" s="13" t="n">
-        <v>119.02</v>
+        <v>118.26</v>
       </c>
       <c r="E327" s="15" t="n">
-        <v>-0.0395</v>
+        <v>-0.043</v>
       </c>
       <c r="F327" s="15" t="n">
-        <v>-0.0562</v>
+        <v>-0.05400000000000001</v>
       </c>
       <c r="G327" s="16" t="n">
         <v>46331</v>
@@ -24929,7 +24959,7 @@
         <v>136</v>
       </c>
       <c r="M327" s="14" t="n">
-        <v>0.1426650983028063</v>
+        <v>0.150008455944529</v>
       </c>
       <c r="N327" s="12" t="inlineStr">
         <is>
@@ -24940,7 +24970,7 @@
         <v>140</v>
       </c>
       <c r="P327" s="14" t="n">
-        <v>0.1762728953117124</v>
+        <v>0.1838322340605445</v>
       </c>
       <c r="Q327" s="19" t="inlineStr">
         <is>
@@ -24981,13 +25011,13 @@
         </is>
       </c>
       <c r="D328" s="4" t="n">
-        <v>103.64</v>
+        <v>102.76</v>
       </c>
       <c r="E328" s="25" t="n">
-        <v>-0.0389</v>
+        <v>-0.053</v>
       </c>
       <c r="F328" s="25" t="n">
-        <v>-0.0978</v>
+        <v>-0.0925</v>
       </c>
       <c r="G328" s="6" t="n">
         <v>46330</v>
@@ -25016,7 +25046,7 @@
         <v>131</v>
       </c>
       <c r="M328" s="5" t="n">
-        <v>0.263990737167117</v>
+        <v>0.2748151031529777</v>
       </c>
       <c r="N328" s="3" t="inlineStr">
         <is>
@@ -25027,7 +25057,7 @@
         <v>121</v>
       </c>
       <c r="P328" s="5" t="n">
-        <v>0.167502894635276</v>
+        <v>0.1775009731413001</v>
       </c>
       <c r="Q328" s="9" t="inlineStr">
         <is>
@@ -25072,13 +25102,13 @@
         </is>
       </c>
       <c r="D329" s="13" t="n">
-        <v>81.63</v>
+        <v>81.42</v>
       </c>
       <c r="E329" s="15" t="n">
-        <v>-0.0529</v>
+        <v>-0.0557</v>
       </c>
       <c r="F329" s="15" t="n">
-        <v>-0.0864</v>
+        <v>-0.0832</v>
       </c>
       <c r="G329" s="16" t="n">
         <v>46322</v>
@@ -25114,7 +25144,7 @@
         <v>107</v>
       </c>
       <c r="P329" s="14" t="n">
-        <v>0.3107926007595248</v>
+        <v>0.3141734217636944</v>
       </c>
       <c r="Q329" s="19" t="inlineStr">
         <is>
@@ -25163,13 +25193,13 @@
         </is>
       </c>
       <c r="D330" s="4" t="n">
-        <v>53.1</v>
+        <v>53.21</v>
       </c>
       <c r="E330" s="25" t="n">
-        <v>-0.045</v>
+        <v>-0.032</v>
       </c>
       <c r="F330" s="25" t="n">
-        <v>-0.1044</v>
+        <v>-0.092</v>
       </c>
       <c r="G330" s="6" t="n"/>
       <c r="H330" s="7" t="inlineStr">
@@ -25188,7 +25218,7 @@
         <v>63</v>
       </c>
       <c r="M330" s="5" t="n">
-        <v>0.1864406779661017</v>
+        <v>0.1839879721856794</v>
       </c>
       <c r="N330" s="3" t="inlineStr"/>
       <c r="O330" s="8" t="n"/>
@@ -25232,13 +25262,13 @@
         </is>
       </c>
       <c r="D331" s="13" t="n">
-        <v>36.21</v>
+        <v>35.53</v>
       </c>
       <c r="E331" s="15" t="n">
-        <v>-0.1841</v>
+        <v>-0.1902</v>
       </c>
       <c r="F331" s="15" t="n">
-        <v>-0.1317</v>
+        <v>-0.1356</v>
       </c>
       <c r="G331" s="16" t="n"/>
       <c r="H331" s="21" t="inlineStr">
@@ -25283,13 +25313,13 @@
         </is>
       </c>
       <c r="D332" s="4" t="n">
-        <v>8.51</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="E332" s="25" t="n">
-        <v>-0.09369999999999999</v>
+        <v>-0.099</v>
       </c>
       <c r="F332" s="5" t="n">
-        <v>0.1139</v>
+        <v>0.0726</v>
       </c>
       <c r="G332" s="6" t="n">
         <v>46331</v>
@@ -25344,13 +25374,13 @@
         </is>
       </c>
       <c r="D333" s="13" t="n">
-        <v>87</v>
+        <v>86.45</v>
       </c>
       <c r="E333" s="15" t="n">
-        <v>-0.0625</v>
+        <v>-0.0633</v>
       </c>
       <c r="F333" s="15" t="n">
-        <v>-0.0944</v>
+        <v>-0.0929</v>
       </c>
       <c r="G333" s="16" t="n">
         <v>46324</v>
@@ -25379,7 +25409,7 @@
         <v>99</v>
       </c>
       <c r="M333" s="14" t="n">
-        <v>0.1379310344827586</v>
+        <v>0.1451706188548293</v>
       </c>
       <c r="N333" s="12" t="inlineStr">
         <is>
@@ -25390,7 +25420,7 @@
         <v>112</v>
       </c>
       <c r="P333" s="14" t="n">
-        <v>0.2873563218390804</v>
+        <v>0.2955465587044534</v>
       </c>
       <c r="Q333" s="19" t="inlineStr">
         <is>
@@ -25431,13 +25461,13 @@
         </is>
       </c>
       <c r="D334" s="4" t="n">
-        <v>105.17</v>
+        <v>104.07</v>
       </c>
       <c r="E334" s="25" t="n">
-        <v>-0.0484</v>
+        <v>-0.0581</v>
       </c>
       <c r="F334" s="25" t="n">
-        <v>-0.0814</v>
+        <v>-0.0818</v>
       </c>
       <c r="G334" s="6" t="n">
         <v>46324</v>
@@ -25466,7 +25496,7 @@
         <v>127</v>
       </c>
       <c r="M334" s="5" t="n">
-        <v>0.2075686982979937</v>
+        <v>0.2203324685307967</v>
       </c>
       <c r="N334" s="3" t="inlineStr"/>
       <c r="O334" s="8" t="n"/>
@@ -25519,7 +25549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H278"/>
+  <dimension ref="A1:H281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -26934,7 +26964,11 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="F36" s="12" t="inlineStr"/>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>Before open</t>
+        </is>
+      </c>
       <c r="G36" s="33" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -27406,7 +27440,11 @@
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="F49" s="12" t="inlineStr"/>
+      <c r="F49" s="12" t="inlineStr">
+        <is>
+          <t>After close</t>
+        </is>
+      </c>
       <c r="G49" s="33" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -35691,47 +35729,155 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="28" t="n">
+      <c r="A278" s="32" t="n">
+        <v>46335</v>
+      </c>
+      <c r="B278" s="12" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C278" s="11" t="inlineStr">
+        <is>
+          <t>CAMT</t>
+        </is>
+      </c>
+      <c r="D278" s="12" t="inlineStr">
+        <is>
+          <t>Camtek</t>
+        </is>
+      </c>
+      <c r="E278" s="12" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F278" s="12" t="inlineStr"/>
+      <c r="G278" s="33" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H278" s="12" t="inlineStr">
+        <is>
+          <t>Nasdaq</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="32" t="n">
+        <v>46335</v>
+      </c>
+      <c r="B279" s="12" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C279" s="11" t="inlineStr">
+        <is>
+          <t>CRWV</t>
+        </is>
+      </c>
+      <c r="D279" s="12" t="inlineStr">
+        <is>
+          <t>CoreWeave</t>
+        </is>
+      </c>
+      <c r="E279" s="12" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F279" s="12" t="inlineStr"/>
+      <c r="G279" s="33" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H279" s="12" t="inlineStr">
+        <is>
+          <t>Nasdaq</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="32" t="n">
+        <v>46335</v>
+      </c>
+      <c r="B280" s="12" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C280" s="11" t="inlineStr">
+        <is>
+          <t>RGTI</t>
+        </is>
+      </c>
+      <c r="D280" s="12" t="inlineStr">
+        <is>
+          <t>Rigetti Computing</t>
+        </is>
+      </c>
+      <c r="E280" s="12" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F280" s="12" t="inlineStr"/>
+      <c r="G280" s="33" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H280" s="12" t="inlineStr">
+        <is>
+          <t>Nasdaq</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="28" t="n">
         <v>46346</v>
       </c>
-      <c r="B278" s="29" t="inlineStr">
+      <c r="B281" s="29" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C278" s="30" t="inlineStr">
+      <c r="C281" s="30" t="inlineStr">
         <is>
           <t>BMNR</t>
         </is>
       </c>
-      <c r="D278" s="29" t="inlineStr">
+      <c r="D281" s="29" t="inlineStr">
         <is>
           <t>BitMine Immersion</t>
         </is>
       </c>
-      <c r="E278" s="29" t="inlineStr">
+      <c r="E281" s="29" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F278" s="29" t="inlineStr">
+      <c r="F281" s="29" t="inlineStr">
         <is>
           <t>After close</t>
         </is>
       </c>
-      <c r="G278" s="31" t="inlineStr">
+      <c r="G281" s="31" t="inlineStr">
         <is>
           <t>Estimated</t>
         </is>
       </c>
-      <c r="H278" s="29" t="inlineStr">
+      <c r="H281" s="29" t="inlineStr">
         <is>
           <t>SEC EDGAR pattern</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H278"/>
+  <autoFilter ref="A1:H281"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -36744,7 +36890,8 @@
     <row r="44" ht="58" customHeight="1">
       <c r="A44" s="38" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>9
+CAMT CRWV RGTI</t>
         </is>
       </c>
       <c r="B44" s="38" t="inlineStr">
@@ -37106,7 +37253,7 @@
     <row r="2">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>Data as of September 14, 2026 at 21:06 UTC</t>
+          <t>Data as of September 15, 2026 at 15:17 UTC</t>
         </is>
       </c>
     </row>

--- a/earnings-data.xlsx
+++ b/earnings-data.xlsx
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>107.58</v>
+        <v>106.42</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.0395</v>
+        <v>0.0282</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.1015</v>
+        <v>0.08960000000000001</v>
       </c>
       <c r="G2" s="6" t="n"/>
       <c r="H2" s="7" t="inlineStr">
@@ -868,7 +868,7 @@
         <v>125</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>0.1619260085517754</v>
+        <v>0.1745912422476978</v>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         <v>144</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>0.3385387618516453</v>
+        <v>0.3531291110693479</v>
       </c>
       <c r="Q2" s="9" t="inlineStr">
         <is>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="D3" s="13" t="n">
-        <v>344.22</v>
+        <v>344.98</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0028</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>-0.0074</v>
+        <v>-0.0052</v>
       </c>
       <c r="G3" s="16" t="n">
         <v>46322</v>
@@ -963,7 +963,7 @@
         <v>438</v>
       </c>
       <c r="M3" s="14" t="n">
-        <v>0.2724420428795536</v>
+        <v>0.2696388196417183</v>
       </c>
       <c r="N3" s="12" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>420</v>
       </c>
       <c r="P3" s="14" t="n">
-        <v>0.2201499041310789</v>
+        <v>0.217461881848223</v>
       </c>
       <c r="Q3" s="19" t="inlineStr">
         <is>
@@ -1019,13 +1019,13 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>670.35</v>
+        <v>670.24</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.1782</v>
+        <v>0.178</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.0377</v>
+        <v>0.0375</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>46330</v>
@@ -1054,7 +1054,7 @@
         <v>835</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>0.2456179607667636</v>
+        <v>0.2458223919789926</v>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>930</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>0.3873349742671738</v>
+        <v>0.3875626641203151</v>
       </c>
       <c r="Q4" s="9" t="inlineStr">
         <is>
@@ -1114,13 +1114,13 @@
         </is>
       </c>
       <c r="D5" s="13" t="n">
-        <v>42.67</v>
+        <v>44.4</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>0.1466</v>
+        <v>0.1929</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>0.09</v>
+        <v>0.1341</v>
       </c>
       <c r="G5" s="16" t="n">
         <v>46329</v>
@@ -1175,13 +1175,13 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>78.14</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.028</v>
+        <v>0.0247</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.1334</v>
+        <v>0.1298</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>46315</v>
@@ -1210,7 +1210,7 @@
         <v>80</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>0.02380342974148963</v>
+        <v>0.02695763799743253</v>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>100</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>0.279754287176862</v>
+        <v>0.2836970474967906</v>
       </c>
       <c r="Q6" s="9" t="inlineStr">
         <is>
@@ -1262,13 +1262,13 @@
         </is>
       </c>
       <c r="D7" s="13" t="n">
-        <v>80.48999999999999</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>-0.0582</v>
+        <v>-0.06559999999999999</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>-0.0152</v>
+        <v>-0.023</v>
       </c>
       <c r="G7" s="16" t="n">
         <v>46315</v>
@@ -1297,7 +1297,7 @@
         <v>91</v>
       </c>
       <c r="M7" s="14" t="n">
-        <v>0.1305752267362406</v>
+        <v>0.139636819035692</v>
       </c>
       <c r="N7" s="12" t="inlineStr"/>
       <c r="O7" s="18" t="n"/>
@@ -1341,13 +1341,13 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>557.1799999999999</v>
+        <v>558.26</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.1314</v>
+        <v>0.1336</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.1653</v>
+        <v>0.1676</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>46329</v>
@@ -1376,7 +1376,7 @@
         <v>569.9299999999999</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>0.02288308984529237</v>
+        <v>0.02090423816859521</v>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>648.04</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>0.16307117987006</v>
+        <v>0.1608211227743345</v>
       </c>
       <c r="Q8" s="9" t="inlineStr">
         <is>
@@ -1428,13 +1428,13 @@
         </is>
       </c>
       <c r="D9" s="13" t="n">
-        <v>192.43</v>
+        <v>190.13</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>-0.0139</v>
+        <v>-0.0257</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>0.0394</v>
+        <v>0.027</v>
       </c>
       <c r="G9" s="16" t="n">
         <v>46330</v>
@@ -1497,13 +1497,13 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>182.15</v>
+        <v>180.47</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.0113</v>
+        <v>0.0019</v>
       </c>
       <c r="F10" s="25" t="n">
-        <v>-0.0534</v>
+        <v>-0.0622</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>46317</v>
@@ -1532,7 +1532,7 @@
         <v>170</v>
       </c>
       <c r="M10" s="25" t="n">
-        <v>-0.06670326653856715</v>
+        <v>-0.05801518257882196</v>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>270</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>0.482294811968158</v>
+        <v>0.4960935335512828</v>
       </c>
       <c r="Q10" s="9" t="inlineStr">
         <is>
@@ -1584,13 +1584,13 @@
         </is>
       </c>
       <c r="D11" s="13" t="n">
-        <v>51.48</v>
+        <v>51.45</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>0.0712</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>0.181</v>
+        <v>0.1803</v>
       </c>
       <c r="G11" s="16" t="n">
         <v>46316</v>
@@ -1619,7 +1619,7 @@
         <v>43</v>
       </c>
       <c r="M11" s="15" t="n">
-        <v>-0.1647241647241647</v>
+        <v>-0.1642371234207969</v>
       </c>
       <c r="N11" s="12" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>50</v>
       </c>
       <c r="P11" s="15" t="n">
-        <v>-0.02874902874902869</v>
+        <v>-0.02818270165208946</v>
       </c>
       <c r="Q11" s="19" t="inlineStr">
         <is>
@@ -1675,13 +1675,13 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>167.4</v>
+        <v>168.32</v>
       </c>
       <c r="E12" s="25" t="n">
-        <v>-0.0663</v>
+        <v>-0.0612</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.1467</v>
+        <v>0.153</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>46331</v>
@@ -1710,7 +1710,7 @@
         <v>181</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>0.08124253285543605</v>
+        <v>0.0753326996197719</v>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>155</v>
       </c>
       <c r="P12" s="25" t="n">
-        <v>-0.07407407407407411</v>
+        <v>-0.07913498098859312</v>
       </c>
       <c r="Q12" s="9" t="inlineStr">
         <is>
@@ -1762,13 +1762,13 @@
         </is>
       </c>
       <c r="D13" s="13" t="n">
-        <v>248.92</v>
+        <v>248.42</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>-0.0474</v>
+        <v>-0.0493</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>0.0068</v>
+        <v>0.0048</v>
       </c>
       <c r="G13" s="16" t="n">
         <v>46324</v>
@@ -1797,7 +1797,7 @@
         <v>322</v>
       </c>
       <c r="M13" s="14" t="n">
-        <v>0.2935883014623173</v>
+        <v>0.2961919330166654</v>
       </c>
       <c r="N13" s="12" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>285</v>
       </c>
       <c r="P13" s="14" t="n">
-        <v>0.1449461674433553</v>
+        <v>0.1472506239433219</v>
       </c>
       <c r="Q13" s="19" t="inlineStr">
         <is>
@@ -1861,13 +1861,13 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2902.24</v>
+        <v>2860.25</v>
       </c>
       <c r="E14" s="25" t="n">
-        <v>-0.0388</v>
+        <v>-0.0527</v>
       </c>
       <c r="F14" s="25" t="n">
-        <v>-0.0473</v>
+        <v>-0.0611</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>46287</v>
@@ -1896,7 +1896,7 @@
         <v>4150</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>0.4299299851149458</v>
+        <v>0.4509221221921161</v>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>3700</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>0.2748773361265782</v>
+        <v>0.2935932173761035</v>
       </c>
       <c r="Q14" s="9" t="inlineStr">
         <is>
@@ -1948,13 +1948,13 @@
         </is>
       </c>
       <c r="D15" s="13" t="n">
-        <v>93.59</v>
+        <v>93.23999999999999</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>0.09539999999999998</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>0.0958</v>
+        <v>0.0917</v>
       </c>
       <c r="G15" s="16" t="n"/>
       <c r="H15" s="21" t="inlineStr">
@@ -1973,7 +1973,7 @@
         <v>65</v>
       </c>
       <c r="M15" s="15" t="n">
-        <v>-0.3054813548456032</v>
+        <v>-0.3028743028743028</v>
       </c>
       <c r="N15" s="12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>85</v>
       </c>
       <c r="P15" s="15" t="n">
-        <v>-0.09178331018271187</v>
+        <v>-0.08837408837408832</v>
       </c>
       <c r="Q15" s="19" t="inlineStr"/>
       <c r="R15" s="18" t="n"/>
@@ -2019,13 +2019,13 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>170.88</v>
+        <v>171.32</v>
       </c>
       <c r="E16" s="25" t="n">
-        <v>-0.1655</v>
+        <v>-0.1633</v>
       </c>
       <c r="F16" s="25" t="n">
-        <v>-0.0594</v>
+        <v>-0.057</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>46322</v>
@@ -2054,7 +2054,7 @@
         <v>214</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>0.2523408239700375</v>
+        <v>0.2491244454821387</v>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>245</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>0.4337546816479401</v>
+        <v>0.4300723791734766</v>
       </c>
       <c r="Q16" s="9" t="inlineStr">
         <is>
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="D17" s="13" t="n">
-        <v>229.56</v>
+        <v>227.28</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>-0.3185</v>
+        <v>-0.3253</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>-0.3352000000000001</v>
+        <v>-0.3418</v>
       </c>
       <c r="G17" s="16" t="n"/>
       <c r="H17" s="21" t="inlineStr">
@@ -2139,7 +2139,7 @@
         <v>375</v>
       </c>
       <c r="M17" s="14" t="n">
-        <v>0.6335598536330371</v>
+        <v>0.6499472016895459</v>
       </c>
       <c r="N17" s="12" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>375</v>
       </c>
       <c r="P17" s="14" t="n">
-        <v>0.6335598536330371</v>
+        <v>0.6499472016895459</v>
       </c>
       <c r="Q17" s="19" t="inlineStr"/>
       <c r="R17" s="18" t="n"/>
@@ -2189,13 +2189,13 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>35.17</v>
+        <v>34.83</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.04190000000000001</v>
+        <v>0.0317</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.0213</v>
+        <v>0.0113</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>46323</v>
@@ -2224,7 +2224,7 @@
         <v>45</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>0.2794995735001421</v>
+        <v>0.2919896640826874</v>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>45</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>0.2794995735001421</v>
+        <v>0.2919896640826874</v>
       </c>
       <c r="Q18" s="9" t="inlineStr">
         <is>
@@ -2276,13 +2276,13 @@
         </is>
       </c>
       <c r="D19" s="13" t="n">
-        <v>138.88</v>
+        <v>140.2</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>-0.0638</v>
+        <v>-0.0549</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>-0.0704</v>
+        <v>-0.06150000000000001</v>
       </c>
       <c r="G19" s="16" t="n">
         <v>46324</v>
@@ -2311,7 +2311,7 @@
         <v>170</v>
       </c>
       <c r="M19" s="14" t="n">
-        <v>0.2240783410138249</v>
+        <v>0.2125534950071328</v>
       </c>
       <c r="N19" s="12" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>177</v>
       </c>
       <c r="P19" s="14" t="n">
-        <v>0.2744815668202765</v>
+        <v>0.2624821683309559</v>
       </c>
       <c r="Q19" s="19" t="inlineStr">
         <is>
@@ -2363,13 +2363,13 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>126.43</v>
+        <v>123.72</v>
       </c>
       <c r="E20" s="25" t="n">
-        <v>-0.3557</v>
+        <v>-0.3695000000000001</v>
       </c>
       <c r="F20" s="25" t="n">
-        <v>-0.4183</v>
+        <v>-0.4308</v>
       </c>
       <c r="G20" s="6" t="n"/>
       <c r="H20" s="7" t="inlineStr">
@@ -2388,7 +2388,7 @@
         <v>220</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>0.7400933322787312</v>
+        <v>0.7782088587132234</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="8" t="n"/>
@@ -2432,13 +2432,13 @@
         </is>
       </c>
       <c r="D21" s="13" t="n">
-        <v>114.26</v>
+        <v>112.79</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>-0.118</v>
+        <v>-0.1293</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>-0.09269999999999999</v>
+        <v>-0.1044</v>
       </c>
       <c r="G21" s="16" t="n"/>
       <c r="H21" s="21" t="inlineStr">
@@ -2483,13 +2483,13 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>85.36</v>
+        <v>85.37</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.0117</v>
+        <v>0.0119</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.1221</v>
+        <v>0.1223</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>46315</v>
@@ -2518,7 +2518,7 @@
         <v>61</v>
       </c>
       <c r="M22" s="25" t="n">
-        <v>-0.2853795688847235</v>
+        <v>-0.2854632774979501</v>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>100</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0.1715089034676664</v>
+        <v>0.1713716762328686</v>
       </c>
       <c r="Q22" s="9" t="inlineStr">
         <is>
@@ -2570,13 +2570,13 @@
         </is>
       </c>
       <c r="D23" s="13" t="n">
-        <v>132.15</v>
+        <v>131.01</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>-0.0028</v>
+        <v>-0.0114</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0.0587</v>
+        <v>0.0496</v>
       </c>
       <c r="G23" s="16" t="n">
         <v>46315</v>
@@ -2608,7 +2608,7 @@
         <v>145</v>
       </c>
       <c r="P23" s="14" t="n">
-        <v>0.09723798713583044</v>
+        <v>0.1067857415464469</v>
       </c>
       <c r="Q23" s="19" t="inlineStr"/>
       <c r="R23" s="18" t="n"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>305.8</v>
+        <v>305.48</v>
       </c>
       <c r="E24" s="25" t="n">
-        <v>-0.0949</v>
+        <v>-0.0959</v>
       </c>
       <c r="F24" s="25" t="n">
-        <v>-0.09759999999999999</v>
+        <v>-0.09849999999999999</v>
       </c>
       <c r="G24" s="6" t="n"/>
       <c r="H24" s="7" t="inlineStr">
@@ -2668,7 +2668,7 @@
         <v>360</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>0.1772400261608894</v>
+        <v>0.178473222469556</v>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>400</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0.3080444735120993</v>
+        <v>0.30941469163284</v>
       </c>
       <c r="Q24" s="9" t="inlineStr">
         <is>
@@ -2728,13 +2728,13 @@
         </is>
       </c>
       <c r="D25" s="13" t="n">
-        <v>195.17</v>
+        <v>194.61</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>-0.0956</v>
+        <v>-0.09820000000000001</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>-0.065</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="G25" s="16" t="n"/>
       <c r="H25" s="21" t="inlineStr">
@@ -2753,7 +2753,7 @@
         <v>255</v>
       </c>
       <c r="M25" s="14" t="n">
-        <v>0.306553261259415</v>
+        <v>0.3103129335594265</v>
       </c>
       <c r="N25" s="12" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>230</v>
       </c>
       <c r="P25" s="14" t="n">
-        <v>0.1784598042731978</v>
+        <v>0.1818508812496788</v>
       </c>
       <c r="Q25" s="19" t="inlineStr">
         <is>
@@ -2809,13 +2809,13 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>255.36</v>
+        <v>252.78</v>
       </c>
       <c r="E26" s="25" t="n">
-        <v>-0.0383</v>
+        <v>-0.048</v>
       </c>
       <c r="F26" s="25" t="n">
-        <v>-0.0461</v>
+        <v>-0.0558</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>46330</v>
@@ -2844,7 +2844,7 @@
         <v>300</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>0.1748120300751879</v>
+        <v>0.1868027533823878</v>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>350</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>0.3706140350877192</v>
+        <v>0.3846032122794525</v>
       </c>
       <c r="Q26" s="9" t="inlineStr">
         <is>
@@ -2896,13 +2896,13 @@
         </is>
       </c>
       <c r="D27" s="13" t="n">
-        <v>36.32</v>
+        <v>36.22</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>-0.0709</v>
+        <v>-0.07339999999999999</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>-0.17</v>
+        <v>-0.1723</v>
       </c>
       <c r="G27" s="16" t="n">
         <v>46289</v>
@@ -2957,13 +2957,13 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>86.06</v>
+        <v>85.16</v>
       </c>
       <c r="E28" s="25" t="n">
-        <v>-0.0462</v>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0562</v>
+      </c>
+      <c r="F28" s="25" t="n">
+        <v>-0.0103</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>46323</v>
@@ -2992,7 +2992,7 @@
         <v>110</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>0.2781780153381361</v>
+        <v>0.2916862376702678</v>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>115</v>
       </c>
       <c r="P28" s="5" t="n">
-        <v>0.3362770160353242</v>
+        <v>0.3503992484734618</v>
       </c>
       <c r="Q28" s="9" t="inlineStr">
         <is>
@@ -3048,13 +3048,13 @@
         </is>
       </c>
       <c r="D29" s="13" t="n">
-        <v>167.63</v>
+        <v>166.86</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>-0.1199</v>
+        <v>-0.124</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>-0.1667</v>
+        <v>-0.1706</v>
       </c>
       <c r="G29" s="16" t="n">
         <v>46317</v>
@@ -3109,13 +3109,13 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>226.34</v>
+        <v>226.26</v>
       </c>
       <c r="E30" s="25" t="n">
-        <v>-0.038</v>
+        <v>-0.0383</v>
       </c>
       <c r="F30" s="25" t="n">
-        <v>-0.0305</v>
+        <v>-0.0308</v>
       </c>
       <c r="G30" s="6" t="n"/>
       <c r="H30" s="7" t="inlineStr">
@@ -3134,7 +3134,7 @@
         <v>245</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>0.08244234337722009</v>
+        <v>0.08282506850525947</v>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>265</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>0.1708049836529115</v>
+        <v>0.171218951648546</v>
       </c>
       <c r="Q30" s="9" t="inlineStr">
         <is>
@@ -3186,13 +3186,13 @@
         </is>
       </c>
       <c r="D31" s="13" t="n">
-        <v>96.56999999999999</v>
+        <v>96.58</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>-0.1052</v>
+        <v>-0.1051</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>-0.08460000000000001</v>
+        <v>-0.08449999999999999</v>
       </c>
       <c r="G31" s="16" t="n">
         <v>46330</v>
@@ -3221,7 +3221,7 @@
         <v>120</v>
       </c>
       <c r="M31" s="14" t="n">
-        <v>0.2426219322771048</v>
+        <v>0.2424932698281218</v>
       </c>
       <c r="N31" s="12" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>115</v>
       </c>
       <c r="P31" s="14" t="n">
-        <v>0.1908460184322254</v>
+        <v>0.1907227169186167</v>
       </c>
       <c r="Q31" s="19" t="inlineStr">
         <is>
@@ -3273,13 +3273,13 @@
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>13.32</v>
+        <v>13.31</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0.0149</v>
+        <v>0.0137</v>
       </c>
       <c r="F32" s="25" t="n">
-        <v>-0.07339999999999999</v>
+        <v>-0.07440000000000001</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>46330</v>
@@ -3334,13 +3334,13 @@
         </is>
       </c>
       <c r="D33" s="13" t="n">
-        <v>124.76</v>
+        <v>124.6</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>-0.173</v>
+        <v>-0.174</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>-0.1923</v>
+        <v>-0.1933</v>
       </c>
       <c r="G33" s="16" t="n"/>
       <c r="H33" s="21" t="inlineStr">
@@ -3359,7 +3359,7 @@
         <v>160</v>
       </c>
       <c r="M33" s="14" t="n">
-        <v>0.2824623276691247</v>
+        <v>0.2841091492776887</v>
       </c>
       <c r="N33" s="12" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>175</v>
       </c>
       <c r="P33" s="14" t="n">
-        <v>0.4026931708881051</v>
+        <v>0.404494382022472</v>
       </c>
       <c r="Q33" s="19" t="inlineStr">
         <is>
@@ -3415,13 +3415,13 @@
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>32.87</v>
+        <v>33.03</v>
       </c>
       <c r="E34" s="25" t="n">
-        <v>-0.0522</v>
+        <v>-0.0476</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.0774</v>
+        <v>0.08259999999999999</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>46317</v>
@@ -3450,7 +3450,7 @@
         <v>35</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>0.06480073014907219</v>
+        <v>0.05964274901604598</v>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>40</v>
       </c>
       <c r="P34" s="5" t="n">
-        <v>0.2169151201703682</v>
+        <v>0.2110202845897668</v>
       </c>
       <c r="Q34" s="9" t="inlineStr">
         <is>
@@ -3502,13 +3502,13 @@
         </is>
       </c>
       <c r="D35" s="13" t="n">
-        <v>358.96</v>
+        <v>356.58</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>0.058</v>
+        <v>0.0509</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>-0.0574</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="G35" s="16" t="n">
         <v>46323</v>
@@ -3537,7 +3537,7 @@
         <v>130</v>
       </c>
       <c r="M35" s="15" t="n">
-        <v>-0.6378426565634053</v>
+        <v>-0.635425430478434</v>
       </c>
       <c r="N35" s="12" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>300</v>
       </c>
       <c r="P35" s="15" t="n">
-        <v>-0.1642522843770893</v>
+        <v>-0.1586740703348477</v>
       </c>
       <c r="Q35" s="19" t="inlineStr">
         <is>
@@ -3589,13 +3589,13 @@
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>71.5</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="E36" s="25" t="n">
-        <v>-0.04650000000000001</v>
+        <v>-0.0475</v>
       </c>
       <c r="F36" s="25" t="n">
-        <v>-0.0132</v>
+        <v>-0.0142</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>46329</v>
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="D37" s="13" t="n">
-        <v>543.34</v>
+        <v>544.3200000000001</v>
       </c>
       <c r="E37" s="14" t="n">
-        <v>0.1014</v>
+        <v>0.1034</v>
       </c>
       <c r="F37" s="14" t="n">
-        <v>0.133</v>
+        <v>0.135</v>
       </c>
       <c r="G37" s="16" t="n"/>
       <c r="H37" s="21" t="inlineStr">
@@ -3675,7 +3675,7 @@
         <v>450</v>
       </c>
       <c r="M37" s="15" t="n">
-        <v>-0.1717893031987338</v>
+        <v>-0.1732804232804234</v>
       </c>
       <c r="N37" s="12" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>635</v>
       </c>
       <c r="P37" s="14" t="n">
-        <v>0.1686973165973423</v>
+        <v>0.1665931804820693</v>
       </c>
       <c r="Q37" s="19" t="inlineStr">
         <is>
@@ -3731,13 +3731,13 @@
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>94.11</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="E38" s="25" t="n">
-        <v>-0.0395</v>
+        <v>-0.0354</v>
       </c>
       <c r="F38" s="25" t="n">
-        <v>-0.0404</v>
+        <v>-0.0363</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>46325</v>
@@ -3766,7 +3766,7 @@
         <v>110</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>0.1688449686537031</v>
+        <v>0.1638980002116178</v>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>105</v>
       </c>
       <c r="P38" s="5" t="n">
-        <v>0.1157156518967166</v>
+        <v>0.1109935456565442</v>
       </c>
       <c r="Q38" s="9" t="inlineStr">
         <is>
@@ -3822,13 +3822,13 @@
         </is>
       </c>
       <c r="D39" s="13" t="n">
-        <v>87.15000000000001</v>
+        <v>87</v>
       </c>
       <c r="E39" s="15" t="n">
-        <v>-0.0339</v>
+        <v>-0.0356</v>
       </c>
       <c r="F39" s="15" t="n">
-        <v>-0.06269999999999999</v>
+        <v>-0.0643</v>
       </c>
       <c r="G39" s="16" t="n">
         <v>46325</v>
@@ -3857,7 +3857,7 @@
         <v>95</v>
       </c>
       <c r="M39" s="14" t="n">
-        <v>0.0900745840504876</v>
+        <v>0.09195402298850575</v>
       </c>
       <c r="N39" s="12" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>100</v>
       </c>
       <c r="P39" s="14" t="n">
-        <v>0.1474469305794606</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="Q39" s="19" t="inlineStr">
         <is>
@@ -3913,13 +3913,13 @@
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>907.74</v>
+        <v>901.35</v>
       </c>
       <c r="E40" s="25" t="n">
-        <v>-0.048</v>
+        <v>-0.0547</v>
       </c>
       <c r="F40" s="25" t="n">
-        <v>-0.0352</v>
+        <v>-0.042</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>46289</v>
@@ -3948,7 +3948,7 @@
         <v>1000</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>0.1016370326304889</v>
+        <v>0.109446940700061</v>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>1100</v>
       </c>
       <c r="P40" s="5" t="n">
-        <v>0.2118007358935378</v>
+        <v>0.2203916347700671</v>
       </c>
       <c r="Q40" s="9" t="inlineStr">
         <is>
@@ -4008,13 +4008,13 @@
         </is>
       </c>
       <c r="D41" s="13" t="n">
-        <v>125.5</v>
+        <v>124.7</v>
       </c>
       <c r="E41" s="14" t="n">
-        <v>0.0451</v>
+        <v>0.0385</v>
       </c>
       <c r="F41" s="15" t="n">
-        <v>-0.002</v>
+        <v>-0.0083</v>
       </c>
       <c r="G41" s="16" t="n"/>
       <c r="H41" s="21" t="inlineStr">
@@ -4032,8 +4032,8 @@
       <c r="L41" s="18" t="n">
         <v>125</v>
       </c>
-      <c r="M41" s="15" t="n">
-        <v>-0.00398406374501992</v>
+      <c r="M41" s="14" t="n">
+        <v>0.002405773857257395</v>
       </c>
       <c r="N41" s="12" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>135</v>
       </c>
       <c r="P41" s="14" t="n">
-        <v>0.07569721115537849</v>
+        <v>0.08259823576583798</v>
       </c>
       <c r="Q41" s="19" t="inlineStr">
         <is>
@@ -4085,13 +4085,13 @@
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>24.32</v>
+        <v>24.73</v>
       </c>
       <c r="E42" s="25" t="n">
-        <v>-0.0176</v>
+        <v>-0.0008</v>
       </c>
       <c r="F42" s="25" t="n">
-        <v>-0.0605</v>
+        <v>-0.0444</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>46330</v>
@@ -4146,13 +4146,13 @@
         </is>
       </c>
       <c r="D43" s="13" t="n">
-        <v>88.5</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="E43" s="14" t="n">
-        <v>0.0175</v>
+        <v>0.0199</v>
       </c>
       <c r="F43" s="14" t="n">
-        <v>0.0851</v>
+        <v>0.0877</v>
       </c>
       <c r="G43" s="16" t="n">
         <v>46315</v>
@@ -4181,7 +4181,7 @@
         <v>90</v>
       </c>
       <c r="M43" s="14" t="n">
-        <v>0.01694915254237288</v>
+        <v>0.0145417653026717</v>
       </c>
       <c r="N43" s="12" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>88</v>
       </c>
       <c r="P43" s="15" t="n">
-        <v>-0.005649717514124294</v>
+        <v>-0.008003607259609895</v>
       </c>
       <c r="Q43" s="19" t="inlineStr">
         <is>
@@ -4241,13 +4241,13 @@
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>61.39</v>
+        <v>62.25</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0.0949</v>
+        <v>0.1102</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.0437</v>
+        <v>0.0583</v>
       </c>
       <c r="G44" s="6" t="n"/>
       <c r="H44" s="7" t="inlineStr">
@@ -4266,7 +4266,7 @@
         <v>58</v>
       </c>
       <c r="M44" s="25" t="n">
-        <v>-0.05522071998696857</v>
+        <v>-0.06827309236947791</v>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>78</v>
       </c>
       <c r="P44" s="5" t="n">
-        <v>0.2705652386382147</v>
+        <v>0.2530120481927711</v>
       </c>
       <c r="Q44" s="9" t="inlineStr">
         <is>
@@ -4318,13 +4318,13 @@
         </is>
       </c>
       <c r="D45" s="13" t="n">
-        <v>62.08</v>
+        <v>62.1</v>
       </c>
       <c r="E45" s="15" t="n">
-        <v>-0.0017</v>
+        <v>-0.0013</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0.0176</v>
+        <v>0.018</v>
       </c>
       <c r="G45" s="16" t="n">
         <v>46322</v>
@@ -4353,7 +4353,7 @@
         <v>70</v>
       </c>
       <c r="M45" s="14" t="n">
-        <v>0.1275773195876289</v>
+        <v>0.1272141706924315</v>
       </c>
       <c r="N45" s="12" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>71</v>
       </c>
       <c r="P45" s="14" t="n">
-        <v>0.1436855670103093</v>
+        <v>0.143317230273752</v>
       </c>
       <c r="Q45" s="19" t="inlineStr">
         <is>
@@ -4413,13 +4413,13 @@
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>49.67</v>
+        <v>49.86</v>
       </c>
       <c r="E46" s="25" t="n">
-        <v>-0.07919999999999999</v>
+        <v>-0.0756</v>
       </c>
       <c r="F46" s="25" t="n">
-        <v>-0.0393</v>
+        <v>-0.0356</v>
       </c>
       <c r="G46" s="6" t="n">
         <v>46296</v>
@@ -4484,13 +4484,13 @@
         </is>
       </c>
       <c r="D47" s="13" t="n">
-        <v>44.51</v>
+        <v>44.63</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>-0.0222</v>
+        <v>-0.0196</v>
       </c>
       <c r="F47" s="15" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.08449999999999999</v>
       </c>
       <c r="G47" s="16" t="n">
         <v>46331</v>
@@ -4545,13 +4545,13 @@
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>70.06999999999999</v>
+        <v>69.81</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0.0956</v>
+        <v>0.0915</v>
       </c>
       <c r="F48" s="25" t="n">
-        <v>-0.0557</v>
+        <v>-0.0593</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>46324</v>
@@ -4606,13 +4606,13 @@
         </is>
       </c>
       <c r="D49" s="13" t="n">
-        <v>135.49</v>
+        <v>135.5</v>
       </c>
       <c r="E49" s="15" t="n">
-        <v>-0.0199</v>
+        <v>-0.0198</v>
       </c>
       <c r="F49" s="15" t="n">
-        <v>-0.0119</v>
+        <v>-0.0118</v>
       </c>
       <c r="G49" s="16" t="n">
         <v>46303</v>
@@ -4641,7 +4641,7 @@
         <v>140</v>
       </c>
       <c r="M49" s="14" t="n">
-        <v>0.03328658941619301</v>
+        <v>0.03321033210332103</v>
       </c>
       <c r="N49" s="12" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>150</v>
       </c>
       <c r="P49" s="14" t="n">
-        <v>0.1070927743744925</v>
+        <v>0.1070110701107011</v>
       </c>
       <c r="Q49" s="19" t="inlineStr">
         <is>
@@ -4701,13 +4701,13 @@
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>146.54</v>
+        <v>146.67</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0.0239</v>
+        <v>0.0248</v>
       </c>
       <c r="F50" s="25" t="n">
-        <v>-0.023</v>
+        <v>-0.0221</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>46318</v>
@@ -4736,7 +4736,7 @@
         <v>164</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>0.1191483553978437</v>
+        <v>0.1181564055362379</v>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>162</v>
       </c>
       <c r="P50" s="5" t="n">
-        <v>0.1055002047222602</v>
+        <v>0.1045203518101862</v>
       </c>
       <c r="Q50" s="9" t="inlineStr">
         <is>
@@ -4800,13 +4800,13 @@
         </is>
       </c>
       <c r="D51" s="13" t="n">
-        <v>80.86</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="E51" s="15" t="n">
-        <v>-0.0122</v>
+        <v>-0.0275</v>
       </c>
       <c r="F51" s="15" t="n">
-        <v>-0.0102</v>
+        <v>-0.0256</v>
       </c>
       <c r="G51" s="16" t="n">
         <v>46322</v>
@@ -4835,7 +4835,7 @@
         <v>100</v>
       </c>
       <c r="M51" s="14" t="n">
-        <v>0.2367054167697255</v>
+        <v>0.256281407035176</v>
       </c>
       <c r="N51" s="12" t="inlineStr"/>
       <c r="O51" s="18" t="n"/>
@@ -4879,13 +4879,13 @@
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>154.66</v>
+        <v>154.4</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0.0242</v>
+        <v>0.0224</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.1079</v>
+        <v>0.106</v>
       </c>
       <c r="G52" s="6" t="n"/>
       <c r="H52" s="7" t="inlineStr">
@@ -4904,7 +4904,7 @@
         <v>140</v>
       </c>
       <c r="M52" s="25" t="n">
-        <v>-0.09478856847277897</v>
+        <v>-0.09326424870466325</v>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>135</v>
       </c>
       <c r="P52" s="25" t="n">
-        <v>-0.1271175481701797</v>
+        <v>-0.1256476683937824</v>
       </c>
       <c r="Q52" s="9" t="inlineStr">
         <is>
@@ -4960,13 +4960,13 @@
         </is>
       </c>
       <c r="D53" s="13" t="n">
-        <v>108.8</v>
+        <v>108.09</v>
       </c>
       <c r="E53" s="15" t="n">
-        <v>-0.0484</v>
+        <v>-0.0546</v>
       </c>
       <c r="F53" s="15" t="n">
-        <v>-0.0476</v>
+        <v>-0.0538</v>
       </c>
       <c r="G53" s="16" t="n"/>
       <c r="H53" s="21" t="inlineStr">
@@ -4985,7 +4985,7 @@
         <v>140</v>
       </c>
       <c r="M53" s="14" t="n">
-        <v>0.286764705882353</v>
+        <v>0.2952169488389305</v>
       </c>
       <c r="N53" s="12" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>140</v>
       </c>
       <c r="P53" s="14" t="n">
-        <v>0.286764705882353</v>
+        <v>0.2952169488389305</v>
       </c>
       <c r="Q53" s="19" t="inlineStr">
         <is>
@@ -5045,13 +5045,13 @@
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>56.21</v>
+        <v>56.72</v>
       </c>
       <c r="E54" s="25" t="n">
-        <v>-0.134</v>
+        <v>-0.126</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>0.0046</v>
+        <v>0.0138</v>
       </c>
       <c r="G54" s="6" t="n">
         <v>46317</v>
@@ -5087,7 +5087,7 @@
         <v>76</v>
       </c>
       <c r="P54" s="5" t="n">
-        <v>0.3520725849492973</v>
+        <v>0.3399153737658674</v>
       </c>
       <c r="Q54" s="9" t="inlineStr">
         <is>
@@ -5128,13 +5128,13 @@
         </is>
       </c>
       <c r="D55" s="13" t="n">
-        <v>139.74</v>
+        <v>141.22</v>
       </c>
       <c r="E55" s="14" t="n">
-        <v>0.09539999999999998</v>
+        <v>0.1071</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0.2182</v>
+        <v>0.2311</v>
       </c>
       <c r="G55" s="16" t="n">
         <v>46331</v>
@@ -5163,7 +5163,7 @@
         <v>183</v>
       </c>
       <c r="M55" s="14" t="n">
-        <v>0.3095749248604551</v>
+        <v>0.2958504461124487</v>
       </c>
       <c r="N55" s="12" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>145</v>
       </c>
       <c r="P55" s="14" t="n">
-        <v>0.03764133390582504</v>
+        <v>0.02676674691969977</v>
       </c>
       <c r="Q55" s="19" t="inlineStr">
         <is>
@@ -5215,13 +5215,13 @@
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>215.73</v>
+        <v>217.77</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0.0643</v>
+        <v>0.07429999999999999</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.1513</v>
+        <v>0.1622</v>
       </c>
       <c r="G56" s="6" t="n">
         <v>46325</v>
@@ -5250,7 +5250,7 @@
         <v>222</v>
       </c>
       <c r="M56" s="5" t="n">
-        <v>0.02906410791266866</v>
+        <v>0.01942416310786605</v>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>225</v>
       </c>
       <c r="P56" s="5" t="n">
-        <v>0.04297037964121824</v>
+        <v>0.0332001653120264</v>
       </c>
       <c r="Q56" s="9" t="inlineStr">
         <is>
@@ -5306,13 +5306,13 @@
         </is>
       </c>
       <c r="D57" s="13" t="n">
-        <v>152.43</v>
+        <v>153.74</v>
       </c>
       <c r="E57" s="14" t="n">
-        <v>0.0429</v>
+        <v>0.0519</v>
       </c>
       <c r="F57" s="14" t="n">
-        <v>0.08960000000000001</v>
+        <v>0.099</v>
       </c>
       <c r="G57" s="16" t="n">
         <v>46331</v>
@@ -5341,7 +5341,7 @@
         <v>196</v>
       </c>
       <c r="M57" s="14" t="n">
-        <v>0.2858361214983927</v>
+        <v>0.2748796669702094</v>
       </c>
       <c r="N57" s="12" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>170</v>
       </c>
       <c r="P57" s="14" t="n">
-        <v>0.1152660237486059</v>
+        <v>0.105762976453753</v>
       </c>
       <c r="Q57" s="19" t="inlineStr">
         <is>
@@ -5400,10 +5400,10 @@
         <v>38.81</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0.0051</v>
+        <v>0.0052</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0.0158</v>
+        <v>0.016</v>
       </c>
       <c r="G58" s="6" t="n">
         <v>46324</v>
@@ -5458,13 +5458,13 @@
         </is>
       </c>
       <c r="D59" s="13" t="n">
-        <v>21.35</v>
+        <v>21.33</v>
       </c>
       <c r="E59" s="14" t="n">
-        <v>0.0198</v>
+        <v>0.0186</v>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0.0509</v>
+        <v>0.04969999999999999</v>
       </c>
       <c r="G59" s="16" t="n">
         <v>46330</v>
@@ -5519,13 +5519,13 @@
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>210.7</v>
+        <v>211.52</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0.0214</v>
+        <v>0.0254</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>0.0775</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="G60" s="6" t="n">
         <v>46328</v>
@@ -5580,13 +5580,13 @@
         </is>
       </c>
       <c r="D61" s="13" t="n">
-        <v>35.31</v>
+        <v>35.67</v>
       </c>
       <c r="E61" s="14" t="n">
-        <v>0.0167</v>
+        <v>0.0271</v>
       </c>
       <c r="F61" s="14" t="n">
-        <v>0.0026</v>
+        <v>0.0128</v>
       </c>
       <c r="G61" s="16" t="n">
         <v>46315</v>
@@ -5622,7 +5622,7 @@
         <v>43</v>
       </c>
       <c r="P61" s="14" t="n">
-        <v>0.2177853299348626</v>
+        <v>0.2054948135688253</v>
       </c>
       <c r="Q61" s="19" t="inlineStr">
         <is>
@@ -5667,13 +5667,13 @@
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>30.67</v>
+        <v>30.77</v>
       </c>
       <c r="E62" s="25" t="n">
-        <v>-0.0512</v>
+        <v>-0.0483</v>
       </c>
       <c r="F62" s="25" t="n">
-        <v>-0.0503</v>
+        <v>-0.0474</v>
       </c>
       <c r="G62" s="6" t="n">
         <v>46316</v>
@@ -5702,7 +5702,7 @@
         <v>35</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>0.1411803064884251</v>
+        <v>0.1374715632109197</v>
       </c>
       <c r="N62" s="3" t="inlineStr"/>
       <c r="O62" s="8" t="n"/>
@@ -5746,13 +5746,13 @@
         </is>
       </c>
       <c r="D63" s="13" t="n">
-        <v>262.58</v>
+        <v>264.93</v>
       </c>
       <c r="E63" s="14" t="n">
-        <v>0.0916</v>
+        <v>0.1014</v>
       </c>
       <c r="F63" s="14" t="n">
-        <v>0.2694</v>
+        <v>0.2807</v>
       </c>
       <c r="G63" s="16" t="n">
         <v>46330</v>
@@ -5807,13 +5807,13 @@
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>53.64</v>
-      </c>
-      <c r="E64" s="25" t="n">
-        <v>-0.004099999999999999</v>
+        <v>54.2</v>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>0.0063</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>0.1415</v>
+        <v>0.1534</v>
       </c>
       <c r="G64" s="6" t="n">
         <v>46311</v>
@@ -5849,7 +5849,7 @@
         <v>63</v>
       </c>
       <c r="P64" s="5" t="n">
-        <v>0.174496644295302</v>
+        <v>0.1623616236162361</v>
       </c>
       <c r="Q64" s="9" t="inlineStr">
         <is>
@@ -5898,13 +5898,13 @@
         </is>
       </c>
       <c r="D65" s="13" t="n">
-        <v>45.7</v>
+        <v>45.96</v>
       </c>
       <c r="E65" s="14" t="n">
-        <v>0.0616</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="F65" s="14" t="n">
-        <v>0.0297</v>
+        <v>0.0356</v>
       </c>
       <c r="G65" s="16" t="n">
         <v>46328</v>
@@ -5959,13 +5959,13 @@
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>71.42</v>
+        <v>71.63</v>
       </c>
       <c r="E66" s="25" t="n">
-        <v>-0.0277</v>
+        <v>-0.0248</v>
       </c>
       <c r="F66" s="25" t="n">
-        <v>-0.0268</v>
+        <v>-0.0238</v>
       </c>
       <c r="G66" s="6" t="n">
         <v>46328</v>
@@ -5994,7 +5994,7 @@
         <v>89</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>0.2461495379445533</v>
+        <v>0.2424961608264694</v>
       </c>
       <c r="N66" s="3" t="inlineStr"/>
       <c r="O66" s="8" t="n"/>
@@ -6050,13 +6050,13 @@
         </is>
       </c>
       <c r="D67" s="13" t="n">
-        <v>168.45</v>
+        <v>169.32</v>
       </c>
       <c r="E67" s="14" t="n">
-        <v>0.0433</v>
+        <v>0.0487</v>
       </c>
       <c r="F67" s="14" t="n">
-        <v>0.1431</v>
+        <v>0.149</v>
       </c>
       <c r="G67" s="16" t="n">
         <v>46325</v>
@@ -6085,7 +6085,7 @@
         <v>185</v>
       </c>
       <c r="M67" s="14" t="n">
-        <v>0.09824873849807071</v>
+        <v>0.09260571698558946</v>
       </c>
       <c r="N67" s="12" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>185</v>
       </c>
       <c r="P67" s="14" t="n">
-        <v>0.09824873849807071</v>
+        <v>0.09260571698558946</v>
       </c>
       <c r="Q67" s="19" t="inlineStr">
         <is>
@@ -6141,13 +6141,13 @@
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>116.68</v>
+        <v>117.55</v>
       </c>
       <c r="E68" s="25" t="n">
-        <v>-0.0356</v>
+        <v>-0.0284</v>
       </c>
       <c r="F68" s="25" t="n">
-        <v>-0.0645</v>
+        <v>-0.0575</v>
       </c>
       <c r="G68" s="6" t="n">
         <v>46329</v>
@@ -6176,7 +6176,7 @@
         <v>120</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>0.02845389098388749</v>
+        <v>0.02084219481071887</v>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>115</v>
       </c>
       <c r="P68" s="25" t="n">
-        <v>-0.01439835447377448</v>
+        <v>-0.02169289663972775</v>
       </c>
       <c r="Q68" s="9" t="inlineStr"/>
       <c r="R68" s="8" t="n"/>
@@ -6222,13 +6222,13 @@
         </is>
       </c>
       <c r="D69" s="13" t="n">
-        <v>309.95</v>
+        <v>304.67</v>
       </c>
       <c r="E69" s="15" t="n">
-        <v>-0.1073</v>
+        <v>-0.1225</v>
       </c>
       <c r="F69" s="15" t="n">
-        <v>-0.1559</v>
+        <v>-0.1703</v>
       </c>
       <c r="G69" s="16" t="n">
         <v>46325</v>
@@ -6257,7 +6257,7 @@
         <v>406</v>
       </c>
       <c r="M69" s="14" t="n">
-        <v>0.3098886917244718</v>
+        <v>0.3325893589785669</v>
       </c>
       <c r="N69" s="12" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>436</v>
       </c>
       <c r="P69" s="14" t="n">
-        <v>0.4066784965316987</v>
+        <v>0.4310565529917615</v>
       </c>
       <c r="Q69" s="19" t="inlineStr">
         <is>
@@ -6305,13 +6305,13 @@
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>322.68</v>
+        <v>324.43</v>
       </c>
       <c r="E70" s="25" t="n">
-        <v>-0.04019999999999999</v>
+        <v>-0.035</v>
       </c>
       <c r="F70" s="25" t="n">
-        <v>-0.0919</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="G70" s="6" t="n">
         <v>46311</v>
@@ -6340,7 +6340,7 @@
         <v>415</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>0.2861038800049585</v>
+        <v>0.2791665382362913</v>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
         <v>380</v>
       </c>
       <c r="P70" s="5" t="n">
-        <v>0.1776372877153836</v>
+        <v>0.1712850229633511</v>
       </c>
       <c r="Q70" s="9" t="inlineStr">
         <is>
@@ -6400,13 +6400,13 @@
         </is>
       </c>
       <c r="D71" s="13" t="n">
-        <v>59.2</v>
+        <v>59.52</v>
       </c>
       <c r="E71" s="15" t="n">
-        <v>-0.0733</v>
+        <v>-0.0684</v>
       </c>
       <c r="F71" s="15" t="n">
-        <v>-0.0337</v>
+        <v>-0.0286</v>
       </c>
       <c r="G71" s="16" t="n">
         <v>46309</v>
@@ -6461,13 +6461,13 @@
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>1050.24</v>
+        <v>1058.66</v>
       </c>
       <c r="E72" s="25" t="n">
-        <v>-0.08439999999999999</v>
+        <v>-0.0771</v>
       </c>
       <c r="F72" s="25" t="n">
-        <v>-0.0205</v>
+        <v>-0.0126</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>46308</v>
@@ -6499,7 +6499,7 @@
         <v>1245</v>
       </c>
       <c r="P72" s="5" t="n">
-        <v>0.1854433272394881</v>
+        <v>0.1760149623108457</v>
       </c>
       <c r="Q72" s="9" t="inlineStr">
         <is>
@@ -6544,13 +6544,13 @@
         </is>
       </c>
       <c r="D73" s="13" t="n">
-        <v>35.81</v>
+        <v>35.46</v>
       </c>
       <c r="E73" s="14" t="n">
-        <v>0.4349</v>
+        <v>0.4207</v>
       </c>
       <c r="F73" s="14" t="n">
-        <v>0.5982</v>
+        <v>0.5822999999999999</v>
       </c>
       <c r="G73" s="16" t="n"/>
       <c r="H73" s="21" t="inlineStr">
@@ -6595,13 +6595,13 @@
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>23.95</v>
+        <v>23.6</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>0.279</v>
+        <v>0.26</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>0.5268</v>
+        <v>0.5041</v>
       </c>
       <c r="G74" s="6" t="n">
         <v>46346</v>
@@ -6656,13 +6656,13 @@
         </is>
       </c>
       <c r="D75" s="13" t="n">
-        <v>515.03</v>
+        <v>516.76</v>
       </c>
       <c r="E75" s="14" t="n">
-        <v>0.0337</v>
+        <v>0.0372</v>
       </c>
       <c r="F75" s="14" t="n">
-        <v>0.0491</v>
+        <v>0.0527</v>
       </c>
       <c r="G75" s="16" t="n">
         <v>46332</v>
@@ -6739,13 +6739,13 @@
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>68.11</v>
+        <v>67.23</v>
       </c>
       <c r="E76" s="25" t="n">
-        <v>-0.011</v>
+        <v>-0.0237</v>
       </c>
       <c r="F76" s="25" t="n">
-        <v>-0.018</v>
+        <v>-0.0306</v>
       </c>
       <c r="G76" s="6" t="n">
         <v>46321</v>
@@ -6773,8 +6773,8 @@
       <c r="L76" s="8" t="n">
         <v>68</v>
       </c>
-      <c r="M76" s="25" t="n">
-        <v>-0.001615034503009829</v>
+      <c r="M76" s="5" t="n">
+        <v>0.01145322028856159</v>
       </c>
       <c r="N76" s="3" t="inlineStr"/>
       <c r="O76" s="8" t="n"/>
@@ -6816,13 +6816,13 @@
         </is>
       </c>
       <c r="D77" s="13" t="n">
-        <v>127.06</v>
+        <v>126.7</v>
       </c>
       <c r="E77" s="15" t="n">
-        <v>-0.09609999999999999</v>
-      </c>
-      <c r="F77" s="14" t="n">
-        <v>0.0012</v>
+        <v>-0.0987</v>
+      </c>
+      <c r="F77" s="15" t="n">
+        <v>-0.0017</v>
       </c>
       <c r="G77" s="16" t="n">
         <v>46310</v>
@@ -6881,13 +6881,13 @@
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>135.4</v>
+        <v>136.17</v>
       </c>
       <c r="E78" s="25" t="n">
-        <v>-0.0225</v>
+        <v>-0.0169</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>0.0467</v>
+        <v>0.0526</v>
       </c>
       <c r="G78" s="6" t="n">
         <v>46308</v>
@@ -6919,7 +6919,7 @@
         <v>140</v>
       </c>
       <c r="P78" s="5" t="n">
-        <v>0.03397341211225993</v>
+        <v>0.02812660644782267</v>
       </c>
       <c r="Q78" s="9" t="inlineStr">
         <is>
@@ -6968,13 +6968,13 @@
         </is>
       </c>
       <c r="D79" s="13" t="n">
-        <v>341.21</v>
+        <v>341.86</v>
       </c>
       <c r="E79" s="14" t="n">
-        <v>0.001</v>
+        <v>0.0029</v>
       </c>
       <c r="F79" s="15" t="n">
-        <v>-0.0311</v>
+        <v>-0.0292</v>
       </c>
       <c r="G79" s="16" t="n">
         <v>46315</v>
@@ -7003,7 +7003,7 @@
         <v>358</v>
       </c>
       <c r="M79" s="14" t="n">
-        <v>0.04920723308226611</v>
+        <v>0.04721230913239333</v>
       </c>
       <c r="N79" s="12" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>374</v>
       </c>
       <c r="P79" s="14" t="n">
-        <v>0.09609917646024449</v>
+        <v>0.09401509389808689</v>
       </c>
       <c r="Q79" s="19" t="inlineStr">
         <is>
@@ -7059,13 +7059,13 @@
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>58.67</v>
+        <v>58.51</v>
       </c>
       <c r="E80" s="25" t="n">
-        <v>-0.0174</v>
+        <v>-0.0201</v>
       </c>
       <c r="F80" s="25" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0107</v>
       </c>
       <c r="G80" s="6" t="n">
         <v>46310</v>
@@ -7094,7 +7094,7 @@
         <v>57</v>
       </c>
       <c r="M80" s="25" t="n">
-        <v>-0.02846429180160221</v>
+        <v>-0.0258075542642283</v>
       </c>
       <c r="N80" s="3" t="inlineStr"/>
       <c r="O80" s="8" t="n"/>
@@ -7136,13 +7136,13 @@
         </is>
       </c>
       <c r="D81" s="13" t="n">
-        <v>12.77</v>
+        <v>12.62</v>
       </c>
       <c r="E81" s="14" t="n">
-        <v>0.0302</v>
+        <v>0.0177</v>
       </c>
       <c r="F81" s="15" t="n">
-        <v>-0.0196</v>
+        <v>-0.0315</v>
       </c>
       <c r="G81" s="16" t="n"/>
       <c r="H81" s="21" t="inlineStr">
@@ -7187,13 +7187,13 @@
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>410.42</v>
+        <v>407.75</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0003</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>0.122</v>
+        <v>0.1147</v>
       </c>
       <c r="G82" s="6" t="n">
         <v>46330</v>
@@ -7260,13 +7260,13 @@
         </is>
       </c>
       <c r="D83" s="13" t="n">
-        <v>89.34999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="E83" s="14" t="n">
-        <v>0.1979</v>
+        <v>0.157</v>
       </c>
       <c r="F83" s="14" t="n">
-        <v>0.4778</v>
+        <v>0.4274</v>
       </c>
       <c r="G83" s="16" t="n"/>
       <c r="H83" s="21" t="inlineStr">
@@ -7311,13 +7311,13 @@
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>44.13</v>
+        <v>42.35</v>
       </c>
       <c r="E84" s="25" t="n">
-        <v>-0.0048</v>
+        <v>-0.0451</v>
       </c>
       <c r="F84" s="25" t="n">
-        <v>-0.1227</v>
+        <v>-0.1582</v>
       </c>
       <c r="G84" s="6" t="n">
         <v>46331</v>
@@ -7372,13 +7372,13 @@
         </is>
       </c>
       <c r="D85" s="13" t="n">
-        <v>957.91</v>
+        <v>976.67</v>
       </c>
       <c r="E85" s="15" t="n">
-        <v>-0.0888</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="F85" s="15" t="n">
-        <v>-0.1007</v>
+        <v>-0.08310000000000001</v>
       </c>
       <c r="G85" s="16" t="n">
         <v>46308</v>
@@ -7407,7 +7407,7 @@
         <v>1325</v>
       </c>
       <c r="M85" s="14" t="n">
-        <v>0.3832197179275715</v>
+        <v>0.3566506598953588</v>
       </c>
       <c r="N85" s="12" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>1210</v>
       </c>
       <c r="P85" s="14" t="n">
-        <v>0.2631666858055559</v>
+        <v>0.2389036214893465</v>
       </c>
       <c r="Q85" s="19" t="inlineStr">
         <is>
@@ -7459,13 +7459,13 @@
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>137.46</v>
+        <v>133.73</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>0.0978</v>
+        <v>0.068</v>
       </c>
       <c r="F86" s="25" t="n">
-        <v>-0.0182</v>
+        <v>-0.0449</v>
       </c>
       <c r="G86" s="6" t="n">
         <v>46324</v>
@@ -7520,13 +7520,13 @@
         </is>
       </c>
       <c r="D87" s="13" t="n">
-        <v>111.09</v>
+        <v>110.45</v>
       </c>
       <c r="E87" s="14" t="n">
-        <v>0.1542</v>
+        <v>0.1475</v>
       </c>
       <c r="F87" s="14" t="n">
-        <v>0.1113</v>
+        <v>0.1049</v>
       </c>
       <c r="G87" s="16" t="n">
         <v>46330</v>
@@ -7581,13 +7581,13 @@
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>88.19</v>
-      </c>
-      <c r="E88" s="5" t="n">
-        <v>0.0017</v>
+        <v>87.09</v>
+      </c>
+      <c r="E88" s="25" t="n">
+        <v>-0.0108</v>
       </c>
       <c r="F88" s="25" t="n">
-        <v>-0.0356</v>
+        <v>-0.04769999999999999</v>
       </c>
       <c r="G88" s="6" t="n">
         <v>46329</v>
@@ -7642,13 +7642,13 @@
         </is>
       </c>
       <c r="D89" s="13" t="n">
-        <v>156.42</v>
+        <v>156.9</v>
       </c>
       <c r="E89" s="14" t="n">
-        <v>0.0137</v>
+        <v>0.0168</v>
       </c>
       <c r="F89" s="14" t="n">
-        <v>0.1201</v>
+        <v>0.1235</v>
       </c>
       <c r="G89" s="16" t="n">
         <v>46324</v>
@@ -7703,13 +7703,13 @@
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>165.09</v>
+        <v>154.07</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>0.1016</v>
+        <v>0.028</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0.0885</v>
+        <v>0.0158</v>
       </c>
       <c r="G90" s="6" t="n">
         <v>46329</v>
@@ -7778,13 +7778,13 @@
         </is>
       </c>
       <c r="D91" s="13" t="n">
-        <v>345.08</v>
+        <v>352.49</v>
       </c>
       <c r="E91" s="15" t="n">
-        <v>-0.044</v>
+        <v>-0.0235</v>
       </c>
       <c r="F91" s="14" t="n">
-        <v>0.0117</v>
+        <v>0.0334</v>
       </c>
       <c r="G91" s="16" t="n">
         <v>46308</v>
@@ -7813,7 +7813,7 @@
         <v>196</v>
       </c>
       <c r="M91" s="15" t="n">
-        <v>-0.432015764460415</v>
+        <v>-0.443955856903742</v>
       </c>
       <c r="N91" s="12" t="inlineStr"/>
       <c r="O91" s="18" t="n"/>
@@ -7857,13 +7857,13 @@
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>101.22</v>
+        <v>100</v>
       </c>
       <c r="E92" s="25" t="n">
-        <v>-0.0699</v>
-      </c>
-      <c r="F92" s="5" t="n">
-        <v>0.0028</v>
+        <v>-0.08109999999999999</v>
+      </c>
+      <c r="F92" s="25" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>46332</v>
@@ -7892,7 +7892,7 @@
         <v>375</v>
       </c>
       <c r="M92" s="5" t="n">
-        <v>2.704801422643746</v>
+        <v>2.75</v>
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>368</v>
       </c>
       <c r="P92" s="5" t="n">
-        <v>2.635645129421063</v>
+        <v>2.68</v>
       </c>
       <c r="Q92" s="9" t="inlineStr">
         <is>
@@ -7956,13 +7956,13 @@
         </is>
       </c>
       <c r="D93" s="13" t="n">
-        <v>364.35</v>
-      </c>
-      <c r="E93" s="15" t="n">
-        <v>-0.0077</v>
+        <v>369.2</v>
+      </c>
+      <c r="E93" s="14" t="n">
+        <v>0.005600000000000001</v>
       </c>
       <c r="F93" s="14" t="n">
-        <v>0.0592</v>
+        <v>0.0733</v>
       </c>
       <c r="G93" s="16" t="n">
         <v>46317</v>
@@ -7994,7 +7994,7 @@
         <v>115</v>
       </c>
       <c r="P93" s="15" t="n">
-        <v>-0.6843694250034308</v>
+        <v>-0.6885157096424702</v>
       </c>
       <c r="Q93" s="19" t="inlineStr">
         <is>
@@ -8043,13 +8043,13 @@
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>571.36</v>
+        <v>573.27</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0.0162</v>
+        <v>0.0196</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0.05110000000000001</v>
+        <v>0.0546</v>
       </c>
       <c r="G94" s="6" t="n">
         <v>46324</v>
@@ -8078,7 +8078,7 @@
         <v>366</v>
       </c>
       <c r="M94" s="25" t="n">
-        <v>-0.3594231307756931</v>
+        <v>-0.3615573813386362</v>
       </c>
       <c r="N94" s="3" t="inlineStr"/>
       <c r="O94" s="8" t="n"/>
@@ -8120,13 +8120,13 @@
         </is>
       </c>
       <c r="D95" s="13" t="n">
-        <v>1784.35</v>
+        <v>1791.98</v>
       </c>
       <c r="E95" s="15" t="n">
-        <v>-0.0083</v>
+        <v>-0.004</v>
       </c>
       <c r="F95" s="15" t="n">
-        <v>-0.09539999999999998</v>
+        <v>-0.0915</v>
       </c>
       <c r="G95" s="16" t="n">
         <v>46330</v>
@@ -8191,13 +8191,13 @@
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>201.02</v>
+        <v>206.28</v>
       </c>
       <c r="E96" s="25" t="n">
-        <v>-0.0788</v>
+        <v>-0.0547</v>
       </c>
       <c r="F96" s="25" t="n">
-        <v>-0.0672</v>
+        <v>-0.0428</v>
       </c>
       <c r="G96" s="6" t="n">
         <v>46309</v>
@@ -8226,7 +8226,7 @@
         <v>668</v>
       </c>
       <c r="M96" s="5" t="n">
-        <v>2.323052432593772</v>
+        <v>2.238316850882296</v>
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         <v>550</v>
       </c>
       <c r="P96" s="5" t="n">
-        <v>1.73604616456074</v>
+        <v>1.666278844289316</v>
       </c>
       <c r="Q96" s="9" t="inlineStr">
         <is>
@@ -8286,13 +8286,13 @@
         </is>
       </c>
       <c r="D97" s="13" t="n">
-        <v>117.11</v>
+        <v>118.37</v>
       </c>
       <c r="E97" s="14" t="n">
-        <v>0.0366</v>
+        <v>0.0478</v>
       </c>
       <c r="F97" s="14" t="n">
-        <v>0.0277</v>
+        <v>0.0388</v>
       </c>
       <c r="G97" s="16" t="n">
         <v>46321</v>
@@ -8321,7 +8321,7 @@
         <v>240</v>
       </c>
       <c r="M97" s="14" t="n">
-        <v>1.049355306976347</v>
+        <v>1.027540762017403</v>
       </c>
       <c r="N97" s="12" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>240</v>
       </c>
       <c r="P97" s="14" t="n">
-        <v>1.049355306976347</v>
+        <v>1.027540762017403</v>
       </c>
       <c r="Q97" s="19" t="inlineStr">
         <is>
@@ -8381,13 +8381,13 @@
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>240.3</v>
+        <v>240.78</v>
       </c>
       <c r="E98" s="25" t="n">
-        <v>-0.05599999999999999</v>
+        <v>-0.0541</v>
       </c>
       <c r="F98" s="25" t="n">
-        <v>-0.04969999999999999</v>
+        <v>-0.0478</v>
       </c>
       <c r="G98" s="6" t="n">
         <v>46310</v>
@@ -8416,7 +8416,7 @@
         <v>113</v>
       </c>
       <c r="M98" s="25" t="n">
-        <v>-0.5297544735746983</v>
+        <v>-0.5306919179333832</v>
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>114</v>
       </c>
       <c r="P98" s="25" t="n">
-        <v>-0.5255930087390762</v>
+        <v>-0.526538749065537</v>
       </c>
       <c r="Q98" s="9" t="inlineStr"/>
       <c r="R98" s="8" t="n"/>
@@ -8466,13 +8466,13 @@
         </is>
       </c>
       <c r="D99" s="13" t="n">
-        <v>20.11</v>
-      </c>
-      <c r="E99" s="14" t="n">
-        <v>0.0037</v>
+        <v>19.7</v>
+      </c>
+      <c r="E99" s="15" t="n">
+        <v>-0.017</v>
       </c>
       <c r="F99" s="14" t="n">
-        <v>0.1016</v>
+        <v>0.0789</v>
       </c>
       <c r="G99" s="16" t="n">
         <v>46324</v>
@@ -8527,13 +8527,13 @@
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>14.56</v>
-      </c>
-      <c r="E100" s="25" t="n">
-        <v>-0.0024</v>
+        <v>14.65</v>
+      </c>
+      <c r="E100" s="5" t="n">
+        <v>0.004099999999999999</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>0.0742</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="G100" s="6" t="n">
         <v>46323</v>
@@ -8588,13 +8588,13 @@
         </is>
       </c>
       <c r="D101" s="13" t="n">
-        <v>105.5</v>
+        <v>105.82</v>
       </c>
       <c r="E101" s="14" t="n">
-        <v>0.0003</v>
+        <v>0.0033</v>
       </c>
       <c r="F101" s="14" t="n">
-        <v>0.063</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="G101" s="16" t="n">
         <v>46323</v>
@@ -8623,7 +8623,7 @@
         <v>285</v>
       </c>
       <c r="M101" s="14" t="n">
-        <v>1.701421800947867</v>
+        <v>1.693252693252693</v>
       </c>
       <c r="N101" s="12" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>285</v>
       </c>
       <c r="P101" s="14" t="n">
-        <v>1.701421800947867</v>
+        <v>1.693252693252693</v>
       </c>
       <c r="Q101" s="19" t="inlineStr">
         <is>
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>413.79</v>
+        <v>412.52</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0048</v>
       </c>
       <c r="F102" s="25" t="n">
-        <v>-0.08220000000000001</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="G102" s="6" t="n">
         <v>46324</v>
@@ -8750,13 +8750,13 @@
         </is>
       </c>
       <c r="D103" s="13" t="n">
-        <v>50.66</v>
+        <v>50.46</v>
       </c>
       <c r="E103" s="15" t="n">
-        <v>-0.0356</v>
+        <v>-0.0394</v>
       </c>
       <c r="F103" s="15" t="n">
-        <v>-0.035</v>
+        <v>-0.0389</v>
       </c>
       <c r="G103" s="16" t="n">
         <v>46311</v>
@@ -8811,13 +8811,13 @@
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>374.17</v>
+        <v>375.62</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>0.04269999999999999</v>
+        <v>0.04679999999999999</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>0.0435</v>
+        <v>0.0476</v>
       </c>
       <c r="G104" s="6" t="n">
         <v>46322</v>
@@ -8846,7 +8846,7 @@
         <v>525</v>
       </c>
       <c r="M104" s="5" t="n">
-        <v>0.4031055402624475</v>
+        <v>0.3976891539321655</v>
       </c>
       <c r="N104" s="3" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         <v>543</v>
       </c>
       <c r="P104" s="5" t="n">
-        <v>0.4512120159285886</v>
+        <v>0.4456099249241254</v>
       </c>
       <c r="Q104" s="9" t="inlineStr">
         <is>
@@ -8902,13 +8902,13 @@
         </is>
       </c>
       <c r="D105" s="13" t="n">
-        <v>70.77</v>
+        <v>71.28</v>
       </c>
       <c r="E105" s="14" t="n">
-        <v>0.0146</v>
+        <v>0.0219</v>
       </c>
       <c r="F105" s="15" t="n">
-        <v>-0.0117</v>
+        <v>-0.0046</v>
       </c>
       <c r="G105" s="16" t="n">
         <v>46314</v>
@@ -8937,7 +8937,7 @@
         <v>412</v>
       </c>
       <c r="M105" s="14" t="n">
-        <v>4.821675851349442</v>
+        <v>4.780022446689114</v>
       </c>
       <c r="N105" s="12" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         <v>350</v>
       </c>
       <c r="P105" s="14" t="n">
-        <v>3.945598417408507</v>
+        <v>3.910213243546577</v>
       </c>
       <c r="Q105" s="19" t="inlineStr">
         <is>
@@ -9084,13 +9084,13 @@
         </is>
       </c>
       <c r="D107" s="13" t="n">
-        <v>261.73</v>
+        <v>263.04</v>
       </c>
       <c r="E107" s="14" t="n">
-        <v>0.0455</v>
+        <v>0.0508</v>
       </c>
       <c r="F107" s="14" t="n">
-        <v>0.0284</v>
+        <v>0.0336</v>
       </c>
       <c r="G107" s="16" t="n">
         <v>46325</v>
@@ -9119,7 +9119,7 @@
         <v>295</v>
       </c>
       <c r="M107" s="14" t="n">
-        <v>0.1271157299507125</v>
+        <v>0.1215024330900242</v>
       </c>
       <c r="N107" s="12" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>246</v>
       </c>
       <c r="P107" s="15" t="n">
-        <v>-0.06010010315974484</v>
+        <v>-0.06478102189781029</v>
       </c>
       <c r="Q107" s="19" t="inlineStr">
         <is>
@@ -9167,13 +9167,13 @@
         </is>
       </c>
       <c r="D108" s="4" t="n">
-        <v>101.75</v>
+        <v>102.03</v>
       </c>
       <c r="E108" s="25" t="n">
-        <v>-0.0781</v>
+        <v>-0.0756</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>0.0106</v>
+        <v>0.0134</v>
       </c>
       <c r="G108" s="6" t="n">
         <v>46316</v>
@@ -9202,7 +9202,7 @@
         <v>112</v>
       </c>
       <c r="M108" s="5" t="n">
-        <v>0.1007371007371007</v>
+        <v>0.09771635793394098</v>
       </c>
       <c r="N108" s="3" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         <v>120</v>
       </c>
       <c r="P108" s="5" t="n">
-        <v>0.1793611793611794</v>
+        <v>0.1761246692149368</v>
       </c>
       <c r="Q108" s="9" t="inlineStr">
         <is>
@@ -9266,13 +9266,13 @@
         </is>
       </c>
       <c r="D109" s="13" t="n">
-        <v>376.43</v>
+        <v>375.65</v>
       </c>
       <c r="E109" s="15" t="n">
-        <v>-0.1024</v>
+        <v>-0.1043</v>
       </c>
       <c r="F109" s="14" t="n">
-        <v>0.0277</v>
+        <v>0.0256</v>
       </c>
       <c r="G109" s="16" t="n">
         <v>46329</v>
@@ -9301,7 +9301,7 @@
         <v>390</v>
       </c>
       <c r="M109" s="14" t="n">
-        <v>0.03604919905427302</v>
+        <v>0.03820045254891528</v>
       </c>
       <c r="N109" s="12" t="inlineStr">
         <is>
@@ -9349,13 +9349,13 @@
         </is>
       </c>
       <c r="D110" s="4" t="n">
-        <v>183.76</v>
+        <v>185.92</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>0.0092</v>
+        <v>0.021</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>0.1618</v>
+        <v>0.1754</v>
       </c>
       <c r="G110" s="6" t="n">
         <v>46331</v>
@@ -9384,7 +9384,7 @@
         <v>161</v>
       </c>
       <c r="M110" s="25" t="n">
-        <v>-0.1238572050500653</v>
+        <v>-0.1340361445783132</v>
       </c>
       <c r="N110" s="3" t="inlineStr">
         <is>
@@ -9395,7 +9395,7 @@
         <v>180</v>
       </c>
       <c r="P110" s="25" t="n">
-        <v>-0.02046147148454501</v>
+        <v>-0.03184165232357997</v>
       </c>
       <c r="Q110" s="9" t="inlineStr">
         <is>
@@ -9436,13 +9436,13 @@
         </is>
       </c>
       <c r="D111" s="13" t="n">
-        <v>43.82</v>
+        <v>43.87</v>
       </c>
       <c r="E111" s="15" t="n">
-        <v>-0.148</v>
+        <v>-0.147</v>
       </c>
       <c r="F111" s="15" t="n">
-        <v>-0.0048</v>
+        <v>-0.0036</v>
       </c>
       <c r="G111" s="16" t="n">
         <v>46323</v>
@@ -9471,7 +9471,7 @@
         <v>55</v>
       </c>
       <c r="M111" s="14" t="n">
-        <v>0.2551346417161113</v>
+        <v>0.2537041258263051</v>
       </c>
       <c r="N111" s="12" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>65</v>
       </c>
       <c r="P111" s="14" t="n">
-        <v>0.4833409402099498</v>
+        <v>0.4816503305219969</v>
       </c>
       <c r="Q111" s="19" t="inlineStr">
         <is>
@@ -9523,13 +9523,13 @@
         </is>
       </c>
       <c r="D112" s="4" t="n">
-        <v>322.39</v>
+        <v>323.29</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0.0316</v>
+        <v>0.0345</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>0.0471</v>
+        <v>0.05</v>
       </c>
       <c r="G112" s="6" t="n">
         <v>46330</v>
@@ -9558,7 +9558,7 @@
         <v>331</v>
       </c>
       <c r="M112" s="5" t="n">
-        <v>0.02670678370917216</v>
+        <v>0.02384855702310612</v>
       </c>
       <c r="N112" s="3" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>330</v>
       </c>
       <c r="P112" s="5" t="n">
-        <v>0.02360495052576077</v>
+        <v>0.0207553589656345</v>
       </c>
       <c r="Q112" s="9" t="inlineStr">
         <is>
@@ -9618,13 +9618,13 @@
         </is>
       </c>
       <c r="D113" s="13" t="n">
-        <v>94.25</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="E113" s="14" t="n">
-        <v>0.0026</v>
+        <v>0.0051</v>
       </c>
       <c r="F113" s="15" t="n">
-        <v>-0.123</v>
+        <v>-0.1208</v>
       </c>
       <c r="G113" s="16" t="n">
         <v>46330</v>
@@ -9653,7 +9653,7 @@
         <v>123</v>
       </c>
       <c r="M113" s="14" t="n">
-        <v>0.3050397877984085</v>
+        <v>0.3017250502698699</v>
       </c>
       <c r="N113" s="12" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>130</v>
       </c>
       <c r="P113" s="14" t="n">
-        <v>0.3793103448275862</v>
+        <v>0.3758069636998625</v>
       </c>
       <c r="Q113" s="19" t="inlineStr">
         <is>
@@ -9705,13 +9705,13 @@
         </is>
       </c>
       <c r="D114" s="4" t="n">
-        <v>207.38</v>
+        <v>209.36</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>0.0234</v>
+        <v>0.0332</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>0.0174</v>
+        <v>0.0271</v>
       </c>
       <c r="G114" s="6" t="n">
         <v>46315</v>
@@ -9740,7 +9740,7 @@
         <v>212</v>
       </c>
       <c r="M114" s="5" t="n">
-        <v>0.02227794387115442</v>
+        <v>0.01260985861673665</v>
       </c>
       <c r="N114" s="3" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>205</v>
       </c>
       <c r="P114" s="25" t="n">
-        <v>-0.01147651653968558</v>
+        <v>-0.02082537256400465</v>
       </c>
       <c r="Q114" s="9" t="inlineStr">
         <is>
@@ -9796,13 +9796,13 @@
         </is>
       </c>
       <c r="D115" s="13" t="n">
-        <v>85.33</v>
+        <v>86.45</v>
       </c>
       <c r="E115" s="15" t="n">
-        <v>-0.0386</v>
+        <v>-0.026</v>
       </c>
       <c r="F115" s="14" t="n">
-        <v>0.1132</v>
+        <v>0.1279</v>
       </c>
       <c r="G115" s="16" t="n">
         <v>46324</v>
@@ -9831,7 +9831,7 @@
         <v>85</v>
       </c>
       <c r="M115" s="15" t="n">
-        <v>-0.003867338567912789</v>
+        <v>-0.01677270098322733</v>
       </c>
       <c r="N115" s="12" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>90</v>
       </c>
       <c r="P115" s="14" t="n">
-        <v>0.05472870033985704</v>
+        <v>0.04106419895893577</v>
       </c>
       <c r="Q115" s="19" t="inlineStr">
         <is>
@@ -9883,13 +9883,13 @@
         </is>
       </c>
       <c r="D116" s="4" t="n">
-        <v>144.54</v>
+        <v>146.3</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0.0405</v>
+        <v>0.05309999999999999</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>0.0764</v>
+        <v>0.0895</v>
       </c>
       <c r="G116" s="6" t="n">
         <v>46324</v>
@@ -9918,7 +9918,7 @@
         <v>165</v>
       </c>
       <c r="M116" s="5" t="n">
-        <v>0.1415525114155252</v>
+        <v>0.1278195488721804</v>
       </c>
       <c r="N116" s="3" t="inlineStr"/>
       <c r="O116" s="8" t="n"/>
@@ -9966,13 +9966,13 @@
         </is>
       </c>
       <c r="D117" s="13" t="n">
-        <v>508.26</v>
+        <v>510.73</v>
       </c>
       <c r="E117" s="15" t="n">
-        <v>-0.0693</v>
+        <v>-0.06480000000000001</v>
       </c>
       <c r="F117" s="15" t="n">
-        <v>-0.1043</v>
+        <v>-0.0999</v>
       </c>
       <c r="G117" s="16" t="n">
         <v>46328</v>
@@ -10037,13 +10037,13 @@
         </is>
       </c>
       <c r="D118" s="4" t="n">
-        <v>371.98</v>
+        <v>377.16</v>
       </c>
       <c r="E118" s="25" t="n">
-        <v>-0.047</v>
+        <v>-0.0337</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>0.07690000000000001</v>
+        <v>0.0919</v>
       </c>
       <c r="G118" s="6" t="n">
         <v>46315</v>
@@ -10072,7 +10072,7 @@
         <v>487</v>
       </c>
       <c r="M118" s="5" t="n">
-        <v>0.3092101725899241</v>
+        <v>0.2912291865521263</v>
       </c>
       <c r="N118" s="3" t="inlineStr">
         <is>
@@ -10082,8 +10082,8 @@
       <c r="O118" s="8" t="n">
         <v>375</v>
       </c>
-      <c r="P118" s="5" t="n">
-        <v>0.008118716060003176</v>
+      <c r="P118" s="25" t="n">
+        <v>-0.005727012408526951</v>
       </c>
       <c r="Q118" s="9" t="inlineStr">
         <is>
@@ -10128,13 +10128,13 @@
         </is>
       </c>
       <c r="D119" s="13" t="n">
-        <v>263.48</v>
+        <v>267.2</v>
       </c>
       <c r="E119" s="14" t="n">
-        <v>0.0042</v>
+        <v>0.0184</v>
       </c>
       <c r="F119" s="14" t="n">
-        <v>0.0412</v>
+        <v>0.05599999999999999</v>
       </c>
       <c r="G119" s="16" t="n">
         <v>46308</v>
@@ -10163,7 +10163,7 @@
         <v>272</v>
       </c>
       <c r="M119" s="14" t="n">
-        <v>0.03233642022164863</v>
+        <v>0.01796407185628747</v>
       </c>
       <c r="N119" s="12" t="inlineStr"/>
       <c r="O119" s="18" t="n"/>
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="D120" s="4" t="n">
-        <v>1143.4</v>
+        <v>1136.11</v>
       </c>
       <c r="E120" s="25" t="n">
-        <v>-0.0336</v>
+        <v>-0.0398</v>
       </c>
       <c r="F120" s="25" t="n">
-        <v>-0.0303</v>
+        <v>-0.0365</v>
       </c>
       <c r="G120" s="6" t="n">
         <v>46324</v>
@@ -10250,7 +10250,7 @@
         <v>1280</v>
       </c>
       <c r="M120" s="5" t="n">
-        <v>0.1194682525800244</v>
+        <v>0.1266514686077934</v>
       </c>
       <c r="N120" s="3" t="inlineStr">
         <is>
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="D121" s="13" t="n">
-        <v>93.61</v>
+        <v>93.75</v>
       </c>
       <c r="E121" s="14" t="n">
-        <v>0.0332</v>
+        <v>0.0348</v>
       </c>
       <c r="F121" s="14" t="n">
-        <v>0.1251</v>
+        <v>0.1268</v>
       </c>
       <c r="G121" s="16" t="n"/>
       <c r="H121" s="21" t="inlineStr">
@@ -10335,7 +10335,7 @@
         <v>102</v>
       </c>
       <c r="M121" s="14" t="n">
-        <v>0.08962717658369833</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="N121" s="12" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         <v>105</v>
       </c>
       <c r="P121" s="14" t="n">
-        <v>0.121675034718513</v>
+        <v>0.12</v>
       </c>
       <c r="Q121" s="19" t="inlineStr">
         <is>
@@ -10387,13 +10387,13 @@
         </is>
       </c>
       <c r="D122" s="4" t="n">
-        <v>143.29</v>
+        <v>143.79</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0.0538</v>
+        <v>0.0575</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>0.1238</v>
+        <v>0.1278</v>
       </c>
       <c r="G122" s="6" t="n">
         <v>46324</v>
@@ -10422,7 +10422,7 @@
         <v>150</v>
       </c>
       <c r="M122" s="5" t="n">
-        <v>0.04682811082420273</v>
+        <v>0.04318798247444195</v>
       </c>
       <c r="N122" s="3" t="inlineStr"/>
       <c r="O122" s="8" t="n"/>
@@ -10466,13 +10466,13 @@
         </is>
       </c>
       <c r="D123" s="13" t="n">
-        <v>138.56</v>
+        <v>138.62</v>
       </c>
       <c r="E123" s="15" t="n">
-        <v>-0.0882</v>
+        <v>-0.08779999999999999</v>
       </c>
       <c r="F123" s="15" t="n">
-        <v>-0.0989</v>
+        <v>-0.09849999999999999</v>
       </c>
       <c r="G123" s="16" t="n">
         <v>46322</v>
@@ -10545,13 +10545,13 @@
         </is>
       </c>
       <c r="D124" s="4" t="n">
-        <v>27.51</v>
+        <v>27.55</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0.0238</v>
+        <v>0.0253</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>0.09820000000000001</v>
+        <v>0.0998</v>
       </c>
       <c r="G124" s="6" t="n">
         <v>46329</v>
@@ -10580,7 +10580,7 @@
         <v>28</v>
       </c>
       <c r="M124" s="5" t="n">
-        <v>0.01781170483460554</v>
+        <v>0.01633393829401086</v>
       </c>
       <c r="N124" s="3" t="inlineStr"/>
       <c r="O124" s="8" t="n"/>
@@ -10624,13 +10624,13 @@
         </is>
       </c>
       <c r="D125" s="13" t="n">
-        <v>280.2</v>
+        <v>281.5</v>
       </c>
       <c r="E125" s="15" t="n">
-        <v>-0.1552</v>
+        <v>-0.1513</v>
       </c>
       <c r="F125" s="15" t="n">
-        <v>-0.124</v>
+        <v>-0.12</v>
       </c>
       <c r="G125" s="16" t="n">
         <v>46324</v>
@@ -10659,7 +10659,7 @@
         <v>418</v>
       </c>
       <c r="M125" s="14" t="n">
-        <v>0.4917915774446824</v>
+        <v>0.4849023090586146</v>
       </c>
       <c r="N125" s="12" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>350</v>
       </c>
       <c r="P125" s="14" t="n">
-        <v>0.2491077801570308</v>
+        <v>0.2433392539964476</v>
       </c>
       <c r="Q125" s="19" t="inlineStr">
         <is>
@@ -10715,13 +10715,13 @@
         </is>
       </c>
       <c r="D126" s="4" t="n">
-        <v>633.84</v>
+        <v>641.39</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>0.0825</v>
+        <v>0.09539999999999998</v>
       </c>
       <c r="F126" s="5" t="n">
-        <v>0.1904</v>
+        <v>0.2045</v>
       </c>
       <c r="G126" s="6" t="n">
         <v>46323</v>
@@ -10750,7 +10750,7 @@
         <v>615</v>
       </c>
       <c r="M126" s="25" t="n">
-        <v>-0.02972358954941315</v>
+        <v>-0.04114501317451159</v>
       </c>
       <c r="N126" s="3" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>570</v>
       </c>
       <c r="P126" s="25" t="n">
-        <v>-0.1007194244604317</v>
+        <v>-0.1113051341617425</v>
       </c>
       <c r="Q126" s="9" t="inlineStr">
         <is>
@@ -10810,13 +10810,13 @@
         </is>
       </c>
       <c r="D127" s="13" t="n">
-        <v>377.61</v>
+        <v>375.93</v>
       </c>
       <c r="E127" s="15" t="n">
-        <v>-0.0455</v>
+        <v>-0.0498</v>
       </c>
       <c r="F127" s="15" t="n">
-        <v>-0.1138</v>
+        <v>-0.1177</v>
       </c>
       <c r="G127" s="16" t="n">
         <v>46322</v>
@@ -10845,7 +10845,7 @@
         <v>526</v>
       </c>
       <c r="M127" s="14" t="n">
-        <v>0.3929715844389714</v>
+        <v>0.3991966589524645</v>
       </c>
       <c r="N127" s="12" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>480</v>
       </c>
       <c r="P127" s="14" t="n">
-        <v>0.2711527766743465</v>
+        <v>0.2768334530364696</v>
       </c>
       <c r="Q127" s="19" t="inlineStr">
         <is>
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="D128" s="4" t="n">
-        <v>73.51000000000001</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.0063</v>
       </c>
       <c r="F128" s="25" t="n">
-        <v>-0.0398</v>
+        <v>-0.0409</v>
       </c>
       <c r="G128" s="6" t="n">
         <v>46329</v>
@@ -10980,7 +10980,7 @@
         </is>
       </c>
       <c r="D129" s="13" t="n">
-        <v>276.54</v>
+        <v>276.53</v>
       </c>
       <c r="E129" s="14" t="n">
         <v>0.0394</v>
@@ -11015,7 +11015,7 @@
         <v>248</v>
       </c>
       <c r="M129" s="15" t="n">
-        <v>-0.1032038764735663</v>
+        <v>-0.103171446136043</v>
       </c>
       <c r="N129" s="12" t="inlineStr"/>
       <c r="O129" s="18" t="n"/>
@@ -11071,13 +11071,13 @@
         </is>
       </c>
       <c r="D130" s="4" t="n">
-        <v>124.43</v>
+        <v>123.79</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>0.2474</v>
+        <v>0.241</v>
       </c>
       <c r="F130" s="5" t="n">
-        <v>0.0789</v>
+        <v>0.07339999999999999</v>
       </c>
       <c r="G130" s="6" t="n">
         <v>46325</v>
@@ -11132,13 +11132,13 @@
         </is>
       </c>
       <c r="D131" s="13" t="n">
-        <v>232.38</v>
+        <v>234.45</v>
       </c>
       <c r="E131" s="15" t="n">
-        <v>-0.0857</v>
+        <v>-0.0776</v>
       </c>
       <c r="F131" s="15" t="n">
-        <v>-0.0195</v>
+        <v>-0.0108</v>
       </c>
       <c r="G131" s="16" t="n">
         <v>46324</v>
@@ -11193,13 +11193,13 @@
         </is>
       </c>
       <c r="D132" s="4" t="n">
-        <v>209.09</v>
+        <v>209.69</v>
       </c>
       <c r="E132" s="25" t="n">
-        <v>-0.0746</v>
+        <v>-0.07200000000000001</v>
       </c>
       <c r="F132" s="25" t="n">
-        <v>-0.0231</v>
+        <v>-0.0203</v>
       </c>
       <c r="G132" s="6" t="n">
         <v>46330</v>
@@ -11228,7 +11228,7 @@
         <v>250</v>
       </c>
       <c r="M132" s="5" t="n">
-        <v>0.1956573724233583</v>
+        <v>0.192236158138204</v>
       </c>
       <c r="N132" s="3" t="inlineStr"/>
       <c r="O132" s="8" t="n"/>
@@ -11272,13 +11272,13 @@
         </is>
       </c>
       <c r="D133" s="13" t="n">
-        <v>171.38</v>
+        <v>170.25</v>
       </c>
       <c r="E133" s="14" t="n">
-        <v>0.0211</v>
+        <v>0.0144</v>
       </c>
       <c r="F133" s="14" t="n">
-        <v>0.1432</v>
+        <v>0.1357</v>
       </c>
       <c r="G133" s="16" t="n">
         <v>46329</v>
@@ -11343,13 +11343,13 @@
         </is>
       </c>
       <c r="D134" s="4" t="n">
-        <v>780.73</v>
+        <v>783.54</v>
       </c>
       <c r="E134" s="25" t="n">
-        <v>-0.1145</v>
+        <v>-0.1113</v>
       </c>
       <c r="F134" s="25" t="n">
-        <v>-0.1131</v>
+        <v>-0.1099</v>
       </c>
       <c r="G134" s="6" t="n">
         <v>46330</v>
@@ -11378,7 +11378,7 @@
         <v>1155</v>
       </c>
       <c r="M134" s="5" t="n">
-        <v>0.479384678441971</v>
+        <v>0.4740791791101923</v>
       </c>
       <c r="N134" s="3" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>1103</v>
       </c>
       <c r="P134" s="5" t="n">
-        <v>0.4127803465986961</v>
+        <v>0.4077137095744953</v>
       </c>
       <c r="Q134" s="9" t="inlineStr">
         <is>
@@ -11430,13 +11430,13 @@
         </is>
       </c>
       <c r="D135" s="13" t="n">
-        <v>533.8099999999999</v>
+        <v>538.02</v>
       </c>
       <c r="E135" s="15" t="n">
-        <v>-0.1674</v>
+        <v>-0.1609</v>
       </c>
       <c r="F135" s="15" t="n">
-        <v>-0.1768</v>
+        <v>-0.1703</v>
       </c>
       <c r="G135" s="16" t="n">
         <v>46331</v>
@@ -11465,7 +11465,7 @@
         <v>874</v>
       </c>
       <c r="M135" s="14" t="n">
-        <v>0.6372866750341883</v>
+        <v>0.624474926582655</v>
       </c>
       <c r="N135" s="12" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>845</v>
       </c>
       <c r="P135" s="14" t="n">
-        <v>0.5829602292950677</v>
+        <v>0.5705735846251069</v>
       </c>
       <c r="Q135" s="19" t="inlineStr">
         <is>
@@ -11525,13 +11525,13 @@
         </is>
       </c>
       <c r="D136" s="4" t="n">
-        <v>201.15</v>
+        <v>198.95</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>0.0169</v>
+        <v>0.005699999999999999</v>
       </c>
       <c r="F136" s="25" t="n">
-        <v>-0.0161</v>
+        <v>-0.0269</v>
       </c>
       <c r="G136" s="6" t="n">
         <v>46288</v>
@@ -11560,7 +11560,7 @@
         <v>250</v>
       </c>
       <c r="M136" s="5" t="n">
-        <v>0.2428535918468804</v>
+        <v>0.2565971349585324</v>
       </c>
       <c r="N136" s="3" t="inlineStr"/>
       <c r="O136" s="8" t="n"/>
@@ -11604,13 +11604,13 @@
         </is>
       </c>
       <c r="D137" s="13" t="n">
-        <v>685.16</v>
+        <v>684.04</v>
       </c>
       <c r="E137" s="14" t="n">
-        <v>0.1421</v>
+        <v>0.1402</v>
       </c>
       <c r="F137" s="14" t="n">
-        <v>0.1472</v>
+        <v>0.1453</v>
       </c>
       <c r="G137" s="16" t="n"/>
       <c r="H137" s="21" t="inlineStr">
@@ -11629,7 +11629,7 @@
         <v>750</v>
       </c>
       <c r="M137" s="14" t="n">
-        <v>0.09463482982077184</v>
+        <v>0.09642710952575878</v>
       </c>
       <c r="N137" s="12" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>641.29</v>
       </c>
       <c r="P137" s="15" t="n">
-        <v>-0.06402883997898302</v>
+        <v>-0.06249634524296825</v>
       </c>
       <c r="Q137" s="19" t="inlineStr">
         <is>
@@ -11681,13 +11681,13 @@
         </is>
       </c>
       <c r="D138" s="4" t="n">
-        <v>146.04</v>
+        <v>147</v>
       </c>
       <c r="E138" s="25" t="n">
-        <v>-0.09880000000000001</v>
+        <v>-0.0929</v>
       </c>
       <c r="F138" s="5" t="n">
-        <v>0.0466</v>
+        <v>0.0535</v>
       </c>
       <c r="G138" s="6" t="n">
         <v>46330</v>
@@ -11723,7 +11723,7 @@
         <v>185</v>
       </c>
       <c r="P138" s="5" t="n">
-        <v>0.2667762256915914</v>
+        <v>0.2585034013605442</v>
       </c>
       <c r="Q138" s="9" t="inlineStr">
         <is>
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="D139" s="13" t="n">
-        <v>390.58</v>
+        <v>392.4</v>
       </c>
       <c r="E139" s="15" t="n">
-        <v>-0.1423</v>
+        <v>-0.1383</v>
       </c>
       <c r="F139" s="15" t="n">
-        <v>-0.0235</v>
+        <v>-0.019</v>
       </c>
       <c r="G139" s="16" t="n">
         <v>46329</v>
@@ -11804,7 +11804,7 @@
         <v>453</v>
       </c>
       <c r="P139" s="14" t="n">
-        <v>0.1598136105279329</v>
+        <v>0.154434250764526</v>
       </c>
       <c r="Q139" s="19" t="inlineStr">
         <is>
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="D140" s="4" t="n">
-        <v>48.97</v>
+        <v>49.41</v>
       </c>
       <c r="E140" s="25" t="n">
-        <v>-0.0441</v>
+        <v>-0.0355</v>
       </c>
       <c r="F140" s="5" t="n">
-        <v>0.0765</v>
+        <v>0.0862</v>
       </c>
       <c r="G140" s="6" t="n">
         <v>46309</v>
@@ -11924,13 +11924,13 @@
         </is>
       </c>
       <c r="D141" s="13" t="n">
-        <v>308.39</v>
+        <v>308.26</v>
       </c>
       <c r="E141" s="15" t="n">
-        <v>-0.0697</v>
+        <v>-0.0701</v>
       </c>
       <c r="F141" s="15" t="n">
-        <v>-0.0147</v>
+        <v>-0.0151</v>
       </c>
       <c r="G141" s="16" t="n">
         <v>46282</v>
@@ -11959,7 +11959,7 @@
         <v>425</v>
       </c>
       <c r="M141" s="14" t="n">
-        <v>0.3781251013327281</v>
+        <v>0.3787062869006683</v>
       </c>
       <c r="N141" s="12" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>323</v>
       </c>
       <c r="P141" s="14" t="n">
-        <v>0.04737507701287336</v>
+        <v>0.04781677804450792</v>
       </c>
       <c r="Q141" s="19" t="inlineStr">
         <is>
@@ -12011,13 +12011,13 @@
         </is>
       </c>
       <c r="D142" s="4" t="n">
-        <v>215.8</v>
+        <v>215.11</v>
       </c>
       <c r="E142" s="25" t="n">
-        <v>-0.1191</v>
+        <v>-0.1219</v>
       </c>
       <c r="F142" s="25" t="n">
-        <v>-0.0699</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="G142" s="6" t="n"/>
       <c r="H142" s="7" t="inlineStr">
@@ -12036,7 +12036,7 @@
         <v>285</v>
       </c>
       <c r="M142" s="5" t="n">
-        <v>0.3206672845227062</v>
+        <v>0.3249035377248848</v>
       </c>
       <c r="N142" s="3" t="inlineStr"/>
       <c r="O142" s="8" t="n"/>
@@ -12084,13 +12084,13 @@
         </is>
       </c>
       <c r="D143" s="13" t="n">
-        <v>1590.55</v>
+        <v>1576.78</v>
       </c>
       <c r="E143" s="15" t="n">
-        <v>-0.1545</v>
+        <v>-0.1618</v>
       </c>
       <c r="F143" s="15" t="n">
-        <v>-0.0499</v>
+        <v>-0.0581</v>
       </c>
       <c r="G143" s="16" t="n">
         <v>46317</v>
@@ -12145,13 +12145,13 @@
         </is>
       </c>
       <c r="D144" s="4" t="n">
-        <v>53.72</v>
+        <v>54.04</v>
       </c>
       <c r="E144" s="25" t="n">
-        <v>-0.0185</v>
+        <v>-0.0128</v>
       </c>
       <c r="F144" s="5" t="n">
-        <v>0.0946</v>
+        <v>0.1011</v>
       </c>
       <c r="G144" s="6" t="n">
         <v>46332</v>
@@ -12206,13 +12206,13 @@
         </is>
       </c>
       <c r="D145" s="13" t="n">
-        <v>356.48</v>
+        <v>358.6</v>
       </c>
       <c r="E145" s="15" t="n">
-        <v>-0.0886</v>
+        <v>-0.0832</v>
       </c>
       <c r="F145" s="15" t="n">
-        <v>-0.0328</v>
+        <v>-0.0271</v>
       </c>
       <c r="G145" s="16" t="n">
         <v>46318</v>
@@ -12241,7 +12241,7 @@
         <v>400</v>
       </c>
       <c r="M145" s="14" t="n">
-        <v>0.1220825852782764</v>
+        <v>0.1154489682097043</v>
       </c>
       <c r="N145" s="12" t="inlineStr"/>
       <c r="O145" s="18" t="n"/>
@@ -12293,13 +12293,13 @@
         </is>
       </c>
       <c r="D146" s="4" t="n">
-        <v>309.03</v>
+        <v>307.05</v>
       </c>
       <c r="E146" s="25" t="n">
-        <v>-0.1635</v>
+        <v>-0.1689</v>
       </c>
       <c r="F146" s="25" t="n">
-        <v>-0.1141</v>
+        <v>-0.1198</v>
       </c>
       <c r="G146" s="6" t="n">
         <v>46315</v>
@@ -12328,7 +12328,7 @@
         <v>390</v>
       </c>
       <c r="M146" s="5" t="n">
-        <v>0.2620133967575964</v>
+        <v>0.2701514411333659</v>
       </c>
       <c r="N146" s="3" t="inlineStr"/>
       <c r="O146" s="8" t="n"/>
@@ -12380,13 +12380,13 @@
         </is>
       </c>
       <c r="D147" s="13" t="n">
-        <v>878.21</v>
+        <v>882.8099999999999</v>
       </c>
       <c r="E147" s="15" t="n">
-        <v>-0.1861</v>
+        <v>-0.1818</v>
       </c>
       <c r="F147" s="15" t="n">
-        <v>-0.1698</v>
+        <v>-0.1655</v>
       </c>
       <c r="G147" s="16" t="n">
         <v>46316</v>
@@ -12415,7 +12415,7 @@
         <v>1259</v>
       </c>
       <c r="M147" s="14" t="n">
-        <v>0.433597886610264</v>
+        <v>0.4261279323976848</v>
       </c>
       <c r="N147" s="12" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>1350</v>
       </c>
       <c r="P147" s="14" t="n">
-        <v>0.5372177497409503</v>
+        <v>0.5292078703231727</v>
       </c>
       <c r="Q147" s="19" t="inlineStr">
         <is>
@@ -12471,13 +12471,13 @@
         </is>
       </c>
       <c r="D148" s="4" t="n">
-        <v>1270.92</v>
+        <v>1269.53</v>
       </c>
       <c r="E148" s="25" t="n">
-        <v>-0.0355</v>
+        <v>-0.0365</v>
       </c>
       <c r="F148" s="25" t="n">
-        <v>-0.08900000000000001</v>
+        <v>-0.08990000000000001</v>
       </c>
       <c r="G148" s="6" t="n">
         <v>46325</v>
@@ -12546,13 +12546,13 @@
         </is>
       </c>
       <c r="D149" s="13" t="n">
-        <v>200.59</v>
+        <v>203.44</v>
       </c>
       <c r="E149" s="15" t="n">
-        <v>-0.1258</v>
+        <v>-0.1134</v>
       </c>
       <c r="F149" s="15" t="n">
-        <v>-0.1086</v>
+        <v>-0.0959</v>
       </c>
       <c r="G149" s="16" t="n">
         <v>46317</v>
@@ -12607,13 +12607,13 @@
         </is>
       </c>
       <c r="D150" s="4" t="n">
-        <v>438.42</v>
+        <v>438.53</v>
       </c>
       <c r="E150" s="25" t="n">
-        <v>-0.1306</v>
+        <v>-0.1304</v>
       </c>
       <c r="F150" s="25" t="n">
-        <v>-0.1028</v>
+        <v>-0.1026</v>
       </c>
       <c r="G150" s="6" t="n">
         <v>46322</v>
@@ -12674,13 +12674,13 @@
         </is>
       </c>
       <c r="D151" s="13" t="n">
-        <v>266.79</v>
+        <v>268.6</v>
       </c>
       <c r="E151" s="15" t="n">
-        <v>-0.0713</v>
+        <v>-0.065</v>
       </c>
       <c r="F151" s="15" t="n">
-        <v>-0.0335</v>
+        <v>-0.027</v>
       </c>
       <c r="G151" s="16" t="n">
         <v>46318</v>
@@ -12712,7 +12712,7 @@
         <v>272</v>
       </c>
       <c r="P151" s="14" t="n">
-        <v>0.0195284680835113</v>
+        <v>0.01265822784810118</v>
       </c>
       <c r="Q151" s="19" t="inlineStr">
         <is>
@@ -12765,13 +12765,13 @@
         </is>
       </c>
       <c r="D152" s="4" t="n">
-        <v>249.71</v>
+        <v>249.66</v>
       </c>
       <c r="E152" s="25" t="n">
-        <v>-0.103</v>
+        <v>-0.1032</v>
       </c>
       <c r="F152" s="25" t="n">
-        <v>-0.1145</v>
+        <v>-0.1147</v>
       </c>
       <c r="G152" s="6" t="n">
         <v>46324</v>
@@ -12836,13 +12836,13 @@
         </is>
       </c>
       <c r="D153" s="13" t="n">
-        <v>359.25</v>
+        <v>362.19</v>
       </c>
       <c r="E153" s="15" t="n">
-        <v>-0.1367</v>
+        <v>-0.1296</v>
       </c>
       <c r="F153" s="15" t="n">
-        <v>-0.3395</v>
+        <v>-0.3341</v>
       </c>
       <c r="G153" s="16" t="n">
         <v>46323</v>
@@ -12897,13 +12897,13 @@
         </is>
       </c>
       <c r="D154" s="4" t="n">
-        <v>530.61</v>
+        <v>533.46</v>
       </c>
       <c r="E154" s="25" t="n">
-        <v>-0.1063</v>
+        <v>-0.1015</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>0.0429</v>
+        <v>0.04849999999999999</v>
       </c>
       <c r="G154" s="6" t="n">
         <v>46315</v>
@@ -12964,13 +12964,13 @@
         </is>
       </c>
       <c r="D155" s="13" t="n">
-        <v>179.8</v>
+        <v>180.96</v>
       </c>
       <c r="E155" s="15" t="n">
-        <v>-0.1517</v>
+        <v>-0.1463</v>
       </c>
       <c r="F155" s="15" t="n">
-        <v>-0.2311</v>
+        <v>-0.2261</v>
       </c>
       <c r="G155" s="16" t="n">
         <v>46330</v>
@@ -12999,7 +12999,7 @@
         <v>575</v>
       </c>
       <c r="M155" s="14" t="n">
-        <v>2.197997775305895</v>
+        <v>2.177497789566755</v>
       </c>
       <c r="N155" s="12" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>237</v>
       </c>
       <c r="P155" s="14" t="n">
-        <v>0.318131256952169</v>
+        <v>0.3096816976127321</v>
       </c>
       <c r="Q155" s="19" t="inlineStr">
         <is>
@@ -13059,13 +13059,13 @@
         </is>
       </c>
       <c r="D156" s="4" t="n">
-        <v>118.46</v>
+        <v>118.3</v>
       </c>
       <c r="E156" s="25" t="n">
-        <v>-0.0007000000000000001</v>
+        <v>-0.002</v>
       </c>
       <c r="F156" s="5" t="n">
-        <v>0.0356</v>
+        <v>0.0342</v>
       </c>
       <c r="G156" s="6" t="n">
         <v>46288</v>
@@ -13094,7 +13094,7 @@
         <v>250</v>
       </c>
       <c r="M156" s="5" t="n">
-        <v>1.110417018402837</v>
+        <v>1.113271344040575</v>
       </c>
       <c r="N156" s="3" t="inlineStr"/>
       <c r="O156" s="8" t="n"/>
@@ -13138,13 +13138,13 @@
         </is>
       </c>
       <c r="D157" s="13" t="n">
-        <v>121.64</v>
+        <v>122.46</v>
       </c>
       <c r="E157" s="15" t="n">
-        <v>-0.0703</v>
+        <v>-0.064</v>
       </c>
       <c r="F157" s="15" t="n">
-        <v>-0.0361</v>
+        <v>-0.0296</v>
       </c>
       <c r="G157" s="16" t="n">
         <v>46315</v>
@@ -13173,7 +13173,7 @@
         <v>95</v>
       </c>
       <c r="M157" s="15" t="n">
-        <v>-0.2190069056231503</v>
+        <v>-0.2242364853829822</v>
       </c>
       <c r="N157" s="12" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>139</v>
       </c>
       <c r="P157" s="14" t="n">
-        <v>0.1427162117724433</v>
+        <v>0.1350645108606893</v>
       </c>
       <c r="Q157" s="19" t="inlineStr">
         <is>
@@ -13229,13 +13229,13 @@
         </is>
       </c>
       <c r="D158" s="4" t="n">
-        <v>923.0700000000001</v>
+        <v>925</v>
       </c>
       <c r="E158" s="25" t="n">
-        <v>-0.124</v>
+        <v>-0.1222</v>
       </c>
       <c r="F158" s="25" t="n">
-        <v>-0.0316</v>
+        <v>-0.0296</v>
       </c>
       <c r="G158" s="6" t="n">
         <v>46331</v>
@@ -13264,7 +13264,7 @@
         <v>125</v>
       </c>
       <c r="M158" s="25" t="n">
-        <v>-0.8645823177007161</v>
+        <v>-0.8648648648648649</v>
       </c>
       <c r="N158" s="3" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>1064</v>
       </c>
       <c r="P158" s="5" t="n">
-        <v>0.1526753117315046</v>
+        <v>0.1502702702702703</v>
       </c>
       <c r="Q158" s="9" t="inlineStr">
         <is>
@@ -13320,13 +13320,13 @@
         </is>
       </c>
       <c r="D159" s="13" t="n">
-        <v>477.55</v>
+        <v>483.71</v>
       </c>
       <c r="E159" s="15" t="n">
-        <v>-0.1436</v>
+        <v>-0.1325</v>
       </c>
       <c r="F159" s="15" t="n">
-        <v>-0.1698</v>
+        <v>-0.1591</v>
       </c>
       <c r="G159" s="16" t="n">
         <v>46325</v>
@@ -13401,13 +13401,13 @@
         </is>
       </c>
       <c r="D160" s="4" t="n">
-        <v>416.56</v>
+        <v>417</v>
       </c>
       <c r="E160" s="25" t="n">
-        <v>-0.06309999999999999</v>
+        <v>-0.0621</v>
       </c>
       <c r="F160" s="25" t="n">
-        <v>-0.09810000000000001</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="G160" s="6" t="n">
         <v>46331</v>
@@ -13462,13 +13462,13 @@
         </is>
       </c>
       <c r="D161" s="13" t="n">
-        <v>34.44</v>
+        <v>33.77</v>
       </c>
       <c r="E161" s="15" t="n">
-        <v>-0.0437</v>
+        <v>-0.0625</v>
       </c>
       <c r="F161" s="15" t="n">
-        <v>-0.2364</v>
+        <v>-0.2514</v>
       </c>
       <c r="G161" s="16" t="n">
         <v>46323</v>
@@ -13537,13 +13537,13 @@
         </is>
       </c>
       <c r="D162" s="4" t="n">
-        <v>193.97</v>
+        <v>195.5</v>
       </c>
       <c r="E162" s="25" t="n">
-        <v>-0.1248</v>
+        <v>-0.1179</v>
       </c>
       <c r="F162" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0103</v>
       </c>
       <c r="G162" s="6" t="n">
         <v>46315</v>
@@ -13616,13 +13616,13 @@
         </is>
       </c>
       <c r="D163" s="13" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="E163" s="15" t="n">
-        <v>-0.013</v>
+        <v>42.77</v>
+      </c>
+      <c r="E163" s="14" t="n">
+        <v>0.009899999999999999</v>
       </c>
       <c r="F163" s="14" t="n">
-        <v>0.0133</v>
+        <v>0.0368</v>
       </c>
       <c r="G163" s="16" t="n"/>
       <c r="H163" s="21" t="inlineStr">
@@ -13667,13 +13667,13 @@
         </is>
       </c>
       <c r="D164" s="4" t="n">
-        <v>419.5</v>
+        <v>422.73</v>
       </c>
       <c r="E164" s="25" t="n">
-        <v>-0.1174</v>
+        <v>-0.1106</v>
       </c>
       <c r="F164" s="25" t="n">
-        <v>-0.1074</v>
+        <v>-0.1005</v>
       </c>
       <c r="G164" s="6" t="n">
         <v>46324</v>
@@ -13705,7 +13705,7 @@
         <v>560</v>
       </c>
       <c r="P164" s="5" t="n">
-        <v>0.3349225268176401</v>
+        <v>0.324722636198046</v>
       </c>
       <c r="Q164" s="9" t="inlineStr">
         <is>
@@ -13758,13 +13758,13 @@
         </is>
       </c>
       <c r="D165" s="13" t="n">
-        <v>283.57</v>
+        <v>283.99</v>
       </c>
       <c r="E165" s="15" t="n">
-        <v>-0.0545</v>
+        <v>-0.05309999999999999</v>
       </c>
       <c r="F165" s="15" t="n">
-        <v>-0.0603</v>
+        <v>-0.05889999999999999</v>
       </c>
       <c r="G165" s="16" t="n">
         <v>46317</v>
@@ -13796,7 +13796,7 @@
         <v>294</v>
       </c>
       <c r="P165" s="14" t="n">
-        <v>0.03678104171809432</v>
+        <v>0.03524771999014047</v>
       </c>
       <c r="Q165" s="19" t="inlineStr">
         <is>
@@ -13841,13 +13841,13 @@
         </is>
       </c>
       <c r="D166" s="4" t="n">
-        <v>238.88</v>
+        <v>234.61</v>
       </c>
       <c r="E166" s="25" t="n">
-        <v>-0.1831</v>
+        <v>-0.1977</v>
       </c>
       <c r="F166" s="25" t="n">
-        <v>-0.175</v>
+        <v>-0.1898</v>
       </c>
       <c r="G166" s="6" t="n">
         <v>46323</v>
@@ -13879,7 +13879,7 @@
         <v>425</v>
       </c>
       <c r="P166" s="5" t="n">
-        <v>0.7791359678499665</v>
+        <v>0.8115169856357358</v>
       </c>
       <c r="Q166" s="9" t="inlineStr">
         <is>
@@ -13920,13 +13920,13 @@
         </is>
       </c>
       <c r="D167" s="13" t="n">
-        <v>217.46</v>
+        <v>217.25</v>
       </c>
       <c r="E167" s="15" t="n">
-        <v>-0.0293</v>
+        <v>-0.0302</v>
       </c>
       <c r="F167" s="15" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.0922</v>
       </c>
       <c r="G167" s="16" t="n">
         <v>46321</v>
@@ -13955,7 +13955,7 @@
         <v>268</v>
       </c>
       <c r="M167" s="14" t="n">
-        <v>0.2324105582635887</v>
+        <v>0.2336018411967779</v>
       </c>
       <c r="N167" s="12" t="inlineStr"/>
       <c r="O167" s="18" t="n"/>
@@ -14003,13 +14003,13 @@
         </is>
       </c>
       <c r="D168" s="4" t="n">
-        <v>305.8</v>
+        <v>302.66</v>
       </c>
       <c r="E168" s="25" t="n">
-        <v>-0.0194</v>
+        <v>-0.0295</v>
       </c>
       <c r="F168" s="25" t="n">
-        <v>-0.1778</v>
+        <v>-0.1862</v>
       </c>
       <c r="G168" s="6" t="n">
         <v>46330</v>
@@ -14078,13 +14078,13 @@
         </is>
       </c>
       <c r="D169" s="13" t="n">
-        <v>317.58</v>
+        <v>319.5</v>
       </c>
       <c r="E169" s="15" t="n">
-        <v>-0.1426</v>
+        <v>-0.1374</v>
       </c>
       <c r="F169" s="15" t="n">
-        <v>-0.1917</v>
+        <v>-0.1868</v>
       </c>
       <c r="G169" s="16" t="n"/>
       <c r="H169" s="21" t="inlineStr">
@@ -14147,13 +14147,13 @@
         </is>
       </c>
       <c r="D170" s="4" t="n">
-        <v>106.82</v>
+        <v>107.5</v>
       </c>
       <c r="E170" s="25" t="n">
-        <v>-0.0907</v>
+        <v>-0.0849</v>
       </c>
       <c r="F170" s="25" t="n">
-        <v>-0.13</v>
+        <v>-0.1245</v>
       </c>
       <c r="G170" s="6" t="n">
         <v>46322</v>
@@ -14226,13 +14226,13 @@
         </is>
       </c>
       <c r="D171" s="13" t="n">
-        <v>96.34999999999999</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="E171" s="15" t="n">
-        <v>-0.3779</v>
+        <v>-0.3848</v>
       </c>
       <c r="F171" s="15" t="n">
-        <v>-0.0592</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="G171" s="16" t="n">
         <v>46331</v>
@@ -14287,13 +14287,13 @@
         </is>
       </c>
       <c r="D172" s="4" t="n">
-        <v>329.38</v>
+        <v>331.34</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>0.07780000000000001</v>
+        <v>0.0843</v>
       </c>
       <c r="F172" s="25" t="n">
-        <v>-0.0131</v>
+        <v>-0.0072</v>
       </c>
       <c r="G172" s="6" t="n">
         <v>46324</v>
@@ -14322,7 +14322,7 @@
         <v>310</v>
       </c>
       <c r="M172" s="25" t="n">
-        <v>-0.05883781650373428</v>
+        <v>-0.06440514275366686</v>
       </c>
       <c r="N172" s="3" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>365</v>
       </c>
       <c r="P172" s="5" t="n">
-        <v>0.1081425708907645</v>
+        <v>0.1015874932093923</v>
       </c>
       <c r="Q172" s="9" t="inlineStr">
         <is>
@@ -14390,13 +14390,13 @@
         </is>
       </c>
       <c r="D173" s="13" t="n">
-        <v>103.53</v>
+        <v>105.04</v>
       </c>
       <c r="E173" s="15" t="n">
-        <v>-0.2816</v>
+        <v>-0.2711</v>
       </c>
       <c r="F173" s="15" t="n">
-        <v>-0.2411</v>
+        <v>-0.23</v>
       </c>
       <c r="G173" s="16" t="n">
         <v>46329</v>
@@ -14451,13 +14451,13 @@
         </is>
       </c>
       <c r="D174" s="4" t="n">
-        <v>195.59</v>
+        <v>193.4</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>0.1507</v>
+        <v>0.1378</v>
       </c>
       <c r="F174" s="5" t="n">
-        <v>0.3623</v>
+        <v>0.3471</v>
       </c>
       <c r="G174" s="6" t="n">
         <v>46296</v>
@@ -14512,13 +14512,13 @@
         </is>
       </c>
       <c r="D175" s="13" t="n">
-        <v>260.46</v>
+        <v>257.76</v>
       </c>
       <c r="E175" s="14" t="n">
-        <v>0.0253</v>
+        <v>0.0146</v>
       </c>
       <c r="F175" s="14" t="n">
-        <v>0.09789999999999999</v>
+        <v>0.0864</v>
       </c>
       <c r="G175" s="16" t="n"/>
       <c r="H175" s="21" t="inlineStr">
@@ -14563,13 +14563,13 @@
         </is>
       </c>
       <c r="D176" s="4" t="n">
-        <v>362.17</v>
+        <v>361.35</v>
       </c>
       <c r="E176" s="25" t="n">
-        <v>-0.07200000000000001</v>
+        <v>-0.0741</v>
       </c>
       <c r="F176" s="25" t="n">
-        <v>-0.0351</v>
+        <v>-0.0373</v>
       </c>
       <c r="G176" s="6" t="n"/>
       <c r="H176" s="7" t="inlineStr">
@@ -14588,7 +14588,7 @@
         <v>515</v>
       </c>
       <c r="M176" s="5" t="n">
-        <v>0.4219841510892674</v>
+        <v>0.4252110142521101</v>
       </c>
       <c r="N176" s="3" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>474</v>
       </c>
       <c r="P176" s="5" t="n">
-        <v>0.308777645856918</v>
+        <v>0.3117476131174761</v>
       </c>
       <c r="Q176" s="9" t="inlineStr">
         <is>
@@ -14648,13 +14648,13 @@
         </is>
       </c>
       <c r="D177" s="13" t="n">
-        <v>229.25</v>
+        <v>226.5</v>
       </c>
       <c r="E177" s="15" t="n">
-        <v>-0.0513</v>
+        <v>-0.06269999999999999</v>
       </c>
       <c r="F177" s="14" t="n">
-        <v>0.0499</v>
+        <v>0.0373</v>
       </c>
       <c r="G177" s="16" t="n"/>
       <c r="H177" s="21" t="inlineStr">
@@ -14699,13 +14699,13 @@
         </is>
       </c>
       <c r="D178" s="4" t="n">
-        <v>250.41</v>
+        <v>250.57</v>
       </c>
       <c r="E178" s="25" t="n">
-        <v>-0.2817</v>
+        <v>-0.2813</v>
       </c>
       <c r="F178" s="25" t="n">
-        <v>-0.1184</v>
+        <v>-0.1179</v>
       </c>
       <c r="G178" s="6" t="n">
         <v>46329</v>
@@ -14760,13 +14760,13 @@
         </is>
       </c>
       <c r="D179" s="13" t="n">
-        <v>259.12</v>
+        <v>252.54</v>
       </c>
       <c r="E179" s="15" t="n">
-        <v>-0.1907</v>
+        <v>-0.2112</v>
       </c>
       <c r="F179" s="15" t="n">
-        <v>-0.1466</v>
+        <v>-0.1682</v>
       </c>
       <c r="G179" s="16" t="n">
         <v>46329</v>
@@ -14821,13 +14821,13 @@
         </is>
       </c>
       <c r="D180" s="4" t="n">
-        <v>33.16</v>
+        <v>33.26</v>
       </c>
       <c r="E180" s="25" t="n">
-        <v>-0.2506</v>
+        <v>-0.2484</v>
       </c>
       <c r="F180" s="25" t="n">
-        <v>-0.2866</v>
+        <v>-0.2844</v>
       </c>
       <c r="G180" s="6" t="n">
         <v>46324</v>
@@ -14882,13 +14882,13 @@
         </is>
       </c>
       <c r="D181" s="13" t="n">
-        <v>419.3</v>
+        <v>421.17</v>
       </c>
       <c r="E181" s="15" t="n">
-        <v>-0.2167</v>
+        <v>-0.2132</v>
       </c>
       <c r="F181" s="15" t="n">
-        <v>-0.2084</v>
+        <v>-0.2048</v>
       </c>
       <c r="G181" s="16" t="n"/>
       <c r="H181" s="21" t="inlineStr">
@@ -14907,7 +14907,7 @@
         <v>740</v>
       </c>
       <c r="M181" s="14" t="n">
-        <v>0.7648461721917481</v>
+        <v>0.7570102333974404</v>
       </c>
       <c r="N181" s="12" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>700</v>
       </c>
       <c r="P181" s="14" t="n">
-        <v>0.669449081803005</v>
+        <v>0.662036707267849</v>
       </c>
       <c r="Q181" s="19" t="inlineStr">
         <is>
@@ -14959,13 +14959,13 @@
         </is>
       </c>
       <c r="D182" s="4" t="n">
-        <v>59.92</v>
+        <v>60.85</v>
       </c>
       <c r="E182" s="25" t="n">
-        <v>-0.117</v>
+        <v>-0.1033</v>
       </c>
       <c r="F182" s="25" t="n">
-        <v>-0.1727</v>
+        <v>-0.1599</v>
       </c>
       <c r="G182" s="6" t="n">
         <v>46331</v>
@@ -15024,13 +15024,13 @@
         </is>
       </c>
       <c r="D183" s="13" t="n">
-        <v>503.34</v>
+        <v>504.2</v>
       </c>
       <c r="E183" s="15" t="n">
-        <v>-0.0053</v>
+        <v>-0.0036</v>
       </c>
       <c r="F183" s="14" t="n">
-        <v>0.0153</v>
+        <v>0.017</v>
       </c>
       <c r="G183" s="16" t="n">
         <v>46329</v>
@@ -15059,7 +15059,7 @@
         <v>615</v>
       </c>
       <c r="M183" s="14" t="n">
-        <v>0.2218381213493862</v>
+        <v>0.2197540658468862</v>
       </c>
       <c r="N183" s="12" t="inlineStr">
         <is>
@@ -15070,7 +15070,7 @@
         <v>579</v>
       </c>
       <c r="P183" s="14" t="n">
-        <v>0.1503158898557636</v>
+        <v>0.1483538278460929</v>
       </c>
       <c r="Q183" s="19" t="inlineStr">
         <is>
@@ -15111,13 +15111,13 @@
         </is>
       </c>
       <c r="D184" s="4" t="n">
-        <v>46.14</v>
+        <v>46.38</v>
       </c>
       <c r="E184" s="25" t="n">
-        <v>-0.2473</v>
+        <v>-0.2434</v>
       </c>
       <c r="F184" s="25" t="n">
-        <v>-0.2669</v>
+        <v>-0.2631</v>
       </c>
       <c r="G184" s="6" t="n">
         <v>46321</v>
@@ -15172,13 +15172,13 @@
         </is>
       </c>
       <c r="D185" s="13" t="n">
-        <v>193.16</v>
+        <v>192.84</v>
       </c>
       <c r="E185" s="15" t="n">
-        <v>-0.0428</v>
+        <v>-0.0444</v>
       </c>
       <c r="F185" s="14" t="n">
-        <v>0.1456</v>
+        <v>0.1437</v>
       </c>
       <c r="G185" s="16" t="n">
         <v>46329</v>
@@ -15207,7 +15207,7 @@
         <v>200</v>
       </c>
       <c r="M185" s="14" t="n">
-        <v>0.03541105819010149</v>
+        <v>0.03712922630159716</v>
       </c>
       <c r="N185" s="12" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>200</v>
       </c>
       <c r="P185" s="14" t="n">
-        <v>0.03541105819010149</v>
+        <v>0.03712922630159716</v>
       </c>
       <c r="Q185" s="19" t="inlineStr">
         <is>
@@ -15263,13 +15263,13 @@
         </is>
       </c>
       <c r="D186" s="4" t="n">
-        <v>77.29000000000001</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="E186" s="25" t="n">
-        <v>-0.0953</v>
+        <v>-0.0911</v>
       </c>
       <c r="F186" s="5" t="n">
-        <v>0.0224</v>
+        <v>0.0271</v>
       </c>
       <c r="G186" s="6" t="n">
         <v>46323</v>
@@ -15301,7 +15301,7 @@
         <v>180</v>
       </c>
       <c r="P186" s="5" t="n">
-        <v>1.328891189028335</v>
+        <v>1.31809401159047</v>
       </c>
       <c r="Q186" s="9" t="inlineStr">
         <is>
@@ -15354,13 +15354,13 @@
         </is>
       </c>
       <c r="D187" s="13" t="n">
-        <v>23.83</v>
+        <v>23.42</v>
       </c>
       <c r="E187" s="15" t="n">
-        <v>-0.2356</v>
+        <v>-0.2489</v>
       </c>
       <c r="F187" s="15" t="n">
-        <v>-0.07580000000000001</v>
+        <v>-0.0919</v>
       </c>
       <c r="G187" s="16" t="n">
         <v>46303</v>
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="D188" s="4" t="n">
-        <v>246.68</v>
+        <v>241.83</v>
       </c>
       <c r="E188" s="25" t="n">
-        <v>-0.09119999999999999</v>
+        <v>-0.1091</v>
       </c>
       <c r="F188" s="25" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.0949</v>
       </c>
       <c r="G188" s="6" t="n">
         <v>46330</v>
@@ -15476,13 +15476,13 @@
         </is>
       </c>
       <c r="D189" s="13" t="n">
-        <v>1582.66</v>
+        <v>1591.48</v>
       </c>
       <c r="E189" s="15" t="n">
-        <v>-0.1596</v>
+        <v>-0.1549</v>
       </c>
       <c r="F189" s="15" t="n">
-        <v>-0.0944</v>
+        <v>-0.08929999999999999</v>
       </c>
       <c r="G189" s="16" t="n">
         <v>46309</v>
@@ -15555,13 +15555,13 @@
         </is>
       </c>
       <c r="D190" s="4" t="n">
-        <v>37.31</v>
+        <v>37.12</v>
       </c>
       <c r="E190" s="25" t="n">
-        <v>-0.065</v>
+        <v>-0.0699</v>
       </c>
       <c r="F190" s="25" t="n">
-        <v>-0.0285</v>
+        <v>-0.0336</v>
       </c>
       <c r="G190" s="6" t="n">
         <v>46324</v>
@@ -15616,13 +15616,13 @@
         </is>
       </c>
       <c r="D191" s="13" t="n">
-        <v>341.7</v>
+        <v>339.27</v>
       </c>
       <c r="E191" s="15" t="n">
-        <v>-0.1293</v>
+        <v>-0.1355</v>
       </c>
       <c r="F191" s="15" t="n">
-        <v>-0.0786</v>
+        <v>-0.0851</v>
       </c>
       <c r="G191" s="16" t="n"/>
       <c r="H191" s="21" t="inlineStr">
@@ -15641,7 +15641,7 @@
         <v>545</v>
       </c>
       <c r="M191" s="14" t="n">
-        <v>0.5949663447468541</v>
+        <v>0.6063901907035695</v>
       </c>
       <c r="N191" s="12" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>582</v>
       </c>
       <c r="P191" s="14" t="n">
-        <v>0.7032484635645303</v>
+        <v>0.715447873375188</v>
       </c>
       <c r="Q191" s="19" t="inlineStr">
         <is>
@@ -15705,13 +15705,13 @@
         </is>
       </c>
       <c r="D192" s="4" t="n">
-        <v>131.98</v>
+        <v>134.66</v>
       </c>
       <c r="E192" s="25" t="n">
-        <v>-0.2318</v>
+        <v>-0.2162</v>
       </c>
       <c r="F192" s="25" t="n">
-        <v>-0.09699999999999999</v>
+        <v>-0.0786</v>
       </c>
       <c r="G192" s="6" t="n">
         <v>46335</v>
@@ -15766,13 +15766,13 @@
         </is>
       </c>
       <c r="D193" s="13" t="n">
-        <v>274.06</v>
+        <v>273.96</v>
       </c>
       <c r="E193" s="15" t="n">
-        <v>-0.1527</v>
+        <v>-0.1531</v>
       </c>
       <c r="F193" s="15" t="n">
-        <v>-0.1698</v>
+        <v>-0.1701</v>
       </c>
       <c r="G193" s="16" t="n">
         <v>46321</v>
@@ -15801,7 +15801,7 @@
         <v>425</v>
       </c>
       <c r="M193" s="14" t="n">
-        <v>0.550755309056411</v>
+        <v>0.5513213607825961</v>
       </c>
       <c r="N193" s="12" t="inlineStr"/>
       <c r="O193" s="18" t="n"/>
@@ -15845,13 +15845,13 @@
         </is>
       </c>
       <c r="D194" s="4" t="n">
-        <v>136.45</v>
+        <v>137.79</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>0.07429999999999999</v>
-      </c>
-      <c r="F194" s="25" t="n">
-        <v>-0.0048</v>
+        <v>0.0849</v>
+      </c>
+      <c r="F194" s="5" t="n">
+        <v>0.005</v>
       </c>
       <c r="G194" s="6" t="n">
         <v>46322</v>
@@ -15906,13 +15906,13 @@
         </is>
       </c>
       <c r="D195" s="13" t="n">
-        <v>329.33</v>
+        <v>334.33</v>
       </c>
       <c r="E195" s="15" t="n">
-        <v>-0.2602</v>
+        <v>-0.249</v>
       </c>
       <c r="F195" s="15" t="n">
-        <v>-0.1204</v>
+        <v>-0.107</v>
       </c>
       <c r="G195" s="16" t="n"/>
       <c r="H195" s="21" t="inlineStr">
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="D196" s="4" t="n">
-        <v>11.37</v>
+        <v>11.25</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>0.0891</v>
+        <v>0.0776</v>
       </c>
       <c r="F196" s="25" t="n">
-        <v>-0.2636</v>
+        <v>-0.2714</v>
       </c>
       <c r="G196" s="6" t="n"/>
       <c r="H196" s="7" t="inlineStr">
@@ -16008,13 +16008,13 @@
         </is>
       </c>
       <c r="D197" s="13" t="n">
-        <v>319.14</v>
+        <v>316.81</v>
       </c>
       <c r="E197" s="15" t="n">
-        <v>-0.0624</v>
+        <v>-0.0693</v>
       </c>
       <c r="F197" s="14" t="n">
-        <v>0.0591</v>
+        <v>0.0513</v>
       </c>
       <c r="G197" s="16" t="n">
         <v>46321</v>
@@ -16069,13 +16069,13 @@
         </is>
       </c>
       <c r="D198" s="4" t="n">
-        <v>273.78</v>
+        <v>271.17</v>
       </c>
       <c r="E198" s="25" t="n">
-        <v>-0.2205</v>
+        <v>-0.2279</v>
       </c>
       <c r="F198" s="25" t="n">
-        <v>-0.0138</v>
+        <v>-0.0232</v>
       </c>
       <c r="G198" s="6" t="n">
         <v>46330</v>
@@ -16130,13 +16130,13 @@
         </is>
       </c>
       <c r="D199" s="13" t="n">
-        <v>49.29</v>
+        <v>49.97</v>
       </c>
       <c r="E199" s="15" t="n">
-        <v>-0.2129</v>
+        <v>-0.202</v>
       </c>
       <c r="F199" s="15" t="n">
-        <v>-0.0371</v>
+        <v>-0.0238</v>
       </c>
       <c r="G199" s="16" t="n">
         <v>46330</v>
@@ -16191,13 +16191,13 @@
         </is>
       </c>
       <c r="D200" s="4" t="n">
-        <v>16.36</v>
+        <v>16.04</v>
       </c>
       <c r="E200" s="25" t="n">
-        <v>-0.187</v>
+        <v>-0.2032</v>
       </c>
       <c r="F200" s="25" t="n">
-        <v>-0.2185</v>
+        <v>-0.234</v>
       </c>
       <c r="G200" s="6" t="n">
         <v>46318</v>
@@ -16252,13 +16252,13 @@
         </is>
       </c>
       <c r="D201" s="13" t="n">
-        <v>150.68</v>
+        <v>150.39</v>
       </c>
       <c r="E201" s="15" t="n">
-        <v>-0.4672</v>
+        <v>-0.4682</v>
       </c>
       <c r="F201" s="15" t="n">
-        <v>-0.2566</v>
+        <v>-0.258</v>
       </c>
       <c r="G201" s="16" t="n"/>
       <c r="H201" s="21" t="inlineStr">
@@ -16303,13 +16303,13 @@
         </is>
       </c>
       <c r="D202" s="4" t="n">
-        <v>258.86</v>
+        <v>255.65</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>0.3555</v>
+        <v>0.3387</v>
       </c>
       <c r="F202" s="5" t="n">
-        <v>0.5159</v>
+        <v>0.4970000000000001</v>
       </c>
       <c r="G202" s="6" t="n"/>
       <c r="H202" s="7" t="inlineStr">
@@ -16328,7 +16328,7 @@
         <v>200</v>
       </c>
       <c r="M202" s="25" t="n">
-        <v>-0.2273815962296222</v>
+        <v>-0.2176804224525719</v>
       </c>
       <c r="N202" s="3" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>250</v>
       </c>
       <c r="P202" s="25" t="n">
-        <v>-0.03422699528702779</v>
+        <v>-0.02210052806571487</v>
       </c>
       <c r="Q202" s="9" t="inlineStr">
         <is>
@@ -16384,13 +16384,13 @@
         </is>
       </c>
       <c r="D203" s="13" t="n">
-        <v>238.22</v>
+        <v>242.49</v>
       </c>
       <c r="E203" s="14" t="n">
-        <v>0.1137</v>
+        <v>0.1337</v>
       </c>
       <c r="F203" s="14" t="n">
-        <v>0.173</v>
+        <v>0.1941</v>
       </c>
       <c r="G203" s="16" t="n"/>
       <c r="H203" s="21" t="inlineStr">
@@ -16409,7 +16409,7 @@
         <v>181.25</v>
       </c>
       <c r="M203" s="15" t="n">
-        <v>-0.2391486860884896</v>
+        <v>-0.2525464967627531</v>
       </c>
       <c r="N203" s="12" t="inlineStr">
         <is>
@@ -16420,7 +16420,7 @@
         <v>177.5</v>
       </c>
       <c r="P203" s="15" t="n">
-        <v>-0.2548904374107968</v>
+        <v>-0.2680110520021444</v>
       </c>
       <c r="Q203" s="19" t="inlineStr">
         <is>
@@ -16461,13 +16461,13 @@
         </is>
       </c>
       <c r="D204" s="4" t="n">
-        <v>82.06999999999999</v>
+        <v>80.92</v>
       </c>
       <c r="E204" s="25" t="n">
-        <v>-0.2258</v>
+        <v>-0.2366</v>
       </c>
       <c r="F204" s="5" t="n">
-        <v>0.121</v>
+        <v>0.1053</v>
       </c>
       <c r="G204" s="6" t="n">
         <v>46335</v>
@@ -16522,13 +16522,13 @@
         </is>
       </c>
       <c r="D205" s="13" t="n">
-        <v>110.7</v>
+        <v>110.07</v>
       </c>
       <c r="E205" s="15" t="n">
-        <v>-0.0195</v>
+        <v>-0.0251</v>
       </c>
       <c r="F205" s="15" t="n">
-        <v>-0.0111</v>
+        <v>-0.0167</v>
       </c>
       <c r="G205" s="16" t="n"/>
       <c r="H205" s="21" t="inlineStr">
@@ -16547,7 +16547,7 @@
         <v>130</v>
       </c>
       <c r="M205" s="14" t="n">
-        <v>0.1743450767841011</v>
+        <v>0.1810665939856456</v>
       </c>
       <c r="N205" s="12" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>150</v>
       </c>
       <c r="P205" s="14" t="n">
-        <v>0.3550135501355013</v>
+        <v>0.3627691469065141</v>
       </c>
       <c r="Q205" s="19" t="inlineStr">
         <is>
@@ -16615,13 +16615,13 @@
         </is>
       </c>
       <c r="D206" s="4" t="n">
-        <v>230.1</v>
+        <v>230.27</v>
       </c>
       <c r="E206" s="25" t="n">
-        <v>-0.0696</v>
+        <v>-0.0689</v>
       </c>
       <c r="F206" s="25" t="n">
-        <v>-0.1105</v>
+        <v>-0.1099</v>
       </c>
       <c r="G206" s="6" t="n">
         <v>46331</v>
@@ -16676,13 +16676,13 @@
         </is>
       </c>
       <c r="D207" s="13" t="n">
-        <v>554.91</v>
+        <v>543.51</v>
       </c>
       <c r="E207" s="14" t="n">
-        <v>0.1565</v>
+        <v>0.1328</v>
       </c>
       <c r="F207" s="14" t="n">
-        <v>0.4001</v>
+        <v>0.3713</v>
       </c>
       <c r="G207" s="16" t="n"/>
       <c r="H207" s="21" t="inlineStr">
@@ -16727,13 +16727,13 @@
         </is>
       </c>
       <c r="D208" s="4" t="n">
-        <v>71.34999999999999</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>0.1927</v>
+        <v>0.2011</v>
       </c>
       <c r="F208" s="5" t="n">
-        <v>0.3529</v>
+        <v>0.3623</v>
       </c>
       <c r="G208" s="6" t="n"/>
       <c r="H208" s="7" t="inlineStr">
@@ -16778,13 +16778,13 @@
         </is>
       </c>
       <c r="D209" s="13" t="n">
-        <v>54.29</v>
+        <v>55.17</v>
       </c>
       <c r="E209" s="14" t="n">
-        <v>0.1404</v>
+        <v>0.1588</v>
       </c>
       <c r="F209" s="14" t="n">
-        <v>0.2226</v>
+        <v>0.2423</v>
       </c>
       <c r="G209" s="16" t="n">
         <v>46330</v>
@@ -16839,13 +16839,13 @@
         </is>
       </c>
       <c r="D210" s="4" t="n">
-        <v>379.98</v>
+        <v>374.91</v>
       </c>
       <c r="E210" s="25" t="n">
-        <v>-0.3652</v>
+        <v>-0.3737</v>
       </c>
       <c r="F210" s="25" t="n">
-        <v>-0.2057</v>
+        <v>-0.2163</v>
       </c>
       <c r="G210" s="6" t="n">
         <v>46328</v>
@@ -16900,13 +16900,13 @@
         </is>
       </c>
       <c r="D211" s="13" t="n">
-        <v>101.98</v>
+        <v>101.69</v>
       </c>
       <c r="E211" s="15" t="n">
-        <v>-0.2619</v>
+        <v>-0.264</v>
       </c>
       <c r="F211" s="15" t="n">
-        <v>-0.034</v>
+        <v>-0.0368</v>
       </c>
       <c r="G211" s="16" t="n">
         <v>46330</v>
@@ -16961,13 +16961,13 @@
         </is>
       </c>
       <c r="D212" s="4" t="n">
-        <v>169.9</v>
+        <v>172.37</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>0.0902</v>
+        <v>0.106</v>
       </c>
       <c r="F212" s="5" t="n">
-        <v>0.0513</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="G212" s="6" t="n">
         <v>46330</v>
@@ -17022,13 +17022,13 @@
         </is>
       </c>
       <c r="D213" s="13" t="n">
-        <v>42.71</v>
+        <v>42.75</v>
       </c>
       <c r="E213" s="15" t="n">
-        <v>-0.2008</v>
+        <v>-0.2</v>
       </c>
       <c r="F213" s="15" t="n">
-        <v>-0.257</v>
+        <v>-0.2563</v>
       </c>
       <c r="G213" s="16" t="n"/>
       <c r="H213" s="21" t="inlineStr">
@@ -17073,13 +17073,13 @@
         </is>
       </c>
       <c r="D214" s="4" t="n">
-        <v>143.69</v>
+        <v>143.57</v>
       </c>
       <c r="E214" s="25" t="n">
-        <v>-0.1704</v>
+        <v>-0.1711</v>
       </c>
       <c r="F214" s="25" t="n">
-        <v>-0.0706</v>
+        <v>-0.07139999999999999</v>
       </c>
       <c r="G214" s="6" t="n">
         <v>46322</v>
@@ -17134,13 +17134,13 @@
         </is>
       </c>
       <c r="D215" s="13" t="n">
-        <v>49.18</v>
+        <v>49.1</v>
       </c>
       <c r="E215" s="14" t="n">
-        <v>0.2137</v>
+        <v>0.2117</v>
       </c>
       <c r="F215" s="14" t="n">
-        <v>0.5031</v>
+        <v>0.5006</v>
       </c>
       <c r="G215" s="16" t="n"/>
       <c r="H215" s="21" t="inlineStr">
@@ -17185,13 +17185,13 @@
         </is>
       </c>
       <c r="D216" s="4" t="n">
-        <v>148.61</v>
+        <v>148.88</v>
       </c>
       <c r="E216" s="25" t="n">
-        <v>-0.1359</v>
+        <v>-0.1344</v>
       </c>
       <c r="F216" s="25" t="n">
-        <v>-0.009399999999999999</v>
+        <v>-0.0076</v>
       </c>
       <c r="G216" s="6" t="n"/>
       <c r="H216" s="7" t="inlineStr">
@@ -17210,7 +17210,7 @@
         <v>190</v>
       </c>
       <c r="M216" s="5" t="n">
-        <v>0.2785142318821074</v>
+        <v>0.2761955937667921</v>
       </c>
       <c r="N216" s="3" t="inlineStr"/>
       <c r="O216" s="8" t="n"/>
@@ -17254,13 +17254,13 @@
         </is>
       </c>
       <c r="D217" s="13" t="n">
-        <v>57.45</v>
+        <v>55.88</v>
       </c>
       <c r="E217" s="15" t="n">
-        <v>-0.0028</v>
+        <v>-0.03</v>
       </c>
       <c r="F217" s="14" t="n">
-        <v>0.2538</v>
+        <v>0.2196</v>
       </c>
       <c r="G217" s="16" t="n"/>
       <c r="H217" s="21" t="inlineStr">
@@ -17279,7 +17279,7 @@
         <v>67</v>
       </c>
       <c r="M217" s="14" t="n">
-        <v>0.1662315056570931</v>
+        <v>0.1989978525411596</v>
       </c>
       <c r="N217" s="12" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>70</v>
       </c>
       <c r="P217" s="14" t="n">
-        <v>0.2184508268059181</v>
+        <v>0.2526843235504652</v>
       </c>
       <c r="Q217" s="19" t="inlineStr">
         <is>
@@ -17331,13 +17331,13 @@
         </is>
       </c>
       <c r="D218" s="4" t="n">
-        <v>246.63</v>
+        <v>241.96</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>0.1462</v>
+        <v>0.1245</v>
       </c>
       <c r="F218" s="5" t="n">
-        <v>0.0998</v>
+        <v>0.0789</v>
       </c>
       <c r="G218" s="6" t="n">
         <v>46330</v>
@@ -17392,13 +17392,13 @@
         </is>
       </c>
       <c r="D219" s="13" t="n">
-        <v>249</v>
+        <v>248.37</v>
       </c>
       <c r="E219" s="14" t="n">
-        <v>0.08800000000000001</v>
+        <v>0.08529999999999999</v>
       </c>
       <c r="F219" s="14" t="n">
-        <v>0.1708</v>
+        <v>0.1679</v>
       </c>
       <c r="G219" s="16" t="n">
         <v>46316</v>
@@ -17434,7 +17434,7 @@
         <v>250</v>
       </c>
       <c r="P219" s="14" t="n">
-        <v>0.004016064257028112</v>
+        <v>0.00656278938680193</v>
       </c>
       <c r="Q219" s="19" t="inlineStr">
         <is>
@@ -17471,13 +17471,13 @@
         </is>
       </c>
       <c r="D220" s="4" t="n">
-        <v>12.36</v>
+        <v>12.67</v>
       </c>
       <c r="E220" s="25" t="n">
-        <v>-0.0779</v>
+        <v>-0.0552</v>
       </c>
       <c r="F220" s="5" t="n">
-        <v>0.3603</v>
+        <v>0.3938</v>
       </c>
       <c r="G220" s="6" t="n"/>
       <c r="H220" s="7" t="inlineStr">
@@ -17522,13 +17522,13 @@
         </is>
       </c>
       <c r="D221" s="13" t="n">
-        <v>98.29000000000001</v>
+        <v>97.14</v>
       </c>
       <c r="E221" s="15" t="n">
-        <v>-0.05019999999999999</v>
+        <v>-0.0614</v>
       </c>
       <c r="F221" s="14" t="n">
-        <v>0.0342</v>
+        <v>0.0221</v>
       </c>
       <c r="G221" s="16" t="n">
         <v>46317</v>
@@ -17583,13 +17583,13 @@
         </is>
       </c>
       <c r="D222" s="4" t="n">
-        <v>331.88</v>
+        <v>329.27</v>
       </c>
       <c r="E222" s="25" t="n">
-        <v>-0.0111</v>
+        <v>-0.0189</v>
       </c>
       <c r="F222" s="5" t="n">
-        <v>0.1401</v>
+        <v>0.1312</v>
       </c>
       <c r="G222" s="6" t="n"/>
       <c r="H222" s="7" t="inlineStr">
@@ -17634,13 +17634,13 @@
         </is>
       </c>
       <c r="D223" s="13" t="n">
-        <v>37.03</v>
+        <v>37.05</v>
       </c>
       <c r="E223" s="15" t="n">
-        <v>-0.2094</v>
+        <v>-0.209</v>
       </c>
       <c r="F223" s="14" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0653</v>
       </c>
       <c r="G223" s="16" t="n">
         <v>46330</v>
@@ -17695,13 +17695,13 @@
         </is>
       </c>
       <c r="D224" s="4" t="n">
-        <v>41.36</v>
+        <v>41.58</v>
       </c>
       <c r="E224" s="25" t="n">
-        <v>-0.0789</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="F224" s="5" t="n">
-        <v>0.2301</v>
+        <v>0.2368</v>
       </c>
       <c r="G224" s="6" t="n">
         <v>46331</v>
@@ -17756,13 +17756,13 @@
         </is>
       </c>
       <c r="D225" s="13" t="n">
-        <v>295.6</v>
+        <v>296.05</v>
       </c>
       <c r="E225" s="15" t="n">
-        <v>-0.2008</v>
+        <v>-0.1996</v>
       </c>
       <c r="F225" s="15" t="n">
-        <v>-0.018</v>
+        <v>-0.0165</v>
       </c>
       <c r="G225" s="16" t="n">
         <v>46289</v>
@@ -17821,13 +17821,13 @@
         </is>
       </c>
       <c r="D226" s="4" t="n">
-        <v>313.8</v>
+        <v>313.36</v>
       </c>
       <c r="E226" s="25" t="n">
-        <v>-0.1311</v>
+        <v>-0.1323</v>
       </c>
       <c r="F226" s="25" t="n">
-        <v>-0.0066</v>
+        <v>-0.008</v>
       </c>
       <c r="G226" s="6" t="n"/>
       <c r="H226" s="7" t="inlineStr">
@@ -17846,7 +17846,7 @@
         <v>390</v>
       </c>
       <c r="M226" s="5" t="n">
-        <v>0.2428298279158699</v>
+        <v>0.244574929793209</v>
       </c>
       <c r="N226" s="3" t="inlineStr"/>
       <c r="O226" s="8" t="n"/>
@@ -17902,13 +17902,13 @@
         </is>
       </c>
       <c r="D227" s="13" t="n">
-        <v>166.63</v>
+        <v>168.02</v>
       </c>
       <c r="E227" s="15" t="n">
-        <v>-0.1902</v>
+        <v>-0.1834</v>
       </c>
       <c r="F227" s="15" t="n">
-        <v>-0.2168</v>
+        <v>-0.2102</v>
       </c>
       <c r="G227" s="16" t="n">
         <v>46330</v>
@@ -17937,7 +17937,7 @@
         <v>305</v>
       </c>
       <c r="M227" s="14" t="n">
-        <v>0.8304026885914901</v>
+        <v>0.8152600880847517</v>
       </c>
       <c r="N227" s="12" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>185</v>
       </c>
       <c r="P227" s="14" t="n">
-        <v>0.1102442537358219</v>
+        <v>0.101059397690751</v>
       </c>
       <c r="Q227" s="19" t="inlineStr">
         <is>
@@ -17989,13 +17989,13 @@
         </is>
       </c>
       <c r="D228" s="4" t="n">
-        <v>78.78</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="E228" s="25" t="n">
-        <v>-0.2259</v>
+        <v>-0.2258</v>
       </c>
       <c r="F228" s="25" t="n">
-        <v>-0.1897</v>
+        <v>-0.1896</v>
       </c>
       <c r="G228" s="6" t="n"/>
       <c r="H228" s="7" t="inlineStr">
@@ -18040,13 +18040,13 @@
         </is>
       </c>
       <c r="D229" s="13" t="n">
-        <v>840.51</v>
+        <v>838.96</v>
       </c>
       <c r="E229" s="15" t="n">
-        <v>-0.1325</v>
+        <v>-0.1341</v>
       </c>
       <c r="F229" s="14" t="n">
-        <v>0.147</v>
+        <v>0.1448</v>
       </c>
       <c r="G229" s="16" t="n">
         <v>46329</v>
@@ -18101,13 +18101,13 @@
         </is>
       </c>
       <c r="D230" s="4" t="n">
-        <v>101.07</v>
-      </c>
-      <c r="E230" s="25" t="n">
-        <v>-0.0005</v>
+        <v>101.14</v>
+      </c>
+      <c r="E230" s="5" t="n">
+        <v>0.0002</v>
       </c>
       <c r="F230" s="25" t="n">
-        <v>-0.0172</v>
+        <v>-0.0164</v>
       </c>
       <c r="G230" s="6" t="n">
         <v>46322</v>
@@ -18162,13 +18162,13 @@
         </is>
       </c>
       <c r="D231" s="13" t="n">
-        <v>267</v>
+        <v>270.87</v>
       </c>
       <c r="E231" s="15" t="n">
-        <v>-0.2235</v>
+        <v>-0.2122</v>
       </c>
       <c r="F231" s="15" t="n">
-        <v>-0.1478</v>
+        <v>-0.1354</v>
       </c>
       <c r="G231" s="16" t="n">
         <v>46323</v>
@@ -18197,7 +18197,7 @@
         <v>450</v>
       </c>
       <c r="M231" s="14" t="n">
-        <v>0.6853932584269663</v>
+        <v>0.6613135452431055</v>
       </c>
       <c r="N231" s="12" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>355</v>
       </c>
       <c r="P231" s="14" t="n">
-        <v>0.3295880149812734</v>
+        <v>0.3105917968028943</v>
       </c>
       <c r="Q231" s="19" t="inlineStr">
         <is>
@@ -18253,13 +18253,13 @@
         </is>
       </c>
       <c r="D232" s="4" t="n">
-        <v>71.02</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="E232" s="25" t="n">
-        <v>-0.1151</v>
+        <v>-0.1093</v>
       </c>
       <c r="F232" s="25" t="n">
-        <v>-0.1228</v>
+        <v>-0.117</v>
       </c>
       <c r="G232" s="6" t="n">
         <v>46331</v>
@@ -18314,13 +18314,13 @@
         </is>
       </c>
       <c r="D233" s="13" t="n">
-        <v>381.27</v>
+        <v>377.67</v>
       </c>
       <c r="E233" s="15" t="n">
-        <v>-0.1309</v>
+        <v>-0.1391</v>
       </c>
       <c r="F233" s="14" t="n">
-        <v>0.2207</v>
+        <v>0.2092</v>
       </c>
       <c r="G233" s="16" t="n"/>
       <c r="H233" s="21" t="inlineStr">
@@ -18426,13 +18426,13 @@
         </is>
       </c>
       <c r="D235" s="13" t="n">
-        <v>1151.56</v>
+        <v>1142.46</v>
       </c>
       <c r="E235" s="15" t="n">
-        <v>-0.1867</v>
+        <v>-0.1932</v>
       </c>
       <c r="F235" s="15" t="n">
-        <v>-0.1223</v>
+        <v>-0.1292</v>
       </c>
       <c r="G235" s="16" t="n">
         <v>46324</v>
@@ -18487,13 +18487,13 @@
         </is>
       </c>
       <c r="D236" s="4" t="n">
-        <v>224.2</v>
+        <v>221.7</v>
       </c>
       <c r="E236" s="25" t="n">
-        <v>-0.0432</v>
+        <v>-0.0539</v>
       </c>
       <c r="F236" s="5" t="n">
-        <v>0.1882</v>
+        <v>0.175</v>
       </c>
       <c r="G236" s="6" t="n"/>
       <c r="H236" s="7" t="inlineStr">
@@ -18512,7 +18512,7 @@
         <v>240</v>
       </c>
       <c r="M236" s="5" t="n">
-        <v>0.07047279214986625</v>
+        <v>0.08254397834912049</v>
       </c>
       <c r="N236" s="3" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>251</v>
       </c>
       <c r="P236" s="5" t="n">
-        <v>0.1195361284567351</v>
+        <v>0.1321605773567885</v>
       </c>
       <c r="Q236" s="9" t="inlineStr">
         <is>
@@ -18564,13 +18564,13 @@
         </is>
       </c>
       <c r="D237" s="13" t="n">
-        <v>500.79</v>
+        <v>497.12</v>
       </c>
       <c r="E237" s="14" t="n">
-        <v>0.0426</v>
+        <v>0.0349</v>
       </c>
       <c r="F237" s="14" t="n">
-        <v>0.2716</v>
+        <v>0.2623</v>
       </c>
       <c r="G237" s="16" t="n">
         <v>46330</v>
@@ -18599,7 +18599,7 @@
         <v>625</v>
       </c>
       <c r="M237" s="14" t="n">
-        <v>0.2480281155773877</v>
+        <v>0.2572417122626328</v>
       </c>
       <c r="N237" s="12" t="inlineStr">
         <is>
@@ -18610,7 +18610,7 @@
         <v>525</v>
       </c>
       <c r="P237" s="14" t="n">
-        <v>0.04834361708500565</v>
+        <v>0.05608303830061151</v>
       </c>
       <c r="Q237" s="19" t="inlineStr">
         <is>
@@ -18663,13 +18663,13 @@
         </is>
       </c>
       <c r="D238" s="4" t="n">
-        <v>472.99</v>
+        <v>469.14</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>0.0348</v>
+        <v>0.0264</v>
       </c>
       <c r="F238" s="5" t="n">
-        <v>0.1444</v>
+        <v>0.1351</v>
       </c>
       <c r="G238" s="6" t="n">
         <v>46324</v>
@@ -18701,7 +18701,7 @@
         <v>525</v>
       </c>
       <c r="P238" s="5" t="n">
-        <v>0.1099600414385082</v>
+        <v>0.1190689346463742</v>
       </c>
       <c r="Q238" s="9" t="inlineStr">
         <is>
@@ -18750,13 +18750,13 @@
         </is>
       </c>
       <c r="D239" s="13" t="n">
-        <v>131.33</v>
+        <v>129.6</v>
       </c>
       <c r="E239" s="14" t="n">
-        <v>0.3445</v>
+        <v>0.3268</v>
       </c>
       <c r="F239" s="14" t="n">
-        <v>0.3846</v>
+        <v>0.3664</v>
       </c>
       <c r="G239" s="16" t="n">
         <v>46324</v>
@@ -18811,13 +18811,13 @@
         </is>
       </c>
       <c r="D240" s="4" t="n">
-        <v>239.55</v>
+        <v>240.02</v>
       </c>
       <c r="E240" s="25" t="n">
-        <v>-0.2686</v>
+        <v>-0.2672</v>
       </c>
       <c r="F240" s="25" t="n">
-        <v>-0.104</v>
+        <v>-0.1023</v>
       </c>
       <c r="G240" s="6" t="n">
         <v>46331</v>
@@ -18872,13 +18872,13 @@
         </is>
       </c>
       <c r="D241" s="13" t="n">
-        <v>932.5700000000001</v>
+        <v>927.6</v>
       </c>
       <c r="E241" s="15" t="n">
-        <v>-0.07829999999999999</v>
+        <v>-0.0832</v>
       </c>
       <c r="F241" s="14" t="n">
-        <v>0.09849999999999999</v>
+        <v>0.0926</v>
       </c>
       <c r="G241" s="16" t="n">
         <v>46295</v>
@@ -18907,7 +18907,7 @@
         <v>1525</v>
       </c>
       <c r="M241" s="14" t="n">
-        <v>0.6352659853951981</v>
+        <v>0.6440275981026304</v>
       </c>
       <c r="N241" s="12" t="inlineStr">
         <is>
@@ -18955,13 +18955,13 @@
         </is>
       </c>
       <c r="D242" s="4" t="n">
-        <v>209.43</v>
+        <v>207.37</v>
       </c>
       <c r="E242" s="25" t="n">
-        <v>-0.221</v>
+        <v>-0.2287</v>
       </c>
       <c r="F242" s="5" t="n">
-        <v>0.1785</v>
+        <v>0.1669</v>
       </c>
       <c r="G242" s="6" t="n"/>
       <c r="H242" s="7" t="inlineStr">
@@ -19006,13 +19006,13 @@
         </is>
       </c>
       <c r="D243" s="13" t="n">
-        <v>327.48</v>
+        <v>327.23</v>
       </c>
       <c r="E243" s="14" t="n">
-        <v>0.0667</v>
+        <v>0.0659</v>
       </c>
       <c r="F243" s="14" t="n">
-        <v>0.1794</v>
+        <v>0.1785</v>
       </c>
       <c r="G243" s="16" t="n">
         <v>46324</v>
@@ -19067,13 +19067,13 @@
         </is>
       </c>
       <c r="D244" s="4" t="n">
-        <v>144.1</v>
+        <v>141.9</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>0.2243</v>
+        <v>0.2056</v>
       </c>
       <c r="F244" s="5" t="n">
-        <v>0.3957</v>
+        <v>0.3745000000000001</v>
       </c>
       <c r="G244" s="6" t="n">
         <v>46323</v>
@@ -19102,7 +19102,7 @@
         <v>160</v>
       </c>
       <c r="M244" s="5" t="n">
-        <v>0.1103400416377516</v>
+        <v>0.1275546159267089</v>
       </c>
       <c r="N244" s="3" t="inlineStr">
         <is>
@@ -19113,7 +19113,7 @@
         <v>150</v>
       </c>
       <c r="P244" s="5" t="n">
-        <v>0.04094378903539213</v>
+        <v>0.0570824524312896</v>
       </c>
       <c r="Q244" s="9" t="inlineStr">
         <is>
@@ -19158,13 +19158,13 @@
         </is>
       </c>
       <c r="D245" s="13" t="n">
-        <v>68.36</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="E245" s="14" t="n">
-        <v>0.0411</v>
+        <v>0.0355</v>
       </c>
       <c r="F245" s="14" t="n">
-        <v>0.2411</v>
+        <v>0.2344</v>
       </c>
       <c r="G245" s="16" t="n"/>
       <c r="H245" s="21" t="inlineStr">
@@ -19209,13 +19209,13 @@
         </is>
       </c>
       <c r="D246" s="4" t="n">
-        <v>212.3</v>
+        <v>212.17</v>
       </c>
       <c r="E246" s="25" t="n">
-        <v>-0.0565</v>
+        <v>-0.0571</v>
       </c>
       <c r="F246" s="5" t="n">
-        <v>0.04679999999999999</v>
+        <v>0.0462</v>
       </c>
       <c r="G246" s="6" t="n"/>
       <c r="H246" s="7" t="inlineStr">
@@ -19234,7 +19234,7 @@
         <v>315</v>
       </c>
       <c r="M246" s="5" t="n">
-        <v>0.483749411210551</v>
+        <v>0.4846585285384363</v>
       </c>
       <c r="N246" s="3" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>413</v>
       </c>
       <c r="P246" s="5" t="n">
-        <v>0.9453603391427224</v>
+        <v>0.9465522929726164</v>
       </c>
       <c r="Q246" s="9" t="inlineStr">
         <is>
@@ -19294,13 +19294,13 @@
         </is>
       </c>
       <c r="D247" s="13" t="n">
-        <v>330.9</v>
+        <v>335.08</v>
       </c>
       <c r="E247" s="15" t="n">
-        <v>-0.2136</v>
+        <v>-0.2037</v>
       </c>
       <c r="F247" s="15" t="n">
-        <v>-0.2436</v>
+        <v>-0.234</v>
       </c>
       <c r="G247" s="16" t="n">
         <v>46331</v>
@@ -19355,13 +19355,13 @@
         </is>
       </c>
       <c r="D248" s="4" t="n">
-        <v>226.15</v>
+        <v>226.35</v>
       </c>
       <c r="E248" s="25" t="n">
-        <v>-0.0282</v>
+        <v>-0.0274</v>
       </c>
       <c r="F248" s="25" t="n">
-        <v>-0.1515</v>
+        <v>-0.1508</v>
       </c>
       <c r="G248" s="6" t="n">
         <v>46322</v>
@@ -19412,13 +19412,13 @@
         </is>
       </c>
       <c r="D249" s="13" t="n">
-        <v>10.57</v>
+        <v>10.6</v>
       </c>
       <c r="E249" s="15" t="n">
-        <v>-0.08410000000000001</v>
+        <v>-0.081</v>
       </c>
       <c r="F249" s="15" t="n">
-        <v>-0.3264</v>
+        <v>-0.3240999999999999</v>
       </c>
       <c r="G249" s="16" t="n"/>
       <c r="H249" s="21" t="inlineStr">
@@ -19463,13 +19463,13 @@
         </is>
       </c>
       <c r="D250" s="4" t="n">
-        <v>187.76</v>
+        <v>190.45</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>0.3108</v>
+        <v>0.3296</v>
       </c>
       <c r="F250" s="5" t="n">
-        <v>0.2571</v>
+        <v>0.2752</v>
       </c>
       <c r="G250" s="6" t="n"/>
       <c r="H250" s="7" t="inlineStr">
@@ -19488,7 +19488,7 @@
         <v>150</v>
       </c>
       <c r="M250" s="25" t="n">
-        <v>-0.2011077971878994</v>
+        <v>-0.2123917038592806</v>
       </c>
       <c r="N250" s="3" t="inlineStr">
         <is>
@@ -19499,7 +19499,7 @@
         <v>130</v>
       </c>
       <c r="P250" s="25" t="n">
-        <v>-0.3076267575628461</v>
+        <v>-0.3174061433447098</v>
       </c>
       <c r="Q250" s="9" t="inlineStr">
         <is>
@@ -19540,13 +19540,13 @@
         </is>
       </c>
       <c r="D251" s="13" t="n">
-        <v>72.47</v>
+        <v>73.2</v>
       </c>
       <c r="E251" s="15" t="n">
-        <v>-0.1308</v>
+        <v>-0.1221</v>
       </c>
       <c r="F251" s="15" t="n">
-        <v>-0.1705</v>
+        <v>-0.1622</v>
       </c>
       <c r="G251" s="16" t="n">
         <v>46328</v>
@@ -19601,13 +19601,13 @@
         </is>
       </c>
       <c r="D252" s="4" t="n">
-        <v>243.46</v>
+        <v>244.16</v>
       </c>
       <c r="E252" s="25" t="n">
-        <v>-0.3067</v>
+        <v>-0.3047</v>
       </c>
       <c r="F252" s="25" t="n">
-        <v>-0.13</v>
+        <v>-0.1275</v>
       </c>
       <c r="G252" s="6" t="n">
         <v>46331</v>
@@ -19662,13 +19662,13 @@
         </is>
       </c>
       <c r="D253" s="13" t="n">
-        <v>143.66</v>
+        <v>140.35</v>
       </c>
       <c r="E253" s="15" t="n">
-        <v>-0.0204</v>
+        <v>-0.043</v>
       </c>
       <c r="F253" s="14" t="n">
-        <v>0.1365</v>
+        <v>0.1103</v>
       </c>
       <c r="G253" s="16" t="n"/>
       <c r="H253" s="21" t="inlineStr">
@@ -19687,7 +19687,7 @@
         <v>280</v>
       </c>
       <c r="M253" s="14" t="n">
-        <v>0.9490463594598357</v>
+        <v>0.9950124688279303</v>
       </c>
       <c r="N253" s="12" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
         <v>245</v>
       </c>
       <c r="P253" s="14" t="n">
-        <v>0.7054155645273563</v>
+        <v>0.745635910224439</v>
       </c>
       <c r="Q253" s="19" t="inlineStr">
         <is>
@@ -19739,13 +19739,13 @@
         </is>
       </c>
       <c r="D254" s="4" t="n">
-        <v>373.23</v>
+        <v>375.09</v>
       </c>
       <c r="E254" s="25" t="n">
-        <v>-0.0067</v>
+        <v>-0.0018</v>
       </c>
       <c r="F254" s="5" t="n">
-        <v>0.0406</v>
+        <v>0.0458</v>
       </c>
       <c r="G254" s="6" t="n"/>
       <c r="H254" s="7" t="inlineStr">
@@ -19764,7 +19764,7 @@
         <v>420</v>
       </c>
       <c r="M254" s="5" t="n">
-        <v>0.1253114701390563</v>
+        <v>0.1197312644965209</v>
       </c>
       <c r="N254" s="3" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>415</v>
       </c>
       <c r="P254" s="5" t="n">
-        <v>0.1119149050183532</v>
+        <v>0.1064011303953719</v>
       </c>
       <c r="Q254" s="9" t="inlineStr">
         <is>
@@ -19824,13 +19824,13 @@
         </is>
       </c>
       <c r="D255" s="13" t="n">
-        <v>14.31</v>
+        <v>14.23</v>
       </c>
       <c r="E255" s="15" t="n">
-        <v>-0.1054</v>
+        <v>-0.1101</v>
       </c>
       <c r="F255" s="14" t="n">
-        <v>0.1774</v>
+        <v>0.1712</v>
       </c>
       <c r="G255" s="16" t="n"/>
       <c r="H255" s="21" t="inlineStr">
@@ -19875,13 +19875,13 @@
         </is>
       </c>
       <c r="D256" s="4" t="n">
-        <v>38.34</v>
+        <v>37.63</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>0.2026</v>
+        <v>0.1804</v>
       </c>
       <c r="F256" s="5" t="n">
-        <v>0.1922</v>
+        <v>0.1701</v>
       </c>
       <c r="G256" s="6" t="n">
         <v>46315</v>
@@ -19936,13 +19936,13 @@
         </is>
       </c>
       <c r="D257" s="13" t="n">
-        <v>171.59</v>
-      </c>
-      <c r="E257" s="15" t="n">
-        <v>-0.0007000000000000001</v>
+        <v>174.39</v>
+      </c>
+      <c r="E257" s="14" t="n">
+        <v>0.0156</v>
       </c>
       <c r="F257" s="14" t="n">
-        <v>0.24</v>
+        <v>0.2603</v>
       </c>
       <c r="G257" s="16" t="n">
         <v>46330</v>
@@ -19997,13 +19997,13 @@
         </is>
       </c>
       <c r="D258" s="4" t="n">
-        <v>171.92</v>
-      </c>
-      <c r="E258" s="25" t="n">
-        <v>-0.0037</v>
+        <v>172.56</v>
+      </c>
+      <c r="E258" s="5" t="n">
+        <v>0.0001</v>
       </c>
       <c r="F258" s="5" t="n">
-        <v>0.2987</v>
+        <v>0.3035</v>
       </c>
       <c r="G258" s="6" t="n">
         <v>46328</v>
@@ -20058,13 +20058,13 @@
         </is>
       </c>
       <c r="D259" s="13" t="n">
-        <v>114.28</v>
+        <v>114.59</v>
       </c>
       <c r="E259" s="15" t="n">
-        <v>-0.1882</v>
+        <v>-0.1859</v>
       </c>
       <c r="F259" s="15" t="n">
-        <v>-0.1619</v>
+        <v>-0.1596</v>
       </c>
       <c r="G259" s="16" t="n"/>
       <c r="H259" s="21" t="inlineStr">
@@ -20119,13 +20119,13 @@
         </is>
       </c>
       <c r="D260" s="4" t="n">
-        <v>16.33</v>
+        <v>16.41</v>
       </c>
       <c r="E260" s="25" t="n">
-        <v>-0.2178</v>
+        <v>-0.2137</v>
       </c>
       <c r="F260" s="25" t="n">
-        <v>-0.0242</v>
+        <v>-0.0191</v>
       </c>
       <c r="G260" s="6" t="n">
         <v>46331</v>
@@ -20180,13 +20180,13 @@
         </is>
       </c>
       <c r="D261" s="13" t="n">
-        <v>187.11</v>
+        <v>187.8</v>
       </c>
       <c r="E261" s="14" t="n">
-        <v>0.1537</v>
+        <v>0.158</v>
       </c>
       <c r="F261" s="14" t="n">
-        <v>0.0892</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="G261" s="16" t="n">
         <v>46330</v>
@@ -20215,7 +20215,7 @@
         <v>265</v>
       </c>
       <c r="M261" s="14" t="n">
-        <v>0.4162791940569717</v>
+        <v>0.4110756123535675</v>
       </c>
       <c r="N261" s="12" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>179</v>
       </c>
       <c r="P261" s="15" t="n">
-        <v>-0.0433434877879323</v>
+        <v>-0.04685835995740155</v>
       </c>
       <c r="Q261" s="19" t="inlineStr">
         <is>
@@ -20271,13 +20271,13 @@
         </is>
       </c>
       <c r="D262" s="4" t="n">
-        <v>116.24</v>
+        <v>118.06</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>0.2103</v>
+        <v>0.2293</v>
       </c>
       <c r="F262" s="5" t="n">
-        <v>0.3595</v>
+        <v>0.3808</v>
       </c>
       <c r="G262" s="6" t="n">
         <v>46322</v>
@@ -20332,13 +20332,13 @@
         </is>
       </c>
       <c r="D263" s="13" t="n">
-        <v>7.86</v>
+        <v>7.84</v>
       </c>
       <c r="E263" s="15" t="n">
-        <v>-0.1314</v>
+        <v>-0.1337</v>
       </c>
       <c r="F263" s="14" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.0051</v>
       </c>
       <c r="G263" s="16" t="n"/>
       <c r="H263" s="21" t="inlineStr">
@@ -20383,13 +20383,13 @@
         </is>
       </c>
       <c r="D264" s="4" t="n">
-        <v>98.77</v>
-      </c>
-      <c r="E264" s="25" t="n">
-        <v>-0.0223</v>
+        <v>103.55</v>
+      </c>
+      <c r="E264" s="5" t="n">
+        <v>0.025</v>
       </c>
       <c r="F264" s="5" t="n">
-        <v>0.2507</v>
+        <v>0.3113</v>
       </c>
       <c r="G264" s="6" t="n"/>
       <c r="H264" s="7" t="inlineStr">
@@ -20434,13 +20434,13 @@
         </is>
       </c>
       <c r="D265" s="13" t="n">
-        <v>15.02</v>
+        <v>15.09</v>
       </c>
       <c r="E265" s="15" t="n">
-        <v>-0.1952</v>
+        <v>-0.1918</v>
       </c>
       <c r="F265" s="14" t="n">
-        <v>0.06480000000000001</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="G265" s="16" t="n">
         <v>46335</v>
@@ -20495,13 +20495,13 @@
         </is>
       </c>
       <c r="D266" s="4" t="n">
-        <v>383.4</v>
+        <v>383.94</v>
       </c>
       <c r="E266" s="25" t="n">
-        <v>-0.0162</v>
+        <v>-0.0148</v>
       </c>
       <c r="F266" s="5" t="n">
-        <v>0.0558</v>
+        <v>0.0573</v>
       </c>
       <c r="G266" s="6" t="n">
         <v>46317</v>
@@ -20570,13 +20570,13 @@
         </is>
       </c>
       <c r="D267" s="13" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="E267" s="15" t="n">
-        <v>-0.1456</v>
+        <v>-0.1544</v>
       </c>
       <c r="F267" s="15" t="n">
-        <v>-0.1867</v>
+        <v>-0.1952</v>
       </c>
       <c r="G267" s="16" t="n">
         <v>46331</v>
@@ -20631,13 +20631,13 @@
         </is>
       </c>
       <c r="D268" s="4" t="n">
-        <v>22.66</v>
+        <v>23.48</v>
       </c>
       <c r="E268" s="5" t="n">
-        <v>0.0385</v>
+        <v>0.0761</v>
       </c>
       <c r="F268" s="5" t="n">
-        <v>0.1579</v>
+        <v>0.1998</v>
       </c>
       <c r="G268" s="6" t="n"/>
       <c r="H268" s="7" t="inlineStr">
@@ -20682,13 +20682,13 @@
         </is>
       </c>
       <c r="D269" s="13" t="n">
-        <v>19.9</v>
+        <v>19.98</v>
       </c>
       <c r="E269" s="14" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="F269" s="14" t="n">
-        <v>0.2691</v>
+        <v>0.2742</v>
       </c>
       <c r="G269" s="16" t="n"/>
       <c r="H269" s="21" t="inlineStr">
@@ -20733,13 +20733,13 @@
         </is>
       </c>
       <c r="D270" s="4" t="n">
-        <v>193.77</v>
+        <v>191.61</v>
       </c>
       <c r="E270" s="25" t="n">
-        <v>-0.1072</v>
+        <v>-0.1171</v>
       </c>
       <c r="F270" s="25" t="n">
-        <v>-0.0176</v>
+        <v>-0.0285</v>
       </c>
       <c r="G270" s="6" t="n">
         <v>46328</v>
@@ -20794,13 +20794,13 @@
         </is>
       </c>
       <c r="D271" s="13" t="n">
-        <v>215.93</v>
+        <v>215.67</v>
       </c>
       <c r="E271" s="14" t="n">
-        <v>0.0389</v>
+        <v>0.0377</v>
       </c>
       <c r="F271" s="14" t="n">
-        <v>0.3577</v>
+        <v>0.3561</v>
       </c>
       <c r="G271" s="16" t="n">
         <v>46316</v>
@@ -20875,13 +20875,13 @@
         </is>
       </c>
       <c r="D272" s="4" t="n">
-        <v>36.44</v>
+        <v>35.64</v>
       </c>
       <c r="E272" s="25" t="n">
-        <v>-0.0479</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="F272" s="5" t="n">
-        <v>0.5072</v>
+        <v>0.4739</v>
       </c>
       <c r="G272" s="6" t="n">
         <v>46329</v>
@@ -20936,13 +20936,13 @@
         </is>
       </c>
       <c r="D273" s="13" t="n">
-        <v>324.13</v>
+        <v>322.98</v>
       </c>
       <c r="E273" s="15" t="n">
-        <v>-0.0181</v>
+        <v>-0.0216</v>
       </c>
       <c r="F273" s="14" t="n">
-        <v>0.2054</v>
+        <v>0.2011</v>
       </c>
       <c r="G273" s="16" t="n"/>
       <c r="H273" s="21" t="inlineStr">
@@ -20961,7 +20961,7 @@
         <v>320</v>
       </c>
       <c r="M273" s="15" t="n">
-        <v>-0.01274180112917655</v>
+        <v>-0.009226577497058698</v>
       </c>
       <c r="N273" s="12" t="inlineStr">
         <is>
@@ -20972,7 +20972,7 @@
         <v>280</v>
       </c>
       <c r="P273" s="15" t="n">
-        <v>-0.1361490759880295</v>
+        <v>-0.1330732553099264</v>
       </c>
       <c r="Q273" s="19" t="inlineStr">
         <is>
@@ -21013,13 +21013,13 @@
         </is>
       </c>
       <c r="D274" s="4" t="n">
-        <v>369.31</v>
+        <v>367.7</v>
       </c>
       <c r="E274" s="25" t="n">
-        <v>-0.1063</v>
+        <v>-0.1102</v>
       </c>
       <c r="F274" s="25" t="n">
-        <v>-0.039</v>
+        <v>-0.0431</v>
       </c>
       <c r="G274" s="6" t="n"/>
       <c r="H274" s="7" t="inlineStr">
@@ -21038,7 +21038,7 @@
         <v>535</v>
       </c>
       <c r="M274" s="5" t="n">
-        <v>0.4486474777287374</v>
+        <v>0.4549904813706827</v>
       </c>
       <c r="N274" s="3" t="inlineStr"/>
       <c r="O274" s="8" t="n"/>
@@ -21082,13 +21082,13 @@
         </is>
       </c>
       <c r="D275" s="13" t="n">
-        <v>6.26</v>
+        <v>6.15</v>
       </c>
       <c r="E275" s="15" t="n">
-        <v>-0.1108</v>
+        <v>-0.1264</v>
       </c>
       <c r="F275" s="15" t="n">
-        <v>-0.0016</v>
+        <v>-0.0191</v>
       </c>
       <c r="G275" s="16" t="n">
         <v>46331</v>
@@ -21143,13 +21143,13 @@
         </is>
       </c>
       <c r="D276" s="4" t="n">
-        <v>87.95999999999999</v>
+        <v>90</v>
       </c>
       <c r="E276" s="5" t="n">
-        <v>0.2987</v>
+        <v>0.3288</v>
       </c>
       <c r="F276" s="5" t="n">
-        <v>0.4821</v>
+        <v>0.5164</v>
       </c>
       <c r="G276" s="6" t="n">
         <v>46322</v>
@@ -21204,13 +21204,13 @@
         </is>
       </c>
       <c r="D277" s="13" t="n">
-        <v>96.66</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="E277" s="15" t="n">
-        <v>-0.1259</v>
+        <v>-0.1199</v>
       </c>
       <c r="F277" s="15" t="n">
-        <v>-0.1525</v>
+        <v>-0.1467</v>
       </c>
       <c r="G277" s="16" t="n">
         <v>46331</v>
@@ -21265,13 +21265,13 @@
         </is>
       </c>
       <c r="D278" s="4" t="n">
-        <v>202.38</v>
+        <v>201.42</v>
       </c>
       <c r="E278" s="25" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.07339999999999999</v>
       </c>
       <c r="F278" s="25" t="n">
-        <v>-0.004500000000000001</v>
+        <v>-0.009300000000000001</v>
       </c>
       <c r="G278" s="6" t="n">
         <v>46330</v>
@@ -21326,13 +21326,13 @@
         </is>
       </c>
       <c r="D279" s="13" t="n">
-        <v>328.08</v>
+        <v>332.85</v>
       </c>
       <c r="E279" s="15" t="n">
-        <v>-0.2596</v>
+        <v>-0.2489</v>
       </c>
       <c r="F279" s="14" t="n">
-        <v>0.0177</v>
+        <v>0.0325</v>
       </c>
       <c r="G279" s="16" t="n">
         <v>46322</v>
@@ -21387,13 +21387,13 @@
         </is>
       </c>
       <c r="D280" s="4" t="n">
-        <v>58.64</v>
+        <v>58.8</v>
       </c>
       <c r="E280" s="5" t="n">
-        <v>0.053</v>
+        <v>0.0558</v>
       </c>
       <c r="F280" s="5" t="n">
-        <v>0.1123</v>
+        <v>0.1153</v>
       </c>
       <c r="G280" s="6" t="n">
         <v>46330</v>
@@ -21448,13 +21448,13 @@
         </is>
       </c>
       <c r="D281" s="13" t="n">
-        <v>414.02</v>
+        <v>413.75</v>
       </c>
       <c r="E281" s="15" t="n">
-        <v>-0.0393</v>
+        <v>-0.04</v>
       </c>
       <c r="F281" s="14" t="n">
-        <v>0.0393</v>
+        <v>0.0386</v>
       </c>
       <c r="G281" s="16" t="n">
         <v>46310</v>
@@ -21531,13 +21531,13 @@
         </is>
       </c>
       <c r="D282" s="4" t="n">
-        <v>112.1</v>
+        <v>112.46</v>
       </c>
       <c r="E282" s="25" t="n">
-        <v>-0.2049</v>
+        <v>-0.2023</v>
       </c>
       <c r="F282" s="25" t="n">
-        <v>-0.1508</v>
+        <v>-0.148</v>
       </c>
       <c r="G282" s="6" t="n">
         <v>46330</v>
@@ -21592,13 +21592,13 @@
         </is>
       </c>
       <c r="D283" s="13" t="n">
-        <v>235.85</v>
+        <v>242.16</v>
       </c>
       <c r="E283" s="14" t="n">
-        <v>0.0317</v>
+        <v>0.0593</v>
       </c>
       <c r="F283" s="14" t="n">
-        <v>0.1406</v>
+        <v>0.1711</v>
       </c>
       <c r="G283" s="16" t="n">
         <v>46324</v>
@@ -21653,13 +21653,13 @@
         </is>
       </c>
       <c r="D284" s="4" t="n">
-        <v>264.43</v>
+        <v>263.43</v>
       </c>
       <c r="E284" s="25" t="n">
-        <v>-0.0653</v>
+        <v>-0.0689</v>
       </c>
       <c r="F284" s="25" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.0725</v>
       </c>
       <c r="G284" s="6" t="n">
         <v>46315</v>
@@ -21688,7 +21688,7 @@
         <v>300</v>
       </c>
       <c r="M284" s="5" t="n">
-        <v>0.1345157508603411</v>
+        <v>0.1388224575788634</v>
       </c>
       <c r="N284" s="3" t="inlineStr">
         <is>
@@ -21699,7 +21699,7 @@
         <v>316</v>
       </c>
       <c r="P284" s="5" t="n">
-        <v>0.1950232575728926</v>
+        <v>0.1995596553164028</v>
       </c>
       <c r="Q284" s="9" t="inlineStr">
         <is>
@@ -21756,13 +21756,13 @@
         </is>
       </c>
       <c r="D285" s="13" t="n">
-        <v>348.73</v>
+        <v>353.13</v>
       </c>
       <c r="E285" s="14" t="n">
-        <v>0.08810000000000001</v>
+        <v>0.1019</v>
       </c>
       <c r="F285" s="14" t="n">
-        <v>0.0915</v>
+        <v>0.1052</v>
       </c>
       <c r="G285" s="16" t="n">
         <v>46330</v>
@@ -21791,7 +21791,7 @@
         <v>335</v>
       </c>
       <c r="M285" s="15" t="n">
-        <v>-0.03937143348722513</v>
+        <v>-0.05134086597003935</v>
       </c>
       <c r="N285" s="12" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>375</v>
       </c>
       <c r="P285" s="14" t="n">
-        <v>0.07533048490235994</v>
+        <v>0.06193186645144849</v>
       </c>
       <c r="Q285" s="19" t="inlineStr">
         <is>
@@ -21843,13 +21843,13 @@
         </is>
       </c>
       <c r="D286" s="4" t="n">
-        <v>42.89</v>
+        <v>43.01</v>
       </c>
       <c r="E286" s="25" t="n">
-        <v>-0.0563</v>
+        <v>-0.0537</v>
       </c>
       <c r="F286" s="5" t="n">
-        <v>0.4795</v>
+        <v>0.4836</v>
       </c>
       <c r="G286" s="6" t="n">
         <v>46330</v>
@@ -21904,13 +21904,13 @@
         </is>
       </c>
       <c r="D287" s="13" t="n">
-        <v>6.01</v>
+        <v>5.96</v>
       </c>
       <c r="E287" s="15" t="n">
-        <v>-0.2405</v>
+        <v>-0.2475</v>
       </c>
       <c r="F287" s="15" t="n">
-        <v>-0.1861</v>
+        <v>-0.1935</v>
       </c>
       <c r="G287" s="16" t="n"/>
       <c r="H287" s="21" t="inlineStr">
@@ -21955,13 +21955,13 @@
         </is>
       </c>
       <c r="D288" s="4" t="n">
-        <v>191.92</v>
-      </c>
-      <c r="E288" s="5" t="n">
-        <v>0.0039</v>
+        <v>190.67</v>
+      </c>
+      <c r="E288" s="25" t="n">
+        <v>-0.0027</v>
       </c>
       <c r="F288" s="5" t="n">
-        <v>0.3256</v>
+        <v>0.317</v>
       </c>
       <c r="G288" s="6" t="n"/>
       <c r="H288" s="7" t="inlineStr">
@@ -22006,13 +22006,13 @@
         </is>
       </c>
       <c r="D289" s="13" t="n">
-        <v>416.68</v>
+        <v>411.96</v>
       </c>
       <c r="E289" s="15" t="n">
-        <v>-0.2226</v>
+        <v>-0.2314</v>
       </c>
       <c r="F289" s="15" t="n">
-        <v>-0.1269</v>
+        <v>-0.1368</v>
       </c>
       <c r="G289" s="16" t="n">
         <v>46324</v>
@@ -22041,7 +22041,7 @@
         <v>730</v>
       </c>
       <c r="M289" s="14" t="n">
-        <v>0.7519439377939906</v>
+        <v>0.7720167006505487</v>
       </c>
       <c r="N289" s="12" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>575</v>
       </c>
       <c r="P289" s="14" t="n">
-        <v>0.3799558414130748</v>
+        <v>0.3957665792795418</v>
       </c>
       <c r="Q289" s="19" t="inlineStr">
         <is>
@@ -22093,13 +22093,13 @@
         </is>
       </c>
       <c r="D290" s="4" t="n">
-        <v>23.6</v>
+        <v>24.02</v>
       </c>
       <c r="E290" s="25" t="n">
-        <v>-0.3249</v>
+        <v>-0.3129</v>
       </c>
       <c r="F290" s="25" t="n">
-        <v>-0.2104</v>
+        <v>-0.1964</v>
       </c>
       <c r="G290" s="6" t="n">
         <v>46330</v>
@@ -22154,13 +22154,13 @@
         </is>
       </c>
       <c r="D291" s="13" t="n">
-        <v>93.3</v>
+        <v>93.06999999999999</v>
       </c>
       <c r="E291" s="15" t="n">
-        <v>-0.1161</v>
+        <v>-0.1183</v>
       </c>
       <c r="F291" s="14" t="n">
-        <v>0.0238</v>
+        <v>0.0213</v>
       </c>
       <c r="G291" s="16" t="n"/>
       <c r="H291" s="21" t="inlineStr">
@@ -22205,13 +22205,13 @@
         </is>
       </c>
       <c r="D292" s="4" t="n">
-        <v>190.84</v>
+        <v>193.89</v>
       </c>
       <c r="E292" s="5" t="n">
-        <v>0.0347</v>
+        <v>0.0512</v>
       </c>
       <c r="F292" s="5" t="n">
-        <v>0.2728</v>
+        <v>0.2931</v>
       </c>
       <c r="G292" s="6" t="n"/>
       <c r="H292" s="7" t="inlineStr">
@@ -22256,13 +22256,13 @@
         </is>
       </c>
       <c r="D293" s="13" t="n">
-        <v>286.99</v>
+        <v>290.56</v>
       </c>
       <c r="E293" s="15" t="n">
-        <v>-0.0461</v>
+        <v>-0.0342</v>
       </c>
       <c r="F293" s="15" t="n">
-        <v>-0.0292</v>
+        <v>-0.0171</v>
       </c>
       <c r="G293" s="16" t="n">
         <v>46331</v>
@@ -22317,13 +22317,13 @@
         </is>
       </c>
       <c r="D294" s="4" t="n">
-        <v>84.22</v>
+        <v>84.77</v>
       </c>
       <c r="E294" s="25" t="n">
-        <v>-0.047</v>
+        <v>-0.0407</v>
       </c>
       <c r="F294" s="5" t="n">
-        <v>0.0444</v>
+        <v>0.0512</v>
       </c>
       <c r="G294" s="6" t="n"/>
       <c r="H294" s="7" t="inlineStr">
@@ -22368,13 +22368,13 @@
         </is>
       </c>
       <c r="D295" s="13" t="n">
-        <v>123.52</v>
+        <v>128.04</v>
       </c>
       <c r="E295" s="15" t="n">
-        <v>-0.1366</v>
+        <v>-0.1051</v>
       </c>
       <c r="F295" s="15" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.0536</v>
       </c>
       <c r="G295" s="16" t="n">
         <v>46331</v>
@@ -22403,7 +22403,7 @@
         <v>166</v>
       </c>
       <c r="M295" s="14" t="n">
-        <v>0.3439119170984457</v>
+        <v>0.2964698531708842</v>
       </c>
       <c r="N295" s="12" t="inlineStr"/>
       <c r="O295" s="18" t="n"/>
@@ -22451,13 +22451,13 @@
         </is>
       </c>
       <c r="D296" s="4" t="n">
-        <v>29.69</v>
+        <v>29.85</v>
       </c>
       <c r="E296" s="25" t="n">
-        <v>-0.0527</v>
+        <v>-0.0475</v>
       </c>
       <c r="F296" s="25" t="n">
-        <v>-0.0077</v>
+        <v>-0.0023</v>
       </c>
       <c r="G296" s="6" t="n">
         <v>46317</v>
@@ -22512,13 +22512,13 @@
         </is>
       </c>
       <c r="D297" s="13" t="n">
-        <v>273.81</v>
+        <v>274.6</v>
       </c>
       <c r="E297" s="15" t="n">
-        <v>-0.0074</v>
+        <v>-0.004500000000000001</v>
       </c>
       <c r="F297" s="14" t="n">
-        <v>0.0036</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="G297" s="16" t="n">
         <v>46322</v>
@@ -22547,7 +22547,7 @@
         <v>275</v>
       </c>
       <c r="M297" s="14" t="n">
-        <v>0.004346079398122778</v>
+        <v>0.001456664238892852</v>
       </c>
       <c r="N297" s="12" t="inlineStr">
         <is>
@@ -22558,7 +22558,7 @@
         <v>312</v>
       </c>
       <c r="P297" s="14" t="n">
-        <v>0.1394762791716884</v>
+        <v>0.1361981063364893</v>
       </c>
       <c r="Q297" s="19" t="inlineStr">
         <is>
@@ -22611,13 +22611,13 @@
         </is>
       </c>
       <c r="D298" s="4" t="n">
-        <v>31.72</v>
+        <v>31.79</v>
       </c>
       <c r="E298" s="25" t="n">
-        <v>-0.1912</v>
+        <v>-0.1894</v>
       </c>
       <c r="F298" s="25" t="n">
-        <v>-0.1519</v>
+        <v>-0.15</v>
       </c>
       <c r="G298" s="6" t="n">
         <v>46322</v>
@@ -22676,13 +22676,13 @@
         </is>
       </c>
       <c r="D299" s="13" t="n">
-        <v>68.51000000000001</v>
+        <v>69.38</v>
       </c>
       <c r="E299" s="14" t="n">
-        <v>0.0019</v>
+        <v>0.0146</v>
       </c>
       <c r="F299" s="14" t="n">
-        <v>0.1735</v>
+        <v>0.1884</v>
       </c>
       <c r="G299" s="16" t="n">
         <v>46310</v>
@@ -22737,13 +22737,13 @@
         </is>
       </c>
       <c r="D300" s="4" t="n">
-        <v>460.35</v>
+        <v>462.96</v>
       </c>
       <c r="E300" s="25" t="n">
-        <v>-0.0295</v>
+        <v>-0.024</v>
       </c>
       <c r="F300" s="25" t="n">
-        <v>-0.103</v>
+        <v>-0.09789999999999999</v>
       </c>
       <c r="G300" s="6" t="n">
         <v>46325</v>
@@ -22772,7 +22772,7 @@
         <v>570</v>
       </c>
       <c r="M300" s="5" t="n">
-        <v>0.2381883349625284</v>
+        <v>0.2312078797304303</v>
       </c>
       <c r="N300" s="3" t="inlineStr">
         <is>
@@ -22783,7 +22783,7 @@
         <v>525</v>
       </c>
       <c r="P300" s="5" t="n">
-        <v>0.140436624307592</v>
+        <v>0.134007257646449</v>
       </c>
       <c r="Q300" s="9" t="inlineStr">
         <is>
@@ -22836,13 +22836,13 @@
         </is>
       </c>
       <c r="D301" s="13" t="n">
-        <v>496.03</v>
+        <v>506.81</v>
       </c>
       <c r="E301" s="15" t="n">
-        <v>-0.0791</v>
+        <v>-0.0591</v>
       </c>
       <c r="F301" s="15" t="n">
-        <v>-0.1183</v>
+        <v>-0.09910000000000001</v>
       </c>
       <c r="G301" s="16" t="n">
         <v>46329</v>
@@ -22871,7 +22871,7 @@
         <v>616</v>
       </c>
       <c r="M301" s="14" t="n">
-        <v>0.2418603713485072</v>
+        <v>0.2154456305124208</v>
       </c>
       <c r="N301" s="12" t="inlineStr"/>
       <c r="O301" s="18" t="n"/>
@@ -22915,13 +22915,13 @@
         </is>
       </c>
       <c r="D302" s="4" t="n">
-        <v>256.82</v>
+        <v>258.82</v>
       </c>
       <c r="E302" s="25" t="n">
-        <v>-0.0582</v>
+        <v>-0.0508</v>
       </c>
       <c r="F302" s="5" t="n">
-        <v>0.08539999999999999</v>
+        <v>0.09390000000000001</v>
       </c>
       <c r="G302" s="6" t="n">
         <v>46321</v>
@@ -22950,7 +22950,7 @@
         <v>283</v>
       </c>
       <c r="M302" s="5" t="n">
-        <v>0.1019391013160969</v>
+        <v>0.09342400123638052</v>
       </c>
       <c r="N302" s="3" t="inlineStr"/>
       <c r="O302" s="8" t="n"/>
@@ -22996,13 +22996,13 @@
         </is>
       </c>
       <c r="D303" s="13" t="n">
-        <v>229.7</v>
+        <v>231.21</v>
       </c>
       <c r="E303" s="15" t="n">
-        <v>-0.092</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="F303" s="15" t="n">
-        <v>-0.0145</v>
+        <v>-0.008</v>
       </c>
       <c r="G303" s="16" t="n">
         <v>46323</v>
@@ -23031,7 +23031,7 @@
         <v>246</v>
       </c>
       <c r="M303" s="14" t="n">
-        <v>0.07096212451023079</v>
+        <v>0.06396782146100943</v>
       </c>
       <c r="N303" s="12" t="inlineStr"/>
       <c r="O303" s="18" t="n"/>
@@ -23079,13 +23079,13 @@
         </is>
       </c>
       <c r="D304" s="4" t="n">
-        <v>104.64</v>
+        <v>104.89</v>
       </c>
       <c r="E304" s="25" t="n">
-        <v>-0.0776</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="F304" s="25" t="n">
-        <v>-0.1084</v>
+        <v>-0.1063</v>
       </c>
       <c r="G304" s="6" t="n">
         <v>46322</v>
@@ -23114,7 +23114,7 @@
         <v>130</v>
       </c>
       <c r="M304" s="5" t="n">
-        <v>0.2423547400611621</v>
+        <v>0.2393936504909906</v>
       </c>
       <c r="N304" s="3" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>128</v>
       </c>
       <c r="P304" s="5" t="n">
-        <v>0.2232415902140673</v>
+        <v>0.2203260558680522</v>
       </c>
       <c r="Q304" s="9" t="inlineStr">
         <is>
@@ -23174,13 +23174,13 @@
         </is>
       </c>
       <c r="D305" s="13" t="n">
-        <v>100.15</v>
+        <v>100.6</v>
       </c>
       <c r="E305" s="15" t="n">
-        <v>-0.1076</v>
+        <v>-0.1036</v>
       </c>
       <c r="F305" s="15" t="n">
-        <v>-0.0469</v>
+        <v>-0.0426</v>
       </c>
       <c r="G305" s="16" t="n">
         <v>46301</v>
@@ -23209,7 +23209,7 @@
         <v>135</v>
       </c>
       <c r="M305" s="14" t="n">
-        <v>0.3479780329505741</v>
+        <v>0.3419483101391651</v>
       </c>
       <c r="N305" s="12" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>125</v>
       </c>
       <c r="P305" s="14" t="n">
-        <v>0.2481278082875686</v>
+        <v>0.242544731610338</v>
       </c>
       <c r="Q305" s="19" t="inlineStr"/>
       <c r="R305" s="18" t="n"/>
@@ -23255,13 +23255,13 @@
         </is>
       </c>
       <c r="D306" s="4" t="n">
-        <v>320.7</v>
+        <v>323.22</v>
       </c>
       <c r="E306" s="25" t="n">
-        <v>-0.08359999999999999</v>
+        <v>-0.0764</v>
       </c>
       <c r="F306" s="25" t="n">
-        <v>-0.0321</v>
+        <v>-0.0244</v>
       </c>
       <c r="G306" s="6" t="n">
         <v>46322</v>
@@ -23290,7 +23290,7 @@
         <v>350</v>
       </c>
       <c r="M306" s="5" t="n">
-        <v>0.09136264421577803</v>
+        <v>0.0828537838005073</v>
       </c>
       <c r="N306" s="3" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>400</v>
       </c>
       <c r="P306" s="5" t="n">
-        <v>0.2472715933894606</v>
+        <v>0.2375471814862941</v>
       </c>
       <c r="Q306" s="9" t="inlineStr">
         <is>
@@ -23342,13 +23342,13 @@
         </is>
       </c>
       <c r="D307" s="13" t="n">
-        <v>97.13</v>
+        <v>96.97</v>
       </c>
       <c r="E307" s="15" t="n">
-        <v>-0.1698</v>
+        <v>-0.1711</v>
       </c>
       <c r="F307" s="14" t="n">
-        <v>0.4</v>
+        <v>0.3977000000000001</v>
       </c>
       <c r="G307" s="16" t="n"/>
       <c r="H307" s="21" t="inlineStr">
@@ -23389,13 +23389,13 @@
         </is>
       </c>
       <c r="D308" s="4" t="n">
-        <v>48.78</v>
+        <v>48.65</v>
       </c>
       <c r="E308" s="25" t="n">
-        <v>-0.261</v>
+        <v>-0.263</v>
       </c>
       <c r="F308" s="25" t="n">
-        <v>-0.13</v>
+        <v>-0.1323</v>
       </c>
       <c r="G308" s="6" t="n">
         <v>46267</v>
@@ -23450,13 +23450,13 @@
         </is>
       </c>
       <c r="D309" s="13" t="n">
-        <v>70.45999999999999</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="E309" s="15" t="n">
-        <v>-0.0547</v>
+        <v>-0.06</v>
       </c>
       <c r="F309" s="15" t="n">
-        <v>-0.1313</v>
+        <v>-0.1362</v>
       </c>
       <c r="G309" s="16" t="n">
         <v>46315</v>
@@ -23485,14 +23485,14 @@
         <v>83</v>
       </c>
       <c r="M309" s="14" t="n">
-        <v>0.1779733181947205</v>
+        <v>0.1845297559583275</v>
       </c>
       <c r="N309" s="12" t="inlineStr"/>
       <c r="O309" s="18" t="n">
         <v>87</v>
       </c>
       <c r="P309" s="14" t="n">
-        <v>0.234743116661936</v>
+        <v>0.2416155273298132</v>
       </c>
       <c r="Q309" s="19" t="inlineStr"/>
       <c r="R309" s="18" t="n"/>
@@ -23527,13 +23527,13 @@
         </is>
       </c>
       <c r="D310" s="4" t="n">
-        <v>178.4</v>
+        <v>177.71</v>
       </c>
       <c r="E310" s="5" t="n">
-        <v>0.0358</v>
+        <v>0.0318</v>
       </c>
       <c r="F310" s="5" t="n">
-        <v>0.049</v>
+        <v>0.045</v>
       </c>
       <c r="G310" s="6" t="n">
         <v>46322</v>
@@ -23562,7 +23562,7 @@
         <v>200</v>
       </c>
       <c r="M310" s="5" t="n">
-        <v>0.1210762331838565</v>
+        <v>0.1254290698328737</v>
       </c>
       <c r="N310" s="3" t="inlineStr"/>
       <c r="O310" s="8" t="n"/>
@@ -23610,13 +23610,13 @@
         </is>
       </c>
       <c r="D311" s="13" t="n">
-        <v>139.5</v>
+        <v>140.11</v>
       </c>
       <c r="E311" s="15" t="n">
-        <v>-0.0572</v>
+        <v>-0.05309999999999999</v>
       </c>
       <c r="F311" s="15" t="n">
-        <v>-0.0104</v>
+        <v>-0.006</v>
       </c>
       <c r="G311" s="16" t="n">
         <v>46317</v>
@@ -23675,13 +23675,13 @@
         </is>
       </c>
       <c r="D312" s="4" t="n">
-        <v>179.09</v>
+        <v>179.27</v>
       </c>
       <c r="E312" s="25" t="n">
-        <v>-0.0951</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="F312" s="5" t="n">
-        <v>0.03</v>
+        <v>0.031</v>
       </c>
       <c r="G312" s="6" t="n">
         <v>46317</v>
@@ -23710,7 +23710,7 @@
         <v>220</v>
       </c>
       <c r="M312" s="5" t="n">
-        <v>0.228432631637724</v>
+        <v>0.2271991967423439</v>
       </c>
       <c r="N312" s="3" t="inlineStr">
         <is>
@@ -23721,7 +23721,7 @@
         <v>230</v>
       </c>
       <c r="P312" s="5" t="n">
-        <v>0.2842704785303479</v>
+        <v>0.2829809784124504</v>
       </c>
       <c r="Q312" s="9" t="inlineStr">
         <is>
@@ -23762,13 +23762,13 @@
         </is>
       </c>
       <c r="D313" s="13" t="n">
-        <v>1006.34</v>
+        <v>1006.98</v>
       </c>
       <c r="E313" s="15" t="n">
-        <v>-0.0832</v>
+        <v>-0.08259999999999999</v>
       </c>
       <c r="F313" s="15" t="n">
-        <v>-0.0134</v>
+        <v>-0.0128</v>
       </c>
       <c r="G313" s="16" t="n">
         <v>46330</v>
@@ -23797,7 +23797,7 @@
         <v>1200</v>
       </c>
       <c r="M313" s="14" t="n">
-        <v>0.192439930838484</v>
+        <v>0.1916820592265983</v>
       </c>
       <c r="N313" s="12" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
         <v>1240</v>
       </c>
       <c r="P313" s="14" t="n">
-        <v>0.2321879285331001</v>
+        <v>0.2314047945341516</v>
       </c>
       <c r="Q313" s="19" t="inlineStr">
         <is>
@@ -23853,13 +23853,13 @@
         </is>
       </c>
       <c r="D314" s="4" t="n">
-        <v>113.9</v>
+        <v>113.93</v>
       </c>
       <c r="E314" s="25" t="n">
-        <v>-0.0349</v>
+        <v>-0.0347</v>
       </c>
       <c r="F314" s="25" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.0959</v>
       </c>
       <c r="G314" s="6" t="n">
         <v>46325</v>
@@ -23888,7 +23888,7 @@
         <v>129</v>
       </c>
       <c r="M314" s="5" t="n">
-        <v>0.1325724319578577</v>
+        <v>0.1322742034582638</v>
       </c>
       <c r="N314" s="3" t="inlineStr">
         <is>
@@ -23899,7 +23899,7 @@
         <v>122</v>
       </c>
       <c r="P314" s="5" t="n">
-        <v>0.07111501316944684</v>
+        <v>0.07083296761169132</v>
       </c>
       <c r="Q314" s="9" t="inlineStr">
         <is>
@@ -23940,13 +23940,13 @@
         </is>
       </c>
       <c r="D315" s="13" t="n">
-        <v>59.06</v>
+        <v>58.71</v>
       </c>
       <c r="E315" s="15" t="n">
-        <v>-0.0536</v>
+        <v>-0.0591</v>
       </c>
       <c r="F315" s="15" t="n">
-        <v>-0.1013</v>
+        <v>-0.1065</v>
       </c>
       <c r="G315" s="16" t="n">
         <v>46328</v>
@@ -23975,14 +23975,14 @@
         <v>65</v>
       </c>
       <c r="M315" s="14" t="n">
-        <v>0.1005756857433118</v>
+        <v>0.1071367739737694</v>
       </c>
       <c r="N315" s="12" t="inlineStr"/>
       <c r="O315" s="18" t="n">
         <v>67</v>
       </c>
       <c r="P315" s="14" t="n">
-        <v>0.1344395529969522</v>
+        <v>0.14120252086527</v>
       </c>
       <c r="Q315" s="19" t="inlineStr">
         <is>
@@ -24023,13 +24023,13 @@
         </is>
       </c>
       <c r="D316" s="4" t="n">
-        <v>135.05</v>
+        <v>135.84</v>
       </c>
       <c r="E316" s="25" t="n">
-        <v>-0.0396</v>
+        <v>-0.034</v>
       </c>
       <c r="F316" s="25" t="n">
-        <v>-0.0984</v>
+        <v>-0.0931</v>
       </c>
       <c r="G316" s="6" t="n">
         <v>46310</v>
@@ -24058,7 +24058,7 @@
         <v>167</v>
       </c>
       <c r="M316" s="5" t="n">
-        <v>0.2365790447982228</v>
+        <v>0.2293875147232037</v>
       </c>
       <c r="N316" s="3" t="inlineStr"/>
       <c r="O316" s="8" t="n"/>
@@ -24102,13 +24102,13 @@
         </is>
       </c>
       <c r="D317" s="13" t="n">
-        <v>295.55</v>
+        <v>296.68</v>
       </c>
       <c r="E317" s="15" t="n">
-        <v>-0.08869999999999999</v>
+        <v>-0.0852</v>
       </c>
       <c r="F317" s="15" t="n">
-        <v>-0.0707</v>
+        <v>-0.0672</v>
       </c>
       <c r="G317" s="16" t="n">
         <v>46330</v>
@@ -24144,7 +24144,7 @@
         <v>316</v>
       </c>
       <c r="P317" s="14" t="n">
-        <v>0.06919302994417184</v>
+        <v>0.06512066873398946</v>
       </c>
       <c r="Q317" s="19" t="inlineStr">
         <is>
@@ -24185,13 +24185,13 @@
         </is>
       </c>
       <c r="D318" s="4" t="n">
-        <v>204.16</v>
+        <v>204.1</v>
       </c>
       <c r="E318" s="25" t="n">
-        <v>-0.079</v>
+        <v>-0.0793</v>
       </c>
       <c r="F318" s="25" t="n">
-        <v>-0.1073</v>
+        <v>-0.1076</v>
       </c>
       <c r="G318" s="6" t="n">
         <v>46328</v>
@@ -24227,7 +24227,7 @@
         <v>215</v>
       </c>
       <c r="P318" s="5" t="n">
-        <v>0.05309561128526648</v>
+        <v>0.0534051935325821</v>
       </c>
       <c r="Q318" s="9" t="inlineStr">
         <is>
@@ -24268,13 +24268,13 @@
         </is>
       </c>
       <c r="D319" s="13" t="n">
-        <v>117.63</v>
+        <v>117.13</v>
       </c>
       <c r="E319" s="15" t="n">
-        <v>-0.0308</v>
+        <v>-0.0349</v>
       </c>
       <c r="F319" s="15" t="n">
-        <v>-0.0316</v>
+        <v>-0.0356</v>
       </c>
       <c r="G319" s="16" t="n">
         <v>46330</v>
@@ -24303,7 +24303,7 @@
         <v>142</v>
       </c>
       <c r="M319" s="14" t="n">
-        <v>0.2071750403808553</v>
+        <v>0.2123281823614787</v>
       </c>
       <c r="N319" s="12" t="inlineStr">
         <is>
@@ -24314,7 +24314,7 @@
         <v>137</v>
       </c>
       <c r="P319" s="14" t="n">
-        <v>0.1646688769871632</v>
+        <v>0.1696405703064971</v>
       </c>
       <c r="Q319" s="19" t="inlineStr">
         <is>
@@ -24363,13 +24363,13 @@
         </is>
       </c>
       <c r="D320" s="4" t="n">
-        <v>233.14</v>
+        <v>232.76</v>
       </c>
       <c r="E320" s="25" t="n">
-        <v>-0.0092</v>
+        <v>-0.0108</v>
       </c>
       <c r="F320" s="25" t="n">
-        <v>-0.0416</v>
+        <v>-0.0431</v>
       </c>
       <c r="G320" s="6" t="n">
         <v>46321</v>
@@ -24398,7 +24398,7 @@
         <v>237</v>
       </c>
       <c r="M320" s="5" t="n">
-        <v>0.01655657544822859</v>
+        <v>0.01821618834851353</v>
       </c>
       <c r="N320" s="3" t="inlineStr">
         <is>
@@ -24409,7 +24409,7 @@
         <v>236</v>
       </c>
       <c r="P320" s="5" t="n">
-        <v>0.01226730719739218</v>
+        <v>0.01391991751159997</v>
       </c>
       <c r="Q320" s="9" t="inlineStr">
         <is>
@@ -24450,13 +24450,13 @@
         </is>
       </c>
       <c r="D321" s="13" t="n">
-        <v>163.47</v>
+        <v>162.04</v>
       </c>
       <c r="E321" s="15" t="n">
-        <v>-0.0378</v>
+        <v>-0.0463</v>
       </c>
       <c r="F321" s="15" t="n">
-        <v>-0.08</v>
+        <v>-0.08800000000000001</v>
       </c>
       <c r="G321" s="16" t="n">
         <v>46330</v>
@@ -24485,7 +24485,7 @@
         <v>200</v>
       </c>
       <c r="M321" s="14" t="n">
-        <v>0.2234660794029486</v>
+        <v>0.2342631449024933</v>
       </c>
       <c r="N321" s="12" t="inlineStr"/>
       <c r="O321" s="18" t="n"/>
@@ -24529,13 +24529,13 @@
         </is>
       </c>
       <c r="D322" s="4" t="n">
-        <v>139.18</v>
+        <v>138.02</v>
       </c>
       <c r="E322" s="5" t="n">
-        <v>0.036</v>
+        <v>0.0273</v>
       </c>
       <c r="F322" s="5" t="n">
-        <v>0.0302</v>
+        <v>0.0215</v>
       </c>
       <c r="G322" s="6" t="n">
         <v>46330</v>
@@ -24564,7 +24564,7 @@
         <v>131</v>
       </c>
       <c r="M322" s="25" t="n">
-        <v>-0.05877281218565891</v>
+        <v>-0.05086219388494428</v>
       </c>
       <c r="N322" s="3" t="inlineStr"/>
       <c r="O322" s="8" t="n"/>
@@ -24608,13 +24608,13 @@
         </is>
       </c>
       <c r="D323" s="13" t="n">
-        <v>29.62</v>
+        <v>29.05</v>
       </c>
       <c r="E323" s="15" t="n">
-        <v>-0.1561</v>
+        <v>-0.1724</v>
       </c>
       <c r="F323" s="15" t="n">
-        <v>-0.1265</v>
+        <v>-0.1433</v>
       </c>
       <c r="G323" s="16" t="n">
         <v>46330</v>
@@ -24687,13 +24687,13 @@
         </is>
       </c>
       <c r="D324" s="4" t="n">
-        <v>35.85</v>
+        <v>35.04</v>
       </c>
       <c r="E324" s="25" t="n">
-        <v>-0.0786</v>
+        <v>-0.09949999999999999</v>
       </c>
       <c r="F324" s="25" t="n">
-        <v>-0.08689999999999999</v>
+        <v>-0.1075</v>
       </c>
       <c r="G324" s="6" t="n">
         <v>46332</v>
@@ -24748,13 +24748,13 @@
         </is>
       </c>
       <c r="D325" s="13" t="n">
-        <v>261.22</v>
+        <v>259.89</v>
       </c>
       <c r="E325" s="15" t="n">
-        <v>-0.061</v>
+        <v>-0.0658</v>
       </c>
       <c r="F325" s="14" t="n">
-        <v>0.035</v>
+        <v>0.0297</v>
       </c>
       <c r="G325" s="16" t="n">
         <v>46332</v>
@@ -24783,7 +24783,7 @@
         <v>384</v>
       </c>
       <c r="M325" s="14" t="n">
-        <v>0.4700252660592603</v>
+        <v>0.4775481934664667</v>
       </c>
       <c r="N325" s="12" t="inlineStr">
         <is>
@@ -24794,7 +24794,7 @@
         <v>380</v>
       </c>
       <c r="P325" s="14" t="n">
-        <v>0.454712502871143</v>
+        <v>0.462157066451191</v>
       </c>
       <c r="Q325" s="19" t="inlineStr"/>
       <c r="R325" s="18" t="n"/>
@@ -24837,13 +24837,13 @@
         </is>
       </c>
       <c r="D326" s="4" t="n">
-        <v>66.36</v>
+        <v>65.92</v>
       </c>
       <c r="E326" s="25" t="n">
-        <v>-0.0706</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="F326" s="25" t="n">
-        <v>-0.099</v>
+        <v>-0.105</v>
       </c>
       <c r="G326" s="6" t="n">
         <v>46324</v>
@@ -24872,7 +24872,7 @@
         <v>79</v>
       </c>
       <c r="M326" s="5" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.1984223300970873</v>
       </c>
       <c r="N326" s="3" t="inlineStr"/>
       <c r="O326" s="8" t="n"/>
@@ -24924,13 +24924,13 @@
         </is>
       </c>
       <c r="D327" s="13" t="n">
-        <v>118.26</v>
+        <v>117.77</v>
       </c>
       <c r="E327" s="15" t="n">
-        <v>-0.043</v>
+        <v>-0.047</v>
       </c>
       <c r="F327" s="15" t="n">
-        <v>-0.05400000000000001</v>
+        <v>-0.0579</v>
       </c>
       <c r="G327" s="16" t="n">
         <v>46331</v>
@@ -24959,7 +24959,7 @@
         <v>136</v>
       </c>
       <c r="M327" s="14" t="n">
-        <v>0.150008455944529</v>
+        <v>0.1547932410630891</v>
       </c>
       <c r="N327" s="12" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>140</v>
       </c>
       <c r="P327" s="14" t="n">
-        <v>0.1838322340605445</v>
+        <v>0.18875774815318</v>
       </c>
       <c r="Q327" s="19" t="inlineStr">
         <is>
@@ -25011,13 +25011,13 @@
         </is>
       </c>
       <c r="D328" s="4" t="n">
-        <v>102.76</v>
+        <v>102.92</v>
       </c>
       <c r="E328" s="25" t="n">
-        <v>-0.053</v>
+        <v>-0.0516</v>
       </c>
       <c r="F328" s="25" t="n">
-        <v>-0.0925</v>
+        <v>-0.0911</v>
       </c>
       <c r="G328" s="6" t="n">
         <v>46330</v>
@@ -25046,7 +25046,7 @@
         <v>131</v>
       </c>
       <c r="M328" s="5" t="n">
-        <v>0.2748151031529777</v>
+        <v>0.2728332685581034</v>
       </c>
       <c r="N328" s="3" t="inlineStr">
         <is>
@@ -25057,7 +25057,7 @@
         <v>121</v>
       </c>
       <c r="P328" s="5" t="n">
-        <v>0.1775009731413001</v>
+        <v>0.1756704236300039</v>
       </c>
       <c r="Q328" s="9" t="inlineStr">
         <is>
@@ -25102,13 +25102,13 @@
         </is>
       </c>
       <c r="D329" s="13" t="n">
-        <v>81.42</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="E329" s="15" t="n">
-        <v>-0.0557</v>
+        <v>-0.0597</v>
       </c>
       <c r="F329" s="15" t="n">
-        <v>-0.0832</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="G329" s="16" t="n">
         <v>46322</v>
@@ -25144,7 +25144,7 @@
         <v>107</v>
       </c>
       <c r="P329" s="14" t="n">
-        <v>0.3141734217636944</v>
+        <v>0.3198470457629211</v>
       </c>
       <c r="Q329" s="19" t="inlineStr">
         <is>
@@ -25193,13 +25193,13 @@
         </is>
       </c>
       <c r="D330" s="4" t="n">
-        <v>53.21</v>
+        <v>53.27</v>
       </c>
       <c r="E330" s="25" t="n">
-        <v>-0.032</v>
+        <v>-0.0309</v>
       </c>
       <c r="F330" s="25" t="n">
-        <v>-0.092</v>
+        <v>-0.091</v>
       </c>
       <c r="G330" s="6" t="n"/>
       <c r="H330" s="7" t="inlineStr">
@@ -25218,7 +25218,7 @@
         <v>63</v>
       </c>
       <c r="M330" s="5" t="n">
-        <v>0.1839879721856794</v>
+        <v>0.1826544021024966</v>
       </c>
       <c r="N330" s="3" t="inlineStr"/>
       <c r="O330" s="8" t="n"/>
@@ -25262,13 +25262,13 @@
         </is>
       </c>
       <c r="D331" s="13" t="n">
-        <v>35.53</v>
+        <v>35.98</v>
       </c>
       <c r="E331" s="15" t="n">
-        <v>-0.1902</v>
+        <v>-0.18</v>
       </c>
       <c r="F331" s="15" t="n">
-        <v>-0.1356</v>
+        <v>-0.1248</v>
       </c>
       <c r="G331" s="16" t="n"/>
       <c r="H331" s="21" t="inlineStr">
@@ -25313,13 +25313,13 @@
         </is>
       </c>
       <c r="D332" s="4" t="n">
-        <v>8.279999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="E332" s="25" t="n">
-        <v>-0.099</v>
+        <v>-0.0827</v>
       </c>
       <c r="F332" s="5" t="n">
-        <v>0.0726</v>
+        <v>0.092</v>
       </c>
       <c r="G332" s="6" t="n">
         <v>46331</v>
@@ -25374,13 +25374,13 @@
         </is>
       </c>
       <c r="D333" s="13" t="n">
-        <v>86.45</v>
+        <v>85.95</v>
       </c>
       <c r="E333" s="15" t="n">
-        <v>-0.0633</v>
+        <v>-0.0687</v>
       </c>
       <c r="F333" s="15" t="n">
-        <v>-0.0929</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="G333" s="16" t="n">
         <v>46324</v>
@@ -25409,7 +25409,7 @@
         <v>99</v>
       </c>
       <c r="M333" s="14" t="n">
-        <v>0.1451706188548293</v>
+        <v>0.1518324607329843</v>
       </c>
       <c r="N333" s="12" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>112</v>
       </c>
       <c r="P333" s="14" t="n">
-        <v>0.2955465587044534</v>
+        <v>0.3030831878999418</v>
       </c>
       <c r="Q333" s="19" t="inlineStr">
         <is>
@@ -25461,13 +25461,13 @@
         </is>
       </c>
       <c r="D334" s="4" t="n">
-        <v>104.07</v>
+        <v>103.51</v>
       </c>
       <c r="E334" s="25" t="n">
-        <v>-0.0581</v>
+        <v>-0.06320000000000001</v>
       </c>
       <c r="F334" s="25" t="n">
-        <v>-0.0818</v>
+        <v>-0.0868</v>
       </c>
       <c r="G334" s="6" t="n">
         <v>46324</v>
@@ -25496,7 +25496,7 @@
         <v>127</v>
       </c>
       <c r="M334" s="5" t="n">
-        <v>0.2203324685307967</v>
+        <v>0.2269345956912375</v>
       </c>
       <c r="N334" s="3" t="inlineStr"/>
       <c r="O334" s="8" t="n"/>
@@ -37253,7 +37253,7 @@
     <row r="2">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>Data as of September 15, 2026 at 15:17 UTC</t>
+          <t>Data as of September 15, 2026 at 20:29 UTC</t>
         </is>
       </c>
     </row>

--- a/earnings-data.xlsx
+++ b/earnings-data.xlsx
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>106.13</v>
+        <v>105.35</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.021</v>
+        <v>0.0135</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.1008</v>
+        <v>0.09269999999999999</v>
       </c>
       <c r="G2" s="6" t="n"/>
       <c r="H2" s="7" t="inlineStr">
@@ -868,7 +868,7 @@
         <v>125</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>0.1778008103269575</v>
+        <v>0.1865211200759374</v>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         <v>144</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>0.3568265334966551</v>
+        <v>0.3668723303274799</v>
       </c>
       <c r="Q2" s="9" t="inlineStr">
         <is>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="D3" s="13" t="n">
-        <v>347.4</v>
+        <v>347.33</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.0091</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>-0.013</v>
+        <v>-0.0132</v>
       </c>
       <c r="G3" s="16" t="n">
         <v>46322</v>
@@ -963,7 +963,7 @@
         <v>438</v>
       </c>
       <c r="M3" s="14" t="n">
-        <v>0.2607944732297064</v>
+        <v>0.2610485705237095</v>
       </c>
       <c r="N3" s="12" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>420</v>
       </c>
       <c r="P3" s="14" t="n">
-        <v>0.2089810017271158</v>
+        <v>0.2092246566665708</v>
       </c>
       <c r="Q3" s="19" t="inlineStr">
         <is>
@@ -1019,13 +1019,13 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>674.7</v>
+        <v>682.3099999999999</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.241</v>
+        <v>0.255</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.0447</v>
+        <v>0.0565</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>46330</v>
@@ -1054,7 +1054,7 @@
         <v>835</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>0.2375870757373647</v>
+        <v>0.2237839105391978</v>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>930</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>0.3783903957314361</v>
+        <v>0.3630168105406634</v>
       </c>
       <c r="Q4" s="9" t="inlineStr">
         <is>
@@ -1114,13 +1114,13 @@
         </is>
       </c>
       <c r="D5" s="13" t="n">
-        <v>43.8</v>
+        <v>43.77</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>0.1321</v>
+        <v>0.1313</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>0.1219</v>
+        <v>0.1212</v>
       </c>
       <c r="G5" s="16" t="n">
         <v>46329</v>
@@ -1175,13 +1175,13 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>75.58</v>
+        <v>75.31</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>-0.0282</v>
+        <v>-0.0316</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.118</v>
+        <v>0.1141</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>46315</v>
@@ -1210,7 +1210,7 @@
         <v>80</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>0.05848107965070127</v>
+        <v>0.0622759261718231</v>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>100</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>0.3231013495633766</v>
+        <v>0.3278449077147789</v>
       </c>
       <c r="Q6" s="9" t="inlineStr">
         <is>
@@ -1262,13 +1262,13 @@
         </is>
       </c>
       <c r="D7" s="13" t="n">
-        <v>79.37</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>-0.08039999999999999</v>
+        <v>-0.08929999999999999</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>-0.0364</v>
+        <v>-0.0458</v>
       </c>
       <c r="G7" s="16" t="n">
         <v>46315</v>
@@ -1297,7 +1297,7 @@
         <v>91</v>
       </c>
       <c r="M7" s="14" t="n">
-        <v>0.1465289152072571</v>
+        <v>0.1577608142493639</v>
       </c>
       <c r="N7" s="12" t="inlineStr"/>
       <c r="O7" s="18" t="n"/>
@@ -1341,13 +1341,13 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>535.55</v>
+        <v>528.84</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.0373</v>
+        <v>0.0243</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.08779999999999999</v>
+        <v>0.0742</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>46329</v>
@@ -1376,7 +1376,7 @@
         <v>569.9299999999999</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>0.06419568667724769</v>
+        <v>0.07769835867180984</v>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>648.04</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>0.2100457473625245</v>
+        <v>0.2253989864609332</v>
       </c>
       <c r="Q8" s="9" t="inlineStr">
         <is>
@@ -1428,13 +1428,13 @@
         </is>
       </c>
       <c r="D9" s="13" t="n">
-        <v>188.94</v>
+        <v>189.3</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>-0.0165</v>
+        <v>-0.0146</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>0.0336</v>
+        <v>0.0356</v>
       </c>
       <c r="G9" s="16" t="n">
         <v>46330</v>
@@ -1497,13 +1497,13 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>171.76</v>
+        <v>166.45</v>
       </c>
       <c r="E10" s="25" t="n">
-        <v>-0.0601</v>
+        <v>-0.0892</v>
       </c>
       <c r="F10" s="25" t="n">
-        <v>-0.1221</v>
+        <v>-0.1492</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>46317</v>
@@ -1531,8 +1531,8 @@
       <c r="L10" s="8" t="n">
         <v>170</v>
       </c>
-      <c r="M10" s="25" t="n">
-        <v>-0.01024685607824867</v>
+      <c r="M10" s="5" t="n">
+        <v>0.02132772604385708</v>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>270</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>0.5719608756404286</v>
+        <v>0.622108741363773</v>
       </c>
       <c r="Q10" s="9" t="inlineStr">
         <is>
@@ -1584,13 +1584,13 @@
         </is>
       </c>
       <c r="D11" s="13" t="n">
-        <v>49.08</v>
-      </c>
-      <c r="E11" s="14" t="n">
-        <v>0.011</v>
+        <v>48.33</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>-0.0043</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>0.1282</v>
+        <v>0.111</v>
       </c>
       <c r="G11" s="16" t="n">
         <v>46316</v>
@@ -1619,7 +1619,7 @@
         <v>43</v>
       </c>
       <c r="M11" s="15" t="n">
-        <v>-0.123879380603097</v>
+        <v>-0.1102834678253672</v>
       </c>
       <c r="N11" s="12" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>50</v>
       </c>
       <c r="P11" s="14" t="n">
-        <v>0.01874490627546866</v>
+        <v>0.03455410717980554</v>
       </c>
       <c r="Q11" s="19" t="inlineStr">
         <is>
@@ -1675,13 +1675,13 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>166.16</v>
+        <v>165.93</v>
       </c>
       <c r="E12" s="25" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-0.09449999999999999</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.1464</v>
+        <v>0.1448</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>46331</v>
@@ -1710,7 +1710,7 @@
         <v>181</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>0.08931150698122294</v>
+        <v>0.09082143072379915</v>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>155</v>
       </c>
       <c r="P12" s="25" t="n">
-        <v>-0.0671641791044776</v>
+        <v>-0.06587115048514437</v>
       </c>
       <c r="Q12" s="9" t="inlineStr">
         <is>
@@ -1762,13 +1762,13 @@
         </is>
       </c>
       <c r="D13" s="13" t="n">
-        <v>251.99</v>
+        <v>251.19</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>-0.0287</v>
+        <v>-0.0318</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>0.008</v>
+        <v>0.0048</v>
       </c>
       <c r="G13" s="16" t="n">
         <v>46324</v>
@@ -1797,7 +1797,7 @@
         <v>322</v>
       </c>
       <c r="M13" s="14" t="n">
-        <v>0.2778284852573514</v>
+        <v>0.2818981647358573</v>
       </c>
       <c r="N13" s="12" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>285</v>
       </c>
       <c r="P13" s="14" t="n">
-        <v>0.130997261796103</v>
+        <v>0.134599307297265</v>
       </c>
       <c r="Q13" s="19" t="inlineStr">
         <is>
@@ -1861,13 +1861,13 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2872.6</v>
+        <v>2844.31</v>
       </c>
       <c r="E14" s="25" t="n">
-        <v>-0.0653</v>
+        <v>-0.0745</v>
       </c>
       <c r="F14" s="25" t="n">
-        <v>-0.0406</v>
+        <v>-0.05</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>46287</v>
@@ -1896,7 +1896,7 @@
         <v>4150</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>0.4446842581633364</v>
+        <v>0.4590533380679321</v>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>3700</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>0.2880317482420108</v>
+        <v>0.3008427351449033</v>
       </c>
       <c r="Q14" s="9" t="inlineStr">
         <is>
@@ -1948,13 +1948,13 @@
         </is>
       </c>
       <c r="D15" s="13" t="n">
-        <v>94.76000000000001</v>
+        <v>94.56</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>0.0858</v>
+        <v>0.08349999999999999</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>0.1131</v>
+        <v>0.1108</v>
       </c>
       <c r="G15" s="16" t="n"/>
       <c r="H15" s="21" t="inlineStr">
@@ -1973,7 +1973,7 @@
         <v>65</v>
       </c>
       <c r="M15" s="15" t="n">
-        <v>-0.3140565639510342</v>
+        <v>-0.3126057529610829</v>
       </c>
       <c r="N15" s="12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>85</v>
       </c>
       <c r="P15" s="15" t="n">
-        <v>-0.1029970451667371</v>
+        <v>-0.1010998307952623</v>
       </c>
       <c r="Q15" s="19" t="inlineStr"/>
       <c r="R15" s="18" t="n"/>
@@ -2019,13 +2019,13 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>169.7</v>
+        <v>170.52</v>
       </c>
       <c r="E16" s="25" t="n">
-        <v>-0.1851</v>
+        <v>-0.1812</v>
       </c>
       <c r="F16" s="25" t="n">
-        <v>-0.05429999999999999</v>
+        <v>-0.0498</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>46322</v>
@@ -2054,7 +2054,7 @@
         <v>214</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>0.2610489098408958</v>
+        <v>0.2549847525216983</v>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>245</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>0.4437242192103714</v>
+        <v>0.4367816091954022</v>
       </c>
       <c r="Q16" s="9" t="inlineStr">
         <is>
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="D17" s="13" t="n">
-        <v>237.41</v>
+        <v>239.54</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>-0.2954</v>
+        <v>-0.2891</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>-0.3258</v>
+        <v>-0.3198</v>
       </c>
       <c r="G17" s="16" t="n"/>
       <c r="H17" s="21" t="inlineStr">
@@ -2139,7 +2139,7 @@
         <v>375</v>
       </c>
       <c r="M17" s="14" t="n">
-        <v>0.5795459331957373</v>
+        <v>0.5655005427068549</v>
       </c>
       <c r="N17" s="12" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>375</v>
       </c>
       <c r="P17" s="14" t="n">
-        <v>0.5795459331957373</v>
+        <v>0.5655005427068549</v>
       </c>
       <c r="Q17" s="19" t="inlineStr"/>
       <c r="R17" s="18" t="n"/>
@@ -2189,13 +2189,13 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>33.88</v>
+        <v>33.51</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.0154</v>
+        <v>0.004500000000000001</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.0225</v>
+        <v>0.0115</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>46323</v>
@@ -2224,7 +2224,7 @@
         <v>45</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>0.3282172373081463</v>
+        <v>0.3428827215756491</v>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>45</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>0.3282172373081463</v>
+        <v>0.3428827215756491</v>
       </c>
       <c r="Q18" s="9" t="inlineStr">
         <is>
@@ -2276,13 +2276,13 @@
         </is>
       </c>
       <c r="D19" s="13" t="n">
-        <v>142.01</v>
+        <v>140.38</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>-0.0252</v>
+        <v>-0.0364</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>-0.0192</v>
+        <v>-0.0305</v>
       </c>
       <c r="G19" s="16" t="n">
         <v>46324</v>
@@ -2311,7 +2311,7 @@
         <v>170</v>
       </c>
       <c r="M19" s="14" t="n">
-        <v>0.1970987958594466</v>
+        <v>0.2109987177660636</v>
       </c>
       <c r="N19" s="12" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>177</v>
       </c>
       <c r="P19" s="14" t="n">
-        <v>0.246391099218365</v>
+        <v>0.2608633708505486</v>
       </c>
       <c r="Q19" s="19" t="inlineStr">
         <is>
@@ -2363,13 +2363,13 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>123.75</v>
+        <v>123.92</v>
       </c>
       <c r="E20" s="25" t="n">
-        <v>-0.3539</v>
+        <v>-0.353</v>
       </c>
       <c r="F20" s="25" t="n">
-        <v>-0.4226</v>
+        <v>-0.4218</v>
       </c>
       <c r="G20" s="6" t="n"/>
       <c r="H20" s="7" t="inlineStr">
@@ -2388,7 +2388,7 @@
         <v>220</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.775338928340865</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="8" t="n"/>
@@ -2432,13 +2432,13 @@
         </is>
       </c>
       <c r="D21" s="13" t="n">
-        <v>113.22</v>
+        <v>114.4</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>-0.1323</v>
+        <v>-0.1232</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>-0.1041</v>
+        <v>-0.09480000000000001</v>
       </c>
       <c r="G21" s="16" t="n"/>
       <c r="H21" s="21" t="inlineStr">
@@ -2483,13 +2483,13 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>87.47</v>
+        <v>86.62</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.0449</v>
+        <v>0.0348</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.154</v>
+        <v>0.1427</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>46315</v>
@@ -2518,7 +2518,7 @@
         <v>61</v>
       </c>
       <c r="M22" s="25" t="n">
-        <v>-0.3026180404710186</v>
+        <v>-0.295774647887324</v>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>100</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0.1432491139819367</v>
+        <v>0.1544677903486492</v>
       </c>
       <c r="Q22" s="9" t="inlineStr">
         <is>
@@ -2570,13 +2570,13 @@
         </is>
       </c>
       <c r="D23" s="13" t="n">
-        <v>131.26</v>
+        <v>130.88</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>-0.0048</v>
+        <v>-0.0077</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.0693</v>
       </c>
       <c r="G23" s="16" t="n">
         <v>46315</v>
@@ -2608,7 +2608,7 @@
         <v>145</v>
       </c>
       <c r="P23" s="14" t="n">
-        <v>0.1046777388389457</v>
+        <v>0.1078850855745722</v>
       </c>
       <c r="Q23" s="19" t="inlineStr"/>
       <c r="R23" s="18" t="n"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>305.23</v>
+        <v>302.51</v>
       </c>
       <c r="E24" s="25" t="n">
-        <v>-0.0956</v>
+        <v>-0.1036</v>
       </c>
       <c r="F24" s="25" t="n">
-        <v>-0.08349999999999999</v>
+        <v>-0.0917</v>
       </c>
       <c r="G24" s="6" t="n"/>
       <c r="H24" s="7" t="inlineStr">
@@ -2668,7 +2668,7 @@
         <v>360</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>0.1794384562461094</v>
+        <v>0.1900433043535751</v>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>400</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0.3104871736067882</v>
+        <v>0.322270338170639</v>
       </c>
       <c r="Q24" s="9" t="inlineStr">
         <is>
@@ -2728,13 +2728,13 @@
         </is>
       </c>
       <c r="D25" s="13" t="n">
-        <v>195.26</v>
+        <v>194.19</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>-0.09449999999999999</v>
+        <v>-0.09949999999999999</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>-0.0461</v>
+        <v>-0.05139999999999999</v>
       </c>
       <c r="G25" s="16" t="n"/>
       <c r="H25" s="21" t="inlineStr">
@@ -2753,7 +2753,7 @@
         <v>255</v>
       </c>
       <c r="M25" s="14" t="n">
-        <v>0.3059510396394551</v>
+        <v>0.3131469179669396</v>
       </c>
       <c r="N25" s="12" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>230</v>
       </c>
       <c r="P25" s="14" t="n">
-        <v>0.1779166239885282</v>
+        <v>0.1844070240486122</v>
       </c>
       <c r="Q25" s="19" t="inlineStr">
         <is>
@@ -2809,13 +2809,13 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>249.25</v>
+        <v>248.48</v>
       </c>
       <c r="E26" s="25" t="n">
-        <v>-0.0664</v>
+        <v>-0.0693</v>
       </c>
       <c r="F26" s="25" t="n">
-        <v>-0.0687</v>
+        <v>-0.0716</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>46330</v>
@@ -2844,7 +2844,7 @@
         <v>300</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>0.2036108324974925</v>
+        <v>0.2073406310367032</v>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>350</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>0.4042126379137412</v>
+        <v>0.4085640695428204</v>
       </c>
       <c r="Q26" s="9" t="inlineStr">
         <is>
@@ -2896,13 +2896,13 @@
         </is>
       </c>
       <c r="D27" s="13" t="n">
-        <v>35.96</v>
+        <v>36.36</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>-0.1025</v>
+        <v>-0.0924</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>-0.1729</v>
+        <v>-0.1636</v>
       </c>
       <c r="G27" s="16" t="n">
         <v>46289</v>
@@ -2957,13 +2957,13 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>84.86</v>
+        <v>84.89</v>
       </c>
       <c r="E28" s="25" t="n">
-        <v>-0.065</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.004</v>
+        <v>0.0043</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>46323</v>
@@ -2992,7 +2992,7 @@
         <v>110</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>0.2962526514258779</v>
+        <v>0.2957945576628578</v>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>115</v>
       </c>
       <c r="P28" s="5" t="n">
-        <v>0.3551732264906906</v>
+        <v>0.3546943102838968</v>
       </c>
       <c r="Q28" s="9" t="inlineStr">
         <is>
@@ -3048,13 +3048,13 @@
         </is>
       </c>
       <c r="D29" s="13" t="n">
-        <v>166.91</v>
+        <v>167.65</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>-0.1098</v>
+        <v>-0.1059</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>-0.1697</v>
+        <v>-0.166</v>
       </c>
       <c r="G29" s="16" t="n">
         <v>46317</v>
@@ -3109,13 +3109,13 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>228.63</v>
+        <v>229.48</v>
       </c>
       <c r="E30" s="25" t="n">
-        <v>-0.0328</v>
+        <v>-0.0292</v>
       </c>
       <c r="F30" s="25" t="n">
-        <v>-0.0303</v>
+        <v>-0.0267</v>
       </c>
       <c r="G30" s="6" t="n"/>
       <c r="H30" s="7" t="inlineStr">
@@ -3134,7 +3134,7 @@
         <v>245</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>0.07160040239688582</v>
+        <v>0.06763116611469414</v>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>265</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>0.1590779862660193</v>
+        <v>0.1547847306954855</v>
       </c>
       <c r="Q30" s="9" t="inlineStr">
         <is>
@@ -3186,13 +3186,13 @@
         </is>
       </c>
       <c r="D31" s="13" t="n">
-        <v>96.90000000000001</v>
+        <v>96.67</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>-0.0859</v>
+        <v>-0.08810000000000001</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>-0.0755</v>
+        <v>-0.07769999999999999</v>
       </c>
       <c r="G31" s="16" t="n">
         <v>46330</v>
@@ -3221,7 +3221,7 @@
         <v>120</v>
       </c>
       <c r="M31" s="14" t="n">
-        <v>0.2383900928792569</v>
+        <v>0.2413365056377366</v>
       </c>
       <c r="N31" s="12" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>115</v>
       </c>
       <c r="P31" s="14" t="n">
-        <v>0.1867905056759545</v>
+        <v>0.1896141512361642</v>
       </c>
       <c r="Q31" s="19" t="inlineStr">
         <is>
@@ -3273,13 +3273,13 @@
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>12.85</v>
+        <v>12.36</v>
       </c>
       <c r="E32" s="25" t="n">
-        <v>-0.0008</v>
+        <v>-0.0389</v>
       </c>
       <c r="F32" s="25" t="n">
-        <v>-0.1382</v>
+        <v>-0.171</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>46330</v>
@@ -3334,13 +3334,13 @@
         </is>
       </c>
       <c r="D33" s="13" t="n">
-        <v>124.5</v>
+        <v>126.55</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>-0.1747</v>
+        <v>-0.1611</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>-0.2004</v>
+        <v>-0.1872</v>
       </c>
       <c r="G33" s="16" t="n"/>
       <c r="H33" s="21" t="inlineStr">
@@ -3359,7 +3359,7 @@
         <v>160</v>
       </c>
       <c r="M33" s="14" t="n">
-        <v>0.285140562248996</v>
+        <v>0.2643224022125643</v>
       </c>
       <c r="N33" s="12" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>175</v>
       </c>
       <c r="P33" s="14" t="n">
-        <v>0.4056224899598393</v>
+        <v>0.3828526274199922</v>
       </c>
       <c r="Q33" s="19" t="inlineStr">
         <is>
@@ -3415,13 +3415,13 @@
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>32.81</v>
+        <v>32.82</v>
       </c>
       <c r="E34" s="25" t="n">
-        <v>-0.0552</v>
+        <v>-0.0547</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.0827</v>
+        <v>0.0832</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>46317</v>
@@ -3450,7 +3450,7 @@
         <v>35</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>0.06674794270039615</v>
+        <v>0.0664229128580134</v>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>40</v>
       </c>
       <c r="P34" s="5" t="n">
-        <v>0.2191405059433099</v>
+        <v>0.218769043266301</v>
       </c>
       <c r="Q34" s="9" t="inlineStr">
         <is>
@@ -3502,13 +3502,13 @@
         </is>
       </c>
       <c r="D35" s="13" t="n">
-        <v>365.32</v>
+        <v>366.2</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>0.08449999999999999</v>
+        <v>0.08710000000000001</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>-0.0115</v>
+        <v>-0.0091</v>
       </c>
       <c r="G35" s="16" t="n">
         <v>46323</v>
@@ -3537,7 +3537,7 @@
         <v>130</v>
       </c>
       <c r="M35" s="15" t="n">
-        <v>-0.6441475966276141</v>
+        <v>-0.645002730748225</v>
       </c>
       <c r="N35" s="12" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>300</v>
       </c>
       <c r="P35" s="15" t="n">
-        <v>-0.1788021460637249</v>
+        <v>-0.1807755324959039</v>
       </c>
       <c r="Q35" s="19" t="inlineStr">
         <is>
@@ -3589,13 +3589,13 @@
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>70.78</v>
+        <v>70.87</v>
       </c>
       <c r="E36" s="25" t="n">
-        <v>-0.052</v>
+        <v>-0.0508</v>
       </c>
       <c r="F36" s="25" t="n">
-        <v>-0.0193</v>
+        <v>-0.018</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>46329</v>
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="D37" s="13" t="n">
-        <v>545.22</v>
+        <v>543.73</v>
       </c>
       <c r="E37" s="14" t="n">
-        <v>0.0551</v>
+        <v>0.0522</v>
       </c>
       <c r="F37" s="14" t="n">
-        <v>0.1171</v>
+        <v>0.114</v>
       </c>
       <c r="G37" s="16" t="n"/>
       <c r="H37" s="21" t="inlineStr">
@@ -3675,7 +3675,7 @@
         <v>450</v>
       </c>
       <c r="M37" s="15" t="n">
-        <v>-0.1746450973918786</v>
+        <v>-0.1723833520313391</v>
       </c>
       <c r="N37" s="12" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>635</v>
       </c>
       <c r="P37" s="14" t="n">
-        <v>0.1646674736803491</v>
+        <v>0.1678590476891104</v>
       </c>
       <c r="Q37" s="19" t="inlineStr">
         <is>
@@ -3731,13 +3731,13 @@
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>95.5</v>
+        <v>95.05</v>
       </c>
       <c r="E38" s="25" t="n">
-        <v>-0.0366</v>
+        <v>-0.0412</v>
       </c>
       <c r="F38" s="25" t="n">
-        <v>-0.0234</v>
+        <v>-0.028</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>46325</v>
@@ -3766,7 +3766,7 @@
         <v>110</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>0.1518324607329843</v>
+        <v>0.1572856391372962</v>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>105</v>
       </c>
       <c r="P38" s="5" t="n">
-        <v>0.09947643979057591</v>
+        <v>0.1046817464492373</v>
       </c>
       <c r="Q38" s="9" t="inlineStr">
         <is>
@@ -3822,13 +3822,13 @@
         </is>
       </c>
       <c r="D39" s="13" t="n">
-        <v>87.03</v>
+        <v>87.73</v>
       </c>
       <c r="E39" s="15" t="n">
-        <v>-0.04849999999999999</v>
+        <v>-0.0408</v>
       </c>
       <c r="F39" s="15" t="n">
-        <v>-0.0534</v>
+        <v>-0.0457</v>
       </c>
       <c r="G39" s="16" t="n">
         <v>46325</v>
@@ -3857,7 +3857,7 @@
         <v>95</v>
       </c>
       <c r="M39" s="14" t="n">
-        <v>0.0915776169137079</v>
+        <v>0.08286789011740563</v>
       </c>
       <c r="N39" s="12" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>100</v>
       </c>
       <c r="P39" s="14" t="n">
-        <v>0.149029070435482</v>
+        <v>0.1398609369656901</v>
       </c>
       <c r="Q39" s="19" t="inlineStr">
         <is>
@@ -3913,13 +3913,13 @@
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>890.63</v>
+        <v>893.9299999999999</v>
       </c>
       <c r="E40" s="25" t="n">
-        <v>-0.0736</v>
+        <v>-0.0701</v>
       </c>
       <c r="F40" s="25" t="n">
-        <v>-0.0483</v>
+        <v>-0.0447</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>46289</v>
@@ -3948,7 +3948,7 @@
         <v>1000</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>0.1228007141012542</v>
+        <v>0.1186558231628875</v>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>1100</v>
       </c>
       <c r="P40" s="5" t="n">
-        <v>0.2350807855113796</v>
+        <v>0.2305214054791763</v>
       </c>
       <c r="Q40" s="9" t="inlineStr">
         <is>
@@ -4008,13 +4008,13 @@
         </is>
       </c>
       <c r="D41" s="13" t="n">
-        <v>123.92</v>
+        <v>124.95</v>
       </c>
       <c r="E41" s="14" t="n">
-        <v>0.0254</v>
-      </c>
-      <c r="F41" s="15" t="n">
-        <v>-0.0067</v>
+        <v>0.034</v>
+      </c>
+      <c r="F41" s="14" t="n">
+        <v>0.0016</v>
       </c>
       <c r="G41" s="16" t="n"/>
       <c r="H41" s="21" t="inlineStr">
@@ -4033,7 +4033,7 @@
         <v>125</v>
       </c>
       <c r="M41" s="14" t="n">
-        <v>0.008715300193673324</v>
+        <v>0.0004001600640255875</v>
       </c>
       <c r="N41" s="12" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>135</v>
       </c>
       <c r="P41" s="14" t="n">
-        <v>0.08941252420916719</v>
+        <v>0.08043217286914764</v>
       </c>
       <c r="Q41" s="19" t="inlineStr">
         <is>
@@ -4085,13 +4085,13 @@
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>24.64</v>
+        <v>24.73</v>
       </c>
       <c r="E42" s="25" t="n">
-        <v>-0.0075</v>
+        <v>-0.0036</v>
       </c>
       <c r="F42" s="25" t="n">
-        <v>-0.0474</v>
+        <v>-0.0437</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>46330</v>
@@ -4146,13 +4146,13 @@
         </is>
       </c>
       <c r="D43" s="13" t="n">
-        <v>87.76000000000001</v>
+        <v>88.06</v>
       </c>
       <c r="E43" s="15" t="n">
-        <v>-0.0119</v>
+        <v>-0.0086</v>
       </c>
       <c r="F43" s="14" t="n">
-        <v>0.0687</v>
+        <v>0.0723</v>
       </c>
       <c r="G43" s="16" t="n">
         <v>46315</v>
@@ -4181,7 +4181,7 @@
         <v>90</v>
       </c>
       <c r="M43" s="14" t="n">
-        <v>0.0255241567912488</v>
+        <v>0.02203043379513965</v>
       </c>
       <c r="N43" s="12" t="inlineStr">
         <is>
@@ -4191,8 +4191,8 @@
       <c r="O43" s="18" t="n">
         <v>88</v>
       </c>
-      <c r="P43" s="14" t="n">
-        <v>0.002734731084776605</v>
+      <c r="P43" s="15" t="n">
+        <v>-0.0006813536225301189</v>
       </c>
       <c r="Q43" s="19" t="inlineStr">
         <is>
@@ -4241,13 +4241,13 @@
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>60.87</v>
+        <v>60.75</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0.0803</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.0429</v>
+        <v>0.04099999999999999</v>
       </c>
       <c r="G44" s="6" t="n"/>
       <c r="H44" s="7" t="inlineStr">
@@ -4266,7 +4266,7 @@
         <v>58</v>
       </c>
       <c r="M44" s="25" t="n">
-        <v>-0.04714966321669127</v>
+        <v>-0.04526748971193416</v>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>78</v>
       </c>
       <c r="P44" s="5" t="n">
-        <v>0.2814194184327256</v>
+        <v>0.2839506172839506</v>
       </c>
       <c r="Q44" s="9" t="inlineStr">
         <is>
@@ -4318,13 +4318,13 @@
         </is>
       </c>
       <c r="D45" s="13" t="n">
-        <v>61.67</v>
+        <v>62.04</v>
       </c>
       <c r="E45" s="15" t="n">
-        <v>-0.0157</v>
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0.0233</v>
+        <v>0.0294</v>
       </c>
       <c r="G45" s="16" t="n">
         <v>46322</v>
@@ -4353,7 +4353,7 @@
         <v>70</v>
       </c>
       <c r="M45" s="14" t="n">
-        <v>0.1350737797956867</v>
+        <v>0.1283043197936815</v>
       </c>
       <c r="N45" s="12" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>71</v>
       </c>
       <c r="P45" s="14" t="n">
-        <v>0.1512891195070536</v>
+        <v>0.1444229529335913</v>
       </c>
       <c r="Q45" s="19" t="inlineStr">
         <is>
@@ -4413,13 +4413,13 @@
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>50.09</v>
+        <v>49.7</v>
       </c>
       <c r="E46" s="25" t="n">
-        <v>-0.09390000000000001</v>
+        <v>-0.1009</v>
       </c>
       <c r="F46" s="25" t="n">
-        <v>-0.0412</v>
+        <v>-0.0486</v>
       </c>
       <c r="G46" s="6" t="n">
         <v>46296</v>
@@ -4484,13 +4484,13 @@
         </is>
       </c>
       <c r="D47" s="13" t="n">
-        <v>44.38</v>
+        <v>44.51</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>-0.0634</v>
+        <v>-0.06059999999999999</v>
       </c>
       <c r="F47" s="15" t="n">
-        <v>-0.0702</v>
+        <v>-0.0674</v>
       </c>
       <c r="G47" s="16" t="n">
         <v>46331</v>
@@ -4545,13 +4545,13 @@
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>69.23999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0.0621</v>
+        <v>0.0692</v>
       </c>
       <c r="F48" s="25" t="n">
-        <v>-0.0726</v>
+        <v>-0.0664</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>46324</v>
@@ -4606,13 +4606,13 @@
         </is>
       </c>
       <c r="D49" s="13" t="n">
-        <v>133.29</v>
+        <v>133.66</v>
       </c>
       <c r="E49" s="15" t="n">
-        <v>-0.0488</v>
+        <v>-0.0462</v>
       </c>
       <c r="F49" s="15" t="n">
-        <v>-0.016</v>
+        <v>-0.0133</v>
       </c>
       <c r="G49" s="16" t="n">
         <v>46303</v>
@@ -4641,7 +4641,7 @@
         <v>140</v>
       </c>
       <c r="M49" s="14" t="n">
-        <v>0.05034136094230631</v>
+        <v>0.04743378722130782</v>
       </c>
       <c r="N49" s="12" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>150</v>
       </c>
       <c r="P49" s="14" t="n">
-        <v>0.1253657438667568</v>
+        <v>0.1222504863085441</v>
       </c>
       <c r="Q49" s="19" t="inlineStr">
         <is>
@@ -4701,13 +4701,13 @@
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>146.78</v>
+        <v>147.55</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0.0232</v>
+        <v>0.0286</v>
       </c>
       <c r="F50" s="25" t="n">
-        <v>-0.0158</v>
+        <v>-0.0106</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>46318</v>
@@ -4736,7 +4736,7 @@
         <v>164</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>0.1173184357541899</v>
+        <v>0.1114876313114198</v>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>162</v>
       </c>
       <c r="P50" s="5" t="n">
-        <v>0.1036926011718218</v>
+        <v>0.09793290410030489</v>
       </c>
       <c r="Q50" s="9" t="inlineStr">
         <is>
@@ -4800,13 +4800,13 @@
         </is>
       </c>
       <c r="D51" s="13" t="n">
-        <v>79.03</v>
+        <v>79.11</v>
       </c>
       <c r="E51" s="15" t="n">
-        <v>-0.0357</v>
+        <v>-0.0348</v>
       </c>
       <c r="F51" s="15" t="n">
-        <v>-0.0217</v>
+        <v>-0.0207</v>
       </c>
       <c r="G51" s="16" t="n">
         <v>46322</v>
@@ -4835,7 +4835,7 @@
         <v>100</v>
       </c>
       <c r="M51" s="14" t="n">
-        <v>0.2653422750854106</v>
+        <v>0.2640626975097965</v>
       </c>
       <c r="N51" s="12" t="inlineStr"/>
       <c r="O51" s="18" t="n"/>
@@ -4879,13 +4879,13 @@
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>158.98</v>
+        <v>159.83</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0.0426</v>
+        <v>0.0482</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.1389</v>
+        <v>0.145</v>
       </c>
       <c r="G52" s="6" t="n"/>
       <c r="H52" s="7" t="inlineStr">
@@ -4904,7 +4904,7 @@
         <v>140</v>
       </c>
       <c r="M52" s="25" t="n">
-        <v>-0.1193860863001635</v>
+        <v>-0.124069323656385</v>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>135</v>
       </c>
       <c r="P52" s="25" t="n">
-        <v>-0.1508365832180148</v>
+        <v>-0.1553525620972284</v>
       </c>
       <c r="Q52" s="9" t="inlineStr">
         <is>
@@ -4960,13 +4960,13 @@
         </is>
       </c>
       <c r="D53" s="13" t="n">
-        <v>106.49</v>
+        <v>106.79</v>
       </c>
       <c r="E53" s="15" t="n">
-        <v>-0.0757</v>
+        <v>-0.073</v>
       </c>
       <c r="F53" s="15" t="n">
-        <v>-0.0509</v>
+        <v>-0.0482</v>
       </c>
       <c r="G53" s="16" t="n"/>
       <c r="H53" s="21" t="inlineStr">
@@ -4985,7 +4985,7 @@
         <v>140</v>
       </c>
       <c r="M53" s="14" t="n">
-        <v>0.3146774345008921</v>
+        <v>0.3109841745481786</v>
       </c>
       <c r="N53" s="12" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>140</v>
       </c>
       <c r="P53" s="14" t="n">
-        <v>0.3146774345008921</v>
+        <v>0.3109841745481786</v>
       </c>
       <c r="Q53" s="19" t="inlineStr">
         <is>
@@ -5045,13 +5045,13 @@
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>56.26</v>
+        <v>56.56</v>
       </c>
       <c r="E54" s="25" t="n">
-        <v>-0.1269</v>
+        <v>-0.1222</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>0.0201</v>
+        <v>0.0257</v>
       </c>
       <c r="G54" s="6" t="n">
         <v>46317</v>
@@ -5087,7 +5087,7 @@
         <v>76</v>
       </c>
       <c r="P54" s="5" t="n">
-        <v>0.3508709562744401</v>
+        <v>0.3437057991513436</v>
       </c>
       <c r="Q54" s="9" t="inlineStr">
         <is>
@@ -5128,13 +5128,13 @@
         </is>
       </c>
       <c r="D55" s="13" t="n">
-        <v>131.82</v>
+        <v>133.19</v>
       </c>
       <c r="E55" s="14" t="n">
-        <v>0.0162</v>
+        <v>0.0267</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0.1395</v>
+        <v>0.1514</v>
       </c>
       <c r="G55" s="16" t="n">
         <v>46331</v>
@@ -5163,7 +5163,7 @@
         <v>183</v>
       </c>
       <c r="M55" s="14" t="n">
-        <v>0.3882567137005007</v>
+        <v>0.3739770253021999</v>
       </c>
       <c r="N55" s="12" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>145</v>
       </c>
       <c r="P55" s="14" t="n">
-        <v>0.09998482779547874</v>
+        <v>0.08867032059463925</v>
       </c>
       <c r="Q55" s="19" t="inlineStr">
         <is>
@@ -5215,13 +5215,13 @@
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>210.55</v>
+        <v>211.57</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0.0234</v>
+        <v>0.0283</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.1099</v>
+        <v>0.1152</v>
       </c>
       <c r="G56" s="6" t="n">
         <v>46325</v>
@@ -5250,7 +5250,7 @@
         <v>222</v>
       </c>
       <c r="M56" s="5" t="n">
-        <v>0.05438138209451431</v>
+        <v>0.04929810464621642</v>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>225</v>
       </c>
       <c r="P56" s="5" t="n">
-        <v>0.06862977914984558</v>
+        <v>0.06347780876305718</v>
       </c>
       <c r="Q56" s="9" t="inlineStr">
         <is>
@@ -5306,13 +5306,13 @@
         </is>
       </c>
       <c r="D57" s="13" t="n">
-        <v>144.15</v>
+        <v>145.47</v>
       </c>
       <c r="E57" s="15" t="n">
-        <v>-0.0306</v>
+        <v>-0.0217</v>
       </c>
       <c r="F57" s="14" t="n">
-        <v>0.0217</v>
+        <v>0.031</v>
       </c>
       <c r="G57" s="16" t="n">
         <v>46331</v>
@@ -5341,7 +5341,7 @@
         <v>196</v>
       </c>
       <c r="M57" s="14" t="n">
-        <v>0.3596947624002774</v>
+        <v>0.3473568433353956</v>
       </c>
       <c r="N57" s="12" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>170</v>
       </c>
       <c r="P57" s="14" t="n">
-        <v>0.1793270898369753</v>
+        <v>0.1686258335051901</v>
       </c>
       <c r="Q57" s="19" t="inlineStr">
         <is>
@@ -5397,13 +5397,13 @@
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>38.44</v>
+        <v>38.45</v>
       </c>
       <c r="E58" s="25" t="n">
-        <v>-0.0052</v>
+        <v>-0.0049</v>
       </c>
       <c r="F58" s="25" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="G58" s="6" t="n">
         <v>46324</v>
@@ -5458,13 +5458,13 @@
         </is>
       </c>
       <c r="D59" s="13" t="n">
-        <v>21.19</v>
+        <v>21.05</v>
       </c>
       <c r="E59" s="15" t="n">
-        <v>-0.0105</v>
+        <v>-0.0173</v>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0.0451</v>
+        <v>0.038</v>
       </c>
       <c r="G59" s="16" t="n">
         <v>46330</v>
@@ -5519,13 +5519,13 @@
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>193.9</v>
+        <v>196.94</v>
       </c>
       <c r="E60" s="25" t="n">
-        <v>-0.07679999999999999</v>
-      </c>
-      <c r="F60" s="25" t="n">
-        <v>-0.0076</v>
+        <v>-0.0623</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>0.008</v>
       </c>
       <c r="G60" s="6" t="n">
         <v>46328</v>
@@ -5580,13 +5580,13 @@
         </is>
       </c>
       <c r="D61" s="13" t="n">
-        <v>33.88</v>
+        <v>34.03</v>
       </c>
       <c r="E61" s="15" t="n">
-        <v>-0.0225</v>
+        <v>-0.0182</v>
       </c>
       <c r="F61" s="15" t="n">
-        <v>-0.035</v>
+        <v>-0.0308</v>
       </c>
       <c r="G61" s="16" t="n">
         <v>46315</v>
@@ -5622,7 +5622,7 @@
         <v>43</v>
       </c>
       <c r="P61" s="14" t="n">
-        <v>0.2691853600944509</v>
+        <v>0.2635909491625036</v>
       </c>
       <c r="Q61" s="19" t="inlineStr">
         <is>
@@ -5667,13 +5667,13 @@
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>31.08</v>
+        <v>31.31</v>
       </c>
       <c r="E62" s="25" t="n">
-        <v>-0.05429999999999999</v>
+        <v>-0.0475</v>
       </c>
       <c r="F62" s="25" t="n">
-        <v>-0.0459</v>
+        <v>-0.039</v>
       </c>
       <c r="G62" s="6" t="n">
         <v>46316</v>
@@ -5702,7 +5702,7 @@
         <v>35</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>0.1261261261261262</v>
+        <v>0.1178537208559566</v>
       </c>
       <c r="N62" s="3" t="inlineStr"/>
       <c r="O62" s="8" t="n"/>
@@ -5746,13 +5746,13 @@
         </is>
       </c>
       <c r="D63" s="13" t="n">
-        <v>269.9</v>
+        <v>274.21</v>
       </c>
       <c r="E63" s="14" t="n">
-        <v>0.1085</v>
+        <v>0.1262</v>
       </c>
       <c r="F63" s="14" t="n">
-        <v>0.2926</v>
+        <v>0.3133</v>
       </c>
       <c r="G63" s="16" t="n">
         <v>46330</v>
@@ -5807,13 +5807,13 @@
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>52.04</v>
+        <v>52.08</v>
       </c>
       <c r="E64" s="25" t="n">
-        <v>-0.022</v>
+        <v>-0.0212</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>0.1218</v>
+        <v>0.1227</v>
       </c>
       <c r="G64" s="6" t="n">
         <v>46311</v>
@@ -5849,7 +5849,7 @@
         <v>63</v>
       </c>
       <c r="P64" s="5" t="n">
-        <v>0.2106072252113759</v>
+        <v>0.2096774193548387</v>
       </c>
       <c r="Q64" s="9" t="inlineStr">
         <is>
@@ -5898,13 +5898,13 @@
         </is>
       </c>
       <c r="D65" s="13" t="n">
-        <v>43.29</v>
+        <v>42.93</v>
       </c>
       <c r="E65" s="15" t="n">
-        <v>-0.0064</v>
+        <v>-0.0147</v>
       </c>
       <c r="F65" s="15" t="n">
-        <v>-0.0241</v>
+        <v>-0.0322</v>
       </c>
       <c r="G65" s="16" t="n">
         <v>46328</v>
@@ -5959,13 +5959,13 @@
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>71.7</v>
+        <v>71.81</v>
       </c>
       <c r="E66" s="25" t="n">
-        <v>-0.0457</v>
+        <v>-0.0442</v>
       </c>
       <c r="F66" s="25" t="n">
-        <v>-0.0332</v>
+        <v>-0.0317</v>
       </c>
       <c r="G66" s="6" t="n">
         <v>46328</v>
@@ -5994,7 +5994,7 @@
         <v>89</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>0.2412831241283124</v>
+        <v>0.2393817017128533</v>
       </c>
       <c r="N66" s="3" t="inlineStr"/>
       <c r="O66" s="8" t="n"/>
@@ -6050,13 +6050,13 @@
         </is>
       </c>
       <c r="D67" s="13" t="n">
-        <v>161.99</v>
+        <v>163.27</v>
       </c>
       <c r="E67" s="15" t="n">
-        <v>-0.0216</v>
+        <v>-0.0138</v>
       </c>
       <c r="F67" s="14" t="n">
-        <v>0.0919</v>
+        <v>0.1005</v>
       </c>
       <c r="G67" s="16" t="n">
         <v>46325</v>
@@ -6085,7 +6085,7 @@
         <v>185</v>
       </c>
       <c r="M67" s="14" t="n">
-        <v>0.1420458052966232</v>
+        <v>0.1330924235928216</v>
       </c>
       <c r="N67" s="12" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>185</v>
       </c>
       <c r="P67" s="14" t="n">
-        <v>0.1420458052966232</v>
+        <v>0.1330924235928216</v>
       </c>
       <c r="Q67" s="19" t="inlineStr">
         <is>
@@ -6141,13 +6141,13 @@
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>116.32</v>
+        <v>116.6</v>
       </c>
       <c r="E68" s="25" t="n">
-        <v>-0.0445</v>
+        <v>-0.0421</v>
       </c>
       <c r="F68" s="25" t="n">
-        <v>-0.0626</v>
+        <v>-0.0603</v>
       </c>
       <c r="G68" s="6" t="n">
         <v>46329</v>
@@ -6176,7 +6176,7 @@
         <v>120</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>0.03163686382393403</v>
+        <v>0.02915951972555751</v>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>115</v>
       </c>
       <c r="P68" s="25" t="n">
-        <v>-0.01134800550206322</v>
+        <v>-0.01372212692967405</v>
       </c>
       <c r="Q68" s="9" t="inlineStr"/>
       <c r="R68" s="8" t="n"/>
@@ -6222,13 +6222,13 @@
         </is>
       </c>
       <c r="D69" s="13" t="n">
-        <v>297.23</v>
+        <v>296.05</v>
       </c>
       <c r="E69" s="15" t="n">
-        <v>-0.1339</v>
+        <v>-0.1374</v>
       </c>
       <c r="F69" s="15" t="n">
-        <v>-0.1807</v>
+        <v>-0.1839</v>
       </c>
       <c r="G69" s="16" t="n">
         <v>46325</v>
@@ -6257,7 +6257,7 @@
         <v>406</v>
       </c>
       <c r="M69" s="14" t="n">
-        <v>0.3659455640413147</v>
+        <v>0.3713899679108258</v>
       </c>
       <c r="N69" s="12" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>436</v>
       </c>
       <c r="P69" s="14" t="n">
-        <v>0.4668775022709685</v>
+        <v>0.4727242019929065</v>
       </c>
       <c r="Q69" s="19" t="inlineStr">
         <is>
@@ -6305,13 +6305,13 @@
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>314.25</v>
+        <v>311.17</v>
       </c>
       <c r="E70" s="25" t="n">
-        <v>-0.0717</v>
+        <v>-0.0808</v>
       </c>
       <c r="F70" s="25" t="n">
-        <v>-0.1071</v>
+        <v>-0.1158</v>
       </c>
       <c r="G70" s="6" t="n">
         <v>46311</v>
@@ -6340,7 +6340,7 @@
         <v>415</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>0.3206046141607001</v>
+        <v>0.3336761255905131</v>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
         <v>380</v>
       </c>
       <c r="P70" s="5" t="n">
-        <v>0.2092283214001591</v>
+        <v>0.2211974162033614</v>
       </c>
       <c r="Q70" s="9" t="inlineStr">
         <is>
@@ -6400,13 +6400,13 @@
         </is>
       </c>
       <c r="D71" s="13" t="n">
-        <v>58.19</v>
+        <v>58.18</v>
       </c>
       <c r="E71" s="15" t="n">
-        <v>-0.0941</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="F71" s="15" t="n">
-        <v>-0.03700000000000001</v>
+        <v>-0.0371</v>
       </c>
       <c r="G71" s="16" t="n">
         <v>46309</v>
@@ -6461,13 +6461,13 @@
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>1051.85</v>
+        <v>1053.96</v>
       </c>
       <c r="E72" s="25" t="n">
-        <v>-0.0888</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="F72" s="25" t="n">
-        <v>-0.0021</v>
+        <v>-0.0001</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>46308</v>
@@ -6499,7 +6499,7 @@
         <v>1245</v>
       </c>
       <c r="P72" s="5" t="n">
-        <v>0.1836288444169797</v>
+        <v>0.1812592508254582</v>
       </c>
       <c r="Q72" s="9" t="inlineStr">
         <is>
@@ -6544,13 +6544,13 @@
         </is>
       </c>
       <c r="D73" s="13" t="n">
-        <v>33.71</v>
+        <v>34.91</v>
       </c>
       <c r="E73" s="14" t="n">
-        <v>0.3692</v>
+        <v>0.418</v>
       </c>
       <c r="F73" s="14" t="n">
-        <v>0.4857</v>
+        <v>0.5386</v>
       </c>
       <c r="G73" s="16" t="n"/>
       <c r="H73" s="21" t="inlineStr">
@@ -6595,13 +6595,13 @@
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>23.63</v>
+        <v>23.89</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>0.2927</v>
+        <v>0.3069</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>0.4209000000000001</v>
+        <v>0.4366</v>
       </c>
       <c r="G74" s="6" t="n">
         <v>46346</v>
@@ -6656,13 +6656,13 @@
         </is>
       </c>
       <c r="D75" s="13" t="n">
-        <v>510.36</v>
+        <v>509.2</v>
       </c>
       <c r="E75" s="14" t="n">
-        <v>0.0147</v>
+        <v>0.0124</v>
       </c>
       <c r="F75" s="14" t="n">
-        <v>0.0389</v>
+        <v>0.0365</v>
       </c>
       <c r="G75" s="16" t="n">
         <v>46332</v>
@@ -6739,13 +6739,13 @@
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>65.51000000000001</v>
+        <v>65.12</v>
       </c>
       <c r="E76" s="25" t="n">
-        <v>-0.0556</v>
+        <v>-0.0613</v>
       </c>
       <c r="F76" s="25" t="n">
-        <v>-0.0498</v>
+        <v>-0.0554</v>
       </c>
       <c r="G76" s="6" t="n">
         <v>46321</v>
@@ -6774,7 +6774,7 @@
         <v>68</v>
       </c>
       <c r="M76" s="5" t="n">
-        <v>0.03800946420393825</v>
+        <v>0.04422604422604415</v>
       </c>
       <c r="N76" s="3" t="inlineStr"/>
       <c r="O76" s="8" t="n"/>
@@ -6816,13 +6816,13 @@
         </is>
       </c>
       <c r="D77" s="13" t="n">
-        <v>124.86</v>
+        <v>125.41</v>
       </c>
       <c r="E77" s="15" t="n">
-        <v>-0.1119</v>
+        <v>-0.108</v>
       </c>
       <c r="F77" s="14" t="n">
-        <v>0.0101</v>
+        <v>0.0146</v>
       </c>
       <c r="G77" s="16" t="n">
         <v>46310</v>
@@ -6881,13 +6881,13 @@
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>133.04</v>
+        <v>132.7</v>
       </c>
       <c r="E78" s="25" t="n">
-        <v>-0.0335</v>
+        <v>-0.036</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>0.0335</v>
+        <v>0.0309</v>
       </c>
       <c r="G78" s="6" t="n">
         <v>46308</v>
@@ -6919,7 +6919,7 @@
         <v>140</v>
       </c>
       <c r="P78" s="5" t="n">
-        <v>0.05231509320505118</v>
+        <v>0.05501130369253966</v>
       </c>
       <c r="Q78" s="9" t="inlineStr">
         <is>
@@ -6968,13 +6968,13 @@
         </is>
       </c>
       <c r="D79" s="13" t="n">
-        <v>339.07</v>
+        <v>341.9</v>
       </c>
       <c r="E79" s="15" t="n">
-        <v>-0.018</v>
+        <v>-0.0098</v>
       </c>
       <c r="F79" s="15" t="n">
-        <v>-0.0382</v>
+        <v>-0.0302</v>
       </c>
       <c r="G79" s="16" t="n">
         <v>46315</v>
@@ -7003,7 +7003,7 @@
         <v>358</v>
       </c>
       <c r="M79" s="14" t="n">
-        <v>0.05582917981537738</v>
+        <v>0.0470897923369407</v>
       </c>
       <c r="N79" s="12" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>374</v>
       </c>
       <c r="P79" s="14" t="n">
-        <v>0.1030170761199753</v>
+        <v>0.09388710149166431</v>
       </c>
       <c r="Q79" s="19" t="inlineStr">
         <is>
@@ -7059,13 +7059,13 @@
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>57.55</v>
+        <v>57.45</v>
       </c>
       <c r="E80" s="25" t="n">
-        <v>-0.0337</v>
+        <v>-0.0354</v>
       </c>
       <c r="F80" s="25" t="n">
-        <v>-0.0209</v>
+        <v>-0.0226</v>
       </c>
       <c r="G80" s="6" t="n">
         <v>46315</v>
@@ -7094,7 +7094,7 @@
         <v>57</v>
       </c>
       <c r="M80" s="25" t="n">
-        <v>-0.009556907037358769</v>
+        <v>-0.007832898172323809</v>
       </c>
       <c r="N80" s="3" t="inlineStr"/>
       <c r="O80" s="8" t="n"/>
@@ -7136,13 +7136,13 @@
         </is>
       </c>
       <c r="D81" s="13" t="n">
-        <v>13.18</v>
+        <v>13.35</v>
       </c>
       <c r="E81" s="14" t="n">
-        <v>0.1236</v>
+        <v>0.1381</v>
       </c>
       <c r="F81" s="15" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.0742</v>
       </c>
       <c r="G81" s="16" t="n"/>
       <c r="H81" s="21" t="inlineStr">
@@ -7187,13 +7187,13 @@
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>405.51</v>
+        <v>404.26</v>
       </c>
       <c r="E82" s="25" t="n">
-        <v>-0.0032</v>
+        <v>-0.0063</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="G82" s="6" t="n">
         <v>46330</v>
@@ -7260,13 +7260,13 @@
         </is>
       </c>
       <c r="D83" s="13" t="n">
-        <v>82.08</v>
+        <v>85.09</v>
       </c>
       <c r="E83" s="14" t="n">
-        <v>0.1444</v>
+        <v>0.1863</v>
       </c>
       <c r="F83" s="14" t="n">
-        <v>0.2542</v>
+        <v>0.3001</v>
       </c>
       <c r="G83" s="16" t="n">
         <v>46337</v>
@@ -7321,13 +7321,13 @@
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>41.83</v>
+        <v>41.35</v>
       </c>
       <c r="E84" s="25" t="n">
-        <v>-0.1042</v>
+        <v>-0.1146</v>
       </c>
       <c r="F84" s="25" t="n">
-        <v>-0.1776</v>
+        <v>-0.1871</v>
       </c>
       <c r="G84" s="6" t="n">
         <v>46331</v>
@@ -7382,13 +7382,13 @@
         </is>
       </c>
       <c r="D85" s="13" t="n">
-        <v>945.16</v>
+        <v>951.47</v>
       </c>
       <c r="E85" s="15" t="n">
-        <v>-0.0916</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="F85" s="15" t="n">
-        <v>-0.1041</v>
+        <v>-0.09820000000000001</v>
       </c>
       <c r="G85" s="16" t="n">
         <v>46308</v>
@@ -7417,7 +7417,7 @@
         <v>1325</v>
       </c>
       <c r="M85" s="14" t="n">
-        <v>0.4018790469338525</v>
+        <v>0.3925820046874836</v>
       </c>
       <c r="N85" s="12" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>1210</v>
       </c>
       <c r="P85" s="14" t="n">
-        <v>0.2802065258792162</v>
+        <v>0.2717163967334755</v>
       </c>
       <c r="Q85" s="19" t="inlineStr">
         <is>
@@ -7469,13 +7469,13 @@
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>130.52</v>
+        <v>132.66</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>0.0276</v>
+        <v>0.0445</v>
       </c>
       <c r="F86" s="25" t="n">
-        <v>-0.0669</v>
+        <v>-0.0516</v>
       </c>
       <c r="G86" s="6" t="n">
         <v>46324</v>
@@ -7530,13 +7530,13 @@
         </is>
       </c>
       <c r="D87" s="13" t="n">
-        <v>106.45</v>
+        <v>109.81</v>
       </c>
       <c r="E87" s="14" t="n">
-        <v>0.163</v>
+        <v>0.1997</v>
       </c>
       <c r="F87" s="14" t="n">
-        <v>0.0722</v>
+        <v>0.1061</v>
       </c>
       <c r="G87" s="16" t="n">
         <v>46330</v>
@@ -7591,13 +7591,13 @@
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>91.70999999999999</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>0.1352</v>
+        <v>0.1263</v>
       </c>
       <c r="F88" s="25" t="n">
-        <v>-0.09140000000000001</v>
+        <v>-0.09849999999999999</v>
       </c>
       <c r="G88" s="6" t="n">
         <v>46329</v>
@@ -7652,13 +7652,13 @@
         </is>
       </c>
       <c r="D89" s="13" t="n">
-        <v>153.63</v>
+        <v>153.3</v>
       </c>
       <c r="E89" s="15" t="n">
-        <v>-0.0163</v>
+        <v>-0.0184</v>
       </c>
       <c r="F89" s="14" t="n">
-        <v>0.0852</v>
+        <v>0.08289999999999999</v>
       </c>
       <c r="G89" s="16" t="n">
         <v>46324</v>
@@ -7713,13 +7713,13 @@
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>157.21</v>
+        <v>156.21</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>0.0267</v>
+        <v>0.0202</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0.0264</v>
+        <v>0.0199</v>
       </c>
       <c r="G90" s="6" t="n">
         <v>46329</v>
@@ -7788,13 +7788,13 @@
         </is>
       </c>
       <c r="D91" s="13" t="n">
-        <v>348.96</v>
+        <v>349.31</v>
       </c>
       <c r="E91" s="15" t="n">
-        <v>-0.0393</v>
+        <v>-0.0384</v>
       </c>
       <c r="F91" s="14" t="n">
-        <v>0.0298</v>
+        <v>0.0308</v>
       </c>
       <c r="G91" s="16" t="n">
         <v>46308</v>
@@ -7823,7 +7823,7 @@
         <v>196</v>
       </c>
       <c r="M91" s="15" t="n">
-        <v>-0.4383310408069693</v>
+        <v>-0.4388938192436518</v>
       </c>
       <c r="N91" s="12" t="inlineStr"/>
       <c r="O91" s="18" t="n"/>
@@ -7867,13 +7867,13 @@
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>98.34999999999999</v>
+        <v>98.19</v>
       </c>
       <c r="E92" s="25" t="n">
-        <v>-0.0825</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>0.0142</v>
+        <v>0.0126</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>46332</v>
@@ -7902,7 +7902,7 @@
         <v>375</v>
       </c>
       <c r="M92" s="5" t="n">
-        <v>2.812913065582105</v>
+        <v>2.819126183929117</v>
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         <v>368</v>
       </c>
       <c r="P92" s="5" t="n">
-        <v>2.741738688357906</v>
+        <v>2.747835828495774</v>
       </c>
       <c r="Q92" s="9" t="inlineStr">
         <is>
@@ -7966,13 +7966,13 @@
         </is>
       </c>
       <c r="D93" s="13" t="n">
-        <v>360.47</v>
+        <v>359.53</v>
       </c>
       <c r="E93" s="15" t="n">
-        <v>-0.0328</v>
+        <v>-0.0354</v>
       </c>
       <c r="F93" s="14" t="n">
-        <v>0.0295</v>
+        <v>0.0268</v>
       </c>
       <c r="G93" s="16" t="n">
         <v>46317</v>
@@ -8004,7 +8004,7 @@
         <v>115</v>
       </c>
       <c r="P93" s="15" t="n">
-        <v>-0.6809720642494521</v>
+        <v>-0.6801379578894667</v>
       </c>
       <c r="Q93" s="19" t="inlineStr">
         <is>
@@ -8053,13 +8053,13 @@
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>565.6900000000001</v>
+        <v>565.73</v>
       </c>
       <c r="E94" s="25" t="n">
-        <v>-0.015</v>
+        <v>-0.0149</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0.0333</v>
+        <v>0.0334</v>
       </c>
       <c r="G94" s="6" t="n">
         <v>46324</v>
@@ -8088,7 +8088,7 @@
         <v>366</v>
       </c>
       <c r="M94" s="25" t="n">
-        <v>-0.3530025278862982</v>
+        <v>-0.3530482739115833</v>
       </c>
       <c r="N94" s="3" t="inlineStr"/>
       <c r="O94" s="8" t="n"/>
@@ -8130,13 +8130,13 @@
         </is>
       </c>
       <c r="D95" s="13" t="n">
-        <v>1788.97</v>
+        <v>1785.24</v>
       </c>
       <c r="E95" s="15" t="n">
-        <v>-0.0144</v>
+        <v>-0.0164</v>
       </c>
       <c r="F95" s="15" t="n">
-        <v>-0.0956</v>
+        <v>-0.0975</v>
       </c>
       <c r="G95" s="16" t="n">
         <v>46330</v>
@@ -8201,13 +8201,13 @@
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>202.57</v>
+        <v>203.52</v>
       </c>
       <c r="E96" s="25" t="n">
-        <v>-0.0688</v>
+        <v>-0.0645</v>
       </c>
       <c r="F96" s="25" t="n">
-        <v>-0.0397</v>
+        <v>-0.0352</v>
       </c>
       <c r="G96" s="6" t="n">
         <v>46309</v>
@@ -8236,7 +8236,7 @@
         <v>668</v>
       </c>
       <c r="M96" s="5" t="n">
-        <v>2.297625512168633</v>
+        <v>2.282232704402516</v>
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>550</v>
       </c>
       <c r="P96" s="5" t="n">
-        <v>1.715110825887348</v>
+        <v>1.702437106918239</v>
       </c>
       <c r="Q96" s="9" t="inlineStr">
         <is>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="D97" s="13" t="n">
-        <v>117.92</v>
+        <v>115.94</v>
       </c>
       <c r="E97" s="14" t="n">
-        <v>0.04219999999999999</v>
+        <v>0.0247</v>
       </c>
       <c r="F97" s="14" t="n">
-        <v>0.05230000000000001</v>
+        <v>0.0346</v>
       </c>
       <c r="G97" s="16" t="n">
         <v>46321</v>
@@ -8331,7 +8331,7 @@
         <v>240</v>
       </c>
       <c r="M97" s="14" t="n">
-        <v>1.03527815468114</v>
+        <v>1.070036225633949</v>
       </c>
       <c r="N97" s="12" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>240</v>
       </c>
       <c r="P97" s="14" t="n">
-        <v>1.03527815468114</v>
+        <v>1.070036225633949</v>
       </c>
       <c r="Q97" s="19" t="inlineStr">
         <is>
@@ -8391,13 +8391,13 @@
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>232.32</v>
+        <v>232.01</v>
       </c>
       <c r="E98" s="25" t="n">
-        <v>-0.0864</v>
+        <v>-0.0876</v>
       </c>
       <c r="F98" s="25" t="n">
-        <v>-0.0712</v>
+        <v>-0.0725</v>
       </c>
       <c r="G98" s="6" t="n">
         <v>46310</v>
@@ -8426,7 +8426,7 @@
         <v>113</v>
       </c>
       <c r="M98" s="25" t="n">
-        <v>-0.5136019283746557</v>
+        <v>-0.5129520279298306</v>
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         <v>114</v>
       </c>
       <c r="P98" s="25" t="n">
-        <v>-0.509297520661157</v>
+        <v>-0.5086418688849619</v>
       </c>
       <c r="Q98" s="9" t="inlineStr"/>
       <c r="R98" s="8" t="n"/>
@@ -8476,13 +8476,13 @@
         </is>
       </c>
       <c r="D99" s="13" t="n">
-        <v>21.56</v>
+        <v>21.88</v>
       </c>
       <c r="E99" s="14" t="n">
-        <v>0.1399</v>
+        <v>0.1571</v>
       </c>
       <c r="F99" s="14" t="n">
-        <v>0.0832</v>
+        <v>0.09949999999999999</v>
       </c>
       <c r="G99" s="16" t="n">
         <v>46324</v>
@@ -8537,13 +8537,13 @@
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>14.84</v>
+        <v>14.82</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>0.0421</v>
+        <v>0.0407</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>0.1141</v>
+        <v>0.1126</v>
       </c>
       <c r="G100" s="6" t="n">
         <v>46323</v>
@@ -8598,13 +8598,13 @@
         </is>
       </c>
       <c r="D101" s="13" t="n">
-        <v>104.55</v>
+        <v>104.85</v>
       </c>
       <c r="E101" s="15" t="n">
-        <v>-0.0222</v>
+        <v>-0.0194</v>
       </c>
       <c r="F101" s="14" t="n">
-        <v>0.0521</v>
+        <v>0.0551</v>
       </c>
       <c r="G101" s="16" t="n">
         <v>46323</v>
@@ -8633,7 +8633,7 @@
         <v>285</v>
       </c>
       <c r="M101" s="14" t="n">
-        <v>1.72596843615495</v>
+        <v>1.718168812589414</v>
       </c>
       <c r="N101" s="12" t="inlineStr">
         <is>
@@ -8644,7 +8644,7 @@
         <v>285</v>
       </c>
       <c r="P101" s="14" t="n">
-        <v>1.72596843615495</v>
+        <v>1.718168812589414</v>
       </c>
       <c r="Q101" s="19" t="inlineStr">
         <is>
@@ -8685,13 +8685,13 @@
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>406.25</v>
+        <v>404.11</v>
       </c>
       <c r="E102" s="25" t="n">
-        <v>-0.0282</v>
+        <v>-0.0333</v>
       </c>
       <c r="F102" s="25" t="n">
-        <v>-0.09390000000000001</v>
+        <v>-0.0987</v>
       </c>
       <c r="G102" s="6" t="n">
         <v>46324</v>
@@ -8760,13 +8760,13 @@
         </is>
       </c>
       <c r="D103" s="13" t="n">
-        <v>48.43</v>
+        <v>48.45</v>
       </c>
       <c r="E103" s="15" t="n">
-        <v>-0.0759</v>
+        <v>-0.0756</v>
       </c>
       <c r="F103" s="15" t="n">
-        <v>-0.0504</v>
+        <v>-0.05</v>
       </c>
       <c r="G103" s="16" t="n">
         <v>46311</v>
@@ -8821,13 +8821,13 @@
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>369.51</v>
+        <v>369.93</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>0.0144</v>
+        <v>0.0156</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>0.0248</v>
+        <v>0.026</v>
       </c>
       <c r="G104" s="6" t="n">
         <v>46322</v>
@@ -8856,7 +8856,7 @@
         <v>525</v>
       </c>
       <c r="M104" s="5" t="n">
-        <v>0.4208005196070472</v>
+        <v>0.4191874138350499</v>
       </c>
       <c r="N104" s="3" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>543</v>
       </c>
       <c r="P104" s="5" t="n">
-        <v>0.4695136802792888</v>
+        <v>0.4678452680236801</v>
       </c>
       <c r="Q104" s="9" t="inlineStr">
         <is>
@@ -8912,13 +8912,13 @@
         </is>
       </c>
       <c r="D105" s="13" t="n">
-        <v>70.12</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E105" s="15" t="n">
-        <v>-0.0007000000000000001</v>
+        <v>-0.001</v>
       </c>
       <c r="F105" s="15" t="n">
-        <v>-0.0359</v>
+        <v>-0.0362</v>
       </c>
       <c r="G105" s="16" t="n">
         <v>46314</v>
@@ -8947,7 +8947,7 @@
         <v>412</v>
       </c>
       <c r="M105" s="14" t="n">
-        <v>4.87564175698802</v>
+        <v>4.877318116975749</v>
       </c>
       <c r="N105" s="12" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>350</v>
       </c>
       <c r="P105" s="14" t="n">
-        <v>3.991443240159726</v>
+        <v>3.992867332382311</v>
       </c>
       <c r="Q105" s="19" t="inlineStr">
         <is>
@@ -9003,13 +9003,13 @@
         </is>
       </c>
       <c r="D106" s="4" t="n">
-        <v>76.72</v>
+        <v>76.47</v>
       </c>
       <c r="E106" s="25" t="n">
-        <v>-0.0341</v>
+        <v>-0.0373</v>
       </c>
       <c r="F106" s="25" t="n">
-        <v>-0.03240000000000001</v>
+        <v>-0.0356</v>
       </c>
       <c r="G106" s="6" t="n">
         <v>46331</v>
@@ -9038,7 +9038,7 @@
         <v>68</v>
       </c>
       <c r="M106" s="25" t="n">
-        <v>-0.113660062565172</v>
+        <v>-0.1107623904799268</v>
       </c>
       <c r="N106" s="3" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         <v>68</v>
       </c>
       <c r="P106" s="25" t="n">
-        <v>-0.113660062565172</v>
+        <v>-0.1107623904799268</v>
       </c>
       <c r="Q106" s="9" t="inlineStr">
         <is>
@@ -9094,13 +9094,13 @@
         </is>
       </c>
       <c r="D107" s="13" t="n">
-        <v>262.72</v>
+        <v>264.02</v>
       </c>
       <c r="E107" s="14" t="n">
-        <v>0.0147</v>
+        <v>0.0197</v>
       </c>
       <c r="F107" s="14" t="n">
-        <v>0.0369</v>
+        <v>0.042</v>
       </c>
       <c r="G107" s="16" t="n">
         <v>46325</v>
@@ -9129,7 +9129,7 @@
         <v>295</v>
       </c>
       <c r="M107" s="14" t="n">
-        <v>0.1228684531059682</v>
+        <v>0.1173395954851906</v>
       </c>
       <c r="N107" s="12" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>246</v>
       </c>
       <c r="P107" s="15" t="n">
-        <v>-0.06364190012180278</v>
+        <v>-0.06825240512082412</v>
       </c>
       <c r="Q107" s="19" t="inlineStr">
         <is>
@@ -9177,13 +9177,13 @@
         </is>
       </c>
       <c r="D108" s="4" t="n">
-        <v>100.98</v>
+        <v>102.23</v>
       </c>
       <c r="E108" s="25" t="n">
-        <v>-0.1039</v>
-      </c>
-      <c r="F108" s="25" t="n">
-        <v>-0.0067</v>
+        <v>-0.09269999999999999</v>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>0.005600000000000001</v>
       </c>
       <c r="G108" s="6" t="n">
         <v>46316</v>
@@ -9212,7 +9212,7 @@
         <v>112</v>
       </c>
       <c r="M108" s="5" t="n">
-        <v>0.1091305208952267</v>
+        <v>0.09556881541621828</v>
       </c>
       <c r="N108" s="3" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>120</v>
       </c>
       <c r="P108" s="5" t="n">
-        <v>0.1883541295306001</v>
+        <v>0.173823730803091</v>
       </c>
       <c r="Q108" s="9" t="inlineStr">
         <is>
@@ -9276,13 +9276,13 @@
         </is>
       </c>
       <c r="D109" s="13" t="n">
-        <v>380.56</v>
+        <v>379.78</v>
       </c>
       <c r="E109" s="15" t="n">
-        <v>-0.1052</v>
+        <v>-0.107</v>
       </c>
       <c r="F109" s="14" t="n">
-        <v>0.045</v>
+        <v>0.0429</v>
       </c>
       <c r="G109" s="16" t="n">
         <v>46329</v>
@@ -9311,7 +9311,7 @@
         <v>390</v>
       </c>
       <c r="M109" s="14" t="n">
-        <v>0.02480554971620769</v>
+        <v>0.02691031649902582</v>
       </c>
       <c r="N109" s="12" t="inlineStr">
         <is>
@@ -9359,13 +9359,13 @@
         </is>
       </c>
       <c r="D110" s="4" t="n">
-        <v>182.79</v>
+        <v>181.38</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>0.0112</v>
+        <v>0.0034</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>0.1833</v>
+        <v>0.1741</v>
       </c>
       <c r="G110" s="6" t="n">
         <v>46331</v>
@@ -9394,7 +9394,7 @@
         <v>161</v>
       </c>
       <c r="M110" s="25" t="n">
-        <v>-0.1192078341265933</v>
+        <v>-0.1123607895027015</v>
       </c>
       <c r="N110" s="3" t="inlineStr">
         <is>
@@ -9405,7 +9405,7 @@
         <v>180</v>
       </c>
       <c r="P110" s="25" t="n">
-        <v>-0.01526341703594284</v>
+        <v>-0.00760833608997682</v>
       </c>
       <c r="Q110" s="9" t="inlineStr">
         <is>
@@ -9446,13 +9446,13 @@
         </is>
       </c>
       <c r="D111" s="13" t="n">
-        <v>43.02</v>
+        <v>43.55</v>
       </c>
       <c r="E111" s="15" t="n">
-        <v>-0.1476</v>
+        <v>-0.1371</v>
       </c>
       <c r="F111" s="15" t="n">
-        <v>-0.0171</v>
+        <v>-0.005</v>
       </c>
       <c r="G111" s="16" t="n">
         <v>46323</v>
@@ -9481,7 +9481,7 @@
         <v>55</v>
       </c>
       <c r="M111" s="14" t="n">
-        <v>0.2784751278475127</v>
+        <v>0.2629161882893227</v>
       </c>
       <c r="N111" s="12" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         <v>65</v>
       </c>
       <c r="P111" s="14" t="n">
-        <v>0.510925151092515</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="Q111" s="19" t="inlineStr">
         <is>
@@ -9533,13 +9533,13 @@
         </is>
       </c>
       <c r="D112" s="4" t="n">
-        <v>313.53</v>
+        <v>309.41</v>
       </c>
       <c r="E112" s="25" t="n">
-        <v>-0.008199999999999999</v>
+        <v>-0.0213</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>0.0314</v>
+        <v>0.0178</v>
       </c>
       <c r="G112" s="6" t="n">
         <v>46330</v>
@@ -9568,7 +9568,7 @@
         <v>331</v>
       </c>
       <c r="M112" s="5" t="n">
-        <v>0.0557203457404396</v>
+        <v>0.0697779645131055</v>
       </c>
       <c r="N112" s="3" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>330</v>
       </c>
       <c r="P112" s="5" t="n">
-        <v>0.05253085829107271</v>
+        <v>0.06654600691638918</v>
       </c>
       <c r="Q112" s="9" t="inlineStr">
         <is>
@@ -9628,13 +9628,13 @@
         </is>
       </c>
       <c r="D113" s="13" t="n">
-        <v>91.15000000000001</v>
+        <v>90.27</v>
       </c>
       <c r="E113" s="15" t="n">
-        <v>-0.0396</v>
+        <v>-0.0489</v>
       </c>
       <c r="F113" s="15" t="n">
-        <v>-0.153</v>
+        <v>-0.1611</v>
       </c>
       <c r="G113" s="16" t="n">
         <v>46330</v>
@@ -9663,7 +9663,7 @@
         <v>123</v>
       </c>
       <c r="M113" s="14" t="n">
-        <v>0.3494240263302248</v>
+        <v>0.3625789298770356</v>
       </c>
       <c r="N113" s="12" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>130</v>
       </c>
       <c r="P113" s="14" t="n">
-        <v>0.4262205156335709</v>
+        <v>0.4401240722277612</v>
       </c>
       <c r="Q113" s="19" t="inlineStr">
         <is>
@@ -9715,13 +9715,13 @@
         </is>
       </c>
       <c r="D114" s="4" t="n">
-        <v>210.35</v>
+        <v>212.5</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>0.05400000000000001</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>0.0459</v>
+        <v>0.0566</v>
       </c>
       <c r="G114" s="6" t="n">
         <v>46315</v>
@@ -9749,8 +9749,8 @@
       <c r="L114" s="8" t="n">
         <v>212</v>
       </c>
-      <c r="M114" s="5" t="n">
-        <v>0.007844069408129336</v>
+      <c r="M114" s="25" t="n">
+        <v>-0.002352941176470588</v>
       </c>
       <c r="N114" s="3" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         <v>205</v>
       </c>
       <c r="P114" s="25" t="n">
-        <v>-0.02543380080817682</v>
+        <v>-0.03529411764705882</v>
       </c>
       <c r="Q114" s="9" t="inlineStr">
         <is>
@@ -9806,13 +9806,13 @@
         </is>
       </c>
       <c r="D115" s="13" t="n">
-        <v>87.7</v>
+        <v>87.93000000000001</v>
       </c>
       <c r="E115" s="15" t="n">
-        <v>-0.0212</v>
+        <v>-0.0186</v>
       </c>
       <c r="F115" s="14" t="n">
-        <v>0.1587</v>
+        <v>0.1617</v>
       </c>
       <c r="G115" s="16" t="n">
         <v>46324</v>
@@ -9841,7 +9841,7 @@
         <v>85</v>
       </c>
       <c r="M115" s="15" t="n">
-        <v>-0.03078677309007985</v>
+        <v>-0.03332196065051753</v>
       </c>
       <c r="N115" s="12" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>90</v>
       </c>
       <c r="P115" s="14" t="n">
-        <v>0.02622576966932722</v>
+        <v>0.02354145342886379</v>
       </c>
       <c r="Q115" s="19" t="inlineStr">
         <is>
@@ -9893,13 +9893,13 @@
         </is>
       </c>
       <c r="D116" s="4" t="n">
-        <v>148.95</v>
+        <v>150.89</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0.0384</v>
+        <v>0.0519</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>0.1181</v>
+        <v>0.1327</v>
       </c>
       <c r="G116" s="6" t="n">
         <v>46324</v>
@@ -9928,7 +9928,7 @@
         <v>165</v>
       </c>
       <c r="M116" s="5" t="n">
-        <v>0.1077542799597181</v>
+        <v>0.09351182980979532</v>
       </c>
       <c r="N116" s="3" t="inlineStr"/>
       <c r="O116" s="8" t="n"/>
@@ -9976,13 +9976,13 @@
         </is>
       </c>
       <c r="D117" s="13" t="n">
-        <v>503.04</v>
+        <v>506.48</v>
       </c>
       <c r="E117" s="15" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.08470000000000001</v>
       </c>
       <c r="F117" s="15" t="n">
-        <v>-0.1078</v>
+        <v>-0.1017</v>
       </c>
       <c r="G117" s="16" t="n">
         <v>46328</v>
@@ -10047,13 +10047,13 @@
         </is>
       </c>
       <c r="D118" s="4" t="n">
-        <v>379.59</v>
+        <v>383.54</v>
       </c>
       <c r="E118" s="25" t="n">
-        <v>-0.0296</v>
+        <v>-0.0195</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="G118" s="6" t="n">
         <v>46315</v>
@@ -10082,7 +10082,7 @@
         <v>487</v>
       </c>
       <c r="M118" s="5" t="n">
-        <v>0.2829631971337497</v>
+        <v>0.2697502216196485</v>
       </c>
       <c r="N118" s="3" t="inlineStr">
         <is>
@@ -10093,7 +10093,7 @@
         <v>375</v>
       </c>
       <c r="P118" s="25" t="n">
-        <v>-0.01209199399351926</v>
+        <v>-0.02226625645304276</v>
       </c>
       <c r="Q118" s="9" t="inlineStr">
         <is>
@@ -10138,13 +10138,13 @@
         </is>
       </c>
       <c r="D119" s="13" t="n">
-        <v>269.32</v>
+        <v>270.22</v>
       </c>
       <c r="E119" s="15" t="n">
-        <v>-0.0066</v>
+        <v>-0.0033</v>
       </c>
       <c r="F119" s="14" t="n">
-        <v>0.0824</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="G119" s="16" t="n">
         <v>46308</v>
@@ -10173,7 +10173,7 @@
         <v>272</v>
       </c>
       <c r="M119" s="14" t="n">
-        <v>0.009950987672657088</v>
+        <v>0.006587225223891542</v>
       </c>
       <c r="N119" s="12" t="inlineStr"/>
       <c r="O119" s="18" t="n"/>
@@ -10225,13 +10225,13 @@
         </is>
       </c>
       <c r="D120" s="4" t="n">
-        <v>1144.43</v>
+        <v>1152.44</v>
       </c>
       <c r="E120" s="25" t="n">
-        <v>-0.0663</v>
-      </c>
-      <c r="F120" s="25" t="n">
-        <v>-0.0022</v>
+        <v>-0.05980000000000001</v>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>0.0048</v>
       </c>
       <c r="G120" s="6" t="n">
         <v>46324</v>
@@ -10260,7 +10260,7 @@
         <v>1280</v>
       </c>
       <c r="M120" s="5" t="n">
-        <v>0.118460718436252</v>
+        <v>0.1106868904237964</v>
       </c>
       <c r="N120" s="3" t="inlineStr">
         <is>
@@ -10320,13 +10320,13 @@
         </is>
       </c>
       <c r="D121" s="13" t="n">
-        <v>92.63</v>
+        <v>92.77</v>
       </c>
       <c r="E121" s="14" t="n">
-        <v>0.0059</v>
+        <v>0.0074</v>
       </c>
       <c r="F121" s="14" t="n">
-        <v>0.1121</v>
+        <v>0.1138</v>
       </c>
       <c r="G121" s="16" t="n"/>
       <c r="H121" s="21" t="inlineStr">
@@ -10345,7 +10345,7 @@
         <v>102</v>
       </c>
       <c r="M121" s="14" t="n">
-        <v>0.1011551333261363</v>
+        <v>0.09949337070173553</v>
       </c>
       <c r="N121" s="12" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>105</v>
       </c>
       <c r="P121" s="14" t="n">
-        <v>0.1335420490121991</v>
+        <v>0.1318314110164925</v>
       </c>
       <c r="Q121" s="19" t="inlineStr">
         <is>
@@ -10397,13 +10397,13 @@
         </is>
       </c>
       <c r="D122" s="4" t="n">
-        <v>146.89</v>
+        <v>147.15</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0.0867</v>
+        <v>0.0886</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>0.1808</v>
+        <v>0.1829</v>
       </c>
       <c r="G122" s="6" t="n">
         <v>46324</v>
@@ -10432,7 +10432,7 @@
         <v>150</v>
       </c>
       <c r="M122" s="5" t="n">
-        <v>0.02117230580706661</v>
+        <v>0.01936799184505603</v>
       </c>
       <c r="N122" s="3" t="inlineStr"/>
       <c r="O122" s="8" t="n"/>
@@ -10476,13 +10476,13 @@
         </is>
       </c>
       <c r="D123" s="13" t="n">
-        <v>140.9</v>
+        <v>140.92</v>
       </c>
       <c r="E123" s="15" t="n">
-        <v>-0.0883</v>
+        <v>-0.0882</v>
       </c>
       <c r="F123" s="15" t="n">
-        <v>-0.0579</v>
+        <v>-0.0578</v>
       </c>
       <c r="G123" s="16" t="n">
         <v>46322</v>
@@ -10555,13 +10555,13 @@
         </is>
       </c>
       <c r="D124" s="4" t="n">
-        <v>27.74</v>
+        <v>27.64</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0.0178</v>
+        <v>0.0143</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>0.1206</v>
+        <v>0.1168</v>
       </c>
       <c r="G124" s="6" t="n">
         <v>46329</v>
@@ -10590,7 +10590,7 @@
         <v>28</v>
       </c>
       <c r="M124" s="5" t="n">
-        <v>0.009372746935832789</v>
+        <v>0.01302460202604918</v>
       </c>
       <c r="N124" s="3" t="inlineStr"/>
       <c r="O124" s="8" t="n"/>
@@ -10634,13 +10634,13 @@
         </is>
       </c>
       <c r="D125" s="13" t="n">
-        <v>280.68</v>
+        <v>280.13</v>
       </c>
       <c r="E125" s="15" t="n">
-        <v>-0.153</v>
+        <v>-0.1546</v>
       </c>
       <c r="F125" s="15" t="n">
-        <v>-0.1205</v>
+        <v>-0.1222</v>
       </c>
       <c r="G125" s="16" t="n">
         <v>46324</v>
@@ -10669,7 +10669,7 @@
         <v>418</v>
       </c>
       <c r="M125" s="14" t="n">
-        <v>0.4892404161322502</v>
+        <v>0.4921643522650198</v>
       </c>
       <c r="N125" s="12" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>350</v>
       </c>
       <c r="P125" s="14" t="n">
-        <v>0.2469716403021234</v>
+        <v>0.2494199121836291</v>
       </c>
       <c r="Q125" s="19" t="inlineStr">
         <is>
@@ -10725,13 +10725,13 @@
         </is>
       </c>
       <c r="D126" s="4" t="n">
-        <v>655.46</v>
+        <v>658.3200000000001</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>0.1128</v>
+        <v>0.1176</v>
       </c>
       <c r="F126" s="5" t="n">
-        <v>0.2456</v>
+        <v>0.251</v>
       </c>
       <c r="G126" s="6" t="n">
         <v>46323</v>
@@ -10760,7 +10760,7 @@
         <v>615</v>
       </c>
       <c r="M126" s="25" t="n">
-        <v>-0.06172764165624147</v>
+        <v>-0.06580386438206351</v>
       </c>
       <c r="N126" s="3" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>570</v>
       </c>
       <c r="P126" s="25" t="n">
-        <v>-0.1303817166570043</v>
+        <v>-0.1341596791833759</v>
       </c>
       <c r="Q126" s="9" t="inlineStr">
         <is>
@@ -10820,13 +10820,13 @@
         </is>
       </c>
       <c r="D127" s="13" t="n">
-        <v>377.24</v>
+        <v>375.21</v>
       </c>
       <c r="E127" s="15" t="n">
-        <v>-0.0424</v>
+        <v>-0.0475</v>
       </c>
       <c r="F127" s="15" t="n">
-        <v>-0.1051</v>
+        <v>-0.1099</v>
       </c>
       <c r="G127" s="16" t="n">
         <v>46308</v>
@@ -10855,7 +10855,7 @@
         <v>526</v>
       </c>
       <c r="M127" s="14" t="n">
-        <v>0.3943378220761319</v>
+        <v>0.4018816129634072</v>
       </c>
       <c r="N127" s="12" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>480</v>
       </c>
       <c r="P127" s="14" t="n">
-        <v>0.2723995334535044</v>
+        <v>0.2792836011833374</v>
       </c>
       <c r="Q127" s="19" t="inlineStr">
         <is>
@@ -10911,13 +10911,13 @@
         </is>
       </c>
       <c r="D128" s="4" t="n">
-        <v>72.28</v>
+        <v>73.02</v>
       </c>
       <c r="E128" s="25" t="n">
-        <v>-0.0227</v>
+        <v>-0.0127</v>
       </c>
       <c r="F128" s="25" t="n">
-        <v>-0.05139999999999999</v>
+        <v>-0.0417</v>
       </c>
       <c r="G128" s="6" t="n">
         <v>46329</v>
@@ -10990,13 +10990,13 @@
         </is>
       </c>
       <c r="D129" s="13" t="n">
-        <v>272.67</v>
+        <v>272.24</v>
       </c>
       <c r="E129" s="14" t="n">
-        <v>0.0125</v>
+        <v>0.0109</v>
       </c>
       <c r="F129" s="14" t="n">
-        <v>0.0683</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="G129" s="16" t="n">
         <v>46330</v>
@@ -11025,7 +11025,7 @@
         <v>248</v>
       </c>
       <c r="M129" s="15" t="n">
-        <v>-0.09047566655664362</v>
+        <v>-0.08903908316191599</v>
       </c>
       <c r="N129" s="12" t="inlineStr"/>
       <c r="O129" s="18" t="n"/>
@@ -11081,13 +11081,13 @@
         </is>
       </c>
       <c r="D130" s="4" t="n">
-        <v>120.81</v>
+        <v>121.57</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>0.2271</v>
+        <v>0.2348</v>
       </c>
       <c r="F130" s="5" t="n">
-        <v>0.0755</v>
+        <v>0.0823</v>
       </c>
       <c r="G130" s="6" t="n">
         <v>46325</v>
@@ -11142,13 +11142,13 @@
         </is>
       </c>
       <c r="D131" s="13" t="n">
-        <v>233.13</v>
+        <v>234.32</v>
       </c>
       <c r="E131" s="15" t="n">
-        <v>-0.0674</v>
+        <v>-0.06269999999999999</v>
       </c>
       <c r="F131" s="15" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0038</v>
       </c>
       <c r="G131" s="16" t="n">
         <v>46324</v>
@@ -11203,13 +11203,13 @@
         </is>
       </c>
       <c r="D132" s="4" t="n">
-        <v>200.29</v>
+        <v>197</v>
       </c>
       <c r="E132" s="25" t="n">
-        <v>-0.1021</v>
+        <v>-0.1168</v>
       </c>
       <c r="F132" s="25" t="n">
-        <v>-0.0438</v>
+        <v>-0.0596</v>
       </c>
       <c r="G132" s="6" t="n">
         <v>46330</v>
@@ -11238,7 +11238,7 @@
         <v>250</v>
       </c>
       <c r="M132" s="5" t="n">
-        <v>0.2481901243197364</v>
+        <v>0.2690355329949238</v>
       </c>
       <c r="N132" s="3" t="inlineStr"/>
       <c r="O132" s="8" t="n"/>
@@ -11282,13 +11282,13 @@
         </is>
       </c>
       <c r="D133" s="13" t="n">
-        <v>165.61</v>
+        <v>164.31</v>
       </c>
       <c r="E133" s="15" t="n">
-        <v>-0.025</v>
+        <v>-0.0327</v>
       </c>
       <c r="F133" s="14" t="n">
-        <v>0.1039</v>
+        <v>0.0953</v>
       </c>
       <c r="G133" s="16" t="n">
         <v>46329</v>
@@ -11353,13 +11353,13 @@
         </is>
       </c>
       <c r="D134" s="4" t="n">
-        <v>798.84</v>
+        <v>798.5700000000001</v>
       </c>
       <c r="E134" s="25" t="n">
-        <v>-0.05</v>
+        <v>-0.0503</v>
       </c>
       <c r="F134" s="25" t="n">
-        <v>-0.0757</v>
+        <v>-0.076</v>
       </c>
       <c r="G134" s="6" t="n">
         <v>46330</v>
@@ -11388,7 +11388,7 @@
         <v>1155</v>
       </c>
       <c r="M134" s="5" t="n">
-        <v>0.4458464773922187</v>
+        <v>0.4463353243923512</v>
       </c>
       <c r="N134" s="3" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>1103</v>
       </c>
       <c r="P134" s="5" t="n">
-        <v>0.3807520905312703</v>
+        <v>0.381218928835293</v>
       </c>
       <c r="Q134" s="9" t="inlineStr">
         <is>
@@ -11440,13 +11440,13 @@
         </is>
       </c>
       <c r="D135" s="13" t="n">
-        <v>527.75</v>
+        <v>523.88</v>
       </c>
       <c r="E135" s="15" t="n">
-        <v>-0.1499</v>
+        <v>-0.1561</v>
       </c>
       <c r="F135" s="15" t="n">
-        <v>-0.1747</v>
+        <v>-0.1807</v>
       </c>
       <c r="G135" s="16" t="n">
         <v>46331</v>
@@ -11475,7 +11475,7 @@
         <v>874</v>
       </c>
       <c r="M135" s="14" t="n">
-        <v>0.6560871624822359</v>
+        <v>0.6683209895395892</v>
       </c>
       <c r="N135" s="12" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>845</v>
       </c>
       <c r="P135" s="14" t="n">
-        <v>0.6011369019422075</v>
+        <v>0.6129648010994885</v>
       </c>
       <c r="Q135" s="19" t="inlineStr">
         <is>
@@ -11535,13 +11535,13 @@
         </is>
       </c>
       <c r="D136" s="4" t="n">
-        <v>196.71</v>
+        <v>197.96</v>
       </c>
       <c r="E136" s="25" t="n">
-        <v>-0.0138</v>
+        <v>-0.0075</v>
       </c>
       <c r="F136" s="25" t="n">
-        <v>-0.0252</v>
+        <v>-0.019</v>
       </c>
       <c r="G136" s="6" t="n">
         <v>46288</v>
@@ -11570,7 +11570,7 @@
         <v>250</v>
       </c>
       <c r="M136" s="5" t="n">
-        <v>0.2709064104519343</v>
+        <v>0.2628813901798343</v>
       </c>
       <c r="N136" s="3" t="inlineStr"/>
       <c r="O136" s="8" t="n"/>
@@ -11614,13 +11614,13 @@
         </is>
       </c>
       <c r="D137" s="13" t="n">
-        <v>676.83</v>
+        <v>685.63</v>
       </c>
       <c r="E137" s="14" t="n">
-        <v>0.1497</v>
+        <v>0.1646</v>
       </c>
       <c r="F137" s="14" t="n">
-        <v>0.155</v>
+        <v>0.17</v>
       </c>
       <c r="G137" s="16" t="n"/>
       <c r="H137" s="21" t="inlineStr">
@@ -11639,7 +11639,7 @@
         <v>750</v>
       </c>
       <c r="M137" s="14" t="n">
-        <v>0.1081069101546917</v>
+        <v>0.09388445663112759</v>
       </c>
       <c r="N137" s="12" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>641.29</v>
       </c>
       <c r="P137" s="15" t="n">
-        <v>-0.05250949278253043</v>
+        <v>-0.06467044907603231</v>
       </c>
       <c r="Q137" s="19" t="inlineStr">
         <is>
@@ -11691,13 +11691,13 @@
         </is>
       </c>
       <c r="D138" s="4" t="n">
-        <v>147.54</v>
+        <v>147.4</v>
       </c>
       <c r="E138" s="25" t="n">
-        <v>-0.0649</v>
+        <v>-0.0658</v>
       </c>
       <c r="F138" s="5" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.07919999999999999</v>
       </c>
       <c r="G138" s="6" t="n">
         <v>46330</v>
@@ -11733,7 +11733,7 @@
         <v>185</v>
       </c>
       <c r="P138" s="5" t="n">
-        <v>0.253897248203877</v>
+        <v>0.2550881953867028</v>
       </c>
       <c r="Q138" s="9" t="inlineStr">
         <is>
@@ -11772,13 +11772,13 @@
         </is>
       </c>
       <c r="D139" s="13" t="n">
-        <v>410.58</v>
+        <v>409.46</v>
       </c>
       <c r="E139" s="15" t="n">
-        <v>-0.0481</v>
+        <v>-0.0507</v>
       </c>
       <c r="F139" s="14" t="n">
-        <v>0.0228</v>
+        <v>0.0201</v>
       </c>
       <c r="G139" s="16" t="n">
         <v>46329</v>
@@ -11814,7 +11814,7 @@
         <v>453</v>
       </c>
       <c r="P139" s="14" t="n">
-        <v>0.1033172585123484</v>
+        <v>0.106335173154887</v>
       </c>
       <c r="Q139" s="19" t="inlineStr">
         <is>
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="D140" s="4" t="n">
-        <v>48.72</v>
+        <v>49.18</v>
       </c>
       <c r="E140" s="25" t="n">
-        <v>-0.0496</v>
+        <v>-0.0408</v>
       </c>
       <c r="F140" s="5" t="n">
-        <v>0.0886</v>
+        <v>0.0987</v>
       </c>
       <c r="G140" s="6" t="n">
         <v>46309</v>
@@ -11934,13 +11934,13 @@
         </is>
       </c>
       <c r="D141" s="13" t="n">
-        <v>304.95</v>
+        <v>305.88</v>
       </c>
       <c r="E141" s="15" t="n">
-        <v>-0.07139999999999999</v>
+        <v>-0.06849999999999999</v>
       </c>
       <c r="F141" s="15" t="n">
-        <v>-0.004099999999999999</v>
+        <v>-0.0011</v>
       </c>
       <c r="G141" s="16" t="n">
         <v>46282</v>
@@ -11969,7 +11969,7 @@
         <v>425</v>
       </c>
       <c r="M141" s="14" t="n">
-        <v>0.3936710936219053</v>
+        <v>0.3894337648751144</v>
       </c>
       <c r="N141" s="12" t="inlineStr">
         <is>
@@ -11980,7 +11980,7 @@
         <v>323</v>
       </c>
       <c r="P141" s="14" t="n">
-        <v>0.05919003115264802</v>
+        <v>0.05596966130508698</v>
       </c>
       <c r="Q141" s="19" t="inlineStr">
         <is>
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="D142" s="4" t="n">
-        <v>214.99</v>
+        <v>214.26</v>
       </c>
       <c r="E142" s="25" t="n">
-        <v>-0.1206</v>
+        <v>-0.1236</v>
       </c>
       <c r="F142" s="25" t="n">
-        <v>-0.0613</v>
+        <v>-0.0644</v>
       </c>
       <c r="G142" s="6" t="n"/>
       <c r="H142" s="7" t="inlineStr">
@@ -12046,7 +12046,7 @@
         <v>285</v>
       </c>
       <c r="M142" s="5" t="n">
-        <v>0.3256430531652634</v>
+        <v>0.3301596191542986</v>
       </c>
       <c r="N142" s="3" t="inlineStr"/>
       <c r="O142" s="8" t="n"/>
@@ -12094,13 +12094,13 @@
         </is>
       </c>
       <c r="D143" s="13" t="n">
-        <v>1588.77</v>
+        <v>1573.96</v>
       </c>
       <c r="E143" s="15" t="n">
-        <v>-0.0864</v>
+        <v>-0.0949</v>
       </c>
       <c r="F143" s="15" t="n">
-        <v>-0.0721</v>
+        <v>-0.08070000000000001</v>
       </c>
       <c r="G143" s="16" t="n">
         <v>46317</v>
@@ -12155,13 +12155,13 @@
         </is>
       </c>
       <c r="D144" s="4" t="n">
-        <v>53.42</v>
+        <v>54.96</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>0</v>
+        <v>0.0288</v>
       </c>
       <c r="F144" s="5" t="n">
-        <v>0.0794</v>
+        <v>0.1105</v>
       </c>
       <c r="G144" s="6" t="n">
         <v>46332</v>
@@ -12216,13 +12216,13 @@
         </is>
       </c>
       <c r="D145" s="13" t="n">
-        <v>355.74</v>
+        <v>355.95</v>
       </c>
       <c r="E145" s="15" t="n">
-        <v>-0.0959</v>
+        <v>-0.09539999999999998</v>
       </c>
       <c r="F145" s="15" t="n">
-        <v>-0.0401</v>
+        <v>-0.0395</v>
       </c>
       <c r="G145" s="16" t="n">
         <v>46318</v>
@@ -12251,7 +12251,7 @@
         <v>400</v>
       </c>
       <c r="M145" s="14" t="n">
-        <v>0.1244167088322932</v>
+        <v>0.1237533361427167</v>
       </c>
       <c r="N145" s="12" t="inlineStr"/>
       <c r="O145" s="18" t="n"/>
@@ -12303,13 +12303,13 @@
         </is>
       </c>
       <c r="D146" s="4" t="n">
-        <v>316.86</v>
+        <v>313.47</v>
       </c>
       <c r="E146" s="25" t="n">
-        <v>-0.1552</v>
+        <v>-0.1643</v>
       </c>
       <c r="F146" s="25" t="n">
-        <v>-0.0716</v>
+        <v>-0.0815</v>
       </c>
       <c r="G146" s="6" t="n">
         <v>46315</v>
@@ -12338,7 +12338,7 @@
         <v>390</v>
       </c>
       <c r="M146" s="5" t="n">
-        <v>0.2308274947926529</v>
+        <v>0.2441381950425877</v>
       </c>
       <c r="N146" s="3" t="inlineStr"/>
       <c r="O146" s="8" t="n"/>
@@ -12390,13 +12390,13 @@
         </is>
       </c>
       <c r="D147" s="13" t="n">
-        <v>946.8200000000001</v>
+        <v>924.9299999999999</v>
       </c>
       <c r="E147" s="15" t="n">
-        <v>-0.0574</v>
+        <v>-0.07919999999999999</v>
       </c>
       <c r="F147" s="15" t="n">
-        <v>-0.1226</v>
+        <v>-0.1429</v>
       </c>
       <c r="G147" s="16" t="n">
         <v>46316</v>
@@ -12425,7 +12425,7 @@
         <v>1259</v>
       </c>
       <c r="M147" s="14" t="n">
-        <v>0.3297142012209289</v>
+        <v>0.3611840896067811</v>
       </c>
       <c r="N147" s="12" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>1350</v>
       </c>
       <c r="P147" s="14" t="n">
-        <v>0.425825394478359</v>
+        <v>0.4595699133988519</v>
       </c>
       <c r="Q147" s="19" t="inlineStr">
         <is>
@@ -12481,13 +12481,13 @@
         </is>
       </c>
       <c r="D148" s="4" t="n">
-        <v>1255.6</v>
+        <v>1262.61</v>
       </c>
       <c r="E148" s="25" t="n">
-        <v>-0.0445</v>
+        <v>-0.0392</v>
       </c>
       <c r="F148" s="25" t="n">
-        <v>-0.0843</v>
+        <v>-0.07919999999999999</v>
       </c>
       <c r="G148" s="6" t="n">
         <v>46325</v>
@@ -12556,13 +12556,13 @@
         </is>
       </c>
       <c r="D149" s="13" t="n">
-        <v>205.5</v>
+        <v>206.49</v>
       </c>
       <c r="E149" s="15" t="n">
-        <v>-0.0975</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="F149" s="15" t="n">
-        <v>-0.09140000000000001</v>
+        <v>-0.08710000000000001</v>
       </c>
       <c r="G149" s="16" t="n">
         <v>46317</v>
@@ -12617,13 +12617,13 @@
         </is>
       </c>
       <c r="D150" s="4" t="n">
-        <v>440.29</v>
+        <v>443.23</v>
       </c>
       <c r="E150" s="25" t="n">
-        <v>-0.09</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="F150" s="25" t="n">
-        <v>-0.09210000000000002</v>
+        <v>-0.0861</v>
       </c>
       <c r="G150" s="6" t="n">
         <v>46322</v>
@@ -12684,13 +12684,13 @@
         </is>
       </c>
       <c r="D151" s="13" t="n">
-        <v>266.76</v>
+        <v>267.51</v>
       </c>
       <c r="E151" s="15" t="n">
-        <v>-0.0629</v>
+        <v>-0.0602</v>
       </c>
       <c r="F151" s="15" t="n">
-        <v>-0.0181</v>
+        <v>-0.0154</v>
       </c>
       <c r="G151" s="16" t="n">
         <v>46318</v>
@@ -12722,7 +12722,7 @@
         <v>272</v>
       </c>
       <c r="P151" s="14" t="n">
-        <v>0.01964312490628283</v>
+        <v>0.01678441927404586</v>
       </c>
       <c r="Q151" s="19" t="inlineStr">
         <is>
@@ -12775,13 +12775,13 @@
         </is>
       </c>
       <c r="D152" s="4" t="n">
-        <v>248.43</v>
+        <v>250.46</v>
       </c>
       <c r="E152" s="25" t="n">
-        <v>-0.1113</v>
+        <v>-0.104</v>
       </c>
       <c r="F152" s="25" t="n">
-        <v>-0.1145</v>
+        <v>-0.1073</v>
       </c>
       <c r="G152" s="6" t="n">
         <v>46324</v>
@@ -12846,13 +12846,13 @@
         </is>
       </c>
       <c r="D153" s="13" t="n">
-        <v>357.55</v>
+        <v>359.08</v>
       </c>
       <c r="E153" s="15" t="n">
-        <v>-0.1302</v>
+        <v>-0.1264</v>
       </c>
       <c r="F153" s="15" t="n">
-        <v>-0.3299</v>
+        <v>-0.327</v>
       </c>
       <c r="G153" s="16" t="n">
         <v>46323</v>
@@ -12907,13 +12907,13 @@
         </is>
       </c>
       <c r="D154" s="4" t="n">
-        <v>527.15</v>
+        <v>538.09</v>
       </c>
       <c r="E154" s="25" t="n">
-        <v>-0.1318</v>
+        <v>-0.1138</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>0.0346</v>
+        <v>0.05599999999999999</v>
       </c>
       <c r="G154" s="6" t="n">
         <v>46315</v>
@@ -12974,13 +12974,13 @@
         </is>
       </c>
       <c r="D155" s="13" t="n">
-        <v>174.6</v>
+        <v>175.09</v>
       </c>
       <c r="E155" s="15" t="n">
-        <v>-0.1606</v>
+        <v>-0.1582</v>
       </c>
       <c r="F155" s="15" t="n">
-        <v>-0.2466</v>
+        <v>-0.2445</v>
       </c>
       <c r="G155" s="16" t="n">
         <v>46330</v>
@@ -13009,7 +13009,7 @@
         <v>575</v>
       </c>
       <c r="M155" s="14" t="n">
-        <v>2.293241695303551</v>
+        <v>2.284025358387115</v>
       </c>
       <c r="N155" s="12" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>237</v>
       </c>
       <c r="P155" s="14" t="n">
-        <v>0.3573883161512028</v>
+        <v>0.3535895825004283</v>
       </c>
       <c r="Q155" s="19" t="inlineStr">
         <is>
@@ -13069,13 +13069,13 @@
         </is>
       </c>
       <c r="D156" s="4" t="n">
-        <v>116.14</v>
+        <v>116.51</v>
       </c>
       <c r="E156" s="25" t="n">
-        <v>-0.0316</v>
+        <v>-0.0285</v>
       </c>
       <c r="F156" s="5" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.0114</v>
       </c>
       <c r="G156" s="6" t="n">
         <v>46288</v>
@@ -13104,7 +13104,7 @@
         <v>250</v>
       </c>
       <c r="M156" s="5" t="n">
-        <v>1.152574479076976</v>
+        <v>1.145738563213458</v>
       </c>
       <c r="N156" s="3" t="inlineStr"/>
       <c r="O156" s="8" t="n"/>
@@ -13148,13 +13148,13 @@
         </is>
       </c>
       <c r="D157" s="13" t="n">
-        <v>118.42</v>
+        <v>117.36</v>
       </c>
       <c r="E157" s="15" t="n">
-        <v>-0.075</v>
+        <v>-0.0833</v>
       </c>
       <c r="F157" s="15" t="n">
-        <v>-0.0475</v>
+        <v>-0.0561</v>
       </c>
       <c r="G157" s="16" t="n">
         <v>46315</v>
@@ -13183,7 +13183,7 @@
         <v>95</v>
       </c>
       <c r="M157" s="15" t="n">
-        <v>-0.1977706468501942</v>
+        <v>-0.1905248807089298</v>
       </c>
       <c r="N157" s="12" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>139</v>
       </c>
       <c r="P157" s="14" t="n">
-        <v>0.1737882114507684</v>
+        <v>0.1843899113837764</v>
       </c>
       <c r="Q157" s="19" t="inlineStr">
         <is>
@@ -13239,13 +13239,13 @@
         </is>
       </c>
       <c r="D158" s="4" t="n">
-        <v>923.38</v>
+        <v>925.29</v>
       </c>
       <c r="E158" s="25" t="n">
-        <v>-0.1137</v>
+        <v>-0.1119</v>
       </c>
       <c r="F158" s="25" t="n">
-        <v>-0.0288</v>
+        <v>-0.0268</v>
       </c>
       <c r="G158" s="6" t="n">
         <v>46331</v>
@@ -13274,7 +13274,7 @@
         <v>125</v>
       </c>
       <c r="M158" s="25" t="n">
-        <v>-0.8646277805453876</v>
+        <v>-0.864907218277513</v>
       </c>
       <c r="N158" s="3" t="inlineStr">
         <is>
@@ -13285,7 +13285,7 @@
         <v>1064</v>
       </c>
       <c r="P158" s="5" t="n">
-        <v>0.1522883319976608</v>
+        <v>0.1499097580218094</v>
       </c>
       <c r="Q158" s="9" t="inlineStr">
         <is>
@@ -13330,13 +13330,13 @@
         </is>
       </c>
       <c r="D159" s="13" t="n">
-        <v>500.64</v>
+        <v>494.47</v>
       </c>
       <c r="E159" s="15" t="n">
-        <v>-0.0825</v>
+        <v>-0.09380000000000001</v>
       </c>
       <c r="F159" s="15" t="n">
-        <v>-0.12</v>
+        <v>-0.1308</v>
       </c>
       <c r="G159" s="16" t="n">
         <v>46325</v>
@@ -13411,13 +13411,13 @@
         </is>
       </c>
       <c r="D160" s="4" t="n">
-        <v>417.42</v>
+        <v>410.05</v>
       </c>
       <c r="E160" s="25" t="n">
-        <v>-0.0375</v>
+        <v>-0.0545</v>
       </c>
       <c r="F160" s="25" t="n">
-        <v>-0.09</v>
+        <v>-0.1061</v>
       </c>
       <c r="G160" s="6" t="n">
         <v>46331</v>
@@ -13472,13 +13472,13 @@
         </is>
       </c>
       <c r="D161" s="13" t="n">
-        <v>33.22</v>
+        <v>33</v>
       </c>
       <c r="E161" s="15" t="n">
-        <v>-0.08550000000000001</v>
+        <v>-0.09140000000000001</v>
       </c>
       <c r="F161" s="15" t="n">
-        <v>-0.2576</v>
+        <v>-0.2624</v>
       </c>
       <c r="G161" s="16" t="n">
         <v>46323</v>
@@ -13547,13 +13547,13 @@
         </is>
       </c>
       <c r="D162" s="4" t="n">
-        <v>192.65</v>
+        <v>193.54</v>
       </c>
       <c r="E162" s="25" t="n">
-        <v>-0.1457</v>
+        <v>-0.1417</v>
       </c>
       <c r="F162" s="25" t="n">
-        <v>-0.0092</v>
+        <v>-0.0046</v>
       </c>
       <c r="G162" s="6" t="n">
         <v>46315</v>
@@ -13626,13 +13626,13 @@
         </is>
       </c>
       <c r="D163" s="13" t="n">
-        <v>45.21</v>
+        <v>44.61</v>
       </c>
       <c r="E163" s="14" t="n">
-        <v>0.1174</v>
+        <v>0.1026</v>
       </c>
       <c r="F163" s="14" t="n">
-        <v>0.1073</v>
+        <v>0.0926</v>
       </c>
       <c r="G163" s="16" t="n"/>
       <c r="H163" s="21" t="inlineStr">
@@ -13677,13 +13677,13 @@
         </is>
       </c>
       <c r="D164" s="4" t="n">
-        <v>419.88</v>
+        <v>423.33</v>
       </c>
       <c r="E164" s="25" t="n">
-        <v>-0.09390000000000001</v>
+        <v>-0.0864</v>
       </c>
       <c r="F164" s="25" t="n">
-        <v>-0.1031</v>
+        <v>-0.0958</v>
       </c>
       <c r="G164" s="6" t="n">
         <v>46324</v>
@@ -13715,7 +13715,7 @@
         <v>560</v>
       </c>
       <c r="P164" s="5" t="n">
-        <v>0.3337143945889302</v>
+        <v>0.32284506177214</v>
       </c>
       <c r="Q164" s="9" t="inlineStr">
         <is>
@@ -13768,13 +13768,13 @@
         </is>
       </c>
       <c r="D165" s="13" t="n">
-        <v>279.15</v>
+        <v>282.48</v>
       </c>
       <c r="E165" s="15" t="n">
-        <v>-0.06559999999999999</v>
+        <v>-0.0544</v>
       </c>
       <c r="F165" s="15" t="n">
-        <v>-0.05769999999999999</v>
+        <v>-0.04650000000000001</v>
       </c>
       <c r="G165" s="16" t="n">
         <v>46317</v>
@@ -13806,7 +13806,7 @@
         <v>294</v>
       </c>
       <c r="P165" s="14" t="n">
-        <v>0.05319720580333163</v>
+        <v>0.0407816482582837</v>
       </c>
       <c r="Q165" s="19" t="inlineStr">
         <is>
@@ -13851,13 +13851,13 @@
         </is>
       </c>
       <c r="D166" s="4" t="n">
-        <v>244.27</v>
+        <v>241.49</v>
       </c>
       <c r="E166" s="25" t="n">
-        <v>-0.1037</v>
+        <v>-0.1139</v>
       </c>
       <c r="F166" s="25" t="n">
-        <v>-0.1625</v>
+        <v>-0.172</v>
       </c>
       <c r="G166" s="6" t="n">
         <v>46323</v>
@@ -13889,7 +13889,7 @@
         <v>425</v>
       </c>
       <c r="P166" s="5" t="n">
-        <v>0.7398780038482007</v>
+        <v>0.7599072425359228</v>
       </c>
       <c r="Q166" s="9" t="inlineStr">
         <is>
@@ -13930,13 +13930,13 @@
         </is>
       </c>
       <c r="D167" s="13" t="n">
-        <v>212.34</v>
+        <v>213.33</v>
       </c>
       <c r="E167" s="15" t="n">
-        <v>-0.0503</v>
+        <v>-0.0458</v>
       </c>
       <c r="F167" s="15" t="n">
-        <v>-0.1117</v>
+        <v>-0.1076</v>
       </c>
       <c r="G167" s="16" t="n">
         <v>46321</v>
@@ -13965,7 +13965,7 @@
         <v>268</v>
       </c>
       <c r="M167" s="14" t="n">
-        <v>0.2621267778091739</v>
+        <v>0.2562696292129564</v>
       </c>
       <c r="N167" s="12" t="inlineStr"/>
       <c r="O167" s="18" t="n"/>
@@ -14013,13 +14013,13 @@
         </is>
       </c>
       <c r="D168" s="4" t="n">
-        <v>304.68</v>
+        <v>305.36</v>
       </c>
       <c r="E168" s="25" t="n">
-        <v>-0.0286</v>
+        <v>-0.0264</v>
       </c>
       <c r="F168" s="25" t="n">
-        <v>-0.1782</v>
+        <v>-0.1764</v>
       </c>
       <c r="G168" s="6" t="n">
         <v>46330</v>
@@ -14088,13 +14088,13 @@
         </is>
       </c>
       <c r="D169" s="13" t="n">
-        <v>317.76</v>
+        <v>319.56</v>
       </c>
       <c r="E169" s="15" t="n">
-        <v>-0.1323</v>
+        <v>-0.1274</v>
       </c>
       <c r="F169" s="15" t="n">
-        <v>-0.1868</v>
+        <v>-0.1822</v>
       </c>
       <c r="G169" s="16" t="n"/>
       <c r="H169" s="21" t="inlineStr">
@@ -14157,13 +14157,13 @@
         </is>
       </c>
       <c r="D170" s="4" t="n">
-        <v>107.34</v>
+        <v>107.6</v>
       </c>
       <c r="E170" s="25" t="n">
-        <v>-0.0579</v>
+        <v>-0.0556</v>
       </c>
       <c r="F170" s="25" t="n">
-        <v>-0.1101</v>
+        <v>-0.1079</v>
       </c>
       <c r="G170" s="6" t="n">
         <v>46322</v>
@@ -14236,13 +14236,13 @@
         </is>
       </c>
       <c r="D171" s="13" t="n">
-        <v>97.86</v>
+        <v>98.06</v>
       </c>
       <c r="E171" s="15" t="n">
-        <v>-0.2553</v>
+        <v>-0.2538</v>
       </c>
       <c r="F171" s="15" t="n">
-        <v>-0.05</v>
+        <v>-0.0481</v>
       </c>
       <c r="G171" s="16" t="n">
         <v>46331</v>
@@ -14297,13 +14297,13 @@
         </is>
       </c>
       <c r="D172" s="4" t="n">
-        <v>332.37</v>
+        <v>337</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>0.0721</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="F172" s="5" t="n">
-        <v>0.0177</v>
+        <v>0.0319</v>
       </c>
       <c r="G172" s="6" t="n">
         <v>46324</v>
@@ -14332,7 +14332,7 @@
         <v>310</v>
       </c>
       <c r="M172" s="25" t="n">
-        <v>-0.06730451003399827</v>
+        <v>-0.08011869436201781</v>
       </c>
       <c r="N172" s="3" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>365</v>
       </c>
       <c r="P172" s="5" t="n">
-        <v>0.09817372205674398</v>
+        <v>0.0830860534124629</v>
       </c>
       <c r="Q172" s="9" t="inlineStr">
         <is>
@@ -14400,13 +14400,13 @@
         </is>
       </c>
       <c r="D173" s="13" t="n">
-        <v>106.41</v>
+        <v>104.6</v>
       </c>
       <c r="E173" s="15" t="n">
-        <v>-0.214</v>
+        <v>-0.2274</v>
       </c>
       <c r="F173" s="15" t="n">
-        <v>-0.192</v>
+        <v>-0.2058</v>
       </c>
       <c r="G173" s="16" t="n">
         <v>46329</v>
@@ -14461,13 +14461,13 @@
         </is>
       </c>
       <c r="D174" s="4" t="n">
-        <v>190.03</v>
+        <v>190.29</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>0.0989</v>
+        <v>0.1004</v>
       </c>
       <c r="F174" s="5" t="n">
-        <v>0.313</v>
+        <v>0.3148</v>
       </c>
       <c r="G174" s="6" t="n">
         <v>46296</v>
@@ -14522,13 +14522,13 @@
         </is>
       </c>
       <c r="D175" s="13" t="n">
-        <v>251</v>
+        <v>252.67</v>
       </c>
       <c r="E175" s="15" t="n">
-        <v>-0.0461</v>
+        <v>-0.0398</v>
       </c>
       <c r="F175" s="14" t="n">
-        <v>0.0693</v>
+        <v>0.0764</v>
       </c>
       <c r="G175" s="16" t="n"/>
       <c r="H175" s="21" t="inlineStr">
@@ -14573,13 +14573,13 @@
         </is>
       </c>
       <c r="D176" s="4" t="n">
-        <v>361.31</v>
+        <v>362.65</v>
       </c>
       <c r="E176" s="25" t="n">
-        <v>-0.0407</v>
+        <v>-0.0371</v>
       </c>
       <c r="F176" s="25" t="n">
-        <v>-0.0299</v>
+        <v>-0.0263</v>
       </c>
       <c r="G176" s="6" t="n"/>
       <c r="H176" s="7" t="inlineStr">
@@ -14598,7 +14598,7 @@
         <v>515</v>
       </c>
       <c r="M176" s="5" t="n">
-        <v>0.4253687968780271</v>
+        <v>0.4201020267475528</v>
       </c>
       <c r="N176" s="3" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>474</v>
       </c>
       <c r="P176" s="5" t="n">
-        <v>0.311892834408126</v>
+        <v>0.3070453605404661</v>
       </c>
       <c r="Q176" s="9" t="inlineStr">
         <is>
@@ -14658,13 +14658,13 @@
         </is>
       </c>
       <c r="D177" s="13" t="n">
-        <v>218.09</v>
+        <v>218.64</v>
       </c>
       <c r="E177" s="15" t="n">
-        <v>-0.1163</v>
+        <v>-0.1141</v>
       </c>
       <c r="F177" s="14" t="n">
-        <v>0.0013</v>
+        <v>0.0039</v>
       </c>
       <c r="G177" s="16" t="n"/>
       <c r="H177" s="21" t="inlineStr">
@@ -14709,13 +14709,13 @@
         </is>
       </c>
       <c r="D178" s="4" t="n">
-        <v>254.86</v>
+        <v>254.43</v>
       </c>
       <c r="E178" s="25" t="n">
-        <v>-0.1895</v>
+        <v>-0.1908</v>
       </c>
       <c r="F178" s="25" t="n">
-        <v>-0.092</v>
+        <v>-0.0935</v>
       </c>
       <c r="G178" s="6" t="n">
         <v>46329</v>
@@ -14770,13 +14770,13 @@
         </is>
       </c>
       <c r="D179" s="13" t="n">
-        <v>282.48</v>
+        <v>293.56</v>
       </c>
       <c r="E179" s="15" t="n">
-        <v>-0.06909999999999999</v>
+        <v>-0.0326</v>
       </c>
       <c r="F179" s="15" t="n">
-        <v>-0.0861</v>
+        <v>-0.05019999999999999</v>
       </c>
       <c r="G179" s="16" t="n">
         <v>46329</v>
@@ -14831,13 +14831,13 @@
         </is>
       </c>
       <c r="D180" s="4" t="n">
-        <v>33.7</v>
+        <v>33.11</v>
       </c>
       <c r="E180" s="25" t="n">
-        <v>-0.1445</v>
+        <v>-0.1594</v>
       </c>
       <c r="F180" s="25" t="n">
-        <v>-0.2731</v>
+        <v>-0.2858</v>
       </c>
       <c r="G180" s="6" t="n">
         <v>46324</v>
@@ -14892,13 +14892,13 @@
         </is>
       </c>
       <c r="D181" s="13" t="n">
-        <v>416.15</v>
+        <v>417.4</v>
       </c>
       <c r="E181" s="15" t="n">
-        <v>-0.1909</v>
+        <v>-0.1885</v>
       </c>
       <c r="F181" s="15" t="n">
-        <v>-0.2084</v>
+        <v>-0.206</v>
       </c>
       <c r="G181" s="16" t="n"/>
       <c r="H181" s="21" t="inlineStr">
@@ -14917,7 +14917,7 @@
         <v>740</v>
       </c>
       <c r="M181" s="14" t="n">
-        <v>0.7782049741679684</v>
+        <v>0.7728797316722569</v>
       </c>
       <c r="N181" s="12" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>700</v>
       </c>
       <c r="P181" s="14" t="n">
-        <v>0.6820857863751052</v>
+        <v>0.6770483948251079</v>
       </c>
       <c r="Q181" s="19" t="inlineStr">
         <is>
@@ -14969,13 +14969,13 @@
         </is>
       </c>
       <c r="D182" s="4" t="n">
-        <v>62.17</v>
+        <v>62.35</v>
       </c>
       <c r="E182" s="25" t="n">
-        <v>-0.0133</v>
+        <v>-0.0105</v>
       </c>
       <c r="F182" s="25" t="n">
-        <v>-0.1527</v>
+        <v>-0.1502</v>
       </c>
       <c r="G182" s="6" t="n">
         <v>46331</v>
@@ -15034,13 +15034,13 @@
         </is>
       </c>
       <c r="D183" s="13" t="n">
-        <v>543.8099999999999</v>
+        <v>545.09</v>
       </c>
       <c r="E183" s="14" t="n">
-        <v>0.1227</v>
+        <v>0.1253</v>
       </c>
       <c r="F183" s="14" t="n">
-        <v>0.0799</v>
+        <v>0.0825</v>
       </c>
       <c r="G183" s="16" t="n">
         <v>46329</v>
@@ -15069,7 +15069,7 @@
         <v>615</v>
       </c>
       <c r="M183" s="14" t="n">
-        <v>0.1309096927235616</v>
+        <v>0.1282540497899429</v>
       </c>
       <c r="N183" s="12" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>579</v>
       </c>
       <c r="P183" s="14" t="n">
-        <v>0.06471010095437756</v>
+        <v>0.06220991029004378</v>
       </c>
       <c r="Q183" s="19" t="inlineStr">
         <is>
@@ -15121,13 +15121,13 @@
         </is>
       </c>
       <c r="D184" s="4" t="n">
-        <v>47.92</v>
+        <v>47.95</v>
       </c>
       <c r="E184" s="25" t="n">
-        <v>-0.1262</v>
+        <v>-0.1256</v>
       </c>
       <c r="F184" s="25" t="n">
-        <v>-0.234</v>
+        <v>-0.2335</v>
       </c>
       <c r="G184" s="6" t="n">
         <v>46321</v>
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="D185" s="13" t="n">
-        <v>203.29</v>
+        <v>199.53</v>
       </c>
       <c r="E185" s="14" t="n">
-        <v>0.05230000000000001</v>
+        <v>0.0329</v>
       </c>
       <c r="F185" s="14" t="n">
-        <v>0.2004</v>
+        <v>0.1782</v>
       </c>
       <c r="G185" s="16" t="n">
         <v>46329</v>
@@ -15216,8 +15216,8 @@
       <c r="L185" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="M185" s="15" t="n">
-        <v>-0.01618377687048056</v>
+      <c r="M185" s="14" t="n">
+        <v>0.00235553550844484</v>
       </c>
       <c r="N185" s="12" t="inlineStr">
         <is>
@@ -15227,8 +15227,8 @@
       <c r="O185" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="P185" s="15" t="n">
-        <v>-0.01618377687048056</v>
+      <c r="P185" s="14" t="n">
+        <v>0.00235553550844484</v>
       </c>
       <c r="Q185" s="19" t="inlineStr">
         <is>
@@ -15273,13 +15273,13 @@
         </is>
       </c>
       <c r="D186" s="4" t="n">
-        <v>77.79000000000001</v>
+        <v>78.37</v>
       </c>
       <c r="E186" s="25" t="n">
-        <v>-0.0251</v>
+        <v>-0.0177</v>
       </c>
       <c r="F186" s="5" t="n">
-        <v>0.0336</v>
+        <v>0.0414</v>
       </c>
       <c r="G186" s="6" t="n">
         <v>46323</v>
@@ -15311,7 +15311,7 @@
         <v>180</v>
       </c>
       <c r="P186" s="5" t="n">
-        <v>1.313922097956035</v>
+        <v>1.296797243843307</v>
       </c>
       <c r="Q186" s="9" t="inlineStr">
         <is>
@@ -15364,13 +15364,13 @@
         </is>
       </c>
       <c r="D187" s="13" t="n">
-        <v>25.67</v>
+        <v>26.38</v>
       </c>
       <c r="E187" s="15" t="n">
-        <v>-0.0998</v>
+        <v>-0.0747</v>
       </c>
       <c r="F187" s="15" t="n">
-        <v>-0.0785</v>
+        <v>-0.0528</v>
       </c>
       <c r="G187" s="16" t="n">
         <v>46303</v>
@@ -15425,13 +15425,13 @@
         </is>
       </c>
       <c r="D188" s="4" t="n">
-        <v>259.96</v>
+        <v>264.9</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>0.0262</v>
+        <v>0.0457</v>
       </c>
       <c r="F188" s="25" t="n">
-        <v>-0.0358</v>
+        <v>-0.0175</v>
       </c>
       <c r="G188" s="6" t="n">
         <v>46330</v>
@@ -15486,13 +15486,13 @@
         </is>
       </c>
       <c r="D189" s="13" t="n">
-        <v>1626.71</v>
+        <v>1629.67</v>
       </c>
       <c r="E189" s="15" t="n">
-        <v>-0.0978</v>
+        <v>-0.09609999999999999</v>
       </c>
       <c r="F189" s="15" t="n">
-        <v>-0.0646</v>
+        <v>-0.0629</v>
       </c>
       <c r="G189" s="16" t="n">
         <v>46309</v>
@@ -15565,13 +15565,13 @@
         </is>
       </c>
       <c r="D190" s="4" t="n">
-        <v>40.18</v>
+        <v>39.99</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>0.1035</v>
+        <v>0.0983</v>
       </c>
       <c r="F190" s="5" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.0837</v>
       </c>
       <c r="G190" s="6" t="n">
         <v>46324</v>
@@ -15626,13 +15626,13 @@
         </is>
       </c>
       <c r="D191" s="13" t="n">
-        <v>350.38</v>
+        <v>347.3</v>
       </c>
       <c r="E191" s="15" t="n">
-        <v>-0.0779</v>
+        <v>-0.0861</v>
       </c>
       <c r="F191" s="15" t="n">
-        <v>-0.0735</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="G191" s="16" t="n"/>
       <c r="H191" s="21" t="inlineStr">
@@ -15651,7 +15651,7 @@
         <v>545</v>
       </c>
       <c r="M191" s="14" t="n">
-        <v>0.5554540784291341</v>
+        <v>0.5692484883386121</v>
       </c>
       <c r="N191" s="12" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>582</v>
       </c>
       <c r="P191" s="14" t="n">
-        <v>0.661053713111479</v>
+        <v>0.6757846242441693</v>
       </c>
       <c r="Q191" s="19" t="inlineStr">
         <is>
@@ -15715,13 +15715,13 @@
         </is>
       </c>
       <c r="D192" s="4" t="n">
-        <v>144.31</v>
+        <v>144.21</v>
       </c>
       <c r="E192" s="25" t="n">
-        <v>-0.07400000000000001</v>
+        <v>-0.0746</v>
       </c>
       <c r="F192" s="25" t="n">
-        <v>-0.0189</v>
+        <v>-0.0196</v>
       </c>
       <c r="G192" s="6" t="n">
         <v>46335</v>
@@ -15776,13 +15776,13 @@
         </is>
       </c>
       <c r="D193" s="13" t="n">
-        <v>280.52</v>
+        <v>280.76</v>
       </c>
       <c r="E193" s="15" t="n">
-        <v>-0.1137</v>
+        <v>-0.113</v>
       </c>
       <c r="F193" s="15" t="n">
-        <v>-0.1498</v>
+        <v>-0.149</v>
       </c>
       <c r="G193" s="16" t="n">
         <v>46321</v>
@@ -15811,7 +15811,7 @@
         <v>425</v>
       </c>
       <c r="M193" s="14" t="n">
-        <v>0.5150434906602026</v>
+        <v>0.5137483972075795</v>
       </c>
       <c r="N193" s="12" t="inlineStr"/>
       <c r="O193" s="18" t="n"/>
@@ -15855,13 +15855,13 @@
         </is>
       </c>
       <c r="D194" s="4" t="n">
-        <v>137.4</v>
+        <v>136.23</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>0.0544</v>
+        <v>0.0454</v>
       </c>
       <c r="F194" s="5" t="n">
-        <v>0.0123</v>
+        <v>0.0037</v>
       </c>
       <c r="G194" s="6" t="n">
         <v>46322</v>
@@ -15916,13 +15916,13 @@
         </is>
       </c>
       <c r="D195" s="13" t="n">
-        <v>354.47</v>
+        <v>344.25</v>
       </c>
       <c r="E195" s="15" t="n">
-        <v>-0.1259</v>
+        <v>-0.1511</v>
       </c>
       <c r="F195" s="15" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.0911</v>
       </c>
       <c r="G195" s="16" t="n"/>
       <c r="H195" s="21" t="inlineStr">
@@ -15967,13 +15967,13 @@
         </is>
       </c>
       <c r="D196" s="4" t="n">
-        <v>11.74</v>
+        <v>11.82</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>0.0673</v>
+        <v>0.0745</v>
       </c>
       <c r="F196" s="25" t="n">
-        <v>-0.2362</v>
+        <v>-0.231</v>
       </c>
       <c r="G196" s="6" t="n">
         <v>46337</v>
@@ -16028,13 +16028,13 @@
         </is>
       </c>
       <c r="D197" s="13" t="n">
-        <v>338.81</v>
+        <v>329.94</v>
       </c>
       <c r="E197" s="14" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.0623</v>
       </c>
       <c r="F197" s="14" t="n">
-        <v>0.1024</v>
+        <v>0.0735</v>
       </c>
       <c r="G197" s="16" t="n">
         <v>46321</v>
@@ -16089,13 +16089,13 @@
         </is>
       </c>
       <c r="D198" s="4" t="n">
-        <v>294.68</v>
+        <v>295.98</v>
       </c>
       <c r="E198" s="25" t="n">
-        <v>-0.0383</v>
+        <v>-0.0341</v>
       </c>
       <c r="F198" s="5" t="n">
-        <v>0.0325</v>
+        <v>0.0371</v>
       </c>
       <c r="G198" s="6" t="n">
         <v>46330</v>
@@ -16150,13 +16150,13 @@
         </is>
       </c>
       <c r="D199" s="13" t="n">
-        <v>54.34</v>
+        <v>55</v>
       </c>
       <c r="E199" s="15" t="n">
-        <v>-0.0824</v>
+        <v>-0.0713</v>
       </c>
       <c r="F199" s="14" t="n">
-        <v>0.0541</v>
+        <v>0.0669</v>
       </c>
       <c r="G199" s="16" t="n">
         <v>46330</v>
@@ -16211,13 +16211,13 @@
         </is>
       </c>
       <c r="D200" s="4" t="n">
-        <v>17.33</v>
+        <v>17.14</v>
       </c>
       <c r="E200" s="25" t="n">
-        <v>-0.0805</v>
+        <v>-0.0907</v>
       </c>
       <c r="F200" s="25" t="n">
-        <v>-0.2262</v>
+        <v>-0.2348</v>
       </c>
       <c r="G200" s="6" t="n">
         <v>46318</v>
@@ -16272,13 +16272,13 @@
         </is>
       </c>
       <c r="D201" s="13" t="n">
-        <v>164.7</v>
+        <v>168.25</v>
       </c>
       <c r="E201" s="15" t="n">
-        <v>-0.3304</v>
+        <v>-0.316</v>
       </c>
       <c r="F201" s="15" t="n">
-        <v>-0.2234</v>
+        <v>-0.2066</v>
       </c>
       <c r="G201" s="16" t="n"/>
       <c r="H201" s="21" t="inlineStr">
@@ -16323,13 +16323,13 @@
         </is>
       </c>
       <c r="D202" s="4" t="n">
-        <v>243.32</v>
+        <v>242.85</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>0.2406</v>
+        <v>0.2381</v>
       </c>
       <c r="F202" s="5" t="n">
-        <v>0.4001</v>
+        <v>0.3974</v>
       </c>
       <c r="G202" s="6" t="n"/>
       <c r="H202" s="7" t="inlineStr">
@@ -16348,7 +16348,7 @@
         <v>200</v>
       </c>
       <c r="M202" s="25" t="n">
-        <v>-0.178037152720697</v>
+        <v>-0.1764463660695903</v>
       </c>
       <c r="N202" s="3" t="inlineStr">
         <is>
@@ -16359,7 +16359,7 @@
         <v>250</v>
       </c>
       <c r="P202" s="5" t="n">
-        <v>0.02745355909912875</v>
+        <v>0.02944204241301217</v>
       </c>
       <c r="Q202" s="9" t="inlineStr">
         <is>
@@ -16404,13 +16404,13 @@
         </is>
       </c>
       <c r="D203" s="13" t="n">
-        <v>245.98</v>
+        <v>245.7</v>
       </c>
       <c r="E203" s="14" t="n">
-        <v>0.1553</v>
+        <v>0.154</v>
       </c>
       <c r="F203" s="14" t="n">
-        <v>0.2393</v>
+        <v>0.2378</v>
       </c>
       <c r="G203" s="16" t="n"/>
       <c r="H203" s="21" t="inlineStr">
@@ -16429,7 +16429,7 @@
         <v>181.25</v>
       </c>
       <c r="M203" s="15" t="n">
-        <v>-0.2631514757297341</v>
+        <v>-0.2623117623117623</v>
       </c>
       <c r="N203" s="12" t="inlineStr">
         <is>
@@ -16440,7 +16440,7 @@
         <v>177.5</v>
       </c>
       <c r="P203" s="15" t="n">
-        <v>-0.2783966176111879</v>
+        <v>-0.2775742775742776</v>
       </c>
       <c r="Q203" s="19" t="inlineStr">
         <is>
@@ -16481,13 +16481,13 @@
         </is>
       </c>
       <c r="D204" s="4" t="n">
-        <v>79.42</v>
+        <v>79.88</v>
       </c>
       <c r="E204" s="25" t="n">
-        <v>-0.1476</v>
+        <v>-0.1426</v>
       </c>
       <c r="F204" s="5" t="n">
-        <v>0.08710000000000001</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="G204" s="6" t="n">
         <v>46335</v>
@@ -16542,13 +16542,13 @@
         </is>
       </c>
       <c r="D205" s="13" t="n">
-        <v>111.09</v>
+        <v>110.24</v>
       </c>
       <c r="E205" s="15" t="n">
-        <v>-0.004699999999999999</v>
-      </c>
-      <c r="F205" s="14" t="n">
-        <v>0.0035</v>
+        <v>-0.0123</v>
+      </c>
+      <c r="F205" s="15" t="n">
+        <v>-0.0042</v>
       </c>
       <c r="G205" s="16" t="n">
         <v>46337</v>
@@ -16577,7 +16577,7 @@
         <v>130</v>
       </c>
       <c r="M205" s="14" t="n">
-        <v>0.1702223422450265</v>
+        <v>0.179245283018868</v>
       </c>
       <c r="N205" s="12" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>150</v>
       </c>
       <c r="P205" s="14" t="n">
-        <v>0.3502565487442614</v>
+        <v>0.36066763425254</v>
       </c>
       <c r="Q205" s="19" t="inlineStr">
         <is>
@@ -16645,13 +16645,13 @@
         </is>
       </c>
       <c r="D206" s="4" t="n">
-        <v>237.34</v>
+        <v>236</v>
       </c>
       <c r="E206" s="25" t="n">
-        <v>-0.0352</v>
+        <v>-0.0407</v>
       </c>
       <c r="F206" s="25" t="n">
-        <v>-0.0983</v>
+        <v>-0.1033</v>
       </c>
       <c r="G206" s="6" t="n">
         <v>46331</v>
@@ -16706,13 +16706,13 @@
         </is>
       </c>
       <c r="D207" s="13" t="n">
-        <v>586.14</v>
+        <v>588.4</v>
       </c>
       <c r="E207" s="14" t="n">
-        <v>0.2507</v>
+        <v>0.2555</v>
       </c>
       <c r="F207" s="14" t="n">
-        <v>0.5349</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="G207" s="16" t="n"/>
       <c r="H207" s="21" t="inlineStr">
@@ -16757,13 +16757,13 @@
         </is>
       </c>
       <c r="D208" s="4" t="n">
-        <v>70.95999999999999</v>
+        <v>70.64</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>0.1824</v>
+        <v>0.1771</v>
       </c>
       <c r="F208" s="5" t="n">
-        <v>0.3567</v>
+        <v>0.3507</v>
       </c>
       <c r="G208" s="6" t="n"/>
       <c r="H208" s="7" t="inlineStr">
@@ -16808,13 +16808,13 @@
         </is>
       </c>
       <c r="D209" s="13" t="n">
-        <v>55.69</v>
+        <v>55.83</v>
       </c>
       <c r="E209" s="14" t="n">
-        <v>0.1305</v>
+        <v>0.1334</v>
       </c>
       <c r="F209" s="14" t="n">
-        <v>0.2456</v>
+        <v>0.2487</v>
       </c>
       <c r="G209" s="16" t="n">
         <v>46330</v>
@@ -16869,13 +16869,13 @@
         </is>
       </c>
       <c r="D210" s="4" t="n">
-        <v>384.86</v>
+        <v>380.92</v>
       </c>
       <c r="E210" s="25" t="n">
-        <v>-0.2025</v>
+        <v>-0.2107</v>
       </c>
       <c r="F210" s="25" t="n">
-        <v>-0.2214</v>
+        <v>-0.2293</v>
       </c>
       <c r="G210" s="6" t="n">
         <v>46328</v>
@@ -16930,13 +16930,13 @@
         </is>
       </c>
       <c r="D211" s="13" t="n">
-        <v>112.1</v>
+        <v>111.53</v>
       </c>
       <c r="E211" s="15" t="n">
-        <v>-0.0984</v>
+        <v>-0.103</v>
       </c>
       <c r="F211" s="14" t="n">
-        <v>0.0645</v>
+        <v>0.0591</v>
       </c>
       <c r="G211" s="16" t="n">
         <v>46330</v>
@@ -16991,13 +16991,13 @@
         </is>
       </c>
       <c r="D212" s="4" t="n">
-        <v>174.97</v>
+        <v>172.58</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>0.1073</v>
+        <v>0.0922</v>
       </c>
       <c r="F212" s="5" t="n">
-        <v>0.0911</v>
+        <v>0.0762</v>
       </c>
       <c r="G212" s="6" t="n">
         <v>46330</v>
@@ -17052,13 +17052,13 @@
         </is>
       </c>
       <c r="D213" s="13" t="n">
-        <v>45.37</v>
+        <v>45.84</v>
       </c>
       <c r="E213" s="15" t="n">
-        <v>-0.09080000000000001</v>
+        <v>-0.0814</v>
       </c>
       <c r="F213" s="15" t="n">
-        <v>-0.2014</v>
+        <v>-0.1931</v>
       </c>
       <c r="G213" s="16" t="n">
         <v>46337</v>
@@ -17113,13 +17113,13 @@
         </is>
       </c>
       <c r="D214" s="4" t="n">
-        <v>148.57</v>
+        <v>147.8</v>
       </c>
       <c r="E214" s="25" t="n">
-        <v>-0.0709</v>
+        <v>-0.0757</v>
       </c>
       <c r="F214" s="25" t="n">
-        <v>-0.0296</v>
+        <v>-0.0346</v>
       </c>
       <c r="G214" s="6" t="n">
         <v>46322</v>
@@ -17174,13 +17174,13 @@
         </is>
       </c>
       <c r="D215" s="13" t="n">
-        <v>49.65</v>
+        <v>50.27</v>
       </c>
       <c r="E215" s="14" t="n">
-        <v>0.1963</v>
+        <v>0.2113</v>
       </c>
       <c r="F215" s="14" t="n">
-        <v>0.4571</v>
+        <v>0.4755</v>
       </c>
       <c r="G215" s="16" t="n"/>
       <c r="H215" s="21" t="inlineStr">
@@ -17225,13 +17225,13 @@
         </is>
       </c>
       <c r="D216" s="4" t="n">
-        <v>144.52</v>
+        <v>144.98</v>
       </c>
       <c r="E216" s="25" t="n">
-        <v>-0.187</v>
+        <v>-0.1844</v>
       </c>
       <c r="F216" s="25" t="n">
-        <v>-0.0313</v>
+        <v>-0.0282</v>
       </c>
       <c r="G216" s="6" t="n"/>
       <c r="H216" s="7" t="inlineStr">
@@ -17250,7 +17250,7 @@
         <v>190</v>
       </c>
       <c r="M216" s="5" t="n">
-        <v>0.3146969277608634</v>
+        <v>0.3105255897365155</v>
       </c>
       <c r="N216" s="3" t="inlineStr"/>
       <c r="O216" s="8" t="n"/>
@@ -17294,13 +17294,13 @@
         </is>
       </c>
       <c r="D217" s="13" t="n">
-        <v>61.43</v>
+        <v>61.04</v>
       </c>
       <c r="E217" s="14" t="n">
-        <v>0.1031</v>
+        <v>0.09609999999999999</v>
       </c>
       <c r="F217" s="14" t="n">
-        <v>0.3786</v>
+        <v>0.3698</v>
       </c>
       <c r="G217" s="16" t="n"/>
       <c r="H217" s="21" t="inlineStr">
@@ -17319,7 +17319,7 @@
         <v>67</v>
       </c>
       <c r="M217" s="14" t="n">
-        <v>0.09067230994628032</v>
+        <v>0.09764089121887289</v>
       </c>
       <c r="N217" s="12" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
         <v>70</v>
       </c>
       <c r="P217" s="14" t="n">
-        <v>0.1395083835259645</v>
+        <v>0.1467889908256881</v>
       </c>
       <c r="Q217" s="19" t="inlineStr">
         <is>
@@ -17371,13 +17371,13 @@
         </is>
       </c>
       <c r="D218" s="4" t="n">
-        <v>232.7</v>
+        <v>229.58</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>0.0286</v>
-      </c>
-      <c r="F218" s="5" t="n">
-        <v>0.0064</v>
+        <v>0.0148</v>
+      </c>
+      <c r="F218" s="25" t="n">
+        <v>-0.006999999999999999</v>
       </c>
       <c r="G218" s="6" t="n">
         <v>46330</v>
@@ -17432,13 +17432,13 @@
         </is>
       </c>
       <c r="D219" s="13" t="n">
-        <v>238.29</v>
+        <v>237.75</v>
       </c>
       <c r="E219" s="14" t="n">
-        <v>0.0242</v>
+        <v>0.0218</v>
       </c>
       <c r="F219" s="14" t="n">
-        <v>0.1187</v>
+        <v>0.1162</v>
       </c>
       <c r="G219" s="16" t="n">
         <v>46316</v>
@@ -17474,7 +17474,7 @@
         <v>250</v>
       </c>
       <c r="P219" s="14" t="n">
-        <v>0.04914180200595916</v>
+        <v>0.05152471083070452</v>
       </c>
       <c r="Q219" s="19" t="inlineStr">
         <is>
@@ -17511,13 +17511,13 @@
         </is>
       </c>
       <c r="D220" s="4" t="n">
-        <v>13.76</v>
+        <v>13.86</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>0.0658</v>
+        <v>0.0736</v>
       </c>
       <c r="F220" s="5" t="n">
-        <v>0.5204</v>
+        <v>0.5315</v>
       </c>
       <c r="G220" s="6" t="n">
         <v>46337</v>
@@ -17572,13 +17572,13 @@
         </is>
       </c>
       <c r="D221" s="13" t="n">
-        <v>109.6</v>
+        <v>108.8</v>
       </c>
       <c r="E221" s="14" t="n">
-        <v>0.1335</v>
+        <v>0.1252</v>
       </c>
       <c r="F221" s="14" t="n">
-        <v>0.1291</v>
+        <v>0.121</v>
       </c>
       <c r="G221" s="16" t="n">
         <v>46317</v>
@@ -17633,13 +17633,13 @@
         </is>
       </c>
       <c r="D222" s="4" t="n">
-        <v>318.05</v>
+        <v>313.13</v>
       </c>
       <c r="E222" s="25" t="n">
-        <v>-0.09230000000000001</v>
+        <v>-0.1064</v>
       </c>
       <c r="F222" s="5" t="n">
-        <v>0.0825</v>
+        <v>0.06570000000000001</v>
       </c>
       <c r="G222" s="6" t="n"/>
       <c r="H222" s="7" t="inlineStr">
@@ -17684,13 +17684,13 @@
         </is>
       </c>
       <c r="D223" s="13" t="n">
-        <v>39.9</v>
+        <v>40.34</v>
       </c>
       <c r="E223" s="15" t="n">
-        <v>-0.0956</v>
+        <v>-0.0857</v>
       </c>
       <c r="F223" s="14" t="n">
-        <v>0.1653</v>
+        <v>0.1782</v>
       </c>
       <c r="G223" s="16" t="n">
         <v>46330</v>
@@ -17745,13 +17745,13 @@
         </is>
       </c>
       <c r="D224" s="4" t="n">
-        <v>43.13</v>
+        <v>43.48</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>0.0269</v>
+        <v>0.0352</v>
       </c>
       <c r="F224" s="5" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="G224" s="6" t="n">
         <v>46331</v>
@@ -17806,13 +17806,13 @@
         </is>
       </c>
       <c r="D225" s="13" t="n">
-        <v>298.94</v>
+        <v>295.94</v>
       </c>
       <c r="E225" s="15" t="n">
-        <v>-0.1172</v>
+        <v>-0.126</v>
       </c>
       <c r="F225" s="15" t="n">
-        <v>-0.0228</v>
+        <v>-0.0326</v>
       </c>
       <c r="G225" s="16" t="n">
         <v>46289</v>
@@ -17871,13 +17871,13 @@
         </is>
       </c>
       <c r="D226" s="4" t="n">
-        <v>336.63</v>
+        <v>331.44</v>
       </c>
       <c r="E226" s="25" t="n">
-        <v>-0.0128</v>
+        <v>-0.028</v>
       </c>
       <c r="F226" s="5" t="n">
-        <v>0.0716</v>
+        <v>0.0551</v>
       </c>
       <c r="G226" s="6" t="n"/>
       <c r="H226" s="7" t="inlineStr">
@@ -17896,7 +17896,7 @@
         <v>390</v>
       </c>
       <c r="M226" s="5" t="n">
-        <v>0.1585420194278585</v>
+        <v>0.1766835626357712</v>
       </c>
       <c r="N226" s="3" t="inlineStr"/>
       <c r="O226" s="8" t="n"/>
@@ -17952,13 +17952,13 @@
         </is>
       </c>
       <c r="D227" s="13" t="n">
-        <v>167.92</v>
+        <v>168.98</v>
       </c>
       <c r="E227" s="15" t="n">
-        <v>-0.1379</v>
+        <v>-0.1325</v>
       </c>
       <c r="F227" s="15" t="n">
-        <v>-0.1911</v>
+        <v>-0.186</v>
       </c>
       <c r="G227" s="16" t="n">
         <v>46330</v>
@@ -17987,7 +17987,7 @@
         <v>305</v>
       </c>
       <c r="M227" s="14" t="n">
-        <v>0.8163411148165794</v>
+        <v>0.8049473310450942</v>
       </c>
       <c r="N227" s="12" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>185</v>
       </c>
       <c r="P227" s="14" t="n">
-        <v>0.1017151024297285</v>
+        <v>0.0948041188306309</v>
       </c>
       <c r="Q227" s="19" t="inlineStr">
         <is>
@@ -18039,13 +18039,13 @@
         </is>
       </c>
       <c r="D228" s="4" t="n">
-        <v>82.43000000000001</v>
+        <v>81.92</v>
       </c>
       <c r="E228" s="25" t="n">
-        <v>-0.1046</v>
+        <v>-0.1101</v>
       </c>
       <c r="F228" s="25" t="n">
-        <v>-0.1762</v>
+        <v>-0.1813</v>
       </c>
       <c r="G228" s="6" t="n"/>
       <c r="H228" s="7" t="inlineStr">
@@ -18090,13 +18090,13 @@
         </is>
       </c>
       <c r="D229" s="13" t="n">
-        <v>911.45</v>
+        <v>893.61</v>
       </c>
       <c r="E229" s="14" t="n">
-        <v>0.0437</v>
+        <v>0.0232</v>
       </c>
       <c r="F229" s="14" t="n">
-        <v>0.1906</v>
+        <v>0.1673</v>
       </c>
       <c r="G229" s="16" t="n">
         <v>46329</v>
@@ -18151,13 +18151,13 @@
         </is>
       </c>
       <c r="D230" s="4" t="n">
-        <v>102.12</v>
+        <v>102.54</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>0.0388</v>
+        <v>0.043</v>
       </c>
       <c r="F230" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0075</v>
       </c>
       <c r="G230" s="6" t="n">
         <v>46322</v>
@@ -18212,13 +18212,13 @@
         </is>
       </c>
       <c r="D231" s="13" t="n">
-        <v>268.42</v>
+        <v>269.31</v>
       </c>
       <c r="E231" s="15" t="n">
-        <v>-0.1814</v>
+        <v>-0.1787</v>
       </c>
       <c r="F231" s="15" t="n">
-        <v>-0.125</v>
+        <v>-0.1221</v>
       </c>
       <c r="G231" s="16" t="n">
         <v>46323</v>
@@ -18247,7 +18247,7 @@
         <v>450</v>
       </c>
       <c r="M231" s="14" t="n">
-        <v>0.6764771626555397</v>
+        <v>0.6709368385875014</v>
       </c>
       <c r="N231" s="12" t="inlineStr">
         <is>
@@ -18258,7 +18258,7 @@
         <v>355</v>
       </c>
       <c r="P231" s="14" t="n">
-        <v>0.3225542060949258</v>
+        <v>0.3181835059968067</v>
       </c>
       <c r="Q231" s="19" t="inlineStr">
         <is>
@@ -18303,13 +18303,13 @@
         </is>
       </c>
       <c r="D232" s="4" t="n">
-        <v>70.51000000000001</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="E232" s="25" t="n">
-        <v>-0.09820000000000001</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="F232" s="25" t="n">
-        <v>-0.1241</v>
+        <v>-0.1204</v>
       </c>
       <c r="G232" s="6" t="n">
         <v>46331</v>
@@ -18364,13 +18364,13 @@
         </is>
       </c>
       <c r="D233" s="13" t="n">
-        <v>402.22</v>
+        <v>393.42</v>
       </c>
       <c r="E233" s="15" t="n">
-        <v>-0.0745</v>
+        <v>-0.09480000000000001</v>
       </c>
       <c r="F233" s="14" t="n">
-        <v>0.2439</v>
+        <v>0.2167</v>
       </c>
       <c r="G233" s="16" t="n"/>
       <c r="H233" s="21" t="inlineStr">
@@ -18415,13 +18415,13 @@
         </is>
       </c>
       <c r="D234" s="4" t="n">
-        <v>241.81</v>
+        <v>240.23</v>
       </c>
       <c r="E234" s="25" t="n">
-        <v>-0.1946</v>
+        <v>-0.1999</v>
       </c>
       <c r="F234" s="25" t="n">
-        <v>-0.2543</v>
+        <v>-0.2592</v>
       </c>
       <c r="G234" s="6" t="n">
         <v>46330</v>
@@ -18476,13 +18476,13 @@
         </is>
       </c>
       <c r="D235" s="13" t="n">
-        <v>1149.57</v>
+        <v>1169.58</v>
       </c>
       <c r="E235" s="15" t="n">
-        <v>-0.1377</v>
+        <v>-0.1227</v>
       </c>
       <c r="F235" s="15" t="n">
-        <v>-0.1349</v>
+        <v>-0.1198</v>
       </c>
       <c r="G235" s="16" t="n">
         <v>46324</v>
@@ -18537,13 +18537,13 @@
         </is>
       </c>
       <c r="D236" s="4" t="n">
-        <v>241.04</v>
+        <v>240.76</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>0.1159</v>
+        <v>0.1146</v>
       </c>
       <c r="F236" s="5" t="n">
-        <v>0.2365</v>
+        <v>0.235</v>
       </c>
       <c r="G236" s="6" t="n"/>
       <c r="H236" s="7" t="inlineStr">
@@ -18562,7 +18562,7 @@
         <v>240</v>
       </c>
       <c r="M236" s="25" t="n">
-        <v>-0.004314636574842317</v>
+        <v>-0.003156670543279577</v>
       </c>
       <c r="N236" s="3" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>251</v>
       </c>
       <c r="P236" s="5" t="n">
-        <v>0.04132094258214408</v>
+        <v>0.04253198205682011</v>
       </c>
       <c r="Q236" s="9" t="inlineStr">
         <is>
@@ -18614,13 +18614,13 @@
         </is>
       </c>
       <c r="D237" s="13" t="n">
-        <v>495.82</v>
+        <v>497.75</v>
       </c>
       <c r="E237" s="14" t="n">
-        <v>0.0295</v>
+        <v>0.0335</v>
       </c>
       <c r="F237" s="14" t="n">
-        <v>0.2325</v>
+        <v>0.2373</v>
       </c>
       <c r="G237" s="16" t="n">
         <v>46330</v>
@@ -18649,7 +18649,7 @@
         <v>625</v>
       </c>
       <c r="M237" s="14" t="n">
-        <v>0.2605380985034892</v>
+        <v>0.2556504269211451</v>
       </c>
       <c r="N237" s="12" t="inlineStr">
         <is>
@@ -18660,7 +18660,7 @@
         <v>525</v>
       </c>
       <c r="P237" s="14" t="n">
-        <v>0.05885200274293092</v>
+        <v>0.05474635861376193</v>
       </c>
       <c r="Q237" s="19" t="inlineStr">
         <is>
@@ -18713,13 +18713,13 @@
         </is>
       </c>
       <c r="D238" s="4" t="n">
-        <v>462.28</v>
+        <v>459.68</v>
       </c>
       <c r="E238" s="25" t="n">
-        <v>-0.0154</v>
+        <v>-0.0209</v>
       </c>
       <c r="F238" s="5" t="n">
-        <v>0.1263</v>
+        <v>0.12</v>
       </c>
       <c r="G238" s="6" t="n">
         <v>46324</v>
@@ -18751,7 +18751,7 @@
         <v>525</v>
       </c>
       <c r="P238" s="5" t="n">
-        <v>0.1356753482737735</v>
+        <v>0.1420988513748695</v>
       </c>
       <c r="Q238" s="9" t="inlineStr">
         <is>
@@ -18800,13 +18800,13 @@
         </is>
       </c>
       <c r="D239" s="13" t="n">
-        <v>128.57</v>
+        <v>132.25</v>
       </c>
       <c r="E239" s="14" t="n">
-        <v>0.3897</v>
+        <v>0.4294</v>
       </c>
       <c r="F239" s="14" t="n">
-        <v>0.3144</v>
+        <v>0.352</v>
       </c>
       <c r="G239" s="16" t="n">
         <v>46324</v>
@@ -18861,13 +18861,13 @@
         </is>
       </c>
       <c r="D240" s="4" t="n">
-        <v>266.2</v>
+        <v>263.14</v>
       </c>
       <c r="E240" s="25" t="n">
-        <v>-0.0911</v>
+        <v>-0.1015</v>
       </c>
       <c r="F240" s="25" t="n">
-        <v>-0.0133</v>
+        <v>-0.0247</v>
       </c>
       <c r="G240" s="6" t="n">
         <v>46331</v>
@@ -18922,13 +18922,13 @@
         </is>
       </c>
       <c r="D241" s="13" t="n">
-        <v>981.2</v>
+        <v>977.5</v>
       </c>
       <c r="E241" s="14" t="n">
-        <v>0.043</v>
+        <v>0.0391</v>
       </c>
       <c r="F241" s="14" t="n">
-        <v>0.1337</v>
+        <v>0.1295</v>
       </c>
       <c r="G241" s="16" t="n">
         <v>46295</v>
@@ -18957,7 +18957,7 @@
         <v>1525</v>
       </c>
       <c r="M241" s="14" t="n">
-        <v>0.5542193232776191</v>
+        <v>0.5601023017902813</v>
       </c>
       <c r="N241" s="12" t="inlineStr">
         <is>
@@ -19005,13 +19005,13 @@
         </is>
       </c>
       <c r="D242" s="4" t="n">
-        <v>211.69</v>
+        <v>217.99</v>
       </c>
       <c r="E242" s="25" t="n">
-        <v>-0.1479</v>
+        <v>-0.1225</v>
       </c>
       <c r="F242" s="5" t="n">
-        <v>0.1592</v>
+        <v>0.1937</v>
       </c>
       <c r="G242" s="6" t="n">
         <v>46336</v>
@@ -19066,13 +19066,13 @@
         </is>
       </c>
       <c r="D243" s="13" t="n">
-        <v>333.08</v>
+        <v>333.94</v>
       </c>
       <c r="E243" s="14" t="n">
-        <v>0.1053</v>
+        <v>0.1081</v>
       </c>
       <c r="F243" s="14" t="n">
-        <v>0.2227</v>
+        <v>0.2258</v>
       </c>
       <c r="G243" s="16" t="n">
         <v>46324</v>
@@ -19127,13 +19127,13 @@
         </is>
       </c>
       <c r="D244" s="4" t="n">
-        <v>139.67</v>
+        <v>138.47</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>0.1689</v>
+        <v>0.1588</v>
       </c>
       <c r="F244" s="5" t="n">
-        <v>0.334</v>
+        <v>0.3225</v>
       </c>
       <c r="G244" s="6" t="n">
         <v>46323</v>
@@ -19162,7 +19162,7 @@
         <v>160</v>
       </c>
       <c r="M244" s="5" t="n">
-        <v>0.1455573852652682</v>
+        <v>0.1554849425868419</v>
       </c>
       <c r="N244" s="3" t="inlineStr">
         <is>
@@ -19173,7 +19173,7 @@
         <v>150</v>
       </c>
       <c r="P244" s="5" t="n">
-        <v>0.07396004868618897</v>
+        <v>0.08326713367516431</v>
       </c>
       <c r="Q244" s="9" t="inlineStr">
         <is>
@@ -19218,13 +19218,13 @@
         </is>
       </c>
       <c r="D245" s="13" t="n">
-        <v>69.61</v>
+        <v>69.97</v>
       </c>
       <c r="E245" s="14" t="n">
-        <v>0.0574</v>
+        <v>0.0629</v>
       </c>
       <c r="F245" s="14" t="n">
-        <v>0.2631</v>
+        <v>0.2696</v>
       </c>
       <c r="G245" s="16" t="n"/>
       <c r="H245" s="21" t="inlineStr">
@@ -19269,13 +19269,13 @@
         </is>
       </c>
       <c r="D246" s="4" t="n">
-        <v>218.87</v>
+        <v>219.34</v>
       </c>
       <c r="E246" s="25" t="n">
-        <v>-0.004</v>
+        <v>-0.0018</v>
       </c>
       <c r="F246" s="5" t="n">
-        <v>0.0767</v>
+        <v>0.079</v>
       </c>
       <c r="G246" s="6" t="n"/>
       <c r="H246" s="7" t="inlineStr">
@@ -19294,7 +19294,7 @@
         <v>315</v>
       </c>
       <c r="M246" s="5" t="n">
-        <v>0.4392104902453511</v>
+        <v>0.4361265615026899</v>
       </c>
       <c r="N246" s="3" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>413</v>
       </c>
       <c r="P246" s="5" t="n">
-        <v>0.8869648649883493</v>
+        <v>0.8829214917479712</v>
       </c>
       <c r="Q246" s="9" t="inlineStr">
         <is>
@@ -19354,13 +19354,13 @@
         </is>
       </c>
       <c r="D247" s="13" t="n">
-        <v>349.06</v>
+        <v>348.07</v>
       </c>
       <c r="E247" s="15" t="n">
-        <v>-0.1072</v>
+        <v>-0.1097</v>
       </c>
       <c r="F247" s="15" t="n">
-        <v>-0.1942</v>
+        <v>-0.1965</v>
       </c>
       <c r="G247" s="16" t="n">
         <v>46331</v>
@@ -19415,13 +19415,13 @@
         </is>
       </c>
       <c r="D248" s="4" t="n">
-        <v>223.43</v>
+        <v>227.95</v>
       </c>
       <c r="E248" s="25" t="n">
-        <v>-0.0225</v>
+        <v>-0.0027</v>
       </c>
       <c r="F248" s="25" t="n">
-        <v>-0.1638</v>
+        <v>-0.1468</v>
       </c>
       <c r="G248" s="6" t="n">
         <v>46322</v>
@@ -19472,13 +19472,13 @@
         </is>
       </c>
       <c r="D249" s="13" t="n">
-        <v>10.1</v>
+        <v>10.96</v>
       </c>
       <c r="E249" s="15" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="F249" s="15" t="n">
-        <v>-0.3536</v>
+        <v>-0.2986</v>
       </c>
       <c r="G249" s="16" t="n"/>
       <c r="H249" s="21" t="inlineStr">
@@ -19523,13 +19523,13 @@
         </is>
       </c>
       <c r="D250" s="4" t="n">
-        <v>189.86</v>
+        <v>190.02</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>0.3192</v>
+        <v>0.3203</v>
       </c>
       <c r="F250" s="5" t="n">
-        <v>0.2793</v>
+        <v>0.2804</v>
       </c>
       <c r="G250" s="6" t="n"/>
       <c r="H250" s="7" t="inlineStr">
@@ -19548,7 +19548,7 @@
         <v>150</v>
       </c>
       <c r="M250" s="25" t="n">
-        <v>-0.2099441693879701</v>
+        <v>-0.2106094095358384</v>
       </c>
       <c r="N250" s="3" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>130</v>
       </c>
       <c r="P250" s="25" t="n">
-        <v>-0.3152849468029075</v>
+        <v>-0.3158614882643933</v>
       </c>
       <c r="Q250" s="9" t="inlineStr">
         <is>
@@ -19600,13 +19600,13 @@
         </is>
       </c>
       <c r="D251" s="13" t="n">
-        <v>68.31</v>
+        <v>68.3</v>
       </c>
       <c r="E251" s="15" t="n">
-        <v>-0.1399</v>
+        <v>-0.14</v>
       </c>
       <c r="F251" s="15" t="n">
-        <v>-0.2121</v>
+        <v>-0.2122</v>
       </c>
       <c r="G251" s="16" t="n">
         <v>46328</v>
@@ -19661,13 +19661,13 @@
         </is>
       </c>
       <c r="D252" s="4" t="n">
-        <v>251.36</v>
+        <v>250.03</v>
       </c>
       <c r="E252" s="25" t="n">
-        <v>-0.2031</v>
+        <v>-0.2073</v>
       </c>
       <c r="F252" s="25" t="n">
-        <v>-0.09759999999999999</v>
+        <v>-0.1024</v>
       </c>
       <c r="G252" s="6" t="n">
         <v>46331</v>
@@ -19722,13 +19722,13 @@
         </is>
       </c>
       <c r="D253" s="13" t="n">
-        <v>150.44</v>
+        <v>150.59</v>
       </c>
       <c r="E253" s="14" t="n">
-        <v>0.0536</v>
+        <v>0.0546</v>
       </c>
       <c r="F253" s="14" t="n">
-        <v>0.2394</v>
+        <v>0.2406</v>
       </c>
       <c r="G253" s="16" t="n"/>
       <c r="H253" s="21" t="inlineStr">
@@ -19747,7 +19747,7 @@
         <v>280</v>
       </c>
       <c r="M253" s="14" t="n">
-        <v>0.8612071257644244</v>
+        <v>0.8593532107045621</v>
       </c>
       <c r="N253" s="12" t="inlineStr">
         <is>
@@ -19758,7 +19758,7 @@
         <v>245</v>
       </c>
       <c r="P253" s="14" t="n">
-        <v>0.6285562350438714</v>
+        <v>0.6269340593664917</v>
       </c>
       <c r="Q253" s="19" t="inlineStr">
         <is>
@@ -19799,13 +19799,13 @@
         </is>
       </c>
       <c r="D254" s="4" t="n">
-        <v>378.63</v>
+        <v>375.06</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>0.012</v>
+        <v>0.0025</v>
       </c>
       <c r="F254" s="5" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0757</v>
       </c>
       <c r="G254" s="6" t="n"/>
       <c r="H254" s="7" t="inlineStr">
@@ -19824,7 +19824,7 @@
         <v>420</v>
       </c>
       <c r="M254" s="5" t="n">
-        <v>0.1092623405435386</v>
+        <v>0.1198208286674132</v>
       </c>
       <c r="N254" s="3" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>415</v>
       </c>
       <c r="P254" s="5" t="n">
-        <v>0.09605683648944882</v>
+        <v>0.1064896283261345</v>
       </c>
       <c r="Q254" s="9" t="inlineStr">
         <is>
@@ -19884,13 +19884,13 @@
         </is>
       </c>
       <c r="D255" s="13" t="n">
-        <v>13.92</v>
+        <v>13.76</v>
       </c>
       <c r="E255" s="15" t="n">
-        <v>-0.1065</v>
+        <v>-0.1168</v>
       </c>
       <c r="F255" s="14" t="n">
-        <v>0.1447</v>
+        <v>0.1316</v>
       </c>
       <c r="G255" s="16" t="n"/>
       <c r="H255" s="21" t="inlineStr">
@@ -19935,13 +19935,13 @@
         </is>
       </c>
       <c r="D256" s="4" t="n">
-        <v>36</v>
+        <v>36.07</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>0.1077</v>
+        <v>0.1098</v>
       </c>
       <c r="F256" s="5" t="n">
-        <v>0.136</v>
+        <v>0.1382</v>
       </c>
       <c r="G256" s="6" t="n">
         <v>46315</v>
@@ -19996,13 +19996,13 @@
         </is>
       </c>
       <c r="D257" s="13" t="n">
-        <v>181.07</v>
+        <v>179.73</v>
       </c>
       <c r="E257" s="14" t="n">
-        <v>0.07730000000000001</v>
+        <v>0.0694</v>
       </c>
       <c r="F257" s="14" t="n">
-        <v>0.3148</v>
+        <v>0.305</v>
       </c>
       <c r="G257" s="16" t="n">
         <v>46330</v>
@@ -20057,13 +20057,13 @@
         </is>
       </c>
       <c r="D258" s="4" t="n">
-        <v>176.33</v>
+        <v>176.24</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>0.0279</v>
+        <v>0.0274</v>
       </c>
       <c r="F258" s="5" t="n">
-        <v>0.3076</v>
+        <v>0.3069</v>
       </c>
       <c r="G258" s="6" t="n">
         <v>46328</v>
@@ -20118,13 +20118,13 @@
         </is>
       </c>
       <c r="D259" s="13" t="n">
-        <v>117.38</v>
+        <v>117.13</v>
       </c>
       <c r="E259" s="15" t="n">
-        <v>-0.1213</v>
+        <v>-0.1231</v>
       </c>
       <c r="F259" s="15" t="n">
-        <v>-0.1278</v>
+        <v>-0.1297</v>
       </c>
       <c r="G259" s="16" t="n"/>
       <c r="H259" s="21" t="inlineStr">
@@ -20179,13 +20179,13 @@
         </is>
       </c>
       <c r="D260" s="4" t="n">
-        <v>17.46</v>
+        <v>17.69</v>
       </c>
       <c r="E260" s="25" t="n">
-        <v>-0.106</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="F260" s="5" t="n">
-        <v>0.0443</v>
+        <v>0.058</v>
       </c>
       <c r="G260" s="6" t="n">
         <v>46331</v>
@@ -20240,13 +20240,13 @@
         </is>
       </c>
       <c r="D261" s="13" t="n">
-        <v>188.36</v>
+        <v>188.71</v>
       </c>
       <c r="E261" s="14" t="n">
-        <v>0.1759</v>
+        <v>0.178</v>
       </c>
       <c r="F261" s="14" t="n">
-        <v>0.1059</v>
+        <v>0.108</v>
       </c>
       <c r="G261" s="16" t="n">
         <v>46330</v>
@@ -20275,7 +20275,7 @@
         <v>265</v>
       </c>
       <c r="M261" s="14" t="n">
-        <v>0.4068804417073688</v>
+        <v>0.4042711038100789</v>
       </c>
       <c r="N261" s="12" t="inlineStr">
         <is>
@@ -20286,7 +20286,7 @@
         <v>179</v>
       </c>
       <c r="P261" s="15" t="n">
-        <v>-0.04969207899766412</v>
+        <v>-0.05145461289809765</v>
       </c>
       <c r="Q261" s="19" t="inlineStr">
         <is>
@@ -20331,13 +20331,13 @@
         </is>
       </c>
       <c r="D262" s="4" t="n">
-        <v>117.19</v>
+        <v>119.51</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>0.2246</v>
+        <v>0.2488</v>
       </c>
       <c r="F262" s="5" t="n">
-        <v>0.3672</v>
+        <v>0.3942</v>
       </c>
       <c r="G262" s="6" t="n">
         <v>46322</v>
@@ -20392,13 +20392,13 @@
         </is>
       </c>
       <c r="D263" s="13" t="n">
-        <v>8.380000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="E263" s="15" t="n">
-        <v>-0.0164</v>
+        <v>-0.009399999999999999</v>
       </c>
       <c r="F263" s="14" t="n">
-        <v>0.0581</v>
+        <v>0.06570000000000001</v>
       </c>
       <c r="G263" s="16" t="n"/>
       <c r="H263" s="21" t="inlineStr">
@@ -20443,13 +20443,13 @@
         </is>
       </c>
       <c r="D264" s="4" t="n">
-        <v>108.18</v>
+        <v>107.83</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>0.0759</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="F264" s="5" t="n">
-        <v>0.3837</v>
+        <v>0.3793</v>
       </c>
       <c r="G264" s="6" t="n"/>
       <c r="H264" s="7" t="inlineStr">
@@ -20494,13 +20494,13 @@
         </is>
       </c>
       <c r="D265" s="13" t="n">
-        <v>15.77</v>
+        <v>15.99</v>
       </c>
       <c r="E265" s="15" t="n">
-        <v>-0.1093</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="F265" s="14" t="n">
-        <v>0.107</v>
+        <v>0.1221</v>
       </c>
       <c r="G265" s="16" t="n">
         <v>46335</v>
@@ -20555,13 +20555,13 @@
         </is>
       </c>
       <c r="D266" s="4" t="n">
-        <v>374.95</v>
+        <v>374.76</v>
       </c>
       <c r="E266" s="25" t="n">
-        <v>-0.0488</v>
+        <v>-0.0492</v>
       </c>
       <c r="F266" s="5" t="n">
-        <v>0.0334</v>
+        <v>0.0329</v>
       </c>
       <c r="G266" s="6" t="n">
         <v>46317</v>
@@ -20630,13 +20630,13 @@
         </is>
       </c>
       <c r="D267" s="13" t="n">
-        <v>3.88</v>
+        <v>3.92</v>
       </c>
       <c r="E267" s="14" t="n">
-        <v>0.1037</v>
+        <v>0.1136</v>
       </c>
       <c r="F267" s="15" t="n">
-        <v>-0.0965</v>
+        <v>-0.08839999999999999</v>
       </c>
       <c r="G267" s="16" t="n">
         <v>46331</v>
@@ -20691,13 +20691,13 @@
         </is>
       </c>
       <c r="D268" s="4" t="n">
-        <v>23.68</v>
+        <v>23.19</v>
       </c>
       <c r="E268" s="5" t="n">
-        <v>0.05309999999999999</v>
+        <v>0.0311</v>
       </c>
       <c r="F268" s="5" t="n">
-        <v>0.2171</v>
+        <v>0.1917</v>
       </c>
       <c r="G268" s="6" t="n"/>
       <c r="H268" s="7" t="inlineStr">
@@ -20742,13 +20742,13 @@
         </is>
       </c>
       <c r="D269" s="13" t="n">
-        <v>20.2</v>
+        <v>20.19</v>
       </c>
       <c r="E269" s="14" t="n">
-        <v>0.0521</v>
+        <v>0.0516</v>
       </c>
       <c r="F269" s="14" t="n">
-        <v>0.3272</v>
+        <v>0.3265</v>
       </c>
       <c r="G269" s="16" t="n"/>
       <c r="H269" s="21" t="inlineStr">
@@ -20793,13 +20793,13 @@
         </is>
       </c>
       <c r="D270" s="4" t="n">
-        <v>199.91</v>
-      </c>
-      <c r="E270" s="5" t="n">
-        <v>0.008199999999999999</v>
+        <v>196.06</v>
+      </c>
+      <c r="E270" s="25" t="n">
+        <v>-0.0112</v>
       </c>
       <c r="F270" s="25" t="n">
-        <v>-0.0097</v>
+        <v>-0.0288</v>
       </c>
       <c r="G270" s="6" t="n">
         <v>46328</v>
@@ -20854,13 +20854,13 @@
         </is>
       </c>
       <c r="D271" s="13" t="n">
-        <v>215.03</v>
+        <v>213.66</v>
       </c>
       <c r="E271" s="14" t="n">
-        <v>0.0217</v>
+        <v>0.0152</v>
       </c>
       <c r="F271" s="14" t="n">
-        <v>0.3579</v>
+        <v>0.3493</v>
       </c>
       <c r="G271" s="16" t="n">
         <v>46316</v>
@@ -20935,13 +20935,13 @@
         </is>
       </c>
       <c r="D272" s="4" t="n">
-        <v>40.38</v>
+        <v>40.35</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>0.0795</v>
+        <v>0.0786</v>
       </c>
       <c r="F272" s="5" t="n">
-        <v>0.6947</v>
+        <v>0.6931999999999999</v>
       </c>
       <c r="G272" s="6" t="n">
         <v>46329</v>
@@ -20996,13 +20996,13 @@
         </is>
       </c>
       <c r="D273" s="13" t="n">
-        <v>343.49</v>
+        <v>338.39</v>
       </c>
       <c r="E273" s="14" t="n">
-        <v>0.0558</v>
+        <v>0.0401</v>
       </c>
       <c r="F273" s="14" t="n">
-        <v>0.2521</v>
+        <v>0.2335</v>
       </c>
       <c r="G273" s="16" t="n"/>
       <c r="H273" s="21" t="inlineStr">
@@ -21021,7 +21021,7 @@
         <v>320</v>
       </c>
       <c r="M273" s="15" t="n">
-        <v>-0.06838627034265921</v>
+        <v>-0.05434557758799015</v>
       </c>
       <c r="N273" s="12" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>280</v>
       </c>
       <c r="P273" s="15" t="n">
-        <v>-0.1848379865498268</v>
+        <v>-0.1725523803894914</v>
       </c>
       <c r="Q273" s="19" t="inlineStr">
         <is>
@@ -21073,13 +21073,13 @@
         </is>
       </c>
       <c r="D274" s="4" t="n">
-        <v>382.6</v>
+        <v>381.17</v>
       </c>
       <c r="E274" s="25" t="n">
-        <v>-0.0539</v>
+        <v>-0.0575</v>
       </c>
       <c r="F274" s="5" t="n">
-        <v>0.0109</v>
+        <v>0.0072</v>
       </c>
       <c r="G274" s="6" t="n"/>
       <c r="H274" s="7" t="inlineStr">
@@ -21098,7 +21098,7 @@
         <v>535</v>
       </c>
       <c r="M274" s="5" t="n">
-        <v>0.3983272347098797</v>
+        <v>0.4035732088044704</v>
       </c>
       <c r="N274" s="3" t="inlineStr"/>
       <c r="O274" s="8" t="n"/>
@@ -21142,13 +21142,13 @@
         </is>
       </c>
       <c r="D275" s="13" t="n">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="E275" s="15" t="n">
-        <v>-0.1352</v>
+        <v>-0.1416</v>
       </c>
       <c r="F275" s="15" t="n">
-        <v>-0.042</v>
+        <v>-0.0491</v>
       </c>
       <c r="G275" s="16" t="n">
         <v>46331</v>
@@ -21203,13 +21203,13 @@
         </is>
       </c>
       <c r="D276" s="4" t="n">
-        <v>88.88</v>
+        <v>91.31999999999999</v>
       </c>
       <c r="E276" s="5" t="n">
-        <v>0.318</v>
+        <v>0.3543</v>
       </c>
       <c r="F276" s="5" t="n">
-        <v>0.4862</v>
+        <v>0.5271</v>
       </c>
       <c r="G276" s="6" t="n">
         <v>46322</v>
@@ -21264,13 +21264,13 @@
         </is>
       </c>
       <c r="D277" s="13" t="n">
-        <v>91.3</v>
+        <v>91.12</v>
       </c>
       <c r="E277" s="15" t="n">
-        <v>-0.1291</v>
+        <v>-0.1308</v>
       </c>
       <c r="F277" s="15" t="n">
-        <v>-0.1963</v>
+        <v>-0.1979</v>
       </c>
       <c r="G277" s="16" t="n">
         <v>46331</v>
@@ -21325,13 +21325,13 @@
         </is>
       </c>
       <c r="D278" s="4" t="n">
-        <v>202.04</v>
-      </c>
-      <c r="E278" s="25" t="n">
-        <v>-0.0143</v>
-      </c>
-      <c r="F278" s="25" t="n">
-        <v>-0.0054</v>
+        <v>206.6</v>
+      </c>
+      <c r="E278" s="5" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="F278" s="5" t="n">
+        <v>0.017</v>
       </c>
       <c r="G278" s="6" t="n">
         <v>46330</v>
@@ -21386,13 +21386,13 @@
         </is>
       </c>
       <c r="D279" s="13" t="n">
-        <v>357.93</v>
+        <v>353.13</v>
       </c>
       <c r="E279" s="15" t="n">
-        <v>-0.1147</v>
+        <v>-0.1265</v>
       </c>
       <c r="F279" s="14" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.058</v>
       </c>
       <c r="G279" s="16" t="n">
         <v>46322</v>
@@ -21447,13 +21447,13 @@
         </is>
       </c>
       <c r="D280" s="4" t="n">
-        <v>57.62</v>
+        <v>57.33</v>
       </c>
       <c r="E280" s="5" t="n">
-        <v>0.0111</v>
+        <v>0.006</v>
       </c>
       <c r="F280" s="5" t="n">
-        <v>0.08289999999999999</v>
+        <v>0.0774</v>
       </c>
       <c r="G280" s="6" t="n">
         <v>46330</v>
@@ -21508,13 +21508,13 @@
         </is>
       </c>
       <c r="D281" s="13" t="n">
-        <v>424.79</v>
+        <v>430.26</v>
       </c>
       <c r="E281" s="14" t="n">
-        <v>0.0275</v>
+        <v>0.0408</v>
       </c>
       <c r="F281" s="14" t="n">
-        <v>0.0559</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="G281" s="16" t="n">
         <v>46310</v>
@@ -21591,13 +21591,13 @@
         </is>
       </c>
       <c r="D282" s="4" t="n">
-        <v>115.71</v>
+        <v>114.77</v>
       </c>
       <c r="E282" s="25" t="n">
-        <v>-0.0795</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="F282" s="25" t="n">
-        <v>-0.1311</v>
+        <v>-0.1382</v>
       </c>
       <c r="G282" s="6" t="n">
         <v>46330</v>
@@ -21652,13 +21652,13 @@
         </is>
       </c>
       <c r="D283" s="13" t="n">
-        <v>244.04</v>
+        <v>246.24</v>
       </c>
       <c r="E283" s="14" t="n">
-        <v>0.0515</v>
+        <v>0.0609</v>
       </c>
       <c r="F283" s="14" t="n">
-        <v>0.1891</v>
+        <v>0.1998</v>
       </c>
       <c r="G283" s="16" t="n">
         <v>46324</v>
@@ -21713,13 +21713,13 @@
         </is>
       </c>
       <c r="D284" s="4" t="n">
-        <v>258.07</v>
+        <v>258.14</v>
       </c>
       <c r="E284" s="25" t="n">
-        <v>-0.0521</v>
+        <v>-0.0518</v>
       </c>
       <c r="F284" s="25" t="n">
-        <v>-0.0915</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="G284" s="6" t="n">
         <v>46315</v>
@@ -21748,7 +21748,7 @@
         <v>300</v>
       </c>
       <c r="M284" s="5" t="n">
-        <v>0.1624752973999303</v>
+        <v>0.1621600681800574</v>
       </c>
       <c r="N284" s="3" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>316</v>
       </c>
       <c r="P284" s="5" t="n">
-        <v>0.2244739799279266</v>
+        <v>0.2241419384829938</v>
       </c>
       <c r="Q284" s="9" t="inlineStr">
         <is>
@@ -21816,13 +21816,13 @@
         </is>
       </c>
       <c r="D285" s="13" t="n">
-        <v>340.79</v>
+        <v>341.57</v>
       </c>
       <c r="E285" s="14" t="n">
-        <v>0.0258</v>
+        <v>0.0282</v>
       </c>
       <c r="F285" s="14" t="n">
-        <v>0.0718</v>
+        <v>0.07429999999999999</v>
       </c>
       <c r="G285" s="16" t="n">
         <v>46330</v>
@@ -21851,7 +21851,7 @@
         <v>335</v>
       </c>
       <c r="M285" s="15" t="n">
-        <v>-0.01698993515067936</v>
+        <v>-0.01923471030828233</v>
       </c>
       <c r="N285" s="12" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>375</v>
       </c>
       <c r="P285" s="14" t="n">
-        <v>0.1003844009507321</v>
+        <v>0.09787159293848993</v>
       </c>
       <c r="Q285" s="19" t="inlineStr">
         <is>
@@ -21903,13 +21903,13 @@
         </is>
       </c>
       <c r="D286" s="4" t="n">
-        <v>42.57</v>
+        <v>41.84</v>
       </c>
       <c r="E286" s="25" t="n">
-        <v>-0.0892</v>
+        <v>-0.1048</v>
       </c>
       <c r="F286" s="5" t="n">
-        <v>0.428</v>
+        <v>0.4036</v>
       </c>
       <c r="G286" s="6" t="n">
         <v>46330</v>
@@ -21964,13 +21964,13 @@
         </is>
       </c>
       <c r="D287" s="13" t="n">
-        <v>6.14</v>
+        <v>6.09</v>
       </c>
       <c r="E287" s="15" t="n">
-        <v>-0.06610000000000001</v>
+        <v>-0.0745</v>
       </c>
       <c r="F287" s="15" t="n">
-        <v>-0.1999</v>
+        <v>-0.207</v>
       </c>
       <c r="G287" s="16" t="n"/>
       <c r="H287" s="21" t="inlineStr">
@@ -22015,13 +22015,13 @@
         </is>
       </c>
       <c r="D288" s="4" t="n">
-        <v>197.56</v>
+        <v>199.28</v>
       </c>
       <c r="E288" s="5" t="n">
-        <v>0.0363</v>
+        <v>0.0453</v>
       </c>
       <c r="F288" s="5" t="n">
-        <v>0.3419</v>
+        <v>0.3536</v>
       </c>
       <c r="G288" s="6" t="n"/>
       <c r="H288" s="7" t="inlineStr">
@@ -22066,13 +22066,13 @@
         </is>
       </c>
       <c r="D289" s="13" t="n">
-        <v>423.56</v>
+        <v>423.87</v>
       </c>
       <c r="E289" s="15" t="n">
-        <v>-0.1463</v>
+        <v>-0.1457</v>
       </c>
       <c r="F289" s="15" t="n">
-        <v>-0.131</v>
+        <v>-0.1304</v>
       </c>
       <c r="G289" s="16" t="n">
         <v>46324</v>
@@ -22101,7 +22101,7 @@
         <v>730</v>
       </c>
       <c r="M289" s="14" t="n">
-        <v>0.7234866370762112</v>
+        <v>0.7222261542454054</v>
       </c>
       <c r="N289" s="12" t="inlineStr">
         <is>
@@ -22112,7 +22112,7 @@
         <v>575</v>
       </c>
       <c r="P289" s="14" t="n">
-        <v>0.3575408442723581</v>
+        <v>0.3565479982069974</v>
       </c>
       <c r="Q289" s="19" t="inlineStr">
         <is>
@@ -22153,13 +22153,13 @@
         </is>
       </c>
       <c r="D290" s="4" t="n">
-        <v>24.08</v>
+        <v>23.74</v>
       </c>
       <c r="E290" s="25" t="n">
-        <v>-0.2347</v>
+        <v>-0.2454</v>
       </c>
       <c r="F290" s="25" t="n">
-        <v>-0.1806</v>
+        <v>-0.192</v>
       </c>
       <c r="G290" s="6" t="n">
         <v>46330</v>
@@ -22214,13 +22214,13 @@
         </is>
       </c>
       <c r="D291" s="13" t="n">
-        <v>93.04000000000001</v>
+        <v>92.16</v>
       </c>
       <c r="E291" s="15" t="n">
-        <v>-0.1115</v>
+        <v>-0.1199</v>
       </c>
       <c r="F291" s="14" t="n">
-        <v>0.0234</v>
+        <v>0.0137</v>
       </c>
       <c r="G291" s="16" t="n"/>
       <c r="H291" s="21" t="inlineStr">
@@ -22265,13 +22265,13 @@
         </is>
       </c>
       <c r="D292" s="4" t="n">
-        <v>195.4</v>
+        <v>197.47</v>
       </c>
       <c r="E292" s="5" t="n">
-        <v>0.05230000000000001</v>
+        <v>0.0634</v>
       </c>
       <c r="F292" s="5" t="n">
-        <v>0.3043</v>
+        <v>0.318</v>
       </c>
       <c r="G292" s="6" t="n"/>
       <c r="H292" s="7" t="inlineStr">
@@ -22316,13 +22316,13 @@
         </is>
       </c>
       <c r="D293" s="13" t="n">
-        <v>284.79</v>
+        <v>286.12</v>
       </c>
       <c r="E293" s="15" t="n">
-        <v>-0.0608</v>
+        <v>-0.0564</v>
       </c>
       <c r="F293" s="15" t="n">
-        <v>-0.0399</v>
+        <v>-0.0354</v>
       </c>
       <c r="G293" s="16" t="n">
         <v>46331</v>
@@ -22377,13 +22377,13 @@
         </is>
       </c>
       <c r="D294" s="4" t="n">
-        <v>86.69</v>
+        <v>86.56</v>
       </c>
       <c r="E294" s="25" t="n">
-        <v>-0.0269</v>
+        <v>-0.0284</v>
       </c>
       <c r="F294" s="5" t="n">
-        <v>0.077</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="G294" s="6" t="n"/>
       <c r="H294" s="7" t="inlineStr">
@@ -22428,13 +22428,13 @@
         </is>
       </c>
       <c r="D295" s="13" t="n">
-        <v>128.82</v>
+        <v>128.46</v>
       </c>
       <c r="E295" s="15" t="n">
-        <v>-0.07200000000000001</v>
+        <v>-0.0746</v>
       </c>
       <c r="F295" s="15" t="n">
-        <v>-0.051</v>
+        <v>-0.0537</v>
       </c>
       <c r="G295" s="16" t="n">
         <v>46331</v>
@@ -22463,7 +22463,7 @@
         <v>166</v>
       </c>
       <c r="M295" s="14" t="n">
-        <v>0.288619779537339</v>
+        <v>0.2922310446831698</v>
       </c>
       <c r="N295" s="12" t="inlineStr"/>
       <c r="O295" s="18" t="n"/>
@@ -22511,13 +22511,13 @@
         </is>
       </c>
       <c r="D296" s="4" t="n">
-        <v>29.59</v>
+        <v>29.49</v>
       </c>
       <c r="E296" s="25" t="n">
-        <v>-0.05110000000000001</v>
+        <v>-0.0545</v>
       </c>
       <c r="F296" s="25" t="n">
-        <v>-0.0255</v>
+        <v>-0.029</v>
       </c>
       <c r="G296" s="6" t="n">
         <v>46317</v>
@@ -22572,13 +22572,13 @@
         </is>
       </c>
       <c r="D297" s="13" t="n">
-        <v>274.38</v>
+        <v>271.68</v>
       </c>
       <c r="E297" s="15" t="n">
-        <v>-0.0201</v>
+        <v>-0.0297</v>
       </c>
       <c r="F297" s="14" t="n">
-        <v>0.0213</v>
+        <v>0.0113</v>
       </c>
       <c r="G297" s="16" t="n">
         <v>46322</v>
@@ -22607,7 +22607,7 @@
         <v>275</v>
       </c>
       <c r="M297" s="14" t="n">
-        <v>0.002259639915445749</v>
+        <v>0.01222025912838631</v>
       </c>
       <c r="N297" s="12" t="inlineStr">
         <is>
@@ -22618,7 +22618,7 @@
         <v>312</v>
       </c>
       <c r="P297" s="14" t="n">
-        <v>0.137109118740433</v>
+        <v>0.1484098939929328</v>
       </c>
       <c r="Q297" s="19" t="inlineStr">
         <is>
@@ -22671,13 +22671,13 @@
         </is>
       </c>
       <c r="D298" s="4" t="n">
-        <v>32.93</v>
+        <v>33.16</v>
       </c>
       <c r="E298" s="25" t="n">
-        <v>-0.1169</v>
+        <v>-0.1108</v>
       </c>
       <c r="F298" s="25" t="n">
-        <v>-0.0968</v>
+        <v>-0.09050000000000001</v>
       </c>
       <c r="G298" s="6" t="n">
         <v>46322</v>
@@ -22736,13 +22736,13 @@
         </is>
       </c>
       <c r="D299" s="13" t="n">
-        <v>71.14</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="E299" s="14" t="n">
-        <v>0.0727</v>
+        <v>0.0683</v>
       </c>
       <c r="F299" s="14" t="n">
-        <v>0.2101</v>
+        <v>0.2051</v>
       </c>
       <c r="G299" s="16" t="n">
         <v>46310</v>
@@ -22797,13 +22797,13 @@
         </is>
       </c>
       <c r="D300" s="4" t="n">
-        <v>456.81</v>
+        <v>458.48</v>
       </c>
       <c r="E300" s="25" t="n">
-        <v>-0.0457</v>
+        <v>-0.0423</v>
       </c>
       <c r="F300" s="25" t="n">
-        <v>-0.1079</v>
+        <v>-0.1046</v>
       </c>
       <c r="G300" s="6" t="n">
         <v>46325</v>
@@ -22832,7 +22832,7 @@
         <v>570</v>
       </c>
       <c r="M300" s="5" t="n">
-        <v>0.247783542391804</v>
+        <v>0.2432385273076252</v>
       </c>
       <c r="N300" s="3" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>525</v>
       </c>
       <c r="P300" s="5" t="n">
-        <v>0.1492743153608721</v>
+        <v>0.1450881172570232</v>
       </c>
       <c r="Q300" s="9" t="inlineStr">
         <is>
@@ -22896,13 +22896,13 @@
         </is>
       </c>
       <c r="D301" s="13" t="n">
-        <v>492.74</v>
+        <v>494.44</v>
       </c>
       <c r="E301" s="15" t="n">
-        <v>-0.0575</v>
+        <v>-0.05429999999999999</v>
       </c>
       <c r="F301" s="15" t="n">
-        <v>-0.11</v>
+        <v>-0.1069</v>
       </c>
       <c r="G301" s="16" t="n">
         <v>46329</v>
@@ -22931,7 +22931,7 @@
         <v>616</v>
       </c>
       <c r="M301" s="14" t="n">
-        <v>0.2501522100905142</v>
+        <v>0.245853895315913</v>
       </c>
       <c r="N301" s="12" t="inlineStr"/>
       <c r="O301" s="18" t="n"/>
@@ -22975,13 +22975,13 @@
         </is>
       </c>
       <c r="D302" s="4" t="n">
-        <v>266.67</v>
+        <v>265.14</v>
       </c>
       <c r="E302" s="5" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.0036</v>
       </c>
       <c r="F302" s="5" t="n">
-        <v>0.1557</v>
+        <v>0.1491</v>
       </c>
       <c r="G302" s="6" t="n">
         <v>46321</v>
@@ -23010,7 +23010,7 @@
         <v>283</v>
       </c>
       <c r="M302" s="5" t="n">
-        <v>0.06123673454081818</v>
+        <v>0.06736063966206537</v>
       </c>
       <c r="N302" s="3" t="inlineStr"/>
       <c r="O302" s="8" t="n"/>
@@ -23056,13 +23056,13 @@
         </is>
       </c>
       <c r="D303" s="13" t="n">
-        <v>234.77</v>
+        <v>235.57</v>
       </c>
       <c r="E303" s="15" t="n">
-        <v>-0.062</v>
+        <v>-0.0588</v>
       </c>
       <c r="F303" s="14" t="n">
-        <v>0.0278</v>
+        <v>0.0313</v>
       </c>
       <c r="G303" s="16" t="n">
         <v>46323</v>
@@ -23091,7 +23091,7 @@
         <v>246</v>
       </c>
       <c r="M303" s="14" t="n">
-        <v>0.04783405034714823</v>
+        <v>0.04427558687438981</v>
       </c>
       <c r="N303" s="12" t="inlineStr"/>
       <c r="O303" s="18" t="n"/>
@@ -23139,13 +23139,13 @@
         </is>
       </c>
       <c r="D304" s="4" t="n">
-        <v>105.43</v>
+        <v>105.45</v>
       </c>
       <c r="E304" s="25" t="n">
-        <v>-0.0654</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="F304" s="25" t="n">
-        <v>-0.0888</v>
+        <v>-0.0886</v>
       </c>
       <c r="G304" s="6" t="n">
         <v>46322</v>
@@ -23174,7 +23174,7 @@
         <v>130</v>
       </c>
       <c r="M304" s="5" t="n">
-        <v>0.2330456226880394</v>
+        <v>0.2328117591275486</v>
       </c>
       <c r="N304" s="3" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>128</v>
       </c>
       <c r="P304" s="5" t="n">
-        <v>0.2140756900313003</v>
+        <v>0.2138454243717401</v>
       </c>
       <c r="Q304" s="9" t="inlineStr">
         <is>
@@ -23234,13 +23234,13 @@
         </is>
       </c>
       <c r="D305" s="13" t="n">
-        <v>99.68000000000001</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="E305" s="15" t="n">
-        <v>-0.0984</v>
+        <v>-0.1028</v>
       </c>
       <c r="F305" s="15" t="n">
-        <v>-0.0192</v>
+        <v>-0.0241</v>
       </c>
       <c r="G305" s="16" t="n">
         <v>46301</v>
@@ -23269,7 +23269,7 @@
         <v>135</v>
       </c>
       <c r="M305" s="14" t="n">
-        <v>0.3543338683788121</v>
+        <v>0.3611615245009073</v>
       </c>
       <c r="N305" s="12" t="inlineStr">
         <is>
@@ -23280,7 +23280,7 @@
         <v>125</v>
       </c>
       <c r="P305" s="14" t="n">
-        <v>0.2540128410914927</v>
+        <v>0.2603347449082475</v>
       </c>
       <c r="Q305" s="19" t="inlineStr"/>
       <c r="R305" s="18" t="n"/>
@@ -23315,13 +23315,13 @@
         </is>
       </c>
       <c r="D306" s="4" t="n">
-        <v>322.1</v>
+        <v>320.94</v>
       </c>
       <c r="E306" s="25" t="n">
-        <v>-0.06709999999999999</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="F306" s="25" t="n">
-        <v>-0.0046</v>
+        <v>-0.008199999999999999</v>
       </c>
       <c r="G306" s="6" t="n">
         <v>46322</v>
@@ -23350,7 +23350,7 @@
         <v>350</v>
       </c>
       <c r="M306" s="5" t="n">
-        <v>0.08661906240298037</v>
+        <v>0.09054651959867889</v>
       </c>
       <c r="N306" s="3" t="inlineStr">
         <is>
@@ -23361,7 +23361,7 @@
         <v>400</v>
       </c>
       <c r="P306" s="5" t="n">
-        <v>0.2418503570319775</v>
+        <v>0.2463388795413473</v>
       </c>
       <c r="Q306" s="9" t="inlineStr">
         <is>
@@ -23402,13 +23402,13 @@
         </is>
       </c>
       <c r="D307" s="13" t="n">
-        <v>103.2</v>
+        <v>103.99</v>
       </c>
       <c r="E307" s="15" t="n">
-        <v>-0.1184</v>
+        <v>-0.1117</v>
       </c>
       <c r="F307" s="14" t="n">
-        <v>0.4758</v>
+        <v>0.4871</v>
       </c>
       <c r="G307" s="16" t="n"/>
       <c r="H307" s="21" t="inlineStr">
@@ -23449,13 +23449,13 @@
         </is>
       </c>
       <c r="D308" s="4" t="n">
-        <v>54.4</v>
+        <v>54.5</v>
       </c>
       <c r="E308" s="25" t="n">
-        <v>-0.0857</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="F308" s="25" t="n">
-        <v>-0.05139999999999999</v>
+        <v>-0.04969999999999999</v>
       </c>
       <c r="G308" s="6" t="n">
         <v>46267</v>
@@ -23510,13 +23510,13 @@
         </is>
       </c>
       <c r="D309" s="13" t="n">
-        <v>68.23</v>
+        <v>68.16</v>
       </c>
       <c r="E309" s="15" t="n">
-        <v>-0.0806</v>
+        <v>-0.0815</v>
       </c>
       <c r="F309" s="15" t="n">
-        <v>-0.1532</v>
+        <v>-0.154</v>
       </c>
       <c r="G309" s="16" t="n">
         <v>46315</v>
@@ -23545,14 +23545,14 @@
         <v>83</v>
       </c>
       <c r="M309" s="14" t="n">
-        <v>0.2164736919243734</v>
+        <v>0.2177230046948357</v>
       </c>
       <c r="N309" s="12" t="inlineStr"/>
       <c r="O309" s="18" t="n">
         <v>87</v>
       </c>
       <c r="P309" s="14" t="n">
-        <v>0.2750989300894034</v>
+        <v>0.2764084507042254</v>
       </c>
       <c r="Q309" s="19" t="inlineStr"/>
       <c r="R309" s="18" t="n"/>
@@ -23587,13 +23587,13 @@
         </is>
       </c>
       <c r="D310" s="4" t="n">
-        <v>176.6</v>
+        <v>175.58</v>
       </c>
       <c r="E310" s="5" t="n">
-        <v>0.0248</v>
+        <v>0.0189</v>
       </c>
       <c r="F310" s="5" t="n">
-        <v>0.0571</v>
+        <v>0.051</v>
       </c>
       <c r="G310" s="6" t="n">
         <v>46322</v>
@@ -23622,7 +23622,7 @@
         <v>200</v>
       </c>
       <c r="M310" s="5" t="n">
-        <v>0.1325028312570782</v>
+        <v>0.1390818999886091</v>
       </c>
       <c r="N310" s="3" t="inlineStr"/>
       <c r="O310" s="8" t="n"/>
@@ -23670,13 +23670,13 @@
         </is>
       </c>
       <c r="D311" s="13" t="n">
-        <v>140.18</v>
+        <v>139.32</v>
       </c>
       <c r="E311" s="15" t="n">
-        <v>-0.0483</v>
+        <v>-0.0542</v>
       </c>
       <c r="F311" s="14" t="n">
-        <v>0.0113</v>
+        <v>0.005</v>
       </c>
       <c r="G311" s="16" t="n">
         <v>46317</v>
@@ -23735,13 +23735,13 @@
         </is>
       </c>
       <c r="D312" s="4" t="n">
-        <v>183.58</v>
+        <v>184.26</v>
       </c>
       <c r="E312" s="25" t="n">
-        <v>-0.05980000000000001</v>
+        <v>-0.0563</v>
       </c>
       <c r="F312" s="5" t="n">
-        <v>0.0416</v>
+        <v>0.0454</v>
       </c>
       <c r="G312" s="6" t="n">
         <v>46317</v>
@@ -23770,7 +23770,7 @@
         <v>220</v>
       </c>
       <c r="M312" s="5" t="n">
-        <v>0.1983876239241747</v>
+        <v>0.1939650493867362</v>
       </c>
       <c r="N312" s="3" t="inlineStr">
         <is>
@@ -23781,7 +23781,7 @@
         <v>230</v>
       </c>
       <c r="P312" s="5" t="n">
-        <v>0.2528597886480008</v>
+        <v>0.2482361879952242</v>
       </c>
       <c r="Q312" s="9" t="inlineStr">
         <is>
@@ -23822,13 +23822,13 @@
         </is>
       </c>
       <c r="D313" s="13" t="n">
-        <v>1025.89</v>
+        <v>1025.94</v>
       </c>
       <c r="E313" s="15" t="n">
-        <v>-0.0546</v>
+        <v>-0.0545</v>
       </c>
       <c r="F313" s="14" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="G313" s="16" t="n">
         <v>46330</v>
@@ -23857,7 +23857,7 @@
         <v>1200</v>
       </c>
       <c r="M313" s="14" t="n">
-        <v>0.1697160514285156</v>
+        <v>0.1696590443885607</v>
       </c>
       <c r="N313" s="12" t="inlineStr">
         <is>
@@ -23868,7 +23868,7 @@
         <v>1240</v>
       </c>
       <c r="P313" s="14" t="n">
-        <v>0.2087065864761328</v>
+        <v>0.2086476792015127</v>
       </c>
       <c r="Q313" s="19" t="inlineStr">
         <is>
@@ -23913,13 +23913,13 @@
         </is>
       </c>
       <c r="D314" s="4" t="n">
-        <v>111.72</v>
+        <v>111.76</v>
       </c>
       <c r="E314" s="25" t="n">
-        <v>-0.049</v>
+        <v>-0.0487</v>
       </c>
       <c r="F314" s="25" t="n">
-        <v>-0.1104</v>
+        <v>-0.1101</v>
       </c>
       <c r="G314" s="6" t="n">
         <v>46325</v>
@@ -23948,7 +23948,7 @@
         <v>129</v>
       </c>
       <c r="M314" s="5" t="n">
-        <v>0.154672395273899</v>
+        <v>0.1542591267000715</v>
       </c>
       <c r="N314" s="3" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>122</v>
       </c>
       <c r="P314" s="5" t="n">
-        <v>0.09201575366988902</v>
+        <v>0.09162491052254827</v>
       </c>
       <c r="Q314" s="9" t="inlineStr">
         <is>
@@ -24000,13 +24000,13 @@
         </is>
       </c>
       <c r="D315" s="13" t="n">
-        <v>57.17</v>
+        <v>57.32</v>
       </c>
       <c r="E315" s="15" t="n">
-        <v>-0.08109999999999999</v>
+        <v>-0.0786</v>
       </c>
       <c r="F315" s="15" t="n">
-        <v>-0.123</v>
+        <v>-0.1206</v>
       </c>
       <c r="G315" s="16" t="n">
         <v>46328</v>
@@ -24035,14 +24035,14 @@
         <v>65</v>
       </c>
       <c r="M315" s="14" t="n">
-        <v>0.1369599440265873</v>
+        <v>0.1339846475924634</v>
       </c>
       <c r="N315" s="12" t="inlineStr"/>
       <c r="O315" s="18" t="n">
         <v>67</v>
       </c>
       <c r="P315" s="14" t="n">
-        <v>0.1719433269197131</v>
+        <v>0.1688764829030007</v>
       </c>
       <c r="Q315" s="19" t="inlineStr">
         <is>
@@ -24083,13 +24083,13 @@
         </is>
       </c>
       <c r="D316" s="4" t="n">
-        <v>134.68</v>
+        <v>135.18</v>
       </c>
       <c r="E316" s="25" t="n">
-        <v>-0.0381</v>
+        <v>-0.0346</v>
       </c>
       <c r="F316" s="25" t="n">
-        <v>-0.0868</v>
+        <v>-0.0834</v>
       </c>
       <c r="G316" s="6" t="n">
         <v>46310</v>
@@ -24118,7 +24118,7 @@
         <v>167</v>
       </c>
       <c r="M316" s="5" t="n">
-        <v>0.2399762399762399</v>
+        <v>0.2353898505696108</v>
       </c>
       <c r="N316" s="3" t="inlineStr"/>
       <c r="O316" s="8" t="n"/>
@@ -24162,13 +24162,13 @@
         </is>
       </c>
       <c r="D317" s="13" t="n">
-        <v>297.57</v>
+        <v>300.76</v>
       </c>
       <c r="E317" s="15" t="n">
-        <v>-0.079</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="F317" s="15" t="n">
-        <v>-0.05690000000000001</v>
+        <v>-0.04679999999999999</v>
       </c>
       <c r="G317" s="16" t="n">
         <v>46330</v>
@@ -24204,7 +24204,7 @@
         <v>316</v>
       </c>
       <c r="P317" s="14" t="n">
-        <v>0.06193500688913536</v>
+        <v>0.05067163186593965</v>
       </c>
       <c r="Q317" s="19" t="inlineStr">
         <is>
@@ -24245,13 +24245,13 @@
         </is>
       </c>
       <c r="D318" s="4" t="n">
-        <v>205.28</v>
+        <v>204.47</v>
       </c>
       <c r="E318" s="25" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.0732</v>
       </c>
       <c r="F318" s="25" t="n">
-        <v>-0.1004</v>
+        <v>-0.1039</v>
       </c>
       <c r="G318" s="6" t="n">
         <v>46328</v>
@@ -24287,7 +24287,7 @@
         <v>215</v>
       </c>
       <c r="P318" s="5" t="n">
-        <v>0.04734996102883866</v>
+        <v>0.05149899740793271</v>
       </c>
       <c r="Q318" s="9" t="inlineStr">
         <is>
@@ -24328,13 +24328,13 @@
         </is>
       </c>
       <c r="D319" s="13" t="n">
-        <v>115.93</v>
+        <v>114.95</v>
       </c>
       <c r="E319" s="15" t="n">
-        <v>-0.0353</v>
+        <v>-0.0434</v>
       </c>
       <c r="F319" s="15" t="n">
-        <v>-0.0355</v>
+        <v>-0.0437</v>
       </c>
       <c r="G319" s="16" t="n">
         <v>46330</v>
@@ -24363,7 +24363,7 @@
         <v>142</v>
       </c>
       <c r="M319" s="14" t="n">
-        <v>0.2248770809971534</v>
+        <v>0.2353197042192257</v>
       </c>
       <c r="N319" s="12" t="inlineStr">
         <is>
@@ -24374,7 +24374,7 @@
         <v>137</v>
       </c>
       <c r="P319" s="14" t="n">
-        <v>0.181747606314155</v>
+        <v>0.1918225315354502</v>
       </c>
       <c r="Q319" s="19" t="inlineStr">
         <is>
@@ -24423,13 +24423,13 @@
         </is>
       </c>
       <c r="D320" s="4" t="n">
-        <v>233.39</v>
+        <v>232.26</v>
       </c>
       <c r="E320" s="25" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-0.0135</v>
       </c>
       <c r="F320" s="25" t="n">
-        <v>-0.04679999999999999</v>
+        <v>-0.05139999999999999</v>
       </c>
       <c r="G320" s="6" t="n">
         <v>46321</v>
@@ -24458,7 +24458,7 @@
         <v>237</v>
       </c>
       <c r="M320" s="5" t="n">
-        <v>0.01546767213676684</v>
+        <v>0.02040816326530616</v>
       </c>
       <c r="N320" s="3" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>236</v>
       </c>
       <c r="P320" s="5" t="n">
-        <v>0.01118299841467078</v>
+        <v>0.01610264358908124</v>
       </c>
       <c r="Q320" s="9" t="inlineStr">
         <is>
@@ -24510,13 +24510,13 @@
         </is>
       </c>
       <c r="D321" s="13" t="n">
-        <v>162.14</v>
+        <v>162.03</v>
       </c>
       <c r="E321" s="15" t="n">
-        <v>-0.0491</v>
+        <v>-0.04969999999999999</v>
       </c>
       <c r="F321" s="15" t="n">
-        <v>-0.0857</v>
+        <v>-0.0863</v>
       </c>
       <c r="G321" s="16" t="n">
         <v>46330</v>
@@ -24545,7 +24545,7 @@
         <v>200</v>
       </c>
       <c r="M321" s="14" t="n">
-        <v>0.2335019119279636</v>
+        <v>0.2343393198790347</v>
       </c>
       <c r="N321" s="12" t="inlineStr"/>
       <c r="O321" s="18" t="n"/>
@@ -24589,13 +24589,13 @@
         </is>
       </c>
       <c r="D322" s="4" t="n">
-        <v>136.66</v>
+        <v>138.24</v>
       </c>
       <c r="E322" s="5" t="n">
-        <v>0.0029</v>
+        <v>0.0145</v>
       </c>
       <c r="F322" s="5" t="n">
-        <v>0.0225</v>
+        <v>0.0343</v>
       </c>
       <c r="G322" s="6" t="n">
         <v>46330</v>
@@ -24624,7 +24624,7 @@
         <v>131</v>
       </c>
       <c r="M322" s="25" t="n">
-        <v>-0.04141665447094978</v>
+        <v>-0.05237268518518524</v>
       </c>
       <c r="N322" s="3" t="inlineStr"/>
       <c r="O322" s="8" t="n"/>
@@ -24668,13 +24668,13 @@
         </is>
       </c>
       <c r="D323" s="13" t="n">
-        <v>29.76</v>
+        <v>29.86</v>
       </c>
       <c r="E323" s="15" t="n">
-        <v>-0.1122</v>
+        <v>-0.1092</v>
       </c>
       <c r="F323" s="15" t="n">
-        <v>-0.1303</v>
+        <v>-0.1274</v>
       </c>
       <c r="G323" s="16" t="n">
         <v>46330</v>
@@ -24747,13 +24747,13 @@
         </is>
       </c>
       <c r="D324" s="4" t="n">
-        <v>35.92</v>
+        <v>35.97</v>
       </c>
       <c r="E324" s="25" t="n">
-        <v>-0.0626</v>
+        <v>-0.0613</v>
       </c>
       <c r="F324" s="25" t="n">
-        <v>-0.0832</v>
+        <v>-0.0819</v>
       </c>
       <c r="G324" s="6" t="n">
         <v>46332</v>
@@ -24808,13 +24808,13 @@
         </is>
       </c>
       <c r="D325" s="13" t="n">
-        <v>266.02</v>
+        <v>262.8</v>
       </c>
       <c r="E325" s="15" t="n">
-        <v>-0.003</v>
+        <v>-0.0151</v>
       </c>
       <c r="F325" s="14" t="n">
-        <v>0.04940000000000001</v>
+        <v>0.0367</v>
       </c>
       <c r="G325" s="16" t="n">
         <v>46332</v>
@@ -24843,7 +24843,7 @@
         <v>384</v>
       </c>
       <c r="M325" s="14" t="n">
-        <v>0.4435004886850614</v>
+        <v>0.4611872146118721</v>
       </c>
       <c r="N325" s="12" t="inlineStr">
         <is>
@@ -24854,7 +24854,7 @@
         <v>380</v>
       </c>
       <c r="P325" s="14" t="n">
-        <v>0.4284640252612587</v>
+        <v>0.4459665144596651</v>
       </c>
       <c r="Q325" s="19" t="inlineStr"/>
       <c r="R325" s="18" t="n"/>
@@ -24897,13 +24897,13 @@
         </is>
       </c>
       <c r="D326" s="4" t="n">
-        <v>65.97</v>
+        <v>66.2</v>
       </c>
       <c r="E326" s="25" t="n">
-        <v>-0.0716</v>
+        <v>-0.0684</v>
       </c>
       <c r="F326" s="25" t="n">
-        <v>-0.09480000000000001</v>
+        <v>-0.0917</v>
       </c>
       <c r="G326" s="6" t="n">
         <v>46324</v>
@@ -24932,7 +24932,7 @@
         <v>79</v>
       </c>
       <c r="M326" s="5" t="n">
-        <v>0.1975140215249356</v>
+        <v>0.1933534743202416</v>
       </c>
       <c r="N326" s="3" t="inlineStr"/>
       <c r="O326" s="8" t="n"/>
@@ -24984,13 +24984,13 @@
         </is>
       </c>
       <c r="D327" s="13" t="n">
-        <v>117.68</v>
+        <v>118.54</v>
       </c>
       <c r="E327" s="15" t="n">
-        <v>-0.0509</v>
+        <v>-0.044</v>
       </c>
       <c r="F327" s="15" t="n">
-        <v>-0.0649</v>
+        <v>-0.0581</v>
       </c>
       <c r="G327" s="16" t="n">
         <v>46331</v>
@@ -25019,7 +25019,7 @@
         <v>136</v>
       </c>
       <c r="M327" s="14" t="n">
-        <v>0.1556764106050305</v>
+        <v>0.1472920533153365</v>
       </c>
       <c r="N327" s="12" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>140</v>
       </c>
       <c r="P327" s="14" t="n">
-        <v>0.1896668932698844</v>
+        <v>0.1810359372363758</v>
       </c>
       <c r="Q327" s="19" t="inlineStr">
         <is>
@@ -25071,13 +25071,13 @@
         </is>
       </c>
       <c r="D328" s="4" t="n">
-        <v>102.89</v>
+        <v>103.31</v>
       </c>
       <c r="E328" s="25" t="n">
-        <v>-0.048</v>
+        <v>-0.0441</v>
       </c>
       <c r="F328" s="25" t="n">
-        <v>-0.0806</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="G328" s="6" t="n">
         <v>46330</v>
@@ -25106,7 +25106,7 @@
         <v>131</v>
       </c>
       <c r="M328" s="5" t="n">
-        <v>0.2732043930411119</v>
+        <v>0.2680282644468105</v>
       </c>
       <c r="N328" s="3" t="inlineStr">
         <is>
@@ -25117,7 +25117,7 @@
         <v>121</v>
       </c>
       <c r="P328" s="5" t="n">
-        <v>0.1760132179998056</v>
+        <v>0.17123221372568</v>
       </c>
       <c r="Q328" s="9" t="inlineStr">
         <is>
@@ -25162,13 +25162,13 @@
         </is>
       </c>
       <c r="D329" s="13" t="n">
-        <v>80.81</v>
+        <v>81.28</v>
       </c>
       <c r="E329" s="15" t="n">
-        <v>-0.06269999999999999</v>
+        <v>-0.0573</v>
       </c>
       <c r="F329" s="15" t="n">
-        <v>-0.08169999999999999</v>
+        <v>-0.0764</v>
       </c>
       <c r="G329" s="16" t="n">
         <v>46322</v>
@@ -25204,7 +25204,7 @@
         <v>107</v>
       </c>
       <c r="P329" s="14" t="n">
-        <v>0.3240935527781215</v>
+        <v>0.3164370078740157</v>
       </c>
       <c r="Q329" s="19" t="inlineStr">
         <is>
@@ -25253,13 +25253,13 @@
         </is>
       </c>
       <c r="D330" s="4" t="n">
-        <v>53.85</v>
+        <v>53.47</v>
       </c>
       <c r="E330" s="25" t="n">
-        <v>-0.0301</v>
+        <v>-0.0369</v>
       </c>
       <c r="F330" s="25" t="n">
-        <v>-0.08039999999999999</v>
+        <v>-0.08689999999999999</v>
       </c>
       <c r="G330" s="6" t="n"/>
       <c r="H330" s="7" t="inlineStr">
@@ -25278,7 +25278,7 @@
         <v>63</v>
       </c>
       <c r="M330" s="5" t="n">
-        <v>0.1699164345403899</v>
+        <v>0.1782307836169815</v>
       </c>
       <c r="N330" s="3" t="inlineStr"/>
       <c r="O330" s="8" t="n"/>
@@ -25322,13 +25322,13 @@
         </is>
       </c>
       <c r="D331" s="13" t="n">
-        <v>38.81</v>
+        <v>39.65</v>
       </c>
       <c r="E331" s="15" t="n">
-        <v>-0.06179999999999999</v>
+        <v>-0.0413</v>
       </c>
       <c r="F331" s="15" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.04480000000000001</v>
       </c>
       <c r="G331" s="16" t="n">
         <v>46336</v>
@@ -25383,13 +25383,13 @@
         </is>
       </c>
       <c r="D332" s="4" t="n">
-        <v>8.880000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="E332" s="5" t="n">
-        <v>0.0272</v>
+        <v>0.0463</v>
       </c>
       <c r="F332" s="5" t="n">
-        <v>0.1149</v>
+        <v>0.1357</v>
       </c>
       <c r="G332" s="6" t="n">
         <v>46331</v>
@@ -25444,13 +25444,13 @@
         </is>
       </c>
       <c r="D333" s="13" t="n">
-        <v>86.11</v>
+        <v>86.76000000000001</v>
       </c>
       <c r="E333" s="15" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.05769999999999999</v>
       </c>
       <c r="F333" s="15" t="n">
-        <v>-0.08839999999999999</v>
+        <v>-0.0815</v>
       </c>
       <c r="G333" s="16" t="n">
         <v>46324</v>
@@ -25479,7 +25479,7 @@
         <v>99</v>
       </c>
       <c r="M333" s="14" t="n">
-        <v>0.1496922540936012</v>
+        <v>0.1410788381742738</v>
       </c>
       <c r="N333" s="12" t="inlineStr">
         <is>
@@ -25490,7 +25490,7 @@
         <v>112</v>
       </c>
       <c r="P333" s="14" t="n">
-        <v>0.3006619440250842</v>
+        <v>0.2909174734900875</v>
       </c>
       <c r="Q333" s="19" t="inlineStr">
         <is>
@@ -25531,13 +25531,13 @@
         </is>
       </c>
       <c r="D334" s="4" t="n">
-        <v>103.88</v>
+        <v>104.73</v>
       </c>
       <c r="E334" s="25" t="n">
-        <v>-0.0646</v>
+        <v>-0.05690000000000001</v>
       </c>
       <c r="F334" s="25" t="n">
-        <v>-0.077</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="G334" s="6" t="n">
         <v>46324</v>
@@ -25566,7 +25566,7 @@
         <v>127</v>
       </c>
       <c r="M334" s="5" t="n">
-        <v>0.2225644974971121</v>
+        <v>0.2126420318915306</v>
       </c>
       <c r="N334" s="3" t="inlineStr"/>
       <c r="O334" s="8" t="n"/>
@@ -37665,7 +37665,7 @@
     <row r="2">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>Data as of September 17, 2026 at 15:20 UTC</t>
+          <t>Data as of September 17, 2026 at 20:36 UTC</t>
         </is>
       </c>
     </row>

--- a/earnings-data.xlsx
+++ b/earnings-data.xlsx
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>103.06</v>
+        <v>102.58</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>-0.0362</v>
+        <v>-0.0407</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>0.0689</v>
+        <v>0.064</v>
       </c>
       <c r="G2" s="7" t="n">
         <v>46338</v>
@@ -878,7 +878,7 @@
         <v>125</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.2128856976518533</v>
+        <v>0.218561123025931</v>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>144</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.397244323694935</v>
+        <v>0.4037824137258725</v>
       </c>
       <c r="Q2" s="10" t="inlineStr">
         <is>
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="D3" s="15" t="n">
-        <v>351.42</v>
+        <v>348.72</v>
       </c>
       <c r="E3" s="16" t="n">
-        <v>0.0194</v>
+        <v>0.0116</v>
       </c>
       <c r="F3" s="17" t="n">
-        <v>-0.0016</v>
+        <v>-0.009300000000000001</v>
       </c>
       <c r="G3" s="18" t="n">
         <v>46322</v>
@@ -973,7 +973,7 @@
         <v>438</v>
       </c>
       <c r="M3" s="16" t="n">
-        <v>0.2463718627283592</v>
+        <v>0.2560220233998622</v>
       </c>
       <c r="N3" s="14" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>420</v>
       </c>
       <c r="P3" s="16" t="n">
-        <v>0.1951511012463718</v>
+        <v>0.2044046799724707</v>
       </c>
       <c r="Q3" s="21" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>675.86</v>
+        <v>664.84</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>0.2378</v>
+        <v>0.2176</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.04650000000000001</v>
+        <v>0.0294</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>46330</v>
@@ -1064,7 +1064,7 @@
         <v>835</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.2354629657029562</v>
+        <v>0.255941279104747</v>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>930</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.3760246204835321</v>
+        <v>0.3988328018771433</v>
       </c>
       <c r="Q4" s="10" t="inlineStr">
         <is>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="D5" s="15" t="n">
-        <v>42.71</v>
+        <v>43.19</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>0.094</v>
+        <v>0.1064</v>
       </c>
       <c r="G5" s="18" t="n">
         <v>46329</v>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>72.06999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>-0.1015</v>
+        <v>-0.1056</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0614</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>46315</v>
@@ -1220,7 +1220,7 @@
         <v>80</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.1100319134175109</v>
+        <v>0.1149825783972125</v>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>100</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.3875398917718886</v>
+        <v>0.3937282229965157</v>
       </c>
       <c r="Q6" s="10" t="inlineStr">
         <is>
@@ -1272,13 +1272,13 @@
         </is>
       </c>
       <c r="D7" s="15" t="n">
-        <v>76.87</v>
+        <v>76.33</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>-0.1208</v>
+        <v>-0.127</v>
       </c>
       <c r="F7" s="17" t="n">
-        <v>-0.0668</v>
+        <v>-0.0733</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>46315</v>
@@ -1307,7 +1307,7 @@
         <v>91</v>
       </c>
       <c r="M7" s="16" t="n">
-        <v>0.1838168336151944</v>
+        <v>0.1921917987685052</v>
       </c>
       <c r="N7" s="14" t="inlineStr"/>
       <c r="O7" s="20" t="n"/>
@@ -1351,13 +1351,13 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>522.73</v>
+        <v>508.95</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-0.0199</v>
+        <v>-0.0458</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.06179999999999999</v>
+        <v>0.0338</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>46329</v>
@@ -1386,7 +1386,7 @@
         <v>569.9299999999999</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.09029518106862038</v>
+        <v>0.1198153060222025</v>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>648.04</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.239722227536204</v>
+        <v>0.2732881422536594</v>
       </c>
       <c r="Q8" s="10" t="inlineStr">
         <is>
@@ -1438,13 +1438,13 @@
         </is>
       </c>
       <c r="D9" s="15" t="n">
-        <v>187.33</v>
+        <v>189.07</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>-0.0712</v>
+        <v>-0.0626</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>0.0248</v>
+        <v>0.0344</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>46330</v>
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>166.87</v>
+        <v>168.27</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-0.0849</v>
+        <v>-0.07730000000000001</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-0.1471</v>
+        <v>-0.1399</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>46317</v>
@@ -1542,7 +1542,7 @@
         <v>170</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.0187571163180919</v>
+        <v>0.01028109585784745</v>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>270</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.6180260082699106</v>
+        <v>0.6045640934212871</v>
       </c>
       <c r="Q10" s="10" t="inlineStr">
         <is>
@@ -1594,13 +1594,13 @@
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>48.08</v>
+        <v>48.03</v>
       </c>
       <c r="E11" s="17" t="n">
-        <v>-0.0259</v>
+        <v>-0.0269</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>0.1053</v>
+        <v>0.1041</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>46316</v>
@@ -1629,7 +1629,7 @@
         <v>43</v>
       </c>
       <c r="M11" s="17" t="n">
-        <v>-0.105657237936772</v>
+        <v>-0.1047262127836769</v>
       </c>
       <c r="N11" s="14" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>50</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>0.03993344425956742</v>
+        <v>0.04101603164688734</v>
       </c>
       <c r="Q11" s="21" t="inlineStr">
         <is>
@@ -1685,13 +1685,13 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>165.26</v>
+        <v>166.11</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-0.1134</v>
+        <v>-0.1088</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.1402</v>
+        <v>0.1461</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>46331</v>
@@ -1720,7 +1720,7 @@
         <v>181</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.09524385816289489</v>
+        <v>0.08963939558124126</v>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>155</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>-0.06208398886602923</v>
+        <v>-0.06688339052435141</v>
       </c>
       <c r="Q12" s="10" t="inlineStr">
         <is>
@@ -1772,13 +1772,13 @@
         </is>
       </c>
       <c r="D13" s="15" t="n">
-        <v>252.76</v>
+        <v>253.67</v>
       </c>
       <c r="E13" s="17" t="n">
-        <v>-0.0492</v>
+        <v>-0.0458</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>0.0111</v>
+        <v>0.0147</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>46324</v>
@@ -1807,7 +1807,7 @@
         <v>322</v>
       </c>
       <c r="M13" s="16" t="n">
-        <v>0.2739357493274253</v>
+        <v>0.2693657113572753</v>
       </c>
       <c r="N13" s="14" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>285</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>0.1275518278208578</v>
+        <v>0.1235069184373399</v>
       </c>
       <c r="Q13" s="21" t="inlineStr">
         <is>
@@ -1871,13 +1871,13 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2842.86</v>
+        <v>2858.63</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-0.0761</v>
+        <v>-0.0709</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>-0.0505</v>
+        <v>-0.0453</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>46287</v>
@@ -1906,7 +1906,7 @@
         <v>4150</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.4597975278416805</v>
+        <v>0.4517443670569468</v>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>3700</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.3015062296419802</v>
+        <v>0.2943263031592056</v>
       </c>
       <c r="Q14" s="10" t="inlineStr">
         <is>
@@ -1958,13 +1958,13 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>94.25</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>0.0564</v>
+        <v>0.0424</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>0.1071</v>
+        <v>0.09230000000000001</v>
       </c>
       <c r="G15" s="18" t="n"/>
       <c r="H15" s="23" t="inlineStr">
@@ -1983,7 +1983,7 @@
         <v>65</v>
       </c>
       <c r="M15" s="17" t="n">
-        <v>-0.3103448275862069</v>
+        <v>-0.301000107538445</v>
       </c>
       <c r="N15" s="14" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>85</v>
       </c>
       <c r="P15" s="17" t="n">
-        <v>-0.09814323607427056</v>
+        <v>-0.08592321755027417</v>
       </c>
       <c r="Q15" s="21" t="inlineStr"/>
       <c r="R15" s="20" t="n"/>
@@ -2029,13 +2029,13 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>168.49</v>
+        <v>167.01</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-0.209</v>
+        <v>-0.2159</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-0.0611</v>
+        <v>-0.0694</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>46322</v>
@@ -2064,7 +2064,7 @@
         <v>214</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.2701050507448512</v>
+        <v>0.2813603975809832</v>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>245</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.4540922309929372</v>
+        <v>0.4669780252679481</v>
       </c>
       <c r="Q16" s="10" t="inlineStr">
         <is>
@@ -2124,13 +2124,13 @@
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>239.04</v>
+        <v>236.51</v>
       </c>
       <c r="E17" s="17" t="n">
-        <v>-0.2917</v>
+        <v>-0.2992</v>
       </c>
       <c r="F17" s="17" t="n">
-        <v>-0.3212</v>
+        <v>-0.3284</v>
       </c>
       <c r="G17" s="18" t="n"/>
       <c r="H17" s="23" t="inlineStr">
@@ -2149,7 +2149,7 @@
         <v>375</v>
       </c>
       <c r="M17" s="16" t="n">
-        <v>0.5687751004016065</v>
+        <v>0.585556636083041</v>
       </c>
       <c r="N17" s="14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>375</v>
       </c>
       <c r="P17" s="16" t="n">
-        <v>0.5687751004016065</v>
+        <v>0.585556636083041</v>
       </c>
       <c r="Q17" s="21" t="inlineStr"/>
       <c r="R17" s="20" t="n"/>
@@ -2199,13 +2199,13 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>33.08</v>
+        <v>33.35</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>-0.0454</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>-0.0014</v>
+        <v>-0.0378</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>0.0066</v>
       </c>
       <c r="G18" s="7" t="n">
         <v>46323</v>
@@ -2234,7 +2234,7 @@
         <v>45</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.3603385731559856</v>
+        <v>0.3493253373313343</v>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>45</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.3603385731559856</v>
+        <v>0.3493253373313343</v>
       </c>
       <c r="Q18" s="10" t="inlineStr">
         <is>
@@ -2286,13 +2286,13 @@
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>138.08</v>
+        <v>138.19</v>
       </c>
       <c r="E19" s="17" t="n">
-        <v>-0.0907</v>
+        <v>-0.09</v>
       </c>
       <c r="F19" s="17" t="n">
-        <v>-0.0463</v>
+        <v>-0.04559999999999999</v>
       </c>
       <c r="G19" s="18" t="n">
         <v>46324</v>
@@ -2321,7 +2321,7 @@
         <v>170</v>
       </c>
       <c r="M19" s="16" t="n">
-        <v>0.2311703360370798</v>
+        <v>0.2301903176785585</v>
       </c>
       <c r="N19" s="14" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>177</v>
       </c>
       <c r="P19" s="16" t="n">
-        <v>0.2818655851680184</v>
+        <v>0.2808452131123815</v>
       </c>
       <c r="Q19" s="21" t="inlineStr">
         <is>
@@ -2373,13 +2373,13 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>123.76</v>
+        <v>121.39</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>-0.353</v>
+        <v>-0.3654</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>-0.4225</v>
+        <v>-0.4336</v>
       </c>
       <c r="G20" s="7" t="n"/>
       <c r="H20" s="12" t="inlineStr">
@@ -2398,7 +2398,7 @@
         <v>220</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.7776341305753069</v>
+        <v>0.812340390476975</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="9" t="n"/>
@@ -2442,13 +2442,13 @@
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>113.88</v>
+        <v>111.96</v>
       </c>
       <c r="E21" s="17" t="n">
-        <v>-0.1363</v>
+        <v>-0.1508</v>
       </c>
       <c r="F21" s="17" t="n">
-        <v>-0.0989</v>
+        <v>-0.1141</v>
       </c>
       <c r="G21" s="18" t="n"/>
       <c r="H21" s="23" t="inlineStr">
@@ -2493,13 +2493,13 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>82.5</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-0.029</v>
+        <v>-0.0314</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>0.0883</v>
+        <v>0.08560000000000001</v>
       </c>
       <c r="G22" s="7" t="n">
         <v>46315</v>
@@ -2528,7 +2528,7 @@
         <v>61</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>-0.2606060606060606</v>
+        <v>-0.2587191639324341</v>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>100</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.2121212121212121</v>
+        <v>0.2152144853566653</v>
       </c>
       <c r="Q22" s="10" t="inlineStr">
         <is>
@@ -2580,13 +2580,13 @@
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>128.81</v>
+        <v>128.15</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>-0.0426</v>
+        <v>-0.0475</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>0.0524</v>
+        <v>0.047</v>
       </c>
       <c r="G23" s="18" t="n">
         <v>46315</v>
@@ -2618,7 +2618,7 @@
         <v>145</v>
       </c>
       <c r="P23" s="16" t="n">
-        <v>0.1256889993012965</v>
+        <v>0.131486539211861</v>
       </c>
       <c r="Q23" s="21" t="inlineStr"/>
       <c r="R23" s="20" t="n"/>
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>301.05</v>
+        <v>300.01</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>-0.1256</v>
+        <v>-0.1286</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>-0.096</v>
+        <v>-0.0992</v>
       </c>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="12" t="inlineStr">
@@ -2678,7 +2678,7 @@
         <v>360</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.1958146487294469</v>
+        <v>0.1999600013332889</v>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>400</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.3286829430327188</v>
+        <v>0.3332888903703211</v>
       </c>
       <c r="Q24" s="10" t="inlineStr">
         <is>
@@ -2738,13 +2738,13 @@
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>193.31</v>
+        <v>192.49</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>-0.1213</v>
+        <v>-0.125</v>
       </c>
       <c r="F25" s="17" t="n">
-        <v>-0.0557</v>
+        <v>-0.0597</v>
       </c>
       <c r="G25" s="18" t="n"/>
       <c r="H25" s="23" t="inlineStr">
@@ -2763,7 +2763,7 @@
         <v>255</v>
       </c>
       <c r="M25" s="16" t="n">
-        <v>0.3191247219492008</v>
+        <v>0.3247441425528598</v>
       </c>
       <c r="N25" s="14" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>230</v>
       </c>
       <c r="P25" s="16" t="n">
-        <v>0.1897987688169262</v>
+        <v>0.1948672658319912</v>
       </c>
       <c r="Q25" s="21" t="inlineStr">
         <is>
@@ -2819,13 +2819,13 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>250.14</v>
+        <v>248.66</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.0703</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>-0.0654</v>
+        <v>-0.0709</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>46330</v>
@@ -2854,7 +2854,7 @@
         <v>300</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.1993283761093788</v>
+        <v>0.2064666613045926</v>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>350</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.3992164387942753</v>
+        <v>0.4075444381886914</v>
       </c>
       <c r="Q26" s="10" t="inlineStr">
         <is>
@@ -2906,13 +2906,13 @@
         </is>
       </c>
       <c r="D27" s="15" t="n">
-        <v>36.34</v>
+        <v>35.56</v>
       </c>
       <c r="E27" s="17" t="n">
-        <v>-0.1148</v>
+        <v>-0.1336</v>
       </c>
       <c r="F27" s="17" t="n">
-        <v>-0.164</v>
+        <v>-0.1818</v>
       </c>
       <c r="G27" s="18" t="n">
         <v>46289</v>
@@ -2967,13 +2967,13 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>84.31999999999999</v>
+        <v>84.70999999999999</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>-0.07539999999999999</v>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>-0.0025</v>
+        <v>-0.0712</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>0.0021</v>
       </c>
       <c r="G28" s="7" t="n">
         <v>46323</v>
@@ -3002,7 +3002,7 @@
         <v>110</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.3045540796963948</v>
+        <v>0.2985479872506199</v>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>115</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.3638519924098673</v>
+        <v>0.3575728957620117</v>
       </c>
       <c r="Q28" s="10" t="inlineStr">
         <is>
@@ -3058,13 +3058,13 @@
         </is>
       </c>
       <c r="D29" s="15" t="n">
-        <v>167.97</v>
+        <v>168.02</v>
       </c>
       <c r="E29" s="17" t="n">
-        <v>-0.143</v>
+        <v>-0.1427</v>
       </c>
       <c r="F29" s="17" t="n">
-        <v>-0.1645</v>
+        <v>-0.1642</v>
       </c>
       <c r="G29" s="18" t="n">
         <v>46317</v>
@@ -3119,13 +3119,13 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>229.35</v>
+        <v>226.77</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>-0.0228</v>
+        <v>-0.0337</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>-0.0273</v>
+        <v>-0.0382</v>
       </c>
       <c r="G30" s="7" t="n"/>
       <c r="H30" s="12" t="inlineStr">
@@ -3144,7 +3144,7 @@
         <v>245</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.06823632003488121</v>
+        <v>0.08038982228689857</v>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>265</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1554392849356878</v>
+        <v>0.1685849098205229</v>
       </c>
       <c r="Q30" s="10" t="inlineStr">
         <is>
@@ -3196,13 +3196,13 @@
         </is>
       </c>
       <c r="D31" s="15" t="n">
-        <v>95.98</v>
+        <v>95.78</v>
       </c>
       <c r="E31" s="17" t="n">
-        <v>-0.0857</v>
+        <v>-0.0877</v>
       </c>
       <c r="F31" s="17" t="n">
-        <v>-0.0842</v>
+        <v>-0.0862</v>
       </c>
       <c r="G31" s="18" t="n">
         <v>46330</v>
@@ -3231,7 +3231,7 @@
         <v>120</v>
       </c>
       <c r="M31" s="16" t="n">
-        <v>0.250260470931444</v>
+        <v>0.252871163082063</v>
       </c>
       <c r="N31" s="14" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>115</v>
       </c>
       <c r="P31" s="16" t="n">
-        <v>0.1981662846426338</v>
+        <v>0.2006681979536437</v>
       </c>
       <c r="Q31" s="21" t="inlineStr">
         <is>
@@ -3283,13 +3283,13 @@
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>12.38</v>
+        <v>12.15</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>-0.0513</v>
+        <v>-0.0693</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>-0.1697</v>
+        <v>-0.1854</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>46330</v>
@@ -3344,13 +3344,13 @@
         </is>
       </c>
       <c r="D33" s="15" t="n">
-        <v>128.07</v>
+        <v>127.31</v>
       </c>
       <c r="E33" s="17" t="n">
-        <v>-0.1137</v>
+        <v>-0.119</v>
       </c>
       <c r="F33" s="17" t="n">
-        <v>-0.1775</v>
+        <v>-0.1823</v>
       </c>
       <c r="G33" s="18" t="n"/>
       <c r="H33" s="23" t="inlineStr">
@@ -3369,7 +3369,7 @@
         <v>160</v>
       </c>
       <c r="M33" s="16" t="n">
-        <v>0.2493167798859999</v>
+        <v>0.2567748016652266</v>
       </c>
       <c r="N33" s="14" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>175</v>
       </c>
       <c r="P33" s="16" t="n">
-        <v>0.3664402280003124</v>
+        <v>0.3745974393213416</v>
       </c>
       <c r="Q33" s="21" t="inlineStr">
         <is>
@@ -3425,13 +3425,13 @@
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>32.69</v>
+        <v>32.17</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>-0.07769999999999999</v>
+        <v>-0.0924</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.0616</v>
       </c>
       <c r="G34" s="7" t="n">
         <v>46317</v>
@@ -3460,7 +3460,7 @@
         <v>35</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.07066381156316924</v>
+        <v>0.08797015853279447</v>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>40</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.223615784643622</v>
+        <v>0.2433944668946222</v>
       </c>
       <c r="Q34" s="10" t="inlineStr">
         <is>
@@ -3512,13 +3512,13 @@
         </is>
       </c>
       <c r="D35" s="15" t="n">
-        <v>364.29</v>
+        <v>364.63</v>
       </c>
       <c r="E35" s="16" t="n">
-        <v>0.0375</v>
+        <v>0.0385</v>
       </c>
       <c r="F35" s="17" t="n">
-        <v>-0.0143</v>
+        <v>-0.0134</v>
       </c>
       <c r="G35" s="18" t="n">
         <v>46323</v>
@@ -3547,7 +3547,7 @@
         <v>130</v>
       </c>
       <c r="M35" s="17" t="n">
-        <v>-0.643141453237805</v>
+        <v>-0.64347420673011</v>
       </c>
       <c r="N35" s="14" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>300</v>
       </c>
       <c r="P35" s="17" t="n">
-        <v>-0.1764802767026271</v>
+        <v>-0.1772481693771769</v>
       </c>
       <c r="Q35" s="21" t="inlineStr">
         <is>
@@ -3599,13 +3599,13 @@
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>70.33</v>
+        <v>70.5</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>-0.09880000000000001</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>-0.0255</v>
+        <v>-0.0231</v>
       </c>
       <c r="G36" s="7" t="n">
         <v>46329</v>
@@ -3660,13 +3660,13 @@
         </is>
       </c>
       <c r="D37" s="15" t="n">
-        <v>541.1900000000001</v>
+        <v>540.88</v>
       </c>
       <c r="E37" s="16" t="n">
-        <v>0.0253</v>
+        <v>0.0247</v>
       </c>
       <c r="F37" s="16" t="n">
-        <v>0.1088</v>
+        <v>0.1082</v>
       </c>
       <c r="G37" s="18" t="n"/>
       <c r="H37" s="23" t="inlineStr">
@@ -3685,7 +3685,7 @@
         <v>450</v>
       </c>
       <c r="M37" s="17" t="n">
-        <v>-0.1684990483933555</v>
+        <v>-0.1680224818813785</v>
       </c>
       <c r="N37" s="14" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>635</v>
       </c>
       <c r="P37" s="16" t="n">
-        <v>0.1733402317115984</v>
+        <v>0.1740127200118326</v>
       </c>
       <c r="Q37" s="21" t="inlineStr">
         <is>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>94.95</v>
+        <v>94.69</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>-0.04099999999999999</v>
+        <v>-0.0436</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>-0.029</v>
+        <v>-0.0317</v>
       </c>
       <c r="G38" s="7" t="n">
         <v>46325</v>
@@ -3776,7 +3776,7 @@
         <v>110</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.158504476040021</v>
+        <v>0.1616855000528039</v>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>105</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.1058451816745655</v>
+        <v>0.1088816136867674</v>
       </c>
       <c r="Q38" s="10" t="inlineStr">
         <is>
@@ -3832,13 +3832,13 @@
         </is>
       </c>
       <c r="D39" s="15" t="n">
-        <v>87.38</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="E39" s="17" t="n">
-        <v>-0.0384</v>
+        <v>-0.0381</v>
       </c>
       <c r="F39" s="17" t="n">
-        <v>-0.0495</v>
+        <v>-0.0492</v>
       </c>
       <c r="G39" s="18" t="n">
         <v>46325</v>
@@ -3867,7 +3867,7 @@
         <v>95</v>
       </c>
       <c r="M39" s="16" t="n">
-        <v>0.0872053101396201</v>
+        <v>0.08695652173913036</v>
       </c>
       <c r="N39" s="14" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>100</v>
       </c>
       <c r="P39" s="16" t="n">
-        <v>0.1444266422522317</v>
+        <v>0.1441647597254004</v>
       </c>
       <c r="Q39" s="21" t="inlineStr">
         <is>
@@ -3923,13 +3923,13 @@
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>894.84</v>
+        <v>895.86</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>-0.0649</v>
+        <v>-0.0639</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>-0.0438</v>
+        <v>-0.04269999999999999</v>
       </c>
       <c r="G40" s="7" t="n">
         <v>46289</v>
@@ -3958,7 +3958,7 @@
         <v>1000</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.1175182155469134</v>
+        <v>0.1162458419842386</v>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>1100</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.2292700371016047</v>
+        <v>0.2278704261826625</v>
       </c>
       <c r="Q40" s="10" t="inlineStr">
         <is>
@@ -4018,13 +4018,13 @@
         </is>
       </c>
       <c r="D41" s="15" t="n">
-        <v>124</v>
+        <v>122.43</v>
       </c>
       <c r="E41" s="16" t="n">
-        <v>0.0138</v>
+        <v>0.001</v>
       </c>
       <c r="F41" s="17" t="n">
-        <v>-0.006</v>
+        <v>-0.0186</v>
       </c>
       <c r="G41" s="18" t="n"/>
       <c r="H41" s="23" t="inlineStr">
@@ -4043,7 +4043,7 @@
         <v>125</v>
       </c>
       <c r="M41" s="16" t="n">
-        <v>0.008064516129032258</v>
+        <v>0.02099158702932282</v>
       </c>
       <c r="N41" s="14" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>135</v>
       </c>
       <c r="P41" s="16" t="n">
-        <v>0.08870967741935484</v>
+        <v>0.1026709139916687</v>
       </c>
       <c r="Q41" s="21" t="inlineStr">
         <is>
@@ -4095,13 +4095,13 @@
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>24.32</v>
+        <v>24.4</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>-0.0529</v>
+        <v>-0.05</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>-0.0594</v>
+        <v>-0.0567</v>
       </c>
       <c r="G42" s="7" t="n">
         <v>46330</v>
@@ -4156,13 +4156,13 @@
         </is>
       </c>
       <c r="D43" s="15" t="n">
-        <v>87.69</v>
+        <v>88.17</v>
       </c>
       <c r="E43" s="17" t="n">
-        <v>-0.0294</v>
+        <v>-0.0241</v>
       </c>
       <c r="F43" s="16" t="n">
-        <v>0.0678</v>
+        <v>0.0737</v>
       </c>
       <c r="G43" s="18" t="n">
         <v>46315</v>
@@ -4191,7 +4191,7 @@
         <v>90</v>
       </c>
       <c r="M43" s="16" t="n">
-        <v>0.02634279849469726</v>
+        <v>0.02075535896563455</v>
       </c>
       <c r="N43" s="14" t="inlineStr">
         <is>
@@ -4201,8 +4201,8 @@
       <c r="O43" s="20" t="n">
         <v>88</v>
       </c>
-      <c r="P43" s="16" t="n">
-        <v>0.00353518075037065</v>
+      <c r="P43" s="17" t="n">
+        <v>-0.001928093455823996</v>
       </c>
       <c r="Q43" s="21" t="inlineStr">
         <is>
@@ -4251,13 +4251,13 @@
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>60.51</v>
+        <v>60.04</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.0669</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>0.0368</v>
+        <v>0.0287</v>
       </c>
       <c r="G44" s="7" t="n"/>
       <c r="H44" s="12" t="inlineStr">
@@ -4276,7 +4276,7 @@
         <v>58</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>-0.04148074698396956</v>
+        <v>-0.03397734843437707</v>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>78</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.2890431333663858</v>
+        <v>0.2991339107261826</v>
       </c>
       <c r="Q44" s="10" t="inlineStr">
         <is>
@@ -4328,13 +4328,13 @@
         </is>
       </c>
       <c r="D45" s="15" t="n">
-        <v>60.9</v>
+        <v>60.81</v>
       </c>
       <c r="E45" s="17" t="n">
-        <v>-0.0508</v>
+        <v>-0.0521</v>
       </c>
       <c r="F45" s="16" t="n">
-        <v>0.0105</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="G45" s="18" t="n">
         <v>46322</v>
@@ -4363,7 +4363,7 @@
         <v>70</v>
       </c>
       <c r="M45" s="16" t="n">
-        <v>0.1494252873563219</v>
+        <v>0.1511264594639039</v>
       </c>
       <c r="N45" s="14" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>71</v>
       </c>
       <c r="P45" s="16" t="n">
-        <v>0.1658456486042693</v>
+        <v>0.1675711231705311</v>
       </c>
       <c r="Q45" s="21" t="inlineStr">
         <is>
@@ -4423,13 +4423,13 @@
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>49.22</v>
+        <v>48.81</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>-0.1285</v>
+        <v>-0.1357</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>-0.0578</v>
+        <v>-0.06559999999999999</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>46296</v>
@@ -4494,13 +4494,13 @@
         </is>
       </c>
       <c r="D47" s="15" t="n">
-        <v>44.91</v>
+        <v>44.69</v>
       </c>
       <c r="E47" s="17" t="n">
-        <v>-0.05309999999999999</v>
+        <v>-0.05769999999999999</v>
       </c>
       <c r="F47" s="17" t="n">
-        <v>-0.059</v>
+        <v>-0.0635</v>
       </c>
       <c r="G47" s="18" t="n">
         <v>46331</v>
@@ -4555,13 +4555,13 @@
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>69.64</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>0.0547</v>
+        <v>0.0535</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>-0.0672</v>
+        <v>-0.0682</v>
       </c>
       <c r="G48" s="7" t="n">
         <v>46324</v>
@@ -4616,13 +4616,13 @@
         </is>
       </c>
       <c r="D49" s="15" t="n">
-        <v>131.23</v>
+        <v>129.6</v>
       </c>
       <c r="E49" s="17" t="n">
-        <v>-0.0796</v>
+        <v>-0.0911</v>
       </c>
       <c r="F49" s="17" t="n">
-        <v>-0.0312</v>
+        <v>-0.0433</v>
       </c>
       <c r="G49" s="18" t="n">
         <v>46303</v>
@@ -4651,7 +4651,7 @@
         <v>140</v>
       </c>
       <c r="M49" s="16" t="n">
-        <v>0.06682923112093279</v>
+        <v>0.08024691358024696</v>
       </c>
       <c r="N49" s="14" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>150</v>
       </c>
       <c r="P49" s="16" t="n">
-        <v>0.1430313190581423</v>
+        <v>0.1574074074074075</v>
       </c>
       <c r="Q49" s="21" t="inlineStr">
         <is>
@@ -4711,13 +4711,13 @@
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>146.48</v>
+        <v>146.15</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>0.0145</v>
+        <v>0.0123</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>-0.0178</v>
+        <v>-0.02</v>
       </c>
       <c r="G50" s="7" t="n">
         <v>46318</v>
@@ -4746,7 +4746,7 @@
         <v>164</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0.1196067722555981</v>
+        <v>0.1221347930208689</v>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>162</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.1059530311305298</v>
+        <v>0.108450222374273</v>
       </c>
       <c r="Q50" s="10" t="inlineStr">
         <is>
@@ -4810,13 +4810,13 @@
         </is>
       </c>
       <c r="D51" s="15" t="n">
-        <v>78.84999999999999</v>
+        <v>79.11</v>
       </c>
       <c r="E51" s="17" t="n">
-        <v>-0.0438</v>
+        <v>-0.0407</v>
       </c>
       <c r="F51" s="17" t="n">
-        <v>-0.0239</v>
+        <v>-0.0207</v>
       </c>
       <c r="G51" s="18" t="n">
         <v>46322</v>
@@ -4845,7 +4845,7 @@
         <v>100</v>
       </c>
       <c r="M51" s="16" t="n">
-        <v>0.2682308180088777</v>
+        <v>0.2640626975097965</v>
       </c>
       <c r="N51" s="14" t="inlineStr"/>
       <c r="O51" s="20" t="n"/>
@@ -4889,13 +4889,13 @@
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>157.65</v>
+        <v>158.18</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0052</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>0.1294</v>
+        <v>0.1332</v>
       </c>
       <c r="G52" s="7" t="n"/>
       <c r="H52" s="12" t="inlineStr">
@@ -4914,7 +4914,7 @@
         <v>140</v>
       </c>
       <c r="M52" s="5" t="n">
-        <v>-0.1119568664763717</v>
+        <v>-0.1149323555443166</v>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>135</v>
       </c>
       <c r="P52" s="5" t="n">
-        <v>-0.1436726926736442</v>
+        <v>-0.1465419142748768</v>
       </c>
       <c r="Q52" s="10" t="inlineStr">
         <is>
@@ -4970,13 +4970,13 @@
         </is>
       </c>
       <c r="D53" s="15" t="n">
-        <v>107.52</v>
+        <v>106.72</v>
       </c>
       <c r="E53" s="17" t="n">
-        <v>-0.0594</v>
+        <v>-0.0663</v>
       </c>
       <c r="F53" s="17" t="n">
-        <v>-0.0417</v>
+        <v>-0.0488</v>
       </c>
       <c r="G53" s="18" t="n"/>
       <c r="H53" s="23" t="inlineStr">
@@ -4995,7 +4995,7 @@
         <v>140</v>
       </c>
       <c r="M53" s="16" t="n">
-        <v>0.3020833333333334</v>
+        <v>0.3118440779610195</v>
       </c>
       <c r="N53" s="14" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>140</v>
       </c>
       <c r="P53" s="16" t="n">
-        <v>0.3020833333333334</v>
+        <v>0.3118440779610195</v>
       </c>
       <c r="Q53" s="21" t="inlineStr">
         <is>
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>56.62</v>
+        <v>57.23</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>-0.122</v>
+        <v>-0.1124</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>0.0266</v>
+        <v>0.0377</v>
       </c>
       <c r="G54" s="7" t="n">
         <v>46317</v>
@@ -5097,7 +5097,7 @@
         <v>76</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.3422818791946309</v>
+        <v>0.3279748383714836</v>
       </c>
       <c r="Q54" s="10" t="inlineStr">
         <is>
@@ -5138,13 +5138,13 @@
         </is>
       </c>
       <c r="D55" s="15" t="n">
-        <v>132.88</v>
+        <v>131.86</v>
       </c>
       <c r="E55" s="16" t="n">
-        <v>0.0177</v>
+        <v>0.0098</v>
       </c>
       <c r="F55" s="16" t="n">
-        <v>0.1487</v>
+        <v>0.1399</v>
       </c>
       <c r="G55" s="18" t="n">
         <v>46331</v>
@@ -5173,7 +5173,7 @@
         <v>183</v>
       </c>
       <c r="M55" s="16" t="n">
-        <v>0.3771824202287779</v>
+        <v>0.3878355831942968</v>
       </c>
       <c r="N55" s="14" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>145</v>
       </c>
       <c r="P55" s="16" t="n">
-        <v>0.09121011438892238</v>
+        <v>0.09965114515395104</v>
       </c>
       <c r="Q55" s="21" t="inlineStr">
         <is>
@@ -5225,13 +5225,13 @@
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>211.41</v>
+        <v>209.51</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>0.0275</v>
+        <v>0.0182</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>0.1144</v>
+        <v>0.1044</v>
       </c>
       <c r="G56" s="7" t="n">
         <v>46325</v>
@@ -5260,7 +5260,7 @@
         <v>222</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>0.05009223783170145</v>
+        <v>0.05961529282611813</v>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>225</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.0642826734780758</v>
+        <v>0.07393441840484946</v>
       </c>
       <c r="Q56" s="10" t="inlineStr">
         <is>
@@ -5316,13 +5316,13 @@
         </is>
       </c>
       <c r="D57" s="15" t="n">
-        <v>145.3</v>
+        <v>144.16</v>
       </c>
       <c r="E57" s="17" t="n">
-        <v>-0.028</v>
+        <v>-0.0356</v>
       </c>
       <c r="F57" s="16" t="n">
-        <v>0.0298</v>
+        <v>0.0218</v>
       </c>
       <c r="G57" s="18" t="n">
         <v>46331</v>
@@ -5351,7 +5351,7 @@
         <v>196</v>
       </c>
       <c r="M57" s="16" t="n">
-        <v>0.3489332415691671</v>
+        <v>0.3596004439511654</v>
       </c>
       <c r="N57" s="14" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>170</v>
       </c>
       <c r="P57" s="16" t="n">
-        <v>0.1699931176875429</v>
+        <v>0.1792452830188679</v>
       </c>
       <c r="Q57" s="21" t="inlineStr">
         <is>
@@ -5407,13 +5407,13 @@
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>38.92</v>
+        <v>38.97</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>0.0211</v>
+        <v>0.0222</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>0.0037</v>
+        <v>0.0048</v>
       </c>
       <c r="G58" s="7" t="n">
         <v>46324</v>
@@ -5468,13 +5468,13 @@
         </is>
       </c>
       <c r="D59" s="15" t="n">
-        <v>21.09</v>
+        <v>21.11</v>
       </c>
       <c r="E59" s="17" t="n">
-        <v>-0.004</v>
+        <v>-0.0031</v>
       </c>
       <c r="F59" s="16" t="n">
-        <v>0.04019999999999999</v>
+        <v>0.0412</v>
       </c>
       <c r="G59" s="18" t="n">
         <v>46330</v>
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>194.99</v>
+        <v>192.04</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>-0.065</v>
+        <v>-0.0791</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>-0.002</v>
+        <v>-0.0171</v>
       </c>
       <c r="G60" s="7" t="n">
         <v>46328</v>
@@ -5590,13 +5590,13 @@
         </is>
       </c>
       <c r="D61" s="15" t="n">
-        <v>33.79</v>
+        <v>33.64</v>
       </c>
       <c r="E61" s="17" t="n">
-        <v>-0.035</v>
+        <v>-0.0394</v>
       </c>
       <c r="F61" s="17" t="n">
-        <v>-0.0375</v>
+        <v>-0.04190000000000001</v>
       </c>
       <c r="G61" s="18" t="n">
         <v>46315</v>
@@ -5632,7 +5632,7 @@
         <v>43</v>
       </c>
       <c r="P61" s="16" t="n">
-        <v>0.2725658478839894</v>
+        <v>0.2782401902497027</v>
       </c>
       <c r="Q61" s="21" t="inlineStr">
         <is>
@@ -5677,13 +5677,13 @@
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>31.74</v>
+        <v>31.8</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>-0.0108</v>
+        <v>-0.0089</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>-0.0259</v>
+        <v>-0.0241</v>
       </c>
       <c r="G62" s="7" t="n">
         <v>46316</v>
@@ -5712,7 +5712,7 @@
         <v>35</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>0.1027095148078135</v>
+        <v>0.10062893081761</v>
       </c>
       <c r="N62" s="3" t="inlineStr"/>
       <c r="O62" s="9" t="n"/>
@@ -5756,13 +5756,13 @@
         </is>
       </c>
       <c r="D63" s="15" t="n">
-        <v>274.99</v>
+        <v>272.73</v>
       </c>
       <c r="E63" s="16" t="n">
-        <v>0.135</v>
+        <v>0.1256</v>
       </c>
       <c r="F63" s="16" t="n">
-        <v>0.317</v>
+        <v>0.3062</v>
       </c>
       <c r="G63" s="18" t="n">
         <v>46323</v>
@@ -5817,13 +5817,13 @@
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>51.38</v>
+        <v>51.11</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>-0.0404</v>
+        <v>-0.04559999999999999</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>0.1077</v>
+        <v>0.1017</v>
       </c>
       <c r="G64" s="7" t="n">
         <v>46311</v>
@@ -5859,7 +5859,7 @@
         <v>63</v>
       </c>
       <c r="P64" s="6" t="n">
-        <v>0.2261580381471389</v>
+        <v>0.2326354920759147</v>
       </c>
       <c r="Q64" s="10" t="inlineStr">
         <is>
@@ -5908,13 +5908,13 @@
         </is>
       </c>
       <c r="D65" s="15" t="n">
-        <v>42.9</v>
+        <v>42.26</v>
       </c>
       <c r="E65" s="17" t="n">
-        <v>-0.0223</v>
+        <v>-0.0368</v>
       </c>
       <c r="F65" s="17" t="n">
-        <v>-0.0329</v>
+        <v>-0.0472</v>
       </c>
       <c r="G65" s="18" t="n">
         <v>46328</v>
@@ -5969,13 +5969,13 @@
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>72.25</v>
+        <v>72.11</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>-0.0135</v>
+        <v>-0.0155</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>-0.0258</v>
+        <v>-0.0277</v>
       </c>
       <c r="G66" s="7" t="n">
         <v>46328</v>
@@ -6004,7 +6004,7 @@
         <v>89</v>
       </c>
       <c r="M66" s="6" t="n">
-        <v>0.2318339100346021</v>
+        <v>0.2342254888364998</v>
       </c>
       <c r="N66" s="3" t="inlineStr"/>
       <c r="O66" s="9" t="n"/>
@@ -6060,13 +6060,13 @@
         </is>
       </c>
       <c r="D67" s="15" t="n">
-        <v>163.16</v>
+        <v>162.95</v>
       </c>
       <c r="E67" s="17" t="n">
-        <v>-0.0098</v>
+        <v>-0.011</v>
       </c>
       <c r="F67" s="16" t="n">
-        <v>0.0998</v>
+        <v>0.0983</v>
       </c>
       <c r="G67" s="18" t="n">
         <v>46325</v>
@@ -6095,7 +6095,7 @@
         <v>185</v>
       </c>
       <c r="M67" s="16" t="n">
-        <v>0.1338563373375828</v>
+        <v>0.1353175820803929</v>
       </c>
       <c r="N67" s="14" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>185</v>
       </c>
       <c r="P67" s="16" t="n">
-        <v>0.1338563373375828</v>
+        <v>0.1353175820803929</v>
       </c>
       <c r="Q67" s="21" t="inlineStr">
         <is>
@@ -6151,13 +6151,13 @@
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>115.93</v>
+        <v>116.23</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>-0.005</v>
+        <v>-0.0024</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>-0.06570000000000001</v>
+        <v>-0.0633</v>
       </c>
       <c r="G68" s="7" t="n">
         <v>46329</v>
@@ -6186,7 +6186,7 @@
         <v>120</v>
       </c>
       <c r="M68" s="6" t="n">
-        <v>0.0351073923919606</v>
+        <v>0.032435687860277</v>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>115</v>
       </c>
       <c r="P68" s="5" t="n">
-        <v>-0.008022082291037753</v>
+        <v>-0.01058246580056787</v>
       </c>
       <c r="Q68" s="10" t="inlineStr"/>
       <c r="R68" s="9" t="n"/>
@@ -6232,13 +6232,13 @@
         </is>
       </c>
       <c r="D69" s="15" t="n">
-        <v>296.61</v>
+        <v>295.63</v>
       </c>
       <c r="E69" s="17" t="n">
-        <v>-0.1487</v>
+        <v>-0.1515</v>
       </c>
       <c r="F69" s="17" t="n">
-        <v>-0.1824</v>
+        <v>-0.1851</v>
       </c>
       <c r="G69" s="18" t="n">
         <v>46325</v>
@@ -6267,7 +6267,7 @@
         <v>406</v>
       </c>
       <c r="M69" s="16" t="n">
-        <v>0.3688007821718755</v>
+        <v>0.3733382944897338</v>
       </c>
       <c r="N69" s="14" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         <v>436</v>
       </c>
       <c r="P69" s="16" t="n">
-        <v>0.469943697110684</v>
+        <v>0.4748164935899604</v>
       </c>
       <c r="Q69" s="21" t="inlineStr">
         <is>
@@ -6315,13 +6315,13 @@
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>309.75</v>
+        <v>311.47</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>-0.08869999999999999</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>-0.1199</v>
+        <v>-0.115</v>
       </c>
       <c r="G70" s="7" t="n">
         <v>46311</v>
@@ -6350,7 +6350,7 @@
         <v>415</v>
       </c>
       <c r="M70" s="6" t="n">
-        <v>0.3397901533494754</v>
+        <v>0.3323915625902975</v>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>380</v>
       </c>
       <c r="P70" s="6" t="n">
-        <v>0.2267958030669895</v>
+        <v>0.2200211898417182</v>
       </c>
       <c r="Q70" s="10" t="inlineStr">
         <is>
@@ -6410,13 +6410,13 @@
         </is>
       </c>
       <c r="D71" s="15" t="n">
-        <v>58.06</v>
+        <v>57.7</v>
       </c>
       <c r="E71" s="17" t="n">
-        <v>-0.0808</v>
+        <v>-0.0867</v>
       </c>
       <c r="F71" s="17" t="n">
-        <v>-0.039</v>
+        <v>-0.0451</v>
       </c>
       <c r="G71" s="18" t="n">
         <v>46309</v>
@@ -6471,13 +6471,13 @@
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>1050.31</v>
+        <v>1068.2</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>-0.09369999999999999</v>
-      </c>
-      <c r="F72" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.07829999999999999</v>
+      </c>
+      <c r="F72" s="6" t="n">
+        <v>0.0134</v>
       </c>
       <c r="G72" s="7" t="n">
         <v>46308</v>
@@ -6509,7 +6509,7 @@
         <v>1245</v>
       </c>
       <c r="P72" s="6" t="n">
-        <v>0.1853643210099876</v>
+        <v>0.1655120763901891</v>
       </c>
       <c r="Q72" s="10" t="inlineStr">
         <is>
@@ -6554,13 +6554,13 @@
         </is>
       </c>
       <c r="D73" s="15" t="n">
-        <v>37.29</v>
+        <v>38.35</v>
       </c>
       <c r="E73" s="16" t="n">
-        <v>0.3852</v>
+        <v>0.4246</v>
       </c>
       <c r="F73" s="16" t="n">
-        <v>0.6435</v>
+        <v>0.6901999999999999</v>
       </c>
       <c r="G73" s="18" t="n"/>
       <c r="H73" s="23" t="inlineStr">
@@ -6605,13 +6605,13 @@
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>25.66</v>
+        <v>26</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>0.2675</v>
+        <v>0.2845</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>0.5427000000000001</v>
+        <v>0.5634</v>
       </c>
       <c r="G74" s="7" t="n">
         <v>46346</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="D75" s="15" t="n">
-        <v>506.95</v>
+        <v>509.6</v>
       </c>
       <c r="E75" s="16" t="n">
-        <v>0.0147</v>
+        <v>0.02</v>
       </c>
       <c r="F75" s="16" t="n">
-        <v>0.0319</v>
+        <v>0.0374</v>
       </c>
       <c r="G75" s="18" t="n">
         <v>46332</v>
@@ -6749,13 +6749,13 @@
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>65.25</v>
+        <v>64.94</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>-0.0872</v>
+        <v>-0.0916</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>-0.0535</v>
+        <v>-0.058</v>
       </c>
       <c r="G76" s="7" t="n">
         <v>46321</v>
@@ -6784,7 +6784,7 @@
         <v>68</v>
       </c>
       <c r="M76" s="6" t="n">
-        <v>0.0421455938697318</v>
+        <v>0.04712041884816758</v>
       </c>
       <c r="N76" s="3" t="inlineStr"/>
       <c r="O76" s="9" t="n"/>
@@ -6826,13 +6826,13 @@
         </is>
       </c>
       <c r="D77" s="15" t="n">
-        <v>124.02</v>
+        <v>125.07</v>
       </c>
       <c r="E77" s="17" t="n">
-        <v>-0.1452</v>
+        <v>-0.138</v>
       </c>
       <c r="F77" s="16" t="n">
-        <v>0.0033</v>
+        <v>0.0118</v>
       </c>
       <c r="G77" s="18" t="n">
         <v>46310</v>
@@ -6891,13 +6891,13 @@
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>132.14</v>
+        <v>131.78</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>-0.005600000000000001</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>0.0266</v>
+        <v>0.0238</v>
       </c>
       <c r="G78" s="7" t="n">
         <v>46308</v>
@@ -6929,7 +6929,7 @@
         <v>140</v>
       </c>
       <c r="P78" s="6" t="n">
-        <v>0.05948236718631765</v>
+        <v>0.06237668842009408</v>
       </c>
       <c r="Q78" s="10" t="inlineStr">
         <is>
@@ -6978,13 +6978,13 @@
         </is>
       </c>
       <c r="D79" s="15" t="n">
-        <v>340.05</v>
+        <v>340.15</v>
       </c>
       <c r="E79" s="17" t="n">
-        <v>-0.0026</v>
+        <v>-0.0023</v>
       </c>
       <c r="F79" s="17" t="n">
-        <v>-0.0354</v>
+        <v>-0.0351</v>
       </c>
       <c r="G79" s="18" t="n">
         <v>46315</v>
@@ -7013,7 +7013,7 @@
         <v>358</v>
       </c>
       <c r="M79" s="16" t="n">
-        <v>0.05278635494780176</v>
+        <v>0.05247684844921365</v>
       </c>
       <c r="N79" s="14" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>374</v>
       </c>
       <c r="P79" s="16" t="n">
-        <v>0.09983825907954709</v>
+        <v>0.09951491988828465</v>
       </c>
       <c r="Q79" s="21" t="inlineStr">
         <is>
@@ -7069,13 +7069,13 @@
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>57.01</v>
+        <v>57.08</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>-0.0316</v>
+        <v>-0.0303</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>-0.0301</v>
+        <v>-0.0288</v>
       </c>
       <c r="G80" s="7" t="n">
         <v>46315</v>
@@ -7104,7 +7104,7 @@
         <v>57</v>
       </c>
       <c r="M80" s="5" t="n">
-        <v>-0.0001754078231888793</v>
+        <v>-0.001401541695865422</v>
       </c>
       <c r="N80" s="3" t="inlineStr"/>
       <c r="O80" s="9" t="n"/>
@@ -7146,13 +7146,13 @@
         </is>
       </c>
       <c r="D81" s="15" t="n">
-        <v>13.57</v>
+        <v>14.45</v>
       </c>
       <c r="E81" s="16" t="n">
-        <v>0.1628</v>
-      </c>
-      <c r="F81" s="17" t="n">
-        <v>-0.05889999999999999</v>
+        <v>0.2382</v>
+      </c>
+      <c r="F81" s="16" t="n">
+        <v>0.0021</v>
       </c>
       <c r="G81" s="18" t="n"/>
       <c r="H81" s="23" t="inlineStr">
@@ -7197,13 +7197,13 @@
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>401.02</v>
+        <v>397.65</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>-0.0149</v>
+        <v>-0.0232</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="G82" s="7" t="n">
         <v>46330</v>
@@ -7270,13 +7270,13 @@
         </is>
       </c>
       <c r="D83" s="15" t="n">
-        <v>91.43000000000001</v>
+        <v>91.88</v>
       </c>
       <c r="E83" s="16" t="n">
-        <v>0.1634</v>
+        <v>0.169</v>
       </c>
       <c r="F83" s="16" t="n">
-        <v>0.3969</v>
+        <v>0.4036999999999999</v>
       </c>
       <c r="G83" s="18" t="n">
         <v>46337</v>
@@ -7331,13 +7331,13 @@
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>41.24</v>
+        <v>38.95</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>-0.125</v>
+        <v>-0.1736</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>-0.1893</v>
+        <v>-0.2343</v>
       </c>
       <c r="G84" s="7" t="n">
         <v>46331</v>
@@ -7392,13 +7392,13 @@
         </is>
       </c>
       <c r="D85" s="15" t="n">
-        <v>946.49</v>
+        <v>943.39</v>
       </c>
       <c r="E85" s="17" t="n">
-        <v>-0.0736</v>
+        <v>-0.0766</v>
       </c>
       <c r="F85" s="17" t="n">
-        <v>-0.1029</v>
+        <v>-0.1058</v>
       </c>
       <c r="G85" s="18" t="n">
         <v>46308</v>
@@ -7427,7 +7427,7 @@
         <v>1325</v>
       </c>
       <c r="M85" s="16" t="n">
-        <v>0.3999091379729315</v>
+        <v>0.4045092697611805</v>
       </c>
       <c r="N85" s="14" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>1210</v>
       </c>
       <c r="P85" s="16" t="n">
-        <v>0.2784075901488658</v>
+        <v>0.2826084652158705</v>
       </c>
       <c r="Q85" s="21" t="inlineStr">
         <is>
@@ -7479,13 +7479,13 @@
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>131.63</v>
+        <v>130.82</v>
       </c>
       <c r="E86" s="6" t="n">
-        <v>0.0118</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>-0.059</v>
+        <v>-0.06480000000000001</v>
       </c>
       <c r="G86" s="7" t="n">
         <v>46324</v>
@@ -7540,13 +7540,13 @@
         </is>
       </c>
       <c r="D87" s="15" t="n">
-        <v>117.36</v>
+        <v>119.87</v>
       </c>
       <c r="E87" s="16" t="n">
-        <v>0.2254</v>
+        <v>0.2516</v>
       </c>
       <c r="F87" s="16" t="n">
-        <v>0.1821</v>
+        <v>0.2074</v>
       </c>
       <c r="G87" s="18" t="n">
         <v>46330</v>
@@ -7601,13 +7601,13 @@
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>92.09</v>
+        <v>98.8</v>
       </c>
       <c r="E88" s="6" t="n">
-        <v>0.122</v>
+        <v>0.2037</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>-0.0876</v>
+        <v>-0.0211</v>
       </c>
       <c r="G88" s="7" t="n">
         <v>46329</v>
@@ -7662,13 +7662,13 @@
         </is>
       </c>
       <c r="D89" s="15" t="n">
-        <v>153.75</v>
+        <v>155.43</v>
       </c>
       <c r="E89" s="17" t="n">
-        <v>-0.0222</v>
+        <v>-0.0115</v>
       </c>
       <c r="F89" s="16" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.09789999999999999</v>
       </c>
       <c r="G89" s="18" t="n">
         <v>46324</v>
@@ -7723,13 +7723,13 @@
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>156.26</v>
+        <v>154.85</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>-0.0417</v>
+        <v>-0.0503</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>0.0202</v>
+        <v>0.011</v>
       </c>
       <c r="G90" s="7" t="n">
         <v>46329</v>
@@ -7798,13 +7798,13 @@
         </is>
       </c>
       <c r="D91" s="15" t="n">
-        <v>346.71</v>
+        <v>348.85</v>
       </c>
       <c r="E91" s="17" t="n">
-        <v>-0.0295</v>
+        <v>-0.0235</v>
       </c>
       <c r="F91" s="16" t="n">
-        <v>0.0231</v>
+        <v>0.0295</v>
       </c>
       <c r="G91" s="18" t="n">
         <v>46308</v>
@@ -7833,7 +7833,7 @@
         <v>196</v>
       </c>
       <c r="M91" s="17" t="n">
-        <v>-0.4346860488592772</v>
+        <v>-0.4381539343557403</v>
       </c>
       <c r="N91" s="14" t="inlineStr"/>
       <c r="O91" s="20" t="n"/>
@@ -7877,13 +7877,13 @@
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>97.95</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>-0.1133</v>
+        <v>-0.1064</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>0.0101</v>
+        <v>0.0179</v>
       </c>
       <c r="G92" s="7" t="n">
         <v>46332</v>
@@ -7912,7 +7912,7 @@
         <v>375</v>
       </c>
       <c r="M92" s="6" t="n">
-        <v>2.828483920367534</v>
+        <v>2.799007192786952</v>
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         <v>368</v>
       </c>
       <c r="P92" s="6" t="n">
-        <v>2.75701888718734</v>
+        <v>2.728092391854929</v>
       </c>
       <c r="Q92" s="10" t="inlineStr">
         <is>
@@ -7976,13 +7976,13 @@
         </is>
       </c>
       <c r="D93" s="15" t="n">
-        <v>357.45</v>
+        <v>357.48</v>
       </c>
       <c r="E93" s="17" t="n">
-        <v>-0.0579</v>
+        <v>-0.0578</v>
       </c>
       <c r="F93" s="16" t="n">
-        <v>0.0209</v>
+        <v>0.021</v>
       </c>
       <c r="G93" s="18" t="n">
         <v>46317</v>
@@ -8014,7 +8014,7 @@
         <v>115</v>
       </c>
       <c r="P93" s="17" t="n">
-        <v>-0.6782766820534341</v>
+        <v>-0.6783036813248294</v>
       </c>
       <c r="Q93" s="21" t="inlineStr">
         <is>
@@ -8063,13 +8063,13 @@
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>565.8200000000001</v>
+        <v>564.61</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>-0.0138</v>
+        <v>-0.0159</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>0.0336</v>
+        <v>0.0314</v>
       </c>
       <c r="G94" s="7" t="n">
         <v>46324</v>
@@ -8098,7 +8098,7 @@
         <v>366</v>
       </c>
       <c r="M94" s="5" t="n">
-        <v>-0.3531511788201195</v>
+        <v>-0.3517649350879368</v>
       </c>
       <c r="N94" s="3" t="inlineStr"/>
       <c r="O94" s="9" t="n"/>
@@ -8140,13 +8140,13 @@
         </is>
       </c>
       <c r="D95" s="15" t="n">
-        <v>1776.16</v>
+        <v>1778.11</v>
       </c>
       <c r="E95" s="17" t="n">
-        <v>-0.0105</v>
+        <v>-0.009399999999999999</v>
       </c>
       <c r="F95" s="17" t="n">
-        <v>-0.1021</v>
+        <v>-0.1011</v>
       </c>
       <c r="G95" s="18" t="n">
         <v>46330</v>
@@ -8211,13 +8211,13 @@
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>202.49</v>
+        <v>202.56</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>-0.0548</v>
+        <v>-0.0545</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>-0.0401</v>
+        <v>-0.0397</v>
       </c>
       <c r="G96" s="7" t="n">
         <v>46309</v>
@@ -8246,7 +8246,7 @@
         <v>668</v>
       </c>
       <c r="M96" s="6" t="n">
-        <v>2.298928342140353</v>
+        <v>2.297788309636651</v>
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>550</v>
       </c>
       <c r="P96" s="6" t="n">
-        <v>1.71618351523532</v>
+        <v>1.715244865718799</v>
       </c>
       <c r="Q96" s="10" t="inlineStr">
         <is>
@@ -8306,13 +8306,13 @@
         </is>
       </c>
       <c r="D97" s="15" t="n">
-        <v>115.44</v>
+        <v>117.66</v>
       </c>
       <c r="E97" s="16" t="n">
-        <v>0.034</v>
+        <v>0.0539</v>
       </c>
       <c r="F97" s="16" t="n">
-        <v>0.0302</v>
+        <v>0.05</v>
       </c>
       <c r="G97" s="18" t="n">
         <v>46321</v>
@@ -8341,7 +8341,7 @@
         <v>240</v>
       </c>
       <c r="M97" s="16" t="n">
-        <v>1.079002079002079</v>
+        <v>1.039775624681285</v>
       </c>
       <c r="N97" s="14" t="inlineStr">
         <is>
@@ -8352,7 +8352,7 @@
         <v>240</v>
       </c>
       <c r="P97" s="16" t="n">
-        <v>1.079002079002079</v>
+        <v>1.039775624681285</v>
       </c>
       <c r="Q97" s="21" t="inlineStr">
         <is>
@@ -8401,13 +8401,13 @@
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>231.93</v>
+        <v>232.76</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>-0.059</v>
+        <v>-0.0556</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>-0.0728</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="G98" s="7" t="n">
         <v>46310</v>
@@ -8436,7 +8436,7 @@
         <v>113</v>
       </c>
       <c r="M98" s="5" t="n">
-        <v>-0.5127840296641228</v>
+        <v>-0.5145213954287678</v>
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         <v>114</v>
       </c>
       <c r="P98" s="5" t="n">
-        <v>-0.508472383908938</v>
+        <v>-0.5102251245918542</v>
       </c>
       <c r="Q98" s="10" t="inlineStr"/>
       <c r="R98" s="9" t="n"/>
@@ -8486,13 +8486,13 @@
         </is>
       </c>
       <c r="D99" s="15" t="n">
-        <v>22.66</v>
+        <v>23.78</v>
       </c>
       <c r="E99" s="16" t="n">
-        <v>0.169</v>
+        <v>0.227</v>
       </c>
       <c r="F99" s="16" t="n">
-        <v>0.1384</v>
+        <v>0.195</v>
       </c>
       <c r="G99" s="18" t="n">
         <v>46324</v>
@@ -8547,13 +8547,13 @@
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>14.37</v>
+        <v>14.34</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>0.0138</v>
+        <v>0.0116</v>
       </c>
       <c r="F100" s="6" t="n">
-        <v>0.0785</v>
+        <v>0.0762</v>
       </c>
       <c r="G100" s="7" t="n">
         <v>46323</v>
@@ -8608,13 +8608,13 @@
         </is>
       </c>
       <c r="D101" s="15" t="n">
-        <v>104.65</v>
+        <v>105.34</v>
       </c>
       <c r="E101" s="17" t="n">
-        <v>-0.0252</v>
+        <v>-0.0188</v>
       </c>
       <c r="F101" s="16" t="n">
-        <v>0.05309999999999999</v>
+        <v>0.0601</v>
       </c>
       <c r="G101" s="18" t="n">
         <v>46323</v>
@@ -8643,7 +8643,7 @@
         <v>285</v>
       </c>
       <c r="M101" s="16" t="n">
-        <v>1.72336359292881</v>
+        <v>1.705524966774255</v>
       </c>
       <c r="N101" s="14" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         <v>285</v>
       </c>
       <c r="P101" s="16" t="n">
-        <v>1.72336359292881</v>
+        <v>1.705524966774255</v>
       </c>
       <c r="Q101" s="21" t="inlineStr">
         <is>
@@ -8695,13 +8695,13 @@
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>404.01</v>
+        <v>404.96</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>-0.05309999999999999</v>
+        <v>-0.0508</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>-0.0989</v>
+        <v>-0.0968</v>
       </c>
       <c r="G102" s="7" t="n">
         <v>46324</v>
@@ -8770,13 +8770,13 @@
         </is>
       </c>
       <c r="D103" s="15" t="n">
-        <v>48.72</v>
+        <v>48.51</v>
       </c>
       <c r="E103" s="17" t="n">
-        <v>-0.044</v>
+        <v>-0.0482</v>
       </c>
       <c r="F103" s="17" t="n">
-        <v>-0.0446</v>
+        <v>-0.0487</v>
       </c>
       <c r="G103" s="18" t="n">
         <v>46311</v>
@@ -8831,13 +8831,13 @@
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>369.18</v>
+        <v>368.21</v>
       </c>
       <c r="E104" s="6" t="n">
-        <v>0.01</v>
+        <v>0.0073</v>
       </c>
       <c r="F104" s="6" t="n">
-        <v>0.0239</v>
+        <v>0.0212</v>
       </c>
       <c r="G104" s="7" t="n">
         <v>46322</v>
@@ -8866,7 +8866,7 @@
         <v>525</v>
       </c>
       <c r="M104" s="6" t="n">
-        <v>0.422070534698521</v>
+        <v>0.4258167893321746</v>
       </c>
       <c r="N104" s="3" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>543</v>
       </c>
       <c r="P104" s="6" t="n">
-        <v>0.4708272387453274</v>
+        <v>0.4747019363949921</v>
       </c>
       <c r="Q104" s="10" t="inlineStr">
         <is>
@@ -8922,13 +8922,13 @@
         </is>
       </c>
       <c r="D105" s="15" t="n">
-        <v>69.64</v>
+        <v>69.86</v>
       </c>
       <c r="E105" s="16" t="n">
-        <v>0.0005</v>
+        <v>0.0036</v>
       </c>
       <c r="F105" s="17" t="n">
-        <v>-0.0424</v>
+        <v>-0.0395</v>
       </c>
       <c r="G105" s="18" t="n">
         <v>46314</v>
@@ -8957,7 +8957,7 @@
         <v>412</v>
       </c>
       <c r="M105" s="16" t="n">
-        <v>4.91614014933946</v>
+        <v>4.897509304322932</v>
       </c>
       <c r="N105" s="14" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>350</v>
       </c>
       <c r="P105" s="16" t="n">
-        <v>4.025847214244687</v>
+        <v>4.01002004008016</v>
       </c>
       <c r="Q105" s="21" t="inlineStr">
         <is>
@@ -9013,13 +9013,13 @@
         </is>
       </c>
       <c r="D106" s="4" t="n">
-        <v>76.51000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>-0.0546</v>
+        <v>-0.0572</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>-0.0351</v>
+        <v>-0.0377</v>
       </c>
       <c r="G106" s="7" t="n">
         <v>46331</v>
@@ -9048,7 +9048,7 @@
         <v>68</v>
       </c>
       <c r="M106" s="5" t="n">
-        <v>-0.1112272905502549</v>
+        <v>-0.108781127129751</v>
       </c>
       <c r="N106" s="3" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>68</v>
       </c>
       <c r="P106" s="5" t="n">
-        <v>-0.1112272905502549</v>
+        <v>-0.108781127129751</v>
       </c>
       <c r="Q106" s="10" t="inlineStr">
         <is>
@@ -9104,13 +9104,13 @@
         </is>
       </c>
       <c r="D107" s="15" t="n">
-        <v>263.87</v>
+        <v>263.91</v>
       </c>
       <c r="E107" s="17" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0077</v>
       </c>
       <c r="F107" s="16" t="n">
-        <v>0.0414</v>
+        <v>0.0416</v>
       </c>
       <c r="G107" s="18" t="n">
         <v>46325</v>
@@ -9139,7 +9139,7 @@
         <v>295</v>
       </c>
       <c r="M107" s="16" t="n">
-        <v>0.1179747602986319</v>
+        <v>0.1178053124171118</v>
       </c>
       <c r="N107" s="14" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>246</v>
       </c>
       <c r="P107" s="17" t="n">
-        <v>-0.06772274225944595</v>
+        <v>-0.06786404456064576</v>
       </c>
       <c r="Q107" s="21" t="inlineStr">
         <is>
@@ -9187,13 +9187,13 @@
         </is>
       </c>
       <c r="D108" s="4" t="n">
-        <v>102.6</v>
+        <v>102.25</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>-0.1034</v>
+        <v>-0.1064</v>
       </c>
       <c r="F108" s="6" t="n">
-        <v>0.0092</v>
+        <v>0.0058</v>
       </c>
       <c r="G108" s="7" t="n">
         <v>46316</v>
@@ -9222,7 +9222,7 @@
         <v>112</v>
       </c>
       <c r="M108" s="6" t="n">
-        <v>0.09161793372319695</v>
+        <v>0.09535452322738386</v>
       </c>
       <c r="N108" s="3" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>120</v>
       </c>
       <c r="P108" s="6" t="n">
-        <v>0.1695906432748539</v>
+        <v>0.1735941320293398</v>
       </c>
       <c r="Q108" s="10" t="inlineStr">
         <is>
@@ -9286,13 +9286,13 @@
         </is>
       </c>
       <c r="D109" s="15" t="n">
-        <v>381.23</v>
+        <v>385.77</v>
       </c>
       <c r="E109" s="17" t="n">
-        <v>-0.1382</v>
+        <v>-0.1279</v>
       </c>
       <c r="F109" s="16" t="n">
-        <v>0.0469</v>
+        <v>0.0593</v>
       </c>
       <c r="G109" s="18" t="n">
         <v>46329</v>
@@ -9321,7 +9321,7 @@
         <v>390</v>
       </c>
       <c r="M109" s="16" t="n">
-        <v>0.02300448548120552</v>
+        <v>0.01096508282137029</v>
       </c>
       <c r="N109" s="14" t="inlineStr">
         <is>
@@ -9369,13 +9369,13 @@
         </is>
       </c>
       <c r="D110" s="4" t="n">
-        <v>180.59</v>
+        <v>180.57</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>-0.0374</v>
+        <v>-0.0375</v>
       </c>
       <c r="F110" s="6" t="n">
-        <v>0.169</v>
+        <v>0.1689</v>
       </c>
       <c r="G110" s="7" t="n">
         <v>46331</v>
@@ -9404,7 +9404,7 @@
         <v>161</v>
       </c>
       <c r="M110" s="5" t="n">
-        <v>-0.1084777673182347</v>
+        <v>-0.1083790219859334</v>
       </c>
       <c r="N110" s="3" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>180</v>
       </c>
       <c r="P110" s="5" t="n">
-        <v>-0.003267069051442513</v>
+        <v>-0.003156670543279577</v>
       </c>
       <c r="Q110" s="10" t="inlineStr">
         <is>
@@ -9456,13 +9456,13 @@
         </is>
       </c>
       <c r="D111" s="15" t="n">
-        <v>43.6</v>
+        <v>43.29</v>
       </c>
       <c r="E111" s="17" t="n">
-        <v>-0.1618</v>
+        <v>-0.1676</v>
       </c>
       <c r="F111" s="17" t="n">
-        <v>-0.004</v>
+        <v>-0.0109</v>
       </c>
       <c r="G111" s="18" t="n">
         <v>46323</v>
@@ -9491,7 +9491,7 @@
         <v>55</v>
       </c>
       <c r="M111" s="16" t="n">
-        <v>0.2614678899082568</v>
+        <v>0.2705012705012705</v>
       </c>
       <c r="N111" s="14" t="inlineStr">
         <is>
@@ -9502,7 +9502,7 @@
         <v>65</v>
       </c>
       <c r="P111" s="16" t="n">
-        <v>0.4908256880733944</v>
+        <v>0.5015015015015015</v>
       </c>
       <c r="Q111" s="21" t="inlineStr">
         <is>
@@ -9543,13 +9543,13 @@
         </is>
       </c>
       <c r="D112" s="4" t="n">
-        <v>306.19</v>
+        <v>308.54</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>-0.0344</v>
+        <v>-0.027</v>
       </c>
       <c r="F112" s="6" t="n">
-        <v>0.0072</v>
+        <v>0.015</v>
       </c>
       <c r="G112" s="7" t="n">
         <v>46330</v>
@@ -9578,7 +9578,7 @@
         <v>331</v>
       </c>
       <c r="M112" s="6" t="n">
-        <v>0.0810281197948986</v>
+        <v>0.07279445128670506</v>
       </c>
       <c r="N112" s="3" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         <v>330</v>
       </c>
       <c r="P112" s="6" t="n">
-        <v>0.07776217381364513</v>
+        <v>0.06955338043689628</v>
       </c>
       <c r="Q112" s="10" t="inlineStr">
         <is>
@@ -9638,13 +9638,13 @@
         </is>
       </c>
       <c r="D113" s="15" t="n">
-        <v>88.73</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="E113" s="17" t="n">
-        <v>-0.0525</v>
+        <v>-0.0495</v>
       </c>
       <c r="F113" s="17" t="n">
-        <v>-0.1754</v>
+        <v>-0.1728</v>
       </c>
       <c r="G113" s="18" t="n">
         <v>46330</v>
@@ -9673,7 +9673,7 @@
         <v>123</v>
       </c>
       <c r="M113" s="16" t="n">
-        <v>0.3862278823396821</v>
+        <v>0.3818672059319177</v>
       </c>
       <c r="N113" s="14" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         <v>130</v>
       </c>
       <c r="P113" s="16" t="n">
-        <v>0.4651189000338103</v>
+        <v>0.4605100550499943</v>
       </c>
       <c r="Q113" s="21" t="inlineStr">
         <is>
@@ -9725,13 +9725,13 @@
         </is>
       </c>
       <c r="D114" s="4" t="n">
-        <v>214.14</v>
+        <v>211.58</v>
       </c>
       <c r="E114" s="6" t="n">
-        <v>0.0125</v>
+        <v>0.0004</v>
       </c>
       <c r="F114" s="6" t="n">
-        <v>0.06480000000000001</v>
+        <v>0.0521</v>
       </c>
       <c r="G114" s="7" t="n">
         <v>46315</v>
@@ -9759,8 +9759,8 @@
       <c r="L114" s="9" t="n">
         <v>212</v>
       </c>
-      <c r="M114" s="5" t="n">
-        <v>-0.009993462220976869</v>
+      <c r="M114" s="6" t="n">
+        <v>0.001985064750921578</v>
       </c>
       <c r="N114" s="3" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         <v>205</v>
       </c>
       <c r="P114" s="5" t="n">
-        <v>-0.04268235733632197</v>
+        <v>-0.03109934776443904</v>
       </c>
       <c r="Q114" s="10" t="inlineStr">
         <is>
@@ -9816,13 +9816,13 @@
         </is>
       </c>
       <c r="D115" s="15" t="n">
-        <v>88.45999999999999</v>
+        <v>89.37</v>
       </c>
       <c r="E115" s="17" t="n">
-        <v>-0.0159</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F115" s="16" t="n">
-        <v>0.1686</v>
+        <v>0.1807</v>
       </c>
       <c r="G115" s="18" t="n">
         <v>46324</v>
@@ -9851,7 +9851,7 @@
         <v>85</v>
       </c>
       <c r="M115" s="17" t="n">
-        <v>-0.03911372371693414</v>
+        <v>-0.04889784043862599</v>
       </c>
       <c r="N115" s="14" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>90</v>
       </c>
       <c r="P115" s="16" t="n">
-        <v>0.01740899841736385</v>
+        <v>0.007049345417925427</v>
       </c>
       <c r="Q115" s="21" t="inlineStr">
         <is>
@@ -9903,13 +9903,13 @@
         </is>
       </c>
       <c r="D116" s="4" t="n">
-        <v>150.09</v>
+        <v>150.02</v>
       </c>
       <c r="E116" s="6" t="n">
-        <v>0.0168</v>
+        <v>0.0164</v>
       </c>
       <c r="F116" s="6" t="n">
-        <v>0.1267</v>
+        <v>0.1262</v>
       </c>
       <c r="G116" s="7" t="n">
         <v>46324</v>
@@ -9938,7 +9938,7 @@
         <v>165</v>
       </c>
       <c r="M116" s="6" t="n">
-        <v>0.09934039576254244</v>
+        <v>0.09985335288628175</v>
       </c>
       <c r="N116" s="3" t="inlineStr"/>
       <c r="O116" s="9" t="n"/>
@@ -9986,13 +9986,13 @@
         </is>
       </c>
       <c r="D117" s="15" t="n">
-        <v>514.14</v>
+        <v>511.46</v>
       </c>
       <c r="E117" s="17" t="n">
-        <v>-0.08550000000000001</v>
+        <v>-0.0902</v>
       </c>
       <c r="F117" s="17" t="n">
-        <v>-0.08810000000000001</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="G117" s="18" t="n">
         <v>46328</v>
@@ -10057,13 +10057,13 @@
         </is>
       </c>
       <c r="D118" s="4" t="n">
-        <v>391.23</v>
+        <v>393.18</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>-0.0163</v>
+        <v>-0.0114</v>
       </c>
       <c r="F118" s="6" t="n">
-        <v>0.1078</v>
+        <v>0.1133</v>
       </c>
       <c r="G118" s="7" t="n">
         <v>46315</v>
@@ -10092,7 +10092,7 @@
         <v>487</v>
       </c>
       <c r="M118" s="6" t="n">
-        <v>0.2447920660481046</v>
+        <v>0.238618444478356</v>
       </c>
       <c r="N118" s="3" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>375</v>
       </c>
       <c r="P118" s="5" t="n">
-        <v>-0.04148454873092559</v>
+        <v>-0.04623836410804213</v>
       </c>
       <c r="Q118" s="10" t="inlineStr">
         <is>
@@ -10148,13 +10148,13 @@
         </is>
       </c>
       <c r="D119" s="15" t="n">
-        <v>268.52</v>
+        <v>270.14</v>
       </c>
       <c r="E119" s="17" t="n">
-        <v>-0.0179</v>
+        <v>-0.012</v>
       </c>
       <c r="F119" s="16" t="n">
-        <v>0.07919999999999999</v>
+        <v>0.0857</v>
       </c>
       <c r="G119" s="18" t="n">
         <v>46308</v>
@@ -10183,7 +10183,7 @@
         <v>272</v>
       </c>
       <c r="M119" s="16" t="n">
-        <v>0.01295992849694629</v>
+        <v>0.006885318723624838</v>
       </c>
       <c r="N119" s="14" t="inlineStr"/>
       <c r="O119" s="20" t="n"/>
@@ -10235,13 +10235,13 @@
         </is>
       </c>
       <c r="D120" s="4" t="n">
-        <v>1146.2</v>
+        <v>1151.71</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>-0.1048</v>
-      </c>
-      <c r="F120" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.1005</v>
+      </c>
+      <c r="F120" s="6" t="n">
+        <v>0.0042</v>
       </c>
       <c r="G120" s="7" t="n">
         <v>46324</v>
@@ -10270,7 +10270,7 @@
         <v>1280</v>
       </c>
       <c r="M120" s="6" t="n">
-        <v>0.1167335543535159</v>
+        <v>0.1113908883312639</v>
       </c>
       <c r="N120" s="3" t="inlineStr">
         <is>
@@ -10330,13 +10330,13 @@
         </is>
       </c>
       <c r="D121" s="15" t="n">
-        <v>92.90000000000001</v>
+        <v>92.17</v>
       </c>
       <c r="E121" s="17" t="n">
-        <v>-0.0131</v>
+        <v>-0.0208</v>
       </c>
       <c r="F121" s="16" t="n">
-        <v>0.1154</v>
+        <v>0.1066</v>
       </c>
       <c r="G121" s="18" t="n"/>
       <c r="H121" s="23" t="inlineStr">
@@ -10355,7 +10355,7 @@
         <v>102</v>
       </c>
       <c r="M121" s="16" t="n">
-        <v>0.0979547900968783</v>
+        <v>0.1066507540414451</v>
       </c>
       <c r="N121" s="14" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>105</v>
       </c>
       <c r="P121" s="16" t="n">
-        <v>0.1302475780409041</v>
+        <v>0.1391993056308994</v>
       </c>
       <c r="Q121" s="21" t="inlineStr">
         <is>
@@ -10407,13 +10407,13 @@
         </is>
       </c>
       <c r="D122" s="4" t="n">
-        <v>146.15</v>
+        <v>146.52</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>-0.0398</v>
+        <v>-0.0373</v>
       </c>
       <c r="F122" s="6" t="n">
-        <v>0.1748</v>
+        <v>0.1778</v>
       </c>
       <c r="G122" s="7" t="n">
         <v>46324</v>
@@ -10442,7 +10442,7 @@
         <v>150</v>
       </c>
       <c r="M122" s="6" t="n">
-        <v>0.02634279849469719</v>
+        <v>0.02375102375102368</v>
       </c>
       <c r="N122" s="3" t="inlineStr"/>
       <c r="O122" s="9" t="n"/>
@@ -10486,13 +10486,13 @@
         </is>
       </c>
       <c r="D123" s="15" t="n">
-        <v>139.93</v>
+        <v>140.43</v>
       </c>
       <c r="E123" s="17" t="n">
-        <v>-0.1271</v>
+        <v>-0.124</v>
       </c>
       <c r="F123" s="17" t="n">
-        <v>-0.0644</v>
+        <v>-0.061</v>
       </c>
       <c r="G123" s="18" t="n">
         <v>46322</v>
@@ -10565,13 +10565,13 @@
         </is>
       </c>
       <c r="D124" s="4" t="n">
-        <v>27.37</v>
+        <v>27.55</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>-0.0308</v>
+        <v>-0.0246</v>
       </c>
       <c r="F124" s="6" t="n">
-        <v>0.1059</v>
+        <v>0.1129</v>
       </c>
       <c r="G124" s="7" t="n">
         <v>46329</v>
@@ -10600,7 +10600,7 @@
         <v>28</v>
       </c>
       <c r="M124" s="6" t="n">
-        <v>0.0230179028132992</v>
+        <v>0.01633393829401086</v>
       </c>
       <c r="N124" s="3" t="inlineStr"/>
       <c r="O124" s="9" t="n"/>
@@ -10644,13 +10644,13 @@
         </is>
       </c>
       <c r="D125" s="15" t="n">
-        <v>278.48</v>
+        <v>274.75</v>
       </c>
       <c r="E125" s="17" t="n">
-        <v>-0.1809</v>
+        <v>-0.1919</v>
       </c>
       <c r="F125" s="17" t="n">
-        <v>-0.1274</v>
+        <v>-0.1391</v>
       </c>
       <c r="G125" s="18" t="n">
         <v>46324</v>
@@ -10679,7 +10679,7 @@
         <v>418</v>
       </c>
       <c r="M125" s="16" t="n">
-        <v>0.5010054582016661</v>
+        <v>0.521383075523203</v>
       </c>
       <c r="N125" s="14" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>350</v>
       </c>
       <c r="P125" s="16" t="n">
-        <v>0.2568227520827348</v>
+        <v>0.2738853503184713</v>
       </c>
       <c r="Q125" s="21" t="inlineStr">
         <is>
@@ -10735,13 +10735,13 @@
         </is>
       </c>
       <c r="D126" s="4" t="n">
-        <v>657.21</v>
+        <v>650.11</v>
       </c>
       <c r="E126" s="6" t="n">
-        <v>0.0712</v>
+        <v>0.0596</v>
       </c>
       <c r="F126" s="6" t="n">
-        <v>0.2489</v>
+        <v>0.2354</v>
       </c>
       <c r="G126" s="7" t="n">
         <v>46323</v>
@@ -10770,7 +10770,7 @@
         <v>615</v>
       </c>
       <c r="M126" s="5" t="n">
-        <v>-0.06422604646916516</v>
+        <v>-0.05400624509698361</v>
       </c>
       <c r="N126" s="3" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>570</v>
       </c>
       <c r="P126" s="5" t="n">
-        <v>-0.1326973113616653</v>
+        <v>-0.1232253003337897</v>
       </c>
       <c r="Q126" s="10" t="inlineStr">
         <is>
@@ -10830,13 +10830,13 @@
         </is>
       </c>
       <c r="D127" s="15" t="n">
-        <v>374.8</v>
+        <v>376.75</v>
       </c>
       <c r="E127" s="17" t="n">
-        <v>-0.0355</v>
+        <v>-0.0305</v>
       </c>
       <c r="F127" s="17" t="n">
-        <v>-0.1109</v>
+        <v>-0.1063</v>
       </c>
       <c r="G127" s="18" t="n">
         <v>46308</v>
@@ -10865,7 +10865,7 @@
         <v>526</v>
       </c>
       <c r="M127" s="16" t="n">
-        <v>0.4034151547491995</v>
+        <v>0.3961512939615129</v>
       </c>
       <c r="N127" s="14" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>480</v>
       </c>
       <c r="P127" s="16" t="n">
-        <v>0.2806830309498399</v>
+        <v>0.2740544127405442</v>
       </c>
       <c r="Q127" s="21" t="inlineStr">
         <is>
@@ -10921,13 +10921,13 @@
         </is>
       </c>
       <c r="D128" s="4" t="n">
-        <v>72.89</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>-0.0495</v>
+        <v>-0.067</v>
       </c>
       <c r="F128" s="5" t="n">
-        <v>-0.0435</v>
+        <v>-0.0612</v>
       </c>
       <c r="G128" s="7" t="n">
         <v>46329</v>
@@ -11000,13 +11000,13 @@
         </is>
       </c>
       <c r="D129" s="15" t="n">
-        <v>270.7</v>
+        <v>271.13</v>
       </c>
       <c r="E129" s="17" t="n">
-        <v>-0.0235</v>
+        <v>-0.022</v>
       </c>
       <c r="F129" s="16" t="n">
-        <v>0.06059999999999999</v>
+        <v>0.0623</v>
       </c>
       <c r="G129" s="18" t="n">
         <v>46330</v>
@@ -11035,7 +11035,7 @@
         <v>248</v>
       </c>
       <c r="M129" s="17" t="n">
-        <v>-0.08385666789804208</v>
+        <v>-0.08530963006675762</v>
       </c>
       <c r="N129" s="14" t="inlineStr"/>
       <c r="O129" s="20" t="n"/>
@@ -11091,13 +11091,13 @@
         </is>
       </c>
       <c r="D130" s="4" t="n">
-        <v>120.31</v>
+        <v>119.89</v>
       </c>
       <c r="E130" s="6" t="n">
-        <v>0.2089</v>
+        <v>0.2047</v>
       </c>
       <c r="F130" s="6" t="n">
-        <v>0.0711</v>
+        <v>0.0673</v>
       </c>
       <c r="G130" s="7" t="n">
         <v>46325</v>
@@ -11152,13 +11152,13 @@
         </is>
       </c>
       <c r="D131" s="15" t="n">
-        <v>236.21</v>
+        <v>237.79</v>
       </c>
       <c r="E131" s="17" t="n">
-        <v>-0.0288</v>
+        <v>-0.0223</v>
       </c>
       <c r="F131" s="16" t="n">
-        <v>0.0043</v>
+        <v>0.011</v>
       </c>
       <c r="G131" s="18" t="n">
         <v>46324</v>
@@ -11213,13 +11213,13 @@
         </is>
       </c>
       <c r="D132" s="4" t="n">
-        <v>196.44</v>
+        <v>198.45</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>-0.1159</v>
+        <v>-0.1069</v>
       </c>
       <c r="F132" s="5" t="n">
-        <v>-0.0623</v>
+        <v>-0.0527</v>
       </c>
       <c r="G132" s="7" t="n">
         <v>46330</v>
@@ -11248,7 +11248,7 @@
         <v>250</v>
       </c>
       <c r="M132" s="6" t="n">
-        <v>0.2726532274485848</v>
+        <v>0.2597631645250694</v>
       </c>
       <c r="N132" s="3" t="inlineStr"/>
       <c r="O132" s="9" t="n"/>
@@ -11292,13 +11292,13 @@
         </is>
       </c>
       <c r="D133" s="15" t="n">
-        <v>163.71</v>
+        <v>163.15</v>
       </c>
       <c r="E133" s="17" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.0732</v>
       </c>
       <c r="F133" s="16" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="G133" s="18" t="n">
         <v>46329</v>
@@ -11363,13 +11363,13 @@
         </is>
       </c>
       <c r="D134" s="4" t="n">
-        <v>804.6799999999999</v>
+        <v>808.16</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>-0.014</v>
+        <v>-0.0098</v>
       </c>
       <c r="F134" s="5" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.065</v>
       </c>
       <c r="G134" s="7" t="n">
         <v>46330</v>
@@ -11398,7 +11398,7 @@
         <v>1155</v>
       </c>
       <c r="M134" s="6" t="n">
-        <v>0.4353531838743352</v>
+        <v>0.4291724411007722</v>
       </c>
       <c r="N134" s="3" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
         <v>1103</v>
       </c>
       <c r="P134" s="6" t="n">
-        <v>0.3707312223492569</v>
+        <v>0.3648287467828153</v>
       </c>
       <c r="Q134" s="10" t="inlineStr">
         <is>
@@ -11450,13 +11450,13 @@
         </is>
       </c>
       <c r="D135" s="15" t="n">
-        <v>525.26</v>
+        <v>532.3</v>
       </c>
       <c r="E135" s="17" t="n">
-        <v>-0.1366</v>
+        <v>-0.125</v>
       </c>
       <c r="F135" s="17" t="n">
-        <v>-0.1786</v>
+        <v>-0.1675</v>
       </c>
       <c r="G135" s="18" t="n">
         <v>46331</v>
@@ -11485,7 +11485,7 @@
         <v>874</v>
       </c>
       <c r="M135" s="16" t="n">
-        <v>0.6639378593458478</v>
+        <v>0.6419312417809507</v>
       </c>
       <c r="N135" s="14" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>845</v>
       </c>
       <c r="P135" s="16" t="n">
-        <v>0.6087271065757911</v>
+        <v>0.5874506857035507</v>
       </c>
       <c r="Q135" s="21" t="inlineStr">
         <is>
@@ -11545,13 +11545,13 @@
         </is>
       </c>
       <c r="D136" s="4" t="n">
-        <v>198.1</v>
+        <v>197.76</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>-0.0245</v>
+        <v>-0.0262</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>-0.0183</v>
+        <v>-0.02</v>
       </c>
       <c r="G136" s="7" t="n">
         <v>46288</v>
@@ -11580,7 +11580,7 @@
         <v>250</v>
       </c>
       <c r="M136" s="6" t="n">
-        <v>0.2619888944977284</v>
+        <v>0.26415857605178</v>
       </c>
       <c r="N136" s="3" t="inlineStr"/>
       <c r="O136" s="9" t="n"/>
@@ -11624,13 +11624,13 @@
         </is>
       </c>
       <c r="D137" s="15" t="n">
-        <v>684.5599999999999</v>
+        <v>682.92</v>
       </c>
       <c r="E137" s="16" t="n">
-        <v>0.179</v>
+        <v>0.1762</v>
       </c>
       <c r="F137" s="16" t="n">
-        <v>0.1682</v>
+        <v>0.1654</v>
       </c>
       <c r="G137" s="18" t="n"/>
       <c r="H137" s="23" t="inlineStr">
@@ -11649,7 +11649,7 @@
         <v>750</v>
       </c>
       <c r="M137" s="16" t="n">
-        <v>0.0955942503213744</v>
+        <v>0.09822526796696544</v>
       </c>
       <c r="N137" s="14" t="inlineStr">
         <is>
@@ -11660,7 +11660,7 @@
         <v>641.29</v>
       </c>
       <c r="P137" s="17" t="n">
-        <v>-0.06320848428187446</v>
+        <v>-0.06095882387395302</v>
       </c>
       <c r="Q137" s="21" t="inlineStr">
         <is>
@@ -11701,13 +11701,13 @@
         </is>
       </c>
       <c r="D138" s="4" t="n">
-        <v>147.84</v>
+        <v>149.77</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>-0.0619</v>
+        <v>-0.04969999999999999</v>
       </c>
       <c r="F138" s="6" t="n">
-        <v>0.0824</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="G138" s="7" t="n">
         <v>46330</v>
@@ -11743,7 +11743,7 @@
         <v>185</v>
       </c>
       <c r="P138" s="6" t="n">
-        <v>0.2513528138528138</v>
+        <v>0.2352273486011884</v>
       </c>
       <c r="Q138" s="10" t="inlineStr">
         <is>
@@ -11782,13 +11782,13 @@
         </is>
       </c>
       <c r="D139" s="15" t="n">
-        <v>416.57</v>
-      </c>
-      <c r="E139" s="17" t="n">
-        <v>-0.0191</v>
+        <v>425.11</v>
+      </c>
+      <c r="E139" s="16" t="n">
+        <v>0.001</v>
       </c>
       <c r="F139" s="16" t="n">
-        <v>0.0378</v>
+        <v>0.059</v>
       </c>
       <c r="G139" s="18" t="n">
         <v>46329</v>
@@ -11824,7 +11824,7 @@
         <v>453</v>
       </c>
       <c r="P139" s="16" t="n">
-        <v>0.08745228893103202</v>
+        <v>0.0656065488932276</v>
       </c>
       <c r="Q139" s="21" t="inlineStr">
         <is>
@@ -11865,13 +11865,13 @@
         </is>
       </c>
       <c r="D140" s="4" t="n">
-        <v>48.83</v>
+        <v>49.01</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>-0.0506</v>
+        <v>-0.0472</v>
       </c>
       <c r="F140" s="6" t="n">
-        <v>0.091</v>
+        <v>0.095</v>
       </c>
       <c r="G140" s="7" t="n">
         <v>46309</v>
@@ -11944,13 +11944,13 @@
         </is>
       </c>
       <c r="D141" s="15" t="n">
-        <v>304.3</v>
+        <v>303.73</v>
       </c>
       <c r="E141" s="17" t="n">
-        <v>-0.0733</v>
+        <v>-0.0751</v>
       </c>
       <c r="F141" s="17" t="n">
-        <v>-0.0063</v>
+        <v>-0.008100000000000001</v>
       </c>
       <c r="G141" s="18" t="n">
         <v>46282</v>
@@ -11979,7 +11979,7 @@
         <v>425</v>
       </c>
       <c r="M141" s="16" t="n">
-        <v>0.3966480446927374</v>
+        <v>0.3992690876765547</v>
       </c>
       <c r="N141" s="14" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>323</v>
       </c>
       <c r="P141" s="16" t="n">
-        <v>0.06145251396648041</v>
+        <v>0.06344450663418161</v>
       </c>
       <c r="Q141" s="21" t="inlineStr">
         <is>
@@ -12031,13 +12031,13 @@
         </is>
       </c>
       <c r="D142" s="4" t="n">
-        <v>214.05</v>
+        <v>214.57</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>-0.1198</v>
+        <v>-0.1177</v>
       </c>
       <c r="F142" s="5" t="n">
-        <v>-0.0654</v>
+        <v>-0.06309999999999999</v>
       </c>
       <c r="G142" s="7" t="n"/>
       <c r="H142" s="12" t="inlineStr">
@@ -12056,7 +12056,7 @@
         <v>285</v>
       </c>
       <c r="M142" s="6" t="n">
-        <v>0.3314646110721793</v>
+        <v>0.3282378710910193</v>
       </c>
       <c r="N142" s="3" t="inlineStr"/>
       <c r="O142" s="9" t="n"/>
@@ -12104,13 +12104,13 @@
         </is>
       </c>
       <c r="D143" s="15" t="n">
-        <v>1607.89</v>
+        <v>1643.9</v>
       </c>
       <c r="E143" s="17" t="n">
-        <v>-0.052</v>
+        <v>-0.0308</v>
       </c>
       <c r="F143" s="17" t="n">
-        <v>-0.0609</v>
+        <v>-0.0399</v>
       </c>
       <c r="G143" s="18" t="n">
         <v>46317</v>
@@ -12165,13 +12165,13 @@
         </is>
       </c>
       <c r="D144" s="4" t="n">
-        <v>54.35</v>
+        <v>54.89</v>
       </c>
       <c r="E144" s="6" t="n">
-        <v>0.0054</v>
+        <v>0.0154</v>
       </c>
       <c r="F144" s="6" t="n">
-        <v>0.09820000000000001</v>
+        <v>0.1091</v>
       </c>
       <c r="G144" s="7" t="n">
         <v>46332</v>
@@ -12226,13 +12226,13 @@
         </is>
       </c>
       <c r="D145" s="15" t="n">
-        <v>351.4</v>
+        <v>352.65</v>
       </c>
       <c r="E145" s="17" t="n">
-        <v>-0.1043</v>
+        <v>-0.1011</v>
       </c>
       <c r="F145" s="17" t="n">
-        <v>-0.0518</v>
+        <v>-0.0484</v>
       </c>
       <c r="G145" s="18" t="n">
         <v>46318</v>
@@ -12261,7 +12261,7 @@
         <v>400</v>
       </c>
       <c r="M145" s="16" t="n">
-        <v>0.1383039271485487</v>
+        <v>0.1342691053452432</v>
       </c>
       <c r="N145" s="14" t="inlineStr"/>
       <c r="O145" s="20" t="n"/>
@@ -12313,13 +12313,13 @@
         </is>
       </c>
       <c r="D146" s="4" t="n">
-        <v>311.9</v>
+        <v>313.67</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>-0.1244</v>
+        <v>-0.1195</v>
       </c>
       <c r="F146" s="5" t="n">
-        <v>-0.0861</v>
+        <v>-0.081</v>
       </c>
       <c r="G146" s="7" t="n">
         <v>46315</v>
@@ -12348,7 +12348,7 @@
         <v>390</v>
       </c>
       <c r="M146" s="6" t="n">
-        <v>0.2504007694773967</v>
+        <v>0.2433449166321292</v>
       </c>
       <c r="N146" s="3" t="inlineStr"/>
       <c r="O146" s="9" t="n"/>
@@ -12400,13 +12400,13 @@
         </is>
       </c>
       <c r="D147" s="15" t="n">
-        <v>933.03</v>
+        <v>939.85</v>
       </c>
       <c r="E147" s="17" t="n">
-        <v>-0.0551</v>
+        <v>-0.0482</v>
       </c>
       <c r="F147" s="17" t="n">
-        <v>-0.1354</v>
+        <v>-0.1291</v>
       </c>
       <c r="G147" s="18" t="n">
         <v>46316</v>
@@ -12435,7 +12435,7 @@
         <v>1259</v>
       </c>
       <c r="M147" s="16" t="n">
-        <v>0.3493671157411873</v>
+        <v>0.3395754641698143</v>
       </c>
       <c r="N147" s="14" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>1350</v>
       </c>
       <c r="P147" s="16" t="n">
-        <v>0.446898813542973</v>
+        <v>0.4363994254402298</v>
       </c>
       <c r="Q147" s="21" t="inlineStr">
         <is>
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="D148" s="4" t="n">
-        <v>1253.73</v>
+        <v>1267.94</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>-0.0407</v>
+        <v>-0.0298</v>
       </c>
       <c r="F148" s="5" t="n">
-        <v>-0.0857</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="G148" s="7" t="n">
         <v>46325</v>
@@ -12566,13 +12566,13 @@
         </is>
       </c>
       <c r="D149" s="15" t="n">
-        <v>205.25</v>
+        <v>206.46</v>
       </c>
       <c r="E149" s="17" t="n">
-        <v>-0.07429999999999999</v>
+        <v>-0.0689</v>
       </c>
       <c r="F149" s="17" t="n">
-        <v>-0.0925</v>
+        <v>-0.0872</v>
       </c>
       <c r="G149" s="18" t="n">
         <v>46317</v>
@@ -12627,13 +12627,13 @@
         </is>
       </c>
       <c r="D150" s="4" t="n">
-        <v>445.72</v>
+        <v>446.92</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>-0.0629</v>
+        <v>-0.0604</v>
       </c>
       <c r="F150" s="5" t="n">
-        <v>-0.081</v>
+        <v>-0.0785</v>
       </c>
       <c r="G150" s="7" t="n">
         <v>46322</v>
@@ -12694,13 +12694,13 @@
         </is>
       </c>
       <c r="D151" s="15" t="n">
-        <v>268.39</v>
+        <v>269.67</v>
       </c>
       <c r="E151" s="17" t="n">
-        <v>-0.0558</v>
+        <v>-0.0513</v>
       </c>
       <c r="F151" s="17" t="n">
-        <v>-0.0121</v>
+        <v>-0.0074</v>
       </c>
       <c r="G151" s="18" t="n">
         <v>46318</v>
@@ -12732,7 +12732,7 @@
         <v>272</v>
       </c>
       <c r="P151" s="16" t="n">
-        <v>0.01345057565483071</v>
+        <v>0.008640189861682739</v>
       </c>
       <c r="Q151" s="21" t="inlineStr">
         <is>
@@ -12785,13 +12785,13 @@
         </is>
       </c>
       <c r="D152" s="4" t="n">
-        <v>247.83</v>
+        <v>246.9</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>-0.1057</v>
+        <v>-0.109</v>
       </c>
       <c r="F152" s="5" t="n">
-        <v>-0.1166</v>
+        <v>-0.1199</v>
       </c>
       <c r="G152" s="7" t="n">
         <v>46324</v>
@@ -12856,13 +12856,13 @@
         </is>
       </c>
       <c r="D153" s="15" t="n">
-        <v>360.85</v>
+        <v>359.82</v>
       </c>
       <c r="E153" s="17" t="n">
-        <v>-0.1395</v>
+        <v>-0.1419</v>
       </c>
       <c r="F153" s="17" t="n">
-        <v>-0.3237</v>
+        <v>-0.3256</v>
       </c>
       <c r="G153" s="18" t="n">
         <v>46323</v>
@@ -12917,13 +12917,13 @@
         </is>
       </c>
       <c r="D154" s="4" t="n">
-        <v>531.75</v>
+        <v>533.88</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>-0.0974</v>
+        <v>-0.09380000000000001</v>
       </c>
       <c r="F154" s="6" t="n">
-        <v>0.0436</v>
+        <v>0.0478</v>
       </c>
       <c r="G154" s="7" t="n">
         <v>46315</v>
@@ -12984,13 +12984,13 @@
         </is>
       </c>
       <c r="D155" s="15" t="n">
-        <v>173.42</v>
+        <v>173</v>
       </c>
       <c r="E155" s="17" t="n">
-        <v>-0.1544</v>
+        <v>-0.1564</v>
       </c>
       <c r="F155" s="17" t="n">
-        <v>-0.2517</v>
+        <v>-0.2535</v>
       </c>
       <c r="G155" s="18" t="n">
         <v>46330</v>
@@ -13019,7 +13019,7 @@
         <v>575</v>
       </c>
       <c r="M155" s="16" t="n">
-        <v>2.315649867374006</v>
+        <v>2.323699421965318</v>
       </c>
       <c r="N155" s="14" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>237</v>
       </c>
       <c r="P155" s="16" t="n">
-        <v>0.3666243801176336</v>
+        <v>0.3699421965317919</v>
       </c>
       <c r="Q155" s="21" t="inlineStr">
         <is>
@@ -13079,13 +13079,13 @@
         </is>
       </c>
       <c r="D156" s="4" t="n">
-        <v>115.58</v>
+        <v>116.16</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>-0.0565</v>
+        <v>-0.0518</v>
       </c>
       <c r="F156" s="6" t="n">
-        <v>0.0033</v>
+        <v>0.0083</v>
       </c>
       <c r="G156" s="7" t="n">
         <v>46288</v>
@@ -13114,7 +13114,7 @@
         <v>250</v>
       </c>
       <c r="M156" s="6" t="n">
-        <v>1.163003979927323</v>
+        <v>1.152203856749311</v>
       </c>
       <c r="N156" s="3" t="inlineStr"/>
       <c r="O156" s="9" t="n"/>
@@ -13158,13 +13158,13 @@
         </is>
       </c>
       <c r="D157" s="15" t="n">
-        <v>115.88</v>
+        <v>116.05</v>
       </c>
       <c r="E157" s="17" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.08960000000000001</v>
       </c>
       <c r="F157" s="17" t="n">
-        <v>-0.068</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="G157" s="18" t="n">
         <v>46315</v>
@@ -13193,7 +13193,7 @@
         <v>95</v>
       </c>
       <c r="M157" s="17" t="n">
-        <v>-0.1801863997238522</v>
+        <v>-0.1813873330461008</v>
       </c>
       <c r="N157" s="14" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>139</v>
       </c>
       <c r="P157" s="16" t="n">
-        <v>0.1995167414566794</v>
+        <v>0.1977595863851788</v>
       </c>
       <c r="Q157" s="21" t="inlineStr">
         <is>
@@ -13249,13 +13249,13 @@
         </is>
       </c>
       <c r="D158" s="4" t="n">
-        <v>932.2</v>
+        <v>942.8200000000001</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>-0.08900000000000001</v>
+        <v>-0.0786</v>
       </c>
       <c r="F158" s="5" t="n">
-        <v>-0.0196</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="G158" s="7" t="n">
         <v>46331</v>
@@ -13284,7 +13284,7 @@
         <v>125</v>
       </c>
       <c r="M158" s="5" t="n">
-        <v>-0.865908603304012</v>
+        <v>-0.8674190195371333</v>
       </c>
       <c r="N158" s="3" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>1064</v>
       </c>
       <c r="P158" s="6" t="n">
-        <v>0.1413859686762497</v>
+        <v>0.1285293056999215</v>
       </c>
       <c r="Q158" s="10" t="inlineStr">
         <is>
@@ -13340,13 +13340,13 @@
         </is>
       </c>
       <c r="D159" s="15" t="n">
-        <v>495.24</v>
+        <v>500.59</v>
       </c>
       <c r="E159" s="17" t="n">
-        <v>-0.0486</v>
+        <v>-0.0383</v>
       </c>
       <c r="F159" s="17" t="n">
-        <v>-0.1295</v>
+        <v>-0.1201</v>
       </c>
       <c r="G159" s="18" t="n">
         <v>46325</v>
@@ -13421,13 +13421,13 @@
         </is>
       </c>
       <c r="D160" s="4" t="n">
-        <v>410.48</v>
+        <v>415.08</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>-0.0526</v>
+        <v>-0.042</v>
       </c>
       <c r="F160" s="5" t="n">
-        <v>-0.1051</v>
+        <v>-0.0951</v>
       </c>
       <c r="G160" s="7" t="n">
         <v>46331</v>
@@ -13482,13 +13482,13 @@
         </is>
       </c>
       <c r="D161" s="15" t="n">
-        <v>33.02</v>
+        <v>32.49</v>
       </c>
       <c r="E161" s="17" t="n">
-        <v>-0.08939999999999999</v>
+        <v>-0.1038</v>
       </c>
       <c r="F161" s="17" t="n">
-        <v>-0.262</v>
+        <v>-0.2737</v>
       </c>
       <c r="G161" s="18" t="n">
         <v>46323</v>
@@ -13557,13 +13557,13 @@
         </is>
       </c>
       <c r="D162" s="4" t="n">
-        <v>192.14</v>
+        <v>193.19</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>-0.128</v>
+        <v>-0.1233</v>
       </c>
       <c r="F162" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0064</v>
       </c>
       <c r="G162" s="7" t="n">
         <v>46315</v>
@@ -13636,13 +13636,13 @@
         </is>
       </c>
       <c r="D163" s="15" t="n">
-        <v>43.13</v>
-      </c>
-      <c r="E163" s="16" t="n">
-        <v>0.0263</v>
+        <v>41.97</v>
+      </c>
+      <c r="E163" s="17" t="n">
+        <v>-0.0011</v>
       </c>
       <c r="F163" s="16" t="n">
-        <v>0.0562</v>
+        <v>0.028</v>
       </c>
       <c r="G163" s="18" t="n"/>
       <c r="H163" s="23" t="inlineStr">
@@ -13687,13 +13687,13 @@
         </is>
       </c>
       <c r="D164" s="4" t="n">
-        <v>423.46</v>
+        <v>428.83</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>-0.0703</v>
+        <v>-0.0585</v>
       </c>
       <c r="F164" s="5" t="n">
-        <v>-0.0955</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="G164" s="7" t="n">
         <v>46324</v>
@@ -13725,7 +13725,7 @@
         <v>560</v>
       </c>
       <c r="P164" s="6" t="n">
-        <v>0.3224389552732254</v>
+        <v>0.3058787864654992</v>
       </c>
       <c r="Q164" s="10" t="inlineStr">
         <is>
@@ -13778,13 +13778,13 @@
         </is>
       </c>
       <c r="D165" s="15" t="n">
-        <v>279.68</v>
+        <v>279.32</v>
       </c>
       <c r="E165" s="17" t="n">
-        <v>-0.0733</v>
+        <v>-0.0745</v>
       </c>
       <c r="F165" s="17" t="n">
-        <v>-0.0559</v>
+        <v>-0.0571</v>
       </c>
       <c r="G165" s="18" t="n">
         <v>46317</v>
@@ -13816,7 +13816,7 @@
         <v>294</v>
       </c>
       <c r="P165" s="16" t="n">
-        <v>0.05120137299771164</v>
+        <v>0.05255620793355294</v>
       </c>
       <c r="Q165" s="21" t="inlineStr">
         <is>
@@ -13861,13 +13861,13 @@
         </is>
       </c>
       <c r="D166" s="4" t="n">
-        <v>246.99</v>
+        <v>248.96</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>-0.0537</v>
+        <v>-0.0461</v>
       </c>
       <c r="F166" s="5" t="n">
-        <v>-0.1532</v>
+        <v>-0.1464</v>
       </c>
       <c r="G166" s="7" t="n">
         <v>46323</v>
@@ -13899,7 +13899,7 @@
         <v>425</v>
       </c>
       <c r="P166" s="6" t="n">
-        <v>0.7207174379529535</v>
+        <v>0.7071015424164524</v>
       </c>
       <c r="Q166" s="10" t="inlineStr">
         <is>
@@ -13940,13 +13940,13 @@
         </is>
       </c>
       <c r="D167" s="15" t="n">
-        <v>212.42</v>
+        <v>211.12</v>
       </c>
       <c r="E167" s="17" t="n">
-        <v>-0.0562</v>
+        <v>-0.062</v>
       </c>
       <c r="F167" s="17" t="n">
-        <v>-0.1114</v>
+        <v>-0.1168</v>
       </c>
       <c r="G167" s="18" t="n">
         <v>46321</v>
@@ -13975,7 +13975,7 @@
         <v>268</v>
       </c>
       <c r="M167" s="16" t="n">
-        <v>0.2616514452499765</v>
+        <v>0.2694202349374763</v>
       </c>
       <c r="N167" s="14" t="inlineStr"/>
       <c r="O167" s="20" t="n"/>
@@ -14023,13 +14023,13 @@
         </is>
       </c>
       <c r="D168" s="4" t="n">
-        <v>307.41</v>
+        <v>313.57</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>-0.0383</v>
+        <v>-0.019</v>
       </c>
       <c r="F168" s="5" t="n">
-        <v>-0.1709</v>
+        <v>-0.1543</v>
       </c>
       <c r="G168" s="7" t="n">
         <v>46330</v>
@@ -14098,13 +14098,13 @@
         </is>
       </c>
       <c r="D169" s="15" t="n">
-        <v>318.3</v>
+        <v>321.99</v>
       </c>
       <c r="E169" s="17" t="n">
-        <v>-0.1157</v>
+        <v>-0.1055</v>
       </c>
       <c r="F169" s="17" t="n">
-        <v>-0.1854</v>
+        <v>-0.176</v>
       </c>
       <c r="G169" s="18" t="n"/>
       <c r="H169" s="23" t="inlineStr">
@@ -14167,13 +14167,13 @@
         </is>
       </c>
       <c r="D170" s="4" t="n">
-        <v>107.81</v>
+        <v>107.59</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>-0.0723</v>
+        <v>-0.0742</v>
       </c>
       <c r="F170" s="5" t="n">
-        <v>-0.1062</v>
+        <v>-0.108</v>
       </c>
       <c r="G170" s="7" t="n">
         <v>46322</v>
@@ -14246,13 +14246,13 @@
         </is>
       </c>
       <c r="D171" s="15" t="n">
-        <v>99.44</v>
+        <v>105.07</v>
       </c>
       <c r="E171" s="17" t="n">
-        <v>-0.1862</v>
-      </c>
-      <c r="F171" s="17" t="n">
-        <v>-0.0348</v>
+        <v>-0.1402</v>
+      </c>
+      <c r="F171" s="16" t="n">
+        <v>0.0199</v>
       </c>
       <c r="G171" s="18" t="n">
         <v>46331</v>
@@ -14307,13 +14307,13 @@
         </is>
       </c>
       <c r="D172" s="4" t="n">
-        <v>333.07</v>
+        <v>335.81</v>
       </c>
       <c r="E172" s="6" t="n">
-        <v>0.0513</v>
+        <v>0.0599</v>
       </c>
       <c r="F172" s="6" t="n">
-        <v>0.0198</v>
+        <v>0.0282</v>
       </c>
       <c r="G172" s="7" t="n">
         <v>46324</v>
@@ -14342,7 +14342,7 @@
         <v>310</v>
       </c>
       <c r="M172" s="5" t="n">
-        <v>-0.06926471912811119</v>
+        <v>-0.07685893808999138</v>
       </c>
       <c r="N172" s="3" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>365</v>
       </c>
       <c r="P172" s="6" t="n">
-        <v>0.09586573392980456</v>
+        <v>0.08692415353920371</v>
       </c>
       <c r="Q172" s="10" t="inlineStr">
         <is>
@@ -14410,13 +14410,13 @@
         </is>
       </c>
       <c r="D173" s="15" t="n">
-        <v>106.13</v>
+        <v>109.09</v>
       </c>
       <c r="E173" s="17" t="n">
-        <v>-0.1606</v>
+        <v>-0.1372</v>
       </c>
       <c r="F173" s="17" t="n">
-        <v>-0.1942</v>
+        <v>-0.1717</v>
       </c>
       <c r="G173" s="18" t="n">
         <v>46329</v>
@@ -14471,13 +14471,13 @@
         </is>
       </c>
       <c r="D174" s="4" t="n">
-        <v>184.12</v>
-      </c>
-      <c r="E174" s="6" t="n">
-        <v>0.0052</v>
+        <v>180.89</v>
+      </c>
+      <c r="E174" s="5" t="n">
+        <v>-0.0124</v>
       </c>
       <c r="F174" s="6" t="n">
-        <v>0.2722</v>
+        <v>0.2498</v>
       </c>
       <c r="G174" s="7" t="n">
         <v>46296</v>
@@ -14532,13 +14532,13 @@
         </is>
       </c>
       <c r="D175" s="15" t="n">
-        <v>249.41</v>
+        <v>248.71</v>
       </c>
       <c r="E175" s="17" t="n">
-        <v>-0.08460000000000001</v>
+        <v>-0.0872</v>
       </c>
       <c r="F175" s="16" t="n">
-        <v>0.0625</v>
+        <v>0.0595</v>
       </c>
       <c r="G175" s="18" t="n"/>
       <c r="H175" s="23" t="inlineStr">
@@ -14583,13 +14583,13 @@
         </is>
       </c>
       <c r="D176" s="4" t="n">
-        <v>369.61</v>
-      </c>
-      <c r="E176" s="5" t="n">
-        <v>-0.0098</v>
-      </c>
-      <c r="F176" s="5" t="n">
-        <v>-0.0077</v>
+        <v>375.59</v>
+      </c>
+      <c r="E176" s="6" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="F176" s="6" t="n">
+        <v>0.008399999999999999</v>
       </c>
       <c r="G176" s="7" t="n"/>
       <c r="H176" s="12" t="inlineStr">
@@ -14608,7 +14608,7 @@
         <v>515</v>
       </c>
       <c r="M176" s="6" t="n">
-        <v>0.3933605692486675</v>
+        <v>0.3711760164008627</v>
       </c>
       <c r="N176" s="3" t="inlineStr">
         <is>
@@ -14619,7 +14619,7 @@
         <v>474</v>
       </c>
       <c r="P176" s="6" t="n">
-        <v>0.2824328346094532</v>
+        <v>0.2620144306291436</v>
       </c>
       <c r="Q176" s="10" t="inlineStr">
         <is>
@@ -14668,13 +14668,13 @@
         </is>
       </c>
       <c r="D177" s="15" t="n">
-        <v>216.83</v>
+        <v>216.67</v>
       </c>
       <c r="E177" s="17" t="n">
-        <v>-0.1371</v>
+        <v>-0.1378</v>
       </c>
       <c r="F177" s="17" t="n">
-        <v>-0.004500000000000001</v>
+        <v>-0.0052</v>
       </c>
       <c r="G177" s="18" t="n"/>
       <c r="H177" s="23" t="inlineStr">
@@ -14719,13 +14719,13 @@
         </is>
       </c>
       <c r="D178" s="4" t="n">
-        <v>259.86</v>
+        <v>262.25</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>-0.1171</v>
+        <v>-0.1089</v>
       </c>
       <c r="F178" s="5" t="n">
-        <v>-0.0741</v>
+        <v>-0.06559999999999999</v>
       </c>
       <c r="G178" s="7" t="n">
         <v>46329</v>
@@ -14780,13 +14780,13 @@
         </is>
       </c>
       <c r="D179" s="15" t="n">
-        <v>297.04</v>
+        <v>303.2</v>
       </c>
       <c r="E179" s="16" t="n">
-        <v>0.0277</v>
+        <v>0.0491</v>
       </c>
       <c r="F179" s="17" t="n">
-        <v>-0.039</v>
+        <v>-0.019</v>
       </c>
       <c r="G179" s="18" t="n">
         <v>46329</v>
@@ -14841,13 +14841,13 @@
         </is>
       </c>
       <c r="D180" s="4" t="n">
-        <v>33.86</v>
+        <v>34.12</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>-0.1171</v>
+        <v>-0.1104</v>
       </c>
       <c r="F180" s="5" t="n">
-        <v>-0.2696</v>
+        <v>-0.2641</v>
       </c>
       <c r="G180" s="7" t="n">
         <v>46324</v>
@@ -14902,13 +14902,13 @@
         </is>
       </c>
       <c r="D181" s="15" t="n">
-        <v>430.58</v>
+        <v>444.58</v>
       </c>
       <c r="E181" s="17" t="n">
-        <v>-0.1322</v>
+        <v>-0.104</v>
       </c>
       <c r="F181" s="17" t="n">
-        <v>-0.1809</v>
+        <v>-0.1543</v>
       </c>
       <c r="G181" s="18" t="n">
         <v>46338</v>
@@ -14937,7 +14937,7 @@
         <v>740</v>
       </c>
       <c r="M181" s="16" t="n">
-        <v>0.7186121046030935</v>
+        <v>0.664492329839399</v>
       </c>
       <c r="N181" s="14" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>700</v>
       </c>
       <c r="P181" s="16" t="n">
-        <v>0.6257141530029263</v>
+        <v>0.5745197714697018</v>
       </c>
       <c r="Q181" s="21" t="inlineStr">
         <is>
@@ -14989,13 +14989,13 @@
         </is>
       </c>
       <c r="D182" s="4" t="n">
-        <v>63.67</v>
+        <v>65.88</v>
       </c>
       <c r="E182" s="6" t="n">
-        <v>0.0756</v>
+        <v>0.113</v>
       </c>
       <c r="F182" s="5" t="n">
-        <v>-0.1323</v>
+        <v>-0.1021</v>
       </c>
       <c r="G182" s="7" t="n">
         <v>46331</v>
@@ -15054,13 +15054,13 @@
         </is>
       </c>
       <c r="D183" s="15" t="n">
-        <v>546.05</v>
+        <v>559.28</v>
       </c>
       <c r="E183" s="16" t="n">
-        <v>0.1707</v>
+        <v>0.1991</v>
       </c>
       <c r="F183" s="16" t="n">
-        <v>0.08439999999999999</v>
+        <v>0.1106</v>
       </c>
       <c r="G183" s="18" t="n">
         <v>46329</v>
@@ -15089,7 +15089,7 @@
         <v>615</v>
       </c>
       <c r="M183" s="16" t="n">
-        <v>0.1262704880505449</v>
+        <v>0.09962809326276646</v>
       </c>
       <c r="N183" s="14" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>579</v>
       </c>
       <c r="P183" s="16" t="n">
-        <v>0.06034245948173253</v>
+        <v>0.03525961951079965</v>
       </c>
       <c r="Q183" s="21" t="inlineStr">
         <is>
@@ -15141,13 +15141,13 @@
         </is>
       </c>
       <c r="D184" s="4" t="n">
-        <v>48.6</v>
+        <v>50.37</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>-0.045</v>
+        <v>-0.0102</v>
       </c>
       <c r="F184" s="5" t="n">
-        <v>-0.2231</v>
+        <v>-0.1949</v>
       </c>
       <c r="G184" s="7" t="n">
         <v>46321</v>
@@ -15202,13 +15202,13 @@
         </is>
       </c>
       <c r="D185" s="15" t="n">
-        <v>197.49</v>
+        <v>199.52</v>
       </c>
       <c r="E185" s="16" t="n">
-        <v>0.0592</v>
+        <v>0.0701</v>
       </c>
       <c r="F185" s="16" t="n">
-        <v>0.1662</v>
+        <v>0.1782</v>
       </c>
       <c r="G185" s="18" t="n">
         <v>46329</v>
@@ -15237,7 +15237,7 @@
         <v>200</v>
       </c>
       <c r="M185" s="16" t="n">
-        <v>0.01270950427869761</v>
+        <v>0.002405773857257367</v>
       </c>
       <c r="N185" s="14" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>200</v>
       </c>
       <c r="P185" s="16" t="n">
-        <v>0.01270950427869761</v>
+        <v>0.002405773857257367</v>
       </c>
       <c r="Q185" s="21" t="inlineStr">
         <is>
@@ -15293,13 +15293,13 @@
         </is>
       </c>
       <c r="D186" s="4" t="n">
-        <v>78.95999999999999</v>
-      </c>
-      <c r="E186" s="6" t="n">
-        <v>0.012</v>
+        <v>77.8</v>
+      </c>
+      <c r="E186" s="5" t="n">
+        <v>-0.0028</v>
       </c>
       <c r="F186" s="6" t="n">
-        <v>0.0492</v>
+        <v>0.0338</v>
       </c>
       <c r="G186" s="7" t="n">
         <v>46323</v>
@@ -15331,7 +15331,7 @@
         <v>180</v>
       </c>
       <c r="P186" s="6" t="n">
-        <v>1.279635258358663</v>
+        <v>1.313624678663239</v>
       </c>
       <c r="Q186" s="10" t="inlineStr">
         <is>
@@ -15384,13 +15384,13 @@
         </is>
       </c>
       <c r="D187" s="15" t="n">
-        <v>26.64</v>
+        <v>28.17</v>
       </c>
       <c r="E187" s="17" t="n">
-        <v>-0.0563</v>
-      </c>
-      <c r="F187" s="17" t="n">
-        <v>-0.0434</v>
+        <v>-0.0021</v>
+      </c>
+      <c r="F187" s="16" t="n">
+        <v>0.0115</v>
       </c>
       <c r="G187" s="18" t="n">
         <v>46303</v>
@@ -15445,13 +15445,13 @@
         </is>
       </c>
       <c r="D188" s="4" t="n">
-        <v>265.8</v>
+        <v>275.45</v>
       </c>
       <c r="E188" s="6" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="F188" s="5" t="n">
-        <v>-0.0141</v>
+        <v>0.1047</v>
+      </c>
+      <c r="F188" s="6" t="n">
+        <v>0.0217</v>
       </c>
       <c r="G188" s="7" t="n">
         <v>46330</v>
@@ -15506,13 +15506,13 @@
         </is>
       </c>
       <c r="D189" s="15" t="n">
-        <v>1641.76</v>
+        <v>1679.1</v>
       </c>
       <c r="E189" s="17" t="n">
-        <v>-0.06280000000000001</v>
+        <v>-0.0415</v>
       </c>
       <c r="F189" s="17" t="n">
-        <v>-0.0559</v>
+        <v>-0.0345</v>
       </c>
       <c r="G189" s="18" t="n">
         <v>46309</v>
@@ -15585,13 +15585,13 @@
         </is>
       </c>
       <c r="D190" s="4" t="n">
-        <v>40.29</v>
+        <v>41.6</v>
       </c>
       <c r="E190" s="6" t="n">
-        <v>0.1298</v>
+        <v>0.1667</v>
       </c>
       <c r="F190" s="6" t="n">
-        <v>0.0919</v>
+        <v>0.1275</v>
       </c>
       <c r="G190" s="7" t="n">
         <v>46324</v>
@@ -15646,13 +15646,13 @@
         </is>
       </c>
       <c r="D191" s="15" t="n">
-        <v>358.75</v>
+        <v>357.42</v>
       </c>
       <c r="E191" s="17" t="n">
-        <v>-0.0103</v>
+        <v>-0.0139</v>
       </c>
       <c r="F191" s="17" t="n">
-        <v>-0.0513</v>
+        <v>-0.0548</v>
       </c>
       <c r="G191" s="18" t="n"/>
       <c r="H191" s="23" t="inlineStr">
@@ -15671,7 +15671,7 @@
         <v>545</v>
       </c>
       <c r="M191" s="16" t="n">
-        <v>0.519163763066202</v>
+        <v>0.5248167422080465</v>
       </c>
       <c r="N191" s="14" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>582</v>
       </c>
       <c r="P191" s="16" t="n">
-        <v>0.6222996515679442</v>
+        <v>0.6283364109451065</v>
       </c>
       <c r="Q191" s="21" t="inlineStr">
         <is>
@@ -15735,13 +15735,13 @@
         </is>
       </c>
       <c r="D192" s="4" t="n">
-        <v>144.79</v>
+        <v>149.34</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>-0.039</v>
-      </c>
-      <c r="F192" s="5" t="n">
-        <v>-0.0156</v>
+        <v>-0.008800000000000001</v>
+      </c>
+      <c r="F192" s="6" t="n">
+        <v>0.0153</v>
       </c>
       <c r="G192" s="7" t="n">
         <v>46335</v>
@@ -15796,13 +15796,13 @@
         </is>
       </c>
       <c r="D193" s="15" t="n">
-        <v>282.5</v>
+        <v>282.88</v>
       </c>
       <c r="E193" s="17" t="n">
-        <v>-0.1031</v>
+        <v>-0.1019</v>
       </c>
       <c r="F193" s="17" t="n">
-        <v>-0.1438</v>
+        <v>-0.1426</v>
       </c>
       <c r="G193" s="18" t="n">
         <v>46321</v>
@@ -15831,7 +15831,7 @@
         <v>425</v>
       </c>
       <c r="M193" s="16" t="n">
-        <v>0.504424778761062</v>
+        <v>0.5024038461538461</v>
       </c>
       <c r="N193" s="14" t="inlineStr"/>
       <c r="O193" s="20" t="n"/>
@@ -15875,13 +15875,13 @@
         </is>
       </c>
       <c r="D194" s="4" t="n">
-        <v>132.59</v>
+        <v>132.78</v>
       </c>
       <c r="E194" s="6" t="n">
-        <v>0.0018</v>
+        <v>0.0032</v>
       </c>
       <c r="F194" s="5" t="n">
-        <v>-0.0232</v>
+        <v>-0.0217</v>
       </c>
       <c r="G194" s="7" t="n">
         <v>46322</v>
@@ -15936,13 +15936,13 @@
         </is>
       </c>
       <c r="D195" s="15" t="n">
-        <v>344.56</v>
+        <v>347.97</v>
       </c>
       <c r="E195" s="17" t="n">
-        <v>-0.1375</v>
+        <v>-0.1289</v>
       </c>
       <c r="F195" s="17" t="n">
-        <v>-0.09029999999999999</v>
+        <v>-0.08130000000000001</v>
       </c>
       <c r="G195" s="18" t="n"/>
       <c r="H195" s="23" t="inlineStr">
@@ -15987,13 +15987,13 @@
         </is>
       </c>
       <c r="D196" s="4" t="n">
-        <v>11.55</v>
+        <v>11.62</v>
       </c>
       <c r="E196" s="6" t="n">
-        <v>0.0276</v>
+        <v>0.0338</v>
       </c>
       <c r="F196" s="5" t="n">
-        <v>-0.2485</v>
+        <v>-0.244</v>
       </c>
       <c r="G196" s="7" t="n">
         <v>46337</v>
@@ -16048,13 +16048,13 @@
         </is>
       </c>
       <c r="D197" s="15" t="n">
-        <v>331.14</v>
+        <v>333.45</v>
       </c>
       <c r="E197" s="16" t="n">
-        <v>0.09880000000000001</v>
+        <v>0.1065</v>
       </c>
       <c r="F197" s="16" t="n">
-        <v>0.0774</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="G197" s="18" t="n">
         <v>46321</v>
@@ -16109,13 +16109,13 @@
         </is>
       </c>
       <c r="D198" s="4" t="n">
-        <v>307.37</v>
+        <v>317.27</v>
       </c>
       <c r="E198" s="6" t="n">
-        <v>0.0692</v>
+        <v>0.1037</v>
       </c>
       <c r="F198" s="6" t="n">
-        <v>0.077</v>
+        <v>0.1117</v>
       </c>
       <c r="G198" s="7" t="n">
         <v>46330</v>
@@ -16170,13 +16170,13 @@
         </is>
       </c>
       <c r="D199" s="15" t="n">
-        <v>56.22</v>
+        <v>57.82</v>
       </c>
       <c r="E199" s="16" t="n">
-        <v>0.0187</v>
+        <v>0.04769999999999999</v>
       </c>
       <c r="F199" s="16" t="n">
-        <v>0.0906</v>
+        <v>0.1216</v>
       </c>
       <c r="G199" s="18" t="n">
         <v>46330</v>
@@ -16231,13 +16231,13 @@
         </is>
       </c>
       <c r="D200" s="4" t="n">
-        <v>17.42</v>
+        <v>17.98</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>-0.0697</v>
+        <v>-0.0398</v>
       </c>
       <c r="F200" s="5" t="n">
-        <v>-0.2225</v>
+        <v>-0.1975</v>
       </c>
       <c r="G200" s="7" t="n">
         <v>46318</v>
@@ -16292,13 +16292,13 @@
         </is>
       </c>
       <c r="D201" s="15" t="n">
-        <v>172.93</v>
+        <v>175.73</v>
       </c>
       <c r="E201" s="17" t="n">
-        <v>-0.2636</v>
+        <v>-0.2516</v>
       </c>
       <c r="F201" s="17" t="n">
-        <v>-0.1846</v>
+        <v>-0.1714</v>
       </c>
       <c r="G201" s="18" t="n"/>
       <c r="H201" s="23" t="inlineStr">
@@ -16343,13 +16343,13 @@
         </is>
       </c>
       <c r="D202" s="4" t="n">
-        <v>239.27</v>
+        <v>237.42</v>
       </c>
       <c r="E202" s="6" t="n">
-        <v>0.161</v>
+        <v>0.152</v>
       </c>
       <c r="F202" s="6" t="n">
-        <v>0.3768</v>
+        <v>0.3661</v>
       </c>
       <c r="G202" s="7" t="n"/>
       <c r="H202" s="12" t="inlineStr">
@@ -16368,7 +16368,7 @@
         <v>200</v>
       </c>
       <c r="M202" s="5" t="n">
-        <v>-0.1641242111422243</v>
+        <v>-0.1576109847527588</v>
       </c>
       <c r="N202" s="3" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>250</v>
       </c>
       <c r="P202" s="6" t="n">
-        <v>0.04484473607221962</v>
+        <v>0.05298626905905152</v>
       </c>
       <c r="Q202" s="10" t="inlineStr">
         <is>
@@ -16424,13 +16424,13 @@
         </is>
       </c>
       <c r="D203" s="15" t="n">
-        <v>236.64</v>
+        <v>237.51</v>
       </c>
       <c r="E203" s="16" t="n">
-        <v>0.1736</v>
+        <v>0.1779</v>
       </c>
       <c r="F203" s="16" t="n">
-        <v>0.1922</v>
+        <v>0.1966</v>
       </c>
       <c r="G203" s="18" t="n"/>
       <c r="H203" s="23" t="inlineStr">
@@ -16449,7 +16449,7 @@
         <v>181.25</v>
       </c>
       <c r="M203" s="17" t="n">
-        <v>-0.2340686274509803</v>
+        <v>-0.2368742368742368</v>
       </c>
       <c r="N203" s="14" t="inlineStr">
         <is>
@@ -16460,7 +16460,7 @@
         <v>177.5</v>
       </c>
       <c r="P203" s="17" t="n">
-        <v>-0.2499154834347532</v>
+        <v>-0.252663045766494</v>
       </c>
       <c r="Q203" s="21" t="inlineStr">
         <is>
@@ -16501,13 +16501,13 @@
         </is>
       </c>
       <c r="D204" s="4" t="n">
-        <v>80.48999999999999</v>
+        <v>81.41</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>-0.1142</v>
+        <v>-0.1041</v>
       </c>
       <c r="F204" s="6" t="n">
-        <v>0.1017</v>
+        <v>0.1143</v>
       </c>
       <c r="G204" s="7" t="n">
         <v>46335</v>
@@ -16562,13 +16562,13 @@
         </is>
       </c>
       <c r="D205" s="15" t="n">
-        <v>108.85</v>
+        <v>109.53</v>
       </c>
       <c r="E205" s="17" t="n">
-        <v>-0.0154</v>
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F205" s="17" t="n">
-        <v>-0.0167</v>
+        <v>-0.0106</v>
       </c>
       <c r="G205" s="18" t="n">
         <v>46337</v>
@@ -16597,7 +16597,7 @@
         <v>130</v>
       </c>
       <c r="M205" s="16" t="n">
-        <v>0.1943040881947635</v>
+        <v>0.1868894366840135</v>
       </c>
       <c r="N205" s="14" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>150</v>
       </c>
       <c r="P205" s="16" t="n">
-        <v>0.3780431786862656</v>
+        <v>0.3694878115584771</v>
       </c>
       <c r="Q205" s="21" t="inlineStr">
         <is>
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="D206" s="4" t="n">
-        <v>229.87</v>
+        <v>229.95</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>-0.0156</v>
+        <v>-0.0153</v>
       </c>
       <c r="F206" s="5" t="n">
-        <v>-0.1266</v>
+        <v>-0.1263</v>
       </c>
       <c r="G206" s="7" t="n">
         <v>46331</v>
@@ -16726,13 +16726,13 @@
         </is>
       </c>
       <c r="D207" s="15" t="n">
-        <v>581.9299999999999</v>
+        <v>571.0700000000001</v>
       </c>
       <c r="E207" s="16" t="n">
-        <v>0.33</v>
+        <v>0.3051</v>
       </c>
       <c r="F207" s="16" t="n">
-        <v>0.5239</v>
+        <v>0.4954</v>
       </c>
       <c r="G207" s="18" t="n"/>
       <c r="H207" s="23" t="inlineStr">
@@ -16777,13 +16777,13 @@
         </is>
       </c>
       <c r="D208" s="4" t="n">
-        <v>69.29000000000001</v>
+        <v>69.11</v>
       </c>
       <c r="E208" s="6" t="n">
-        <v>0.1156</v>
+        <v>0.1126</v>
       </c>
       <c r="F208" s="6" t="n">
-        <v>0.3249</v>
+        <v>0.3213</v>
       </c>
       <c r="G208" s="7" t="n"/>
       <c r="H208" s="12" t="inlineStr">
@@ -16828,13 +16828,13 @@
         </is>
       </c>
       <c r="D209" s="15" t="n">
-        <v>55.05</v>
+        <v>55.2</v>
       </c>
       <c r="E209" s="16" t="n">
-        <v>0.1099</v>
+        <v>0.1129</v>
       </c>
       <c r="F209" s="16" t="n">
-        <v>0.2313</v>
+        <v>0.2346</v>
       </c>
       <c r="G209" s="18" t="n">
         <v>46330</v>
@@ -16889,13 +16889,13 @@
         </is>
       </c>
       <c r="D210" s="4" t="n">
-        <v>386.48</v>
+        <v>389.08</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>-0.1498</v>
+        <v>-0.144</v>
       </c>
       <c r="F210" s="5" t="n">
-        <v>-0.2181</v>
+        <v>-0.2128</v>
       </c>
       <c r="G210" s="7" t="n">
         <v>46328</v>
@@ -16950,13 +16950,13 @@
         </is>
       </c>
       <c r="D211" s="15" t="n">
-        <v>115.64</v>
+        <v>118.51</v>
       </c>
       <c r="E211" s="16" t="n">
-        <v>0.006</v>
+        <v>0.031</v>
       </c>
       <c r="F211" s="16" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.1254</v>
       </c>
       <c r="G211" s="18" t="n">
         <v>46330</v>
@@ -17011,13 +17011,13 @@
         </is>
       </c>
       <c r="D212" s="4" t="n">
-        <v>166.34</v>
+        <v>169.78</v>
       </c>
       <c r="E212" s="6" t="n">
-        <v>0.0883</v>
+        <v>0.1108</v>
       </c>
       <c r="F212" s="6" t="n">
-        <v>0.0373</v>
+        <v>0.0587</v>
       </c>
       <c r="G212" s="7" t="n">
         <v>46330</v>
@@ -17072,13 +17072,13 @@
         </is>
       </c>
       <c r="D213" s="15" t="n">
-        <v>46.54</v>
+        <v>47.84</v>
       </c>
       <c r="E213" s="17" t="n">
-        <v>-0.04190000000000001</v>
+        <v>-0.0152</v>
       </c>
       <c r="F213" s="17" t="n">
-        <v>-0.1807</v>
+        <v>-0.1579</v>
       </c>
       <c r="G213" s="18" t="n">
         <v>46337</v>
@@ -17133,13 +17133,13 @@
         </is>
       </c>
       <c r="D214" s="4" t="n">
-        <v>150.79</v>
+        <v>150.12</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.0153</v>
       </c>
       <c r="F214" s="5" t="n">
-        <v>-0.0151</v>
+        <v>-0.0195</v>
       </c>
       <c r="G214" s="7" t="n">
         <v>46322</v>
@@ -17194,13 +17194,13 @@
         </is>
       </c>
       <c r="D215" s="15" t="n">
-        <v>49.5</v>
+        <v>49.26</v>
       </c>
       <c r="E215" s="16" t="n">
-        <v>0.162</v>
+        <v>0.1563</v>
       </c>
       <c r="F215" s="16" t="n">
-        <v>0.4529</v>
+        <v>0.4458</v>
       </c>
       <c r="G215" s="18" t="n"/>
       <c r="H215" s="23" t="inlineStr">
@@ -17245,13 +17245,13 @@
         </is>
       </c>
       <c r="D216" s="4" t="n">
-        <v>142.4</v>
+        <v>144.26</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>-0.214</v>
+        <v>-0.2038</v>
       </c>
       <c r="F216" s="5" t="n">
-        <v>-0.0455</v>
+        <v>-0.033</v>
       </c>
       <c r="G216" s="7" t="n"/>
       <c r="H216" s="12" t="inlineStr">
@@ -17270,7 +17270,7 @@
         <v>190</v>
       </c>
       <c r="M216" s="6" t="n">
-        <v>0.3342696629213482</v>
+        <v>0.3170664078746708</v>
       </c>
       <c r="N216" s="3" t="inlineStr"/>
       <c r="O216" s="9" t="n"/>
@@ -17314,13 +17314,13 @@
         </is>
       </c>
       <c r="D217" s="15" t="n">
-        <v>60.53</v>
+        <v>60.65</v>
       </c>
       <c r="E217" s="16" t="n">
-        <v>0.1392</v>
+        <v>0.1416</v>
       </c>
       <c r="F217" s="16" t="n">
-        <v>0.3583</v>
+        <v>0.3612</v>
       </c>
       <c r="G217" s="18" t="n"/>
       <c r="H217" s="23" t="inlineStr">
@@ -17339,7 +17339,7 @@
         <v>67</v>
       </c>
       <c r="M217" s="16" t="n">
-        <v>0.106889145878077</v>
+        <v>0.1046990931574609</v>
       </c>
       <c r="N217" s="14" t="inlineStr">
         <is>
@@ -17350,7 +17350,7 @@
         <v>70</v>
       </c>
       <c r="P217" s="16" t="n">
-        <v>0.1564513464397819</v>
+        <v>0.1541632316570487</v>
       </c>
       <c r="Q217" s="21" t="inlineStr">
         <is>
@@ -17391,13 +17391,13 @@
         </is>
       </c>
       <c r="D218" s="4" t="n">
-        <v>221.52</v>
+        <v>216.27</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>-0.0833</v>
+        <v>-0.105</v>
       </c>
       <c r="F218" s="5" t="n">
-        <v>-0.04190000000000001</v>
+        <v>-0.0646</v>
       </c>
       <c r="G218" s="7" t="n">
         <v>46330</v>
@@ -17452,13 +17452,13 @@
         </is>
       </c>
       <c r="D219" s="15" t="n">
-        <v>230.37</v>
+        <v>230.16</v>
       </c>
       <c r="E219" s="17" t="n">
-        <v>-0.0286</v>
+        <v>-0.0295</v>
       </c>
       <c r="F219" s="16" t="n">
-        <v>0.0815</v>
+        <v>0.0806</v>
       </c>
       <c r="G219" s="18" t="n">
         <v>46316</v>
@@ -17494,7 +17494,7 @@
         <v>250</v>
       </c>
       <c r="P219" s="16" t="n">
-        <v>0.08521074792724745</v>
+        <v>0.08620090371915191</v>
       </c>
       <c r="Q219" s="21" t="inlineStr">
         <is>
@@ -17531,13 +17531,13 @@
         </is>
       </c>
       <c r="D220" s="4" t="n">
-        <v>12.83</v>
+        <v>13.27</v>
       </c>
       <c r="E220" s="6" t="n">
-        <v>0.0264</v>
+        <v>0.0612</v>
       </c>
       <c r="F220" s="6" t="n">
-        <v>0.4177</v>
+        <v>0.4657</v>
       </c>
       <c r="G220" s="7" t="n">
         <v>46337</v>
@@ -17592,13 +17592,13 @@
         </is>
       </c>
       <c r="D221" s="15" t="n">
-        <v>108.04</v>
+        <v>108.56</v>
       </c>
       <c r="E221" s="16" t="n">
-        <v>0.1642</v>
+        <v>0.1698</v>
       </c>
       <c r="F221" s="16" t="n">
-        <v>0.1131</v>
+        <v>0.1185</v>
       </c>
       <c r="G221" s="18" t="n">
         <v>46317</v>
@@ -17653,13 +17653,13 @@
         </is>
       </c>
       <c r="D222" s="4" t="n">
-        <v>307.36</v>
+        <v>303.1</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>-0.152</v>
+        <v>-0.1638</v>
       </c>
       <c r="F222" s="6" t="n">
-        <v>0.0461</v>
+        <v>0.0316</v>
       </c>
       <c r="G222" s="7" t="n"/>
       <c r="H222" s="12" t="inlineStr">
@@ -17704,13 +17704,13 @@
         </is>
       </c>
       <c r="D223" s="15" t="n">
-        <v>38.12</v>
+        <v>39.15</v>
       </c>
       <c r="E223" s="17" t="n">
-        <v>-0.1209</v>
+        <v>-0.09699999999999999</v>
       </c>
       <c r="F223" s="16" t="n">
-        <v>0.1133</v>
+        <v>0.1435</v>
       </c>
       <c r="G223" s="18" t="n">
         <v>46330</v>
@@ -17765,13 +17765,13 @@
         </is>
       </c>
       <c r="D224" s="4" t="n">
-        <v>44.26</v>
+        <v>46.72</v>
       </c>
       <c r="E224" s="6" t="n">
-        <v>0.0331</v>
+        <v>0.09050000000000001</v>
       </c>
       <c r="F224" s="6" t="n">
-        <v>0.101</v>
+        <v>0.1621</v>
       </c>
       <c r="G224" s="7" t="n">
         <v>46331</v>
@@ -17826,13 +17826,13 @@
         </is>
       </c>
       <c r="D225" s="15" t="n">
-        <v>298.51</v>
+        <v>299.59</v>
       </c>
       <c r="E225" s="17" t="n">
-        <v>-0.07519999999999999</v>
+        <v>-0.0718</v>
       </c>
       <c r="F225" s="17" t="n">
-        <v>-0.0242</v>
+        <v>-0.0207</v>
       </c>
       <c r="G225" s="18" t="n">
         <v>46289</v>
@@ -17891,13 +17891,13 @@
         </is>
       </c>
       <c r="D226" s="4" t="n">
-        <v>332.93</v>
+        <v>335.51</v>
       </c>
       <c r="E226" s="6" t="n">
-        <v>0.04219999999999999</v>
+        <v>0.0503</v>
       </c>
       <c r="F226" s="6" t="n">
-        <v>0.05980000000000001</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="G226" s="7" t="n"/>
       <c r="H226" s="12" t="inlineStr">
@@ -17916,7 +17916,7 @@
         <v>390</v>
       </c>
       <c r="M226" s="6" t="n">
-        <v>0.1714174150722374</v>
+        <v>0.1624094661858067</v>
       </c>
       <c r="N226" s="3" t="inlineStr"/>
       <c r="O226" s="9" t="n"/>
@@ -17972,13 +17972,13 @@
         </is>
       </c>
       <c r="D227" s="15" t="n">
-        <v>172.21</v>
+        <v>176.99</v>
       </c>
       <c r="E227" s="17" t="n">
-        <v>-0.08039999999999999</v>
+        <v>-0.0549</v>
       </c>
       <c r="F227" s="17" t="n">
-        <v>-0.1705</v>
+        <v>-0.1474</v>
       </c>
       <c r="G227" s="18" t="n">
         <v>46330</v>
@@ -18007,7 +18007,7 @@
         <v>305</v>
       </c>
       <c r="M227" s="16" t="n">
-        <v>0.7710934324371406</v>
+        <v>0.7232612011978077</v>
       </c>
       <c r="N227" s="14" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>185</v>
       </c>
       <c r="P227" s="16" t="n">
-        <v>0.07426978688810168</v>
+        <v>0.04525679416916205</v>
       </c>
       <c r="Q227" s="21" t="inlineStr">
         <is>
@@ -18059,13 +18059,13 @@
         </is>
       </c>
       <c r="D228" s="4" t="n">
-        <v>81.69</v>
+        <v>83.18000000000001</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>-0.0533</v>
+        <v>-0.036</v>
       </c>
       <c r="F228" s="5" t="n">
-        <v>-0.1836</v>
+        <v>-0.1687</v>
       </c>
       <c r="G228" s="7" t="n"/>
       <c r="H228" s="12" t="inlineStr">
@@ -18110,13 +18110,13 @@
         </is>
       </c>
       <c r="D229" s="15" t="n">
-        <v>906.99</v>
+        <v>931.67</v>
       </c>
       <c r="E229" s="16" t="n">
-        <v>0.0959</v>
+        <v>0.1257</v>
       </c>
       <c r="F229" s="16" t="n">
-        <v>0.1848</v>
+        <v>0.217</v>
       </c>
       <c r="G229" s="18" t="n">
         <v>46329</v>
@@ -18171,13 +18171,13 @@
         </is>
       </c>
       <c r="D230" s="4" t="n">
-        <v>102.62</v>
+        <v>101.23</v>
       </c>
       <c r="E230" s="6" t="n">
-        <v>0.0214</v>
-      </c>
-      <c r="F230" s="6" t="n">
-        <v>0.0083</v>
+        <v>0.0076</v>
+      </c>
+      <c r="F230" s="5" t="n">
+        <v>-0.0054</v>
       </c>
       <c r="G230" s="7" t="n">
         <v>46322</v>
@@ -18232,13 +18232,13 @@
         </is>
       </c>
       <c r="D231" s="15" t="n">
-        <v>280.8</v>
+        <v>288.05</v>
       </c>
       <c r="E231" s="17" t="n">
-        <v>-0.0858</v>
+        <v>-0.0622</v>
       </c>
       <c r="F231" s="17" t="n">
-        <v>-0.08460000000000001</v>
+        <v>-0.061</v>
       </c>
       <c r="G231" s="18" t="n">
         <v>46323</v>
@@ -18267,7 +18267,7 @@
         <v>450</v>
       </c>
       <c r="M231" s="16" t="n">
-        <v>0.6025641025641025</v>
+        <v>0.562228779725742</v>
       </c>
       <c r="N231" s="14" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>355</v>
       </c>
       <c r="P231" s="16" t="n">
-        <v>0.2642450142450142</v>
+        <v>0.2324249262280854</v>
       </c>
       <c r="Q231" s="21" t="inlineStr">
         <is>
@@ -18323,13 +18323,13 @@
         </is>
       </c>
       <c r="D232" s="4" t="n">
-        <v>71.76000000000001</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.0495</v>
       </c>
       <c r="F232" s="5" t="n">
-        <v>-0.1087</v>
+        <v>-0.09</v>
       </c>
       <c r="G232" s="7" t="n">
         <v>46331</v>
@@ -18384,13 +18384,13 @@
         </is>
       </c>
       <c r="D233" s="15" t="n">
-        <v>384.01</v>
+        <v>383.3</v>
       </c>
       <c r="E233" s="17" t="n">
-        <v>-0.1283</v>
+        <v>-0.1299</v>
       </c>
       <c r="F233" s="16" t="n">
-        <v>0.1876</v>
+        <v>0.1854</v>
       </c>
       <c r="G233" s="18" t="n"/>
       <c r="H233" s="23" t="inlineStr">
@@ -18435,13 +18435,13 @@
         </is>
       </c>
       <c r="D234" s="4" t="n">
-        <v>245.34</v>
+        <v>252.16</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>-0.1288</v>
+        <v>-0.1045</v>
       </c>
       <c r="F234" s="5" t="n">
-        <v>-0.2434</v>
+        <v>-0.2224</v>
       </c>
       <c r="G234" s="7" t="n">
         <v>46330</v>
@@ -18496,13 +18496,13 @@
         </is>
       </c>
       <c r="D235" s="15" t="n">
-        <v>1193.63</v>
+        <v>1220.59</v>
       </c>
       <c r="E235" s="17" t="n">
-        <v>-0.0819</v>
+        <v>-0.0612</v>
       </c>
       <c r="F235" s="17" t="n">
-        <v>-0.1017</v>
+        <v>-0.0814</v>
       </c>
       <c r="G235" s="18" t="n">
         <v>46324</v>
@@ -18557,13 +18557,13 @@
         </is>
       </c>
       <c r="D236" s="4" t="n">
-        <v>239.62</v>
+        <v>244.21</v>
       </c>
       <c r="E236" s="6" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.0293</v>
       </c>
       <c r="F236" s="6" t="n">
-        <v>0.2292</v>
+        <v>0.2528</v>
       </c>
       <c r="G236" s="7" t="n"/>
       <c r="H236" s="12" t="inlineStr">
@@ -18581,8 +18581,8 @@
       <c r="L236" s="9" t="n">
         <v>240</v>
       </c>
-      <c r="M236" s="6" t="n">
-        <v>0.0015858442534012</v>
+      <c r="M236" s="5" t="n">
+        <v>-0.01723926129151144</v>
       </c>
       <c r="N236" s="3" t="inlineStr">
         <is>
@@ -18593,7 +18593,7 @@
         <v>251</v>
       </c>
       <c r="P236" s="6" t="n">
-        <v>0.04749186211501542</v>
+        <v>0.02780393923262762</v>
       </c>
       <c r="Q236" s="10" t="inlineStr">
         <is>
@@ -18634,13 +18634,13 @@
         </is>
       </c>
       <c r="D237" s="15" t="n">
-        <v>492.51</v>
+        <v>493.6</v>
       </c>
       <c r="E237" s="16" t="n">
-        <v>0.0169</v>
+        <v>0.0192</v>
       </c>
       <c r="F237" s="16" t="n">
-        <v>0.2243</v>
+        <v>0.227</v>
       </c>
       <c r="G237" s="18" t="n">
         <v>46330</v>
@@ -18669,7 +18669,7 @@
         <v>625</v>
       </c>
       <c r="M237" s="16" t="n">
-        <v>0.2690097662991615</v>
+        <v>0.2662074554294975</v>
       </c>
       <c r="N237" s="14" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>525</v>
       </c>
       <c r="P237" s="16" t="n">
-        <v>0.06596820369129562</v>
+        <v>0.06361426256077791</v>
       </c>
       <c r="Q237" s="21" t="inlineStr">
         <is>
@@ -18733,13 +18733,13 @@
         </is>
       </c>
       <c r="D238" s="4" t="n">
-        <v>457.98</v>
+        <v>458.9</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>-0.0475</v>
+        <v>-0.04559999999999999</v>
       </c>
       <c r="F238" s="6" t="n">
-        <v>0.1159</v>
+        <v>0.1181</v>
       </c>
       <c r="G238" s="7" t="n">
         <v>46324</v>
@@ -18771,7 +18771,7 @@
         <v>525</v>
       </c>
       <c r="P238" s="6" t="n">
-        <v>0.1463382680466395</v>
+        <v>0.1440400958814557</v>
       </c>
       <c r="Q238" s="10" t="inlineStr">
         <is>
@@ -18820,13 +18820,13 @@
         </is>
       </c>
       <c r="D239" s="15" t="n">
-        <v>145.79</v>
+        <v>153.96</v>
       </c>
       <c r="E239" s="16" t="n">
-        <v>0.3985</v>
+        <v>0.4768</v>
       </c>
       <c r="F239" s="16" t="n">
-        <v>0.4904</v>
+        <v>0.5739</v>
       </c>
       <c r="G239" s="18" t="n">
         <v>46324</v>
@@ -18881,13 +18881,13 @@
         </is>
       </c>
       <c r="D240" s="4" t="n">
-        <v>274.27</v>
+        <v>276.15</v>
       </c>
       <c r="E240" s="6" t="n">
-        <v>0.0159</v>
+        <v>0.0229</v>
       </c>
       <c r="F240" s="6" t="n">
-        <v>0.0166</v>
+        <v>0.0235</v>
       </c>
       <c r="G240" s="7" t="n">
         <v>46331</v>
@@ -18942,13 +18942,13 @@
         </is>
       </c>
       <c r="D241" s="15" t="n">
-        <v>994.59</v>
+        <v>1015.29</v>
       </c>
       <c r="E241" s="16" t="n">
-        <v>0.0613</v>
+        <v>0.0834</v>
       </c>
       <c r="F241" s="16" t="n">
-        <v>0.1492</v>
+        <v>0.1731</v>
       </c>
       <c r="G241" s="18" t="n">
         <v>46295</v>
@@ -18977,7 +18977,7 @@
         <v>1525</v>
       </c>
       <c r="M241" s="16" t="n">
-        <v>0.5332951266350958</v>
+        <v>0.5020339016438653</v>
       </c>
       <c r="N241" s="14" t="inlineStr">
         <is>
@@ -19025,13 +19025,13 @@
         </is>
       </c>
       <c r="D242" s="4" t="n">
-        <v>214.59</v>
+        <v>223.52</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>-0.0416</v>
+        <v>-0.0017</v>
       </c>
       <c r="F242" s="6" t="n">
-        <v>0.1751</v>
+        <v>0.224</v>
       </c>
       <c r="G242" s="7" t="n">
         <v>46336</v>
@@ -19086,13 +19086,13 @@
         </is>
       </c>
       <c r="D243" s="15" t="n">
-        <v>314.63</v>
+        <v>323.32</v>
       </c>
       <c r="E243" s="16" t="n">
-        <v>0.0779</v>
+        <v>0.1077</v>
       </c>
       <c r="F243" s="16" t="n">
-        <v>0.1549</v>
+        <v>0.1868</v>
       </c>
       <c r="G243" s="18" t="n">
         <v>46324</v>
@@ -19147,13 +19147,13 @@
         </is>
       </c>
       <c r="D244" s="4" t="n">
-        <v>136.43</v>
+        <v>135.26</v>
       </c>
       <c r="E244" s="6" t="n">
-        <v>0.0726</v>
+        <v>0.0634</v>
       </c>
       <c r="F244" s="6" t="n">
-        <v>0.3031</v>
+        <v>0.2919</v>
       </c>
       <c r="G244" s="7" t="n">
         <v>46323</v>
@@ -19182,7 +19182,7 @@
         <v>160</v>
       </c>
       <c r="M244" s="6" t="n">
-        <v>0.1727625888734149</v>
+        <v>0.1829069939376017</v>
       </c>
       <c r="N244" s="3" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>150</v>
       </c>
       <c r="P244" s="6" t="n">
-        <v>0.09946492706882645</v>
+        <v>0.1089753068165016</v>
       </c>
       <c r="Q244" s="10" t="inlineStr">
         <is>
@@ -19238,13 +19238,13 @@
         </is>
       </c>
       <c r="D245" s="15" t="n">
-        <v>68.91</v>
+        <v>69.84</v>
       </c>
       <c r="E245" s="16" t="n">
-        <v>0.0533</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="F245" s="16" t="n">
-        <v>0.2504</v>
+        <v>0.2673</v>
       </c>
       <c r="G245" s="18" t="n"/>
       <c r="H245" s="23" t="inlineStr">
@@ -19289,13 +19289,13 @@
         </is>
       </c>
       <c r="D246" s="4" t="n">
-        <v>219.27</v>
+        <v>221.88</v>
       </c>
       <c r="E246" s="6" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0199</v>
       </c>
       <c r="F246" s="6" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.0915</v>
       </c>
       <c r="G246" s="7" t="n"/>
       <c r="H246" s="12" t="inlineStr">
@@ -19314,7 +19314,7 @@
         <v>315</v>
       </c>
       <c r="M246" s="6" t="n">
-        <v>0.4365850321521411</v>
+        <v>0.4196863169280692</v>
       </c>
       <c r="N246" s="3" t="inlineStr">
         <is>
@@ -19325,7 +19325,7 @@
         <v>413</v>
       </c>
       <c r="P246" s="6" t="n">
-        <v>0.8835225977105851</v>
+        <v>0.861366504416802</v>
       </c>
       <c r="Q246" s="10" t="inlineStr">
         <is>
@@ -19374,13 +19374,13 @@
         </is>
       </c>
       <c r="D247" s="15" t="n">
-        <v>347.01</v>
+        <v>357.02</v>
       </c>
       <c r="E247" s="17" t="n">
-        <v>-0.09949999999999999</v>
+        <v>-0.0735</v>
       </c>
       <c r="F247" s="17" t="n">
-        <v>-0.1989</v>
+        <v>-0.1758</v>
       </c>
       <c r="G247" s="18" t="n">
         <v>46331</v>
@@ -19435,13 +19435,13 @@
         </is>
       </c>
       <c r="D248" s="4" t="n">
-        <v>226.7</v>
+        <v>228</v>
       </c>
       <c r="E248" s="6" t="n">
-        <v>0.003</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="F248" s="5" t="n">
-        <v>-0.1515</v>
+        <v>-0.1466</v>
       </c>
       <c r="G248" s="7" t="n">
         <v>46322</v>
@@ -19492,13 +19492,13 @@
         </is>
       </c>
       <c r="D249" s="15" t="n">
-        <v>10.96</v>
+        <v>10.81</v>
       </c>
       <c r="E249" s="16" t="n">
-        <v>0.0142</v>
+        <v>0.0001</v>
       </c>
       <c r="F249" s="17" t="n">
-        <v>-0.2986</v>
+        <v>-0.3083</v>
       </c>
       <c r="G249" s="18" t="n"/>
       <c r="H249" s="23" t="inlineStr">
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="D250" s="4" t="n">
-        <v>183.29</v>
+        <v>182.26</v>
       </c>
       <c r="E250" s="6" t="n">
-        <v>0.298</v>
+        <v>0.2907</v>
       </c>
       <c r="F250" s="6" t="n">
-        <v>0.235</v>
+        <v>0.2281</v>
       </c>
       <c r="G250" s="7" t="n"/>
       <c r="H250" s="12" t="inlineStr">
@@ -19568,7 +19568,7 @@
         <v>150</v>
       </c>
       <c r="M250" s="5" t="n">
-        <v>-0.1816247476676305</v>
+        <v>-0.176999890266652</v>
       </c>
       <c r="N250" s="3" t="inlineStr">
         <is>
@@ -19579,7 +19579,7 @@
         <v>130</v>
       </c>
       <c r="P250" s="5" t="n">
-        <v>-0.2907414479786131</v>
+        <v>-0.2867332382310984</v>
       </c>
       <c r="Q250" s="10" t="inlineStr">
         <is>
@@ -19620,13 +19620,13 @@
         </is>
       </c>
       <c r="D251" s="15" t="n">
-        <v>69.13</v>
+        <v>70.02</v>
       </c>
       <c r="E251" s="17" t="n">
-        <v>-0.0973</v>
+        <v>-0.0857</v>
       </c>
       <c r="F251" s="17" t="n">
-        <v>-0.2027</v>
+        <v>-0.1924</v>
       </c>
       <c r="G251" s="18" t="n">
         <v>46328</v>
@@ -19681,13 +19681,13 @@
         </is>
       </c>
       <c r="D252" s="4" t="n">
-        <v>257.5</v>
+        <v>264.88</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>-0.1402</v>
+        <v>-0.1156</v>
       </c>
       <c r="F252" s="5" t="n">
-        <v>-0.0755</v>
+        <v>-0.049</v>
       </c>
       <c r="G252" s="7" t="n">
         <v>46331</v>
@@ -19742,13 +19742,13 @@
         </is>
       </c>
       <c r="D253" s="15" t="n">
-        <v>145.95</v>
+        <v>147.8</v>
       </c>
       <c r="E253" s="16" t="n">
-        <v>0.0149</v>
+        <v>0.0277</v>
       </c>
       <c r="F253" s="16" t="n">
-        <v>0.2025</v>
+        <v>0.2177</v>
       </c>
       <c r="G253" s="18" t="n"/>
       <c r="H253" s="23" t="inlineStr">
@@ -19767,7 +19767,7 @@
         <v>280</v>
       </c>
       <c r="M253" s="16" t="n">
-        <v>0.918465227817746</v>
+        <v>0.8944519621109606</v>
       </c>
       <c r="N253" s="14" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>245</v>
       </c>
       <c r="P253" s="16" t="n">
-        <v>0.6786570743405277</v>
+        <v>0.6576454668470906</v>
       </c>
       <c r="Q253" s="21" t="inlineStr">
         <is>
@@ -19819,13 +19819,13 @@
         </is>
       </c>
       <c r="D254" s="4" t="n">
-        <v>358.62</v>
-      </c>
-      <c r="E254" s="5" t="n">
-        <v>-0.0032</v>
+        <v>363.47</v>
+      </c>
+      <c r="E254" s="6" t="n">
+        <v>0.0103</v>
       </c>
       <c r="F254" s="6" t="n">
-        <v>0.0286</v>
+        <v>0.0425</v>
       </c>
       <c r="G254" s="7" t="n"/>
       <c r="H254" s="12" t="inlineStr">
@@ -19844,7 +19844,7 @@
         <v>420</v>
       </c>
       <c r="M254" s="6" t="n">
-        <v>0.1711560983771122</v>
+        <v>0.1555286543593693</v>
       </c>
       <c r="N254" s="3" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>415</v>
       </c>
       <c r="P254" s="6" t="n">
-        <v>0.1572137638726228</v>
+        <v>0.1417723608550911</v>
       </c>
       <c r="Q254" s="10" t="inlineStr">
         <is>
@@ -19904,13 +19904,13 @@
         </is>
       </c>
       <c r="D255" s="15" t="n">
-        <v>13.38</v>
+        <v>13.39</v>
       </c>
       <c r="E255" s="17" t="n">
-        <v>-0.1524</v>
+        <v>-0.1515</v>
       </c>
       <c r="F255" s="16" t="n">
-        <v>0.0999</v>
+        <v>0.1012</v>
       </c>
       <c r="G255" s="18" t="n"/>
       <c r="H255" s="23" t="inlineStr">
@@ -19955,13 +19955,13 @@
         </is>
       </c>
       <c r="D256" s="4" t="n">
-        <v>35.26</v>
+        <v>35.03</v>
       </c>
       <c r="E256" s="6" t="n">
-        <v>0.0423</v>
+        <v>0.0356</v>
       </c>
       <c r="F256" s="6" t="n">
-        <v>0.1127</v>
+        <v>0.1056</v>
       </c>
       <c r="G256" s="7" t="n">
         <v>46315</v>
@@ -20016,13 +20016,13 @@
         </is>
       </c>
       <c r="D257" s="15" t="n">
-        <v>181.59</v>
+        <v>180.75</v>
       </c>
       <c r="E257" s="16" t="n">
-        <v>0.1007</v>
+        <v>0.0956</v>
       </c>
       <c r="F257" s="16" t="n">
-        <v>0.3185</v>
+        <v>0.3124</v>
       </c>
       <c r="G257" s="18" t="n">
         <v>46330</v>
@@ -20077,13 +20077,13 @@
         </is>
       </c>
       <c r="D258" s="4" t="n">
-        <v>174.47</v>
-      </c>
-      <c r="E258" s="5" t="n">
-        <v>-0.004099999999999999</v>
+        <v>177.63</v>
+      </c>
+      <c r="E258" s="6" t="n">
+        <v>0.0139</v>
       </c>
       <c r="F258" s="6" t="n">
-        <v>0.2938</v>
+        <v>0.3172</v>
       </c>
       <c r="G258" s="7" t="n">
         <v>46328</v>
@@ -20138,13 +20138,13 @@
         </is>
       </c>
       <c r="D259" s="15" t="n">
-        <v>119.2</v>
+        <v>120.53</v>
       </c>
       <c r="E259" s="17" t="n">
-        <v>-0.05429999999999999</v>
+        <v>-0.0438</v>
       </c>
       <c r="F259" s="17" t="n">
-        <v>-0.1143</v>
+        <v>-0.1044</v>
       </c>
       <c r="G259" s="18" t="n"/>
       <c r="H259" s="23" t="inlineStr">
@@ -20199,13 +20199,13 @@
         </is>
       </c>
       <c r="D260" s="4" t="n">
-        <v>16.67</v>
+        <v>17.13</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>-0.1369</v>
-      </c>
-      <c r="F260" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.1136</v>
+      </c>
+      <c r="F260" s="6" t="n">
+        <v>0.0242</v>
       </c>
       <c r="G260" s="7" t="n">
         <v>46331</v>
@@ -20260,13 +20260,13 @@
         </is>
       </c>
       <c r="D261" s="15" t="n">
-        <v>183.52</v>
+        <v>177.74</v>
       </c>
       <c r="E261" s="16" t="n">
-        <v>0.1335</v>
+        <v>0.0978</v>
       </c>
       <c r="F261" s="16" t="n">
-        <v>0.0775</v>
+        <v>0.0436</v>
       </c>
       <c r="G261" s="18" t="n">
         <v>46330</v>
@@ -20295,7 +20295,7 @@
         <v>265</v>
       </c>
       <c r="M261" s="16" t="n">
-        <v>0.4439843068875326</v>
+        <v>0.4909418251378417</v>
       </c>
       <c r="N261" s="14" t="inlineStr">
         <is>
@@ -20305,8 +20305,8 @@
       <c r="O261" s="20" t="n">
         <v>179</v>
       </c>
-      <c r="P261" s="17" t="n">
-        <v>-0.02462946817785533</v>
+      <c r="P261" s="16" t="n">
+        <v>0.007089006413862895</v>
       </c>
       <c r="Q261" s="21" t="inlineStr">
         <is>
@@ -20351,13 +20351,13 @@
         </is>
       </c>
       <c r="D262" s="4" t="n">
-        <v>117.77</v>
+        <v>117.21</v>
       </c>
       <c r="E262" s="6" t="n">
-        <v>0.2165</v>
+        <v>0.2107</v>
       </c>
       <c r="F262" s="6" t="n">
-        <v>0.3739</v>
+        <v>0.3674</v>
       </c>
       <c r="G262" s="7" t="n">
         <v>46322</v>
@@ -20412,13 +20412,13 @@
         </is>
       </c>
       <c r="D263" s="15" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="E263" s="17" t="n">
-        <v>-0.0107</v>
+        <v>8.69</v>
+      </c>
+      <c r="E263" s="16" t="n">
+        <v>0.0327</v>
       </c>
       <c r="F263" s="16" t="n">
-        <v>0.0518</v>
+        <v>0.09789999999999999</v>
       </c>
       <c r="G263" s="18" t="n"/>
       <c r="H263" s="23" t="inlineStr">
@@ -20463,13 +20463,13 @@
         </is>
       </c>
       <c r="D264" s="4" t="n">
-        <v>104.99</v>
+        <v>106.5</v>
       </c>
       <c r="E264" s="6" t="n">
-        <v>0.0522</v>
+        <v>0.0674</v>
       </c>
       <c r="F264" s="6" t="n">
-        <v>0.3429</v>
+        <v>0.3623</v>
       </c>
       <c r="G264" s="7" t="n"/>
       <c r="H264" s="12" t="inlineStr">
@@ -20514,13 +20514,13 @@
         </is>
       </c>
       <c r="D265" s="15" t="n">
-        <v>15.23</v>
+        <v>15.78</v>
       </c>
       <c r="E265" s="17" t="n">
-        <v>-0.1038</v>
+        <v>-0.0718</v>
       </c>
       <c r="F265" s="16" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.1074</v>
       </c>
       <c r="G265" s="18" t="n">
         <v>46335</v>
@@ -20575,13 +20575,13 @@
         </is>
       </c>
       <c r="D266" s="4" t="n">
-        <v>371.39</v>
+        <v>372.71</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>-0.0882</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="F266" s="6" t="n">
-        <v>0.0236</v>
+        <v>0.0272</v>
       </c>
       <c r="G266" s="7" t="n">
         <v>46317</v>
@@ -20650,13 +20650,13 @@
         </is>
       </c>
       <c r="D267" s="15" t="n">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="E267" s="16" t="n">
-        <v>0.09359999999999999</v>
+        <v>0.1096</v>
       </c>
       <c r="F267" s="17" t="n">
-        <v>-0.1302</v>
+        <v>-0.1174</v>
       </c>
       <c r="G267" s="18" t="n">
         <v>46331</v>
@@ -20711,13 +20711,13 @@
         </is>
       </c>
       <c r="D268" s="4" t="n">
-        <v>22.33</v>
+        <v>22.53</v>
       </c>
       <c r="E268" s="6" t="n">
-        <v>0.0474</v>
+        <v>0.057</v>
       </c>
       <c r="F268" s="6" t="n">
-        <v>0.1475</v>
+        <v>0.158</v>
       </c>
       <c r="G268" s="7" t="n"/>
       <c r="H268" s="12" t="inlineStr">
@@ -20762,13 +20762,13 @@
         </is>
       </c>
       <c r="D269" s="15" t="n">
-        <v>19.52</v>
+        <v>19.82</v>
       </c>
       <c r="E269" s="16" t="n">
-        <v>0.0172</v>
+        <v>0.0326</v>
       </c>
       <c r="F269" s="16" t="n">
-        <v>0.2825</v>
+        <v>0.3019</v>
       </c>
       <c r="G269" s="18" t="n"/>
       <c r="H269" s="23" t="inlineStr">
@@ -20813,13 +20813,13 @@
         </is>
       </c>
       <c r="D270" s="4" t="n">
-        <v>196.94</v>
+        <v>200.2</v>
       </c>
       <c r="E270" s="6" t="n">
-        <v>0.0124</v>
+        <v>0.0291</v>
       </c>
       <c r="F270" s="5" t="n">
-        <v>-0.0244</v>
+        <v>-0.0083</v>
       </c>
       <c r="G270" s="7" t="n">
         <v>46328</v>
@@ -20874,13 +20874,13 @@
         </is>
       </c>
       <c r="D271" s="15" t="n">
-        <v>210.01</v>
+        <v>209.49</v>
       </c>
       <c r="E271" s="17" t="n">
-        <v>-0.0259</v>
+        <v>-0.0284</v>
       </c>
       <c r="F271" s="16" t="n">
-        <v>0.3262</v>
+        <v>0.3229</v>
       </c>
       <c r="G271" s="18" t="n">
         <v>46316</v>
@@ -20955,13 +20955,13 @@
         </is>
       </c>
       <c r="D272" s="4" t="n">
-        <v>38.54</v>
+        <v>39.16</v>
       </c>
       <c r="E272" s="6" t="n">
-        <v>0.0536</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="F272" s="6" t="n">
-        <v>0.6173</v>
+        <v>0.6433</v>
       </c>
       <c r="G272" s="7" t="n">
         <v>46329</v>
@@ -21016,13 +21016,13 @@
         </is>
       </c>
       <c r="D273" s="15" t="n">
-        <v>332.68</v>
+        <v>331.93</v>
       </c>
       <c r="E273" s="16" t="n">
-        <v>0.0236</v>
+        <v>0.0213</v>
       </c>
       <c r="F273" s="16" t="n">
-        <v>0.2127</v>
+        <v>0.2099</v>
       </c>
       <c r="G273" s="18" t="n"/>
       <c r="H273" s="23" t="inlineStr">
@@ -21041,7 +21041,7 @@
         <v>320</v>
       </c>
       <c r="M273" s="17" t="n">
-        <v>-0.03811470482145006</v>
+        <v>-0.03594131292742447</v>
       </c>
       <c r="N273" s="14" t="inlineStr">
         <is>
@@ -21052,7 +21052,7 @@
         <v>280</v>
       </c>
       <c r="P273" s="17" t="n">
-        <v>-0.1583503667187688</v>
+        <v>-0.1564486488114964</v>
       </c>
       <c r="Q273" s="21" t="inlineStr">
         <is>
@@ -21093,13 +21093,13 @@
         </is>
       </c>
       <c r="D274" s="4" t="n">
-        <v>381.64</v>
+        <v>384.93</v>
       </c>
       <c r="E274" s="5" t="n">
-        <v>-0.0488</v>
+        <v>-0.0406</v>
       </c>
       <c r="F274" s="6" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0171</v>
       </c>
       <c r="G274" s="7" t="n"/>
       <c r="H274" s="12" t="inlineStr">
@@ -21118,7 +21118,7 @@
         <v>535</v>
       </c>
       <c r="M274" s="6" t="n">
-        <v>0.4018446703699822</v>
+        <v>0.3898630919907515</v>
       </c>
       <c r="N274" s="3" t="inlineStr"/>
       <c r="O274" s="9" t="n"/>
@@ -21162,13 +21162,13 @@
         </is>
       </c>
       <c r="D275" s="15" t="n">
-        <v>5.86</v>
+        <v>5.93</v>
       </c>
       <c r="E275" s="17" t="n">
-        <v>-0.1816</v>
+        <v>-0.1718</v>
       </c>
       <c r="F275" s="17" t="n">
-        <v>-0.07139999999999999</v>
+        <v>-0.0602</v>
       </c>
       <c r="G275" s="18" t="n">
         <v>46331</v>
@@ -21223,13 +21223,13 @@
         </is>
       </c>
       <c r="D276" s="4" t="n">
-        <v>89.31999999999999</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="E276" s="6" t="n">
-        <v>0.3043</v>
+        <v>0.2966</v>
       </c>
       <c r="F276" s="6" t="n">
-        <v>0.4936</v>
+        <v>0.4848</v>
       </c>
       <c r="G276" s="7" t="n">
         <v>46322</v>
@@ -21284,13 +21284,13 @@
         </is>
       </c>
       <c r="D277" s="15" t="n">
-        <v>92.14</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="E277" s="17" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-0.07719999999999999</v>
       </c>
       <c r="F277" s="17" t="n">
-        <v>-0.1889</v>
+        <v>-0.1798</v>
       </c>
       <c r="G277" s="18" t="n">
         <v>46331</v>
@@ -21345,13 +21345,13 @@
         </is>
       </c>
       <c r="D278" s="4" t="n">
-        <v>205.53</v>
+        <v>205.76</v>
       </c>
       <c r="E278" s="6" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0107</v>
       </c>
       <c r="F278" s="6" t="n">
-        <v>0.0118</v>
+        <v>0.0129</v>
       </c>
       <c r="G278" s="7" t="n">
         <v>46330</v>
@@ -21406,13 +21406,13 @@
         </is>
       </c>
       <c r="D279" s="15" t="n">
-        <v>363.22</v>
+        <v>371.42</v>
       </c>
       <c r="E279" s="17" t="n">
-        <v>-0.0433</v>
+        <v>-0.0217</v>
       </c>
       <c r="F279" s="16" t="n">
-        <v>0.0883</v>
+        <v>0.1128</v>
       </c>
       <c r="G279" s="18" t="n">
         <v>46322</v>
@@ -21467,13 +21467,13 @@
         </is>
       </c>
       <c r="D280" s="4" t="n">
-        <v>57.45</v>
+        <v>57.58</v>
       </c>
       <c r="E280" s="5" t="n">
-        <v>-0.0304</v>
+        <v>-0.0282</v>
       </c>
       <c r="F280" s="6" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="G280" s="7" t="n">
         <v>46330</v>
@@ -21528,13 +21528,13 @@
         </is>
       </c>
       <c r="D281" s="15" t="n">
-        <v>432.9</v>
+        <v>433.26</v>
       </c>
       <c r="E281" s="16" t="n">
-        <v>0.0505</v>
+        <v>0.05139999999999999</v>
       </c>
       <c r="F281" s="16" t="n">
-        <v>0.0761</v>
+        <v>0.077</v>
       </c>
       <c r="G281" s="18" t="n">
         <v>46310</v>
@@ -21611,13 +21611,13 @@
         </is>
       </c>
       <c r="D282" s="4" t="n">
-        <v>116.62</v>
+        <v>118.04</v>
       </c>
       <c r="E282" s="6" t="n">
-        <v>0.0021</v>
+        <v>0.0143</v>
       </c>
       <c r="F282" s="5" t="n">
-        <v>-0.1243</v>
+        <v>-0.1136</v>
       </c>
       <c r="G282" s="7" t="n">
         <v>46330</v>
@@ -21672,13 +21672,13 @@
         </is>
       </c>
       <c r="D283" s="15" t="n">
-        <v>240.2</v>
+        <v>244.03</v>
       </c>
       <c r="E283" s="16" t="n">
-        <v>0.08259999999999999</v>
+        <v>0.0999</v>
       </c>
       <c r="F283" s="16" t="n">
-        <v>0.1703</v>
+        <v>0.189</v>
       </c>
       <c r="G283" s="18" t="n">
         <v>46324</v>
@@ -21733,13 +21733,13 @@
         </is>
       </c>
       <c r="D284" s="4" t="n">
-        <v>264.22</v>
+        <v>266.61</v>
       </c>
       <c r="E284" s="5" t="n">
-        <v>-0.0121</v>
+        <v>-0.0031</v>
       </c>
       <c r="F284" s="5" t="n">
-        <v>-0.0699</v>
+        <v>-0.06150000000000001</v>
       </c>
       <c r="G284" s="7" t="n">
         <v>46315</v>
@@ -21768,7 +21768,7 @@
         <v>300</v>
       </c>
       <c r="M284" s="6" t="n">
-        <v>0.1354174551510104</v>
+        <v>0.1252391133115787</v>
       </c>
       <c r="N284" s="3" t="inlineStr">
         <is>
@@ -21779,7 +21779,7 @@
         <v>316</v>
       </c>
       <c r="P284" s="6" t="n">
-        <v>0.1959730527590643</v>
+        <v>0.1852518660215295</v>
       </c>
       <c r="Q284" s="10" t="inlineStr">
         <is>
@@ -21836,13 +21836,13 @@
         </is>
       </c>
       <c r="D285" s="15" t="n">
-        <v>336.92</v>
+        <v>337.45</v>
       </c>
       <c r="E285" s="17" t="n">
-        <v>-0.0287</v>
+        <v>-0.0272</v>
       </c>
       <c r="F285" s="16" t="n">
-        <v>0.0596</v>
+        <v>0.0613</v>
       </c>
       <c r="G285" s="18" t="n">
         <v>46330</v>
@@ -21871,7 +21871,7 @@
         <v>335</v>
       </c>
       <c r="M285" s="17" t="n">
-        <v>-0.00569868217974598</v>
+        <v>-0.007260334864424326</v>
       </c>
       <c r="N285" s="14" t="inlineStr">
         <is>
@@ -21882,7 +21882,7 @@
         <v>375</v>
       </c>
       <c r="P285" s="16" t="n">
-        <v>0.1130238632316276</v>
+        <v>0.1112757445547489</v>
       </c>
       <c r="Q285" s="21" t="inlineStr">
         <is>
@@ -21923,13 +21923,13 @@
         </is>
       </c>
       <c r="D286" s="4" t="n">
-        <v>41.13</v>
+        <v>41.54</v>
       </c>
       <c r="E286" s="5" t="n">
-        <v>-0.1269</v>
+        <v>-0.1182</v>
       </c>
       <c r="F286" s="6" t="n">
-        <v>0.3797</v>
+        <v>0.3935</v>
       </c>
       <c r="G286" s="7" t="n">
         <v>46330</v>
@@ -21984,13 +21984,13 @@
         </is>
       </c>
       <c r="D287" s="15" t="n">
-        <v>6.32</v>
+        <v>6.55</v>
       </c>
       <c r="E287" s="17" t="n">
-        <v>-0.0706</v>
+        <v>-0.0375</v>
       </c>
       <c r="F287" s="17" t="n">
-        <v>-0.1771</v>
+        <v>-0.1478</v>
       </c>
       <c r="G287" s="18" t="n"/>
       <c r="H287" s="23" t="inlineStr">
@@ -22035,13 +22035,13 @@
         </is>
       </c>
       <c r="D288" s="4" t="n">
-        <v>193.98</v>
+        <v>193.79</v>
       </c>
       <c r="E288" s="5" t="n">
-        <v>-0.0224</v>
+        <v>-0.0233</v>
       </c>
       <c r="F288" s="6" t="n">
-        <v>0.3176</v>
+        <v>0.3163</v>
       </c>
       <c r="G288" s="7" t="n"/>
       <c r="H288" s="12" t="inlineStr">
@@ -22086,13 +22086,13 @@
         </is>
       </c>
       <c r="D289" s="15" t="n">
-        <v>434.22</v>
+        <v>441.72</v>
       </c>
       <c r="E289" s="17" t="n">
-        <v>-0.0603</v>
+        <v>-0.0441</v>
       </c>
       <c r="F289" s="17" t="n">
-        <v>-0.1091</v>
+        <v>-0.09380000000000001</v>
       </c>
       <c r="G289" s="18" t="n">
         <v>46324</v>
@@ -22121,7 +22121,7 @@
         <v>730</v>
       </c>
       <c r="M289" s="16" t="n">
-        <v>0.6811754410206806</v>
+        <v>0.6526306257357601</v>
       </c>
       <c r="N289" s="14" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>575</v>
       </c>
       <c r="P289" s="16" t="n">
-        <v>0.3242135323108101</v>
+        <v>0.3017296024630987</v>
       </c>
       <c r="Q289" s="21" t="inlineStr">
         <is>
@@ -22173,13 +22173,13 @@
         </is>
       </c>
       <c r="D290" s="4" t="n">
-        <v>24.78</v>
+        <v>25.63</v>
       </c>
       <c r="E290" s="5" t="n">
-        <v>-0.1482</v>
+        <v>-0.1191</v>
       </c>
       <c r="F290" s="5" t="n">
-        <v>-0.1566</v>
+        <v>-0.1278</v>
       </c>
       <c r="G290" s="7" t="n">
         <v>46330</v>
@@ -22234,13 +22234,13 @@
         </is>
       </c>
       <c r="D291" s="15" t="n">
-        <v>89.93000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="E291" s="17" t="n">
-        <v>-0.1632</v>
+        <v>-0.1737</v>
       </c>
       <c r="F291" s="17" t="n">
-        <v>-0.0108</v>
+        <v>-0.0232</v>
       </c>
       <c r="G291" s="18" t="n"/>
       <c r="H291" s="23" t="inlineStr">
@@ -22285,13 +22285,13 @@
         </is>
       </c>
       <c r="D292" s="4" t="n">
-        <v>194.2</v>
+        <v>197.28</v>
       </c>
       <c r="E292" s="6" t="n">
-        <v>0.052</v>
+        <v>0.0687</v>
       </c>
       <c r="F292" s="6" t="n">
-        <v>0.2962</v>
+        <v>0.3168</v>
       </c>
       <c r="G292" s="7" t="n"/>
       <c r="H292" s="12" t="inlineStr">
@@ -22336,13 +22336,13 @@
         </is>
       </c>
       <c r="D293" s="15" t="n">
-        <v>282.13</v>
+        <v>284.07</v>
       </c>
       <c r="E293" s="17" t="n">
-        <v>-0.0696</v>
+        <v>-0.06320000000000001</v>
       </c>
       <c r="F293" s="17" t="n">
-        <v>-0.0489</v>
+        <v>-0.0423</v>
       </c>
       <c r="G293" s="18" t="n">
         <v>46331</v>
@@ -22397,13 +22397,13 @@
         </is>
       </c>
       <c r="D294" s="4" t="n">
-        <v>85.81</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="E294" s="5" t="n">
-        <v>-0.0702</v>
+        <v>-0.065</v>
       </c>
       <c r="F294" s="6" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.0721</v>
       </c>
       <c r="G294" s="7" t="n"/>
       <c r="H294" s="12" t="inlineStr">
@@ -22448,13 +22448,13 @@
         </is>
       </c>
       <c r="D295" s="15" t="n">
-        <v>128.86</v>
+        <v>129.04</v>
       </c>
       <c r="E295" s="17" t="n">
-        <v>-0.0775</v>
+        <v>-0.0762</v>
       </c>
       <c r="F295" s="17" t="n">
-        <v>-0.0508</v>
+        <v>-0.0495</v>
       </c>
       <c r="G295" s="18" t="n">
         <v>46331</v>
@@ -22483,7 +22483,7 @@
         <v>166</v>
       </c>
       <c r="M295" s="16" t="n">
-        <v>0.2882197733974855</v>
+        <v>0.2864228146311222</v>
       </c>
       <c r="N295" s="14" t="inlineStr"/>
       <c r="O295" s="20" t="n"/>
@@ -22531,13 +22531,13 @@
         </is>
       </c>
       <c r="D296" s="4" t="n">
-        <v>29.03</v>
+        <v>28.73</v>
       </c>
       <c r="E296" s="5" t="n">
-        <v>-0.08550000000000001</v>
+        <v>-0.0953</v>
       </c>
       <c r="F296" s="5" t="n">
-        <v>-0.044</v>
+        <v>-0.0542</v>
       </c>
       <c r="G296" s="7" t="n">
         <v>46317</v>
@@ -22592,13 +22592,13 @@
         </is>
       </c>
       <c r="D297" s="15" t="n">
-        <v>268.82</v>
+        <v>269.55</v>
       </c>
       <c r="E297" s="17" t="n">
-        <v>-0.0588</v>
+        <v>-0.0562</v>
       </c>
       <c r="F297" s="16" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0034</v>
       </c>
       <c r="G297" s="18" t="n">
         <v>46322</v>
@@ -22627,7 +22627,7 @@
         <v>275</v>
       </c>
       <c r="M297" s="16" t="n">
-        <v>0.02298936091064656</v>
+        <v>0.02021888332405857</v>
       </c>
       <c r="N297" s="14" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>312</v>
       </c>
       <c r="P297" s="16" t="n">
-        <v>0.1606279294695336</v>
+        <v>0.1574846967167501</v>
       </c>
       <c r="Q297" s="21" t="inlineStr">
         <is>
@@ -22691,13 +22691,13 @@
         </is>
       </c>
       <c r="D298" s="4" t="n">
-        <v>33.49</v>
+        <v>32.79</v>
       </c>
       <c r="E298" s="5" t="n">
-        <v>-0.07440000000000001</v>
+        <v>-0.09369999999999999</v>
       </c>
       <c r="F298" s="5" t="n">
-        <v>-0.0815</v>
+        <v>-0.1007</v>
       </c>
       <c r="G298" s="7" t="n">
         <v>46322</v>
@@ -22756,13 +22756,13 @@
         </is>
       </c>
       <c r="D299" s="15" t="n">
-        <v>70.78</v>
+        <v>71.5</v>
       </c>
       <c r="E299" s="16" t="n">
-        <v>0.0245</v>
+        <v>0.035</v>
       </c>
       <c r="F299" s="16" t="n">
-        <v>0.2039</v>
+        <v>0.2163</v>
       </c>
       <c r="G299" s="18" t="n">
         <v>46310</v>
@@ -22817,13 +22817,13 @@
         </is>
       </c>
       <c r="D300" s="4" t="n">
-        <v>456.95</v>
+        <v>460.13</v>
       </c>
       <c r="E300" s="5" t="n">
-        <v>-0.0503</v>
+        <v>-0.0436</v>
       </c>
       <c r="F300" s="5" t="n">
-        <v>-0.1076</v>
+        <v>-0.1014</v>
       </c>
       <c r="G300" s="7" t="n">
         <v>46325</v>
@@ -22852,7 +22852,7 @@
         <v>570</v>
       </c>
       <c r="M300" s="6" t="n">
-        <v>0.2474012474012474</v>
+        <v>0.2387803446851977</v>
       </c>
       <c r="N300" s="3" t="inlineStr">
         <is>
@@ -22863,7 +22863,7 @@
         <v>525</v>
       </c>
       <c r="P300" s="6" t="n">
-        <v>0.1489222015537805</v>
+        <v>0.1409818964205768</v>
       </c>
       <c r="Q300" s="10" t="inlineStr">
         <is>
@@ -22916,13 +22916,13 @@
         </is>
       </c>
       <c r="D301" s="15" t="n">
-        <v>492.14</v>
+        <v>490.77</v>
       </c>
       <c r="E301" s="17" t="n">
-        <v>-0.081</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="F301" s="17" t="n">
-        <v>-0.1111</v>
+        <v>-0.1135</v>
       </c>
       <c r="G301" s="18" t="n">
         <v>46329</v>
@@ -22951,7 +22951,7 @@
         <v>616</v>
       </c>
       <c r="M301" s="16" t="n">
-        <v>0.2516763522574877</v>
+        <v>0.2551704464413065</v>
       </c>
       <c r="N301" s="14" t="inlineStr"/>
       <c r="O301" s="20" t="n"/>
@@ -22995,13 +22995,13 @@
         </is>
       </c>
       <c r="D302" s="4" t="n">
-        <v>251.55</v>
+        <v>249.04</v>
       </c>
       <c r="E302" s="6" t="n">
-        <v>0.0113</v>
+        <v>0.0012</v>
       </c>
       <c r="F302" s="6" t="n">
-        <v>0.0902</v>
+        <v>0.0793</v>
       </c>
       <c r="G302" s="7" t="n">
         <v>46321</v>
@@ -23030,7 +23030,7 @@
         <v>283</v>
       </c>
       <c r="M302" s="6" t="n">
-        <v>0.1250248459550785</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="N302" s="3" t="inlineStr"/>
       <c r="O302" s="9" t="n"/>
@@ -23076,13 +23076,13 @@
         </is>
       </c>
       <c r="D303" s="15" t="n">
-        <v>234.84</v>
+        <v>233.09</v>
       </c>
       <c r="E303" s="17" t="n">
-        <v>-0.07139999999999999</v>
+        <v>-0.0784</v>
       </c>
       <c r="F303" s="16" t="n">
-        <v>0.0281</v>
+        <v>0.0204</v>
       </c>
       <c r="G303" s="18" t="n">
         <v>46316</v>
@@ -23111,7 +23111,7 @@
         <v>246</v>
       </c>
       <c r="M303" s="16" t="n">
-        <v>0.04752171691364332</v>
+        <v>0.05538633145995107</v>
       </c>
       <c r="N303" s="14" t="inlineStr"/>
       <c r="O303" s="20" t="n"/>
@@ -23159,13 +23159,13 @@
         </is>
       </c>
       <c r="D304" s="4" t="n">
-        <v>104.13</v>
+        <v>104.53</v>
       </c>
       <c r="E304" s="5" t="n">
-        <v>-0.0859</v>
+        <v>-0.0824</v>
       </c>
       <c r="F304" s="5" t="n">
-        <v>-0.1</v>
+        <v>-0.0965</v>
       </c>
       <c r="G304" s="7" t="n">
         <v>46322</v>
@@ -23194,7 +23194,7 @@
         <v>130</v>
       </c>
       <c r="M304" s="6" t="n">
-        <v>0.2484394506866417</v>
+        <v>0.2436621065722759</v>
       </c>
       <c r="N304" s="3" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>128</v>
       </c>
       <c r="P304" s="6" t="n">
-        <v>0.2292326899068473</v>
+        <v>0.2245288433942409</v>
       </c>
       <c r="Q304" s="10" t="inlineStr">
         <is>
@@ -23254,13 +23254,13 @@
         </is>
       </c>
       <c r="D305" s="15" t="n">
-        <v>98.19</v>
+        <v>98.42</v>
       </c>
       <c r="E305" s="17" t="n">
-        <v>-0.1206</v>
+        <v>-0.1186</v>
       </c>
       <c r="F305" s="17" t="n">
-        <v>-0.0338</v>
+        <v>-0.0316</v>
       </c>
       <c r="G305" s="18" t="n">
         <v>46301</v>
@@ -23289,7 +23289,7 @@
         <v>135</v>
       </c>
       <c r="M305" s="16" t="n">
-        <v>0.3748854262144822</v>
+        <v>0.3716724243040032</v>
       </c>
       <c r="N305" s="14" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>125</v>
       </c>
       <c r="P305" s="16" t="n">
-        <v>0.2730420613097057</v>
+        <v>0.2700670595407437</v>
       </c>
       <c r="Q305" s="21" t="inlineStr"/>
       <c r="R305" s="20" t="n"/>
@@ -23335,13 +23335,13 @@
         </is>
       </c>
       <c r="D306" s="4" t="n">
-        <v>317.25</v>
+        <v>320.74</v>
       </c>
       <c r="E306" s="5" t="n">
-        <v>-0.1028</v>
+        <v>-0.0929</v>
       </c>
       <c r="F306" s="5" t="n">
-        <v>-0.0196</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="G306" s="7" t="n">
         <v>46322</v>
@@ -23370,7 +23370,7 @@
         <v>350</v>
       </c>
       <c r="M306" s="6" t="n">
-        <v>0.103230890464933</v>
+        <v>0.09122653862941944</v>
       </c>
       <c r="N306" s="3" t="inlineStr">
         <is>
@@ -23381,7 +23381,7 @@
         <v>400</v>
       </c>
       <c r="P306" s="6" t="n">
-        <v>0.2608353033884949</v>
+        <v>0.2471160441479079</v>
       </c>
       <c r="Q306" s="10" t="inlineStr">
         <is>
@@ -23422,13 +23422,13 @@
         </is>
       </c>
       <c r="D307" s="15" t="n">
-        <v>103.26</v>
+        <v>104.32</v>
       </c>
       <c r="E307" s="17" t="n">
-        <v>-0.078</v>
+        <v>-0.06860000000000001</v>
       </c>
       <c r="F307" s="16" t="n">
-        <v>0.4767</v>
+        <v>0.4918</v>
       </c>
       <c r="G307" s="18" t="n"/>
       <c r="H307" s="23" t="inlineStr">
@@ -23469,13 +23469,13 @@
         </is>
       </c>
       <c r="D308" s="4" t="n">
-        <v>53.59</v>
+        <v>51.59</v>
       </c>
       <c r="E308" s="5" t="n">
-        <v>-0.043</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="F308" s="5" t="n">
-        <v>-0.06559999999999999</v>
+        <v>-0.1004</v>
       </c>
       <c r="G308" s="7" t="n">
         <v>46267</v>
@@ -23530,13 +23530,13 @@
         </is>
       </c>
       <c r="D309" s="15" t="n">
-        <v>68.31999999999999</v>
+        <v>68.03</v>
       </c>
       <c r="E309" s="17" t="n">
-        <v>-0.08169999999999999</v>
+        <v>-0.08560000000000001</v>
       </c>
       <c r="F309" s="17" t="n">
-        <v>-0.1521</v>
+        <v>-0.1557</v>
       </c>
       <c r="G309" s="18" t="n">
         <v>46315</v>
@@ -23565,14 +23565,14 @@
         <v>83</v>
       </c>
       <c r="M309" s="16" t="n">
-        <v>0.2148711943793912</v>
+        <v>0.220049977950904</v>
       </c>
       <c r="N309" s="14" t="inlineStr"/>
       <c r="O309" s="20" t="n">
         <v>87</v>
       </c>
       <c r="P309" s="16" t="n">
-        <v>0.2734192037470727</v>
+        <v>0.2788475672497427</v>
       </c>
       <c r="Q309" s="21" t="inlineStr"/>
       <c r="R309" s="20" t="n"/>
@@ -23607,13 +23607,13 @@
         </is>
       </c>
       <c r="D310" s="4" t="n">
-        <v>173.79</v>
+        <v>174.07</v>
       </c>
       <c r="E310" s="5" t="n">
-        <v>-0.004</v>
+        <v>-0.0024</v>
       </c>
       <c r="F310" s="6" t="n">
-        <v>0.0403</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="G310" s="7" t="n">
         <v>46322</v>
@@ -23642,7 +23642,7 @@
         <v>200</v>
       </c>
       <c r="M310" s="6" t="n">
-        <v>0.150814201047241</v>
+        <v>0.1489630608375941</v>
       </c>
       <c r="N310" s="3" t="inlineStr"/>
       <c r="O310" s="9" t="n"/>
@@ -23690,13 +23690,13 @@
         </is>
       </c>
       <c r="D311" s="15" t="n">
-        <v>138.28</v>
+        <v>139.59</v>
       </c>
       <c r="E311" s="17" t="n">
-        <v>-0.1083</v>
-      </c>
-      <c r="F311" s="17" t="n">
-        <v>-0.0025</v>
+        <v>-0.0999</v>
+      </c>
+      <c r="F311" s="16" t="n">
+        <v>0.006999999999999999</v>
       </c>
       <c r="G311" s="18" t="n">
         <v>46317</v>
@@ -23755,13 +23755,13 @@
         </is>
       </c>
       <c r="D312" s="4" t="n">
-        <v>183.5</v>
+        <v>182.22</v>
       </c>
       <c r="E312" s="5" t="n">
-        <v>-0.046</v>
+        <v>-0.0527</v>
       </c>
       <c r="F312" s="6" t="n">
-        <v>0.0411</v>
+        <v>0.0339</v>
       </c>
       <c r="G312" s="7" t="n">
         <v>46317</v>
@@ -23790,7 +23790,7 @@
         <v>220</v>
       </c>
       <c r="M312" s="6" t="n">
-        <v>0.1989100817438692</v>
+        <v>0.2073317967292284</v>
       </c>
       <c r="N312" s="3" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>230</v>
       </c>
       <c r="P312" s="6" t="n">
-        <v>0.2534059945504087</v>
+        <v>0.2622105147623752</v>
       </c>
       <c r="Q312" s="10" t="inlineStr">
         <is>
@@ -23842,13 +23842,13 @@
         </is>
       </c>
       <c r="D313" s="15" t="n">
-        <v>1017.65</v>
+        <v>1021.24</v>
       </c>
       <c r="E313" s="17" t="n">
-        <v>-0.0552</v>
+        <v>-0.0518</v>
       </c>
       <c r="F313" s="16" t="n">
-        <v>0.0003</v>
+        <v>0.0039</v>
       </c>
       <c r="G313" s="18" t="n">
         <v>46330</v>
@@ -23877,7 +23877,7 @@
         <v>1200</v>
       </c>
       <c r="M313" s="16" t="n">
-        <v>0.179187343389181</v>
+        <v>0.1750421056754534</v>
       </c>
       <c r="N313" s="14" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>1240</v>
       </c>
       <c r="P313" s="16" t="n">
-        <v>0.2184935881688203</v>
+        <v>0.2142101758646351</v>
       </c>
       <c r="Q313" s="21" t="inlineStr">
         <is>
@@ -23933,13 +23933,13 @@
         </is>
       </c>
       <c r="D314" s="4" t="n">
-        <v>111.6</v>
+        <v>110.98</v>
       </c>
       <c r="E314" s="5" t="n">
-        <v>-0.0507</v>
+        <v>-0.05599999999999999</v>
       </c>
       <c r="F314" s="5" t="n">
-        <v>-0.1114</v>
+        <v>-0.1163</v>
       </c>
       <c r="G314" s="7" t="n">
         <v>46325</v>
@@ -23968,7 +23968,7 @@
         <v>129</v>
       </c>
       <c r="M314" s="6" t="n">
-        <v>0.1559139784946237</v>
+        <v>0.1623715984862137</v>
       </c>
       <c r="N314" s="3" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
         <v>122</v>
       </c>
       <c r="P314" s="6" t="n">
-        <v>0.09318996415770615</v>
+        <v>0.09929717066138039</v>
       </c>
       <c r="Q314" s="10" t="inlineStr">
         <is>
@@ -24020,13 +24020,13 @@
         </is>
       </c>
       <c r="D315" s="15" t="n">
-        <v>56.97</v>
+        <v>56.69</v>
       </c>
       <c r="E315" s="17" t="n">
-        <v>-0.0949</v>
+        <v>-0.09949999999999999</v>
       </c>
       <c r="F315" s="17" t="n">
-        <v>-0.1259</v>
+        <v>-0.1303</v>
       </c>
       <c r="G315" s="18" t="n">
         <v>46328</v>
@@ -24055,14 +24055,14 @@
         <v>65</v>
       </c>
       <c r="M315" s="16" t="n">
-        <v>0.1409513779182026</v>
+        <v>0.1465866995942847</v>
       </c>
       <c r="N315" s="14" t="inlineStr"/>
       <c r="O315" s="20" t="n">
         <v>67</v>
       </c>
       <c r="P315" s="16" t="n">
-        <v>0.1760575741618396</v>
+        <v>0.181866290351032</v>
       </c>
       <c r="Q315" s="21" t="inlineStr">
         <is>
@@ -24103,13 +24103,13 @@
         </is>
       </c>
       <c r="D316" s="4" t="n">
-        <v>134.4</v>
+        <v>134.82</v>
       </c>
       <c r="E316" s="5" t="n">
-        <v>-0.0488</v>
+        <v>-0.0459</v>
       </c>
       <c r="F316" s="5" t="n">
-        <v>-0.08869999999999999</v>
+        <v>-0.0858</v>
       </c>
       <c r="G316" s="7" t="n">
         <v>46310</v>
@@ -24138,7 +24138,7 @@
         <v>167</v>
       </c>
       <c r="M316" s="6" t="n">
-        <v>0.2425595238095238</v>
+        <v>0.238688621866192</v>
       </c>
       <c r="N316" s="3" t="inlineStr"/>
       <c r="O316" s="9" t="n"/>
@@ -24182,13 +24182,13 @@
         </is>
       </c>
       <c r="D317" s="15" t="n">
-        <v>299.7</v>
+        <v>295.9</v>
       </c>
       <c r="E317" s="17" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.08990000000000001</v>
       </c>
       <c r="F317" s="17" t="n">
-        <v>-0.05019999999999999</v>
+        <v>-0.0622</v>
       </c>
       <c r="G317" s="18" t="n">
         <v>46330</v>
@@ -24224,7 +24224,7 @@
         <v>316</v>
       </c>
       <c r="P317" s="16" t="n">
-        <v>0.05438772105438776</v>
+        <v>0.06792835417370742</v>
       </c>
       <c r="Q317" s="21" t="inlineStr">
         <is>
@@ -24265,13 +24265,13 @@
         </is>
       </c>
       <c r="D318" s="4" t="n">
-        <v>204.48</v>
+        <v>205.18</v>
       </c>
       <c r="E318" s="5" t="n">
-        <v>-0.08380000000000001</v>
+        <v>-0.08070000000000001</v>
       </c>
       <c r="F318" s="5" t="n">
-        <v>-0.1039</v>
+        <v>-0.1009</v>
       </c>
       <c r="G318" s="7" t="n">
         <v>46328</v>
@@ -24307,7 +24307,7 @@
         <v>215</v>
       </c>
       <c r="P318" s="6" t="n">
-        <v>0.05144757433489833</v>
+        <v>0.04786041524515056</v>
       </c>
       <c r="Q318" s="10" t="inlineStr">
         <is>
@@ -24348,13 +24348,13 @@
         </is>
       </c>
       <c r="D319" s="15" t="n">
-        <v>114.9</v>
+        <v>114.07</v>
       </c>
       <c r="E319" s="17" t="n">
-        <v>-0.0587</v>
+        <v>-0.0655</v>
       </c>
       <c r="F319" s="17" t="n">
-        <v>-0.0441</v>
+        <v>-0.051</v>
       </c>
       <c r="G319" s="18" t="n">
         <v>46330</v>
@@ -24383,7 +24383,7 @@
         <v>142</v>
       </c>
       <c r="M319" s="16" t="n">
-        <v>0.2358572671888598</v>
+        <v>0.2448496537213992</v>
       </c>
       <c r="N319" s="14" t="inlineStr">
         <is>
@@ -24394,7 +24394,7 @@
         <v>137</v>
       </c>
       <c r="P319" s="16" t="n">
-        <v>0.1923411662315056</v>
+        <v>0.2010169194354345</v>
       </c>
       <c r="Q319" s="21" t="inlineStr">
         <is>
@@ -24443,13 +24443,13 @@
         </is>
       </c>
       <c r="D320" s="4" t="n">
-        <v>231.55</v>
+        <v>228.99</v>
       </c>
       <c r="E320" s="5" t="n">
-        <v>-0.0177</v>
+        <v>-0.0286</v>
       </c>
       <c r="F320" s="5" t="n">
-        <v>-0.05429999999999999</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="G320" s="7" t="n">
         <v>46321</v>
@@ -24478,7 +24478,7 @@
         <v>237</v>
       </c>
       <c r="M320" s="6" t="n">
-        <v>0.02353703303822064</v>
+        <v>0.03497969343639456</v>
       </c>
       <c r="N320" s="3" t="inlineStr">
         <is>
@@ -24489,7 +24489,7 @@
         <v>236</v>
       </c>
       <c r="P320" s="6" t="n">
-        <v>0.01921831137983152</v>
+        <v>0.0306126905105026</v>
       </c>
       <c r="Q320" s="10" t="inlineStr">
         <is>
@@ -24530,13 +24530,13 @@
         </is>
       </c>
       <c r="D321" s="15" t="n">
-        <v>160.45</v>
+        <v>160.29</v>
       </c>
       <c r="E321" s="17" t="n">
-        <v>-0.0634</v>
+        <v>-0.0643</v>
       </c>
       <c r="F321" s="17" t="n">
-        <v>-0.09519999999999999</v>
+        <v>-0.09609999999999999</v>
       </c>
       <c r="G321" s="18" t="n">
         <v>46330</v>
@@ -24565,7 +24565,7 @@
         <v>200</v>
       </c>
       <c r="M321" s="16" t="n">
-        <v>0.2464942349641634</v>
+        <v>0.2477384740158463</v>
       </c>
       <c r="N321" s="14" t="inlineStr"/>
       <c r="O321" s="20" t="n"/>
@@ -24609,13 +24609,13 @@
         </is>
       </c>
       <c r="D322" s="4" t="n">
-        <v>136.06</v>
+        <v>136.07</v>
       </c>
       <c r="E322" s="5" t="n">
-        <v>-0.0191</v>
+        <v>-0.019</v>
       </c>
       <c r="F322" s="6" t="n">
-        <v>0.018</v>
+        <v>0.0181</v>
       </c>
       <c r="G322" s="7" t="n">
         <v>46330</v>
@@ -24644,7 +24644,7 @@
         <v>131</v>
       </c>
       <c r="M322" s="5" t="n">
-        <v>-0.03718947523151552</v>
+        <v>-0.03726023370324093</v>
       </c>
       <c r="N322" s="3" t="inlineStr"/>
       <c r="O322" s="9" t="n"/>
@@ -24688,13 +24688,13 @@
         </is>
       </c>
       <c r="D323" s="15" t="n">
-        <v>29.47</v>
+        <v>29.96</v>
       </c>
       <c r="E323" s="17" t="n">
-        <v>-0.1348</v>
+        <v>-0.1204</v>
       </c>
       <c r="F323" s="17" t="n">
-        <v>-0.1388</v>
+        <v>-0.1245</v>
       </c>
       <c r="G323" s="18" t="n">
         <v>46330</v>
@@ -24767,13 +24767,13 @@
         </is>
       </c>
       <c r="D324" s="4" t="n">
-        <v>35.49</v>
+        <v>36.08</v>
       </c>
       <c r="E324" s="5" t="n">
-        <v>-0.09970000000000001</v>
+        <v>-0.08470000000000001</v>
       </c>
       <c r="F324" s="5" t="n">
-        <v>-0.09420000000000001</v>
+        <v>-0.0791</v>
       </c>
       <c r="G324" s="7" t="n">
         <v>46332</v>
@@ -24828,13 +24828,13 @@
         </is>
       </c>
       <c r="D325" s="15" t="n">
-        <v>258.2</v>
+        <v>254.68</v>
       </c>
       <c r="E325" s="17" t="n">
-        <v>-0.0583</v>
+        <v>-0.0711</v>
       </c>
       <c r="F325" s="16" t="n">
-        <v>0.0185</v>
+        <v>0.004699999999999999</v>
       </c>
       <c r="G325" s="18" t="n">
         <v>46332</v>
@@ -24863,7 +24863,7 @@
         <v>384</v>
       </c>
       <c r="M325" s="16" t="n">
-        <v>0.4872192099147948</v>
+        <v>0.5077744620700486</v>
       </c>
       <c r="N325" s="14" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
         <v>380</v>
       </c>
       <c r="P325" s="16" t="n">
-        <v>0.471727343144849</v>
+        <v>0.4920684780901523</v>
       </c>
       <c r="Q325" s="21" t="inlineStr"/>
       <c r="R325" s="20" t="n"/>
@@ -24917,13 +24917,13 @@
         </is>
       </c>
       <c r="D326" s="4" t="n">
-        <v>65.47</v>
+        <v>65.33</v>
       </c>
       <c r="E326" s="5" t="n">
-        <v>-0.0728</v>
+        <v>-0.07480000000000001</v>
       </c>
       <c r="F326" s="5" t="n">
-        <v>-0.1017</v>
+        <v>-0.1036</v>
       </c>
       <c r="G326" s="7" t="n">
         <v>46324</v>
@@ -24952,7 +24952,7 @@
         <v>79</v>
       </c>
       <c r="M326" s="6" t="n">
-        <v>0.2066595387200245</v>
+        <v>0.2092453696617175</v>
       </c>
       <c r="N326" s="3" t="inlineStr"/>
       <c r="O326" s="9" t="n"/>
@@ -25004,13 +25004,13 @@
         </is>
       </c>
       <c r="D327" s="15" t="n">
-        <v>117.43</v>
+        <v>117.46</v>
       </c>
       <c r="E327" s="17" t="n">
-        <v>-0.0499</v>
+        <v>-0.04969999999999999</v>
       </c>
       <c r="F327" s="17" t="n">
-        <v>-0.0669</v>
+        <v>-0.0667</v>
       </c>
       <c r="G327" s="18" t="n">
         <v>46331</v>
@@ -25039,7 +25039,7 @@
         <v>136</v>
       </c>
       <c r="M327" s="16" t="n">
-        <v>0.1581367623264923</v>
+        <v>0.1578409671377491</v>
       </c>
       <c r="N327" s="14" t="inlineStr">
         <is>
@@ -25050,7 +25050,7 @@
         <v>140</v>
       </c>
       <c r="P327" s="16" t="n">
-        <v>0.1921996082772715</v>
+        <v>0.1918951132300358</v>
       </c>
       <c r="Q327" s="21" t="inlineStr">
         <is>
@@ -25091,13 +25091,13 @@
         </is>
       </c>
       <c r="D328" s="4" t="n">
-        <v>101.89</v>
+        <v>102.01</v>
       </c>
       <c r="E328" s="5" t="n">
-        <v>-0.0563</v>
+        <v>-0.0551</v>
       </c>
       <c r="F328" s="5" t="n">
-        <v>-0.08960000000000001</v>
+        <v>-0.0885</v>
       </c>
       <c r="G328" s="7" t="n">
         <v>46330</v>
@@ -25126,7 +25126,7 @@
         <v>131</v>
       </c>
       <c r="M328" s="6" t="n">
-        <v>0.2857002649916577</v>
+        <v>0.2841878247230663</v>
       </c>
       <c r="N328" s="3" t="inlineStr">
         <is>
@@ -25137,7 +25137,7 @@
         <v>121</v>
       </c>
       <c r="P328" s="6" t="n">
-        <v>0.1875552065953479</v>
+        <v>0.1861582197823742</v>
       </c>
       <c r="Q328" s="10" t="inlineStr">
         <is>
@@ -25182,13 +25182,13 @@
         </is>
       </c>
       <c r="D329" s="15" t="n">
-        <v>80.64</v>
+        <v>80.53</v>
       </c>
       <c r="E329" s="17" t="n">
-        <v>-0.0613</v>
+        <v>-0.0626</v>
       </c>
       <c r="F329" s="17" t="n">
-        <v>-0.08359999999999999</v>
+        <v>-0.0849</v>
       </c>
       <c r="G329" s="18" t="n">
         <v>46322</v>
@@ -25224,7 +25224,7 @@
         <v>107</v>
       </c>
       <c r="P329" s="16" t="n">
-        <v>0.3268849206349206</v>
+        <v>0.3286973798584378</v>
       </c>
       <c r="Q329" s="21" t="inlineStr">
         <is>
@@ -25273,13 +25273,13 @@
         </is>
       </c>
       <c r="D330" s="4" t="n">
-        <v>53.01</v>
+        <v>53.31</v>
       </c>
       <c r="E330" s="5" t="n">
-        <v>-0.03759999999999999</v>
+        <v>-0.0321</v>
       </c>
       <c r="F330" s="5" t="n">
-        <v>-0.09480000000000001</v>
+        <v>-0.0897</v>
       </c>
       <c r="G330" s="7" t="n"/>
       <c r="H330" s="12" t="inlineStr">
@@ -25298,7 +25298,7 @@
         <v>63</v>
       </c>
       <c r="M330" s="6" t="n">
-        <v>0.1884550084889644</v>
+        <v>0.1817670230725942</v>
       </c>
       <c r="N330" s="3" t="inlineStr"/>
       <c r="O330" s="9" t="n"/>
@@ -25342,13 +25342,13 @@
         </is>
       </c>
       <c r="D331" s="15" t="n">
-        <v>38.19</v>
+        <v>38.01</v>
       </c>
       <c r="E331" s="17" t="n">
-        <v>-0.1106</v>
+        <v>-0.1148</v>
       </c>
       <c r="F331" s="17" t="n">
-        <v>-0.08</v>
+        <v>-0.0843</v>
       </c>
       <c r="G331" s="18" t="n">
         <v>46336</v>
@@ -25403,13 +25403,13 @@
         </is>
       </c>
       <c r="D332" s="4" t="n">
-        <v>8.640000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E332" s="5" t="n">
-        <v>-0.07049999999999999</v>
+        <v>-0.1071</v>
       </c>
       <c r="F332" s="6" t="n">
-        <v>0.0848</v>
+        <v>0.0421</v>
       </c>
       <c r="G332" s="7" t="n">
         <v>46331</v>
@@ -25464,13 +25464,13 @@
         </is>
       </c>
       <c r="D333" s="15" t="n">
-        <v>85.97</v>
+        <v>85.53</v>
       </c>
       <c r="E333" s="17" t="n">
-        <v>-0.0675</v>
+        <v>-0.0723</v>
       </c>
       <c r="F333" s="17" t="n">
-        <v>-0.08990000000000001</v>
+        <v>-0.0946</v>
       </c>
       <c r="G333" s="18" t="n">
         <v>46324</v>
@@ -25499,7 +25499,7 @@
         <v>99</v>
       </c>
       <c r="M333" s="16" t="n">
-        <v>0.1515644992439223</v>
+        <v>0.1574886004910558</v>
       </c>
       <c r="N333" s="14" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>112</v>
       </c>
       <c r="P333" s="16" t="n">
-        <v>0.3027800395486798</v>
+        <v>0.3094820530807904</v>
       </c>
       <c r="Q333" s="21" t="inlineStr">
         <is>
@@ -25551,13 +25551,13 @@
         </is>
       </c>
       <c r="D334" s="4" t="n">
-        <v>103.54</v>
+        <v>103.22</v>
       </c>
       <c r="E334" s="5" t="n">
-        <v>-0.053</v>
+        <v>-0.05599999999999999</v>
       </c>
       <c r="F334" s="5" t="n">
-        <v>-0.08</v>
+        <v>-0.08289999999999999</v>
       </c>
       <c r="G334" s="7" t="n">
         <v>46324</v>
@@ -25586,7 +25586,7 @@
         <v>127</v>
       </c>
       <c r="M334" s="6" t="n">
-        <v>0.2265790998647865</v>
+        <v>0.2303817089711296</v>
       </c>
       <c r="N334" s="3" t="inlineStr"/>
       <c r="O334" s="9" t="n"/>
@@ -37810,7 +37810,7 @@
     <row r="2">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>Data as of September 18, 2026 at 14:39 UTC</t>
+          <t>Data as of September 18, 2026 at 20:00 UTC</t>
         </is>
       </c>
     </row>

--- a/earnings-data.xlsx
+++ b/earnings-data.xlsx
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>104.38</v>
+        <v>104.23</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>-0.0315</v>
+        <v>-0.0329</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>0.1244</v>
+        <v>0.1228</v>
       </c>
       <c r="G2" s="7" t="n">
         <v>46338</v>
@@ -878,7 +878,7 @@
         <v>125</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.197547422877946</v>
+        <v>0.199270843327257</v>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>144</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.3795746311553938</v>
+        <v>0.3815600115130001</v>
       </c>
       <c r="Q2" s="10" t="inlineStr">
         <is>
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="D3" s="15" t="n">
-        <v>356.03</v>
+        <v>354.97</v>
       </c>
       <c r="E3" s="16" t="n">
-        <v>0.0325</v>
+        <v>0.0294</v>
       </c>
       <c r="F3" s="16" t="n">
-        <v>0.1207</v>
+        <v>0.1173</v>
       </c>
       <c r="G3" s="17" t="n">
         <v>46322</v>
@@ -973,7 +973,7 @@
         <v>438</v>
       </c>
       <c r="M3" s="16" t="n">
-        <v>0.230233407297138</v>
+        <v>0.2339070907400624</v>
       </c>
       <c r="N3" s="14" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>420</v>
       </c>
       <c r="P3" s="16" t="n">
-        <v>0.1796758700109542</v>
+        <v>0.1831985801617037</v>
       </c>
       <c r="Q3" s="20" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>728.6</v>
+        <v>741.24</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>0.325</v>
+        <v>0.348</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.2021</v>
+        <v>0.223</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>46330</v>
@@ -1064,7 +1064,7 @@
         <v>835</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.1460334888827889</v>
+        <v>0.1264907452377098</v>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>930</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.2764205325281361</v>
+        <v>0.2546543629593654</v>
       </c>
       <c r="Q4" s="10" t="inlineStr">
         <is>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="D5" s="15" t="n">
-        <v>43.13</v>
+        <v>43.16</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>0.0553</v>
+        <v>0.05599999999999999</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>0.1532</v>
+        <v>0.154</v>
       </c>
       <c r="G5" s="17" t="n">
         <v>46329</v>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>73.68000000000001</v>
+        <v>73.36</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>-0.0742</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.0696</v>
+        <v>0.0649</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>46315</v>
@@ -1220,7 +1220,7 @@
         <v>80</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.08577633007600424</v>
+        <v>0.0905125408942203</v>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>100</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.3572204125950053</v>
+        <v>0.3631406761177753</v>
       </c>
       <c r="Q6" s="10" t="inlineStr">
         <is>
@@ -1272,13 +1272,13 @@
         </is>
       </c>
       <c r="D7" s="15" t="n">
-        <v>75.38</v>
+        <v>75.59</v>
       </c>
       <c r="E7" s="25" t="n">
-        <v>-0.139</v>
+        <v>-0.1365</v>
       </c>
       <c r="F7" s="25" t="n">
-        <v>-0.03240000000000001</v>
+        <v>-0.0297</v>
       </c>
       <c r="G7" s="17" t="n">
         <v>46315</v>
@@ -1307,7 +1307,7 @@
         <v>91</v>
       </c>
       <c r="M7" s="16" t="n">
-        <v>0.207216768373574</v>
+        <v>0.2038629448339727</v>
       </c>
       <c r="N7" s="14" t="inlineStr"/>
       <c r="O7" s="19" t="n"/>
@@ -1351,13 +1351,13 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>517.9</v>
+        <v>516.77</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-0.0296</v>
+        <v>-0.0318</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.1043</v>
+        <v>0.1019</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>46329</v>
@@ -1386,7 +1386,7 @@
         <v>569.9299999999999</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.1004634099246958</v>
+        <v>0.1028697486309189</v>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>648.04</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.2512840316663448</v>
+        <v>0.2540201637091936</v>
       </c>
       <c r="Q8" s="10" t="inlineStr">
         <is>
@@ -1438,13 +1438,13 @@
         </is>
       </c>
       <c r="D9" s="15" t="n">
-        <v>192.37</v>
+        <v>191.12</v>
       </c>
       <c r="E9" s="25" t="n">
-        <v>-0.004</v>
+        <v>-0.0105</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>0.0721</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="G9" s="17" t="n">
         <v>46330</v>
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>167.25</v>
+        <v>165.27</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-0.0863</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-0.0186</v>
+        <v>-0.0302</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>46317</v>
@@ -1542,7 +1542,7 @@
         <v>170</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.0164424514200299</v>
+        <v>0.02861983421068548</v>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>270</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.6143497757847534</v>
+        <v>0.6336903249228534</v>
       </c>
       <c r="Q10" s="10" t="inlineStr">
         <is>
@@ -1594,13 +1594,13 @@
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>48.08</v>
+        <v>47.68</v>
       </c>
       <c r="E11" s="25" t="n">
-        <v>-0.0276</v>
+        <v>-0.0358</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>0.0973</v>
+        <v>0.08810000000000001</v>
       </c>
       <c r="G11" s="17" t="n">
         <v>46316</v>
@@ -1629,7 +1629,7 @@
         <v>43</v>
       </c>
       <c r="M11" s="25" t="n">
-        <v>-0.105657237936772</v>
+        <v>-0.09815436241610738</v>
       </c>
       <c r="N11" s="14" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>50</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>0.03993344425956742</v>
+        <v>0.04865771812080538</v>
       </c>
       <c r="Q11" s="20" t="inlineStr">
         <is>
@@ -1685,13 +1685,13 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>166.47</v>
+        <v>166.84</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-0.1112</v>
+        <v>-0.1092</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.2101</v>
+        <v>0.2128</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>46331</v>
@@ -1720,7 +1720,7 @@
         <v>181</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.08728299393284077</v>
+        <v>0.08487173339726682</v>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>155</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>-0.06890130353817504</v>
+        <v>-0.0709661951570367</v>
       </c>
       <c r="Q12" s="10" t="inlineStr">
         <is>
@@ -1772,13 +1772,13 @@
         </is>
       </c>
       <c r="D13" s="15" t="n">
-        <v>257.81</v>
+        <v>258.45</v>
       </c>
       <c r="E13" s="25" t="n">
-        <v>-0.0032</v>
+        <v>-0.0007000000000000001</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>0.1034</v>
+        <v>0.1061</v>
       </c>
       <c r="G13" s="17" t="n">
         <v>46324</v>
@@ -1807,7 +1807,7 @@
         <v>322</v>
       </c>
       <c r="M13" s="16" t="n">
-        <v>0.2489818083084442</v>
+        <v>0.2458889533758948</v>
       </c>
       <c r="N13" s="14" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>285</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>0.1054652651177223</v>
+        <v>0.1027278003482299</v>
       </c>
       <c r="Q13" s="20" t="inlineStr">
         <is>
@@ -1871,13 +1871,13 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2840.74</v>
+        <v>2803.25</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-0.0396</v>
+        <v>-0.05230000000000001</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>-0.0283</v>
+        <v>-0.0411</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>46287</v>
@@ -1906,7 +1906,7 @@
         <v>4150</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.4608869519913826</v>
+        <v>0.4804245072683492</v>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>3700</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.3024775234621966</v>
+        <v>0.3198965486488897</v>
       </c>
       <c r="Q14" s="10" t="inlineStr">
         <is>
@@ -1958,13 +1958,13 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>94.19</v>
+        <v>93.22</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.08529999999999999</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>0.1156</v>
+        <v>0.1041</v>
       </c>
       <c r="G15" s="17" t="n"/>
       <c r="H15" s="22" t="inlineStr">
@@ -1983,7 +1983,7 @@
         <v>65</v>
       </c>
       <c r="M15" s="25" t="n">
-        <v>-0.3099055101390806</v>
+        <v>-0.3027247371808625</v>
       </c>
       <c r="N15" s="14" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>85</v>
       </c>
       <c r="P15" s="25" t="n">
-        <v>-0.09756874402802843</v>
+        <v>-0.08817850246728169</v>
       </c>
       <c r="Q15" s="20" t="inlineStr"/>
       <c r="R15" s="19" t="n"/>
@@ -2029,13 +2029,13 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>168.01</v>
+        <v>168.52</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-0.1985</v>
+        <v>-0.1961</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-0.0279</v>
+        <v>-0.0249</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>46322</v>
@@ -2064,7 +2064,7 @@
         <v>214</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.2737337063270044</v>
+        <v>0.2698789461191549</v>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>245</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.4582465329444677</v>
+        <v>0.453833372893425</v>
       </c>
       <c r="Q16" s="10" t="inlineStr">
         <is>
@@ -2124,13 +2124,13 @@
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>247.55</v>
+        <v>251.8</v>
       </c>
       <c r="E17" s="25" t="n">
-        <v>-0.2418</v>
+        <v>-0.2288</v>
       </c>
       <c r="F17" s="25" t="n">
-        <v>-0.2708</v>
+        <v>-0.2583</v>
       </c>
       <c r="G17" s="17" t="n"/>
       <c r="H17" s="22" t="inlineStr">
@@ -2149,7 +2149,7 @@
         <v>375</v>
       </c>
       <c r="M17" s="16" t="n">
-        <v>0.5148454857604524</v>
+        <v>0.489277204130262</v>
       </c>
       <c r="N17" s="14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>375</v>
       </c>
       <c r="P17" s="16" t="n">
-        <v>0.5148454857604524</v>
+        <v>0.489277204130262</v>
       </c>
       <c r="Q17" s="20" t="inlineStr"/>
       <c r="R17" s="19" t="n"/>
@@ -2199,13 +2199,13 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>33.28</v>
+        <v>33.14</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>-0.098</v>
+        <v>-0.1019</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0.0398</v>
+        <v>0.0353</v>
       </c>
       <c r="G18" s="7" t="n">
         <v>46323</v>
@@ -2234,7 +2234,7 @@
         <v>45</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.3521634615384615</v>
+        <v>0.3578756789378394</v>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>45</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.3521634615384615</v>
+        <v>0.3578756789378394</v>
       </c>
       <c r="Q18" s="10" t="inlineStr">
         <is>
@@ -2286,13 +2286,13 @@
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>139.36</v>
+        <v>139.25</v>
       </c>
       <c r="E19" s="25" t="n">
-        <v>-0.06059999999999999</v>
+        <v>-0.0613</v>
       </c>
       <c r="F19" s="25" t="n">
-        <v>-0.0194</v>
+        <v>-0.0202</v>
       </c>
       <c r="G19" s="17" t="n">
         <v>46324</v>
@@ -2321,7 +2321,7 @@
         <v>170</v>
       </c>
       <c r="M19" s="16" t="n">
-        <v>0.2198622273249138</v>
+        <v>0.2208258527827648</v>
       </c>
       <c r="N19" s="14" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>177</v>
       </c>
       <c r="P19" s="16" t="n">
-        <v>0.2700918484500573</v>
+        <v>0.2710951526032316</v>
       </c>
       <c r="Q19" s="20" t="inlineStr">
         <is>
@@ -2373,13 +2373,13 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>123.68</v>
+        <v>123.63</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>-0.325</v>
+        <v>-0.3253</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>-0.3948</v>
+        <v>-0.395</v>
       </c>
       <c r="G20" s="7" t="n"/>
       <c r="H20" s="12" t="inlineStr">
@@ -2398,7 +2398,7 @@
         <v>220</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.778783958602846</v>
+        <v>0.7795033567904232</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="9" t="n"/>
@@ -2442,13 +2442,13 @@
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>114.45</v>
+        <v>112.33</v>
       </c>
       <c r="E21" s="25" t="n">
-        <v>-0.1295</v>
+        <v>-0.1456</v>
       </c>
       <c r="F21" s="25" t="n">
-        <v>-0.0272</v>
+        <v>-0.0452</v>
       </c>
       <c r="G21" s="17" t="n"/>
       <c r="H21" s="22" t="inlineStr">
@@ -2493,13 +2493,13 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>84.26000000000001</v>
+        <v>83.95</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-0.0417</v>
+        <v>-0.0453</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>0.0445</v>
+        <v>0.0407</v>
       </c>
       <c r="G22" s="7" t="n">
         <v>46315</v>
@@ -2528,7 +2528,7 @@
         <v>61</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>-0.2760503204367434</v>
+        <v>-0.2733770101250745</v>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>100</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.1868027533823878</v>
+        <v>0.1911852293031566</v>
       </c>
       <c r="Q22" s="10" t="inlineStr">
         <is>
@@ -2580,13 +2580,13 @@
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>127.85</v>
+        <v>126.45</v>
       </c>
       <c r="E23" s="25" t="n">
-        <v>-0.04559999999999999</v>
+        <v>-0.0561</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>0.065</v>
+        <v>0.0533</v>
       </c>
       <c r="G23" s="17" t="n">
         <v>46315</v>
@@ -2618,7 +2618,7 @@
         <v>145</v>
       </c>
       <c r="P23" s="16" t="n">
-        <v>0.134141572154869</v>
+        <v>0.1466982997232107</v>
       </c>
       <c r="Q23" s="20" t="inlineStr"/>
       <c r="R23" s="19" t="n"/>
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>298.91</v>
+        <v>297.2</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>-0.1094</v>
+        <v>-0.1144</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>-0.0795</v>
+        <v>-0.08470000000000001</v>
       </c>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="12" t="inlineStr">
@@ -2678,7 +2678,7 @@
         <v>360</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.2043758991000635</v>
+        <v>0.2113055181695828</v>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>400</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.338195443444515</v>
+        <v>0.3458950201884253</v>
       </c>
       <c r="Q24" s="10" t="inlineStr">
         <is>
@@ -2738,13 +2738,13 @@
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>192.48</v>
+        <v>190.98</v>
       </c>
       <c r="E25" s="25" t="n">
-        <v>-0.1093</v>
+        <v>-0.1162</v>
       </c>
       <c r="F25" s="25" t="n">
-        <v>-0.04679999999999999</v>
+        <v>-0.0542</v>
       </c>
       <c r="G25" s="17" t="n"/>
       <c r="H25" s="22" t="inlineStr">
@@ -2763,7 +2763,7 @@
         <v>255</v>
       </c>
       <c r="M25" s="16" t="n">
-        <v>0.3248129675810474</v>
+        <v>0.3352183474709394</v>
       </c>
       <c r="N25" s="14" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>230</v>
       </c>
       <c r="P25" s="16" t="n">
-        <v>0.1949293433083957</v>
+        <v>0.204314587914965</v>
       </c>
       <c r="Q25" s="20" t="inlineStr">
         <is>
@@ -2819,13 +2819,13 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>248.7</v>
+        <v>247.88</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>-0.08210000000000001</v>
+        <v>-0.0851</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>-0.0537</v>
+        <v>-0.0568</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>46330</v>
@@ -2854,7 +2854,7 @@
         <v>300</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.2062726176115803</v>
+        <v>0.2102630304986284</v>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>350</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.407318053880177</v>
+        <v>0.4119735355817331</v>
       </c>
       <c r="Q26" s="10" t="inlineStr">
         <is>
@@ -2906,13 +2906,13 @@
         </is>
       </c>
       <c r="D27" s="15" t="n">
-        <v>36.28</v>
+        <v>36.1</v>
       </c>
       <c r="E27" s="25" t="n">
-        <v>-0.1098</v>
+        <v>-0.1143</v>
       </c>
       <c r="F27" s="25" t="n">
-        <v>-0.1148</v>
+        <v>-0.1193</v>
       </c>
       <c r="G27" s="17" t="n">
         <v>46289</v>
@@ -2967,13 +2967,13 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>83.47</v>
+        <v>82.88</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-0.0699</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>-0.0306</v>
+        <v>-0.0375</v>
       </c>
       <c r="G28" s="7" t="n">
         <v>46323</v>
@@ -3002,7 +3002,7 @@
         <v>110</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.3178387444590871</v>
+        <v>0.3272200772200773</v>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>115</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.3777405055708638</v>
+        <v>0.3875482625482626</v>
       </c>
       <c r="Q28" s="10" t="inlineStr">
         <is>
@@ -3058,13 +3058,13 @@
         </is>
       </c>
       <c r="D29" s="15" t="n">
-        <v>169.85</v>
+        <v>167.92</v>
       </c>
       <c r="E29" s="25" t="n">
-        <v>-0.0964</v>
+        <v>-0.1067</v>
       </c>
       <c r="F29" s="25" t="n">
-        <v>-0.0735</v>
+        <v>-0.08410000000000001</v>
       </c>
       <c r="G29" s="17" t="n">
         <v>46317</v>
@@ -3119,13 +3119,13 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>230</v>
+        <v>231.25</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>-0.0378</v>
+        <v>-0.0326</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>-0.0103</v>
+        <v>-0.0049</v>
       </c>
       <c r="G30" s="7" t="n"/>
       <c r="H30" s="12" t="inlineStr">
@@ -3144,7 +3144,7 @@
         <v>245</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.06521739130434782</v>
+        <v>0.05945945945945946</v>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>265</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1521739130434783</v>
+        <v>0.145945945945946</v>
       </c>
       <c r="Q30" s="10" t="inlineStr">
         <is>
@@ -3196,13 +3196,13 @@
         </is>
       </c>
       <c r="D31" s="15" t="n">
-        <v>94.48</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="E31" s="25" t="n">
-        <v>-0.1177</v>
+        <v>-0.1137</v>
       </c>
       <c r="F31" s="25" t="n">
-        <v>-0.08460000000000001</v>
+        <v>-0.0805</v>
       </c>
       <c r="G31" s="17" t="n">
         <v>46330</v>
@@ -3231,7 +3231,7 @@
         <v>120</v>
       </c>
       <c r="M31" s="16" t="n">
-        <v>0.2701100762066045</v>
+        <v>0.2644889357218124</v>
       </c>
       <c r="N31" s="14" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>115</v>
       </c>
       <c r="P31" s="16" t="n">
-        <v>0.2171888230313293</v>
+        <v>0.2118018967334035</v>
       </c>
       <c r="Q31" s="20" t="inlineStr">
         <is>
@@ -3283,13 +3283,13 @@
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>12.56</v>
+        <v>12.54</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>-0.0335</v>
+        <v>-0.0354</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>-0.1201</v>
+        <v>-0.1218</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>46330</v>
@@ -3344,13 +3344,13 @@
         </is>
       </c>
       <c r="D33" s="15" t="n">
-        <v>129.84</v>
+        <v>130.96</v>
       </c>
       <c r="E33" s="25" t="n">
-        <v>-0.0761</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="F33" s="25" t="n">
-        <v>-0.1541</v>
+        <v>-0.1467</v>
       </c>
       <c r="G33" s="17" t="n"/>
       <c r="H33" s="22" t="inlineStr">
@@ -3369,7 +3369,7 @@
         <v>160</v>
       </c>
       <c r="M33" s="16" t="n">
-        <v>0.2322858903265557</v>
+        <v>0.2217470983506414</v>
       </c>
       <c r="N33" s="14" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>175</v>
       </c>
       <c r="P33" s="16" t="n">
-        <v>0.3478126925446703</v>
+        <v>0.336285888821014</v>
       </c>
       <c r="Q33" s="20" t="inlineStr">
         <is>
@@ -3425,13 +3425,13 @@
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>32.65</v>
+        <v>32.33</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>-0.0665</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>0.077</v>
+        <v>0.0663</v>
       </c>
       <c r="G34" s="7" t="n">
         <v>46317</v>
@@ -3460,7 +3460,7 @@
         <v>35</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.07197549770290969</v>
+        <v>0.08258583359109192</v>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>40</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.2251148545176111</v>
+        <v>0.2372409526755336</v>
       </c>
       <c r="Q34" s="10" t="inlineStr">
         <is>
@@ -3512,13 +3512,13 @@
         </is>
       </c>
       <c r="D35" s="15" t="n">
-        <v>375.12</v>
+        <v>375.3</v>
       </c>
       <c r="E35" s="16" t="n">
-        <v>0.0338</v>
+        <v>0.0343</v>
       </c>
       <c r="F35" s="16" t="n">
-        <v>0.1734</v>
+        <v>0.1739</v>
       </c>
       <c r="G35" s="17" t="n">
         <v>46323</v>
@@ -3547,7 +3547,7 @@
         <v>130</v>
       </c>
       <c r="M35" s="25" t="n">
-        <v>-0.6534442311793559</v>
+        <v>-0.6536104449773514</v>
       </c>
       <c r="N35" s="14" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>300</v>
       </c>
       <c r="P35" s="25" t="n">
-        <v>-0.200255918106206</v>
+        <v>-0.2006394884092726</v>
       </c>
       <c r="Q35" s="20" t="inlineStr">
         <is>
@@ -3599,13 +3599,13 @@
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>70.94</v>
+        <v>70.84</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>-0.09970000000000001</v>
+        <v>-0.101</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.0295</v>
+        <v>0.028</v>
       </c>
       <c r="G36" s="7" t="n">
         <v>46329</v>
@@ -3660,13 +3660,13 @@
         </is>
       </c>
       <c r="D37" s="15" t="n">
-        <v>560</v>
+        <v>557.86</v>
       </c>
       <c r="E37" s="16" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.0698</v>
       </c>
       <c r="F37" s="16" t="n">
-        <v>0.1716</v>
+        <v>0.1672</v>
       </c>
       <c r="G37" s="17" t="n"/>
       <c r="H37" s="22" t="inlineStr">
@@ -3685,7 +3685,7 @@
         <v>450</v>
       </c>
       <c r="M37" s="25" t="n">
-        <v>-0.1964285714285714</v>
+        <v>-0.1933460007887284</v>
       </c>
       <c r="N37" s="14" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>635</v>
       </c>
       <c r="P37" s="16" t="n">
-        <v>0.1339285714285714</v>
+        <v>0.1382784211092389</v>
       </c>
       <c r="Q37" s="20" t="inlineStr">
         <is>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>95.61</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>-0.0323</v>
+        <v>-0.0335</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>-0.006</v>
+        <v>-0.0073</v>
       </c>
       <c r="G38" s="7" t="n">
         <v>46325</v>
@@ -3776,7 +3776,7 @@
         <v>110</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.1505072691141094</v>
+        <v>0.1519530840925752</v>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>105</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.09821148415437717</v>
+        <v>0.09959158027018541</v>
       </c>
       <c r="Q38" s="10" t="inlineStr">
         <is>
@@ -3832,13 +3832,13 @@
         </is>
       </c>
       <c r="D39" s="15" t="n">
-        <v>86.69</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="E39" s="25" t="n">
-        <v>-0.0481</v>
+        <v>-0.0529</v>
       </c>
       <c r="F39" s="25" t="n">
-        <v>-0.03759999999999999</v>
+        <v>-0.0424</v>
       </c>
       <c r="G39" s="17" t="n">
         <v>46325</v>
@@ -3867,7 +3867,7 @@
         <v>95</v>
       </c>
       <c r="M39" s="16" t="n">
-        <v>0.09585880724420351</v>
+        <v>0.1013215859030836</v>
       </c>
       <c r="N39" s="14" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>100</v>
       </c>
       <c r="P39" s="16" t="n">
-        <v>0.1535355865728458</v>
+        <v>0.1592858798979828</v>
       </c>
       <c r="Q39" s="20" t="inlineStr">
         <is>
@@ -3923,13 +3923,13 @@
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>896.3200000000001</v>
+        <v>898.48</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>-0.05429999999999999</v>
+        <v>-0.052</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>-0.0321</v>
+        <v>-0.0298</v>
       </c>
       <c r="G40" s="7" t="n">
         <v>46289</v>
@@ -3958,7 +3958,7 @@
         <v>1000</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.1156729739378793</v>
+        <v>0.1129908289555694</v>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>1100</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.2272402713316672</v>
+        <v>0.2242899118511263</v>
       </c>
       <c r="Q40" s="10" t="inlineStr">
         <is>
@@ -4018,13 +4018,13 @@
         </is>
       </c>
       <c r="D41" s="15" t="n">
-        <v>123.44</v>
-      </c>
-      <c r="E41" s="16" t="n">
-        <v>0.0002</v>
+        <v>121.91</v>
+      </c>
+      <c r="E41" s="25" t="n">
+        <v>-0.0122</v>
       </c>
       <c r="F41" s="16" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.05860000000000001</v>
       </c>
       <c r="G41" s="17" t="n"/>
       <c r="H41" s="22" t="inlineStr">
@@ -4043,7 +4043,7 @@
         <v>125</v>
       </c>
       <c r="M41" s="16" t="n">
-        <v>0.01263771872974726</v>
+        <v>0.02534656713969324</v>
       </c>
       <c r="N41" s="14" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>135</v>
       </c>
       <c r="P41" s="16" t="n">
-        <v>0.09364873622812704</v>
+        <v>0.1073742925108687</v>
       </c>
       <c r="Q41" s="20" t="inlineStr">
         <is>
@@ -4095,13 +4095,13 @@
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>24.42</v>
+        <v>24.37</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>-0.0453</v>
+        <v>-0.0473</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>-0.0371</v>
+        <v>-0.039</v>
       </c>
       <c r="G42" s="7" t="n">
         <v>46330</v>
@@ -4156,13 +4156,13 @@
         </is>
       </c>
       <c r="D43" s="15" t="n">
-        <v>87.84999999999999</v>
+        <v>87.12</v>
       </c>
       <c r="E43" s="25" t="n">
-        <v>-0.0357</v>
+        <v>-0.0437</v>
       </c>
       <c r="F43" s="16" t="n">
-        <v>0.0823</v>
+        <v>0.0733</v>
       </c>
       <c r="G43" s="17" t="n">
         <v>46315</v>
@@ -4191,7 +4191,7 @@
         <v>90</v>
       </c>
       <c r="M43" s="16" t="n">
-        <v>0.02447353443369386</v>
+        <v>0.03305785123966937</v>
       </c>
       <c r="N43" s="14" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>88</v>
       </c>
       <c r="P43" s="16" t="n">
-        <v>0.001707455890722888</v>
+        <v>0.01010101010101005</v>
       </c>
       <c r="Q43" s="20" t="inlineStr">
         <is>
@@ -4251,13 +4251,13 @@
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>60.23</v>
+        <v>59.69</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>0.04019999999999999</v>
+        <v>0.0309</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="G44" s="7" t="n"/>
       <c r="H44" s="12" t="inlineStr">
@@ -4276,7 +4276,7 @@
         <v>58</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>-0.03702473850240739</v>
+        <v>-0.02831295024292172</v>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>78</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.2950356964967625</v>
+        <v>0.3067515496733121</v>
       </c>
       <c r="Q44" s="10" t="inlineStr">
         <is>
@@ -4328,13 +4328,13 @@
         </is>
       </c>
       <c r="D45" s="15" t="n">
-        <v>60.59</v>
+        <v>60.17</v>
       </c>
       <c r="E45" s="25" t="n">
-        <v>-0.0599</v>
+        <v>-0.0664</v>
       </c>
       <c r="F45" s="16" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.002</v>
       </c>
       <c r="G45" s="17" t="n">
         <v>46322</v>
@@ -4363,7 +4363,7 @@
         <v>70</v>
       </c>
       <c r="M45" s="16" t="n">
-        <v>0.1553061561313747</v>
+        <v>0.1633704503905601</v>
       </c>
       <c r="N45" s="14" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>71</v>
       </c>
       <c r="P45" s="16" t="n">
-        <v>0.1718105297903944</v>
+        <v>0.1799900282532823</v>
       </c>
       <c r="Q45" s="20" t="inlineStr">
         <is>
@@ -4423,13 +4423,13 @@
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>49.35</v>
+        <v>48.89</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>-0.1095</v>
+        <v>-0.1177</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>-0.0168</v>
+        <v>-0.0259</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>46296</v>
@@ -4494,13 +4494,13 @@
         </is>
       </c>
       <c r="D47" s="15" t="n">
-        <v>44.22</v>
+        <v>44</v>
       </c>
       <c r="E47" s="25" t="n">
-        <v>-0.0746</v>
+        <v>-0.0793</v>
       </c>
       <c r="F47" s="25" t="n">
-        <v>-0.0546</v>
+        <v>-0.0594</v>
       </c>
       <c r="G47" s="17" t="n">
         <v>46331</v>
@@ -4555,13 +4555,13 @@
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>68.75</v>
+        <v>68.53</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>0.0403</v>
+        <v>0.0369</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>-0.0461</v>
+        <v>-0.0493</v>
       </c>
       <c r="G48" s="7" t="n">
         <v>46324</v>
@@ -4616,13 +4616,13 @@
         </is>
       </c>
       <c r="D49" s="15" t="n">
-        <v>129.42</v>
+        <v>129.59</v>
       </c>
       <c r="E49" s="25" t="n">
-        <v>-0.098</v>
+        <v>-0.0968</v>
       </c>
       <c r="F49" s="25" t="n">
-        <v>-0.04099999999999999</v>
+        <v>-0.0397</v>
       </c>
       <c r="G49" s="17" t="n">
         <v>46303</v>
@@ -4651,7 +4651,7 @@
         <v>140</v>
       </c>
       <c r="M49" s="16" t="n">
-        <v>0.08174934322361314</v>
+        <v>0.08033027239756151</v>
       </c>
       <c r="N49" s="14" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>150</v>
       </c>
       <c r="P49" s="16" t="n">
-        <v>0.1590171534538712</v>
+        <v>0.1574967204259588</v>
       </c>
       <c r="Q49" s="20" t="inlineStr">
         <is>
@@ -4711,13 +4711,13 @@
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>146.6</v>
+        <v>146.08</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>0.0132</v>
+        <v>0.0097</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>-0.0026</v>
+        <v>-0.0061</v>
       </c>
       <c r="G50" s="7" t="n">
         <v>46318</v>
@@ -4746,7 +4746,7 @@
         <v>164</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0.1186903137789905</v>
+        <v>0.1226725082146768</v>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>162</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.1050477489768077</v>
+        <v>0.1089813800657173</v>
       </c>
       <c r="Q50" s="10" t="inlineStr">
         <is>
@@ -4810,13 +4810,13 @@
         </is>
       </c>
       <c r="D51" s="15" t="n">
-        <v>78.68000000000001</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="E51" s="25" t="n">
-        <v>-0.0644</v>
+        <v>-0.0674</v>
       </c>
       <c r="F51" s="25" t="n">
-        <v>-0.0373</v>
+        <v>-0.0404</v>
       </c>
       <c r="G51" s="17" t="n">
         <v>46322</v>
@@ -4845,7 +4845,7 @@
         <v>100</v>
       </c>
       <c r="M51" s="16" t="n">
-        <v>0.2709710218607015</v>
+        <v>0.2750223128904755</v>
       </c>
       <c r="N51" s="14" t="inlineStr"/>
       <c r="O51" s="19" t="n"/>
@@ -4889,13 +4889,13 @@
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>158.42</v>
+        <v>157.71</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>-0.0424</v>
+        <v>-0.0467</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>0.178</v>
+        <v>0.1727</v>
       </c>
       <c r="G52" s="7" t="n"/>
       <c r="H52" s="12" t="inlineStr">
@@ -4914,7 +4914,7 @@
         <v>140</v>
       </c>
       <c r="M52" s="5" t="n">
-        <v>-0.1162731978285569</v>
+        <v>-0.1122947181535731</v>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>135</v>
       </c>
       <c r="P52" s="5" t="n">
-        <v>-0.1478348693346799</v>
+        <v>-0.1439984782195169</v>
       </c>
       <c r="Q52" s="10" t="inlineStr">
         <is>
@@ -4970,13 +4970,13 @@
         </is>
       </c>
       <c r="D53" s="15" t="n">
-        <v>107.57</v>
+        <v>107.44</v>
       </c>
       <c r="E53" s="16" t="n">
-        <v>0.0374</v>
+        <v>0.0361</v>
       </c>
       <c r="F53" s="25" t="n">
-        <v>-0.0076</v>
+        <v>-0.0089</v>
       </c>
       <c r="G53" s="17" t="n"/>
       <c r="H53" s="22" t="inlineStr">
@@ -4995,7 +4995,7 @@
         <v>140</v>
       </c>
       <c r="M53" s="16" t="n">
-        <v>0.3014781072789812</v>
+        <v>0.3030528667163068</v>
       </c>
       <c r="N53" s="14" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>140</v>
       </c>
       <c r="P53" s="16" t="n">
-        <v>0.3014781072789812</v>
+        <v>0.3030528667163068</v>
       </c>
       <c r="Q53" s="20" t="inlineStr">
         <is>
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>57.35</v>
+        <v>57.83</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>-0.08</v>
+        <v>-0.0723</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>0.0225</v>
+        <v>0.031</v>
       </c>
       <c r="G54" s="7" t="n">
         <v>46317</v>
@@ -5097,7 +5097,7 @@
         <v>76</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.3251961639058413</v>
+        <v>0.3141967836762926</v>
       </c>
       <c r="Q54" s="10" t="inlineStr">
         <is>
@@ -5138,13 +5138,13 @@
         </is>
       </c>
       <c r="D55" s="15" t="n">
-        <v>127.54</v>
+        <v>127.53</v>
       </c>
       <c r="E55" s="25" t="n">
-        <v>-0.05429999999999999</v>
+        <v>-0.0544</v>
       </c>
       <c r="F55" s="16" t="n">
-        <v>0.0611</v>
+        <v>0.061</v>
       </c>
       <c r="G55" s="17" t="n">
         <v>46331</v>
@@ -5173,7 +5173,7 @@
         <v>183</v>
       </c>
       <c r="M55" s="16" t="n">
-        <v>0.4348439705190528</v>
+        <v>0.4349564808280404</v>
       </c>
       <c r="N55" s="14" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>145</v>
       </c>
       <c r="P55" s="16" t="n">
-        <v>0.1368982280068997</v>
+        <v>0.1369873755194856</v>
       </c>
       <c r="Q55" s="20" t="inlineStr">
         <is>
@@ -5225,13 +5225,13 @@
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>204.86</v>
+        <v>203.67</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>-0.002</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>0.0537</v>
+        <v>0.0476</v>
       </c>
       <c r="G56" s="7" t="n">
         <v>46325</v>
@@ -5260,7 +5260,7 @@
         <v>222</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>0.08366689446451228</v>
+        <v>0.08999852702901759</v>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>225</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.09831104168700569</v>
+        <v>0.104728236853734</v>
       </c>
       <c r="Q56" s="10" t="inlineStr">
         <is>
@@ -5316,13 +5316,13 @@
         </is>
       </c>
       <c r="D57" s="15" t="n">
-        <v>140.95</v>
+        <v>141.38</v>
       </c>
       <c r="E57" s="25" t="n">
-        <v>-0.0791</v>
+        <v>-0.0762</v>
       </c>
       <c r="F57" s="25" t="n">
-        <v>-0.0312</v>
+        <v>-0.0282</v>
       </c>
       <c r="G57" s="17" t="n">
         <v>46331</v>
@@ -5351,7 +5351,7 @@
         <v>196</v>
       </c>
       <c r="M57" s="16" t="n">
-        <v>0.3905640297978007</v>
+        <v>0.3863347008063376</v>
       </c>
       <c r="N57" s="14" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>170</v>
       </c>
       <c r="P57" s="16" t="n">
-        <v>0.2061014544164598</v>
+        <v>0.2024331588626397</v>
       </c>
       <c r="Q57" s="20" t="inlineStr">
         <is>
@@ -5407,13 +5407,13 @@
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>38.74</v>
+        <v>38.47</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>0.0192</v>
+        <v>0.0121</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="G58" s="7" t="n">
         <v>46324</v>
@@ -5468,13 +5468,13 @@
         </is>
       </c>
       <c r="D59" s="15" t="n">
-        <v>20.81</v>
+        <v>20.9</v>
       </c>
       <c r="E59" s="25" t="n">
-        <v>-0.0182</v>
+        <v>-0.0137</v>
       </c>
       <c r="F59" s="16" t="n">
-        <v>0.0189</v>
+        <v>0.0235</v>
       </c>
       <c r="G59" s="17" t="n">
         <v>46330</v>
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>187.87</v>
+        <v>189.27</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>-0.1084</v>
+        <v>-0.1018</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>-0.0857</v>
+        <v>-0.0789</v>
       </c>
       <c r="G60" s="7" t="n">
         <v>46328</v>
@@ -5590,13 +5590,13 @@
         </is>
       </c>
       <c r="D61" s="15" t="n">
-        <v>33.18</v>
+        <v>33.39</v>
       </c>
       <c r="E61" s="25" t="n">
-        <v>-0.0611</v>
+        <v>-0.0552</v>
       </c>
       <c r="F61" s="16" t="n">
-        <v>0.0144</v>
+        <v>0.0208</v>
       </c>
       <c r="G61" s="17" t="n">
         <v>46315</v>
@@ -5632,7 +5632,7 @@
         <v>43</v>
       </c>
       <c r="P61" s="16" t="n">
-        <v>0.2959614225437011</v>
+        <v>0.2878107217729859</v>
       </c>
       <c r="Q61" s="20" t="inlineStr">
         <is>
@@ -5677,13 +5677,13 @@
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>31.76</v>
+        <v>31.72</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>0.0253</v>
+        <v>0.0239</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>-0.0307</v>
+        <v>-0.032</v>
       </c>
       <c r="G62" s="7" t="n">
         <v>46316</v>
@@ -5712,7 +5712,7 @@
         <v>35</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>0.1020151133501259</v>
+        <v>0.1034047919293821</v>
       </c>
       <c r="N62" s="3" t="inlineStr"/>
       <c r="O62" s="9" t="n"/>
@@ -5756,13 +5756,13 @@
         </is>
       </c>
       <c r="D63" s="15" t="n">
-        <v>265.64</v>
+        <v>261.75</v>
       </c>
       <c r="E63" s="16" t="n">
-        <v>0.09369999999999999</v>
+        <v>0.07769999999999999</v>
       </c>
       <c r="F63" s="16" t="n">
-        <v>0.2834</v>
+        <v>0.2646</v>
       </c>
       <c r="G63" s="17" t="n">
         <v>46323</v>
@@ -5817,13 +5817,13 @@
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>51.3</v>
+        <v>51.76</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>-0.04769999999999999</v>
+        <v>-0.0392</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>0.0864</v>
+        <v>0.09609999999999999</v>
       </c>
       <c r="G64" s="7" t="n">
         <v>46311</v>
@@ -5859,7 +5859,7 @@
         <v>63</v>
       </c>
       <c r="P64" s="6" t="n">
-        <v>0.2280701754385966</v>
+        <v>0.2171561051004637</v>
       </c>
       <c r="Q64" s="10" t="inlineStr">
         <is>
@@ -5908,13 +5908,13 @@
         </is>
       </c>
       <c r="D65" s="15" t="n">
-        <v>41.65</v>
+        <v>41.72</v>
       </c>
       <c r="E65" s="25" t="n">
-        <v>-0.08</v>
+        <v>-0.0784</v>
       </c>
       <c r="F65" s="25" t="n">
-        <v>-0.07730000000000001</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="G65" s="17" t="n">
         <v>46328</v>
@@ -5969,13 +5969,13 @@
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>71.97</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>0.021</v>
+        <v>0.0165</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>-0.0436</v>
+        <v>-0.0478</v>
       </c>
       <c r="G66" s="7" t="n">
         <v>46328</v>
@@ -6004,7 +6004,7 @@
         <v>89</v>
       </c>
       <c r="M66" s="6" t="n">
-        <v>0.2366263720994859</v>
+        <v>0.242149337055129</v>
       </c>
       <c r="N66" s="3" t="inlineStr"/>
       <c r="O66" s="9" t="n"/>
@@ -6060,13 +6060,13 @@
         </is>
       </c>
       <c r="D67" s="15" t="n">
-        <v>158.32</v>
+        <v>158.3</v>
       </c>
       <c r="E67" s="25" t="n">
-        <v>-0.0411</v>
+        <v>-0.0412</v>
       </c>
       <c r="F67" s="16" t="n">
-        <v>0.0091</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="G67" s="17" t="n">
         <v>46325</v>
@@ -6095,7 +6095,7 @@
         <v>185</v>
       </c>
       <c r="M67" s="16" t="n">
-        <v>0.1685194542698333</v>
+        <v>0.1686670878079595</v>
       </c>
       <c r="N67" s="14" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>185</v>
       </c>
       <c r="P67" s="16" t="n">
-        <v>0.1685194542698333</v>
+        <v>0.1686670878079595</v>
       </c>
       <c r="Q67" s="20" t="inlineStr">
         <is>
@@ -6151,13 +6151,13 @@
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>115.6</v>
+        <v>115.18</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>-0.004</v>
+        <v>-0.0077</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>-0.0703</v>
+        <v>-0.0737</v>
       </c>
       <c r="G68" s="7" t="n">
         <v>46329</v>
@@ -6186,7 +6186,7 @@
         <v>120</v>
       </c>
       <c r="M68" s="6" t="n">
-        <v>0.03806228373702427</v>
+        <v>0.04184754297621109</v>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>115</v>
       </c>
       <c r="P68" s="5" t="n">
-        <v>-0.005190311418685072</v>
+        <v>-0.001562771314464376</v>
       </c>
       <c r="Q68" s="10" t="inlineStr"/>
       <c r="R68" s="9" t="n"/>
@@ -6232,13 +6232,13 @@
         </is>
       </c>
       <c r="D69" s="15" t="n">
-        <v>293.11</v>
+        <v>290.82</v>
       </c>
       <c r="E69" s="25" t="n">
-        <v>-0.1746</v>
+        <v>-0.181</v>
       </c>
       <c r="F69" s="25" t="n">
-        <v>-0.1761</v>
+        <v>-0.1826</v>
       </c>
       <c r="G69" s="17" t="n">
         <v>46325</v>
@@ -6267,7 +6267,7 @@
         <v>406</v>
       </c>
       <c r="M69" s="16" t="n">
-        <v>0.3851455085121626</v>
+        <v>0.3960525410907091</v>
       </c>
       <c r="N69" s="14" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         <v>436</v>
       </c>
       <c r="P69" s="16" t="n">
-        <v>0.4874961618504998</v>
+        <v>0.4992091327969191</v>
       </c>
       <c r="Q69" s="20" t="inlineStr">
         <is>
@@ -6315,13 +6315,13 @@
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>313.11</v>
+        <v>313.59</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>-0.06809999999999999</v>
+        <v>-0.0667</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>-0.08130000000000001</v>
+        <v>-0.0799</v>
       </c>
       <c r="G70" s="7" t="n">
         <v>46311</v>
@@ -6350,7 +6350,7 @@
         <v>415</v>
       </c>
       <c r="M70" s="6" t="n">
-        <v>0.3254127942256714</v>
+        <v>0.3233840364807553</v>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>380</v>
       </c>
       <c r="P70" s="6" t="n">
-        <v>0.2136309923030244</v>
+        <v>0.2117733346088843</v>
       </c>
       <c r="Q70" s="10" t="inlineStr">
         <is>
@@ -6410,13 +6410,13 @@
         </is>
       </c>
       <c r="D71" s="15" t="n">
-        <v>58.02</v>
+        <v>57.96</v>
       </c>
       <c r="E71" s="25" t="n">
-        <v>-0.0595</v>
+        <v>-0.0605</v>
       </c>
       <c r="F71" s="25" t="n">
-        <v>-0.0532</v>
+        <v>-0.0542</v>
       </c>
       <c r="G71" s="17" t="n">
         <v>46309</v>
@@ -6471,13 +6471,13 @@
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>1085.02</v>
+        <v>1090.27</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>-0.06179999999999999</v>
+        <v>-0.0573</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>0.0461</v>
+        <v>0.0512</v>
       </c>
       <c r="G72" s="7" t="n">
         <v>46308</v>
@@ -6509,7 +6509,7 @@
         <v>1245</v>
       </c>
       <c r="P72" s="6" t="n">
-        <v>0.1474442867412583</v>
+        <v>0.1419189741990516</v>
       </c>
       <c r="Q72" s="10" t="inlineStr">
         <is>
@@ -6554,13 +6554,13 @@
         </is>
       </c>
       <c r="D73" s="15" t="n">
-        <v>39.51</v>
+        <v>40.14</v>
       </c>
       <c r="E73" s="16" t="n">
-        <v>0.2992</v>
+        <v>0.32</v>
       </c>
       <c r="F73" s="16" t="n">
-        <v>0.63</v>
+        <v>0.6559</v>
       </c>
       <c r="G73" s="17" t="n"/>
       <c r="H73" s="22" t="inlineStr">
@@ -6605,13 +6605,13 @@
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>27.61</v>
+        <v>28.25</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>0.2093</v>
+        <v>0.2374</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>0.6640999999999999</v>
+        <v>0.7028</v>
       </c>
       <c r="G74" s="7" t="n">
         <v>46346</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="D75" s="15" t="n">
-        <v>506.56</v>
+        <v>502.01</v>
       </c>
       <c r="E75" s="16" t="n">
-        <v>0.0217</v>
+        <v>0.0125</v>
       </c>
       <c r="F75" s="16" t="n">
-        <v>0.032</v>
+        <v>0.0227</v>
       </c>
       <c r="G75" s="17" t="n">
         <v>46332</v>
@@ -6749,13 +6749,13 @@
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>65.04000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>-0.1081</v>
+        <v>-0.1182</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>-0.0106</v>
+        <v>-0.0219</v>
       </c>
       <c r="G76" s="7" t="n">
         <v>46321</v>
@@ -6784,7 +6784,7 @@
         <v>68</v>
       </c>
       <c r="M76" s="6" t="n">
-        <v>0.04551045510455094</v>
+        <v>0.057542768273717</v>
       </c>
       <c r="N76" s="3" t="inlineStr"/>
       <c r="O76" s="9" t="n"/>
@@ -6826,13 +6826,13 @@
         </is>
       </c>
       <c r="D77" s="15" t="n">
-        <v>126.9</v>
+        <v>126.41</v>
       </c>
       <c r="E77" s="25" t="n">
-        <v>-0.1149</v>
+        <v>-0.1184</v>
       </c>
       <c r="F77" s="16" t="n">
-        <v>0.0193</v>
+        <v>0.0153</v>
       </c>
       <c r="G77" s="17" t="n">
         <v>46310</v>
@@ -6891,13 +6891,13 @@
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>134.38</v>
+        <v>135.05</v>
       </c>
       <c r="E78" s="6" t="n">
-        <v>0.0207</v>
+        <v>0.0258</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>0.019</v>
+        <v>0.024</v>
       </c>
       <c r="G78" s="7" t="n">
         <v>46308</v>
@@ -6929,7 +6929,7 @@
         <v>140</v>
       </c>
       <c r="P78" s="6" t="n">
-        <v>0.04182169965768719</v>
+        <v>0.03665309144761191</v>
       </c>
       <c r="Q78" s="10" t="inlineStr">
         <is>
@@ -6978,13 +6978,13 @@
         </is>
       </c>
       <c r="D79" s="15" t="n">
-        <v>339.44</v>
+        <v>337.26</v>
       </c>
       <c r="E79" s="25" t="n">
-        <v>-0.004500000000000001</v>
+        <v>-0.0109</v>
       </c>
       <c r="F79" s="25" t="n">
-        <v>-0.0391</v>
+        <v>-0.0453</v>
       </c>
       <c r="G79" s="17" t="n">
         <v>46315</v>
@@ -7013,7 +7013,7 @@
         <v>358</v>
       </c>
       <c r="M79" s="16" t="n">
-        <v>0.05467829366014613</v>
+        <v>0.06149558204352728</v>
       </c>
       <c r="N79" s="14" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>374</v>
       </c>
       <c r="P79" s="16" t="n">
-        <v>0.1018147537119962</v>
+        <v>0.1089367253750816</v>
       </c>
       <c r="Q79" s="20" t="inlineStr">
         <is>
@@ -7069,13 +7069,13 @@
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>56.96</v>
+        <v>56.55</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>-0.0243</v>
+        <v>-0.0313</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>-0.0288</v>
+        <v>-0.0358</v>
       </c>
       <c r="G80" s="7" t="n">
         <v>46315</v>
@@ -7104,7 +7104,7 @@
         <v>57</v>
       </c>
       <c r="M80" s="6" t="n">
-        <v>0.000702247191011221</v>
+        <v>0.007957559681697663</v>
       </c>
       <c r="N80" s="3" t="inlineStr"/>
       <c r="O80" s="9" t="n"/>
@@ -7146,13 +7146,13 @@
         </is>
       </c>
       <c r="D81" s="15" t="n">
-        <v>14.86</v>
+        <v>14.76</v>
       </c>
       <c r="E81" s="16" t="n">
-        <v>0.2408</v>
+        <v>0.2321</v>
       </c>
       <c r="F81" s="25" t="n">
-        <v>-0.04769999999999999</v>
+        <v>-0.0545</v>
       </c>
       <c r="G81" s="17" t="n"/>
       <c r="H81" s="22" t="inlineStr">
@@ -7197,13 +7197,13 @@
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>398.68</v>
+        <v>397.22</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>-0.0442</v>
+        <v>-0.04769999999999999</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>0.0929</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="G82" s="7" t="n">
         <v>46330</v>
@@ -7270,13 +7270,13 @@
         </is>
       </c>
       <c r="D83" s="15" t="n">
-        <v>94.23999999999999</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="E83" s="16" t="n">
-        <v>0.0712</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="F83" s="16" t="n">
-        <v>0.5156000000000001</v>
+        <v>0.5196000000000001</v>
       </c>
       <c r="G83" s="17" t="n">
         <v>46337</v>
@@ -7331,13 +7331,13 @@
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>39.58</v>
+        <v>39.37</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>-0.1742</v>
+        <v>-0.1786</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>-0.1457</v>
+        <v>-0.1502</v>
       </c>
       <c r="G84" s="7" t="n">
         <v>46331</v>
@@ -7392,13 +7392,13 @@
         </is>
       </c>
       <c r="D85" s="15" t="n">
-        <v>952.47</v>
+        <v>959.39</v>
       </c>
       <c r="E85" s="25" t="n">
-        <v>-0.08349999999999999</v>
+        <v>-0.07690000000000001</v>
       </c>
       <c r="F85" s="25" t="n">
-        <v>-0.1137</v>
+        <v>-0.1073</v>
       </c>
       <c r="G85" s="17" t="n">
         <v>46308</v>
@@ -7427,7 +7427,7 @@
         <v>1325</v>
       </c>
       <c r="M85" s="16" t="n">
-        <v>0.3911199302865181</v>
+        <v>0.3810858983312313</v>
       </c>
       <c r="N85" s="14" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>1210</v>
       </c>
       <c r="P85" s="16" t="n">
-        <v>0.2703812193559902</v>
+        <v>0.2612180656458792</v>
       </c>
       <c r="Q85" s="20" t="inlineStr">
         <is>
@@ -7479,13 +7479,13 @@
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>133.9</v>
+        <v>132.61</v>
       </c>
       <c r="E86" s="6" t="n">
-        <v>0.03759999999999999</v>
+        <v>0.0276</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>-0.0284</v>
+        <v>-0.0377</v>
       </c>
       <c r="G86" s="7" t="n">
         <v>46324</v>
@@ -7540,13 +7540,13 @@
         </is>
       </c>
       <c r="D87" s="15" t="n">
-        <v>124.33</v>
+        <v>123.3</v>
       </c>
       <c r="E87" s="16" t="n">
-        <v>0.1499</v>
+        <v>0.1403</v>
       </c>
       <c r="F87" s="16" t="n">
-        <v>0.224</v>
+        <v>0.2138</v>
       </c>
       <c r="G87" s="17" t="n">
         <v>46330</v>
@@ -7601,13 +7601,13 @@
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>105.74</v>
+        <v>103.42</v>
       </c>
       <c r="E88" s="6" t="n">
-        <v>0.3077</v>
+        <v>0.279</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>-0.1014</v>
+        <v>-0.1211</v>
       </c>
       <c r="G88" s="7" t="n">
         <v>46329</v>
@@ -7662,13 +7662,13 @@
         </is>
       </c>
       <c r="D89" s="15" t="n">
-        <v>155.23</v>
+        <v>155.37</v>
       </c>
       <c r="E89" s="25" t="n">
-        <v>-0.0374</v>
+        <v>-0.0365</v>
       </c>
       <c r="F89" s="16" t="n">
-        <v>0.0839</v>
+        <v>0.0849</v>
       </c>
       <c r="G89" s="17" t="n">
         <v>46324</v>
@@ -7723,13 +7723,13 @@
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>153.18</v>
+        <v>151.56</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>-0.07829999999999999</v>
+        <v>-0.08810000000000001</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>0.0334</v>
+        <v>0.0225</v>
       </c>
       <c r="G90" s="7" t="n">
         <v>46329</v>
@@ -7798,13 +7798,13 @@
         </is>
       </c>
       <c r="D91" s="15" t="n">
-        <v>351.38</v>
-      </c>
-      <c r="E91" s="25" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>352.04</v>
+      </c>
+      <c r="E91" s="16" t="n">
+        <v>0.0013</v>
       </c>
       <c r="F91" s="16" t="n">
-        <v>0.0042</v>
+        <v>0.0061</v>
       </c>
       <c r="G91" s="17" t="n">
         <v>46308</v>
@@ -7833,7 +7833,7 @@
         <v>196</v>
       </c>
       <c r="M91" s="25" t="n">
-        <v>-0.4421993283624566</v>
+        <v>-0.4432450857857062</v>
       </c>
       <c r="N91" s="14" t="inlineStr"/>
       <c r="O91" s="19" t="n"/>
@@ -7877,13 +7877,13 @@
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>100.9</v>
+        <v>100.83</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>-0.0698</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>0.05139999999999999</v>
+        <v>0.0506</v>
       </c>
       <c r="G92" s="7" t="n">
         <v>46332</v>
@@ -7912,7 +7912,7 @@
         <v>375</v>
       </c>
       <c r="M92" s="6" t="n">
-        <v>2.716551040634291</v>
+        <v>2.719131210949123</v>
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         <v>368</v>
       </c>
       <c r="P92" s="6" t="n">
-        <v>2.647175421209118</v>
+        <v>2.649707428344739</v>
       </c>
       <c r="Q92" s="10" t="inlineStr">
         <is>
@@ -7976,13 +7976,13 @@
         </is>
       </c>
       <c r="D93" s="15" t="n">
-        <v>362.94</v>
+        <v>358.19</v>
       </c>
       <c r="E93" s="25" t="n">
-        <v>-0.0537</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="F93" s="16" t="n">
-        <v>0.09230000000000001</v>
+        <v>0.078</v>
       </c>
       <c r="G93" s="17" t="n">
         <v>46317</v>
@@ -8014,7 +8014,7 @@
         <v>115</v>
       </c>
       <c r="P93" s="25" t="n">
-        <v>-0.6831432192648923</v>
+        <v>-0.6789413439794523</v>
       </c>
       <c r="Q93" s="20" t="inlineStr">
         <is>
@@ -8063,13 +8063,13 @@
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>564.67</v>
+        <v>567.65</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>-0.0275</v>
+        <v>-0.0224</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>0.06480000000000001</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="G94" s="7" t="n">
         <v>46324</v>
@@ -8098,7 +8098,7 @@
         <v>366</v>
       </c>
       <c r="M94" s="5" t="n">
-        <v>-0.3518338144402925</v>
+        <v>-0.3552365013652779</v>
       </c>
       <c r="N94" s="3" t="inlineStr"/>
       <c r="O94" s="9" t="n"/>
@@ -8140,13 +8140,13 @@
         </is>
       </c>
       <c r="D95" s="15" t="n">
-        <v>1786.62</v>
+        <v>1774.64</v>
       </c>
       <c r="E95" s="25" t="n">
-        <v>-0.005</v>
+        <v>-0.0117</v>
       </c>
       <c r="F95" s="25" t="n">
-        <v>-0.0892</v>
+        <v>-0.0953</v>
       </c>
       <c r="G95" s="17" t="n">
         <v>46330</v>
@@ -8211,13 +8211,13 @@
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>205.21</v>
+        <v>206.12</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>-0.042</v>
+        <v>-0.0377</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>-0.0463</v>
+        <v>-0.0421</v>
       </c>
       <c r="G96" s="7" t="n">
         <v>46309</v>
@@ -8246,7 +8246,7 @@
         <v>668</v>
       </c>
       <c r="M96" s="6" t="n">
-        <v>2.255201988207202</v>
+        <v>2.240830584125752</v>
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>550</v>
       </c>
       <c r="P96" s="6" t="n">
-        <v>1.680181277715511</v>
+        <v>1.668348534834077</v>
       </c>
       <c r="Q96" s="10" t="inlineStr">
         <is>
@@ -8306,13 +8306,13 @@
         </is>
       </c>
       <c r="D97" s="15" t="n">
-        <v>116.46</v>
+        <v>116.47</v>
       </c>
       <c r="E97" s="16" t="n">
         <v>0.0516</v>
       </c>
       <c r="F97" s="16" t="n">
-        <v>0.0852</v>
+        <v>0.08529999999999999</v>
       </c>
       <c r="G97" s="17" t="n">
         <v>46321</v>
@@ -8341,7 +8341,7 @@
         <v>240</v>
       </c>
       <c r="M97" s="16" t="n">
-        <v>1.060793405461103</v>
+        <v>1.060616467759938</v>
       </c>
       <c r="N97" s="14" t="inlineStr">
         <is>
@@ -8352,7 +8352,7 @@
         <v>240</v>
       </c>
       <c r="P97" s="16" t="n">
-        <v>1.060793405461103</v>
+        <v>1.060616467759938</v>
       </c>
       <c r="Q97" s="20" t="inlineStr">
         <is>
@@ -8401,13 +8401,13 @@
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>233.38</v>
+        <v>233.25</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>-0.0401</v>
+        <v>-0.0406</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>-0.06370000000000001</v>
+        <v>-0.06419999999999999</v>
       </c>
       <c r="G98" s="7" t="n">
         <v>46310</v>
@@ -8436,7 +8436,7 @@
         <v>113</v>
       </c>
       <c r="M98" s="5" t="n">
-        <v>-0.5158111234895878</v>
+        <v>-0.5155412647374062</v>
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         <v>114</v>
       </c>
       <c r="P98" s="5" t="n">
-        <v>-0.5115262661753364</v>
+        <v>-0.5112540192926045</v>
       </c>
       <c r="Q98" s="10" t="inlineStr"/>
       <c r="R98" s="9" t="n"/>
@@ -8486,13 +8486,13 @@
         </is>
       </c>
       <c r="D99" s="15" t="n">
-        <v>24.5</v>
+        <v>24.18</v>
       </c>
       <c r="E99" s="16" t="n">
-        <v>0.2352</v>
+        <v>0.2194</v>
       </c>
       <c r="F99" s="16" t="n">
-        <v>0.0266</v>
+        <v>0.0134</v>
       </c>
       <c r="G99" s="17" t="n">
         <v>46324</v>
@@ -8547,13 +8547,13 @@
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>14.58</v>
-      </c>
-      <c r="E100" s="5" t="n">
-        <v>-0.0007000000000000001</v>
+        <v>14.62</v>
+      </c>
+      <c r="E100" s="6" t="n">
+        <v>0.0021</v>
       </c>
       <c r="F100" s="6" t="n">
-        <v>0.1037</v>
+        <v>0.1067</v>
       </c>
       <c r="G100" s="7" t="n">
         <v>46323</v>
@@ -8608,13 +8608,13 @@
         </is>
       </c>
       <c r="D101" s="15" t="n">
-        <v>105.63</v>
+        <v>105.38</v>
       </c>
       <c r="E101" s="25" t="n">
-        <v>-0.0356</v>
+        <v>-0.0379</v>
       </c>
       <c r="F101" s="16" t="n">
-        <v>0.092</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="G101" s="17" t="n">
         <v>46323</v>
@@ -8643,7 +8643,7 @@
         <v>285</v>
       </c>
       <c r="M101" s="16" t="n">
-        <v>1.698097131496734</v>
+        <v>1.704498007211995</v>
       </c>
       <c r="N101" s="14" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         <v>285</v>
       </c>
       <c r="P101" s="16" t="n">
-        <v>1.698097131496734</v>
+        <v>1.704498007211995</v>
       </c>
       <c r="Q101" s="20" t="inlineStr">
         <is>
@@ -8695,13 +8695,13 @@
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>406.56</v>
+        <v>404.47</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>-0.0573</v>
+        <v>-0.0622</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>-0.032</v>
+        <v>-0.03700000000000001</v>
       </c>
       <c r="G102" s="7" t="n">
         <v>46324</v>
@@ -8770,13 +8770,13 @@
         </is>
       </c>
       <c r="D103" s="15" t="n">
-        <v>49.09</v>
+        <v>49</v>
       </c>
       <c r="E103" s="25" t="n">
-        <v>-0.0264</v>
+        <v>-0.0282</v>
       </c>
       <c r="F103" s="25" t="n">
-        <v>-0.0412</v>
+        <v>-0.043</v>
       </c>
       <c r="G103" s="17" t="n">
         <v>46311</v>
@@ -8831,13 +8831,13 @@
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>367.79</v>
+        <v>369.95</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0029</v>
       </c>
       <c r="F104" s="6" t="n">
-        <v>0.046</v>
+        <v>0.0522</v>
       </c>
       <c r="G104" s="7" t="n">
         <v>46322</v>
@@ -8866,7 +8866,7 @@
         <v>525</v>
       </c>
       <c r="M104" s="6" t="n">
-        <v>0.4274450093803528</v>
+        <v>0.4191106906338695</v>
       </c>
       <c r="N104" s="3" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>543</v>
       </c>
       <c r="P104" s="6" t="n">
-        <v>0.4763859811305364</v>
+        <v>0.467765914312745</v>
       </c>
       <c r="Q104" s="10" t="inlineStr">
         <is>
@@ -8922,13 +8922,13 @@
         </is>
       </c>
       <c r="D105" s="15" t="n">
-        <v>69.59999999999999</v>
+        <v>68.79000000000001</v>
       </c>
       <c r="E105" s="16" t="n">
-        <v>0.0146</v>
+        <v>0.0028</v>
       </c>
       <c r="F105" s="25" t="n">
-        <v>-0.0522</v>
+        <v>-0.06320000000000001</v>
       </c>
       <c r="G105" s="17" t="n">
         <v>46314</v>
@@ -8957,7 +8957,7 @@
         <v>412</v>
       </c>
       <c r="M105" s="16" t="n">
-        <v>4.919540229885057</v>
+        <v>4.989242622474196</v>
       </c>
       <c r="N105" s="14" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>350</v>
       </c>
       <c r="P105" s="16" t="n">
-        <v>4.028735632183908</v>
+        <v>4.087948829771769</v>
       </c>
       <c r="Q105" s="20" t="inlineStr">
         <is>
@@ -9013,13 +9013,13 @@
         </is>
       </c>
       <c r="D106" s="4" t="n">
-        <v>77.81999999999999</v>
+        <v>77.91</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>-0.0528</v>
+        <v>-0.0517</v>
       </c>
       <c r="F106" s="6" t="n">
-        <v>0.0174</v>
+        <v>0.0186</v>
       </c>
       <c r="G106" s="7" t="n">
         <v>46331</v>
@@ -9048,7 +9048,7 @@
         <v>68</v>
       </c>
       <c r="M106" s="5" t="n">
-        <v>-0.1261886404523258</v>
+        <v>-0.1271980490309331</v>
       </c>
       <c r="N106" s="3" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>68</v>
       </c>
       <c r="P106" s="5" t="n">
-        <v>-0.1261886404523258</v>
+        <v>-0.1271980490309331</v>
       </c>
       <c r="Q106" s="10" t="inlineStr">
         <is>
@@ -9104,13 +9104,13 @@
         </is>
       </c>
       <c r="D107" s="15" t="n">
-        <v>264.69</v>
+        <v>264.48</v>
       </c>
       <c r="E107" s="25" t="n">
-        <v>-0.001</v>
+        <v>-0.0018</v>
       </c>
       <c r="F107" s="16" t="n">
-        <v>0.0302</v>
+        <v>0.0294</v>
       </c>
       <c r="G107" s="17" t="n">
         <v>46325</v>
@@ -9139,7 +9139,7 @@
         <v>295</v>
       </c>
       <c r="M107" s="16" t="n">
-        <v>0.1145113151233519</v>
+        <v>0.1153962492437991</v>
       </c>
       <c r="N107" s="14" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>246</v>
       </c>
       <c r="P107" s="25" t="n">
-        <v>-0.07061090332086591</v>
+        <v>-0.06987295825771331</v>
       </c>
       <c r="Q107" s="20" t="inlineStr">
         <is>
@@ -9187,13 +9187,13 @@
         </is>
       </c>
       <c r="D108" s="4" t="n">
-        <v>102.86</v>
+        <v>102.98</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>-0.1182</v>
+        <v>-0.1171</v>
       </c>
       <c r="F108" s="6" t="n">
-        <v>0.0209</v>
+        <v>0.0221</v>
       </c>
       <c r="G108" s="7" t="n">
         <v>46316</v>
@@ -9222,7 +9222,7 @@
         <v>112</v>
       </c>
       <c r="M108" s="6" t="n">
-        <v>0.08885864281547735</v>
+        <v>0.08758982326665368</v>
       </c>
       <c r="N108" s="3" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>120</v>
       </c>
       <c r="P108" s="6" t="n">
-        <v>0.16663426015944</v>
+        <v>0.1652748106428432</v>
       </c>
       <c r="Q108" s="10" t="inlineStr">
         <is>
@@ -9286,13 +9286,13 @@
         </is>
       </c>
       <c r="D109" s="15" t="n">
-        <v>391.74</v>
+        <v>393.16</v>
       </c>
       <c r="E109" s="25" t="n">
-        <v>-0.1083</v>
+        <v>-0.1051</v>
       </c>
       <c r="F109" s="16" t="n">
-        <v>0.0545</v>
+        <v>0.0583</v>
       </c>
       <c r="G109" s="17" t="n">
         <v>46329</v>
@@ -9321,7 +9321,7 @@
         <v>390</v>
       </c>
       <c r="M109" s="25" t="n">
-        <v>-0.004441721550007681</v>
+        <v>-0.008037440227897102</v>
       </c>
       <c r="N109" s="14" t="inlineStr">
         <is>
@@ -9369,13 +9369,13 @@
         </is>
       </c>
       <c r="D110" s="4" t="n">
-        <v>180.43</v>
+        <v>180.7</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>-0.0603</v>
+        <v>-0.05889999999999999</v>
       </c>
       <c r="F110" s="6" t="n">
-        <v>0.1795</v>
+        <v>0.1813</v>
       </c>
       <c r="G110" s="7" t="n">
         <v>46331</v>
@@ -9404,7 +9404,7 @@
         <v>161</v>
       </c>
       <c r="M110" s="5" t="n">
-        <v>-0.1076871917086959</v>
+        <v>-0.1090204759269507</v>
       </c>
       <c r="N110" s="3" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>180</v>
       </c>
       <c r="P110" s="5" t="n">
-        <v>-0.002383195699163148</v>
+        <v>-0.003873824017708847</v>
       </c>
       <c r="Q110" s="10" t="inlineStr">
         <is>
@@ -9456,13 +9456,13 @@
         </is>
       </c>
       <c r="D111" s="15" t="n">
-        <v>43.19</v>
+        <v>43.72</v>
       </c>
       <c r="E111" s="25" t="n">
-        <v>-0.1424</v>
-      </c>
-      <c r="F111" s="25" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.132</v>
+      </c>
+      <c r="F111" s="16" t="n">
+        <v>0.0032</v>
       </c>
       <c r="G111" s="17" t="n">
         <v>46323</v>
@@ -9491,7 +9491,7 @@
         <v>55</v>
       </c>
       <c r="M111" s="16" t="n">
-        <v>0.2734429266033805</v>
+        <v>0.2580054894784996</v>
       </c>
       <c r="N111" s="14" t="inlineStr">
         <is>
@@ -9502,7 +9502,7 @@
         <v>65</v>
       </c>
       <c r="P111" s="16" t="n">
-        <v>0.5049780041676315</v>
+        <v>0.4867337602927722</v>
       </c>
       <c r="Q111" s="20" t="inlineStr">
         <is>
@@ -9543,13 +9543,13 @@
         </is>
       </c>
       <c r="D112" s="4" t="n">
-        <v>313.19</v>
+        <v>316.49</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>-0.0152</v>
+        <v>-0.0049</v>
       </c>
       <c r="F112" s="6" t="n">
-        <v>0.0267</v>
+        <v>0.0375</v>
       </c>
       <c r="G112" s="7" t="n">
         <v>46330</v>
@@ -9578,7 +9578,7 @@
         <v>331</v>
       </c>
       <c r="M112" s="6" t="n">
-        <v>0.0568664389029024</v>
+        <v>0.04584663022528355</v>
       </c>
       <c r="N112" s="3" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         <v>330</v>
       </c>
       <c r="P112" s="6" t="n">
-        <v>0.05367348893642837</v>
+        <v>0.0426869727321558</v>
       </c>
       <c r="Q112" s="10" t="inlineStr">
         <is>
@@ -9638,13 +9638,13 @@
         </is>
       </c>
       <c r="D113" s="15" t="n">
-        <v>87.78</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="E113" s="25" t="n">
-        <v>-0.0563</v>
+        <v>-0.0583</v>
       </c>
       <c r="F113" s="25" t="n">
-        <v>-0.1788</v>
+        <v>-0.1805</v>
       </c>
       <c r="G113" s="17" t="n">
         <v>46330</v>
@@ -9673,7 +9673,7 @@
         <v>123</v>
       </c>
       <c r="M113" s="16" t="n">
-        <v>0.4012303485987697</v>
+        <v>0.404109589041096</v>
       </c>
       <c r="N113" s="14" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         <v>130</v>
       </c>
       <c r="P113" s="16" t="n">
-        <v>0.4809751651856915</v>
+        <v>0.4840182648401827</v>
       </c>
       <c r="Q113" s="20" t="inlineStr">
         <is>
@@ -9725,13 +9725,13 @@
         </is>
       </c>
       <c r="D114" s="4" t="n">
-        <v>213.9</v>
+        <v>215.84</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>-0.0226</v>
+        <v>-0.0138</v>
       </c>
       <c r="F114" s="6" t="n">
-        <v>0.1112</v>
+        <v>0.1212</v>
       </c>
       <c r="G114" s="7" t="n">
         <v>46315</v>
@@ -9760,7 +9760,7 @@
         <v>212</v>
       </c>
       <c r="M114" s="5" t="n">
-        <v>-0.00888265544647034</v>
+        <v>-0.0177909562638992</v>
       </c>
       <c r="N114" s="3" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         <v>205</v>
       </c>
       <c r="P114" s="5" t="n">
-        <v>-0.04160822814399254</v>
+        <v>-0.05022238695329875</v>
       </c>
       <c r="Q114" s="10" t="inlineStr">
         <is>
@@ -9816,13 +9816,13 @@
         </is>
       </c>
       <c r="D115" s="15" t="n">
-        <v>88.51000000000001</v>
+        <v>89.17</v>
       </c>
       <c r="E115" s="25" t="n">
-        <v>-0.0415</v>
+        <v>-0.0343</v>
       </c>
       <c r="F115" s="16" t="n">
-        <v>0.2558</v>
+        <v>0.2652</v>
       </c>
       <c r="G115" s="17" t="n">
         <v>46324</v>
@@ -9851,7 +9851,7 @@
         <v>85</v>
       </c>
       <c r="M115" s="25" t="n">
-        <v>-0.03965653598463456</v>
+        <v>-0.04676460693058205</v>
       </c>
       <c r="N115" s="14" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>90</v>
       </c>
       <c r="P115" s="16" t="n">
-        <v>0.01683425601626929</v>
+        <v>0.009308063249971944</v>
       </c>
       <c r="Q115" s="20" t="inlineStr">
         <is>
@@ -9903,13 +9903,13 @@
         </is>
       </c>
       <c r="D116" s="4" t="n">
-        <v>151.1</v>
+        <v>150.56</v>
       </c>
       <c r="E116" s="6" t="n">
-        <v>0.034</v>
+        <v>0.0304</v>
       </c>
       <c r="F116" s="6" t="n">
-        <v>0.1546</v>
+        <v>0.1505</v>
       </c>
       <c r="G116" s="7" t="n">
         <v>46324</v>
@@ -9938,7 +9938,7 @@
         <v>165</v>
       </c>
       <c r="M116" s="6" t="n">
-        <v>0.09199205823957649</v>
+        <v>0.09590860786397448</v>
       </c>
       <c r="N116" s="3" t="inlineStr"/>
       <c r="O116" s="9" t="n"/>
@@ -9986,13 +9986,13 @@
         </is>
       </c>
       <c r="D117" s="15" t="n">
-        <v>515.76</v>
+        <v>515.3</v>
       </c>
       <c r="E117" s="25" t="n">
-        <v>-0.07389999999999999</v>
+        <v>-0.0747</v>
       </c>
       <c r="F117" s="25" t="n">
-        <v>-0.0438</v>
+        <v>-0.0446</v>
       </c>
       <c r="G117" s="17" t="n">
         <v>46328</v>
@@ -10057,13 +10057,13 @@
         </is>
       </c>
       <c r="D118" s="4" t="n">
-        <v>398.57</v>
+        <v>401.65</v>
       </c>
       <c r="E118" s="6" t="n">
-        <v>0.0522</v>
+        <v>0.0603</v>
       </c>
       <c r="F118" s="6" t="n">
-        <v>0.2004</v>
+        <v>0.2097</v>
       </c>
       <c r="G118" s="7" t="n">
         <v>46315</v>
@@ -10092,7 +10092,7 @@
         <v>487</v>
       </c>
       <c r="M118" s="6" t="n">
-        <v>0.2218681787389919</v>
+        <v>0.2124984439188349</v>
       </c>
       <c r="N118" s="3" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>375</v>
       </c>
       <c r="P118" s="5" t="n">
-        <v>-0.05913641267531423</v>
+        <v>-0.06635130088385405</v>
       </c>
       <c r="Q118" s="10" t="inlineStr">
         <is>
@@ -10148,13 +10148,13 @@
         </is>
       </c>
       <c r="D119" s="15" t="n">
-        <v>271.35</v>
-      </c>
-      <c r="E119" s="16" t="n">
-        <v>0.004099999999999999</v>
+        <v>269.47</v>
+      </c>
+      <c r="E119" s="25" t="n">
+        <v>-0.0028</v>
       </c>
       <c r="F119" s="16" t="n">
-        <v>0.0466</v>
+        <v>0.0393</v>
       </c>
       <c r="G119" s="17" t="n">
         <v>46308</v>
@@ -10183,7 +10183,7 @@
         <v>272</v>
       </c>
       <c r="M119" s="16" t="n">
-        <v>0.002395430256126689</v>
+        <v>0.009388800237503145</v>
       </c>
       <c r="N119" s="14" t="inlineStr"/>
       <c r="O119" s="19" t="n"/>
@@ -10235,13 +10235,13 @@
         </is>
       </c>
       <c r="D120" s="4" t="n">
-        <v>1160.03</v>
+        <v>1164.89</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>-0.076</v>
+        <v>-0.0721</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>-0.0218</v>
+        <v>-0.0177</v>
       </c>
       <c r="G120" s="7" t="n">
         <v>46324</v>
@@ -10270,7 +10270,7 @@
         <v>1280</v>
       </c>
       <c r="M120" s="6" t="n">
-        <v>0.1034197391446773</v>
+        <v>0.09881619723750731</v>
       </c>
       <c r="N120" s="3" t="inlineStr">
         <is>
@@ -10330,13 +10330,13 @@
         </is>
       </c>
       <c r="D121" s="15" t="n">
-        <v>91.84</v>
+        <v>91.75</v>
       </c>
       <c r="E121" s="25" t="n">
-        <v>-0.0162</v>
+        <v>-0.0171</v>
       </c>
       <c r="F121" s="16" t="n">
-        <v>0.1199</v>
+        <v>0.1188</v>
       </c>
       <c r="G121" s="17" t="n"/>
       <c r="H121" s="22" t="inlineStr">
@@ -10355,7 +10355,7 @@
         <v>102</v>
       </c>
       <c r="M121" s="16" t="n">
-        <v>0.1106271777003484</v>
+        <v>0.111716621253406</v>
       </c>
       <c r="N121" s="14" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>105</v>
       </c>
       <c r="P121" s="16" t="n">
-        <v>0.1432926829268292</v>
+        <v>0.1444141689373297</v>
       </c>
       <c r="Q121" s="20" t="inlineStr">
         <is>
@@ -10407,13 +10407,13 @@
         </is>
       </c>
       <c r="D122" s="4" t="n">
-        <v>148.93</v>
+        <v>149.5</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>-0.0237</v>
+        <v>-0.02</v>
       </c>
       <c r="F122" s="6" t="n">
-        <v>0.1414</v>
+        <v>0.1458</v>
       </c>
       <c r="G122" s="7" t="n">
         <v>46324</v>
@@ -10442,7 +10442,7 @@
         <v>150</v>
       </c>
       <c r="M122" s="6" t="n">
-        <v>0.007184583361310636</v>
+        <v>0.003344481605351171</v>
       </c>
       <c r="N122" s="3" t="inlineStr"/>
       <c r="O122" s="9" t="n"/>
@@ -10486,13 +10486,13 @@
         </is>
       </c>
       <c r="D123" s="15" t="n">
-        <v>141.29</v>
+        <v>140.98</v>
       </c>
       <c r="E123" s="25" t="n">
-        <v>-0.1106</v>
+        <v>-0.1126</v>
       </c>
       <c r="F123" s="25" t="n">
-        <v>-0.0951</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="G123" s="17" t="n">
         <v>46322</v>
@@ -10565,13 +10565,13 @@
         </is>
       </c>
       <c r="D124" s="4" t="n">
-        <v>27.63</v>
+        <v>27.74</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>-0.0159</v>
+        <v>-0.0118</v>
       </c>
       <c r="F124" s="6" t="n">
-        <v>0.1046</v>
+        <v>0.1092</v>
       </c>
       <c r="G124" s="7" t="n">
         <v>46329</v>
@@ -10600,7 +10600,7 @@
         <v>28</v>
       </c>
       <c r="M124" s="6" t="n">
-        <v>0.01339124140427076</v>
+        <v>0.009372746935832789</v>
       </c>
       <c r="N124" s="3" t="inlineStr"/>
       <c r="O124" s="9" t="n"/>
@@ -10644,13 +10644,13 @@
         </is>
       </c>
       <c r="D125" s="15" t="n">
-        <v>273.7</v>
+        <v>274.19</v>
       </c>
       <c r="E125" s="25" t="n">
-        <v>-0.1692</v>
+        <v>-0.1677</v>
       </c>
       <c r="F125" s="25" t="n">
-        <v>-0.1419</v>
+        <v>-0.1404</v>
       </c>
       <c r="G125" s="17" t="n">
         <v>46324</v>
@@ -10679,7 +10679,7 @@
         <v>418</v>
       </c>
       <c r="M125" s="16" t="n">
-        <v>0.5272195834855682</v>
+        <v>0.5244903169335132</v>
       </c>
       <c r="N125" s="14" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>350</v>
       </c>
       <c r="P125" s="16" t="n">
-        <v>0.2787723785166241</v>
+        <v>0.2764871074802144</v>
       </c>
       <c r="Q125" s="20" t="inlineStr">
         <is>
@@ -10735,13 +10735,13 @@
         </is>
       </c>
       <c r="D126" s="4" t="n">
-        <v>656.83</v>
+        <v>658.76</v>
       </c>
       <c r="E126" s="6" t="n">
-        <v>0.0438</v>
+        <v>0.0469</v>
       </c>
       <c r="F126" s="6" t="n">
-        <v>0.1477</v>
+        <v>0.151</v>
       </c>
       <c r="G126" s="7" t="n">
         <v>46323</v>
@@ -10770,7 +10770,7 @@
         <v>615</v>
       </c>
       <c r="M126" s="5" t="n">
-        <v>-0.06368466726550255</v>
+        <v>-0.06642783411257513</v>
       </c>
       <c r="N126" s="3" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>570</v>
       </c>
       <c r="P126" s="5" t="n">
-        <v>-0.1321955452704658</v>
+        <v>-0.1347379925921428</v>
       </c>
       <c r="Q126" s="10" t="inlineStr">
         <is>
@@ -10830,13 +10830,13 @@
         </is>
       </c>
       <c r="D127" s="15" t="n">
-        <v>374.71</v>
+        <v>377.56</v>
       </c>
       <c r="E127" s="25" t="n">
-        <v>-0.0395</v>
+        <v>-0.0322</v>
       </c>
       <c r="F127" s="25" t="n">
-        <v>-0.1153</v>
+        <v>-0.1086</v>
       </c>
       <c r="G127" s="17" t="n">
         <v>46308</v>
@@ -10865,7 +10865,7 @@
         <v>526</v>
       </c>
       <c r="M127" s="16" t="n">
-        <v>0.4037522350617812</v>
+        <v>0.3931560546668079</v>
       </c>
       <c r="N127" s="14" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>480</v>
       </c>
       <c r="P127" s="16" t="n">
-        <v>0.2809906327559981</v>
+        <v>0.2713211145248437</v>
       </c>
       <c r="Q127" s="20" t="inlineStr">
         <is>
@@ -10921,13 +10921,13 @@
         </is>
       </c>
       <c r="D128" s="4" t="n">
-        <v>71.23</v>
+        <v>71.33</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>-0.08359999999999999</v>
+        <v>-0.0823</v>
       </c>
       <c r="F128" s="5" t="n">
-        <v>-0.04480000000000001</v>
+        <v>-0.0434</v>
       </c>
       <c r="G128" s="7" t="n">
         <v>46329</v>
@@ -11000,13 +11000,13 @@
         </is>
       </c>
       <c r="D129" s="15" t="n">
-        <v>270.91</v>
+        <v>269.94</v>
       </c>
       <c r="E129" s="25" t="n">
-        <v>-0.0353</v>
+        <v>-0.0387</v>
       </c>
       <c r="F129" s="16" t="n">
-        <v>0.1154</v>
+        <v>0.1114</v>
       </c>
       <c r="G129" s="17" t="n">
         <v>46330</v>
@@ -11035,7 +11035,7 @@
         <v>248</v>
       </c>
       <c r="M129" s="25" t="n">
-        <v>-0.08456683031265004</v>
+        <v>-0.08127732088612283</v>
       </c>
       <c r="N129" s="14" t="inlineStr"/>
       <c r="O129" s="19" t="n"/>
@@ -11091,13 +11091,13 @@
         </is>
       </c>
       <c r="D130" s="4" t="n">
-        <v>121.81</v>
+        <v>119.9</v>
       </c>
       <c r="E130" s="6" t="n">
-        <v>0.1404</v>
+        <v>0.1226</v>
       </c>
       <c r="F130" s="6" t="n">
-        <v>0.0387</v>
+        <v>0.0224</v>
       </c>
       <c r="G130" s="7" t="n">
         <v>46325</v>
@@ -11152,13 +11152,13 @@
         </is>
       </c>
       <c r="D131" s="15" t="n">
-        <v>242.04</v>
+        <v>241.23</v>
       </c>
       <c r="E131" s="16" t="n">
-        <v>0.0104</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F131" s="16" t="n">
-        <v>0.0037</v>
+        <v>0.0004</v>
       </c>
       <c r="G131" s="17" t="n">
         <v>46324</v>
@@ -11213,13 +11213,13 @@
         </is>
       </c>
       <c r="D132" s="4" t="n">
-        <v>201.3</v>
+        <v>201.15</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>-0.0602</v>
+        <v>-0.0609</v>
       </c>
       <c r="F132" s="5" t="n">
-        <v>-0.0379</v>
+        <v>-0.0386</v>
       </c>
       <c r="G132" s="7" t="n">
         <v>46330</v>
@@ -11248,7 +11248,7 @@
         <v>250</v>
       </c>
       <c r="M132" s="6" t="n">
-        <v>0.2419274714356681</v>
+        <v>0.2428535918468804</v>
       </c>
       <c r="N132" s="3" t="inlineStr"/>
       <c r="O132" s="9" t="n"/>
@@ -11292,13 +11292,13 @@
         </is>
       </c>
       <c r="D133" s="15" t="n">
-        <v>164.19</v>
+        <v>164.62</v>
       </c>
       <c r="E133" s="25" t="n">
-        <v>-0.0987</v>
+        <v>-0.0964</v>
       </c>
       <c r="F133" s="16" t="n">
-        <v>0.137</v>
+        <v>0.14</v>
       </c>
       <c r="G133" s="17" t="n">
         <v>46329</v>
@@ -11363,13 +11363,13 @@
         </is>
       </c>
       <c r="D134" s="4" t="n">
-        <v>821.58</v>
+        <v>816.5</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>-0.0076</v>
+        <v>-0.0138</v>
       </c>
       <c r="F134" s="5" t="n">
-        <v>-0.08160000000000001</v>
+        <v>-0.0872</v>
       </c>
       <c r="G134" s="7" t="n">
         <v>46330</v>
@@ -11398,7 +11398,7 @@
         <v>1155</v>
       </c>
       <c r="M134" s="6" t="n">
-        <v>0.4058277952238369</v>
+        <v>0.4145744029393754</v>
       </c>
       <c r="N134" s="3" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
         <v>1103</v>
       </c>
       <c r="P134" s="6" t="n">
-        <v>0.3425351152657075</v>
+        <v>0.3508879363135334</v>
       </c>
       <c r="Q134" s="10" t="inlineStr">
         <is>
@@ -11450,13 +11450,13 @@
         </is>
       </c>
       <c r="D135" s="15" t="n">
-        <v>534.25</v>
+        <v>534.78</v>
       </c>
       <c r="E135" s="25" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.09</v>
       </c>
       <c r="F135" s="25" t="n">
-        <v>-0.1967</v>
+        <v>-0.1959</v>
       </c>
       <c r="G135" s="17" t="n">
         <v>46331</v>
@@ -11485,7 +11485,7 @@
         <v>874</v>
       </c>
       <c r="M135" s="16" t="n">
-        <v>0.6359382311651849</v>
+        <v>0.6343169153670669</v>
       </c>
       <c r="N135" s="14" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>845</v>
       </c>
       <c r="P135" s="16" t="n">
-        <v>0.5816565278427702</v>
+        <v>0.5800890085642695</v>
       </c>
       <c r="Q135" s="20" t="inlineStr">
         <is>
@@ -11545,13 +11545,13 @@
         </is>
       </c>
       <c r="D136" s="4" t="n">
-        <v>198.16</v>
+        <v>196.88</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>-0.0276</v>
+        <v>-0.0339</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>-0.025</v>
+        <v>-0.0313</v>
       </c>
       <c r="G136" s="7" t="n">
         <v>46288</v>
@@ -11580,7 +11580,7 @@
         <v>250</v>
       </c>
       <c r="M136" s="6" t="n">
-        <v>0.2616067823980622</v>
+        <v>0.2698090207232832</v>
       </c>
       <c r="N136" s="3" t="inlineStr"/>
       <c r="O136" s="9" t="n"/>
@@ -11624,13 +11624,13 @@
         </is>
       </c>
       <c r="D137" s="15" t="n">
-        <v>691.8099999999999</v>
+        <v>684.73</v>
       </c>
       <c r="E137" s="16" t="n">
-        <v>0.06849999999999999</v>
+        <v>0.0575</v>
       </c>
       <c r="F137" s="16" t="n">
-        <v>0.1341</v>
+        <v>0.1225</v>
       </c>
       <c r="G137" s="17" t="n"/>
       <c r="H137" s="22" t="inlineStr">
@@ -11649,7 +11649,7 @@
         <v>750</v>
       </c>
       <c r="M137" s="16" t="n">
-        <v>0.08411268990040627</v>
+        <v>0.09532224380412714</v>
       </c>
       <c r="N137" s="14" t="inlineStr">
         <is>
@@ -11660,7 +11660,7 @@
         <v>641.29</v>
       </c>
       <c r="P137" s="25" t="n">
-        <v>-0.07302583079169134</v>
+        <v>-0.06344106436113513</v>
       </c>
       <c r="Q137" s="20" t="inlineStr">
         <is>
@@ -11701,13 +11701,13 @@
         </is>
       </c>
       <c r="D138" s="4" t="n">
-        <v>151.91</v>
+        <v>151.72</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>-0.034</v>
+        <v>-0.0352</v>
       </c>
       <c r="F138" s="6" t="n">
-        <v>0.0484</v>
+        <v>0.0471</v>
       </c>
       <c r="G138" s="7" t="n">
         <v>46330</v>
@@ -11743,7 +11743,7 @@
         <v>185</v>
       </c>
       <c r="P138" s="6" t="n">
-        <v>0.2178263445461129</v>
+        <v>0.2193514368573689</v>
       </c>
       <c r="Q138" s="10" t="inlineStr">
         <is>
@@ -11782,13 +11782,13 @@
         </is>
       </c>
       <c r="D139" s="15" t="n">
-        <v>437.82</v>
+        <v>435.43</v>
       </c>
       <c r="E139" s="16" t="n">
-        <v>0.0444</v>
+        <v>0.0387</v>
       </c>
       <c r="F139" s="16" t="n">
-        <v>0.0547</v>
+        <v>0.0489</v>
       </c>
       <c r="G139" s="17" t="n">
         <v>46329</v>
@@ -11824,7 +11824,7 @@
         <v>453</v>
       </c>
       <c r="P139" s="16" t="n">
-        <v>0.03467178292448953</v>
+        <v>0.04035091748386651</v>
       </c>
       <c r="Q139" s="20" t="inlineStr">
         <is>
@@ -11865,13 +11865,13 @@
         </is>
       </c>
       <c r="D140" s="4" t="n">
-        <v>49.39</v>
+        <v>49.65</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>-0.0365</v>
+        <v>-0.0314</v>
       </c>
       <c r="F140" s="6" t="n">
-        <v>0.0702</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="G140" s="7" t="n">
         <v>46309</v>
@@ -11944,13 +11944,13 @@
         </is>
       </c>
       <c r="D141" s="15" t="n">
-        <v>292.42</v>
+        <v>295.79</v>
       </c>
       <c r="E141" s="25" t="n">
-        <v>-0.1005</v>
+        <v>-0.0901</v>
       </c>
       <c r="F141" s="25" t="n">
-        <v>-0.0735</v>
+        <v>-0.06280000000000001</v>
       </c>
       <c r="G141" s="17" t="n">
         <v>46282</v>
@@ -11979,7 +11979,7 @@
         <v>425</v>
       </c>
       <c r="M141" s="16" t="n">
-        <v>0.4533889610833732</v>
+        <v>0.4368301835761857</v>
       </c>
       <c r="N141" s="14" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>323</v>
       </c>
       <c r="P141" s="16" t="n">
-        <v>0.1045756104233636</v>
+        <v>0.09199093951790113</v>
       </c>
       <c r="Q141" s="20" t="inlineStr">
         <is>
@@ -12031,13 +12031,13 @@
         </is>
       </c>
       <c r="D142" s="4" t="n">
-        <v>217.11</v>
+        <v>216.14</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>-0.1037</v>
+        <v>-0.1077</v>
       </c>
       <c r="F142" s="5" t="n">
-        <v>-0.0506</v>
+        <v>-0.0548</v>
       </c>
       <c r="G142" s="7" t="n"/>
       <c r="H142" s="12" t="inlineStr">
@@ -12056,7 +12056,7 @@
         <v>285</v>
       </c>
       <c r="M142" s="6" t="n">
-        <v>0.3126986320298465</v>
+        <v>0.3185898029055243</v>
       </c>
       <c r="N142" s="3" t="inlineStr"/>
       <c r="O142" s="9" t="n"/>
@@ -12104,13 +12104,13 @@
         </is>
       </c>
       <c r="D143" s="15" t="n">
-        <v>1642.3</v>
+        <v>1632.59</v>
       </c>
       <c r="E143" s="25" t="n">
-        <v>-0.008</v>
+        <v>-0.0139</v>
       </c>
       <c r="F143" s="25" t="n">
-        <v>-0.1031</v>
+        <v>-0.1084</v>
       </c>
       <c r="G143" s="17" t="n">
         <v>46317</v>
@@ -12165,13 +12165,13 @@
         </is>
       </c>
       <c r="D144" s="4" t="n">
-        <v>55.4</v>
+        <v>54.74</v>
       </c>
       <c r="E144" s="6" t="n">
-        <v>0.0568</v>
+        <v>0.0443</v>
       </c>
       <c r="F144" s="6" t="n">
-        <v>0.04019999999999999</v>
+        <v>0.0278</v>
       </c>
       <c r="G144" s="7" t="n">
         <v>46332</v>
@@ -12226,13 +12226,13 @@
         </is>
       </c>
       <c r="D145" s="15" t="n">
-        <v>354.66</v>
+        <v>353.9</v>
       </c>
       <c r="E145" s="25" t="n">
-        <v>-0.0771</v>
+        <v>-0.0791</v>
       </c>
       <c r="F145" s="25" t="n">
-        <v>-0.0711</v>
+        <v>-0.0731</v>
       </c>
       <c r="G145" s="17" t="n">
         <v>46318</v>
@@ -12261,7 +12261,7 @@
         <v>400</v>
       </c>
       <c r="M145" s="16" t="n">
-        <v>0.1278407488862572</v>
+        <v>0.1302627860977678</v>
       </c>
       <c r="N145" s="14" t="inlineStr"/>
       <c r="O145" s="19" t="n"/>
@@ -12313,13 +12313,13 @@
         </is>
       </c>
       <c r="D146" s="4" t="n">
-        <v>321.86</v>
+        <v>319.01</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>-0.0761</v>
+        <v>-0.0843</v>
       </c>
       <c r="F146" s="5" t="n">
-        <v>-0.07780000000000001</v>
+        <v>-0.0859</v>
       </c>
       <c r="G146" s="7" t="n">
         <v>46315</v>
@@ -12348,7 +12348,7 @@
         <v>390</v>
       </c>
       <c r="M146" s="6" t="n">
-        <v>0.2117069533337475</v>
+        <v>0.2225322090216608</v>
       </c>
       <c r="N146" s="3" t="inlineStr"/>
       <c r="O146" s="9" t="n"/>
@@ -12400,13 +12400,13 @@
         </is>
       </c>
       <c r="D147" s="15" t="n">
-        <v>961.45</v>
-      </c>
-      <c r="E147" s="16" t="n">
-        <v>0.0048</v>
+        <v>946.22</v>
+      </c>
+      <c r="E147" s="25" t="n">
+        <v>-0.0111</v>
       </c>
       <c r="F147" s="25" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0824</v>
       </c>
       <c r="G147" s="17" t="n">
         <v>46316</v>
@@ -12435,7 +12435,7 @@
         <v>1259</v>
       </c>
       <c r="M147" s="16" t="n">
-        <v>0.3094804722034427</v>
+        <v>0.330557375663165</v>
       </c>
       <c r="N147" s="14" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>1350</v>
       </c>
       <c r="P147" s="16" t="n">
-        <v>0.4041291798845493</v>
+        <v>0.4267295132210268</v>
       </c>
       <c r="Q147" s="20" t="inlineStr">
         <is>
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="D148" s="4" t="n">
-        <v>1272.17</v>
+        <v>1277.79</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>-0.0305</v>
+        <v>-0.0263</v>
       </c>
       <c r="F148" s="5" t="n">
-        <v>-0.0697</v>
+        <v>-0.06559999999999999</v>
       </c>
       <c r="G148" s="7" t="n">
         <v>46325</v>
@@ -12566,13 +12566,13 @@
         </is>
       </c>
       <c r="D149" s="15" t="n">
-        <v>206.87</v>
+        <v>206.48</v>
       </c>
       <c r="E149" s="25" t="n">
-        <v>-0.0418</v>
+        <v>-0.0436</v>
       </c>
       <c r="F149" s="25" t="n">
-        <v>-0.16</v>
+        <v>-0.1616</v>
       </c>
       <c r="G149" s="17" t="n">
         <v>46317</v>
@@ -12627,13 +12627,13 @@
         </is>
       </c>
       <c r="D150" s="4" t="n">
-        <v>453.75</v>
+        <v>457.49</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>-0.0346</v>
+        <v>-0.0267</v>
       </c>
       <c r="F150" s="5" t="n">
-        <v>-0.0709</v>
+        <v>-0.06320000000000001</v>
       </c>
       <c r="G150" s="7" t="n">
         <v>46322</v>
@@ -12694,13 +12694,13 @@
         </is>
       </c>
       <c r="D151" s="15" t="n">
-        <v>268.68</v>
+        <v>267.52</v>
       </c>
       <c r="E151" s="25" t="n">
-        <v>-0.0482</v>
+        <v>-0.05230000000000001</v>
       </c>
       <c r="F151" s="25" t="n">
-        <v>-0.0297</v>
+        <v>-0.0339</v>
       </c>
       <c r="G151" s="17" t="n">
         <v>46318</v>
@@ -12732,7 +12732,7 @@
         <v>272</v>
       </c>
       <c r="P151" s="16" t="n">
-        <v>0.01235670686318294</v>
+        <v>0.01674641148325366</v>
       </c>
       <c r="Q151" s="20" t="inlineStr">
         <is>
@@ -12785,13 +12785,13 @@
         </is>
       </c>
       <c r="D152" s="4" t="n">
-        <v>247.86</v>
+        <v>246.93</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>-0.0707</v>
+        <v>-0.0742</v>
       </c>
       <c r="F152" s="5" t="n">
-        <v>-0.1729</v>
+        <v>-0.176</v>
       </c>
       <c r="G152" s="7" t="n">
         <v>46324</v>
@@ -12856,13 +12856,13 @@
         </is>
       </c>
       <c r="D153" s="15" t="n">
-        <v>365.99</v>
+        <v>363.64</v>
       </c>
       <c r="E153" s="25" t="n">
-        <v>-0.0915</v>
+        <v>-0.0974</v>
       </c>
       <c r="F153" s="25" t="n">
-        <v>-0.3196</v>
+        <v>-0.324</v>
       </c>
       <c r="G153" s="17" t="n">
         <v>46323</v>
@@ -12917,13 +12917,13 @@
         </is>
       </c>
       <c r="D154" s="4" t="n">
-        <v>537.09</v>
+        <v>535.4</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>-0.047</v>
+        <v>-0.05</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>-0.0554</v>
+        <v>-0.0584</v>
       </c>
       <c r="G154" s="7" t="n">
         <v>46315</v>
@@ -12984,13 +12984,13 @@
         </is>
       </c>
       <c r="D155" s="15" t="n">
-        <v>174.28</v>
+        <v>175.36</v>
       </c>
       <c r="E155" s="25" t="n">
-        <v>-0.1559</v>
+        <v>-0.1507</v>
       </c>
       <c r="F155" s="25" t="n">
-        <v>-0.2446</v>
+        <v>-0.2399</v>
       </c>
       <c r="G155" s="17" t="n">
         <v>46330</v>
@@ -13019,7 +13019,7 @@
         <v>575</v>
       </c>
       <c r="M155" s="16" t="n">
-        <v>2.299288501262337</v>
+        <v>2.278968978102189</v>
       </c>
       <c r="N155" s="14" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>237</v>
       </c>
       <c r="P155" s="16" t="n">
-        <v>0.35988065182465</v>
+        <v>0.3515054744525546</v>
       </c>
       <c r="Q155" s="20" t="inlineStr">
         <is>
@@ -13079,13 +13079,13 @@
         </is>
       </c>
       <c r="D156" s="4" t="n">
-        <v>115.51</v>
+        <v>115.01</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>-0.0721</v>
+        <v>-0.0761</v>
       </c>
       <c r="F156" s="6" t="n">
-        <v>0.0438</v>
+        <v>0.0393</v>
       </c>
       <c r="G156" s="7" t="n">
         <v>46288</v>
@@ -13114,7 +13114,7 @@
         <v>250</v>
       </c>
       <c r="M156" s="6" t="n">
-        <v>1.164314777941304</v>
+        <v>1.173724023997913</v>
       </c>
       <c r="N156" s="3" t="inlineStr"/>
       <c r="O156" s="9" t="n"/>
@@ -13158,13 +13158,13 @@
         </is>
       </c>
       <c r="D157" s="15" t="n">
-        <v>114.33</v>
+        <v>114.73</v>
       </c>
       <c r="E157" s="25" t="n">
-        <v>-0.1275</v>
+        <v>-0.1244</v>
       </c>
       <c r="F157" s="25" t="n">
-        <v>-0.1256</v>
+        <v>-0.1225</v>
       </c>
       <c r="G157" s="17" t="n">
         <v>46315</v>
@@ -13193,7 +13193,7 @@
         <v>95</v>
       </c>
       <c r="M157" s="25" t="n">
-        <v>-0.1690719846059652</v>
+        <v>-0.1719689706266888</v>
       </c>
       <c r="N157" s="14" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>139</v>
       </c>
       <c r="P157" s="16" t="n">
-        <v>0.2157788856817983</v>
+        <v>0.2115401377146343</v>
       </c>
       <c r="Q157" s="20" t="inlineStr">
         <is>
@@ -13249,13 +13249,13 @@
         </is>
       </c>
       <c r="D158" s="4" t="n">
-        <v>963.63</v>
+        <v>958.17</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>-0.038</v>
+        <v>-0.0435</v>
       </c>
       <c r="F158" s="5" t="n">
-        <v>-0.0222</v>
+        <v>-0.0277</v>
       </c>
       <c r="G158" s="7" t="n">
         <v>46331</v>
@@ -13284,7 +13284,7 @@
         <v>125</v>
       </c>
       <c r="M158" s="5" t="n">
-        <v>-0.870282162240694</v>
+        <v>-0.8695429829779684</v>
       </c>
       <c r="N158" s="3" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>1064</v>
       </c>
       <c r="P158" s="6" t="n">
-        <v>0.1041582350072123</v>
+        <v>0.1104501288915329</v>
       </c>
       <c r="Q158" s="10" t="inlineStr">
         <is>
@@ -13340,13 +13340,13 @@
         </is>
       </c>
       <c r="D159" s="15" t="n">
-        <v>500.76</v>
+        <v>492.56</v>
       </c>
       <c r="E159" s="25" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0258</v>
       </c>
       <c r="F159" s="25" t="n">
-        <v>-0.1588</v>
+        <v>-0.1726</v>
       </c>
       <c r="G159" s="17" t="n">
         <v>46325</v>
@@ -13421,13 +13421,13 @@
         </is>
       </c>
       <c r="D160" s="4" t="n">
-        <v>422.68</v>
+        <v>424.89</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>-0.0329</v>
+        <v>-0.0279</v>
       </c>
       <c r="F160" s="5" t="n">
-        <v>-0.0824</v>
+        <v>-0.0776</v>
       </c>
       <c r="G160" s="7" t="n">
         <v>46331</v>
@@ -13482,13 +13482,13 @@
         </is>
       </c>
       <c r="D161" s="15" t="n">
-        <v>32.63</v>
+        <v>32.35</v>
       </c>
       <c r="E161" s="25" t="n">
-        <v>-0.116</v>
+        <v>-0.1235</v>
       </c>
       <c r="F161" s="25" t="n">
-        <v>-0.1727</v>
+        <v>-0.1798</v>
       </c>
       <c r="G161" s="17" t="n">
         <v>46323</v>
@@ -13557,13 +13557,13 @@
         </is>
       </c>
       <c r="D162" s="4" t="n">
-        <v>194.97</v>
+        <v>194.34</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>-0.0712</v>
+        <v>-0.0742</v>
       </c>
       <c r="F162" s="5" t="n">
-        <v>-0.0678</v>
+        <v>-0.0709</v>
       </c>
       <c r="G162" s="7" t="n">
         <v>46315</v>
@@ -13636,13 +13636,13 @@
         </is>
       </c>
       <c r="D163" s="15" t="n">
-        <v>43.56</v>
+        <v>43.96</v>
       </c>
       <c r="E163" s="16" t="n">
-        <v>0.0414</v>
+        <v>0.0509</v>
       </c>
       <c r="F163" s="16" t="n">
-        <v>0.0737</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="G163" s="17" t="n"/>
       <c r="H163" s="22" t="inlineStr">
@@ -13687,13 +13687,13 @@
         </is>
       </c>
       <c r="D164" s="4" t="n">
-        <v>434.51</v>
+        <v>433.32</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>-0.0417</v>
+        <v>-0.0444</v>
       </c>
       <c r="F164" s="5" t="n">
-        <v>-0.09420000000000001</v>
+        <v>-0.09669999999999999</v>
       </c>
       <c r="G164" s="7" t="n">
         <v>46324</v>
@@ -13725,7 +13725,7 @@
         <v>560</v>
       </c>
       <c r="P164" s="6" t="n">
-        <v>0.2888080826678328</v>
+        <v>0.292347456844826</v>
       </c>
       <c r="Q164" s="10" t="inlineStr">
         <is>
@@ -13778,13 +13778,13 @@
         </is>
       </c>
       <c r="D165" s="15" t="n">
-        <v>272.87</v>
+        <v>269.63</v>
       </c>
       <c r="E165" s="25" t="n">
-        <v>-0.1142</v>
+        <v>-0.1247</v>
       </c>
       <c r="F165" s="25" t="n">
-        <v>-0.1034</v>
+        <v>-0.114</v>
       </c>
       <c r="G165" s="17" t="n">
         <v>46317</v>
@@ -13816,7 +13816,7 @@
         <v>294</v>
       </c>
       <c r="P165" s="16" t="n">
-        <v>0.07743614175248285</v>
+        <v>0.0903831176056077</v>
       </c>
       <c r="Q165" s="20" t="inlineStr">
         <is>
@@ -13861,13 +13861,13 @@
         </is>
       </c>
       <c r="D166" s="4" t="n">
-        <v>254.53</v>
+        <v>250.86</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>-0.0283</v>
+        <v>-0.0423</v>
       </c>
       <c r="F166" s="5" t="n">
-        <v>-0.1628</v>
+        <v>-0.1749</v>
       </c>
       <c r="G166" s="7" t="n">
         <v>46323</v>
@@ -13899,7 +13899,7 @@
         <v>425</v>
       </c>
       <c r="P166" s="6" t="n">
-        <v>0.6697442344713787</v>
+        <v>0.694172048154349</v>
       </c>
       <c r="Q166" s="10" t="inlineStr">
         <is>
@@ -13940,13 +13940,13 @@
         </is>
       </c>
       <c r="D167" s="15" t="n">
-        <v>208.82</v>
+        <v>207.04</v>
       </c>
       <c r="E167" s="25" t="n">
-        <v>-0.068</v>
+        <v>-0.076</v>
       </c>
       <c r="F167" s="25" t="n">
-        <v>-0.1199</v>
+        <v>-0.1274</v>
       </c>
       <c r="G167" s="17" t="n">
         <v>46321</v>
@@ -13975,7 +13975,7 @@
         <v>268</v>
       </c>
       <c r="M167" s="16" t="n">
-        <v>0.2834019729910929</v>
+        <v>0.2944358578052551</v>
       </c>
       <c r="N167" s="14" t="inlineStr"/>
       <c r="O167" s="19" t="n"/>
@@ -14023,13 +14023,13 @@
         </is>
       </c>
       <c r="D168" s="4" t="n">
-        <v>321.3</v>
+        <v>317.69</v>
       </c>
       <c r="E168" s="6" t="n">
-        <v>0.03</v>
+        <v>0.0184</v>
       </c>
       <c r="F168" s="5" t="n">
-        <v>-0.1071</v>
+        <v>-0.1172</v>
       </c>
       <c r="G168" s="7" t="n">
         <v>46330</v>
@@ -14098,13 +14098,13 @@
         </is>
       </c>
       <c r="D169" s="15" t="n">
-        <v>326.33</v>
+        <v>325.16</v>
       </c>
       <c r="E169" s="25" t="n">
-        <v>-0.0493</v>
+        <v>-0.0527</v>
       </c>
       <c r="F169" s="25" t="n">
-        <v>-0.2078</v>
+        <v>-0.2107</v>
       </c>
       <c r="G169" s="17" t="n"/>
       <c r="H169" s="22" t="inlineStr">
@@ -14167,13 +14167,13 @@
         </is>
       </c>
       <c r="D170" s="4" t="n">
-        <v>108.07</v>
+        <v>107.24</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>-0.0472</v>
+        <v>-0.0545</v>
       </c>
       <c r="F170" s="5" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.0824</v>
       </c>
       <c r="G170" s="7" t="n">
         <v>46322</v>
@@ -14246,13 +14246,13 @@
         </is>
       </c>
       <c r="D171" s="15" t="n">
-        <v>108.1</v>
+        <v>108.67</v>
       </c>
       <c r="E171" s="25" t="n">
-        <v>-0.134</v>
+        <v>-0.1294</v>
       </c>
       <c r="F171" s="25" t="n">
-        <v>-0.035</v>
+        <v>-0.0299</v>
       </c>
       <c r="G171" s="17" t="n">
         <v>46331</v>
@@ -14307,13 +14307,13 @@
         </is>
       </c>
       <c r="D172" s="4" t="n">
-        <v>338.76</v>
+        <v>338.98</v>
       </c>
       <c r="E172" s="6" t="n">
-        <v>0.0951</v>
+        <v>0.0958</v>
       </c>
       <c r="F172" s="6" t="n">
-        <v>0.05309999999999999</v>
+        <v>0.0538</v>
       </c>
       <c r="G172" s="7" t="n">
         <v>46324</v>
@@ -14342,7 +14342,7 @@
         <v>310</v>
       </c>
       <c r="M172" s="5" t="n">
-        <v>-0.08489786279371825</v>
+        <v>-0.08549176942592489</v>
       </c>
       <c r="N172" s="3" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>365</v>
       </c>
       <c r="P172" s="6" t="n">
-        <v>0.07745896800094465</v>
+        <v>0.07675969083721748</v>
       </c>
       <c r="Q172" s="10" t="inlineStr">
         <is>
@@ -14410,13 +14410,13 @@
         </is>
       </c>
       <c r="D173" s="15" t="n">
-        <v>113.4</v>
+        <v>113.15</v>
       </c>
       <c r="E173" s="25" t="n">
-        <v>-0.1076</v>
+        <v>-0.1095</v>
       </c>
       <c r="F173" s="25" t="n">
-        <v>-0.1986</v>
+        <v>-0.2004</v>
       </c>
       <c r="G173" s="17" t="n">
         <v>46329</v>
@@ -14471,13 +14471,13 @@
         </is>
       </c>
       <c r="D174" s="4" t="n">
-        <v>186.87</v>
+        <v>186.11</v>
       </c>
       <c r="E174" s="6" t="n">
-        <v>0.0086</v>
+        <v>0.004500000000000001</v>
       </c>
       <c r="F174" s="6" t="n">
-        <v>0.3469</v>
+        <v>0.3414</v>
       </c>
       <c r="G174" s="7" t="n">
         <v>46296</v>
@@ -14532,13 +14532,13 @@
         </is>
       </c>
       <c r="D175" s="15" t="n">
-        <v>248.45</v>
+        <v>249.52</v>
       </c>
       <c r="E175" s="25" t="n">
-        <v>-0.0975</v>
+        <v>-0.09359999999999999</v>
       </c>
       <c r="F175" s="16" t="n">
-        <v>0.171</v>
+        <v>0.176</v>
       </c>
       <c r="G175" s="17" t="n"/>
       <c r="H175" s="22" t="inlineStr">
@@ -14583,13 +14583,13 @@
         </is>
       </c>
       <c r="D176" s="4" t="n">
-        <v>380.28</v>
+        <v>383</v>
       </c>
       <c r="E176" s="6" t="n">
-        <v>0.0193</v>
+        <v>0.0266</v>
       </c>
       <c r="F176" s="6" t="n">
-        <v>0.0002</v>
+        <v>0.0074</v>
       </c>
       <c r="G176" s="7" t="n"/>
       <c r="H176" s="12" t="inlineStr">
@@ -14608,7 +14608,7 @@
         <v>515</v>
       </c>
       <c r="M176" s="6" t="n">
-        <v>0.3542652782160514</v>
+        <v>0.3446475195822454</v>
       </c>
       <c r="N176" s="3" t="inlineStr">
         <is>
@@ -14619,7 +14619,7 @@
         <v>474</v>
       </c>
       <c r="P176" s="6" t="n">
-        <v>0.2464499842221522</v>
+        <v>0.237597911227154</v>
       </c>
       <c r="Q176" s="10" t="inlineStr">
         <is>
@@ -14668,13 +14668,13 @@
         </is>
       </c>
       <c r="D177" s="15" t="n">
-        <v>218.97</v>
+        <v>218.85</v>
       </c>
       <c r="E177" s="25" t="n">
-        <v>-0.1373</v>
+        <v>-0.1378</v>
       </c>
       <c r="F177" s="16" t="n">
-        <v>0.0668</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="G177" s="17" t="n"/>
       <c r="H177" s="22" t="inlineStr">
@@ -14719,13 +14719,13 @@
         </is>
       </c>
       <c r="D178" s="4" t="n">
-        <v>265.16</v>
+        <v>262.74</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>-0.0723</v>
+        <v>-0.0808</v>
       </c>
       <c r="F178" s="5" t="n">
-        <v>-0.1586</v>
+        <v>-0.1663</v>
       </c>
       <c r="G178" s="7" t="n">
         <v>46329</v>
@@ -14780,13 +14780,13 @@
         </is>
       </c>
       <c r="D179" s="15" t="n">
-        <v>328.98</v>
+        <v>340.74</v>
       </c>
       <c r="E179" s="16" t="n">
-        <v>0.1544</v>
+        <v>0.1957</v>
       </c>
       <c r="F179" s="16" t="n">
-        <v>0.0061</v>
+        <v>0.0421</v>
       </c>
       <c r="G179" s="17" t="n">
         <v>46329</v>
@@ -14841,13 +14841,13 @@
         </is>
       </c>
       <c r="D180" s="4" t="n">
-        <v>34.53</v>
+        <v>35.5</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>-0.0708</v>
+        <v>-0.0447</v>
       </c>
       <c r="F180" s="5" t="n">
-        <v>-0.3104</v>
+        <v>-0.291</v>
       </c>
       <c r="G180" s="7" t="n">
         <v>46324</v>
@@ -14902,13 +14902,13 @@
         </is>
       </c>
       <c r="D181" s="15" t="n">
-        <v>463.39</v>
+        <v>464.24</v>
       </c>
       <c r="E181" s="25" t="n">
-        <v>-0.0588</v>
+        <v>-0.057</v>
       </c>
       <c r="F181" s="25" t="n">
-        <v>-0.1766</v>
+        <v>-0.1751</v>
       </c>
       <c r="G181" s="17" t="n">
         <v>46338</v>
@@ -14937,7 +14937,7 @@
         <v>740</v>
       </c>
       <c r="M181" s="16" t="n">
-        <v>0.5969269945402361</v>
+        <v>0.5940031018438738</v>
       </c>
       <c r="N181" s="14" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>700</v>
       </c>
       <c r="P181" s="16" t="n">
-        <v>0.5106066164569801</v>
+        <v>0.5078407720144752</v>
       </c>
       <c r="Q181" s="20" t="inlineStr">
         <is>
@@ -14989,13 +14989,13 @@
         </is>
       </c>
       <c r="D182" s="4" t="n">
-        <v>67.95</v>
+        <v>71.09</v>
       </c>
       <c r="E182" s="6" t="n">
-        <v>0.1513</v>
+        <v>0.2045</v>
       </c>
       <c r="F182" s="5" t="n">
-        <v>-0.09119999999999999</v>
+        <v>-0.0492</v>
       </c>
       <c r="G182" s="7" t="n">
         <v>46331</v>
@@ -15054,13 +15054,13 @@
         </is>
       </c>
       <c r="D183" s="15" t="n">
-        <v>611.8200000000001</v>
+        <v>615.52</v>
       </c>
       <c r="E183" s="16" t="n">
-        <v>0.2928</v>
+        <v>0.3006</v>
       </c>
       <c r="F183" s="16" t="n">
-        <v>0.1337</v>
+        <v>0.1405</v>
       </c>
       <c r="G183" s="17" t="n">
         <v>46329</v>
@@ -15088,8 +15088,8 @@
       <c r="L183" s="19" t="n">
         <v>615</v>
       </c>
-      <c r="M183" s="16" t="n">
-        <v>0.00519760713935463</v>
+      <c r="M183" s="25" t="n">
+        <v>-0.0008448141408889749</v>
       </c>
       <c r="N183" s="14" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>579</v>
       </c>
       <c r="P183" s="25" t="n">
-        <v>-0.05364322840051003</v>
+        <v>-0.0593319469716662</v>
       </c>
       <c r="Q183" s="20" t="inlineStr">
         <is>
@@ -15141,13 +15141,13 @@
         </is>
       </c>
       <c r="D184" s="4" t="n">
-        <v>51.42</v>
+        <v>52.19</v>
       </c>
       <c r="E184" s="6" t="n">
-        <v>0.0231</v>
+        <v>0.0384</v>
       </c>
       <c r="F184" s="5" t="n">
-        <v>-0.2129</v>
+        <v>-0.2011</v>
       </c>
       <c r="G184" s="7" t="n">
         <v>46321</v>
@@ -15202,13 +15202,13 @@
         </is>
       </c>
       <c r="D185" s="15" t="n">
-        <v>202.68</v>
+        <v>205.42</v>
       </c>
       <c r="E185" s="16" t="n">
-        <v>0.07440000000000001</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="F185" s="16" t="n">
-        <v>0.1476</v>
+        <v>0.1631</v>
       </c>
       <c r="G185" s="17" t="n">
         <v>46329</v>
@@ -15237,7 +15237,7 @@
         <v>200</v>
       </c>
       <c r="M185" s="25" t="n">
-        <v>-0.01322281428853368</v>
+        <v>-0.02638496738389635</v>
       </c>
       <c r="N185" s="14" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>200</v>
       </c>
       <c r="P185" s="25" t="n">
-        <v>-0.01322281428853368</v>
+        <v>-0.02638496738389635</v>
       </c>
       <c r="Q185" s="20" t="inlineStr">
         <is>
@@ -15293,13 +15293,13 @@
         </is>
       </c>
       <c r="D186" s="4" t="n">
-        <v>80.86</v>
+        <v>80.72</v>
       </c>
       <c r="E186" s="6" t="n">
-        <v>0.0299</v>
+        <v>0.0282</v>
       </c>
       <c r="F186" s="6" t="n">
-        <v>0.0272</v>
+        <v>0.0255</v>
       </c>
       <c r="G186" s="7" t="n">
         <v>46323</v>
@@ -15331,7 +15331,7 @@
         <v>180</v>
       </c>
       <c r="P186" s="6" t="n">
-        <v>1.226069750185506</v>
+        <v>1.229930624380575</v>
       </c>
       <c r="Q186" s="10" t="inlineStr">
         <is>
@@ -15384,13 +15384,13 @@
         </is>
       </c>
       <c r="D187" s="15" t="n">
-        <v>28.32</v>
+        <v>28.19</v>
       </c>
       <c r="E187" s="16" t="n">
-        <v>0.0406</v>
+        <v>0.036</v>
       </c>
       <c r="F187" s="25" t="n">
-        <v>-0.0527</v>
+        <v>-0.05690000000000001</v>
       </c>
       <c r="G187" s="17" t="n">
         <v>46303</v>
@@ -15445,13 +15445,13 @@
         </is>
       </c>
       <c r="D188" s="4" t="n">
-        <v>319.57</v>
+        <v>322.9</v>
       </c>
       <c r="E188" s="6" t="n">
-        <v>0.3134</v>
+        <v>0.3271</v>
       </c>
       <c r="F188" s="6" t="n">
-        <v>0.1291</v>
+        <v>0.1408</v>
       </c>
       <c r="G188" s="7" t="n">
         <v>46330</v>
@@ -15506,13 +15506,13 @@
         </is>
       </c>
       <c r="D189" s="15" t="n">
-        <v>1704.14</v>
+        <v>1711.32</v>
       </c>
       <c r="E189" s="25" t="n">
-        <v>-0.0338</v>
+        <v>-0.0297</v>
       </c>
       <c r="F189" s="25" t="n">
-        <v>-0.0548</v>
+        <v>-0.0508</v>
       </c>
       <c r="G189" s="17" t="n">
         <v>46309</v>
@@ -15585,13 +15585,13 @@
         </is>
       </c>
       <c r="D190" s="4" t="n">
-        <v>43.38</v>
+        <v>43.73</v>
       </c>
       <c r="E190" s="6" t="n">
-        <v>0.188</v>
+        <v>0.1978</v>
       </c>
       <c r="F190" s="6" t="n">
-        <v>0.0992</v>
+        <v>0.1082</v>
       </c>
       <c r="G190" s="7" t="n">
         <v>46324</v>
@@ -15646,13 +15646,13 @@
         </is>
       </c>
       <c r="D191" s="15" t="n">
-        <v>360.77</v>
+        <v>362.66</v>
       </c>
       <c r="E191" s="25" t="n">
-        <v>-0.0208</v>
+        <v>-0.0157</v>
       </c>
       <c r="F191" s="25" t="n">
-        <v>-0.0808</v>
+        <v>-0.076</v>
       </c>
       <c r="G191" s="17" t="n"/>
       <c r="H191" s="22" t="inlineStr">
@@ -15671,7 +15671,7 @@
         <v>545</v>
       </c>
       <c r="M191" s="16" t="n">
-        <v>0.510657759791557</v>
+        <v>0.5027849776650305</v>
       </c>
       <c r="N191" s="14" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>582</v>
       </c>
       <c r="P191" s="16" t="n">
-        <v>0.6132161765113509</v>
+        <v>0.604808911928528</v>
       </c>
       <c r="Q191" s="20" t="inlineStr">
         <is>
@@ -15735,13 +15735,13 @@
         </is>
       </c>
       <c r="D192" s="4" t="n">
-        <v>151.04</v>
+        <v>149.63</v>
       </c>
       <c r="E192" s="6" t="n">
-        <v>0.0288</v>
+        <v>0.0192</v>
       </c>
       <c r="F192" s="5" t="n">
-        <v>-0.0267</v>
+        <v>-0.0358</v>
       </c>
       <c r="G192" s="7" t="n">
         <v>46335</v>
@@ -15796,13 +15796,13 @@
         </is>
       </c>
       <c r="D193" s="15" t="n">
-        <v>293.5</v>
+        <v>294.9</v>
       </c>
       <c r="E193" s="25" t="n">
-        <v>-0.08</v>
+        <v>-0.0756</v>
       </c>
       <c r="F193" s="25" t="n">
-        <v>-0.1118</v>
+        <v>-0.1076</v>
       </c>
       <c r="G193" s="17" t="n">
         <v>46321</v>
@@ -15831,7 +15831,7 @@
         <v>425</v>
       </c>
       <c r="M193" s="16" t="n">
-        <v>0.4480408858603067</v>
+        <v>0.4411664971176671</v>
       </c>
       <c r="N193" s="14" t="inlineStr"/>
       <c r="O193" s="19" t="n"/>
@@ -15875,13 +15875,13 @@
         </is>
       </c>
       <c r="D194" s="4" t="n">
-        <v>133.82</v>
+        <v>134.25</v>
       </c>
       <c r="E194" s="6" t="n">
-        <v>0.0251</v>
+        <v>0.0283</v>
       </c>
       <c r="F194" s="6" t="n">
-        <v>0.062</v>
+        <v>0.0654</v>
       </c>
       <c r="G194" s="7" t="n">
         <v>46322</v>
@@ -15936,13 +15936,13 @@
         </is>
       </c>
       <c r="D195" s="15" t="n">
-        <v>361.39</v>
+        <v>365.96</v>
       </c>
       <c r="E195" s="25" t="n">
-        <v>-0.08689999999999999</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="F195" s="25" t="n">
-        <v>-0.1132</v>
+        <v>-0.102</v>
       </c>
       <c r="G195" s="17" t="n"/>
       <c r="H195" s="22" t="inlineStr">
@@ -15987,13 +15987,13 @@
         </is>
       </c>
       <c r="D196" s="4" t="n">
-        <v>11.51</v>
+        <v>11.56</v>
       </c>
       <c r="E196" s="6" t="n">
-        <v>0.0416</v>
+        <v>0.0462</v>
       </c>
       <c r="F196" s="5" t="n">
-        <v>-0.1814</v>
+        <v>-0.1778</v>
       </c>
       <c r="G196" s="7" t="n">
         <v>46337</v>
@@ -16048,13 +16048,13 @@
         </is>
       </c>
       <c r="D197" s="15" t="n">
-        <v>345.57</v>
+        <v>344.4</v>
       </c>
       <c r="E197" s="16" t="n">
-        <v>0.1653</v>
+        <v>0.1614</v>
       </c>
       <c r="F197" s="16" t="n">
-        <v>0.0323</v>
+        <v>0.0288</v>
       </c>
       <c r="G197" s="17" t="n">
         <v>46321</v>
@@ -16109,13 +16109,13 @@
         </is>
       </c>
       <c r="D198" s="4" t="n">
-        <v>328.2</v>
+        <v>321.52</v>
       </c>
       <c r="E198" s="6" t="n">
-        <v>0.1336</v>
+        <v>0.1105</v>
       </c>
       <c r="F198" s="6" t="n">
-        <v>0.0478</v>
+        <v>0.0265</v>
       </c>
       <c r="G198" s="7" t="n">
         <v>46330</v>
@@ -16170,13 +16170,13 @@
         </is>
       </c>
       <c r="D199" s="15" t="n">
-        <v>60.6</v>
+        <v>60.62</v>
       </c>
       <c r="E199" s="16" t="n">
-        <v>0.1147</v>
+        <v>0.1149</v>
       </c>
       <c r="F199" s="16" t="n">
-        <v>0.1118</v>
+        <v>0.112</v>
       </c>
       <c r="G199" s="17" t="n">
         <v>46330</v>
@@ -16231,13 +16231,13 @@
         </is>
       </c>
       <c r="D200" s="4" t="n">
-        <v>18.34</v>
+        <v>18.36</v>
       </c>
       <c r="E200" s="6" t="n">
-        <v>0.0298</v>
+        <v>0.0309</v>
       </c>
       <c r="F200" s="5" t="n">
-        <v>-0.2346</v>
+        <v>-0.2337</v>
       </c>
       <c r="G200" s="7" t="n">
         <v>46318</v>
@@ -16292,13 +16292,13 @@
         </is>
       </c>
       <c r="D201" s="15" t="n">
-        <v>185.24</v>
+        <v>187.27</v>
       </c>
       <c r="E201" s="25" t="n">
-        <v>-0.1966</v>
+        <v>-0.1878</v>
       </c>
       <c r="F201" s="25" t="n">
-        <v>-0.2167</v>
+        <v>-0.2082</v>
       </c>
       <c r="G201" s="17" t="n"/>
       <c r="H201" s="22" t="inlineStr">
@@ -16343,13 +16343,13 @@
         </is>
       </c>
       <c r="D202" s="4" t="n">
-        <v>237.89</v>
+        <v>236.42</v>
       </c>
       <c r="E202" s="6" t="n">
-        <v>0.1373</v>
+        <v>0.1303</v>
       </c>
       <c r="F202" s="6" t="n">
-        <v>0.5159</v>
+        <v>0.5065</v>
       </c>
       <c r="G202" s="7" t="n"/>
       <c r="H202" s="12" t="inlineStr">
@@ -16368,7 +16368,7 @@
         <v>200</v>
       </c>
       <c r="M202" s="5" t="n">
-        <v>-0.1592752953045525</v>
+        <v>-0.1540478808899416</v>
       </c>
       <c r="N202" s="3" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>250</v>
       </c>
       <c r="P202" s="6" t="n">
-        <v>0.0509058808693094</v>
+        <v>0.05744014888757302</v>
       </c>
       <c r="Q202" s="10" t="inlineStr">
         <is>
@@ -16424,13 +16424,13 @@
         </is>
       </c>
       <c r="D203" s="15" t="n">
-        <v>247.25</v>
+        <v>249.35</v>
       </c>
       <c r="E203" s="16" t="n">
-        <v>0.2881</v>
+        <v>0.299</v>
       </c>
       <c r="F203" s="16" t="n">
-        <v>0.348</v>
+        <v>0.3594</v>
       </c>
       <c r="G203" s="17" t="n"/>
       <c r="H203" s="22" t="inlineStr">
@@ -16449,7 +16449,7 @@
         <v>181.25</v>
       </c>
       <c r="M203" s="25" t="n">
-        <v>-0.2669362992922144</v>
+        <v>-0.2731100862241829</v>
       </c>
       <c r="N203" s="14" t="inlineStr">
         <is>
@@ -16460,7 +16460,7 @@
         <v>177.5</v>
       </c>
       <c r="P203" s="25" t="n">
-        <v>-0.282103134479272</v>
+        <v>-0.2881491878885101</v>
       </c>
       <c r="Q203" s="20" t="inlineStr">
         <is>
@@ -16501,13 +16501,13 @@
         </is>
       </c>
       <c r="D204" s="4" t="n">
-        <v>86.44</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0275</v>
       </c>
       <c r="F204" s="6" t="n">
-        <v>0.0659</v>
+        <v>0.0534</v>
       </c>
       <c r="G204" s="7" t="n">
         <v>46335</v>
@@ -16562,13 +16562,13 @@
         </is>
       </c>
       <c r="D205" s="15" t="n">
-        <v>109.61</v>
-      </c>
-      <c r="E205" s="25" t="n">
-        <v>-0.0129</v>
+        <v>111.46</v>
+      </c>
+      <c r="E205" s="16" t="n">
+        <v>0.0038</v>
       </c>
       <c r="F205" s="25" t="n">
-        <v>-0.028</v>
+        <v>-0.0115</v>
       </c>
       <c r="G205" s="17" t="n">
         <v>46337</v>
@@ -16597,7 +16597,7 @@
         <v>130</v>
       </c>
       <c r="M205" s="16" t="n">
-        <v>0.1860231730681507</v>
+        <v>0.1663376996231833</v>
       </c>
       <c r="N205" s="14" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>150</v>
       </c>
       <c r="P205" s="16" t="n">
-        <v>0.368488276617097</v>
+        <v>0.3457742687959807</v>
       </c>
       <c r="Q205" s="20" t="inlineStr">
         <is>
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="D206" s="4" t="n">
-        <v>241.24</v>
+        <v>245.05</v>
       </c>
       <c r="E206" s="6" t="n">
-        <v>0.0239</v>
-      </c>
-      <c r="F206" s="5" t="n">
-        <v>-0.0129</v>
+        <v>0.04</v>
+      </c>
+      <c r="F206" s="6" t="n">
+        <v>0.0027</v>
       </c>
       <c r="G206" s="7" t="n">
         <v>46331</v>
@@ -16726,13 +16726,13 @@
         </is>
       </c>
       <c r="D207" s="15" t="n">
-        <v>574.25</v>
+        <v>575.3099999999999</v>
       </c>
       <c r="E207" s="16" t="n">
-        <v>0.299</v>
+        <v>0.3014</v>
       </c>
       <c r="F207" s="16" t="n">
-        <v>0.3071</v>
+        <v>0.3095</v>
       </c>
       <c r="G207" s="17" t="n"/>
       <c r="H207" s="22" t="inlineStr">
@@ -16777,13 +16777,13 @@
         </is>
       </c>
       <c r="D208" s="4" t="n">
-        <v>68.54000000000001</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="E208" s="6" t="n">
-        <v>0.1056</v>
+        <v>0.106</v>
       </c>
       <c r="F208" s="6" t="n">
-        <v>0.4572</v>
+        <v>0.4577000000000001</v>
       </c>
       <c r="G208" s="7" t="n"/>
       <c r="H208" s="12" t="inlineStr">
@@ -16828,13 +16828,13 @@
         </is>
       </c>
       <c r="D209" s="15" t="n">
-        <v>56.03</v>
+        <v>56.4</v>
       </c>
       <c r="E209" s="16" t="n">
-        <v>0.1365</v>
+        <v>0.144</v>
       </c>
       <c r="F209" s="16" t="n">
-        <v>0.3784</v>
+        <v>0.3875</v>
       </c>
       <c r="G209" s="17" t="n">
         <v>46330</v>
@@ -16889,13 +16889,13 @@
         </is>
       </c>
       <c r="D210" s="4" t="n">
-        <v>402.47</v>
+        <v>401.57</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>-0.07829999999999999</v>
+        <v>-0.08039999999999999</v>
       </c>
       <c r="F210" s="5" t="n">
-        <v>-0.2226</v>
+        <v>-0.2244</v>
       </c>
       <c r="G210" s="7" t="n">
         <v>46328</v>
@@ -16950,13 +16950,13 @@
         </is>
       </c>
       <c r="D211" s="15" t="n">
-        <v>118.87</v>
+        <v>119.31</v>
       </c>
       <c r="E211" s="16" t="n">
-        <v>0.0413</v>
+        <v>0.0451</v>
       </c>
       <c r="F211" s="16" t="n">
-        <v>0.05429999999999999</v>
+        <v>0.0582</v>
       </c>
       <c r="G211" s="17" t="n">
         <v>46330</v>
@@ -17011,13 +17011,13 @@
         </is>
       </c>
       <c r="D212" s="4" t="n">
-        <v>173.99</v>
+        <v>175.23</v>
       </c>
       <c r="E212" s="6" t="n">
-        <v>0.1334</v>
+        <v>0.1415</v>
       </c>
       <c r="F212" s="6" t="n">
-        <v>0.1481</v>
+        <v>0.1563</v>
       </c>
       <c r="G212" s="7" t="n">
         <v>46330</v>
@@ -17072,13 +17072,13 @@
         </is>
       </c>
       <c r="D213" s="15" t="n">
-        <v>48.37</v>
+        <v>48.57</v>
       </c>
       <c r="E213" s="16" t="n">
-        <v>0.0067</v>
+        <v>0.0108</v>
       </c>
       <c r="F213" s="25" t="n">
-        <v>-0.1501</v>
+        <v>-0.1465</v>
       </c>
       <c r="G213" s="17" t="n">
         <v>46337</v>
@@ -17133,13 +17133,13 @@
         </is>
       </c>
       <c r="D214" s="4" t="n">
-        <v>159.6</v>
+        <v>158.98</v>
       </c>
       <c r="E214" s="6" t="n">
-        <v>0.06509999999999999</v>
+        <v>0.061</v>
       </c>
       <c r="F214" s="6" t="n">
-        <v>0.0227</v>
+        <v>0.0187</v>
       </c>
       <c r="G214" s="7" t="n">
         <v>46322</v>
@@ -17194,13 +17194,13 @@
         </is>
       </c>
       <c r="D215" s="15" t="n">
-        <v>49.48</v>
+        <v>49.79</v>
       </c>
       <c r="E215" s="16" t="n">
-        <v>0.1874</v>
+        <v>0.1949</v>
       </c>
       <c r="F215" s="16" t="n">
-        <v>0.6373</v>
+        <v>0.6476000000000001</v>
       </c>
       <c r="G215" s="17" t="n"/>
       <c r="H215" s="22" t="inlineStr">
@@ -17245,13 +17245,13 @@
         </is>
       </c>
       <c r="D216" s="4" t="n">
-        <v>149.89</v>
+        <v>149.38</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>-0.2077</v>
+        <v>-0.2104</v>
       </c>
       <c r="F216" s="6" t="n">
-        <v>0.1409</v>
+        <v>0.137</v>
       </c>
       <c r="G216" s="7" t="n"/>
       <c r="H216" s="12" t="inlineStr">
@@ -17270,7 +17270,7 @@
         <v>190</v>
       </c>
       <c r="M216" s="6" t="n">
-        <v>0.2675962372406432</v>
+        <v>0.2719239523363235</v>
       </c>
       <c r="N216" s="3" t="inlineStr"/>
       <c r="O216" s="9" t="n"/>
@@ -17314,13 +17314,13 @@
         </is>
       </c>
       <c r="D217" s="15" t="n">
-        <v>61.13</v>
+        <v>61.75</v>
       </c>
       <c r="E217" s="16" t="n">
-        <v>0.1437</v>
+        <v>0.1553</v>
       </c>
       <c r="F217" s="16" t="n">
-        <v>0.2832</v>
+        <v>0.2962</v>
       </c>
       <c r="G217" s="17" t="n"/>
       <c r="H217" s="22" t="inlineStr">
@@ -17339,7 +17339,7 @@
         <v>67</v>
       </c>
       <c r="M217" s="16" t="n">
-        <v>0.09602486504171433</v>
+        <v>0.08502024291497975</v>
       </c>
       <c r="N217" s="14" t="inlineStr">
         <is>
@@ -17350,7 +17350,7 @@
         <v>70</v>
       </c>
       <c r="P217" s="16" t="n">
-        <v>0.1451006052674627</v>
+        <v>0.1336032388663968</v>
       </c>
       <c r="Q217" s="20" t="inlineStr">
         <is>
@@ -17391,13 +17391,13 @@
         </is>
       </c>
       <c r="D218" s="4" t="n">
-        <v>213.12</v>
+        <v>213.86</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>-0.112</v>
+        <v>-0.109</v>
       </c>
       <c r="F218" s="6" t="n">
-        <v>0.1216</v>
+        <v>0.1255</v>
       </c>
       <c r="G218" s="7" t="n">
         <v>46330</v>
@@ -17452,13 +17452,13 @@
         </is>
       </c>
       <c r="D219" s="15" t="n">
-        <v>229.73</v>
+        <v>231.93</v>
       </c>
       <c r="E219" s="25" t="n">
-        <v>-0.0252</v>
+        <v>-0.0159</v>
       </c>
       <c r="F219" s="16" t="n">
-        <v>0.1117</v>
+        <v>0.1223</v>
       </c>
       <c r="G219" s="17" t="n">
         <v>46316</v>
@@ -17494,7 +17494,7 @@
         <v>250</v>
       </c>
       <c r="P219" s="16" t="n">
-        <v>0.0882340138423367</v>
+        <v>0.07791143879618848</v>
       </c>
       <c r="Q219" s="20" t="inlineStr">
         <is>
@@ -17531,13 +17531,13 @@
         </is>
       </c>
       <c r="D220" s="4" t="n">
-        <v>14.1</v>
+        <v>13.96</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>-0.0014</v>
+        <v>-0.0113</v>
       </c>
       <c r="F220" s="6" t="n">
-        <v>0.4551</v>
+        <v>0.4407</v>
       </c>
       <c r="G220" s="7" t="n">
         <v>46337</v>
@@ -17592,13 +17592,13 @@
         </is>
       </c>
       <c r="D221" s="15" t="n">
-        <v>123.07</v>
+        <v>121.78</v>
       </c>
       <c r="E221" s="16" t="n">
-        <v>0.3663</v>
+        <v>0.3521</v>
       </c>
       <c r="F221" s="16" t="n">
-        <v>0.2278</v>
+        <v>0.215</v>
       </c>
       <c r="G221" s="17" t="n">
         <v>46317</v>
@@ -17653,13 +17653,13 @@
         </is>
       </c>
       <c r="D222" s="4" t="n">
-        <v>303.17</v>
+        <v>304.12</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>-0.1739</v>
+        <v>-0.1713</v>
       </c>
       <c r="F222" s="6" t="n">
-        <v>0.07690000000000001</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="G222" s="7" t="n"/>
       <c r="H222" s="12" t="inlineStr">
@@ -17704,13 +17704,13 @@
         </is>
       </c>
       <c r="D223" s="15" t="n">
-        <v>40.3</v>
+        <v>40.51</v>
       </c>
       <c r="E223" s="25" t="n">
-        <v>-0.1016</v>
+        <v>-0.09699999999999999</v>
       </c>
       <c r="F223" s="16" t="n">
-        <v>0.1829</v>
+        <v>0.189</v>
       </c>
       <c r="G223" s="17" t="n">
         <v>46330</v>
@@ -17765,13 +17765,13 @@
         </is>
       </c>
       <c r="D224" s="4" t="n">
-        <v>47.18</v>
+        <v>47.23</v>
       </c>
       <c r="E224" s="6" t="n">
-        <v>0.1266</v>
+        <v>0.1277</v>
       </c>
       <c r="F224" s="6" t="n">
-        <v>0.1626</v>
+        <v>0.1639</v>
       </c>
       <c r="G224" s="7" t="n">
         <v>46331</v>
@@ -17826,13 +17826,13 @@
         </is>
       </c>
       <c r="D225" s="15" t="n">
-        <v>301.14</v>
+        <v>303.67</v>
       </c>
       <c r="E225" s="25" t="n">
-        <v>-0.0385</v>
+        <v>-0.0305</v>
       </c>
       <c r="F225" s="25" t="n">
-        <v>-0.0649</v>
+        <v>-0.057</v>
       </c>
       <c r="G225" s="17" t="n">
         <v>46289</v>
@@ -17891,13 +17891,13 @@
         </is>
       </c>
       <c r="D226" s="4" t="n">
-        <v>340.8</v>
+        <v>342.03</v>
       </c>
       <c r="E226" s="6" t="n">
-        <v>0.0781</v>
+        <v>0.0819</v>
       </c>
       <c r="F226" s="6" t="n">
-        <v>0.0482</v>
+        <v>0.052</v>
       </c>
       <c r="G226" s="7" t="n"/>
       <c r="H226" s="12" t="inlineStr">
@@ -17916,7 +17916,7 @@
         <v>390</v>
       </c>
       <c r="M226" s="6" t="n">
-        <v>0.1443661971830986</v>
+        <v>0.1402508551881415</v>
       </c>
       <c r="N226" s="3" t="inlineStr"/>
       <c r="O226" s="9" t="n"/>
@@ -17972,13 +17972,13 @@
         </is>
       </c>
       <c r="D227" s="15" t="n">
-        <v>183.38</v>
+        <v>183.97</v>
       </c>
       <c r="E227" s="25" t="n">
-        <v>-0.0033</v>
+        <v>-0.0001</v>
       </c>
       <c r="F227" s="25" t="n">
-        <v>-0.1616</v>
+        <v>-0.1589</v>
       </c>
       <c r="G227" s="17" t="n">
         <v>46330</v>
@@ -18007,7 +18007,7 @@
         <v>305</v>
       </c>
       <c r="M227" s="16" t="n">
-        <v>0.6632130003271894</v>
+        <v>0.6578790020111975</v>
       </c>
       <c r="N227" s="14" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>185</v>
       </c>
       <c r="P227" s="16" t="n">
-        <v>0.008834114952557556</v>
+        <v>0.005598738924824706</v>
       </c>
       <c r="Q227" s="20" t="inlineStr">
         <is>
@@ -18059,13 +18059,13 @@
         </is>
       </c>
       <c r="D228" s="4" t="n">
-        <v>83.69</v>
+        <v>84.08</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>-0.024</v>
+        <v>-0.0195</v>
       </c>
       <c r="F228" s="5" t="n">
-        <v>-0.2111</v>
+        <v>-0.2074</v>
       </c>
       <c r="G228" s="7" t="n"/>
       <c r="H228" s="12" t="inlineStr">
@@ -18110,13 +18110,13 @@
         </is>
       </c>
       <c r="D229" s="15" t="n">
-        <v>967.1799999999999</v>
+        <v>954.49</v>
       </c>
       <c r="E229" s="16" t="n">
-        <v>0.1159</v>
+        <v>0.1013</v>
       </c>
       <c r="F229" s="16" t="n">
-        <v>0.1602</v>
+        <v>0.145</v>
       </c>
       <c r="G229" s="17" t="n">
         <v>46329</v>
@@ -18171,13 +18171,13 @@
         </is>
       </c>
       <c r="D230" s="4" t="n">
-        <v>104.31</v>
+        <v>105.12</v>
       </c>
       <c r="E230" s="6" t="n">
-        <v>0.0862</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="F230" s="6" t="n">
-        <v>0.0137</v>
+        <v>0.0216</v>
       </c>
       <c r="G230" s="7" t="n">
         <v>46322</v>
@@ -18232,13 +18232,13 @@
         </is>
       </c>
       <c r="D231" s="15" t="n">
-        <v>300.95</v>
+        <v>302.28</v>
       </c>
       <c r="E231" s="25" t="n">
-        <v>-0.0416</v>
+        <v>-0.0373</v>
       </c>
       <c r="F231" s="25" t="n">
-        <v>-0.05889999999999999</v>
+        <v>-0.0547</v>
       </c>
       <c r="G231" s="17" t="n">
         <v>46323</v>
@@ -18267,7 +18267,7 @@
         <v>450</v>
       </c>
       <c r="M231" s="16" t="n">
-        <v>0.4952649941850806</v>
+        <v>0.4886859865025805</v>
       </c>
       <c r="N231" s="14" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>355</v>
       </c>
       <c r="P231" s="16" t="n">
-        <v>0.1795979398571192</v>
+        <v>0.1744078337964802</v>
       </c>
       <c r="Q231" s="20" t="inlineStr">
         <is>
@@ -18323,13 +18323,13 @@
         </is>
       </c>
       <c r="D232" s="4" t="n">
-        <v>74.34</v>
+        <v>74.78</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>-0.0229</v>
+        <v>-0.0171</v>
       </c>
       <c r="F232" s="5" t="n">
-        <v>-0.0862</v>
+        <v>-0.0808</v>
       </c>
       <c r="G232" s="7" t="n">
         <v>46331</v>
@@ -18384,13 +18384,13 @@
         </is>
       </c>
       <c r="D233" s="15" t="n">
-        <v>396.9</v>
+        <v>407.3</v>
       </c>
       <c r="E233" s="25" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.0546</v>
       </c>
       <c r="F233" s="16" t="n">
-        <v>0.3268</v>
+        <v>0.3616</v>
       </c>
       <c r="G233" s="17" t="n"/>
       <c r="H233" s="22" t="inlineStr">
@@ -18435,13 +18435,13 @@
         </is>
       </c>
       <c r="D234" s="4" t="n">
-        <v>255.68</v>
+        <v>256.92</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>-0.0839</v>
+        <v>-0.0795</v>
       </c>
       <c r="F234" s="5" t="n">
-        <v>-0.2595</v>
+        <v>-0.256</v>
       </c>
       <c r="G234" s="7" t="n">
         <v>46330</v>
@@ -18496,13 +18496,13 @@
         </is>
       </c>
       <c r="D235" s="15" t="n">
-        <v>1261.24</v>
+        <v>1277.68</v>
       </c>
       <c r="E235" s="25" t="n">
-        <v>-0.0418</v>
+        <v>-0.0293</v>
       </c>
       <c r="F235" s="25" t="n">
-        <v>-0.0973</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="G235" s="17" t="n">
         <v>46324</v>
@@ -18557,13 +18557,13 @@
         </is>
       </c>
       <c r="D236" s="4" t="n">
-        <v>255.5</v>
+        <v>257.38</v>
       </c>
       <c r="E236" s="6" t="n">
-        <v>0.0779</v>
+        <v>0.0858</v>
       </c>
       <c r="F236" s="6" t="n">
-        <v>0.2206</v>
+        <v>0.2296</v>
       </c>
       <c r="G236" s="7" t="n"/>
       <c r="H236" s="12" t="inlineStr">
@@ -18582,7 +18582,7 @@
         <v>240</v>
       </c>
       <c r="M236" s="5" t="n">
-        <v>-0.06066536203522505</v>
+        <v>-0.0675266143445489</v>
       </c>
       <c r="N236" s="3" t="inlineStr">
         <is>
@@ -18593,7 +18593,7 @@
         <v>251</v>
       </c>
       <c r="P236" s="5" t="n">
-        <v>-0.01761252446183953</v>
+        <v>-0.02478825083534072</v>
       </c>
       <c r="Q236" s="10" t="inlineStr">
         <is>
@@ -18634,13 +18634,13 @@
         </is>
       </c>
       <c r="D237" s="15" t="n">
-        <v>495.45</v>
+        <v>501.61</v>
       </c>
       <c r="E237" s="16" t="n">
-        <v>0.0253</v>
+        <v>0.038</v>
       </c>
       <c r="F237" s="16" t="n">
-        <v>0.2984</v>
+        <v>0.3146</v>
       </c>
       <c r="G237" s="17" t="n">
         <v>46330</v>
@@ -18669,7 +18669,7 @@
         <v>625</v>
       </c>
       <c r="M237" s="16" t="n">
-        <v>0.2614794631143405</v>
+        <v>0.2459879189011383</v>
       </c>
       <c r="N237" s="14" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>525</v>
       </c>
       <c r="P237" s="16" t="n">
-        <v>0.05964274901604604</v>
+        <v>0.04662985187695617</v>
       </c>
       <c r="Q237" s="20" t="inlineStr">
         <is>
@@ -18733,13 +18733,13 @@
         </is>
       </c>
       <c r="D238" s="4" t="n">
-        <v>461.29</v>
+        <v>461.36</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>-0.0399</v>
+        <v>-0.0398</v>
       </c>
       <c r="F238" s="6" t="n">
-        <v>0.1333</v>
+        <v>0.1335</v>
       </c>
       <c r="G238" s="7" t="n">
         <v>46324</v>
@@ -18771,7 +18771,7 @@
         <v>525</v>
       </c>
       <c r="P238" s="6" t="n">
-        <v>0.1381126839948839</v>
+        <v>0.1379400034680076</v>
       </c>
       <c r="Q238" s="10" t="inlineStr">
         <is>
@@ -18820,13 +18820,13 @@
         </is>
       </c>
       <c r="D239" s="15" t="n">
-        <v>166.01</v>
+        <v>168.5</v>
       </c>
       <c r="E239" s="16" t="n">
-        <v>0.3921</v>
+        <v>0.413</v>
       </c>
       <c r="F239" s="16" t="n">
-        <v>0.773</v>
+        <v>0.7996</v>
       </c>
       <c r="G239" s="17" t="n">
         <v>46324</v>
@@ -18881,13 +18881,13 @@
         </is>
       </c>
       <c r="D240" s="4" t="n">
-        <v>281.36</v>
+        <v>279.11</v>
       </c>
       <c r="E240" s="6" t="n">
-        <v>0.0553</v>
+        <v>0.0469</v>
       </c>
       <c r="F240" s="5" t="n">
-        <v>-0.0052</v>
+        <v>-0.0131</v>
       </c>
       <c r="G240" s="7" t="n">
         <v>46331</v>
@@ -18942,13 +18942,13 @@
         </is>
       </c>
       <c r="D241" s="15" t="n">
-        <v>1042.26</v>
+        <v>1043.96</v>
       </c>
       <c r="E241" s="16" t="n">
-        <v>0.0781</v>
+        <v>0.07980000000000001</v>
       </c>
       <c r="F241" s="16" t="n">
-        <v>0.0526</v>
+        <v>0.05429999999999999</v>
       </c>
       <c r="G241" s="17" t="n">
         <v>46295</v>
@@ -18977,7 +18977,7 @@
         <v>1525</v>
       </c>
       <c r="M241" s="16" t="n">
-        <v>0.4631665803158521</v>
+        <v>0.4607839380819188</v>
       </c>
       <c r="N241" s="14" t="inlineStr">
         <is>
@@ -19025,13 +19025,13 @@
         </is>
       </c>
       <c r="D242" s="4" t="n">
-        <v>232.27</v>
+        <v>232.8</v>
       </c>
       <c r="E242" s="6" t="n">
-        <v>0.0599</v>
+        <v>0.0624</v>
       </c>
       <c r="F242" s="6" t="n">
-        <v>0.05110000000000001</v>
+        <v>0.0535</v>
       </c>
       <c r="G242" s="7" t="n">
         <v>46336</v>
@@ -19086,13 +19086,13 @@
         </is>
       </c>
       <c r="D243" s="15" t="n">
-        <v>346.67</v>
+        <v>351.67</v>
       </c>
       <c r="E243" s="16" t="n">
-        <v>0.1826</v>
+        <v>0.1997</v>
       </c>
       <c r="F243" s="16" t="n">
-        <v>0.3215999999999999</v>
+        <v>0.3406</v>
       </c>
       <c r="G243" s="17" t="n">
         <v>46324</v>
@@ -19147,13 +19147,13 @@
         </is>
       </c>
       <c r="D244" s="4" t="n">
-        <v>137.38</v>
+        <v>137.68</v>
       </c>
       <c r="E244" s="6" t="n">
-        <v>0.0693</v>
+        <v>0.0716</v>
       </c>
       <c r="F244" s="6" t="n">
-        <v>0.4942</v>
+        <v>0.4975</v>
       </c>
       <c r="G244" s="7" t="n">
         <v>46323</v>
@@ -19182,7 +19182,7 @@
         <v>160</v>
       </c>
       <c r="M244" s="6" t="n">
-        <v>0.164652787887611</v>
+        <v>0.1621150493898895</v>
       </c>
       <c r="N244" s="3" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>150</v>
       </c>
       <c r="P244" s="6" t="n">
-        <v>0.09186198864463535</v>
+        <v>0.08948285880302144</v>
       </c>
       <c r="Q244" s="10" t="inlineStr">
         <is>
@@ -19238,13 +19238,13 @@
         </is>
       </c>
       <c r="D245" s="15" t="n">
-        <v>70.25</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="E245" s="16" t="n">
-        <v>0.0386</v>
+        <v>0.0355</v>
       </c>
       <c r="F245" s="16" t="n">
-        <v>0.3348</v>
+        <v>0.3308</v>
       </c>
       <c r="G245" s="17" t="n"/>
       <c r="H245" s="22" t="inlineStr">
@@ -19289,13 +19289,13 @@
         </is>
       </c>
       <c r="D246" s="4" t="n">
-        <v>226.05</v>
+        <v>227.38</v>
       </c>
       <c r="E246" s="6" t="n">
-        <v>0.0528</v>
+        <v>0.059</v>
       </c>
       <c r="F246" s="6" t="n">
-        <v>0.0828</v>
+        <v>0.0892</v>
       </c>
       <c r="G246" s="7" t="n"/>
       <c r="H246" s="12" t="inlineStr">
@@ -19314,7 +19314,7 @@
         <v>315</v>
       </c>
       <c r="M246" s="6" t="n">
-        <v>0.3934970139349701</v>
+        <v>0.3853461166329493</v>
       </c>
       <c r="N246" s="3" t="inlineStr">
         <is>
@@ -19325,7 +19325,7 @@
         <v>413</v>
       </c>
       <c r="P246" s="6" t="n">
-        <v>0.8270294182702941</v>
+        <v>0.8163426862520891</v>
       </c>
       <c r="Q246" s="10" t="inlineStr">
         <is>
@@ -19374,13 +19374,13 @@
         </is>
       </c>
       <c r="D247" s="15" t="n">
-        <v>364.82</v>
+        <v>362.81</v>
       </c>
       <c r="E247" s="25" t="n">
-        <v>-0.0323</v>
+        <v>-0.03759999999999999</v>
       </c>
       <c r="F247" s="25" t="n">
-        <v>-0.1988</v>
+        <v>-0.2033</v>
       </c>
       <c r="G247" s="17" t="n">
         <v>46331</v>
@@ -19435,13 +19435,13 @@
         </is>
       </c>
       <c r="D248" s="4" t="n">
-        <v>230.42</v>
+        <v>232.41</v>
       </c>
       <c r="E248" s="6" t="n">
-        <v>0.0215</v>
+        <v>0.0304</v>
       </c>
       <c r="F248" s="5" t="n">
-        <v>-0.169</v>
+        <v>-0.1619</v>
       </c>
       <c r="G248" s="7" t="n">
         <v>46322</v>
@@ -19495,10 +19495,10 @@
         <v>10.97</v>
       </c>
       <c r="E249" s="16" t="n">
-        <v>0.0155</v>
+        <v>0.0148</v>
       </c>
       <c r="F249" s="25" t="n">
-        <v>-0.3433</v>
+        <v>-0.2981</v>
       </c>
       <c r="G249" s="17" t="n"/>
       <c r="H249" s="22" t="inlineStr">
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="D250" s="4" t="n">
-        <v>190.37</v>
+        <v>191.33</v>
       </c>
       <c r="E250" s="6" t="n">
-        <v>0.4087</v>
+        <v>0.4158</v>
       </c>
       <c r="F250" s="6" t="n">
-        <v>0.3987</v>
+        <v>0.4058</v>
       </c>
       <c r="G250" s="7" t="n"/>
       <c r="H250" s="12" t="inlineStr">
@@ -19568,7 +19568,7 @@
         <v>150</v>
       </c>
       <c r="M250" s="5" t="n">
-        <v>-0.2120607238535484</v>
+        <v>-0.2160142162755449</v>
       </c>
       <c r="N250" s="3" t="inlineStr">
         <is>
@@ -19579,7 +19579,7 @@
         <v>130</v>
       </c>
       <c r="P250" s="5" t="n">
-        <v>-0.3171192940064086</v>
+        <v>-0.3205456541054723</v>
       </c>
       <c r="Q250" s="10" t="inlineStr">
         <is>
@@ -19620,13 +19620,13 @@
         </is>
       </c>
       <c r="D251" s="15" t="n">
-        <v>70.59999999999999</v>
+        <v>71.72</v>
       </c>
       <c r="E251" s="25" t="n">
-        <v>-0.0486</v>
+        <v>-0.0336</v>
       </c>
       <c r="F251" s="25" t="n">
-        <v>-0.2167</v>
+        <v>-0.2043</v>
       </c>
       <c r="G251" s="17" t="n">
         <v>46328</v>
@@ -19681,13 +19681,13 @@
         </is>
       </c>
       <c r="D252" s="4" t="n">
-        <v>275.03</v>
+        <v>275.98</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>-0.0624</v>
+        <v>-0.0591</v>
       </c>
       <c r="F252" s="5" t="n">
-        <v>-0.0558</v>
+        <v>-0.0525</v>
       </c>
       <c r="G252" s="7" t="n">
         <v>46331</v>
@@ -19742,13 +19742,13 @@
         </is>
       </c>
       <c r="D253" s="15" t="n">
-        <v>148.79</v>
+        <v>148.56</v>
       </c>
       <c r="E253" s="16" t="n">
-        <v>0.0158</v>
+        <v>0.0143</v>
       </c>
       <c r="F253" s="16" t="n">
-        <v>0.2395</v>
+        <v>0.2376</v>
       </c>
       <c r="G253" s="17" t="n"/>
       <c r="H253" s="22" t="inlineStr">
@@ -19767,7 +19767,7 @@
         <v>280</v>
       </c>
       <c r="M253" s="16" t="n">
-        <v>0.8818468983130587</v>
+        <v>0.8847603661820139</v>
       </c>
       <c r="N253" s="14" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>245</v>
       </c>
       <c r="P253" s="16" t="n">
-        <v>0.6466160360239265</v>
+        <v>0.6491653204092622</v>
       </c>
       <c r="Q253" s="20" t="inlineStr">
         <is>
@@ -19819,13 +19819,13 @@
         </is>
       </c>
       <c r="D254" s="4" t="n">
-        <v>371.03</v>
+        <v>371.76</v>
       </c>
       <c r="E254" s="6" t="n">
-        <v>0.0368</v>
+        <v>0.0388</v>
       </c>
       <c r="F254" s="6" t="n">
-        <v>0.1394</v>
+        <v>0.1417</v>
       </c>
       <c r="G254" s="7" t="n"/>
       <c r="H254" s="12" t="inlineStr">
@@ -19844,7 +19844,7 @@
         <v>420</v>
       </c>
       <c r="M254" s="6" t="n">
-        <v>0.1319839366088996</v>
+        <v>0.1297611362169142</v>
       </c>
       <c r="N254" s="3" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>415</v>
       </c>
       <c r="P254" s="6" t="n">
-        <v>0.1185079373635556</v>
+        <v>0.1163115988809985</v>
       </c>
       <c r="Q254" s="10" t="inlineStr">
         <is>
@@ -19904,13 +19904,13 @@
         </is>
       </c>
       <c r="D255" s="15" t="n">
-        <v>13.57</v>
+        <v>13.59</v>
       </c>
       <c r="E255" s="25" t="n">
-        <v>-0.1718</v>
+        <v>-0.1708</v>
       </c>
       <c r="F255" s="16" t="n">
-        <v>0.3309</v>
+        <v>0.3324</v>
       </c>
       <c r="G255" s="17" t="n"/>
       <c r="H255" s="22" t="inlineStr">
@@ -19955,13 +19955,13 @@
         </is>
       </c>
       <c r="D256" s="4" t="n">
-        <v>35.08</v>
+        <v>34.97</v>
       </c>
       <c r="E256" s="6" t="n">
-        <v>0.0453</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="F256" s="6" t="n">
-        <v>0.3487</v>
+        <v>0.3443</v>
       </c>
       <c r="G256" s="7" t="n">
         <v>46315</v>
@@ -20016,13 +20016,13 @@
         </is>
       </c>
       <c r="D257" s="15" t="n">
-        <v>184.64</v>
+        <v>184.04</v>
       </c>
       <c r="E257" s="16" t="n">
-        <v>0.1154</v>
+        <v>0.1118</v>
       </c>
       <c r="F257" s="16" t="n">
-        <v>0.4559</v>
+        <v>0.4512</v>
       </c>
       <c r="G257" s="17" t="n">
         <v>46330</v>
@@ -20077,13 +20077,13 @@
         </is>
       </c>
       <c r="D258" s="4" t="n">
-        <v>182.75</v>
+        <v>183.09</v>
       </c>
       <c r="E258" s="6" t="n">
-        <v>0.0156</v>
+        <v>0.0175</v>
       </c>
       <c r="F258" s="6" t="n">
-        <v>0.4813</v>
+        <v>0.4841</v>
       </c>
       <c r="G258" s="7" t="n">
         <v>46328</v>
@@ -20138,13 +20138,13 @@
         </is>
       </c>
       <c r="D259" s="15" t="n">
-        <v>121.6</v>
+        <v>121.82</v>
       </c>
       <c r="E259" s="25" t="n">
-        <v>-0.0565</v>
+        <v>-0.0548</v>
       </c>
       <c r="F259" s="25" t="n">
-        <v>-0.123</v>
+        <v>-0.1214</v>
       </c>
       <c r="G259" s="17" t="n"/>
       <c r="H259" s="22" t="inlineStr">
@@ -20199,13 +20199,13 @@
         </is>
       </c>
       <c r="D260" s="4" t="n">
-        <v>17.51</v>
+        <v>17.7</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>-0.1412</v>
+        <v>-0.1319</v>
       </c>
       <c r="F260" s="6" t="n">
-        <v>0.024</v>
+        <v>0.0351</v>
       </c>
       <c r="G260" s="7" t="n">
         <v>46331</v>
@@ -20260,13 +20260,13 @@
         </is>
       </c>
       <c r="D261" s="15" t="n">
-        <v>192.37</v>
+        <v>194.23</v>
       </c>
       <c r="E261" s="16" t="n">
-        <v>0.1967</v>
+        <v>0.2083</v>
       </c>
       <c r="F261" s="16" t="n">
-        <v>0.1242</v>
+        <v>0.1351</v>
       </c>
       <c r="G261" s="17" t="n">
         <v>46330</v>
@@ -20295,7 +20295,7 @@
         <v>265</v>
       </c>
       <c r="M261" s="16" t="n">
-        <v>0.3775536726100743</v>
+        <v>0.3643618390567884</v>
       </c>
       <c r="N261" s="14" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>179</v>
       </c>
       <c r="P261" s="25" t="n">
-        <v>-0.06950148151998754</v>
+        <v>-0.07841219173145235</v>
       </c>
       <c r="Q261" s="20" t="inlineStr">
         <is>
@@ -20351,13 +20351,13 @@
         </is>
       </c>
       <c r="D262" s="4" t="n">
-        <v>117.87</v>
+        <v>117.21</v>
       </c>
       <c r="E262" s="6" t="n">
-        <v>0.2335</v>
+        <v>0.2266</v>
       </c>
       <c r="F262" s="6" t="n">
-        <v>0.359</v>
+        <v>0.3514</v>
       </c>
       <c r="G262" s="7" t="n">
         <v>46322</v>
@@ -20412,13 +20412,13 @@
         </is>
       </c>
       <c r="D263" s="15" t="n">
-        <v>8.949999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="E263" s="16" t="n">
-        <v>0.0039</v>
+        <v>0.004500000000000001</v>
       </c>
       <c r="F263" s="16" t="n">
-        <v>0.1393</v>
+        <v>0.1399</v>
       </c>
       <c r="G263" s="17" t="n">
         <v>46339</v>
@@ -20473,13 +20473,13 @@
         </is>
       </c>
       <c r="D264" s="4" t="n">
-        <v>112.47</v>
+        <v>112.96</v>
       </c>
       <c r="E264" s="6" t="n">
-        <v>0.1237</v>
+        <v>0.1286</v>
       </c>
       <c r="F264" s="6" t="n">
-        <v>0.5486</v>
+        <v>0.5553</v>
       </c>
       <c r="G264" s="7" t="n"/>
       <c r="H264" s="12" t="inlineStr">
@@ -20524,13 +20524,13 @@
         </is>
       </c>
       <c r="D265" s="15" t="n">
-        <v>16.14</v>
+        <v>16.53</v>
       </c>
       <c r="E265" s="25" t="n">
-        <v>-0.09910000000000001</v>
+        <v>-0.0771</v>
       </c>
       <c r="F265" s="16" t="n">
-        <v>0.08650000000000001</v>
+        <v>0.1131</v>
       </c>
       <c r="G265" s="17" t="n">
         <v>46335</v>
@@ -20585,13 +20585,13 @@
         </is>
       </c>
       <c r="D266" s="4" t="n">
-        <v>369.41</v>
+        <v>365.4</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>-0.1029</v>
+        <v>-0.1127</v>
       </c>
       <c r="F266" s="6" t="n">
-        <v>0.04019999999999999</v>
+        <v>0.0289</v>
       </c>
       <c r="G266" s="7" t="n">
         <v>46317</v>
@@ -20660,13 +20660,13 @@
         </is>
       </c>
       <c r="D267" s="15" t="n">
-        <v>3.92</v>
+        <v>4.04</v>
       </c>
       <c r="E267" s="16" t="n">
-        <v>0.1807</v>
-      </c>
-      <c r="F267" s="25" t="n">
-        <v>-0.0249</v>
+        <v>0.2169</v>
+      </c>
+      <c r="F267" s="16" t="n">
+        <v>0.005</v>
       </c>
       <c r="G267" s="17" t="n">
         <v>46331</v>
@@ -20721,13 +20721,13 @@
         </is>
       </c>
       <c r="D268" s="4" t="n">
-        <v>23.55</v>
+        <v>23.8</v>
       </c>
       <c r="E268" s="6" t="n">
-        <v>0.1111</v>
+        <v>0.1232</v>
       </c>
       <c r="F268" s="6" t="n">
-        <v>0.3547</v>
+        <v>0.3694</v>
       </c>
       <c r="G268" s="7" t="n"/>
       <c r="H268" s="12" t="inlineStr">
@@ -20772,13 +20772,13 @@
         </is>
       </c>
       <c r="D269" s="15" t="n">
-        <v>20.14</v>
+        <v>20.32</v>
       </c>
       <c r="E269" s="16" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.0901</v>
       </c>
       <c r="F269" s="16" t="n">
-        <v>0.4066</v>
+        <v>0.4195</v>
       </c>
       <c r="G269" s="17" t="n"/>
       <c r="H269" s="22" t="inlineStr">
@@ -20823,13 +20823,13 @@
         </is>
       </c>
       <c r="D270" s="4" t="n">
-        <v>203.17</v>
+        <v>209.47</v>
       </c>
       <c r="E270" s="6" t="n">
-        <v>0.0756</v>
+        <v>0.109</v>
       </c>
       <c r="F270" s="5" t="n">
-        <v>-0.0704</v>
+        <v>-0.0416</v>
       </c>
       <c r="G270" s="7" t="n">
         <v>46328</v>
@@ -20884,13 +20884,13 @@
         </is>
       </c>
       <c r="D271" s="15" t="n">
-        <v>209.9</v>
+        <v>209.22</v>
       </c>
       <c r="E271" s="25" t="n">
-        <v>-0.0401</v>
+        <v>-0.0433</v>
       </c>
       <c r="F271" s="16" t="n">
-        <v>0.434</v>
+        <v>0.4293</v>
       </c>
       <c r="G271" s="17" t="n">
         <v>46316</v>
@@ -20965,13 +20965,13 @@
         </is>
       </c>
       <c r="D272" s="4" t="n">
-        <v>41.02</v>
+        <v>41.2</v>
       </c>
       <c r="E272" s="6" t="n">
-        <v>0.1014</v>
+        <v>0.1063</v>
       </c>
       <c r="F272" s="6" t="n">
-        <v>0.3147</v>
+        <v>0.3205</v>
       </c>
       <c r="G272" s="7" t="n">
         <v>46329</v>
@@ -21026,13 +21026,13 @@
         </is>
       </c>
       <c r="D273" s="15" t="n">
-        <v>332.6</v>
-      </c>
-      <c r="E273" s="25" t="n">
-        <v>-0.0005</v>
+        <v>339.39</v>
+      </c>
+      <c r="E273" s="16" t="n">
+        <v>0.0199</v>
       </c>
       <c r="F273" s="16" t="n">
-        <v>0.2545</v>
+        <v>0.2801</v>
       </c>
       <c r="G273" s="17" t="n"/>
       <c r="H273" s="22" t="inlineStr">
@@ -21051,7 +21051,7 @@
         <v>320</v>
       </c>
       <c r="M273" s="25" t="n">
-        <v>-0.0378833433553819</v>
+        <v>-0.05713191313827746</v>
       </c>
       <c r="N273" s="14" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>280</v>
       </c>
       <c r="P273" s="25" t="n">
-        <v>-0.1581479254359592</v>
+        <v>-0.1749904239959928</v>
       </c>
       <c r="Q273" s="20" t="inlineStr">
         <is>
@@ -21103,13 +21103,13 @@
         </is>
       </c>
       <c r="D274" s="4" t="n">
-        <v>401.13</v>
+        <v>401.85</v>
       </c>
       <c r="E274" s="6" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="F274" s="6" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="G274" s="7" t="n"/>
       <c r="H274" s="12" t="inlineStr">
@@ -21128,7 +21128,7 @@
         <v>535</v>
       </c>
       <c r="M274" s="6" t="n">
-        <v>0.3337322065165906</v>
+        <v>0.3313425407490356</v>
       </c>
       <c r="N274" s="3" t="inlineStr"/>
       <c r="O274" s="9" t="n"/>
@@ -21172,13 +21172,13 @@
         </is>
       </c>
       <c r="D275" s="15" t="n">
-        <v>6.11</v>
+        <v>6.17</v>
       </c>
       <c r="E275" s="25" t="n">
-        <v>-0.1653</v>
+        <v>-0.1571</v>
       </c>
       <c r="F275" s="25" t="n">
-        <v>-0.0177</v>
+        <v>-0.008</v>
       </c>
       <c r="G275" s="17" t="n">
         <v>46331</v>
@@ -21233,13 +21233,13 @@
         </is>
       </c>
       <c r="D276" s="4" t="n">
-        <v>89.38</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="E276" s="6" t="n">
-        <v>0.3312</v>
+        <v>0.3217</v>
       </c>
       <c r="F276" s="6" t="n">
-        <v>0.478</v>
+        <v>0.4675</v>
       </c>
       <c r="G276" s="7" t="n">
         <v>46322</v>
@@ -21294,13 +21294,13 @@
         </is>
       </c>
       <c r="D277" s="15" t="n">
-        <v>94.18000000000001</v>
+        <v>95.36</v>
       </c>
       <c r="E277" s="25" t="n">
-        <v>-0.0356</v>
+        <v>-0.0236</v>
       </c>
       <c r="F277" s="25" t="n">
-        <v>-0.1991</v>
+        <v>-0.1891</v>
       </c>
       <c r="G277" s="17" t="n">
         <v>46331</v>
@@ -21355,13 +21355,13 @@
         </is>
       </c>
       <c r="D278" s="4" t="n">
-        <v>209.3</v>
+        <v>210.01</v>
       </c>
       <c r="E278" s="6" t="n">
-        <v>0.0284</v>
+        <v>0.0319</v>
       </c>
       <c r="F278" s="6" t="n">
-        <v>0.0529</v>
+        <v>0.0564</v>
       </c>
       <c r="G278" s="7" t="n">
         <v>46330</v>
@@ -21416,13 +21416,13 @@
         </is>
       </c>
       <c r="D279" s="15" t="n">
-        <v>379.64</v>
+        <v>381.54</v>
       </c>
       <c r="E279" s="16" t="n">
-        <v>0.0104</v>
+        <v>0.0154</v>
       </c>
       <c r="F279" s="16" t="n">
-        <v>0.0158</v>
+        <v>0.0208</v>
       </c>
       <c r="G279" s="17" t="n">
         <v>46322</v>
@@ -21477,13 +21477,13 @@
         </is>
       </c>
       <c r="D280" s="4" t="n">
-        <v>57.87</v>
+        <v>57.75</v>
       </c>
       <c r="E280" s="5" t="n">
-        <v>-0.0395</v>
+        <v>-0.0415</v>
       </c>
       <c r="F280" s="6" t="n">
-        <v>0.1494</v>
+        <v>0.147</v>
       </c>
       <c r="G280" s="7" t="n">
         <v>46330</v>
@@ -21538,13 +21538,13 @@
         </is>
       </c>
       <c r="D281" s="15" t="n">
-        <v>442.33</v>
+        <v>445.14</v>
       </c>
       <c r="E281" s="16" t="n">
-        <v>0.0558</v>
+        <v>0.0625</v>
       </c>
       <c r="F281" s="16" t="n">
-        <v>0.0644</v>
+        <v>0.0711</v>
       </c>
       <c r="G281" s="17" t="n">
         <v>46310</v>
@@ -21621,13 +21621,13 @@
         </is>
       </c>
       <c r="D282" s="4" t="n">
-        <v>125.44</v>
+        <v>124.02</v>
       </c>
       <c r="E282" s="6" t="n">
-        <v>0.1348</v>
+        <v>0.1219</v>
       </c>
       <c r="F282" s="5" t="n">
-        <v>-0.134</v>
+        <v>-0.1438</v>
       </c>
       <c r="G282" s="7" t="n">
         <v>46330</v>
@@ -21682,13 +21682,13 @@
         </is>
       </c>
       <c r="D283" s="15" t="n">
-        <v>260.28</v>
+        <v>266.06</v>
       </c>
       <c r="E283" s="16" t="n">
-        <v>0.1553</v>
+        <v>0.1809</v>
       </c>
       <c r="F283" s="16" t="n">
-        <v>0.4065</v>
+        <v>0.4377</v>
       </c>
       <c r="G283" s="17" t="n">
         <v>46324</v>
@@ -21743,13 +21743,13 @@
         </is>
       </c>
       <c r="D284" s="4" t="n">
-        <v>269.55</v>
+        <v>270.87</v>
       </c>
       <c r="E284" s="6" t="n">
-        <v>0.0196</v>
+        <v>0.0246</v>
       </c>
       <c r="F284" s="5" t="n">
-        <v>-0.0542</v>
+        <v>-0.0495</v>
       </c>
       <c r="G284" s="7" t="n">
         <v>46315</v>
@@ -21778,7 +21778,7 @@
         <v>300</v>
       </c>
       <c r="M284" s="6" t="n">
-        <v>0.1129660545353366</v>
+        <v>0.1075423634954037</v>
       </c>
       <c r="N284" s="3" t="inlineStr">
         <is>
@@ -21789,7 +21789,7 @@
         <v>316</v>
       </c>
       <c r="P284" s="6" t="n">
-        <v>0.1723242441105546</v>
+        <v>0.1666112895484919</v>
       </c>
       <c r="Q284" s="10" t="inlineStr">
         <is>
@@ -21846,13 +21846,13 @@
         </is>
       </c>
       <c r="D285" s="15" t="n">
-        <v>331.51</v>
+        <v>332.46</v>
       </c>
       <c r="E285" s="25" t="n">
-        <v>-0.0548</v>
+        <v>-0.0521</v>
       </c>
       <c r="F285" s="16" t="n">
-        <v>0.1504</v>
+        <v>0.1537</v>
       </c>
       <c r="G285" s="17" t="n">
         <v>46330</v>
@@ -21881,7 +21881,7 @@
         <v>335</v>
       </c>
       <c r="M285" s="16" t="n">
-        <v>0.01052758589484483</v>
+        <v>0.007640016844131687</v>
       </c>
       <c r="N285" s="14" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>375</v>
       </c>
       <c r="P285" s="16" t="n">
-        <v>0.1311875961509457</v>
+        <v>0.1279552427359683</v>
       </c>
       <c r="Q285" s="20" t="inlineStr">
         <is>
@@ -21933,13 +21933,13 @@
         </is>
       </c>
       <c r="D286" s="4" t="n">
-        <v>43.08</v>
+        <v>43.21</v>
       </c>
       <c r="E286" s="5" t="n">
-        <v>-0.08199999999999999</v>
+        <v>-0.0793</v>
       </c>
       <c r="F286" s="6" t="n">
-        <v>0.4886</v>
+        <v>0.4931</v>
       </c>
       <c r="G286" s="7" t="n">
         <v>46330</v>
@@ -21994,13 +21994,13 @@
         </is>
       </c>
       <c r="D287" s="15" t="n">
-        <v>7.2</v>
+        <v>7.24</v>
       </c>
       <c r="E287" s="16" t="n">
-        <v>0.0707</v>
+        <v>0.0766</v>
       </c>
       <c r="F287" s="25" t="n">
-        <v>-0.07400000000000001</v>
+        <v>-0.0689</v>
       </c>
       <c r="G287" s="17" t="n"/>
       <c r="H287" s="22" t="inlineStr">
@@ -22045,13 +22045,13 @@
         </is>
       </c>
       <c r="D288" s="4" t="n">
-        <v>193.97</v>
+        <v>191.92</v>
       </c>
       <c r="E288" s="5" t="n">
-        <v>-0.0302</v>
+        <v>-0.0404</v>
       </c>
       <c r="F288" s="6" t="n">
-        <v>0.5169</v>
+        <v>0.5009</v>
       </c>
       <c r="G288" s="7" t="n"/>
       <c r="H288" s="12" t="inlineStr">
@@ -22096,13 +22096,13 @@
         </is>
       </c>
       <c r="D289" s="15" t="n">
-        <v>441.63</v>
+        <v>448.17</v>
       </c>
       <c r="E289" s="25" t="n">
-        <v>-0.0388</v>
+        <v>-0.0245</v>
       </c>
       <c r="F289" s="25" t="n">
-        <v>-0.209</v>
+        <v>-0.1973</v>
       </c>
       <c r="G289" s="17" t="n">
         <v>46324</v>
@@ -22131,7 +22131,7 @@
         <v>730</v>
       </c>
       <c r="M289" s="16" t="n">
-        <v>0.6529674161628513</v>
+        <v>0.6288461967556953</v>
       </c>
       <c r="N289" s="14" t="inlineStr">
         <is>
@@ -22142,7 +22142,7 @@
         <v>575</v>
       </c>
       <c r="P289" s="16" t="n">
-        <v>0.3019948825940267</v>
+        <v>0.2829952919651025</v>
       </c>
       <c r="Q289" s="20" t="inlineStr">
         <is>
@@ -22183,13 +22183,13 @@
         </is>
       </c>
       <c r="D290" s="4" t="n">
-        <v>27.66</v>
+        <v>27.71</v>
       </c>
       <c r="E290" s="6" t="n">
-        <v>0.0738</v>
+        <v>0.0757</v>
       </c>
       <c r="F290" s="6" t="n">
-        <v>0.0655</v>
+        <v>0.0674</v>
       </c>
       <c r="G290" s="7" t="n">
         <v>46330</v>
@@ -22244,13 +22244,13 @@
         </is>
       </c>
       <c r="D291" s="15" t="n">
-        <v>89.56</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="E291" s="25" t="n">
-        <v>-0.1663</v>
+        <v>-0.1539</v>
       </c>
       <c r="F291" s="16" t="n">
-        <v>0.06480000000000001</v>
+        <v>0.08070000000000001</v>
       </c>
       <c r="G291" s="17" t="n"/>
       <c r="H291" s="22" t="inlineStr">
@@ -22295,13 +22295,13 @@
         </is>
       </c>
       <c r="D292" s="4" t="n">
-        <v>204.45</v>
+        <v>207.13</v>
       </c>
       <c r="E292" s="6" t="n">
-        <v>0.1249</v>
+        <v>0.1397</v>
       </c>
       <c r="F292" s="6" t="n">
-        <v>0.4635</v>
+        <v>0.4827</v>
       </c>
       <c r="G292" s="7" t="n"/>
       <c r="H292" s="12" t="inlineStr">
@@ -22346,13 +22346,13 @@
         </is>
       </c>
       <c r="D293" s="15" t="n">
-        <v>282.29</v>
+        <v>279.46</v>
       </c>
       <c r="E293" s="25" t="n">
-        <v>-0.07480000000000001</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="F293" s="25" t="n">
-        <v>-0.0408</v>
+        <v>-0.0504</v>
       </c>
       <c r="G293" s="17" t="n">
         <v>46331</v>
@@ -22407,13 +22407,13 @@
         </is>
       </c>
       <c r="D294" s="4" t="n">
-        <v>86.02</v>
+        <v>86.09</v>
       </c>
       <c r="E294" s="5" t="n">
-        <v>-0.1135</v>
+        <v>-0.1127</v>
       </c>
       <c r="F294" s="6" t="n">
-        <v>0.0283</v>
+        <v>0.0292</v>
       </c>
       <c r="G294" s="7" t="n"/>
       <c r="H294" s="12" t="inlineStr">
@@ -22458,13 +22458,13 @@
         </is>
       </c>
       <c r="D295" s="15" t="n">
-        <v>130.82</v>
+        <v>129.79</v>
       </c>
       <c r="E295" s="25" t="n">
-        <v>-0.05429999999999999</v>
+        <v>-0.0617</v>
       </c>
       <c r="F295" s="25" t="n">
-        <v>-0.0479</v>
+        <v>-0.0554</v>
       </c>
       <c r="G295" s="17" t="n">
         <v>46331</v>
@@ -22493,7 +22493,7 @@
         <v>166</v>
       </c>
       <c r="M295" s="16" t="n">
-        <v>0.2689191255159762</v>
+        <v>0.2789891362970954</v>
       </c>
       <c r="N295" s="14" t="inlineStr"/>
       <c r="O295" s="19" t="n"/>
@@ -22541,13 +22541,13 @@
         </is>
       </c>
       <c r="D296" s="4" t="n">
-        <v>28.13</v>
+        <v>28.27</v>
       </c>
       <c r="E296" s="5" t="n">
-        <v>-0.1304</v>
+        <v>-0.1261</v>
       </c>
       <c r="F296" s="5" t="n">
-        <v>-0.08960000000000001</v>
+        <v>-0.0851</v>
       </c>
       <c r="G296" s="7" t="n">
         <v>46317</v>
@@ -22602,13 +22602,13 @@
         </is>
       </c>
       <c r="D297" s="15" t="n">
-        <v>270.43</v>
+        <v>269.98</v>
       </c>
       <c r="E297" s="25" t="n">
-        <v>-0.0398</v>
+        <v>-0.0414</v>
       </c>
       <c r="F297" s="16" t="n">
-        <v>0.0277</v>
+        <v>0.026</v>
       </c>
       <c r="G297" s="17" t="n">
         <v>46322</v>
@@ -22637,7 +22637,7 @@
         <v>275</v>
       </c>
       <c r="M297" s="16" t="n">
-        <v>0.01689901268350402</v>
+        <v>0.01859396992369798</v>
       </c>
       <c r="N297" s="14" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>312</v>
       </c>
       <c r="P297" s="16" t="n">
-        <v>0.15371815257183</v>
+        <v>0.155641158604341</v>
       </c>
       <c r="Q297" s="20" t="inlineStr">
         <is>
@@ -22701,13 +22701,13 @@
         </is>
       </c>
       <c r="D298" s="4" t="n">
-        <v>33.43</v>
+        <v>33.42</v>
       </c>
       <c r="E298" s="5" t="n">
-        <v>-0.0532</v>
+        <v>-0.0535</v>
       </c>
       <c r="F298" s="5" t="n">
-        <v>-0.1272</v>
+        <v>-0.1274</v>
       </c>
       <c r="G298" s="7" t="n">
         <v>46322</v>
@@ -22766,13 +22766,13 @@
         </is>
       </c>
       <c r="D299" s="15" t="n">
-        <v>72.13</v>
+        <v>72.16</v>
       </c>
       <c r="E299" s="25" t="n">
-        <v>-0.0591</v>
+        <v>-0.0587</v>
       </c>
       <c r="F299" s="16" t="n">
-        <v>0.1359</v>
+        <v>0.1364</v>
       </c>
       <c r="G299" s="17" t="n">
         <v>46310</v>
@@ -22827,13 +22827,13 @@
         </is>
       </c>
       <c r="D300" s="4" t="n">
-        <v>458.88</v>
+        <v>457.5</v>
       </c>
       <c r="E300" s="5" t="n">
-        <v>-0.0588</v>
+        <v>-0.0617</v>
       </c>
       <c r="F300" s="5" t="n">
-        <v>-0.09369999999999999</v>
+        <v>-0.0964</v>
       </c>
       <c r="G300" s="7" t="n">
         <v>46325</v>
@@ -22862,7 +22862,7 @@
         <v>570</v>
       </c>
       <c r="M300" s="6" t="n">
-        <v>0.2421548117154812</v>
+        <v>0.2459016393442623</v>
       </c>
       <c r="N300" s="3" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>525</v>
       </c>
       <c r="P300" s="6" t="n">
-        <v>0.1440899581589958</v>
+        <v>0.1475409836065574</v>
       </c>
       <c r="Q300" s="10" t="inlineStr">
         <is>
@@ -22926,13 +22926,13 @@
         </is>
       </c>
       <c r="D301" s="15" t="n">
-        <v>499.92</v>
+        <v>499.67</v>
       </c>
       <c r="E301" s="25" t="n">
-        <v>-0.0654</v>
+        <v>-0.0659</v>
       </c>
       <c r="F301" s="25" t="n">
-        <v>-0.0859</v>
+        <v>-0.0863</v>
       </c>
       <c r="G301" s="17" t="n">
         <v>46329</v>
@@ -22961,7 +22961,7 @@
         <v>616</v>
       </c>
       <c r="M301" s="16" t="n">
-        <v>0.232197151544247</v>
+        <v>0.232813657013629</v>
       </c>
       <c r="N301" s="14" t="inlineStr"/>
       <c r="O301" s="19" t="n"/>
@@ -23005,13 +23005,13 @@
         </is>
       </c>
       <c r="D302" s="4" t="n">
-        <v>244.87</v>
-      </c>
-      <c r="E302" s="6" t="n">
-        <v>0.0051</v>
+        <v>242.4</v>
+      </c>
+      <c r="E302" s="5" t="n">
+        <v>-0.005</v>
       </c>
       <c r="F302" s="6" t="n">
-        <v>0.0154</v>
+        <v>0.0052</v>
       </c>
       <c r="G302" s="7" t="n">
         <v>46321</v>
@@ -23040,7 +23040,7 @@
         <v>283</v>
       </c>
       <c r="M302" s="6" t="n">
-        <v>0.1557152774941806</v>
+        <v>0.1674917491749175</v>
       </c>
       <c r="N302" s="3" t="inlineStr"/>
       <c r="O302" s="9" t="n"/>
@@ -23086,13 +23086,13 @@
         </is>
       </c>
       <c r="D303" s="15" t="n">
-        <v>240.54</v>
+        <v>238.31</v>
       </c>
       <c r="E303" s="25" t="n">
-        <v>-0.0484</v>
+        <v>-0.0573</v>
       </c>
       <c r="F303" s="16" t="n">
-        <v>0.0284</v>
+        <v>0.0189</v>
       </c>
       <c r="G303" s="17" t="n">
         <v>46316</v>
@@ -23121,7 +23121,7 @@
         <v>246</v>
       </c>
       <c r="M303" s="16" t="n">
-        <v>0.02269892741332006</v>
+        <v>0.03226889345810079</v>
       </c>
       <c r="N303" s="14" t="inlineStr"/>
       <c r="O303" s="19" t="n"/>
@@ -23169,13 +23169,13 @@
         </is>
       </c>
       <c r="D304" s="4" t="n">
-        <v>105.43</v>
+        <v>104.93</v>
       </c>
       <c r="E304" s="5" t="n">
-        <v>-0.0721</v>
+        <v>-0.0766</v>
       </c>
       <c r="F304" s="5" t="n">
-        <v>-0.0731</v>
+        <v>-0.0775</v>
       </c>
       <c r="G304" s="7" t="n">
         <v>46322</v>
@@ -23204,7 +23204,7 @@
         <v>130</v>
       </c>
       <c r="M304" s="6" t="n">
-        <v>0.2330456226880394</v>
+        <v>0.2389211855522729</v>
       </c>
       <c r="N304" s="3" t="inlineStr">
         <is>
@@ -23215,7 +23215,7 @@
         <v>128</v>
       </c>
       <c r="P304" s="6" t="n">
-        <v>0.2140756900313003</v>
+        <v>0.2198608596206994</v>
       </c>
       <c r="Q304" s="10" t="inlineStr">
         <is>
@@ -23264,13 +23264,13 @@
         </is>
       </c>
       <c r="D305" s="15" t="n">
-        <v>99.15000000000001</v>
+        <v>99.01000000000001</v>
       </c>
       <c r="E305" s="25" t="n">
-        <v>-0.0873</v>
+        <v>-0.0886</v>
       </c>
       <c r="F305" s="25" t="n">
-        <v>-0.0536</v>
+        <v>-0.055</v>
       </c>
       <c r="G305" s="17" t="n">
         <v>46301</v>
@@ -23299,7 +23299,7 @@
         <v>135</v>
       </c>
       <c r="M305" s="16" t="n">
-        <v>0.361573373676248</v>
+        <v>0.3634986365013634</v>
       </c>
       <c r="N305" s="14" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>125</v>
       </c>
       <c r="P305" s="16" t="n">
-        <v>0.2607160867372667</v>
+        <v>0.2624987375012625</v>
       </c>
       <c r="Q305" s="20" t="inlineStr"/>
       <c r="R305" s="19" t="n"/>
@@ -23345,13 +23345,13 @@
         </is>
       </c>
       <c r="D306" s="4" t="n">
-        <v>324.01</v>
+        <v>321.31</v>
       </c>
       <c r="E306" s="5" t="n">
-        <v>-0.06509999999999999</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="F306" s="6" t="n">
-        <v>0.0434</v>
+        <v>0.0347</v>
       </c>
       <c r="G306" s="7" t="n">
         <v>46322</v>
@@ -23380,7 +23380,7 @@
         <v>350</v>
       </c>
       <c r="M306" s="6" t="n">
-        <v>0.08021357365513414</v>
+        <v>0.08929071613083937</v>
       </c>
       <c r="N306" s="3" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>400</v>
       </c>
       <c r="P306" s="6" t="n">
-        <v>0.2345297984630104</v>
+        <v>0.2449036755781021</v>
       </c>
       <c r="Q306" s="10" t="inlineStr">
         <is>
@@ -23432,13 +23432,13 @@
         </is>
       </c>
       <c r="D307" s="15" t="n">
-        <v>112.74</v>
+        <v>113.66</v>
       </c>
       <c r="E307" s="16" t="n">
-        <v>0.0386</v>
+        <v>0.0471</v>
       </c>
       <c r="F307" s="16" t="n">
-        <v>0.4994</v>
+        <v>0.5115999999999999</v>
       </c>
       <c r="G307" s="17" t="n"/>
       <c r="H307" s="22" t="inlineStr">
@@ -23479,13 +23479,13 @@
         </is>
       </c>
       <c r="D308" s="4" t="n">
-        <v>51.62</v>
+        <v>51.15</v>
       </c>
       <c r="E308" s="5" t="n">
-        <v>-0.08789999999999999</v>
+        <v>-0.09630000000000001</v>
       </c>
       <c r="F308" s="5" t="n">
-        <v>-0.0857</v>
+        <v>-0.094</v>
       </c>
       <c r="G308" s="7" t="n">
         <v>46267</v>
@@ -23540,13 +23540,13 @@
         </is>
       </c>
       <c r="D309" s="15" t="n">
-        <v>67.84999999999999</v>
+        <v>67.62</v>
       </c>
       <c r="E309" s="25" t="n">
-        <v>-0.08160000000000001</v>
+        <v>-0.08470000000000001</v>
       </c>
       <c r="F309" s="25" t="n">
-        <v>-0.1499</v>
+        <v>-0.1527</v>
       </c>
       <c r="G309" s="17" t="n">
         <v>46315</v>
@@ -23575,14 +23575,14 @@
         <v>83</v>
       </c>
       <c r="M309" s="16" t="n">
-        <v>0.2232866617538689</v>
+        <v>0.2274475007394261</v>
       </c>
       <c r="N309" s="14" t="inlineStr"/>
       <c r="O309" s="19" t="n">
         <v>87</v>
       </c>
       <c r="P309" s="16" t="n">
-        <v>0.2822402358142964</v>
+        <v>0.2866015971606033</v>
       </c>
       <c r="Q309" s="20" t="inlineStr"/>
       <c r="R309" s="19" t="n"/>
@@ -23617,13 +23617,13 @@
         </is>
       </c>
       <c r="D310" s="4" t="n">
-        <v>174.84</v>
+        <v>174.6</v>
       </c>
       <c r="E310" s="5" t="n">
-        <v>-0.005500000000000001</v>
+        <v>-0.0068</v>
       </c>
       <c r="F310" s="6" t="n">
-        <v>0.0619</v>
+        <v>0.0604</v>
       </c>
       <c r="G310" s="7" t="n">
         <v>46322</v>
@@ -23652,7 +23652,7 @@
         <v>200</v>
       </c>
       <c r="M310" s="6" t="n">
-        <v>0.1439029970258522</v>
+        <v>0.145475372279496</v>
       </c>
       <c r="N310" s="3" t="inlineStr"/>
       <c r="O310" s="9" t="n"/>
@@ -23700,13 +23700,13 @@
         </is>
       </c>
       <c r="D311" s="15" t="n">
-        <v>141.99</v>
+        <v>143.21</v>
       </c>
       <c r="E311" s="25" t="n">
-        <v>-0.0665</v>
+        <v>-0.0584</v>
       </c>
       <c r="F311" s="16" t="n">
-        <v>0.0475</v>
+        <v>0.0565</v>
       </c>
       <c r="G311" s="17" t="n">
         <v>46317</v>
@@ -23765,13 +23765,13 @@
         </is>
       </c>
       <c r="D312" s="4" t="n">
-        <v>186.84</v>
+        <v>186.33</v>
       </c>
       <c r="E312" s="5" t="n">
-        <v>-0.0198</v>
+        <v>-0.0225</v>
       </c>
       <c r="F312" s="6" t="n">
-        <v>0.0418</v>
+        <v>0.039</v>
       </c>
       <c r="G312" s="7" t="n">
         <v>46317</v>
@@ -23800,7 +23800,7 @@
         <v>220</v>
       </c>
       <c r="M312" s="6" t="n">
-        <v>0.1774780560907728</v>
+        <v>0.1807009069929694</v>
       </c>
       <c r="N312" s="3" t="inlineStr">
         <is>
@@ -23811,7 +23811,7 @@
         <v>230</v>
       </c>
       <c r="P312" s="6" t="n">
-        <v>0.2309997859130807</v>
+        <v>0.2343691300381044</v>
       </c>
       <c r="Q312" s="10" t="inlineStr">
         <is>
@@ -23852,13 +23852,13 @@
         </is>
       </c>
       <c r="D313" s="15" t="n">
-        <v>1051.04</v>
+        <v>1057.26</v>
       </c>
       <c r="E313" s="25" t="n">
-        <v>-0.0135</v>
+        <v>-0.0076</v>
       </c>
       <c r="F313" s="16" t="n">
-        <v>0.0169</v>
+        <v>0.0229</v>
       </c>
       <c r="G313" s="17" t="n">
         <v>46330</v>
@@ -23887,7 +23887,7 @@
         <v>1200</v>
       </c>
       <c r="M313" s="16" t="n">
-        <v>0.1417262901507079</v>
+        <v>0.1350093638272516</v>
       </c>
       <c r="N313" s="14" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>1240</v>
       </c>
       <c r="P313" s="16" t="n">
-        <v>0.1797838331557315</v>
+        <v>0.17284300928816</v>
       </c>
       <c r="Q313" s="20" t="inlineStr">
         <is>
@@ -23943,13 +23943,13 @@
         </is>
       </c>
       <c r="D314" s="4" t="n">
-        <v>110.15</v>
+        <v>110.63</v>
       </c>
       <c r="E314" s="5" t="n">
-        <v>-0.0565</v>
+        <v>-0.05230000000000001</v>
       </c>
       <c r="F314" s="5" t="n">
-        <v>-0.1176</v>
+        <v>-0.1138</v>
       </c>
       <c r="G314" s="7" t="n">
         <v>46325</v>
@@ -23978,7 +23978,7 @@
         <v>129</v>
       </c>
       <c r="M314" s="6" t="n">
-        <v>0.1711302768951429</v>
+        <v>0.1660489921359487</v>
       </c>
       <c r="N314" s="3" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>122</v>
       </c>
       <c r="P314" s="6" t="n">
-        <v>0.1075805719473445</v>
+        <v>0.1027750158184941</v>
       </c>
       <c r="Q314" s="10" t="inlineStr">
         <is>
@@ -24030,13 +24030,13 @@
         </is>
       </c>
       <c r="D315" s="15" t="n">
-        <v>57.08</v>
+        <v>56.65</v>
       </c>
       <c r="E315" s="25" t="n">
-        <v>-0.0883</v>
+        <v>-0.095</v>
       </c>
       <c r="F315" s="25" t="n">
-        <v>-0.1181</v>
+        <v>-0.1247</v>
       </c>
       <c r="G315" s="17" t="n">
         <v>46328</v>
@@ -24065,14 +24065,14 @@
         <v>65</v>
       </c>
       <c r="M315" s="16" t="n">
-        <v>0.1387526278906798</v>
+        <v>0.147396293027361</v>
       </c>
       <c r="N315" s="14" t="inlineStr"/>
       <c r="O315" s="19" t="n">
         <v>67</v>
       </c>
       <c r="P315" s="16" t="n">
-        <v>0.1737911702873161</v>
+        <v>0.1827007943512798</v>
       </c>
       <c r="Q315" s="20" t="inlineStr">
         <is>
@@ -24113,13 +24113,13 @@
         </is>
       </c>
       <c r="D316" s="4" t="n">
-        <v>135.24</v>
+        <v>135.82</v>
       </c>
       <c r="E316" s="5" t="n">
-        <v>-0.0463</v>
+        <v>-0.04219999999999999</v>
       </c>
       <c r="F316" s="5" t="n">
-        <v>-0.06809999999999999</v>
+        <v>-0.0641</v>
       </c>
       <c r="G316" s="7" t="n">
         <v>46310</v>
@@ -24148,7 +24148,7 @@
         <v>167</v>
       </c>
       <c r="M316" s="6" t="n">
-        <v>0.2348417627920733</v>
+        <v>0.2295685466058019</v>
       </c>
       <c r="N316" s="3" t="inlineStr"/>
       <c r="O316" s="9" t="n"/>
@@ -24192,13 +24192,13 @@
         </is>
       </c>
       <c r="D317" s="15" t="n">
-        <v>297.33</v>
+        <v>296.67</v>
       </c>
       <c r="E317" s="25" t="n">
-        <v>-0.078</v>
+        <v>-0.0801</v>
       </c>
       <c r="F317" s="25" t="n">
-        <v>-0.0561</v>
+        <v>-0.0582</v>
       </c>
       <c r="G317" s="17" t="n">
         <v>46330</v>
@@ -24234,7 +24234,7 @@
         <v>316</v>
       </c>
       <c r="P317" s="16" t="n">
-        <v>0.06279218376887639</v>
+        <v>0.06515657127448</v>
       </c>
       <c r="Q317" s="20" t="inlineStr">
         <is>
@@ -24275,13 +24275,13 @@
         </is>
       </c>
       <c r="D318" s="4" t="n">
-        <v>205.04</v>
+        <v>204.98</v>
       </c>
       <c r="E318" s="5" t="n">
-        <v>-0.0607</v>
+        <v>-0.061</v>
       </c>
       <c r="F318" s="5" t="n">
-        <v>-0.0895</v>
+        <v>-0.0898</v>
       </c>
       <c r="G318" s="7" t="n">
         <v>46328</v>
@@ -24317,7 +24317,7 @@
         <v>215</v>
       </c>
       <c r="P318" s="6" t="n">
-        <v>0.04857588763168166</v>
+        <v>0.04888281783588648</v>
       </c>
       <c r="Q318" s="10" t="inlineStr">
         <is>
@@ -24358,13 +24358,13 @@
         </is>
       </c>
       <c r="D319" s="15" t="n">
-        <v>113.95</v>
+        <v>113.74</v>
       </c>
       <c r="E319" s="25" t="n">
-        <v>-0.0634</v>
+        <v>-0.06509999999999999</v>
       </c>
       <c r="F319" s="25" t="n">
-        <v>-0.0504</v>
+        <v>-0.0522</v>
       </c>
       <c r="G319" s="17" t="n">
         <v>46330</v>
@@ -24393,7 +24393,7 @@
         <v>142</v>
       </c>
       <c r="M319" s="16" t="n">
-        <v>0.2461605967529618</v>
+        <v>0.2484614032002814</v>
       </c>
       <c r="N319" s="14" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>137</v>
       </c>
       <c r="P319" s="16" t="n">
-        <v>0.2022817025010969</v>
+        <v>0.2045014946368912</v>
       </c>
       <c r="Q319" s="20" t="inlineStr">
         <is>
@@ -24453,13 +24453,13 @@
         </is>
       </c>
       <c r="D320" s="4" t="n">
-        <v>232.04</v>
+        <v>232.76</v>
       </c>
       <c r="E320" s="5" t="n">
-        <v>-0.03</v>
+        <v>-0.027</v>
       </c>
       <c r="F320" s="5" t="n">
-        <v>-0.0608</v>
+        <v>-0.0578</v>
       </c>
       <c r="G320" s="7" t="n">
         <v>46321</v>
@@ -24488,7 +24488,7 @@
         <v>237</v>
       </c>
       <c r="M320" s="6" t="n">
-        <v>0.02137562489225999</v>
+        <v>0.01821618834851353</v>
       </c>
       <c r="N320" s="3" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>236</v>
       </c>
       <c r="P320" s="6" t="n">
-        <v>0.01706602309946564</v>
+        <v>0.01391991751159997</v>
       </c>
       <c r="Q320" s="10" t="inlineStr">
         <is>
@@ -24540,13 +24540,13 @@
         </is>
       </c>
       <c r="D321" s="15" t="n">
-        <v>159.64</v>
+        <v>158.27</v>
       </c>
       <c r="E321" s="25" t="n">
-        <v>-0.0432</v>
+        <v>-0.05139999999999999</v>
       </c>
       <c r="F321" s="25" t="n">
-        <v>-0.1033</v>
+        <v>-0.111</v>
       </c>
       <c r="G321" s="17" t="n">
         <v>46330</v>
@@ -24575,7 +24575,7 @@
         <v>200</v>
       </c>
       <c r="M321" s="16" t="n">
-        <v>0.2528188423953897</v>
+        <v>0.2636633600808744</v>
       </c>
       <c r="N321" s="14" t="inlineStr"/>
       <c r="O321" s="19" t="n"/>
@@ -24619,13 +24619,13 @@
         </is>
       </c>
       <c r="D322" s="4" t="n">
-        <v>134.96</v>
+        <v>133.97</v>
       </c>
       <c r="E322" s="5" t="n">
-        <v>-0.0032</v>
-      </c>
-      <c r="F322" s="6" t="n">
-        <v>0.004099999999999999</v>
+        <v>-0.0105</v>
+      </c>
+      <c r="F322" s="5" t="n">
+        <v>-0.0033</v>
       </c>
       <c r="G322" s="7" t="n">
         <v>46330</v>
@@ -24654,7 +24654,7 @@
         <v>131</v>
       </c>
       <c r="M322" s="5" t="n">
-        <v>-0.02934202726733853</v>
+        <v>-0.02216914234530118</v>
       </c>
       <c r="N322" s="3" t="inlineStr"/>
       <c r="O322" s="9" t="n"/>
@@ -24698,13 +24698,13 @@
         </is>
       </c>
       <c r="D323" s="15" t="n">
-        <v>30.07</v>
+        <v>29.95</v>
       </c>
       <c r="E323" s="25" t="n">
-        <v>-0.0958</v>
+        <v>-0.0992</v>
       </c>
       <c r="F323" s="25" t="n">
-        <v>-0.1055</v>
+        <v>-0.1089</v>
       </c>
       <c r="G323" s="17" t="n">
         <v>46330</v>
@@ -24777,13 +24777,13 @@
         </is>
       </c>
       <c r="D324" s="4" t="n">
-        <v>36.03</v>
+        <v>35.83</v>
       </c>
       <c r="E324" s="5" t="n">
-        <v>-0.075</v>
+        <v>-0.0801</v>
       </c>
       <c r="F324" s="5" t="n">
-        <v>-0.1221</v>
+        <v>-0.1269</v>
       </c>
       <c r="G324" s="7" t="n">
         <v>46332</v>
@@ -24838,13 +24838,13 @@
         </is>
       </c>
       <c r="D325" s="15" t="n">
-        <v>265.35</v>
+        <v>262.11</v>
       </c>
       <c r="E325" s="25" t="n">
-        <v>-0.0276</v>
+        <v>-0.0395</v>
       </c>
       <c r="F325" s="25" t="n">
-        <v>-0.0372</v>
+        <v>-0.0489</v>
       </c>
       <c r="G325" s="17" t="n">
         <v>46332</v>
@@ -24873,7 +24873,7 @@
         <v>384</v>
       </c>
       <c r="M325" s="16" t="n">
-        <v>0.4471452798191067</v>
+        <v>0.46503376445004</v>
       </c>
       <c r="N325" s="14" t="inlineStr">
         <is>
@@ -24884,7 +24884,7 @@
         <v>380</v>
       </c>
       <c r="P325" s="16" t="n">
-        <v>0.432070849820991</v>
+        <v>0.4497729960703521</v>
       </c>
       <c r="Q325" s="20" t="inlineStr"/>
       <c r="R325" s="19" t="n"/>
@@ -24927,13 +24927,13 @@
         </is>
       </c>
       <c r="D326" s="4" t="n">
-        <v>64.95</v>
+        <v>64.7</v>
       </c>
       <c r="E326" s="5" t="n">
-        <v>-0.0486</v>
+        <v>-0.05230000000000001</v>
       </c>
       <c r="F326" s="5" t="n">
-        <v>-0.1241</v>
+        <v>-0.1274</v>
       </c>
       <c r="G326" s="7" t="n">
         <v>46324</v>
@@ -24962,7 +24962,7 @@
         <v>79</v>
       </c>
       <c r="M326" s="6" t="n">
-        <v>0.216320246343341</v>
+        <v>0.2210200927357032</v>
       </c>
       <c r="N326" s="3" t="inlineStr"/>
       <c r="O326" s="9" t="n"/>
@@ -25014,13 +25014,13 @@
         </is>
       </c>
       <c r="D327" s="15" t="n">
-        <v>117.49</v>
+        <v>116.74</v>
       </c>
       <c r="E327" s="25" t="n">
-        <v>-0.0197</v>
+        <v>-0.0259</v>
       </c>
       <c r="F327" s="25" t="n">
-        <v>-0.0911</v>
+        <v>-0.0969</v>
       </c>
       <c r="G327" s="17" t="n">
         <v>46331</v>
@@ -25049,7 +25049,7 @@
         <v>136</v>
       </c>
       <c r="M327" s="16" t="n">
-        <v>0.1575453230062134</v>
+        <v>0.1649820113071784</v>
       </c>
       <c r="N327" s="14" t="inlineStr">
         <is>
@@ -25060,7 +25060,7 @@
         <v>140</v>
       </c>
       <c r="P327" s="16" t="n">
-        <v>0.1915907736828667</v>
+        <v>0.1992461881103307</v>
       </c>
       <c r="Q327" s="20" t="inlineStr">
         <is>
@@ -25101,13 +25101,13 @@
         </is>
       </c>
       <c r="D328" s="4" t="n">
-        <v>101.72</v>
+        <v>101.58</v>
       </c>
       <c r="E328" s="5" t="n">
-        <v>-0.0277</v>
+        <v>-0.0291</v>
       </c>
       <c r="F328" s="5" t="n">
-        <v>-0.1215</v>
+        <v>-0.1228</v>
       </c>
       <c r="G328" s="7" t="n">
         <v>46330</v>
@@ -25136,7 +25136,7 @@
         <v>131</v>
       </c>
       <c r="M328" s="6" t="n">
-        <v>0.2878489972473457</v>
+        <v>0.2896239417208112</v>
       </c>
       <c r="N328" s="3" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>121</v>
       </c>
       <c r="P328" s="6" t="n">
-        <v>0.1895399134880063</v>
+        <v>0.1911793660169325</v>
       </c>
       <c r="Q328" s="10" t="inlineStr">
         <is>
@@ -25192,13 +25192,13 @@
         </is>
       </c>
       <c r="D329" s="15" t="n">
-        <v>80.09</v>
+        <v>79.63</v>
       </c>
       <c r="E329" s="25" t="n">
-        <v>-0.0426</v>
+        <v>-0.0481</v>
       </c>
       <c r="F329" s="25" t="n">
-        <v>-0.108</v>
+        <v>-0.1132</v>
       </c>
       <c r="G329" s="17" t="n">
         <v>46322</v>
@@ -25234,7 +25234,7 @@
         <v>107</v>
       </c>
       <c r="P329" s="16" t="n">
-        <v>0.3359970033712074</v>
+        <v>0.3437146803968354</v>
       </c>
       <c r="Q329" s="20" t="inlineStr">
         <is>
@@ -25283,13 +25283,13 @@
         </is>
       </c>
       <c r="D330" s="4" t="n">
-        <v>53.33</v>
+        <v>52.92</v>
       </c>
       <c r="E330" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0112</v>
       </c>
       <c r="F330" s="5" t="n">
-        <v>-0.1023</v>
+        <v>-0.1092</v>
       </c>
       <c r="G330" s="7" t="n"/>
       <c r="H330" s="12" t="inlineStr">
@@ -25308,7 +25308,7 @@
         <v>63</v>
       </c>
       <c r="M330" s="6" t="n">
-        <v>0.1813238327395462</v>
+        <v>0.1904761904761904</v>
       </c>
       <c r="N330" s="3" t="inlineStr"/>
       <c r="O330" s="9" t="n"/>
@@ -25413,13 +25413,13 @@
         </is>
       </c>
       <c r="D332" s="4" t="n">
-        <v>8.880000000000001</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="E332" s="5" t="n">
-        <v>-0.0559</v>
-      </c>
-      <c r="F332" s="6" t="n">
-        <v>0.0074</v>
+        <v>-0.0649</v>
+      </c>
+      <c r="F332" s="5" t="n">
+        <v>-0.0023</v>
       </c>
       <c r="G332" s="7" t="n">
         <v>46331</v>
@@ -25474,13 +25474,13 @@
         </is>
       </c>
       <c r="D333" s="15" t="n">
-        <v>85.98999999999999</v>
+        <v>85.45999999999999</v>
       </c>
       <c r="E333" s="25" t="n">
-        <v>-0.0332</v>
+        <v>-0.0391</v>
       </c>
       <c r="F333" s="25" t="n">
-        <v>-0.1098</v>
+        <v>-0.1153</v>
       </c>
       <c r="G333" s="17" t="n">
         <v>46324</v>
@@ -25509,7 +25509,7 @@
         <v>99</v>
       </c>
       <c r="M333" s="16" t="n">
-        <v>0.151296662402605</v>
+        <v>0.1584366955300726</v>
       </c>
       <c r="N333" s="14" t="inlineStr">
         <is>
@@ -25520,7 +25520,7 @@
         <v>112</v>
       </c>
       <c r="P333" s="16" t="n">
-        <v>0.3024770322130481</v>
+        <v>0.310554645448163</v>
       </c>
       <c r="Q333" s="20" t="inlineStr">
         <is>
@@ -25561,13 +25561,13 @@
         </is>
       </c>
       <c r="D334" s="4" t="n">
-        <v>103.26</v>
+        <v>103.48</v>
       </c>
       <c r="E334" s="5" t="n">
-        <v>-0.0259</v>
+        <v>-0.0239</v>
       </c>
       <c r="F334" s="5" t="n">
-        <v>-0.0999</v>
+        <v>-0.098</v>
       </c>
       <c r="G334" s="7" t="n">
         <v>46324</v>
@@ -25596,7 +25596,7 @@
         <v>127</v>
       </c>
       <c r="M334" s="6" t="n">
-        <v>0.2299050939376331</v>
+        <v>0.2272902976420564</v>
       </c>
       <c r="N334" s="3" t="inlineStr"/>
       <c r="O334" s="9" t="n"/>
@@ -37861,7 +37861,7 @@
     <row r="2">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>Data as of September 21, 2026 at 16:37 UTC</t>
+          <t>Data as of September 21, 2026 at 21:16 UTC</t>
         </is>
       </c>
     </row>

--- a/earnings-data.xlsx
+++ b/earnings-data.xlsx
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>104.23</v>
+        <v>103.91</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>-0.0329</v>
+        <v>-0.06059999999999999</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>0.1228</v>
+        <v>0.0955</v>
       </c>
       <c r="G2" s="7" t="n">
         <v>46338</v>
@@ -878,7 +878,7 @@
         <v>125</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.199270843327257</v>
+        <v>0.2029641035511501</v>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>144</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.3815600115130001</v>
+        <v>0.3858146472909249</v>
       </c>
       <c r="Q2" s="10" t="inlineStr">
         <is>
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="D3" s="15" t="n">
-        <v>354.97</v>
+        <v>358.92</v>
       </c>
       <c r="E3" s="16" t="n">
-        <v>0.0294</v>
+        <v>0.0312</v>
       </c>
       <c r="F3" s="16" t="n">
-        <v>0.1173</v>
+        <v>0.1225</v>
       </c>
       <c r="G3" s="17" t="n">
         <v>46322</v>
@@ -973,7 +973,7 @@
         <v>438</v>
       </c>
       <c r="M3" s="16" t="n">
-        <v>0.2339070907400624</v>
+        <v>0.2203276496155132</v>
       </c>
       <c r="N3" s="14" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>420</v>
       </c>
       <c r="P3" s="16" t="n">
-        <v>0.1831985801617037</v>
+        <v>0.170177198261451</v>
       </c>
       <c r="Q3" s="20" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>741.24</v>
+        <v>749.54</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>0.348</v>
+        <v>0.3408</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.223</v>
+        <v>0.2593</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>46330</v>
@@ -1064,7 +1064,7 @@
         <v>835</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.1264907452377098</v>
+        <v>0.1140165968460656</v>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>930</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.2546543629593654</v>
+        <v>0.2407610000800492</v>
       </c>
       <c r="Q4" s="10" t="inlineStr">
         <is>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="D5" s="15" t="n">
-        <v>43.16</v>
+        <v>43.03</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>0.05599999999999999</v>
+        <v>0.0312</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>0.154</v>
+        <v>0.1351</v>
       </c>
       <c r="G5" s="17" t="n">
         <v>46329</v>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>73.36</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>-0.07829999999999999</v>
+        <v>-0.1034</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.0649</v>
+        <v>0.0235</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>46315</v>
@@ -1220,7 +1220,7 @@
         <v>80</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.0905125408942203</v>
+        <v>0.1151379983272931</v>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>100</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.3631406761177753</v>
+        <v>0.3939224979091164</v>
       </c>
       <c r="Q6" s="10" t="inlineStr">
         <is>
@@ -1272,13 +1272,13 @@
         </is>
       </c>
       <c r="D7" s="15" t="n">
-        <v>75.59</v>
+        <v>75</v>
       </c>
       <c r="E7" s="25" t="n">
-        <v>-0.1365</v>
+        <v>-0.1568</v>
       </c>
       <c r="F7" s="25" t="n">
-        <v>-0.0297</v>
+        <v>-0.05860000000000001</v>
       </c>
       <c r="G7" s="17" t="n">
         <v>46315</v>
@@ -1307,7 +1307,7 @@
         <v>91</v>
       </c>
       <c r="M7" s="16" t="n">
-        <v>0.2038629448339727</v>
+        <v>0.2133333333333333</v>
       </c>
       <c r="N7" s="14" t="inlineStr"/>
       <c r="O7" s="19" t="n"/>
@@ -1351,13 +1351,13 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>516.77</v>
+        <v>509.96</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-0.0318</v>
+        <v>-0.0518</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.1019</v>
+        <v>0.0566</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>46329</v>
@@ -1386,7 +1386,7 @@
         <v>569.9299999999999</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.1028697486309189</v>
+        <v>0.1175974586242058</v>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>648.04</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.2540201637091936</v>
+        <v>0.2707663346144795</v>
       </c>
       <c r="Q8" s="10" t="inlineStr">
         <is>
@@ -1438,13 +1438,13 @@
         </is>
       </c>
       <c r="D9" s="15" t="n">
-        <v>191.12</v>
+        <v>190.41</v>
       </c>
       <c r="E9" s="25" t="n">
-        <v>-0.0105</v>
+        <v>-0.0155</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.0542</v>
       </c>
       <c r="G9" s="17" t="n">
         <v>46330</v>
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>165.27</v>
+        <v>164.85</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.0973</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-0.0302</v>
+        <v>-0.08460000000000001</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>46317</v>
@@ -1542,7 +1542,7 @@
         <v>170</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.02861983421068548</v>
+        <v>0.03124052168638159</v>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>270</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.6336903249228534</v>
+        <v>0.637852593266606</v>
       </c>
       <c r="Q10" s="10" t="inlineStr">
         <is>
@@ -1594,13 +1594,13 @@
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>47.68</v>
+        <v>47.2</v>
       </c>
       <c r="E11" s="25" t="n">
-        <v>-0.0358</v>
+        <v>-0.0588</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>0.08810000000000001</v>
+        <v>0.0177</v>
       </c>
       <c r="G11" s="17" t="n">
         <v>46316</v>
@@ -1629,7 +1629,7 @@
         <v>43</v>
       </c>
       <c r="M11" s="25" t="n">
-        <v>-0.09815436241610738</v>
+        <v>-0.08898305084745768</v>
       </c>
       <c r="N11" s="14" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>50</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>0.04865771812080538</v>
+        <v>0.05932203389830502</v>
       </c>
       <c r="Q11" s="20" t="inlineStr">
         <is>
@@ -1685,13 +1685,13 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>166.84</v>
+        <v>162.88</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-0.1092</v>
+        <v>-0.1437</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.2128</v>
+        <v>0.1544</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>46331</v>
@@ -1720,7 +1720,7 @@
         <v>181</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.08487173339726682</v>
+        <v>0.1112475442043222</v>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>155</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>-0.0709661951570367</v>
+        <v>-0.04837917485265223</v>
       </c>
       <c r="Q12" s="10" t="inlineStr">
         <is>
@@ -1772,13 +1772,13 @@
         </is>
       </c>
       <c r="D13" s="15" t="n">
-        <v>258.45</v>
+        <v>255.68</v>
       </c>
       <c r="E13" s="25" t="n">
-        <v>-0.0007000000000000001</v>
+        <v>-0.0244</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>0.1061</v>
+        <v>0.1015</v>
       </c>
       <c r="G13" s="17" t="n">
         <v>46324</v>
@@ -1807,7 +1807,7 @@
         <v>322</v>
       </c>
       <c r="M13" s="16" t="n">
-        <v>0.2458889533758948</v>
+        <v>0.2593867334167709</v>
       </c>
       <c r="N13" s="14" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>285</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>0.1027278003482299</v>
+        <v>0.1146745932415519</v>
       </c>
       <c r="Q13" s="20" t="inlineStr">
         <is>
@@ -1871,13 +1871,13 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2803.25</v>
+        <v>2959.06</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-0.05230000000000001</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>-0.0411</v>
+        <v>-0.0167</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>0.0005999999999999999</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>46287</v>
@@ -1906,7 +1906,7 @@
         <v>4150</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.4804245072683492</v>
+        <v>0.4024724067778281</v>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>3700</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.3198965486488897</v>
+        <v>0.2503970855609552</v>
       </c>
       <c r="Q14" s="10" t="inlineStr">
         <is>
@@ -1958,13 +1958,13 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>93.22</v>
+        <v>94.88</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>0.08529999999999999</v>
+        <v>0.08460000000000001</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>0.1041</v>
+        <v>0.1106</v>
       </c>
       <c r="G15" s="17" t="n"/>
       <c r="H15" s="22" t="inlineStr">
@@ -1983,7 +1983,7 @@
         <v>65</v>
       </c>
       <c r="M15" s="25" t="n">
-        <v>-0.3027247371808625</v>
+        <v>-0.3149241146711635</v>
       </c>
       <c r="N15" s="14" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>85</v>
       </c>
       <c r="P15" s="25" t="n">
-        <v>-0.08817850246728169</v>
+        <v>-0.1041315345699831</v>
       </c>
       <c r="Q15" s="20" t="inlineStr"/>
       <c r="R15" s="19" t="n"/>
@@ -2029,13 +2029,13 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>168.52</v>
+        <v>162.51</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-0.1961</v>
+        <v>-0.2383</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-0.0249</v>
+        <v>-0.0842</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>46322</v>
@@ -2064,7 +2064,7 @@
         <v>214</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.2698789461191549</v>
+        <v>0.3168420404898161</v>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>245</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.453833372893425</v>
+        <v>0.5075995323364717</v>
       </c>
       <c r="Q16" s="10" t="inlineStr">
         <is>
@@ -2124,13 +2124,13 @@
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>251.8</v>
+        <v>251.63</v>
       </c>
       <c r="E17" s="25" t="n">
-        <v>-0.2288</v>
+        <v>-0.2389</v>
       </c>
       <c r="F17" s="25" t="n">
-        <v>-0.2583</v>
+        <v>-0.281</v>
       </c>
       <c r="G17" s="17" t="n"/>
       <c r="H17" s="22" t="inlineStr">
@@ -2149,7 +2149,7 @@
         <v>375</v>
       </c>
       <c r="M17" s="16" t="n">
-        <v>0.489277204130262</v>
+        <v>0.4902833525414299</v>
       </c>
       <c r="N17" s="14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>375</v>
       </c>
       <c r="P17" s="16" t="n">
-        <v>0.489277204130262</v>
+        <v>0.4902833525414299</v>
       </c>
       <c r="Q17" s="20" t="inlineStr"/>
       <c r="R17" s="19" t="n"/>
@@ -2199,13 +2199,13 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>33.14</v>
+        <v>33.28</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>-0.1019</v>
+        <v>-0.1247</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0.0353</v>
+        <v>0.0469</v>
       </c>
       <c r="G18" s="7" t="n">
         <v>46323</v>
@@ -2234,7 +2234,7 @@
         <v>45</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.3578756789378394</v>
+        <v>0.3521634615384615</v>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>45</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.3578756789378394</v>
+        <v>0.3521634615384615</v>
       </c>
       <c r="Q18" s="10" t="inlineStr">
         <is>
@@ -2286,13 +2286,13 @@
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>139.25</v>
+        <v>141.33</v>
       </c>
       <c r="E19" s="25" t="n">
-        <v>-0.0613</v>
+        <v>-0.0513</v>
       </c>
       <c r="F19" s="25" t="n">
-        <v>-0.0202</v>
+        <v>-0.03700000000000001</v>
       </c>
       <c r="G19" s="17" t="n">
         <v>46324</v>
@@ -2321,7 +2321,7 @@
         <v>170</v>
       </c>
       <c r="M19" s="16" t="n">
-        <v>0.2208258527827648</v>
+        <v>0.202858557984858</v>
       </c>
       <c r="N19" s="14" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>177</v>
       </c>
       <c r="P19" s="16" t="n">
-        <v>0.2710951526032316</v>
+        <v>0.2523880280195286</v>
       </c>
       <c r="Q19" s="20" t="inlineStr">
         <is>
@@ -2373,13 +2373,13 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>123.63</v>
+        <v>132.09</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>-0.3253</v>
+        <v>-0.2635</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>-0.395</v>
+        <v>-0.3589</v>
       </c>
       <c r="G20" s="7" t="n"/>
       <c r="H20" s="12" t="inlineStr">
@@ -2398,7 +2398,7 @@
         <v>220</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.7795033567904232</v>
+        <v>0.6655310772957831</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="9" t="n"/>
@@ -2442,13 +2442,13 @@
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>112.33</v>
+        <v>114.7</v>
       </c>
       <c r="E21" s="25" t="n">
-        <v>-0.1456</v>
+        <v>-0.1612</v>
       </c>
       <c r="F21" s="25" t="n">
-        <v>-0.0452</v>
+        <v>-0.04769999999999999</v>
       </c>
       <c r="G21" s="17" t="n"/>
       <c r="H21" s="22" t="inlineStr">
@@ -2493,13 +2493,13 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>83.95</v>
+        <v>83.7</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-0.0453</v>
+        <v>-0.0377</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>0.0407</v>
+        <v>0.0128</v>
       </c>
       <c r="G22" s="7" t="n">
         <v>46315</v>
@@ -2528,7 +2528,7 @@
         <v>61</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>-0.2733770101250745</v>
+        <v>-0.2712066905615293</v>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>100</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.1911852293031566</v>
+        <v>0.1947431302270012</v>
       </c>
       <c r="Q22" s="10" t="inlineStr">
         <is>
@@ -2580,13 +2580,13 @@
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>126.45</v>
+        <v>129.87</v>
       </c>
       <c r="E23" s="25" t="n">
-        <v>-0.0561</v>
+        <v>-0.0429</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>0.0533</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="G23" s="17" t="n">
         <v>46315</v>
@@ -2618,7 +2618,7 @@
         <v>145</v>
       </c>
       <c r="P23" s="16" t="n">
-        <v>0.1466982997232107</v>
+        <v>0.1165011165011165</v>
       </c>
       <c r="Q23" s="20" t="inlineStr"/>
       <c r="R23" s="19" t="n"/>
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>297.2</v>
+        <v>301.04</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>-0.1144</v>
+        <v>-0.1078</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>-0.08470000000000001</v>
+        <v>-0.0959</v>
       </c>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="12" t="inlineStr">
@@ -2678,7 +2678,7 @@
         <v>360</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.2113055181695828</v>
+        <v>0.1958543715120913</v>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>400</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.3458950201884253</v>
+        <v>0.3287270794578793</v>
       </c>
       <c r="Q24" s="10" t="inlineStr">
         <is>
@@ -2738,13 +2738,13 @@
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>190.98</v>
+        <v>193.95</v>
       </c>
       <c r="E25" s="25" t="n">
-        <v>-0.1162</v>
+        <v>-0.1061</v>
       </c>
       <c r="F25" s="25" t="n">
-        <v>-0.0542</v>
+        <v>-0.0659</v>
       </c>
       <c r="G25" s="17" t="n"/>
       <c r="H25" s="22" t="inlineStr">
@@ -2763,7 +2763,7 @@
         <v>255</v>
       </c>
       <c r="M25" s="16" t="n">
-        <v>0.3352183474709394</v>
+        <v>0.3147718484145399</v>
       </c>
       <c r="N25" s="14" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>230</v>
       </c>
       <c r="P25" s="16" t="n">
-        <v>0.204314587914965</v>
+        <v>0.185872647589585</v>
       </c>
       <c r="Q25" s="20" t="inlineStr">
         <is>
@@ -2819,13 +2819,13 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>247.88</v>
+        <v>251.02</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>-0.0851</v>
+        <v>-0.079</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>-0.0568</v>
+        <v>-0.0519</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>46330</v>
@@ -2854,7 +2854,7 @@
         <v>300</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.2102630304986284</v>
+        <v>0.1951238945103975</v>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>350</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.4119735355817331</v>
+        <v>0.3943112102621305</v>
       </c>
       <c r="Q26" s="10" t="inlineStr">
         <is>
@@ -2906,13 +2906,13 @@
         </is>
       </c>
       <c r="D27" s="15" t="n">
-        <v>36.1</v>
+        <v>36.19</v>
       </c>
       <c r="E27" s="25" t="n">
-        <v>-0.1143</v>
+        <v>-0.1118</v>
       </c>
       <c r="F27" s="25" t="n">
-        <v>-0.1193</v>
+        <v>-0.132</v>
       </c>
       <c r="G27" s="17" t="n">
         <v>46289</v>
@@ -2967,13 +2967,13 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>82.88</v>
+        <v>86.23</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>-0.0699</v>
+        <v>-0.0491</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>-0.0375</v>
+        <v>-0.0134</v>
       </c>
       <c r="G28" s="7" t="n">
         <v>46323</v>
@@ -3002,7 +3002,7 @@
         <v>110</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.3272200772200773</v>
+        <v>0.275658123622869</v>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>115</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.3875482625482626</v>
+        <v>0.3336425837875449</v>
       </c>
       <c r="Q28" s="10" t="inlineStr">
         <is>
@@ -3058,13 +3058,13 @@
         </is>
       </c>
       <c r="D29" s="15" t="n">
-        <v>167.92</v>
+        <v>167.85</v>
       </c>
       <c r="E29" s="25" t="n">
-        <v>-0.1067</v>
+        <v>-0.1083</v>
       </c>
       <c r="F29" s="25" t="n">
-        <v>-0.08410000000000001</v>
+        <v>-0.0866</v>
       </c>
       <c r="G29" s="17" t="n">
         <v>46317</v>
@@ -3119,13 +3119,13 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>231.25</v>
+        <v>231.04</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>-0.0326</v>
+        <v>-0.0434</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0329</v>
       </c>
       <c r="G30" s="7" t="n"/>
       <c r="H30" s="12" t="inlineStr">
@@ -3144,7 +3144,7 @@
         <v>245</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.05945945945945946</v>
+        <v>0.06042243767313023</v>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>265</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.145945945945946</v>
+        <v>0.1469875346260388</v>
       </c>
       <c r="Q30" s="10" t="inlineStr">
         <is>
@@ -3196,13 +3196,13 @@
         </is>
       </c>
       <c r="D31" s="15" t="n">
-        <v>94.90000000000001</v>
+        <v>95.43000000000001</v>
       </c>
       <c r="E31" s="25" t="n">
-        <v>-0.1137</v>
+        <v>-0.1122</v>
       </c>
       <c r="F31" s="25" t="n">
-        <v>-0.0805</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="G31" s="17" t="n">
         <v>46330</v>
@@ -3231,7 +3231,7 @@
         <v>120</v>
       </c>
       <c r="M31" s="16" t="n">
-        <v>0.2644889357218124</v>
+        <v>0.2574662055957245</v>
       </c>
       <c r="N31" s="14" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>115</v>
       </c>
       <c r="P31" s="16" t="n">
-        <v>0.2118018967334035</v>
+        <v>0.2050717803625693</v>
       </c>
       <c r="Q31" s="20" t="inlineStr">
         <is>
@@ -3283,13 +3283,13 @@
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>12.54</v>
-      </c>
-      <c r="E32" s="5" t="n">
-        <v>-0.0354</v>
+        <v>13.63</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>0.0401</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>-0.1218</v>
+        <v>-0.04650000000000001</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>46330</v>
@@ -3344,13 +3344,13 @@
         </is>
       </c>
       <c r="D33" s="15" t="n">
-        <v>130.96</v>
+        <v>130.28</v>
       </c>
       <c r="E33" s="25" t="n">
-        <v>-0.06809999999999999</v>
+        <v>-0.0741</v>
       </c>
       <c r="F33" s="25" t="n">
-        <v>-0.1467</v>
+        <v>-0.1552</v>
       </c>
       <c r="G33" s="17" t="n"/>
       <c r="H33" s="22" t="inlineStr">
@@ -3369,7 +3369,7 @@
         <v>160</v>
       </c>
       <c r="M33" s="16" t="n">
-        <v>0.2217470983506414</v>
+        <v>0.2281240405280933</v>
       </c>
       <c r="N33" s="14" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>175</v>
       </c>
       <c r="P33" s="16" t="n">
-        <v>0.336285888821014</v>
+        <v>0.3432606693276021</v>
       </c>
       <c r="Q33" s="20" t="inlineStr">
         <is>
@@ -3425,13 +3425,13 @@
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>32.33</v>
+        <v>33.1</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>-0.07580000000000001</v>
+        <v>-0.0785</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>0.0663</v>
+        <v>0.06709999999999999</v>
       </c>
       <c r="G34" s="7" t="n">
         <v>46317</v>
@@ -3460,7 +3460,7 @@
         <v>35</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.08258583359109192</v>
+        <v>0.0574018126888217</v>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>40</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.2372409526755336</v>
+        <v>0.2084592145015105</v>
       </c>
       <c r="Q34" s="10" t="inlineStr">
         <is>
@@ -3512,13 +3512,13 @@
         </is>
       </c>
       <c r="D35" s="15" t="n">
-        <v>375.3</v>
+        <v>376.32</v>
       </c>
       <c r="E35" s="16" t="n">
-        <v>0.0343</v>
+        <v>0.0784</v>
       </c>
       <c r="F35" s="16" t="n">
-        <v>0.1739</v>
+        <v>0.2022</v>
       </c>
       <c r="G35" s="17" t="n">
         <v>46323</v>
@@ -3547,7 +3547,7 @@
         <v>130</v>
       </c>
       <c r="M35" s="25" t="n">
-        <v>-0.6536104449773514</v>
+        <v>-0.6545493197278911</v>
       </c>
       <c r="N35" s="14" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>300</v>
       </c>
       <c r="P35" s="25" t="n">
-        <v>-0.2006394884092726</v>
+        <v>-0.2028061224489796</v>
       </c>
       <c r="Q35" s="20" t="inlineStr">
         <is>
@@ -3599,13 +3599,13 @@
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>70.84</v>
+        <v>70.22</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>-0.101</v>
+        <v>-0.1144</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.028</v>
+        <v>0.0649</v>
       </c>
       <c r="G36" s="7" t="n">
         <v>46329</v>
@@ -3660,13 +3660,13 @@
         </is>
       </c>
       <c r="D37" s="15" t="n">
-        <v>557.86</v>
+        <v>558</v>
       </c>
       <c r="E37" s="16" t="n">
-        <v>0.0698</v>
+        <v>0.0357</v>
       </c>
       <c r="F37" s="16" t="n">
-        <v>0.1672</v>
+        <v>0.1738</v>
       </c>
       <c r="G37" s="17" t="n"/>
       <c r="H37" s="22" t="inlineStr">
@@ -3685,7 +3685,7 @@
         <v>450</v>
       </c>
       <c r="M37" s="25" t="n">
-        <v>-0.1933460007887284</v>
+        <v>-0.1935483870967742</v>
       </c>
       <c r="N37" s="14" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>635</v>
       </c>
       <c r="P37" s="16" t="n">
-        <v>0.1382784211092389</v>
+        <v>0.1379928315412186</v>
       </c>
       <c r="Q37" s="20" t="inlineStr">
         <is>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>95.48999999999999</v>
+        <v>96.31</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>-0.0335</v>
+        <v>-0.0607</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>-0.0073</v>
+        <v>-0.0136</v>
       </c>
       <c r="G38" s="7" t="n">
         <v>46325</v>
@@ -3776,7 +3776,7 @@
         <v>110</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.1519530840925752</v>
+        <v>0.1421451562662236</v>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>105</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.09959158027018541</v>
+        <v>0.09022946734503164</v>
       </c>
       <c r="Q38" s="10" t="inlineStr">
         <is>
@@ -3832,13 +3832,13 @@
         </is>
       </c>
       <c r="D39" s="15" t="n">
-        <v>86.26000000000001</v>
+        <v>87.17</v>
       </c>
       <c r="E39" s="25" t="n">
-        <v>-0.0529</v>
+        <v>-0.0581</v>
       </c>
       <c r="F39" s="25" t="n">
-        <v>-0.0424</v>
+        <v>-0.0394</v>
       </c>
       <c r="G39" s="17" t="n">
         <v>46325</v>
@@ -3867,7 +3867,7 @@
         <v>95</v>
       </c>
       <c r="M39" s="16" t="n">
-        <v>0.1013215859030836</v>
+        <v>0.08982448089939198</v>
       </c>
       <c r="N39" s="14" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>100</v>
       </c>
       <c r="P39" s="16" t="n">
-        <v>0.1592858798979828</v>
+        <v>0.1471836641046231</v>
       </c>
       <c r="Q39" s="20" t="inlineStr">
         <is>
@@ -3923,13 +3923,13 @@
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>898.48</v>
+        <v>900.54</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>-0.052</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>-0.0298</v>
+        <v>-0.0369</v>
       </c>
       <c r="G40" s="7" t="n">
         <v>46289</v>
@@ -3958,7 +3958,7 @@
         <v>1000</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.1129908289555694</v>
+        <v>0.1104448442045884</v>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>1100</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.2242899118511263</v>
+        <v>0.2214893286250472</v>
       </c>
       <c r="Q40" s="10" t="inlineStr">
         <is>
@@ -4018,13 +4018,13 @@
         </is>
       </c>
       <c r="D41" s="15" t="n">
-        <v>121.91</v>
+        <v>123.46</v>
       </c>
       <c r="E41" s="25" t="n">
-        <v>-0.0122</v>
+        <v>-0.0149</v>
       </c>
       <c r="F41" s="16" t="n">
-        <v>0.05860000000000001</v>
+        <v>0.05309999999999999</v>
       </c>
       <c r="G41" s="17" t="n"/>
       <c r="H41" s="22" t="inlineStr">
@@ -4043,7 +4043,7 @@
         <v>125</v>
       </c>
       <c r="M41" s="16" t="n">
-        <v>0.02534656713969324</v>
+        <v>0.01247367568443226</v>
       </c>
       <c r="N41" s="14" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>135</v>
       </c>
       <c r="P41" s="16" t="n">
-        <v>0.1073742925108687</v>
+        <v>0.09347156973918684</v>
       </c>
       <c r="Q41" s="20" t="inlineStr">
         <is>
@@ -4095,13 +4095,13 @@
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>24.37</v>
+        <v>24.31</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>-0.0473</v>
+        <v>-0.0532</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>-0.039</v>
+        <v>-0.0532</v>
       </c>
       <c r="G42" s="7" t="n">
         <v>46330</v>
@@ -4156,13 +4156,13 @@
         </is>
       </c>
       <c r="D43" s="15" t="n">
-        <v>87.12</v>
+        <v>88.27</v>
       </c>
       <c r="E43" s="25" t="n">
-        <v>-0.0437</v>
+        <v>-0.0404</v>
       </c>
       <c r="F43" s="16" t="n">
-        <v>0.0733</v>
+        <v>0.0732</v>
       </c>
       <c r="G43" s="17" t="n">
         <v>46315</v>
@@ -4191,7 +4191,7 @@
         <v>90</v>
       </c>
       <c r="M43" s="16" t="n">
-        <v>0.03305785123966937</v>
+        <v>0.01959895774328769</v>
       </c>
       <c r="N43" s="14" t="inlineStr">
         <is>
@@ -4201,8 +4201,8 @@
       <c r="O43" s="19" t="n">
         <v>88</v>
       </c>
-      <c r="P43" s="16" t="n">
-        <v>0.01010101010101005</v>
+      <c r="P43" s="25" t="n">
+        <v>-0.003058796873229818</v>
       </c>
       <c r="Q43" s="20" t="inlineStr">
         <is>
@@ -4251,13 +4251,13 @@
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>59.69</v>
+        <v>59.63</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>0.0309</v>
+        <v>0.009300000000000001</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.04849999999999999</v>
       </c>
       <c r="G44" s="7" t="n"/>
       <c r="H44" s="12" t="inlineStr">
@@ -4276,7 +4276,7 @@
         <v>58</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>-0.02831295024292172</v>
+        <v>-0.02733523394264636</v>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>78</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.3067515496733121</v>
+        <v>0.3080664095254066</v>
       </c>
       <c r="Q44" s="10" t="inlineStr">
         <is>
@@ -4328,13 +4328,13 @@
         </is>
       </c>
       <c r="D45" s="15" t="n">
-        <v>60.17</v>
+        <v>61.1</v>
       </c>
       <c r="E45" s="25" t="n">
-        <v>-0.0664</v>
+        <v>-0.0557</v>
       </c>
       <c r="F45" s="16" t="n">
-        <v>0.002</v>
+        <v>0.0095</v>
       </c>
       <c r="G45" s="17" t="n">
         <v>46322</v>
@@ -4363,7 +4363,7 @@
         <v>70</v>
       </c>
       <c r="M45" s="16" t="n">
-        <v>0.1633704503905601</v>
+        <v>0.1456628477905073</v>
       </c>
       <c r="N45" s="14" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>71</v>
       </c>
       <c r="P45" s="16" t="n">
-        <v>0.1799900282532823</v>
+        <v>0.1620294599018003</v>
       </c>
       <c r="Q45" s="20" t="inlineStr">
         <is>
@@ -4423,13 +4423,13 @@
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>48.89</v>
+        <v>49.28</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>-0.1177</v>
+        <v>-0.123</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>-0.0259</v>
+        <v>-0.0135</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>46296</v>
@@ -4494,13 +4494,13 @@
         </is>
       </c>
       <c r="D47" s="15" t="n">
-        <v>44</v>
+        <v>44.77</v>
       </c>
       <c r="E47" s="25" t="n">
-        <v>-0.0793</v>
+        <v>-0.0848</v>
       </c>
       <c r="F47" s="25" t="n">
-        <v>-0.0594</v>
+        <v>-0.0423</v>
       </c>
       <c r="G47" s="17" t="n">
         <v>46331</v>
@@ -4555,13 +4555,13 @@
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>68.53</v>
+        <v>68.83</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>0.0369</v>
+        <v>0.0053</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>-0.0493</v>
+        <v>-0.057</v>
       </c>
       <c r="G48" s="7" t="n">
         <v>46324</v>
@@ -4616,13 +4616,13 @@
         </is>
       </c>
       <c r="D49" s="15" t="n">
-        <v>129.59</v>
+        <v>130.54</v>
       </c>
       <c r="E49" s="25" t="n">
-        <v>-0.0968</v>
+        <v>-0.0977</v>
       </c>
       <c r="F49" s="25" t="n">
-        <v>-0.0397</v>
+        <v>-0.0446</v>
       </c>
       <c r="G49" s="17" t="n">
         <v>46303</v>
@@ -4651,7 +4651,7 @@
         <v>140</v>
       </c>
       <c r="M49" s="16" t="n">
-        <v>0.08033027239756151</v>
+        <v>0.07246820897809107</v>
       </c>
       <c r="N49" s="14" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>150</v>
       </c>
       <c r="P49" s="16" t="n">
-        <v>0.1574967204259588</v>
+        <v>0.1490730810479547</v>
       </c>
       <c r="Q49" s="20" t="inlineStr">
         <is>
@@ -4711,16 +4711,16 @@
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>146.08</v>
+        <v>147.41</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>0.0097</v>
-      </c>
-      <c r="F50" s="5" t="n">
-        <v>-0.0061</v>
+        <v>0.005600000000000001</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>46318</v>
+        <v>46317</v>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>Oct 23</t>
+          <t>Oct 22</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
@@ -4746,7 +4746,7 @@
         <v>164</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0.1226725082146768</v>
+        <v>0.1125432467268164</v>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>162</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.1089813800657173</v>
+        <v>0.09897564615697717</v>
       </c>
       <c r="Q50" s="10" t="inlineStr">
         <is>
@@ -4810,13 +4810,13 @@
         </is>
       </c>
       <c r="D51" s="15" t="n">
-        <v>78.43000000000001</v>
+        <v>78.76000000000001</v>
       </c>
       <c r="E51" s="25" t="n">
-        <v>-0.0674</v>
+        <v>-0.0608</v>
       </c>
       <c r="F51" s="25" t="n">
-        <v>-0.0404</v>
+        <v>-0.05230000000000001</v>
       </c>
       <c r="G51" s="17" t="n">
         <v>46322</v>
@@ -4845,7 +4845,7 @@
         <v>100</v>
       </c>
       <c r="M51" s="16" t="n">
-        <v>0.2750223128904755</v>
+        <v>0.2696800406297612</v>
       </c>
       <c r="N51" s="14" t="inlineStr"/>
       <c r="O51" s="19" t="n"/>
@@ -4889,13 +4889,13 @@
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>157.71</v>
+        <v>159.06</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>-0.0467</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>0.1727</v>
+        <v>0.1629</v>
       </c>
       <c r="G52" s="7" t="n"/>
       <c r="H52" s="12" t="inlineStr">
@@ -4914,7 +4914,7 @@
         <v>140</v>
       </c>
       <c r="M52" s="5" t="n">
-        <v>-0.1122947181535731</v>
+        <v>-0.1198289953476676</v>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>135</v>
       </c>
       <c r="P52" s="5" t="n">
-        <v>-0.1439984782195169</v>
+        <v>-0.1512636740852508</v>
       </c>
       <c r="Q52" s="10" t="inlineStr">
         <is>
@@ -4970,13 +4970,13 @@
         </is>
       </c>
       <c r="D53" s="15" t="n">
-        <v>107.44</v>
+        <v>108.33</v>
       </c>
       <c r="E53" s="16" t="n">
-        <v>0.0361</v>
+        <v>0.0173</v>
       </c>
       <c r="F53" s="25" t="n">
-        <v>-0.0089</v>
+        <v>-0.0104</v>
       </c>
       <c r="G53" s="17" t="n"/>
       <c r="H53" s="22" t="inlineStr">
@@ -4995,7 +4995,7 @@
         <v>140</v>
       </c>
       <c r="M53" s="16" t="n">
-        <v>0.3030528667163068</v>
+        <v>0.292347456844826</v>
       </c>
       <c r="N53" s="14" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>140</v>
       </c>
       <c r="P53" s="16" t="n">
-        <v>0.3030528667163068</v>
+        <v>0.292347456844826</v>
       </c>
       <c r="Q53" s="20" t="inlineStr">
         <is>
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>57.83</v>
+        <v>57.44</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>-0.0723</v>
+        <v>-0.0735</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>0.031</v>
+        <v>0.0032</v>
       </c>
       <c r="G54" s="7" t="n">
         <v>46317</v>
@@ -5097,7 +5097,7 @@
         <v>76</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.3141967836762926</v>
+        <v>0.3231197771587744</v>
       </c>
       <c r="Q54" s="10" t="inlineStr">
         <is>
@@ -5138,13 +5138,13 @@
         </is>
       </c>
       <c r="D55" s="15" t="n">
-        <v>127.53</v>
+        <v>126.42</v>
       </c>
       <c r="E55" s="25" t="n">
-        <v>-0.0544</v>
+        <v>-0.052</v>
       </c>
       <c r="F55" s="16" t="n">
-        <v>0.061</v>
+        <v>0.0512</v>
       </c>
       <c r="G55" s="17" t="n">
         <v>46331</v>
@@ -5173,7 +5173,7 @@
         <v>183</v>
       </c>
       <c r="M55" s="16" t="n">
-        <v>0.4349564808280404</v>
+        <v>0.4475557664926436</v>
       </c>
       <c r="N55" s="14" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>145</v>
       </c>
       <c r="P55" s="16" t="n">
-        <v>0.1369873755194856</v>
+        <v>0.1469704160734061</v>
       </c>
       <c r="Q55" s="20" t="inlineStr">
         <is>
@@ -5225,13 +5225,13 @@
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>203.67</v>
-      </c>
-      <c r="E56" s="5" t="n">
-        <v>-0.007800000000000001</v>
+        <v>203.99</v>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v>0.0044</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>0.0476</v>
+        <v>0.0472</v>
       </c>
       <c r="G56" s="7" t="n">
         <v>46325</v>
@@ -5260,7 +5260,7 @@
         <v>222</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>0.08999852702901759</v>
+        <v>0.08828864160007839</v>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>225</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.104728236853734</v>
+        <v>0.1029952448649443</v>
       </c>
       <c r="Q56" s="10" t="inlineStr">
         <is>
@@ -5316,13 +5316,13 @@
         </is>
       </c>
       <c r="D57" s="15" t="n">
-        <v>141.38</v>
+        <v>140.91</v>
       </c>
       <c r="E57" s="25" t="n">
-        <v>-0.0762</v>
+        <v>-0.0619</v>
       </c>
       <c r="F57" s="25" t="n">
-        <v>-0.0282</v>
+        <v>-0.0374</v>
       </c>
       <c r="G57" s="17" t="n">
         <v>46331</v>
@@ -5351,7 +5351,7 @@
         <v>196</v>
       </c>
       <c r="M57" s="16" t="n">
-        <v>0.3863347008063376</v>
+        <v>0.3909587680079484</v>
       </c>
       <c r="N57" s="14" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>170</v>
       </c>
       <c r="P57" s="16" t="n">
-        <v>0.2024331588626397</v>
+        <v>0.2064438293946491</v>
       </c>
       <c r="Q57" s="20" t="inlineStr">
         <is>
@@ -5407,13 +5407,13 @@
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>38.47</v>
+        <v>38.59</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>0.0121</v>
+        <v>0.006</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0036</v>
       </c>
       <c r="G58" s="7" t="n">
         <v>46324</v>
@@ -5468,13 +5468,13 @@
         </is>
       </c>
       <c r="D59" s="15" t="n">
-        <v>20.9</v>
+        <v>20.92</v>
       </c>
       <c r="E59" s="25" t="n">
-        <v>-0.0137</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F59" s="16" t="n">
-        <v>0.0235</v>
+        <v>0.0273</v>
       </c>
       <c r="G59" s="17" t="n">
         <v>46330</v>
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>189.27</v>
+        <v>187.23</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>-0.1018</v>
+        <v>-0.08929999999999999</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>-0.0789</v>
+        <v>-0.08529999999999999</v>
       </c>
       <c r="G60" s="7" t="n">
         <v>46328</v>
@@ -5590,13 +5590,13 @@
         </is>
       </c>
       <c r="D61" s="15" t="n">
-        <v>33.39</v>
+        <v>33.28</v>
       </c>
       <c r="E61" s="25" t="n">
-        <v>-0.0552</v>
-      </c>
-      <c r="F61" s="16" t="n">
-        <v>0.0208</v>
+        <v>-0.0388</v>
+      </c>
+      <c r="F61" s="25" t="n">
+        <v>-0.0022</v>
       </c>
       <c r="G61" s="17" t="n">
         <v>46315</v>
@@ -5632,7 +5632,7 @@
         <v>43</v>
       </c>
       <c r="P61" s="16" t="n">
-        <v>0.2878107217729859</v>
+        <v>0.2920673076923077</v>
       </c>
       <c r="Q61" s="20" t="inlineStr">
         <is>
@@ -5677,13 +5677,13 @@
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>31.72</v>
+        <v>31.65</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>0.0239</v>
+        <v>0.0208</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>-0.032</v>
+        <v>-0.03700000000000001</v>
       </c>
       <c r="G62" s="7" t="n">
         <v>46316</v>
@@ -5712,7 +5712,7 @@
         <v>35</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>0.1034047919293821</v>
+        <v>0.1058451816745656</v>
       </c>
       <c r="N62" s="3" t="inlineStr"/>
       <c r="O62" s="9" t="n"/>
@@ -5756,13 +5756,13 @@
         </is>
       </c>
       <c r="D63" s="15" t="n">
-        <v>261.75</v>
+        <v>260.92</v>
       </c>
       <c r="E63" s="16" t="n">
-        <v>0.07769999999999999</v>
+        <v>0.0784</v>
       </c>
       <c r="F63" s="16" t="n">
-        <v>0.2646</v>
+        <v>0.2619</v>
       </c>
       <c r="G63" s="17" t="n">
         <v>46323</v>
@@ -5817,13 +5817,13 @@
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>51.76</v>
+        <v>52.68</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>-0.0392</v>
+        <v>-0.0244</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>0.09609999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="G64" s="7" t="n">
         <v>46311</v>
@@ -5859,7 +5859,7 @@
         <v>63</v>
       </c>
       <c r="P64" s="6" t="n">
-        <v>0.2171561051004637</v>
+        <v>0.1958997722095672</v>
       </c>
       <c r="Q64" s="10" t="inlineStr">
         <is>
@@ -5908,13 +5908,13 @@
         </is>
       </c>
       <c r="D65" s="15" t="n">
-        <v>41.72</v>
+        <v>41.57</v>
       </c>
       <c r="E65" s="25" t="n">
-        <v>-0.0784</v>
+        <v>-0.0702</v>
       </c>
       <c r="F65" s="25" t="n">
-        <v>-0.07580000000000001</v>
+        <v>-0.0789</v>
       </c>
       <c r="G65" s="17" t="n">
         <v>46328</v>
@@ -5969,13 +5969,13 @@
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>71.65000000000001</v>
+        <v>71.92</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>0.0165</v>
+        <v>0.0134</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>-0.0478</v>
+        <v>-0.0281</v>
       </c>
       <c r="G66" s="7" t="n">
         <v>46328</v>
@@ -6004,7 +6004,7 @@
         <v>89</v>
       </c>
       <c r="M66" s="6" t="n">
-        <v>0.242149337055129</v>
+        <v>0.2374860956618465</v>
       </c>
       <c r="N66" s="3" t="inlineStr"/>
       <c r="O66" s="9" t="n"/>
@@ -6060,13 +6060,13 @@
         </is>
       </c>
       <c r="D67" s="15" t="n">
-        <v>158.3</v>
+        <v>159.34</v>
       </c>
       <c r="E67" s="25" t="n">
-        <v>-0.0412</v>
+        <v>-0.0287</v>
       </c>
       <c r="F67" s="16" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.0153</v>
       </c>
       <c r="G67" s="17" t="n">
         <v>46325</v>
@@ -6095,7 +6095,7 @@
         <v>185</v>
       </c>
       <c r="M67" s="16" t="n">
-        <v>0.1686670878079595</v>
+        <v>0.1610392870591189</v>
       </c>
       <c r="N67" s="14" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>185</v>
       </c>
       <c r="P67" s="16" t="n">
-        <v>0.1686670878079595</v>
+        <v>0.1610392870591189</v>
       </c>
       <c r="Q67" s="20" t="inlineStr">
         <is>
@@ -6151,13 +6151,13 @@
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>115.18</v>
+        <v>114.54</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>-0.0077</v>
+        <v>-0.031</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>-0.0737</v>
+        <v>-0.08810000000000001</v>
       </c>
       <c r="G68" s="7" t="n">
         <v>46329</v>
@@ -6186,7 +6186,7 @@
         <v>120</v>
       </c>
       <c r="M68" s="6" t="n">
-        <v>0.04184754297621109</v>
+        <v>0.04766893661602928</v>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
@@ -6196,8 +6196,8 @@
       <c r="O68" s="9" t="n">
         <v>115</v>
       </c>
-      <c r="P68" s="5" t="n">
-        <v>-0.001562771314464376</v>
+      <c r="P68" s="6" t="n">
+        <v>0.004016064257028057</v>
       </c>
       <c r="Q68" s="10" t="inlineStr"/>
       <c r="R68" s="9" t="n"/>
@@ -6232,13 +6232,13 @@
         </is>
       </c>
       <c r="D69" s="15" t="n">
-        <v>290.82</v>
+        <v>284.51</v>
       </c>
       <c r="E69" s="25" t="n">
-        <v>-0.181</v>
+        <v>-0.2077</v>
       </c>
       <c r="F69" s="25" t="n">
-        <v>-0.1826</v>
+        <v>-0.2134</v>
       </c>
       <c r="G69" s="17" t="n">
         <v>46325</v>
@@ -6267,7 +6267,7 @@
         <v>406</v>
       </c>
       <c r="M69" s="16" t="n">
-        <v>0.3960525410907091</v>
+        <v>0.4270148676672174</v>
       </c>
       <c r="N69" s="14" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         <v>436</v>
       </c>
       <c r="P69" s="16" t="n">
-        <v>0.4992091327969191</v>
+        <v>0.5324593160170118</v>
       </c>
       <c r="Q69" s="20" t="inlineStr">
         <is>
@@ -6315,13 +6315,13 @@
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>313.59</v>
+        <v>308.64</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>-0.0667</v>
+        <v>-0.0851</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>-0.0799</v>
+        <v>-0.0537</v>
       </c>
       <c r="G70" s="7" t="n">
         <v>46311</v>
@@ -6350,7 +6350,7 @@
         <v>415</v>
       </c>
       <c r="M70" s="6" t="n">
-        <v>0.3233840364807553</v>
+        <v>0.3446086054950752</v>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>380</v>
       </c>
       <c r="P70" s="6" t="n">
-        <v>0.2117733346088843</v>
+        <v>0.2312078797304303</v>
       </c>
       <c r="Q70" s="10" t="inlineStr">
         <is>
@@ -6410,13 +6410,13 @@
         </is>
       </c>
       <c r="D71" s="15" t="n">
-        <v>57.96</v>
+        <v>56.37</v>
       </c>
       <c r="E71" s="25" t="n">
-        <v>-0.0605</v>
+        <v>-0.0956</v>
       </c>
       <c r="F71" s="25" t="n">
-        <v>-0.0542</v>
+        <v>-0.0915</v>
       </c>
       <c r="G71" s="17" t="n">
         <v>46309</v>
@@ -6471,13 +6471,13 @@
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>1090.27</v>
+        <v>1071.97</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>-0.0573</v>
+        <v>-0.0858</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>0.0512</v>
+        <v>0.0154</v>
       </c>
       <c r="G72" s="7" t="n">
         <v>46308</v>
@@ -6509,7 +6509,7 @@
         <v>1245</v>
       </c>
       <c r="P72" s="6" t="n">
-        <v>0.1419189741990516</v>
+        <v>0.1614130992471804</v>
       </c>
       <c r="Q72" s="10" t="inlineStr">
         <is>
@@ -6554,13 +6554,13 @@
         </is>
       </c>
       <c r="D73" s="15" t="n">
-        <v>40.14</v>
+        <v>41.03</v>
       </c>
       <c r="E73" s="16" t="n">
-        <v>0.32</v>
+        <v>0.3406</v>
       </c>
       <c r="F73" s="16" t="n">
-        <v>0.6559</v>
+        <v>0.7126</v>
       </c>
       <c r="G73" s="17" t="n"/>
       <c r="H73" s="22" t="inlineStr">
@@ -6605,13 +6605,13 @@
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>28.25</v>
+        <v>27.99</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>0.2374</v>
+        <v>0.1593</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>0.7028</v>
+        <v>0.7723</v>
       </c>
       <c r="G74" s="7" t="n">
         <v>46346</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="D75" s="15" t="n">
-        <v>502.01</v>
-      </c>
-      <c r="E75" s="16" t="n">
-        <v>0.0125</v>
+        <v>503.51</v>
+      </c>
+      <c r="E75" s="25" t="n">
+        <v>-0.0016</v>
       </c>
       <c r="F75" s="16" t="n">
-        <v>0.0227</v>
+        <v>0.0173</v>
       </c>
       <c r="G75" s="17" t="n">
         <v>46332</v>
@@ -6749,13 +6749,13 @@
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>64.3</v>
+        <v>61.73</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>-0.1182</v>
+        <v>-0.1728</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>-0.0219</v>
+        <v>-0.0877</v>
       </c>
       <c r="G76" s="7" t="n">
         <v>46321</v>
@@ -6784,7 +6784,7 @@
         <v>68</v>
       </c>
       <c r="M76" s="6" t="n">
-        <v>0.057542768273717</v>
+        <v>0.1015713591446623</v>
       </c>
       <c r="N76" s="3" t="inlineStr"/>
       <c r="O76" s="9" t="n"/>
@@ -6826,13 +6826,13 @@
         </is>
       </c>
       <c r="D77" s="15" t="n">
-        <v>126.41</v>
+        <v>123.8</v>
       </c>
       <c r="E77" s="25" t="n">
-        <v>-0.1184</v>
-      </c>
-      <c r="F77" s="16" t="n">
-        <v>0.0153</v>
+        <v>-0.1381</v>
+      </c>
+      <c r="F77" s="25" t="n">
+        <v>-0.04769999999999999</v>
       </c>
       <c r="G77" s="17" t="n">
         <v>46310</v>
@@ -6891,13 +6891,13 @@
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>135.05</v>
-      </c>
-      <c r="E78" s="6" t="n">
-        <v>0.0258</v>
-      </c>
-      <c r="F78" s="6" t="n">
-        <v>0.024</v>
+        <v>131.4</v>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>-0.006</v>
       </c>
       <c r="G78" s="7" t="n">
         <v>46308</v>
@@ -6929,7 +6929,7 @@
         <v>140</v>
       </c>
       <c r="P78" s="6" t="n">
-        <v>0.03665309144761191</v>
+        <v>0.06544901065449006</v>
       </c>
       <c r="Q78" s="10" t="inlineStr">
         <is>
@@ -6978,13 +6978,13 @@
         </is>
       </c>
       <c r="D79" s="15" t="n">
-        <v>337.26</v>
+        <v>334.58</v>
       </c>
       <c r="E79" s="25" t="n">
-        <v>-0.0109</v>
+        <v>-0.0325</v>
       </c>
       <c r="F79" s="25" t="n">
-        <v>-0.0453</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G79" s="17" t="n">
         <v>46315</v>
@@ -7013,7 +7013,7 @@
         <v>358</v>
       </c>
       <c r="M79" s="16" t="n">
-        <v>0.06149558204352728</v>
+        <v>0.06999820670691619</v>
       </c>
       <c r="N79" s="14" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>374</v>
       </c>
       <c r="P79" s="16" t="n">
-        <v>0.1089367253750816</v>
+        <v>0.1178193556100186</v>
       </c>
       <c r="Q79" s="20" t="inlineStr">
         <is>
@@ -7069,13 +7069,13 @@
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>56.55</v>
+        <v>56.03</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>-0.0313</v>
+        <v>-0.0443</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>-0.0358</v>
+        <v>-0.0517</v>
       </c>
       <c r="G80" s="7" t="n">
         <v>46315</v>
@@ -7104,7 +7104,7 @@
         <v>57</v>
       </c>
       <c r="M80" s="6" t="n">
-        <v>0.007957559681697663</v>
+        <v>0.01731215420310546</v>
       </c>
       <c r="N80" s="3" t="inlineStr"/>
       <c r="O80" s="9" t="n"/>
@@ -7146,13 +7146,13 @@
         </is>
       </c>
       <c r="D81" s="15" t="n">
-        <v>14.76</v>
+        <v>14.95</v>
       </c>
       <c r="E81" s="16" t="n">
-        <v>0.2321</v>
-      </c>
-      <c r="F81" s="25" t="n">
-        <v>-0.0545</v>
+        <v>0.2531</v>
+      </c>
+      <c r="F81" s="16" t="n">
+        <v>0.0296</v>
       </c>
       <c r="G81" s="17" t="n"/>
       <c r="H81" s="22" t="inlineStr">
@@ -7197,13 +7197,13 @@
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>397.22</v>
+        <v>394.72</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>-0.04769999999999999</v>
+        <v>-0.0464</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.06509999999999999</v>
       </c>
       <c r="G82" s="7" t="n">
         <v>46330</v>
@@ -7270,13 +7270,13 @@
         </is>
       </c>
       <c r="D83" s="15" t="n">
-        <v>94.48999999999999</v>
+        <v>93.3</v>
       </c>
       <c r="E83" s="16" t="n">
-        <v>0.07400000000000001</v>
+        <v>0.0636</v>
       </c>
       <c r="F83" s="16" t="n">
-        <v>0.5196000000000001</v>
+        <v>0.4962</v>
       </c>
       <c r="G83" s="17" t="n">
         <v>46337</v>
@@ -7331,13 +7331,13 @@
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>39.37</v>
+        <v>38.89</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>-0.1786</v>
+        <v>-0.1898</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>-0.1502</v>
+        <v>-0.1957</v>
       </c>
       <c r="G84" s="7" t="n">
         <v>46331</v>
@@ -7392,13 +7392,13 @@
         </is>
       </c>
       <c r="D85" s="15" t="n">
-        <v>959.39</v>
+        <v>942.14</v>
       </c>
       <c r="E85" s="25" t="n">
-        <v>-0.07690000000000001</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="F85" s="25" t="n">
-        <v>-0.1073</v>
+        <v>-0.1122</v>
       </c>
       <c r="G85" s="17" t="n">
         <v>46308</v>
@@ -7427,7 +7427,7 @@
         <v>1325</v>
       </c>
       <c r="M85" s="16" t="n">
-        <v>0.3810858983312313</v>
+        <v>0.4063727259218375</v>
       </c>
       <c r="N85" s="14" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>1210</v>
       </c>
       <c r="P85" s="16" t="n">
-        <v>0.2612180656458792</v>
+        <v>0.2843101874456026</v>
       </c>
       <c r="Q85" s="20" t="inlineStr">
         <is>
@@ -7479,13 +7479,13 @@
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>132.61</v>
+        <v>129.74</v>
       </c>
       <c r="E86" s="6" t="n">
-        <v>0.0276</v>
+        <v>0.0061</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>-0.0377</v>
+        <v>-0.07480000000000001</v>
       </c>
       <c r="G86" s="7" t="n">
         <v>46324</v>
@@ -7540,13 +7540,13 @@
         </is>
       </c>
       <c r="D87" s="15" t="n">
-        <v>123.3</v>
+        <v>124.31</v>
       </c>
       <c r="E87" s="16" t="n">
-        <v>0.1403</v>
+        <v>0.1997</v>
       </c>
       <c r="F87" s="16" t="n">
-        <v>0.2138</v>
+        <v>0.3098</v>
       </c>
       <c r="G87" s="17" t="n">
         <v>46330</v>
@@ -7601,13 +7601,13 @@
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>103.42</v>
+        <v>107.01</v>
       </c>
       <c r="E88" s="6" t="n">
-        <v>0.279</v>
+        <v>0.345</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>-0.1211</v>
+        <v>-0.0271</v>
       </c>
       <c r="G88" s="7" t="n">
         <v>46329</v>
@@ -7662,13 +7662,13 @@
         </is>
       </c>
       <c r="D89" s="15" t="n">
-        <v>155.37</v>
+        <v>153.43</v>
       </c>
       <c r="E89" s="25" t="n">
-        <v>-0.0365</v>
+        <v>-0.0587</v>
       </c>
       <c r="F89" s="16" t="n">
-        <v>0.0849</v>
+        <v>0.0524</v>
       </c>
       <c r="G89" s="17" t="n">
         <v>46324</v>
@@ -7723,13 +7723,13 @@
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>151.56</v>
+        <v>150.04</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>-0.08810000000000001</v>
-      </c>
-      <c r="F90" s="6" t="n">
-        <v>0.0225</v>
+        <v>-0.1201</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>-0.0036</v>
       </c>
       <c r="G90" s="7" t="n">
         <v>46329</v>
@@ -7798,13 +7798,13 @@
         </is>
       </c>
       <c r="D91" s="15" t="n">
-        <v>352.04</v>
-      </c>
-      <c r="E91" s="16" t="n">
-        <v>0.0013</v>
-      </c>
-      <c r="F91" s="16" t="n">
-        <v>0.0061</v>
+        <v>338.87</v>
+      </c>
+      <c r="E91" s="25" t="n">
+        <v>-0.0492</v>
+      </c>
+      <c r="F91" s="25" t="n">
+        <v>-0.0406</v>
       </c>
       <c r="G91" s="17" t="n">
         <v>46308</v>
@@ -7833,7 +7833,7 @@
         <v>196</v>
       </c>
       <c r="M91" s="25" t="n">
-        <v>-0.4432450857857062</v>
+        <v>-0.421607105969841</v>
       </c>
       <c r="N91" s="14" t="inlineStr"/>
       <c r="O91" s="19" t="n"/>
@@ -7877,13 +7877,13 @@
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>100.83</v>
+        <v>98.92</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>-0.07049999999999999</v>
-      </c>
-      <c r="F92" s="6" t="n">
-        <v>0.0506</v>
+        <v>-0.07829999999999999</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>-0.0044</v>
       </c>
       <c r="G92" s="7" t="n">
         <v>46332</v>
@@ -7912,7 +7912,7 @@
         <v>375</v>
       </c>
       <c r="M92" s="6" t="n">
-        <v>2.719131210949123</v>
+        <v>2.79094217549535</v>
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         <v>368</v>
       </c>
       <c r="P92" s="6" t="n">
-        <v>2.649707428344739</v>
+        <v>2.72017792155277</v>
       </c>
       <c r="Q92" s="10" t="inlineStr">
         <is>
@@ -7976,13 +7976,13 @@
         </is>
       </c>
       <c r="D93" s="15" t="n">
-        <v>358.19</v>
+        <v>352.99</v>
       </c>
       <c r="E93" s="25" t="n">
-        <v>-0.06610000000000001</v>
+        <v>-0.1075</v>
       </c>
       <c r="F93" s="16" t="n">
-        <v>0.078</v>
+        <v>0.0111</v>
       </c>
       <c r="G93" s="17" t="n">
         <v>46317</v>
@@ -8014,7 +8014,7 @@
         <v>115</v>
       </c>
       <c r="P93" s="25" t="n">
-        <v>-0.6789413439794523</v>
+        <v>-0.6742117340434574</v>
       </c>
       <c r="Q93" s="20" t="inlineStr">
         <is>
@@ -8063,13 +8063,13 @@
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>567.65</v>
+        <v>559.33</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>-0.0224</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.0364</v>
       </c>
       <c r="G94" s="7" t="n">
         <v>46324</v>
@@ -8098,7 +8098,7 @@
         <v>366</v>
       </c>
       <c r="M94" s="5" t="n">
-        <v>-0.3552365013652779</v>
+        <v>-0.345645683228148</v>
       </c>
       <c r="N94" s="3" t="inlineStr"/>
       <c r="O94" s="9" t="n"/>
@@ -8140,13 +8140,13 @@
         </is>
       </c>
       <c r="D95" s="15" t="n">
-        <v>1774.64</v>
+        <v>1750.5</v>
       </c>
       <c r="E95" s="25" t="n">
-        <v>-0.0117</v>
+        <v>-0.0368</v>
       </c>
       <c r="F95" s="25" t="n">
-        <v>-0.0953</v>
+        <v>-0.1224</v>
       </c>
       <c r="G95" s="17" t="n">
         <v>46330</v>
@@ -8211,13 +8211,13 @@
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>206.12</v>
+        <v>199.1</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>-0.0377</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>-0.0421</v>
+        <v>-0.0717</v>
       </c>
       <c r="G96" s="7" t="n">
         <v>46309</v>
@@ -8246,7 +8246,7 @@
         <v>668</v>
       </c>
       <c r="M96" s="6" t="n">
-        <v>2.240830584125752</v>
+        <v>2.3550979407333</v>
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>550</v>
       </c>
       <c r="P96" s="6" t="n">
-        <v>1.668348534834077</v>
+        <v>1.762430939226519</v>
       </c>
       <c r="Q96" s="10" t="inlineStr">
         <is>
@@ -8306,13 +8306,13 @@
         </is>
       </c>
       <c r="D97" s="15" t="n">
-        <v>116.47</v>
+        <v>113.45</v>
       </c>
       <c r="E97" s="16" t="n">
-        <v>0.0516</v>
+        <v>0.0139</v>
       </c>
       <c r="F97" s="16" t="n">
-        <v>0.08529999999999999</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="G97" s="17" t="n">
         <v>46321</v>
@@ -8341,7 +8341,7 @@
         <v>240</v>
       </c>
       <c r="M97" s="16" t="n">
-        <v>1.060616467759938</v>
+        <v>1.115469369766417</v>
       </c>
       <c r="N97" s="14" t="inlineStr">
         <is>
@@ -8352,7 +8352,7 @@
         <v>240</v>
       </c>
       <c r="P97" s="16" t="n">
-        <v>1.060616467759938</v>
+        <v>1.115469369766417</v>
       </c>
       <c r="Q97" s="20" t="inlineStr">
         <is>
@@ -8401,13 +8401,13 @@
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>233.25</v>
+        <v>227.7</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>-0.0406</v>
+        <v>-0.06559999999999999</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="G98" s="7" t="n">
         <v>46310</v>
@@ -8436,7 +8436,7 @@
         <v>113</v>
       </c>
       <c r="M98" s="5" t="n">
-        <v>-0.5155412647374062</v>
+        <v>-0.5037329819938515</v>
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         <v>114</v>
       </c>
       <c r="P98" s="5" t="n">
-        <v>-0.5112540192926045</v>
+        <v>-0.4993412384716732</v>
       </c>
       <c r="Q98" s="10" t="inlineStr"/>
       <c r="R98" s="9" t="n"/>
@@ -8486,13 +8486,13 @@
         </is>
       </c>
       <c r="D99" s="15" t="n">
-        <v>24.18</v>
+        <v>24.71</v>
       </c>
       <c r="E99" s="16" t="n">
-        <v>0.2194</v>
+        <v>0.2355</v>
       </c>
       <c r="F99" s="16" t="n">
-        <v>0.0134</v>
+        <v>0.0968</v>
       </c>
       <c r="G99" s="17" t="n">
         <v>46324</v>
@@ -8547,13 +8547,13 @@
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>14.62</v>
-      </c>
-      <c r="E100" s="6" t="n">
-        <v>0.0021</v>
+        <v>14.48</v>
+      </c>
+      <c r="E100" s="5" t="n">
+        <v>-0.0166</v>
       </c>
       <c r="F100" s="6" t="n">
-        <v>0.1067</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="G100" s="7" t="n">
         <v>46323</v>
@@ -8608,13 +8608,13 @@
         </is>
       </c>
       <c r="D101" s="15" t="n">
-        <v>105.38</v>
+        <v>101.9</v>
       </c>
       <c r="E101" s="25" t="n">
-        <v>-0.0379</v>
+        <v>-0.0799</v>
       </c>
       <c r="F101" s="16" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.027</v>
       </c>
       <c r="G101" s="17" t="n">
         <v>46323</v>
@@ -8643,7 +8643,7 @@
         <v>285</v>
       </c>
       <c r="M101" s="16" t="n">
-        <v>1.704498007211995</v>
+        <v>1.796859666339548</v>
       </c>
       <c r="N101" s="14" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         <v>285</v>
       </c>
       <c r="P101" s="16" t="n">
-        <v>1.704498007211995</v>
+        <v>1.796859666339548</v>
       </c>
       <c r="Q101" s="20" t="inlineStr">
         <is>
@@ -8695,13 +8695,13 @@
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>404.47</v>
+        <v>403.79</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>-0.0622</v>
+        <v>-0.0726</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>-0.03700000000000001</v>
+        <v>-0.053</v>
       </c>
       <c r="G102" s="7" t="n">
         <v>46324</v>
@@ -8770,13 +8770,13 @@
         </is>
       </c>
       <c r="D103" s="15" t="n">
-        <v>49</v>
+        <v>48.13</v>
       </c>
       <c r="E103" s="25" t="n">
-        <v>-0.0282</v>
+        <v>-0.0526</v>
       </c>
       <c r="F103" s="25" t="n">
-        <v>-0.043</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G103" s="17" t="n">
         <v>46311</v>
@@ -8831,13 +8831,13 @@
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>369.95</v>
+        <v>364.26</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0475</v>
       </c>
       <c r="F104" s="6" t="n">
-        <v>0.0522</v>
+        <v>0.0239</v>
       </c>
       <c r="G104" s="7" t="n">
         <v>46322</v>
@@ -8866,7 +8866,7 @@
         <v>525</v>
       </c>
       <c r="M104" s="6" t="n">
-        <v>0.4191106906338695</v>
+        <v>0.441278207873497</v>
       </c>
       <c r="N104" s="3" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>543</v>
       </c>
       <c r="P104" s="6" t="n">
-        <v>0.467765914312745</v>
+        <v>0.490693460714874</v>
       </c>
       <c r="Q104" s="10" t="inlineStr">
         <is>
@@ -8922,13 +8922,13 @@
         </is>
       </c>
       <c r="D105" s="15" t="n">
-        <v>68.79000000000001</v>
-      </c>
-      <c r="E105" s="16" t="n">
-        <v>0.0028</v>
+        <v>68.19</v>
+      </c>
+      <c r="E105" s="25" t="n">
+        <v>-0.0216</v>
       </c>
       <c r="F105" s="25" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-0.09630000000000001</v>
       </c>
       <c r="G105" s="17" t="n">
         <v>46314</v>
@@ -8957,7 +8957,7 @@
         <v>412</v>
       </c>
       <c r="M105" s="16" t="n">
-        <v>4.989242622474196</v>
+        <v>5.041941633670627</v>
       </c>
       <c r="N105" s="14" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>350</v>
       </c>
       <c r="P105" s="16" t="n">
-        <v>4.087948829771769</v>
+        <v>4.132717407244464</v>
       </c>
       <c r="Q105" s="20" t="inlineStr">
         <is>
@@ -9013,13 +9013,13 @@
         </is>
       </c>
       <c r="D106" s="4" t="n">
-        <v>77.91</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>-0.0517</v>
+        <v>-0.04849999999999999</v>
       </c>
       <c r="F106" s="6" t="n">
-        <v>0.0186</v>
+        <v>0.0036</v>
       </c>
       <c r="G106" s="7" t="n">
         <v>46331</v>
@@ -9048,7 +9048,7 @@
         <v>68</v>
       </c>
       <c r="M106" s="5" t="n">
-        <v>-0.1271980490309331</v>
+        <v>-0.1217874208962935</v>
       </c>
       <c r="N106" s="3" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>68</v>
       </c>
       <c r="P106" s="5" t="n">
-        <v>-0.1271980490309331</v>
+        <v>-0.1217874208962935</v>
       </c>
       <c r="Q106" s="10" t="inlineStr">
         <is>
@@ -9104,13 +9104,13 @@
         </is>
       </c>
       <c r="D107" s="15" t="n">
-        <v>264.48</v>
-      </c>
-      <c r="E107" s="25" t="n">
-        <v>-0.0018</v>
+        <v>265.91</v>
+      </c>
+      <c r="E107" s="16" t="n">
+        <v>0.0053</v>
       </c>
       <c r="F107" s="16" t="n">
-        <v>0.0294</v>
+        <v>0.0253</v>
       </c>
       <c r="G107" s="17" t="n">
         <v>46325</v>
@@ -9139,7 +9139,7 @@
         <v>295</v>
       </c>
       <c r="M107" s="16" t="n">
-        <v>0.1153962492437991</v>
+        <v>0.1093979165883193</v>
       </c>
       <c r="N107" s="14" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>246</v>
       </c>
       <c r="P107" s="25" t="n">
-        <v>-0.06987295825771331</v>
+        <v>-0.07487495769245242</v>
       </c>
       <c r="Q107" s="20" t="inlineStr">
         <is>
@@ -9187,13 +9187,13 @@
         </is>
       </c>
       <c r="D108" s="4" t="n">
-        <v>102.98</v>
+        <v>104.15</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>-0.1171</v>
+        <v>-0.1073</v>
       </c>
       <c r="F108" s="6" t="n">
-        <v>0.0221</v>
+        <v>0.0106</v>
       </c>
       <c r="G108" s="7" t="n">
         <v>46316</v>
@@ -9222,7 +9222,7 @@
         <v>112</v>
       </c>
       <c r="M108" s="6" t="n">
-        <v>0.08758982326665368</v>
+        <v>0.07537205952952467</v>
       </c>
       <c r="N108" s="3" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>120</v>
       </c>
       <c r="P108" s="6" t="n">
-        <v>0.1652748106428432</v>
+        <v>0.1521843494959193</v>
       </c>
       <c r="Q108" s="10" t="inlineStr">
         <is>
@@ -9286,13 +9286,13 @@
         </is>
       </c>
       <c r="D109" s="15" t="n">
-        <v>393.16</v>
+        <v>407.32</v>
       </c>
       <c r="E109" s="25" t="n">
-        <v>-0.1051</v>
+        <v>-0.0823</v>
       </c>
       <c r="F109" s="16" t="n">
-        <v>0.0583</v>
+        <v>0.0832</v>
       </c>
       <c r="G109" s="17" t="n">
         <v>46329</v>
@@ -9321,7 +9321,7 @@
         <v>390</v>
       </c>
       <c r="M109" s="25" t="n">
-        <v>-0.008037440227897102</v>
+        <v>-0.04252185014239417</v>
       </c>
       <c r="N109" s="14" t="inlineStr">
         <is>
@@ -9369,13 +9369,13 @@
         </is>
       </c>
       <c r="D110" s="4" t="n">
-        <v>180.7</v>
+        <v>181.51</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>-0.05889999999999999</v>
+        <v>-0.0484</v>
       </c>
       <c r="F110" s="6" t="n">
-        <v>0.1813</v>
+        <v>0.1609</v>
       </c>
       <c r="G110" s="7" t="n">
         <v>46331</v>
@@ -9404,7 +9404,7 @@
         <v>161</v>
       </c>
       <c r="M110" s="5" t="n">
-        <v>-0.1090204759269507</v>
+        <v>-0.112996529116853</v>
       </c>
       <c r="N110" s="3" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>180</v>
       </c>
       <c r="P110" s="5" t="n">
-        <v>-0.003873824017708847</v>
+        <v>-0.008319100875984744</v>
       </c>
       <c r="Q110" s="10" t="inlineStr">
         <is>
@@ -9456,13 +9456,13 @@
         </is>
       </c>
       <c r="D111" s="15" t="n">
-        <v>43.72</v>
+        <v>44.61</v>
       </c>
       <c r="E111" s="25" t="n">
-        <v>-0.132</v>
+        <v>-0.0898</v>
       </c>
       <c r="F111" s="16" t="n">
-        <v>0.0032</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="G111" s="17" t="n">
         <v>46323</v>
@@ -9491,7 +9491,7 @@
         <v>55</v>
       </c>
       <c r="M111" s="16" t="n">
-        <v>0.2580054894784996</v>
+        <v>0.2329074198610177</v>
       </c>
       <c r="N111" s="14" t="inlineStr">
         <is>
@@ -9502,7 +9502,7 @@
         <v>65</v>
       </c>
       <c r="P111" s="16" t="n">
-        <v>0.4867337602927722</v>
+        <v>0.4570724052902937</v>
       </c>
       <c r="Q111" s="20" t="inlineStr">
         <is>
@@ -9543,13 +9543,13 @@
         </is>
       </c>
       <c r="D112" s="4" t="n">
-        <v>316.49</v>
+        <v>315.1</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0268</v>
       </c>
       <c r="F112" s="6" t="n">
-        <v>0.0375</v>
+        <v>0.0168</v>
       </c>
       <c r="G112" s="7" t="n">
         <v>46330</v>
@@ -9578,7 +9578,7 @@
         <v>331</v>
       </c>
       <c r="M112" s="6" t="n">
-        <v>0.04584663022528355</v>
+        <v>0.05046017137416686</v>
       </c>
       <c r="N112" s="3" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         <v>330</v>
       </c>
       <c r="P112" s="6" t="n">
-        <v>0.0426869727321558</v>
+        <v>0.04728657569025699</v>
       </c>
       <c r="Q112" s="10" t="inlineStr">
         <is>
@@ -9638,13 +9638,13 @@
         </is>
       </c>
       <c r="D113" s="15" t="n">
-        <v>87.59999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="E113" s="25" t="n">
-        <v>-0.0583</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="F113" s="25" t="n">
-        <v>-0.1805</v>
+        <v>-0.1897</v>
       </c>
       <c r="G113" s="17" t="n">
         <v>46330</v>
@@ -9673,7 +9673,7 @@
         <v>123</v>
       </c>
       <c r="M113" s="16" t="n">
-        <v>0.404109589041096</v>
+        <v>0.4089347079037801</v>
       </c>
       <c r="N113" s="14" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         <v>130</v>
       </c>
       <c r="P113" s="16" t="n">
-        <v>0.4840182648401827</v>
+        <v>0.4891179839633448</v>
       </c>
       <c r="Q113" s="20" t="inlineStr">
         <is>
@@ -9725,13 +9725,13 @@
         </is>
       </c>
       <c r="D114" s="4" t="n">
-        <v>215.84</v>
-      </c>
-      <c r="E114" s="5" t="n">
-        <v>-0.0138</v>
+        <v>219.49</v>
+      </c>
+      <c r="E114" s="6" t="n">
+        <v>0.0204</v>
       </c>
       <c r="F114" s="6" t="n">
-        <v>0.1212</v>
+        <v>0.1462</v>
       </c>
       <c r="G114" s="7" t="n">
         <v>46315</v>
@@ -9760,7 +9760,7 @@
         <v>212</v>
       </c>
       <c r="M114" s="5" t="n">
-        <v>-0.0177909562638992</v>
+        <v>-0.03412456148343892</v>
       </c>
       <c r="N114" s="3" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         <v>205</v>
       </c>
       <c r="P114" s="5" t="n">
-        <v>-0.05022238695329875</v>
+        <v>-0.06601667501936311</v>
       </c>
       <c r="Q114" s="10" t="inlineStr">
         <is>
@@ -9816,13 +9816,13 @@
         </is>
       </c>
       <c r="D115" s="15" t="n">
-        <v>89.17</v>
+        <v>89.18000000000001</v>
       </c>
       <c r="E115" s="25" t="n">
-        <v>-0.0343</v>
+        <v>-0.0206</v>
       </c>
       <c r="F115" s="16" t="n">
-        <v>0.2652</v>
+        <v>0.2466</v>
       </c>
       <c r="G115" s="17" t="n">
         <v>46324</v>
@@ -9851,7 +9851,7 @@
         <v>85</v>
       </c>
       <c r="M115" s="25" t="n">
-        <v>-0.04676460693058205</v>
+        <v>-0.04687149585108776</v>
       </c>
       <c r="N115" s="14" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>90</v>
       </c>
       <c r="P115" s="16" t="n">
-        <v>0.009308063249971944</v>
+        <v>0.009194886745907077</v>
       </c>
       <c r="Q115" s="20" t="inlineStr">
         <is>
@@ -9903,13 +9903,13 @@
         </is>
       </c>
       <c r="D116" s="4" t="n">
-        <v>150.56</v>
+        <v>151.93</v>
       </c>
       <c r="E116" s="6" t="n">
-        <v>0.0304</v>
+        <v>0.0354</v>
       </c>
       <c r="F116" s="6" t="n">
-        <v>0.1505</v>
+        <v>0.1749</v>
       </c>
       <c r="G116" s="7" t="n">
         <v>46324</v>
@@ -9938,7 +9938,7 @@
         <v>165</v>
       </c>
       <c r="M116" s="6" t="n">
-        <v>0.09590860786397448</v>
+        <v>0.0860264595537418</v>
       </c>
       <c r="N116" s="3" t="inlineStr"/>
       <c r="O116" s="9" t="n"/>
@@ -9986,10 +9986,10 @@
         </is>
       </c>
       <c r="D117" s="15" t="n">
-        <v>515.3</v>
+        <v>520.04</v>
       </c>
       <c r="E117" s="25" t="n">
-        <v>-0.0747</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="F117" s="25" t="n">
         <v>-0.0446</v>
@@ -10057,13 +10057,13 @@
         </is>
       </c>
       <c r="D118" s="4" t="n">
-        <v>401.65</v>
+        <v>400.45</v>
       </c>
       <c r="E118" s="6" t="n">
-        <v>0.0603</v>
+        <v>0.07200000000000001</v>
       </c>
       <c r="F118" s="6" t="n">
-        <v>0.2097</v>
+        <v>0.1865</v>
       </c>
       <c r="G118" s="7" t="n">
         <v>46315</v>
@@ -10092,7 +10092,7 @@
         <v>487</v>
       </c>
       <c r="M118" s="6" t="n">
-        <v>0.2124984439188349</v>
+        <v>0.2161318516668748</v>
       </c>
       <c r="N118" s="3" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>375</v>
       </c>
       <c r="P118" s="5" t="n">
-        <v>-0.06635130088385405</v>
+        <v>-0.06355350230990134</v>
       </c>
       <c r="Q118" s="10" t="inlineStr">
         <is>
@@ -10148,13 +10148,13 @@
         </is>
       </c>
       <c r="D119" s="15" t="n">
-        <v>269.47</v>
+        <v>269.14</v>
       </c>
       <c r="E119" s="25" t="n">
-        <v>-0.0028</v>
+        <v>-0.0143</v>
       </c>
       <c r="F119" s="16" t="n">
-        <v>0.0393</v>
+        <v>0.0218</v>
       </c>
       <c r="G119" s="17" t="n">
         <v>46308</v>
@@ -10183,7 +10183,7 @@
         <v>272</v>
       </c>
       <c r="M119" s="16" t="n">
-        <v>0.009388800237503145</v>
+        <v>0.01062643977112289</v>
       </c>
       <c r="N119" s="14" t="inlineStr"/>
       <c r="O119" s="19" t="n"/>
@@ -10235,13 +10235,13 @@
         </is>
       </c>
       <c r="D120" s="4" t="n">
-        <v>1164.89</v>
+        <v>1174.39</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>-0.0721</v>
+        <v>-0.0582</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>-0.0177</v>
+        <v>-0.0181</v>
       </c>
       <c r="G120" s="7" t="n">
         <v>46324</v>
@@ -10270,7 +10270,7 @@
         <v>1280</v>
       </c>
       <c r="M120" s="6" t="n">
-        <v>0.09881619723750731</v>
+        <v>0.08992753684891722</v>
       </c>
       <c r="N120" s="3" t="inlineStr">
         <is>
@@ -10330,13 +10330,13 @@
         </is>
       </c>
       <c r="D121" s="15" t="n">
-        <v>91.75</v>
+        <v>91.48999999999999</v>
       </c>
       <c r="E121" s="25" t="n">
-        <v>-0.0171</v>
+        <v>-0.0152</v>
       </c>
       <c r="F121" s="16" t="n">
-        <v>0.1188</v>
+        <v>0.09949999999999999</v>
       </c>
       <c r="G121" s="17" t="n"/>
       <c r="H121" s="22" t="inlineStr">
@@ -10355,7 +10355,7 @@
         <v>102</v>
       </c>
       <c r="M121" s="16" t="n">
-        <v>0.111716621253406</v>
+        <v>0.114875942725981</v>
       </c>
       <c r="N121" s="14" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>105</v>
       </c>
       <c r="P121" s="16" t="n">
-        <v>0.1444141689373297</v>
+        <v>0.1476664116296864</v>
       </c>
       <c r="Q121" s="20" t="inlineStr">
         <is>
@@ -10407,13 +10407,13 @@
         </is>
       </c>
       <c r="D122" s="4" t="n">
-        <v>149.5</v>
-      </c>
-      <c r="E122" s="5" t="n">
-        <v>-0.02</v>
+        <v>152.53</v>
+      </c>
+      <c r="E122" s="6" t="n">
+        <v>0.0124</v>
       </c>
       <c r="F122" s="6" t="n">
-        <v>0.1458</v>
+        <v>0.1637</v>
       </c>
       <c r="G122" s="7" t="n">
         <v>46324</v>
@@ -10441,8 +10441,8 @@
       <c r="L122" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="M122" s="6" t="n">
-        <v>0.003344481605351171</v>
+      <c r="M122" s="5" t="n">
+        <v>-0.01658690093752049</v>
       </c>
       <c r="N122" s="3" t="inlineStr"/>
       <c r="O122" s="9" t="n"/>
@@ -10486,13 +10486,13 @@
         </is>
       </c>
       <c r="D123" s="15" t="n">
-        <v>140.98</v>
+        <v>141.56</v>
       </c>
       <c r="E123" s="25" t="n">
-        <v>-0.1126</v>
+        <v>-0.1042</v>
       </c>
       <c r="F123" s="25" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.0868</v>
       </c>
       <c r="G123" s="17" t="n">
         <v>46322</v>
@@ -10565,13 +10565,13 @@
         </is>
       </c>
       <c r="D124" s="4" t="n">
-        <v>27.74</v>
+        <v>27.93</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0013</v>
       </c>
       <c r="F124" s="6" t="n">
-        <v>0.1092</v>
+        <v>0.1383</v>
       </c>
       <c r="G124" s="7" t="n">
         <v>46329</v>
@@ -10600,7 +10600,7 @@
         <v>28</v>
       </c>
       <c r="M124" s="6" t="n">
-        <v>0.009372746935832789</v>
+        <v>0.002506265664160411</v>
       </c>
       <c r="N124" s="3" t="inlineStr"/>
       <c r="O124" s="9" t="n"/>
@@ -10644,13 +10644,13 @@
         </is>
       </c>
       <c r="D125" s="15" t="n">
-        <v>274.19</v>
+        <v>276.13</v>
       </c>
       <c r="E125" s="25" t="n">
-        <v>-0.1677</v>
+        <v>-0.1577</v>
       </c>
       <c r="F125" s="25" t="n">
-        <v>-0.1404</v>
+        <v>-0.1639</v>
       </c>
       <c r="G125" s="17" t="n">
         <v>46324</v>
@@ -10679,7 +10679,7 @@
         <v>418</v>
       </c>
       <c r="M125" s="16" t="n">
-        <v>0.5244903169335132</v>
+        <v>0.5137797414261399</v>
       </c>
       <c r="N125" s="14" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>350</v>
       </c>
       <c r="P125" s="16" t="n">
-        <v>0.2764871074802144</v>
+        <v>0.2675189222467678</v>
       </c>
       <c r="Q125" s="20" t="inlineStr">
         <is>
@@ -10735,13 +10735,13 @@
         </is>
       </c>
       <c r="D126" s="4" t="n">
-        <v>658.76</v>
+        <v>660.38</v>
       </c>
       <c r="E126" s="6" t="n">
-        <v>0.0469</v>
+        <v>0.0503</v>
       </c>
       <c r="F126" s="6" t="n">
-        <v>0.151</v>
+        <v>0.1621</v>
       </c>
       <c r="G126" s="7" t="n">
         <v>46323</v>
@@ -10770,7 +10770,7 @@
         <v>615</v>
       </c>
       <c r="M126" s="5" t="n">
-        <v>-0.06642783411257513</v>
+        <v>-0.06871801084224234</v>
       </c>
       <c r="N126" s="3" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>570</v>
       </c>
       <c r="P126" s="5" t="n">
-        <v>-0.1347379925921428</v>
+        <v>-0.1368605954147612</v>
       </c>
       <c r="Q126" s="10" t="inlineStr">
         <is>
@@ -10830,13 +10830,13 @@
         </is>
       </c>
       <c r="D127" s="15" t="n">
-        <v>377.56</v>
+        <v>374.51</v>
       </c>
       <c r="E127" s="25" t="n">
-        <v>-0.0322</v>
+        <v>-0.0608</v>
       </c>
       <c r="F127" s="25" t="n">
-        <v>-0.1086</v>
+        <v>-0.1099</v>
       </c>
       <c r="G127" s="17" t="n">
         <v>46308</v>
@@ -10865,7 +10865,7 @@
         <v>526</v>
       </c>
       <c r="M127" s="16" t="n">
-        <v>0.3931560546668079</v>
+        <v>0.4045018824597474</v>
       </c>
       <c r="N127" s="14" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>480</v>
       </c>
       <c r="P127" s="16" t="n">
-        <v>0.2713211145248437</v>
+        <v>0.2816747216362714</v>
       </c>
       <c r="Q127" s="20" t="inlineStr">
         <is>
@@ -10921,13 +10921,13 @@
         </is>
       </c>
       <c r="D128" s="4" t="n">
-        <v>71.33</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>-0.0823</v>
+        <v>-0.0683</v>
       </c>
       <c r="F128" s="5" t="n">
-        <v>-0.0434</v>
+        <v>-0.0458</v>
       </c>
       <c r="G128" s="7" t="n">
         <v>46329</v>
@@ -11000,13 +11000,13 @@
         </is>
       </c>
       <c r="D129" s="15" t="n">
-        <v>269.94</v>
+        <v>267.54</v>
       </c>
       <c r="E129" s="25" t="n">
-        <v>-0.0387</v>
+        <v>-0.0547</v>
       </c>
       <c r="F129" s="16" t="n">
-        <v>0.1114</v>
+        <v>0.0698</v>
       </c>
       <c r="G129" s="17" t="n">
         <v>46330</v>
@@ -11035,7 +11035,7 @@
         <v>248</v>
       </c>
       <c r="M129" s="25" t="n">
-        <v>-0.08127732088612283</v>
+        <v>-0.07303580772968535</v>
       </c>
       <c r="N129" s="14" t="inlineStr"/>
       <c r="O129" s="19" t="n"/>
@@ -11091,13 +11091,13 @@
         </is>
       </c>
       <c r="D130" s="4" t="n">
-        <v>119.9</v>
+        <v>121.66</v>
       </c>
       <c r="E130" s="6" t="n">
-        <v>0.1226</v>
+        <v>0.1047</v>
       </c>
       <c r="F130" s="6" t="n">
-        <v>0.0224</v>
+        <v>0.0037</v>
       </c>
       <c r="G130" s="7" t="n">
         <v>46325</v>
@@ -11152,13 +11152,13 @@
         </is>
       </c>
       <c r="D131" s="15" t="n">
-        <v>241.23</v>
+        <v>244.68</v>
       </c>
       <c r="E131" s="16" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.0097</v>
       </c>
       <c r="F131" s="16" t="n">
-        <v>0.0004</v>
+        <v>0.0112</v>
       </c>
       <c r="G131" s="17" t="n">
         <v>46324</v>
@@ -11213,13 +11213,13 @@
         </is>
       </c>
       <c r="D132" s="4" t="n">
-        <v>201.15</v>
+        <v>198.55</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>-0.0609</v>
+        <v>-0.0566</v>
       </c>
       <c r="F132" s="5" t="n">
-        <v>-0.0386</v>
+        <v>-0.0524</v>
       </c>
       <c r="G132" s="7" t="n">
         <v>46330</v>
@@ -11248,7 +11248,7 @@
         <v>250</v>
       </c>
       <c r="M132" s="6" t="n">
-        <v>0.2428535918468804</v>
+        <v>0.2591286829513976</v>
       </c>
       <c r="N132" s="3" t="inlineStr"/>
       <c r="O132" s="9" t="n"/>
@@ -11292,13 +11292,13 @@
         </is>
       </c>
       <c r="D133" s="15" t="n">
-        <v>164.62</v>
+        <v>162.9</v>
       </c>
       <c r="E133" s="25" t="n">
-        <v>-0.0964</v>
+        <v>-0.1216</v>
       </c>
       <c r="F133" s="16" t="n">
-        <v>0.14</v>
+        <v>0.09390000000000001</v>
       </c>
       <c r="G133" s="17" t="n">
         <v>46329</v>
@@ -11363,13 +11363,13 @@
         </is>
       </c>
       <c r="D134" s="4" t="n">
-        <v>816.5</v>
+        <v>805.98</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>-0.0138</v>
+        <v>-0.0062</v>
       </c>
       <c r="F134" s="5" t="n">
-        <v>-0.0872</v>
+        <v>-0.0931</v>
       </c>
       <c r="G134" s="7" t="n">
         <v>46330</v>
@@ -11398,7 +11398,7 @@
         <v>1155</v>
       </c>
       <c r="M134" s="6" t="n">
-        <v>0.4145744029393754</v>
+        <v>0.4330380406461699</v>
       </c>
       <c r="N134" s="3" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
         <v>1103</v>
       </c>
       <c r="P134" s="6" t="n">
-        <v>0.3508879363135334</v>
+        <v>0.3685203106776843</v>
       </c>
       <c r="Q134" s="10" t="inlineStr">
         <is>
@@ -11450,13 +11450,13 @@
         </is>
       </c>
       <c r="D135" s="15" t="n">
-        <v>534.78</v>
+        <v>524.58</v>
       </c>
       <c r="E135" s="25" t="n">
-        <v>-0.09</v>
+        <v>-0.0823</v>
       </c>
       <c r="F135" s="25" t="n">
-        <v>-0.1959</v>
+        <v>-0.2107</v>
       </c>
       <c r="G135" s="17" t="n">
         <v>46331</v>
@@ -11485,7 +11485,7 @@
         <v>874</v>
       </c>
       <c r="M135" s="16" t="n">
-        <v>0.6343169153670669</v>
+        <v>0.6660947805863737</v>
       </c>
       <c r="N135" s="14" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>845</v>
       </c>
       <c r="P135" s="16" t="n">
-        <v>0.5800890085642695</v>
+        <v>0.6108124594914025</v>
       </c>
       <c r="Q135" s="20" t="inlineStr">
         <is>
@@ -11545,13 +11545,13 @@
         </is>
       </c>
       <c r="D136" s="4" t="n">
-        <v>196.88</v>
+        <v>196.79</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>-0.0339</v>
+        <v>-0.0512</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>-0.0313</v>
+        <v>-0.0443</v>
       </c>
       <c r="G136" s="7" t="n">
         <v>46288</v>
@@ -11580,7 +11580,7 @@
         <v>250</v>
       </c>
       <c r="M136" s="6" t="n">
-        <v>0.2698090207232832</v>
+        <v>0.2703897555770111</v>
       </c>
       <c r="N136" s="3" t="inlineStr"/>
       <c r="O136" s="9" t="n"/>
@@ -11624,13 +11624,13 @@
         </is>
       </c>
       <c r="D137" s="15" t="n">
-        <v>684.73</v>
+        <v>693.78</v>
       </c>
       <c r="E137" s="16" t="n">
-        <v>0.0575</v>
+        <v>0.0696</v>
       </c>
       <c r="F137" s="16" t="n">
-        <v>0.1225</v>
+        <v>0.1045</v>
       </c>
       <c r="G137" s="17" t="n"/>
       <c r="H137" s="22" t="inlineStr">
@@ -11649,7 +11649,7 @@
         <v>750</v>
       </c>
       <c r="M137" s="16" t="n">
-        <v>0.09532224380412714</v>
+        <v>0.08103433365043677</v>
       </c>
       <c r="N137" s="14" t="inlineStr">
         <is>
@@ -11660,7 +11660,7 @@
         <v>641.29</v>
       </c>
       <c r="P137" s="25" t="n">
-        <v>-0.06344106436113513</v>
+        <v>-0.07565798956441525</v>
       </c>
       <c r="Q137" s="20" t="inlineStr">
         <is>
@@ -11701,13 +11701,13 @@
         </is>
       </c>
       <c r="D138" s="4" t="n">
-        <v>151.72</v>
+        <v>153.76</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>-0.0352</v>
+        <v>-0.0242</v>
       </c>
       <c r="F138" s="6" t="n">
-        <v>0.0471</v>
+        <v>0.0394</v>
       </c>
       <c r="G138" s="7" t="n">
         <v>46330</v>
@@ -11743,7 +11743,7 @@
         <v>185</v>
       </c>
       <c r="P138" s="6" t="n">
-        <v>0.2193514368573689</v>
+        <v>0.2031737773152966</v>
       </c>
       <c r="Q138" s="10" t="inlineStr">
         <is>
@@ -11782,13 +11782,13 @@
         </is>
       </c>
       <c r="D139" s="15" t="n">
-        <v>435.43</v>
+        <v>439.49</v>
       </c>
       <c r="E139" s="16" t="n">
-        <v>0.0387</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="F139" s="16" t="n">
-        <v>0.0489</v>
+        <v>0.0877</v>
       </c>
       <c r="G139" s="17" t="n">
         <v>46329</v>
@@ -11824,7 +11824,7 @@
         <v>453</v>
       </c>
       <c r="P139" s="16" t="n">
-        <v>0.04035091748386651</v>
+        <v>0.03074017611322212</v>
       </c>
       <c r="Q139" s="20" t="inlineStr">
         <is>
@@ -11865,13 +11865,13 @@
         </is>
       </c>
       <c r="D140" s="4" t="n">
-        <v>49.65</v>
+        <v>49.79</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>-0.0314</v>
+        <v>-0.0291</v>
       </c>
       <c r="F140" s="6" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.05889999999999999</v>
       </c>
       <c r="G140" s="7" t="n">
         <v>46309</v>
@@ -11944,13 +11944,13 @@
         </is>
       </c>
       <c r="D141" s="15" t="n">
-        <v>295.79</v>
+        <v>295.44</v>
       </c>
       <c r="E141" s="25" t="n">
-        <v>-0.0901</v>
+        <v>-0.1156</v>
       </c>
       <c r="F141" s="25" t="n">
-        <v>-0.06280000000000001</v>
+        <v>-0.062</v>
       </c>
       <c r="G141" s="17" t="n">
         <v>46282</v>
@@ -11979,7 +11979,7 @@
         <v>425</v>
       </c>
       <c r="M141" s="16" t="n">
-        <v>0.4368301835761857</v>
+        <v>0.4385323585161116</v>
       </c>
       <c r="N141" s="14" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>323</v>
       </c>
       <c r="P141" s="16" t="n">
-        <v>0.09199093951790113</v>
+        <v>0.0932845924722448</v>
       </c>
       <c r="Q141" s="20" t="inlineStr">
         <is>
@@ -12031,13 +12031,13 @@
         </is>
       </c>
       <c r="D142" s="4" t="n">
-        <v>216.14</v>
+        <v>220.7</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>-0.1077</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="F142" s="5" t="n">
-        <v>-0.0548</v>
+        <v>-0.0432</v>
       </c>
       <c r="G142" s="7" t="n"/>
       <c r="H142" s="12" t="inlineStr">
@@ -12056,7 +12056,7 @@
         <v>285</v>
       </c>
       <c r="M142" s="6" t="n">
-        <v>0.3185898029055243</v>
+        <v>0.2913457181694609</v>
       </c>
       <c r="N142" s="3" t="inlineStr"/>
       <c r="O142" s="9" t="n"/>
@@ -12104,13 +12104,13 @@
         </is>
       </c>
       <c r="D143" s="15" t="n">
-        <v>1632.59</v>
-      </c>
-      <c r="E143" s="25" t="n">
-        <v>-0.0139</v>
+        <v>1610.63</v>
+      </c>
+      <c r="E143" s="16" t="n">
+        <v>0.0005999999999999999</v>
       </c>
       <c r="F143" s="25" t="n">
-        <v>-0.1084</v>
+        <v>-0.0709</v>
       </c>
       <c r="G143" s="17" t="n">
         <v>46317</v>
@@ -12165,13 +12165,13 @@
         </is>
       </c>
       <c r="D144" s="4" t="n">
-        <v>54.74</v>
+        <v>54.35</v>
       </c>
       <c r="E144" s="6" t="n">
-        <v>0.0443</v>
+        <v>0.0599</v>
       </c>
       <c r="F144" s="6" t="n">
-        <v>0.0278</v>
+        <v>0.0414</v>
       </c>
       <c r="G144" s="7" t="n">
         <v>46332</v>
@@ -12226,13 +12226,13 @@
         </is>
       </c>
       <c r="D145" s="15" t="n">
-        <v>353.9</v>
+        <v>345.69</v>
       </c>
       <c r="E145" s="25" t="n">
-        <v>-0.0791</v>
+        <v>-0.0992</v>
       </c>
       <c r="F145" s="25" t="n">
-        <v>-0.0731</v>
+        <v>-0.1062</v>
       </c>
       <c r="G145" s="17" t="n">
         <v>46318</v>
@@ -12261,7 +12261,7 @@
         <v>400</v>
       </c>
       <c r="M145" s="16" t="n">
-        <v>0.1302627860977678</v>
+        <v>0.1571060776996731</v>
       </c>
       <c r="N145" s="14" t="inlineStr"/>
       <c r="O145" s="19" t="n"/>
@@ -12313,13 +12313,13 @@
         </is>
       </c>
       <c r="D146" s="4" t="n">
-        <v>319.01</v>
+        <v>316.86</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>-0.0843</v>
+        <v>-0.0731</v>
       </c>
       <c r="F146" s="5" t="n">
-        <v>-0.0859</v>
+        <v>-0.1042</v>
       </c>
       <c r="G146" s="7" t="n">
         <v>46315</v>
@@ -12348,7 +12348,7 @@
         <v>390</v>
       </c>
       <c r="M146" s="6" t="n">
-        <v>0.2225322090216608</v>
+        <v>0.2308274947926529</v>
       </c>
       <c r="N146" s="3" t="inlineStr"/>
       <c r="O146" s="9" t="n"/>
@@ -12400,13 +12400,13 @@
         </is>
       </c>
       <c r="D147" s="15" t="n">
-        <v>946.22</v>
-      </c>
-      <c r="E147" s="25" t="n">
-        <v>-0.0111</v>
+        <v>953.83</v>
+      </c>
+      <c r="E147" s="16" t="n">
+        <v>0.0125</v>
       </c>
       <c r="F147" s="25" t="n">
-        <v>-0.0824</v>
+        <v>-0.06</v>
       </c>
       <c r="G147" s="17" t="n">
         <v>46316</v>
@@ -12435,7 +12435,7 @@
         <v>1259</v>
       </c>
       <c r="M147" s="16" t="n">
-        <v>0.330557375663165</v>
+        <v>0.3199417086902278</v>
       </c>
       <c r="N147" s="14" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>1350</v>
       </c>
       <c r="P147" s="16" t="n">
-        <v>0.4267295132210268</v>
+        <v>0.4153465502238344</v>
       </c>
       <c r="Q147" s="20" t="inlineStr">
         <is>
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="D148" s="4" t="n">
-        <v>1277.79</v>
+        <v>1282.49</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>-0.0263</v>
+        <v>-0.0298</v>
       </c>
       <c r="F148" s="5" t="n">
-        <v>-0.06559999999999999</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="G148" s="7" t="n">
         <v>46325</v>
@@ -12566,13 +12566,13 @@
         </is>
       </c>
       <c r="D149" s="15" t="n">
-        <v>206.48</v>
+        <v>209.4</v>
       </c>
       <c r="E149" s="25" t="n">
-        <v>-0.0436</v>
+        <v>-0.025</v>
       </c>
       <c r="F149" s="25" t="n">
-        <v>-0.1616</v>
+        <v>-0.1388</v>
       </c>
       <c r="G149" s="17" t="n">
         <v>46317</v>
@@ -12627,13 +12627,13 @@
         </is>
       </c>
       <c r="D150" s="4" t="n">
-        <v>457.49</v>
+        <v>456.6</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>-0.0267</v>
+        <v>-0.0218</v>
       </c>
       <c r="F150" s="5" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-0.0607</v>
       </c>
       <c r="G150" s="7" t="n">
         <v>46322</v>
@@ -12694,13 +12694,13 @@
         </is>
       </c>
       <c r="D151" s="15" t="n">
-        <v>267.52</v>
+        <v>268.91</v>
       </c>
       <c r="E151" s="25" t="n">
-        <v>-0.05230000000000001</v>
+        <v>-0.053</v>
       </c>
       <c r="F151" s="25" t="n">
-        <v>-0.0339</v>
+        <v>-0.0499</v>
       </c>
       <c r="G151" s="17" t="n">
         <v>46318</v>
@@ -12732,7 +12732,7 @@
         <v>272</v>
       </c>
       <c r="P151" s="16" t="n">
-        <v>0.01674641148325366</v>
+        <v>0.01149083336432254</v>
       </c>
       <c r="Q151" s="20" t="inlineStr">
         <is>
@@ -12785,13 +12785,13 @@
         </is>
       </c>
       <c r="D152" s="4" t="n">
-        <v>246.93</v>
+        <v>241.56</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>-0.0742</v>
+        <v>-0.0809</v>
       </c>
       <c r="F152" s="5" t="n">
-        <v>-0.176</v>
+        <v>-0.1954</v>
       </c>
       <c r="G152" s="7" t="n">
         <v>46324</v>
@@ -12856,13 +12856,13 @@
         </is>
       </c>
       <c r="D153" s="15" t="n">
-        <v>363.64</v>
+        <v>365.07</v>
       </c>
       <c r="E153" s="25" t="n">
-        <v>-0.0974</v>
+        <v>-0.08529999999999999</v>
       </c>
       <c r="F153" s="25" t="n">
-        <v>-0.324</v>
+        <v>-0.3254</v>
       </c>
       <c r="G153" s="17" t="n">
         <v>46323</v>
@@ -12917,13 +12917,13 @@
         </is>
       </c>
       <c r="D154" s="4" t="n">
-        <v>535.4</v>
+        <v>521.1799999999999</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>-0.05</v>
+        <v>-0.0762</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>-0.0584</v>
+        <v>-0.1054</v>
       </c>
       <c r="G154" s="7" t="n">
         <v>46315</v>
@@ -12984,13 +12984,13 @@
         </is>
       </c>
       <c r="D155" s="15" t="n">
-        <v>175.36</v>
+        <v>175.48</v>
       </c>
       <c r="E155" s="25" t="n">
-        <v>-0.1507</v>
+        <v>-0.1291</v>
       </c>
       <c r="F155" s="25" t="n">
-        <v>-0.2399</v>
+        <v>-0.2469</v>
       </c>
       <c r="G155" s="17" t="n">
         <v>46330</v>
@@ -13019,7 +13019,7 @@
         <v>575</v>
       </c>
       <c r="M155" s="16" t="n">
-        <v>2.278968978102189</v>
+        <v>2.27672669250057</v>
       </c>
       <c r="N155" s="14" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>237</v>
       </c>
       <c r="P155" s="16" t="n">
-        <v>0.3515054744525546</v>
+        <v>0.3505812628219741</v>
       </c>
       <c r="Q155" s="20" t="inlineStr">
         <is>
@@ -13079,13 +13079,13 @@
         </is>
       </c>
       <c r="D156" s="4" t="n">
-        <v>115.01</v>
+        <v>113.7</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>-0.0761</v>
+        <v>-0.0977</v>
       </c>
       <c r="F156" s="6" t="n">
-        <v>0.0393</v>
+        <v>0.0013</v>
       </c>
       <c r="G156" s="7" t="n">
         <v>46288</v>
@@ -13114,7 +13114,7 @@
         <v>250</v>
       </c>
       <c r="M156" s="6" t="n">
-        <v>1.173724023997913</v>
+        <v>1.198768689533861</v>
       </c>
       <c r="N156" s="3" t="inlineStr"/>
       <c r="O156" s="9" t="n"/>
@@ -13158,13 +13158,13 @@
         </is>
       </c>
       <c r="D157" s="15" t="n">
-        <v>114.73</v>
+        <v>112.82</v>
       </c>
       <c r="E157" s="25" t="n">
-        <v>-0.1244</v>
+        <v>-0.1317</v>
       </c>
       <c r="F157" s="25" t="n">
-        <v>-0.1225</v>
+        <v>-0.1468</v>
       </c>
       <c r="G157" s="17" t="n">
         <v>46315</v>
@@ -13193,7 +13193,7 @@
         <v>95</v>
       </c>
       <c r="M157" s="25" t="n">
-        <v>-0.1719689706266888</v>
+        <v>-0.1579507179578089</v>
       </c>
       <c r="N157" s="14" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>139</v>
       </c>
       <c r="P157" s="16" t="n">
-        <v>0.2115401377146343</v>
+        <v>0.2320510547775218</v>
       </c>
       <c r="Q157" s="20" t="inlineStr">
         <is>
@@ -13249,13 +13249,13 @@
         </is>
       </c>
       <c r="D158" s="4" t="n">
-        <v>958.17</v>
+        <v>955.9</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>-0.0435</v>
+        <v>-0.0575</v>
       </c>
       <c r="F158" s="5" t="n">
-        <v>-0.0277</v>
+        <v>-0.032</v>
       </c>
       <c r="G158" s="7" t="n">
         <v>46331</v>
@@ -13284,7 +13284,7 @@
         <v>125</v>
       </c>
       <c r="M158" s="5" t="n">
-        <v>-0.8695429829779684</v>
+        <v>-0.8692331833873836</v>
       </c>
       <c r="N158" s="3" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>1064</v>
       </c>
       <c r="P158" s="6" t="n">
-        <v>0.1104501288915329</v>
+        <v>0.1130871430065907</v>
       </c>
       <c r="Q158" s="10" t="inlineStr">
         <is>
@@ -13340,13 +13340,13 @@
         </is>
       </c>
       <c r="D159" s="15" t="n">
-        <v>492.56</v>
-      </c>
-      <c r="E159" s="25" t="n">
-        <v>-0.0258</v>
+        <v>497.79</v>
+      </c>
+      <c r="E159" s="16" t="n">
+        <v>0.0038</v>
       </c>
       <c r="F159" s="25" t="n">
-        <v>-0.1726</v>
+        <v>-0.1635</v>
       </c>
       <c r="G159" s="17" t="n">
         <v>46325</v>
@@ -13421,13 +13421,13 @@
         </is>
       </c>
       <c r="D160" s="4" t="n">
-        <v>424.89</v>
+        <v>424.05</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>-0.0279</v>
+        <v>-0.0131</v>
       </c>
       <c r="F160" s="5" t="n">
-        <v>-0.0776</v>
+        <v>-0.0825</v>
       </c>
       <c r="G160" s="7" t="n">
         <v>46331</v>
@@ -13482,13 +13482,13 @@
         </is>
       </c>
       <c r="D161" s="15" t="n">
-        <v>32.35</v>
+        <v>32.78</v>
       </c>
       <c r="E161" s="25" t="n">
-        <v>-0.1235</v>
+        <v>-0.1202</v>
       </c>
       <c r="F161" s="25" t="n">
-        <v>-0.1798</v>
+        <v>-0.1499</v>
       </c>
       <c r="G161" s="17" t="n">
         <v>46323</v>
@@ -13557,13 +13557,13 @@
         </is>
       </c>
       <c r="D162" s="4" t="n">
-        <v>194.34</v>
+        <v>189.38</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>-0.0742</v>
+        <v>-0.09480000000000001</v>
       </c>
       <c r="F162" s="5" t="n">
-        <v>-0.0709</v>
+        <v>-0.11</v>
       </c>
       <c r="G162" s="7" t="n">
         <v>46315</v>
@@ -13636,13 +13636,13 @@
         </is>
       </c>
       <c r="D163" s="15" t="n">
-        <v>43.96</v>
+        <v>44.21</v>
       </c>
       <c r="E163" s="16" t="n">
-        <v>0.0509</v>
+        <v>0.1044</v>
       </c>
       <c r="F163" s="16" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.1011</v>
       </c>
       <c r="G163" s="17" t="n"/>
       <c r="H163" s="22" t="inlineStr">
@@ -13687,13 +13687,13 @@
         </is>
       </c>
       <c r="D164" s="4" t="n">
-        <v>433.32</v>
+        <v>436.31</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>-0.0444</v>
+        <v>-0.0368</v>
       </c>
       <c r="F164" s="5" t="n">
-        <v>-0.09669999999999999</v>
+        <v>-0.0929</v>
       </c>
       <c r="G164" s="7" t="n">
         <v>46324</v>
@@ -13725,7 +13725,7 @@
         <v>560</v>
       </c>
       <c r="P164" s="6" t="n">
-        <v>0.292347456844826</v>
+        <v>0.283491095780523</v>
       </c>
       <c r="Q164" s="10" t="inlineStr">
         <is>
@@ -13778,13 +13778,13 @@
         </is>
       </c>
       <c r="D165" s="15" t="n">
-        <v>269.63</v>
+        <v>270.99</v>
       </c>
       <c r="E165" s="25" t="n">
-        <v>-0.1247</v>
+        <v>-0.1254</v>
       </c>
       <c r="F165" s="25" t="n">
-        <v>-0.114</v>
+        <v>-0.1182</v>
       </c>
       <c r="G165" s="17" t="n">
         <v>46317</v>
@@ -13816,7 +13816,7 @@
         <v>294</v>
       </c>
       <c r="P165" s="16" t="n">
-        <v>0.0903831176056077</v>
+        <v>0.08491088232038078</v>
       </c>
       <c r="Q165" s="20" t="inlineStr">
         <is>
@@ -13861,13 +13861,13 @@
         </is>
       </c>
       <c r="D166" s="4" t="n">
-        <v>250.86</v>
+        <v>254.13</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>-0.0423</v>
+        <v>-0.0033</v>
       </c>
       <c r="F166" s="5" t="n">
-        <v>-0.1749</v>
+        <v>-0.1248</v>
       </c>
       <c r="G166" s="7" t="n">
         <v>46323</v>
@@ -13899,7 +13899,7 @@
         <v>425</v>
       </c>
       <c r="P166" s="6" t="n">
-        <v>0.694172048154349</v>
+        <v>0.6723724078227679</v>
       </c>
       <c r="Q166" s="10" t="inlineStr">
         <is>
@@ -13940,13 +13940,13 @@
         </is>
       </c>
       <c r="D167" s="15" t="n">
-        <v>207.04</v>
+        <v>207.82</v>
       </c>
       <c r="E167" s="25" t="n">
-        <v>-0.076</v>
+        <v>-0.0823</v>
       </c>
       <c r="F167" s="25" t="n">
-        <v>-0.1274</v>
+        <v>-0.1295</v>
       </c>
       <c r="G167" s="17" t="n">
         <v>46321</v>
@@ -13975,7 +13975,7 @@
         <v>268</v>
       </c>
       <c r="M167" s="16" t="n">
-        <v>0.2944358578052551</v>
+        <v>0.2895775190068329</v>
       </c>
       <c r="N167" s="14" t="inlineStr"/>
       <c r="O167" s="19" t="n"/>
@@ -14023,13 +14023,13 @@
         </is>
       </c>
       <c r="D168" s="4" t="n">
-        <v>317.69</v>
+        <v>321</v>
       </c>
       <c r="E168" s="6" t="n">
-        <v>0.0184</v>
+        <v>0.0328</v>
       </c>
       <c r="F168" s="5" t="n">
-        <v>-0.1172</v>
+        <v>-0.1133</v>
       </c>
       <c r="G168" s="7" t="n">
         <v>46330</v>
@@ -14098,13 +14098,13 @@
         </is>
       </c>
       <c r="D169" s="15" t="n">
-        <v>325.16</v>
+        <v>322.4</v>
       </c>
       <c r="E169" s="25" t="n">
-        <v>-0.0527</v>
+        <v>-0.0323</v>
       </c>
       <c r="F169" s="25" t="n">
-        <v>-0.2107</v>
+        <v>-0.2305</v>
       </c>
       <c r="G169" s="17" t="n"/>
       <c r="H169" s="22" t="inlineStr">
@@ -14167,13 +14167,13 @@
         </is>
       </c>
       <c r="D170" s="4" t="n">
-        <v>107.24</v>
+        <v>106.94</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>-0.0545</v>
+        <v>-0.0634</v>
       </c>
       <c r="F170" s="5" t="n">
-        <v>-0.0824</v>
+        <v>-0.107</v>
       </c>
       <c r="G170" s="7" t="n">
         <v>46322</v>
@@ -14246,13 +14246,13 @@
         </is>
       </c>
       <c r="D171" s="15" t="n">
-        <v>108.67</v>
+        <v>104.6</v>
       </c>
       <c r="E171" s="25" t="n">
-        <v>-0.1294</v>
-      </c>
-      <c r="F171" s="25" t="n">
-        <v>-0.0299</v>
+        <v>-0.0282</v>
+      </c>
+      <c r="F171" s="16" t="n">
+        <v>0.0444</v>
       </c>
       <c r="G171" s="17" t="n">
         <v>46331</v>
@@ -14307,13 +14307,13 @@
         </is>
       </c>
       <c r="D172" s="4" t="n">
-        <v>338.98</v>
+        <v>343.12</v>
       </c>
       <c r="E172" s="6" t="n">
-        <v>0.0958</v>
+        <v>0.1056</v>
       </c>
       <c r="F172" s="6" t="n">
-        <v>0.0538</v>
+        <v>0.0303</v>
       </c>
       <c r="G172" s="7" t="n">
         <v>46324</v>
@@ -14342,7 +14342,7 @@
         <v>310</v>
       </c>
       <c r="M172" s="5" t="n">
-        <v>-0.08549176942592489</v>
+        <v>-0.09652599673583587</v>
       </c>
       <c r="N172" s="3" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>365</v>
       </c>
       <c r="P172" s="6" t="n">
-        <v>0.07675969083721748</v>
+        <v>0.0637677780368384</v>
       </c>
       <c r="Q172" s="10" t="inlineStr">
         <is>
@@ -14410,13 +14410,13 @@
         </is>
       </c>
       <c r="D173" s="15" t="n">
-        <v>113.15</v>
+        <v>113.43</v>
       </c>
       <c r="E173" s="25" t="n">
-        <v>-0.1095</v>
+        <v>-0.0815</v>
       </c>
       <c r="F173" s="25" t="n">
-        <v>-0.2004</v>
+        <v>-0.1541</v>
       </c>
       <c r="G173" s="17" t="n">
         <v>46329</v>
@@ -14471,13 +14471,13 @@
         </is>
       </c>
       <c r="D174" s="4" t="n">
-        <v>186.11</v>
-      </c>
-      <c r="E174" s="6" t="n">
-        <v>0.004500000000000001</v>
+        <v>182.99</v>
+      </c>
+      <c r="E174" s="5" t="n">
+        <v>-0.019</v>
       </c>
       <c r="F174" s="6" t="n">
-        <v>0.3414</v>
+        <v>0.2449</v>
       </c>
       <c r="G174" s="7" t="n">
         <v>46296</v>
@@ -14532,13 +14532,13 @@
         </is>
       </c>
       <c r="D175" s="15" t="n">
-        <v>249.52</v>
+        <v>241.51</v>
       </c>
       <c r="E175" s="25" t="n">
-        <v>-0.09359999999999999</v>
+        <v>-0.1258</v>
       </c>
       <c r="F175" s="16" t="n">
-        <v>0.176</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="G175" s="17" t="n"/>
       <c r="H175" s="22" t="inlineStr">
@@ -14583,13 +14583,13 @@
         </is>
       </c>
       <c r="D176" s="4" t="n">
-        <v>383</v>
+        <v>384.2</v>
       </c>
       <c r="E176" s="6" t="n">
-        <v>0.0266</v>
+        <v>0.0351</v>
       </c>
       <c r="F176" s="6" t="n">
-        <v>0.0074</v>
+        <v>0.0332</v>
       </c>
       <c r="G176" s="7" t="n"/>
       <c r="H176" s="12" t="inlineStr">
@@ -14608,7 +14608,7 @@
         <v>515</v>
       </c>
       <c r="M176" s="6" t="n">
-        <v>0.3446475195822454</v>
+        <v>0.3404476834981781</v>
       </c>
       <c r="N176" s="3" t="inlineStr">
         <is>
@@ -14619,7 +14619,7 @@
         <v>474</v>
       </c>
       <c r="P176" s="6" t="n">
-        <v>0.237597911227154</v>
+        <v>0.2337324310255076</v>
       </c>
       <c r="Q176" s="10" t="inlineStr">
         <is>
@@ -14668,13 +14668,13 @@
         </is>
       </c>
       <c r="D177" s="15" t="n">
-        <v>218.85</v>
+        <v>216.96</v>
       </c>
       <c r="E177" s="25" t="n">
-        <v>-0.1378</v>
+        <v>-0.1472</v>
       </c>
       <c r="F177" s="16" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0344</v>
       </c>
       <c r="G177" s="17" t="n"/>
       <c r="H177" s="22" t="inlineStr">
@@ -14719,13 +14719,13 @@
         </is>
       </c>
       <c r="D178" s="4" t="n">
-        <v>262.74</v>
+        <v>264.91</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>-0.0808</v>
+        <v>-0.0355</v>
       </c>
       <c r="F178" s="5" t="n">
-        <v>-0.1663</v>
+        <v>-0.1286</v>
       </c>
       <c r="G178" s="7" t="n">
         <v>46329</v>
@@ -14780,13 +14780,13 @@
         </is>
       </c>
       <c r="D179" s="15" t="n">
-        <v>340.74</v>
+        <v>361.54</v>
       </c>
       <c r="E179" s="16" t="n">
-        <v>0.1957</v>
+        <v>0.3027</v>
       </c>
       <c r="F179" s="16" t="n">
-        <v>0.0421</v>
+        <v>0.2399</v>
       </c>
       <c r="G179" s="17" t="n">
         <v>46329</v>
@@ -14841,13 +14841,13 @@
         </is>
       </c>
       <c r="D180" s="4" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="E180" s="5" t="n">
-        <v>-0.0447</v>
+        <v>35.68</v>
+      </c>
+      <c r="E180" s="6" t="n">
+        <v>0.0014</v>
       </c>
       <c r="F180" s="5" t="n">
-        <v>-0.291</v>
+        <v>-0.2249</v>
       </c>
       <c r="G180" s="7" t="n">
         <v>46324</v>
@@ -14902,13 +14902,13 @@
         </is>
       </c>
       <c r="D181" s="15" t="n">
-        <v>464.24</v>
+        <v>463.94</v>
       </c>
       <c r="E181" s="25" t="n">
-        <v>-0.057</v>
+        <v>-0.0418</v>
       </c>
       <c r="F181" s="25" t="n">
-        <v>-0.1751</v>
+        <v>-0.1348</v>
       </c>
       <c r="G181" s="17" t="n">
         <v>46338</v>
@@ -14937,7 +14937,7 @@
         <v>740</v>
       </c>
       <c r="M181" s="16" t="n">
-        <v>0.5940031018438738</v>
+        <v>0.595033840582834</v>
       </c>
       <c r="N181" s="14" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>700</v>
       </c>
       <c r="P181" s="16" t="n">
-        <v>0.5078407720144752</v>
+        <v>0.508815795145924</v>
       </c>
       <c r="Q181" s="20" t="inlineStr">
         <is>
@@ -14989,13 +14989,13 @@
         </is>
       </c>
       <c r="D182" s="4" t="n">
-        <v>71.09</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="E182" s="6" t="n">
-        <v>0.2045</v>
-      </c>
-      <c r="F182" s="5" t="n">
-        <v>-0.0492</v>
+        <v>0.2454</v>
+      </c>
+      <c r="F182" s="6" t="n">
+        <v>0.0053</v>
       </c>
       <c r="G182" s="7" t="n">
         <v>46331</v>
@@ -15054,13 +15054,13 @@
         </is>
       </c>
       <c r="D183" s="15" t="n">
-        <v>615.52</v>
+        <v>617.02</v>
       </c>
       <c r="E183" s="16" t="n">
-        <v>0.3006</v>
+        <v>0.3509</v>
       </c>
       <c r="F183" s="16" t="n">
-        <v>0.1405</v>
+        <v>0.1821</v>
       </c>
       <c r="G183" s="17" t="n">
         <v>46329</v>
@@ -15089,7 +15089,7 @@
         <v>615</v>
       </c>
       <c r="M183" s="25" t="n">
-        <v>-0.0008448141408889749</v>
+        <v>-0.003273799876827302</v>
       </c>
       <c r="N183" s="14" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>579</v>
       </c>
       <c r="P183" s="25" t="n">
-        <v>-0.0593319469716662</v>
+        <v>-0.06161874817672034</v>
       </c>
       <c r="Q183" s="20" t="inlineStr">
         <is>
@@ -15141,13 +15141,13 @@
         </is>
       </c>
       <c r="D184" s="4" t="n">
-        <v>52.19</v>
+        <v>52.89</v>
       </c>
       <c r="E184" s="6" t="n">
-        <v>0.0384</v>
+        <v>0.1042</v>
       </c>
       <c r="F184" s="5" t="n">
-        <v>-0.2011</v>
+        <v>-0.1858</v>
       </c>
       <c r="G184" s="7" t="n">
         <v>46321</v>
@@ -15202,13 +15202,13 @@
         </is>
       </c>
       <c r="D185" s="15" t="n">
-        <v>205.42</v>
+        <v>205.51</v>
       </c>
       <c r="E185" s="16" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.0922</v>
       </c>
       <c r="F185" s="16" t="n">
-        <v>0.1631</v>
+        <v>0.1811</v>
       </c>
       <c r="G185" s="17" t="n">
         <v>46329</v>
@@ -15237,7 +15237,7 @@
         <v>200</v>
       </c>
       <c r="M185" s="25" t="n">
-        <v>-0.02638496738389635</v>
+        <v>-0.02681134737968951</v>
       </c>
       <c r="N185" s="14" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>200</v>
       </c>
       <c r="P185" s="25" t="n">
-        <v>-0.02638496738389635</v>
+        <v>-0.02681134737968951</v>
       </c>
       <c r="Q185" s="20" t="inlineStr">
         <is>
@@ -15293,13 +15293,13 @@
         </is>
       </c>
       <c r="D186" s="4" t="n">
-        <v>80.72</v>
+        <v>81.84</v>
       </c>
       <c r="E186" s="6" t="n">
-        <v>0.0282</v>
+        <v>0.05230000000000001</v>
       </c>
       <c r="F186" s="6" t="n">
-        <v>0.0255</v>
+        <v>0.0721</v>
       </c>
       <c r="G186" s="7" t="n">
         <v>46323</v>
@@ -15331,7 +15331,7 @@
         <v>180</v>
       </c>
       <c r="P186" s="6" t="n">
-        <v>1.229930624380575</v>
+        <v>1.19941348973607</v>
       </c>
       <c r="Q186" s="10" t="inlineStr">
         <is>
@@ -15384,13 +15384,13 @@
         </is>
       </c>
       <c r="D187" s="15" t="n">
-        <v>28.19</v>
+        <v>28.41</v>
       </c>
       <c r="E187" s="16" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="F187" s="25" t="n">
-        <v>-0.05690000000000001</v>
+        <v>0.0565</v>
+      </c>
+      <c r="F187" s="16" t="n">
+        <v>0.0449</v>
       </c>
       <c r="G187" s="17" t="n">
         <v>46303</v>
@@ -15445,13 +15445,13 @@
         </is>
       </c>
       <c r="D188" s="4" t="n">
-        <v>322.9</v>
+        <v>329.87</v>
       </c>
       <c r="E188" s="6" t="n">
-        <v>0.3271</v>
+        <v>0.3815</v>
       </c>
       <c r="F188" s="6" t="n">
-        <v>0.1408</v>
+        <v>0.2687</v>
       </c>
       <c r="G188" s="7" t="n">
         <v>46330</v>
@@ -15506,13 +15506,13 @@
         </is>
       </c>
       <c r="D189" s="15" t="n">
-        <v>1711.32</v>
+        <v>1726.94</v>
       </c>
       <c r="E189" s="25" t="n">
-        <v>-0.0297</v>
+        <v>-0.0076</v>
       </c>
       <c r="F189" s="25" t="n">
-        <v>-0.0508</v>
+        <v>-0.0172</v>
       </c>
       <c r="G189" s="17" t="n">
         <v>46309</v>
@@ -15585,13 +15585,13 @@
         </is>
       </c>
       <c r="D190" s="4" t="n">
-        <v>43.73</v>
+        <v>44.53</v>
       </c>
       <c r="E190" s="6" t="n">
-        <v>0.1978</v>
+        <v>0.2287</v>
       </c>
       <c r="F190" s="6" t="n">
-        <v>0.1082</v>
+        <v>0.2086</v>
       </c>
       <c r="G190" s="7" t="n">
         <v>46324</v>
@@ -15646,13 +15646,13 @@
         </is>
       </c>
       <c r="D191" s="15" t="n">
-        <v>362.66</v>
-      </c>
-      <c r="E191" s="25" t="n">
-        <v>-0.0157</v>
+        <v>362.01</v>
+      </c>
+      <c r="E191" s="16" t="n">
+        <v>0.009000000000000001</v>
       </c>
       <c r="F191" s="25" t="n">
-        <v>-0.076</v>
+        <v>-0.0521</v>
       </c>
       <c r="G191" s="17" t="n"/>
       <c r="H191" s="22" t="inlineStr">
@@ -15671,7 +15671,7 @@
         <v>545</v>
       </c>
       <c r="M191" s="16" t="n">
-        <v>0.5027849776650305</v>
+        <v>0.5054832739427088</v>
       </c>
       <c r="N191" s="14" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>582</v>
       </c>
       <c r="P191" s="16" t="n">
-        <v>0.604808911928528</v>
+        <v>0.6076903952929478</v>
       </c>
       <c r="Q191" s="20" t="inlineStr">
         <is>
@@ -15735,13 +15735,13 @@
         </is>
       </c>
       <c r="D192" s="4" t="n">
-        <v>149.63</v>
+        <v>147.29</v>
       </c>
       <c r="E192" s="6" t="n">
-        <v>0.0192</v>
+        <v>0.0348</v>
       </c>
       <c r="F192" s="5" t="n">
-        <v>-0.0358</v>
+        <v>-0.0034</v>
       </c>
       <c r="G192" s="7" t="n">
         <v>46335</v>
@@ -15796,13 +15796,13 @@
         </is>
       </c>
       <c r="D193" s="15" t="n">
-        <v>294.9</v>
+        <v>298</v>
       </c>
       <c r="E193" s="25" t="n">
-        <v>-0.0756</v>
+        <v>-0.0567</v>
       </c>
       <c r="F193" s="25" t="n">
-        <v>-0.1076</v>
+        <v>-0.0866</v>
       </c>
       <c r="G193" s="17" t="n">
         <v>46321</v>
@@ -15831,7 +15831,7 @@
         <v>425</v>
       </c>
       <c r="M193" s="16" t="n">
-        <v>0.4411664971176671</v>
+        <v>0.4261744966442953</v>
       </c>
       <c r="N193" s="14" t="inlineStr"/>
       <c r="O193" s="19" t="n"/>
@@ -15875,13 +15875,13 @@
         </is>
       </c>
       <c r="D194" s="4" t="n">
-        <v>134.25</v>
+        <v>131.34</v>
       </c>
       <c r="E194" s="6" t="n">
-        <v>0.0283</v>
+        <v>0.0064</v>
       </c>
       <c r="F194" s="6" t="n">
-        <v>0.0654</v>
+        <v>0.0059</v>
       </c>
       <c r="G194" s="7" t="n">
         <v>46322</v>
@@ -15936,13 +15936,13 @@
         </is>
       </c>
       <c r="D195" s="15" t="n">
-        <v>365.96</v>
+        <v>368.52</v>
       </c>
       <c r="E195" s="25" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.0092</v>
       </c>
       <c r="F195" s="25" t="n">
-        <v>-0.102</v>
+        <v>-0.0574</v>
       </c>
       <c r="G195" s="17" t="n"/>
       <c r="H195" s="22" t="inlineStr">
@@ -15987,13 +15987,13 @@
         </is>
       </c>
       <c r="D196" s="4" t="n">
-        <v>11.56</v>
+        <v>11.49</v>
       </c>
       <c r="E196" s="6" t="n">
-        <v>0.0462</v>
+        <v>0</v>
       </c>
       <c r="F196" s="5" t="n">
-        <v>-0.1778</v>
+        <v>-0.1917</v>
       </c>
       <c r="G196" s="7" t="n">
         <v>46337</v>
@@ -16048,13 +16048,13 @@
         </is>
       </c>
       <c r="D197" s="15" t="n">
-        <v>344.4</v>
+        <v>350.48</v>
       </c>
       <c r="E197" s="16" t="n">
-        <v>0.1614</v>
+        <v>0.1898</v>
       </c>
       <c r="F197" s="16" t="n">
-        <v>0.0288</v>
+        <v>0.1481</v>
       </c>
       <c r="G197" s="17" t="n">
         <v>46321</v>
@@ -16109,13 +16109,13 @@
         </is>
       </c>
       <c r="D198" s="4" t="n">
-        <v>321.52</v>
+        <v>309.48</v>
       </c>
       <c r="E198" s="6" t="n">
-        <v>0.1105</v>
+        <v>0.1234</v>
       </c>
       <c r="F198" s="6" t="n">
-        <v>0.0265</v>
+        <v>0.0959</v>
       </c>
       <c r="G198" s="7" t="n">
         <v>46330</v>
@@ -16170,13 +16170,13 @@
         </is>
       </c>
       <c r="D199" s="15" t="n">
-        <v>60.62</v>
+        <v>62.03</v>
       </c>
       <c r="E199" s="16" t="n">
-        <v>0.1149</v>
+        <v>0.2092</v>
       </c>
       <c r="F199" s="16" t="n">
-        <v>0.112</v>
+        <v>0.2235</v>
       </c>
       <c r="G199" s="17" t="n">
         <v>46330</v>
@@ -16231,13 +16231,13 @@
         </is>
       </c>
       <c r="D200" s="4" t="n">
-        <v>18.36</v>
+        <v>18.43</v>
       </c>
       <c r="E200" s="6" t="n">
-        <v>0.0309</v>
+        <v>0.0672</v>
       </c>
       <c r="F200" s="5" t="n">
-        <v>-0.2337</v>
+        <v>-0.1899</v>
       </c>
       <c r="G200" s="7" t="n">
         <v>46318</v>
@@ -16292,13 +16292,13 @@
         </is>
       </c>
       <c r="D201" s="15" t="n">
-        <v>187.27</v>
+        <v>190.31</v>
       </c>
       <c r="E201" s="25" t="n">
-        <v>-0.1878</v>
+        <v>-0.1451</v>
       </c>
       <c r="F201" s="25" t="n">
-        <v>-0.2082</v>
+        <v>-0.1072</v>
       </c>
       <c r="G201" s="17" t="n"/>
       <c r="H201" s="22" t="inlineStr">
@@ -16343,13 +16343,13 @@
         </is>
       </c>
       <c r="D202" s="4" t="n">
-        <v>236.42</v>
+        <v>231.2</v>
       </c>
       <c r="E202" s="6" t="n">
-        <v>0.1303</v>
+        <v>0.1059</v>
       </c>
       <c r="F202" s="6" t="n">
-        <v>0.5065</v>
+        <v>0.4127</v>
       </c>
       <c r="G202" s="7" t="n"/>
       <c r="H202" s="12" t="inlineStr">
@@ -16368,7 +16368,7 @@
         <v>200</v>
       </c>
       <c r="M202" s="5" t="n">
-        <v>-0.1540478808899416</v>
+        <v>-0.1349480968858131</v>
       </c>
       <c r="N202" s="3" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>250</v>
       </c>
       <c r="P202" s="6" t="n">
-        <v>0.05744014888757302</v>
+        <v>0.08131487889273362</v>
       </c>
       <c r="Q202" s="10" t="inlineStr">
         <is>
@@ -16424,13 +16424,13 @@
         </is>
       </c>
       <c r="D203" s="15" t="n">
-        <v>249.35</v>
+        <v>247.1</v>
       </c>
       <c r="E203" s="16" t="n">
-        <v>0.299</v>
+        <v>0.2959</v>
       </c>
       <c r="F203" s="16" t="n">
-        <v>0.3594</v>
+        <v>0.3482</v>
       </c>
       <c r="G203" s="17" t="n"/>
       <c r="H203" s="22" t="inlineStr">
@@ -16449,7 +16449,7 @@
         <v>181.25</v>
       </c>
       <c r="M203" s="25" t="n">
-        <v>-0.2731100862241829</v>
+        <v>-0.2664912990692027</v>
       </c>
       <c r="N203" s="14" t="inlineStr">
         <is>
@@ -16460,7 +16460,7 @@
         <v>177.5</v>
       </c>
       <c r="P203" s="25" t="n">
-        <v>-0.2881491878885101</v>
+        <v>-0.2816673411574261</v>
       </c>
       <c r="Q203" s="20" t="inlineStr">
         <is>
@@ -16501,13 +16501,13 @@
         </is>
       </c>
       <c r="D204" s="4" t="n">
-        <v>85.43000000000001</v>
-      </c>
-      <c r="E204" s="5" t="n">
-        <v>-0.0275</v>
+        <v>86.34</v>
+      </c>
+      <c r="E204" s="6" t="n">
+        <v>0.001</v>
       </c>
       <c r="F204" s="6" t="n">
-        <v>0.0534</v>
+        <v>0.2012</v>
       </c>
       <c r="G204" s="7" t="n">
         <v>46335</v>
@@ -16562,13 +16562,13 @@
         </is>
       </c>
       <c r="D205" s="15" t="n">
-        <v>111.46</v>
-      </c>
-      <c r="E205" s="16" t="n">
-        <v>0.0038</v>
+        <v>107.16</v>
+      </c>
+      <c r="E205" s="25" t="n">
+        <v>-0.0278</v>
       </c>
       <c r="F205" s="25" t="n">
-        <v>-0.0115</v>
+        <v>-0.0614</v>
       </c>
       <c r="G205" s="17" t="n">
         <v>46337</v>
@@ -16597,7 +16597,7 @@
         <v>130</v>
       </c>
       <c r="M205" s="16" t="n">
-        <v>0.1663376996231833</v>
+        <v>0.2131392310563643</v>
       </c>
       <c r="N205" s="14" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>150</v>
       </c>
       <c r="P205" s="16" t="n">
-        <v>0.3457742687959807</v>
+        <v>0.3997760358342666</v>
       </c>
       <c r="Q205" s="20" t="inlineStr">
         <is>
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="D206" s="4" t="n">
-        <v>245.05</v>
+        <v>246.43</v>
       </c>
       <c r="E206" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="F206" s="6" t="n">
-        <v>0.0027</v>
+        <v>0.0915</v>
+      </c>
+      <c r="F206" s="5" t="n">
+        <v>-0.0017</v>
       </c>
       <c r="G206" s="7" t="n">
         <v>46331</v>
@@ -16726,13 +16726,13 @@
         </is>
       </c>
       <c r="D207" s="15" t="n">
-        <v>575.3099999999999</v>
+        <v>563.14</v>
       </c>
       <c r="E207" s="16" t="n">
-        <v>0.3014</v>
+        <v>0.3</v>
       </c>
       <c r="F207" s="16" t="n">
-        <v>0.3095</v>
+        <v>0.2872</v>
       </c>
       <c r="G207" s="17" t="n"/>
       <c r="H207" s="22" t="inlineStr">
@@ -16777,13 +16777,13 @@
         </is>
       </c>
       <c r="D208" s="4" t="n">
-        <v>68.56999999999999</v>
+        <v>66.39</v>
       </c>
       <c r="E208" s="6" t="n">
-        <v>0.106</v>
+        <v>0.0611</v>
       </c>
       <c r="F208" s="6" t="n">
-        <v>0.4577000000000001</v>
+        <v>0.3161</v>
       </c>
       <c r="G208" s="7" t="n"/>
       <c r="H208" s="12" t="inlineStr">
@@ -16828,13 +16828,13 @@
         </is>
       </c>
       <c r="D209" s="15" t="n">
-        <v>56.4</v>
+        <v>55.95</v>
       </c>
       <c r="E209" s="16" t="n">
-        <v>0.144</v>
+        <v>0.1407</v>
       </c>
       <c r="F209" s="16" t="n">
-        <v>0.3875</v>
+        <v>0.3443</v>
       </c>
       <c r="G209" s="17" t="n">
         <v>46330</v>
@@ -16889,13 +16889,13 @@
         </is>
       </c>
       <c r="D210" s="4" t="n">
-        <v>401.57</v>
+        <v>397.55</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>-0.08039999999999999</v>
+        <v>-0.05599999999999999</v>
       </c>
       <c r="F210" s="5" t="n">
-        <v>-0.2244</v>
+        <v>-0.1649</v>
       </c>
       <c r="G210" s="7" t="n">
         <v>46328</v>
@@ -16950,13 +16950,13 @@
         </is>
       </c>
       <c r="D211" s="15" t="n">
-        <v>119.31</v>
+        <v>121.06</v>
       </c>
       <c r="E211" s="16" t="n">
-        <v>0.0451</v>
+        <v>0.122</v>
       </c>
       <c r="F211" s="16" t="n">
-        <v>0.0582</v>
+        <v>0.1636</v>
       </c>
       <c r="G211" s="17" t="n">
         <v>46330</v>
@@ -17011,13 +17011,13 @@
         </is>
       </c>
       <c r="D212" s="4" t="n">
-        <v>175.23</v>
+        <v>172.41</v>
       </c>
       <c r="E212" s="6" t="n">
-        <v>0.1415</v>
+        <v>0.1344</v>
       </c>
       <c r="F212" s="6" t="n">
-        <v>0.1563</v>
+        <v>0.1315</v>
       </c>
       <c r="G212" s="7" t="n">
         <v>46330</v>
@@ -17072,13 +17072,13 @@
         </is>
       </c>
       <c r="D213" s="15" t="n">
-        <v>48.57</v>
+        <v>48.78</v>
       </c>
       <c r="E213" s="16" t="n">
-        <v>0.0108</v>
+        <v>0.0616</v>
       </c>
       <c r="F213" s="25" t="n">
-        <v>-0.1465</v>
+        <v>-0.08869999999999999</v>
       </c>
       <c r="G213" s="17" t="n">
         <v>46337</v>
@@ -17133,13 +17133,13 @@
         </is>
       </c>
       <c r="D214" s="4" t="n">
-        <v>158.98</v>
+        <v>158.37</v>
       </c>
       <c r="E214" s="6" t="n">
-        <v>0.061</v>
+        <v>0.08810000000000001</v>
       </c>
       <c r="F214" s="6" t="n">
-        <v>0.0187</v>
+        <v>0.0799</v>
       </c>
       <c r="G214" s="7" t="n">
         <v>46322</v>
@@ -17194,13 +17194,13 @@
         </is>
       </c>
       <c r="D215" s="15" t="n">
-        <v>49.79</v>
+        <v>48.13</v>
       </c>
       <c r="E215" s="16" t="n">
-        <v>0.1949</v>
+        <v>0.1451</v>
       </c>
       <c r="F215" s="16" t="n">
-        <v>0.6476000000000001</v>
+        <v>0.5387</v>
       </c>
       <c r="G215" s="17" t="n"/>
       <c r="H215" s="22" t="inlineStr">
@@ -17245,13 +17245,13 @@
         </is>
       </c>
       <c r="D216" s="4" t="n">
-        <v>149.38</v>
+        <v>147.86</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>-0.2104</v>
+        <v>-0.2295</v>
       </c>
       <c r="F216" s="6" t="n">
-        <v>0.137</v>
+        <v>0.0697</v>
       </c>
       <c r="G216" s="7" t="n"/>
       <c r="H216" s="12" t="inlineStr">
@@ -17270,7 +17270,7 @@
         <v>190</v>
       </c>
       <c r="M216" s="6" t="n">
-        <v>0.2719239523363235</v>
+        <v>0.2849993236845664</v>
       </c>
       <c r="N216" s="3" t="inlineStr"/>
       <c r="O216" s="9" t="n"/>
@@ -17314,13 +17314,13 @@
         </is>
       </c>
       <c r="D217" s="15" t="n">
-        <v>61.75</v>
+        <v>61.38</v>
       </c>
       <c r="E217" s="16" t="n">
-        <v>0.1553</v>
+        <v>0.1706</v>
       </c>
       <c r="F217" s="16" t="n">
-        <v>0.2962</v>
+        <v>0.287</v>
       </c>
       <c r="G217" s="17" t="n"/>
       <c r="H217" s="22" t="inlineStr">
@@ -17339,7 +17339,7 @@
         <v>67</v>
       </c>
       <c r="M217" s="16" t="n">
-        <v>0.08502024291497975</v>
+        <v>0.09156076898012377</v>
       </c>
       <c r="N217" s="14" t="inlineStr">
         <is>
@@ -17350,7 +17350,7 @@
         <v>70</v>
       </c>
       <c r="P217" s="16" t="n">
-        <v>0.1336032388663968</v>
+        <v>0.140436624307592</v>
       </c>
       <c r="Q217" s="20" t="inlineStr">
         <is>
@@ -17391,13 +17391,13 @@
         </is>
       </c>
       <c r="D218" s="4" t="n">
-        <v>213.86</v>
+        <v>212.81</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>-0.109</v>
+        <v>-0.1284</v>
       </c>
       <c r="F218" s="6" t="n">
-        <v>0.1255</v>
+        <v>0.0387</v>
       </c>
       <c r="G218" s="7" t="n">
         <v>46330</v>
@@ -17452,13 +17452,13 @@
         </is>
       </c>
       <c r="D219" s="15" t="n">
-        <v>231.93</v>
-      </c>
-      <c r="E219" s="25" t="n">
-        <v>-0.0159</v>
+        <v>231.59</v>
+      </c>
+      <c r="E219" s="16" t="n">
+        <v>0.0024</v>
       </c>
       <c r="F219" s="16" t="n">
-        <v>0.1223</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="G219" s="17" t="n">
         <v>46316</v>
@@ -17494,7 +17494,7 @@
         <v>250</v>
       </c>
       <c r="P219" s="16" t="n">
-        <v>0.07791143879618848</v>
+        <v>0.07949393324409515</v>
       </c>
       <c r="Q219" s="20" t="inlineStr">
         <is>
@@ -17531,13 +17531,13 @@
         </is>
       </c>
       <c r="D220" s="4" t="n">
-        <v>13.96</v>
-      </c>
-      <c r="E220" s="5" t="n">
-        <v>-0.0113</v>
+        <v>13.8</v>
+      </c>
+      <c r="E220" s="6" t="n">
+        <v>0.0575</v>
       </c>
       <c r="F220" s="6" t="n">
-        <v>0.4407</v>
+        <v>0.5385</v>
       </c>
       <c r="G220" s="7" t="n">
         <v>46337</v>
@@ -17592,13 +17592,13 @@
         </is>
       </c>
       <c r="D221" s="15" t="n">
-        <v>121.78</v>
+        <v>121.64</v>
       </c>
       <c r="E221" s="16" t="n">
-        <v>0.3521</v>
+        <v>0.3939</v>
       </c>
       <c r="F221" s="16" t="n">
-        <v>0.215</v>
+        <v>0.3175</v>
       </c>
       <c r="G221" s="17" t="n">
         <v>46317</v>
@@ -17653,13 +17653,13 @@
         </is>
       </c>
       <c r="D222" s="4" t="n">
-        <v>304.12</v>
+        <v>289.95</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>-0.1713</v>
-      </c>
-      <c r="F222" s="6" t="n">
-        <v>0.08019999999999999</v>
+        <v>-0.2162</v>
+      </c>
+      <c r="F222" s="5" t="n">
+        <v>-0.0215</v>
       </c>
       <c r="G222" s="7" t="n"/>
       <c r="H222" s="12" t="inlineStr">
@@ -17704,13 +17704,13 @@
         </is>
       </c>
       <c r="D223" s="15" t="n">
-        <v>40.51</v>
+        <v>40.06</v>
       </c>
       <c r="E223" s="25" t="n">
-        <v>-0.09699999999999999</v>
+        <v>-0.0244</v>
       </c>
       <c r="F223" s="16" t="n">
-        <v>0.189</v>
+        <v>0.2199</v>
       </c>
       <c r="G223" s="17" t="n">
         <v>46330</v>
@@ -17765,13 +17765,13 @@
         </is>
       </c>
       <c r="D224" s="4" t="n">
-        <v>47.23</v>
+        <v>48.15</v>
       </c>
       <c r="E224" s="6" t="n">
-        <v>0.1277</v>
+        <v>0.2095</v>
       </c>
       <c r="F224" s="6" t="n">
-        <v>0.1639</v>
+        <v>0.2989</v>
       </c>
       <c r="G224" s="7" t="n">
         <v>46331</v>
@@ -17826,13 +17826,13 @@
         </is>
       </c>
       <c r="D225" s="15" t="n">
-        <v>303.67</v>
+        <v>302.83</v>
       </c>
       <c r="E225" s="25" t="n">
-        <v>-0.0305</v>
+        <v>-0.0068</v>
       </c>
       <c r="F225" s="25" t="n">
-        <v>-0.057</v>
+        <v>-0.0312</v>
       </c>
       <c r="G225" s="17" t="n">
         <v>46289</v>
@@ -17891,13 +17891,13 @@
         </is>
       </c>
       <c r="D226" s="4" t="n">
-        <v>342.03</v>
+        <v>341.99</v>
       </c>
       <c r="E226" s="6" t="n">
-        <v>0.0819</v>
+        <v>0.1009</v>
       </c>
       <c r="F226" s="6" t="n">
-        <v>0.052</v>
+        <v>0.0732</v>
       </c>
       <c r="G226" s="7" t="n"/>
       <c r="H226" s="12" t="inlineStr">
@@ -17916,7 +17916,7 @@
         <v>390</v>
       </c>
       <c r="M226" s="6" t="n">
-        <v>0.1402508551881415</v>
+        <v>0.1403842217608702</v>
       </c>
       <c r="N226" s="3" t="inlineStr"/>
       <c r="O226" s="9" t="n"/>
@@ -17972,13 +17972,13 @@
         </is>
       </c>
       <c r="D227" s="15" t="n">
-        <v>183.97</v>
-      </c>
-      <c r="E227" s="25" t="n">
-        <v>-0.0001</v>
+        <v>183.81</v>
+      </c>
+      <c r="E227" s="16" t="n">
+        <v>0.0123</v>
       </c>
       <c r="F227" s="25" t="n">
-        <v>-0.1589</v>
+        <v>-0.1269</v>
       </c>
       <c r="G227" s="17" t="n">
         <v>46330</v>
@@ -18007,7 +18007,7 @@
         <v>305</v>
       </c>
       <c r="M227" s="16" t="n">
-        <v>0.6578790020111975</v>
+        <v>0.6593221261084815</v>
       </c>
       <c r="N227" s="14" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>185</v>
       </c>
       <c r="P227" s="16" t="n">
-        <v>0.005598738924824706</v>
+        <v>0.006474076492029801</v>
       </c>
       <c r="Q227" s="20" t="inlineStr">
         <is>
@@ -18059,13 +18059,13 @@
         </is>
       </c>
       <c r="D228" s="4" t="n">
-        <v>84.08</v>
-      </c>
-      <c r="E228" s="5" t="n">
-        <v>-0.0195</v>
+        <v>86.5</v>
+      </c>
+      <c r="E228" s="6" t="n">
+        <v>0.0358</v>
       </c>
       <c r="F228" s="5" t="n">
-        <v>-0.2074</v>
+        <v>-0.1464</v>
       </c>
       <c r="G228" s="7" t="n"/>
       <c r="H228" s="12" t="inlineStr">
@@ -18110,13 +18110,13 @@
         </is>
       </c>
       <c r="D229" s="15" t="n">
-        <v>954.49</v>
+        <v>958.62</v>
       </c>
       <c r="E229" s="16" t="n">
-        <v>0.1013</v>
+        <v>0.1547</v>
       </c>
       <c r="F229" s="16" t="n">
-        <v>0.145</v>
+        <v>0.2564</v>
       </c>
       <c r="G229" s="17" t="n">
         <v>46329</v>
@@ -18171,13 +18171,13 @@
         </is>
       </c>
       <c r="D230" s="4" t="n">
-        <v>105.12</v>
+        <v>104.47</v>
       </c>
       <c r="E230" s="6" t="n">
-        <v>0.09470000000000001</v>
-      </c>
-      <c r="F230" s="6" t="n">
-        <v>0.0216</v>
+        <v>0.0747</v>
+      </c>
+      <c r="F230" s="5" t="n">
+        <v>-0.0124</v>
       </c>
       <c r="G230" s="7" t="n">
         <v>46322</v>
@@ -18232,13 +18232,13 @@
         </is>
       </c>
       <c r="D231" s="15" t="n">
-        <v>302.28</v>
+        <v>302.45</v>
       </c>
       <c r="E231" s="25" t="n">
-        <v>-0.0373</v>
+        <v>-0.0249</v>
       </c>
       <c r="F231" s="25" t="n">
-        <v>-0.0547</v>
+        <v>-0.009000000000000001</v>
       </c>
       <c r="G231" s="17" t="n">
         <v>46323</v>
@@ -18267,7 +18267,7 @@
         <v>450</v>
       </c>
       <c r="M231" s="16" t="n">
-        <v>0.4886859865025805</v>
+        <v>0.4878492312778973</v>
       </c>
       <c r="N231" s="14" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>355</v>
       </c>
       <c r="P231" s="16" t="n">
-        <v>0.1744078337964802</v>
+        <v>0.1737477268970078</v>
       </c>
       <c r="Q231" s="20" t="inlineStr">
         <is>
@@ -18323,13 +18323,13 @@
         </is>
       </c>
       <c r="D232" s="4" t="n">
-        <v>74.78</v>
-      </c>
-      <c r="E232" s="5" t="n">
-        <v>-0.0171</v>
+        <v>75.18000000000001</v>
+      </c>
+      <c r="E232" s="6" t="n">
+        <v>0.0131</v>
       </c>
       <c r="F232" s="5" t="n">
-        <v>-0.0808</v>
+        <v>-0.0466</v>
       </c>
       <c r="G232" s="7" t="n">
         <v>46331</v>
@@ -18384,13 +18384,13 @@
         </is>
       </c>
       <c r="D233" s="15" t="n">
-        <v>407.3</v>
-      </c>
-      <c r="E233" s="25" t="n">
-        <v>-0.0546</v>
+        <v>411.58</v>
+      </c>
+      <c r="E233" s="16" t="n">
+        <v>0.0221</v>
       </c>
       <c r="F233" s="16" t="n">
-        <v>0.3616</v>
+        <v>0.3801</v>
       </c>
       <c r="G233" s="17" t="n"/>
       <c r="H233" s="22" t="inlineStr">
@@ -18435,13 +18435,13 @@
         </is>
       </c>
       <c r="D234" s="4" t="n">
-        <v>256.92</v>
+        <v>255.28</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>-0.0795</v>
+        <v>-0.0512</v>
       </c>
       <c r="F234" s="5" t="n">
-        <v>-0.256</v>
+        <v>-0.2245</v>
       </c>
       <c r="G234" s="7" t="n">
         <v>46330</v>
@@ -18496,13 +18496,13 @@
         </is>
       </c>
       <c r="D235" s="15" t="n">
-        <v>1277.68</v>
-      </c>
-      <c r="E235" s="25" t="n">
-        <v>-0.0293</v>
-      </c>
-      <c r="F235" s="25" t="n">
-        <v>-0.08550000000000001</v>
+        <v>1357.68</v>
+      </c>
+      <c r="E235" s="16" t="n">
+        <v>0.0565</v>
+      </c>
+      <c r="F235" s="16" t="n">
+        <v>0.0179</v>
       </c>
       <c r="G235" s="17" t="n">
         <v>46324</v>
@@ -18557,13 +18557,13 @@
         </is>
       </c>
       <c r="D236" s="4" t="n">
-        <v>257.38</v>
+        <v>263.54</v>
       </c>
       <c r="E236" s="6" t="n">
-        <v>0.0858</v>
+        <v>0.1494</v>
       </c>
       <c r="F236" s="6" t="n">
-        <v>0.2296</v>
+        <v>0.3568</v>
       </c>
       <c r="G236" s="7" t="n"/>
       <c r="H236" s="12" t="inlineStr">
@@ -18582,7 +18582,7 @@
         <v>240</v>
       </c>
       <c r="M236" s="5" t="n">
-        <v>-0.0675266143445489</v>
+        <v>-0.08932230401457092</v>
       </c>
       <c r="N236" s="3" t="inlineStr">
         <is>
@@ -18593,7 +18593,7 @@
         <v>251</v>
       </c>
       <c r="P236" s="5" t="n">
-        <v>-0.02478825083534072</v>
+        <v>-0.04758290961523875</v>
       </c>
       <c r="Q236" s="10" t="inlineStr">
         <is>
@@ -18634,13 +18634,13 @@
         </is>
       </c>
       <c r="D237" s="15" t="n">
-        <v>501.61</v>
+        <v>495.76</v>
       </c>
       <c r="E237" s="16" t="n">
-        <v>0.038</v>
+        <v>0.0173</v>
       </c>
       <c r="F237" s="16" t="n">
-        <v>0.3146</v>
+        <v>0.2988</v>
       </c>
       <c r="G237" s="17" t="n">
         <v>46330</v>
@@ -18669,7 +18669,7 @@
         <v>625</v>
       </c>
       <c r="M237" s="16" t="n">
-        <v>0.2459879189011383</v>
+        <v>0.2606906567694046</v>
       </c>
       <c r="N237" s="14" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>525</v>
       </c>
       <c r="P237" s="16" t="n">
-        <v>0.04662985187695617</v>
+        <v>0.05898015168629984</v>
       </c>
       <c r="Q237" s="20" t="inlineStr">
         <is>
@@ -18733,13 +18733,13 @@
         </is>
       </c>
       <c r="D238" s="4" t="n">
-        <v>461.36</v>
+        <v>456</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>-0.0398</v>
+        <v>-0.053</v>
       </c>
       <c r="F238" s="6" t="n">
-        <v>0.1335</v>
+        <v>0.09140000000000001</v>
       </c>
       <c r="G238" s="7" t="n">
         <v>46324</v>
@@ -18771,7 +18771,7 @@
         <v>525</v>
       </c>
       <c r="P238" s="6" t="n">
-        <v>0.1379400034680076</v>
+        <v>0.1513157894736842</v>
       </c>
       <c r="Q238" s="10" t="inlineStr">
         <is>
@@ -18820,13 +18820,13 @@
         </is>
       </c>
       <c r="D239" s="15" t="n">
-        <v>168.5</v>
+        <v>168.6</v>
       </c>
       <c r="E239" s="16" t="n">
-        <v>0.413</v>
+        <v>0.3749</v>
       </c>
       <c r="F239" s="16" t="n">
-        <v>0.7996</v>
+        <v>0.8392000000000001</v>
       </c>
       <c r="G239" s="17" t="n">
         <v>46324</v>
@@ -18881,13 +18881,13 @@
         </is>
       </c>
       <c r="D240" s="4" t="n">
-        <v>279.11</v>
+        <v>276.6</v>
       </c>
       <c r="E240" s="6" t="n">
-        <v>0.0469</v>
-      </c>
-      <c r="F240" s="5" t="n">
-        <v>-0.0131</v>
+        <v>0.0745</v>
+      </c>
+      <c r="F240" s="6" t="n">
+        <v>0.036</v>
       </c>
       <c r="G240" s="7" t="n">
         <v>46331</v>
@@ -18942,13 +18942,13 @@
         </is>
       </c>
       <c r="D241" s="15" t="n">
-        <v>1043.96</v>
+        <v>1075.51</v>
       </c>
       <c r="E241" s="16" t="n">
-        <v>0.07980000000000001</v>
+        <v>0.1813</v>
       </c>
       <c r="F241" s="16" t="n">
-        <v>0.05429999999999999</v>
+        <v>0.1678</v>
       </c>
       <c r="G241" s="17" t="n">
         <v>46295</v>
@@ -18977,7 +18977,7 @@
         <v>1525</v>
       </c>
       <c r="M241" s="16" t="n">
-        <v>0.4607839380819188</v>
+        <v>0.4179319578618516</v>
       </c>
       <c r="N241" s="14" t="inlineStr">
         <is>
@@ -19025,13 +19025,13 @@
         </is>
       </c>
       <c r="D242" s="4" t="n">
-        <v>232.8</v>
+        <v>236.9</v>
       </c>
       <c r="E242" s="6" t="n">
-        <v>0.0624</v>
+        <v>0.1232</v>
       </c>
       <c r="F242" s="6" t="n">
-        <v>0.0535</v>
+        <v>0.2616</v>
       </c>
       <c r="G242" s="7" t="n">
         <v>46336</v>
@@ -19086,13 +19086,13 @@
         </is>
       </c>
       <c r="D243" s="15" t="n">
-        <v>351.67</v>
+        <v>350.83</v>
       </c>
       <c r="E243" s="16" t="n">
-        <v>0.1997</v>
+        <v>0.2514</v>
       </c>
       <c r="F243" s="16" t="n">
-        <v>0.3406</v>
+        <v>0.3383</v>
       </c>
       <c r="G243" s="17" t="n">
         <v>46324</v>
@@ -19147,13 +19147,13 @@
         </is>
       </c>
       <c r="D244" s="4" t="n">
-        <v>137.68</v>
+        <v>136.32</v>
       </c>
       <c r="E244" s="6" t="n">
-        <v>0.0716</v>
+        <v>0.0646</v>
       </c>
       <c r="F244" s="6" t="n">
-        <v>0.4975</v>
+        <v>0.38</v>
       </c>
       <c r="G244" s="7" t="n">
         <v>46323</v>
@@ -19182,7 +19182,7 @@
         <v>160</v>
       </c>
       <c r="M244" s="6" t="n">
-        <v>0.1621150493898895</v>
+        <v>0.1737089201877935</v>
       </c>
       <c r="N244" s="3" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>150</v>
       </c>
       <c r="P244" s="6" t="n">
-        <v>0.08948285880302144</v>
+        <v>0.1003521126760564</v>
       </c>
       <c r="Q244" s="10" t="inlineStr">
         <is>
@@ -19238,13 +19238,13 @@
         </is>
       </c>
       <c r="D245" s="15" t="n">
-        <v>70.04000000000001</v>
+        <v>69.58</v>
       </c>
       <c r="E245" s="16" t="n">
-        <v>0.0355</v>
+        <v>0.0435</v>
       </c>
       <c r="F245" s="16" t="n">
-        <v>0.3308</v>
+        <v>0.2642</v>
       </c>
       <c r="G245" s="17" t="n"/>
       <c r="H245" s="22" t="inlineStr">
@@ -19289,13 +19289,13 @@
         </is>
       </c>
       <c r="D246" s="4" t="n">
-        <v>227.38</v>
+        <v>228.58</v>
       </c>
       <c r="E246" s="6" t="n">
-        <v>0.059</v>
+        <v>0.0964</v>
       </c>
       <c r="F246" s="6" t="n">
-        <v>0.0892</v>
+        <v>0.1051</v>
       </c>
       <c r="G246" s="7" t="n"/>
       <c r="H246" s="12" t="inlineStr">
@@ -19314,7 +19314,7 @@
         <v>315</v>
       </c>
       <c r="M246" s="6" t="n">
-        <v>0.3853461166329493</v>
+        <v>0.3780733222504155</v>
       </c>
       <c r="N246" s="3" t="inlineStr">
         <is>
@@ -19325,7 +19325,7 @@
         <v>413</v>
       </c>
       <c r="P246" s="6" t="n">
-        <v>0.8163426862520891</v>
+        <v>0.8068072447283225</v>
       </c>
       <c r="Q246" s="10" t="inlineStr">
         <is>
@@ -19374,13 +19374,13 @@
         </is>
       </c>
       <c r="D247" s="15" t="n">
-        <v>362.81</v>
+        <v>358.9</v>
       </c>
       <c r="E247" s="25" t="n">
-        <v>-0.03759999999999999</v>
+        <v>-0.0106</v>
       </c>
       <c r="F247" s="25" t="n">
-        <v>-0.2033</v>
+        <v>-0.1806</v>
       </c>
       <c r="G247" s="17" t="n">
         <v>46331</v>
@@ -19435,13 +19435,13 @@
         </is>
       </c>
       <c r="D248" s="4" t="n">
-        <v>232.41</v>
+        <v>232.66</v>
       </c>
       <c r="E248" s="6" t="n">
-        <v>0.0304</v>
+        <v>0.0459</v>
       </c>
       <c r="F248" s="5" t="n">
-        <v>-0.1619</v>
+        <v>-0.1359</v>
       </c>
       <c r="G248" s="7" t="n">
         <v>46322</v>
@@ -19492,13 +19492,13 @@
         </is>
       </c>
       <c r="D249" s="15" t="n">
-        <v>10.97</v>
+        <v>11.41</v>
       </c>
       <c r="E249" s="16" t="n">
-        <v>0.0148</v>
+        <v>0.0868</v>
       </c>
       <c r="F249" s="25" t="n">
-        <v>-0.2981</v>
+        <v>-0.2764</v>
       </c>
       <c r="G249" s="17" t="n"/>
       <c r="H249" s="22" t="inlineStr">
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="D250" s="4" t="n">
-        <v>191.33</v>
+        <v>190.38</v>
       </c>
       <c r="E250" s="6" t="n">
-        <v>0.4158</v>
+        <v>0.4536</v>
       </c>
       <c r="F250" s="6" t="n">
-        <v>0.4058</v>
+        <v>0.3746</v>
       </c>
       <c r="G250" s="7" t="n"/>
       <c r="H250" s="12" t="inlineStr">
@@ -19568,7 +19568,7 @@
         <v>150</v>
       </c>
       <c r="M250" s="5" t="n">
-        <v>-0.2160142162755449</v>
+        <v>-0.212102111566341</v>
       </c>
       <c r="N250" s="3" t="inlineStr">
         <is>
@@ -19579,7 +19579,7 @@
         <v>130</v>
       </c>
       <c r="P250" s="5" t="n">
-        <v>-0.3205456541054723</v>
+        <v>-0.3171551633574955</v>
       </c>
       <c r="Q250" s="10" t="inlineStr">
         <is>
@@ -19620,13 +19620,13 @@
         </is>
       </c>
       <c r="D251" s="15" t="n">
-        <v>71.72</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="E251" s="25" t="n">
-        <v>-0.0336</v>
+        <v>-0.0026</v>
       </c>
       <c r="F251" s="25" t="n">
-        <v>-0.2043</v>
+        <v>-0.1736</v>
       </c>
       <c r="G251" s="17" t="n">
         <v>46328</v>
@@ -19681,13 +19681,13 @@
         </is>
       </c>
       <c r="D252" s="4" t="n">
-        <v>275.98</v>
+        <v>275.46</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>-0.0591</v>
-      </c>
-      <c r="F252" s="5" t="n">
-        <v>-0.0525</v>
+        <v>-0.0263</v>
+      </c>
+      <c r="F252" s="6" t="n">
+        <v>0.0104</v>
       </c>
       <c r="G252" s="7" t="n">
         <v>46331</v>
@@ -19742,13 +19742,13 @@
         </is>
       </c>
       <c r="D253" s="15" t="n">
-        <v>148.56</v>
+        <v>148.8</v>
       </c>
       <c r="E253" s="16" t="n">
-        <v>0.0143</v>
+        <v>0.0446</v>
       </c>
       <c r="F253" s="16" t="n">
-        <v>0.2376</v>
+        <v>0.294</v>
       </c>
       <c r="G253" s="17" t="n"/>
       <c r="H253" s="22" t="inlineStr">
@@ -19767,7 +19767,7 @@
         <v>280</v>
       </c>
       <c r="M253" s="16" t="n">
-        <v>0.8847603661820139</v>
+        <v>0.8817204301075268</v>
       </c>
       <c r="N253" s="14" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>245</v>
       </c>
       <c r="P253" s="16" t="n">
-        <v>0.6491653204092622</v>
+        <v>0.6465053763440859</v>
       </c>
       <c r="Q253" s="20" t="inlineStr">
         <is>
@@ -19819,13 +19819,13 @@
         </is>
       </c>
       <c r="D254" s="4" t="n">
-        <v>371.76</v>
+        <v>367.9</v>
       </c>
       <c r="E254" s="6" t="n">
-        <v>0.0388</v>
+        <v>0.0484</v>
       </c>
       <c r="F254" s="6" t="n">
-        <v>0.1417</v>
+        <v>0.1362</v>
       </c>
       <c r="G254" s="7" t="n"/>
       <c r="H254" s="12" t="inlineStr">
@@ -19844,7 +19844,7 @@
         <v>420</v>
       </c>
       <c r="M254" s="6" t="n">
-        <v>0.1297611362169142</v>
+        <v>0.1416145691764067</v>
       </c>
       <c r="N254" s="3" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>415</v>
       </c>
       <c r="P254" s="6" t="n">
-        <v>0.1163115988809985</v>
+        <v>0.1280239195433542</v>
       </c>
       <c r="Q254" s="10" t="inlineStr">
         <is>
@@ -19904,13 +19904,13 @@
         </is>
       </c>
       <c r="D255" s="15" t="n">
-        <v>13.59</v>
+        <v>13.26</v>
       </c>
       <c r="E255" s="25" t="n">
-        <v>-0.1708</v>
+        <v>-0.2001</v>
       </c>
       <c r="F255" s="16" t="n">
-        <v>0.3324</v>
+        <v>0.2228</v>
       </c>
       <c r="G255" s="17" t="n"/>
       <c r="H255" s="22" t="inlineStr">
@@ -19955,13 +19955,13 @@
         </is>
       </c>
       <c r="D256" s="4" t="n">
-        <v>34.97</v>
-      </c>
-      <c r="E256" s="6" t="n">
-        <v>0.04190000000000001</v>
+        <v>34.23</v>
+      </c>
+      <c r="E256" s="5" t="n">
+        <v>-0.0015</v>
       </c>
       <c r="F256" s="6" t="n">
-        <v>0.3443</v>
+        <v>0.2763</v>
       </c>
       <c r="G256" s="7" t="n">
         <v>46315</v>
@@ -20016,13 +20016,13 @@
         </is>
       </c>
       <c r="D257" s="15" t="n">
-        <v>184.04</v>
+        <v>184.43</v>
       </c>
       <c r="E257" s="16" t="n">
-        <v>0.1118</v>
+        <v>0.1455</v>
       </c>
       <c r="F257" s="16" t="n">
-        <v>0.4512</v>
+        <v>0.446</v>
       </c>
       <c r="G257" s="17" t="n">
         <v>46330</v>
@@ -20077,13 +20077,13 @@
         </is>
       </c>
       <c r="D258" s="4" t="n">
-        <v>183.09</v>
+        <v>184.19</v>
       </c>
       <c r="E258" s="6" t="n">
-        <v>0.0175</v>
+        <v>0.0472</v>
       </c>
       <c r="F258" s="6" t="n">
-        <v>0.4841</v>
+        <v>0.4984</v>
       </c>
       <c r="G258" s="7" t="n">
         <v>46328</v>
@@ -20138,13 +20138,13 @@
         </is>
       </c>
       <c r="D259" s="15" t="n">
-        <v>121.82</v>
+        <v>122.55</v>
       </c>
       <c r="E259" s="25" t="n">
-        <v>-0.0548</v>
+        <v>-0.0292</v>
       </c>
       <c r="F259" s="25" t="n">
-        <v>-0.1214</v>
+        <v>-0.0926</v>
       </c>
       <c r="G259" s="17" t="n"/>
       <c r="H259" s="22" t="inlineStr">
@@ -20199,13 +20199,13 @@
         </is>
       </c>
       <c r="D260" s="4" t="n">
-        <v>17.7</v>
+        <v>17.36</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>-0.1319</v>
+        <v>-0.0704</v>
       </c>
       <c r="F260" s="6" t="n">
-        <v>0.0351</v>
+        <v>0.0713</v>
       </c>
       <c r="G260" s="7" t="n">
         <v>46331</v>
@@ -20260,13 +20260,13 @@
         </is>
       </c>
       <c r="D261" s="15" t="n">
-        <v>194.23</v>
+        <v>194.35</v>
       </c>
       <c r="E261" s="16" t="n">
-        <v>0.2083</v>
+        <v>0.226</v>
       </c>
       <c r="F261" s="16" t="n">
-        <v>0.1351</v>
+        <v>0.164</v>
       </c>
       <c r="G261" s="17" t="n">
         <v>46330</v>
@@ -20295,7 +20295,7 @@
         <v>265</v>
       </c>
       <c r="M261" s="16" t="n">
-        <v>0.3643618390567884</v>
+        <v>0.3635194237200927</v>
       </c>
       <c r="N261" s="14" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>179</v>
       </c>
       <c r="P261" s="25" t="n">
-        <v>-0.07841219173145235</v>
+        <v>-0.07898121944944685</v>
       </c>
       <c r="Q261" s="20" t="inlineStr">
         <is>
@@ -20351,13 +20351,13 @@
         </is>
       </c>
       <c r="D262" s="4" t="n">
-        <v>117.21</v>
+        <v>118.11</v>
       </c>
       <c r="E262" s="6" t="n">
-        <v>0.2266</v>
+        <v>0.2384</v>
       </c>
       <c r="F262" s="6" t="n">
-        <v>0.3514</v>
+        <v>0.3652</v>
       </c>
       <c r="G262" s="7" t="n">
         <v>46322</v>
@@ -20412,13 +20412,13 @@
         </is>
       </c>
       <c r="D263" s="15" t="n">
-        <v>8.960000000000001</v>
+        <v>8.91</v>
       </c>
       <c r="E263" s="16" t="n">
-        <v>0.004500000000000001</v>
+        <v>0.08130000000000001</v>
       </c>
       <c r="F263" s="16" t="n">
-        <v>0.1399</v>
+        <v>0.1992</v>
       </c>
       <c r="G263" s="17" t="n">
         <v>46339</v>
@@ -20473,13 +20473,13 @@
         </is>
       </c>
       <c r="D264" s="4" t="n">
-        <v>112.96</v>
+        <v>110.81</v>
       </c>
       <c r="E264" s="6" t="n">
-        <v>0.1286</v>
+        <v>0.1302</v>
       </c>
       <c r="F264" s="6" t="n">
-        <v>0.5553</v>
+        <v>0.5129</v>
       </c>
       <c r="G264" s="7" t="n"/>
       <c r="H264" s="12" t="inlineStr">
@@ -20524,13 +20524,13 @@
         </is>
       </c>
       <c r="D265" s="15" t="n">
-        <v>16.53</v>
+        <v>16.25</v>
       </c>
       <c r="E265" s="25" t="n">
-        <v>-0.0771</v>
+        <v>-0.0073</v>
       </c>
       <c r="F265" s="16" t="n">
-        <v>0.1131</v>
+        <v>0.1484</v>
       </c>
       <c r="G265" s="17" t="n">
         <v>46335</v>
@@ -20585,13 +20585,13 @@
         </is>
       </c>
       <c r="D266" s="4" t="n">
-        <v>365.4</v>
+        <v>361.74</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>-0.1127</v>
-      </c>
-      <c r="F266" s="6" t="n">
-        <v>0.0289</v>
+        <v>-0.1294</v>
+      </c>
+      <c r="F266" s="5" t="n">
+        <v>-0.0152</v>
       </c>
       <c r="G266" s="7" t="n">
         <v>46317</v>
@@ -20660,13 +20660,13 @@
         </is>
       </c>
       <c r="D267" s="15" t="n">
-        <v>4.04</v>
+        <v>4.14</v>
       </c>
       <c r="E267" s="16" t="n">
-        <v>0.2169</v>
+        <v>0.3285</v>
       </c>
       <c r="F267" s="16" t="n">
-        <v>0.005</v>
+        <v>0.052</v>
       </c>
       <c r="G267" s="17" t="n">
         <v>46331</v>
@@ -20721,13 +20721,13 @@
         </is>
       </c>
       <c r="D268" s="4" t="n">
-        <v>23.8</v>
+        <v>23.72</v>
       </c>
       <c r="E268" s="6" t="n">
-        <v>0.1232</v>
+        <v>0.139</v>
       </c>
       <c r="F268" s="6" t="n">
-        <v>0.3694</v>
+        <v>0.3073</v>
       </c>
       <c r="G268" s="7" t="n"/>
       <c r="H268" s="12" t="inlineStr">
@@ -20772,13 +20772,13 @@
         </is>
       </c>
       <c r="D269" s="15" t="n">
-        <v>20.32</v>
+        <v>20.33</v>
       </c>
       <c r="E269" s="16" t="n">
-        <v>0.0901</v>
+        <v>0.1216</v>
       </c>
       <c r="F269" s="16" t="n">
-        <v>0.4195</v>
+        <v>0.3602</v>
       </c>
       <c r="G269" s="17" t="n"/>
       <c r="H269" s="22" t="inlineStr">
@@ -20823,13 +20823,13 @@
         </is>
       </c>
       <c r="D270" s="4" t="n">
-        <v>209.47</v>
+        <v>209.32</v>
       </c>
       <c r="E270" s="6" t="n">
-        <v>0.109</v>
-      </c>
-      <c r="F270" s="5" t="n">
-        <v>-0.0416</v>
+        <v>0.1289</v>
+      </c>
+      <c r="F270" s="6" t="n">
+        <v>0.0043</v>
       </c>
       <c r="G270" s="7" t="n">
         <v>46328</v>
@@ -20884,13 +20884,13 @@
         </is>
       </c>
       <c r="D271" s="15" t="n">
-        <v>209.22</v>
+        <v>208.77</v>
       </c>
       <c r="E271" s="25" t="n">
-        <v>-0.0433</v>
+        <v>-0.0452</v>
       </c>
       <c r="F271" s="16" t="n">
-        <v>0.4293</v>
+        <v>0.3048</v>
       </c>
       <c r="G271" s="17" t="n">
         <v>46316</v>
@@ -20965,13 +20965,13 @@
         </is>
       </c>
       <c r="D272" s="4" t="n">
-        <v>41.2</v>
+        <v>40.79</v>
       </c>
       <c r="E272" s="6" t="n">
-        <v>0.1063</v>
+        <v>0.1599</v>
       </c>
       <c r="F272" s="6" t="n">
-        <v>0.3205</v>
+        <v>0.3553</v>
       </c>
       <c r="G272" s="7" t="n">
         <v>46329</v>
@@ -21026,13 +21026,13 @@
         </is>
       </c>
       <c r="D273" s="15" t="n">
-        <v>339.39</v>
+        <v>335.51</v>
       </c>
       <c r="E273" s="16" t="n">
-        <v>0.0199</v>
+        <v>0.0394</v>
       </c>
       <c r="F273" s="16" t="n">
-        <v>0.2801</v>
+        <v>0.2516</v>
       </c>
       <c r="G273" s="17" t="n"/>
       <c r="H273" s="22" t="inlineStr">
@@ -21051,7 +21051,7 @@
         <v>320</v>
       </c>
       <c r="M273" s="25" t="n">
-        <v>-0.05713191313827746</v>
+        <v>-0.04622813030908167</v>
       </c>
       <c r="N273" s="14" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>280</v>
       </c>
       <c r="P273" s="25" t="n">
-        <v>-0.1749904239959928</v>
+        <v>-0.1654496140204465</v>
       </c>
       <c r="Q273" s="20" t="inlineStr">
         <is>
@@ -21103,13 +21103,13 @@
         </is>
       </c>
       <c r="D274" s="4" t="n">
-        <v>401.85</v>
+        <v>407.81</v>
       </c>
       <c r="E274" s="6" t="n">
-        <v>0.01</v>
+        <v>0.0337</v>
       </c>
       <c r="F274" s="6" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.0919</v>
       </c>
       <c r="G274" s="7" t="n"/>
       <c r="H274" s="12" t="inlineStr">
@@ -21128,7 +21128,7 @@
         <v>535</v>
       </c>
       <c r="M274" s="6" t="n">
-        <v>0.3313425407490356</v>
+        <v>0.3118854368455898</v>
       </c>
       <c r="N274" s="3" t="inlineStr"/>
       <c r="O274" s="9" t="n"/>
@@ -21172,13 +21172,13 @@
         </is>
       </c>
       <c r="D275" s="15" t="n">
-        <v>6.17</v>
+        <v>6.16</v>
       </c>
       <c r="E275" s="25" t="n">
-        <v>-0.1571</v>
+        <v>-0.1207</v>
       </c>
       <c r="F275" s="25" t="n">
-        <v>-0.008</v>
+        <v>-0.0008</v>
       </c>
       <c r="G275" s="17" t="n">
         <v>46331</v>
@@ -21233,13 +21233,13 @@
         </is>
       </c>
       <c r="D276" s="4" t="n">
-        <v>88.73999999999999</v>
+        <v>89.62</v>
       </c>
       <c r="E276" s="6" t="n">
-        <v>0.3217</v>
+        <v>0.3404</v>
       </c>
       <c r="F276" s="6" t="n">
-        <v>0.4675</v>
+        <v>0.4885</v>
       </c>
       <c r="G276" s="7" t="n">
         <v>46322</v>
@@ -21294,13 +21294,13 @@
         </is>
       </c>
       <c r="D277" s="15" t="n">
-        <v>95.36</v>
-      </c>
-      <c r="E277" s="25" t="n">
-        <v>-0.0236</v>
+        <v>95.34999999999999</v>
+      </c>
+      <c r="E277" s="16" t="n">
+        <v>0.0178</v>
       </c>
       <c r="F277" s="25" t="n">
-        <v>-0.1891</v>
+        <v>-0.1562</v>
       </c>
       <c r="G277" s="17" t="n">
         <v>46331</v>
@@ -21355,13 +21355,13 @@
         </is>
       </c>
       <c r="D278" s="4" t="n">
-        <v>210.01</v>
+        <v>210.91</v>
       </c>
       <c r="E278" s="6" t="n">
-        <v>0.0319</v>
+        <v>0.042</v>
       </c>
       <c r="F278" s="6" t="n">
-        <v>0.0564</v>
+        <v>0.0393</v>
       </c>
       <c r="G278" s="7" t="n">
         <v>46330</v>
@@ -21416,13 +21416,13 @@
         </is>
       </c>
       <c r="D279" s="15" t="n">
-        <v>381.54</v>
+        <v>387.02</v>
       </c>
       <c r="E279" s="16" t="n">
-        <v>0.0154</v>
+        <v>0.06059999999999999</v>
       </c>
       <c r="F279" s="16" t="n">
-        <v>0.0208</v>
+        <v>0.106</v>
       </c>
       <c r="G279" s="17" t="n">
         <v>46322</v>
@@ -21477,13 +21477,13 @@
         </is>
       </c>
       <c r="D280" s="4" t="n">
-        <v>57.75</v>
+        <v>58.6</v>
       </c>
       <c r="E280" s="5" t="n">
-        <v>-0.0415</v>
+        <v>-0.034</v>
       </c>
       <c r="F280" s="6" t="n">
-        <v>0.147</v>
+        <v>0.1076</v>
       </c>
       <c r="G280" s="7" t="n">
         <v>46330</v>
@@ -21538,13 +21538,13 @@
         </is>
       </c>
       <c r="D281" s="15" t="n">
-        <v>445.14</v>
+        <v>446.33</v>
       </c>
       <c r="E281" s="16" t="n">
-        <v>0.0625</v>
+        <v>0.0883</v>
       </c>
       <c r="F281" s="16" t="n">
-        <v>0.0711</v>
+        <v>0.1064</v>
       </c>
       <c r="G281" s="17" t="n">
         <v>46310</v>
@@ -21621,13 +21621,13 @@
         </is>
       </c>
       <c r="D282" s="4" t="n">
-        <v>124.02</v>
+        <v>124.41</v>
       </c>
       <c r="E282" s="6" t="n">
-        <v>0.1219</v>
+        <v>0.1614</v>
       </c>
       <c r="F282" s="5" t="n">
-        <v>-0.1438</v>
+        <v>-0.0533</v>
       </c>
       <c r="G282" s="7" t="n">
         <v>46330</v>
@@ -21682,13 +21682,13 @@
         </is>
       </c>
       <c r="D283" s="15" t="n">
-        <v>266.06</v>
+        <v>279.11</v>
       </c>
       <c r="E283" s="16" t="n">
-        <v>0.1809</v>
+        <v>0.2539</v>
       </c>
       <c r="F283" s="16" t="n">
-        <v>0.4377</v>
+        <v>0.4578</v>
       </c>
       <c r="G283" s="17" t="n">
         <v>46324</v>
@@ -21743,13 +21743,13 @@
         </is>
       </c>
       <c r="D284" s="4" t="n">
-        <v>270.87</v>
+        <v>268.7</v>
       </c>
       <c r="E284" s="6" t="n">
-        <v>0.0246</v>
+        <v>0.0377</v>
       </c>
       <c r="F284" s="5" t="n">
-        <v>-0.0495</v>
+        <v>-0.0389</v>
       </c>
       <c r="G284" s="7" t="n">
         <v>46315</v>
@@ -21778,7 +21778,7 @@
         <v>300</v>
       </c>
       <c r="M284" s="6" t="n">
-        <v>0.1075423634954037</v>
+        <v>0.1164867882396725</v>
       </c>
       <c r="N284" s="3" t="inlineStr">
         <is>
@@ -21789,7 +21789,7 @@
         <v>316</v>
       </c>
       <c r="P284" s="6" t="n">
-        <v>0.1666112895484919</v>
+        <v>0.1760327502791217</v>
       </c>
       <c r="Q284" s="10" t="inlineStr">
         <is>
@@ -21846,13 +21846,13 @@
         </is>
       </c>
       <c r="D285" s="15" t="n">
-        <v>332.46</v>
+        <v>326.15</v>
       </c>
       <c r="E285" s="25" t="n">
-        <v>-0.0521</v>
+        <v>-0.0833</v>
       </c>
       <c r="F285" s="16" t="n">
-        <v>0.1537</v>
+        <v>0.09759999999999999</v>
       </c>
       <c r="G285" s="17" t="n">
         <v>46330</v>
@@ -21881,7 +21881,7 @@
         <v>335</v>
       </c>
       <c r="M285" s="16" t="n">
-        <v>0.007640016844131687</v>
+        <v>0.02713475394757021</v>
       </c>
       <c r="N285" s="14" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>375</v>
       </c>
       <c r="P285" s="16" t="n">
-        <v>0.1279552427359683</v>
+        <v>0.1497777096428025</v>
       </c>
       <c r="Q285" s="20" t="inlineStr">
         <is>
@@ -21933,13 +21933,13 @@
         </is>
       </c>
       <c r="D286" s="4" t="n">
-        <v>43.21</v>
+        <v>43.22</v>
       </c>
       <c r="E286" s="5" t="n">
-        <v>-0.0793</v>
+        <v>-0.0636</v>
       </c>
       <c r="F286" s="6" t="n">
-        <v>0.4931</v>
+        <v>0.5102</v>
       </c>
       <c r="G286" s="7" t="n">
         <v>46330</v>
@@ -21994,13 +21994,13 @@
         </is>
       </c>
       <c r="D287" s="15" t="n">
-        <v>7.24</v>
+        <v>7.04</v>
       </c>
       <c r="E287" s="16" t="n">
-        <v>0.0766</v>
+        <v>0.08810000000000001</v>
       </c>
       <c r="F287" s="25" t="n">
-        <v>-0.0689</v>
+        <v>-0.0236</v>
       </c>
       <c r="G287" s="17" t="n"/>
       <c r="H287" s="22" t="inlineStr">
@@ -22045,13 +22045,13 @@
         </is>
       </c>
       <c r="D288" s="4" t="n">
-        <v>191.92</v>
+        <v>188.36</v>
       </c>
       <c r="E288" s="5" t="n">
-        <v>-0.0404</v>
+        <v>-0.0542</v>
       </c>
       <c r="F288" s="6" t="n">
-        <v>0.5009</v>
+        <v>0.3918</v>
       </c>
       <c r="G288" s="7" t="n"/>
       <c r="H288" s="12" t="inlineStr">
@@ -22096,13 +22096,13 @@
         </is>
       </c>
       <c r="D289" s="15" t="n">
-        <v>448.17</v>
-      </c>
-      <c r="E289" s="25" t="n">
-        <v>-0.0245</v>
+        <v>453.33</v>
+      </c>
+      <c r="E289" s="16" t="n">
+        <v>0.0412</v>
       </c>
       <c r="F289" s="25" t="n">
-        <v>-0.1973</v>
+        <v>-0.1279</v>
       </c>
       <c r="G289" s="17" t="n">
         <v>46324</v>
@@ -22131,7 +22131,7 @@
         <v>730</v>
       </c>
       <c r="M289" s="16" t="n">
-        <v>0.6288461967556953</v>
+        <v>0.6103059581320451</v>
       </c>
       <c r="N289" s="14" t="inlineStr">
         <is>
@@ -22142,7 +22142,7 @@
         <v>575</v>
       </c>
       <c r="P289" s="16" t="n">
-        <v>0.2829952919651025</v>
+        <v>0.2683916793505835</v>
       </c>
       <c r="Q289" s="20" t="inlineStr">
         <is>
@@ -22183,13 +22183,13 @@
         </is>
       </c>
       <c r="D290" s="4" t="n">
-        <v>27.71</v>
+        <v>27.99</v>
       </c>
       <c r="E290" s="6" t="n">
-        <v>0.0757</v>
+        <v>0.1305</v>
       </c>
       <c r="F290" s="6" t="n">
-        <v>0.0674</v>
+        <v>0.2122</v>
       </c>
       <c r="G290" s="7" t="n">
         <v>46330</v>
@@ -22244,13 +22244,13 @@
         </is>
       </c>
       <c r="D291" s="15" t="n">
-        <v>90.90000000000001</v>
+        <v>90.72</v>
       </c>
       <c r="E291" s="25" t="n">
-        <v>-0.1539</v>
+        <v>-0.1346</v>
       </c>
       <c r="F291" s="16" t="n">
-        <v>0.08070000000000001</v>
+        <v>0.031</v>
       </c>
       <c r="G291" s="17" t="n"/>
       <c r="H291" s="22" t="inlineStr">
@@ -22295,13 +22295,13 @@
         </is>
       </c>
       <c r="D292" s="4" t="n">
-        <v>207.13</v>
+        <v>206.46</v>
       </c>
       <c r="E292" s="6" t="n">
-        <v>0.1397</v>
+        <v>0.1727</v>
       </c>
       <c r="F292" s="6" t="n">
-        <v>0.4827</v>
+        <v>0.4507</v>
       </c>
       <c r="G292" s="7" t="n"/>
       <c r="H292" s="12" t="inlineStr">
@@ -22346,13 +22346,13 @@
         </is>
       </c>
       <c r="D293" s="15" t="n">
-        <v>279.46</v>
+        <v>283.52</v>
       </c>
       <c r="E293" s="25" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.0742</v>
       </c>
       <c r="F293" s="25" t="n">
-        <v>-0.0504</v>
+        <v>-0.0482</v>
       </c>
       <c r="G293" s="17" t="n">
         <v>46331</v>
@@ -22407,13 +22407,13 @@
         </is>
       </c>
       <c r="D294" s="4" t="n">
-        <v>86.09</v>
+        <v>87.05</v>
       </c>
       <c r="E294" s="5" t="n">
-        <v>-0.1127</v>
+        <v>-0.1038</v>
       </c>
       <c r="F294" s="6" t="n">
-        <v>0.0292</v>
+        <v>0.0398</v>
       </c>
       <c r="G294" s="7" t="n"/>
       <c r="H294" s="12" t="inlineStr">
@@ -22458,13 +22458,13 @@
         </is>
       </c>
       <c r="D295" s="15" t="n">
-        <v>129.79</v>
+        <v>131.24</v>
       </c>
       <c r="E295" s="25" t="n">
-        <v>-0.0617</v>
+        <v>-0.0397</v>
       </c>
       <c r="F295" s="25" t="n">
-        <v>-0.0554</v>
+        <v>-0.0469</v>
       </c>
       <c r="G295" s="17" t="n">
         <v>46331</v>
@@ -22493,7 +22493,7 @@
         <v>166</v>
       </c>
       <c r="M295" s="16" t="n">
-        <v>0.2789891362970954</v>
+        <v>0.264858274916184</v>
       </c>
       <c r="N295" s="14" t="inlineStr"/>
       <c r="O295" s="19" t="n"/>
@@ -22541,13 +22541,13 @@
         </is>
       </c>
       <c r="D296" s="4" t="n">
-        <v>28.27</v>
+        <v>28.47</v>
       </c>
       <c r="E296" s="5" t="n">
-        <v>-0.1261</v>
+        <v>-0.09449999999999999</v>
       </c>
       <c r="F296" s="5" t="n">
-        <v>-0.0851</v>
+        <v>-0.0459</v>
       </c>
       <c r="G296" s="7" t="n">
         <v>46317</v>
@@ -22602,13 +22602,13 @@
         </is>
       </c>
       <c r="D297" s="15" t="n">
-        <v>269.98</v>
+        <v>273.48</v>
       </c>
       <c r="E297" s="25" t="n">
-        <v>-0.0414</v>
+        <v>-0.047</v>
       </c>
       <c r="F297" s="16" t="n">
-        <v>0.026</v>
+        <v>0.0176</v>
       </c>
       <c r="G297" s="17" t="n">
         <v>46322</v>
@@ -22637,7 +22637,7 @@
         <v>275</v>
       </c>
       <c r="M297" s="16" t="n">
-        <v>0.01859396992369798</v>
+        <v>0.005557993271902814</v>
       </c>
       <c r="N297" s="14" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>312</v>
       </c>
       <c r="P297" s="16" t="n">
-        <v>0.155641158604341</v>
+        <v>0.1408512505484861</v>
       </c>
       <c r="Q297" s="20" t="inlineStr">
         <is>
@@ -22701,13 +22701,13 @@
         </is>
       </c>
       <c r="D298" s="4" t="n">
-        <v>33.42</v>
+        <v>34.42</v>
       </c>
       <c r="E298" s="5" t="n">
-        <v>-0.0535</v>
+        <v>-0.016</v>
       </c>
       <c r="F298" s="5" t="n">
-        <v>-0.1274</v>
+        <v>-0.08070000000000001</v>
       </c>
       <c r="G298" s="7" t="n">
         <v>46322</v>
@@ -22766,13 +22766,13 @@
         </is>
       </c>
       <c r="D299" s="15" t="n">
-        <v>72.16</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="E299" s="25" t="n">
-        <v>-0.0587</v>
+        <v>-0.0584</v>
       </c>
       <c r="F299" s="16" t="n">
-        <v>0.1364</v>
+        <v>0.1703</v>
       </c>
       <c r="G299" s="17" t="n">
         <v>46310</v>
@@ -22827,13 +22827,13 @@
         </is>
       </c>
       <c r="D300" s="4" t="n">
-        <v>457.5</v>
+        <v>461.24</v>
       </c>
       <c r="E300" s="5" t="n">
-        <v>-0.0617</v>
+        <v>-0.0587</v>
       </c>
       <c r="F300" s="5" t="n">
-        <v>-0.0964</v>
+        <v>-0.09960000000000001</v>
       </c>
       <c r="G300" s="7" t="n">
         <v>46325</v>
@@ -22862,7 +22862,7 @@
         <v>570</v>
       </c>
       <c r="M300" s="6" t="n">
-        <v>0.2459016393442623</v>
+        <v>0.2357991501170757</v>
       </c>
       <c r="N300" s="3" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>525</v>
       </c>
       <c r="P300" s="6" t="n">
-        <v>0.1475409836065574</v>
+        <v>0.1382360593183592</v>
       </c>
       <c r="Q300" s="10" t="inlineStr">
         <is>
@@ -22926,13 +22926,13 @@
         </is>
       </c>
       <c r="D301" s="15" t="n">
-        <v>499.67</v>
+        <v>496.28</v>
       </c>
       <c r="E301" s="25" t="n">
-        <v>-0.0659</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="F301" s="25" t="n">
-        <v>-0.0863</v>
+        <v>-0.1132</v>
       </c>
       <c r="G301" s="17" t="n">
         <v>46329</v>
@@ -22961,7 +22961,7 @@
         <v>616</v>
       </c>
       <c r="M301" s="16" t="n">
-        <v>0.232813657013629</v>
+        <v>0.2412347868138955</v>
       </c>
       <c r="N301" s="14" t="inlineStr"/>
       <c r="O301" s="19" t="n"/>
@@ -23005,13 +23005,13 @@
         </is>
       </c>
       <c r="D302" s="4" t="n">
-        <v>242.4</v>
+        <v>243.74</v>
       </c>
       <c r="E302" s="5" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="F302" s="6" t="n">
-        <v>0.0052</v>
+        <v>-0.0037</v>
+      </c>
+      <c r="F302" s="5" t="n">
+        <v>-0.0154</v>
       </c>
       <c r="G302" s="7" t="n">
         <v>46321</v>
@@ -23040,7 +23040,7 @@
         <v>283</v>
       </c>
       <c r="M302" s="6" t="n">
-        <v>0.1674917491749175</v>
+        <v>0.1610732748010174</v>
       </c>
       <c r="N302" s="3" t="inlineStr"/>
       <c r="O302" s="9" t="n"/>
@@ -23086,13 +23086,13 @@
         </is>
       </c>
       <c r="D303" s="15" t="n">
-        <v>238.31</v>
+        <v>238.98</v>
       </c>
       <c r="E303" s="25" t="n">
-        <v>-0.0573</v>
-      </c>
-      <c r="F303" s="16" t="n">
-        <v>0.0189</v>
+        <v>-0.0398</v>
+      </c>
+      <c r="F303" s="25" t="n">
+        <v>-0.06059999999999999</v>
       </c>
       <c r="G303" s="17" t="n">
         <v>46316</v>
@@ -23121,7 +23121,7 @@
         <v>246</v>
       </c>
       <c r="M303" s="16" t="n">
-        <v>0.03226889345810079</v>
+        <v>0.02937484308310323</v>
       </c>
       <c r="N303" s="14" t="inlineStr"/>
       <c r="O303" s="19" t="n"/>
@@ -23169,13 +23169,13 @@
         </is>
       </c>
       <c r="D304" s="4" t="n">
-        <v>104.93</v>
+        <v>106.93</v>
       </c>
       <c r="E304" s="5" t="n">
-        <v>-0.0766</v>
+        <v>-0.0557</v>
       </c>
       <c r="F304" s="5" t="n">
-        <v>-0.0775</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="G304" s="7" t="n">
         <v>46322</v>
@@ -23204,7 +23204,7 @@
         <v>130</v>
       </c>
       <c r="M304" s="6" t="n">
-        <v>0.2389211855522729</v>
+        <v>0.2157486205929112</v>
       </c>
       <c r="N304" s="3" t="inlineStr">
         <is>
@@ -23215,7 +23215,7 @@
         <v>128</v>
       </c>
       <c r="P304" s="6" t="n">
-        <v>0.2198608596206994</v>
+        <v>0.1970447956607125</v>
       </c>
       <c r="Q304" s="10" t="inlineStr">
         <is>
@@ -23264,13 +23264,13 @@
         </is>
       </c>
       <c r="D305" s="15" t="n">
-        <v>99.01000000000001</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="E305" s="25" t="n">
-        <v>-0.0886</v>
+        <v>-0.0602</v>
       </c>
       <c r="F305" s="25" t="n">
-        <v>-0.055</v>
+        <v>-0.0658</v>
       </c>
       <c r="G305" s="17" t="n">
         <v>46301</v>
@@ -23299,7 +23299,7 @@
         <v>135</v>
       </c>
       <c r="M305" s="16" t="n">
-        <v>0.3634986365013634</v>
+        <v>0.3505402160864347</v>
       </c>
       <c r="N305" s="14" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>125</v>
       </c>
       <c r="P305" s="16" t="n">
-        <v>0.2624987375012625</v>
+        <v>0.2505002000800321</v>
       </c>
       <c r="Q305" s="20" t="inlineStr"/>
       <c r="R305" s="19" t="n"/>
@@ -23345,13 +23345,13 @@
         </is>
       </c>
       <c r="D306" s="4" t="n">
-        <v>321.31</v>
+        <v>325.95</v>
       </c>
       <c r="E306" s="5" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.0599</v>
       </c>
       <c r="F306" s="6" t="n">
-        <v>0.0347</v>
+        <v>0.0266</v>
       </c>
       <c r="G306" s="7" t="n">
         <v>46322</v>
@@ -23380,7 +23380,7 @@
         <v>350</v>
       </c>
       <c r="M306" s="6" t="n">
-        <v>0.08929071613083937</v>
+        <v>0.07378432274888791</v>
       </c>
       <c r="N306" s="3" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>400</v>
       </c>
       <c r="P306" s="6" t="n">
-        <v>0.2449036755781021</v>
+        <v>0.2271820831415862</v>
       </c>
       <c r="Q306" s="10" t="inlineStr">
         <is>
@@ -23432,13 +23432,13 @@
         </is>
       </c>
       <c r="D307" s="15" t="n">
-        <v>113.66</v>
+        <v>109.2</v>
       </c>
       <c r="E307" s="16" t="n">
-        <v>0.0471</v>
+        <v>0.0872</v>
       </c>
       <c r="F307" s="16" t="n">
-        <v>0.5115999999999999</v>
+        <v>0.4646</v>
       </c>
       <c r="G307" s="17" t="n"/>
       <c r="H307" s="22" t="inlineStr">
@@ -23479,13 +23479,13 @@
         </is>
       </c>
       <c r="D308" s="4" t="n">
-        <v>51.15</v>
+        <v>51.33</v>
       </c>
       <c r="E308" s="5" t="n">
-        <v>-0.09630000000000001</v>
+        <v>-0.0141</v>
       </c>
       <c r="F308" s="5" t="n">
-        <v>-0.094</v>
+        <v>-0.0183</v>
       </c>
       <c r="G308" s="7" t="n">
         <v>46267</v>
@@ -23540,13 +23540,13 @@
         </is>
       </c>
       <c r="D309" s="15" t="n">
-        <v>67.62</v>
+        <v>67.3</v>
       </c>
       <c r="E309" s="25" t="n">
-        <v>-0.08470000000000001</v>
+        <v>-0.09759999999999999</v>
       </c>
       <c r="F309" s="25" t="n">
-        <v>-0.1527</v>
+        <v>-0.1653</v>
       </c>
       <c r="G309" s="17" t="n">
         <v>46315</v>
@@ -23575,14 +23575,14 @@
         <v>83</v>
       </c>
       <c r="M309" s="16" t="n">
-        <v>0.2274475007394261</v>
+        <v>0.2332838038632987</v>
       </c>
       <c r="N309" s="14" t="inlineStr"/>
       <c r="O309" s="19" t="n">
         <v>87</v>
       </c>
       <c r="P309" s="16" t="n">
-        <v>0.2866015971606033</v>
+        <v>0.2927191679049035</v>
       </c>
       <c r="Q309" s="20" t="inlineStr"/>
       <c r="R309" s="19" t="n"/>
@@ -23617,13 +23617,13 @@
         </is>
       </c>
       <c r="D310" s="4" t="n">
-        <v>174.6</v>
+        <v>175.77</v>
       </c>
       <c r="E310" s="5" t="n">
-        <v>-0.0068</v>
+        <v>-0.0147</v>
       </c>
       <c r="F310" s="6" t="n">
-        <v>0.0604</v>
+        <v>0.0546</v>
       </c>
       <c r="G310" s="7" t="n">
         <v>46322</v>
@@ -23652,7 +23652,7 @@
         <v>200</v>
       </c>
       <c r="M310" s="6" t="n">
-        <v>0.145475372279496</v>
+        <v>0.1378506002161916</v>
       </c>
       <c r="N310" s="3" t="inlineStr"/>
       <c r="O310" s="9" t="n"/>
@@ -23700,13 +23700,13 @@
         </is>
       </c>
       <c r="D311" s="15" t="n">
-        <v>143.21</v>
+        <v>140.91</v>
       </c>
       <c r="E311" s="25" t="n">
-        <v>-0.0584</v>
+        <v>-0.0725</v>
       </c>
       <c r="F311" s="16" t="n">
-        <v>0.0565</v>
+        <v>0.0104</v>
       </c>
       <c r="G311" s="17" t="n">
         <v>46317</v>
@@ -23765,13 +23765,13 @@
         </is>
       </c>
       <c r="D312" s="4" t="n">
-        <v>186.33</v>
+        <v>186.38</v>
       </c>
       <c r="E312" s="5" t="n">
-        <v>-0.0225</v>
-      </c>
-      <c r="F312" s="6" t="n">
-        <v>0.039</v>
+        <v>-0.0115</v>
+      </c>
+      <c r="F312" s="5" t="n">
+        <v>-0.0638</v>
       </c>
       <c r="G312" s="7" t="n">
         <v>46317</v>
@@ -23800,7 +23800,7 @@
         <v>220</v>
       </c>
       <c r="M312" s="6" t="n">
-        <v>0.1807009069929694</v>
+        <v>0.1803841613907072</v>
       </c>
       <c r="N312" s="3" t="inlineStr">
         <is>
@@ -23811,7 +23811,7 @@
         <v>230</v>
       </c>
       <c r="P312" s="6" t="n">
-        <v>0.2343691300381044</v>
+        <v>0.2340379869084666</v>
       </c>
       <c r="Q312" s="10" t="inlineStr">
         <is>
@@ -23852,13 +23852,13 @@
         </is>
       </c>
       <c r="D313" s="15" t="n">
-        <v>1057.26</v>
-      </c>
-      <c r="E313" s="25" t="n">
-        <v>-0.0076</v>
-      </c>
-      <c r="F313" s="16" t="n">
-        <v>0.0229</v>
+        <v>1056.62</v>
+      </c>
+      <c r="E313" s="16" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="F313" s="25" t="n">
+        <v>-0.0255</v>
       </c>
       <c r="G313" s="17" t="n">
         <v>46330</v>
@@ -23887,7 +23887,7 @@
         <v>1200</v>
       </c>
       <c r="M313" s="16" t="n">
-        <v>0.1350093638272516</v>
+        <v>0.1356968446556001</v>
       </c>
       <c r="N313" s="14" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>1240</v>
       </c>
       <c r="P313" s="16" t="n">
-        <v>0.17284300928816</v>
+        <v>0.17355340614412</v>
       </c>
       <c r="Q313" s="20" t="inlineStr">
         <is>
@@ -23943,13 +23943,13 @@
         </is>
       </c>
       <c r="D314" s="4" t="n">
-        <v>110.63</v>
+        <v>110.61</v>
       </c>
       <c r="E314" s="5" t="n">
-        <v>-0.05230000000000001</v>
+        <v>-0.059</v>
       </c>
       <c r="F314" s="5" t="n">
-        <v>-0.1138</v>
+        <v>-0.1227</v>
       </c>
       <c r="G314" s="7" t="n">
         <v>46325</v>
@@ -23978,7 +23978,7 @@
         <v>129</v>
       </c>
       <c r="M314" s="6" t="n">
-        <v>0.1660489921359487</v>
+        <v>0.1662598318416056</v>
       </c>
       <c r="N314" s="3" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>122</v>
       </c>
       <c r="P314" s="6" t="n">
-        <v>0.1027750158184941</v>
+        <v>0.1029744146098906</v>
       </c>
       <c r="Q314" s="10" t="inlineStr">
         <is>
@@ -24030,13 +24030,13 @@
         </is>
       </c>
       <c r="D315" s="15" t="n">
-        <v>56.65</v>
+        <v>56.72</v>
       </c>
       <c r="E315" s="25" t="n">
-        <v>-0.095</v>
+        <v>-0.1022</v>
       </c>
       <c r="F315" s="25" t="n">
-        <v>-0.1247</v>
+        <v>-0.1354</v>
       </c>
       <c r="G315" s="17" t="n">
         <v>46328</v>
@@ -24065,14 +24065,14 @@
         <v>65</v>
       </c>
       <c r="M315" s="16" t="n">
-        <v>0.147396293027361</v>
+        <v>0.1459802538787024</v>
       </c>
       <c r="N315" s="14" t="inlineStr"/>
       <c r="O315" s="19" t="n">
         <v>67</v>
       </c>
       <c r="P315" s="16" t="n">
-        <v>0.1827007943512798</v>
+        <v>0.1812411847672779</v>
       </c>
       <c r="Q315" s="20" t="inlineStr">
         <is>
@@ -24113,13 +24113,13 @@
         </is>
       </c>
       <c r="D316" s="4" t="n">
-        <v>135.82</v>
+        <v>134.76</v>
       </c>
       <c r="E316" s="5" t="n">
-        <v>-0.04219999999999999</v>
+        <v>-0.06</v>
       </c>
       <c r="F316" s="5" t="n">
-        <v>-0.0641</v>
+        <v>-0.0872</v>
       </c>
       <c r="G316" s="7" t="n">
         <v>46310</v>
@@ -24148,7 +24148,7 @@
         <v>167</v>
       </c>
       <c r="M316" s="6" t="n">
-        <v>0.2295685466058019</v>
+        <v>0.2392401306025528</v>
       </c>
       <c r="N316" s="3" t="inlineStr"/>
       <c r="O316" s="9" t="n"/>
@@ -24192,13 +24192,13 @@
         </is>
       </c>
       <c r="D317" s="15" t="n">
-        <v>296.67</v>
+        <v>295.55</v>
       </c>
       <c r="E317" s="25" t="n">
-        <v>-0.0801</v>
+        <v>-0.09050000000000001</v>
       </c>
       <c r="F317" s="25" t="n">
-        <v>-0.0582</v>
+        <v>-0.08349999999999999</v>
       </c>
       <c r="G317" s="17" t="n">
         <v>46330</v>
@@ -24234,7 +24234,7 @@
         <v>316</v>
       </c>
       <c r="P317" s="16" t="n">
-        <v>0.06515657127448</v>
+        <v>0.06919302994417184</v>
       </c>
       <c r="Q317" s="20" t="inlineStr">
         <is>
@@ -24275,13 +24275,13 @@
         </is>
       </c>
       <c r="D318" s="4" t="n">
-        <v>204.98</v>
+        <v>205.22</v>
       </c>
       <c r="E318" s="5" t="n">
-        <v>-0.061</v>
+        <v>-0.0703</v>
       </c>
       <c r="F318" s="5" t="n">
-        <v>-0.0898</v>
+        <v>-0.1069</v>
       </c>
       <c r="G318" s="7" t="n">
         <v>46328</v>
@@ -24317,7 +24317,7 @@
         <v>215</v>
       </c>
       <c r="P318" s="6" t="n">
-        <v>0.04888281783588648</v>
+        <v>0.04765617386219667</v>
       </c>
       <c r="Q318" s="10" t="inlineStr">
         <is>
@@ -24358,13 +24358,13 @@
         </is>
       </c>
       <c r="D319" s="15" t="n">
-        <v>113.74</v>
+        <v>114.13</v>
       </c>
       <c r="E319" s="25" t="n">
-        <v>-0.06509999999999999</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="F319" s="25" t="n">
-        <v>-0.0522</v>
+        <v>-0.06320000000000001</v>
       </c>
       <c r="G319" s="17" t="n">
         <v>46330</v>
@@ -24393,7 +24393,7 @@
         <v>142</v>
       </c>
       <c r="M319" s="16" t="n">
-        <v>0.2484614032002814</v>
+        <v>0.2441952159817752</v>
       </c>
       <c r="N319" s="14" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>137</v>
       </c>
       <c r="P319" s="16" t="n">
-        <v>0.2045014946368912</v>
+        <v>0.2003855252781916</v>
       </c>
       <c r="Q319" s="20" t="inlineStr">
         <is>
@@ -24453,13 +24453,13 @@
         </is>
       </c>
       <c r="D320" s="4" t="n">
-        <v>232.76</v>
+        <v>231.28</v>
       </c>
       <c r="E320" s="5" t="n">
-        <v>-0.027</v>
+        <v>-0.0364</v>
       </c>
       <c r="F320" s="5" t="n">
-        <v>-0.0578</v>
+        <v>-0.0825</v>
       </c>
       <c r="G320" s="7" t="n">
         <v>46321</v>
@@ -24488,7 +24488,7 @@
         <v>237</v>
       </c>
       <c r="M320" s="6" t="n">
-        <v>0.01821618834851353</v>
+        <v>0.02473192666897267</v>
       </c>
       <c r="N320" s="3" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>236</v>
       </c>
       <c r="P320" s="6" t="n">
-        <v>0.01391991751159997</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="Q320" s="10" t="inlineStr">
         <is>
@@ -24540,13 +24540,13 @@
         </is>
       </c>
       <c r="D321" s="15" t="n">
-        <v>158.27</v>
+        <v>158.07</v>
       </c>
       <c r="E321" s="25" t="n">
-        <v>-0.05139999999999999</v>
+        <v>-0.0581</v>
       </c>
       <c r="F321" s="25" t="n">
-        <v>-0.111</v>
+        <v>-0.118</v>
       </c>
       <c r="G321" s="17" t="n">
         <v>46330</v>
@@ -24575,7 +24575,7 @@
         <v>200</v>
       </c>
       <c r="M321" s="16" t="n">
-        <v>0.2636633600808744</v>
+        <v>0.2652622255962549</v>
       </c>
       <c r="N321" s="14" t="inlineStr"/>
       <c r="O321" s="19" t="n"/>
@@ -24619,13 +24619,13 @@
         </is>
       </c>
       <c r="D322" s="4" t="n">
-        <v>133.97</v>
+        <v>134.04</v>
       </c>
       <c r="E322" s="5" t="n">
-        <v>-0.0105</v>
+        <v>-0.042</v>
       </c>
       <c r="F322" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0046</v>
       </c>
       <c r="G322" s="7" t="n">
         <v>46330</v>
@@ -24654,7 +24654,7 @@
         <v>131</v>
       </c>
       <c r="M322" s="5" t="n">
-        <v>-0.02216914234530118</v>
+        <v>-0.02267979707549979</v>
       </c>
       <c r="N322" s="3" t="inlineStr"/>
       <c r="O322" s="9" t="n"/>
@@ -24698,13 +24698,13 @@
         </is>
       </c>
       <c r="D323" s="15" t="n">
-        <v>29.95</v>
+        <v>30.3</v>
       </c>
       <c r="E323" s="25" t="n">
-        <v>-0.0992</v>
+        <v>-0.0786</v>
       </c>
       <c r="F323" s="25" t="n">
-        <v>-0.1089</v>
+        <v>-0.0965</v>
       </c>
       <c r="G323" s="17" t="n">
         <v>46330</v>
@@ -24777,13 +24777,13 @@
         </is>
       </c>
       <c r="D324" s="4" t="n">
-        <v>35.83</v>
+        <v>36.21</v>
       </c>
       <c r="E324" s="5" t="n">
-        <v>-0.0801</v>
+        <v>-0.0609</v>
       </c>
       <c r="F324" s="5" t="n">
-        <v>-0.1269</v>
+        <v>-0.1142</v>
       </c>
       <c r="G324" s="7" t="n">
         <v>46332</v>
@@ -24838,13 +24838,13 @@
         </is>
       </c>
       <c r="D325" s="15" t="n">
-        <v>262.11</v>
+        <v>263.64</v>
       </c>
       <c r="E325" s="25" t="n">
-        <v>-0.0395</v>
+        <v>-0.0358</v>
       </c>
       <c r="F325" s="25" t="n">
-        <v>-0.0489</v>
+        <v>-0.0391</v>
       </c>
       <c r="G325" s="17" t="n">
         <v>46332</v>
@@ -24873,7 +24873,7 @@
         <v>384</v>
       </c>
       <c r="M325" s="16" t="n">
-        <v>0.46503376445004</v>
+        <v>0.456531634046427</v>
       </c>
       <c r="N325" s="14" t="inlineStr">
         <is>
@@ -24884,7 +24884,7 @@
         <v>380</v>
       </c>
       <c r="P325" s="16" t="n">
-        <v>0.4497729960703521</v>
+        <v>0.4413594295251101</v>
       </c>
       <c r="Q325" s="20" t="inlineStr"/>
       <c r="R325" s="19" t="n"/>
@@ -24927,13 +24927,13 @@
         </is>
       </c>
       <c r="D326" s="4" t="n">
-        <v>64.7</v>
+        <v>64.86</v>
       </c>
       <c r="E326" s="5" t="n">
-        <v>-0.05230000000000001</v>
+        <v>-0.052</v>
       </c>
       <c r="F326" s="5" t="n">
-        <v>-0.1274</v>
+        <v>-0.1317</v>
       </c>
       <c r="G326" s="7" t="n">
         <v>46324</v>
@@ -24962,7 +24962,7 @@
         <v>79</v>
       </c>
       <c r="M326" s="6" t="n">
-        <v>0.2210200927357032</v>
+        <v>0.2180080172679618</v>
       </c>
       <c r="N326" s="3" t="inlineStr"/>
       <c r="O326" s="9" t="n"/>
@@ -25014,13 +25014,13 @@
         </is>
       </c>
       <c r="D327" s="15" t="n">
-        <v>116.74</v>
+        <v>116.8</v>
       </c>
       <c r="E327" s="25" t="n">
-        <v>-0.0259</v>
+        <v>-0.0424</v>
       </c>
       <c r="F327" s="25" t="n">
-        <v>-0.0969</v>
+        <v>-0.1051</v>
       </c>
       <c r="G327" s="17" t="n">
         <v>46331</v>
@@ -25049,7 +25049,7 @@
         <v>136</v>
       </c>
       <c r="M327" s="16" t="n">
-        <v>0.1649820113071784</v>
+        <v>0.1643835616438356</v>
       </c>
       <c r="N327" s="14" t="inlineStr">
         <is>
@@ -25060,7 +25060,7 @@
         <v>140</v>
       </c>
       <c r="P327" s="16" t="n">
-        <v>0.1992461881103307</v>
+        <v>0.1986301369863014</v>
       </c>
       <c r="Q327" s="20" t="inlineStr">
         <is>
@@ -25101,13 +25101,13 @@
         </is>
       </c>
       <c r="D328" s="4" t="n">
-        <v>101.58</v>
+        <v>101.76</v>
       </c>
       <c r="E328" s="5" t="n">
-        <v>-0.0291</v>
+        <v>-0.0381</v>
       </c>
       <c r="F328" s="5" t="n">
-        <v>-0.1228</v>
+        <v>-0.1224</v>
       </c>
       <c r="G328" s="7" t="n">
         <v>46330</v>
@@ -25136,7 +25136,7 @@
         <v>131</v>
       </c>
       <c r="M328" s="6" t="n">
-        <v>0.2896239417208112</v>
+        <v>0.2873427672955974</v>
       </c>
       <c r="N328" s="3" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>121</v>
       </c>
       <c r="P328" s="6" t="n">
-        <v>0.1911793660169325</v>
+        <v>0.1890723270440251</v>
       </c>
       <c r="Q328" s="10" t="inlineStr">
         <is>
@@ -25192,13 +25192,13 @@
         </is>
       </c>
       <c r="D329" s="15" t="n">
-        <v>79.63</v>
+        <v>79.64</v>
       </c>
       <c r="E329" s="25" t="n">
-        <v>-0.0481</v>
+        <v>-0.053</v>
       </c>
       <c r="F329" s="25" t="n">
-        <v>-0.1132</v>
+        <v>-0.1129</v>
       </c>
       <c r="G329" s="17" t="n">
         <v>46322</v>
@@ -25234,7 +25234,7 @@
         <v>107</v>
       </c>
       <c r="P329" s="16" t="n">
-        <v>0.3437146803968354</v>
+        <v>0.3435459568056253</v>
       </c>
       <c r="Q329" s="20" t="inlineStr">
         <is>
@@ -25283,13 +25283,13 @@
         </is>
       </c>
       <c r="D330" s="4" t="n">
-        <v>52.92</v>
+        <v>53.27</v>
       </c>
       <c r="E330" s="5" t="n">
-        <v>-0.0112</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F330" s="5" t="n">
-        <v>-0.1092</v>
+        <v>-0.1129</v>
       </c>
       <c r="G330" s="7" t="n"/>
       <c r="H330" s="12" t="inlineStr">
@@ -25308,7 +25308,7 @@
         <v>63</v>
       </c>
       <c r="M330" s="6" t="n">
-        <v>0.1904761904761904</v>
+        <v>0.1826544021024966</v>
       </c>
       <c r="N330" s="3" t="inlineStr"/>
       <c r="O330" s="9" t="n"/>
@@ -25352,13 +25352,13 @@
         </is>
       </c>
       <c r="D331" s="15" t="n">
-        <v>40.18</v>
-      </c>
-      <c r="E331" s="25" t="n">
-        <v>-0.0454</v>
-      </c>
-      <c r="F331" s="25" t="n">
-        <v>-0.0868</v>
+        <v>40.49</v>
+      </c>
+      <c r="E331" s="16" t="n">
+        <v>0.0203</v>
+      </c>
+      <c r="F331" s="16" t="n">
+        <v>0.0061</v>
       </c>
       <c r="G331" s="17" t="n">
         <v>46336</v>
@@ -25413,13 +25413,13 @@
         </is>
       </c>
       <c r="D332" s="4" t="n">
-        <v>8.789999999999999</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="E332" s="5" t="n">
-        <v>-0.0649</v>
-      </c>
-      <c r="F332" s="5" t="n">
-        <v>-0.0023</v>
+        <v>-0.0204</v>
+      </c>
+      <c r="F332" s="6" t="n">
+        <v>0.0958</v>
       </c>
       <c r="G332" s="7" t="n">
         <v>46331</v>
@@ -25474,13 +25474,13 @@
         </is>
       </c>
       <c r="D333" s="15" t="n">
-        <v>85.45999999999999</v>
+        <v>85.42</v>
       </c>
       <c r="E333" s="25" t="n">
-        <v>-0.0391</v>
+        <v>-0.0519</v>
       </c>
       <c r="F333" s="25" t="n">
-        <v>-0.1153</v>
+        <v>-0.1216</v>
       </c>
       <c r="G333" s="17" t="n">
         <v>46324</v>
@@ -25509,7 +25509,7 @@
         <v>99</v>
       </c>
       <c r="M333" s="16" t="n">
-        <v>0.1584366955300726</v>
+        <v>0.1589791617888082</v>
       </c>
       <c r="N333" s="14" t="inlineStr">
         <is>
@@ -25520,7 +25520,7 @@
         <v>112</v>
       </c>
       <c r="P333" s="16" t="n">
-        <v>0.310554645448163</v>
+        <v>0.3111683446499648</v>
       </c>
       <c r="Q333" s="20" t="inlineStr">
         <is>
@@ -25561,13 +25561,13 @@
         </is>
       </c>
       <c r="D334" s="4" t="n">
-        <v>103.48</v>
+        <v>103.54</v>
       </c>
       <c r="E334" s="5" t="n">
-        <v>-0.0239</v>
+        <v>-0.0375</v>
       </c>
       <c r="F334" s="5" t="n">
-        <v>-0.098</v>
+        <v>-0.1056</v>
       </c>
       <c r="G334" s="7" t="n">
         <v>46324</v>
@@ -25596,7 +25596,7 @@
         <v>127</v>
       </c>
       <c r="M334" s="6" t="n">
-        <v>0.2272902976420564</v>
+        <v>0.2265790998647865</v>
       </c>
       <c r="N334" s="3" t="inlineStr"/>
       <c r="O334" s="9" t="n"/>
@@ -27292,7 +27292,11 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F42" s="14" t="inlineStr"/>
+      <c r="F42" s="14" t="inlineStr">
+        <is>
+          <t>Before open</t>
+        </is>
+      </c>
       <c r="G42" s="33" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -27328,7 +27332,11 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="F43" s="14" t="inlineStr"/>
+      <c r="F43" s="14" t="inlineStr">
+        <is>
+          <t>Before open</t>
+        </is>
+      </c>
       <c r="G43" s="33" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -28228,7 +28236,11 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="F67" s="14" t="inlineStr"/>
+      <c r="F67" s="14" t="inlineStr">
+        <is>
+          <t>Before open</t>
+        </is>
+      </c>
       <c r="G67" s="33" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -28431,20 +28443,24 @@
       </c>
       <c r="C73" s="13" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D73" s="14" t="inlineStr">
         <is>
-          <t>Pool Corp</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="F73" s="14" t="inlineStr"/>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="F73" s="14" t="inlineStr">
+        <is>
+          <t>Before open</t>
+        </is>
+      </c>
       <c r="G73" s="33" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -28467,17 +28483,17 @@
       </c>
       <c r="C74" s="13" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>Roper Technologies</t>
+          <t>Pool Corp</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr"/>
@@ -28493,78 +28509,78 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="28" t="n">
+      <c r="A75" s="32" t="n">
         <v>46317</v>
       </c>
-      <c r="B75" s="29" t="inlineStr">
+      <c r="B75" s="14" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C75" s="30" t="inlineStr">
+      <c r="C75" s="13" t="inlineStr">
+        <is>
+          <t>ROP</t>
+        </is>
+      </c>
+      <c r="D75" s="14" t="inlineStr">
+        <is>
+          <t>Roper Technologies</t>
+        </is>
+      </c>
+      <c r="E75" s="14" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F75" s="14" t="inlineStr"/>
+      <c r="G75" s="33" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H75" s="14" t="inlineStr">
+        <is>
+          <t>Nasdaq</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="28" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B76" s="29" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C76" s="30" t="inlineStr">
         <is>
           <t>TMUS</t>
         </is>
       </c>
-      <c r="D75" s="29" t="inlineStr">
+      <c r="D76" s="29" t="inlineStr">
         <is>
           <t>T-Mobile US</t>
         </is>
       </c>
-      <c r="E75" s="29" t="inlineStr">
+      <c r="E76" s="29" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="F75" s="29" t="inlineStr">
+      <c r="F76" s="29" t="inlineStr">
         <is>
           <t>After close</t>
         </is>
       </c>
-      <c r="G75" s="31" t="inlineStr">
+      <c r="G76" s="31" t="inlineStr">
         <is>
           <t>Estimated</t>
         </is>
       </c>
-      <c r="H75" s="29" t="inlineStr">
+      <c r="H76" s="29" t="inlineStr">
         <is>
           <t>CoinCodex</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="32" t="n">
-        <v>46317</v>
-      </c>
-      <c r="B76" s="14" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="C76" s="13" t="inlineStr">
-        <is>
-          <t>TSCO</t>
-        </is>
-      </c>
-      <c r="D76" s="14" t="inlineStr">
-        <is>
-          <t>Tractor Supply</t>
-        </is>
-      </c>
-      <c r="E76" s="14" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="F76" s="14" t="inlineStr"/>
-      <c r="G76" s="33" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H76" s="14" t="inlineStr">
-        <is>
-          <t>Nasdaq</t>
         </is>
       </c>
     </row>
@@ -28579,17 +28595,17 @@
       </c>
       <c r="C77" s="13" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>TSCO</t>
         </is>
       </c>
       <c r="D77" s="14" t="inlineStr">
         <is>
-          <t>Union Pacific</t>
+          <t>Tractor Supply</t>
         </is>
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F77" s="14" t="inlineStr"/>
@@ -28606,33 +28622,29 @@
     </row>
     <row r="78">
       <c r="A78" s="32" t="n">
-        <v>46318</v>
+        <v>46317</v>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C78" s="13" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Union Pacific</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F78" s="14" t="inlineStr">
-        <is>
-          <t>Before open</t>
-        </is>
-      </c>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F78" s="14" t="inlineStr"/>
       <c r="G78" s="33" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -28655,20 +28667,24 @@
       </c>
       <c r="C79" s="13" t="inlineStr">
         <is>
-          <t>CORZ</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="D79" s="14" t="inlineStr">
         <is>
-          <t>Core Scientific</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="E79" s="14" t="inlineStr">
         <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="F79" s="14" t="inlineStr"/>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F79" s="14" t="inlineStr">
+        <is>
+          <t>Before open</t>
+        </is>
+      </c>
       <c r="G79" s="33" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -28691,17 +28707,17 @@
       </c>
       <c r="C80" s="13" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>CORZ</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>Core Scientific</t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F80" s="14" t="inlineStr"/>
@@ -28727,12 +28743,12 @@
       </c>
       <c r="C81" s="13" t="inlineStr">
         <is>
-          <t>ITW</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D81" s="14" t="inlineStr">
         <is>
-          <t>Illinois Tool Works</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="E81" s="14" t="inlineStr">
@@ -28763,17 +28779,17 @@
       </c>
       <c r="C82" s="13" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>ITW</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Illinois Tool Works</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F82" s="14" t="inlineStr"/>
@@ -37334,13 +37350,13 @@
       <c r="D36" s="38" t="inlineStr">
         <is>
           <t>22
-BKR BX CBRE DLR DOW FCX FIX HON INTC KNSL POOL ROP TMUS TSCO UNP</t>
+BKR BX CBRE DLR DOW FCX FIX HON INTC KNSL PG POOL ROP TMUS TSCO UNP</t>
         </is>
       </c>
       <c r="E36" s="38" t="inlineStr">
         <is>
           <t>23
-AXP CORZ GD ITW PG</t>
+AXP CORZ GD ITW</t>
         </is>
       </c>
       <c r="F36" s="38" t="inlineStr">
@@ -37861,7 +37877,7 @@
     <row r="2">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>Data as of September 21, 2026 at 21:16 UTC</t>
+          <t>Data as of September 22, 2026 at 15:11 UTC</t>
         </is>
       </c>
     </row>

--- a/earnings-data.xlsx
+++ b/earnings-data.xlsx
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>103.76</v>
+        <v>103.46</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>-0.0619</v>
+        <v>-0.0646</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>0.094</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="G2" s="7" t="n">
         <v>46338</v>
@@ -878,7 +878,7 @@
         <v>125</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.2047031611410948</v>
+        <v>0.2081964044075006</v>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>144</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.3878180416345412</v>
+        <v>0.3918422578774406</v>
       </c>
       <c r="Q2" s="10" t="inlineStr">
         <is>
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="D3" s="15" t="n">
-        <v>342.15</v>
+        <v>337.83</v>
       </c>
       <c r="E3" s="16" t="n">
-        <v>-0.017</v>
+        <v>-0.0294</v>
       </c>
       <c r="F3" s="17" t="n">
-        <v>0.0701</v>
+        <v>0.0566</v>
       </c>
       <c r="G3" s="18" t="n">
         <v>46322</v>
@@ -973,7 +973,7 @@
         <v>438</v>
       </c>
       <c r="M3" s="17" t="n">
-        <v>0.2801402893467778</v>
+        <v>0.2965100790338336</v>
       </c>
       <c r="N3" s="14" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>420</v>
       </c>
       <c r="P3" s="17" t="n">
-        <v>0.2275317843051294</v>
+        <v>0.2432288429091556</v>
       </c>
       <c r="Q3" s="21" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>746.47</v>
+        <v>744.1</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>0.3353</v>
+        <v>0.3311</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.2542</v>
+        <v>0.2502</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>46330</v>
@@ -1064,7 +1064,7 @@
         <v>835</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.118598202205045</v>
+        <v>0.1221609998656094</v>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>930</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.2458638659289723</v>
+        <v>0.2498320118263674</v>
       </c>
       <c r="Q4" s="10" t="inlineStr">
         <is>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="D5" s="15" t="n">
-        <v>39.82</v>
+        <v>40.48</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>-0.0458</v>
+        <v>-0.03</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>0.0504</v>
+        <v>0.0678</v>
       </c>
       <c r="G5" s="18" t="n">
         <v>46329</v>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>71.70999999999999</v>
+        <v>71.36</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>-0.1037</v>
+        <v>-0.1081</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.0231</v>
+        <v>0.0181</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>46315</v>
@@ -1220,7 +1220,7 @@
         <v>80</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.1156045181982988</v>
+        <v>0.1210762331838565</v>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>100</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.3945056477478735</v>
+        <v>0.4013452914798206</v>
       </c>
       <c r="Q6" s="10" t="inlineStr">
         <is>
@@ -1272,13 +1272,13 @@
         </is>
       </c>
       <c r="D7" s="15" t="n">
-        <v>75.69</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>-0.1489</v>
+        <v>-0.1512</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>-0.0498</v>
+        <v>-0.05230000000000001</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>46315</v>
@@ -1307,7 +1307,7 @@
         <v>91</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>0.2022724270048884</v>
+        <v>0.2054576765134456</v>
       </c>
       <c r="N7" s="14" t="inlineStr"/>
       <c r="O7" s="20" t="n"/>
@@ -1351,13 +1351,13 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>501.3</v>
+        <v>510.4</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-0.0679</v>
+        <v>-0.051</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.0386</v>
+        <v>0.0575</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>46329</v>
@@ -1386,7 +1386,7 @@
         <v>569.9299999999999</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.1369040494713743</v>
+        <v>0.1166340125391849</v>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>648.04</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.292718930779972</v>
+        <v>0.2696708463949843</v>
       </c>
       <c r="Q8" s="10" t="inlineStr">
         <is>
@@ -1438,13 +1438,13 @@
         </is>
       </c>
       <c r="D9" s="15" t="n">
-        <v>189.83</v>
+        <v>189.08</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>-0.0186</v>
+        <v>-0.0224</v>
       </c>
       <c r="F9" s="17" t="n">
-        <v>0.051</v>
+        <v>0.04679999999999999</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>46330</v>
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>164.61</v>
+        <v>165.66</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.0929</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.0801</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>46317</v>
@@ -1542,7 +1542,7 @@
         <v>170</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.03274406172164501</v>
+        <v>0.02619823735361586</v>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>270</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.6402405686167303</v>
+        <v>0.629844259326331</v>
       </c>
       <c r="Q10" s="10" t="inlineStr">
         <is>
@@ -1594,13 +1594,13 @@
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>46.9</v>
+        <v>46.52</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="F11" s="17" t="n">
-        <v>0.0113</v>
+        <v>0.003</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>46316</v>
@@ -1629,7 +1629,7 @@
         <v>43</v>
       </c>
       <c r="M11" s="16" t="n">
-        <v>-0.0831556503198294</v>
+        <v>-0.07566638005159078</v>
       </c>
       <c r="N11" s="14" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>50</v>
       </c>
       <c r="P11" s="17" t="n">
-        <v>0.06609808102345419</v>
+        <v>0.07480653482373166</v>
       </c>
       <c r="Q11" s="21" t="inlineStr">
         <is>
@@ -1685,13 +1685,13 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>153.66</v>
+        <v>149.58</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-0.1922</v>
+        <v>-0.2136</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.08900000000000001</v>
+        <v>0.0601</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>46331</v>
@@ -1720,7 +1720,7 @@
         <v>181</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.1779252896004165</v>
+        <v>0.2100548201631233</v>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>155</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.008720551867760011</v>
+        <v>0.03623479074742604</v>
       </c>
       <c r="Q12" s="10" t="inlineStr">
         <is>
@@ -1772,13 +1772,13 @@
         </is>
       </c>
       <c r="D13" s="15" t="n">
-        <v>250.74</v>
+        <v>249.27</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>-0.0432</v>
+        <v>-0.0488</v>
       </c>
       <c r="F13" s="17" t="n">
-        <v>0.0803</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>46324</v>
@@ -1807,7 +1807,7 @@
         <v>322</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>0.2841987716359575</v>
+        <v>0.2917719741645605</v>
       </c>
       <c r="N13" s="14" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>285</v>
       </c>
       <c r="P13" s="17" t="n">
-        <v>0.1366355587461115</v>
+        <v>0.1433385485618004</v>
       </c>
       <c r="Q13" s="21" t="inlineStr">
         <is>
@@ -1871,13 +1871,13 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2822.83</v>
+        <v>2843.34</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-0.062</v>
+        <v>-0.0552</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>-0.0455</v>
+        <v>-0.0386</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>46287</v>
@@ -1906,7 +1906,7 @@
         <v>4150</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.470155836518671</v>
+        <v>0.4595510913221774</v>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>3700</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.3107413482214657</v>
+        <v>0.3012865151547123</v>
       </c>
       <c r="Q14" s="10" t="inlineStr">
         <is>
@@ -1958,13 +1958,13 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>94</v>
+        <v>90.8</v>
       </c>
       <c r="E15" s="17" t="n">
-        <v>0.0745</v>
+        <v>0.038</v>
       </c>
       <c r="F15" s="17" t="n">
-        <v>0.1003</v>
+        <v>0.0629</v>
       </c>
       <c r="G15" s="18" t="n"/>
       <c r="H15" s="23" t="inlineStr">
@@ -1983,7 +1983,7 @@
         <v>65</v>
       </c>
       <c r="M15" s="16" t="n">
-        <v>-0.3085106382978723</v>
+        <v>-0.2841409691629956</v>
       </c>
       <c r="N15" s="14" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>85</v>
       </c>
       <c r="P15" s="16" t="n">
-        <v>-0.09574468085106383</v>
+        <v>-0.06387665198237882</v>
       </c>
       <c r="Q15" s="21" t="inlineStr"/>
       <c r="R15" s="20" t="n"/>
@@ -2029,13 +2029,13 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>157</v>
+        <v>155.9</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-0.2642</v>
+        <v>-0.2693</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-0.1153</v>
+        <v>-0.1215</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>46322</v>
@@ -2064,7 +2064,7 @@
         <v>214</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.3630573248407643</v>
+        <v>0.372674791533034</v>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>245</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.5605095541401274</v>
+        <v>0.5715202052597819</v>
       </c>
       <c r="Q16" s="10" t="inlineStr">
         <is>
@@ -2124,13 +2124,13 @@
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>257.83</v>
+        <v>257.33</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>-0.2202</v>
+        <v>-0.2217</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>-0.2633</v>
+        <v>-0.2647</v>
       </c>
       <c r="G17" s="18" t="n"/>
       <c r="H17" s="23" t="inlineStr">
@@ -2149,7 +2149,7 @@
         <v>375</v>
       </c>
       <c r="M17" s="17" t="n">
-        <v>0.4544467284644922</v>
+        <v>0.4572727626005519</v>
       </c>
       <c r="N17" s="14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>375</v>
       </c>
       <c r="P17" s="17" t="n">
-        <v>0.4544467284644922</v>
+        <v>0.4572727626005519</v>
       </c>
       <c r="Q17" s="21" t="inlineStr"/>
       <c r="R17" s="20" t="n"/>
@@ -2199,13 +2199,13 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>32.41</v>
+        <v>32.71</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>-0.1475</v>
+        <v>-0.1397</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0.0195</v>
+        <v>0.0289</v>
       </c>
       <c r="G18" s="7" t="n">
         <v>46323</v>
@@ -2234,7 +2234,7 @@
         <v>45</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.3884603517432892</v>
+        <v>0.3757260776520941</v>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>45</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.3884603517432892</v>
+        <v>0.3757260776520941</v>
       </c>
       <c r="Q18" s="10" t="inlineStr">
         <is>
@@ -2286,13 +2286,13 @@
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>142.23</v>
+        <v>140.17</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>-0.0452</v>
+        <v>-0.0591</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>-0.0309</v>
+        <v>-0.0449</v>
       </c>
       <c r="G19" s="18" t="n">
         <v>46324</v>
@@ -2321,7 +2321,7 @@
         <v>170</v>
       </c>
       <c r="M19" s="17" t="n">
-        <v>0.195247134922309</v>
+        <v>0.2128130127702077</v>
       </c>
       <c r="N19" s="14" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>177</v>
       </c>
       <c r="P19" s="17" t="n">
-        <v>0.24446319341911</v>
+        <v>0.2627523721195692</v>
       </c>
       <c r="Q19" s="21" t="inlineStr">
         <is>
@@ -2373,13 +2373,13 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>132.55</v>
+        <v>132.36</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>-0.2608</v>
+        <v>-0.2619</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>-0.3567</v>
+        <v>-0.3576</v>
       </c>
       <c r="G20" s="7" t="n"/>
       <c r="H20" s="12" t="inlineStr">
@@ -2398,7 +2398,7 @@
         <v>220</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.6597510373443982</v>
+        <v>0.6621335750982168</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="9" t="n"/>
@@ -2442,13 +2442,13 @@
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>113.97</v>
+        <v>113.16</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>-0.1666</v>
+        <v>-0.1725</v>
       </c>
       <c r="F21" s="16" t="n">
-        <v>-0.0538</v>
+        <v>-0.0605</v>
       </c>
       <c r="G21" s="18" t="n"/>
       <c r="H21" s="23" t="inlineStr">
@@ -2493,13 +2493,13 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>83.66</v>
+        <v>83.77</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-0.0382</v>
+        <v>-0.0369</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>0.0123</v>
+        <v>0.0137</v>
       </c>
       <c r="G22" s="7" t="n">
         <v>46315</v>
@@ -2528,7 +2528,7 @@
         <v>61</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>-0.2708582357159933</v>
+        <v>-0.2718156858063746</v>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>100</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.1953143676786996</v>
+        <v>0.1937447773665991</v>
       </c>
       <c r="Q22" s="10" t="inlineStr">
         <is>
@@ -2580,13 +2580,13 @@
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>128.85</v>
+        <v>128.76</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>-0.0504</v>
+        <v>-0.05110000000000001</v>
       </c>
       <c r="F23" s="17" t="n">
-        <v>0.0373</v>
+        <v>0.0366</v>
       </c>
       <c r="G23" s="18" t="n">
         <v>46315</v>
@@ -2618,7 +2618,7 @@
         <v>145</v>
       </c>
       <c r="P23" s="17" t="n">
-        <v>0.1253395421032208</v>
+        <v>0.1261261261261262</v>
       </c>
       <c r="Q23" s="21" t="inlineStr"/>
       <c r="R23" s="20" t="n"/>
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>300.42</v>
+        <v>296.72</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>-0.1097</v>
+        <v>-0.1206</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>-0.0978</v>
+        <v>-0.1089</v>
       </c>
       <c r="G24" s="7" t="n">
         <v>46343</v>
@@ -2688,7 +2688,7 @@
         <v>360</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.1983223487118034</v>
+        <v>0.2132650310056618</v>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>400</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.3314692763464482</v>
+        <v>0.3480722566729575</v>
       </c>
       <c r="Q24" s="10" t="inlineStr">
         <is>
@@ -2748,13 +2748,13 @@
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>193.13</v>
+        <v>191.36</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>-0.1099</v>
+        <v>-0.1181</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>-0.0699</v>
+        <v>-0.0784</v>
       </c>
       <c r="G25" s="18" t="n"/>
       <c r="H25" s="23" t="inlineStr">
@@ -2773,7 +2773,7 @@
         <v>255</v>
       </c>
       <c r="M25" s="17" t="n">
-        <v>0.320354165587946</v>
+        <v>0.332566889632107</v>
       </c>
       <c r="N25" s="14" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>230</v>
       </c>
       <c r="P25" s="17" t="n">
-        <v>0.1909076787655983</v>
+        <v>0.2019230769230768</v>
       </c>
       <c r="Q25" s="21" t="inlineStr">
         <is>
@@ -2829,13 +2829,13 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>238.7</v>
+        <v>238.32</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>-0.1242</v>
+        <v>-0.1256</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>-0.0984</v>
+        <v>-0.0999</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>46330</v>
@@ -2864,7 +2864,7 @@
         <v>300</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.2568077084206117</v>
+        <v>0.2588116817724069</v>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>350</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.466275659824047</v>
+        <v>0.4686136287344747</v>
       </c>
       <c r="Q26" s="10" t="inlineStr">
         <is>
@@ -2916,13 +2916,13 @@
         </is>
       </c>
       <c r="D27" s="15" t="n">
-        <v>36.24</v>
+        <v>36.05</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>-0.1106</v>
+        <v>-0.1153</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>-0.1308</v>
+        <v>-0.1355</v>
       </c>
       <c r="G27" s="18" t="n">
         <v>46289</v>
@@ -2977,13 +2977,13 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>85.34999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>-0.0588</v>
+        <v>-0.0527</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>-0.0235</v>
+        <v>-0.0172</v>
       </c>
       <c r="G28" s="7" t="n">
         <v>46323</v>
@@ -3012,7 +3012,7 @@
         <v>110</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.2888107791446984</v>
+        <v>0.2805587892898719</v>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>115</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.3473930872876392</v>
+        <v>0.338766006984866</v>
       </c>
       <c r="Q28" s="10" t="inlineStr">
         <is>
@@ -3068,13 +3068,13 @@
         </is>
       </c>
       <c r="D29" s="15" t="n">
-        <v>167.03</v>
+        <v>166.61</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>-0.1127</v>
+        <v>-0.1149</v>
       </c>
       <c r="F29" s="16" t="n">
-        <v>-0.0911</v>
+        <v>-0.0934</v>
       </c>
       <c r="G29" s="18" t="n">
         <v>46317</v>
@@ -3129,13 +3129,13 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>235</v>
+        <v>233.98</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>-0.027</v>
+        <v>-0.0312</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>-0.0163</v>
+        <v>-0.0206</v>
       </c>
       <c r="G30" s="7" t="n"/>
       <c r="H30" s="12" t="inlineStr">
@@ -3154,7 +3154,7 @@
         <v>245</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.0425531914893617</v>
+        <v>0.04709804256774088</v>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>265</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.1276595744680851</v>
+        <v>0.1325754337977605</v>
       </c>
       <c r="Q30" s="10" t="inlineStr">
         <is>
@@ -3206,13 +3206,13 @@
         </is>
       </c>
       <c r="D31" s="15" t="n">
-        <v>94.26000000000001</v>
+        <v>94.14</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>-0.1231</v>
+        <v>-0.1242</v>
       </c>
       <c r="F31" s="16" t="n">
-        <v>-0.08710000000000001</v>
+        <v>-0.0882</v>
       </c>
       <c r="G31" s="18" t="n">
         <v>46330</v>
@@ -3241,7 +3241,7 @@
         <v>120</v>
       </c>
       <c r="M31" s="17" t="n">
-        <v>0.273074474856779</v>
+        <v>0.2746972594008923</v>
       </c>
       <c r="N31" s="14" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>115</v>
       </c>
       <c r="P31" s="17" t="n">
-        <v>0.2200297050710799</v>
+        <v>0.2215848735925218</v>
       </c>
       <c r="Q31" s="21" t="inlineStr">
         <is>
@@ -3293,13 +3293,13 @@
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>13.14</v>
+        <v>13.17</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>0.0031</v>
+        <v>0.0053</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>-0.0805</v>
+        <v>-0.0784</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>46330</v>
@@ -3354,13 +3354,13 @@
         </is>
       </c>
       <c r="D33" s="15" t="n">
-        <v>131.85</v>
+        <v>131.59</v>
       </c>
       <c r="E33" s="16" t="n">
-        <v>-0.0629</v>
+        <v>-0.06480000000000001</v>
       </c>
       <c r="F33" s="16" t="n">
-        <v>-0.145</v>
+        <v>-0.1467</v>
       </c>
       <c r="G33" s="18" t="n"/>
       <c r="H33" s="23" t="inlineStr">
@@ -3379,7 +3379,7 @@
         <v>160</v>
       </c>
       <c r="M33" s="17" t="n">
-        <v>0.2135001896094047</v>
+        <v>0.2158978645793753</v>
       </c>
       <c r="N33" s="14" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>175</v>
       </c>
       <c r="P33" s="17" t="n">
-        <v>0.3272658323852864</v>
+        <v>0.3298882893836917</v>
       </c>
       <c r="Q33" s="21" t="inlineStr">
         <is>
@@ -3435,13 +3435,13 @@
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>32.53</v>
+        <v>32.29</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>-0.09420000000000001</v>
+        <v>-0.1011</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>0.0488</v>
+        <v>0.0409</v>
       </c>
       <c r="G34" s="7" t="n">
         <v>46317</v>
@@ -3470,7 +3470,7 @@
         <v>35</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.07592991085152163</v>
+        <v>0.08392691235676683</v>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>40</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.2296341838303105</v>
+        <v>0.2387736141220192</v>
       </c>
       <c r="Q34" s="10" t="inlineStr">
         <is>
@@ -3522,13 +3522,13 @@
         </is>
       </c>
       <c r="D35" s="15" t="n">
-        <v>380.38</v>
+        <v>380.12</v>
       </c>
       <c r="E35" s="17" t="n">
-        <v>0.0901</v>
+        <v>0.08929999999999999</v>
       </c>
       <c r="F35" s="17" t="n">
-        <v>0.2152</v>
+        <v>0.2143</v>
       </c>
       <c r="G35" s="18" t="n">
         <v>46323</v>
@@ -3557,7 +3557,7 @@
         <v>130</v>
       </c>
       <c r="M35" s="16" t="n">
-        <v>-0.6582365003417635</v>
+        <v>-0.6580027359781122</v>
       </c>
       <c r="N35" s="14" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
         <v>300</v>
       </c>
       <c r="P35" s="16" t="n">
-        <v>-0.211315000788685</v>
+        <v>-0.2107755445648743</v>
       </c>
       <c r="Q35" s="21" t="inlineStr">
         <is>
@@ -3609,13 +3609,13 @@
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>69.34999999999999</v>
+        <v>69.42</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>-0.1254</v>
+        <v>-0.1245</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.0516</v>
+        <v>0.0528</v>
       </c>
       <c r="G36" s="7" t="n">
         <v>46329</v>
@@ -3670,13 +3670,13 @@
         </is>
       </c>
       <c r="D37" s="15" t="n">
-        <v>551.37</v>
+        <v>543.8099999999999</v>
       </c>
       <c r="E37" s="17" t="n">
-        <v>0.0234</v>
+        <v>0.009399999999999999</v>
       </c>
       <c r="F37" s="17" t="n">
-        <v>0.1599</v>
+        <v>0.144</v>
       </c>
       <c r="G37" s="18" t="n"/>
       <c r="H37" s="23" t="inlineStr">
@@ -3695,7 +3695,7 @@
         <v>450</v>
       </c>
       <c r="M37" s="16" t="n">
-        <v>-0.1838511344469231</v>
+        <v>-0.1725051028851988</v>
       </c>
       <c r="N37" s="14" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>635</v>
       </c>
       <c r="P37" s="17" t="n">
-        <v>0.1516767325026751</v>
+        <v>0.1676872437064417</v>
       </c>
       <c r="Q37" s="21" t="inlineStr">
         <is>
@@ -3751,13 +3751,13 @@
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>96.13</v>
+        <v>96.02</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>-0.0625</v>
+        <v>-0.0635</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>-0.0155</v>
+        <v>-0.0166</v>
       </c>
       <c r="G38" s="7" t="n">
         <v>46325</v>
@@ -3786,7 +3786,7 @@
         <v>110</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.1442837823780298</v>
+        <v>0.1455946677775464</v>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>105</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.09227088317902846</v>
+        <v>0.09352218287856701</v>
       </c>
       <c r="Q38" s="10" t="inlineStr">
         <is>
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="D39" s="15" t="n">
-        <v>86.66</v>
+        <v>85.93000000000001</v>
       </c>
       <c r="E39" s="16" t="n">
-        <v>-0.0636</v>
+        <v>-0.07150000000000001</v>
       </c>
       <c r="F39" s="16" t="n">
-        <v>-0.0451</v>
+        <v>-0.05309999999999999</v>
       </c>
       <c r="G39" s="18" t="n">
         <v>46325</v>
@@ -3877,7 +3877,7 @@
         <v>95</v>
       </c>
       <c r="M39" s="17" t="n">
-        <v>0.09623817216708982</v>
+        <v>0.1055510299080646</v>
       </c>
       <c r="N39" s="14" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>100</v>
       </c>
       <c r="P39" s="17" t="n">
-        <v>0.1539349180706209</v>
+        <v>0.1637379262190154</v>
       </c>
       <c r="Q39" s="21" t="inlineStr">
         <is>
@@ -3933,13 +3933,13 @@
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>895.91</v>
+        <v>904.7</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>-0.07769999999999999</v>
+        <v>-0.0687</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>-0.0418</v>
+        <v>-0.03240000000000001</v>
       </c>
       <c r="G40" s="7" t="n">
         <v>46289</v>
@@ -3968,7 +3968,7 @@
         <v>1000</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.1161835452221764</v>
+        <v>0.1053387863380126</v>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>1100</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.227801899744394</v>
+        <v>0.2158726649718138</v>
       </c>
       <c r="Q40" s="10" t="inlineStr">
         <is>
@@ -4028,13 +4028,13 @@
         </is>
       </c>
       <c r="D41" s="15" t="n">
-        <v>120.96</v>
+        <v>120.6</v>
       </c>
       <c r="E41" s="16" t="n">
-        <v>-0.0349</v>
+        <v>-0.0377</v>
       </c>
       <c r="F41" s="17" t="n">
-        <v>0.0318</v>
+        <v>0.0287</v>
       </c>
       <c r="G41" s="18" t="n"/>
       <c r="H41" s="23" t="inlineStr">
@@ -4053,7 +4053,7 @@
         <v>125</v>
       </c>
       <c r="M41" s="17" t="n">
-        <v>0.03339947089947095</v>
+        <v>0.03648424543946937</v>
       </c>
       <c r="N41" s="14" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>135</v>
       </c>
       <c r="P41" s="17" t="n">
-        <v>0.1160714285714286</v>
+        <v>0.1194029850746269</v>
       </c>
       <c r="Q41" s="21" t="inlineStr">
         <is>
@@ -4105,13 +4105,13 @@
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>23.68</v>
+        <v>23.79</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>-0.07730000000000001</v>
+        <v>-0.0732</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>-0.07730000000000001</v>
+        <v>-0.0732</v>
       </c>
       <c r="G42" s="7" t="n">
         <v>46330</v>
@@ -4166,13 +4166,13 @@
         </is>
       </c>
       <c r="D43" s="15" t="n">
-        <v>88.51000000000001</v>
+        <v>88.09</v>
       </c>
       <c r="E43" s="16" t="n">
-        <v>-0.0378</v>
+        <v>-0.0424</v>
       </c>
       <c r="F43" s="17" t="n">
-        <v>0.0762</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="G43" s="18" t="n">
         <v>46315</v>
@@ -4201,7 +4201,7 @@
         <v>90</v>
       </c>
       <c r="M43" s="17" t="n">
-        <v>0.01683425601626929</v>
+        <v>0.02168237030309906</v>
       </c>
       <c r="N43" s="14" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>88</v>
       </c>
       <c r="P43" s="16" t="n">
-        <v>-0.005762060784092251</v>
+        <v>-0.001021682370303138</v>
       </c>
       <c r="Q43" s="21" t="inlineStr">
         <is>
@@ -4261,13 +4261,13 @@
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>58.46</v>
+        <v>57.64</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>-0.0106</v>
+        <v>-0.0244</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>0.0279</v>
+        <v>0.0135</v>
       </c>
       <c r="G44" s="7" t="n"/>
       <c r="H44" s="12" t="inlineStr">
@@ -4285,8 +4285,8 @@
       <c r="L44" s="9" t="n">
         <v>58</v>
       </c>
-      <c r="M44" s="5" t="n">
-        <v>-0.007868628121792693</v>
+      <c r="M44" s="6" t="n">
+        <v>0.006245662734212343</v>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>78</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.3342456380431064</v>
+        <v>0.3532269257460097</v>
       </c>
       <c r="Q44" s="10" t="inlineStr">
         <is>
@@ -4338,13 +4338,13 @@
         </is>
       </c>
       <c r="D45" s="15" t="n">
-        <v>61.01</v>
+        <v>61.44</v>
       </c>
       <c r="E45" s="16" t="n">
-        <v>-0.057</v>
+        <v>-0.0504</v>
       </c>
       <c r="F45" s="17" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.0152</v>
       </c>
       <c r="G45" s="18" t="n">
         <v>46322</v>
@@ -4373,7 +4373,7 @@
         <v>70</v>
       </c>
       <c r="M45" s="17" t="n">
-        <v>0.1473528929683659</v>
+        <v>0.1393229166666667</v>
       </c>
       <c r="N45" s="14" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>71</v>
       </c>
       <c r="P45" s="17" t="n">
-        <v>0.1637436485821997</v>
+        <v>0.1555989583333334</v>
       </c>
       <c r="Q45" s="21" t="inlineStr">
         <is>
@@ -4433,13 +4433,13 @@
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>48.68</v>
+        <v>49.09</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>-0.1338</v>
+        <v>-0.1265</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>-0.0256</v>
+        <v>-0.0174</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>46296</v>
@@ -4504,13 +4504,13 @@
         </is>
       </c>
       <c r="D47" s="15" t="n">
-        <v>43.88</v>
+        <v>43.91</v>
       </c>
       <c r="E47" s="16" t="n">
-        <v>-0.1031</v>
+        <v>-0.1024</v>
       </c>
       <c r="F47" s="16" t="n">
-        <v>-0.0614</v>
+        <v>-0.06059999999999999</v>
       </c>
       <c r="G47" s="18" t="n">
         <v>46331</v>
@@ -4565,13 +4565,13 @@
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>69.25</v>
+        <v>68.95</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>0.0114</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>-0.0512</v>
+        <v>-0.0554</v>
       </c>
       <c r="G48" s="7" t="n">
         <v>46324</v>
@@ -4626,13 +4626,13 @@
         </is>
       </c>
       <c r="D49" s="15" t="n">
-        <v>130.29</v>
+        <v>130.18</v>
       </c>
       <c r="E49" s="16" t="n">
-        <v>-0.09939999999999999</v>
+        <v>-0.1002</v>
       </c>
       <c r="F49" s="16" t="n">
-        <v>-0.0464</v>
+        <v>-0.0473</v>
       </c>
       <c r="G49" s="18" t="n">
         <v>46303</v>
@@ -4661,7 +4661,7 @@
         <v>140</v>
       </c>
       <c r="M49" s="17" t="n">
-        <v>0.07452605725688854</v>
+        <v>0.07543401444154242</v>
       </c>
       <c r="N49" s="14" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>150</v>
       </c>
       <c r="P49" s="17" t="n">
-        <v>0.1512779184895234</v>
+        <v>0.1522507297587954</v>
       </c>
       <c r="Q49" s="21" t="inlineStr">
         <is>
@@ -4721,13 +4721,13 @@
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>147.8</v>
+        <v>147.39</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>0.008199999999999999</v>
-      </c>
-      <c r="F50" s="6" t="n">
-        <v>0.0026</v>
+        <v>0.0054</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>-0.0001</v>
       </c>
       <c r="G50" s="7" t="n">
         <v>46317</v>
@@ -4756,7 +4756,7 @@
         <v>164</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0.1096075778078484</v>
+        <v>0.1126942126331502</v>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
         <v>162</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.09607577807848436</v>
+        <v>0.09912477101567281</v>
       </c>
       <c r="Q50" s="10" t="inlineStr">
         <is>
@@ -4820,13 +4820,13 @@
         </is>
       </c>
       <c r="D51" s="15" t="n">
-        <v>78.14</v>
+        <v>77.14</v>
       </c>
       <c r="E51" s="16" t="n">
-        <v>-0.0682</v>
+        <v>-0.0801</v>
       </c>
       <c r="F51" s="16" t="n">
-        <v>-0.05980000000000001</v>
+        <v>-0.0718</v>
       </c>
       <c r="G51" s="18" t="n">
         <v>46322</v>
@@ -4855,7 +4855,7 @@
         <v>100</v>
       </c>
       <c r="M51" s="17" t="n">
-        <v>0.279754287176862</v>
+        <v>0.2963443090484832</v>
       </c>
       <c r="N51" s="14" t="inlineStr"/>
       <c r="O51" s="20" t="n"/>
@@ -4899,13 +4899,13 @@
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>157.9</v>
+        <v>156.26</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>-0.0706</v>
+        <v>-0.08019999999999999</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>0.1544</v>
+        <v>0.1424</v>
       </c>
       <c r="G52" s="7" t="n"/>
       <c r="H52" s="12" t="inlineStr">
@@ -4924,7 +4924,7 @@
         <v>140</v>
       </c>
       <c r="M52" s="5" t="n">
-        <v>-0.1133628879037366</v>
+        <v>-0.1040573403302188</v>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>135</v>
       </c>
       <c r="P52" s="5" t="n">
-        <v>-0.1450284990500317</v>
+        <v>-0.1360552924612824</v>
       </c>
       <c r="Q52" s="10" t="inlineStr">
         <is>
@@ -4980,13 +4980,13 @@
         </is>
       </c>
       <c r="D53" s="15" t="n">
-        <v>109.65</v>
+        <v>110.53</v>
       </c>
       <c r="E53" s="17" t="n">
-        <v>0.0297</v>
+        <v>0.0379</v>
       </c>
       <c r="F53" s="17" t="n">
-        <v>0.0017</v>
+        <v>0.0097</v>
       </c>
       <c r="G53" s="18" t="n"/>
       <c r="H53" s="23" t="inlineStr">
@@ -5005,7 +5005,7 @@
         <v>140</v>
       </c>
       <c r="M53" s="17" t="n">
-        <v>0.2767897856817145</v>
+        <v>0.2666244458518049</v>
       </c>
       <c r="N53" s="14" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>140</v>
       </c>
       <c r="P53" s="17" t="n">
-        <v>0.2767897856817145</v>
+        <v>0.2666244458518049</v>
       </c>
       <c r="Q53" s="21" t="inlineStr">
         <is>
@@ -5065,13 +5065,13 @@
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>57.76</v>
+        <v>58.03</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>-0.0683</v>
+        <v>-0.0639</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0136</v>
       </c>
       <c r="G54" s="7" t="n">
         <v>46317</v>
@@ -5107,7 +5107,7 @@
         <v>76</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0.3157894736842106</v>
+        <v>0.3096674134068585</v>
       </c>
       <c r="Q54" s="10" t="inlineStr">
         <is>
@@ -5148,13 +5148,13 @@
         </is>
       </c>
       <c r="D55" s="15" t="n">
-        <v>128.15</v>
+        <v>128.09</v>
       </c>
       <c r="E55" s="16" t="n">
-        <v>-0.039</v>
+        <v>-0.0394</v>
       </c>
       <c r="F55" s="17" t="n">
-        <v>0.06559999999999999</v>
+        <v>0.06509999999999999</v>
       </c>
       <c r="G55" s="18" t="n">
         <v>46331</v>
@@ -5183,7 +5183,7 @@
         <v>183</v>
       </c>
       <c r="M55" s="17" t="n">
-        <v>0.428014046039797</v>
+        <v>0.4286829572956515</v>
       </c>
       <c r="N55" s="14" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>145</v>
       </c>
       <c r="P55" s="17" t="n">
-        <v>0.131486539211861</v>
+        <v>0.1320165508626747</v>
       </c>
       <c r="Q55" s="21" t="inlineStr">
         <is>
@@ -5235,13 +5235,13 @@
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>205.74</v>
+        <v>205.51</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>0.013</v>
+        <v>0.0119</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>0.0562</v>
+        <v>0.055</v>
       </c>
       <c r="G56" s="7" t="n">
         <v>46325</v>
@@ -5270,7 +5270,7 @@
         <v>222</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>0.07903178769320497</v>
+        <v>0.08023940440854464</v>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>225</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0.09361329833770773</v>
+        <v>0.0948372341978493</v>
       </c>
       <c r="Q56" s="10" t="inlineStr">
         <is>
@@ -5326,13 +5326,13 @@
         </is>
       </c>
       <c r="D57" s="15" t="n">
-        <v>141.88</v>
+        <v>141.84</v>
       </c>
       <c r="E57" s="16" t="n">
-        <v>-0.0554</v>
+        <v>-0.0557</v>
       </c>
       <c r="F57" s="16" t="n">
-        <v>-0.0308</v>
+        <v>-0.0311</v>
       </c>
       <c r="G57" s="18" t="n">
         <v>46331</v>
@@ -5361,7 +5361,7 @@
         <v>196</v>
       </c>
       <c r="M57" s="17" t="n">
-        <v>0.381449111925571</v>
+        <v>0.3818386914833615</v>
       </c>
       <c r="N57" s="14" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>170</v>
       </c>
       <c r="P57" s="17" t="n">
-        <v>0.1981956583027911</v>
+        <v>0.1985335589396503</v>
       </c>
       <c r="Q57" s="21" t="inlineStr">
         <is>
@@ -5417,13 +5417,13 @@
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>37.88</v>
+        <v>37.57</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>-0.0124</v>
+        <v>-0.0206</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>-0.0218</v>
+        <v>-0.03</v>
       </c>
       <c r="G58" s="7" t="n">
         <v>46324</v>
@@ -5478,13 +5478,13 @@
         </is>
       </c>
       <c r="D59" s="15" t="n">
-        <v>20.64</v>
+        <v>20.49</v>
       </c>
       <c r="E59" s="16" t="n">
-        <v>-0.0209</v>
+        <v>-0.028</v>
       </c>
       <c r="F59" s="17" t="n">
-        <v>0.0138</v>
+        <v>0.0064</v>
       </c>
       <c r="G59" s="18" t="n">
         <v>46330</v>
@@ -5539,13 +5539,13 @@
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>187.51</v>
+        <v>185.65</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>-0.08800000000000001</v>
+        <v>-0.09699999999999999</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>-0.0839</v>
+        <v>-0.09300000000000001</v>
       </c>
       <c r="G60" s="7" t="n">
         <v>46328</v>
@@ -5600,13 +5600,13 @@
         </is>
       </c>
       <c r="D61" s="15" t="n">
-        <v>33.19</v>
+        <v>33.01</v>
       </c>
       <c r="E61" s="16" t="n">
-        <v>-0.0417</v>
+        <v>-0.04679999999999999</v>
       </c>
       <c r="F61" s="16" t="n">
-        <v>-0.0052</v>
+        <v>-0.0105</v>
       </c>
       <c r="G61" s="18" t="n">
         <v>46315</v>
@@ -5642,7 +5642,7 @@
         <v>43</v>
       </c>
       <c r="P61" s="17" t="n">
-        <v>0.29557095510696</v>
+        <v>0.3026355649803091</v>
       </c>
       <c r="Q61" s="21" t="inlineStr">
         <is>
@@ -5687,13 +5687,13 @@
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>31.61</v>
+        <v>31.37</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>0.0197</v>
+        <v>0.0119</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>-0.038</v>
+        <v>-0.0453</v>
       </c>
       <c r="G62" s="7" t="n">
         <v>46316</v>
@@ -5722,7 +5722,7 @@
         <v>35</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>0.1072445428661816</v>
+        <v>0.1157156518967166</v>
       </c>
       <c r="N62" s="3" t="inlineStr"/>
       <c r="O62" s="9" t="n"/>
@@ -5766,13 +5766,13 @@
         </is>
       </c>
       <c r="D63" s="15" t="n">
-        <v>253.53</v>
+        <v>256.48</v>
       </c>
       <c r="E63" s="17" t="n">
-        <v>0.0478</v>
+        <v>0.06</v>
       </c>
       <c r="F63" s="17" t="n">
-        <v>0.2261</v>
+        <v>0.2404</v>
       </c>
       <c r="G63" s="18" t="n">
         <v>46323</v>
@@ -5827,13 +5827,13 @@
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>52.38</v>
+        <v>51.87</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>-0.03</v>
+        <v>-0.0394</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>-0.0008</v>
+        <v>-0.0105</v>
       </c>
       <c r="G64" s="7" t="n">
         <v>46311</v>
@@ -5869,7 +5869,7 @@
         <v>63</v>
       </c>
       <c r="P64" s="6" t="n">
-        <v>0.2027491408934707</v>
+        <v>0.2145748987854252</v>
       </c>
       <c r="Q64" s="10" t="inlineStr">
         <is>
@@ -5918,13 +5918,13 @@
         </is>
       </c>
       <c r="D65" s="15" t="n">
-        <v>41.76</v>
+        <v>40.93</v>
       </c>
       <c r="E65" s="16" t="n">
-        <v>-0.0659</v>
+        <v>-0.08449999999999999</v>
       </c>
       <c r="F65" s="16" t="n">
-        <v>-0.0746</v>
+        <v>-0.0931</v>
       </c>
       <c r="G65" s="18" t="n">
         <v>46328</v>
@@ -5979,13 +5979,13 @@
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>71.95999999999999</v>
+        <v>71.11</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>0.0139</v>
+        <v>0.002</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>-0.0276</v>
+        <v>-0.0391</v>
       </c>
       <c r="G66" s="7" t="n">
         <v>46328</v>
@@ -6014,7 +6014,7 @@
         <v>89</v>
       </c>
       <c r="M66" s="6" t="n">
-        <v>0.236798221234019</v>
+        <v>0.2515820559696245</v>
       </c>
       <c r="N66" s="3" t="inlineStr"/>
       <c r="O66" s="9" t="n"/>
@@ -6070,13 +6070,13 @@
         </is>
       </c>
       <c r="D67" s="15" t="n">
-        <v>161.07</v>
+        <v>161.23</v>
       </c>
       <c r="E67" s="16" t="n">
-        <v>-0.0182</v>
+        <v>-0.0172</v>
       </c>
       <c r="F67" s="17" t="n">
-        <v>0.0263</v>
+        <v>0.0273</v>
       </c>
       <c r="G67" s="18" t="n">
         <v>46325</v>
@@ -6105,7 +6105,7 @@
         <v>185</v>
       </c>
       <c r="M67" s="17" t="n">
-        <v>0.1485689451791147</v>
+        <v>0.1474291384977983</v>
       </c>
       <c r="N67" s="14" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         <v>185</v>
       </c>
       <c r="P67" s="17" t="n">
-        <v>0.1485689451791147</v>
+        <v>0.1474291384977983</v>
       </c>
       <c r="Q67" s="21" t="inlineStr">
         <is>
@@ -6161,13 +6161,13 @@
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>115.14</v>
+        <v>115.23</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>-0.0259</v>
+        <v>-0.0251</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>-0.0833</v>
+        <v>-0.08259999999999999</v>
       </c>
       <c r="G68" s="7" t="n">
         <v>46329</v>
@@ -6196,7 +6196,7 @@
         <v>120</v>
       </c>
       <c r="M68" s="6" t="n">
-        <v>0.04220948410630536</v>
+        <v>0.04139546992970577</v>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         <v>115</v>
       </c>
       <c r="P68" s="5" t="n">
-        <v>-0.001215911064790695</v>
+        <v>-0.001996007984031971</v>
       </c>
       <c r="Q68" s="10" t="inlineStr"/>
       <c r="R68" s="9" t="n"/>
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="D69" s="15" t="n">
-        <v>283.26</v>
+        <v>281.6</v>
       </c>
       <c r="E69" s="16" t="n">
-        <v>-0.2112</v>
+        <v>-0.2158</v>
       </c>
       <c r="F69" s="16" t="n">
-        <v>-0.2169</v>
+        <v>-0.2215</v>
       </c>
       <c r="G69" s="18" t="n">
         <v>46325</v>
@@ -6277,7 +6277,7 @@
         <v>406</v>
       </c>
       <c r="M69" s="17" t="n">
-        <v>0.4333121513803573</v>
+        <v>0.4417613636363635</v>
       </c>
       <c r="N69" s="14" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>436</v>
       </c>
       <c r="P69" s="17" t="n">
-        <v>0.5392219162606793</v>
+        <v>0.5482954545454545</v>
       </c>
       <c r="Q69" s="21" t="inlineStr">
         <is>
@@ -6325,13 +6325,13 @@
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>303.84</v>
+        <v>301.96</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>-0.0993</v>
+        <v>-0.1049</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>-0.06849999999999999</v>
+        <v>-0.0742</v>
       </c>
       <c r="G70" s="7" t="n">
         <v>46311</v>
@@ -6360,7 +6360,7 @@
         <v>415</v>
       </c>
       <c r="M70" s="6" t="n">
-        <v>0.3658504476040022</v>
+        <v>0.3743542191018679</v>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>380</v>
       </c>
       <c r="P70" s="6" t="n">
-        <v>0.2506582411795683</v>
+        <v>0.2584448271294212</v>
       </c>
       <c r="Q70" s="10" t="inlineStr">
         <is>
@@ -6420,13 +6420,13 @@
         </is>
       </c>
       <c r="D71" s="15" t="n">
-        <v>56.08</v>
+        <v>56</v>
       </c>
       <c r="E71" s="16" t="n">
-        <v>-0.1002</v>
+        <v>-0.1016</v>
       </c>
       <c r="F71" s="16" t="n">
-        <v>-0.09609999999999999</v>
+        <v>-0.0975</v>
       </c>
       <c r="G71" s="18" t="n">
         <v>46309</v>
@@ -6481,13 +6481,13 @@
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>1067.19</v>
+        <v>1060.89</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>-0.08990000000000001</v>
+        <v>-0.0953</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>0.0109</v>
+        <v>0.0049</v>
       </c>
       <c r="G72" s="7" t="n">
         <v>46308</v>
@@ -6519,7 +6519,7 @@
         <v>1245</v>
       </c>
       <c r="P72" s="6" t="n">
-        <v>0.1666151294521125</v>
+        <v>0.1735429686395384</v>
       </c>
       <c r="Q72" s="10" t="inlineStr">
         <is>
@@ -6564,13 +6564,13 @@
         </is>
       </c>
       <c r="D73" s="15" t="n">
-        <v>40.51</v>
+        <v>40.11</v>
       </c>
       <c r="E73" s="17" t="n">
-        <v>0.3236</v>
+        <v>0.3104</v>
       </c>
       <c r="F73" s="17" t="n">
-        <v>0.6909000000000001</v>
+        <v>0.674</v>
       </c>
       <c r="G73" s="18" t="n"/>
       <c r="H73" s="23" t="inlineStr">
@@ -6615,13 +6615,13 @@
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>27.92</v>
+        <v>27.46</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>0.1566</v>
+        <v>0.1375</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>0.7681999999999999</v>
+        <v>0.7391</v>
       </c>
       <c r="G74" s="7" t="n">
         <v>46346</v>
@@ -6676,13 +6676,13 @@
         </is>
       </c>
       <c r="D75" s="15" t="n">
-        <v>508.33</v>
+        <v>507.17</v>
       </c>
       <c r="E75" s="17" t="n">
-        <v>0.008</v>
+        <v>0.005699999999999999</v>
       </c>
       <c r="F75" s="17" t="n">
-        <v>0.0271</v>
+        <v>0.0247</v>
       </c>
       <c r="G75" s="18" t="n">
         <v>46332</v>
@@ -6759,13 +6759,13 @@
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>61.95</v>
+        <v>61.7</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>-0.1698</v>
+        <v>-0.1731</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>-0.08439999999999999</v>
+        <v>-0.08810000000000001</v>
       </c>
       <c r="G76" s="7" t="n">
         <v>46321</v>
@@ -6794,7 +6794,7 @@
         <v>68</v>
       </c>
       <c r="M76" s="6" t="n">
-        <v>0.09765940274414846</v>
+        <v>0.1021069692058346</v>
       </c>
       <c r="N76" s="3" t="inlineStr"/>
       <c r="O76" s="9" t="n"/>
@@ -6836,13 +6836,13 @@
         </is>
       </c>
       <c r="D77" s="15" t="n">
-        <v>119.42</v>
+        <v>119.27</v>
       </c>
       <c r="E77" s="16" t="n">
-        <v>-0.1686</v>
+        <v>-0.1697</v>
       </c>
       <c r="F77" s="16" t="n">
-        <v>-0.0814</v>
+        <v>-0.0825</v>
       </c>
       <c r="G77" s="18" t="n">
         <v>46310</v>
@@ -6901,13 +6901,13 @@
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>132.74</v>
+        <v>131.93</v>
       </c>
       <c r="E78" s="6" t="n">
-        <v>0.007800000000000001</v>
-      </c>
-      <c r="F78" s="6" t="n">
-        <v>0.0042</v>
+        <v>0.0016</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>-0.002</v>
       </c>
       <c r="G78" s="7" t="n">
         <v>46308</v>
@@ -6939,7 +6939,7 @@
         <v>140</v>
       </c>
       <c r="P78" s="6" t="n">
-        <v>0.0546933855657676</v>
+        <v>0.06116880163723181</v>
       </c>
       <c r="Q78" s="10" t="inlineStr">
         <is>
@@ -6988,13 +6988,13 @@
         </is>
       </c>
       <c r="D79" s="15" t="n">
-        <v>336.16</v>
+        <v>335.21</v>
       </c>
       <c r="E79" s="16" t="n">
-        <v>-0.028</v>
+        <v>-0.0307</v>
       </c>
       <c r="F79" s="16" t="n">
-        <v>-0.06559999999999999</v>
+        <v>-0.0682</v>
       </c>
       <c r="G79" s="18" t="n">
         <v>46315</v>
@@ -7023,7 +7023,7 @@
         <v>358</v>
       </c>
       <c r="M79" s="17" t="n">
-        <v>0.06496906235126122</v>
+        <v>0.06798723188449038</v>
       </c>
       <c r="N79" s="14" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>374</v>
       </c>
       <c r="P79" s="17" t="n">
-        <v>0.1125654450261779</v>
+        <v>0.1157185048178754</v>
       </c>
       <c r="Q79" s="21" t="inlineStr">
         <is>
@@ -7079,13 +7079,13 @@
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>55.88</v>
+        <v>55.59</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>-0.0469</v>
+        <v>-0.0519</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>-0.05429999999999999</v>
+        <v>-0.0592</v>
       </c>
       <c r="G80" s="7" t="n">
         <v>46315</v>
@@ -7114,7 +7114,7 @@
         <v>57</v>
       </c>
       <c r="M80" s="6" t="n">
-        <v>0.0200429491768074</v>
+        <v>0.02536427415002692</v>
       </c>
       <c r="N80" s="3" t="inlineStr"/>
       <c r="O80" s="9" t="n"/>
@@ -7156,13 +7156,13 @@
         </is>
       </c>
       <c r="D81" s="15" t="n">
-        <v>14.94</v>
+        <v>14.46</v>
       </c>
       <c r="E81" s="17" t="n">
-        <v>0.2519</v>
-      </c>
-      <c r="F81" s="17" t="n">
-        <v>0.0286</v>
+        <v>0.2121</v>
+      </c>
+      <c r="F81" s="16" t="n">
+        <v>-0.004099999999999999</v>
       </c>
       <c r="G81" s="18" t="n"/>
       <c r="H81" s="23" t="inlineStr">
@@ -7207,13 +7207,13 @@
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>395.32</v>
+        <v>395.16</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>-0.0449</v>
+        <v>-0.0453</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>0.0668</v>
+        <v>0.0663</v>
       </c>
       <c r="G82" s="7" t="n">
         <v>46330</v>
@@ -7280,13 +7280,13 @@
         </is>
       </c>
       <c r="D83" s="15" t="n">
-        <v>93.03</v>
+        <v>91.72</v>
       </c>
       <c r="E83" s="17" t="n">
-        <v>0.0605</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="F83" s="17" t="n">
-        <v>0.4917</v>
+        <v>0.4708</v>
       </c>
       <c r="G83" s="18" t="n">
         <v>46337</v>
@@ -7341,13 +7341,13 @@
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>38.78</v>
+        <v>38.46</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>-0.1922</v>
+        <v>-0.1988</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>-0.198</v>
+        <v>-0.2046</v>
       </c>
       <c r="G84" s="7" t="n">
         <v>46331</v>
@@ -7402,13 +7402,13 @@
         </is>
       </c>
       <c r="D85" s="15" t="n">
-        <v>946.11</v>
+        <v>936.36</v>
       </c>
       <c r="E85" s="16" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.0964</v>
       </c>
       <c r="F85" s="16" t="n">
-        <v>-0.1085</v>
+        <v>-0.1177</v>
       </c>
       <c r="G85" s="18" t="n">
         <v>46308</v>
@@ -7437,7 +7437,7 @@
         <v>1325</v>
       </c>
       <c r="M85" s="17" t="n">
-        <v>0.4004714039593705</v>
+        <v>0.4150540390448118</v>
       </c>
       <c r="N85" s="14" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         <v>1210</v>
       </c>
       <c r="P85" s="17" t="n">
-        <v>0.2789210556911987</v>
+        <v>0.292238028108847</v>
       </c>
       <c r="Q85" s="21" t="inlineStr">
         <is>
@@ -7489,13 +7489,13 @@
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>130.4</v>
+        <v>129.94</v>
       </c>
       <c r="E86" s="6" t="n">
-        <v>0.0113</v>
+        <v>0.0077</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>-0.0701</v>
+        <v>-0.07339999999999999</v>
       </c>
       <c r="G86" s="7" t="n">
         <v>46324</v>
@@ -7550,13 +7550,13 @@
         </is>
       </c>
       <c r="D87" s="15" t="n">
-        <v>125.6</v>
+        <v>122.7</v>
       </c>
       <c r="E87" s="17" t="n">
-        <v>0.2121</v>
+        <v>0.1841</v>
       </c>
       <c r="F87" s="17" t="n">
-        <v>0.3233</v>
+        <v>0.2928</v>
       </c>
       <c r="G87" s="18" t="n">
         <v>46330</v>
@@ -7611,13 +7611,13 @@
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>105.79</v>
+        <v>102.46</v>
       </c>
       <c r="E88" s="6" t="n">
-        <v>0.3297</v>
+        <v>0.2878</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>-0.0382</v>
+        <v>-0.06849999999999999</v>
       </c>
       <c r="G88" s="7" t="n">
         <v>46329</v>
@@ -7672,13 +7672,13 @@
         </is>
       </c>
       <c r="D89" s="15" t="n">
-        <v>157.17</v>
+        <v>156.35</v>
       </c>
       <c r="E89" s="16" t="n">
-        <v>-0.0357</v>
+        <v>-0.0407</v>
       </c>
       <c r="F89" s="17" t="n">
-        <v>0.0781</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="G89" s="18" t="n">
         <v>46324</v>
@@ -7733,13 +7733,13 @@
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>148.4</v>
+        <v>148.33</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>-0.1297</v>
+        <v>-0.1301</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>-0.0145</v>
+        <v>-0.0149</v>
       </c>
       <c r="G90" s="7" t="n">
         <v>46329</v>
@@ -7808,13 +7808,13 @@
         </is>
       </c>
       <c r="D91" s="15" t="n">
-        <v>338.89</v>
+        <v>337.53</v>
       </c>
       <c r="E91" s="16" t="n">
-        <v>-0.0491</v>
+        <v>-0.0529</v>
       </c>
       <c r="F91" s="16" t="n">
-        <v>-0.0405</v>
+        <v>-0.0444</v>
       </c>
       <c r="G91" s="18" t="n">
         <v>46308</v>
@@ -7843,7 +7843,7 @@
         <v>196</v>
       </c>
       <c r="M91" s="16" t="n">
-        <v>-0.4216412405205229</v>
+        <v>-0.4193108760702752</v>
       </c>
       <c r="N91" s="14" t="inlineStr"/>
       <c r="O91" s="20" t="n"/>
@@ -7887,13 +7887,13 @@
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>96.84999999999999</v>
+        <v>97.20999999999999</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>-0.09759999999999999</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>-0.0253</v>
+        <v>-0.0216</v>
       </c>
       <c r="G92" s="7" t="n">
         <v>46332</v>
@@ -7922,7 +7922,7 @@
         <v>375</v>
       </c>
       <c r="M92" s="6" t="n">
-        <v>2.871966959215281</v>
+        <v>2.857627816068306</v>
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>368</v>
       </c>
       <c r="P92" s="6" t="n">
-        <v>2.799690242643263</v>
+        <v>2.785618763501698</v>
       </c>
       <c r="Q92" s="10" t="inlineStr">
         <is>
@@ -7986,13 +7986,13 @@
         </is>
       </c>
       <c r="D93" s="15" t="n">
-        <v>347.61</v>
+        <v>339.38</v>
       </c>
       <c r="E93" s="16" t="n">
-        <v>-0.1211</v>
+        <v>-0.1419</v>
       </c>
       <c r="F93" s="16" t="n">
-        <v>-0.0043</v>
+        <v>-0.0278</v>
       </c>
       <c r="G93" s="18" t="n">
         <v>46317</v>
@@ -8024,7 +8024,7 @@
         <v>115</v>
       </c>
       <c r="P93" s="16" t="n">
-        <v>-0.6691694715341906</v>
+        <v>-0.6611467971005952</v>
       </c>
       <c r="Q93" s="21" t="inlineStr">
         <is>
@@ -8073,13 +8073,13 @@
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>560.23</v>
+        <v>559.92</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>-0.06610000000000001</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>0.0381</v>
+        <v>0.0375</v>
       </c>
       <c r="G94" s="7" t="n">
         <v>46324</v>
@@ -8108,7 +8108,7 @@
         <v>366</v>
       </c>
       <c r="M94" s="5" t="n">
-        <v>-0.3466968923477858</v>
+        <v>-0.3463351907415345</v>
       </c>
       <c r="N94" s="3" t="inlineStr"/>
       <c r="O94" s="9" t="n"/>
@@ -8150,13 +8150,13 @@
         </is>
       </c>
       <c r="D95" s="15" t="n">
-        <v>1764.85</v>
+        <v>1741.87</v>
       </c>
       <c r="E95" s="16" t="n">
-        <v>-0.0289</v>
+        <v>-0.0415</v>
       </c>
       <c r="F95" s="16" t="n">
-        <v>-0.1152</v>
+        <v>-0.1268</v>
       </c>
       <c r="G95" s="18" t="n">
         <v>46330</v>
@@ -8221,13 +8221,13 @@
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>200.13</v>
+        <v>198.39</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.0733</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>-0.0669</v>
+        <v>-0.075</v>
       </c>
       <c r="G96" s="7" t="n">
         <v>46309</v>
@@ -8256,7 +8256,7 @@
         <v>668</v>
       </c>
       <c r="M96" s="6" t="n">
-        <v>2.337830410233348</v>
+        <v>2.367105196834518</v>
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>550</v>
       </c>
       <c r="P96" s="6" t="n">
-        <v>1.748213661120272</v>
+        <v>1.772317153082313</v>
       </c>
       <c r="Q96" s="10" t="inlineStr">
         <is>
@@ -8316,13 +8316,13 @@
         </is>
       </c>
       <c r="D97" s="15" t="n">
-        <v>114.75</v>
+        <v>113.92</v>
       </c>
       <c r="E97" s="17" t="n">
-        <v>0.0256</v>
+        <v>0.0181</v>
       </c>
       <c r="F97" s="17" t="n">
-        <v>0.0489</v>
+        <v>0.0413</v>
       </c>
       <c r="G97" s="18" t="n">
         <v>46321</v>
@@ -8351,7 +8351,7 @@
         <v>240</v>
       </c>
       <c r="M97" s="17" t="n">
-        <v>1.091503267973856</v>
+        <v>1.106741573033708</v>
       </c>
       <c r="N97" s="14" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>240</v>
       </c>
       <c r="P97" s="17" t="n">
-        <v>1.091503267973856</v>
+        <v>1.106741573033708</v>
       </c>
       <c r="Q97" s="21" t="inlineStr">
         <is>
@@ -8411,13 +8411,13 @@
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>226.2</v>
+        <v>224.03</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>-0.0717</v>
+        <v>-0.0806</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>-0.09880000000000001</v>
+        <v>-0.1074</v>
       </c>
       <c r="G98" s="7" t="n">
         <v>46310</v>
@@ -8446,7 +8446,7 @@
         <v>113</v>
       </c>
       <c r="M98" s="5" t="n">
-        <v>-0.5004420866489832</v>
+        <v>-0.495603267419542</v>
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>114</v>
       </c>
       <c r="P98" s="5" t="n">
-        <v>-0.4960212201591512</v>
+        <v>-0.4911395795205999</v>
       </c>
       <c r="Q98" s="10" t="inlineStr"/>
       <c r="R98" s="9" t="n"/>
@@ -8496,13 +8496,13 @@
         </is>
       </c>
       <c r="D99" s="15" t="n">
-        <v>25.24</v>
+        <v>24.69</v>
       </c>
       <c r="E99" s="17" t="n">
-        <v>0.2618</v>
+        <v>0.2345</v>
       </c>
       <c r="F99" s="17" t="n">
-        <v>0.1201</v>
+        <v>0.0959</v>
       </c>
       <c r="G99" s="18" t="n">
         <v>46324</v>
@@ -8557,13 +8557,13 @@
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>14.38</v>
+        <v>14.2</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>-0.0234</v>
+        <v>-0.0353</v>
       </c>
       <c r="F100" s="6" t="n">
-        <v>0.0617</v>
+        <v>0.0487</v>
       </c>
       <c r="G100" s="7" t="n">
         <v>46323</v>
@@ -8618,13 +8618,13 @@
         </is>
       </c>
       <c r="D101" s="15" t="n">
-        <v>105.03</v>
+        <v>104.83</v>
       </c>
       <c r="E101" s="16" t="n">
-        <v>-0.0516</v>
+        <v>-0.0535</v>
       </c>
       <c r="F101" s="17" t="n">
-        <v>0.05860000000000001</v>
+        <v>0.0565</v>
       </c>
       <c r="G101" s="18" t="n">
         <v>46323</v>
@@ -8653,7 +8653,7 @@
         <v>285</v>
       </c>
       <c r="M101" s="17" t="n">
-        <v>1.713510425592688</v>
+        <v>1.718687398645426</v>
       </c>
       <c r="N101" s="14" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>285</v>
       </c>
       <c r="P101" s="17" t="n">
-        <v>1.713510425592688</v>
+        <v>1.718687398645426</v>
       </c>
       <c r="Q101" s="21" t="inlineStr">
         <is>
@@ -8705,13 +8705,13 @@
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>407.27</v>
+        <v>406.5</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.0664</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>-0.0449</v>
+        <v>-0.0467</v>
       </c>
       <c r="G102" s="7" t="n">
         <v>46324</v>
@@ -8780,13 +8780,13 @@
         </is>
       </c>
       <c r="D103" s="15" t="n">
-        <v>47.76</v>
+        <v>47</v>
       </c>
       <c r="E103" s="16" t="n">
-        <v>-0.0599</v>
+        <v>-0.075</v>
       </c>
       <c r="F103" s="16" t="n">
-        <v>-0.07719999999999999</v>
+        <v>-0.092</v>
       </c>
       <c r="G103" s="18" t="n">
         <v>46311</v>
@@ -8841,13 +8841,13 @@
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>363</v>
+        <v>361.52</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>-0.0508</v>
+        <v>-0.0546</v>
       </c>
       <c r="F104" s="6" t="n">
-        <v>0.0204</v>
+        <v>0.0162</v>
       </c>
       <c r="G104" s="7" t="n">
         <v>46322</v>
@@ -8876,7 +8876,7 @@
         <v>525</v>
       </c>
       <c r="M104" s="6" t="n">
-        <v>0.4462809917355372</v>
+        <v>0.4522018145607436</v>
       </c>
       <c r="N104" s="3" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>543</v>
       </c>
       <c r="P104" s="6" t="n">
-        <v>0.4958677685950413</v>
+        <v>0.501991591059969</v>
       </c>
       <c r="Q104" s="10" t="inlineStr">
         <is>
@@ -8932,13 +8932,13 @@
         </is>
       </c>
       <c r="D105" s="15" t="n">
-        <v>68.18000000000001</v>
+        <v>67.67</v>
       </c>
       <c r="E105" s="16" t="n">
-        <v>-0.0217</v>
+        <v>-0.0291</v>
       </c>
       <c r="F105" s="16" t="n">
-        <v>-0.0964</v>
+        <v>-0.1032</v>
       </c>
       <c r="G105" s="18" t="n">
         <v>46314</v>
@@ -8967,7 +8967,7 @@
         <v>412</v>
       </c>
       <c r="M105" s="17" t="n">
-        <v>5.042827808741566</v>
+        <v>5.088370031032953</v>
       </c>
       <c r="N105" s="14" t="inlineStr">
         <is>
@@ -8978,7 +8978,7 @@
         <v>350</v>
       </c>
       <c r="P105" s="17" t="n">
-        <v>4.133470225872689</v>
+        <v>4.172159006945471</v>
       </c>
       <c r="Q105" s="21" t="inlineStr">
         <is>
@@ -9023,13 +9023,13 @@
         </is>
       </c>
       <c r="D106" s="4" t="n">
-        <v>75.22</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>-0.0756</v>
+        <v>-0.0823</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>-0.025</v>
+        <v>-0.032</v>
       </c>
       <c r="G106" s="7" t="n">
         <v>46331</v>
@@ -9058,7 +9058,7 @@
         <v>68</v>
       </c>
       <c r="M106" s="5" t="n">
-        <v>-0.09598511034299387</v>
+        <v>-0.08944831280128557</v>
       </c>
       <c r="N106" s="3" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>68</v>
       </c>
       <c r="P106" s="5" t="n">
-        <v>-0.09598511034299387</v>
+        <v>-0.08944831280128557</v>
       </c>
       <c r="Q106" s="10" t="inlineStr">
         <is>
@@ -9114,13 +9114,13 @@
         </is>
       </c>
       <c r="D107" s="15" t="n">
-        <v>266.06</v>
+        <v>265.08</v>
       </c>
       <c r="E107" s="17" t="n">
-        <v>0.0058</v>
+        <v>0.0021</v>
       </c>
       <c r="F107" s="17" t="n">
-        <v>0.0258</v>
+        <v>0.0221</v>
       </c>
       <c r="G107" s="18" t="n">
         <v>46325</v>
@@ -9149,7 +9149,7 @@
         <v>295</v>
       </c>
       <c r="M107" s="17" t="n">
-        <v>0.1087724573404495</v>
+        <v>0.1128715859363212</v>
       </c>
       <c r="N107" s="14" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>246</v>
       </c>
       <c r="P107" s="16" t="n">
-        <v>-0.07539652709915058</v>
+        <v>-0.07197827071072878</v>
       </c>
       <c r="Q107" s="21" t="inlineStr">
         <is>
@@ -9197,13 +9197,13 @@
         </is>
       </c>
       <c r="D108" s="4" t="n">
-        <v>104.22</v>
+        <v>103.49</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>-0.1067</v>
+        <v>-0.113</v>
       </c>
       <c r="F108" s="6" t="n">
-        <v>0.0113</v>
+        <v>0.0042</v>
       </c>
       <c r="G108" s="7" t="n">
         <v>46316</v>
@@ -9232,7 +9232,7 @@
         <v>112</v>
       </c>
       <c r="M108" s="6" t="n">
-        <v>0.07464977931299176</v>
+        <v>0.08223016716590981</v>
       </c>
       <c r="N108" s="3" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>120</v>
       </c>
       <c r="P108" s="6" t="n">
-        <v>0.1514104778353483</v>
+        <v>0.1595323219634748</v>
       </c>
       <c r="Q108" s="10" t="inlineStr">
         <is>
@@ -9296,13 +9296,13 @@
         </is>
       </c>
       <c r="D109" s="15" t="n">
-        <v>408.5</v>
+        <v>406.09</v>
       </c>
       <c r="E109" s="16" t="n">
-        <v>-0.0796</v>
+        <v>-0.0851</v>
       </c>
       <c r="F109" s="17" t="n">
-        <v>0.0863</v>
+        <v>0.0799</v>
       </c>
       <c r="G109" s="18" t="n">
         <v>46329</v>
@@ -9331,7 +9331,7 @@
         <v>390</v>
       </c>
       <c r="M109" s="16" t="n">
-        <v>-0.04528763769889841</v>
+        <v>-0.03962175872343563</v>
       </c>
       <c r="N109" s="14" t="inlineStr">
         <is>
@@ -9379,13 +9379,13 @@
         </is>
       </c>
       <c r="D110" s="4" t="n">
-        <v>183.4</v>
+        <v>182.52</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>-0.0385</v>
+        <v>-0.0431</v>
       </c>
       <c r="F110" s="6" t="n">
-        <v>0.1729</v>
+        <v>0.1673</v>
       </c>
       <c r="G110" s="7" t="n">
         <v>46331</v>
@@ -9414,7 +9414,7 @@
         <v>161</v>
       </c>
       <c r="M110" s="5" t="n">
-        <v>-0.1221374045801527</v>
+        <v>-0.1179048871356564</v>
       </c>
       <c r="N110" s="3" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         <v>180</v>
       </c>
       <c r="P110" s="5" t="n">
-        <v>-0.01853871319520178</v>
+        <v>-0.01380670611439848</v>
       </c>
       <c r="Q110" s="10" t="inlineStr">
         <is>
@@ -9466,13 +9466,13 @@
         </is>
       </c>
       <c r="D111" s="15" t="n">
-        <v>44.98</v>
+        <v>44.62</v>
       </c>
       <c r="E111" s="16" t="n">
-        <v>-0.08220000000000001</v>
+        <v>-0.08960000000000001</v>
       </c>
       <c r="F111" s="17" t="n">
-        <v>0.0165</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="G111" s="18" t="n">
         <v>46323</v>
@@ -9501,7 +9501,7 @@
         <v>55</v>
       </c>
       <c r="M111" s="17" t="n">
-        <v>0.2227656736327257</v>
+        <v>0.232631107126849</v>
       </c>
       <c r="N111" s="14" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         <v>65</v>
       </c>
       <c r="P111" s="17" t="n">
-        <v>0.4450867052023122</v>
+        <v>0.4567458538771852</v>
       </c>
       <c r="Q111" s="21" t="inlineStr">
         <is>
@@ -9553,13 +9553,13 @@
         </is>
       </c>
       <c r="D112" s="4" t="n">
-        <v>317.45</v>
+        <v>312.28</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>-0.0195</v>
+        <v>-0.0355</v>
       </c>
       <c r="F112" s="6" t="n">
-        <v>0.0244</v>
+        <v>0.0077</v>
       </c>
       <c r="G112" s="7" t="n">
         <v>46330</v>
@@ -9588,7 +9588,7 @@
         <v>331</v>
       </c>
       <c r="M112" s="6" t="n">
-        <v>0.04268388722633489</v>
+        <v>0.059946202126297</v>
       </c>
       <c r="N112" s="3" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>330</v>
       </c>
       <c r="P112" s="6" t="n">
-        <v>0.0395337848480076</v>
+        <v>0.0567439477392085</v>
       </c>
       <c r="Q112" s="10" t="inlineStr">
         <is>
@@ -9648,13 +9648,13 @@
         </is>
       </c>
       <c r="D113" s="15" t="n">
-        <v>86.19</v>
+        <v>85.86</v>
       </c>
       <c r="E113" s="16" t="n">
-        <v>-0.0842</v>
+        <v>-0.0877</v>
       </c>
       <c r="F113" s="16" t="n">
-        <v>-0.2</v>
+        <v>-0.2031</v>
       </c>
       <c r="G113" s="18" t="n">
         <v>46330</v>
@@ -9683,7 +9683,7 @@
         <v>123</v>
       </c>
       <c r="M113" s="17" t="n">
-        <v>0.4270797076226941</v>
+        <v>0.43256464011181</v>
       </c>
       <c r="N113" s="14" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
         <v>130</v>
       </c>
       <c r="P113" s="17" t="n">
-        <v>0.5082956259426848</v>
+        <v>0.5140927090612625</v>
       </c>
       <c r="Q113" s="21" t="inlineStr">
         <is>
@@ -9735,13 +9735,13 @@
         </is>
       </c>
       <c r="D114" s="4" t="n">
-        <v>221.36</v>
+        <v>221.56</v>
       </c>
       <c r="E114" s="6" t="n">
-        <v>0.0291</v>
+        <v>0.03</v>
       </c>
       <c r="F114" s="6" t="n">
-        <v>0.1559</v>
+        <v>0.157</v>
       </c>
       <c r="G114" s="7" t="n">
         <v>46315</v>
@@ -9770,7 +9770,7 @@
         <v>212</v>
       </c>
       <c r="M114" s="5" t="n">
-        <v>-0.04228406216118546</v>
+        <v>-0.0431485827766745</v>
       </c>
       <c r="N114" s="3" t="inlineStr">
         <is>
@@ -9781,7 +9781,7 @@
         <v>205</v>
       </c>
       <c r="P114" s="5" t="n">
-        <v>-0.07390675822190103</v>
+        <v>-0.07474273334536921</v>
       </c>
       <c r="Q114" s="10" t="inlineStr">
         <is>
@@ -9826,13 +9826,13 @@
         </is>
       </c>
       <c r="D115" s="15" t="n">
-        <v>89.15000000000001</v>
+        <v>87.73</v>
       </c>
       <c r="E115" s="16" t="n">
-        <v>-0.0209</v>
+        <v>-0.0366</v>
       </c>
       <c r="F115" s="17" t="n">
-        <v>0.2462</v>
+        <v>0.2263</v>
       </c>
       <c r="G115" s="18" t="n">
         <v>46324</v>
@@ -9861,7 +9861,7 @@
         <v>85</v>
       </c>
       <c r="M115" s="16" t="n">
-        <v>-0.04655075715086938</v>
+        <v>-0.03111820357916338</v>
       </c>
       <c r="N115" s="14" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>90</v>
       </c>
       <c r="P115" s="17" t="n">
-        <v>0.009534492428491243</v>
+        <v>0.02587484326912112</v>
       </c>
       <c r="Q115" s="21" t="inlineStr">
         <is>
@@ -9913,13 +9913,13 @@
         </is>
       </c>
       <c r="D116" s="4" t="n">
-        <v>151.99</v>
+        <v>151.37</v>
       </c>
       <c r="E116" s="6" t="n">
-        <v>0.0357</v>
+        <v>0.0316</v>
       </c>
       <c r="F116" s="6" t="n">
-        <v>0.1754</v>
+        <v>0.1706</v>
       </c>
       <c r="G116" s="7" t="n">
         <v>46324</v>
@@ -9948,7 +9948,7 @@
         <v>165</v>
       </c>
       <c r="M116" s="6" t="n">
-        <v>0.08559773669320343</v>
+        <v>0.09004426240338241</v>
       </c>
       <c r="N116" s="3" t="inlineStr"/>
       <c r="O116" s="9" t="n"/>
@@ -9996,13 +9996,13 @@
         </is>
       </c>
       <c r="D117" s="15" t="n">
-        <v>522.1</v>
+        <v>522.02</v>
       </c>
       <c r="E117" s="16" t="n">
-        <v>-0.0669</v>
+        <v>-0.067</v>
       </c>
       <c r="F117" s="16" t="n">
-        <v>-0.0408</v>
+        <v>-0.04099999999999999</v>
       </c>
       <c r="G117" s="18" t="n">
         <v>46328</v>
@@ -10067,13 +10067,13 @@
         </is>
       </c>
       <c r="D118" s="4" t="n">
-        <v>400.44</v>
+        <v>398.3</v>
       </c>
       <c r="E118" s="6" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="F118" s="6" t="n">
-        <v>0.1865</v>
+        <v>0.1801</v>
       </c>
       <c r="G118" s="7" t="n">
         <v>46315</v>
@@ -10102,7 +10102,7 @@
         <v>487</v>
       </c>
       <c r="M118" s="6" t="n">
-        <v>0.2161622215562881</v>
+        <v>0.2226964599548079</v>
       </c>
       <c r="N118" s="3" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>375</v>
       </c>
       <c r="P118" s="5" t="n">
-        <v>-0.0635301168714414</v>
+        <v>-0.05849861913130808</v>
       </c>
       <c r="Q118" s="10" t="inlineStr">
         <is>
@@ -10158,13 +10158,13 @@
         </is>
       </c>
       <c r="D119" s="15" t="n">
-        <v>269.82</v>
+        <v>269.17</v>
       </c>
       <c r="E119" s="16" t="n">
-        <v>-0.0118</v>
+        <v>-0.0142</v>
       </c>
       <c r="F119" s="17" t="n">
-        <v>0.0244</v>
+        <v>0.0219</v>
       </c>
       <c r="G119" s="18" t="n">
         <v>46308</v>
@@ -10193,7 +10193,7 @@
         <v>272</v>
       </c>
       <c r="M119" s="17" t="n">
-        <v>0.008079460380994762</v>
+        <v>0.01051380168666636</v>
       </c>
       <c r="N119" s="14" t="inlineStr"/>
       <c r="O119" s="20" t="n"/>
@@ -10245,13 +10245,13 @@
         </is>
       </c>
       <c r="D120" s="4" t="n">
-        <v>1159.58</v>
+        <v>1150.99</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.07690000000000001</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>-0.0305</v>
+        <v>-0.0377</v>
       </c>
       <c r="G120" s="7" t="n">
         <v>46324</v>
@@ -10280,7 +10280,7 @@
         <v>1280</v>
       </c>
       <c r="M120" s="6" t="n">
-        <v>0.1038479449455838</v>
+        <v>0.1120861171686982</v>
       </c>
       <c r="N120" s="3" t="inlineStr">
         <is>
@@ -10340,13 +10340,13 @@
         </is>
       </c>
       <c r="D121" s="15" t="n">
-        <v>90.72</v>
+        <v>89.3</v>
       </c>
       <c r="E121" s="16" t="n">
-        <v>-0.0235</v>
+        <v>-0.0388</v>
       </c>
       <c r="F121" s="17" t="n">
-        <v>0.09029999999999999</v>
+        <v>0.0732</v>
       </c>
       <c r="G121" s="18" t="n">
         <v>46343</v>
@@ -10375,7 +10375,7 @@
         <v>102</v>
       </c>
       <c r="M121" s="17" t="n">
-        <v>0.1243386243386244</v>
+        <v>0.1422172452407615</v>
       </c>
       <c r="N121" s="14" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>105</v>
       </c>
       <c r="P121" s="17" t="n">
-        <v>0.1574074074074074</v>
+        <v>0.1758118701007839</v>
       </c>
       <c r="Q121" s="21" t="inlineStr">
         <is>
@@ -10427,13 +10427,13 @@
         </is>
       </c>
       <c r="D122" s="4" t="n">
-        <v>147.8</v>
+        <v>148.08</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>-0.019</v>
+        <v>-0.0171</v>
       </c>
       <c r="F122" s="6" t="n">
-        <v>0.1276</v>
+        <v>0.1298</v>
       </c>
       <c r="G122" s="7" t="n">
         <v>46324</v>
@@ -10462,7 +10462,7 @@
         <v>150</v>
       </c>
       <c r="M122" s="6" t="n">
-        <v>0.01488497970230033</v>
+        <v>0.01296596434359797</v>
       </c>
       <c r="N122" s="3" t="inlineStr"/>
       <c r="O122" s="9" t="n"/>
@@ -10506,13 +10506,13 @@
         </is>
       </c>
       <c r="D123" s="15" t="n">
-        <v>142.31</v>
+        <v>142.71</v>
       </c>
       <c r="E123" s="16" t="n">
-        <v>-0.09939999999999999</v>
+        <v>-0.0969</v>
       </c>
       <c r="F123" s="16" t="n">
-        <v>-0.0819</v>
+        <v>-0.0793</v>
       </c>
       <c r="G123" s="18" t="n">
         <v>46322</v>
@@ -10585,13 +10585,13 @@
         </is>
       </c>
       <c r="D124" s="4" t="n">
-        <v>27.95</v>
-      </c>
-      <c r="E124" s="5" t="n">
-        <v>-0.0005</v>
+        <v>28.18</v>
+      </c>
+      <c r="E124" s="6" t="n">
+        <v>0.0075</v>
       </c>
       <c r="F124" s="6" t="n">
-        <v>0.1392</v>
+        <v>0.1483</v>
       </c>
       <c r="G124" s="7" t="n">
         <v>46329</v>
@@ -10619,8 +10619,8 @@
       <c r="L124" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="M124" s="6" t="n">
-        <v>0.001788908765652977</v>
+      <c r="M124" s="5" t="n">
+        <v>-0.006387508871540089</v>
       </c>
       <c r="N124" s="3" t="inlineStr"/>
       <c r="O124" s="9" t="n"/>
@@ -10664,13 +10664,13 @@
         </is>
       </c>
       <c r="D125" s="15" t="n">
-        <v>274.1</v>
+        <v>273.4</v>
       </c>
       <c r="E125" s="16" t="n">
-        <v>-0.1638</v>
+        <v>-0.166</v>
       </c>
       <c r="F125" s="16" t="n">
-        <v>-0.17</v>
+        <v>-0.1721</v>
       </c>
       <c r="G125" s="18" t="n">
         <v>46324</v>
@@ -10699,7 +10699,7 @@
         <v>418</v>
       </c>
       <c r="M125" s="17" t="n">
-        <v>0.5249908792411527</v>
+        <v>0.5288953913679592</v>
       </c>
       <c r="N125" s="14" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>350</v>
       </c>
       <c r="P125" s="17" t="n">
-        <v>0.2769062385990513</v>
+        <v>0.280175566934894</v>
       </c>
       <c r="Q125" s="21" t="inlineStr">
         <is>
@@ -10755,13 +10755,13 @@
         </is>
       </c>
       <c r="D126" s="4" t="n">
-        <v>658.92</v>
+        <v>665.3</v>
       </c>
       <c r="E126" s="6" t="n">
-        <v>0.048</v>
+        <v>0.0581</v>
       </c>
       <c r="F126" s="6" t="n">
-        <v>0.1595</v>
+        <v>0.1708</v>
       </c>
       <c r="G126" s="7" t="n">
         <v>46323</v>
@@ -10790,7 +10790,7 @@
         <v>615</v>
       </c>
       <c r="M126" s="5" t="n">
-        <v>-0.06665452558732465</v>
+        <v>-0.07560499022997137</v>
       </c>
       <c r="N126" s="3" t="inlineStr">
         <is>
@@ -10801,7 +10801,7 @@
         <v>570</v>
       </c>
       <c r="P126" s="5" t="n">
-        <v>-0.1349480968858131</v>
+        <v>-0.1432436494814369</v>
       </c>
       <c r="Q126" s="10" t="inlineStr">
         <is>
@@ -10850,13 +10850,13 @@
         </is>
       </c>
       <c r="D127" s="15" t="n">
-        <v>371.27</v>
+        <v>371.29</v>
       </c>
       <c r="E127" s="16" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.0689</v>
       </c>
       <c r="F127" s="16" t="n">
-        <v>-0.1176</v>
+        <v>-0.1175</v>
       </c>
       <c r="G127" s="18" t="n">
         <v>46308</v>
@@ -10885,7 +10885,7 @@
         <v>526</v>
       </c>
       <c r="M127" s="17" t="n">
-        <v>0.4167586931343767</v>
+        <v>0.4166823776562794</v>
       </c>
       <c r="N127" s="14" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>480</v>
       </c>
       <c r="P127" s="17" t="n">
-        <v>0.2928596439249065</v>
+        <v>0.2927900024239812</v>
       </c>
       <c r="Q127" s="21" t="inlineStr">
         <is>
@@ -10941,13 +10941,13 @@
         </is>
       </c>
       <c r="D128" s="4" t="n">
-        <v>72</v>
+        <v>71.61</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>-0.067</v>
+        <v>-0.07200000000000001</v>
       </c>
       <c r="F128" s="5" t="n">
-        <v>-0.0445</v>
+        <v>-0.0496</v>
       </c>
       <c r="G128" s="7" t="n">
         <v>46329</v>
@@ -11020,13 +11020,13 @@
         </is>
       </c>
       <c r="D129" s="15" t="n">
-        <v>265.45</v>
+        <v>263.68</v>
       </c>
       <c r="E129" s="16" t="n">
-        <v>-0.062</v>
+        <v>-0.0683</v>
       </c>
       <c r="F129" s="17" t="n">
-        <v>0.0614</v>
+        <v>0.05429999999999999</v>
       </c>
       <c r="G129" s="18" t="n">
         <v>46330</v>
@@ -11055,7 +11055,7 @@
         <v>248</v>
       </c>
       <c r="M129" s="16" t="n">
-        <v>-0.06573742701073644</v>
+        <v>-0.05946601941747575</v>
       </c>
       <c r="N129" s="14" t="inlineStr"/>
       <c r="O129" s="20" t="n"/>
@@ -11111,13 +11111,13 @@
         </is>
       </c>
       <c r="D130" s="4" t="n">
-        <v>123.09</v>
+        <v>121.68</v>
       </c>
       <c r="E130" s="6" t="n">
-        <v>0.1177</v>
+        <v>0.1049</v>
       </c>
       <c r="F130" s="6" t="n">
-        <v>0.0155</v>
+        <v>0.0039</v>
       </c>
       <c r="G130" s="7" t="n">
         <v>46325</v>
@@ -11172,13 +11172,13 @@
         </is>
       </c>
       <c r="D131" s="15" t="n">
-        <v>246.81</v>
+        <v>246.45</v>
       </c>
       <c r="E131" s="17" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="F131" s="17" t="n">
         <v>0.0185</v>
-      </c>
-      <c r="F131" s="17" t="n">
-        <v>0.02</v>
       </c>
       <c r="G131" s="18" t="n">
         <v>46324</v>
@@ -11233,13 +11233,13 @@
         </is>
       </c>
       <c r="D132" s="4" t="n">
-        <v>203.41</v>
+        <v>199.93</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>-0.0335</v>
+        <v>-0.05</v>
       </c>
       <c r="F132" s="5" t="n">
-        <v>-0.0292</v>
+        <v>-0.0458</v>
       </c>
       <c r="G132" s="7" t="n">
         <v>46330</v>
@@ -11268,7 +11268,7 @@
         <v>250</v>
       </c>
       <c r="M132" s="6" t="n">
-        <v>0.2290447863920161</v>
+        <v>0.2504376531786125</v>
       </c>
       <c r="N132" s="3" t="inlineStr"/>
       <c r="O132" s="9" t="n"/>
@@ -11312,13 +11312,13 @@
         </is>
       </c>
       <c r="D133" s="15" t="n">
-        <v>164.21</v>
+        <v>163.45</v>
       </c>
       <c r="E133" s="16" t="n">
-        <v>-0.1145</v>
+        <v>-0.1186</v>
       </c>
       <c r="F133" s="17" t="n">
-        <v>0.1027</v>
+        <v>0.09759999999999999</v>
       </c>
       <c r="G133" s="18" t="n">
         <v>46329</v>
@@ -11383,13 +11383,13 @@
         </is>
       </c>
       <c r="D134" s="4" t="n">
-        <v>808.79</v>
-      </c>
-      <c r="E134" s="5" t="n">
-        <v>-0.0027</v>
+        <v>812.02</v>
+      </c>
+      <c r="E134" s="6" t="n">
+        <v>0.0012</v>
       </c>
       <c r="F134" s="5" t="n">
-        <v>-0.08990000000000001</v>
+        <v>-0.0863</v>
       </c>
       <c r="G134" s="7" t="n">
         <v>46330</v>
@@ -11418,7 +11418,7 @@
         <v>1155</v>
       </c>
       <c r="M134" s="6" t="n">
-        <v>0.4280591995449994</v>
+        <v>0.4223787591438635</v>
       </c>
       <c r="N134" s="3" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>1103</v>
       </c>
       <c r="P134" s="6" t="n">
-        <v>0.3637656251931899</v>
+        <v>0.3583409275633606</v>
       </c>
       <c r="Q134" s="10" t="inlineStr">
         <is>
@@ -11470,13 +11470,13 @@
         </is>
       </c>
       <c r="D135" s="15" t="n">
-        <v>519.4</v>
+        <v>524.65</v>
       </c>
       <c r="E135" s="16" t="n">
-        <v>-0.09140000000000001</v>
+        <v>-0.08220000000000001</v>
       </c>
       <c r="F135" s="16" t="n">
-        <v>-0.2185</v>
+        <v>-0.2106</v>
       </c>
       <c r="G135" s="18" t="n">
         <v>46331</v>
@@ -11505,7 +11505,7 @@
         <v>874</v>
       </c>
       <c r="M135" s="17" t="n">
-        <v>0.6827108201771275</v>
+        <v>0.6658724864195178</v>
       </c>
       <c r="N135" s="14" t="inlineStr">
         <is>
@@ -11516,7 +11516,7 @@
         <v>845</v>
       </c>
       <c r="P135" s="17" t="n">
-        <v>0.626877165960724</v>
+        <v>0.6105975412179548</v>
       </c>
       <c r="Q135" s="21" t="inlineStr">
         <is>
@@ -11565,13 +11565,13 @@
         </is>
       </c>
       <c r="D136" s="4" t="n">
-        <v>197.28</v>
+        <v>191.97</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>-0.0488</v>
+        <v>-0.07440000000000001</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>-0.04190000000000001</v>
+        <v>-0.0677</v>
       </c>
       <c r="G136" s="7" t="n">
         <v>46288</v>
@@ -11600,7 +11600,7 @@
         <v>250</v>
       </c>
       <c r="M136" s="6" t="n">
-        <v>0.2672343876723439</v>
+        <v>0.3022868156482784</v>
       </c>
       <c r="N136" s="3" t="inlineStr"/>
       <c r="O136" s="9" t="n"/>
@@ -11644,13 +11644,13 @@
         </is>
       </c>
       <c r="D137" s="15" t="n">
-        <v>712.39</v>
+        <v>709.48</v>
       </c>
       <c r="E137" s="17" t="n">
-        <v>0.0983</v>
+        <v>0.09380000000000001</v>
       </c>
       <c r="F137" s="17" t="n">
-        <v>0.1341</v>
+        <v>0.1295</v>
       </c>
       <c r="G137" s="18" t="n"/>
       <c r="H137" s="23" t="inlineStr">
@@ -11669,7 +11669,7 @@
         <v>750</v>
       </c>
       <c r="M137" s="17" t="n">
-        <v>0.05279411558275666</v>
+        <v>0.05711225122625018</v>
       </c>
       <c r="N137" s="14" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         <v>641.29</v>
       </c>
       <c r="P137" s="16" t="n">
-        <v>-0.09980488215724537</v>
+        <v>-0.09611264588149074</v>
       </c>
       <c r="Q137" s="21" t="inlineStr">
         <is>
@@ -11721,13 +11721,13 @@
         </is>
       </c>
       <c r="D138" s="4" t="n">
-        <v>155.15</v>
+        <v>154.59</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>-0.0153</v>
+        <v>-0.0189</v>
       </c>
       <c r="F138" s="6" t="n">
-        <v>0.0488</v>
+        <v>0.045</v>
       </c>
       <c r="G138" s="7" t="n">
         <v>46330</v>
@@ -11763,7 +11763,7 @@
         <v>185</v>
       </c>
       <c r="P138" s="6" t="n">
-        <v>0.1923944569771189</v>
+        <v>0.1967138883498286</v>
       </c>
       <c r="Q138" s="10" t="inlineStr">
         <is>
@@ -11802,13 +11802,13 @@
         </is>
       </c>
       <c r="D139" s="15" t="n">
-        <v>440.39</v>
+        <v>438.76</v>
       </c>
       <c r="E139" s="17" t="n">
-        <v>0.0776</v>
+        <v>0.0736</v>
       </c>
       <c r="F139" s="17" t="n">
-        <v>0.08990000000000001</v>
+        <v>0.0859</v>
       </c>
       <c r="G139" s="18" t="n">
         <v>46329</v>
@@ -11844,7 +11844,7 @@
         <v>453</v>
       </c>
       <c r="P139" s="17" t="n">
-        <v>0.02863371102886082</v>
+        <v>0.03245510073844473</v>
       </c>
       <c r="Q139" s="21" t="inlineStr">
         <is>
@@ -11885,13 +11885,13 @@
         </is>
       </c>
       <c r="D140" s="4" t="n">
-        <v>50.47</v>
+        <v>50.99</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>-0.0159</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F140" s="6" t="n">
-        <v>0.0733</v>
+        <v>0.08439999999999999</v>
       </c>
       <c r="G140" s="7" t="n">
         <v>46309</v>
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="D141" s="15" t="n">
-        <v>293.83</v>
+        <v>291.5</v>
       </c>
       <c r="E141" s="16" t="n">
-        <v>-0.1204</v>
+        <v>-0.1274</v>
       </c>
       <c r="F141" s="16" t="n">
-        <v>-0.06709999999999999</v>
+        <v>-0.0745</v>
       </c>
       <c r="G141" s="18" t="n">
         <v>46282</v>
@@ -11999,7 +11999,7 @@
         <v>425</v>
       </c>
       <c r="M141" s="17" t="n">
-        <v>0.4464145934724161</v>
+        <v>0.4579759862778731</v>
       </c>
       <c r="N141" s="14" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>323</v>
       </c>
       <c r="P141" s="17" t="n">
-        <v>0.09927509103903624</v>
+        <v>0.1080617495711835</v>
       </c>
       <c r="Q141" s="21" t="inlineStr">
         <is>
@@ -12051,13 +12051,13 @@
         </is>
       </c>
       <c r="D142" s="4" t="n">
-        <v>223.11</v>
+        <v>221.17</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>-0.0564</v>
+        <v>-0.0646</v>
       </c>
       <c r="F142" s="5" t="n">
-        <v>-0.0328</v>
+        <v>-0.0412</v>
       </c>
       <c r="G142" s="7" t="n"/>
       <c r="H142" s="12" t="inlineStr">
@@ -12076,7 +12076,7 @@
         <v>285</v>
       </c>
       <c r="M142" s="6" t="n">
-        <v>0.2773967997848594</v>
+        <v>0.2886015282361984</v>
       </c>
       <c r="N142" s="3" t="inlineStr"/>
       <c r="O142" s="9" t="n"/>
@@ -12124,13 +12124,13 @@
         </is>
       </c>
       <c r="D143" s="15" t="n">
-        <v>1634.99</v>
+        <v>1625.9</v>
       </c>
       <c r="E143" s="17" t="n">
-        <v>0.0157</v>
+        <v>0.0101</v>
       </c>
       <c r="F143" s="16" t="n">
-        <v>-0.05690000000000001</v>
+        <v>-0.0621</v>
       </c>
       <c r="G143" s="18" t="n">
         <v>46317</v>
@@ -12185,13 +12185,13 @@
         </is>
       </c>
       <c r="D144" s="4" t="n">
-        <v>54.02</v>
+        <v>53.06</v>
       </c>
       <c r="E144" s="6" t="n">
-        <v>0.0534</v>
+        <v>0.0347</v>
       </c>
       <c r="F144" s="6" t="n">
-        <v>0.0351</v>
+        <v>0.0167</v>
       </c>
       <c r="G144" s="7" t="n">
         <v>46332</v>
@@ -12246,13 +12246,13 @@
         </is>
       </c>
       <c r="D145" s="15" t="n">
-        <v>346.43</v>
+        <v>343.33</v>
       </c>
       <c r="E145" s="16" t="n">
-        <v>-0.0973</v>
+        <v>-0.1054</v>
       </c>
       <c r="F145" s="16" t="n">
-        <v>-0.1043</v>
+        <v>-0.1123</v>
       </c>
       <c r="G145" s="18" t="n">
         <v>46318</v>
@@ -12281,7 +12281,7 @@
         <v>400</v>
       </c>
       <c r="M145" s="17" t="n">
-        <v>0.1546344138787056</v>
+        <v>0.1650598549500481</v>
       </c>
       <c r="N145" s="14" t="inlineStr"/>
       <c r="O145" s="20" t="n"/>
@@ -12333,13 +12333,13 @@
         </is>
       </c>
       <c r="D146" s="4" t="n">
-        <v>321.14</v>
+        <v>319.8</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>-0.0605</v>
+        <v>-0.0645</v>
       </c>
       <c r="F146" s="5" t="n">
-        <v>-0.09210000000000002</v>
+        <v>-0.0959</v>
       </c>
       <c r="G146" s="7" t="n">
         <v>46315</v>
@@ -12368,7 +12368,7 @@
         <v>390</v>
       </c>
       <c r="M146" s="6" t="n">
-        <v>0.2144236158684686</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="N146" s="3" t="inlineStr"/>
       <c r="O146" s="9" t="n"/>
@@ -12420,10 +12420,10 @@
         </is>
       </c>
       <c r="D147" s="15" t="n">
-        <v>951.88</v>
+        <v>951.8200000000001</v>
       </c>
       <c r="E147" s="17" t="n">
-        <v>0.0104</v>
+        <v>0.0103</v>
       </c>
       <c r="F147" s="16" t="n">
         <v>-0.062</v>
@@ -12455,7 +12455,7 @@
         <v>1259</v>
       </c>
       <c r="M147" s="17" t="n">
-        <v>0.3226457116443249</v>
+        <v>0.3227290874324977</v>
       </c>
       <c r="N147" s="14" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         <v>1350</v>
       </c>
       <c r="P147" s="17" t="n">
-        <v>0.4182459973946296</v>
+        <v>0.4183353995503351</v>
       </c>
       <c r="Q147" s="21" t="inlineStr">
         <is>
@@ -12511,13 +12511,13 @@
         </is>
       </c>
       <c r="D148" s="4" t="n">
-        <v>1267.99</v>
+        <v>1270.67</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>-0.0408</v>
+        <v>-0.0388</v>
       </c>
       <c r="F148" s="5" t="n">
-        <v>-0.08289999999999999</v>
+        <v>-0.081</v>
       </c>
       <c r="G148" s="7" t="n">
         <v>46330</v>
@@ -12589,7 +12589,7 @@
         <v>212.57</v>
       </c>
       <c r="E149" s="16" t="n">
-        <v>-0.0103</v>
+        <v>-0.0102</v>
       </c>
       <c r="F149" s="16" t="n">
         <v>-0.1258</v>
@@ -12647,13 +12647,13 @@
         </is>
       </c>
       <c r="D150" s="4" t="n">
-        <v>463.88</v>
+        <v>463.7</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>-0.0062</v>
+        <v>-0.0066</v>
       </c>
       <c r="F150" s="5" t="n">
-        <v>-0.0457</v>
+        <v>-0.0461</v>
       </c>
       <c r="G150" s="7" t="n">
         <v>46322</v>
@@ -12714,13 +12714,13 @@
         </is>
       </c>
       <c r="D151" s="15" t="n">
-        <v>273.38</v>
+        <v>273.42</v>
       </c>
       <c r="E151" s="16" t="n">
-        <v>-0.0372</v>
+        <v>-0.0371</v>
       </c>
       <c r="F151" s="16" t="n">
-        <v>-0.0341</v>
+        <v>-0.0339</v>
       </c>
       <c r="G151" s="18" t="n">
         <v>46318</v>
@@ -12752,7 +12752,7 @@
         <v>272</v>
       </c>
       <c r="P151" s="16" t="n">
-        <v>-0.005047918648035684</v>
+        <v>-0.005193475239558247</v>
       </c>
       <c r="Q151" s="21" t="inlineStr">
         <is>
@@ -12805,13 +12805,13 @@
         </is>
       </c>
       <c r="D152" s="4" t="n">
-        <v>242.16</v>
+        <v>239.21</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>-0.0786</v>
+        <v>-0.08990000000000001</v>
       </c>
       <c r="F152" s="5" t="n">
-        <v>-0.1934</v>
+        <v>-0.2032</v>
       </c>
       <c r="G152" s="7" t="n">
         <v>46324</v>
@@ -12876,13 +12876,13 @@
         </is>
       </c>
       <c r="D153" s="15" t="n">
-        <v>371.8</v>
+        <v>372.34</v>
       </c>
       <c r="E153" s="16" t="n">
-        <v>-0.0684</v>
+        <v>-0.06709999999999999</v>
       </c>
       <c r="F153" s="16" t="n">
-        <v>-0.3129</v>
+        <v>-0.3119</v>
       </c>
       <c r="G153" s="18" t="n">
         <v>46323</v>
@@ -12937,13 +12937,13 @@
         </is>
       </c>
       <c r="D154" s="4" t="n">
-        <v>528.79</v>
+        <v>524.6799999999999</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>-0.06269999999999999</v>
+        <v>-0.0699</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>-0.0924</v>
+        <v>-0.09939999999999999</v>
       </c>
       <c r="G154" s="7" t="n">
         <v>46315</v>
@@ -13004,13 +13004,13 @@
         </is>
       </c>
       <c r="D155" s="15" t="n">
-        <v>177.98</v>
+        <v>177.72</v>
       </c>
       <c r="E155" s="16" t="n">
-        <v>-0.1166</v>
+        <v>-0.1179</v>
       </c>
       <c r="F155" s="16" t="n">
-        <v>-0.2361</v>
+        <v>-0.2372</v>
       </c>
       <c r="G155" s="18" t="n">
         <v>46330</v>
@@ -13039,7 +13039,7 @@
         <v>575</v>
       </c>
       <c r="M155" s="17" t="n">
-        <v>2.230700078660524</v>
+        <v>2.235426513616925</v>
       </c>
       <c r="N155" s="14" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>237</v>
       </c>
       <c r="P155" s="17" t="n">
-        <v>0.3316102932913811</v>
+        <v>0.3335584064821067</v>
       </c>
       <c r="Q155" s="21" t="inlineStr">
         <is>
@@ -13099,13 +13099,13 @@
         </is>
       </c>
       <c r="D156" s="4" t="n">
-        <v>106.46</v>
+        <v>104.49</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>-0.1551</v>
+        <v>-0.1708</v>
       </c>
       <c r="F156" s="5" t="n">
-        <v>-0.0624</v>
+        <v>-0.07980000000000001</v>
       </c>
       <c r="G156" s="7" t="n">
         <v>46288</v>
@@ -13134,7 +13134,7 @@
         <v>250</v>
       </c>
       <c r="M156" s="6" t="n">
-        <v>1.348299830922412</v>
+        <v>1.392573452004977</v>
       </c>
       <c r="N156" s="3" t="inlineStr"/>
       <c r="O156" s="9" t="n"/>
@@ -13178,13 +13178,13 @@
         </is>
       </c>
       <c r="D157" s="15" t="n">
-        <v>112.41</v>
+        <v>112.09</v>
       </c>
       <c r="E157" s="16" t="n">
-        <v>-0.1349</v>
+        <v>-0.1374</v>
       </c>
       <c r="F157" s="16" t="n">
-        <v>-0.15</v>
+        <v>-0.1524</v>
       </c>
       <c r="G157" s="18" t="n">
         <v>46315</v>
@@ -13213,7 +13213,7 @@
         <v>95</v>
       </c>
       <c r="M157" s="16" t="n">
-        <v>-0.1548794591228538</v>
+        <v>-0.1524667677758944</v>
       </c>
       <c r="N157" s="14" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>139</v>
       </c>
       <c r="P157" s="17" t="n">
-        <v>0.2365447913886665</v>
+        <v>0.2400749397805335</v>
       </c>
       <c r="Q157" s="21" t="inlineStr">
         <is>
@@ -13269,13 +13269,13 @@
         </is>
       </c>
       <c r="D158" s="4" t="n">
-        <v>974.4</v>
+        <v>971.21</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>-0.0393</v>
+        <v>-0.0424</v>
       </c>
       <c r="F158" s="5" t="n">
-        <v>-0.0133</v>
+        <v>-0.0165</v>
       </c>
       <c r="G158" s="7" t="n">
         <v>46331</v>
@@ -13304,7 +13304,7 @@
         <v>125</v>
       </c>
       <c r="M158" s="5" t="n">
-        <v>-0.8717159277504105</v>
+        <v>-0.87129457069017</v>
       </c>
       <c r="N158" s="3" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>1064</v>
       </c>
       <c r="P158" s="6" t="n">
-        <v>0.09195402298850577</v>
+        <v>0.09554061428527297</v>
       </c>
       <c r="Q158" s="10" t="inlineStr">
         <is>
@@ -13360,13 +13360,13 @@
         </is>
       </c>
       <c r="D159" s="15" t="n">
-        <v>505.86</v>
+        <v>500.26</v>
       </c>
       <c r="E159" s="17" t="n">
-        <v>0.0201</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="F159" s="16" t="n">
-        <v>-0.1499</v>
+        <v>-0.1593</v>
       </c>
       <c r="G159" s="18" t="n">
         <v>46325</v>
@@ -13441,13 +13441,13 @@
         </is>
       </c>
       <c r="D160" s="4" t="n">
-        <v>434.21</v>
+        <v>432.89</v>
       </c>
       <c r="E160" s="6" t="n">
-        <v>0.0105</v>
+        <v>0.0074</v>
       </c>
       <c r="F160" s="5" t="n">
-        <v>-0.0605</v>
+        <v>-0.0633</v>
       </c>
       <c r="G160" s="7" t="n">
         <v>46331</v>
@@ -13502,13 +13502,13 @@
         </is>
       </c>
       <c r="D161" s="15" t="n">
-        <v>32.56</v>
+        <v>32.49</v>
       </c>
       <c r="E161" s="16" t="n">
-        <v>-0.1261</v>
+        <v>-0.128</v>
       </c>
       <c r="F161" s="16" t="n">
-        <v>-0.1556</v>
+        <v>-0.1574</v>
       </c>
       <c r="G161" s="18" t="n">
         <v>46323</v>
@@ -13577,13 +13577,13 @@
         </is>
       </c>
       <c r="D162" s="4" t="n">
-        <v>193.91</v>
+        <v>192.19</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>-0.0732</v>
+        <v>-0.0814</v>
       </c>
       <c r="F162" s="5" t="n">
-        <v>-0.08869999999999999</v>
+        <v>-0.0968</v>
       </c>
       <c r="G162" s="7" t="n">
         <v>46315</v>
@@ -13656,13 +13656,13 @@
         </is>
       </c>
       <c r="D163" s="15" t="n">
-        <v>43.88</v>
+        <v>43.69</v>
       </c>
       <c r="E163" s="17" t="n">
-        <v>0.09630000000000001</v>
+        <v>0.09140000000000001</v>
       </c>
       <c r="F163" s="17" t="n">
-        <v>0.09300000000000001</v>
+        <v>0.0882</v>
       </c>
       <c r="G163" s="18" t="n"/>
       <c r="H163" s="23" t="inlineStr">
@@ -13707,13 +13707,13 @@
         </is>
       </c>
       <c r="D164" s="4" t="n">
-        <v>440.67</v>
+        <v>437.09</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>-0.0271</v>
+        <v>-0.035</v>
       </c>
       <c r="F164" s="5" t="n">
-        <v>-0.08380000000000001</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="G164" s="7" t="n">
         <v>46324</v>
@@ -13745,7 +13745,7 @@
         <v>560</v>
       </c>
       <c r="P164" s="6" t="n">
-        <v>0.2707922027821272</v>
+        <v>0.2812006680546341</v>
       </c>
       <c r="Q164" s="10" t="inlineStr">
         <is>
@@ -13798,13 +13798,13 @@
         </is>
       </c>
       <c r="D165" s="15" t="n">
-        <v>275.27</v>
+        <v>275.53</v>
       </c>
       <c r="E165" s="16" t="n">
-        <v>-0.1116</v>
+        <v>-0.1108</v>
       </c>
       <c r="F165" s="16" t="n">
-        <v>-0.1043</v>
+        <v>-0.1034</v>
       </c>
       <c r="G165" s="18" t="n">
         <v>46317</v>
@@ -13836,7 +13836,7 @@
         <v>294</v>
       </c>
       <c r="P165" s="17" t="n">
-        <v>0.06804228575580347</v>
+        <v>0.06703444271041277</v>
       </c>
       <c r="Q165" s="21" t="inlineStr">
         <is>
@@ -13881,13 +13881,13 @@
         </is>
       </c>
       <c r="D166" s="4" t="n">
-        <v>253.57</v>
+        <v>248.78</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>-0.005500000000000001</v>
+        <v>-0.0243</v>
       </c>
       <c r="F166" s="5" t="n">
-        <v>-0.1267</v>
+        <v>-0.1432</v>
       </c>
       <c r="G166" s="7" t="n">
         <v>46323</v>
@@ -13919,7 +13919,7 @@
         <v>425</v>
       </c>
       <c r="P166" s="6" t="n">
-        <v>0.6760657806522854</v>
+        <v>0.7083366830131039</v>
       </c>
       <c r="Q166" s="10" t="inlineStr">
         <is>
@@ -13960,13 +13960,13 @@
         </is>
       </c>
       <c r="D167" s="15" t="n">
-        <v>208</v>
+        <v>207.88</v>
       </c>
       <c r="E167" s="16" t="n">
-        <v>-0.0815</v>
+        <v>-0.08199999999999999</v>
       </c>
       <c r="F167" s="16" t="n">
-        <v>-0.1288</v>
+        <v>-0.1293</v>
       </c>
       <c r="G167" s="18" t="n">
         <v>46321</v>
@@ -13995,7 +13995,7 @@
         <v>268</v>
       </c>
       <c r="M167" s="17" t="n">
-        <v>0.2884615384615384</v>
+        <v>0.2892053107562055</v>
       </c>
       <c r="N167" s="14" t="inlineStr"/>
       <c r="O167" s="20" t="n"/>
@@ -14043,13 +14043,13 @@
         </is>
       </c>
       <c r="D168" s="4" t="n">
-        <v>327.39</v>
+        <v>325.37</v>
       </c>
       <c r="E168" s="6" t="n">
-        <v>0.0534</v>
+        <v>0.0469</v>
       </c>
       <c r="F168" s="5" t="n">
-        <v>-0.0956</v>
+        <v>-0.1012</v>
       </c>
       <c r="G168" s="7" t="n">
         <v>46330</v>
@@ -14118,13 +14118,13 @@
         </is>
       </c>
       <c r="D169" s="15" t="n">
-        <v>327.77</v>
+        <v>326.23</v>
       </c>
       <c r="E169" s="16" t="n">
-        <v>-0.0161</v>
+        <v>-0.0208</v>
       </c>
       <c r="F169" s="16" t="n">
-        <v>-0.2177</v>
+        <v>-0.2214</v>
       </c>
       <c r="G169" s="18" t="n"/>
       <c r="H169" s="23" t="inlineStr">
@@ -14187,13 +14187,13 @@
         </is>
       </c>
       <c r="D170" s="4" t="n">
-        <v>108.53</v>
+        <v>108.64</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>-0.0495</v>
+        <v>-0.04849999999999999</v>
       </c>
       <c r="F170" s="5" t="n">
-        <v>-0.09369999999999999</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="G170" s="7" t="n">
         <v>46322</v>
@@ -14266,13 +14266,13 @@
         </is>
       </c>
       <c r="D171" s="15" t="n">
-        <v>104.11</v>
+        <v>101.06</v>
       </c>
       <c r="E171" s="16" t="n">
-        <v>-0.0327</v>
+        <v>-0.061</v>
       </c>
       <c r="F171" s="17" t="n">
-        <v>0.0395</v>
+        <v>0.0091</v>
       </c>
       <c r="G171" s="18" t="n">
         <v>46331</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="D172" s="4" t="n">
-        <v>338.01</v>
+        <v>337.02</v>
       </c>
       <c r="E172" s="6" t="n">
-        <v>0.0892</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="F172" s="6" t="n">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
       <c r="G172" s="7" t="n">
         <v>46324</v>
@@ -14362,7 +14362,7 @@
         <v>310</v>
       </c>
       <c r="M172" s="5" t="n">
-        <v>-0.08286737078784649</v>
+        <v>-0.08017328348465962</v>
       </c>
       <c r="N172" s="3" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>365</v>
       </c>
       <c r="P172" s="6" t="n">
-        <v>0.07984970858850332</v>
+        <v>0.08302177912290078</v>
       </c>
       <c r="Q172" s="10" t="inlineStr">
         <is>
@@ -14430,13 +14430,13 @@
         </is>
       </c>
       <c r="D173" s="15" t="n">
-        <v>114.51</v>
+        <v>118.43</v>
       </c>
       <c r="E173" s="16" t="n">
-        <v>-0.0727</v>
+        <v>-0.04099999999999999</v>
       </c>
       <c r="F173" s="16" t="n">
-        <v>-0.146</v>
+        <v>-0.1169</v>
       </c>
       <c r="G173" s="18" t="n">
         <v>46329</v>
@@ -14491,13 +14491,13 @@
         </is>
       </c>
       <c r="D174" s="4" t="n">
-        <v>183.91</v>
+        <v>183.52</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>-0.014</v>
+        <v>-0.0161</v>
       </c>
       <c r="F174" s="6" t="n">
-        <v>0.2512</v>
+        <v>0.2485</v>
       </c>
       <c r="G174" s="7" t="n">
         <v>46296</v>
@@ -14552,13 +14552,13 @@
         </is>
       </c>
       <c r="D175" s="15" t="n">
-        <v>241.2</v>
+        <v>240.69</v>
       </c>
       <c r="E175" s="16" t="n">
-        <v>-0.1269</v>
+        <v>-0.1288</v>
       </c>
       <c r="F175" s="17" t="n">
-        <v>0.07150000000000001</v>
+        <v>0.0692</v>
       </c>
       <c r="G175" s="18" t="n"/>
       <c r="H175" s="23" t="inlineStr">
@@ -14603,13 +14603,13 @@
         </is>
       </c>
       <c r="D176" s="4" t="n">
-        <v>384.17</v>
+        <v>385.23</v>
       </c>
       <c r="E176" s="6" t="n">
-        <v>0.035</v>
+        <v>0.0379</v>
       </c>
       <c r="F176" s="6" t="n">
-        <v>0.0331</v>
+        <v>0.036</v>
       </c>
       <c r="G176" s="7" t="n"/>
       <c r="H176" s="12" t="inlineStr">
@@ -14628,7 +14628,7 @@
         <v>515</v>
       </c>
       <c r="M176" s="6" t="n">
-        <v>0.3405523596324543</v>
+        <v>0.3368636918204708</v>
       </c>
       <c r="N176" s="3" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>474</v>
       </c>
       <c r="P176" s="6" t="n">
-        <v>0.2338287737199677</v>
+        <v>0.2304337668405887</v>
       </c>
       <c r="Q176" s="10" t="inlineStr">
         <is>
@@ -14688,13 +14688,13 @@
         </is>
       </c>
       <c r="D177" s="15" t="n">
-        <v>219.18</v>
+        <v>217.15</v>
       </c>
       <c r="E177" s="16" t="n">
-        <v>-0.1385</v>
+        <v>-0.1465</v>
       </c>
       <c r="F177" s="17" t="n">
-        <v>0.045</v>
+        <v>0.0353</v>
       </c>
       <c r="G177" s="18" t="n"/>
       <c r="H177" s="23" t="inlineStr">
@@ -14739,13 +14739,13 @@
         </is>
       </c>
       <c r="D178" s="4" t="n">
-        <v>276.67</v>
+        <v>279.43</v>
       </c>
       <c r="E178" s="6" t="n">
-        <v>0.0073</v>
+        <v>0.0173</v>
       </c>
       <c r="F178" s="5" t="n">
-        <v>-0.08990000000000001</v>
+        <v>-0.0808</v>
       </c>
       <c r="G178" s="7" t="n">
         <v>46329</v>
@@ -14800,13 +14800,13 @@
         </is>
       </c>
       <c r="D179" s="15" t="n">
-        <v>358.08</v>
+        <v>360.46</v>
       </c>
       <c r="E179" s="17" t="n">
-        <v>0.2902</v>
+        <v>0.2988</v>
       </c>
       <c r="F179" s="17" t="n">
-        <v>0.2281</v>
+        <v>0.2362</v>
       </c>
       <c r="G179" s="18" t="n">
         <v>46329</v>
@@ -14861,13 +14861,13 @@
         </is>
       </c>
       <c r="D180" s="4" t="n">
-        <v>35.54</v>
+        <v>35.11</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>-0.0025</v>
+        <v>-0.0146</v>
       </c>
       <c r="F180" s="5" t="n">
-        <v>-0.2279</v>
+        <v>-0.2372</v>
       </c>
       <c r="G180" s="7" t="n">
         <v>46324</v>
@@ -14922,13 +14922,13 @@
         </is>
       </c>
       <c r="D181" s="15" t="n">
-        <v>471.76</v>
+        <v>474.38</v>
       </c>
       <c r="E181" s="16" t="n">
-        <v>-0.0257</v>
+        <v>-0.0203</v>
       </c>
       <c r="F181" s="16" t="n">
-        <v>-0.1203</v>
+        <v>-0.1154</v>
       </c>
       <c r="G181" s="18" t="n">
         <v>46338</v>
@@ -14957,7 +14957,7 @@
         <v>740</v>
       </c>
       <c r="M181" s="17" t="n">
-        <v>0.5685942004409021</v>
+        <v>0.5599308571187656</v>
       </c>
       <c r="N181" s="14" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>700</v>
       </c>
       <c r="P181" s="17" t="n">
-        <v>0.483805324741394</v>
+        <v>0.4756102702474809</v>
       </c>
       <c r="Q181" s="21" t="inlineStr">
         <is>
@@ -15009,13 +15009,13 @@
         </is>
       </c>
       <c r="D182" s="4" t="n">
-        <v>68.23999999999999</v>
+        <v>69.13</v>
       </c>
       <c r="E182" s="6" t="n">
-        <v>0.2028</v>
+        <v>0.2186</v>
       </c>
       <c r="F182" s="5" t="n">
-        <v>-0.0291</v>
+        <v>-0.0164</v>
       </c>
       <c r="G182" s="7" t="n">
         <v>46331</v>
@@ -15074,13 +15074,13 @@
         </is>
       </c>
       <c r="D183" s="15" t="n">
-        <v>616.15</v>
+        <v>614.61</v>
       </c>
       <c r="E183" s="17" t="n">
-        <v>0.349</v>
+        <v>0.3456</v>
       </c>
       <c r="F183" s="17" t="n">
-        <v>0.1805</v>
+        <v>0.1775</v>
       </c>
       <c r="G183" s="18" t="n">
         <v>46329</v>
@@ -15108,8 +15108,8 @@
       <c r="L183" s="20" t="n">
         <v>615</v>
       </c>
-      <c r="M183" s="16" t="n">
-        <v>-0.001866428629392157</v>
+      <c r="M183" s="17" t="n">
+        <v>0.0006345487382242175</v>
       </c>
       <c r="N183" s="14" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>579</v>
       </c>
       <c r="P183" s="16" t="n">
-        <v>-0.06029375963645213</v>
+        <v>-0.0579391809440133</v>
       </c>
       <c r="Q183" s="21" t="inlineStr">
         <is>
@@ -15161,13 +15161,13 @@
         </is>
       </c>
       <c r="D184" s="4" t="n">
-        <v>53.53</v>
+        <v>53.32</v>
       </c>
       <c r="E184" s="6" t="n">
-        <v>0.1175</v>
+        <v>0.1132</v>
       </c>
       <c r="F184" s="5" t="n">
-        <v>-0.176</v>
+        <v>-0.1792</v>
       </c>
       <c r="G184" s="7" t="n">
         <v>46321</v>
@@ -15222,13 +15222,13 @@
         </is>
       </c>
       <c r="D185" s="15" t="n">
-        <v>201.91</v>
+        <v>203.47</v>
       </c>
       <c r="E185" s="17" t="n">
-        <v>0.0731</v>
+        <v>0.0814</v>
       </c>
       <c r="F185" s="17" t="n">
-        <v>0.1605</v>
+        <v>0.1694</v>
       </c>
       <c r="G185" s="18" t="n">
         <v>46329</v>
@@ -15257,7 +15257,7 @@
         <v>200</v>
       </c>
       <c r="M185" s="16" t="n">
-        <v>-0.009459660244663447</v>
+        <v>-0.01705411117118002</v>
       </c>
       <c r="N185" s="14" t="inlineStr">
         <is>
@@ -15268,7 +15268,7 @@
         <v>200</v>
       </c>
       <c r="P185" s="16" t="n">
-        <v>-0.009459660244663447</v>
+        <v>-0.01705411117118002</v>
       </c>
       <c r="Q185" s="21" t="inlineStr">
         <is>
@@ -15313,13 +15313,13 @@
         </is>
       </c>
       <c r="D186" s="4" t="n">
-        <v>82.38</v>
+        <v>82.19</v>
       </c>
       <c r="E186" s="6" t="n">
-        <v>0.0592</v>
+        <v>0.0568</v>
       </c>
       <c r="F186" s="6" t="n">
-        <v>0.07919999999999999</v>
+        <v>0.0767</v>
       </c>
       <c r="G186" s="7" t="n">
         <v>46323</v>
@@ -15351,7 +15351,7 @@
         <v>180</v>
       </c>
       <c r="P186" s="6" t="n">
-        <v>1.184996358339403</v>
+        <v>1.190047451028106</v>
       </c>
       <c r="Q186" s="10" t="inlineStr">
         <is>
@@ -15404,13 +15404,13 @@
         </is>
       </c>
       <c r="D187" s="15" t="n">
-        <v>28.5</v>
+        <v>27.23</v>
       </c>
       <c r="E187" s="17" t="n">
-        <v>0.0599</v>
+        <v>0.0126</v>
       </c>
       <c r="F187" s="17" t="n">
-        <v>0.0482</v>
+        <v>0.0015</v>
       </c>
       <c r="G187" s="18" t="n">
         <v>46303</v>
@@ -15465,13 +15465,13 @@
         </is>
       </c>
       <c r="D188" s="4" t="n">
-        <v>327.02</v>
+        <v>332.56</v>
       </c>
       <c r="E188" s="6" t="n">
-        <v>0.3696</v>
+        <v>0.3927</v>
       </c>
       <c r="F188" s="6" t="n">
-        <v>0.2577</v>
+        <v>0.279</v>
       </c>
       <c r="G188" s="7" t="n">
         <v>46330</v>
@@ -15526,13 +15526,13 @@
         </is>
       </c>
       <c r="D189" s="15" t="n">
-        <v>1730.43</v>
-      </c>
-      <c r="E189" s="16" t="n">
-        <v>-0.005600000000000001</v>
+        <v>1744.61</v>
+      </c>
+      <c r="E189" s="17" t="n">
+        <v>0.0026</v>
       </c>
       <c r="F189" s="16" t="n">
-        <v>-0.0152</v>
+        <v>-0.0071</v>
       </c>
       <c r="G189" s="18" t="n">
         <v>46309</v>
@@ -15605,13 +15605,13 @@
         </is>
       </c>
       <c r="D190" s="4" t="n">
-        <v>44.01</v>
+        <v>43.93</v>
       </c>
       <c r="E190" s="6" t="n">
-        <v>0.2145</v>
+        <v>0.2122</v>
       </c>
       <c r="F190" s="6" t="n">
-        <v>0.1948</v>
+        <v>0.1925</v>
       </c>
       <c r="G190" s="7" t="n">
         <v>46324</v>
@@ -15666,13 +15666,13 @@
         </is>
       </c>
       <c r="D191" s="15" t="n">
-        <v>356.77</v>
+        <v>354.99</v>
       </c>
       <c r="E191" s="16" t="n">
-        <v>-0.005600000000000001</v>
+        <v>-0.0105</v>
       </c>
       <c r="F191" s="16" t="n">
-        <v>-0.0659</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="G191" s="18" t="n"/>
       <c r="H191" s="23" t="inlineStr">
@@ -15691,7 +15691,7 @@
         <v>545</v>
       </c>
       <c r="M191" s="17" t="n">
-        <v>0.5275948089805758</v>
+        <v>0.5352545142116679</v>
       </c>
       <c r="N191" s="14" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>582</v>
       </c>
       <c r="P191" s="17" t="n">
-        <v>0.6313030804159543</v>
+        <v>0.63948280233246</v>
       </c>
       <c r="Q191" s="21" t="inlineStr">
         <is>
@@ -15755,13 +15755,13 @@
         </is>
       </c>
       <c r="D192" s="4" t="n">
-        <v>146.81</v>
+        <v>147.06</v>
       </c>
       <c r="E192" s="6" t="n">
-        <v>0.0315</v>
+        <v>0.0332</v>
       </c>
       <c r="F192" s="5" t="n">
-        <v>-0.0066</v>
+        <v>-0.0049</v>
       </c>
       <c r="G192" s="7" t="n">
         <v>46335</v>
@@ -15816,13 +15816,13 @@
         </is>
       </c>
       <c r="D193" s="15" t="n">
-        <v>309.24</v>
+        <v>309.09</v>
       </c>
       <c r="E193" s="16" t="n">
-        <v>-0.0211</v>
+        <v>-0.0216</v>
       </c>
       <c r="F193" s="16" t="n">
-        <v>-0.0521</v>
+        <v>-0.0526</v>
       </c>
       <c r="G193" s="18" t="n">
         <v>46321</v>
@@ -15851,7 +15851,7 @@
         <v>425</v>
       </c>
       <c r="M193" s="17" t="n">
-        <v>0.3743370844651403</v>
+        <v>0.3750040441295417</v>
       </c>
       <c r="N193" s="14" t="inlineStr"/>
       <c r="O193" s="20" t="n"/>
@@ -15895,13 +15895,13 @@
         </is>
       </c>
       <c r="D194" s="4" t="n">
-        <v>140.76</v>
+        <v>141.16</v>
       </c>
       <c r="E194" s="6" t="n">
-        <v>0.0786</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="F194" s="6" t="n">
-        <v>0.078</v>
+        <v>0.08109999999999999</v>
       </c>
       <c r="G194" s="7" t="n">
         <v>46322</v>
@@ -15956,13 +15956,13 @@
         </is>
       </c>
       <c r="D195" s="15" t="n">
-        <v>361.25</v>
+        <v>355.91</v>
       </c>
       <c r="E195" s="16" t="n">
-        <v>-0.0288</v>
+        <v>-0.0431</v>
       </c>
       <c r="F195" s="16" t="n">
-        <v>-0.076</v>
+        <v>-0.0897</v>
       </c>
       <c r="G195" s="18" t="n"/>
       <c r="H195" s="23" t="inlineStr">
@@ -16007,13 +16007,13 @@
         </is>
       </c>
       <c r="D196" s="4" t="n">
-        <v>11.86</v>
+        <v>11.5</v>
       </c>
       <c r="E196" s="6" t="n">
-        <v>0.0322</v>
+        <v>0.0009</v>
       </c>
       <c r="F196" s="5" t="n">
-        <v>-0.1657</v>
+        <v>-0.191</v>
       </c>
       <c r="G196" s="7" t="n">
         <v>46337</v>
@@ -16068,13 +16068,13 @@
         </is>
       </c>
       <c r="D197" s="15" t="n">
-        <v>365.57</v>
+        <v>361.84</v>
       </c>
       <c r="E197" s="17" t="n">
-        <v>0.241</v>
+        <v>0.2284</v>
       </c>
       <c r="F197" s="17" t="n">
-        <v>0.1975</v>
+        <v>0.1853</v>
       </c>
       <c r="G197" s="18" t="n">
         <v>46321</v>
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="D198" s="4" t="n">
-        <v>303.48</v>
+        <v>300.6</v>
       </c>
       <c r="E198" s="6" t="n">
-        <v>0.1016</v>
+        <v>0.0911</v>
       </c>
       <c r="F198" s="6" t="n">
-        <v>0.0747</v>
+        <v>0.0645</v>
       </c>
       <c r="G198" s="7" t="n">
         <v>46330</v>
@@ -16190,13 +16190,13 @@
         </is>
       </c>
       <c r="D199" s="15" t="n">
-        <v>64.56999999999999</v>
+        <v>64.48</v>
       </c>
       <c r="E199" s="17" t="n">
-        <v>0.2587</v>
+        <v>0.2569</v>
       </c>
       <c r="F199" s="17" t="n">
-        <v>0.2736</v>
+        <v>0.2718</v>
       </c>
       <c r="G199" s="18" t="n">
         <v>46330</v>
@@ -16251,13 +16251,13 @@
         </is>
       </c>
       <c r="D200" s="4" t="n">
-        <v>18.88</v>
+        <v>18.1</v>
       </c>
       <c r="E200" s="6" t="n">
-        <v>0.0929</v>
+        <v>0.0481</v>
       </c>
       <c r="F200" s="5" t="n">
-        <v>-0.1703</v>
+        <v>-0.2044</v>
       </c>
       <c r="G200" s="7" t="n">
         <v>46318</v>
@@ -16312,13 +16312,13 @@
         </is>
       </c>
       <c r="D201" s="15" t="n">
-        <v>194.61</v>
+        <v>193.87</v>
       </c>
       <c r="E201" s="16" t="n">
-        <v>-0.1258</v>
+        <v>-0.1291</v>
       </c>
       <c r="F201" s="16" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.09050000000000001</v>
       </c>
       <c r="G201" s="18" t="n"/>
       <c r="H201" s="23" t="inlineStr">
@@ -16363,13 +16363,13 @@
         </is>
       </c>
       <c r="D202" s="4" t="n">
-        <v>238.07</v>
+        <v>237.58</v>
       </c>
       <c r="E202" s="6" t="n">
-        <v>0.1388</v>
+        <v>0.1364</v>
       </c>
       <c r="F202" s="6" t="n">
-        <v>0.4547</v>
+        <v>0.4517</v>
       </c>
       <c r="G202" s="7" t="n"/>
       <c r="H202" s="12" t="inlineStr">
@@ -16388,7 +16388,7 @@
         <v>200</v>
       </c>
       <c r="M202" s="5" t="n">
-        <v>-0.1599109505607594</v>
+        <v>-0.1581782978365183</v>
       </c>
       <c r="N202" s="3" t="inlineStr">
         <is>
@@ -16399,7 +16399,7 @@
         <v>250</v>
       </c>
       <c r="P202" s="6" t="n">
-        <v>0.05011131179905073</v>
+        <v>0.05227712770435216</v>
       </c>
       <c r="Q202" s="10" t="inlineStr">
         <is>
@@ -16444,13 +16444,13 @@
         </is>
       </c>
       <c r="D203" s="15" t="n">
-        <v>258.45</v>
+        <v>262.49</v>
       </c>
       <c r="E203" s="17" t="n">
-        <v>0.3554</v>
+        <v>0.3766</v>
       </c>
       <c r="F203" s="17" t="n">
-        <v>0.4102</v>
+        <v>0.4322</v>
       </c>
       <c r="G203" s="18" t="n"/>
       <c r="H203" s="23" t="inlineStr">
@@ -16469,7 +16469,7 @@
         <v>181.25</v>
       </c>
       <c r="M203" s="16" t="n">
-        <v>-0.2987038111820468</v>
+        <v>-0.3094975046668445</v>
       </c>
       <c r="N203" s="14" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>177.5</v>
       </c>
       <c r="P203" s="16" t="n">
-        <v>-0.3132133875024182</v>
+        <v>-0.3237837631909787</v>
       </c>
       <c r="Q203" s="21" t="inlineStr">
         <is>
@@ -16521,13 +16521,13 @@
         </is>
       </c>
       <c r="D204" s="4" t="n">
-        <v>89.11</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="E204" s="6" t="n">
-        <v>0.0332</v>
+        <v>0.0075</v>
       </c>
       <c r="F204" s="6" t="n">
-        <v>0.2397</v>
+        <v>0.209</v>
       </c>
       <c r="G204" s="7" t="n">
         <v>46335</v>
@@ -16582,13 +16582,13 @@
         </is>
       </c>
       <c r="D205" s="15" t="n">
-        <v>106.32</v>
+        <v>106.43</v>
       </c>
       <c r="E205" s="16" t="n">
-        <v>-0.0355</v>
+        <v>-0.0345</v>
       </c>
       <c r="F205" s="16" t="n">
-        <v>-0.0688</v>
+        <v>-0.0678</v>
       </c>
       <c r="G205" s="18" t="n">
         <v>46337</v>
@@ -16617,7 +16617,7 @@
         <v>130</v>
       </c>
       <c r="M205" s="17" t="n">
-        <v>0.2227238525206923</v>
+        <v>0.2214601146293338</v>
       </c>
       <c r="N205" s="14" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>150</v>
       </c>
       <c r="P205" s="17" t="n">
-        <v>0.4108352144469527</v>
+        <v>0.409377055341539</v>
       </c>
       <c r="Q205" s="21" t="inlineStr">
         <is>
@@ -16685,13 +16685,13 @@
         </is>
       </c>
       <c r="D206" s="4" t="n">
-        <v>254.46</v>
+        <v>251.49</v>
       </c>
       <c r="E206" s="6" t="n">
-        <v>0.1271</v>
+        <v>0.1139</v>
       </c>
       <c r="F206" s="6" t="n">
-        <v>0.0308</v>
+        <v>0.0188</v>
       </c>
       <c r="G206" s="7" t="n">
         <v>46331</v>
@@ -16746,13 +16746,13 @@
         </is>
       </c>
       <c r="D207" s="15" t="n">
-        <v>550.78</v>
+        <v>549.83</v>
       </c>
       <c r="E207" s="17" t="n">
-        <v>0.2715</v>
+        <v>0.2693</v>
       </c>
       <c r="F207" s="17" t="n">
-        <v>0.2589</v>
+        <v>0.2568</v>
       </c>
       <c r="G207" s="18" t="n"/>
       <c r="H207" s="23" t="inlineStr">
@@ -16797,13 +16797,13 @@
         </is>
       </c>
       <c r="D208" s="4" t="n">
-        <v>68.51000000000001</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="E208" s="6" t="n">
-        <v>0.0951</v>
+        <v>0.1108</v>
       </c>
       <c r="F208" s="6" t="n">
-        <v>0.3582</v>
+        <v>0.3777</v>
       </c>
       <c r="G208" s="7" t="n"/>
       <c r="H208" s="12" t="inlineStr">
@@ -16848,13 +16848,13 @@
         </is>
       </c>
       <c r="D209" s="15" t="n">
-        <v>58.85</v>
+        <v>58.51</v>
       </c>
       <c r="E209" s="17" t="n">
-        <v>0.1998</v>
+        <v>0.1929</v>
       </c>
       <c r="F209" s="17" t="n">
-        <v>0.414</v>
+        <v>0.4058</v>
       </c>
       <c r="G209" s="18" t="n">
         <v>46330</v>
@@ -16909,13 +16909,13 @@
         </is>
       </c>
       <c r="D210" s="4" t="n">
-        <v>402.08</v>
+        <v>400.85</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>-0.0452</v>
+        <v>-0.0482</v>
       </c>
       <c r="F210" s="5" t="n">
-        <v>-0.1554</v>
+        <v>-0.1579</v>
       </c>
       <c r="G210" s="7" t="n">
         <v>46328</v>
@@ -16970,13 +16970,13 @@
         </is>
       </c>
       <c r="D211" s="15" t="n">
-        <v>129.85</v>
+        <v>131.26</v>
       </c>
       <c r="E211" s="17" t="n">
-        <v>0.2034</v>
+        <v>0.2165</v>
       </c>
       <c r="F211" s="17" t="n">
-        <v>0.2481</v>
+        <v>0.2616</v>
       </c>
       <c r="G211" s="18" t="n">
         <v>46330</v>
@@ -17031,13 +17031,13 @@
         </is>
       </c>
       <c r="D212" s="4" t="n">
-        <v>176.51</v>
+        <v>178.74</v>
       </c>
       <c r="E212" s="6" t="n">
-        <v>0.1614</v>
+        <v>0.176</v>
       </c>
       <c r="F212" s="6" t="n">
-        <v>0.1585</v>
+        <v>0.1731</v>
       </c>
       <c r="G212" s="7" t="n">
         <v>46330</v>
@@ -17092,13 +17092,13 @@
         </is>
       </c>
       <c r="D213" s="15" t="n">
-        <v>47.57</v>
+        <v>46.42</v>
       </c>
       <c r="E213" s="17" t="n">
-        <v>0.0353</v>
+        <v>0.0102</v>
       </c>
       <c r="F213" s="16" t="n">
-        <v>-0.1113</v>
+        <v>-0.1328</v>
       </c>
       <c r="G213" s="18" t="n">
         <v>46337</v>
@@ -17153,13 +17153,13 @@
         </is>
       </c>
       <c r="D214" s="4" t="n">
-        <v>155.24</v>
+        <v>154.48</v>
       </c>
       <c r="E214" s="6" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.0614</v>
       </c>
       <c r="F214" s="6" t="n">
-        <v>0.05860000000000001</v>
+        <v>0.0534</v>
       </c>
       <c r="G214" s="7" t="n">
         <v>46322</v>
@@ -17214,13 +17214,13 @@
         </is>
       </c>
       <c r="D215" s="15" t="n">
-        <v>49.05</v>
+        <v>49.01</v>
       </c>
       <c r="E215" s="17" t="n">
-        <v>0.167</v>
+        <v>0.1661</v>
       </c>
       <c r="F215" s="17" t="n">
-        <v>0.5681</v>
+        <v>0.5668</v>
       </c>
       <c r="G215" s="18" t="n"/>
       <c r="H215" s="23" t="inlineStr">
@@ -17265,13 +17265,13 @@
         </is>
       </c>
       <c r="D216" s="4" t="n">
-        <v>153.43</v>
+        <v>152.89</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>-0.2004</v>
+        <v>-0.2032</v>
       </c>
       <c r="F216" s="6" t="n">
-        <v>0.11</v>
+        <v>0.1061</v>
       </c>
       <c r="G216" s="7" t="n"/>
       <c r="H216" s="12" t="inlineStr">
@@ -17290,7 +17290,7 @@
         <v>190</v>
       </c>
       <c r="M216" s="6" t="n">
-        <v>0.2383497360359773</v>
+        <v>0.2427235267185559</v>
       </c>
       <c r="N216" s="3" t="inlineStr"/>
       <c r="O216" s="9" t="n"/>
@@ -17334,13 +17334,13 @@
         </is>
       </c>
       <c r="D217" s="15" t="n">
-        <v>61.88</v>
+        <v>62.33</v>
       </c>
       <c r="E217" s="17" t="n">
-        <v>0.1803</v>
+        <v>0.1888</v>
       </c>
       <c r="F217" s="17" t="n">
-        <v>0.2977</v>
+        <v>0.307</v>
       </c>
       <c r="G217" s="18" t="n"/>
       <c r="H217" s="23" t="inlineStr">
@@ -17359,7 +17359,7 @@
         <v>67</v>
       </c>
       <c r="M217" s="17" t="n">
-        <v>0.08274078862314152</v>
+        <v>0.07492379271618806</v>
       </c>
       <c r="N217" s="14" t="inlineStr">
         <is>
@@ -17370,7 +17370,7 @@
         <v>70</v>
       </c>
       <c r="P217" s="17" t="n">
-        <v>0.1312217194570135</v>
+        <v>0.1230547088079577</v>
       </c>
       <c r="Q217" s="21" t="inlineStr">
         <is>
@@ -17411,13 +17411,13 @@
         </is>
       </c>
       <c r="D218" s="4" t="n">
-        <v>224.49</v>
+        <v>226.03</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>-0.0806</v>
+        <v>-0.07429999999999999</v>
       </c>
       <c r="F218" s="6" t="n">
-        <v>0.09570000000000001</v>
+        <v>0.1032</v>
       </c>
       <c r="G218" s="7" t="n">
         <v>46330</v>
@@ -17472,13 +17472,13 @@
         </is>
       </c>
       <c r="D219" s="15" t="n">
-        <v>235.43</v>
+        <v>232.76</v>
       </c>
       <c r="E219" s="17" t="n">
-        <v>0.019</v>
+        <v>0.0074</v>
       </c>
       <c r="F219" s="17" t="n">
-        <v>0.0992</v>
+        <v>0.0867</v>
       </c>
       <c r="G219" s="18" t="n">
         <v>46316</v>
@@ -17514,7 +17514,7 @@
         <v>250</v>
       </c>
       <c r="P219" s="17" t="n">
-        <v>0.06188676039587136</v>
+        <v>0.0740677092283898</v>
       </c>
       <c r="Q219" s="21" t="inlineStr">
         <is>
@@ -17551,13 +17551,13 @@
         </is>
       </c>
       <c r="D220" s="4" t="n">
-        <v>14.19</v>
+        <v>13.83</v>
       </c>
       <c r="E220" s="6" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.05980000000000001</v>
       </c>
       <c r="F220" s="6" t="n">
-        <v>0.5814</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="G220" s="7" t="n">
         <v>46337</v>
@@ -17612,13 +17612,13 @@
         </is>
       </c>
       <c r="D221" s="15" t="n">
-        <v>120.93</v>
+        <v>122.6</v>
       </c>
       <c r="E221" s="17" t="n">
-        <v>0.3859</v>
+        <v>0.405</v>
       </c>
       <c r="F221" s="17" t="n">
-        <v>0.3099</v>
+        <v>0.328</v>
       </c>
       <c r="G221" s="18" t="n">
         <v>46317</v>
@@ -17673,13 +17673,13 @@
         </is>
       </c>
       <c r="D222" s="4" t="n">
-        <v>288.94</v>
+        <v>286.8</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>-0.2189</v>
+        <v>-0.2247</v>
       </c>
       <c r="F222" s="5" t="n">
-        <v>-0.0249</v>
+        <v>-0.0322</v>
       </c>
       <c r="G222" s="7" t="n"/>
       <c r="H222" s="12" t="inlineStr">
@@ -17724,13 +17724,13 @@
         </is>
       </c>
       <c r="D223" s="15" t="n">
-        <v>43.74</v>
+        <v>42.54</v>
       </c>
       <c r="E223" s="17" t="n">
-        <v>0.0653</v>
+        <v>0.036</v>
       </c>
       <c r="F223" s="17" t="n">
-        <v>0.3319</v>
+        <v>0.2954</v>
       </c>
       <c r="G223" s="18" t="n">
         <v>46330</v>
@@ -17785,13 +17785,13 @@
         </is>
       </c>
       <c r="D224" s="4" t="n">
-        <v>48.98</v>
+        <v>47.05</v>
       </c>
       <c r="E224" s="6" t="n">
-        <v>0.2303</v>
+        <v>0.1819</v>
       </c>
       <c r="F224" s="6" t="n">
-        <v>0.3213</v>
+        <v>0.2692</v>
       </c>
       <c r="G224" s="7" t="n">
         <v>46331</v>
@@ -17846,13 +17846,13 @@
         </is>
       </c>
       <c r="D225" s="15" t="n">
-        <v>308.32</v>
+        <v>308.75</v>
       </c>
       <c r="E225" s="17" t="n">
-        <v>0.0112</v>
+        <v>0.0127</v>
       </c>
       <c r="F225" s="16" t="n">
-        <v>-0.0137</v>
+        <v>-0.0123</v>
       </c>
       <c r="G225" s="18" t="n">
         <v>46289</v>
@@ -17911,13 +17911,13 @@
         </is>
       </c>
       <c r="D226" s="4" t="n">
-        <v>347.86</v>
+        <v>353.36</v>
       </c>
       <c r="E226" s="6" t="n">
-        <v>0.1197</v>
+        <v>0.1374</v>
       </c>
       <c r="F226" s="6" t="n">
-        <v>0.0916</v>
+        <v>0.1089</v>
       </c>
       <c r="G226" s="7" t="n"/>
       <c r="H226" s="12" t="inlineStr">
@@ -17936,7 +17936,7 @@
         <v>390</v>
       </c>
       <c r="M226" s="6" t="n">
-        <v>0.1211406887828436</v>
+        <v>0.1036902875254697</v>
       </c>
       <c r="N226" s="3" t="inlineStr"/>
       <c r="O226" s="9" t="n"/>
@@ -17992,13 +17992,13 @@
         </is>
       </c>
       <c r="D227" s="15" t="n">
-        <v>186.82</v>
+        <v>187.86</v>
       </c>
       <c r="E227" s="17" t="n">
-        <v>0.0289</v>
+        <v>0.0346</v>
       </c>
       <c r="F227" s="16" t="n">
-        <v>-0.1126</v>
+        <v>-0.1076</v>
       </c>
       <c r="G227" s="18" t="n">
         <v>46330</v>
@@ -18027,7 +18027,7 @@
         <v>305</v>
       </c>
       <c r="M227" s="17" t="n">
-        <v>0.6325875173964244</v>
+        <v>0.6235494517193654</v>
       </c>
       <c r="N227" s="14" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>185</v>
       </c>
       <c r="P227" s="16" t="n">
-        <v>-0.009741997644791741</v>
+        <v>-0.01522410305546691</v>
       </c>
       <c r="Q227" s="21" t="inlineStr">
         <is>
@@ -18079,13 +18079,13 @@
         </is>
       </c>
       <c r="D228" s="4" t="n">
-        <v>90.44</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="E228" s="6" t="n">
-        <v>0.083</v>
+        <v>0.08789999999999999</v>
       </c>
       <c r="F228" s="5" t="n">
-        <v>-0.1075</v>
+        <v>-0.1034</v>
       </c>
       <c r="G228" s="7" t="n"/>
       <c r="H228" s="12" t="inlineStr">
@@ -18130,13 +18130,13 @@
         </is>
       </c>
       <c r="D229" s="15" t="n">
-        <v>953.59</v>
+        <v>937</v>
       </c>
       <c r="E229" s="17" t="n">
-        <v>0.1487</v>
+        <v>0.1287</v>
       </c>
       <c r="F229" s="17" t="n">
-        <v>0.2498</v>
+        <v>0.2281</v>
       </c>
       <c r="G229" s="18" t="n">
         <v>46329</v>
@@ -18191,13 +18191,13 @@
         </is>
       </c>
       <c r="D230" s="4" t="n">
-        <v>106.11</v>
+        <v>104.65</v>
       </c>
       <c r="E230" s="6" t="n">
-        <v>0.0916</v>
-      </c>
-      <c r="F230" s="6" t="n">
-        <v>0.0031</v>
+        <v>0.0765</v>
+      </c>
+      <c r="F230" s="5" t="n">
+        <v>-0.0107</v>
       </c>
       <c r="G230" s="7" t="n">
         <v>46322</v>
@@ -18252,13 +18252,13 @@
         </is>
       </c>
       <c r="D231" s="15" t="n">
-        <v>305.89</v>
+        <v>307.28</v>
       </c>
       <c r="E231" s="16" t="n">
-        <v>-0.0138</v>
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F231" s="17" t="n">
-        <v>0.0022</v>
+        <v>0.0068</v>
       </c>
       <c r="G231" s="18" t="n">
         <v>46323</v>
@@ -18287,7 +18287,7 @@
         <v>450</v>
       </c>
       <c r="M231" s="17" t="n">
-        <v>0.4711170682271406</v>
+        <v>0.4644623795886489</v>
       </c>
       <c r="N231" s="14" t="inlineStr">
         <is>
@@ -18298,7 +18298,7 @@
         <v>355</v>
       </c>
       <c r="P231" s="17" t="n">
-        <v>0.1605479093791886</v>
+        <v>0.1552980994532675</v>
       </c>
       <c r="Q231" s="21" t="inlineStr">
         <is>
@@ -18343,13 +18343,13 @@
         </is>
       </c>
       <c r="D232" s="4" t="n">
-        <v>75.23999999999999</v>
+        <v>75.53</v>
       </c>
       <c r="E232" s="6" t="n">
-        <v>0.0139</v>
+        <v>0.0178</v>
       </c>
       <c r="F232" s="5" t="n">
-        <v>-0.0459</v>
+        <v>-0.04219999999999999</v>
       </c>
       <c r="G232" s="7" t="n">
         <v>46331</v>
@@ -18404,13 +18404,13 @@
         </is>
       </c>
       <c r="D233" s="15" t="n">
-        <v>433.06</v>
+        <v>428.36</v>
       </c>
       <c r="E233" s="17" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="F233" s="17" t="n">
-        <v>0.4521</v>
+        <v>0.4364</v>
       </c>
       <c r="G233" s="18" t="n"/>
       <c r="H233" s="23" t="inlineStr">
@@ -18455,13 +18455,13 @@
         </is>
       </c>
       <c r="D234" s="4" t="n">
-        <v>262</v>
+        <v>262.72</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>-0.0262</v>
+        <v>-0.0236</v>
       </c>
       <c r="F234" s="5" t="n">
-        <v>-0.2041</v>
+        <v>-0.2019</v>
       </c>
       <c r="G234" s="7" t="n">
         <v>46330</v>
@@ -18516,13 +18516,13 @@
         </is>
       </c>
       <c r="D235" s="15" t="n">
-        <v>1325.64</v>
+        <v>1355.47</v>
       </c>
       <c r="E235" s="17" t="n">
-        <v>0.0316</v>
-      </c>
-      <c r="F235" s="16" t="n">
-        <v>-0.0061</v>
+        <v>0.0548</v>
+      </c>
+      <c r="F235" s="17" t="n">
+        <v>0.0162</v>
       </c>
       <c r="G235" s="18" t="n">
         <v>46324</v>
@@ -18577,13 +18577,13 @@
         </is>
       </c>
       <c r="D236" s="4" t="n">
-        <v>259.8</v>
+        <v>260.9</v>
       </c>
       <c r="E236" s="6" t="n">
-        <v>0.1331</v>
+        <v>0.1379</v>
       </c>
       <c r="F236" s="6" t="n">
-        <v>0.3376</v>
+        <v>0.3433</v>
       </c>
       <c r="G236" s="7" t="n"/>
       <c r="H236" s="12" t="inlineStr">
@@ -18602,7 +18602,7 @@
         <v>240</v>
       </c>
       <c r="M236" s="5" t="n">
-        <v>-0.07621247113163976</v>
+        <v>-0.08010732081257178</v>
       </c>
       <c r="N236" s="3" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>251</v>
       </c>
       <c r="P236" s="5" t="n">
-        <v>-0.03387220939183992</v>
+        <v>-0.03794557301648133</v>
       </c>
       <c r="Q236" s="10" t="inlineStr">
         <is>
@@ -18654,13 +18654,13 @@
         </is>
       </c>
       <c r="D237" s="15" t="n">
-        <v>498.44</v>
+        <v>500.59</v>
       </c>
       <c r="E237" s="17" t="n">
-        <v>0.0228</v>
+        <v>0.0273</v>
       </c>
       <c r="F237" s="17" t="n">
-        <v>0.3058</v>
+        <v>0.3115</v>
       </c>
       <c r="G237" s="18" t="n">
         <v>46330</v>
@@ -18689,7 +18689,7 @@
         <v>625</v>
       </c>
       <c r="M237" s="17" t="n">
-        <v>0.2539122060829789</v>
+        <v>0.2485267384486307</v>
       </c>
       <c r="N237" s="14" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>525</v>
       </c>
       <c r="P237" s="17" t="n">
-        <v>0.05328625310970227</v>
+        <v>0.04876246029684977</v>
       </c>
       <c r="Q237" s="21" t="inlineStr">
         <is>
@@ -18753,13 +18753,13 @@
         </is>
       </c>
       <c r="D238" s="4" t="n">
-        <v>462.91</v>
+        <v>460.44</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>-0.0386</v>
+        <v>-0.0438</v>
       </c>
       <c r="F238" s="6" t="n">
-        <v>0.1079</v>
+        <v>0.102</v>
       </c>
       <c r="G238" s="7" t="n">
         <v>46324</v>
@@ -18791,7 +18791,7 @@
         <v>525</v>
       </c>
       <c r="P238" s="6" t="n">
-        <v>0.1341297444427642</v>
+        <v>0.1402137086265312</v>
       </c>
       <c r="Q238" s="10" t="inlineStr">
         <is>
@@ -18840,13 +18840,13 @@
         </is>
       </c>
       <c r="D239" s="15" t="n">
-        <v>165.17</v>
+        <v>162.2</v>
       </c>
       <c r="E239" s="17" t="n">
-        <v>0.3469</v>
+        <v>0.3227</v>
       </c>
       <c r="F239" s="17" t="n">
-        <v>0.8018000000000001</v>
+        <v>0.7694</v>
       </c>
       <c r="G239" s="18" t="n">
         <v>46324</v>
@@ -18901,13 +18901,13 @@
         </is>
       </c>
       <c r="D240" s="4" t="n">
-        <v>277.18</v>
+        <v>275.84</v>
       </c>
       <c r="E240" s="6" t="n">
-        <v>0.0767</v>
+        <v>0.07150000000000001</v>
       </c>
       <c r="F240" s="6" t="n">
-        <v>0.0382</v>
+        <v>0.0331</v>
       </c>
       <c r="G240" s="7" t="n">
         <v>46331</v>
@@ -18962,13 +18962,13 @@
         </is>
       </c>
       <c r="D241" s="15" t="n">
-        <v>1079.05</v>
+        <v>1071.88</v>
       </c>
       <c r="E241" s="17" t="n">
-        <v>0.1852</v>
+        <v>0.1773</v>
       </c>
       <c r="F241" s="17" t="n">
-        <v>0.1717</v>
+        <v>0.1639</v>
       </c>
       <c r="G241" s="18" t="n">
         <v>46295</v>
@@ -18997,7 +18997,7 @@
         <v>1525</v>
       </c>
       <c r="M241" s="17" t="n">
-        <v>0.4132802001760809</v>
+        <v>0.4227338881218045</v>
       </c>
       <c r="N241" s="14" t="inlineStr">
         <is>
@@ -19045,13 +19045,13 @@
         </is>
       </c>
       <c r="D242" s="4" t="n">
-        <v>234.51</v>
+        <v>226.61</v>
       </c>
       <c r="E242" s="6" t="n">
-        <v>0.1119</v>
+        <v>0.07440000000000001</v>
       </c>
       <c r="F242" s="6" t="n">
-        <v>0.2489</v>
+        <v>0.2068</v>
       </c>
       <c r="G242" s="7" t="n">
         <v>46336</v>
@@ -19106,13 +19106,13 @@
         </is>
       </c>
       <c r="D243" s="15" t="n">
-        <v>356.45</v>
+        <v>352.33</v>
       </c>
       <c r="E243" s="17" t="n">
-        <v>0.2714</v>
+        <v>0.2568</v>
       </c>
       <c r="F243" s="17" t="n">
-        <v>0.3597</v>
+        <v>0.344</v>
       </c>
       <c r="G243" s="18" t="n">
         <v>46324</v>
@@ -19167,13 +19167,13 @@
         </is>
       </c>
       <c r="D244" s="4" t="n">
-        <v>139.36</v>
+        <v>140.78</v>
       </c>
       <c r="E244" s="6" t="n">
-        <v>0.0883</v>
+        <v>0.09939999999999999</v>
       </c>
       <c r="F244" s="6" t="n">
-        <v>0.4108</v>
+        <v>0.4252</v>
       </c>
       <c r="G244" s="7" t="n">
         <v>46323</v>
@@ -19202,7 +19202,7 @@
         <v>160</v>
       </c>
       <c r="M244" s="6" t="n">
-        <v>0.1481056257175659</v>
+        <v>0.136525074584458</v>
       </c>
       <c r="N244" s="3" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>150</v>
       </c>
       <c r="P244" s="6" t="n">
-        <v>0.07634902411021803</v>
+        <v>0.06549225742292938</v>
       </c>
       <c r="Q244" s="10" t="inlineStr">
         <is>
@@ -19258,13 +19258,13 @@
         </is>
       </c>
       <c r="D245" s="15" t="n">
-        <v>69.63</v>
+        <v>69.68000000000001</v>
       </c>
       <c r="E245" s="17" t="n">
-        <v>0.0442</v>
+        <v>0.045</v>
       </c>
       <c r="F245" s="17" t="n">
-        <v>0.2651</v>
+        <v>0.266</v>
       </c>
       <c r="G245" s="18" t="n"/>
       <c r="H245" s="23" t="inlineStr">
@@ -19309,13 +19309,13 @@
         </is>
       </c>
       <c r="D246" s="4" t="n">
-        <v>225.92</v>
+        <v>225.51</v>
       </c>
       <c r="E246" s="6" t="n">
-        <v>0.0837</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="F246" s="6" t="n">
-        <v>0.0922</v>
+        <v>0.09029999999999999</v>
       </c>
       <c r="G246" s="7" t="n"/>
       <c r="H246" s="12" t="inlineStr">
@@ -19334,7 +19334,7 @@
         <v>315</v>
       </c>
       <c r="M246" s="6" t="n">
-        <v>0.3942988668555242</v>
+        <v>0.396833843288546</v>
       </c>
       <c r="N246" s="3" t="inlineStr">
         <is>
@@ -19345,7 +19345,7 @@
         <v>413</v>
       </c>
       <c r="P246" s="6" t="n">
-        <v>0.8280807365439095</v>
+        <v>0.8314043723116492</v>
       </c>
       <c r="Q246" s="10" t="inlineStr">
         <is>
@@ -19394,13 +19394,13 @@
         </is>
       </c>
       <c r="D247" s="15" t="n">
-        <v>367.39</v>
+        <v>365.73</v>
       </c>
       <c r="E247" s="17" t="n">
-        <v>0.0128</v>
+        <v>0.008199999999999999</v>
       </c>
       <c r="F247" s="16" t="n">
-        <v>-0.1612</v>
+        <v>-0.165</v>
       </c>
       <c r="G247" s="18" t="n">
         <v>46331</v>
@@ -19455,13 +19455,13 @@
         </is>
       </c>
       <c r="D248" s="4" t="n">
-        <v>234.41</v>
+        <v>235.44</v>
       </c>
       <c r="E248" s="6" t="n">
-        <v>0.0538</v>
+        <v>0.0584</v>
       </c>
       <c r="F248" s="5" t="n">
-        <v>-0.1294</v>
+        <v>-0.1255</v>
       </c>
       <c r="G248" s="7" t="n">
         <v>46322</v>
@@ -19512,13 +19512,13 @@
         </is>
       </c>
       <c r="D249" s="15" t="n">
-        <v>11.91</v>
+        <v>11.64</v>
       </c>
       <c r="E249" s="17" t="n">
-        <v>0.1342</v>
+        <v>0.1086</v>
       </c>
       <c r="F249" s="16" t="n">
-        <v>-0.2449</v>
+        <v>-0.2619</v>
       </c>
       <c r="G249" s="18" t="n"/>
       <c r="H249" s="23" t="inlineStr">
@@ -19563,13 +19563,13 @@
         </is>
       </c>
       <c r="D250" s="4" t="n">
-        <v>202.7</v>
+        <v>205.36</v>
       </c>
       <c r="E250" s="6" t="n">
-        <v>0.5477000000000001</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="F250" s="6" t="n">
-        <v>0.4635</v>
+        <v>0.4827</v>
       </c>
       <c r="G250" s="7" t="n"/>
       <c r="H250" s="12" t="inlineStr">
@@ -19588,7 +19588,7 @@
         <v>150</v>
       </c>
       <c r="M250" s="5" t="n">
-        <v>-0.259990133201776</v>
+        <v>-0.2695753798208025</v>
       </c>
       <c r="N250" s="3" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>130</v>
       </c>
       <c r="P250" s="5" t="n">
-        <v>-0.3586581154415392</v>
+        <v>-0.3669653291780289</v>
       </c>
       <c r="Q250" s="10" t="inlineStr">
         <is>
@@ -19640,13 +19640,13 @@
         </is>
       </c>
       <c r="D251" s="15" t="n">
-        <v>73.87</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="E251" s="17" t="n">
-        <v>0.027</v>
+        <v>0.0302</v>
       </c>
       <c r="F251" s="16" t="n">
-        <v>-0.1491</v>
+        <v>-0.1464</v>
       </c>
       <c r="G251" s="18" t="n">
         <v>46328</v>
@@ -19701,13 +19701,13 @@
         </is>
       </c>
       <c r="D252" s="4" t="n">
-        <v>282.45</v>
+        <v>282.31</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>-0.0016</v>
+        <v>-0.0021</v>
       </c>
       <c r="F252" s="6" t="n">
-        <v>0.0361</v>
+        <v>0.0355</v>
       </c>
       <c r="G252" s="7" t="n">
         <v>46331</v>
@@ -19762,13 +19762,13 @@
         </is>
       </c>
       <c r="D253" s="15" t="n">
-        <v>147.03</v>
+        <v>144.56</v>
       </c>
       <c r="E253" s="17" t="n">
-        <v>0.0322</v>
+        <v>0.0148</v>
       </c>
       <c r="F253" s="17" t="n">
-        <v>0.2786</v>
+        <v>0.2572</v>
       </c>
       <c r="G253" s="18" t="n"/>
       <c r="H253" s="23" t="inlineStr">
@@ -19787,7 +19787,7 @@
         <v>280</v>
       </c>
       <c r="M253" s="17" t="n">
-        <v>0.904373257158403</v>
+        <v>0.9369120088544549</v>
       </c>
       <c r="N253" s="14" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>245</v>
       </c>
       <c r="P253" s="17" t="n">
-        <v>0.6663266000136027</v>
+        <v>0.694798007747648</v>
       </c>
       <c r="Q253" s="21" t="inlineStr">
         <is>
@@ -19839,13 +19839,13 @@
         </is>
       </c>
       <c r="D254" s="4" t="n">
-        <v>386.11</v>
+        <v>393.3</v>
       </c>
       <c r="E254" s="6" t="n">
-        <v>0.1003</v>
+        <v>0.1208</v>
       </c>
       <c r="F254" s="6" t="n">
-        <v>0.1925</v>
+        <v>0.2147</v>
       </c>
       <c r="G254" s="7" t="n"/>
       <c r="H254" s="12" t="inlineStr">
@@ -19864,7 +19864,7 @@
         <v>420</v>
       </c>
       <c r="M254" s="6" t="n">
-        <v>0.08777291445443004</v>
+        <v>0.0678871090770404</v>
       </c>
       <c r="N254" s="3" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>415</v>
       </c>
       <c r="P254" s="6" t="n">
-        <v>0.07482323690140112</v>
+        <v>0.05517416730231373</v>
       </c>
       <c r="Q254" s="10" t="inlineStr">
         <is>
@@ -19924,13 +19924,13 @@
         </is>
       </c>
       <c r="D255" s="15" t="n">
-        <v>13.06</v>
+        <v>13.04</v>
       </c>
       <c r="E255" s="16" t="n">
-        <v>-0.2121</v>
+        <v>-0.213</v>
       </c>
       <c r="F255" s="17" t="n">
-        <v>0.2043</v>
+        <v>0.203</v>
       </c>
       <c r="G255" s="18" t="n"/>
       <c r="H255" s="23" t="inlineStr">
@@ -19975,13 +19975,13 @@
         </is>
       </c>
       <c r="D256" s="4" t="n">
-        <v>35.05</v>
+        <v>35.18</v>
       </c>
       <c r="E256" s="6" t="n">
-        <v>0.0225</v>
+        <v>0.0263</v>
       </c>
       <c r="F256" s="6" t="n">
-        <v>0.3069</v>
+        <v>0.3117</v>
       </c>
       <c r="G256" s="7" t="n">
         <v>46315</v>
@@ -20036,13 +20036,13 @@
         </is>
       </c>
       <c r="D257" s="15" t="n">
-        <v>175.41</v>
+        <v>177.2</v>
       </c>
       <c r="E257" s="17" t="n">
-        <v>0.0895</v>
+        <v>0.1006</v>
       </c>
       <c r="F257" s="17" t="n">
-        <v>0.3753</v>
+        <v>0.3893</v>
       </c>
       <c r="G257" s="18" t="n">
         <v>46330</v>
@@ -20097,13 +20097,13 @@
         </is>
       </c>
       <c r="D258" s="4" t="n">
-        <v>191.74</v>
+        <v>191.79</v>
       </c>
       <c r="E258" s="6" t="n">
-        <v>0.0901</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="F258" s="6" t="n">
-        <v>0.5599000000000001</v>
+        <v>0.5603</v>
       </c>
       <c r="G258" s="7" t="n">
         <v>46328</v>
@@ -20158,13 +20158,13 @@
         </is>
       </c>
       <c r="D259" s="15" t="n">
-        <v>125.21</v>
+        <v>124.5</v>
       </c>
       <c r="E259" s="16" t="n">
-        <v>-0.008199999999999999</v>
+        <v>-0.0138</v>
       </c>
       <c r="F259" s="16" t="n">
-        <v>-0.073</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="G259" s="18" t="n">
         <v>46343</v>
@@ -20229,13 +20229,13 @@
         </is>
       </c>
       <c r="D260" s="4" t="n">
-        <v>17.42</v>
+        <v>16.81</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>-0.0672</v>
+        <v>-0.1001</v>
       </c>
       <c r="F260" s="6" t="n">
-        <v>0.075</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="G260" s="7" t="n">
         <v>46331</v>
@@ -20290,13 +20290,13 @@
         </is>
       </c>
       <c r="D261" s="15" t="n">
-        <v>195.67</v>
+        <v>197.24</v>
       </c>
       <c r="E261" s="17" t="n">
-        <v>0.2343</v>
+        <v>0.2442</v>
       </c>
       <c r="F261" s="17" t="n">
-        <v>0.1719</v>
+        <v>0.1813</v>
       </c>
       <c r="G261" s="18" t="n">
         <v>46330</v>
@@ -20325,7 +20325,7 @@
         <v>265</v>
       </c>
       <c r="M261" s="17" t="n">
-        <v>0.3543210507487097</v>
+        <v>0.3435408639221253</v>
       </c>
       <c r="N261" s="14" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>179</v>
       </c>
       <c r="P261" s="16" t="n">
-        <v>-0.08519446006030555</v>
+        <v>-0.09247617116203614</v>
       </c>
       <c r="Q261" s="21" t="inlineStr">
         <is>
@@ -20381,13 +20381,13 @@
         </is>
       </c>
       <c r="D262" s="4" t="n">
-        <v>118.96</v>
+        <v>119.59</v>
       </c>
       <c r="E262" s="6" t="n">
-        <v>0.2474</v>
+        <v>0.254</v>
       </c>
       <c r="F262" s="6" t="n">
-        <v>0.3751</v>
+        <v>0.3824</v>
       </c>
       <c r="G262" s="7" t="n">
         <v>46322</v>
@@ -20442,13 +20442,13 @@
         </is>
       </c>
       <c r="D263" s="15" t="n">
-        <v>9.52</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="E263" s="17" t="n">
-        <v>0.1553</v>
+        <v>0.1068</v>
       </c>
       <c r="F263" s="17" t="n">
-        <v>0.2813</v>
+        <v>0.2275</v>
       </c>
       <c r="G263" s="18" t="n">
         <v>46339</v>
@@ -20503,13 +20503,13 @@
         </is>
       </c>
       <c r="D264" s="4" t="n">
-        <v>112.93</v>
+        <v>115.57</v>
       </c>
       <c r="E264" s="6" t="n">
-        <v>0.1519</v>
+        <v>0.1788</v>
       </c>
       <c r="F264" s="6" t="n">
-        <v>0.542</v>
+        <v>0.578</v>
       </c>
       <c r="G264" s="7" t="n"/>
       <c r="H264" s="12" t="inlineStr">
@@ -20554,13 +20554,13 @@
         </is>
       </c>
       <c r="D265" s="15" t="n">
-        <v>16.49</v>
-      </c>
-      <c r="E265" s="17" t="n">
-        <v>0.006999999999999999</v>
+        <v>16</v>
+      </c>
+      <c r="E265" s="16" t="n">
+        <v>-0.0223</v>
       </c>
       <c r="F265" s="17" t="n">
-        <v>0.165</v>
+        <v>0.1311</v>
       </c>
       <c r="G265" s="18" t="n">
         <v>46335</v>
@@ -20615,10 +20615,10 @@
         </is>
       </c>
       <c r="D266" s="4" t="n">
-        <v>366.33</v>
+        <v>366.36</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>-0.1184</v>
+        <v>-0.1183</v>
       </c>
       <c r="F266" s="5" t="n">
         <v>-0.0027</v>
@@ -20690,13 +20690,13 @@
         </is>
       </c>
       <c r="D267" s="15" t="n">
-        <v>4.11</v>
+        <v>4.05</v>
       </c>
       <c r="E267" s="17" t="n">
-        <v>0.3189</v>
+        <v>0.2981</v>
       </c>
       <c r="F267" s="17" t="n">
-        <v>0.0444</v>
+        <v>0.0279</v>
       </c>
       <c r="G267" s="18" t="n">
         <v>46331</v>
@@ -20751,13 +20751,13 @@
         </is>
       </c>
       <c r="D268" s="4" t="n">
-        <v>24.09</v>
+        <v>24.1</v>
       </c>
       <c r="E268" s="6" t="n">
-        <v>0.1573</v>
+        <v>0.1575</v>
       </c>
       <c r="F268" s="6" t="n">
-        <v>0.3283</v>
+        <v>0.3286</v>
       </c>
       <c r="G268" s="7" t="n"/>
       <c r="H268" s="12" t="inlineStr">
@@ -20802,13 +20802,13 @@
         </is>
       </c>
       <c r="D269" s="15" t="n">
-        <v>21.09</v>
+        <v>21.41</v>
       </c>
       <c r="E269" s="17" t="n">
-        <v>0.1633</v>
+        <v>0.1809</v>
       </c>
       <c r="F269" s="17" t="n">
-        <v>0.4107</v>
+        <v>0.4321</v>
       </c>
       <c r="G269" s="18" t="n"/>
       <c r="H269" s="23" t="inlineStr">
@@ -20853,13 +20853,13 @@
         </is>
       </c>
       <c r="D270" s="4" t="n">
-        <v>219.25</v>
+        <v>221.89</v>
       </c>
       <c r="E270" s="6" t="n">
-        <v>0.1825</v>
+        <v>0.1968</v>
       </c>
       <c r="F270" s="6" t="n">
-        <v>0.0519</v>
+        <v>0.0646</v>
       </c>
       <c r="G270" s="7" t="n">
         <v>46328</v>
@@ -20914,13 +20914,13 @@
         </is>
       </c>
       <c r="D271" s="15" t="n">
-        <v>212.11</v>
+        <v>210.62</v>
       </c>
       <c r="E271" s="16" t="n">
-        <v>-0.03</v>
+        <v>-0.0368</v>
       </c>
       <c r="F271" s="17" t="n">
-        <v>0.3257</v>
+        <v>0.3164</v>
       </c>
       <c r="G271" s="18" t="n">
         <v>46316</v>
@@ -20995,13 +20995,13 @@
         </is>
       </c>
       <c r="D272" s="4" t="n">
-        <v>41.45</v>
+        <v>41.44</v>
       </c>
       <c r="E272" s="6" t="n">
-        <v>0.1786</v>
+        <v>0.1783</v>
       </c>
       <c r="F272" s="6" t="n">
-        <v>0.3771</v>
+        <v>0.3767</v>
       </c>
       <c r="G272" s="7" t="n">
         <v>46329</v>
@@ -21056,13 +21056,13 @@
         </is>
       </c>
       <c r="D273" s="15" t="n">
-        <v>339.82</v>
+        <v>334.81</v>
       </c>
       <c r="E273" s="17" t="n">
-        <v>0.0528</v>
+        <v>0.0373</v>
       </c>
       <c r="F273" s="17" t="n">
-        <v>0.2677</v>
+        <v>0.249</v>
       </c>
       <c r="G273" s="18" t="n"/>
       <c r="H273" s="23" t="inlineStr">
@@ -21081,7 +21081,7 @@
         <v>320</v>
       </c>
       <c r="M273" s="16" t="n">
-        <v>-0.0583249955858984</v>
+        <v>-0.04423404318867418</v>
       </c>
       <c r="N273" s="14" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>280</v>
       </c>
       <c r="P273" s="16" t="n">
-        <v>-0.1760343711376611</v>
+        <v>-0.1637047877900899</v>
       </c>
       <c r="Q273" s="21" t="inlineStr">
         <is>
@@ -21133,13 +21133,13 @@
         </is>
       </c>
       <c r="D274" s="4" t="n">
-        <v>415.33</v>
+        <v>413.06</v>
       </c>
       <c r="E274" s="6" t="n">
-        <v>0.0528</v>
+        <v>0.047</v>
       </c>
       <c r="F274" s="6" t="n">
-        <v>0.1121</v>
+        <v>0.106</v>
       </c>
       <c r="G274" s="7" t="n"/>
       <c r="H274" s="12" t="inlineStr">
@@ -21158,7 +21158,7 @@
         <v>535</v>
       </c>
       <c r="M274" s="6" t="n">
-        <v>0.2881323285098597</v>
+        <v>0.2952113494407592</v>
       </c>
       <c r="N274" s="3" t="inlineStr"/>
       <c r="O274" s="9" t="n"/>
@@ -21202,13 +21202,13 @@
         </is>
       </c>
       <c r="D275" s="15" t="n">
-        <v>6.09</v>
+        <v>6.01</v>
       </c>
       <c r="E275" s="16" t="n">
-        <v>-0.1294</v>
+        <v>-0.1414</v>
       </c>
       <c r="F275" s="16" t="n">
-        <v>-0.0106</v>
+        <v>-0.0244</v>
       </c>
       <c r="G275" s="18" t="n">
         <v>46331</v>
@@ -21263,13 +21263,13 @@
         </is>
       </c>
       <c r="D276" s="4" t="n">
-        <v>90.52</v>
+        <v>91.45</v>
       </c>
       <c r="E276" s="6" t="n">
-        <v>0.3539</v>
+        <v>0.3678</v>
       </c>
       <c r="F276" s="6" t="n">
-        <v>0.5034000000000001</v>
+        <v>0.5189</v>
       </c>
       <c r="G276" s="7" t="n">
         <v>46322</v>
@@ -21324,13 +21324,13 @@
         </is>
       </c>
       <c r="D277" s="15" t="n">
-        <v>97.93000000000001</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="E277" s="17" t="n">
-        <v>0.0454</v>
+        <v>0.0472</v>
       </c>
       <c r="F277" s="16" t="n">
-        <v>-0.1334</v>
+        <v>-0.1319</v>
       </c>
       <c r="G277" s="18" t="n">
         <v>46331</v>
@@ -21385,13 +21385,13 @@
         </is>
       </c>
       <c r="D278" s="4" t="n">
-        <v>214.57</v>
+        <v>214.39</v>
       </c>
       <c r="E278" s="6" t="n">
-        <v>0.0601</v>
+        <v>0.0592</v>
       </c>
       <c r="F278" s="6" t="n">
-        <v>0.0573</v>
+        <v>0.0564</v>
       </c>
       <c r="G278" s="7" t="n">
         <v>46330</v>
@@ -21446,13 +21446,13 @@
         </is>
       </c>
       <c r="D279" s="15" t="n">
-        <v>385.94</v>
+        <v>389.14</v>
       </c>
       <c r="E279" s="17" t="n">
-        <v>0.05769999999999999</v>
+        <v>0.0664</v>
       </c>
       <c r="F279" s="17" t="n">
-        <v>0.1029</v>
+        <v>0.1121</v>
       </c>
       <c r="G279" s="18" t="n">
         <v>46322</v>
@@ -21507,13 +21507,13 @@
         </is>
       </c>
       <c r="D280" s="4" t="n">
-        <v>59.59</v>
+        <v>59.32</v>
       </c>
       <c r="E280" s="5" t="n">
-        <v>-0.0178</v>
+        <v>-0.0223</v>
       </c>
       <c r="F280" s="6" t="n">
-        <v>0.1263</v>
+        <v>0.1211</v>
       </c>
       <c r="G280" s="7" t="n">
         <v>46330</v>
@@ -21568,13 +21568,13 @@
         </is>
       </c>
       <c r="D281" s="15" t="n">
-        <v>449.35</v>
+        <v>446.57</v>
       </c>
       <c r="E281" s="17" t="n">
-        <v>0.09570000000000001</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="F281" s="17" t="n">
-        <v>0.1139</v>
+        <v>0.107</v>
       </c>
       <c r="G281" s="18" t="n">
         <v>46310</v>
@@ -21651,13 +21651,13 @@
         </is>
       </c>
       <c r="D282" s="4" t="n">
-        <v>126.71</v>
+        <v>125.82</v>
       </c>
       <c r="E282" s="6" t="n">
-        <v>0.1829</v>
+        <v>0.1746</v>
       </c>
       <c r="F282" s="5" t="n">
-        <v>-0.0358</v>
+        <v>-0.0425</v>
       </c>
       <c r="G282" s="7" t="n">
         <v>46330</v>
@@ -21712,13 +21712,13 @@
         </is>
       </c>
       <c r="D283" s="15" t="n">
-        <v>294.23</v>
+        <v>290.7</v>
       </c>
       <c r="E283" s="17" t="n">
-        <v>0.3219</v>
+        <v>0.306</v>
       </c>
       <c r="F283" s="17" t="n">
-        <v>0.5367999999999999</v>
+        <v>0.5183</v>
       </c>
       <c r="G283" s="18" t="n">
         <v>46324</v>
@@ -21773,13 +21773,13 @@
         </is>
       </c>
       <c r="D284" s="4" t="n">
-        <v>271.03</v>
+        <v>272.62</v>
       </c>
       <c r="E284" s="6" t="n">
-        <v>0.0467</v>
+        <v>0.0528</v>
       </c>
       <c r="F284" s="5" t="n">
-        <v>-0.0306</v>
+        <v>-0.0249</v>
       </c>
       <c r="G284" s="7" t="n">
         <v>46315</v>
@@ -21808,7 +21808,7 @@
         <v>300</v>
       </c>
       <c r="M284" s="6" t="n">
-        <v>0.1068885363243922</v>
+        <v>0.1004328369158536</v>
       </c>
       <c r="N284" s="3" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         <v>316</v>
       </c>
       <c r="P284" s="6" t="n">
-        <v>0.1659225915950265</v>
+        <v>0.1591225882180324</v>
       </c>
       <c r="Q284" s="10" t="inlineStr">
         <is>
@@ -21876,13 +21876,13 @@
         </is>
       </c>
       <c r="D285" s="15" t="n">
-        <v>334.34</v>
+        <v>332.53</v>
       </c>
       <c r="E285" s="16" t="n">
-        <v>-0.0603</v>
+        <v>-0.0654</v>
       </c>
       <c r="F285" s="17" t="n">
-        <v>0.1252</v>
+        <v>0.1191</v>
       </c>
       <c r="G285" s="18" t="n">
         <v>46330</v>
@@ -21911,7 +21911,7 @@
         <v>335</v>
       </c>
       <c r="M285" s="17" t="n">
-        <v>0.001974038404019935</v>
+        <v>0.007427901241993286</v>
       </c>
       <c r="N285" s="14" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>375</v>
       </c>
       <c r="P285" s="17" t="n">
-        <v>0.1216127295567387</v>
+        <v>0.1277177998977537</v>
       </c>
       <c r="Q285" s="21" t="inlineStr">
         <is>
@@ -21963,13 +21963,13 @@
         </is>
       </c>
       <c r="D286" s="4" t="n">
-        <v>42.67</v>
+        <v>44.1</v>
       </c>
       <c r="E286" s="5" t="n">
-        <v>-0.0756</v>
+        <v>-0.0446</v>
       </c>
       <c r="F286" s="6" t="n">
-        <v>0.4909000000000001</v>
+        <v>0.5409</v>
       </c>
       <c r="G286" s="7" t="n">
         <v>46330</v>
@@ -22024,13 +22024,13 @@
         </is>
       </c>
       <c r="D287" s="15" t="n">
-        <v>6.88</v>
+        <v>6.92</v>
       </c>
       <c r="E287" s="17" t="n">
-        <v>0.0626</v>
+        <v>0.0696</v>
       </c>
       <c r="F287" s="16" t="n">
-        <v>-0.04650000000000001</v>
+        <v>-0.04019999999999999</v>
       </c>
       <c r="G287" s="18" t="n"/>
       <c r="H287" s="23" t="inlineStr">
@@ -22075,13 +22075,13 @@
         </is>
       </c>
       <c r="D288" s="4" t="n">
-        <v>192.81</v>
+        <v>192.38</v>
       </c>
       <c r="E288" s="5" t="n">
-        <v>-0.0318</v>
+        <v>-0.034</v>
       </c>
       <c r="F288" s="6" t="n">
-        <v>0.4246</v>
+        <v>0.4215</v>
       </c>
       <c r="G288" s="7" t="n"/>
       <c r="H288" s="12" t="inlineStr">
@@ -22126,13 +22126,13 @@
         </is>
       </c>
       <c r="D289" s="15" t="n">
-        <v>466.22</v>
+        <v>473.69</v>
       </c>
       <c r="E289" s="17" t="n">
-        <v>0.0708</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="F289" s="16" t="n">
-        <v>-0.1031</v>
+        <v>-0.08869999999999999</v>
       </c>
       <c r="G289" s="18" t="n">
         <v>46324</v>
@@ -22161,7 +22161,7 @@
         <v>730</v>
       </c>
       <c r="M289" s="17" t="n">
-        <v>0.5657843936339066</v>
+        <v>0.5410922755388545</v>
       </c>
       <c r="N289" s="14" t="inlineStr">
         <is>
@@ -22172,7 +22172,7 @@
         <v>575</v>
       </c>
       <c r="P289" s="17" t="n">
-        <v>0.2333233237527347</v>
+        <v>0.2138740526504676</v>
       </c>
       <c r="Q289" s="21" t="inlineStr">
         <is>
@@ -22213,13 +22213,13 @@
         </is>
       </c>
       <c r="D290" s="4" t="n">
-        <v>27.8</v>
+        <v>27.14</v>
       </c>
       <c r="E290" s="6" t="n">
-        <v>0.1228</v>
+        <v>0.09609999999999999</v>
       </c>
       <c r="F290" s="6" t="n">
-        <v>0.204</v>
+        <v>0.1754</v>
       </c>
       <c r="G290" s="7" t="n">
         <v>46330</v>
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="D291" s="15" t="n">
-        <v>92.45999999999999</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="E291" s="16" t="n">
-        <v>-0.118</v>
+        <v>-0.1233</v>
       </c>
       <c r="F291" s="17" t="n">
-        <v>0.0509</v>
+        <v>0.0444</v>
       </c>
       <c r="G291" s="18" t="n"/>
       <c r="H291" s="23" t="inlineStr">
@@ -22325,13 +22325,13 @@
         </is>
       </c>
       <c r="D292" s="4" t="n">
-        <v>213.99</v>
+        <v>214.45</v>
       </c>
       <c r="E292" s="6" t="n">
-        <v>0.2154</v>
+        <v>0.2181</v>
       </c>
       <c r="F292" s="6" t="n">
-        <v>0.5036</v>
+        <v>0.5068</v>
       </c>
       <c r="G292" s="7" t="n"/>
       <c r="H292" s="12" t="inlineStr">
@@ -22376,13 +22376,13 @@
         </is>
       </c>
       <c r="D293" s="15" t="n">
-        <v>287.98</v>
+        <v>286.97</v>
       </c>
       <c r="E293" s="16" t="n">
-        <v>-0.0596</v>
+        <v>-0.0629</v>
       </c>
       <c r="F293" s="16" t="n">
-        <v>-0.0332</v>
+        <v>-0.0366</v>
       </c>
       <c r="G293" s="18" t="n">
         <v>46331</v>
@@ -22437,13 +22437,13 @@
         </is>
       </c>
       <c r="D294" s="4" t="n">
-        <v>85.70999999999999</v>
+        <v>84.95</v>
       </c>
       <c r="E294" s="5" t="n">
-        <v>-0.1176</v>
+        <v>-0.1254</v>
       </c>
       <c r="F294" s="6" t="n">
-        <v>0.0238</v>
+        <v>0.0147</v>
       </c>
       <c r="G294" s="7" t="n">
         <v>46343</v>
@@ -22498,13 +22498,13 @@
         </is>
       </c>
       <c r="D295" s="15" t="n">
-        <v>131.54</v>
+        <v>130.88</v>
       </c>
       <c r="E295" s="16" t="n">
-        <v>-0.0375</v>
+        <v>-0.0424</v>
       </c>
       <c r="F295" s="16" t="n">
-        <v>-0.0447</v>
+        <v>-0.0495</v>
       </c>
       <c r="G295" s="18" t="n">
         <v>46331</v>
@@ -22533,7 +22533,7 @@
         <v>166</v>
       </c>
       <c r="M295" s="17" t="n">
-        <v>0.2619735441690741</v>
+        <v>0.2683374083129585</v>
       </c>
       <c r="N295" s="14" t="inlineStr"/>
       <c r="O295" s="20" t="n"/>
@@ -22581,13 +22581,13 @@
         </is>
       </c>
       <c r="D296" s="4" t="n">
-        <v>28.8</v>
+        <v>28.65</v>
       </c>
       <c r="E296" s="5" t="n">
-        <v>-0.08410000000000001</v>
+        <v>-0.08869999999999999</v>
       </c>
       <c r="F296" s="5" t="n">
-        <v>-0.035</v>
+        <v>-0.0399</v>
       </c>
       <c r="G296" s="7" t="n">
         <v>46317</v>
@@ -22642,13 +22642,13 @@
         </is>
       </c>
       <c r="D297" s="15" t="n">
-        <v>275.49</v>
+        <v>276.72</v>
       </c>
       <c r="E297" s="16" t="n">
-        <v>-0.04</v>
+        <v>-0.0358</v>
       </c>
       <c r="F297" s="17" t="n">
-        <v>0.0251</v>
+        <v>0.0297</v>
       </c>
       <c r="G297" s="18" t="n">
         <v>46322</v>
@@ -22677,7 +22677,7 @@
         <v>275</v>
       </c>
       <c r="M297" s="16" t="n">
-        <v>-0.001778648952775088</v>
+        <v>-0.006215669268574831</v>
       </c>
       <c r="N297" s="14" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>312</v>
       </c>
       <c r="P297" s="17" t="n">
-        <v>0.1325274964608515</v>
+        <v>0.1274934952298351</v>
       </c>
       <c r="Q297" s="21" t="inlineStr">
         <is>
@@ -22741,13 +22741,13 @@
         </is>
       </c>
       <c r="D298" s="4" t="n">
-        <v>35.72</v>
+        <v>35.47</v>
       </c>
       <c r="E298" s="6" t="n">
-        <v>0.0212</v>
+        <v>0.014</v>
       </c>
       <c r="F298" s="5" t="n">
-        <v>-0.0459</v>
+        <v>-0.0526</v>
       </c>
       <c r="G298" s="7" t="n">
         <v>46322</v>
@@ -22806,13 +22806,13 @@
         </is>
       </c>
       <c r="D299" s="15" t="n">
-        <v>72.53</v>
+        <v>72.58</v>
       </c>
       <c r="E299" s="16" t="n">
-        <v>-0.0678</v>
+        <v>-0.06709999999999999</v>
       </c>
       <c r="F299" s="17" t="n">
-        <v>0.1585</v>
+        <v>0.1594</v>
       </c>
       <c r="G299" s="18" t="n">
         <v>46310</v>
@@ -22867,13 +22867,13 @@
         </is>
       </c>
       <c r="D300" s="4" t="n">
-        <v>470.38</v>
+        <v>469.72</v>
       </c>
       <c r="E300" s="5" t="n">
-        <v>-0.0401</v>
+        <v>-0.0414</v>
       </c>
       <c r="F300" s="5" t="n">
-        <v>-0.0818</v>
+        <v>-0.08310000000000001</v>
       </c>
       <c r="G300" s="7" t="n">
         <v>46325</v>
@@ -22902,7 +22902,7 @@
         <v>570</v>
       </c>
       <c r="M300" s="6" t="n">
-        <v>0.2117862154003146</v>
+        <v>0.2134888869965085</v>
       </c>
       <c r="N300" s="3" t="inlineStr">
         <is>
@@ -22913,7 +22913,7 @@
         <v>525</v>
       </c>
       <c r="P300" s="6" t="n">
-        <v>0.116118882605553</v>
+        <v>0.117687132759942</v>
       </c>
       <c r="Q300" s="10" t="inlineStr">
         <is>
@@ -22966,13 +22966,13 @@
         </is>
       </c>
       <c r="D301" s="15" t="n">
-        <v>494.43</v>
+        <v>490.45</v>
       </c>
       <c r="E301" s="16" t="n">
-        <v>-0.0725</v>
+        <v>-0.08</v>
       </c>
       <c r="F301" s="16" t="n">
-        <v>-0.1164</v>
+        <v>-0.1236</v>
       </c>
       <c r="G301" s="18" t="n">
         <v>46329</v>
@@ -23001,7 +23001,7 @@
         <v>616</v>
       </c>
       <c r="M301" s="17" t="n">
-        <v>0.2458790930971017</v>
+        <v>0.2559893974920991</v>
       </c>
       <c r="N301" s="14" t="inlineStr"/>
       <c r="O301" s="20" t="n"/>
@@ -23045,13 +23045,13 @@
         </is>
       </c>
       <c r="D302" s="4" t="n">
-        <v>248.18</v>
+        <v>246.98</v>
       </c>
       <c r="E302" s="6" t="n">
-        <v>0.0145</v>
-      </c>
-      <c r="F302" s="6" t="n">
-        <v>0.0025</v>
+        <v>0.009599999999999999</v>
+      </c>
+      <c r="F302" s="5" t="n">
+        <v>-0.0023</v>
       </c>
       <c r="G302" s="7" t="n">
         <v>46321</v>
@@ -23080,7 +23080,7 @@
         <v>283</v>
       </c>
       <c r="M302" s="6" t="n">
-        <v>0.1403013941494076</v>
+        <v>0.1458417685642563</v>
       </c>
       <c r="N302" s="3" t="inlineStr"/>
       <c r="O302" s="9" t="n"/>
@@ -23126,13 +23126,13 @@
         </is>
       </c>
       <c r="D303" s="15" t="n">
-        <v>241.19</v>
+        <v>240.98</v>
       </c>
       <c r="E303" s="16" t="n">
-        <v>-0.0309</v>
+        <v>-0.0317</v>
       </c>
       <c r="F303" s="16" t="n">
-        <v>-0.0519</v>
+        <v>-0.0527</v>
       </c>
       <c r="G303" s="18" t="n">
         <v>46316</v>
@@ -23161,7 +23161,7 @@
         <v>246</v>
       </c>
       <c r="M303" s="17" t="n">
-        <v>0.01994278369749991</v>
+        <v>0.02083160428251311</v>
       </c>
       <c r="N303" s="14" t="inlineStr"/>
       <c r="O303" s="20" t="n"/>
@@ -23209,13 +23209,13 @@
         </is>
       </c>
       <c r="D304" s="4" t="n">
-        <v>107.6</v>
+        <v>107.2</v>
       </c>
       <c r="E304" s="5" t="n">
-        <v>-0.04969999999999999</v>
+        <v>-0.0533</v>
       </c>
       <c r="F304" s="5" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.0759</v>
       </c>
       <c r="G304" s="7" t="n">
         <v>46322</v>
@@ -23244,7 +23244,7 @@
         <v>130</v>
       </c>
       <c r="M304" s="6" t="n">
-        <v>0.2081784386617101</v>
+        <v>0.2126865671641791</v>
       </c>
       <c r="N304" s="3" t="inlineStr">
         <is>
@@ -23255,7 +23255,7 @@
         <v>128</v>
       </c>
       <c r="P304" s="6" t="n">
-        <v>0.1895910780669146</v>
+        <v>0.1940298507462686</v>
       </c>
       <c r="Q304" s="10" t="inlineStr">
         <is>
@@ -23304,13 +23304,13 @@
         </is>
       </c>
       <c r="D305" s="15" t="n">
-        <v>100.28</v>
+        <v>100.06</v>
       </c>
       <c r="E305" s="16" t="n">
-        <v>-0.0572</v>
+        <v>-0.0592</v>
       </c>
       <c r="F305" s="16" t="n">
-        <v>-0.0629</v>
+        <v>-0.0649</v>
       </c>
       <c r="G305" s="18" t="n">
         <v>46301</v>
@@ -23339,7 +23339,7 @@
         <v>135</v>
       </c>
       <c r="M305" s="17" t="n">
-        <v>0.3462305544475469</v>
+        <v>0.3491904857085748</v>
       </c>
       <c r="N305" s="14" t="inlineStr">
         <is>
@@ -23350,7 +23350,7 @@
         <v>125</v>
       </c>
       <c r="P305" s="17" t="n">
-        <v>0.2465097726366175</v>
+        <v>0.2492504497301619</v>
       </c>
       <c r="Q305" s="21" t="inlineStr"/>
       <c r="R305" s="20" t="n"/>
@@ -23385,13 +23385,13 @@
         </is>
       </c>
       <c r="D306" s="4" t="n">
-        <v>326.33</v>
+        <v>326.46</v>
       </c>
       <c r="E306" s="5" t="n">
-        <v>-0.0588</v>
+        <v>-0.0585</v>
       </c>
       <c r="F306" s="6" t="n">
-        <v>0.0278</v>
+        <v>0.0282</v>
       </c>
       <c r="G306" s="7" t="n">
         <v>46322</v>
@@ -23420,7 +23420,7 @@
         <v>350</v>
       </c>
       <c r="M306" s="6" t="n">
-        <v>0.07253393803818226</v>
+        <v>0.07210684310482149</v>
       </c>
       <c r="N306" s="3" t="inlineStr">
         <is>
@@ -23431,7 +23431,7 @@
         <v>400</v>
       </c>
       <c r="P306" s="6" t="n">
-        <v>0.2257530720436369</v>
+        <v>0.2252649635483674</v>
       </c>
       <c r="Q306" s="10" t="inlineStr">
         <is>
@@ -23472,13 +23472,13 @@
         </is>
       </c>
       <c r="D307" s="15" t="n">
-        <v>109.54</v>
+        <v>109.65</v>
       </c>
       <c r="E307" s="17" t="n">
-        <v>0.0907</v>
+        <v>0.0917</v>
       </c>
       <c r="F307" s="17" t="n">
-        <v>0.4692</v>
+        <v>0.4706</v>
       </c>
       <c r="G307" s="18" t="n"/>
       <c r="H307" s="23" t="inlineStr">
@@ -23519,13 +23519,13 @@
         </is>
       </c>
       <c r="D308" s="4" t="n">
-        <v>51.19</v>
+        <v>50.11</v>
       </c>
       <c r="E308" s="5" t="n">
-        <v>-0.0169</v>
+        <v>-0.03759999999999999</v>
       </c>
       <c r="F308" s="5" t="n">
-        <v>-0.021</v>
+        <v>-0.0417</v>
       </c>
       <c r="G308" s="7" t="n">
         <v>46267</v>
@@ -23580,13 +23580,13 @@
         </is>
       </c>
       <c r="D309" s="15" t="n">
-        <v>66.77</v>
+        <v>67.12</v>
       </c>
       <c r="E309" s="16" t="n">
-        <v>-0.1047</v>
+        <v>-0.1</v>
       </c>
       <c r="F309" s="16" t="n">
-        <v>-0.1719</v>
+        <v>-0.1676</v>
       </c>
       <c r="G309" s="18" t="n">
         <v>46315</v>
@@ -23615,14 +23615,14 @@
         <v>83</v>
       </c>
       <c r="M309" s="17" t="n">
-        <v>0.2430732364834507</v>
+        <v>0.236591179976162</v>
       </c>
       <c r="N309" s="14" t="inlineStr"/>
       <c r="O309" s="20" t="n">
         <v>87</v>
       </c>
       <c r="P309" s="17" t="n">
-        <v>0.302980380410364</v>
+        <v>0.2961859356376638</v>
       </c>
       <c r="Q309" s="21" t="inlineStr"/>
       <c r="R309" s="20" t="n"/>
@@ -23657,13 +23657,13 @@
         </is>
       </c>
       <c r="D310" s="4" t="n">
-        <v>173.4</v>
+        <v>170.78</v>
       </c>
       <c r="E310" s="5" t="n">
-        <v>-0.028</v>
+        <v>-0.04269999999999999</v>
       </c>
       <c r="F310" s="6" t="n">
-        <v>0.0403</v>
+        <v>0.0247</v>
       </c>
       <c r="G310" s="7" t="n">
         <v>46322</v>
@@ -23692,7 +23692,7 @@
         <v>200</v>
       </c>
       <c r="M310" s="6" t="n">
-        <v>0.1534025374855824</v>
+        <v>0.1710973181871414</v>
       </c>
       <c r="N310" s="3" t="inlineStr"/>
       <c r="O310" s="9" t="n"/>
@@ -23740,13 +23740,13 @@
         </is>
       </c>
       <c r="D311" s="15" t="n">
-        <v>137.64</v>
+        <v>136.41</v>
       </c>
       <c r="E311" s="16" t="n">
-        <v>-0.0941</v>
+        <v>-0.1022</v>
       </c>
       <c r="F311" s="16" t="n">
-        <v>-0.0131</v>
+        <v>-0.0219</v>
       </c>
       <c r="G311" s="18" t="n">
         <v>46317</v>
@@ -23805,13 +23805,13 @@
         </is>
       </c>
       <c r="D312" s="4" t="n">
-        <v>183.32</v>
+        <v>181.45</v>
       </c>
       <c r="E312" s="5" t="n">
-        <v>-0.0277</v>
+        <v>-0.0377</v>
       </c>
       <c r="F312" s="5" t="n">
-        <v>-0.07919999999999999</v>
+        <v>-0.0886</v>
       </c>
       <c r="G312" s="7" t="n">
         <v>46317</v>
@@ -23840,7 +23840,7 @@
         <v>220</v>
       </c>
       <c r="M312" s="6" t="n">
-        <v>0.2000872790748419</v>
+        <v>0.2124552218241941</v>
       </c>
       <c r="N312" s="3" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>230</v>
       </c>
       <c r="P312" s="6" t="n">
-        <v>0.254636700850971</v>
+        <v>0.2675668228162029</v>
       </c>
       <c r="Q312" s="10" t="inlineStr">
         <is>
@@ -23892,13 +23892,13 @@
         </is>
       </c>
       <c r="D313" s="15" t="n">
-        <v>1044.28</v>
+        <v>1037.66</v>
       </c>
       <c r="E313" s="16" t="n">
-        <v>-0.0103</v>
+        <v>-0.0166</v>
       </c>
       <c r="F313" s="16" t="n">
-        <v>-0.0369</v>
+        <v>-0.043</v>
       </c>
       <c r="G313" s="18" t="n">
         <v>46330</v>
@@ -23927,7 +23927,7 @@
         <v>1200</v>
       </c>
       <c r="M313" s="17" t="n">
-        <v>0.1491170950319838</v>
+        <v>0.1564481622111288</v>
       </c>
       <c r="N313" s="14" t="inlineStr">
         <is>
@@ -23938,7 +23938,7 @@
         <v>1240</v>
       </c>
       <c r="P313" s="17" t="n">
-        <v>0.1874209981997166</v>
+        <v>0.1949964342848331</v>
       </c>
       <c r="Q313" s="21" t="inlineStr">
         <is>
@@ -23983,13 +23983,13 @@
         </is>
       </c>
       <c r="D314" s="4" t="n">
-        <v>110.1</v>
+        <v>109.39</v>
       </c>
       <c r="E314" s="5" t="n">
-        <v>-0.0633</v>
+        <v>-0.0693</v>
       </c>
       <c r="F314" s="5" t="n">
-        <v>-0.1267</v>
+        <v>-0.1324</v>
       </c>
       <c r="G314" s="7" t="n">
         <v>46325</v>
@@ -24018,7 +24018,7 @@
         <v>129</v>
       </c>
       <c r="M314" s="6" t="n">
-        <v>0.1716621253405995</v>
+        <v>0.1792668434043331</v>
       </c>
       <c r="N314" s="3" t="inlineStr">
         <is>
@@ -24029,7 +24029,7 @@
         <v>122</v>
       </c>
       <c r="P314" s="6" t="n">
-        <v>0.1080835603996367</v>
+        <v>0.1152756193436329</v>
       </c>
       <c r="Q314" s="10" t="inlineStr">
         <is>
@@ -24070,13 +24070,13 @@
         </is>
       </c>
       <c r="D315" s="15" t="n">
-        <v>55.44</v>
+        <v>55.61</v>
       </c>
       <c r="E315" s="16" t="n">
-        <v>-0.1224</v>
+        <v>-0.1197</v>
       </c>
       <c r="F315" s="16" t="n">
-        <v>-0.1549</v>
+        <v>-0.1523</v>
       </c>
       <c r="G315" s="18" t="n">
         <v>46328</v>
@@ -24105,14 +24105,14 @@
         <v>65</v>
       </c>
       <c r="M315" s="17" t="n">
-        <v>0.1724386724386725</v>
+        <v>0.1688545225678835</v>
       </c>
       <c r="N315" s="14" t="inlineStr"/>
       <c r="O315" s="20" t="n">
         <v>67</v>
       </c>
       <c r="P315" s="17" t="n">
-        <v>0.2085137085137086</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="Q315" s="21" t="inlineStr">
         <is>
@@ -24153,13 +24153,13 @@
         </is>
       </c>
       <c r="D316" s="4" t="n">
-        <v>135.03</v>
+        <v>133.96</v>
       </c>
       <c r="E316" s="5" t="n">
-        <v>-0.0581</v>
+        <v>-0.06559999999999999</v>
       </c>
       <c r="F316" s="5" t="n">
-        <v>-0.08529999999999999</v>
+        <v>-0.0926</v>
       </c>
       <c r="G316" s="7" t="n">
         <v>46310</v>
@@ -24188,7 +24188,7 @@
         <v>167</v>
       </c>
       <c r="M316" s="6" t="n">
-        <v>0.2367622009923721</v>
+        <v>0.2466407882950134</v>
       </c>
       <c r="N316" s="3" t="inlineStr"/>
       <c r="O316" s="9" t="n"/>
@@ -24232,13 +24232,13 @@
         </is>
       </c>
       <c r="D317" s="15" t="n">
-        <v>287.77</v>
+        <v>286.73</v>
       </c>
       <c r="E317" s="16" t="n">
-        <v>-0.1145</v>
+        <v>-0.1177</v>
       </c>
       <c r="F317" s="16" t="n">
-        <v>-0.1077</v>
+        <v>-0.1109</v>
       </c>
       <c r="G317" s="18" t="n">
         <v>46330</v>
@@ -24274,7 +24274,7 @@
         <v>316</v>
       </c>
       <c r="P317" s="17" t="n">
-        <v>0.09809917642561775</v>
+        <v>0.1020820981411083</v>
       </c>
       <c r="Q317" s="21" t="inlineStr">
         <is>
@@ -24315,13 +24315,13 @@
         </is>
       </c>
       <c r="D318" s="4" t="n">
-        <v>205.13</v>
+        <v>204.16</v>
       </c>
       <c r="E318" s="5" t="n">
-        <v>-0.0707</v>
+        <v>-0.0751</v>
       </c>
       <c r="F318" s="5" t="n">
-        <v>-0.1073</v>
+        <v>-0.1115</v>
       </c>
       <c r="G318" s="7" t="n">
         <v>46328</v>
@@ -24357,7 +24357,7 @@
         <v>215</v>
       </c>
       <c r="P318" s="6" t="n">
-        <v>0.04811582898649639</v>
+        <v>0.05309561128526648</v>
       </c>
       <c r="Q318" s="10" t="inlineStr">
         <is>
@@ -24398,13 +24398,13 @@
         </is>
       </c>
       <c r="D319" s="15" t="n">
-        <v>112.67</v>
+        <v>112.32</v>
       </c>
       <c r="E319" s="16" t="n">
-        <v>-0.0872</v>
+        <v>-0.09</v>
       </c>
       <c r="F319" s="16" t="n">
-        <v>-0.07519999999999999</v>
+        <v>-0.0781</v>
       </c>
       <c r="G319" s="18" t="n">
         <v>46330</v>
@@ -24433,7 +24433,7 @@
         <v>142</v>
       </c>
       <c r="M319" s="17" t="n">
-        <v>0.2603177420786367</v>
+        <v>0.2642450142450143</v>
       </c>
       <c r="N319" s="14" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>137</v>
       </c>
       <c r="P319" s="17" t="n">
-        <v>0.2159403567941777</v>
+        <v>0.2197293447293448</v>
       </c>
       <c r="Q319" s="21" t="inlineStr">
         <is>
@@ -24493,13 +24493,13 @@
         </is>
       </c>
       <c r="D320" s="4" t="n">
-        <v>230.08</v>
+        <v>229.87</v>
       </c>
       <c r="E320" s="5" t="n">
-        <v>-0.0414</v>
+        <v>-0.04219999999999999</v>
       </c>
       <c r="F320" s="5" t="n">
-        <v>-0.0872</v>
+        <v>-0.08810000000000001</v>
       </c>
       <c r="G320" s="7" t="n">
         <v>46321</v>
@@ -24528,7 +24528,7 @@
         <v>237</v>
       </c>
       <c r="M320" s="6" t="n">
-        <v>0.0300764951321279</v>
+        <v>0.03101753164832294</v>
       </c>
       <c r="N320" s="3" t="inlineStr">
         <is>
@@ -24539,7 +24539,7 @@
         <v>236</v>
       </c>
       <c r="P320" s="6" t="n">
-        <v>0.02573018080667588</v>
+        <v>0.02666724670465914</v>
       </c>
       <c r="Q320" s="10" t="inlineStr">
         <is>
@@ -24580,13 +24580,13 @@
         </is>
       </c>
       <c r="D321" s="15" t="n">
-        <v>156.42</v>
+        <v>156.24</v>
       </c>
       <c r="E321" s="16" t="n">
-        <v>-0.0679</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="F321" s="16" t="n">
-        <v>-0.1272</v>
+        <v>-0.1282</v>
       </c>
       <c r="G321" s="18" t="n">
         <v>46330</v>
@@ -24615,7 +24615,7 @@
         <v>200</v>
       </c>
       <c r="M321" s="17" t="n">
-        <v>0.2786088735455825</v>
+        <v>0.2800819252432155</v>
       </c>
       <c r="N321" s="14" t="inlineStr"/>
       <c r="O321" s="20" t="n"/>
@@ -24659,13 +24659,13 @@
         </is>
       </c>
       <c r="D322" s="4" t="n">
-        <v>132.84</v>
+        <v>133.06</v>
       </c>
       <c r="E322" s="5" t="n">
-        <v>-0.0505</v>
+        <v>-0.049</v>
       </c>
       <c r="F322" s="5" t="n">
-        <v>-0.0135</v>
+        <v>-0.0119</v>
       </c>
       <c r="G322" s="7" t="n">
         <v>46330</v>
@@ -24694,7 +24694,7 @@
         <v>131</v>
       </c>
       <c r="M322" s="5" t="n">
-        <v>-0.01385124962360737</v>
+        <v>-0.01548173756200212</v>
       </c>
       <c r="N322" s="3" t="inlineStr"/>
       <c r="O322" s="9" t="n"/>
@@ -24738,13 +24738,13 @@
         </is>
       </c>
       <c r="D323" s="15" t="n">
-        <v>29.65</v>
+        <v>29.22</v>
       </c>
       <c r="E323" s="16" t="n">
-        <v>-0.09820000000000001</v>
+        <v>-0.1113</v>
       </c>
       <c r="F323" s="16" t="n">
-        <v>-0.1157</v>
+        <v>-0.1285</v>
       </c>
       <c r="G323" s="18" t="n">
         <v>46330</v>
@@ -24817,13 +24817,13 @@
         </is>
       </c>
       <c r="D324" s="4" t="n">
-        <v>35.35</v>
+        <v>35.22</v>
       </c>
       <c r="E324" s="5" t="n">
-        <v>-0.0832</v>
+        <v>-0.0866</v>
       </c>
       <c r="F324" s="5" t="n">
-        <v>-0.1353</v>
+        <v>-0.1385</v>
       </c>
       <c r="G324" s="7" t="n">
         <v>46332</v>
@@ -24878,13 +24878,13 @@
         </is>
       </c>
       <c r="D325" s="15" t="n">
-        <v>263.57</v>
+        <v>263.88</v>
       </c>
       <c r="E325" s="16" t="n">
-        <v>-0.0361</v>
+        <v>-0.0349</v>
       </c>
       <c r="F325" s="16" t="n">
-        <v>-0.0393</v>
+        <v>-0.0382</v>
       </c>
       <c r="G325" s="18" t="n">
         <v>46332</v>
@@ -24913,7 +24913,7 @@
         <v>384</v>
       </c>
       <c r="M325" s="17" t="n">
-        <v>0.4569184656827409</v>
+        <v>0.4552069122328331</v>
       </c>
       <c r="N325" s="14" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>380</v>
       </c>
       <c r="P325" s="17" t="n">
-        <v>0.4417422316652123</v>
+        <v>0.4400485068970745</v>
       </c>
       <c r="Q325" s="21" t="inlineStr"/>
       <c r="R325" s="20" t="n"/>
@@ -24967,13 +24967,13 @@
         </is>
       </c>
       <c r="D326" s="4" t="n">
-        <v>63.17</v>
+        <v>63.15</v>
       </c>
       <c r="E326" s="5" t="n">
-        <v>-0.0767</v>
+        <v>-0.077</v>
       </c>
       <c r="F326" s="5" t="n">
-        <v>-0.1543</v>
+        <v>-0.1546</v>
       </c>
       <c r="G326" s="7" t="n">
         <v>46324</v>
@@ -25002,7 +25002,7 @@
         <v>79</v>
       </c>
       <c r="M326" s="6" t="n">
-        <v>0.2505936362197245</v>
+        <v>0.2509897070467142</v>
       </c>
       <c r="N326" s="3" t="inlineStr"/>
       <c r="O326" s="9" t="n"/>
@@ -25054,13 +25054,13 @@
         </is>
       </c>
       <c r="D327" s="15" t="n">
-        <v>114.54</v>
+        <v>114.17</v>
       </c>
       <c r="E327" s="16" t="n">
-        <v>-0.0609</v>
+        <v>-0.064</v>
       </c>
       <c r="F327" s="16" t="n">
-        <v>-0.1224</v>
+        <v>-0.1253</v>
       </c>
       <c r="G327" s="18" t="n">
         <v>46331</v>
@@ -25089,7 +25089,7 @@
         <v>136</v>
       </c>
       <c r="M327" s="17" t="n">
-        <v>0.1873581281648332</v>
+        <v>0.1912060961723745</v>
       </c>
       <c r="N327" s="14" t="inlineStr">
         <is>
@@ -25100,7 +25100,7 @@
         <v>140</v>
       </c>
       <c r="P327" s="17" t="n">
-        <v>0.2222804260520342</v>
+        <v>0.226241569589209</v>
       </c>
       <c r="Q327" s="21" t="inlineStr">
         <is>
@@ -25141,13 +25141,13 @@
         </is>
       </c>
       <c r="D328" s="4" t="n">
-        <v>99.5</v>
+        <v>99.23</v>
       </c>
       <c r="E328" s="5" t="n">
-        <v>-0.0594</v>
+        <v>-0.062</v>
       </c>
       <c r="F328" s="5" t="n">
-        <v>-0.1418</v>
+        <v>-0.1442</v>
       </c>
       <c r="G328" s="7" t="n">
         <v>46330</v>
@@ -25176,7 +25176,7 @@
         <v>131</v>
       </c>
       <c r="M328" s="6" t="n">
-        <v>0.3165829145728643</v>
+        <v>0.3201652725990123</v>
       </c>
       <c r="N328" s="3" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>121</v>
       </c>
       <c r="P328" s="6" t="n">
-        <v>0.2160804020100502</v>
+        <v>0.2193892975914541</v>
       </c>
       <c r="Q328" s="10" t="inlineStr">
         <is>
@@ -25232,13 +25232,13 @@
         </is>
       </c>
       <c r="D329" s="15" t="n">
-        <v>77.84</v>
+        <v>77.02</v>
       </c>
       <c r="E329" s="16" t="n">
-        <v>-0.07440000000000001</v>
+        <v>-0.0842</v>
       </c>
       <c r="F329" s="16" t="n">
-        <v>-0.133</v>
+        <v>-0.1421</v>
       </c>
       <c r="G329" s="18" t="n">
         <v>46322</v>
@@ -25274,7 +25274,7 @@
         <v>107</v>
       </c>
       <c r="P329" s="17" t="n">
-        <v>0.3746145940390544</v>
+        <v>0.3892495455725786</v>
       </c>
       <c r="Q329" s="21" t="inlineStr">
         <is>
@@ -25323,13 +25323,13 @@
         </is>
       </c>
       <c r="D330" s="4" t="n">
-        <v>52.37</v>
+        <v>52.22</v>
       </c>
       <c r="E330" s="5" t="n">
-        <v>-0.0255</v>
+        <v>-0.0283</v>
       </c>
       <c r="F330" s="5" t="n">
-        <v>-0.1279</v>
+        <v>-0.1304</v>
       </c>
       <c r="G330" s="7" t="n"/>
       <c r="H330" s="12" t="inlineStr">
@@ -25348,7 +25348,7 @@
         <v>63</v>
       </c>
       <c r="M330" s="6" t="n">
-        <v>0.2029788046591561</v>
+        <v>0.2064343163538874</v>
       </c>
       <c r="N330" s="3" t="inlineStr"/>
       <c r="O330" s="9" t="n"/>
@@ -25392,13 +25392,13 @@
         </is>
       </c>
       <c r="D331" s="15" t="n">
-        <v>39.82</v>
-      </c>
-      <c r="E331" s="17" t="n">
-        <v>0.0033</v>
+        <v>38.82</v>
+      </c>
+      <c r="E331" s="16" t="n">
+        <v>-0.0219</v>
       </c>
       <c r="F331" s="16" t="n">
-        <v>-0.0107</v>
+        <v>-0.0355</v>
       </c>
       <c r="G331" s="18" t="n">
         <v>46336</v>
@@ -25453,13 +25453,13 @@
         </is>
       </c>
       <c r="D332" s="4" t="n">
-        <v>8.789999999999999</v>
+        <v>8.68</v>
       </c>
       <c r="E332" s="5" t="n">
-        <v>-0.0287</v>
+        <v>-0.0409</v>
       </c>
       <c r="F332" s="6" t="n">
-        <v>0.08650000000000001</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="G332" s="7" t="n">
         <v>46331</v>
@@ -25514,13 +25514,13 @@
         </is>
       </c>
       <c r="D333" s="15" t="n">
-        <v>83.67</v>
+        <v>83.47</v>
       </c>
       <c r="E333" s="16" t="n">
-        <v>-0.07139999999999999</v>
+        <v>-0.0736</v>
       </c>
       <c r="F333" s="16" t="n">
-        <v>-0.1396</v>
+        <v>-0.1417</v>
       </c>
       <c r="G333" s="18" t="n">
         <v>46324</v>
@@ -25549,7 +25549,7 @@
         <v>99</v>
       </c>
       <c r="M333" s="17" t="n">
-        <v>0.1832197920401577</v>
+        <v>0.1860548700131784</v>
       </c>
       <c r="N333" s="14" t="inlineStr">
         <is>
@@ -25560,7 +25560,7 @@
         <v>112</v>
       </c>
       <c r="P333" s="17" t="n">
-        <v>0.3385920879646229</v>
+        <v>0.3417994489037978</v>
       </c>
       <c r="Q333" s="21" t="inlineStr">
         <is>
@@ -25601,13 +25601,13 @@
         </is>
       </c>
       <c r="D334" s="4" t="n">
-        <v>101.82</v>
+        <v>101.17</v>
       </c>
       <c r="E334" s="5" t="n">
-        <v>-0.0535</v>
+        <v>-0.0596</v>
       </c>
       <c r="F334" s="5" t="n">
-        <v>-0.1205</v>
+        <v>-0.1261</v>
       </c>
       <c r="G334" s="7" t="n">
         <v>46324</v>
@@ -25636,7 +25636,7 @@
         <v>127</v>
       </c>
       <c r="M334" s="6" t="n">
-        <v>0.2472991553722256</v>
+        <v>0.2553128397746367</v>
       </c>
       <c r="N334" s="3" t="inlineStr"/>
       <c r="O334" s="9" t="n"/>
@@ -38074,7 +38074,7 @@
     <row r="2">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>Data as of September 23, 2026 at 15:12 UTC</t>
+          <t>Data as of September 23, 2026 at 20:43 UTC</t>
         </is>
       </c>
     </row>

--- a/earnings-data.xlsx
+++ b/earnings-data.xlsx
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>104.69</v>
+        <v>106.15</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>-0.0451</v>
+        <v>-0.0317</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>0.0832</v>
+        <v>0.0983</v>
       </c>
       <c r="G2" s="7" t="n">
         <v>46338</v>
@@ -878,7 +878,7 @@
         <v>125</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.1940013372814978</v>
+        <v>0.1775788977861516</v>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>144</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.3754895405482854</v>
+        <v>0.3565708902496467</v>
       </c>
       <c r="Q2" s="10" t="inlineStr">
         <is>
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="D3" s="15" t="n">
-        <v>344.62</v>
+        <v>343.92</v>
       </c>
       <c r="E3" s="16" t="n">
-        <v>0.0077</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="F3" s="16" t="n">
-        <v>0.0553</v>
+        <v>0.0532</v>
       </c>
       <c r="G3" s="17" t="n">
         <v>46322</v>
@@ -973,7 +973,7 @@
         <v>438</v>
       </c>
       <c r="M3" s="16" t="n">
-        <v>0.2709651210028437</v>
+        <v>0.2735519888346126</v>
       </c>
       <c r="N3" s="14" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>420</v>
       </c>
       <c r="P3" s="16" t="n">
-        <v>0.2187336776739597</v>
+        <v>0.2212142358688066</v>
       </c>
       <c r="Q3" s="20" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>750.65</v>
+        <v>751.66</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>0.3029</v>
+        <v>0.3046</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.264</v>
+        <v>0.2657</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>46330</v>
@@ -1064,7 +1064,7 @@
         <v>835</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.1123692799573703</v>
+        <v>0.1108745975574063</v>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>930</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.238926263904616</v>
+        <v>0.2372615278184286</v>
       </c>
       <c r="Q4" s="10" t="inlineStr">
         <is>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="D5" s="15" t="n">
-        <v>41.33</v>
+        <v>40.55</v>
       </c>
       <c r="E5" s="23" t="n">
-        <v>-0.0175</v>
+        <v>-0.0361</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>0.0653</v>
+        <v>0.0451</v>
       </c>
       <c r="G5" s="17" t="n">
         <v>46329</v>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>71.3</v>
+        <v>71.14</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>-0.1247</v>
+        <v>-0.1266</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.0128</v>
+        <v>0.0106</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>46315</v>
@@ -1220,7 +1220,7 @@
         <v>80</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.1220196353436186</v>
+        <v>0.1245431543435479</v>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>100</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.4025245441795232</v>
+        <v>0.4056789429294349</v>
       </c>
       <c r="Q6" s="10" t="inlineStr">
         <is>
@@ -1272,13 +1272,13 @@
         </is>
       </c>
       <c r="D7" s="15" t="n">
-        <v>75.65000000000001</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>-0.1392</v>
+        <v>-0.1336</v>
       </c>
       <c r="F7" s="23" t="n">
-        <v>-0.08199999999999999</v>
+        <v>-0.076</v>
       </c>
       <c r="G7" s="17" t="n">
         <v>46315</v>
@@ -1307,7 +1307,7 @@
         <v>91</v>
       </c>
       <c r="M7" s="16" t="n">
-        <v>0.2029081295439523</v>
+        <v>0.1950098489822717</v>
       </c>
       <c r="N7" s="14" t="inlineStr"/>
       <c r="O7" s="19" t="n"/>
@@ -1351,13 +1351,13 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>513.77</v>
+        <v>510.01</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-0.0659</v>
+        <v>-0.0728</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.0385</v>
+        <v>0.0309</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>46317</v>
@@ -1386,7 +1386,7 @@
         <v>569.9299999999999</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.1093096132510656</v>
+        <v>0.1174878923942667</v>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>648.04</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.2613426241314207</v>
+        <v>0.2706417521225074</v>
       </c>
       <c r="Q8" s="10" t="inlineStr">
         <is>
@@ -1438,13 +1438,13 @@
         </is>
       </c>
       <c r="D9" s="15" t="n">
-        <v>181.23</v>
+        <v>182.67</v>
       </c>
       <c r="E9" s="23" t="n">
-        <v>-0.0355</v>
+        <v>-0.0278</v>
       </c>
       <c r="F9" s="23" t="n">
-        <v>-0.0089</v>
+        <v>-0.001</v>
       </c>
       <c r="G9" s="17" t="n">
         <v>46330</v>
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>165.9</v>
+        <v>165.43</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-0.07629999999999999</v>
+        <v>-0.0789</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-0.0638</v>
+        <v>-0.0665</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>46317</v>
@@ -1542,7 +1542,7 @@
         <v>170</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.02471368294153101</v>
+        <v>0.02762497733180193</v>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>270</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.6274864376130198</v>
+        <v>0.6321102581152148</v>
       </c>
       <c r="Q10" s="10" t="inlineStr">
         <is>
@@ -1594,13 +1594,13 @@
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>47.21</v>
+        <v>47.08</v>
       </c>
       <c r="E11" s="23" t="n">
-        <v>-0.0595</v>
+        <v>-0.062</v>
       </c>
       <c r="F11" s="23" t="n">
-        <v>-0.0024</v>
+        <v>-0.0051</v>
       </c>
       <c r="G11" s="17" t="n">
         <v>46316</v>
@@ -1629,7 +1629,7 @@
         <v>43</v>
       </c>
       <c r="M11" s="23" t="n">
-        <v>-0.08917602202923111</v>
+        <v>-0.08666100254885298</v>
       </c>
       <c r="N11" s="14" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>50</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>0.05909764880321964</v>
+        <v>0.06202209005947328</v>
       </c>
       <c r="Q11" s="20" t="inlineStr">
         <is>
@@ -1685,13 +1685,13 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>155.27</v>
+        <v>157.47</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-0.1744</v>
+        <v>-0.1627</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.0573</v>
+        <v>0.0722</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>46331</v>
@@ -1720,7 +1720,7 @@
         <v>181</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.1657113415341018</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>155</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>-0.001738906421073036</v>
+        <v>-0.01568552740204483</v>
       </c>
       <c r="Q12" s="10" t="inlineStr">
         <is>
@@ -1772,13 +1772,13 @@
         </is>
       </c>
       <c r="D13" s="15" t="n">
-        <v>249.25</v>
+        <v>249.67</v>
       </c>
       <c r="E13" s="23" t="n">
-        <v>-0.0424</v>
+        <v>-0.0408</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>0.07719999999999999</v>
+        <v>0.079</v>
       </c>
       <c r="G13" s="17" t="n">
         <v>46324</v>
@@ -1807,7 +1807,7 @@
         <v>322</v>
       </c>
       <c r="M13" s="16" t="n">
-        <v>0.2918756268806419</v>
+        <v>0.2897024071774743</v>
       </c>
       <c r="N13" s="14" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>285</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>0.1434302908726179</v>
+        <v>0.1415067889614292</v>
       </c>
       <c r="Q13" s="20" t="inlineStr">
         <is>
@@ -1871,13 +1871,13 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2863.86</v>
+        <v>2872.16</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-0.0451</v>
+        <v>-0.0423</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>-0.0687</v>
+        <v>-0.066</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>46287</v>
@@ -1906,7 +1906,7 @@
         <v>4150</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.4490931819292842</v>
+        <v>0.4449055762910145</v>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>3700</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.2919625959369522</v>
+        <v>0.2882290680184948</v>
       </c>
       <c r="Q14" s="10" t="inlineStr">
         <is>
@@ -1958,13 +1958,13 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>90.06</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>0.03</v>
+        <v>0.0351</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>0.0182</v>
+        <v>0.0233</v>
       </c>
       <c r="G15" s="17" t="n"/>
       <c r="H15" s="22" t="inlineStr">
@@ -1983,7 +1983,7 @@
         <v>65</v>
       </c>
       <c r="M15" s="23" t="n">
-        <v>-0.2782589384854541</v>
+        <v>-0.2818473096895371</v>
       </c>
       <c r="N15" s="14" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>85</v>
       </c>
       <c r="P15" s="23" t="n">
-        <v>-0.05618476571174775</v>
+        <v>-0.0608772511324716</v>
       </c>
       <c r="Q15" s="20" t="inlineStr"/>
       <c r="R15" s="19" t="n"/>
@@ -2029,13 +2029,13 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>162.31</v>
+        <v>163.95</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-0.223</v>
+        <v>-0.2151</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-0.1311</v>
+        <v>-0.1223</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>46322</v>
@@ -2064,7 +2064,7 @@
         <v>214</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.318464666379151</v>
+        <v>0.305275998780116</v>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>245</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.509457211508841</v>
+        <v>0.4943580359865814</v>
       </c>
       <c r="Q16" s="10" t="inlineStr">
         <is>
@@ -2124,13 +2124,13 @@
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>253.54</v>
+        <v>254.69</v>
       </c>
       <c r="E17" s="23" t="n">
-        <v>-0.1925</v>
+        <v>-0.1889</v>
       </c>
       <c r="F17" s="23" t="n">
-        <v>-0.2918</v>
+        <v>-0.2886</v>
       </c>
       <c r="G17" s="17" t="n"/>
       <c r="H17" s="22" t="inlineStr">
@@ -2149,7 +2149,7 @@
         <v>375</v>
       </c>
       <c r="M17" s="16" t="n">
-        <v>0.4790565591228209</v>
+        <v>0.4723781852448074</v>
       </c>
       <c r="N17" s="14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>375</v>
       </c>
       <c r="P17" s="16" t="n">
-        <v>0.4790565591228209</v>
+        <v>0.4723781852448074</v>
       </c>
       <c r="Q17" s="20" t="inlineStr"/>
       <c r="R17" s="19" t="n"/>
@@ -2199,13 +2199,13 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>31.49</v>
+        <v>31.33</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>-0.1568</v>
+        <v>-0.161</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-0.0517</v>
+        <v>-0.0563</v>
       </c>
       <c r="G18" s="7" t="n">
         <v>46323</v>
@@ -2234,7 +2234,7 @@
         <v>45</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.4290250873293109</v>
+        <v>0.4363230130864986</v>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>45</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.4290250873293109</v>
+        <v>0.4363230130864986</v>
       </c>
       <c r="Q18" s="10" t="inlineStr">
         <is>
@@ -2286,13 +2286,13 @@
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>140.39</v>
+        <v>141.51</v>
       </c>
       <c r="E19" s="23" t="n">
-        <v>-0.0594</v>
+        <v>-0.0519</v>
       </c>
       <c r="F19" s="23" t="n">
-        <v>-0.0492</v>
+        <v>-0.0416</v>
       </c>
       <c r="G19" s="17" t="n">
         <v>46324</v>
@@ -2321,7 +2321,7 @@
         <v>170</v>
       </c>
       <c r="M19" s="16" t="n">
-        <v>0.2109124581522902</v>
+        <v>0.2013285280192213</v>
       </c>
       <c r="N19" s="14" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>177</v>
       </c>
       <c r="P19" s="16" t="n">
-        <v>0.2607735593703256</v>
+        <v>0.2507949968200128</v>
       </c>
       <c r="Q19" s="20" t="inlineStr">
         <is>
@@ -2373,13 +2373,13 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>135.16</v>
+        <v>136.43</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>0.0424</v>
+        <v>0.0522</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>-0.3426</v>
+        <v>-0.3364</v>
       </c>
       <c r="G20" s="7" t="n"/>
       <c r="H20" s="12" t="inlineStr">
@@ -2398,7 +2398,7 @@
         <v>220</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.6277005031074283</v>
+        <v>0.6125485597009455</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="9" t="n"/>
@@ -2442,13 +2442,13 @@
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>113.25</v>
+        <v>114.07</v>
       </c>
       <c r="E21" s="23" t="n">
-        <v>-0.1432</v>
+        <v>-0.137</v>
       </c>
       <c r="F21" s="23" t="n">
-        <v>-0.09789999999999999</v>
+        <v>-0.09140000000000001</v>
       </c>
       <c r="G21" s="17" t="n"/>
       <c r="H21" s="22" t="inlineStr">
@@ -2493,13 +2493,13 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>82.44</v>
+        <v>82.63</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-0.0451</v>
+        <v>-0.0429</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-0.0528</v>
+        <v>-0.0507</v>
       </c>
       <c r="G22" s="7" t="n">
         <v>46315</v>
@@ -2528,7 +2528,7 @@
         <v>61</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>-0.2600679281901989</v>
+        <v>-0.2617693331719714</v>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>100</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.21300339640951</v>
+        <v>0.210214207914801</v>
       </c>
       <c r="Q22" s="10" t="inlineStr">
         <is>
@@ -2580,13 +2580,13 @@
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>129.24</v>
+        <v>129.61</v>
       </c>
       <c r="E23" s="23" t="n">
-        <v>-0.0735</v>
+        <v>-0.0708</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>0.0121</v>
+        <v>0.015</v>
       </c>
       <c r="G23" s="17" t="n">
         <v>46315</v>
@@ -2618,7 +2618,7 @@
         <v>145</v>
       </c>
       <c r="P23" s="16" t="n">
-        <v>0.1219436706901887</v>
+        <v>0.1187408378983102</v>
       </c>
       <c r="Q23" s="20" t="inlineStr"/>
       <c r="R23" s="19" t="n"/>
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>292.33</v>
+        <v>293.2</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>-0.127</v>
+        <v>-0.1244</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>-0.1302</v>
+        <v>-0.1276</v>
       </c>
       <c r="G24" s="7" t="n">
         <v>46343</v>
@@ -2688,7 +2688,7 @@
         <v>360</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.2314849656210448</v>
+        <v>0.227830832196453</v>
       </c>
       <c r="N24" s="3" t="inlineSt